--- a/onboarding/01. BigSpill - Gridwork and Grid Geometry.xlsx
+++ b/onboarding/01. BigSpill - Gridwork and Grid Geometry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PatrickHogan\Downloads\BigSpill\ready\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAC21B4-6C9B-4ECA-9751-A087763749CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82171C58-A494-466A-B2A1-904096EA6B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC51E23B-0A7B-48A2-94F9-79121C6422FB}"/>
   </bookViews>
@@ -32,7 +32,7 @@
     <definedName name="Coalesceλ">_xlfn.LAMBDA(_xlpm.array_1,_xlpm.array_2,_xlop.array_3,_xlop.array_4,_xlop.ignore,_xlop.fill_value, _xlfn.LET(_xlpm.Include3, NOT(_xlfn.ISOMITTED(_xlpm.array_3)), _xlpm.Include4, NOT(_xlfn.ISOMITTED(_xlpm.array_4)), _xlpm.array_3, IF(_xlfn.ISOMITTED(_xlpm.array_3), FALSE, _xlpm.array_3), _xlpm.array_4, IF(_xlfn.ISOMITTED(_xlpm.array_4), FALSE, _xlpm.array_4), _xlpm.ignore, IF(_xlfn.ISOMITTED(_xlpm.ignore), "", _xlpm.ignore), _xlpm.fill_value, IF(_xlfn.ISOMITTED(_xlpm.fill_value), "", _xlpm.fill_value), _xlpm.h, ROWS(_xlpm.array_1), _xlpm.w, COLUMNS(_xlpm.array_1), _xlpm.h₂, ROWS(_xlpm.array_2), _xlpm.w₂, COLUMNS(_xlpm.array_2), _xlpm.h₃, ROWS(_xlpm.array_3), _xlpm.w₃, COLUMNS(_xlpm.array_3), _xlpm.h₄, ROWS(_xlpm.array_4), _xlpm.w₄, COLUMNS(_xlpm.array_4), _xlpm.S_2, OR(_xlpm.h &lt;&gt; _xlpm.h₂, _xlpm.w &lt;&gt; _xlpm.w₂), _xlpm.S_3, _xlpm.Include3 * OR(_xlpm.h &lt;&gt; _xlpm.h₃, _xlpm.w &lt;&gt; _xlpm.w₃), _xlpm.S_4, _xlpm.Include4 * OR(_xlpm.h &lt;&gt; _xlpm.h₄, _xlpm.w &lt;&gt; _xlpm.w₄), _xlpm.ShapeMismatch?, OR(_xlpm.S_2, _xlpm.S_3, _xlpm.S_4), IF(_xlpm.ShapeMismatch?, "#DIMENSIONS!", _xlfn.LET(_xlpm.Occupiedλ, _xlfn.LAMBDA(_xlpm.arr, _xlfn.LAMBDA((_xlpm.arr &lt;&gt; FALSE) * (LEN(_xlpm.arr) &lt;&gt; 0) * (_xlpm.arr &lt;&gt; _xlpm.ignore))), _xlpm.m_1, _xlpm.Occupiedλ(_xlpm.array_1), _xlpm.m_2, _xlpm.Occupiedλ(_xlpm.array_2), _xlpm.m_3, _xlpm.Occupiedλ(_xlpm.array_3), _xlpm.m_4, _xlpm.Occupiedλ(_xlpm.array_4), _xlpm.final, IF(_xlpm.m_1(), _xlpm.array_1, IF(_xlpm.m_2(), _xlpm.array_2, IF(_xlpm.m_3(), _xlpm.array_3, IF(_xlpm.m_4(), _xlpm.array_4, _xlpm.fill_value)))), _xlpm.final))))</definedName>
     <definedName name="CombinationsRλ">_xlfn.LAMBDA(_xlpm.items,_xlpm.items_chosen, Enumerateλ(_xlpm.items, _xlpm.items_chosen, 3))</definedName>
     <definedName name="Combinationsλ">_xlfn.LAMBDA(_xlpm.items,_xlpm.items_chosen, Enumerateλ(_xlpm.items, _xlpm.items_chosen, 4))</definedName>
-    <definedName name="Convolveλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.kernel,_xlop.function, _xlfn.LET(_xlpm.h, ROWS(_xlpm.array), _xlpm.w, COLUMNS(_xlpm.array), _xlpm.h_, ROWS(_xlpm.kernel), _xlpm.w_, COLUMNS(_xlpm.kernel), _xlpm.InvalidKernel?, OR(_xlpm.h_ &gt; _xlpm.h, _xlpm.w_ &gt; _xlpm.w), _xlpm.IsScalar?, AND(_xlpm.h = 1, _xlpm.w = 1), _xlpm.IsScalarKernel?, AND(_xlpm.h_ = 1, _xlpm.w_ = 1), _xlpm.function, IF(_xlfn.ISOMITTED(_xlpm.function), _xlfn.LAMBDA(_xlpm.v, SUM(_xlpm.v * _xlpm.kernel)), _xlpm.function), _xlpm.InvalidFn?, TYPE(_xlpm.function) &lt;&gt; 128, _xlpm.StandardMap, _xlfn.LAMBDA(_xlfn.MAP(_xlpm.array, _xlpm.function)), IF(_xlpm.InvalidKernel?, "#KERNEL!", IF(_xlpm.InvalidFn?, "#FUNCTION!", IF((_xlpm.IsScalar?) + (_xlpm.IsScalarKernel?), _xlpm.StandardMap(), _xlfn.LET(_xlpm.anch_r, _xlpm.h - _xlpm.h_ + 1, _xlpm.anch_c, _xlpm.w - _xlpm.w_ + 1, _xlpm.i, _xlfn.LAMBDA(Resizeλ(_xlfn.SEQUENCE(_xlpm.anch_r), , _xlpm.anch_c)), _xlpm.j, _xlfn.LAMBDA(Resizeλ(_xlfn.SEQUENCE(, _xlpm.anch_c), _xlpm.anch_r)), _xlpm.BlockAggλ, _xlfn.LAMBDA(_xlpm.i_,_xlpm.j_, _xlfn.LET(_xlpm.block, _xlfn.TAKE(_xlfn.DROP(_xlpm.array, _xlpm.i_ - 1, _xlpm.j_ - 1), _xlpm.h_, _xlpm.w_), _xlpm.total, _xlpm.function(_xlpm.block), _xlpm.total)), _xlpm.result, _xlfn.MAP(_xlpm.i(), _xlpm.j(), _xlpm.BlockAggλ), _xlpm.result))))))</definedName>
+    <definedName name="Convolveλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.kernel,_xlop.function, _xlfn.LET(_xlpm.h, ROWS(_xlpm.array), _xlpm.w, COLUMNS(_xlpm.array), _xlpm.h_, ROWS(_xlpm.kernel), _xlpm.w_, COLUMNS(_xlpm.kernel), _xlpm.InvalidKernel?, OR(_xlpm.h_ &gt; _xlpm.h, _xlpm.w_ &gt; _xlpm.w), _xlpm.IsScalar?, AND(_xlpm.h = 1, _xlpm.w = 1), _xlpm.IsScalarKernel?, AND(_xlpm.h_ = 1, _xlpm.w_ = 1), _xlpm.function, IF(_xlfn.ISOMITTED(_xlpm.function), _xlfn.LAMBDA(_xlpm.v, SUM(_xlpm.v * _xlpm.kernel)), _xlpm.function), _xlpm.InvalidFn?, TYPE(_xlpm.function) &lt;&gt; 128, _xlpm.StandardMap, _xlfn.LAMBDA(_xlfn.MAP(_xlpm.array, _xlpm.function)), IF(_xlpm.InvalidKernel?, "#KERNEL!", IF(_xlpm.InvalidFn?, "#FUNCTION!", IF((_xlpm.IsScalar?) + (_xlpm.IsScalarKernel?), _xlpm.StandardMap(), _xlfn.LET(_xlpm.anch_r, _xlpm.h - _xlpm.h_ + 1, _xlpm.anch_c, _xlpm.w - _xlpm.w_ + 1, _xlpm.i, _xlfn.LAMBDA(Resizeλ(IF(_xlpm.anch_r = 1, 1, _xlfn.SEQUENCE(_xlpm.anch_r)), , _xlpm.anch_c)), _xlpm.j, _xlfn.LAMBDA(Resizeλ(IF(_xlpm.anch_c = 1, 1, _xlfn.SEQUENCE(, _xlpm.anch_c)), _xlpm.anch_r)), _xlpm.BlockAggλ, _xlfn.LAMBDA(_xlpm.i_,_xlpm.j_, _xlfn.LET(_xlpm.block, _xlfn.TAKE(_xlfn.DROP(_xlpm.array, _xlpm.i_ - 1, _xlpm.j_ - 1), _xlpm.h_, _xlpm.w_), _xlpm.total, _xlpm.function(_xlpm.block), _xlpm.total)), _xlpm.result, _xlfn.MAP(_xlpm.i(), _xlpm.j(), _xlpm.BlockAggλ), _xlpm.result))))))</definedName>
     <definedName name="Countdownλ">_xlfn.LAMBDA(_xlpm.array,_xlop.Horizontal?, IF(AND(ROWS(_xlpm.array) = 1, COLUMNS(_xlpm.array) = 1), _xlpm.array, _xlfn.LET(_xlpm.h, ROWS(_xlpm.array), _xlpm.w, COLUMNS(_xlpm.array), _xlpm.Is2D?, AND(_xlpm.h &gt; 1, _xlpm.w &gt; 1), _xlpm.array, IF(_xlpm.Is2D?, _xlfn.TOCOL(_xlpm.array), _xlpm.array), _xlpm.NoDir?, _xlfn.ISOMITTED(_xlpm.Horizontal?), _xlpm.fn, IF(_xlpm.NoDir?, _xleta.VSTACK, _xleta.HSTACK), _xlpm.kept, IF(_xlpm.NoDir?, _xlfn.DROP(_xlpm.array, -1), _xlfn.DROP(_xlpm.array, , -1)), _xlpm.bool, _xlpm.array = _xlpm.fn("omit", _xlpm.kept), _xlpm.acc, _xlfn.SCAN(0, _xlpm.bool, _xlfn.LAMBDA(_xlpm.a,_xlpm.v, IF(_xlpm.a = 0, 1, IF(_xlpm.v, _xlpm.a + 1, 1)))), _xlpm.cg, _xlfn.SCAN(0, NOT(_xlpm.bool), _xleta.SUM), _xlpm.sorted, _xlfn.SORTBY(_xlpm.acc, _xlpm.cg, 1, _xlpm.acc, -1), _xlpm.deliver, IF(_xlpm.Is2D?, _xlfn.WRAPROWS(_xlpm.sorted, _xlpm.w), _xlpm.sorted), _xlpm.deliver)))</definedName>
     <definedName name="Dec2Binλ">_xlfn.LAMBDA(_xlpm.numbers,_xlop.Array_Form_2D, IF(OR(ISTEXT(_xlpm.numbers), ISERROR(--_xlpm.numbers), _xlpm.numbers &lt; 0), #VALUE!, _xlfn.LET(_xlpm.h, ROWS(_xlpm.numbers), _xlpm.w, COLUMNS(_xlpm.numbers), _xlpm.IsScalar?, AND(_xlpm.h = 1, _xlpm.w = 1), _xlpm.IsVertical?, _xlpm.h &gt; _xlpm.w, _xlpm.Is2D?, AND(_xlpm.h &gt; 1, _xlpm.w &gt; 1), _xlpm.numbers, _xlfn.TOCOL(_xlpm.numbers), _xlpm.IsVector?, _xlfn.ISOMITTED(_xlpm.Array_Form_2D), _xlpm.bits, MAX(IFERROR(INT(LOG(_xlpm.numbers, 2)) + 1, 1)), _xlpm.bin_arr, _xlfn.LAMBDA(MOD(_xlfn.BITRSHIFT(_xlpm.numbers, _xlfn.SEQUENCE(, _xlpm.bits, _xlpm.bits - 1, -1)), 2)), _xlpm.bin_vector, _xlfn.LAMBDA(_xlfn.BYROW(_xlpm.bin_arr(), _xleta.CONCAT)), _xlpm.bin_result, _xlfn.LAMBDA(IF(_xlpm.IsVector?, _xlpm.bin_vector(), _xlpm.bin_arr())), _xlpm.deliver, IF(_xlpm.Is2D?, _xlfn.WRAPROWS(_xlpm.bin_vector(), _xlpm.w), IF(OR(_xlpm.IsScalar?, _xlpm.IsVertical?), _xlpm.bin_result(), TRANSPOSE(_xlpm.bin_result()))), _xlpm.deliver)))</definedName>
     <definedName name="Dec2Grayλ">_xlfn.LAMBDA(_xlpm.number,_xlop.concise, Bin2Grayλ(Dec2Binλ(_xlpm.number), _xlpm.concise))</definedName>
@@ -55,8 +55,10 @@
     <definedName name="Grainλ">_xlfn.LAMBDA(_xlpm.array_2D,_xlpm.depth,_xlpm.width,_xlpm.function, IF(NOT(TYPE(_xlpm.array_2D) = 64), "#array_2D!", IF(OR(_xlpm.depth &gt; ROWS(_xlpm.array_2D), _xlpm.width &gt; COLUMNS(_xlpm.array_2D), ISTEXT(_xlpm.depth), ISTEXT(_xlpm.width)), "#DIMENSIONS!", IF(TYPE(_xlpm.function) &lt;&gt; 128, "#ETA FUNCTION!", _xlfn.LET(_xlpm.h, ROWS(_xlpm.array_2D), _xlpm.w, COLUMNS(_xlpm.array_2D), _xlpm.x, ROUNDUP(_xlpm.h / _xlpm.depth, 0), _xlpm.y, ROUNDUP(_xlpm.w / _xlpm.width, 0), _xlpm.down, _xlfn.LAMBDA(_xlfn.SEQUENCE(_xlpm.x, , 1, _xlpm.depth) * _xlfn.SEQUENCE(, _xlpm.y, 1, 0)), _xlpm.across, _xlfn.LAMBDA(_xlfn.SEQUENCE(, _xlpm.y, 1, _xlpm.width) * _xlfn.SEQUENCE(_xlpm.x, , 1, 0)), _xlpm.Blocksλ, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, _xlfn.LET(_xlpm.i, _xlfn.LAMBDA(_xlfn.SEQUENCE(_xlpm.depth, , _xlpm.r) * _xlfn.SEQUENCE(, _xlpm.width, 1, 0)), _xlpm.j, _xlfn.LAMBDA(_xlfn.SEQUENCE(, _xlpm.width, _xlpm.c) * _xlfn.SEQUENCE(_xlpm.depth, , 1, 0)), _xlpm.block, _xlfn.TOCOL(INDEX(_xlpm.array_2D, _xlpm.i(), _xlpm.j()), 2), _xlpm.result, _xlpm.function(_xlpm.block), _xlpm.result)), _xlpm.deliver, _xlfn.MAP(_xlpm.down(), _xlpm.across(), _xlpm.Blocksλ), _xlpm.deliver)))))</definedName>
     <definedName name="GroupbyBinλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.values,_xlpm.bin_width,_xlpm.function,_xlop.field_header,_xlop.chart_prep, _xlfn.LET(_xlpm.i, ROWS(_xlpm.array), _xlpm.j, COLUMNS(_xlpm.array), _xlpm.i_, ROWS(_xlpm.values), _xlpm.j_, COLUMNS(_xlpm.values), _xlpm.Headers?, NOT(_xlfn.ISOMITTED(_xlpm.field_header)), _xlpm.Is2D?, AND(_xlpm.i &gt; 1, _xlpm.j &gt; 1), _xlpm.ShapeMismatch?, _xlpm.i &lt;&gt; _xlpm.i_, _xlpm.InvalidBin?, OR(ISTEXT(_xlpm.bin_width), _xlpm.bin_width &lt; 1), _xlpm.InvalidFn?, TYPE(_xlpm.function) &lt;&gt; 128, _xlpm.NonNumeric?, NOT(AND(ISNUMBER(IF(_xlpm.Headers?, _xlfn.DROP(_xlpm.array, 1), _xlpm.array)))), IF(_xlpm.Is2D?, "#1D-ARRAY!", IF(_xlpm.ShapeMismatch?, "#DIMENSIONS!", IF(_xlpm.NonNumeric?, "#NUM!", IF(_xlpm.InvalidBin?, "#BIN-WIDTH!", IF(_xlpm.InvalidFn?, "#INVALID-FUNCTION!", _xlfn.LET(_xlpm.NoChart?, _xlfn.ISOMITTED(_xlpm.chart_prep), _xlpm.arr, IF(_xlpm.Headers?, _xlfn.DROP(_xlpm.array, 1), _xlpm.array), _xlpm.val, IF(_xlpm.Headers?, _xlfn.DROP(_xlpm.values, 1), _xlpm.values), _xlpm.row_header, _xlfn.HSTACK("Bin Start " &amp; IF(_xlpm.Headers?, _xlfn.TAKE(_xlpm.array, 1), "") &amp; " Value", "Bin End"), _xlpm.val_header, _xlfn.EXPAND(IF(_xlpm.Headers?, _xlfn.TAKE(_xlpm.values, 1), "Total"), , _xlpm.j_, ""), _xlpm.header, _xlfn.HSTACK(_xlpm.row_header, _xlpm.val_header), _xlpm.min, MIN(_xlpm.arr), _xlpm.start, FLOOR(_xlpm.min, _xlpm.bin_width), _xlpm.max, MAX(_xlpm.arr), _xlpm.end, CEILING(_xlpm.max, _xlpm.bin_width), _xlpm.k, (_xlpm.end - _xlpm.start) / _xlpm.bin_width, _xlpm.bin, _xlfn.SEQUENCE(_xlpm.k + 1, , _xlpm.start, _xlpm.bin_width), _xlpm.bin_start, _xlfn.DROP(_xlpm.bin, -1), _xlpm.bin_end, _xlfn.DROP(_xlpm.bin, 1), _xlpm.idx, _xlfn.XMATCH(_xlpm.arr, _xlpm.bin_start, -1), _xlpm.row_start, INDEX(_xlpm.bin_start, _xlpm.idx), _xlpm.row_end, INDEX(_xlpm.bin_end, _xlpm.idx), _xlpm.row_fields, _xlfn.HSTACK(_xlpm.row_start, _xlpm.row_end), _xlpm.agg, _xlfn.GROUPBY(_xlpm.row_fields, _xlpm.val, _xlpm.function, _xlpm.Headers?, 0), _xlpm.a, _xlfn.CHOOSECOLS(_xlpm.agg, 1) &amp; " - &lt;" &amp; _xlfn.CHOOSECOLS(_xlpm.agg, 2), _xlpm.b, _xlfn.DROP(_xlpm.agg, , 2), _xlpm.chart_labels, {"Bin","Aggregate"}, _xlpm.data, _xlfn.VSTACK(_xlpm.header, _xlpm.agg), _xlpm.chart, _xlfn.VSTACK(_xlpm.chart_labels, _xlfn.HSTACK(_xlpm.a, _xlpm.b)), _xlpm.delivery, IF(_xlpm.NoChart?, _xlpm.data, _xlpm.chart), _xlpm.delivery))))))))</definedName>
     <definedName name="GroupbyDateλ">_xlfn.LAMBDA(_xlpm.row_fields,_xlpm.values,_xlpm.interval,_xlpm.function,_xlop.format,_xlop.field_headers,_xlop.filter_array, ValidateGDλ(_xlpm.row_fields, _xlpm.values, _xlpm.interval, _xlpm.function, _xlpm.field_headers, _xlpm.filter_array, _xlfn.LET(_xlpm.NumInterval?, NOT(ISTEXT(_xlpm.interval)), _xlpm.const, {"minute";"hour";"day";"week";"fortnight";"month";"quarter";"year"}, _xlpm.interval, IF(_xlpm.NumInterval?, _xlpm.interval, _xlfn.XMATCH(LOWER(_xlpm.interval) &amp; "*", _xlpm.const, 2)), _xlpm.Includes_end?, (_xlpm.interval = 4) + (_xlpm.interval = 5), _xlpm.unit, CHOOSE(_xlpm.interval, 1440, 24, 1, 1, 1, 1, 1, 1), _xlpm.NoFormat?, _xlfn.ISOMITTED(_xlpm.format), _xlpm.Header?, NOT(_xlfn.ISOMITTED(_xlpm.field_headers)), _xlpm.Filter?, NOT(_xlfn.ISOMITTED(_xlpm.filter_array)), _xlpm.date_col, IF(_xlpm.Header?, _xlfn.DROP(_xlfn.TAKE(_xlpm.row_fields, , 1), 1), _xlfn.TAKE(_xlpm.row_fields, , 1)), _xlpm.dates, IF(_xlpm.interval &lt; 3, ROUND(_xlpm.date_col * _xlpm.unit, 0) / _xlpm.unit, INT(_xlpm.date_col)), _xlpm.values_header, _xlfn.TAKE(_xlpm.values, 1), _xlpm.values, IF(_xlpm.Header?, _xlfn.DROP(_xlpm.values, 1), _xlpm.values), _xlpm.row_details, _xlfn.DROP(_xlfn.DROP(_xlpm.row_fields, , 1), _xlpm.Header?), _xlpm.filter_used, IF(_xlpm.Header? * _xlpm.Filter?, _xlfn.DROP(_xlpm.filter_array, 1), _xlpm.filter_array), _xlpm.w, COLUMNS(_xlpm.row_fields), _xlpm.w_, COLUMNS(_xlpm.values), _xlpm.j, _xlpm.w + _xlpm.w_, _xlpm.min, INT(MIN(_xlpm.dates)), _xlpm.max, INT(MAX(_xlpm.dates)), _xlpm.m, MONTH(_xlpm.min), _xlpm.d, DAY(_xlpm.min), _xlpm.y, YEAR(_xlpm.min), _xlpm.first, MIN(_xlpm.dates), _xlpm.last, MAX(_xlpm.dates), _xlpm.hr, HOUR(_xlpm.first), _xlpm.mm, MINUTE(_xlpm.first), _xlpm.seconds, (_xlpm.last - _xlpm.first) * 86400, _xlpm.minutes, CEILING(_xlpm.seconds / 60, 1), _xlpm.hours, _xlpm.minutes / 60, _xlpm.days, _xlpm.max - _xlpm.min, _xlpm.weeks, CEILING(_xlpm.days / 7, 1), _xlpm.fortnight, CEILING(_xlpm.days / 14, 1), _xlpm.months, DATEDIF(_xlpm.min, _xlpm.max, "m"), _xlpm.quarters, CEILING(_xlpm.months / 3, 1), _xlpm.years, CEILING(_xlpm.months / 12, 1), _xlpm.h_mm, IF(_xlpm.days &gt; 1, "m/d/yyy h:mm AM/PM", "h:mm AM/PM"), _xlpm.mmmm, "mmmm yyy", _xlpm.day, "m/d/yyy", _xlpm.yyy, "yyy", _xlpm.fmt, IF(_xlpm.NoFormat?, _xlfn.SWITCH(_xlpm.interval, 1, _xlpm.h_mm, 2, _xlpm.h_mm, 3, _xlpm.day, 4, _xlpm.day, 5, _xlpm.day, 6, _xlpm.mmmm, 7, _xlpm.mmmm, 8, _xlpm.yyy, _xlpm.mmmm), _xlpm.format), _xlpm.min_arr, _xlfn.LAMBDA(_xlfn.SEQUENCE(_xlfn.SINGLE(_xlpm.minutes) + 1, , _xlpm.first, 1 / 1440)), _xlpm.hrs_arr, _xlfn.LAMBDA(_xlfn.SEQUENCE(_xlfn.SINGLE(_xlpm.hours) + 1, , _xlpm.first, 1 / 24)), _xlpm.days_arr, _xlfn.LAMBDA(_xlfn.SEQUENCE(_xlpm.days + 1, , _xlpm.min, 1)), _xlpm.weeks_arr, _xlfn.LAMBDA(DATE(_xlpm.y, _xlpm.m, _xlfn.SEQUENCE(_xlpm.weeks + 1, , _xlpm.d, 7))), _xlpm.fort_arr, _xlfn.LAMBDA(DATE(_xlpm.y, _xlpm.m, _xlfn.SEQUENCE(_xlpm.fortnight + 1, , _xlpm.d, 14))), _xlpm.month_arr, _xlfn.LAMBDA(DATE(_xlpm.y, _xlpm.m + _xlfn.SEQUENCE(_xlpm.months + 1, , 0), _xlpm.d)), _xlpm.qtrs_arr, _xlfn.LAMBDA(DATE(_xlpm.y, _xlpm.m + _xlfn.SEQUENCE(_xlpm.quarters + 1, , 0, 3), _xlpm.d)), _xlpm.yrs_arr, _xlfn.LAMBDA(DATE(_xlpm.y + _xlfn.SEQUENCE(_xlfn.SINGLE(_xlpm.years) + 1, , 0), _xlpm.m, 1)), _xlpm.bin, _xlfn.LAMBDA(IF(_xlpm.interval &lt; 3, ROUND(CHOOSE(_xlpm.interval, _xlpm.min_arr(), _xlpm.hrs_arr()) * _xlpm.unit, 0) / _xlpm.unit, CHOOSE(_xlpm.interval - 2, _xlpm.days_arr(), _xlpm.weeks_arr(), _xlpm.fort_arr(), _xlpm.month_arr(), _xlpm.qtrs_arr(), _xlpm.yrs_arr()))), _xlpm.i, _xlfn.LAMBDA(IF(_xlpm.interval = 8, _xlfn.XMATCH(YEAR(_xlpm.dates), YEAR(_xlpm.bin())), _xlfn.XMATCH(_xlpm.dates, _xlpm.bin(), -1))), _xlpm.date_field, _xlfn.LAMBDA(INDEX(_xlpm.bin(), _xlpm.i())), _xlpm.row_labels, IF(_xlpm.w = 1, _xlpm.date_field(), _xlfn.HSTACK(_xlpm.date_field(), _xlpm.row_details)), _xlpm.total_label, _xlfn.SWITCH(_xlpm.interval, 1, "Totals by minute", 2, "Totals by hour", 3, "Totals by Day", 4, "Weekly Totals", 5, "Biweekly Totals", 6, "Monthly Totals", 7, "Totals by Quarter", 8, "Yearly Totals", ""), _xlpm.total_header, _xlfn.EXPAND(IF(OR(_xlpm.interval = 4, _xlpm.interval = 5), _xlfn.HSTACK(_xlpm.total_label, "Ending Date"), _xlpm.total_label), , _xlpm.w + _xlpm.Includes_end?, ""), _xlpm.agg_header, IF(_xlpm.Header?, _xlpm.values_header, _xlfn.EXPAND("", , _xlpm.w_, "")), _xlpm.no_filter, _xlfn.GROUPBY(_xlpm.row_labels, _xlpm.values, _xlpm.function, _xlpm.Header?), _xlpm.filter_inc, _xlfn.GROUPBY(_xlpm.row_labels, _xlpm.values, _xlpm.function, _xlpm.Header?, , , _xlpm.filter_used), _xlpm.agg, IF(_xlpm.Filter?, _xlpm.filter_inc, _xlpm.no_filter), _xlpm.row_label, _xlfn.LAMBDA(_xlfn.TAKE(_xlpm.agg, , 1)), _xlpm.a, _xlfn.LAMBDA(TEXT(_xlpm.row_label(), _xlpm.fmt)), _xlpm.bin_end, _xlfn.LAMBDA(IF(_xlpm.interval = 4, TEXT(_xlpm.a() + 6, _xlpm.fmt), IF(_xlpm.interval = 5, TEXT(_xlpm.a() + 13, _xlpm.fmt), 0))), _xlpm.b, _xlfn.LAMBDA(_xlfn.DROP(_xlpm.agg, , 1)), _xlpm.stack, _xlfn.VSTACK(_xlfn.HSTACK(_xlpm.total_header, _xlpm.agg_header), _xlfn.HSTACK(_xlpm.a(), _xlpm.b())), _xlpm.stack_end, IFERROR(_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.total_header, _xlpm.agg_header), _xlfn.HSTACK(_xlpm.a(), _xlpm.bin_end(), _xlpm.b())), ""), _xlpm.delivery, IF(OR(_xlpm.interval = 4, _xlpm.interval = 5), _xlpm.stack_end, _xlpm.stack), _xlpm.delivery)))</definedName>
+    <definedName name="GroupIndexλ">_xlfn.LAMBDA(_xlpm.vector,_xlop.Horizontal?, _xlfn.LET(_xlpm.vector, _xlfn.TOCOL(_xlpm.vector), _xlpm.height, ROWS(_xlpm.vector), _xlpm.width, COLUMNS(_xlpm.vector), _xlpm.IsVertical?, _xlfn.ISOMITTED(_xlpm.Horizontal?), _xlpm.IsScalar?, AND(_xlpm.height = 1, _xlpm.width = 1), _xlpm.SpillRisk?, IF(_xlpm.IsVertical?, _xlpm.height &gt; 1048576, _xlpm.height &gt; 16384), IF(_xlpm.IsScalar?, _xlpm.vector, IF(_xlpm.SpillRisk?, #NUM!, _xlfn.LET(_xlpm.idx, _xlfn.XMATCH(_xlpm.vector, _xlfn.UNIQUE(_xlpm.vector)), _xlpm.final, IF(_xlpm.IsVertical?, _xlpm.idx, _xlfn.TOROW(_xlpm.idx)), _xlpm.final)))))</definedName>
     <definedName name="Histogramλ">_xlfn.LAMBDA(_xlpm.array,_xlop.bin_width,_xlop.include_Pareto, IF(COUNT(_xlpm.array) &lt;= 1, #VALUE!, IF(AND(NOT(_xlfn.ISOMITTED(_xlpm.bin_width)), OR(_xlpm.bin_width &lt; 0, _xlpm.bin_width &gt; 1000)), "#BIN-WIDTH!", _xlfn.LET(_xlpm.n, COUNT(_xlpm.array), _xlpm.SmallData?, _xlpm.n &lt; 200, _xlpm.Add_Pareto?, NOT(_xlfn.ISOMITTED(_xlpm.include_Pareto)), _xlpm.min, MIN(_xlpm.array), _xlpm.max, MAX(_xlpm.array), _xlpm.range, _xlpm.max - _xlpm.min, _xlpm.iqr, QUARTILE(_xlpm.array, 3) - QUARTILE(_xlpm.array, 1), _xlpm.s, SKEW(_xlpm.array), _xlpm.IsSkewed?, IF(_xlpm.SmallData?, FALSE, ABS(_xlpm.s) &gt; 0.2), _xlpm.IsFixed?, NOT(_xlfn.ISOMITTED(_xlpm.bin_width)), _xlpm.Sturge, CEILING(LOG(_xlpm.n, 2) + 1, 1), _xlpm.SRR, CEILING(SQRT(_xlpm.n), 1), _xlpm.Rice, CEILING(2 * _xlpm.n ^ (1 / 3), 1), _xlpm.Scott, CEILING(3.5 * _xlfn.STDEV.P(_xlpm.array) / _xlpm.n ^ (1 / 3), 1), _xlpm.Freedman, CEILING(2 * _xlpm.iqr / _xlpm.n ^ (1 / 3), 1), _xlpm.fixed, CEILING(_xlpm.range / _xlpm.bin_width, 1 / _xlpm.bin_width), _xlpm.k, IF(_xlpm.IsFixed?, _xlpm.fixed, IF(_xlpm.n &lt;= 30, MAX(_xlpm.Sturge, _xlpm.Rice), IF(_xlpm.IsSkewed?, MIN(_xlpm.Freedman, 15), MIN(_xlpm.Scott, 15)))), _xlpm.k_, MIN(IF(_xlpm.k = 1, 5, _xlpm.k), 100), _xlpm.interval, IF(_xlpm.range = 0, 1, MAX(_xlpm.range / _xlpm.k_, 0.1)), _xlpm.bin_upper, CEILING(_xlpm.max, _xlpm.interval), _xlpm.bin_lower, FLOOR(_xlpm.min, _xlpm.interval), _xlpm.bin_arr, _xlfn.SEQUENCE(1 + (_xlpm.bin_upper - _xlpm.bin_lower) / _xlpm.interval, , _xlpm.bin_lower, _xlpm.interval), _xlpm.bin_start, _xlfn.DROP(_xlpm.bin_arr, -1), _xlpm.bin_end, _xlfn.DROP(_xlpm.bin_arr, 1), _xlpm.bin_header, {"Start","End","Total"}, _xlpm.bin_labels, _xlfn.HSTACK(_xlfn.VSTACK("&lt;", _xlpm.bin_start), _xlfn.VSTACK(_xlfn.TAKE(_xlpm.bin_start, 1), _xlpm.bin_end)), _xlpm.freq, _xlfn.DROP(FREQUENCY(_xlpm.array, _xlpm.bin_arr), -1), _xlpm.Pareto, _xlfn.BYROW(_xlpm.freq, _xlfn.LAMBDA(_xlpm.v, _xlfn.PERCENTOF(_xlpm.v, _xlpm.freq))), _xlpm.stack, _xlfn.VSTACK(_xlpm.bin_header, _xlfn.HSTACK(_xlpm.bin_labels, _xlpm.freq)), _xlpm.deliver, IF(_xlpm.Add_Pareto?, _xlfn._xlws.SORT(_xlfn.HSTACK(_xlpm.stack, _xlfn.VSTACK("Cumulative %", _xlpm.Pareto)), 3, -1), _xlpm.stack), _xlpm.deliver))))</definedName>
     <definedName name="InputGrid">Gridwork!$B$5:$K$14</definedName>
+    <definedName name="Instanceλ">_xlfn.LAMBDA(_xlpm.vector,_xlop.Horizontal?,_xlop.Descend?, _xlfn.LET(_xlpm.vector, _xlfn.TOCOL(_xlpm.vector), _xlpm.height, ROWS(_xlpm.vector), _xlpm.width, COLUMNS(_xlpm.vector), _xlpm.IsVertical?, _xlfn.ISOMITTED(_xlpm.Horizontal?), _xlpm.IsDescend?, AND(NOT(_xlfn.ISOMITTED(_xlpm.Descend?)), _xlpm.Descend? = TRUE), _xlpm.IsScalar?, AND(_xlpm.height = 1, _xlpm.width = 1), _xlpm.SpillRisk?, IF(_xlpm.IsVertical?, _xlpm.height &gt; 1048576, _xlpm.height &gt; 16384), IF(_xlpm.IsScalar?, _xlpm.vector, IF(_xlpm.SpillRisk?, #NUM!, _xlfn.LET(_xlpm.idxλ, IF(_xlpm.IsDescend?, Countdownλ, Streakλ), _xlpm.i, MGridλ(_xlpm.vector), _xlpm.sorted, _xlfn._xlws.SORT(_xlfn.HSTACK(_xlpm.i, _xlpm.vector), 2), _xlpm.idx, _xlpm.idxλ(_xlfn.TAKE(_xlpm.sorted, , -1)), _xlpm.new_arr, _xlfn.HSTACK(_xlpm.sorted, _xlpm.idx), _xlpm.inst, _xlfn.TAKE(_xlfn._xlws.SORT(_xlpm.new_arr), , -1), _xlpm.final, IF(_xlpm.IsVertical?, _xlpm.inst, _xlfn.TOROW(_xlpm.inst)), _xlpm.final)))))</definedName>
     <definedName name="InsulateColsλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.columns_before,_xlop.columns_after,_xlop.pad_with, _xlfn.LET(_xlpm.array_v, TRANSPOSE(_xlpm.array), _xlpm.padded_v, InsulateRowsλ(_xlpm.array_v, _xlpm.columns_before, _xlpm.columns_after, _xlpm.pad_with), _xlpm.result, TRANSPOSE(_xlpm.padded_v), _xlpm.result))</definedName>
     <definedName name="InsulateRowsλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.rows_before,_xlop.rows_after,_xlop.pad_with, _xlfn.LET(_xlpm.h, ROWS(_xlpm.array), _xlpm.w, COLUMNS(_xlpm.array), _xlpm.rows_after, IF(_xlfn.ISOMITTED(_xlpm.rows_after), _xlpm.rows_before, _xlpm.rows_after), _xlpm.pad_with, INDEX(IF(_xlfn.ISOMITTED(_xlpm.pad_with), "", _xlpm.pad_with), 1, 1), _xlpm.InvalidPadCount?, OR(ISTEXT(_xlpm.rows_before), ISTEXT(_xlpm.rows_after), _xlpm.rows_before &lt; 0, _xlpm.rows_after &lt; 0), _xlpm.NoPadding?, AND(_xlpm.rows_before = 0, _xlpm.rows_after = 0), IF(_xlpm.InvalidPadCount?, "#ROWS-BEFORE/AFTER!", IF(_xlpm.NoPadding?, _xlpm.array, _xlfn.LET(_xlpm.pad_before, _xlfn.EXPAND(_xlpm.pad_with, _xlpm.rows_before, _xlpm.w, _xlpm.pad_with), _xlpm.pad_after, _xlfn.EXPAND(_xlpm.pad_with, _xlpm.rows_after, _xlpm.w, _xlpm.pad_with), _xlpm.before_only?, AND(_xlpm.rows_before &lt;&gt; 0, _xlpm.rows_after = 0), _xlpm.after_only?, AND(_xlpm.rows_before = 0, _xlpm.rows_after &lt;&gt; 0), _xlpm.fully_insulated?, AND(_xlpm.rows_before &lt;&gt; 0, _xlpm.rows_after &lt;&gt; 0), _xlpm.k, _xlpm.rows_after + _xlpm.h, _xlpm.expand_only, _xlfn.EXPAND(_xlpm.array, _xlpm.k, _xlpm.w, _xlpm.pad_with), _xlpm.insulate_before, _xlfn.VSTACK(_xlpm.pad_before, _xlpm.array), _xlpm.insulate_all, _xlfn.VSTACK(_xlpm.pad_before, _xlpm.array, _xlpm.pad_after), _xlpm.result, IF(_xlpm.fully_insulated?, _xlpm.insulate_all, IF(_xlpm.before_only?, _xlpm.insulate_before, _xlpm.expand_only)), _xlpm.result)))))</definedName>
     <definedName name="Join2Dλ">_xlfn.LAMBDA(_xlpm.array_1,_xlpm.array_2,_xlop.array_3,_xlop.array_4,_xlop.delimiter,_xlop.ignore, _xlfn.LET(_xlpm.Include3?, NOT(_xlfn.ISOMITTED(_xlpm.array_3)), _xlpm.Include4?, NOT(_xlfn.ISOMITTED(_xlpm.array_4)), _xlpm.array_3, IF(_xlfn.ISOMITTED(_xlpm.array_3), FALSE, _xlpm.array_3), _xlpm.array_4, IF(_xlfn.ISOMITTED(_xlpm.array_4), FALSE, _xlpm.array_4), _xlpm.delimiter, IF(_xlfn.ISOMITTED(_xlpm.delimiter), ", ", _xlpm.delimiter), _xlpm.ignore, IF(_xlfn.ISOMITTED(_xlpm.ignore), "", _xlpm.ignore), _xlpm.h, ROWS(_xlpm.array_1), _xlpm.w, COLUMNS(_xlpm.array_1), _xlpm.h₂, ROWS(_xlpm.array_2), _xlpm.w₂, COLUMNS(_xlpm.array_2), _xlpm.h₃, ROWS(_xlpm.array_3), _xlpm.w₃, COLUMNS(_xlpm.array_3), _xlpm.h₄, ROWS(_xlpm.array_4), _xlpm.w₄, COLUMNS(_xlpm.array_4), _xlpm.S_2, OR(_xlpm.h &lt;&gt; _xlpm.h₂, _xlpm.w &lt;&gt; _xlpm.w₂), _xlpm.S_3, _xlpm.Include3? * OR(_xlpm.h &lt;&gt; _xlpm.h₃, _xlpm.w &lt;&gt; _xlpm.w₃), _xlpm.S_4, _xlpm.Include4? * OR(_xlpm.h &lt;&gt; _xlpm.h₄, _xlpm.w &lt;&gt; _xlpm.w₄), _xlpm.ShapeMismatch?, OR(_xlpm.S_2, _xlpm.S_3, _xlpm.S_4), IF(_xlpm.ShapeMismatch?, "#DIMENSIONS!", _xlfn.LET(_xlpm.Occupiedλ, _xlfn.LAMBDA(_xlpm.a, (_xlpm.a &lt;&gt; FALSE) * (LEN(_xlpm.a) &lt;&gt; 0) * (_xlpm.a &lt;&gt; _xlpm.ignore)), _xlpm.m_1, _xlpm.Occupiedλ(_xlpm.array_1), _xlpm.m_2, _xlpm.Occupiedλ(_xlpm.array_2), _xlpm.m_3, _xlpm.Occupiedλ(_xlpm.array_3), _xlpm.m_4, _xlpm.Occupiedλ(_xlpm.array_4), _xlpm.joined, IF(_xlpm.m_1, _xlpm.array_1 &amp; _xlpm.delimiter, "") &amp; IF(_xlpm.m_2, _xlpm.array_2 &amp; _xlpm.delimiter, "") &amp; IF(_xlpm.m_3, _xlpm.array_3 &amp; _xlpm.delimiter, "") &amp; IF(_xlpm.m_4, _xlpm.array_4 &amp; _xlpm.delimiter, ""), _xlpm.final, _xlfn.TEXTBEFORE(_xlpm.joined, _xlpm.delimiter, -1, 1, , _xlpm.joined), _xlpm.final))))</definedName>
@@ -70,6 +72,8 @@
     <definedName name="MooreAggλ">_xlfn.LAMBDA(_xlpm.array_2D,_xlpm.function,_xlop.IsvonNeumann?,_xlop.omit_center, IF(TYPE(_xlpm.array_2D) &lt;&gt; 64, "#array_2D!", IF(TYPE(_xlpm.function) &lt;&gt; 128, "#ETA FUNCTION!", _xlfn.LET(_xlpm.IsvonNeumann?, NOT(_xlfn.ISOMITTED(_xlpm.IsvonNeumann?)), _xlpm.omit_center, NOT(_xlfn.ISOMITTED(_xlpm.omit_center)), _xlpm.height, ROWS(_xlpm.array_2D), _xlpm.width, COLUMNS(_xlpm.array_2D), _xlpm.M, _xlfn.VSTACK("omit", _xlfn.HSTACK("omit", _xlpm.array_2D, "omit"), "omit"), _xlpm.a, _xlfn.TOCOL(_xlfn.DROP(_xlpm.M, -2, -2)), _xlpm.b, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 1), _xlpm.height, _xlpm.width)), _xlpm.c, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 2), _xlpm.height)), _xlpm.d, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), _xlpm.height, _xlpm.width)), _xlpm.center, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, _xlpm.width)), _xlpm.f, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, -_xlpm.width)), _xlpm.g, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, _xlpm.width)), _xlpm.h, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, -_xlpm.width)), _xlpm.i, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), -_xlpm.height, -_xlpm.width)), _xlpm.Moore_no_center, _xlfn.HSTACK(_xlpm.a, _xlpm.b, _xlpm.c, _xlpm.d, _xlpm.f, _xlpm.g, _xlpm.h, _xlpm.i), _xlpm.Moore_with_center, _xlfn.HSTACK(_xlpm.a, _xlpm.b, _xlpm.c, _xlpm.d, _xlpm.center, _xlpm.f, _xlpm.g, _xlpm.h, _xlpm.i), _xlpm.von_no_center, _xlfn.HSTACK(_xlpm.b, _xlpm.d, _xlpm.f, _xlpm.h), _xlpm.von_with_center, _xlfn.HSTACK(_xlpm.b, _xlpm.d, _xlpm.f, _xlpm.h, _xlpm.center), _xlpm.Aggregateλ, _xlfn.LAMBDA(_xlpm.v, _xlpm.function(_xlfn.TOCOL(_xlfn.IFS(_xlpm.v, _xlpm.v), 2))), _xlpm.agg, IF(_xlpm.IsvonNeumann?, IF(_xlpm.omit_center, _xlfn.BYROW(_xlpm.von_no_center, _xlpm.Aggregateλ), _xlfn.BYROW(_xlpm.von_with_center, _xlpm.Aggregateλ)), IF(_xlpm.omit_center, _xlfn.BYROW(_xlpm.Moore_no_center, _xlpm.Aggregateλ), _xlfn.BYROW(_xlpm.Moore_with_center, _xlpm.Aggregateλ))), _xlpm.deliver, IFERROR(_xlfn.WRAPROWS(_xlpm.agg, _xlpm.width), 0), _xlpm.deliver))))</definedName>
     <definedName name="MooreSelectλ">_xlfn.LAMBDA(_xlpm.array_2D,_xlpm.neighbor, IF(TYPE(_xlpm.array_2D) &lt;&gt; 64, "#array_2D!", IF(NOT(AND(_xlpm.neighbor &gt;= 1, _xlpm.neighbor &lt;= 9, NOT(ISTEXT(_xlpm.neighbor)))), "#NEIGHBOR!", _xlfn.LET(_xlpm.height, ROWS(_xlpm.array_2D), _xlpm.width, COLUMNS(_xlpm.array_2D), _xlpm.hpad, _xlfn.EXPAND(0, , _xlpm.width + 2, 0), _xlpm.vpad, _xlfn.EXPAND(0, _xlpm.height, , 0), _xlpm.M, _xlfn.VSTACK(_xlpm.hpad, _xlfn.HSTACK(_xlpm.vpad, _xlpm.array_2D, _xlpm.vpad), _xlpm.hpad), _xlpm.a, _xlfn.DROP(_xlpm.M, -2, -2), _xlpm.b, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 1), _xlpm.height, _xlpm.width), _xlpm.c, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 2), _xlpm.height), _xlpm.d, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), _xlpm.height, _xlpm.width), _xlpm.center, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, _xlpm.width), _xlpm.f, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, -_xlpm.width), _xlpm.g, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, _xlpm.width), _xlpm.h, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, -_xlpm.width), _xlpm.i, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), -_xlpm.height, -_xlpm.width), _xlpm.Moore, _xlfn.HSTACK(_xlpm.a, _xlpm.b, _xlpm.c, _xlpm.d, _xlpm.center, _xlpm.f, _xlpm.g, _xlpm.h, _xlpm.i), _xlpm.start, (_xlpm.neighbor - 1) * _xlpm.width + 1, _xlpm.select_neighbor, _xlfn.CHOOSECOLS(_xlpm.Moore, _xlfn.SEQUENCE(, _xlpm.width, _xlpm.start)), _xlpm.select_neighbor))))</definedName>
     <definedName name="NumbersOnlyλ">_xlfn.LAMBDA(_xlpm.array, _xlfn.LET(_xlpm.array, IF(TYPE(_xlpm.array) &lt;&gt; 64, _xlpm.array, _xlfn.TOCOL(_xlpm.array)), _xlpm.ex, Explodeλ(_xlpm.array), _xlpm.Keep, IFERROR((CODE(_xlpm.ex) &gt;= 48) * (CODE(_xlpm.ex) &lt;= 57), FALSE), _xlpm.Result, IF(_xlpm.Keep, _xlpm.ex, ""), _xlpm.final, IFERROR(_xlfn.BYROW(_xlpm.Result, _xleta.CONCAT) + 0, ""), _xlpm.final))</definedName>
+    <definedName name="OccurrenceRangeλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.crit_vector,_xlpm.start_occurrence,_xlop.end_occurrence,_xlop.Horizontal?, _xlfn.LET(_xlpm.IsVertical?, NOT(AND(NOT(_xlfn.ISOMITTED(_xlpm.Horizontal?)), _xlpm.Horizontal? = TRUE)), _xlpm.array, IF(_xlpm.IsVertical?, _xlpm.array, TRANSPOSE(_xlpm.array)), _xlpm.crit_vector, IF(_xlpm.IsVertical?, _xlpm.crit_vector, TRANSPOSE(_xlpm.crit_vector)), _xlpm.IncludeEnd?, NOT(_xlfn.ISOMITTED(_xlpm.end_occurrence)), _xlpm.start_occurrence, INDEX(_xlpm.start_occurrence, 1, 1), _xlpm.end_occurrence, IF(_xlpm.IncludeEnd?, INDEX(_xlpm.end_occurrence, 1, 1), FALSE), _xlpm.height, ROWS(_xlpm.array), _xlpm.height_, ROWS(_xlpm.crit_vector), _xlpm.height_mismatch?, _xlpm.height &lt;&gt; _xlpm.height_, _xlpm.InvalidOccurrence?, OR(ISTEXT(_xlpm.start_occurrence), _xlpm.start_occurrence &lt; 1, AND(_xlpm.IncludeEnd?, ISTEXT(_xlpm.end_occurrence)), AND(_xlpm.IncludeEnd?, _xlpm.end_occurrence &lt; _xlpm.start_occurrence)), IF(_xlpm.height_mismatch?, #VALUE!, IF(_xlpm.InvalidOccurrence?, #VALUE!, _xlfn.LET(_xlpm.inst, Instanceλ(_xlpm.crit_vector), _xlpm.bool, IF(_xlpm.IncludeEnd?, (_xlpm.inst &gt;= _xlpm.start_occurrence) * (_xlpm.inst &lt;= _xlpm.end_occurrence), (_xlpm.inst &gt;= _xlpm.start_occurrence)), _xlpm.result, _xlfn._xlws.FILTER(_xlpm.array, _xlpm.bool, 0), _xlpm.final, IF(_xlpm.IsVertical?, _xlpm.result, TRANSPOSE(_xlpm.result)), _xlpm.final)))))</definedName>
+    <definedName name="Occurrenceλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.crit_vector,_xlpm.Nᵀᴴ_occurrence, _xlfn.LET(_xlpm.height, ROWS(_xlpm.array), _xlpm.height_, ROWS(_xlpm.crit_vector), _xlpm.height_mismatch?, _xlpm.height &lt;&gt; _xlpm.height_, _xlpm.InvalidOccurrence?, OR(ISTEXT(_xlpm.Nᵀᴴ_occurrence), _xlpm.Nᵀᴴ_occurrence = 0), IF(_xlpm.height_mismatch?, #VALUE!, IF(_xlpm.InvalidOccurrence?, #VALUE!, _xlfn.LET(_xlpm.Descend?, SIGN(_xlpm.Nᵀᴴ_occurrence) = -1, _xlpm.bool, Instanceλ(_xlpm.crit_vector, , _xlpm.Descend?) = ABS(_xlpm.Nᵀᴴ_occurrence), _xlpm.final, _xlfn._xlws.FILTER(_xlpm.array, _xlpm.bool, 0), _xlpm.final)))))</definedName>
     <definedName name="Padλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.rows_before,_xlop.rows_after,_xlop.cols_before,_xlop.cols_after,_xlop.pad_with, _xlfn.LET(_xlpm.Iλ, _xlfn.LAMBDA(_xlpm.x, INDEX(_xlpm.x, 1, 1)), _xlpm.rows_before, _xlpm.Iλ(_xlpm.rows_before), _xlpm.rows_after, _xlpm.Iλ(IF(_xlfn.ISOMITTED(_xlpm.rows_after), _xlpm.rows_before, _xlpm.rows_after)), _xlpm.cols_before, _xlpm.Iλ(IF(_xlfn.ISOMITTED(_xlpm.cols_before), _xlpm.rows_before, _xlpm.cols_before)), _xlpm.cols_after, _xlpm.Iλ(IF(_xlfn.ISOMITTED(_xlpm.cols_after), _xlpm.rows_before, _xlpm.cols_after)), _xlpm.InvalidIns?, OR(ISTEXT(_xlpm.rows_before), ISTEXT(_xlpm.rows_after), ISTEXT(_xlpm.cols_before), ISTEXT(_xlpm.cols_after)), IF(_xlpm.InvalidIns?, "#TEXT-PAD!", _xlfn.LET(_xlpm.padded_rows, InsulateRowsλ(_xlpm.array, _xlpm.rows_before, _xlpm.rows_after, _xlpm.pad_with), _xlpm.padded_all, InsulateColsλ(_xlpm.padded_rows, _xlpm.cols_before, _xlpm.cols_after, _xlpm.pad_with), _xlpm.padded_all))))</definedName>
     <definedName name="Pairwiseλ">_xlfn.LAMBDA(_xlpm.vector_1,_xlpm.vector_2, _xlfn.LET(_xlpm.v, _xlfn.TOCOL(_xlpm.vector_1), _xlpm.v₂, _xlfn.TOCOL(_xlpm.vector_2), _xlpm.k, COUNTA(_xlpm.v), _xlpm.k₂, COUNTA(_xlpm.v₂), _xlpm.Is2DInput?, OR(AND(ROWS(_xlpm.vector_1) &gt; 1, COLUMNS(_xlpm.vector_1) &gt; 1), AND(ROWS(_xlpm.vector_2) &gt; 1, COLUMNS(_xlpm.vector_2) &gt; 1)), _xlpm.Is2Big?, _xlpm.k * _xlpm.k₂ &gt; 1000000, IF(_xlpm.Is2DInput?, #VALUE!, IF(_xlpm.Is2Big?, #NUM!, _xlfn.LET(_xlpm.x, Echoλ(_xlpm.v, _xlpm.k₂), _xlpm.y, Resizeλ(_xlpm.v₂, _xlpm.k), _xlpm.pairs, _xlfn.HSTACK(_xlpm.x, _xlpm.y), _xlpm.pairs)))))</definedName>
     <definedName name="PermRλ">_xlfn.LAMBDA(_xlpm.items,_xlpm.items_chosen, Enumerateλ(_xlpm.items, _xlpm.items_chosen, 1))</definedName>
@@ -114,6 +118,7 @@
     <definedName name="ValidateDiagλ">_xlfn.LAMBDA(_xlpm.array,_xlop.col_index,_xlop.function,_xlop.row_wise_stack?,_xlop.on_valid, _xlfn.LET(_xlpm.IsArray?, TYPE(_xlpm.array) = 64, _xlpm.Not_Array, NOT(_xlpm.IsArray?), _xlpm.No_Col_Index, _xlfn.ISOMITTED(_xlpm.col_index), _xlpm.ColIndex_Included, NOT(_xlpm.No_Col_Index), _xlpm.Not_Valid_ColIndex?, NOT(AND(_xlpm.col_index &lt;&gt; 0, ABS(_xlpm.col_index) &lt;= COLUMNS(_xlpm.array))), _xlpm.No_Function, _xlfn.ISOMITTED(_xlpm.function), _xlpm.Function_Included, NOT(_xlpm.No_Function), _xlpm.Invalid_Function?, AND(_xlpm.Function_Included, ISERROR(_xlfn.BYROW({1,1}, _xlpm.function))), _xlpm.RowWiseStack?, NOT(_xlfn.ISOMITTED(_xlpm.row_wise_stack?)), _xlpm.IsDiagIndex?, _xlpm.ColIndex_Included, _xlpm.IsByDiag?, AND(_xlpm.No_Col_Index, _xlpm.Function_Included), _xlpm.IsDiagMap?, AND(_xlpm.No_Col_Index, _xlpm.No_Function), _xlpm.gate_DiagIndex, IF(_xlpm.Not_Array, "#NOT-ARRAY!", IF(_xlpm.Not_Valid_ColIndex?, "#COLUMN-INDEX!", _xlpm.on_valid)), _xlpm.gate_ByDiag, IF(_xlpm.Not_Array, "#NOT-ARRAY!", IF(_xlpm.Invalid_Function?, "#FUNCTION!", _xlpm.on_valid)), _xlpm.gate_DiagMap, IF(_xlpm.Not_Array, "#NOT-ARRAY!", _xlpm.on_valid), _xlpm.decide, IF(_xlpm.IsDiagIndex?, _xlpm.gate_DiagIndex, IF(_xlpm.IsDiagMap?, _xlpm.gate_DiagMap, IF(_xlpm.IsByDiag?, _xlpm.gate_ByDiag, "#UNROUTED!"))), _xlpm.decide))</definedName>
     <definedName name="ValidateGDλ">_xlfn.LAMBDA(_xlpm.row_fields,_xlpm.values,_xlpm.interval,_xlpm.function,_xlop.field_headers,_xlop.filter_array,_xlop.On_Valid, _xlfn.LET(_xlpm.No_Field_Headers?, _xlfn.ISOMITTED(_xlpm.field_headers), _xlpm.FilterIncluded?, NOT(_xlfn.ISOMITTED(_xlpm.filter_array)), _xlpm.Date_col, IF(_xlpm.No_Field_Headers?, _xlfn.TAKE(_xlpm.row_fields, , 1), _xlfn.DROP(_xlfn.TAKE(_xlpm.row_fields, , 1), 1)), _xlpm.Values_col, IF(_xlpm.No_Field_Headers?, _xlfn.TAKE(_xlpm.values, , 1), _xlfn.DROP(_xlfn.TAKE(_xlpm.values, , 1), 1)), _xlpm.Bool, IFERROR(IF(_xlpm.No_Field_Headers?, _xlpm.filter_array, _xlfn.DROP(_xlpm.filter_array, 1)), 0), _xlpm.No_Dates?, OR(_xlpm.Date_col &lt; 0, _xlpm.Date_col &gt; 2958465, NOT(AND(ISNUMBER(_xlpm.Date_col)))), _xlpm.No_Times?, AND(_xlpm.Date_col - INT(_xlpm.Date_col) = 0), _xlpm.i_d, ROWS(_xlpm.Date_col), _xlpm.i_v, ROWS(_xlpm.Values_col), _xlpm.i_f, IF(_xlpm.FilterIncluded?, ROWS(_xlpm.Bool), 0), _xlpm.Const, {"minute";"hour";"day";"week";"fortnight";"month";"quarter";"year"}, _xlpm.TextInterval?, ISTEXT(_xlpm.interval), _xlpm.NumericInterval?, ISNUMBER(_xlpm.interval), _xlpm.InvalidInterval?, IF(AND(_xlpm.NumericInterval?, OR(_xlpm.interval &lt; 1, _xlpm.interval &gt; 8)), TRUE, IF(AND(_xlpm.TextInterval?, ISNA(_xlfn.XMATCH(_xlpm.interval &amp; "*", _xlpm.Const, 2))), TRUE, FALSE)), _xlpm.IsTime?, _xlpm.interval &lt; 3, _xlpm.EmptyInputs?, OR(_xlfn.ISOMITTED(_xlpm.row_fields), _xlfn.ISOMITTED(_xlpm.values)), _xlpm.HaltDates?, AND(_xlpm.interval &gt; 2, _xlpm.No_Dates?), _xlpm.HaltTime?, AND(_xlpm.IsTime?, _xlpm.No_Times?), _xlpm.ShapeMismatch?, OR(_xlpm.i_d &lt;&gt; _xlpm.i_v, AND(_xlpm.FilterIncluded?, _xlpm.i_d &lt;&gt; _xlpm.i_f)), _xlpm.InvalidFn?, TYPE(_xlpm.function) &lt;&gt; 128, _xlpm.EmptyFilter?, AND(_xlpm.FilterIncluded?, NOT(OR(_xlpm.Bool))), _xlpm.conditions, _xlfn.VSTACK(_xlpm.EmptyInputs?, _xlpm.HaltDates?, _xlpm.HaltTime?, _xlpm.ShapeMismatch?, _xlpm.InvalidInterval?, _xlpm.InvalidFn?, _xlpm.EmptyFilter?), _xlpm.halt, OR(_xlpm.conditions), _xlpm.errors, {"#EMPTY-INPUT!";"#NO-DATES!";"#NO-TIMES!";"#DIMENSIONS!";"#INTERVAL!";"#INVALID-FUNCTION!";"#EMPTY-FILTER!"}, _xlpm.alert, _xlfn._xlws.FILTER(_xlpm.errors, _xlpm.conditions, ""), IF(_xlpm.halt, _xlpm.alert, _xlpm.On_Valid)))</definedName>
     <definedName name="ValidateStaircaseλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.block_size,_xlop.block_offset,_xlop.on_valid, _xlfn.LET(_xlpm.NotArray?, TYPE(_xlpm.array) &lt;&gt; 64, _xlpm.InvalidBlockSize?, OR(ISTEXT(_xlpm.block_size), _xlpm.block_size &lt;= 0, _xlpm.block_size &gt; COUNTA(_xlpm.array)), _xlpm.InvalidBlockOffset?, OR(ISTEXT(_xlpm.block_offset), _xlpm.block_offset &lt; 0), IF(_xlpm.NotArray?, "#NOT-ARRAY!", IF(_xlpm.InvalidBlockSize?, "#BLOCK-SIZE!", IF(_xlpm.InvalidBlockOffset?, "#BLOCK-OFFSET!", _xlpm.on_valid)))))</definedName>
+    <definedName name="Waveλ">_xlfn.LAMBDA(_xlpm.crest,_xlop.rep_count, _xlfn.LET(_xlpm.Standard?, _xlfn.ISOMITTED(_xlpm.rep_count), _xlpm.rep_count, IF(_xlpm.Standard?, 1, INDEX(_xlpm.rep_count, 1, 1)), _xlpm.crest, INDEX(_xlpm.crest, 1, 1), _xlpm.InvalidN?, OR(ISTEXT(_xlpm.crest), _xlpm.crest &lt; 0), _xlpm.SpillRisk?, _xlpm.rep_count * (_xlpm.crest * 2 - 1) &gt; 1048576, IF(_xlpm.InvalidN?, #VALUE!, IF(_xlpm.SpillRisk?, #NUM!, _xlfn.LET(_xlpm.k, _xlpm.crest * 2 - 1, _xlpm.seq, _xlfn.SEQUENCE(_xlpm.k), _xlpm.m, MAX(_xlpm.seq), _xlpm.w, IF(_xlpm.seq &gt; _xlpm.crest, _xlpm.m - _xlpm.seq + 1, _xlpm.seq), _xlpm.final, IF(_xlpm.Standard?, _xlpm.w, Echoλ(_xlpm.w, _xlpm.rep_count)), _xlpm.final)))))</definedName>
     <definedName name="WrapCols2Dλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.new_width,_xlop.pad_with, _xlfn.LET(_xlpm.h, ROWS(_xlpm.array), _xlpm.w, COLUMNS(_xlpm.array), _xlpm.blocks, CEILING(_xlpm.w / _xlpm.new_width, 1), _xlpm.pad_with, IF(_xlfn.ISOMITTED(_xlpm.pad_with), NA(), _xlpm.pad_with), _xlpm.r, _xlpm.blocks * _xlpm.h, _xlpm.Is1D?, OR(_xlpm.h = 1, _xlpm.w = 1), _xlpm.IsScalar?, AND(_xlpm.h = 1, _xlpm.w = 1), _xlpm.InvalidDim?, _xlpm.new_width &gt;= _xlpm.w, _xlpm.SpillRisk?, _xlpm.r &gt; 1048576, IF(_xlpm.IsScalar?, "#VALUE!", IF(_xlpm.Is1D?, "#VALUE!", IF(_xlpm.InvalidDim?, "#WIDTH!", IF(_xlpm.SpillRisk?, "#NUM!", _xlfn.LET(_xlpm.modulo, _xlfn.LAMBDA(MOD(_xlfn.SEQUENCE(_xlpm.r), _xlpm.h)), _xlpm.i, _xlfn.LAMBDA(IF(_xlpm.modulo() = 0, _xlpm.h, _xlpm.modulo()) * _xlfn.SEQUENCE(, _xlpm.new_width, 1, 0)), _xlpm.j, _xlfn.LAMBDA(Echoλ(_xlfn.SEQUENCE(_xlpm.r / _xlpm.h, , 1, _xlpm.new_width), _xlpm.h) + _xlfn.SEQUENCE(, _xlpm.new_width, 0, 1)), _xlpm.result, IFERROR(INDEX(_xlpm.array, _xlpm.i(), _xlpm.j()), _xlpm.pad_with), _xlpm.result)))))))</definedName>
     <definedName name="WrapRows2Dλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.new_height,_xlop.pad_with, _xlfn.LET(_xlpm.h, ROWS(_xlpm.array), _xlpm.w, COLUMNS(_xlpm.array), _xlpm.blocks, CEILING(_xlpm.h / _xlpm.new_height, 1), _xlpm.pad_with, IF(_xlfn.ISOMITTED(_xlpm.pad_with), NA(), _xlpm.pad_with), _xlpm.c, _xlpm.blocks * _xlpm.w, _xlpm.Is1D?, OR(_xlpm.h = 1, _xlpm.w = 1), _xlpm.IsScalar?, AND(_xlpm.h = 1, _xlpm.w = 1), _xlpm.InvalidDim?, _xlpm.new_height &gt;= _xlpm.h, _xlpm.SpillRisk?, _xlpm.c &gt; 16384, IF(_xlpm.IsScalar?, "#VALUE!", IF(_xlpm.Is1D?, "#VALUE!", IF(_xlpm.InvalidDim?, "#HEIGHT!", IF(_xlpm.SpillRisk?, "#NUM!", _xlfn.LET(_xlpm.i, _xlfn.LAMBDA(_xlfn.TOROW(Echoλ(_xlfn.SEQUENCE(, _xlpm.blocks, 1, _xlpm.new_height), _xlpm.w)) + _xlfn.SEQUENCE(_xlpm.new_height, , 0, 1)), _xlpm.modulo, _xlfn.LAMBDA(MOD(_xlfn.SEQUENCE(, _xlpm.w * _xlpm.blocks), _xlpm.w)), _xlpm.j, _xlfn.LAMBDA(IF(_xlpm.modulo() = 0, _xlpm.w, _xlpm.modulo()) * _xlfn.SEQUENCE(_xlpm.new_height, , 1, 0)), _xlpm.result, IFERROR(INDEX(_xlpm.array, _xlpm.i(), _xlpm.j()), _xlpm.pad_with), _xlpm.result)))))))</definedName>
     <definedName name="Zipλ">_xlfn.LAMBDA(_xlpm.array_1,_xlop.array_2,_xlop.array_3,_xlop.array_4,_xlop.zip_longest,_xlop.fill_value, _xlfn.LET(_xlpm.ZipLong?, IF(_xlfn.ISOMITTED(_xlpm.zip_longest), FALSE, _xlpm.zip_longest), _xlpm.fnλ, IF(_xlpm.ZipLong?, _xleta.MAX, _xleta.MIN), _xlpm.fill_value, IF(_xlpm.ZipLong?, IF(_xlfn.ISOMITTED(_xlpm.fill_value), NA(), _xlpm.fill_value), NA()), _xlpm.Two, NOT(_xlfn.ISOMITTED(_xlpm.array_2)), _xlpm.Three, NOT(_xlfn.ISOMITTED(_xlpm.array_3)), _xlpm.Four, NOT(_xlfn.ISOMITTED(_xlpm.array_4)), _xlpm.m, IF(_xlpm.Four, 4, IF(_xlpm.Three, 3, IF(_xlpm.Two, 2, 1))), _xlpm.array_1, _xlfn.TOCOL(_xlpm.array_1), _xlpm.array_2, IF(_xlpm.m &gt;= 2, _xlfn.TOCOL(_xlpm.array_2), FALSE), _xlpm.array_3, IF(_xlpm.m &gt;= 3, _xlfn.TOCOL(_xlpm.array_3), FALSE), _xlpm.array_4, IF(_xlpm.m = 4, _xlfn.TOCOL(_xlpm.array_4), FALSE), _xlpm.k₁, ROWS(_xlpm.array_1), _xlpm.k₂, ROWS(_xlpm.array_2), _xlpm.k₃, ROWS(_xlpm.array_3), _xlpm.k₄, ROWS(_xlpm.array_4), _xlpm.LZ, CHOOSE(_xlpm.m, _xlpm.k₁, _xlpm.fnλ(_xlpm.k₁, _xlpm.k₂), _xlpm.fnλ(_xlpm.k₁, _xlpm.k₂, _xlpm.k₃), _xlpm.fnλ(_xlpm.k₁, _xlpm.k₂, _xlpm.k₃, _xlpm.k₄)), _xlpm.Normalizeλ, _xlfn.LAMBDA(_xlpm.array, IF(_xlpm.ZipLong?, _xlfn.EXPAND(_xlpm.array, _xlpm.LZ, , _xlpm.fill_value), _xlfn.TAKE(_xlpm.array, _xlpm.LZ))), _xlpm.a, _xlpm.Normalizeλ(_xlpm.array_1), _xlpm.b, _xlpm.Normalizeλ(_xlpm.array_2), _xlpm.c, _xlpm.Normalizeλ(_xlpm.array_3), _xlpm.d, _xlpm.Normalizeλ(_xlpm.array_4), _xlpm.zipped, CHOOSE(_xlpm.m, _xlpm.a, _xlfn.HSTACK(_xlpm.a, _xlpm.b), _xlfn.HSTACK(_xlpm.a, _xlpm.b, _xlpm.c), _xlfn.HSTACK(_xlpm.a, _xlpm.b, _xlpm.c, _xlpm.d)), _xlpm.zipped))</definedName>
@@ -12517,7 +12522,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuACAAIABfAF8AXwBfACAAIABfACAAIAAgACAAIAAgACAAIABfAF8AXwBfAF8AIAAgACAAIAAgACAAIABfACAAXwAgAF8AIABcAG4AIAB8ACAAIABfACAAXABcACgAXwApACAAIAAgACAAIAAgAC8AIABfAF8AXwBfAHwAIAAgACAAIAAgACgAXwApACAAfAAgAHwAXABuACAAfAAgAHwAXwApACAAfABfACAAIABfAF8AIABfAHwAIAAoAF8AXwBfACAAIABfACAAXwBfACAAIABfAHwAIAB8ACAAfABcAG4AIAB8ACAAIABfACAAPAB8ACAAfAAvACAAXwBgACAAfABcAFwAXwBfAF8AIABcAFwAfAAgACcAXwAgAFwAXAB8ACAAfAAgAHwAIAB8AFwAbgAgAHwAIAB8AF8AKQAgAHwAIAB8ACAAKABfAHwAIAB8AF8AXwBfAF8AKQAgAHwAIAB8AF8AKQAgAHwAIAB8ACAAfAAgAHwAXABuACAAfABfAF8AXwBfAC8AfABfAHwAXABcAF8AXwAsACAAfABfAF8AXwBfAF8ALwB8ACAALgBfAF8ALwB8AF8AfABfAHwAXwB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXwBfAC8AIAB8ACAAIAAgACAAIAAgAHwAIAB8ACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAfABfAF8AXwAvACAAIAAgACAAIAAgACAAfABfAHwAIAAgACAAIAAgACAAIAAgACAAIABcAG4AXABuAFwAbgBNAG8AZAB1AGwAZQA6ACAAIABCAGkAZwBTAHAAaQBsAGwAXABuAFIAZQBwAG8AOgAgACAAIAAgAGgAdAB0AHAAcwA6AC8ALwBnAGkAdABoAHUAYgAuAGMAbwBtAC8AUABhAHQAcgBpAGMAawAyADcAOAA4AC8AQgBpAGcAUwBwAGkAbABsAC0ARQB4AGMAZQBsAC0ATABhAG0AYgBkAGEALQBMAGkAYgByAGEAcgB5AFwAbgBMAGkAYwBlAG4AcwBlADoAIABNAEkAVAAgACgAcwBlAGUAIABMAEkAQwBFAE4AUwBFACAAZgBpAGwAZQApAFwAbgBBAHUAdABoAG8AcgA6ACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBEAGEAdABlADoAIAAgACAAIAA5AC8AMwAvADIAMAAyADYAXABuAFwAbgBWAGUAcgBzAGkAbwBuACAAaABpAHMAdABvAHIAeQA6AFwAbgAgACAAIAAgADcALwA2AC8AMgAwADIANgAgABMgIABJAG4AaQB0AGkAYQBsACAAcgBlAGwAZQBhAHMAZQBcAG4AIAAgACAAIAA5AC8AMwAvADIAMAAyADYAIAATICAAQQBkAGQAZQBkACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AyAAYQBuAGQAIABRAHUAYQBkAHcAaQBzAGUAuwMgAHQAbwAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBwAGQAYQB0AGUAZAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgAGMAYQB0AGUAZwBvAHIAeQAgAGIAbABvAGMAawBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBwAGQAYQB0AGUAZAAgAFQAZQBzAHMAZQBsAGwAYQB0AGUAuwMgAHQAbwAgAGEAYwBjAGUAcAB0ACAAMQBEACAAYQByAHIAYQB5AHMAXABuAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6AFwAbgAgACAAIAAgAE4AbwBuAGUAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AcgBlACAAbQBvAGQAdQBsAGUAIABhAGcAZwByAGUAZwBhAHQAbwByACAAZgBvAHIAIABhAGwAbAAgAEIAaQBnAFMAcABpAGwAbAAgAGYAdQBuAGMAdABpAG8AbgBzAC4AXABuAFwAbgBQAHUAcgBwAG8AcwBlADoAXABuACAAIAAgACAAUAByAG8AdgBpAGQAZQBzACAAYQAgAHMAaQBuAGcAbABlACAAaQBtAHAAbwByAHQAIABwAG8AaQBuAHQAIABmAG8AcgAgAHQAaABlACAAZQBuAHQAaQByAGUAIABsAGkAYgByAGEAcgB5AC4AXABuAFwAbgBDAG8AbgB0AGUAbgB0AHMAOgBcAG4AIAAgACAAIABHAHIAaQBkAHcAbwByAGsALAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkALAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcALAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACwAXABuACAAIAAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgAsACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACwAIABUAGUAeAB0ACwAIABFAG4AZwBpAG4AZQBlAHIAaQBuAGcALABcAG4AIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzACwAIABEAGkAYQBnAG4AbwBzAHQAaQBjAHMAXABuAFwAbgBcAG4AXABuAFwAbgAtAC0ALQBUAGEAYgBsAGUAIABvAGYAIABDAG8AbgB0AGUAbgB0AHMALQAtAC0AXABuAFwAbgAjACMAIAAwADEAIAAtACAAWwBHAFcAXQAgAEcAcgBpAGQAdwBvAHIAawBcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBXADAAMQBdACAAIABEAEcAcgBpAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFcAMAAyAF0AIAAgAEMARwByAGkAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAVwAwADMAXQAgACAATQBHAHIAaQBkALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBXADAANABdACAAIABUAEcAcgBpAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFcAMAA1AF0AIAAgAFAAbwBsAGEAcgBHAHIAaQBkALsDXABuAFwAbgAjACMAIAAwADIAIAAtACAAWwBHAEcAXQAgACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQBcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBHADAAMQBdACAAIABDAGkAcgBjAGwAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARwAwADIAXQAgACAARABpAGEAbQBvAG4AZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARwAwADMAXQAgACAAUABsAHUAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARwAwADQAXQAgACAAUAB5AHIAYQBtAGkAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARwAwADUAXQAgACAAUgBpAG4AZwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARwAwADYAXQAgACAAUwBxAHUAYQByAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA3AF0AIAAgAFQAcgBpAGEAbgBnAGwAZQC7A1wAbgBcAG4AIwAjACAAMAAzACAALQAgAFsAUwBBAF0AIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAG8AcgBlACAAUwBoAGEAcABpAG4AZwAgAFAAcgBpAG0AaQB0AGkAdgBlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAAMQBdAFwAdABSAGUAUwBoAGEAcABlADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADIAXQBcAHQAUgBlAFMAaQB6AGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMAAzAF0AXAB0AFMAYwBhAG4AMgBEALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAANABdAFwAdABUAHIAYQB2AGUAcgBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMAA1AF0AXAB0AFQAYQBrAGUAQgBsAG8AYwBrALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAANgBdAFwAdABEAFMAdABhAGMAawC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAGYAbABvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAANwBdAFwAdABXAHIAYQBwAFIAbwB3AHMAMgBEALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAAOABdAFwAdABXAHIAYQBwAEMAbwBsAHMAMgBEALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAAOQBdAFwAdABTAHQAYQBpAHIAYwBhAHMAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAxADAAXQBcAHQAVQBuAFAAaQB2AG8AdAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAxADEAXQBcAHQAWgBpAHAAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQAzAF0AXAB0AFMAbABpAGMAZQBCAHkARABlAGcAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADEANABdAFwAdABQAGEAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAxADUAXQBcAHQASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA2AF0AXAB0AEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAG4AdABlAHIAcABvAGwAYQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAxADcAXQBcAHQATQBhAGcAbgBpAGYAeQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAxADgAXQBcAHQAWgBvAG8AbQC7A1wAbgBcAG4AIwAjACAAMAA0ACAALQAgAFsARwBBAF0AIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABlAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAAMQBdAFwAdABEAGUAbABlAHQAZQBSAG8AdwBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAAMgBdAFwAdABEAGUAbABlAHQAZQBDAG8AbABzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAAMwBdAFwAdABEAGUAbABlAHQAZQBXAGgAZQByAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMAA0AF0AXAB0AFAAaQBuAGMAaAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADUAXQBcAHQAUgBlAG0AbwB2AGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMAA2AF0AXAB0AFMAcQB1AGUAZQB6AGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAeABwAGEAbgBzAGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADcAXQBcAHQASwByAG8AbgBlAGMAawBlAHIAUAByAG8AZAC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBpAGwAdABlAHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAAOABdAFwAdABFAHgAYwBsAHUAZABlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAAOQBdAFwAdABTAG4AYQBwALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAG8AbABsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADAAXQBcAHQAUwBoAGkAZgB0ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEAMQBdAFwAdABTAGgAaQBmAHQAUgBvAHcAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADIAXQBcAHQAUwBoAGkAZgB0AEMAbwBsAHMAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADMAXQBcAHQARQBtAGIAZQBkALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEANABdAFwAdABLAGUAZQBwAFIAbwB3AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQA1AF0AXAB0AEsAZQBlAHAAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AHIAdQBjAHQAdQByAGEAbAAgAE0AYQBwAHAAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEANgBdAFwAdABCAGwAbwBjAGsATQBhAHAAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQA3AF0AXAB0AEMAbwBuAHYAbwBsAHYAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADgAXQBcAHQARgBvAGwAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADkAXQBcAHQASgBvAGkAbgAyAEQAuwNcAG4AXABuACMAIwAgADAANQAgAC0AIABbAFIAUABdACAAIABSAGUAcABlAHQAaQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFIAUAAwADEAXQBcAHQARQBjAGgAbwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFIAUAAwADIAXQBcAHQAUgBlAHAAZQBhAHQAUgBvAHcAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFIAUAAwADMAXQBcAHQAUgBlAHAAZQBhAHQAQwBvAGwAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFIAUAAwADQAXQBcAHQAVABlAHMAcwBlAGwAbABhAHQAZQC7A1wAbgBcAG4AIwAjACAAMAA2ACAALQAgAFsARwBSAF0AIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBlAHEAdQBlAG4AYwBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAAxAF0AXAB0AFMAdAByAGUAYQBrALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADAAMgBdAFwAdABDAG8AdQBuAHQAZABvAHcAbgC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADMAXQBcAHQAQgB5AEQAaQBhAGcAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA0AF0AXAB0AEQAaQBhAGcATQBhAHAAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA1AF0AXAB0AEQAaQBhAGcASQBuAGQAZQB4ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADAANgBdAFwAdABQAGEAaQByAHcAaQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA2AGEAXQBcAHQAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBcAHQAIAAgACAAIAAgACAAIAAgAFsARwBSADAANgBiAF0AIABRAHUAYQBkAHcAaQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA3AF0AXAB0AEcAcgBvAHUAcABiAHkAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA4AF0AXAB0AEcAcgBvAHUAcABiAHkARABhAHQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADkAXQBcAHQAUABpAHYAbwB0AGIAeQBDAGEAdAC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQAwAF0AXAB0AEcAcgBhAGkAbgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADEAXQBcAHQATQBvAG8AcgBlAEEAZwBnALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADEAMgBdAFwAdABNAG8AbwByAGUAUwBlAGwAZQBjAHQAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdABhAHQAaQBzAHQAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADEAMwBdAFwAdABIAGkAcwB0AG8AZwByAGEAbQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADQAXQBcAHQATQBvAGQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADUAXQBcAHQAWgBvAG4AZQBTAHQAYQB0ALsDXABuAFwAbgAjACMAIAAwADcAIAAtACAAWwBUAFgAXQAgACAAVABlAHgAdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAAxAF0AXAB0AEEAbABpAGcAbgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADIAXQBcAHQAQQBsAGkAZwBuAEQAaQBzAHQAaQBuAGMAdAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADMAXQBcAHQAQQBsAGkAZwBuAFUAbgBpAHEAdQBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAANABdAFwAdABDAG8AYQBsAGUAcwBjAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAA1AF0AXAB0AEUAeABwAGwAbwBkAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAA2AF0AXAB0AE4AdQBtAGIAZQByAHMATwBuAGwAeQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADcAXQBcAHQAVABlAHgAdABPAG4AbAB5ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAAOABdAFwAdABTAHAAbABpAHQAuwNcAG4AXABuACMAIwAgADAAOAAgAC0AIABbAEUATgBdACAAIABFAG4AZwBpAG4AZQBlAHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARQBOADAAMQBdAFwAdABCAGkAbgAyAEQAZQBjALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARQBOADAAMgBdAFwAdABCAGkAbgAyAEcAcgBhAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBFAE4AMAAzAF0AXAB0AEIAaQB0AEMAbwB1AG4AdAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEUATgAwADQAXQBcAHQARABlAGMAMgBCAGkAbgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEUATgAwADUAXQBcAHQARABlAGMAMgBHAHIAYQB5ALsDXABuAFwAbgAjACMAIAAwADkAIAAtACAAWwBDAEIAXQAgACAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAAxAF0AXAB0AFAAZQByAG0AUgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADIAXQBcAHQAUABlAHIAbQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADMAXQBcAHQAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAUgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADQAXQBcAHQAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAA1AF0AXAB0AEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAANgBdAFwAdABLAG4AYQBwAFMAYQBjAGsAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAA3AF0AXAB0AFMAdQBiAHMAZQB0AEcAZQBuALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAAOABdAFwAdABTAHUAYgBzAGUAdABTAHUAbQC7A1wAbgBcAG4AIwAjACAAMQAwACAALQAgAFsARwBEAF0AIAAgAEcAcgBpAGQAIABEAGkAYQBnAG4AbwBzAHQAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBEADAAMQBdACAAIABSAGUAdgBlAGEAbAC7A1wAbgBcAG4AXABuAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8ALwAgAFsARwBXAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAC8ALwAgAC0ALQAtACMAIwAgADAAMQAgAC0AIABHAHIAaQBkAHcAbwByAGsAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwByAGkAZAB3AG8AcgBrACAAZABlAGYAaQBuAGUAcwAgAHQAaABlACAAZgBvAHUAbgBkAGEAdABpAG8AbgBhAGwAIABjAG8AbwByAGQAaQBuAGEAdABlACAAcwB5AHMAdABlAG0AcwAgAGYAbwByACAAMgBEACAAYQByAHIAYQB5AHMALgAgAEUAYQBjAGgAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACAAcAByAG8AZAB1AGMAZQBzACAAYQAgAGMAZQBuAHQAZQByAGUAZAAsACAAcwB5AG0AbQBlAHQAcgBpAGMAYQBsACAAZwBlAG8AbQBlAHQAcgBpAGMAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGcAcgBpAGQALgBcAG4AXABuAEYAdQBuAGMAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAEQARwByAGkAZAC7AyAAIAAgACAAIAAgAC0AIABEAGkAcgBlAGMAdABpAG8AbgAgAGcAcgBpAGQAIAAoADAAsAAtADMANgAwALAAKQAgAHUAcwBpAG4AZwAgAGMAZQBuAHQAZQByAGUAZAAgAEMAYQByAHQAZQBzAGkAYQBuACAAYQB4AGUAcwBcAG4AXABuACAAIAAgACAAIiAgAEMARwByAGkAZAC7AyAAIAAgACAAIAAgAC0AIABDAGEAcgB0AGUAcwBpAGEAbgAgAGcAcgBpAGQAIAAoAHIAbwB3ACAAbwByACAAYwBvAGwAdQBtAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMALAAgAGMAZQBuAHQAZQByAGUAZAApAFwAbgBcAG4AIAAgACAAIAAiICAATQBHAHIAaQBkALsDIAAgACAAIAAgACAALQAgAE0AZQBzAGgAIABnAHIAaQBkACAAKAAxABEgYgBhAHMAZQBkACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAKQBcAG4AXABuACAAIAAgACAAIiAgAFQARwByAGkAZAC7AyAAIAAgACAAIAAgAC0AIABUAGgAcgBlAHMAaABvAGwAZABlAGQAIABtAGUAcwBoACAAZwByAGkAZAAgACgAaQBuAGQAaQBjAGUAcwAgAHcAcgBhAHAAIABhAGYAdABlAHIAIABhACAAbABpAG0AaQB0ACkAXABuAFwAbgAgACAAIAAgACIgIABQAG8AbABhAHIARwByAGkAZAC7AyAAIAAtACAAUABvAGwAYQByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgAgACAAIAATICAAcgBhAGQAaQBhAGwAIABkAGkAcwB0AGEAbgBjAGUAIABmAHIAbwBtACAAZwByAGkAZAAgAGMAZQBuAHQAZQByAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAaABpACAAEyAgAGEAbgBnAGwAZQAgAGkAbgAgAHIAYQBkAGkAYQBuAHMAIAB1AHMAaQBuAGcAIABBAFQAQQBOADIAKAB5ACwAIAB4ACkAXABuAFwAbgAgACAAIAAgACIgIABSAGUAcwBpAHoAZQC7AyAAIAAgACAAIAAtACAAVQB0AGkAbABpAHQAeQAgAGYAbwByACAAYgByAG8AYQBkAGMAYQBzAHQAaQBuAGcAIABjAG8AbwByAGQAaQBuAGEAdABlACAAdgBlAGMAdABvAHIAcwAgAHQAbwAgAGcAcgBpAGQAIABzAGgAYQBwAGUAXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIABBAGwAbAAgAGYAdQBuAGMAdABpAG8AbgBzACAAYQByAGUAIABzAGgAYQBwAGUALQBkAHIAaQB2AGUAbgA6ACAAdABoAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAbwBmACAAdABoAGUAIABzAHUAcABwAGwAaQBlAGQAIABnAHIAaQBkACAAZABlAHQAZQByAG0AaQBuAGUAXABuACAAIAAgACAAdABoAGUAIABjAG8AbwByAGQAaQBuAGEAdABlACAAZQB4AHQAZQBuAHQAcwAuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQBzADoAXABuACAAIAAgACAARwByAGkAZAA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgACAAIAAyACAAIAAgADMAIAAgACAANAAgACAAIAA1AFwAbgAgACAAIAAgACAAIAAgACAANgAgACAAIAA3ACAAIAAgADgAIAAgACAAOQAgACAAIAAxADAAXABuACAAIAAgACAAIAAgACAAIAAxADEAIAAgADEAMgAgACAAMQAzACAAIAAxADQAIAAgADEANQBcAG4AIAAgACAAIAAgACAAIAAgADEANgAgACAAMQA3ACAAIAAxADgAIAAgADEAOQAgACAAMgAwAFwAbgAgACAAIAAgACAAIAAgACAAMgAxACAAIAAyADIAIAAgADIAMwAgACAAMgA0ACAAIAAyADUAXABuAFwAbgAgACAAIAAgAEQARwByAGkAZAC7AygAZwByAGkAZAApADoAXABuACAAIAAgACAAIAAgACAAIAAyADIANQAuADAAMAAgADIAMAA2AC4ANQA3ACAAMQA4ADAALgAwADAAIAAxADUAMwAuADQAMwAgADEAMwA1AC4AMAAwAFwAbgAgACAAIAAgACAAIAAgACAAMgA0ADMALgA0ADMAIAAyADIANQAuADAAMAAgADEAOAAwAC4AMAAwACAAMQAzADUALgAwADAAIAAxADEANgAuADUANwBcAG4AIAAgACAAIAAgACAAIAAgADIANwAwAC4AMAAwACAAMgA3ADAALgAwADAAIAAgACAAMAAuADAAMAAgACAAOQAwAC4AMAAwACAAIAA5ADAALgAwADAAXABuACAAIAAgACAAIAAgACAAIAAyADkANgAuADUANwAgADMAMQA1AC4AMAAwACAAIAAgADAALgAwADAAIAAgADQANQAuADAAMAAgACAANgAzAC4ANAAzAFwAbgAgACAAIAAgACAAIAAgACAAMwAxADUALgAwADAAIAAzADMAMwAuADQAMwAgACAAIAAwAC4AMAAwACAAIAAyADYALgA1ADcAIAAgADQANQAuADAAMABcAG4AXABuACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACkAIAAtACAAcgBvAHcAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgAC0AMgAgAC0AMgAgAC0AMgAgAC0AMgAgAC0AMgBcAG4AIAAgACAAIAAgACAAIAAgAC0AMQAgAC0AMQAgAC0AMQAgAC0AMQAgAC0AMQBcAG4AIAAgACAAIAAgACAAIAAgACAAMAAgACAAMAAgACAAMAAgACAAMAAgACAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAMQAgACAAMQAgACAAMQAgACAAMQAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACAAMgAgACAAMgAgACAAMgAgACAAMgAgACAAMgBcAG4AXABuACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAMQApACAALQAgAGMAbwBsAHUAbQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAtADIAIAAtADEAIAAgADAAIAAgADEAIAAgADIAXABuACAAIAAgACAAIAAgACAAIAAtADIAIAAtADEAIAAgADAAIAAgADEAIAAgADIAXABuACAAIAAgACAAIAAgACAAIAAtADIAIAAtADEAIAAgADAAIAAgADEAIAAgADIAXABuACAAIAAgACAAIAAgACAAIAAtADIAIAAtADEAIAAgADAAIAAgADEAIAAgADIAXABuACAAIAAgACAAIAAgACAAIAAtADIAIAAtADEAIAAgADAAIAAgADEAIAAgADIAXABuAFwAbgAgACAAIAAgAE0ARwByAGkAZAC7AygAZwByAGkAZAApACAALQAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADEAIAAxACAAMQAgADEAXABuACAAIAAgACAAIAAgACAAIAAyACAAMgAgADIAIAAyACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADMAIAAzACAAMwAgADMAIAAzAFwAbgAgACAAIAAgACAAIAAgACAANAAgADQAIAA0ACAANAAgADQAXABuACAAIAAgACAAIAAgACAAIAA1ACAANQAgADUAIAA1ACAANQBcAG4AXABuACAAIAAgACAATQBHAHIAaQBkALsDKABnAHIAaQBkACwAMQApACAALQAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAANAAgADUAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAA0ACAANQBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADQAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAANAAgADUAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAA0ACAANQBcAG4AXABuACAAIAAgACAAVABHAHIAaQBkALsDKABnAHIAaQBkACwAMwApACAALQAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAsACAAdABoAHIAZQBzAGgAbwBsAGQAIAAzADoAXABuACAAIAAgACAAIAAgACAAIAAxACAAMQAgADEAIAAxACAAMQBcAG4AIAAgACAAIAAgACAAIAAgADIAIAAyACAAMgAgADIAIAAyAFwAbgAgACAAIAAgACAAIAAgACAAMwAgADMAIAAzACAAMwAgADMAXABuACAAIAAgACAAIAAgACAAIAAxACAAMQAgADEAIAAxACAAMQBcAG4AIAAgACAAIAAgACAAIAAgADIAIAAyACAAMgAgADIAIAAyAFwAbgBcAG4AIAAgACAAIABUAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAzACwAMQApACAALQAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAsACAAdABoAHIAZQBzAGgAbwBsAGQAIAAzADoAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAAxACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADEAIAAyAFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAAMQAgADIAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAAxACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADEAIAAyAFwAbgBcAG4AIAAgACAAIABQAG8AbABhAHIARwByAGkAZAC7AygAZwByAGkAZAApACAALQAgAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgADIALgA4ADMAIAAyAC4AMgA0ACAAMgAuADAAMAAgADIALgAyADQAIAAyAC4AOAAzAFwAbgAgACAAIAAgACAAIAAgACAAMgAuADIANAAgADEALgA0ADEAIAAxAC4AMAAwACAAMQAuADQAMQAgADIALgAyADQAXABuACAAIAAgACAAIAAgACAAIAAyAC4AMAAwACAAMQAuADAAMAAgADAALgAwADAAIAAxAC4AMAAwACAAMgAuADAAMABcAG4AIAAgACAAIAAgACAAIAAgADIALgAyADQAIAAxAC4ANAAxACAAMQAuADAAMAAgADEALgA0ADEAIAAyAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAMgAuADgAMwAgADIALgAyADQAIAAyAC4AMAAwACAAMgAuADIANAAgADIALgA4ADMAXABuAFwAbgAgACAAIAAgAFAAbwBsAGEAcgBHAHIAaQBkALsDKABnAHIAaQBkACwAMQApACAALQAgAHAAaABpADoAXABuACAAIAAgACAAIAAgACAAIAAtADIALgAzADYAIAAtADIALgAwADMAIAAtADEALgA1ADcAIAAtADEALgAxADEAIAAtADAALgA3ADkAXABuACAAIAAgACAAIAAgACAAIAAtADIALgA2ADgAIAAtADIALgAzADYAIAAtADEALgA1ADcAIAAtADAALgA3ADkAIAAtADAALgA0ADYAXABuACAAIAAgACAAIAAgACAAIAAgADMALgAxADQAIAAgADMALgAxADQAIAAgADAALgAwADAAIAAgADAALgAwADAAIAAgADAALgAwADAAXABuACAAIAAgACAAIAAgACAAIAAgADIALgA2ADgAIAAgADIALgAzADYAIAAgADEALgA1ADcAIAAgADAALgA3ADkAIAAgADAALgA0ADYAXABuACAAIAAgACAAIAAgACAAIAAgADIALgAzADYAIAAgADIALgAwADMAIAAgADEALgA1ADcAIAAgADEALgAxADEAIAAgADAALgA3ADkAXABuACoALwBcAG4AXABuAFwAbgBcAG4ALwAqAFsARwBXADAAMQBdAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABHAHIAaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkAHcAbwByAGsAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAGMAbwB1AG4AdABlAHIAESBjAGwAbwBjAGsAdwBpAHMAZQAgAGQAaQByAGUAYwB0AGkAbwBuACAAZwByAGkAZAAgAGkAbgAgAGQAZQBnAHIAZQBlAHMAIAAoADAAsAATIDMANgAwALAAKQAgAHUAcwBpAG4AZwBcAG4AIAAgACAAIABjAGUAbgB0AGUAcgBlAGQAIABDAGEAcgB0AGUAcwBpAGEAbgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAGYAcgBvAG0AIABDAEcAcgBpAGQAuwMuAFwAbgBcAG4AIAAgACAAIABBAG4AZwBsAGUAIABjAG8AbgB2AGUAbgB0AGkAbwBuADoAXABuACAAIAAgACAAIAAgACAAIAAwALAAIAAgACAAPQAgACsAWAAgAGQAaQByAGUAYwB0AGkAbwBuACAAKAByAGkAZwBoAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgADkAMACwACAAIAA9ACAAKwBZACAAZABpAHIAZQBjAHQAaQBvAG4AIAAoAHUAcAApAFwAbgAgACAAIAAgACAAIAAgACAAMQA4ADAAsAAgAD0AIAATIFgAIABkAGkAcgBlAGMAdABpAG8AbgAgACgAbABlAGYAdAApAFwAbgAgACAAIAAgACAAIAAgACAAMgA3ADAAsAAgAD0AIAATIFkAIABkAGkAcgBlAGMAdABpAG8AbgAgACgAZABvAHcAbgApAFwAbgBcAG4AIAAgACAAIABUAGgAZQAgAGMAZQBuAHQAZQByACAAYwBlAGwAbAAgACgAMAAsADAAKQAgAHIAZQB0AHUAcgBuAHMAIAAwALAAIAB2AGkAYQAgAEkARgBFAFIAUgBPAFIAIABmAGEAbABsAGIAYQBjAGsALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByADoAXABuACAAIAAgACAAZwByAGkAZAAgAC0AIABBACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHMAaQB6AGUALgAgACAAIAAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAYQB3ACAAYQBuAGcAbABlACAAaQBuACAAZABlAGcAcgBlAGUAcwAgACgAbQBhAHkAIABiAGUAIABuAGUAZwBhAHQAaQB2AGUAKQBcAG4AIAAgACAAIAB0AGgAZQB0AGEALAAgAEkARgBFAFIAUgBPAFIAKABEAEUARwBSAEUARQBTACgAQQBUAEEATgAyACgAQwBHAHIAaQBkALsDKABnAHIAaQBkACkALAAgAEMARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQApACkALAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIAB0AG8AIAAwALAAEyAzADYAMACwAFwAbgAgACAAIAAgAGEAbgBnAGwAZQAsACAATQBPAEQAKAB0AGgAZQB0AGEAIAArACAAMwA2ADAALAAgADMANgAwACkALABcAG4AXABuACAAIAAgACAAYQBuAGcAbABlAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqAFsARwBXADAAMgBdAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAQwBHAHIAaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkAHcAbwByAGsAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABjAGUAbgB0AGUAcgBlAGQAIABDAGEAcgB0AGUAcwBpAGEAbgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAIABnAHIAaQBkAHMAIABhAGwAaQBnAG4AZQBkACAAdABvACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIABhAFwAbgAgACAAIAAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAuACAAUgBlAHQAdQByAG4AcwAgAGUAaQB0AGgAZQByACAAcgBvAHcAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIABvAHIAIABjAG8AbAB1AG0AbgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAuAFwAbgBcAG4AIAAgACAAIABDAG8AbwByAGQAaQBuAGEAdABlACAAcgBhAG4AZwBlAHMAIABhAHIAZQAgAGMAZQBuAHQAZQByAGUAZAAgAHMAdQBjAGgAIAB0AGgAYQB0ADoAXABuACAAIAAgACAAIAAgACAAIABSAG8AdwA6ACAAIAAtACgAaAAgAC0AIAAxACkAIAAvACAAMgAgACAALgAuAC4AIAAgACsAKABoACAALQAgADEAKQAgAC8AIAAyAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAGwAOgAgACAALQAoAHcAIAAtACAAMQApACAALwAgADIAIAAgAC4ALgAuACAAIAArACgAdwAgAC0AIAAxACkAIAAvACAAMgBcAG4AXABuACAAIAAgACAAVwBvAHIAawBzACAAZgBvAHIAIABiAG8AdABoACAAMQBEACAAYQBuAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABBACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHMAaQB6AGUALgBcAG4AIAAgACAAIABbAGMAbwBsAF8AaQBuAGQAZQB4AF0AIAAtACAASQBmACAAVABSAFUARQAsACAAcgBlAHQAdQByAG4AIABjAG8AbAB1AG0AbgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAuACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAcgBlAHQAdQByAG4AIAByAG8AdwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEMARwByAGkAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIABtAG8AZABlAFwAbgAgACAAIAAgAFIAbwB3AEkAZAB4AD8ALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABHAHIAaQBkACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQByAHQAaQBuAGcAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAAoAGMAZQBuAHQAZQByAGUAZAApAFwAbgAgACAAIAAgAGkAXwBzAHQAYQByAHQALAAgAC0AIAAoAGgAIAAtACAAMQApACAALwAgADIALABcAG4AIAAgACAAIABqAF8AcwB0AGEAcgB0ACwAIAAtACAAKAB3ACAALQAgADEAKQAgAC8AIAAyACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGUAcgByAGUAZAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAIABnAGUAbgBlAHIAYQB0AG8AcgBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoAGgALAAsAGkAXwBzAHQAYQByAHQAKQAsACwAdwApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcALABqAF8AcwB0AGEAcgB0ACkALABoACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAHIAbwB3ACAAbwByACAAYwBvAGwAdQBtAG4AIABjAG8AbwByAGQAaQBuAGEAdABlACAAZwByAGkAZABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAWwBHAFcAMAAzAF0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABNAEcAcgBpAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAHIAbwB3ABEgaQBuAGQAZQB4ACAAbwByACAAYwBvAGwAdQBtAG4AESBpAG4AZABlAHgAIABnAHIAaQBkAHMAIABtAGEAdABjAGgAaQBuAGcAIAB0AGgAZQAgAHMAaABhAHAAZQAgAG8AZgAgAGEAIABzAHUAcABwAGwAaQBlAGQAXABuACAAIAAgACAAYQByAHIAYQB5AC4AIABUAGgAaQBzACAAaQBzACAAdABoAGUAIABFAHgAYwBlAGwAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAbwBmACAATQBBAFQATABBAEIAGSBzACAAbQBlAHMAaABnAHIAaQBkACAAbwByACAATgB1AG0AUAB5ABkgcwAgAGkAbgBkAGkAYwBlAHMALgBcAG4AXABuACAAIAAgACAAQgB5ACAAZABlAGYAYQB1AGwAdAAsACAATQBHAHIAaQBkALsDIAByAGUAdAB1AHIAbgBzACAAcgBvAHcAIABpAG4AZABpAGMAZQBzAC4AIABXAGgAZQBuACAAdABoAGUAIABvAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGkAcwAgAFQAUgBVAEUALABcAG4AIAAgACAAIABpAHQAIAByAGUAdAB1AHIAbgBzACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAaQBuAHMAdABlAGEAZAAuAFwAbgBcAG4AIAAgACAAIABXAG8AcgBrAHMAIABmAG8AcgAgAGIAbwB0AGgAIAAxAEQAIABhAG4AZAAgADIARAAgAGEAcgByAGEAeQBzAC4AIABPAHUAdABwAHUAdAAgAGEAbAB3AGEAeQBzACAAbQBhAHQAYwBoAGUAcwAgAHQAaABlACAAZwBlAG8AbQBlAHQAcgB5ACAAbwBmACAAdABoAGUAXABuACAAIAAgACAAaQBuAHAAdQB0ACAAZwByAGkAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABBACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHMAaQB6AGUALgBcAG4AIAAgACAAIABbAGMAbwBsAF8AaQBuAGQAZQB4AF0AIAAtACAASQBmACAAVABSAFUARQAsACAAcgBlAHQAdQByAG4AIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMALgAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHIAZQB0AHUAcgBuACAAcgBvAHcAIABpAG4AZABpAGMAZQBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0ARwByAGkAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIABtAG8AZABlAFwAbgAgACAAIAAgAFIAbwB3AEkAZAB4AD8ALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABHAHIAaQBkACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABpAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABSAGUAcwBpAHoAZQC7AygAUwBFAFEAVQBFAE4AQwBFACgAaAApACwALAB3ACkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoACwAdwApACwAaAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAZwByAGkAZABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIABJAEYAKABSAG8AdwBJAGQAeAA/ACwAIABpACgAKQAsACAAagAoACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADQAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFQARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcgBvAHcAESBpAG4AZABlAHgAIABvAHIAIABjAG8AbAB1AG0AbgARIGkAbgBkAGUAeAAgAGcAcgBpAGQAcwAgAHcAaABvAHMAZQAgAHYAYQBsAHUAZQBzACAAdwByAGEAcAAgAHcAaQB0AGgAaQBuACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkAFwAbgAgACAAIAAgAHQAaAByAGUAcwBoAG8AbABkAC4AIABJAG4AZABpAGMAZQBzACAAYwB5AGMAbABlACAAZgByAG8AbQAgADEAIAB0AG8AIAB0AGgAcgBlAHMAaABvAGwAZAAsACAAcgBlAHAAZQBhAHQAaQBuAGcAIABhAHMAIABuAGUAZQBkAGUAZAAgAHQAbwAgAG0AYQB0AGMAaAAgAHQAaABlAFwAbgAgACAAIAAgAHMAaABhAHAAZQAgAG8AZgAgAHQAaABlACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5AC4AXABuAFwAbgAgACAAIAAgAEIAeQAgAGQAZQBmAGEAdQBsAHQALAAgAFQARwByAGkAZAC7AyAAcgBlAHQAdQByAG4AcwAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAuACAAVwBoAGUAbgAgAHQAaABlACAAbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAIABpAHMAIABUAFIAVQBFACwAXABuACAAIAAgACAAaQB0ACAAcgBlAHQAdQByAG4AcwAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAGkAbgBzAHQAZQBhAGQALgBcAG4AXABuACAAIAAgACAATgBvAG4AESBpAG4AdABlAGcAZQByACAAdABoAHIAZQBzAGgAbwBsAGQAcwAgAGEAcgBlACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAHUAcwBpAG4AZwAgAEkATgBUACgAdABoAHIAZQBzAGgAbwBsAGQAKQAuACAAVABoAHIAZQBzAGgAbwBsAGQAcwAgAG0AdQBzAHQAIABiAGUAXABuACAAIAAgACAAcABvAHMAaQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAALQAgAEEAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAZABlAHQAZQByAG0AaQBuAGUAIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAcwBpAHoAZQAuAFwAbgAgACAAIAAgAHQAaAByAGUAcwBoAG8AbABkACAAIAAgAC0AIABNAGEAeABpAG0AdQBtACAAaQBuAGQAZQB4ACAAdgBhAGwAdQBlACAAYgBlAGYAbwByAGUAIAB3AHIAYQBwAHAAaQBuAGcAIAAoAG0AdQBzAHQAIABiAGUAIAA+ACAAMAApAC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzAC4AIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAByAGUAdAB1AHIAbgAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBUAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAHQAaAByAGUAcwBoAG8AbABkACwAXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACwAXABuAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAHQAaAByAGUAcwBoAG8AbABkACkALAAgAHQAaAByAGUAcwBoAG8AbABkACAAPAA9ACAAMAApACwAXAAiACMAVABIAFIARQBTAEgATwBMAEQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIAB0AGgAcgBlAHMAaABvAGwAZABcAG4AIAAgACAAIAB0ACwAIAAgACAAIAAgACAAIABJAE4AVAAoAHQAaAByAGUAcwBoAG8AbABkACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIABtAG8AZABlAFwAbgAgACAAIAAgAFIAbwB3AEkAZAB4AD8ALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABHAHIAaQBkACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIAB3AHIAYQBwAHAAZQBkACAAaQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAIAAxACAAKwAgAE0ATwBEACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoAGgALAAsADAAKQAsACwAdwApACwAIAB0ACkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAIAAxACAAKwAgAE0ATwBEACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoACwAdwAsADAAKQAsAGgAKQAsACAAdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAZwByAGkAZABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIABJAEYAKABSAG8AdwBJAGQAeAA/ACwAIABpACgAKQAsACAAagAoACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqAFsARwBXADAANQBdAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUABvAGwAYQByAEcAcgBpAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEMARwByAGkAZAC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAZwByAGkAZAAgAG8AZgAgAHAAbwBsAGEAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAGEAbABpAGcAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAaABhAHAAZQAgAG8AZgAgAGEAIABzAHUAcABwAGwAaQBlAGQAXABuACAAIAAgACAAYQByAHIAYQB5AC4AIABDAG8AbwByAGQAaQBuAGEAdABlAHMAIABhAHIAZQAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAYwBlAG4AdABlAHIAZQBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIABwAHIAbwBkAHUAYwBlAGQAXABuACAAIAAgACAAYgB5ACAAQwBHAHIAaQBkALsDLgBcAG4AXABuACAAIAAgACAAVAB3AG8AIABjAG8AbwByAGQAaQBuAGEAdABlACAAZgBpAGUAbABkAHMAIABhAHIAZQAgAGEAdgBhAGkAbABhAGIAbABlADoAXABuACAAIAAgACAAIAAgACAAIAByACAAIAAgACAALQAgAHIAYQBkAGkAYQBsACAAZABpAHMAdABhAG4AYwBlACAAZgByAG8AbQAgAHQAaABlACAAYwBlAG4AdABlAHIAXABuACAAIAAgACAAIAAgACAAIABwAGgAaQAgACAALQAgAGEAbgBnAGwAZQAgAGkAbgAgAHIAYQBkAGkAYQBuAHMALAAgAHUAcwBpAG4AZwAgAHQAaABlACAAQQBUAEEATgAyACgAeQAsACAAeAApACAAYwBvAG4AdgBlAG4AdABpAG8AbgBcAG4AXABuACAAIAAgACAASQBmACAAcABoAGkAXwBjAG8AbwByAGQAaQBuAGEAdABlACAAaQBzACAAbwBtAGkAdAB0AGUAZAAsACAAdABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIAByAGUAdAB1AHIAbgBzACAAdABoAGUAIAByAGEAZABpAGEAbAAgAGQAaQBzAHQAYQBuAGMAZQAgAGcAcgBpAGQALgBcAG4AIAAgACAAIABJAGYAIABUAFIAVQBFACwAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAHIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAGEAbgBnAHUAbABhAHIAIABnAHIAaQBkAC4AXABuAFwAbgAgACAAIAAgAFQAaABlACAAYwBlAG4AdABlAHIAIABjAGUAbABsACAAKAAwACwAMAApACAAcgBlAHQAdQByAG4AcwAgAHAAaABpACAAPQAgADAAIAB2AGkAYQAgAEkARgBFAFIAUgBPAFIAIABmAGEAbABsAGIAYQBjAGsALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAGYAcgBvAG0AIAB3AGgAaQBjAGgAIAB0AG8AIABnAGUAbgBlAHIAYQB0AGUAIABwAG8AbABhAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMALgBcAG4AIAAgACAAIABbAHAAaABpAF8AYwBvAG8AcgBkAGkAbgBhAHQAZQBdACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuACAAcABoAGkAOwAgAGkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHIAZQB0AHUAcgBuACAAcgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBQAG8AbABhAHIARwByAGkAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAWwBwAGgAaQBfAGMAbwBvAHIAZABpAG4AYQB0AGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABJAHMAUgA/ACwAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABwAGgAaQBfAGMAbwBvAHIAZABpAG4AYQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGEAcgB0AGUAcwBpAGEAbgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAbwBsAGEAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAUwBRAFIAVAAoAHgAXgAyACAAKwAgAHkAXgAyACkALABcAG4AIAAgACAAIABwAGgAaQAsACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEEAVABBAE4AMgAoAHkALAAgAHgAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgAgAG8AcgAgAHAAaABpAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIABJAEYAKABJAHMAUgA/ACwAIAByACwAIABwAGgAaQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAjACMAIAAwADIAIAAtACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAgACoALwBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVABoAGkAcwAgAG0AbwBkAHUAbABlACAAZABlAGYAaQBuAGUAcwAgAGEAIABmAGEAbQBpAGwAeQAgAG8AZgAgAGcAZQBvAG0AZQB0AHIAaQBjACAAZQB4AHQAcgBhAGMAdABpAG8AbgAgAG8AcABlAHIAYQB0AG8AcgBzACAAZgBvAHIAIAAyAEQAIABhAHIAcgBhAHkAcwAuAFwAbgAgACAAIAAgAEUAYQBjAGgAIABmAHUAbgBjAHQAaQBvAG4AIAByAGUAdAB1AHIAbgBzACAAYQAgAHIAZQBnAGkAbwBuACAAbwBmACAAdABoAGUAIABnAHIAaQBkACAAZABlAGYAaQBuAGUAZAAgAGIAeQAgAGEAIABzAHAAZQBjAGkAZgBpAGMAIABzAGgAYQBwAGUALABcAG4AIAAgACAAIABwAHIAZQBzAGUAcgB2AGkAbgBnACAAdABoAGUAIABnAGUAbwBtAGUAdAByAHkAIABvAGYAIAB0AGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkACAAYQByAGUAYQAuACAAQwBlAG4AdABlAHIAcwAgAG0AYQB5ACAAYgBlACAAcwBwAGUAYwBpAGYAaQBlAGQAIABiAHkAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhACAAbwByACAAZQB4AHAAbABpAGMAaQB0ACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACwAIABhAG4AZAAgAG8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAGwAIAB2AGEAbAB1AGUAcwAgAGMAbwBuAHQAcgBvAGwAIAB3AGgAYQB0AFwAbgAgACAAIAAgAGEAcABwAGUAYQByAHMAIABvAHUAdABzAGkAZABlACAAdABoAGUAIABlAHgAdAByAGEAYwB0AGUAZAAgAHIAZQBnAGkAbwBuAC4AXABuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAiICAAQwBpAHIAYwBsAGUAuwMgACAAIAAtACAAIAAgAEMAaQByAGMAdQBsAGEAcgAgAHIAZQBnAGkAbwBuACAAYgB5ACAAdABhAHIAZwBlAHQAIABvAHIAIAB7AHIAbwB3ACwAIABjAG8AbAB9ACAAYwBlAG4AdABlAHIALgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAARABpAGEAbQBvAG4AZAC7AyAAIAAtACAAIAAgAE0AYQBuAGgAYQB0AHQAYQBuABEgcgBhAGQAaQB1AHMAIABkAGkAYQBtAG8AbgBkAC4AXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFAAbAB1AHMAuwMgACAAIAAgACAALQAgACAAIABDAHIAbwBzAHMAESBzAGgAYQBwAGUAZAAgAHIAZQBnAGkAbwBuACAAKAB2AG8AbgAgAE4AZQB1AG0AYQBuAG4AIABuAGUAaQBnAGgAYgBvAHIAaABvAG8AZAApAC4AXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFAAeQByAGEAbQBpAGQAuwMgACAALQAgACAAIABEAGkAcgBlAGMAdABpAG8AbgBhAGwAIABoAGEAbABmABEgZABpAGEAbQBvAG4AZAAgACgAZgBvAHUAcgAgAHAAaQBlAGMAZQBzACkALgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUgBpAG4AZwC7AyAAIAAgACAAIAAtACAAIAAgAEwAYQB5AGUAcgARIGIAYQBzAGUAZAAgAHAAZQByAGkAbQBlAHQAZQByACAAZQB4AHQAcgBhAGMAdABpAG8AbgAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABTAHEAdQBhAHIAZQC7AyAAIAAgAC0AIAAgACAAQwBoAGUAYgB5AHMAaABlAHYAESByAGEAZABpAHUAcwAgAHMAcQB1AGEAcgBlAC4AXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFQAcgBpAGEAbgBnAGwAZQC7AyAALQAgACAAIABEAGkAcgBlAGMAdABpAG8AbgBhAGwAIAB0AHIAaQBhAG4AZwB1AGwAYQByACAAcgBlAGcAaQBvAG4AIAAoAGEAYgBvAHYAZQAgAG8AcgAgAGIAZQBsAG8AdwApAC4AXABuAFwAbgAgACAAIAAgAFUAdABpAGwAaQB0AGkAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAiICAAQwBHAHIAaQBkALsDLAAgAE0ARwByAGkAZAC7AywAIABSAGUAcwBpAHoAZQC7AywAIABTAHEAdQBlAGUAegBlALsDXABuAFwAbgAgACAAIAAgAEEAbABsACAAZgB1AG4AYwB0AGkAbwBuAHMAIABhAHIAZQAgAHMAaABhAHAAZQARIGQAcgBpAHYAZQBuADoAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGcAcgBpAGQAIABkAGUAdABlAHIAbQBpAG4AZQBzACAAdABoAGUAIABjAG8AbwByAGQAaQBuAGEAdABlAFwAbgAgACAAIAAgAGUAeAB0AGUAbgB0AHMAIABhAG4AZAAgAHQAaABlACAAZwBlAG8AbQBlAHQAcgB5ACAAbwBmACAAdABoAGUAIABlAHgAdAByAGEAYwB0AGUAZAAgAHIAZQBnAGkAbwBuAC4AXABuAC8AKgBcAG4AXABuACAAIAAgACAARQB4AGEAbQBwAGwAZQBzADoAXABuAFwAbgBcAG4ARwByAGkAZABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AMQBcAHQAMgBcAHQAMwBcAHQANABcAHQANQBcAHQANgBcAHQANwBcAHQAOABcAHQAOQBcAHQAMQAwAFwAbgAxADEAXAB0ADEAMgBcAHQAMQAzAFwAdAAxADQAXAB0ADEANQBcAHQAMQA2AFwAdAAxADcAXAB0ADEAOABcAHQAMQA5AFwAdAAyADAAXABuADIAMQBcAHQAMgAyAFwAdAAyADMAXAB0ADIANABcAHQAMgA1AFwAdAAyADYAXAB0ADIANwBcAHQAMgA4AFwAdAAyADkAXAB0ADMAMABcAG4AMwAxAFwAdAAzADIAXAB0ADMAMwBcAHQAMwA0AFwAdAAzADUAXAB0ADMANgBcAHQAMwA3AFwAdAAzADgAXAB0ADMAOQBcAHQANAAwAFwAbgA0ADEAXAB0ADQAMgBcAHQANAAzAFwAdAA0ADQAXAB0ADQANQBcAHQANAA2AFwAdAA0ADcAXAB0ADQAOABcAHQANAA5AFwAdAA1ADAAXABuADUAMQBcAHQANQAyAFwAdAA1ADMAXAB0ADUANABcAHQANQA1AFwAdAA1ADYAXAB0ADUANwBcAHQANQA4AFwAdAA1ADkAXAB0ADYAMABcAG4ANgAxAFwAdAA2ADIAXAB0ADYAMwBcAHQANgA0AFwAdAA2ADUAXAB0ADYANgBcAHQANgA3AFwAdAA2ADgAXAB0ADYAOQBcAHQANwAwAFwAbgA3ADEAXAB0ADcAMgBcAHQANwAzAFwAdAA3ADQAXAB0ADcANQBcAHQANwA2AFwAdAA3ADcAXAB0ADcAOABcAHQANwA5AFwAdAA4ADAAXABuADgAMQBcAHQAOAAyAFwAdAA4ADMAXAB0ADgANABcAHQAOAA1AFwAdAA4ADYAXAB0ADgANwBcAHQAOAA4AFwAdAA4ADkAXAB0ADkAMABcAG4AOQAxAFwAdAA5ADIAXAB0ADkAMwBcAHQAOQA0AFwAdAA5ADUAXAB0ADkANgBcAHQAOQA3AFwAdAA5ADgAXAB0ADkAOQBcAHQAMQAwADAAXABuAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBDAGkAcgBjAGwAZQC7AygAZwByAGkAZAAsADQANQAsADUALABcACIAXAAiACkAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdAAyAFwAdAAzAFwAdAA0AFwAdAA1AFwAdAA2AFwAdAA3AFwAdAA4AFwAdABcAHQAXABuADEAMQBcAHQAMQAyAFwAdAAxADMAXAB0ADEANABcAHQAMQA1AFwAdAAxADYAXAB0ADEANwBcAHQAMQA4AFwAdAAxADkAXAB0AFwAbgAyADEAXAB0ADIAMgBcAHQAMgAzAFwAdAAyADQAXAB0ADIANQBcAHQAMgA2AFwAdAAyADcAXAB0ADIAOABcAHQAMgA5AFwAdABcAG4AMwAxAFwAdAAzADIAXAB0ADMAMwBcAHQAMwA0AFwAdAAzADUAXAB0ADMANgBcAHQAMwA3AFwAdAAzADgAXAB0ADMAOQBcAHQAXABuADQAMQBcAHQANAAyAFwAdAA0ADMAXAB0ADQANABcAHQANAA1AFwAdAA0ADYAXAB0ADQANwBcAHQANAA4AFwAdAA0ADkAXAB0ADUAMABcAG4ANQAxAFwAdAA1ADIAXAB0ADUAMwBcAHQANQA0AFwAdAA1ADUAXAB0ADUANgBcAHQANQA3AFwAdAA1ADgAXAB0ADUAOQBcAHQAXABuADYAMQBcAHQANgAyAFwAdAA2ADMAXAB0ADYANABcAHQANgA1AFwAdAA2ADYAXAB0ADYANwBcAHQANgA4AFwAdAA2ADkAXAB0AFwAbgA3ADEAXAB0ADcAMgBcAHQANwAzAFwAdAA3ADQAXAB0ADcANQBcAHQANwA2AFwAdAA3ADcAXAB0ADcAOABcAHQANwA5AFwAdABcAG4AXAB0ADgAMgBcAHQAOAAzAFwAdAA4ADQAXAB0ADgANQBcAHQAOAA2AFwAdAA4ADcAXAB0ADgAOABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdABcAHQAOQA1AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBEAGkAYQBtAG8AbgBkALsDKABnAHIAaQBkACwAewA1ACwANQB9ACwAMwAsAFwAIgBcACIAKQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAMQA1AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0ADIANABcAHQAMgA1AFwAdAAyADYAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0ADMAMwBcAHQAMwA0AFwAdAAzADUAXAB0ADMANgBcAHQAMwA3AFwAdABcAHQAXAB0AFwAdABcAG4ANAAyAFwAdAA0ADMAXAB0ADQANABcAHQANAA1AFwAdAA0ADYAXAB0ADQANwBcAHQANAA4AFwAdABcAHQAXAB0AFwAbgBcAHQANQAzAFwAdAA1ADQAXAB0ADUANQBcAHQANQA2AFwAdAA1ADcAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0ADYANABcAHQANgA1AFwAdAA2ADYAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQANwA1AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AUABsAHUAcwC7AygAZwByAGkAZAAsADUANwAsADMALABcACIAXAAiACkAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADIANwBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAMwA3AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdAA0ADcAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuADUANABcAHQANQA1AFwAdAA1ADYAXAB0ADUANwBcAHQANQA4AFwAdAA1ADkAXAB0ADYAMABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQANgA3AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdAA3ADcAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADgANwBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFAAeQByAGEAbQBpAGQAuwMoAGcAcgBpAGQALAAyACwAXAAiAHgAXAAiACkAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0ADEAMABcAG4AeABcAHQAeABcAHQAeABcAHQAeABcAHQAeABcAHQAeABcAHQAeABcAHQAeABcAHQAMQA5AFwAdAAyADAAXABuAHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0ADIAOABcAHQAMgA5AFwAdAAzADAAXABuAHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0ADMANwBcAHQAMwA4AFwAdAAzADkAXAB0ADQAMABcAG4AeABcAHQAeABcAHQAeABcAHQAeABcAHQAeABcAHQANAA2AFwAdAA0ADcAXAB0ADQAOABcAHQANAA5AFwAdAA1ADAAXABuAHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0ADUANQBcAHQANQA2AFwAdAA1ADcAXAB0ADUAOABcAHQANQA5AFwAdAA2ADAAXABuAHgAXAB0AHgAXAB0AHgAXAB0ADYANABcAHQANgA1AFwAdAA2ADYAXAB0ADYANwBcAHQANgA4AFwAdAA2ADkAXAB0ADcAMABcAG4AeABcAHQAeABcAHQANwAzAFwAdAA3ADQAXAB0ADcANQBcAHQANwA2AFwAdAA3ADcAXAB0ADcAOABcAHQANwA5AFwAdAA4ADAAXABuAHgAXAB0ADgAMgBcAHQAOAAzAFwAdAA4ADQAXAB0ADgANQBcAHQAOAA2AFwAdAA4ADcAXAB0ADgAOABcAHQAOAA5AFwAdAA5ADAAXABuADkAMQBcAHQAOQAyAFwAdAA5ADMAXAB0ADkANABcAHQAOQA1AFwAdAA5ADYAXAB0ADkANwBcAHQAOQA4AFwAdAA5ADkAXAB0ADEAMAAwAFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AUgBpAG4AZwC7AygAZwByAGkAZAAsADIALABcACIALQBcACIAKQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4ALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAG4ALQBcAHQAMQAyAFwAdAAxADMAXAB0ADEANABcAHQAMQA1AFwAdAAxADYAXAB0ADEANwBcAHQAMQA4AFwAdAAxADkAXAB0AC0AXABuAC0AXAB0ADIAMgBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQAMgA5AFwAdAAtAFwAbgAtAFwAdAAzADIAXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0ADMAOQBcAHQALQBcAG4ALQBcAHQANAAyAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAA0ADkAXAB0AC0AXABuAC0AXAB0ADUAMgBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQANQA5AFwAdAAtAFwAbgAtAFwAdAA2ADIAXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0ADYAOQBcAHQALQBcAG4ALQBcAHQANwAyAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAA3ADkAXAB0AC0AXABuAC0AXAB0ADgAMgBcAHQAOAAzAFwAdAA4ADQAXAB0ADgANQBcAHQAOAA2AFwAdAA4ADcAXAB0ADgAOABcAHQAOAA5AFwAdAAtAFwAbgAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AUwBxAHUAYQByAGUAuwMoAGcAcgBpAGQALAAyADcALAAzACwAXAAiAFwAIgApAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgA0AFwAdAA1AFwAdAA2AFwAdAA3AFwAdAA4AFwAdAA5AFwAdAAxADAAXAB0AFwAdABcAHQAXABuADEANABcAHQAMQA1AFwAdAAxADYAXAB0ADEANwBcAHQAMQA4AFwAdAAxADkAXAB0ADIAMABcAHQAXAB0AFwAdABcAG4AMgA0AFwAdAAyADUAXAB0ADIANgBcAHQAMgA3AFwAdAAyADgAXAB0ADIAOQBcAHQAMwAwAFwAdABcAHQAXAB0AFwAbgAzADQAXAB0ADMANQBcAHQAMwA2AFwAdAAzADcAXAB0ADMAOABcAHQAMwA5AFwAdAA0ADAAXAB0AFwAdABcAHQAXABuADQANABcAHQANAA1AFwAdAA0ADYAXAB0ADQANwBcAHQANAA4AFwAdAA0ADkAXAB0ADUAMABcAHQAXAB0AFwAdABcAG4ANQA0AFwAdAA1ADUAXAB0ADUANgBcAHQANQA3AFwAdAA1ADgAXAB0ADUAOQBcAHQANgAwAFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AVAByAGkAYQBuAGcAbABlALsDKABnAHIAaQBkACwANAA0ACwAMwAsACwAXAAiAFwAIgApACAALQAgAEEAYgBvAHYAZQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAMQA0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0ADIAMwBcAHQAMgA0AFwAdAAyADUAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0ADMAMgBcAHQAMwAzAFwAdAAzADQAXAB0ADMANQBcAHQAMwA2AFwAdABcAHQAXAB0AFwAdABcAG4ANAAxAFwAdAA0ADIAXAB0ADQAMwBcAHQANAA0AFwAdAA0ADUAXAB0ADQANgBcAHQANAA3AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AVAByAGkAYQBuAGcAbABlALsDKABnAHIAaQBkACwANAA0ACwAMwAsADEALABcACIAXAAiACkAIAAtACAAQgBlAGwAbwB3AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgA0ADEAXAB0ADQAMgBcAHQANAAzAFwAdAA0ADQAXAB0ADQANQBcAHQANAA2AFwAdAA0ADcAXAB0AFwAdABcAHQAXABuAFwAdAA1ADIAXAB0ADUAMwBcAHQANQA0AFwAdAA1ADUAXAB0ADUANgBcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQANgAzAFwAdAA2ADQAXAB0ADYANQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdAA3ADQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBHADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEMAaQByAGMAbABlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQwBHAHIAaQBkALsDLAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAIABjAGkAcgBjAHUAbABhAHIAIAByAGUAZwBpAG8AbgAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgB5ACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAXABuACAAIAAgACAAcgBhAGQAaQB1AHMAIAAoAGUAeAB0AGUAbgBkACkALgAgAFQAaABlACAAYwBlAG4AdABlAHIAIABtAGEAeQAgAGIAZQAgAGcAaQB2AGUAbgAgAGEAcwAgAGEAIABzAGMAYQBsAGEAcgAgAGMAcgBpAHQAZQByAGkAbwBuACAAbwByACAAYQBzACAAZQB4AHAAbABpAGMAaQB0AFwAbgAgACAAIAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgAgAFQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgAgAHAAcgBlAHMAZQByAHYAZQBzACAAaQB0AHMAIABnAGUAbwBtAGUAdAByAGkAYwAgAHMAaABhAHAAZQAsAFwAbgAgACAAIAAgAGEAbgBkACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAbwBuAGwAeQAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAIABhAHIAZQAgAGEAdQB0AG8AbQBhAHQAaQBjAGEAbABsAHkAIAByAGUAbQBvAHYAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACAAIAAgACAAIAAgAC0AIABDAGUAbgB0AGUAcgAgAG8AZgAgAHQAaABlACAAYwBpAHIAYwBsAGUALgAgAE0AYQB5ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgBcAG4AIAAgACAAIABlAHgAdABlAG4AZAAgACAAIAAgACAAIAAtACAAUgBhAGQAaQB1AHMAIABvAGYAIAB0AGgAZQAgAGMAaQByAGMAbABlACAAKABtAHUAcwB0ACAAYgBlACAAYQAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAKQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdAC0AIABTAGMAYQBsAGEAcgAgAHUAcwBlAGQAIABvAHUAdABzAGkAZABlACAAdABoAGUAIABjAGkAcgBjAGwAZQAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAGkAcgBjAGwAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAdABhAHIAZwBlAHQALABcAG4AIAAgACAAIABlAHgAdABlAG4AZAAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABnAHIAaQBkACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABhAHIAZwBlAHQAIABpAG4AdABlAHIAcAByAGUAdABhAHQAaQBvAG4AXABuACAAIAAgACAASQBzAEkAXwBKAD8ALAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAKAB0AGEAcgBnAGUAdAApACAAPQAgADIALABcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABUAEEASwBFACgAdABhAHIAZwBlAHQALAAgADEALAAgADEAKQAsACAAMAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAtADEALAAgAC0AMQApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBvAG8AbABlAGEAbgAgAG0AYQB0AGMAaAAgAGYAbwByACAAcwBjAGEAbABhAHIAIAB0AGEAcgBnAGUAdABcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAGcAcgBpAGQAIAA9ACAAdABhAHIAZwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABYAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEUAeAB0AGUAbgBkAD8ALAAgAE8AUgAoAEkAUwBUAEUAWABUACgAZQB4AHQAZQBuAGQAKQAsACAAZQB4AHQAZQBuAGQAIAA8ACAAMQApACwAXABuACAAIAAgACAATgBvAFQAYQByAGcAZQB0AD8ALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABOAE8AVAAoAE8AUgAoAGIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAbABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIAAwACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAZwByAGkAZAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAXAAiACMAMQBEAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEUAeAB0AGUAbgBkAD8ALAAgAFwAIgAjAEUAWABUAEUATgBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBUAGEAcgBnAGUAdAA/ACwAIABcACIAIwBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABpACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEkATgBEAEUAWAAoAGoALAAgAHIALAAgAGMAKQAsACAAVABPAEMATwBMACgASQBGACgAYgBvAG8AbAAsACAAagAsACAATgBBACgAKQApACwAIAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGkAcgBjAGwAZQAgAG0AYQBzAGsAXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACgAaQAgAC0AIAB4ACkAXgAyACAAKwAgACgAagAgAC0AIAB5ACkAXgAyACAAPAA9ACAAZQB4AHQAZQBuAGQAXgAyACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABhAG4AZAAgAHMAcQB1AGUAZQB6AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAFMAcQB1AGUAZQB6AGUAuwMoAEkARgAoAG0AYQBzAGsALAAgAGcAcgBpAGQALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBHADAAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEQAaQBhAG0AbwBuAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAGQAaQBhAG0AbwBuAGQAESBzAGgAYQBwAGUAZAAgAHIAZQBnAGkAbwBuACAAKABNAGEAbgBoAGEAdAB0AGEAbgAgAHIAYQBkAGkAdQBzACkAIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGIAeQBcAG4AIAAgACAAIABzAHAAZQBjAGkAZgB5AGkAbgBnACAAdABoAGUAIABjAGUAbgB0AGUAcgAgAGEAbgBkACAAYQAgAGQAaQBzAHQAYQBuAGMAZQAuACAAVABoAGUAIABjAGUAbgB0AGUAcgAgAG0AYQB5ACAAYgBlACAAZwBpAHYAZQBuACAAYQBzACAAYQAgAHMAYwBhAGwAYQByAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAbwBuACAAbwByACAAYQBzACAAZQB4AHAAbABpAGMAaQB0ACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAewByAG8AdwAsACAAYwBvAGwAfQAuACAAVABoAGUAIABlAHgAdAByAGEAYwB0AGUAZAAgAHIAZQBnAGkAbwBuAFwAbgAgACAAIAAgAHAAcgBlAHMAZQByAHYAZQBzACAAaQB0AHMAIABnAGUAbwBtAGUAdAByAGkAYwAgAHMAaABhAHAAZQAsACAAYQBuAGQAIAByAG8AdwBzAC8AYwBvAGwAdQBtAG4AcwAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABvAG4AbAB5ACAAZgBpAGwAbABfAHYAYQBsAHUAZQBcAG4AIAAgACAAIABhAHIAZQAgAGEAdQB0AG8AbQBhAHQAaQBjAGEAbABsAHkAIAByAGUAbQBvAHYAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACAAIAAgACAAIAAgAC0AIABDAGUAbgB0AGUAcgAgAG8AZgAgAHQAaABlACAAZABpAGEAbQBvAG4AZAAuACAATQBhAHkAIABiAGUAIABhACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBmACAAdABoAGUAIABmAG8AcgBtACAAewByAG8AdwAsACAAYwBvAGwAfQAuAFwAbgAgACAAIAAgAGQAaQBzAHQAYQBuAGMAZQAgACAAIAAgAC0AIABNAGEAbgBoAGEAdAB0AGEAbgAgAHIAYQBkAGkAdQBzACAAbwBmACAAdABoAGUAIABkAGkAYQBtAG8AbgBkACAAKABtAHUAcwB0ACAAYgBlACAAYQAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAKQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdAC0AIABTAGMAYQBsAGEAcgAgAHUAcwBlAGQAIABvAHUAdABzAGkAZABlACAAdABoAGUAIABkAGkAYQBtAG8AbgBkAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAwAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAaQBhAG0AbwBuAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACwAXABuACAAIAAgACAAZABpAHMAdABhAG4AYwBlACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABnAHIAaQBkACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAYQByAGcAZQB0ACAAaQBuAHQAZQByAHAAcgBlAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBJAF8ASgA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVAAoAHQAYQByAGcAZQB0ACkAIAA9ACAAMgAsAFwAbgAgACAAIAAgAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABUAEEASwBFACgAdABhAHIAZwBlAHQALAAgADEALAAgADEAKQAsACAAMAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAFQAQQBLAEUAKAB0AGEAcgBnAGUAdAAsACAALQAxACwAIAAtADEAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAdABjAGgAIABmAG8AcgAgAHMAYwBhAGwAYQByACAAdABhAHIAZwBlAHQAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEYAQQBMAFMARQAsACAAZwByAGkAZAAgAD0AIAB0AGEAcgBnAGUAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBwAHUAdAAgAHYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABEAGkAcwB0AGEAbgBjAGUAPwAsACAATwBSACgASQBTAFQARQBYAFQAKABkAGkAcwB0AGEAbgBjAGUAKQAsACAAZABpAHMAdABhAG4AYwBlACAAPAAgADEAKQAsAFwAbgAgACAAIAAgAE4AbwBUAGEAcgBnAGUAdAA/ACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAE4ATwBUACgATwBSACgAYgBvAG8AbAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAbABsAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIAAwACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAZwByAGkAZAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAXAAiACMAMQBEAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEQAaQBzAHQAYQBuAGMAZQA/ACwAIABcACIAIwBEAEkAUwBUAEEATgBDAEUAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAFQAYQByAGcAZQB0AD8ALAAgAFwAIgAjAFQAQQBSAEcARQBUACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE0AZQBzAGgAIABnAHIAaQBkAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbgB0AGUAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEkATgBEAEUAWAAoAGkALAAgAHIALAAgAGMAKQAsACAAVABPAEMATwBMACgASQBGACgAYgBvAG8AbAAsACAAaQAsACAATgBBACgAKQApACwAIAAyACkAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAagAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABqACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBhAG0AbwBuAGQAIABtAGEAcwBrACAAKABNAGEAbgBoAGEAdAB0AGEAbgAgAGQAaQBzAHQAYQBuAGMAZQApAFwAbgAgACAAIAAgAG0AYQBzAGsALAAgACAAIABBAEIAUwAoAGkAIAAtACAAeAApACAAKwAgAEEAQgBTACgAagAgAC0AIAB5ACkAIAA8AD0AIABkAGkAcwB0AGEAbgBjAGUALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAGEAbgBkACAAcwBxAHUAZQBlAHoAZQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAUwBxAHUAZQBlAHoAZQC7AygASQBGACgAbQBhAHMAawAsACAAZwByAGkAZAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEcAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUABsAHUAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEMARwByAGkAZAC7AywAIABTAHEAdQBlAGUAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhACAAcABsAHUAcwARIHMAaABhAHAAZQBkACAAcgBlAGcAaQBvAG4AIAAoAGUAeAB0AGUAbgBkAGUAZAAgAHYAbwBuACAATgBlAHUAbQBhAG4AbgAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACkAIABmAHIAbwBtACAAYQAgADIARABcAG4AIAAgACAAIABhAHIAcgBhAHkAIABiAHkAIABzAHAAZQBjAGkAZgB5AGkAbgBnACAAdABoAGUAIABjAGUAbgB0AGUAcgAgAGEAbgBkACAAYQBuACAAZQB4AHQAZQBuAGQAIAB2AGEAbAB1AGUALgAgAFQAaABlACAAYwBlAG4AdABlAHIAIABtAGEAeQAgAGIAZQAgAGcAaQB2AGUAbgBcAG4AIAAgACAAIABhAHMAIABhACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGEAcwAgAGUAeABwAGwAaQBjAGkAdAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgAgAFQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAXABuACAAIAAgACAAcgBlAGcAaQBvAG4AIABwAHIAZQBzAGUAcgB2AGUAcwAgAGkAdABzACAAZwBlAG8AbQBlAHQAcgBpAGMAIABzAGgAYQBwAGUALAAgAGEAbgBkACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAbwBuAGwAeQBcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACAAYQByAGUAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAgACAAIAAgACAAIAAtACAAQwBlAG4AdABlAHIAIABvAGYAIAB0AGgAZQAgAHAAbAB1AHMALgAgAE0AYQB5ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgBcAG4AIAAgACAAIABlAHgAdABlAG4AZAAgACAAIAAgACAAIAAtACAAUgBhAGQAaQB1AHMAIABvAGYAIAB0AGgAZQAgAHAAbAB1AHMAIABhAHIAbQBzACAAKABtAHUAcwB0ACAAYgBlACAAYQAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAKQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdAC0AIABTAGMAYQBsAGEAcgAgAHUAcwBlAGQAIABvAHUAdABzAGkAZABlACAAdABoAGUAIABwAGwAdQBzAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAwAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFAAbAB1AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACwAXABuACAAIAAgACAAZQB4AHQAZQBuAGQALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAYQByAGcAZQB0ACAAaQBuAHQAZQByAHAAcgBlAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBJAF8ASgA/ACwAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUACgAdABhAHIAZwBlAHQAKQAgAD0AIAAyACwAXABuACAAIAAgACAAcgAsACAASQBGACgASQBzAEkAXwBKAD8ALAAgACAAIABUAEEASwBFACgAdABhAHIAZwBlAHQALAAgADEALAAgADEAKQAsACAAMAApACwAXABuACAAIAAgACAAYwAsACAASQBGACgASQBzAEkAXwBKAD8ALAAgACAAIABUAEEASwBFACgAdABhAHIAZwBlAHQALAAgAC0AMQAsACAALQAxACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAG8AbwBsAGUAYQBuACAAbQBhAHQAYwBoACAAZgBvAHIAIABzAGMAYQBsAGEAcgAgAHQAYQByAGcAZQB0AFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEYAQQBMAFMARQAsACAAZwByAGkAZAAgAD0AIAB0AGEAcgBnAGUAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBwAHUAdAAgAHYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAMQBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAFgATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARQB4AHQAZQBuAGQAPwAsACAATwBSACgASQBTAFQARQBYAFQAKABlAHgAdABlAG4AZAApACwAIABlAHgAdABlAG4AZAAgADwAIAAxACkALABcAG4AIAAgACAAIABOAG8AVABhAHIAZwBlAHQAPwAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAE4ATwBUACgATwBSACgAYgBvAG8AbAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAbABsAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgADAALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABnAHIAaQBkACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABcACIAIwAxAEQALQBBAFIAUgBBAFkAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQARQB4AHQAZQBuAGQAPwAsACAAXAAiACMARQBYAFQARQBOAEQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAFQAYQByAGcAZQB0AD8ALAAgAFwAIgAjAFQAQQBSAEcARQBUACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE0AZQBzAGgAIABnAHIAaQBkAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbgB0AGUAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEkATgBEAEUAWAAoAGkALAAgAHIALAAgAGMAKQAsACAAVABPAEMATwBMACgASQBGACgAYgBvAG8AbAAsACAAaQAsACAATgBBACgAKQApACwAIAAyACkAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAagAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABqACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAbAB1AHMAIABtAGEAcwBrACAAKABoAG8AcgBpAHoAbwBuAHQAYQBsACAAKwAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgBtAHMAKQBcAG4AIAAgACAAIABtAGEAcwBrACwAIAAgACAAKABpACAAPQAgAHgAKQAgACoAIAAoAEEAQgBTACgAagAgAC0AIAB5ACkAIAA8AD0AIABlAHgAdABlAG4AZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABqACAAPQAgAHkAKQAgACoAIAAoAEEAQgBTACgAaQAgAC0AIAB4ACkAIAA8AD0AIABlAHgAdABlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABhAG4AZAAgAHMAcQB1AGUAZQB6AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAFMAcQB1AGUAZQB6AGUAuwMoAEkARgAoAG0AYQBzAGsALAAgAGcAcgBpAGQALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBHADAANABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFAAeQByAGEAbQBpAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABNAEcAcgBpAGQAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAG8AbgBlACAAbwBmACAAZgBvAHUAcgAgAHQAcgBpAGEAbgBnAHUAbABhAHIAIABcACIAcAB5AHIAYQBtAGkAZABcACIAIAByAGUAZwBpAG8AbgBzACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAaQBsAGUAXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBpAG4AZwAgAHMAaABhAHAAZQAuACAAUAB5AHIAYQBtAGkAZAAgAHIAZQBnAGkAbwBuAHMAIABhAHIAZQAgAGQAZQBmAGkAbgBlAGQAIAB1AHMAaQBuAGcAIAByAG8AdwAvAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGcAZQBuAGUAcgBhAHQAZQBkACAAYgB5ACAATQBHAHIAaQBkALsDLgAgAEEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAIABjAG8AbgB0AHIAbwBsAHMAIAB3AGgAYQB0ACAAYQBwAHAAZQBhAHIAcwAgAG8AdQB0AHMAaQBkAGUAIAB0AGgAZQBcAG4AIAAgACAAIABzAGUAbABlAGMAdABlAGQAIAByAGUAZwBpAG8AbgAuAFwAbgBcAG4AIAAgACAAIABQAHkAcgBhAG0AaQBkACAAcABpAGUAYwBlAHMAIAAoAGMAbABvAGMAawB3AGkAcwBlACkAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAtACAAVQBwAHAAZQByACAAcgBpAGcAaAB0AFwAbgAgACAAIAAgACAAIAAgACAAMgAgAC0AIABMAG8AdwBlAHIAIAByAGkAZwBoAHQAXABuACAAIAAgACAAIAAgACAAIAAzACAALQAgAEwAbwB3AGUAcgAgAGwAZQBmAHQAXABuACAAIAAgACAAIAAgACAAIAA0ACAALQAgAFUAcABwAGUAcgAgAGwAZQBmAHQAXABuAFwAbgAgACAAIAAgAFAAeQByAGEAbQBpAGQAIABlAHgAdAByAGEAYwB0AGkAbwBuAHMAIABhAHIAZQAgAG0AbwBzAHQAIABtAGUAYQBuAGkAbgBnAGYAdQBsACAAbwBuACAAcwBxAHUAYQByAGUAIABvAHIAIABuAGUAYQByABEgcwBxAHUAYQByAGUAIABtAGEAdAByAGkAYwBlAHMALgBcAG4AIAAgACAAIABPAG4AIAB0AGEAbABsACAAbwByACAAbgBhAHIAcgBvAHcAIABtAGEAdAByAGkAYwBlAHMALAAgAHQAaABlACAAcgBlAHMAdQBsAHQAaQBuAGcAIABzAGgAYQBwAGUAcwAgAG0AYQB5ACAAYgBlACAAdgBpAHMAdQBhAGwAbAB5ACAAcwBrAGUAdwBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdwBoAGkAYwBoACAAdABvACAAZQB4AHQAcgBhAGMAdAAgAHQAaABlACAAcgBlAGcAaQBvAG4ALgBcAG4AIAAgACAAIABbAHAAaQBlAGMAZQBdACAAIAAgACAAIAAgAC0AIABJAG4AdABlAGcAZQByACAAMQATIDQAIABzAGUAbABlAGMAdABpAG4AZwAgAHQAaABlACAAcAB5AHIAYQBtAGkAZAAgAHIAZQBnAGkAbwBuAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAxAC4AXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0AIAAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAcgBlAGcAaQBvAG4ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAFwAIgBcACIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUAB5AHIAYQBtAGkAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAHAAaQBlAGMAZQBdACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGUAIABwAGkAZQBjAGUAXABuACAAIAAgACAAcABpAGUAYwBlACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGkAZQBjAGUAKQAsACAAMQAsACAAcABpAGUAYwBlACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAFAAaQBlAGMAZQA/ACwAIABPAFIAKABwAGkAZQBjAGUAIAA8ACAAMQAsACAAcABpAGUAYwBlACAAPgAgADQALAAgAEkAUwBUAEUAWABUACgAcABpAGUAYwBlACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAbABsAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIABcACIAXAAiACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABQAGkAZQBjAGUAPwAsACAAXAAiACMAUABJAEUAQwBFACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGEAcgByAGEAeQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAeQByAGEAbQBpAGQAIABtAGEAcwBrAHMAIAAoAGMAbABvAGMAawB3AGkAcwBlACkAXABuACAAIAAgACAAdQBwAHAAZQByAF8AcgBpAGcAaAB0ACwAIABpACAAPAA9ACAAagAsACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAMQBcAG4AIAAgACAAIABsAG8AdwBlAHIAXwByAGkAZwBoAHQALAAgAGkAIAArACAAagAgAD4APQAgAGgAIAArACAAMQAsACAAIAAvAC8AIAAyAFwAbgAgACAAIAAgAGwAbwB3AGUAcgBfAGwAZQBmAHQALAAgACAAaQAgAD4APQAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgADMAXABuACAAIAAgACAAdQBwAHAAZQByAF8AbABlAGYAdAAsACAAIABpACAAKwAgAGoAIAA8AD0AIABoACAAKwAgADEALAAgACAALwAvACAANABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIAByAGUAZwBpAG8AbgBcAG4AIAAgACAAIABtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgAEkARgAoAHAAaQBlAGMAZQAgAD0AIAAxACwAIAB1AHAAcABlAHIAXwByAGkAZwBoAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHAAaQBlAGMAZQAgAD0AIAAyACwAIABsAG8AdwBlAHIAXwByAGkAZwBoAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcABpAGUAYwBlACAAPQAgADMALAAgAGwAbwB3AGUAcgBfAGwAZQBmAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHUAcABwAGUAcgBfAGwAZQBmAHQAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAbQBhAHMAawBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgAEkARgAoAG0AYQBzAGsALAAgAGEAcgByAGEAeQAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBHADAANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFIAaQBuAGcAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABNAEcAcgBpAGQAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAIABzAGkAbgBnAGwAZQAgAHIAaQBuAGcAIAAoAGwAYQB5AGUAcgApACAAZgByAG8AbQAgAGEAIAAyAEQAIABnAHIAaQBkACAAdwBoAGkAbABlACAAcAByAGUAcwBlAHIAdgBpAG4AZwAgAHQAaABlACAAbwB2AGUAcgBhAGwAbABcAG4AIAAgACAAIABzAGgAYQBwAGUAIABvAGYAIAB0AGgAZQAgAGcAcgBpAGQALgAgAEwAYQB5AGUAcgAgADEAIABjAG8AcgByAGUAcwBwAG8AbgBkAHMAIAB0AG8AIAB0AGgAZQAgAG8AdQB0AGUAcgBtAG8AcwB0ACAAcABlAHIAaQBtAGUAdABlAHIALAAgAGEAbgBkACAAaABpAGcAaABlAHIAXABuACAAIAAgACAAbABhAHkAZQByAHMAIABtAG8AdgBlACAAaQBuAHcAYQByAGQALgAgAFQAaABlACAAbwB1AHQAcAB1AHQAIABhAGwAdwBhAHkAcwAgAG0AYQB0AGMAaABlAHMAIAB0AGgAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABvAGYAIAB0AGgAZQAgAGkAbgBwAHUAdABcAG4AIAAgACAAIABnAHIAaQBkACwAIAB3AGkAdABoACAAYQBsAGwAIABuAG8AbgARIHIAaQBuAGcAIABjAGUAbABsAHMAIABmAGkAbABsAGUAZAAgAHUAcwBpAG4AZwAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAcgBlAHAAcgBlAHMAZQBuAHQAaQBuAGcAIAB0AGgAZQAgAGYAdQBsAGwAIABnAHIAaQBkAC4AXABuACAAIAAgACAAbABhAHkAZQByACAAIAAgACAAIAAgACAALQAgAEkAbgB0AGUAZwBlAHIAIABlIiAAMQAgAHMAcABlAGMAaQBmAHkAaQBuAGcAIAB3AGgAaQBjAGgAIAByAGkAbgBnACAAdABvACAAZQB4AHQAcgBhAGMAdAAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGEAeQBlAHIAcwAgAGUAeABjAGUAZQBkAGkAbgBnACAAdABoAGUAIABpAG4AbgBlAHIAbQBvAHMAdAAgAHIAaQBuAGcAIAByAGUAdAB1AHIAbgAgAFwAIgAjAE0AQQBYAC0ATABBAFkARQBSADoAIABuAFwAIgAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdAC0AIABTAGMAYQBsAGEAcgAgAHUAcwBlAGQAIAB0AG8AIABmAGkAbABsACAAbgBvAG4AESByAGkAbgBnACAAYwBlAGwAbABzAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAwAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVABoAGkAcwAgAGYAdQBuAGMAdABpAG8AbgAgAHAAZQByAGYAbwByAG0AcwAgAG4AbwAgAHIAbwB0AGEAdABpAG8AbgA7ACAAaQB0ACAAbwBuAGwAeQAgAGUAeAB0AHIAYQBjAHQAcwAgAHQAaABlACAAcgBpAG4AZwAgAG0AYQBzAGsALgBcAG4AIAAgACAAIAAiICAARABlAGcAZQBuAGUAcgBhAHQAZQAgAHIAaQBuAGcAcwAgACgAMQDXAE4ALAAgAE4A1wAxACwAIAAyANcATgAsACAAZQB0AGMALgApACAAYQByAGUAIABwAHIAZQBzAGUAcgB2AGUAZAAgAGUAeABhAGMAdABsAHkALgBcAG4AIAAgACAAIAAiICAAUgBpAG4AZwBSAG8AdABhAHQAZQC7AyAAYQBuAGQAIABSAGkAbgBnAFIAbwB0AGEAdABlAFIAZQB2ALsDIAByAGUAbAB5ACAAbwBuACAAUgBpAG4AZwC7AyAAdABvACAAaQBkAGUAbgB0AGkAZgB5ACAAcgBpAG4AZwAgAGIAbwB1AG4AZABhAHIAaQBlAHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBpAG4AZwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAbABhAHkAZQByACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABnAHIAaQBkACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQATABhAHkAZQByAD8ALAAgAE8AUgAoAEkAUwBUAEUAWABUACgAbABhAHkAZQByACkALAAgAGwAYQB5AGUAcgAgADwAPQAgADAAKQAsAFwAbgAgACAAIAAgAE0AYQB4AEwAYQB5AGUAcgAsACAAIAAgACAAIAAgAEkATgBUACgAKABNAEkATgAoAGgALAAgAHcAKQAgACsAIAAxACkAIAAvACAAMgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABMAGEAeQBlAHIAPwAsACAAXAAiACMATABBAFkARQBSACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGwAYQB5AGUAcgAgAD4AIABNAGEAeABMAGEAeQBlAHIALAAgAFwAIgAjAE0AQQBYAC0ATABBAFkARQBSADoAIABcACIAIAAmACAATQBhAHgATABhAHkAZQByACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAGwAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ARwByAGkAZAC7AygAZwByAGkAZAApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGkAbgBnACAAZQBkAGcAZQBzAFwAbgAgACAAIAAgAHQAbwBwACwAIAAgACAAIAAgACAAIAAgACAAKAAoAGkAIAA9ACAAbABhAHkAZQByACkAIAArACAAKABpACAAPQAgADEAIAArACAAaAAgAC0AIABsAGEAeQBlAHIAKQApACAAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAKABqACAAPgAgAGwAYQB5AGUAcgAgAC0AIAAxACkAIAAqACAAKABqACAAPAA9ACAAMQAgACsAIAB3ACAALQAgAGwAYQB5AGUAcgApACkALABcAG4AXABuACAAIAAgACAAcwBpAGQAZQAsACAAIAAgACAAIAAgACAAIAAoACgAagAgAD0AIABsAGEAeQBlAHIAKQAgACsAIAAoAGoAIAA9ACAAMQAgACsAIAB3ACAALQAgAGwAYQB5AGUAcgApACkAIAAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKAAoAGkAIAA+ACAAbABhAHkAZQByACAALQAgADEAKQAgACoAIAAoAGkAIAA8AD0AIAAxACAAKwAgAGgAIAAtACAAbABhAHkAZQByACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbQBiAGkAbgBlAGQAIAByAGkAbgBnACAAbQBhAHMAawBcAG4AIAAgACAAIABtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKAB0AG8AcAAgACsAIABzAGkAZABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAbQBhAHMAawBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgAEkARgAoAG0AYQBzAGsALAAgAGcAcgBpAGQALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADYAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAHEAdQBhAHIAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEMARwByAGkAZAC7AywAIABTAHEAdQBlAGUAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhACAAcwBxAHUAYQByAGUAESBzAGgAYQBwAGUAZAAgAHIAZQBnAGkAbwBuACAAKABDAGgAZQBiAHkAcwBoAGUAdgAgAHIAYQBkAGkAdQBzACkAIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGIAeQBcAG4AIAAgACAAIABzAHAAZQBjAGkAZgB5AGkAbgBnACAAdABoAGUAIABjAGUAbgB0AGUAcgAgAGEAbgBkACAAYQBuACAAZQB4AHQAZQBuAGQAIAB2AGEAbAB1AGUALgAgAFQAaABlACAAYwBlAG4AdABlAHIAIABtAGEAeQAgAGIAZQAgAGcAaQB2AGUAbgAgAGEAcwAgAGEAXABuACAAIAAgACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGEAcwAgAGUAeABwAGwAaQBjAGkAdAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgAgAFQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgBcAG4AIAAgACAAIABwAHIAZQBzAGUAcgB2AGUAcwAgAGkAdABzACAAZwBlAG8AbQBlAHQAcgBpAGMAIABzAGgAYQBwAGUALAAgAGEAbgBkACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAbwBuAGwAeQAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAXABuACAAIAAgACAAYQByAGUAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAgACAAIAAgACAAIAAtACAAQwBlAG4AdABlAHIAIABvAGYAIAB0AGgAZQAgAHMAcQB1AGEAcgBlAC4AIABNAGEAeQAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAgAGMAcgBpAHQAZQByAGkAbwBuACAAbwByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIAB0AGgAZQAgAGYAbwByAG0AIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AXABuACAAIAAgACAAZQB4AHQAZQBuAGQAIAAgACAAIAAgACAALQAgAEMAaABlAGIAeQBzAGgAZQB2ACAAcgBhAGQAaQB1AHMAIABvAGYAIAB0AGgAZQAgAHMAcQB1AGEAcgBlACAAKABtAHUAcwB0ACAAYgBlACAAYQAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAKQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdAC0AIABTAGMAYQBsAGEAcgAgAHUAcwBlAGQAIABvAHUAdABzAGkAZABlACAAdABoAGUAIABzAHEAdQBhAHIAZQAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHEAdQBhAHIAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAdABhAHIAZwBlAHQALABcAG4AIAAgACAAIABlAHgAdABlAG4AZAAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABnAHIAaQBkACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABhAHIAZwBlAHQAIABpAG4AdABlAHIAcAByAGUAdABhAHQAaQBvAG4AXABuACAAIAAgACAASQBzAEkAXwBKAD8ALAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAKAB0AGEAcgBnAGUAdAApACAAPQAgADIALABcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABUAEEASwBFACgAdABhAHIAZwBlAHQALAAgADEALAAgADEAKQAsACAAMAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAtADEALAAgAC0AMQApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBvAG8AbABlAGEAbgAgAG0AYQB0AGMAaAAgAGYAbwByACAAcwBjAGEAbABhAHIAIAB0AGEAcgBnAGUAdABcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAGcAcgBpAGQAIAA9ACAAdABhAHIAZwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABYAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEUAeAB0AGUAbgBkAD8ALAAgAE8AUgAoAEkAUwBUAEUAWABUACgAZQB4AHQAZQBuAGQAKQAsACAAZQB4AHQAZQBuAGQAIAA8ACAAMQApACwAXABuACAAIAAgACAATgBvAFQAYQByAGcAZQB0AD8ALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABOAE8AVAAoAE8AUgAoAGIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAbABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIAAwACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAZwByAGkAZAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAXAAiACMAMQBEAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEUAeAB0AGUAbgBkAD8ALAAgAFwAIgAjAEUAWABUAEUATgBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBUAGEAcgBnAGUAdAA/ACwAIABcACIAIwBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbgB0AGUAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABpACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABqACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGoALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBxAHUAYQByAGUAIABtAGEAcwBrACAAKABDAGgAZQBiAHkAcwBoAGUAdgAgAGQAaQBzAHQAYQBuAGMAZQApAFwAbgAgACAAIAAgAG0AYQBzAGsALAAgACAAIAAgACAAIAAgACAAKABBAEIAUwAoAGkAIAAtACAAeAApACAAPAA9ACAAZQB4AHQAZQBuAGQAKQAgACoAIAAoAEEAQgBTACgAagAgAC0AIAB5ACkAIAA8AD0AIABlAHgAdABlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABhAG4AZAAgAHMAcQB1AGUAZQB6AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABTAHEAdQBlAGUAegBlALsDKABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABUAHIAaQBhAG4AZwBsAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAGQAaQByAGUAYwB0AGkAbwBuAGEAbAAgAHQAcgBpAGEAbgBnAHUAbABhAHIAIAByAGUAZwBpAG8AbgAgACgAdQBwAHAAZQByACAAbwByACAAbABvAHcAZQByACkAIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGIAeQBcAG4AIAAgACAAIABzAHAAZQBjAGkAZgB5AGkAbgBnACAAdABoAGUAIABjAGUAbgB0AGUAcgAgAGEAbgBkACAAYQAgAE0AYQBuAGgAYQB0AHQAYQBuACAAcgBhAGQAaQB1AHMALgAgAFQAaABlACAAYwBlAG4AdABlAHIAIABtAGEAeQAgAGIAZQAgAGcAaQB2AGUAbgAgAGEAcwAgAGEAXABuACAAIAAgACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGEAcwAgAGUAeABwAGwAaQBjAGkAdAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgAgAFQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgBcAG4AIAAgACAAIABwAHIAZQBzAGUAcgB2AGUAcwAgAGkAdABzACAAZwBlAG8AbQBlAHQAcgBpAGMAIABzAGgAYQBwAGUALAAgAGEAbgBkACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAbwBuAGwAeQAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAXABuACAAIAAgACAAYQByAGUAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAgACAAIAAgACAAIAAtACAAQwBlAG4AdABlAHIAIABvAGYAIAB0AGgAZQAgAHQAcgBpAGEAbgBnAGwAZQAuACAATQBhAHkAIABiAGUAIABhACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBmACAAdABoAGUAIABmAG8AcgBtACAAewByAG8AdwAsACAAYwBvAGwAfQAuAFwAbgAgACAAIAAgAHIAYQBkAGkAdQBzACAAIAAgACAAIAAgAC0AIABNAGEAbgBoAGEAdAB0AGEAbgAgAHIAYQBkAGkAdQBzACAAbwBmACAAdABoAGUAIAB0AHIAaQBhAG4AZwBsAGUAIAAoAG0AdQBzAHQAIABiAGUAIABhACAAcABvAHMAaQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgApAC4AXABuACAAIAAgACAAWwBiAGUAbABvAHcAXQAgACAAIAAgACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAGwAbwB3AGUAcgAgAHQAcgBpAGEAbgBnAGwAZQA7ACAAaQBmACAAbwBtAGkAdAB0AGUAZAAsACAAcgBlAHQAdQByAG4AcwAgAHUAcABwAGUAcgAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdAC0AIABTAGMAYQBsAGEAcgAgAHUAcwBlAGQAIABvAHUAdABzAGkAZABlACAAdABoAGUAIAB0AHIAaQBhAG4AZwBsAGUALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADAALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVAByAGkAYQBuAGcAbABlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAsAFwAbgAgACAAIAAgAHIAYQBkAGkAdQBzACwAXABuACAAIAAgACAAWwBiAGUAbABvAHcAXQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABnAHIAaQBkACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABhAHIAZwBlAHQAIABpAG4AdABlAHIAcAByAGUAdABhAHQAaQBvAG4AXABuACAAIAAgACAASQBzAEkAXwBKAD8ALAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAKAB0AGEAcgBnAGUAdAApACAAPQAgADIALABcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABUAEEASwBFACgAdABhAHIAZwBlAHQALAAgADEALAAgADEAKQAsACAAMAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAtADEALAAgAC0AMQApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBvAG8AbABlAGEAbgAgAG0AYQB0AGMAaAAgAGYAbwByACAAcwBjAGEAbABhAHIAIAB0AGEAcgBnAGUAdABcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAGcAcgBpAGQAIAA9ACAAdABhAHIAZwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABYAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAFIAYQBkAGkAdQBzAD8ALAAgAE8AUgAoAEkAUwBUAEUAWABUACgAcgBhAGQAaQB1AHMAKQAsACAAcgBhAGQAaQB1AHMAIAA8ACAAMQApACwAXABuACAAIAAgACAATgBvAFQAYQByAGcAZQB0AD8ALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABOAE8AVAAoAE8AUgAoAGIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIAAwACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AIAAgACAAIABJAHMAQQBiAG8AdgBlAD8ALAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYgBlAGwAbwB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAZwByAGkAZAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAXAAiACMAMQBEAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFIAYQBkAGkAdQBzAD8ALAAgAFwAIgAjAFIAQQBEAEkAVQBTACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBUAGEAcgBnAGUAdAA/ACwAIABcACIAIwBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbgB0AGUAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABpACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABqACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGoALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AIABtAGEAcwBrAFwAbgAgACAAIAAgAGQAaQByACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEEAYgBvAHYAZQA/ACwAIAAoAGkAIAA8AD0AIAB4ACkALAAgACgAaQAgAD4APQAgAHgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAcgBpAGEAbgBnAGwAZQAgAG0AYQBzAGsAIAAoAE0AYQBuAGgAYQB0AHQAYQBuACAAZABpAHMAdABhAG4AYwBlACAAKwAgAGQAaQByAGUAYwB0AGkAbwBuACkAXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACAAIAAgACAAIAAoAEEAQgBTACgAaQAgAC0AIAB4ACkAIAArACAAQQBCAFMAKABqACAALQAgAHkAKQAgADwAPQAgAHIAYQBkAGkAdQBzACkAIAAqACAAZABpAHIALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAGEAbgBkACAAcwBxAHUAZQBlAHoAZQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgAFMAcQB1AGUAZQB6AGUAuwMoAEkARgAoAG0AYQBzAGsALAAgAGcAcgBpAGQALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AIwAjACAAMAAzACAALQAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AIAAqAC8AXABuAFwAbgAvACoAXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAaABhAHAAaQBuAGcAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHIAZQBzAGgAYQBwAGUALAAgAHIAZQBzAGkAegBlACwAIAB3AHIAYQBwACwAIABwAGEAZAAsACAAdAByAGEAdgBlAHIAcwBlACwAIABvAHIAIAByAGUAZgBsAG8AdwAgAGcAcgBpAGQAcwAgAHcAaABpAGwAZQBcAG4AIAAgACAAIABwAHIAZQBzAGUAcgB2AGkAbgBnACAAdABoAGUAIABzAHQAcgB1AGMAdAB1AHIAZQAgAG8AZgAgAHQAaABlACAAdQBuAGQAZQByAGwAeQBpAG4AZwAgAGQAYQB0AGEALgBcAG4AXABuACAAIAAgACAAUwB1AGIAIABjAGEAdABlAGcAbwByAGkAZQBzADoAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEMAbwByAGUAIABTAGgAYQBwAGkAbgBnACAAUAByAGkAbQBpAHQAaQB2AGUAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBTAGgAYQBwAGUAMgBEALsDLAAgAFIAZQBzAGkAegBlALsDLAAgAFMAYwBhAG4AMgBEALsDLAAgAFQAcgBhAHYAZQByAHMAZQC7AywAIABUAGEAawBlAEIAbABvAGMAawC7AywAIABEAFMAdABhAGMAawC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABSAGUAZgBsAG8AdwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFcAcgBhAHAAUgBvAHcAcwAyAEQAuwMsACAAVwByAGEAcABDAG8AbABzADIARAC7AywAIABTAHQAYQBpAHIAYwBhAHMAZQC7AywAIABVAG4AUABpAHYAbwB0ALsDLAAgAFoAaQBwALsDLAAgAFMAbABpAGMAZQBCAHkARABlAGcAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUABhAGQAZABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAYQBkALsDLAAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDLAAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEkAbgB0AGUAcgBwAG8AbABhAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAGEAZwBuAGkAZgB5ALsDLAAgAFoAbwBvAG0AuwNcAG4AXABuACAAIAAgACAAQQBsAGwAIABzAGgAYQBwAGkAbgBnACAAZgB1AG4AYwB0AGkAbwBuAHMAIABwAHIAZQBzAGUAcgB2AGUAIAAyAEQAIABnAGUAbwBtAGUAdAByAHkAIABhAG4AZAAgAHIAZQB0AHUAcgBuACAAYQByAHIAYQB5AHMAIAB3AGgAbwBzAGUAIABzAHQAcgB1AGMAdAB1AHIAZQBcAG4AIAAgACAAIABpAHMAIABlAHgAcABsAGkAYwBpAHQAbAB5ACAAZABlAGYAaQBuAGUAZAAgAGIAeQAgAHQAaABlACAAdAByAGEAbgBzAGYAbwByAG0AYQB0AGkAbwBuACAAcgB1AGwAZQBzAC4AXABuACoALwBcAG4AXABuAFwAbgBcAG4ALwAvACAAIABDAG8AcgBlACAAUwBoAGEAcABpAG4AZwAgAFAAcgBpAG0AaQB0AGkAdgBlAHMAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFIAZQBTAGgAYQBwAGUAMgBEALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHMAaABhAHAAZQBzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABhACAAbgBlAHcAIABjAG8AbAB1AG0AbgAgAHcAaQBkAHQAaAAgAHUAcwBpAG4AZwAgAHIAbwB3ABEgbQBhAGoAbwByACAAbwByAGQAZQByAC4AIABBAGwAbAAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgAGEAcgBlACAAcAByAGUAcwBlAHIAdgBlAGQAIABpAG4AIAByAGUAYQBkAGkAbgBnACAAbwByAGQAZQByACwAIABhAG4AZAAgAHQAaABlACAAZgBpAG4AYQBsACAAYgBsAG8AYwBrACAAaQBzACAAcABhAGQAZABlAGQAIABpAGYAIABuAGUAZQBkAGUAZAAuAFwAbgAgACAAIAAgAE8AbgBlABEgZABpAG0AZQBuAHMAaQBvAG4AYQBsACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHIAZQBqAGUAYwB0AGUAZAAuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQA6AFwAbgAgACAAIAAgAEkAbgBwAHUAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAewAxACwAMgAsADMALAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgADUALAA2ACwANwAsADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAOQAsADEAMAAsADEAMQAsADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAxADMALAAxADQALAAxADUALAAxADYAfQBcAG4AXABuACAAIAAgACAAPQBSAGUAUwBoAGEAcABlADIARAC7AygAYQByAHIAYQB5ACwAIAAyACkAXABuAFwAbgAgACAAIAAgAE8AdQB0AHAAdQB0ADoAXABuACAAIAAgACAAIAAgACAAIAB7ADEALAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgADMALAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgADUALAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgADcALAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgADkALAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMQAxACwAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgADEAMwAsADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAxADUALAAxADYAfQBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIAByAGUAcwBoAGEAcABlAC4AIABPAG4AZQARIGQAaQBtAGUAbgBzAGkAbwBuAGEAbAAgAGEAcgByAGEAeQBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQALgBcAG4AIAAgACAAIABuAGUAdwBfAHcAaQBkAHQAaAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABpAG4AIAB0AGgAZQAgAHIAZQBzAGgAYQBwAGUAZAAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAdABvACAAZgBpAGwAbAAgAGkAbgBjAG8AbQBwAGwAZQB0AGUAIABmAGkAbgBhAGwAIAByAG8AdwBzAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABOAEEAKAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHMAaABhAHAAaQBuAGcAIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAAgAHMAdAByAGkAYwB0AGwAeQAgAGkAbgAgAHIAbwB3ABEgbQBhAGoAbwByACAAbwByAGQAZQByAC4AXABuACAAIAAgACAAIiAgAG4AZQB3AF8AdwBpAGQAdABoACAAbQB1AHMAdAAgAGIAZQAgAGwAZQBzAHMAIAB0AGgAYQBuACAAbwByACAAZQBxAHUAYQBsACAAdABvACAAdABoAGUAIABvAHIAaQBnAGkAbgBhAGwAIAB3AGkAZAB0AGgALgBcAG4AIAAgACAAIAAiICAAVABoAGkAcwAgAGYAdQBuAGMAdABpAG8AbgAgAGQAbwBlAHMAIABuAG8AdAAgAGYAbABhAHQAdABlAG4AIABvAHIAIAByAGUAESB3AHIAYQBwACAAMQBEACAAYQByAHIAYQB5AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBlAFMAaABhAHAAZQAyAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAbgBlAHcAXwB3AGkAZAB0AGgALABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAG4AZQB3AF8AaABlAGkAZwBoAHQALAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAEMATwBVAE4AVABBACgAYQByAHIAYQB5ACkAIAAvACAAbgBlAHcAXwB3AGkAZAB0AGgALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgAHAAYQBkAF8AdwBpAHQAaAAsACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGEAZABfAHcAaQB0AGgAKQAsACAATgBBACgAKQAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABXAGkAZAB0AGgALAAgACAAIABuAGUAdwBfAHcAaQBkAHQAaAAgAD4AIAB3ACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBlAGMAdABvAHIAIABoAGEAbgBkAGwAaQBuAGcAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABYAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAIAAgAGgAIAA+ACAAdwAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABhAHIAcgBhAHkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABXAGkAZAB0AGgALAAgAFwAIgAjAFcASQBEAFQASAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABDAEUASQBMAEkATgBHACgAUwBFAFEAVQBFAE4AQwBFACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAbgBlAHcAXwB3AGkAZAB0AGgAKQAgAC8AIAB3ACwAIAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABtAG8AZAB1AGwAbwAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgATQBPAEQAKABTAEUAUQBVAEUATgBDAEUAKABuAGUAdwBfAGgAZQBpAGcAaAB0ACwAIABuAGUAdwBfAHcAaQBkAHQAaAApACwAIAB3ACkAKQAsAFwAbgBcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgAbQBvAGQAdQBsAG8AKAApACAAPQAgADAALAAgAHcALAAgAG0AbwBkAHUAbABvACgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUAByAGUAcwBlAG4AdABcAG4AIAAgACAAIAByAGUAcwBoAGEAcABlAGQALAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAGkAKAApACwAIABqACgAKQApACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwBoAGEAcABlAGQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADAAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHAAZQBhAHQAcwAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIAB2AGUAcgB0AGkAYwBhAGwAbAB5ACAAYQBuAGQALwBvAHIAIABoAG8AcgBpAHoAbwBuAHQAYQBsAGwAeQAgAGIAeQAgAGkAbgB0AGUAZwBlAHIAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzAC4AXABuACAAIAAgACAAVQBzAGUAcgBzACAAbQBhAHkAIABzAHAAZQBjAGkAZgB5ACAAaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAAsACAAbwByACAAYgBvAHQAaAAuACAASQBmACAAZQBpAHQAaABlAHIAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGkAcwAgAG8AbQBpAHQAdABlAGQALABcAG4AIAAgACAAIAB0AGgAZQAgAG8AbQBpAHQAdABlAGQAIABkAGkAbQBlAG4AcwBpAG8AbgAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADEALgAgAEcAZQBvAG0AZQB0AHIAeQAgAGkAcwAgAHAAcgBlAHMAZQByAHYAZQBkADsAIABuAG8AIABmAGwAYQB0AHQAZQBuAGkAbgBnAFwAbgAgACAAIAAgAG8AYwBjAHUAcgBzAC4AXABuAFwAbgBFAHgAYQBtAHAAbABlADoAXABuACAAIAAgACAASQBuAHAAdQB0ADoAXABuACAAIAAgACAAIAAgACAAIAB7ADEALAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgADMALAA0AH0AXABuAFwAbgAgACAAIAAgAD0AUgBlAHMAaQB6AGUAuwMoAGEAcgByAGEAeQAsACAAMgAsACAAMwApAFwAbgBcAG4AIAAgACAAIABPAHUAdABwAHUAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAewAxACwAMgAsADEALAAyACwAMQAsADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMwAsADQALAAzACwANAAsADMALAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgADEALAAyACwAMQAsADIALAAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAzACwANAAsADMALAA0ACwAMwAsADQAfQBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIAByAGUAcABlAGEAdABlAGQALgBcAG4AIAAgACAAIABbAGgAZQBpAGcAaAB0AF0AIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAB2AGUAcgB0AGkAYwBhAGwAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdAAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMQAuAFwAbgAgACAAIAAgAFsAdwBpAGQAdABoAF0AIAAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGgAbwByAGkAegBvAG4AdABhAGwAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdAAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQBwAGUAdABpAHQAaQBvAG4AIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAAgAHYAaQBhACAAaQBuAGQAZQB4ACAAcgBlAG0AYQBwAHAAaQBuAGcALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABnAGUAbwBtAGUAdAByAHkAIABpAHMAIAAoAGgAIADXACAAaABlAGkAZwBoAHQAKQAgAGIAeQAgACgAdwAgANcAIAB3AGkAZAB0AGgAKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBSAGUAcwBpAHoAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGgAZQBpAGcAaAB0AF0ALABcAG4AIAAgACAAIABbAHcAaQBkAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAG0AaQBzAHMAaQBvAG4AIABjAGgAZQBjAGsAcwBcAG4AIAAgACAAIABIAGUAaQBnAGgAdABPAG0AaQB0AHQAZQBkAD8ALAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABoAGUAaQBnAGgAdAApACwAXABuACAAIAAgACAAVwBpAGQAdABoAE8AbQBpAHQAdABlAGQAPwAsACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAdwBpAGQAdABoACkALABcAG4AIAAgACAAIABOAG8ASABXAEkAbgBwAHUAdAA/ACwAIAAgACAAIAAgACAASABlAGkAZwBoAHQATwBtAGkAdAB0AGUAZAA/ACAAKwAgAFcAaQBkAHQAaABPAG0AaQB0AHQAZQBkAD8AIAA9ACAAMgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBhAHUAbAB0ACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAsACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgATgBvAEgAVwBJAG4AcAB1AHQAPwAsACAASABlAGkAZwBoAHQATwBtAGkAdAB0AGUAZAA/ACkALAAgADEALAAgAGgAZQBpAGcAaAB0ACkALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgATgBvAEgAVwBJAG4AcAB1AHQAPwAsACAAVwBpAGQAdABoAE8AbQBpAHQAdABlAGQAPwApACwAIAAxACwAIAB3AGkAZAB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABOAG8AUgBlAHAAZQBhAHQAPwAsACAAIAAgACAAIAAgACAAQQBOAEQAKABoAGUAaQBnAGgAdAAgAD0AIAAxACwAIAB3AGkAZAB0AGgAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEUAeABwAGEAbgBkAFMAYwBhAGwAYQByACwAIAAgACAAIABFAFgAUABBAE4ARAAoAGEAcgByAGEAeQAsACAAaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAAsACAAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABSAGUAcABlAGEAdAA/ACwAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAaABlAGkAZwBoAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAHcAaQBkAHQAaAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAEEATgBEACgASQBTAE4AVQBNAEIARQBSACgAaABlAGkAZwBoAHQAKQAsACAAaABlAGkAZwBoAHQAIAA8AD0AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKAB3AGkAZAB0AGgAKQAsACAAIAB3AGkAZAB0AGgAIAA8AD0AIAAwACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgATgBvAFIAZQBwAGUAYQB0AD8ALAAgAGEAcgByAGEAeQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABFAHgAcABhAG4AZABTAGMAYQBsAGEAcgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABSAGUAcABlAGEAdAA/ACwAIABhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARQB4AHAAYQBuAGQAZQBkACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaAAgACoAIABoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgAGsAgiAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB3ACAAKgAgAHcAaQBkAHQAaAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAAxACAAKwAgAE0ATwBEACgAUwBFAFEAVQBFAE4AQwBFACgAawAsACwAMAAsACkALAAgAGgAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAawCCICwAIAAxACwAIAAwACkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoADEAIAArACAATQBPAEQAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAawCCICwAIAAwACkALAAgAHcAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKABrACwALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBuAHMAdAByAHUAYwB0ACAAcgBlAHAAZQBhAHQAZQBkACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAGkAKAApACwAIABqACgAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADMAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAGMAYQBuADIARAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFIAZQBTAGgAYQBwAGUAMgBEALsDLAAgAFQAcgBhAHYAZQByAHMAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQAgAHQAcgBhAHYAZQByAHMAYQBsABEgYQB3AGEAcgBlACAAMgBEACAAcwBjAGEAbgBuAGkAbgBnACAAbwBwAGUAcgBhAHQAbwByACAAdABoAGEAdAAgAGUAeAB0AGUAbgBkAHMAIABFAHgAYwBlAGwAGSBzACAAbgBhAHQAaQB2AGUAIABTAEMAQQBOAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAuACAAUwBjAGEAbgAyAEQAuwMgAHMAdQBwAHAAbwByAHQAcwAgAGYAaQB2AGUAIAB0AHIAYQB2AGUAcgBzAGEAbAAgAG0AbwBkAGUAcwAsACAAYQBsAGwAbwB3AGkAbgBnACAAYQBjAGMAdQBtAHUAbABhAHQAaQBvAG4AIAB0AG8AXABuACAAIAAgACAAYgBlAGcAaQBuACAAYQB0ACAAZABpAGYAZgBlAHIAZQBuAHQAIABjAG8AcgBuAGUAcgBzACAAYQBuAGQAIABwAHIAbwBjAGUAZQBkACAAaQBuACAAZABpAGYAZgBlAHIAZQBuAHQAIABvAHIAZABlAHIAcwAuACAARgBvAHIAIAAyAEQAIABhAHIAcgBhAHkAcwAsAFwAbgAgACAAIAAgAGcAZQBvAG0AZQB0AHIAeQAgAGkAcwAgAHAAcgBlAHMAZQByAHYAZQBkAC4AXABuAFwAbgAgACAAIAAgAEYAbwByACAAMQBEACAAYQByAHIAYQB5AHMALAAgAFMAYwBhAG4AMgBEALsDIABiAGUAaABhAHYAZQBzACAAbABpAGsAZQAgAG4AYQB0AGkAdgBlACAAUwBDAEEATgAsACAAdwBpAHQAaAAgAG8AcAB0AGkAbwBuAGEAbAAgAHIAZQB2AGUAcgBzAGUAXABuACAAIAAgACAAbwByAGQAZQByACAAdwBoAGUAbgAgAGQAaQByAGUAYwB0AGkAbwBuACAAPQAgAC0AMQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwB2AGEAbAB1AGUAIAAgAC0AIABTAGEAbQBlACAAbQBlAGEAbgBpAG4AZwAgAGEAcwAgAG4AYQB0AGkAdgBlACAAUwBDAEEATgAuAFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgADEARAAgAHYAZQBjAHQAbwByAHMAIABhAHIAZQAgAHMAdQBwAHAAbwByAHQAZQBkACAAdwBpAHQAaABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHMAdAByAGkAYwB0AGUAZAAgAGQAaQByAGUAYwB0AGkAbwBuACAAcwBlAG0AYQBuAHQAaQBjAHMALgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AIAAgACAAIAAgACAAIAAtACAAUwBhAG0AZQAgAG0AZQBhAG4AaQBuAGcAIABhAHMAIABuAGEAdABpAHYAZQAgAFMAQwBBAE4ALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAZABpAHIAZQBjAHQAaQBvAG4AXQAgACAAIAAgAC0AIABUAHIAYQB2AGUAcgBzAGEAbAAgAGMAbwBkAGUALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADAAIAAoAHMAdABhAG4AZABhAHIAZAAgAHIAbwB3ABEgbQBhAGoAbwByACkALgBcAG4AXABuAEQAaQByAGUAYwB0AGkAbwBuACAAQwBvAGQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAwACAAIAAgAC0AIABTAHQAYQBuAGQAYQByAGQAIAByAG8AdwARIG0AYQBqAG8AcgAgACgAbABlAGYAdAAgAJIhIAByAGkAZwBoAHQALAAgAHQAbwBwACAAkiEgAGIAbwB0AHQAbwBtACkAXABuACAAIAAgACAAIAAgACAALQAxACAAIAAgAC0AIABDAG8AbAB1AG0AbgARIG0AYQBqAG8AcgAgAGYAcgBvAG0AIABOAFcAIABjAG8AcgBuAGUAcgAgACgAdABvAHAAIACSISAAYgBvAHQAdABvAG0ALAAgAGwAZQBmAHQAIACSISAAcgBpAGcAaAB0ACkAXABuACAAIAAgACAAIAAgACAAIAAxACAAIAAgAC0AIABOAEUAIAB0AHIAYQB2AGUAcgBzAGEAbAAgACgAYwBvAGwAdQBtAG4AESBtAGEAagBvAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgADIAIAAgACAALQAgAFMARQAgAHQAcgBhAHYAZQByAHMAYQBsACAAKABjAG8AbAB1AG0AbgARIG0AYQBqAG8AcgAsACAAYgBvAHQAdABvAG0AIACSISAAdABvAHAAKQBcAG4AIAAgACAAIAAgACAAIAAgADMAIAAgACAALQAgAFMAVwAgAHQAcgBhAHYAZQByAHMAYQBsACAAKAByAG8AdwARIG0AYQBqAG8AcgAsACAAcgBpAGcAaAB0ACAAkiEgAGwAZQBmAHQAKQBcAG4AXABuAEUAcgByAG8AcgAgAEMAbwBuAGQAaQB0AGkAbwBuAHMAOgBcAG4AIAAgACAAIAAiICAAXAAiACMAZABpAHIAZQBjAHQAaQBvAG4AIQBcACIAIAAtACAASQBuAHYAYQBsAGkAZAAgAGQAaQByAGUAYwB0AGkAbwBuACAAZgBvAHIAIAAxAEQAIABhAHIAcgBhAHkAcwAgAG8AcgAgAHUAbgByAGUAYwBvAGcAbgBpAHoAZQBkACAAYwBvAGQAZQAuAFwAbgAgACAAIAAgACIgIAAxAEQAIABhAHIAcgBhAHkAcwAgAG8AbgBsAHkAIABzAHUAcABwAG8AcgB0ACAAZABpAHIAZQBjAHQAaQBvAG4AIAA9ACAAMAAgACgAZgBvAHIAdwBhAHIAZAApACAAbwByACAALQAxACAAKAByAGUAdgBlAHIAcwBlACkALgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGIAeQBwAGEAcwBzACAAdAByAGEAdgBlAHIAcwBhAGwAIABhAG4AZAAgAHUAcwBlACAAbgBhAHQAaQB2AGUAIABTAEMAQQBOACAAZABpAHIAZQBjAHQAbAB5AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAMgBEACAAdAByAGEAdgBlAHIAcwBhAGwAIAB1AHMAZQBzACAAVAByAGEAdgBlAHIAcwBlALsDIAB0AG8AIAByAGUAbwByAGQAZQByACAAdABoAGUAIABhAHIAcgBhAHkALAAgAFMAQwBBAE4AIAB0AG8AIABhAGMAYwB1AG0AdQBsAGEAdABlACwAXABuACAAIAAgACAAIAAgAGEAbgBkACAAUgBlAFMAaABhAHAAZQAyAEQAuwMgAHQAbwAgAHIAZQBzAHQAbwByAGUAIABvAHIAaQBnAGkAbgBhAGwAIABnAGUAbwBtAGUAdAByAHkALgBcAG4AIAAgACAAIAAiICAATgBvACAAZgBsAGEAdAB0AGUAbgBpAG4AZwAgAGkAcwAgAHAAZQByAGYAbwByAG0AZQBkADsAIABnAGUAbwBtAGUAdAByAHkAIABpAHMAIABwAHIAZQBzAGUAcgB2AGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAGMAYQBuADIARAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACwAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAXABuACAAIAAgACAAWwBkAGkAcgBlAGMAdABpAG8AbgBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAMAApAFwAbgAgACAAIAAgAGQAaQByAGUAYwB0AGkAbwBuACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABkAGkAcgBlAGMAdABpAG8AbgApACwAIAAwACwAIABkAGkAcgBlAGMAdABpAG8AbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AbgARIDIARAAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZAAxAEQARABpAHIAPwAsACAAIAAgACAAIABBAE4ARAAoAEkAcwAxAEQAPwAsACAAZABpAHIAZQBjAHQAaQBvAG4AIAA8AD4AIAAwACwAIABkAGkAcgBlAGMAdABpAG8AbgAgADwAPgAgAC0AMQApACwAXABuACAAIAAgACAASQBzAFIAZQB2AGUAcgBzAGUAPwAsACAAIAAgACAAIAAgACAAIABkAGkAcgBlAGMAdABpAG8AbgAgAD0AIAAtADEALABcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAIAAgACAAIAAgAEEATgBEACgASQBzADEARAA/ACwAIABoACAAPgAgAHcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABoAGEAbgBkAGwAaQBuAGcAXABuACAAIAAgACAAZQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgAGgALAAgAHcAKQAsAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAZQAsACwAIABlACwAIAAtADEAKQAsAFwAbgAgACAAIAAgAHIAZQB2AF8AYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAGkAZAB4ACkALAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACwAIABpAGQAeAApACkALABcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBSAGUAdgBlAHIAcwBlAD8ALAAgAHIAZQB2AF8AYQByAHIAYQB5ACwAIABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABTAEMAQQBOACgAaQBuAGkAdABpAGEAbABfAHYAYQBsAHUAZQAsACAAYQByAHIAYQB5ACwAIABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAMQBEAEQAaQByAD8ALAAgAFwAIgAjAGQAaQByAGUAYwB0AGkAbwBuACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFMAQwBBAE4AKABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACwAIAB2AGUAYwB0AG8AcgAsACAAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE4AQQAoAFgATQBBAFQAQwBIACgAZABpAHIAZQBjAHQAaQBvAG4ALAAgAHsALQAxADsAMAA7ADEAOwAyADsAMwA7AFwAIgBOAEUAXAAiADsAXAAiAFMARQBcACIAOwBcACIAUwBXAFwAIgB9ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMAZABpAHIAZQBjAHQAaQBvAG4AIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAMgBEACAAcwBjAGEAbgAgAG0AbwBkAGUAcwBcAG4AIAAgACAAIABzAHQAYQBuAGQAYQByAGQALAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBDAEEATgAoAGkAbgBpAHQAaQBhAGwAXwB2AGEAbAB1AGUALAAgAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACkAKQAsACAALwAvACAAMABcAG4AXABuACAAIAAgACAAcwB0AGEAbgBkAGEAcgBkAF8AYgB5AGMAbwBsACwAIAAgACAAIABMAEEATQBCAEQAQQAoAFQAUgBBAE4AUwBQAE8AUwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBDAEEATgAoAGkAbgBpAHQAaQBhAGwAXwB2AGEAbAB1AGUALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYQByAHIAYQB5ACkALAAgAGYAdQBuAGMAdABpAG8AbgApACkAKQAsACAALwAvACAALQAxAFwAbgBcAG4AIAAgACAAIAB0AHIAYQB2AGUAcgBzAGEAbAAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAFMAaABhAHAAZQAyAEQAuwMoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAQwBBAE4AKABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACwAVAByAGEAdgBlAHIAcwBlALsDKABhAHIAcgBhAHkALAAgAGQAaQByAGUAYwB0AGkAbwBuACkALABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAKQApACwAIAAvAC8AIAAxACwAIAAyACwAIAAzAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAG0AbwBkAGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABkAGkAcgBlAGMAdABpAG8AbgAgAD0AIAAwACwAIAAgAHMAdABhAG4AZABhAHIAZAAoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZABpAHIAZQBjAHQAaQBvAG4AIAA9ACAALQAxACwAIABzAHQAYQBuAGQAYQByAGQAXwBiAHkAYwBvAGwAKAApACwAIAB0AHIAYQB2AGUAcgBzAGEAbAAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADAANABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFQAcgBhAHYAZQByAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBtAGEAcABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABhACAAbgBlAHcAIAB0AHIAYQB2AGUAcgBzAGEAbAAgAG8AcgBkAGUAcgAgAGIAeQAgAHIAbwB0AGEAdABpAG4AZwAgAHQAaABlACAAdAByAGEAdgBlAHIAcwBhAGwAIABhAHgAaQBzAFwAbgAgACAAIAAgAHQAbwAgAG8AbgBlACAAbwBmACAAdABoAHIAZQBlACAAZABpAGEAZwBvAG4AYQBsACAAZABpAHIAZQBjAHQAaQBvAG4AcwAuACAAVABoAGUAIABzAGUAbABlAGMAdABlAGQAIABhAHgAaQBzACAAaQBzACAAcgBlAG0AYQBwAHAAZQBkACAAdABvACAAYQBcAG4AIAAgACAAIAB0AG8AcAARIGwAZQBmAHQAEyBhAG4AYwBoAG8AcgBlAGQAIAB0AHIAYQB2AGUAcgBzAGEAbAAgAG8AcgBkAGUAcgAuACAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAMQBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHIAZQBqAGUAYwB0AGUAZAAuAFwAbgBcAG4AQQBjAGMAZQBwAHQAZQBkACAARABpAHIAZQBjAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACAAIABcACIATgBFAFwAIgAgAG8AcgAgADEAIAAgAJIhIABOAG8AcgB0AGgAZQBhAHMAdAAgACAAKACXISkAXABuACAAIAAgACAAIAAgAFwAIgBTAEUAXAAiACAAbwByACAAMgAgACAAkiEgAFMAbwB1AHQAaABlAGEAcwB0ACAAIAAoAJghKQBcAG4AIAAgACAAIAAgACAAXAAiAFMAVwBcACIAIABvAHIAIAAzACAAIACSISAAUwBvAHUAdABoAHcAZQBzAHQAIAAgACgAmSEpAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAbgBlAHcAXwBhAHgAaQBzACAAIAAgAC0AIABEAGkAcgBlAGMAdABpAG8AbgAgAGMAbwBkAGUAIAAoAFwAIgBOAEUAXAAiACwAXAAiAFMARQBcACIALABcACIAUwBXAFwAIgApACAAbwByACAAaQBuAHQAZQBnAGUAcgAgADEAEyAzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARwBlAG8AbQBlAHQAcgB5ACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQAOwAgAG8AbgBsAHkAIAB0AHIAYQB2AGUAcgBzAGEAbAAgAG8AcgBkAGUAcgAgAGMAaABhAG4AZwBlAHMALgBcAG4AIAAgACAAIAAiICAASQBuAHYAYQBsAGkAZAAgAGQAaQByAGUAYwB0AGkAbwBuACAAYwBvAGQAZQBzACAAcgBlAHQAdQByAG4AIABcACIAIwBBAFgASQBTACEAXAAiAC4AXABuACAAIAAgACAAIiAgADEARAAgAGEAcgByAGEAeQBzACAAcgBlAHQAdQByAG4AIABcACIAIwAyAEQALQBBAFIAUgBBAFkAIQBcACIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVAByAGEAdgBlAHIAcwBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG4AZQB3AF8AYQB4AGkAcwAsAFwAbgBcAG4ASQBGACgATwBSACgAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPQAgADEALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgAD0AIAAxACkALABcACIAIwAyAEQALQBBAFIAUgBBAFkAIQBcACIALABcAG4AXABuACAAIAAgACAASQBGACgAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKABuAGUAdwBfAGEAeABpAHMAKQAsACAATwBSACgAbgBlAHcAXwBhAHgAaQBzACAAPAA9ACAAMAAsACAAbgBlAHcAXwBhAHgAaQBzACAAPgAgADMAKQApACwAXAAiACMAQQBYAEkAUwAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHgAaQBzACAAdAByAGEAdgBlAHIAcwBhAGwAIABpAG4AZABpAGMAZQBzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIAB4AF8ATgBFACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAHcALAAsADEALAAwACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALABoACkAKQAsAFwAbgAgACAAIAAgAHkAXwBOAEUALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAdwAsACwAdwAsAC0AMQApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAaAAsADEALAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAB4AF8AUwBFACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGgALAAsAGgALAAtADEAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsAHcALAAxACwAMAApACkALABcAG4AIAAgACAAIAB5AF8AUwBFACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGgALAAsAHcALAAwACkAIAArACAAUwBFAFEAVQBFAE4AQwBFACgALAB3ACwAMAAsAC0AMQApACkALABcAG4AXABuACAAIAAgACAAeABfAFMAVwAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAB3ACwALABoACwAMAApACAAKwAgAFMARQBRAFUARQBOAEMARQAoACwAaAAsADAALAAtADEAKQApACwAXABuACAAIAAgACAAeQBfAFMAVwAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAB3ACwALAAxACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALABoACwAMQAsADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAeABpAHMAIABtAG8AZABlACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAbQBvAGQAZQAsACAAIAAgACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAbgBlAHcAXwBhAHgAaQBzACkALABuAGUAdwBfAGEAeABpAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAbgBlAHcAXwBhAHgAaQBzACwAIABcACIATgBFAFwAIgAsADEALAAgAFwAIgBTAEUAXAAiACwAMgAsACAAXAAiAFMAVwBcACIALAAzACwAIAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABzAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAG0AbwBkAGUALAAgAHgAXwBOAEUALAAgAHgAXwBTAEUALAAgAHgAXwBTAFcAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgAEMASABPAE8AUwBFACgAbQBvAGQAZQAsACAAeQBfAE4ARQAsACAAeQBfAFMARQAsACAAeQBfAFMAVwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBtAGEAcAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAHgAKAApACwAIAB5ACgAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADAANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFQAYQBrAGUAQgBsAG8AYwBrALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAATQBHAHIAaQBkALsDLAAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhACAAcgBlAGMAdABhAG4AZwB1AGwAYQByACAAYgBsAG8AYwBrACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAHkAIABzAHAAZQBjAGkAZgB5AGkAbgBnACAAYQBuACAAYQBuAGMAaABvAHIAIAB2AGEAbAB1AGUAXABuACAAIAAgACAAKABzAHQAYQByAHQAXwBhAHQAKQAgAGEAbgBkACAAYQBuACAAbwBwAHQAaQBvAG4AYQBsACAAcwB0AG8AcABwAGkAbgBnACAAdgBhAGwAdQBlACAAKABzAHQAbwBwAF8AdwBoAGUAbgApAC4AIABUAGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAGwAbwBjAGEAdABlAHMAXABuACAAIAAgACAAdABoAGUAIABmAGkAcgBzAHQAIABvAGMAYwB1AHIAcgBlAG4AYwBlACAAbwBmACAAcwB0AGEAcgB0AF8AYQB0ACwAIAB0AGgAZQBuACAAcgBlAHQAdQByAG4AcwAgAGEAbABsACAAcgBvAHcAcwAgAGYAcgBvAG0AIAB0AGgAYQB0ACAAcABvAGkAbgB0AFwAbgAgACAAIAAgAGQAbwB3AG4AdwBhAHIAZAAgAGEAbgBkACAAYQBsAGwAIABjAG8AbAB1AG0AbgBzACAAdABvACAAdABoAGUAIAByAGkAZwBoAHQALAAgAHMAdABvAHAAcABpAG4AZwAgAGUAaQB0AGgAZQByACAAYQB0ACAAdABoAGUAIABmAGkAcgBzAHQAXABuACAAIAAgACAAbwBjAGMAdQByAHIAZQBuAGMAZQAgAG8AZgAgAHMAdABvAHAAXwB3AGgAZQBuACAAbwByACAAYQB0ACAAdABoAGUAIABlAG4AZAAgAG8AZgAgAHQAaABlACAAZABhAHQAYQAuAFwAbgBcAG4AIAAgACAAIABCAG8AdABoACAAcwB0AGEAcgB0AF8AYQB0ACAAYQBuAGQAIABzAHQAbwBwAF8AdwBoAGUAbgAgAHIAZQBsAHkAIABvAG4AIABFAHgAYwBlAGwAJwBzACAAbgBhAHQAaQB2AGUAIABlAHEAdQBhAGwAaQB0AHkAIABjAG8AbQBwAGEAcgBpAHMAbwBuAFwAbgAgACAAIAAgACgAYQByAHIAYQB5ACAAPQAgAHQAZQByAG0AKQAuACAAVABoAGkAcwAgAHAAcgBvAHYAaQBkAGUAcwAgAGYAYQBzAHQALAAgAHYAZQBjAHQAbwByAGkAegBlAGQAIABtAGEAdABjAGgAaQBuAGcAIABiAHUAdAAgAGQAbwBlAHMAIABuAG8AdAAgAHMAdQBwAHAAbwByAHQAXABuACAAIAAgACAAdwBpAGwAZABjAGEAcgBkAHMAIABvAHIAIAByAGUAZwB1AGwAYQByACAAZQB4AHAAcgBlAHMAcwBpAG8AbgBzAC4AIABJAGYAIABzAHQAbwBwAF8AdwBoAGUAbgAgAGkAcwAgAG8AbQBpAHQAdABlAGQALAAgAHQAaABlACAAYgBsAG8AYwBrACAAZQB4AHQAZQBuAGQAcwBcAG4AIAAgACAAIAB0AG8AIAB0AGgAZQAgAGIAbwB0AHQAbwBtACAAbwBmACAAdABoAGUAIABhAHIAcgBhAHkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABzAHQAYQByAHQAXwBhAHQAIAAgACAAIAAgAC0AIABBAG4AYwBoAG8AcgAgAHYAYQBsAHUAZQAgAG0AYQByAGsAaQBuAGcAIAB0AGgAZQAgAGYAaQByAHMAdAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIABbAHMAdABvAHAAXwB3AGgAZQBuAF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABzAHQAbwBwAHAAaQBuAGcAIAB2AGEAbAB1AGUALgAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHQAaABlACAAYgBsAG8AYwBrACAAYwBvAG4AdABpAG4AdQBlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABvACAAdABoAGUAIABlAG4AZAAgAG8AZgAgAHQAaABlACAAYQByAHIAYQB5AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARwBlAG8AbQBlAHQAcgB5ACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQAOwAgAG4AbwAgAGYAbABhAHQAdABlAG4AaQBuAGcAIABvAGMAYwB1AHIAcwAuAFwAbgAgACAAIAAgACIgIABJAGYAIABzAHQAYQByAHQAXwBhAHQAIABpAHMAIABuAG8AdAAgAGYAbwB1AG4AZAAsACAAcgBlAHQAdQByAG4AcwAgAFwAIgAjAE4ATwAtAEEATgBDAEgATwBSACEAXAAiAC4AXABuACAAIAAgACAAIiAgAEkAZgAgAHMAdABvAHAAXwB3AGgAZQBuACAAbwBjAGMAdQByAHMAIABiAGUAZgBvAHIAZQAgAHMAdABhAHIAdABfAGEAdAAsACAAcgBlAHQAdQByAG4AcwAgAFwAIgAjAE4ATwAtAFMATABJAEMARQAhAFwAIgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBUAGEAawBlAEIAbABvAGMAawC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABzAHQAYQByAHQAXwBhAHQALABcAG4AIAAgACAAIABbAHMAdABvAHAAXwB3AGgAZQBuAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABzAHQAbwBwAHAAaQBuAGcAIABwAG8AaQBuAHQAXABuACAAIAAgACAARABvAE4AbwB0AFMAdABvAHAAPwAsACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAHMAdABvAHAAXwB3AGgAZQBuACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGEAcgByAGEAeQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBjAGEAbAAgAGgAZQBsAHAAZQByAHMAXABuACAAIAAgACAAQQBuAGMAaABvAHIAuwMsACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAGEAcgByACwAIABjAG8AbgBkAGkAdABpAG8AbgAsACAAaQBkAHgALAAgAE4AKABhAHIAcgAgAD0AIABjAG8AbgBkAGkAdABpAG8AbgApACAAKgAgAGkAZAB4ACkALABcAG4AIAAgACAAIABJAEQAWAC7AywAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAYQByAHIALAAgAE0ASQBOACgASQBGACgAYQByAHIAIAA8AD4AIAAwACwAIABhAHIAcgApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgAgAHAAbwBzAGkAdABpAG8AbgBzAFwAbgAgACAAIAAgAHIAbwB3AF8AcwB0AGEAcgB0ACwAIAAgACAAIAAgACAAQQBuAGMAaABvAHIAuwMoAGEAcgByAGEAeQAsACAAcwB0AGEAcgB0AF8AYQB0ACwAIABpACkALABcAG4AIAAgACAAIABjAG8AbABfAHMAdABhAHIAdAAsACAAIAAgACAAIAAgAEEAbgBjAGgAbwByALsDKABhAHIAcgBhAHkALAAgAHMAdABhAHIAdABfAGEAdAAsACAAagApACwAXABuAFwAbgAgACAAIAAgAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBEAFgAuwMoAHIAbwB3AF8AcwB0AGEAcgB0ACkALABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARABYALsDKABjAG8AbABfAHMAdABhAHIAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABvAHAAcABpAG4AZwAgAHAAbwBzAGkAdABpAG8AbgBzAFwAbgAgACAAIAAgAHIAbwB3AF8AcwB0AG8AcAAsACAAIAAgACAAIAAgACAASQBGACgARABvAE4AbwB0AFMAdABvAHAAPwAsACAAMAAsACAAQQBuAGMAaABvAHIAuwMoAGEAcgByAGEAeQAsACAAcwB0AG8AcABfAHcAaABlAG4ALAAgAGkAKQApACwAXABuACAAIAAgACAAbgBvAF8AcgAsACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAHIAbwB3AF8AcwB0AG8AcAApACAAPQAgADAALABcAG4AIAAgACAAIAByAF8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAEQAbwBOAG8AdABTAHQAbwBwAD8ALAAgAG4AbwBfAHIAKQAsACAAaAAsACAASQBEAFgAuwMoAHIAbwB3AF8AcwB0AG8AcAApACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAXABuACAAIAAgACAAVwBoAGUAcgBlAE4AbwB0AEYAbwB1AG4AZAA/ACwAIABBAE4ARAAoAHIAIAA9ACAAMAAsACAAYwAgAD0AIAAwACkALABcAG4AIAAgACAAIABOAG8AUwBsAGkAYwBlAD8ALAAgACAAIAAgACAAIAAgAEEATgBEACgATgBPAFQAKABuAG8AXwByACkALAAgAHIAXwAgADwAPQAgAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAFcAaABlAHIAZQBOAG8AdABGAG8AdQBuAGQAPwAsACAAXAAiACMATgBPAC0AQQBOAEMASABPAFIAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AUwBsAGkAYwBlAD8ALAAgAFwAIgAjAE4ATwAtAFMATABJAEMARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHUAdABwAHUAdAAgAGcAZQBvAG0AZQB0AHIAeQBcAG4AIAAgACAAIAByAG8AdwBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG4AbwBfAHIALAAgAGgAIAAtACAAcgAgACsAIAAxACwAIAByAF8AIAAtACAAcgApACwAXABuACAAIAAgACAAYwBvAGwAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAB3ACAALQAgAGMAIAArACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAByAG8AdwBzACAAPQAgADEALAByACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIABjAG8AbABzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoAHIAbwB3AHMALAAsACAAcgApACwALAAgAGMAbwBsAHMAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGMAbwBsAHMAIAA9ACAAMQAsAFMARQBRAFUARQBOAEMARQAoAHIAbwB3AHMALAAsACAAYwAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsACAAYwBvAGwAcwAsACAAYwApACwAIAByAG8AdwBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYgBsAG8AYwBrAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIAB4ACwAIAB5ACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADYAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABEAFMAdABhAGMAawC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAcABwAHIAbwB4AGkAbQBhAHQAZQBzACAATgB1AG0AUAB5ACcAcwAgAGQAcwB0AGEAYwBrACAAZgBvAHIAIABFAHgAYwBlAGwAJwBzACAAMgBEACAAYQByAHIAYQB5ACAAbQBvAGQAZQBsAC4AIABEAFMAdABhAGMAawC7AyAAcwB0AGEAYwBrAHMAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABlACAAMgBEACAAYQByAHIAYQB5AHMAIABhAGwAbwBuAGcAIABhACAAXAAiAGQAZQBwAHQAaABcACIAIABkAGkAbQBlAG4AcwBpAG8AbgAgAGIAeQAgAHQAcgBhAG4AcwBwAG8AcwBpAG4AZwAgAGUAYQBjAGgAIABpAG4AcAB1AHQAXABuACAAIAAgACAAYQBuAGQAIABoAG8AcgBpAHoAbwBuAHQAYQBsAGwAeQAgAGMAbwBuAGMAYQB0AGUAbgBhAHQAaQBuAGcAIAB0AGgAZQAgAGwAYQB5AGUAcgBzAC4AIABVAHAAIAB0AG8AIABmAG8AdQByACAAYQByAHIAYQB5AHMAIABtAGEAeQAgAGIAZQBcAG4AIAAgACAAIABzAHUAcABwAGwAaQBlAGQALgAgAE0AaQBzAHMAaQBuAGcAIABhAHIAcgBhAHkAcwAgAGEAcgBlACAAaQBnAG4AbwByAGUAZAAuAFwAbgBcAG4AIAAgACAAIABBAGwAbAAgAGEAcgByAGEAeQBzACAAbQB1AHMAdAAgAGIAZQAgAG4AbwBuABEgcwBjAGEAbABhAHIAIABhAG4AZAAgAG4AbwBuABEgZQBtAHAAdAB5AC4AIABHAGUAbwBtAGUAdAByAHkAIABtAHUAcwB0ACAAbQBhAHQAYwBoACAAYQBjAHIAbwBzAHMAXABuACAAIAAgACAAYQBsAGwAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkAcwAgACgAcwBhAG0AZQAgAGgAZQBpAGcAaAB0ACAA1wAgAHcAaQBkAHQAaAApAC4AIABNAGkAcwBtAGEAdABjAGgAZQBkACAAZQBsAGUAbQBlAG4AdABzACAAYQByAGUAIABwAGEAZABkAGUAZABcAG4AIAAgACAAIAB1AHMAaQBuAGcAIABwAGEAZABfAHcAaQB0AGgALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAYgBhAHMAZQAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMgBdACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABzAGUAYwBvAG4AZAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMwBdACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAB0AGgAaQByAGQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAZgBvAHUAcgB0AGgAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACAAIAAtACAARgBpAGwAbAAgAHYAYQBsAHUAZQAgAGYAbwByACAAbQBpAHMAbQBhAHQAYwBoAGUAZAAgAG8AcgAgAG0AaQBzAHMAaQBuAGcAIABlAGwAZQBtAGUAbgB0AHMALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAE4AQQAoACkALgBcAG4AXABuAEIAZQBoAGEAdgBpAG8AcgA6AFwAbgAgACAAIAAgACIgIABUAHcAbwAgAGEAcgByAGEAeQBzACAAIACSISAAZABlAHAAdABoACAAPQAgADIAXABuACAAIAAgACAAIiAgAFQAaAByAGUAZQAgAGEAcgByAGEAeQBzACAAkiEgAGQAZQBwAHQAaAAgAD0AIAAzAFwAbgAgACAAIAAgACIgIABGAG8AdQByACAAYQByAHIAYQB5AHMAIAAgAJIhIABkAGUAcAB0AGgAIAA9ACAANABcAG4AIAAgACAAIAAiICAARQBhAGMAaAAgAGEAcgByAGEAeQAgAGkAcwAgAHQAcgBhAG4AcwBwAG8AcwBlAGQAIABzAG8AIABkAGUAcAB0AGgAIABiAGUAYwBvAG0AZQBzACAAdwBpAGQAdABoACwAIAB0AGgAZQBuACAASABTAFQAQQBDAEsAZQBkAC4AXABuAFwAbgBFAHIAcgBvAHIAIABDAG8AbgBkAGkAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAFwAIgAjAEUATQBQAFQAWQAtAEEAUgBSAEEAWQAhAFwAIgAgACAAIAAtACAATwBuAGUAIAByAGUAcQB1AGkAcgBlAGQAIABhAHIAcgBhAHkAIABpAHMAIABlAG0AcAB0AHkAIAB3AGgAaQBsAGUAIAB0AGgAZQAgAG8AdABoAGUAcgAgAGkAcwAgAG4AbwB0AC4AXABuACAAIAAgACAAIiAgAFwAIgAjAFMAQwBBAEwAQQBSAC0ARQBSAFIATwBSACEAXAAiACAAIAAtACAAQQBuAHkAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABpAHMAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFQAaABpAHMAIABpAHMAIABhACAAMgBEACAAYQBwAHAAcgBvAHgAaQBtAGEAdABpAG8AbgAgAG8AZgAgAGQAZQBwAHQAaAAgAHMAdABhAGMAawBpAG4AZwAuAFwAbgAgACAAIAAgACIgIABBAGwAbAAgAGEAcgByAGEAeQBzACAAbQB1AHMAdAAgAHMAaABhAHIAZQAgAGcAZQBvAG0AZQB0AHIAeQAgAG8AcgAgAHAAYQBkAGQAaQBuAGcAIAB3AGkAbABsACAAYgBlACAAYQBwAHAAbABpAGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAFMAdABhAGMAawC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACwAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAyAF0ALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8ANABdACwAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBxAHUAaQByAGUAZAAgAGEAcgByAGEAeQAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGEALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABhAHIAcgBhAHkAXwAxACkALABcAG4AIAAgACAAIABiACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMgApACwAIAAwACwAIABDAE8AVQBOAFQAQQAoAGEAcgByAGEAeQBfADIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGEAcgByAGEAeQAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkALAAgADAALAAgAEMATwBVAE4AVABBACgAYQByAHIAYQB5AF8AMwApACkALABcAG4AIAAgACAAIABkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACwAIAAwACwAIABDAE8AVQBOAFQAQQAoAGEAcgByAGEAeQBfADQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAGMAawBpAG4AZwAgAG0AbwBkAGUAcwBcAG4AIAAgACAAIAByAGUAcQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAYwAgAD0AIAAwACwAIABkACAAPQAgADAAKQAsAFwAbgAgACAAIAAgAEMAXwBvAG4AbAB5ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABjACAAPAA+ACAAMAAsACAAZAAgAD0AIAAwACkALABcAG4AIAAgACAAIABEAF8AbwBuAGwAeQAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAYwAgAD0AIAAwACwAIABkACAAPAA+ACAAMAApACwAXABuACAAIAAgACAAQQBsAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGMAIAA8AD4AIAAwACwAIABkACAAPAA+ACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABFAG0AcAB0AHkAQQByAHIAPwAsACAAIAAgACAAIAAgAE8AUgAoAGEAIAA9ACAAMAAsACAAYgAgAD0AIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGEAbABhAHIAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEMAbABhAG0AcAC7AywAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABwAGEAcgBhAG0ALAAgAEEATgBEACgAcABhAHIAYQBtACAAPQAgADEALAAgAEkAUwBFAFIAUgBPAFIAKABwAGEAcgBhAG0AKQApACkALABcAG4AIAAgACAAIABTAGMAYQBsAGEAcgBFAHIAcgA/ACwAIAAgACAAIAAgAE8AUgAoAEMAbABhAG0AcAC7AygAYQApACwAIABDAGwAYQBtAHAAuwMoAGIAKQAsACAAQwBsAGEAbQBwALsDKABjACkALAAgAEMAbABhAG0AcAC7AygAZAApACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABFAG0AcAB0AHkAQQByAHIAPwAsACAAXAAiACMARQBNAFAAVABZAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAUwBjAGEAbABhAHIARQByAHIAPwAsACAAXAAiACMAUwBDAEEATABBAFIALQBFAFIAUgBPAFIAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUABhAGQAZABpAG4AZwBcAG4AIAAgACAAIABwAGEAZABfAHcAaQB0AGgALAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABhAGQAXwB3AGkAdABoACkALAAgAE4AQQAoACkALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAcgBhAG4AcwBwAG8AcwBlAGQAIABsAGEAeQBlAHIAcwBcAG4AIAAgACAAIABhAEAdLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAYgBAHSwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGMAQB0sACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwAsACAAVABSAEEATgBTAFAATwBTAEUAKABhAHIAcgBhAHkAXwAzACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGQAQB0sACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZAAsACAAVABSAEEATgBTAFAATwBTAEUAKABhAHIAcgBhAHkAXwA0ACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAIAB2AGEAcgBpAGEAbgB0AHMAXABuACAAIAAgACAAcgBlAHEAXwBzAHQAYQBjAGsALAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGEAQB0sACAAYgBAHSkALABcAG4AIAAgACAAIABDAF8AbwBuAGwAeQBfAHMAdABhAGMAawAsACAAIAAgAEgAUwBUAEEAQwBLACgAYQBAHSwAIABiAEAdLAAgAGMAQB0pACwAXABuACAAIAAgACAARABfAG8AbgBsAHkAXwBzAHQAYQBjAGsALAAgACAAIABIAFMAVABBAEMASwAoAGEAQB0sACAAYgBAHSwAIABkAEAdKQAsAFwAbgAgACAAIAAgAGEAbABsAF8AcwB0AGEAYwBrACwAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhAEAdLAAgAGIAQB0sACAAYwBAHSwAIABkAEAdKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGYAaQBuAGEAbAAgAHMAdABhAGMAawBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcgBlAHEALAByAGUAcQBfAHMAdABhAGMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEMAXwBvAG4AbAB5ACwAQwBfAG8AbgBsAHkAXwBzAHQAYQBjAGsALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEQAXwBvAG4AbAB5ACwARABfAG8AbgBsAHkAXwBzAHQAYQBjAGsALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBsAGwALABhAGwAbABfAHMAdABhAGMAawAsACAARgBBAEwAUwBFACkAKQApACkALABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADAANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFcAcgBhAHAAUgBvAHcAcwAyAEQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABFAGMAaABvALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABXAHIAYQBwAHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAHIAbwB3ACAAYgBsAG8AYwBrAHMAIABvAGYAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAIABoAGUAaQBnAGgAdAAgAHcAaABpAGwAZQAgAHAAcgBlAHMAZQByAHYAaQBuAGcAXABuACAAIAAgACAAYwBvAGwAdQBtAG4AIAB3AGkAZAB0AGgALgAgAFQAaABlACAAdwByAGEAcABwAGUAZAAgAGIAbABvAGMAawBzACAAYQByAGUAIABzAHQAYQBjAGsAZQBkACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkAIABpAG4AIAB0AGgAZQAgAG8AdQB0AHAAdQB0AC4AXABuACAAIAAgACAASgBhAGcAZwBlAGQAIABvAHIAIABpAG4AYwBvAG0AcABsAGUAdABlACAAZgBpAG4AYQBsACAAYgBsAG8AYwBrAHMAIABhAHIAZQAgAHAAYQBkAGQAZQBkACAAdwBpAHQAaAAgAE4AQQAoACkAIAB1AG4AbABlAHMAcwAgAGEAIABmAGkAbABsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQAgAGkAcwAgAHMAdQBwAHAAbABpAGUAZAAgAHYAaQBhACAAcABhAGQAXwB3AGkAdABoAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAKAAxAEQAIABhAHIAcgBhAHkAcwAgAG4AbwB0ACAAcwB1AHAAcABvAHIAdABlAGQAKQAuAFwAbgAgACAAIAAgAG4AZQB3AF8AaABlAGkAZwBoAHQAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGkAbgAgAGUAYQBjAGgAIAB3AHIAYQBwAHAAZQBkACAAYgBsAG8AYwBrAC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACAAIAAgAC0AIABGAGkAbABsACAAdgBhAGwAdQBlACAAdQBzAGUAZAAgAHQAbwAgAHAAYQBkACAAaQBuAGMAbwBtAHAAbABlAHQAZQAgAGIAbABvAGMAawBzAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABOAEEAKAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIAB3AGkAZAB0AGgAIAA9ACAAYgBsAG8AYwBrAHMAIADXACAAbwByAGkAZwBpAG4AYQBsACAAdwBpAGQAdABoAC4AXABuACAAIAAgACAAIiAgAG4AZQB3AF8AaABlAGkAZwBoAHQAIABtAHUAcwB0ACAAYgBlACAAcwB0AHIAaQBjAHQAbAB5ACAAbABlAHMAcwAgAHQAaABhAG4AIAB0AGgAZQAgAGEAcgByAGEAeQAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAIiAgAFMAcABpAGwAbAAgAHIAaQBzAGsAIABpAHMAIABjAGgAZQBjAGsAZQBkACAAYQBnAGEAaQBuAHMAdAAgAEUAeABjAGUAbAAZIHMAIAAxADYALAAzADgANAARIGMAbwBsAHUAbQBuACAAbABpAG0AaQB0AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFcAcgBhAHAAUgBvAHcAcwAyAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGIAbABvAGMAawBzACwAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAGgAIAAvACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAcABhAGQAXwB3AGkAdABoACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHAAYQBkAF8AdwBpAHQAaAApACwAIABOAEEAKAApACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABvAHUAdABwAHUAdAAgAHcAaQBkAHQAaABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABvAGMAawBzACAAKgAgAHcALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEQAaQBtAD8ALAAgACAAIAAgAG4AZQB3AF8AaABlAGkAZwBoAHQAIAA+AD0AIABoACwAXABuACAAIAAgACAAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAIAAgACAAIABjACAAPgAgADEANgAzADgANAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABEAGkAbQA/ACwAIABcACIAIwBIAEUASQBHAEgAVAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABTAHAAaQBsAGwAUgBpAHMAawA/ACwAIABcACIAIwBOAFUATQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAVABPAFIATwBXACgARQBjAGgAbwC7AygAUwBFAFEAVQBFAE4AQwBFACgALAAgAGIAbABvAGMAawBzACwAIAAxACwAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACkALAAgAHcAKQApACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACsAIABTAEUAUQBVAEUATgBDAEUAKABuAGUAdwBfAGgAZQBpAGcAaAB0ACwALAAgADAALAAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAG0AbwBkAHUAbABvACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAE8ARAAoAFMARQBRAFUARQBOAEMARQAoACwAIAB3ACAAKgAgAGIAbABvAGMAawBzACkALAAgAHcAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAG0AbwBkAHUAbABvACgAKQAgAD0AIAAwACwAIAB3ACwAIABtAG8AZAB1AGwAbwAoACkAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKABuAGUAdwBfAGgAZQBpAGcAaAB0ACwALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFcAcgBhAHAAcABlAGQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpACgAKQAsACAAagAoACkAKQAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMAA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVwByAGEAcABDAG8AbABzADIARAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEUAYwBoAG8AuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFcAcgBhAHAAcwAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYwBvAGwAdQBtAG4AIABiAGwAbwBjAGsAcwAgAG8AZgAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZAAgAHcAaQBkAHQAaAAgAHcAaABpAGwAZQAgAHAAcgBlAHMAZQByAHYAaQBuAGcAXABuACAAIAAgACAAcgBvAHcAIABoAGUAaQBnAGgAdAAuACAAVABoAGUAIAB3AHIAYQBwAHAAZQBkACAAYgBsAG8AYwBrAHMAIABhAHIAZQAgAHMAdABhAGMAawBlAGQAIAB2AGUAcgB0AGkAYwBhAGwAbAB5ACAAaQBuACAAdABoAGUAIABvAHUAdABwAHUAdAAuAFwAbgAgACAAIAAgAEoAYQBnAGcAZQBkACAAbwByACAAaQBuAGMAbwBtAHAAbABlAHQAZQAgAGYAaQBuAGEAbAAgAGIAbABvAGMAawBzACAAYQByAGUAIABwAGEAZABkAGUAZAAgAHcAaQB0AGgAIABOAEEAKAApACAAdQBuAGwAZQBzAHMAIABhACAAZgBpAGwAbABcAG4AIAAgACAAIAB2AGEAbAB1AGUAIABpAHMAIABzAHUAcABwAGwAaQBlAGQAIAB2AGkAYQAgAHAAYQBkAF8AdwBpAHQAaAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkAIAAoADEARAAgAGEAcgByAGEAeQBzACAAbgBvAHQAIABzAHUAcABwAG8AcgB0AGUAZAApAC4AXABuACAAIAAgACAAbgBlAHcAXwB3AGkAZAB0AGgAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAYwBvAGwAdQBtAG4AcwAgAGkAbgAgAGUAYQBjAGgAIAB3AHIAYQBwAHAAZQBkACAAYgBsAG8AYwBrAC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACAAIAAtACAARgBpAGwAbAAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIAB0AG8AIABwAGEAZAAgAGkAbgBjAG8AbQBwAGwAZQB0AGUAIABiAGwAbwBjAGsAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAATgBBACgAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAaABlAGkAZwBoAHQAIAA9ACAAYgBsAG8AYwBrAHMAIADXACAAbwByAGkAZwBpAG4AYQBsACAAaABlAGkAZwBoAHQALgBcAG4AIAAgACAAIAAiICAAbgBlAHcAXwB3AGkAZAB0AGgAIABtAHUAcwB0ACAAYgBlACAAcwB0AHIAaQBjAHQAbAB5ACAAbABlAHMAcwAgAHQAaABhAG4AIAB0AGgAZQAgAGEAcgByAGEAeQAgAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgACIgIABTAHAAaQBsAGwAIAByAGkAcwBrACAAaQBzACAAYwBoAGUAYwBrAGUAZAAgAGEAZwBhAGkAbgBzAHQAIABFAHgAYwBlAGwAGSBzACAAMQAsADAANAA4ACwANQA3ADYAESByAG8AdwAgAGwAaQBtAGkAdAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBXAHIAYQBwAEMAbwBsAHMAMgBEALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACwAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAaABhAHAAZQBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAYgBsAG8AYwBrAHMALAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAdwAgAC8AIABuAGUAdwBfAHcAaQBkAHQAaAAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAcABhAGQAXwB3AGkAdABoACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHAAYQBkAF8AdwBpAHQAaAApACwAIABOAEEAKAApACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABvAHUAdABwAHUAdAAgAGgAZQBpAGcAaAB0AFwAbgAgACAAIAAgAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBsAG8AYwBrAHMAIAAqACAAaAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAMQBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARABpAG0APwAsACAAIAAgACAAbgBlAHcAXwB3AGkAZAB0AGgAIAA+AD0AIAB3ACwAXABuACAAIAAgACAAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAIAAgACAAIAByACAAPgAgADEAMAA0ADgANQA3ADYALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQARABpAG0APwAsACAAXAAiACMAVwBJAEQAVABIACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgAFwAIgAjAE4AVQBNACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGkAYwBlAHMAIAAoAGQAZQBmAGUAcgByAGUAZAApAFwAbgAgACAAIAAgAG0AbwBkAHUAbABvACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAE8ARAAoAFMARQBRAFUARQBOAEMARQAoAHIAKQAsACAAaAApACkALABcAG4AXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAG0AbwBkAHUAbABvACgAKQAgAD0AIAAwACwAIABoACwAIABtAG8AZAB1AGwAbwAoACkAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAbgBlAHcAXwB3AGkAZAB0AGgALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABFAGMAaABvALsDKABTAEUAUQBVAEUATgBDAEUAKAByACAALwAgAGgALAAsACAAMQAsACAAbgBlAHcAXwB3AGkAZAB0AGgAKQAsACAAaAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAArACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG4AZQB3AF8AdwBpAGQAdABoACwAIAAwACwAIAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABXAHIAYQBwAHAAZQBkACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAaQAoACkALAAgAGoAKAApACkALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADAAOQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFMAdABhAGkAcgBjAGEAcwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAVgBhAGwAaQBkAGEAdABlAFMAdABhAGkAcgBjAGEAcwBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgBzAHQAcgB1AGMAdABzACAAZABpAGEAZwBvAG4AYQBsACAAcwB0AGEAaQByAGMAYQBzAGUAIABwAGEAdAB0AGUAcgBuAHMAIABmAHIAbwBtACAAYQAgAHYAZQBjAHQAbwByACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AIABUAGgAZQAgAGkAbgBwAHUAdABcAG4AIAAgACAAIABhAHIAcgBhAHkAIABpAHMAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHIAbwB3ABEgdwBpAHMAZQAsACAAcABhAHIAdABpAHQAaQBvAG4AZQBkACAAaQBuAHQAbwAgAGIAbABvAGMAawBzACAAbwBmACAAcwBpAHoAZQAgAGIAbABvAGMAawBfAHMAaQB6AGUALAAgAGEAbgBkAFwAbgAgACAAIAAgAGEAcgByAGEAbgBnAGUAZAAgAGkAbgB0AG8AIABkAGkAYQBnAG8AbgBhAGwAIABcACIAcwB0AGUAcABzAFwAIgAuACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwAgAGMAbwBuAHQAcgBvAGwAIABiAGwAbwBjAGsAIABzAHAAYQBjAGkAbgBnACwAXABuACAAIAAgACAAaABvAHIAaQB6AG8AbgB0AGEAbAAvAHYAZQByAHQAaQBjAGEAbAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAsACAAYQBuAGQAIABhAG4AdABpABEgZABpAGEAZwBvAG4AYQBsACAAbABhAHkAbwB1AHQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAGYAbABhAHQAdABlAG4AZQBkACAAcgBvAHcAESB3AGkAcwBlACkALgBcAG4AIAAgACAAIABiAGwAbwBjAGsAXwBzAGkAegBlACAAIAAgACAAIAAgAC0AIABSAG8AdwBzAC8AYwBvAGwAdQBtAG4AcwAgAGkAbgAgAGUAYQBjAGgAIABzAHQAYQBpAHIAYwBhAHMAZQAgAGIAbABvAGMAawAuAFwAbgAgACAAIAAgAFsAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHMAcABhAGMAaQBuAGcAIABiAGUAdAB3AGUAZQBuACAAcwB0AGEAaQByAGMAYQBzAGUAIABiAGwAbwBjAGsAcwAuAFwAbgAgACAAIAAgAFsASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHQAbwBnAGcAbABlACAAZgBvAHIAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALgBcAG4AIAAgACAAIABbAEkAcwBBAG4AdABpAEQAaQBhAGcAPwBdACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAB0AG8AZwBnAGwAZQAgAGYAbwByACAAYQBuAHQAaQARIGQAaQBhAGcAbwBuAGEAbAAgAGwAYQB5AG8AdQB0AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBuAHAAdQB0ACAAaQBzACAAZgBsAGEAdAB0AGUAbgBlAGQAIAB1AHMAaQBuAGcAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIAAiICAAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAwAC4AXABuACAAIAAgACAAIiAgAE8AcgBpAGUAbgB0AGEAdABpAG8AbgAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAHYAZQByAHQAaQBjAGEAbAAgAHUAbgBsAGUAcwBzACAASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAgAGkAcwAgAHAAcgBvAHYAaQBkAGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHQAYQBpAHIAYwBhAHMAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABiAGwAbwBjAGsAXwBzAGkAegBlACwAXABuACAAIAAgACAAWwBiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdABdACwAXABuACAAIAAgACAAWwBJAHMASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0ALABcAG4AIAAgACAAIABbAEkAcwBBAG4AdABpAEQAaQBhAGcAPwBdACwAXABuAFwAbgBWAGEAbABpAGQAYQB0AGUAUwB0AGEAaQByAGMAYQBzAGUAuwMoAGEAcgByAGEAeQAsACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAsACAAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIABOAG8ATwBmAGYAcwBlAHQAPwAsACAAIAAgACAAIAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAApACwAXABuACAAIAAgACAAWgBlAHIAbwBPAGYAZgBzAGUAdAA/ACwAIAAgACAAIAAgACAAIAAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACAAPQAgADAALABcAG4AIAAgACAAIABjAG8AbABfAG8AZgBmAHMAZQB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAE8AZgBmAHMAZQB0AD8ALAAgADAALAAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACkALABcAG4AXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwApACwAXABuACAAIAAgACAATgBvAEEAbgB0AGkARABpAGEAZwA/ACwAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgASQBzAEEAbgB0AGkARABpAGEAZwA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdABcAG4AIAAgACAAIABmAGwAYQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABmAGwAYQB0ACkALABcAG4AIAAgACAAIABzAGUAcQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABrACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGEAcgB0AGkAdABpAG8AbgAgAGkAbgB0AG8AIABiAGwAbwBjAGsAcwBcAG4AIAAgACAAIABWACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAFIATwBXACgARQBYAFAAQQBOAEQAKABXAFIAQQBQAFIATwBXAFMAKABzAGUAcQAoACkALAAgAGIAbABvAGMAawBfAHMAaQB6AGUAKQAsACwAYgBsAG8AYwBrAF8AcwBpAHoAZQAgACsAIABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAAsADAAKQApACwAXABuAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAVgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAbgBjAGgAbwByAHMAIABhAG4AZAAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAYgBsAG8AYwBrAF8AcwBpAHoAZQApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIAB3AGkAZAB0AGgALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAGMAbwBsAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBBAG4AdABpAEQAaQBhAGcAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAIAB3AGkAZAB0AGgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAIAB3AGkAZAB0AGgALAAgAHcAaQBkAHQAaAAsACAALQAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAE0ATwBEACgAYwBvAGwAXwBhAHIAcgAoACkALAAgAGIAbABvAGMAawBfAHMAaQB6AGUAIAArACAAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAKQApACwAXABuAFwAbgAgACAAIAAgAGoAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAE8AUgAoAE4AbwBPAGYAZgBzAGUAdAA/ACwAIABaAGUAcgBvAE8AZgBmAHMAZQB0AD8AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAagAoACkAIAA9ACAAMAAsACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAsACAAagAoACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAGkAKAApACAAPQAgAGoAXwAoACkALAAgAFYALAAgAE4AQQAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABzAHQAYQBpAHIAYwBhAHMAZQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAEkARgBOAEEAKABJAE4ARABFAFgAKABmAGwAYQB0ACwAIABpAGQAeAAoACkAKQAsACAAXAAiAFwAIgApACwALAAgAC0AYwBvAGwAXwBvAGYAZgBzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAcgBlAHMAdQBsAHQAKQAsACAAcgBlAHMAdQBsAHQAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBAC0AQwBPAFIARQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAFMAdABhAGkAcgBjAGEAcwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnACAAKABWAGEAbABpAGQAYQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABWAGEAbABpAGQAYQB0AGkAbwBuACAAaABlAGwAcABlAHIAIABmAG8AcgAgAFMAdABhAGkAcgBjAGEAcwBlALsDLgAgAEUAbgBzAHUAcgBlAHMAIABhAHIAcgBhAHkAIABpAHMAIAB2AGEAbABpAGQALAAgAGIAbABvAGMAawBfAHMAaQB6AGUAIABpAHMAXABuACAAIAAgACAAcABvAHMAaQB0AGkAdgBlACAAYQBuAGQAIABkAG8AZQBzACAAbgBvAHQAIABlAHgAYwBlAGUAZAAgAGEAcgByAGEAeQAgAGwAZQBuAGcAdABoACwAIABhAG4AZAAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACAAaQBzACAAbgBvAG4AESBuAGUAZwBhAHQAaQB2AGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABiAGwAbwBjAGsAXwBzAGkAegBlACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIABiAGwAbwBjAGsAIABzAGkAegBlAC4AXABuACAAIAAgACAAWwBiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdABdACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcwBwAGEAYwBpAG4AZwAgAGIAZQB0AHcAZQBlAG4AIABiAGwAbwBjAGsAcwAuAFwAbgAgACAAIAAgAFsAbwBuAF8AdgBhAGwAaQBkAF0AIAAgACAAIAAgACAALQAgAEUAeABwAHIAZQBzAHMAaQBvAG4AIAB0AG8AIABlAHYAYQBsAHUAYQB0AGUAIAB3AGgAZQBuACAAdgBhAGwAaQBkAGEAdABpAG8AbgAgAHAAYQBzAHMAZQBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBTAHQAYQBpAHIAYwBhAHMAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABiAGwAbwBjAGsAXwBzAGkAegBlACwAXABuACAAIAAgACAAWwBiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdABdACwAXABuACAAIAAgACAAWwBvAG4AXwB2AGEAbABpAGQAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEMAaABlAGMAawBzAFwAbgAgACAAIAAgAE4AbwB0AEEAcgByAGEAeQA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABhAHIAcgBhAHkAKQAgADwAPgAgADYANAAsAFwAbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEIAbABvAGMAawBTAGkAegBlAD8ALAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAGIAbABvAGMAawBfAHMAaQB6AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABvAGMAawBfAHMAaQB6AGUAIAA8AD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAgAD4AIABDAE8AVQBOAFQAQQAoAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABCAGwAbwBjAGsATwBmAGYAcwBlAHQAPwAsACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAApACwAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAIAA8ACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgATgBvAHQAQQByAHIAYQB5AD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAE4ATwBUAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABCAGwAbwBjAGsAUwBpAHoAZQA/ACwAIAAgAFwAIgAjAEIATABPAEMASwAtAFMASQBaAEUAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAQgBsAG8AYwBrAE8AZgBmAHMAZQB0AD8ALAAgAFwAIgAjAEIATABPAEMASwAtAE8ARgBGAFMARQBUACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AbgBfAHYAYQBsAGkAZABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADEAMABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFUAbgBQAGkAdgBvAHQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAcABlAGEAdABSAG8AdwBzALsDLAAgAFIAZQBzAGkAegBlALsDLAAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABhACAAYQByAHIAYQB5AF8AMgBEACAAaQBuAHQAbwAgAGEAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHIAbwB3ABEgdwBpAHMAZQAgAHQAYQBiAGwAZQAgAGIAeQAgAHAAcgBvAHYAaQBkAGkAbgBnACAAcgBvAHcAIABsAGEAYgBlAGwAcwAsAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuACAAbABhAGIAZQBsAHMALAAgAGEAbgBkACAAYQAgAHYAYQBsAHUAZQAgAGEAcgByAGEAeQBfADIARAAuACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAdABlAHIAaQBuAGcAIAByAGUAbQBvAHYAZQBzACAAYgBsAGEAbgBrAHMALABcAG4AIAAgACAAIABlAHIAcgBvAHIAcwAsACAAYQBuAGQAIAB6AGUAcgBvAHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAByAG8AdwBzACAAIAAgACAAIAAgACAAIAAtACAAVgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5ACAAbwBmACAAcgBvAHcAIABsAGEAYgBlAGwAcwAuAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAHMAIAAgACAAIAAgAC0AIABIAG8AcgBpAHoAbwBuAHQAYQBsACAAYQByAHIAYQB5ACAAbwBmACAAYwBvAGwAdQBtAG4AIABsAGEAYgBlAGwAcwAuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACAAIAAgACAAIAAgAC0AIABhAHIAcgBhAHkAXwAyAEQAIABvAGYAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAHUAbgBwAGkAdgBvAHQALgBcAG4AIAAgACAAIABbAGkAZwBuAG8AcgBlAF0AIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsADoAIABpAGYAIABUAFIAVQBFACwAIAByAGUAbQBvAHYAZQAgAGIAbABhAG4AawBzACwAIABlAHIAcgBvAHIAcwAsACAAYQBuAGQAIAB6AGUAcgBvAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIAByAG8AdwBzACAAbQB1AHMAdAAgAG0AYQB0AGMAaAAgAHQAaABlACAAaABlAGkAZwBoAHQAIABvAGYAIAB2AGEAbAB1AGUAcwAuAFwAbgAgACAAIAAgACIgIABjAG8AbAB1AG0AbgBzACAAbQB1AHMAdAAgAG0AYQB0AGMAaAAgAHQAaABlACAAdwBpAGQAdABoACAAbwBmACAAdgBhAGwAdQBlAHMALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhACAAMwARIGMAbwBsAHUAbQBuACAAdABhAGIAbABlADoAIAB7AHIAbwB3AF8AbABhAGIAZQBsACwAIABjAG8AbAB1AG0AbgBfAGwAYQBiAGUAbAAsACAAdgBhAGwAdQBlAH0ALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVQBuAFAAaQB2AG8AdAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAByAG8AdwBzACwAXABuACAAIAAgACAAYwBvAGwAdQBtAG4AcwAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAG8AdwBzACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABjAG8AbAB1AG0AbgBzACkALABcAG4AXABuACAAIAAgACAAaABfAHYALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAdgBhAGwAdQBlAHMAKQAsAFwAbgAgACAAIAAgAHcAXwB2ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAHYAYQBsAHUAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACwAIABoAF8AdgAgAD0AIAAxACwAIAB3AF8AdgAgAD0AIAAxACkALABcAG4AIAAgACAAIABOAG8AUABpAHYAbwB0AD8ALAAgACAAIAAgACAAIAAgAHcAXwB2ACAAPQAgADEALABcAG4AXABuACAAIAAgACAAUgBvAHcATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIABoACAAPAA+ACAAaABfAHYALABcAG4AIAAgACAAIABDAG8AbABNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgAHcAIAA8AD4AIAB3AF8AdgAsAFwAbgBcAG4AIAAgACAAIABTAHAAaQBsAGwAUgBpAHMAawA/ACwAIAAgACAAIAAgAGgAXwB2ACAAKgAgAHcAXwB2ACAAPgAgADEAMAA0ADgANQA3ADYALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGEAbABhAHIAIABwAGEAcwBzAHQAaAByAG8AdQBnAGgAXABuACAAIAAgACAATwByAGkAZwBEAGEAdABhACwAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHIAbwB3AHMALAAgAGMAbwBsAHUAbQBuAHMALAAgAHYAYQBsAHUAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAAMQARIGMAbwBsAHUAbQBuACAAcABhAHMAcwB0AGgAcgBvAHUAZwBoAFwAbgAgACAAIAAgAE8AcgBpAGcARABhAHQAYQBQAGEAZAAsACAAIAAgACAASABTAFQAQQBDAEsAKABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AygAcgBvAHcAcwAsACAAMQAsACAAMAApACwAVgBTAFQAQQBDAEsAKABjAG8AbAB1AG0AbgBzACwAIAB2AGEAbAB1AGUAcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAATwByAGkAZwBEAGEAdABhACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATgBvAFAAaQB2AG8AdAA/ACwAIABPAHIAaQBnAEQAYQB0AGEAUABhAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAFIAbwB3AE0AaQBzAG0AYQB0AGMAaAA/ACwAIABcACIAIwBEAEkATQAtAFIATwBXAFMALwBWAEEATABVAEUAUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABDAG8AbABNAGkAcwBtAGEAdABjAGgAPwAsACAAXAAiACMARABJAE0ALQBDAE8ATAAvAFYAQQBMAFUARQBTACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAXAAiACMAUgBPAFcALQBMAEkATQBJAFQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQgByAG8AYQBkAGMAYQBzAHQAIAByAG8AdwAgAGwAYQBiAGUAbABzACAAKAByAGUAcABlAGEAdAAgAGUAYQBjAGgAIAByAG8AdwAgAGwAYQBiAGUAbAAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAG8AbAB1AG0AbgBzACkAXABuACAAIAAgACAAcgBvAHcAXwBsAGEAYgBlAGwAcwAsACAAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDKAByAG8AdwBzACwAIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgByAG8AYQBkAGMAYQBzAHQAIABjAG8AbAB1AG0AbgAgAGwAYQBiAGUAbABzACAAKAByAGUAcABlAGEAdAAgAGUAYQBjAGgAIABjAG8AbAB1AG0AbgAgAGwAYQBiAGUAbAAgAGQAbwB3AG4AIABhAGwAbAAgAHIAbwB3AHMAKQBcAG4AIAAgACAAIABhAHQAdAByAGkAYgB1AHQAZQAsACAAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDKABUAFIAQQBOAFMAUABPAFMARQAoAGMAbwBsAHUAbQBuAHMAKQAsAGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAdgBhAGwAdQBlAHMAXABuACAAIAAgACAAZgBsAGEAdABfAHYAYQBsAHUAZQBzACwAIAAgACAAIABUAE8AQwBPAEwAKAB2AGEAbAB1AGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAGMAawAgAGkAbgB0AG8AIAAzABEgYwBvAGwAdQBtAG4AIAB0AGEAYgBsAGUAXABuACAAIAAgACAAcwB0AGEAYwBrACwAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHIAbwB3AF8AbABhAGIAZQBsAHMALAAgAGEAdAB0AHIAaQBiAHUAdABlACwAIABmAGwAYQB0AF8AdgBhAGwAdQBlAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGkAbAB0AGUAcgBpAG4AZwBcAG4AIAAgACAAIABrAGUAZQBwAF8AbQBhAHMAawAsACAAIAAgACAAIAAgAE4ATwBUACgASQBTAEIATABBAE4ASwAoAGYAbABhAHQAXwB2AGEAbAB1AGUAcwApACAAKwAgACgASQBGAEUAUgBSAE8AUgAoAGYAbABhAHQAXwB2AGEAbAB1AGUAcwAsACAAMAApACAAPQAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBsAHQAZQByAGUAZAAsACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABzAHQAYQBjAGsALAAgAGsAZQBlAHAAXwBtAGEAcwBrACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZwBuAG8AcgBlACkALAAgAHMAdABhAGMAawAsACAAZgBpAGwAdABlAHIAZQBkACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABaAGkAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFoAaQBwAHMAIAB0AG8AZwBlAHQAaABlAHIAIAAxABMgNAAgAGEAcgByAGEAeQBzACAAYgB5ACAAZgBsAGEAdAB0AGUAbgBpAG4AZwAgAGUAYQBjAGgAIABpAG4AcAB1AHQAIAB3AGkAdABoACAAVABPAEMATwBMACAAYQBuAGQAIABhAGwAaQBnAG4AaQBuAGcAXABuACAAIAAgACAAdABoAGUAbQAgAGIAeQAgAGwAZQBuAGcAdABoAC4AIABCAHkAIABkAGUAZgBhAHUAbAB0ACwAIABaAGkAcAC7AyAAcABlAHIAZgBvAHIAbQBzACAAYQAgAHMAdAByAGkAYwB0ACAAegBpAHAALAAgAHAAYQBpAHIAaQBuAGcAIABlAGwAZQBtAGUAbgB0AHMAXABuACAAIAAgACAAbwBuAGwAeQAgAHUAcAAgAHQAbwAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAHMAaABvAHIAdABlAHMAdAAgAGEAcgByAGEAeQAuACAASQBmACAAegBpAHAAXwBsAG8AbgBnAGUAcwB0ACAAPQAgAFQAUgBVAEUALAAgAFoAaQBwALsDXABuACAAIAAgACAAYwBvAG4AdABpAG4AdQBlAHMAIAB1AG4AdABpAGwAIAB0AGgAZQAgAGwAbwBuAGcAZQBzAHQAIABhAHIAcgBhAHkAIABpAHMAIABjAG8AbgBzAHUAbQBlAGQALAAgAHAAYQBkAGQAaQBuAGcAIABzAGgAbwByAHQAZQByACAAYQByAHIAYQB5AHMAIAB3AGkAdABoAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAIAAoAGQAZQBmAGEAdQBsAHQAOgAgACMATgAvAEEAKQAuAFwAbgBcAG4AIAAgACAAIABUAGgAZQAgAHIAZQBzAHUAbAB0ACAAaQBzACAAYQAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5ACAAcwB0AGEAYwBrAGUAZAAgAHQAYQBiAGwAZQAgAHcAaABlAHIAZQAgAGUAYQBjAGgAIABjAG8AbAB1AG0AbgAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQBcAG4AIAAgACAAIAB6AGkAcABwAGUAZAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAsACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAHQAbwAgAGEAIABjAG8AbQBtAG8AbgAgAGwAZQBuAGcAdABoAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAAIAAgAC0AIABGAGkAcgBzAHQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAyAF0AIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABzAGUAYwBvAG4AZAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMwBdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAdABoAGkAcgBkACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0AIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAG8AdQByAHQAaAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAegBpAHAAXwBsAG8AbgBnAGUAcwB0AF0AIAAtACAAVABSAFUARQAgAHQAbwAgAHoAaQBwACAAdQBuAHQAaQBsACAAdABoAGUAIABsAG8AbgBnAGUAcwB0ACAAYQByAHIAYQB5ACAAaQBzACAAYwBvAG4AcwB1AG0AZQBkAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIABaAGkAcAC7AyAAdQBzAGUAcwAgAHMAdAByAGkAYwB0ACAAbQBvAGQAZQAgACgAcwBoAG8AcgB0AGUAcwB0ACAAYQByAHIAYQB5ACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAgACAALQAgAFYAYQBsAHUAZQAgAHUAcwBlAGQAIAB0AG8AIABwAGEAZAAgAHMAaABvAHIAdABlAHIAIABhAHIAcgBhAHkAcwAgAHcAaABlAG4AIAB6AGkAcABfAGwAbwBuAGcAZQBzAHQAIAA9ACAAVABSAFUARQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBaAGkAcAC7Az0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMgBdACwAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAzAF0ALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAsAFwAbgAgACAAIAAgAFsAegBpAHAAXwBsAG8AbgBnAGUAcwB0AF0ALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGUAdAAgAHoAaQBwACAAbQBvAGQAZQBcAG4AIAAgACAAIABaAGkAcABMAG8AbgBnAD8ALAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAegBpAHAAXwBsAG8AbgBnAGUAcwB0ACkALAAgAEYAQQBMAFMARQAsACAAegBpAHAAXwBsAG8AbgBnAGUAcwB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAHQAIABmAHUAbgBjAHQAaQBvAG4AIABmAG8AcgAgAGQAZQB0AGUAcgBtAGkAbgBpAG4AZwAgAGwAZQBuAGcAdABoACAAbwBmACAAegBpAHAAXABuACAAIAAgACAAZgBuALsDLAAgACAAIAAgACAAIAAgACAAIABJAEYAKABaAGkAcABMAG8AbgBnAD8ALABNAEEAWAAsAE0ASQBOACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAHQAIABmAGkAbABsAF8AdgBhAGwAdQBlAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALAAgACAASQBGACgAWgBpAHAATABvAG4AZwA/ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAATgBBACgAKQAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIABOAEEAKAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQByAHIAYQB5AHMAIABzAHUAcABwAGwAaQBlAGQAXABuACAAIAAgACAAVAB3AG8ALAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMgApACkALABcAG4AIAAgACAAIABUAGgAcgBlAGUALAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkAKQAsAFwAbgAgACAAIAAgAEYAbwB1AHIALAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGEAcgByAGEAeQBzACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgAG0ALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgARgBvAHUAcgAsACAANAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABUAGgAcgBlAGUALAAgADMALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABUAHcAbwAsACAAMgAsADEAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEALAAgACAAIAAgACAAVABPAEMATwBMACgAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgAsACAAIAAgACAAIABJAEYAKABtACAAPgA9ACAAMgAsAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADIAKQAsAEYAQQBMAFMARQApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMwAsACAAIAAgACAAIABJAEYAKABtACAAPgA9ACAAMwAsAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADMAKQAsAEYAQQBMAFMARQApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8ANAAsACAAIAAgACAAIABJAEYAKABtACAAPQAgACAANAAsAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADQAKQAsAEYAQQBMAFMARQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAZQBuAGcAdABoACAAbwBmACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAAawCBICwAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMQApACwAIAAgACAAawCCICwAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGsAgyAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADMAKQAsACAAIAAgAGsAhCAsACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAATABlAG4AZwB0AGgAIABvAGYAIAB6AGkAcABcAG4AIAAgACAAIABMAFoALAAgACAAIAAgACAAIAAgACAAIAAgAEMASABPAE8AUwBFACgAbQAsAGsAgSAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBuALsDKABrAIEgLABrAIIgKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBuALsDKABrAIEgLABrAIIgLABrAIMgKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBuALsDKABrAIEgLABrAIIgLABrAIMgLABrAIQgKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAeQBzACAALQAgAG4AbwByAG0AYQBsAGkAegBlAGQAIABmAG8AcgAgAHoAaQBwACAAbQBvAGQAZQBcAG4AIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AywAIAAgAEwAQQBNAEIARABBACgAYQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAFoAaQBwAEwAbwBuAGcAPwAsAEUAWABQAEEATgBEACgAYQByAHIAYQB5ACwATABaACwALABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABhAHIAcgBhAHkALABMAFoAKQApACkALABcAG4AXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AygAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AygAYQByAHIAYQB5AF8AMgApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AygAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AygAYQByAHIAYQB5AF8ANAApACwAXABuACAAIAAgACAAXABuACAAIAAgACAALwAvACAAQQByAHIAYQBuAGcAZQBtAGUAbgB0AFwAbgAgACAAIAAgAHoAaQBwAHAAZQBkACwAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKABtACwAYQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGEALABiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACwAYgAsAGMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGEALABiACwAYwAsAGQAKQApACwAXABuACAAIAAgACAAegBpAHAAcABlAGQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADMAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAGwAaQBjAGUAQgB5AEQAZQBnALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAARABHAHIAaQBkALsDLAAgAEQAZQBsAGUAdABlAFcAaABlAHIAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQBuACAAYQBuAGcAdQBsAGEAcgAgAHMAbABpAGMAZQAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAdQBzAGkAbgBnACAAZABlAGcAcgBlAGUAIABiAG8AdQBuAGQAcwAgAGkAbgAgAGEAIAAwALAAIAAtACAAMwA2ADAAsABcAG4AIAAgACAAIABjAGkAcgBjAHUAbABhAHIAIABzAHkAcwB0AGUAbQAuACAAVABoAGUAIABzAGwAaQBjAGUAIABwAHIAZQBzAGUAcgB2AGUAcwAgAHQAaABlACAAbwByAGkAZwBpAG4AYQBsACAAZwBlAG8AbQBlAHQAcgB5AC4AIABJAGYAIABtAGEAeABfAGQAZQBnAHIAZQBlACAAaQBzAFwAbgAgACAAIAAgAG8AbQBpAHQAdABlAGQALAAgAGkAdAAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADMANgAwALAALgBcAG4AXABuACAAIAAgACAAVwByAGEAcAARIGEAcgBvAHUAbgBkACAAaQBzACAAcwB1AHAAcABvAHIAdABlAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABJAGYAIABtAGkAbgBfAGQAZQBnAHIAZQBlACAAPAA9ACAAbQBhAHgAXwBkAGUAZwByAGUAZQA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBsAGkAYwBlACAAPQAgAFsAbQBpAG4AXwBkAGUAZwByAGUAZQAsACAAbQBhAHgAXwBkAGUAZwByAGUAZQBdAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEkAZgAgAG0AaQBuAF8AZABlAGcAcgBlAGUAIAA+ACAAbQBhAHgAXwBkAGUAZwByAGUAZQA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBsAGkAYwBlACAAYwByAG8AcwBzAGUAcwAgADMANgAwALAAIACSISAAMACwACAAYQBuAGQAIABpAG4AYwBsAHUAZABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBuAGcAbABlAHMAIAA+AD0AIABtAGkAbgBfAGQAZQBnAHIAZQBlACAAIABPAFIAIAAgAGEAbgBnAGwAZQBzACAAPAA9ACAAbQBhAHgAXwBkAGUAZwByAGUAZQBcAG4AXABuACAAIAAgACAAVgBhAGwAdQBlAHMAIABvAHUAdABzAGkAZABlACAAdABoAGUAIABzAGwAaQBjAGUAIABhAHIAZQAgAHIAZQBwAGwAYQBjAGUAZAAgAHcAaQB0AGgAIABmAGkAbABsAF8AdgBhAGwAdQBlACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgAFwAIgBcACIAKQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAcwBsAGkAYwBlAC4AXABuACAAIAAgACAAbQBpAG4AXwBkAGUAZwByAGUAZQAgACAAIAAgAC0AIABTAHQAYQByAHQAaQBuAGcAIABkAGUAZwByAGUAZQAgACgAMAAtADMANgAwACkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAbQBhAHgAXwBkAGUAZwByAGUAZQBdACAAIAAtACAARQBuAGQAaQBuAGcAIABkAGUAZwByAGUAZQAgACgAZABlAGYAYQB1AGwAdAAgAD0AIAAzADYAMAApAC4AXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0AIAAgAC0AIABGAGkAbABsACAAdgBhAGwAdQBlACAAZgBvAHIAIABvAHUAdAARIG8AZgARIHMAbABpAGMAZQAgAGMAZQBsAGwAcwAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABcACIAXAAiACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABVAHMAZQBzACAARABHAHIAaQBkALsDIAB0AG8AIABjAG8AbQBwAHUAdABlACAAcABlAHIAESBjAGUAbABsACAAYQBuAGcAbABlAHMALgBcAG4AIAAgACAAIAAiICAARABlAGwAZQB0AGUAVwBoAGUAcgBlALsDIAByAGUAbQBvAHYAZQBzACAATgBBACgAKQAgAHcAaABpAGwAZQAgAHAAcgBlAHMAZQByAHYAaQBuAGcAIABzAGgAYQBwAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBsAGkAYwBlAEIAeQBEAGUAZwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAbQBpAG4AXwBkAGUAZwByAGUAZQAsAFwAbgAgACAAIAAgAFsAbQBhAHgAXwBkAGUAZwByAGUAZQBdACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgAgACAAIAAgAG0AYQB4AF8AZABlAGcAcgBlAGUALAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGEAeABfAGQAZQBnAHIAZQBlACkALAAgADMANgAwACwAIABtAGEAeABfAGQAZQBnAHIAZQBlACkALABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIABcACIAXAAiACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEQAZQBnAD8ALAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAbQBpAG4AXwBkAGUAZwByAGUAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAG0AYQB4AF8AZABlAGcAcgBlAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBpAG4AXwBkAGUAZwByAGUAZQAgADwAIAAwACwAIABtAGkAbgBfAGQAZQBnAHIAZQBlACAAPgAgADMANgAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGEAeABfAGQAZQBnAHIAZQBlACAAPAAgADAALAAgAG0AYQB4AF8AZABlAGcAcgBlAGUAIAA+ACAAMwA2ADAAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEQAZQBnAD8ALAAgAFwAIgAjAEQARQBHAFIARQBFACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEEAbgBnAGwAZQAgAGYAaQBlAGwAZAAgACgAMAATIDMANgAwACkAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABXAHIAYQBwABEgYQB3AGEAcgBlACAAbQBhAHMAawBcAG4AIAAgACAAIABtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG0AaQBuAF8AZABlAGcAcgBlAGUAIAA8AD0AIABtAGEAeABfAGQAZQBnAHIAZQBlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAZAAgAD4APQAgAG0AaQBuAF8AZABlAGcAcgBlAGUAKQAgACoAIAAoAGQAIAA8AD0AIABtAGEAeABfAGQAZQBnAHIAZQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABkACAAPgA9ACAAbQBpAG4AXwBkAGUAZwByAGUAZQApACAAKwAgACgAZAAgADwAPQAgAG0AYQB4AF8AZABlAGcAcgBlAGUAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAbQBhAHMAawBlAGQALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABOAEEAKAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAG0AbwB2AGUAIABOAEEAIABiAHUAdAAgAHAAcgBlAHMAZQByAHYAZQAgAHMAaABhAHAAZQBcAG4AIAAgACAAIABjAGwAZQBhAG4AZQBkACwAIAAgACAAIAAgACAAIAAgAEQAZQBsAGUAdABlAFcAaABlAHIAZQC7AygAbQBhAHMAawBlAGQALAAgAEwAQQBNAEIARABBACgAdgAsACAAQQBOAEQAKABJAFMATgBBACgAdgApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBwAGwAYQBjAGUAIAByAGUAbQBvAHYAZQBkACAAdgBhAGwAdQBlAHMAIAB3AGkAdABoACAAZgBpAGwAbABfAHYAYQBsAHUAZQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEkARgBOAEEAKABjAGwAZQBhAG4AZQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUABhAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AywAIABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQBwAHAAbABpAGUAcwAgAHIAbwB3ACAAYQBuAGQALwBvAHIAIABjAG8AbAB1AG0AbgAgAHAAYQBkAGQAaQBuAGcAIAB0AG8AIABhAG4AeQAgAGEAcgByAGEAeQAuACAAUABhAGQAuwMgAGcAZQBuAGUAcgBhAGwAaQB6AGUAcwAgAHQAaABlACAAYgBlAGgAYQB2AGkAbwByAFwAbgAgACAAIAAgAG8AZgAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDIABhAG4AZAAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDIABiAHkAIABhAGwAbABvAHcAaQBuAGcAIABhAGwAbAAgAGYAbwB1AHIAIABzAGkAZABlAHMAIABvAGYAIABhAG4AIABhAHIAcgBhAHkAIAB0AG8AXABuACAAIAAgACAAYgBlACAAcABhAGQAZABlAGQAIABpAG4AIABhACAAcwBpAG4AZwBsAGUAIABvAHAAZQByAGEAdABpAG8AbgAuACAAUABhAGQAZABpAG4AZwAgAGMAbwB1AG4AdABzACAAbQBhAHkAIABiAGUAIABzAHUAcABwAGwAaQBlAGQAIABpAG4AZABlAHAAZQBuAGQAZQBuAHQAbAB5AFwAbgAgACAAIAAgAG8AcgAgAG8AbQBpAHQAdABlAGQAIABmAG8AcgAgAGMAbwBuAHYAZQBuAGkAZQBuAGMAZQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAIAAgACAALQAgAFIAbwB3AHMAIAB0AG8AIABwAGEAZAAgAGEAYgBvAHYAZQAgAHQAaABlACAAYQByAHIAYQB5AC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAHIAbwB3AHMAXwBhAGYAdABlAHIAXQAgACAAIAAtACAAUgBvAHcAcwAgAHQAbwAgAHAAYQBkACAAYgBlAGwAbwB3ACAAKABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAKQAuAFwAbgAgACAAIAAgAFsAYwBvAGwAcwBfAGIAZQBmAG8AcgBlAF0AIAAgAC0AIABDAG8AbAB1AG0AbgBzACAAdABvACAAcABhAGQAIABsAGUAZgB0ACAAKABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAKQAuAFwAbgAgACAAIAAgAFsAYwBvAGwAcwBfAGEAZgB0AGUAcgBdACAAIAAgAC0AIABDAG8AbAB1AG0AbgBzACAAdABvACAAcABhAGQAIAByAGkAZwBoAHQAIAAoAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQApAC4AXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACAAcABhAGQAZABpAG4AZwAgAHYAYQBsAHUAZQAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABcACIAXAAiACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABBAG4AeQAgAG8AbQBpAHQAdABlAGQAIABwAGEAZABkAGkAbgBnACAAYwBvAHUAbgB0ACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlAFwAbgAgACAAIAAgACAAIAAoAFQAaABpAHMAIABhAGwAbABvAHcAcwAgAGYAbwByACAAZQBhAHMAeQAgAHAAYQBkAGQAaQBuAGcAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPQBQAGEAZAC7AygAYQByAHIAYQB5ACwAMwApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGQAZABzACAAcABhAGQAZABpAG4AZwAgAGMAbwB1AG4AdAAgAG8AZgAgADMAIABhAGwAbAAgAGEAcgBvAHUAbgBkACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAiICAATgBlAGcAYQB0AGkAdgBlACAAbwByACAAdABlAHgAdAAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwAgAHIAZQB0AHUAcgBuACAAXAAiACMAVABFAFgAVAAtAFAAQQBEACEAXAAiAC4AXABuACAAIAAgACAAIiAgAEQAZQBsAGUAZwBhAHQAZQBzACAAcgBvAHcAIABwAGEAZABkAGkAbgBnACAAdABvACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMgAGEAbgBkACAAYwBvAGwAdQBtAG4AIABwAGEAZABkAGkAbgBnACAAdABvACAASQBuAHMAdQBsAGEAdABlAEMAbwBsAHMAuwMuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBQAGEAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUALABcAG4AIAAgACAAIABbAHIAbwB3AHMAXwBhAGYAdABlAHIAXQAsAFwAbgAgACAAIAAgAFsAYwBvAGwAcwBfAGIAZQBmAG8AcgBlAF0ALABcAG4AIAAgACAAIABbAGMAbwBsAHMAXwBhAGYAdABlAHIAXQAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGMAYQBsAGEAcgBpAHoAZQAgAGEAbgB5ACAAYQByAHIAYQB5ACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAASQC7AywAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAeAAsACAASQBOAEQARQBYACgAeAAsACAAMQAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwAgACgAbwBtAGkAdAB0AGUAZAAgAJIhIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAKQBcAG4AIAAgACAAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUALAAgACAAIAAgACAAIAAgACAASQC7AygAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkALABcAG4AIAAgACAAIAByAG8AdwBzAF8AYQBmAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAASQC7AygASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBzAF8AYQBmAHQAZQByACkALAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgApACkALABcAG4AIAAgACAAIABjAG8AbABzAF8AYgBlAGYAbwByAGUALAAgACAAIAAgACAAIAAgACAASQC7AygASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABjAG8AbABzAF8AYgBlAGYAbwByAGUAKQAsACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIABjAG8AbABzAF8AYgBlAGYAbwByAGUAKQApACwAXABuACAAIAAgACAAYwBvAGwAcwBfAGEAZgB0AGUAcgAsACAAIAAgACAAIAAgACAAIAAgAEkAuwMoAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAcwBfAGEAZgB0AGUAcgApACwAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUALAAgAGMAbwBsAHMAXwBhAGYAdABlAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAZQAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEkAbgBzAD8ALAAgACAAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAByAG8AdwBzAF8AYgBlAGYAbwByAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAHIAbwB3AHMAXwBhAGYAdABlAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAGMAbwBsAHMAXwBiAGUAZgBvAHIAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAYwBvAGwAcwBfAGEAZgB0AGUAcgApACkALABcAG4AXABuACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABJAG4AcwA/ACwAIABcACIAIwBUAEUAWABUAC0AUABBAEQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAcgBvAHcAIABwAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgAHAAYQBkAGQAZQBkAF8AcgBvAHcAcwAsACAAIAAgACAAIAAgACAAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AygAYQByAHIAYQB5ACwAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUALAAgAHIAbwB3AHMAXwBhAGYAdABlAHIALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAGMAbwBsAHUAbQBuACAAcABhAGQAZABpAG4AZwBcAG4AIAAgACAAIABwAGEAZABkAGUAZABfAGEAbABsACwAIAAgACAAIAAgACAAIAAgACAASQBuAHMAdQBsAGEAdABlAEMAbwBsAHMAuwMoAHAAYQBkAGQAZQBkAF8AcgBvAHcAcwAsACAAYwBvAGwAcwBfAGIAZQBmAG8AcgBlACwAIABjAG8AbABzAF8AYQBmAHQAZQByACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIABwAGEAZABkAGUAZABfAGEAbABsAFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADEANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAIAAoAFAAYQBkAGQAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAZABkAHMAIAByAG8AdwBzACAAbwBmACAAcABhAGQAZABpAG4AZwAgAGIAZQBmAG8AcgBlACAAYQBuAGQALwBvAHIAIABhAGYAdABlAHIAIABhAG4AIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDXABuACAAIAAgACAAZwBlAG4AZQByAGEAbABpAHoAZQBzACAARQBYAFAAQQBOAEQAIABiAHkAIABzAHUAcABwAG8AcgB0AGkAbgBnACAAcwB5AG0AbQBlAHQAcgBpAGMAYQBsACAAcABhAGQAZABpAG4AZwAsACAAegBlAHIAbwARIHAAYQBkAGQAaQBuAGcAIABvAG4AIABlAGkAdABoAGUAcgBcAG4AIAAgACAAIABzAGkAZABlACwAIABhAG4AZAAgAHMAYwBhAGwAYQByAGkAegBlAGQAIABwAGEAZABkAGkAbgBnACAAdgBhAGwAdQBlAHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAALQAgAEkAbgBwAHUAdAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIALAAgADEARAAsACAAbwByACAAMgBEACkALgBcAG4AIAAgACAAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAIAAgACAALQAgAFIAbwB3AHMAIAB0AG8AIABwAGEAZAAgAGEAYgBvAHYAZQAgAHQAaABlACAAYQByAHIAYQB5AC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAHIAbwB3AHMAXwBhAGYAdABlAHIAXQAgACAALQAgAFIAbwB3AHMAIAB0AG8AIABwAGEAZAAgAGIAZQBsAG8AdwAgACgAZABlAGYAYQB1AGwAdABzACAAdABvACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkALgBcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACAAIAAgACAALQAgAFMAYwBhAGwAYQByACAAcABhAGQAZABpAG4AZwAgAHYAYQBsAHUAZQAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABcACIAXAAiACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIABiAG8AdABoACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAYQBuAGQAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAPQAgADAALAAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBzACAAcgBlAHQAdQByAG4AZQBkAC4AXABuACAAIAAgACAAIiAgAHIAbwB3AHMAXwBhAGYAdABlAHIAIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAIAB1AG4AbABlAHMAcwAgAGUAeABwAGwAaQBjAGkAdABsAHkAIABzAGUAdAAgAHQAbwAgADAALgBcAG4AIAAgACAAIAAiICAAcABhAGQAXwB3AGkAdABoACAAaQBzACAAcwBjAGEAbABhAHIAaQB6AGUAZAAgAHQAbwAgAGEAIAAxANcAMQAgAHYAYQBsAHUAZQAuAFwAbgAgACAAIAAgACIgIABOAGUAZwBhAHQAaQB2AGUAIABvAHIAIAB0AGUAeAB0ACAAcABhAGQAZABpAG4AZwAgAGMAbwB1AG4AdABzACAAcgBlAHQAdQByAG4AIABcACIAIwBSAE8AVwBTAC0AQgBFAEYATwBSAEUALwBBAEYAVABFAFIAIQBcACIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAXABuACAAIAAgACAAWwByAG8AdwBzAF8AYQBmAHQAZQByAF0ALABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgAgACAAIAAgAHIAbwB3AHMAXwBhAGYAdABlAHIALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AHMAXwBhAGYAdABlAHIAKQAsACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIAByAG8AdwBzAF8AYQBmAHQAZQByACkALABcAG4AIAAgACAAIABwAGEAZABfAHcAaQB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGEAZABfAHcAaQB0AGgAKQAsACAAXAAiAFwAIgAsACAAcABhAGQAXwB3AGkAdABoACkALAAgADEALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAUABhAGQAQwBvAHUAbgB0AD8ALAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAcgBvAHcAcwBfAGEAZgB0AGUAcgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgADwAIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAbwB3AHMAXwBhAGYAdABlAHIAIAA8ACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwARIHAAYQBkAGQAaQBuAGcAIABzAGMAZQBuAGEAcgBpAG8AXABuACAAIAAgACAATgBvAFAAYQBkAGQAaQBuAGcAPwAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAPQAgADAALAAgAHIAbwB3AHMAXwBhAGYAdABlAHIAIAA9ACAAMAApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAUABhAGQAQwBvAHUAbgB0AD8ALAAgAFwAIgAjAFIATwBXAFMALQBCAEUARgBPAFIARQAvAEEARgBUAEUAUgAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBQAGEAZABkAGkAbgBnAD8ALAAgAGEAcgByAGEAeQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAZABkAGkAbgBnACAAYgBsAG8AYwBrAHMAXABuACAAIAAgACAAcABhAGQAXwBiAGUAZgBvAHIAZQAsACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAcABhAGQAXwB3AGkAdABoACwAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUALAAgAHcALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuACAAIAAgACAAcABhAGQAXwBhAGYAdABlAHIALAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAcABhAGQAXwB3AGkAdABoACwAIAByAG8AdwBzAF8AYQBmAHQAZQByACwAIAB3ACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABiAGUAZgBvAHIAZQBfAG8AbgBsAHkAPwAsACAAIAAgACAAIAAgACAAQQBOAEQAKAByAG8AdwBzAF8AYgBlAGYAbwByAGUAIAA8AD4AIAAwACwAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAPQAgADAAKQAsAFwAbgAgACAAIAAgAGEAZgB0AGUAcgBfAG8AbgBsAHkAPwAsACAAIAAgACAAIAAgACAAIABBAE4ARAAoAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgAD0AIAAwACwAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAPAA+ACAAMAApACwAXABuACAAIAAgACAAZgB1AGwAbAB5AF8AaQBuAHMAdQBsAGEAdABlAGQAPwAsACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAPAA+ACAAMAAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAgADwAPgAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBuAGQAYQByAGQAIABFAFgAUABBAE4ARAAgAGYAbwByACAAYQBmAHQAZQByABEgbwBuAGwAeQAgAGMAYQBzAGUAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAbwB3AHMAXwBhAGYAdABlAHIAIAArACAAaAAsAFwAbgAgACAAIAAgAGUAeABwAGEAbgBkAF8AbwBuAGwAeQAsACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAGEAcgByAGEAeQAsACAAawAsACAAdwAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQByAHIAYQBuAGcAZQBtAGUAbgB0AHMAXABuACAAIAAgACAAaQBuAHMAdQBsAGEAdABlAF8AYgBlAGYAbwByAGUALAAgACAAIAAgAFYAUwBUAEEAQwBLACgAcABhAGQAXwBiAGUAZgBvAHIAZQAsACAAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABpAG4AcwB1AGwAYQB0AGUAXwBhAGwAbAAsACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABwAGEAZABfAGIAZQBmAG8AcgBlACwAIABhAHIAcgBhAHkALAAgAHAAYQBkAF8AYQBmAHQAZQByACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAdQBsAGwAeQBfAGkAbgBzAHUAbABhAHQAZQBkAD8ALAAgAGkAbgBzAHUAbABhAHQAZQBfAGEAbABsACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYgBlAGYAbwByAGUAXwBvAG4AbAB5AD8ALAAgACAAIABpAG4AcwB1AGwAYQB0AGUAXwBiAGUAZgBvAHIAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGUAeABwAGEAbgBkAF8AbwBuAGwAeQApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADYAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnACAAKABQAGEAZABkAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQBkAGQAcwAgAGMAbwBsAHUAbQBuAHMAIABvAGYAIABwAGEAZABkAGkAbgBnACAAYgBlAGYAbwByAGUAIABhAG4AZAAvAG8AcgAgAGEAZgB0AGUAcgAgAGEAbgAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuACAASQBuAHMAdQBsAGEAdABlAEMAbwBsAHMAuwMgAGkAcwBcAG4AIAAgACAAIAB0AGgAZQAgAGMAbwBsAHUAbQBuABEgbwByAGkAZQBuAHQAZQBkACAAYwBvAHUAbgB0AGUAcgBwAGEAcgB0ACAAdABvACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMuACAAVABoAGUAIABhAHIAcgBhAHkAIABpAHMAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAdABvAFwAbgAgACAAIAAgAHYAZQByAHQAaQBjAGEAbAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAsACAAcABhAGQAZABlAGQAIAB2AGkAYQAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDLAAgAGEAbgBkACAAcgBlAHMAdABvAHIAZQBkACAAdABvACAAaQB0AHMAIABvAHIAaQBnAGkAbgBhAGwAXABuACAAIAAgACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAYwBvAGwAdQBtAG4AcwBfAGIAZQBmAG8AcgBlACAAIAAgAC0AIABDAG8AbAB1AG0AbgBzACAAdABvACAAcABhAGQAIAB0AG8AIAB0AGgAZQAgAGwAZQBmAHQALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAYwBvAGwAdQBtAG4AcwBfAGEAZgB0AGUAcgBdACAAIAAtACAAQwBvAGwAdQBtAG4AcwAgAHQAbwAgAHAAYQBkACAAdABvACAAdABoAGUAIAByAGkAZwBoAHQAIAAoAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAGMAbwBsAHUAbQBuAHMAXwBiAGUAZgBvAHIAZQApAC4AXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAHAAYQBkAGQAaQBuAGcAIAB2AGEAbAB1AGUAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAYgBvAHQAaAAgAGMAbwBsAHUAbQBuAHMAXwBiAGUAZgBvAHIAZQAgAGEAbgBkACAAYwBvAGwAdQBtAG4AcwBfAGEAZgB0AGUAcgAgAD0AIAAwACwAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgAgACAAIAAgACIgIABjAG8AbAB1AG0AbgBzAF8AYQBmAHQAZQByACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAYwBvAGwAdQBtAG4AcwBfAGIAZQBmAG8AcgBlACAAdQBuAGwAZQBzAHMAIABlAHgAcABsAGkAYwBpAHQAbAB5ACAAcwBlAHQAIAB0AG8AIAAwAC4AXABuACAAIAAgACAAIiAgAHAAYQBkAF8AdwBpAHQAaAAgAGkAcwAgAHMAYwBhAGwAYQByAGkAegBlAGQAIAB0AG8AIABhACAAMQDXADEAIAB2AGEAbAB1AGUALgBcAG4AIAAgACAAIAAiICAATgBlAGcAYQB0AGkAdgBlACAAcABhAGQAZABpAG4AZwAgAGMAbwB1AG4AdABzACAAaABhAGwAdAAgAGkAbgBzAGkAZABlACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABjAG8AbAB1AG0AbgBzAF8AYgBlAGYAbwByAGUALABcAG4AIAAgACAAIABbAGMAbwBsAHUAbQBuAHMAXwBhAGYAdABlAHIAXQAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHQAbwAgAHYAZQByAHQAaQBjAGEAbAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwB2ACwAIAAgACAAIAAgACAAIAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAcgBvAHcAESBwAGEAZABkAGkAbgBnACAAaQBuACAAdgBlAHIAdABpAGMAYQBsACAAcwBwAGEAYwBlAFwAbgAgACAAIAAgAHAAYQBkAGQAZQBkAF8AdgAsACAAIAAgACAAIAAgACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMoAGEAcgByAGEAeQBfAHYALAAgAGMAbwBsAHUAbQBuAHMAXwBiAGUAZgBvAHIAZQAsACAAYwBvAGwAdQBtAG4AcwBfAGEAZgB0AGUAcgAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgAG8AcgBpAGcAaQBuAGEAbAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAcABhAGQAZABlAGQAXwB2ACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABNAGEAZwBuAGkAZgB5ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnACAAKABJAG4AdABlAHIAcABvAGwAYQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAcABhAG4AZABzACAAZQBhAGMAaAAgAGUAbABlAG0AZQBuAHQAIABvAGYAIABhAG4AIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYQAgAGIAbABvAGMAawAgAG8AZgAgAHMAcABlAGMAaQBmAGkAZQBkACAAaABlAGkAZwBoAHQAIABhAG4AZABcAG4AIAAgACAAIAB3AGkAZAB0AGgAIAB1AHMAaQBuAGcAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAaQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgAuACAAUwB1AHAAcABvAHIAdABzACAAcwBjAGEAbABhAHIAcwAsACAAMQBEACAAYQByAHIAYQB5AHMALAAgAGEAbgBkAFwAbgAgACAAIAAgADIARAAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgAEkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAHQAbwAgAG0AYQBnAG4AaQBmAHkALgBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAgACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwBzACAAZgBvAHIAIABlAGEAYwBoACAAbQBhAGcAbgBpAGYAaQBlAGQAIABlAGwAZQBtAGUAbgB0ACAAKABwAG8AcwBpAHQAaQB2AGUAIABzAGMAYQBsAGEAcgApAC4AXABuACAAIAAgACAAdwBpAGQAdABoACAAIAAgACAAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAG0AYQBnAG4AaQBmAGkAZQBkACAAZQBsAGUAbQBlAG4AdAAgACgAcABvAHMAaQB0AGkAdgBlACAAcwBjAGEAbABhAHIAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAGgAZQBpAGcAaAB0ACAAYQBuAGQAIAB3AGkAZAB0AGgAIABtAHUAcwB0ACAAYgBlACAAcwBjAGEAbABhAHIALAAgAG4AdQBtAGUAcgBpAGMALAAgAGEAbgBkACAAPgAgADAALgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAG4AZQBhAHIAZQBzAHQAESBuAGUAaQBnAGgAYgBvAHIAIABlAHgAcABhAG4AcwBpAG8AbgAgAHYAaQBhACAAaQBuAGQAZQB4ACAAcgBlAHAAbABpAGMAYQB0AGkAbwBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0AYQBnAG4AaQBmAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAaABlAGkAZwBoAHQALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuAEkARgAoAE8AUgAoAEMATwBVAE4AVAAoAGgAZQBpAGcAaAB0ACkAIAA8AD4AIAAxACwAIABDAE8AVQBOAFQAKAB3AGkAZAB0AGgAKQAgADwAPgAgADEAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAGgAZQBpAGcAaAB0ACkALAAgAEkAUwBUAEUAWABUACgAdwBpAGQAdABoACkAKQAsAFwAIgAjAFQARQBYAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABoAGUAaQBnAGgAdAAgADwAPQAgADAALAAgAHcAaQBkAHQAaAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzACAAbwBmACAAbQBhAGcAbgBpAGYAaQBlAGQAIABvAHUAdABwAHUAdABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAKgAgAGgAZQBpAGcAaAB0ACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgACoAIAB3AGkAZAB0AGgALABcAG4AXABuACAAIAAgACAALwAvACAATQBlAHMAaAAgAGcAcgBpAGQAIABmAG8AcgAgAG4AZQBhAHIAZQBzAHQAESBuAGUAaQBnAGgAYgBvAHIAIAByAGUAcABsAGkAYwBhAHQAaQBvAG4AXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKABpACwALAAsACAAMQAgAC8AIABoAGUAaQBnAGgAdAApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAagAsACAAMQAsACAAMAApACkALABcAG4AXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAagAsACwAIAAxACAALwAgAHcAaQBkAHQAaAApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACoAIABTAEUAUQBVAEUATgBDAEUAKABpACwALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGUAcgByAGUAZAAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAeAAoACkALAAgAHkAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADgAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABaAG8AbwBtALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnACAAKABLAGUAcgBuAGUAbAAgAEUAeABwAGEAbgBzAGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHAAYQBuAGQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAbwBmACAAYQBuACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGEAIABiAGwAbwBjAGsAIAB3AGgAbwBzAGUAIABzAGkAegBlACAAbQBhAHQAYwBoAGUAcwAgAHQAaABlAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACAA1wAgAHcAaQBkAHQAaAAgAG8AZgAgAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAuACAARQBhAGMAaAAgAGUAeABwAGEAbgBkAGUAZAAgAGIAbABvAGMAawAgAGkAcwAgAGYAbwByAG0AZQBkACAAYgB5ACAAYQBkAGQAaQBuAGcAIAB0AGgAZQBcAG4AIAAgACAAIABlAGwAZQBtAGUAbgB0ACAAdgBhAGwAdQBlACAAdABvACAAdABoAGUAIAB6AG8AbwBtAF8AawBlAHIAbgBlAGwALgAgAEkAbgB0AGUAbgBkAGUAZAAgAHMAdAByAGkAYwB0AGwAeQAgAGYAbwByACAAbgB1AG0AZQByAGkAYwAgAGEAcgByAGEAeQBzACAAYQBuAGQAXABuACAAIAAgACAAbgB1AG0AZQByAGkAYwAgAGsAZQByAG4AZQBsAHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABuAHUAbQBlAHIAaQBjACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgBzACAAYQBsAGwAbwB3AGUAZAApAC4AXABuACAAIAAgACAAegBvAG8AbQBfAGsAZQByAG4AZQBsACAAIAAtACAATgB1AG0AZQByAGkAYwAgAGsAZQByAG4AZQBsACAAZABlAGYAaQBuAGkAbgBnACAAZQB4AHAAYQBuAHMAaQBvAG4AIABoAGUAaQBnAGgAdAAgAGEAbgBkACAAdwBpAGQAdABoAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAEEAUgBSAEEAWQAhAFwAIgAgAGkAZgAgAGEAbgB5ACAAYQByAHIAYQB5ACAAZQBsAGUAbQBlAG4AdABzACAAYQByAGUAIABuAG8AbgARIG4AdQBtAGUAcgBpAGMALgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAEsARQBSAE4ARQBMACEAXAAiACAAaQBmACAAYQBuAHkAIABrAGUAcgBuAGUAbAAgAGUAbABlAG0AZQBuAHQAcwAgAGEAcgBlACAAbgBvAG4AESBuAHUAbQBlAHIAaQBjAC4AXABuACAAIAAgACAAIiAgAEkAZgAgAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAgAGkAcwAgADEA1wAxACwAIABaAG8AbwBtALsDIAByAGUAZAB1AGMAZQBzACAAdABvACAAYQByAHIAYQB5ACAAKwAgAHMAYwBhAGwAYQByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFoAbwBvAG0AuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAegBvAG8AbQBfAGsAZQByAG4AZQBsACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASwBlAHIAbgBlAGwAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAegBvAG8AbQBfAGsAZQByAG4AZQBsACkALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBUAGUAeAB0AEsAZQByAG4AZQBsAD8ALAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAApACkALABcAG4AIAAgACAAIABJAHMAVABlAHgAdABBAHIAcgBhAHkAPwAsACAAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKABhAHIAcgBhAHkAKQApACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAEsAZQByAG4AZQBsAD8ALAAgACAAIAAgAEEATgBEACgAaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAVABlAHgAdABLAGUAcgBuAGUAbAA/ACwAIABcACIAIwBLAEUAUgBOAEUATAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBUAGUAeAB0AEEAcgByAGEAeQA/ACwAIABcACIAIwBBAFIAUgBBAFkAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgBLAGUAcgBuAGUAbAA/ACwAIABhAHIAcgBhAHkAIAArACAAegBvAG8AbQBfAGsAZQByAG4AZQBsACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AdQB0AHAAdQB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkAIAAqACAAaABlAGkAZwBoAHQALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAAqACAAdwBpAGQAdABoACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AZQBzAGgAIABnAHIAaQBkACAAZgBvAHIAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAZQB4AHAAYQBuAHMAaQBvAG4AXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAE4AVAAoAFMARQBRAFUARQBOAEMARQAoAGkALAAsACwAIAAxACAALwAgAGgAZQBpAGcAaAB0ACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAagAsACAAMQAsACAAMAApACkALABcAG4AXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAE4AVAAoAFMARQBRAFUARQBOAEMARQAoACwAIABqACwALAAgADEAIAAvACAAdwBpAGQAdABoACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACoAIABTAEUAUQBVAEUATgBDAEUAKABpACwALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBkAGUAZAAgAGEAcgByAGEAeQAgACgAbgBlAGEAcgBlAHMAdAARIG4AZQBpAGcAaABiAG8AcgApAFwAbgAgACAAIAAgAHoAbwBvAG0AZQBkACwAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIAB4ACgAKQAsACAAeQAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAGkAegBlACAAawBlAHIAbgBlAGwAIAB0AG8AIABtAGEAdABjAGgAIAB6AG8AbwBtAGUAZAAgAGIAbABvAGMAawAgAHMAdAByAHUAYwB0AHUAcgBlAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAB6AG8AbwBtAGUAZAAoACkAKQAgAC8AIABoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAB6AG8AbwBtAGUAZAAoACkAKQAgAC8AIAB3AGkAZAB0AGgALABcAG4AIAAgACAAIABrAGUAcgBuAGUAbABfAG0AYQBnACwAIABSAGUAcwBpAHoAZQC7AygAegBvAG8AbQBfAGsAZQByAG4AZQBsACwAIABoACwAIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBpAG4AYQBsACAAegBvAG8AbQBlAGQAIABvAHUAdABwAHUAdABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAegBvAG8AbQBlAGQAKAApACAAKwAgAGsAZQByAG4AZQBsAF8AbQBhAGcALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8ALwAgAFsARwBBAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAC8ALwAgAC0ALQAtACMAIwAgADAANAAgAC0AIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQBcAG4ALwAvACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgAGYAdQBuAGMAdABpAG8AbgBzACAAcAByAG8AdgBpAGQAZQAgAGEAIAB0AG8AbwBsAGsAaQB0ACAAZgBvAHIAIABzAHQAcgB1AGMAdAB1AHIAYQBsACAAZQBkAGkAdABpAG4AZwAgAG8AZgBcAG4AIAAgACAAIAAyAEQAIABhAHIAcgBhAHkAcwAuACAAVABoAGUAcwBlACAAbwBwAGUAcgBhAHQAbwByAHMAIABzAHUAcABwAG8AcgB0ACAAZABlAGwAZQB0AGkAbwBuACwAIABzAGUAbABlAGMAdABpAG8AbgAsACAAZgBpAGwAdABlAHIAaQBuAGcALAAgAHIAbwBsAGwAaQBuAGcALABcAG4AIAAgACAAIABlAHgAcABhAG4AcwBpAG8AbgAsACAAYQBuAGQAIABzAHQAcgB1AGMAdAB1AHIAYQBsACAAbQBhAHAAcABpAG4AZwAuAFwAbgBcAG4AIAAgACAAIABTAHUAYgARIGMAYQB0AGUAZwBvAHIAaQBlAHMAOgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAARABlAGwAZQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAZQB0AGUAUgBvAHcAcwC7AywAIABEAGUAbABlAHQAZQBDAG8AbABzALsDLAAgAEQAZQBsAGUAdABlAFcAaABlAHIAZQC7AywAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGkAbgBjAGgAuwMsACAAUgBlAG0AbwB2AGUAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABFAHgAcABhAG4AcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEsAcgBvAG4AZQBjAGsAZQByAFAAcgBvAGQAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAARgBpAGwAdABlAHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAHgAYwBsAHUAZABlALsDLAAgAFMAbgBhAHAAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUgBvAGwAbABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAaABpAGYAdAC7AywAIABTAGgAaQBmAHQAUgBvAHcAcwC7AywAIABTAGgAaQBmAHQAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABTAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAbQBiAGUAZAC7AywAIABLAGUAZQBwAFIAbwB3AHMAuwMsACAASwBlAGUAcABDAG8AbABzALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgBsAG8AYwBrAE0AYQBwALsDLAAgAEMAbwBuAHYAbwBsAHYAZQC7AywAIABGAG8AbABkALsDLAAgAEoAbwBpAG4AMgBEALsDXABuACoALwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABlAGwAZQB0AGUAUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEQAZQBsAGUAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUwB0AHIAZQBhAGsAuwMsACAAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEQAZQBsAGUAdABlAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAGEAcwBlAGQAIABvAG4AIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AcwAuACAAQQAgAHAAbwBzAGkAdABpAHYAZQBcAG4AIAAgACAAIABkAGUAbABlAHQAZQAgAHYAYQBsAHUAZQAgAHQAcgBpAG0AcwAgAHIAbwB3AHMAIABmAHIAbwBtACAAdABoAGUAIAB0AG8AcAAgAG8AZgAgAGUAYQBjAGgAIABzAHUAYgBnAHIAbwB1AHAAIAByAHUAbgA7ACAAYQAgAG4AZQBnAGEAdABpAHYAZQAgAGQAZQBsAGUAdABlAFwAbgAgACAAIAAgAHYAYQBsAHUAZQAgAHQAcgBpAG0AcwAgAHIAbwB3AHMAIABmAHIAbwBtACAAdABoAGUAIABiAG8AdAB0AG8AbQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGQAZQBsAGUAdABlACAAIAAgACAAIAAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACAAaQBuAHQAZQBnAGUAcgA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPgAgADAAIACSISAAdAByAGkAbQAgAGYAcgBvAG0AIAB0AG8AcAAgAG8AZgAgAGUAYQBjAGgAIAByAHUAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADwAIAAwACAAkiEgAHQAcgBpAG0AIABmAHIAbwBtACAAYgBvAHQAdABvAG0AIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACAAIAAtACAAUwB1AGIAZwByAG8AdQBwACAAbABhAGIAZQBsAHMAIAAoAHMAYQBtAGUAIABoAGUAaQBnAGgAdAAgAGEAcwAgAGEAcgByAGEAeQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAbwBuAGwAeQAgAG8AbgBlACAAcwB1AGIAZwByAG8AdQBwACAAZQB4AGkAcwB0AHMALAAgAEQAUgBPAFAAKAApACAAaQBzACAAdQBzAGUAZAAgAGEAcwAgAGEAIABmAGEAcwB0ACAAcABhAHQAaAAuAFwAbgAgACAAIAAgACIgIABkAGUAbABlAHQAZQAgAG0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIAOwAgAHQAZQB4AHQAIABvAHIAIAB2AGUAYwB0AG8AcgAgAGkAbgBwAHUAdABzACAAaABhAGwAdAAgAHcAaQB0AGgAIABhAG4AIABlAHIAcgBvAHIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABlAGwAZQB0AGUAUgBvAHcAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABkAGUAbABlAHQAZQAsAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAdQBiAGcAcgBvAHUAcAAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAE8AbgBlAFMAdQBiAEcAcgBvAHUAcAA/ACwAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAFUATgBJAFEAVQBFACgAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkAKQAgAD0AIAAxACwAXABuACAAIAAgACAARABpAHMAYwBhAHIAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgAEAAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkAIAA8AD4AIABSAE8AVwBTACgAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkALABcAG4AIAAgACAAIABJAHMAVABlAHgAdAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABkAGUAbABlAHQAZQApACwAXABuACAAIAAgACAATgBvAHQAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgATgBPAFQAKABJAHMAVABlAHgAdAA/ACkALAAgAEMATwBVAE4AVABBACgAZABlAGwAZQB0AGUAKQAgAD4AIAAxACkALABcAG4AIAAgACAAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgAEkAcwBUAGUAeAB0AD8ALAAgAE4AbwB0AFMAYwBhAGwAYQByAD8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHIAcgBvAHIAIABoAGEAbgBkAGwAaQBuAGcAXABuACAAIAAgACAAaABhAGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAHMAYwBlAG4AYQByAGkAbwBzACkALABcAG4AIAAgACAAIABlAHIAcgBvAHIAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAewBcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiADsAIABcACIAIwBUAEUAWABUACEAXAAiADsAIABcACIAIwBTAEMAQQBMAEEAUgAhAFwAIgB9ACwAXABuACAAIAAgACAAYQBsAGUAcgB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAUgBSAEEAWQBUAE8AVABFAFgAVAAoAEYASQBMAFQARQBSACgAZQByAHIAbwByAHMALAAgAHMAYwBlAG4AYQByAGkAbwBzACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAARABpAHMAYwBhAHIAZAAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAaABhAGwAdAAsACAAYQBsAGUAcgB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuADoAIAArAHQAbwBwACwAIAATIGIAbwB0AHQAbwBtAFwAbgAgACAAIAAgAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAHUAbgAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAYQBzAGMAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAGUAYQBrALsDKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUAKQAsAFwAbgAgACAAIAAgAGQAZQBzAGMAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAG8AdQBuAHQAZABvAHcAbgC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkALABcAG4AIAAgACAAIABkAGUAbABlAHQAZQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBCAFMAKABkAGUAbABlAHQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAaQBuAGQAZQB4ACAAYgBhAHMAZQBkACAAbwBuACAAcwBpAGcAbgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcwAgAD0AIAAtADEALAAgAGQAZQBzAGMAZQBuAGQALAAgAGEAcwBjAGUAbgBkACkALABcAG4AXABuACAAIAAgACAALwAvACAASwBlAGUAcAAgAHIAbwB3AHMAIAB3AGgAZQByAGUAIABpAG4AZABlAHgAIAA+ACAAZABlAGwAZQB0AGUAXABuACAAIAAgACAAawBlAGUAcAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgAaQBkAHgAIAA8AD0AIABkAGUAbABlAHQAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAawBlAGUAcAA/ACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABEAGUAbABlAHQAZQBDAG8AbABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARABlAGwAZQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABTAHQAcgBlAGEAawC7AywAIABDAG8AdQBuAHQAZABvAHcAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARABlAGwAZQB0AGUAcwAgAGMAbwBsAHUAbQBuAHMAIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGIAYQBzAGUAZAAgAG8AbgAgAGMAbwBuAHQAaQBnAHUAbwB1AHMAIABzAHUAYgBnAHIAbwB1AHAAIAByAHUAbgBzAC4AIABBACAAcABvAHMAaQB0AGkAdgBlAFwAbgAgACAAIAAgAGQAZQBsAGUAdABlACAAdgBhAGwAdQBlACAAdAByAGkAbQBzACAAYwBvAGwAdQBtAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAZQBmAHQAIABvAGYAIABlAGEAYwBoACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AOwAgAGEAIABuAGUAZwBhAHQAaQB2AGUAXABuACAAIAAgACAAZABlAGwAZQB0AGUAIAB2AGEAbAB1AGUAIAB0AHIAaQBtAHMAIABjAG8AbAB1AG0AbgBzACAAZgByAG8AbQAgAHQAaABlACAAcgBpAGcAaAB0AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAZABlAGwAZQB0AGUAIAAgACAAIAAgACAAIAAgACAAIAAtACAAUwBjAGEAbABhAHIAIABpAG4AdABlAGcAZQByADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA+ACAAMAAgAJIhIAB0AHIAaQBtACAAZgByAG8AbQAgAGwAZQBmAHQAIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA8ACAAMAAgAJIhIAB0AHIAaQBtACAAZgByAG8AbQAgAHIAaQBnAGgAdAAgAG8AZgAgAGUAYQBjAGgAIAByAHUAbgBcAG4AIAAgACAAIABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUAIAAgAC0AIABTAHUAYgBnAHIAbwB1AHAAIABsAGEAYgBlAGwAcwAgACgAcwBhAG0AZQAgAHcAaQBkAHQAaAAgAGEAcwAgAGEAcgByAGEAeQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAbwBuAGwAeQAgAG8AbgBlACAAcwB1AGIAZwByAG8AdQBwACAAZQB4AGkAcwB0AHMALAAgAEQAUgBPAFAAKAApACAAaQBzACAAdQBzAGUAZAAgAGEAcwAgAGEAIABmAGEAcwB0ACAAcABhAHQAaAAuAFwAbgAgACAAIAAgACIgIABkAGUAbABlAHQAZQAgAG0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIAOwAgAHQAZQB4AHQAIABvAHIAIAB2AGUAYwB0AG8AcgAgAGkAbgBwAHUAdABzACAAaABhAGwAdAAgAHcAaQB0AGgAIABhAG4AIABlAHIAcgBvAHIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABlAGwAZQB0AGUAQwBvAGwAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABkAGUAbABlAHQAZQAsAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAdQBiAGcAcgBvAHUAcAAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAE8AbgBlAFMAdQBiAEcAcgBvAHUAcAA/ACwAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAFUATgBJAFEAVQBFACgAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACwAIAAxACkAKQAgAD0AIAAxACwAXABuACAAIAAgACAARABpAHMAYwBhAHIAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgACwAIABAAGQAZQBsAGUAdABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACAAPAA+ACAAQwBPAEwAVQBNAE4AUwAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAASQBzAFQAZQB4AHQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAZABlAGwAZQB0AGUAKQAsAFwAbgAgACAAIAAgAE4AbwB0AFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgASQBzAFQAZQB4AHQAPwApACwAIABDAE8AVQBOAFQAQQAoAGQAZQBsAGUAdABlACkAIAA+ACAAMQApACwAXABuACAAIAAgACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABJAHMAVABlAHgAdAA/ACwAIABOAG8AdABTAGMAYQBsAGEAcgA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQByAHIAbwByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAGgAYQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABzAGMAZQBuAGEAcgBpAG8AcwApACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgA7ACAAXAAiACMAVABFAFgAVAAhAFwAIgA7ACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIAfQAsAFwAbgAgACAAIAAgAGEAbABlAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAFIAUgBBAFkAVABPAFQARQBYAFQAKABGAEkATABUAEUAUgAoAGUAcgByAG8AcgBzACwAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAMAApACkALABcAG4AXABuACAAIAAgACAASQBGACgATwBuAGUAUwB1AGIARwByAG8AdQBwAD8ALAAgAEQAaQBzAGMAYQByAGQALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGgAYQBsAHQALAAgAGEAbABlAHIAdAAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgA6ACAAKwBsAGUAZgB0ACwAIAATIHIAaQBnAGgAdABcAG4AIAAgACAAIABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGQAZQBsAGUAdABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgB1AG4AIABpAG4AZABpAGMAZQBzACAAKABoAG8AcgBpAHoAbwBuAHQAYQBsACkAXABuACAAIAAgACAAYQBzAGMAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAGUAYQBrALsDKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALAAgAFQAUgBVAEUAKQAsAFwAbgAgACAAIAAgAGQAZQBzAGMAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAG8AdQBuAHQAZABvAHcAbgC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACwAIABUAFIAVQBFACkALABcAG4AIAAgACAAIABkAGUAbABlAHQAZQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBCAFMAKABkAGUAbABlAHQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAaQBuAGQAZQB4ACAAYgBhAHMAZQBkACAAbwBuACAAcwBpAGcAbgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcwAgAD0AIAAtADEALAAgAGQAZQBzAGMAZQBuAGQALAAgAGEAcwBjAGUAbgBkACkALABcAG4AXABuACAAIAAgACAALwAvACAASwBlAGUAcAAgAGMAbwBsAHUAbQBuAHMAIAB3AGgAZQByAGUAIABpAG4AZABlAHgAIAA+ACAAZABlAGwAZQB0AGUAXABuACAAIAAgACAAawBlAGUAcAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgAaQBkAHgAIAA8AD0AIABkAGUAbABlAHQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAHUAbQBuABEgdwBpAHMAZQAgAGYAaQBsAHQAZQByAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAawBlAGUAcAA/ACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAwADMAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABEAGUAbABlAHQAZQBXAGgAZQByAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABEAGUAbABlAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBtAG8AdgBlAHMAIAB2AGUAcgB0AGkAYwBhAGwAIABhAG4AZAAgAGgAbwByAGkAegBvAG4AdABhAGwAIAB2AGUAYwB0AG8AcgBzACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAGEAcwBlAGQAIABvAG4AIABhACAAcAByAGUAZABpAGMAYQB0AGUAXABuACAAIAAgACAATABhAG0AYgBkAGEALgAgAFQAaABlACAAcAByAGUAZABpAGMAYQB0AGUAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAZQBhAGMAaAAgAHIAbwB3ACAAYQBuAGQAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AOwAgAGEAbgB5ACAAdgBlAGMAdABvAHIAIABmAG8AcgBcAG4AIAAgACAAIAB3AGgAaQBjAGgAIAB0AGgAZQAgAHAAcgBlAGQAaQBjAGEAdABlACAAcgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAHMAIAByAGUAbQBvAHYAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgAC0AIABMAGEAbQBiAGQAYQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABlAGEAYwBoACAAcgBvAHcAIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAdgBlAGMAdABvAHIALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABUAGgAZQAgAHAAcgBlAGQAaQBjAGEAdABlACAAaQBzACAAZQB2AGEAbAB1AGEAdABlAGQAIABpAG4AZABlAHAAZQBuAGQAZQBuAHQAbAB5ACAAZgBvAHIAIAByAG8AdwBzACAAKABCAFkAUgBPAFcAKQAgAGEAbgBkACAAYwBvAGwAdQBtAG4AcwAgACgAQgBZAEMATwBMACkALgBcAG4AIAAgACAAIAAiICAASQBmACAAbgBvACAAcgBvAHcAcwAgAG8AcgAgAGMAbwBsAHUAbQBuAHMAIABhAHIAZQAgAHIAZQBtAG8AdgBlAGQALAAgAFwAIgAjAEUATQBQAFQAWQAtAEEAUgBSAEEAWQAhAFwAIgAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAGUAbABlAHQAZQBXAGgAZQByAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAcwBlAHEAdQBlAG4AYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAUgBPAFcAUwAoAGEAcgByAGEAeQApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBlAGcAYQB0AGUAZAAgAHAAcgBlAGQAaQBjAGEAdABlACAAKABUAFIAVQBFACAAPQAgAGsAZQBlAHAAKQBcAG4AIAAgACAAIABmAG4ALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALAAgAE4ATwBUACgAZgB1AG4AYwB0AGkAbwBuACgAdgApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAdABvACAAawBlAGUAcABcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABJAEYAKABCAFkAUgBPAFcAKABhAHIAcgBhAHkALAAgAGYAbgApACwAIABpACwAIABOAEEAKAApACkALAAgADIAKQAsAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBSAE8AVwAoAEkARgAoAEIAWQBDAE8ATAAoAGEAcgByAGEAeQAsACAAZgBuACkALAAgAGoALAAgAE4AQQAoACkAKQAsACAAMgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwAgAHIAZQBtAG8AdgBhAGwAcwA/AFwAbgAgACAAIAAgAEkAcwBFAG0AcAB0AHkAPwAsACAAIAAgAEEATgBEACgASQBTAEUAUgBSAE8AUgAoAGEAKQAsACAASQBTAEUAUgBSAE8AUgAoAGIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AZQB3ACAAcwBoAGEAcABlAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIABhACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIAB5ACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIABiACAAKgAgAFMARQBRAFUARQBOAEMARQAoAHgALAAgACwAIAAxACwAIAAwACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAASQBGACgASQBzAEUAbQBwAHQAeQA/ACwAIABcACIAIwBFAE0AUABUAFkALQBBAFIAUgBBAFkAIQBcACIALAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAcgAsACAAYwApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABQAGkAbgBjAGgAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABEAGUAbABlAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBtAG8AdgBlAHMAIABhAG4AeQAgAGYAdQBsAGwAIAByAG8AdwBzACAAbwByACAAYwBvAGwAdQBtAG4AcwAgAHcAaABvAHMAZQAgAGMAZQBsAGwAcwAgAGEAbABsACAAaABhAHYAZQAgAEwARQBOACgAYwBlAGwAbAApACAAPQAgADAALgAgAFIAbwB3AHMAIABvAHIAXABuACAAIAAgACAAYwBvAGwAdQBtAG4AcwAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABvAG4AbAB5ACAAZQBtAHAAdAB5ACAAcwB0AHIAaQBuAGcAcwAgAG8AcgAgAGUAcgByAG8AcgBzACAAYQByAGUAIABkAGkAcwBjAGEAcgBkAGUAZAAuACAAUABpAG4AYwBoALsDIABpAHMAIABhAFwAbgAgACAAIAAgAHMAdAByAHUAYwB0AHUAcgBhAGwAIABjAGwAZQBhAG4AdQBwACAAbwBwAGUAcgBhAHQAbwByACAAZgBvAHIAIAB0AHIAaQBtAG0AaQBuAGcAIAB3AGgAaQB0AGUAcwBwAGEAYwBlABEgbwBuAGwAeQAgAG8AcgAgAG4AdQBsAGwAIAByAGUAZwBpAG8AbgBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdwBoAGkAYwBoACAAZQBtAHAAdAB5ACAAcgBvAHcAcwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBzACAAZQBtAHAAdAB5ACwAIABQAGkAbgBjAGgAuwMgAHIAZQB0AHUAcgBuAHMAIAAwAC4AXABuACAAIAAgACAAIiAgAEUAcgByAG8AcgBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAbgBvAG4AESBlAG0AcAB0AHkAOwAgAG8AbgBsAHkAIAByAG8AdwBzAC8AYwBvAGwAdQBtAG4AcwAgAHcAaABlAHIAZQAgAEwARQBOACgAYwBlAGwAbAApACAAPQAgADAAIABmAG8AcgBcAG4AIAAgACAAIAAgACAAYQBsAGwAIABjAGUAbABsAHMAIABhAHIAZQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AIAAgACAAIAAiICAAUABpAG4AYwBoALsDIABwAHIAZQBzAGUAcgB2AGUAcwAgAHQAaABlACAAZABpAG0AZQBuAHMAaQBvAG4AYQBsAGkAdAB5ACAAbwBmACAAbgBvAG4AESBlAG0AcAB0AHkAIAByAGUAZwBpAG8AbgBzACAAYQBuAGQAIABkAG8AZQBzACAAbgBvAHQAIABhAGwAdABlAHIAXABuACAAIAAgACAAIAAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBuAHQAZQBuAHQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABpAG4AYwBoALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgBcAG4ASQBGACgAQwBPAFUATgBUAEEAKABhAHIAcgBhAHkAKQAgAD0AIAAwACwAMAAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AbgARIGUAbQBwAHQAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBOACgAYQByAHIAYQB5ACkAIAA8AD4AIAAwACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3AC8AYwBvAGwAdQBtAG4AIABrAGUAZQBwACAAZgBsAGEAZwBzAFwAbgAgACAAIAAgAE8AUgC7AywAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALAAgAEkARgBFAFIAUgBPAFIAKABPAFIAKABUAE8AQwBPAEwAKAB2ACwAIAAyACkAKQAsACAARgBBAEwAUwBFACkAKQAsAFwAbgAgACAAIAAgAG0AYQByAGsAXwByAG8AdwBzACwAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKABiAG8AbwBsACwAIABPAFIAuwMpACwAXABuACAAIAAgACAAbQBhAHIAawBfAGMAbwBsAHMALAAgACAAIAAgACAAIAAgACAAIAAgAEIAWQBDAE8ATAAoAGIAbwBvAGwALAAgAE8AUgC7AykALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAG0AbwB2AGUAIABlAG0AcAB0AHkAIAByAG8AdwBzAFwAbgAgACAAIAAgAGYAaQByAHMAdABfAHAAYQBzAHMALAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAbQBhAHIAawBfAHIAbwB3AHMALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAbQBvAHYAZQAgAGUAbQBwAHQAeQAgAGMAbwBsAHUAbQBuAHMAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAZgBpAHIAcwB0AF8AcABhAHMAcwAsACAAbQBhAHIAawBfAGMAbwBsAHMALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUgBlAG0AbwB2AGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABEAGUAbABlAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBtAG8AdgBlAHMAIABzAHAAZQBjAGkAZgBpAGMAIAByAG8AdwBzACAAYQBuAGQALwBvAHIAIABjAG8AbAB1AG0AbgBzACAAZgByAG8AbQAgAGEAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkALgAgAFIAZQBtAG8AdgBlALsDIABzAHUAcABwAG8AcgB0AHMAXABuACAAIAAgACAAcwBjAGEAbABhAHIAcwAsACAAMQBEACAAYQByAHIAYQB5AHMALAAgAGEAbgBkACAAMgBEACAAYQByAHIAYQB5AHMAIABmAG8AcgAgAGIAbwB0AGgAIAByAG8AdwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AIABpAG4AZABlAHgAIABpAG4AcAB1AHQAcwAuACAAQQBsAGwAXABuACAAIAAgACAAaQBuAGQAZQB4ACAAaQBuAHAAdQB0AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAYgBlAGYAbwByAGUAIABlAHYAYQBsAHUAYQB0AGkAbwBuAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdwBoAGkAYwBoACAAcgBvAHcAcwAgAGEAbgBkAC8AbwByACAAYwBvAGwAdQBtAG4AcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAuAFwAbgAgACAAIAAgAFsAcgBvAHcAcwBdACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcgBvAHcAIABpAG4AZABlAHgAIABvAHIAIABhAHIAcgBhAHkAIABvAGYAIABpAG4AZABpAGMAZQBzACAAdABvACAAcgBlAG0AbwB2AGUALgBcAG4AIAAgACAAIABbAGMAbwBsAHMAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAbwByACAAYQByAHIAYQB5ACAAbwBmACAAaQBuAGQAaQBjAGUAcwAgAHQAbwAgAHIAZQBtAG8AdgBlAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAEkATgBWAEEATABJAEQALQBSAE8AVwAhAFwAIgAgAGkAZgAgAGEAbgB5ACAAcgBvAHcAIABpAG4AZABlAHgAIABpAHMAIABvAHUAdAAgAG8AZgAgAGIAbwB1AG4AZABzAC4AXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBJAE4AVgBBAEwASQBEAC0AQwBPAEwAIQBcACIAIABpAGYAIABhAG4AeQAgAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAaQBzACAAbwB1AHQAIABvAGYAIABiAG8AdQBuAGQAcwAuAFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYQByAGUAIAByAGUAdAB1AHIAbgBlAGQAIAB1AG4AYwBoAGEAbgBnAGUAZAAuAFwAbgAgACAAIAAgACIgIABSAG8AdwAvAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAaQBuAHAAdQB0AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAdwBpAHQAaAAgAFQATwBDAE8ATAAgAGYAbwByACAAYwBvAG4AcwBpAHMAdABlAG4AYwB5AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBtAG8AdgBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAcgBvAHcAcwBdACwAXABuACAAIAAgACAAWwBjAG8AbABzAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByACAAcAByAGUAcwBlAG4AYwBlAFwAbgAgACAAIAAgAHIAbwB3AHMAXwBpAG4AYwAsACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAcwApACkALABcAG4AIAAgACAAIABjAG8AbABzAF8AaQBuAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAHMAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBtAG8AdgBhAGwAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBSAG8AdwBzAD8ALAAgACAAIAAgACAAIAAgACAAQQBOAEQAKAByAG8AdwBzAF8AaQBuAGMALAAgAE4ATwBUACgAYwBvAGwAcwBfAGkAbgBjACkAKQAsAFwAbgAgACAAIAAgAFIAZQBtAG8AdgBlAEMAbwBsAHMAPwAsACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGMAbwBsAHMAXwBpAG4AYwAsACAATgBPAFQAKAByAG8AdwBzAF8AaQBuAGMAKQApACwAXABuACAAIAAgACAAUgBlAG0AbwB2AGUAUgBDAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGkAbgBjACwAIABjAG8AbABzAF8AaQBuAGMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGEAbAB0AGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAFQAZQB4AHQAUgBvAHcAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHIAbwB3AHMAKQApACwAXABuACAAIAAgACAAVABlAHgAdABDAG8AbABzAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYwBvAGwAcwApACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABSAG8AdwA/ACwAIAAgACAAIAAgACAAIAAgAEkARgAoAFQAZQB4AHQAUgBvAHcAcwA/ACwAIABUAFIAVQBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKAByAG8AdwBzAF8AaQBuAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAE0ASQBOACgAcgBvAHcAcwApACAAPAAgADEALAAgAE0AQQBYACgAcgBvAHcAcwApACAAPgAgAGgAKQApACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABDAG8AbAA/ACwAIAAgACAAIAAgACAAIAAgAEkARgAoAFQAZQB4AHQAQwBvAGwAcwA/ACwAIABUAFIAVQBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABjAG8AbABzAF8AaQBuAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAE0ASQBOACgAYwBvAGwAcwApACAAPAAgADEALAAgAE0AQQBYACgAYwBvAGwAcwApACAAPgAgAHcAKQApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGEAcgByAGEAeQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAUgBvAHcAPwAsACAAXAAiACMASQBOAFYAQQBMAEkARAAtAFIATwBXACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEMAbwBsAD8ALAAgAFwAIgAjAEkATgBWAEEATABJAEQALQBDAE8ATAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAvAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAdgBlAGMAdABvAHIAcwBcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAaAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBvAG8AbABlAGEAbgAgAG0AYQBzAGsAcwBcAG4AIAAgACAAIAByAG0AYQBzAGsALAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAFMATgBBACgAWABNAEEAVABDAEgAKAByACwAIABUAE8AQwBPAEwAKAByAG8AdwBzACkAKQApACkALABcAG4AIAAgACAAIABjAG0AYQBzAGsALAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAFMATgBBACgAWABNAEEAVABDAEgAKABjACwAIABUAE8AQwBPAEwAKABjAG8AbABzACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBvAHcALQBvAG4AbAB5ACAAcgBlAG0AbwB2AGEAbABcAG4AIAAgACAAIAByAG8AdwBzAF8AbwBuAGwAeQAsACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAcgBtAGEAcwBrACgAKQAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAdQBtAG4ALQBvAG4AbAB5ACAAcgBlAG0AbwB2AGEAbABcAG4AIAAgACAAIABjAG8AbABzAF8AbwBuAGwAeQAsACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAYwBtAGEAcwBrACgAKQAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBvAHQAaAAgAHIAbwB3AHMAIABhAG4AZAAgAGMAbwBsAHUAbQBuAHMAXABuACAAIAAgACAAUgBDAF8AcgAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAHIAbQBhAHMAawAoACkALAAgADAAKQApACwAXABuACAAIAAgACAAUgBDACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARgBJAEwAVABFAFIAKABSAEMAXwByACgAKQAsACAAYwBtAGEAcwBrACgAKQAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgAEkARgAoAFIAZQBtAG8AdgBlAFIAbwB3AHMAPwAsACAAcgBvAHcAcwBfAG8AbgBsAHkAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAFIAZQBtAG8AdgBlAEMAbwBsAHMAPwAsACAAYwBvAGwAcwBfAG8AbgBsAHkAKAApACwAIABSAEMAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEQAZQBsAGUAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAG0AbwB2AGUAcwAgAG4AdQBsAGwAIABhAG4AZAAgAHMAdAByAGEAaQBnAGgAdAARIHoAZQByAG8AIAB2AGUAcgB0AGkAYwBhAGwAIABvAHIAIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAdgBlAGMAdABvAHIAcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAUwB1AHAAcABvAHIAdABzACAAYQBuACAAbwBwAHQAaQBvAG4AYQBsACAAYwB1AHMAdABvAG0AIABzAGMAYQBsAGEAcgAgAGMAcgBpAHQAZQByAGkAbwBuACAAZgBvAHIAIAByAGUAbQBvAHYAYQBsAC4AIABTAHEAdQBlAGUAegBlALsDIABjAGEAbgAgAGEAbABzAG8AXABuACAAIAAgACAAbwBwAHQAaQBvAG4AYQBsAGwAeQAgAHMAdQBwAHAAcgBlAHMAcwAgAHoAZQByAG8AcwAgAGkAbgAgAHQAaABlACAAZgBpAG4AYQBsACAAbwB1AHQAcAB1AHQAIABiAHkAIAByAGUAcABsAGEAYwBpAG4AZwAgAHQAaABlAG0AIAB3AGkAdABoACAAXAAiAFwAIgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYQByAGUAIAByAGUAbQBvAHYAZQBkAC4AXABuACAAIAAgACAAWwBjAHUAcwB0AG8AbQBfAGMAcgBpAHQAZQByAGkAYQBdAC0AIABPAHAAdABpAG8AbgBhAGwAIABzAGMAYQBsAGEAcgAgAHUAcwBlAGQAIABhAHMAIAB0AGgAZQAgAHIAZQBtAG8AdgBhAGwAIABjAHIAaQB0AGUAcgBpAG8AbgAuAFwAbgAgACAAIAAgAFsAcwB1AHAAcAByAGUAcwBzAF8AegBlAHIAbwBzAF0AIAAtACAASQBmACAAcAByAG8AdgBpAGQAZQBkACwAIAB6AGUAcgBvAHMAIABpAG4AIAB0AGgAZQAgAGYAaQBuAGEAbAAgAHIAZQBzAHUAbAB0ACAAYQByAGUAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAXAAiAFwAIgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAGIAbwB0AGgAIAByAG8AdwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AIAB2AGUAYwB0AG8AcgBzACAAYQByAGUAIAByAGUAbQBvAHYAZQBkACwAIAB0AGgAZQAgAHIAZQBzAHUAbAB0ACAAbQBhAHkAIABzAGgAcgBpAG4AawAgAGkAbgAgAGIAbwB0AGgAXABuACAAIAAgACAAIAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMALgBcAG4AIAAgACAAIAAiICAASQBmACAAbgBvACAAcgBvAHcAcwAgAG8AcgAgAGMAbwBsAHUAbQBuAHMAIAByAGUAbQBhAGkAbgAsACAAXAAiACMARQBNAFAAVABZAC0AQQBSAFIAQQBZACEAXAAiACAAaQBzACAAcgBlAHQAdQByAG4AZQBkAC4AXABuACAAIAAgACAAIiAgAHMAdQBwAHAAcgBlAHMAcwBfAHoAZQByAG8AcwAgAG8AbgBsAHkAIABhAGYAZgBlAGMAdABzACAAdABoAGUAIAAqAG8AdQB0AHAAdQB0ACoALAAgAG4AbwB0ACAAdABoAGUAIAByAGUAbQBvAHYAYQBsACAAbABvAGcAaQBjAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAcQB1AGUAZQB6AGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBjAHUAcwB0AG8AbQBfAGMAcgBpAHQAZQByAGkAYQBdACwAXABuACAAIAAgACAAWwBzAHUAcABwAHIAZQBzAHMAXwB6AGUAcgBvAHMAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFoAZQByAG8AESBzAHUAcABwAHIAZQBzAHMAaQBvAG4AIABmAGwAYQBnAFwAbgAgACAAIAAgAEgAaQBkAGUAWgBlAHIAbwA/ACwAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAcwB1AHAAcAByAGUAcwBzAF8AegBlAHIAbwBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABzAGUAcQB1AGUAbgBjAGUAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAUgBPAFcAUwAoAGEAcgByAGEAeQApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAbQBvAHYAYQBsADoAIAByAGUAbQBvAHYAZQAgAGEAbABsABEgegBlAHIAbwAgAHYAZQBjAHQAbwByAHMAXABuACAAIAAgACAASwBlAGUAcAC7AywAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAdgAsACAATgBPAFQAKABBAE4ARAAoAFQATwBDAE8ATAAoAHYALAAgADIAKQAgAD0AIAAwACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAdQBzAHQAbwBtACAAcgBlAG0AbwB2AGEAbAA6ACAAcgBlAG0AbwB2AGUAIAB2AGUAYwB0AG8AcgBzACAAZQBxAHUAYQBsACAAdABvACAAYwB1AHMAdABvAG0AXwBjAHIAaQB0AGUAcgBpAGEAXABuACAAIAAgACAAQwB1AHMAdABvAG0AuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAdgAsACAATgBPAFQAKABBAE4ARAAoAFQATwBDAE8ATAAoAHYALAAgADIAKQAgAD0AIABjAHUAcwB0AG8AbQBfAGMAcgBpAHQAZQByAGkAYQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAHAAcgBlAGQAaQBjAGEAdABlAFwAbgAgACAAIAAgAGYAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGMAdQBzAHQAbwBtAF8AYwByAGkAdABlAHIAaQBhACkALAAgAEsAZQBlAHAAuwMsACAAQwB1AHMAdABvAG0AuwMpACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3AC8AYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAdABvACAAawBlAGUAcABcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgASQBGACgAQgBZAFIATwBXACgAYQByAHIAYQB5ACwAIABmAG4AKQAsACAAaQAsACAATgBBACgAKQApACwAIAAyACkALABcAG4AIAAgACAAIABiACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAFIATwBXACgASQBGACgAQgBZAEMATwBMACgAYQByAHIAYQB5ACwAIABmAG4AKQAsACAAagAsACAATgBBACgAKQApACwAIAAyACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvACAAcgBvAHcAcwAgAG8AcgAgAGMAbwBsAHUAbQBuAHMAIAByAGUAbQBhAGkAbgA/AFwAbgAgACAAIAAgAEkAcwBFAG0AcAB0AHkAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAEkAUwBFAFIAUgBPAFIAKABhACkALAAgAEkAUwBFAFIAUgBPAFIAKABiACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAGUAdwAgAHMAaABhAHAAZQBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAeQAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAeAAsACAALAAgADEALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAcgBlAHMAdQBsAHQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAcgAsACAAYwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHoAZQByAG8AIABzAHUAcABwAHIAZQBzAHMAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXwBiACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHIAZQBzAHUAbAB0ACAAPQAgADAALAAgAFwAIgBcACIALAAgAHIAZQBzAHUAbAB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBpAG4AYQBsACAAbwB1AHQAcAB1AHQAXABuACAAIAAgACAAbwB1AHQAcAB1AHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBFAG0AcAB0AHkAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAEUATQBQAFQAWQAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEgAaQBkAGUAWgBlAHIAbwA/ACwAIAByAGUAcwB1AGwAdABfAGIALAAgAHIAZQBzAHUAbAB0ACkAKQAsAFwAbgBcAG4AIAAgACAAIABvAHUAdABwAHUAdABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADAANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEsAcgBvAG4AZQBjAGsAZQByAFAAcgBvAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABFAHgAcABhAG4AcwBpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAATQBhAGcAbgBpAGYAeQC7AywAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG0AcAB1AHQAZQBzACAAdABoAGUAIABLAHIAbwBuAGUAYwBrAGUAcgAgAHAAcgBvAGQAdQBjAHQAIABvAGYAIAB0AHcAbwAgAGEAcgByAGEAeQBzAC4AIABUAGgAZQAgAGYAaQByAHMAdAAgAGEAcgByAGEAeQAgAGkAcwAgAGUAeABwAGEAbgBkAGUAZABcAG4AIAAgACAAIAB1AHMAaQBuAGcAIABNAGEAZwBuAGkAZgB5ALsDIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQAgAGgAZQBpAGcAaAB0ACAAYQBuAGQAIAB3AGkAZAB0AGgAIABvAGYAIABhAHIAcgBhAHkAXwAyACwAIAB3AGgAaQBsAGUAIABhAHIAcgBhAHkAXwAyACAAaQBzAFwAbgAgACAAIAAgAHIAZQBzAGkAegBlAGQAIAB1AHMAaQBuAGcAIABSAGUAcwBpAHoAZQC7AyAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAbwBmACAAYQByAHIAYQB5AF8AMQAuACAAVABoAGUAaQByACAAZQBsAGUAbQBlAG4AdAARIHcAaQBzAGUAXABuACAAIAAgACAAcAByAG8AZAB1AGMAdAAgAHkAaQBlAGwAZABzACAAdABoAGUAIABmAHUAbABsACAASwByAG8AbgBlAGMAawBlAHIAIABlAHgAcABhAG4AcwBpAG8AbgAuAFwAbgBcAG4AIAAgACAAIABBAGwAdABoAG8AdQBnAGgAIABLAHIAbwBuAGUAYwBrAGUAcgAgAHAAcgBvAGQAdQBjAHQAcwAgAGEAcgBlACAAdAByAGEAZABpAHQAaQBvAG4AYQBsAGwAeQAgAGQAZQBmAGkAbgBlAGQAIABmAG8AcgAgAG0AYQB0AHIAaQBjAGUAcwAsACAAdABoAGkAcwBcAG4AIAAgACAAIABpAG0AcABsAGUAbQBlAG4AdABhAHQAaQBvAG4AIABhAGwAcwBvACAAcwB1AHAAcABvAHIAdABzACAAcwBjAGEAbABhAHIAcwAgAGEAbgBkACAAMQBEACAAYQByAHIAYQB5AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgBzACAAYQBjAGMAZQBwAHQAZQBkACkALgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgBzACAAYQBjAGMAZQBwAHQAZQBkACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABCAHIAbwBhAGQAYwBhAHMAdABpAG4AZwAgAGkAcwAgAHAAZQByAGYAbwByAG0AZQBkACAAdgBpAGEAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAZQB4AHAAYQBuAHMAaQBvAG4ALgBcAG4AIAAgACAAIAAiICAAVABoAGUAIABvAHUAdABwAHUAdAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABhAHIAZQAgACgAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAqAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyACkAKQAgANcAXABuACAAIAAgACAAIAAgACgAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADEAKQAqAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyACkAKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBLAHIAbwBuAGUAYwBrAGUAcgBQAHIAbwBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEALABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAaACCICwAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIAB3AIIgLAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHIAbwBhAGQAYwBhAHMAdAAgAGEAcgByAGEAeQBfADEAIABiAHkAIABtAGEAZwBuAGkAZgB5AGkAbgBnACAAZQBhAGMAaAAgAGUAbABlAG0AZQBuAHQAIABpAG4AdABvACAAYQBuACAAaACCICAA1wAgAHcAgiAgAGIAbABvAGMAawBcAG4AIAAgACAAIABBACwAIAAgACAAIAAgACAATQBhAGcAbgBpAGYAeQC7AygAYQByAHIAYQB5AF8AMQAsACAAaACCICwAIAB3AIIgKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHIAbwBhAGQAYwBhAHMAdAAgAGEAcgByAGEAeQBfADIAIABiAHkAIAByAGUAcwBpAHoAaQBuAGcAIABpAHQAIAB0AG8AIABtAGEAdABjAGgAIABhAHIAcgBhAHkAXwAxABkgcwAgAHMAdAByAHUAYwB0AHUAcgBlAFwAbgAgACAAIAAgAEIALAAgACAAIAAgACAAIABSAGUAcwBpAHoAZQC7AygAYQByAHIAYQB5AF8AMgAsACAAaAAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbABlAG0AZQBuAHQAESB3AGkAcwBlACAAcAByAG8AZAB1AGMAdAAgAHkAaQBlAGwAZABzACAAdABoAGUAIABLAHIAbwBuAGUAYwBrAGUAcgAgAGUAeABwAGEAbgBzAGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIABBACAAKgAgAEIALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAwADgAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABFAHgAYwBsAHUAZABlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARgBpAGwAdABlAHIAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEYAaQBsAHQAZQByAHMAIABhAG4AIABhAHIAcgBhAHkAIAAoADEARAAgAG8AcgAgADIARAApACAAYgB5ACAAZQB4AGMAbAB1AGQAaQBuAGcAIABhAG4AeQAgAHIAbwB3ACAAdABoAGEAdAAgAGMAbwBuAHQAYQBpAG4AcwAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAG8AbgAuACAARQB4AGMAbAB1AGQAZQC7AyAAaQBzACAAYQAgAHMAaQBtAHAAbABpAGYAaQBlAGQAIABhAGwAdABlAHIAbgBhAHQAaQB2AGUAIAB0AG8AIABGAEkATABUAEUAUgAgAHcAaABlAHIAZQAgAHQAaABlACAAdQBzAGUAcgBcAG4AIAAgACAAIABzAHUAcABwAGwAaQBlAHMAIAB0AGgAZQAgAGUAeABjAGwAdQBzAGkAbwBuACAAdgBhAGwAdQBlAHMAIABkAGkAcgBlAGMAdABsAHkAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABhACAAYgBvAG8AbABlAGEAbgAgAG0AYQBzAGsALgBcAG4AXABuACAAIAAgACAAVABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIABjAGgAZQBjAGsAcwAgAGUAYQBjAGgAIAByAG8AdwAgAGYAbwByACAAdABoAGUAIABwAHIAZQBzAGUAbgBjAGUAIABvAGYAIABhAG4AeQAgAHYAYQBsAHUAZQAgAGkAbgAgACcAZQB4AGMAbAB1AGQAZQAnAC4AXABuACAAIAAgACAAUgBvAHcAcwAgAHQAaABhAHQAIABjAG8AbgB0AGEAaQBuACAAdABoAGUAIABlAHgAYwBsAHUAcwBpAG8AbgAgAGMAcgBpAHQAZQByAGkAbwBuACAAYQByAGUAIAByAGUAbQBvAHYAZQBkADsAIABhAGwAbAAgAG8AdABoAGUAcgBzACAAYQByAGUAIABrAGUAcAB0AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAGYAaQBsAHQAZQByAC4AXABuACAAIAAgACAAZQB4AGMAbAB1AGQAZQAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACAAbwByACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAdgBhAGwAdQBlAHMAIAB0AG8AIABvAG0AaQB0AC4AXABuACAAIAAgACAAWwBpAGYAXwBlAG0AcAB0AHkAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAYQBsAGwAYgBhAGMAawAgAHYAYQBsAHUAZQAgAHcAaABlAG4AIABuAG8AIAByAG8AdwBzACAAcgBlAG0AYQBpAG4AIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAMAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQAgADIARAAgAGUAeABjAGwAdQBkAGUAIABhAHIAcgBhAHkAIABpAHMAIABpAG4AdgBhAGwAaQBkACAAYQBuAGQAIABoAGEAbAB0AHMAIAB3AGkAdABoACAAXAAiACMAMgBEAC0ARQBYAEMATABVAEQARQAhAFwAIgAuAFwAbgAgACAAIAAgACIgIABNAGEAdABjAGgAaQBuAGcAIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAAgAHUAcwBpAG4AZwAgAFgATQBBAFQAQwBIADsAIABuAG8AbgARIG0AYQB0AGMAaABlAHMAIABhAHIAZQAgAHQAcgBlAGEAdABlAGQAIABhAHMAIAB6AGUAcgBvAC4AXABuACAAIAAgACAAIiAgAEYAaQBsAHQAZQByAGkAbgBnACAAaQBzACAAcgBvAHcAESB3AGkAcwBlADsAIABjAG8AbAB1AG0AbgBzACAAYQByAGUAIABwAHIAZQBzAGUAcgB2AGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBFAHgAYwBsAHUAZABlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGUAeABjAGwAdQBkAGUALABcAG4AIAAgACAAIABbAGkAZgBfAGUAbQBwAHQAeQBdACwAXABuAFwAbgBJAEYAKABBAE4ARAAoAFIATwBXAFMAKABlAHgAYwBsAHUAZABlACkAIAA+ACAAMQAsACAAQwBPAEwAVQBNAE4AUwAoAGUAeABjAGwAdQBkAGUAKQAgAD4AIAAxACkALABcACIAIwAyAEQALQBFAFgAQwBMAFUARABFACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAYQBsAGwAYgBhAGMAawBcAG4AIAAgACAAIABpAGYAXwBlAG0AcAB0AHkALAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAaQBmAF8AZQBtAHAAdAB5ACkALAAgADAALAAgAGkAZgBfAGUAbQBwAHQAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAUgBVAEUAIAA9ACAAawBlAGUAcAAgAHIAbwB3ACwAIABGAEEATABTAEUAIAA9ACAAZQB4AGMAbAB1AGQAZQAgAHIAbwB3AFwAbgAgACAAIAAgAGsAZQBlAHAAPwAsACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABCAFkAUgBPAFcAKABJAEYATgBBACgAWABNAEEAVABDAEgAKABhAHIAcgBhAHkALAAgAGUAeABjAGwAdQBkAGUAKQAsACAAMAApACwATwBSACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYQByAHIAYQB5ACwAIABrAGUAZQBwAD8ALAAgAGkAZgBfAGUAbQBwAHQAeQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAwADkAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAG4AYQBwALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARgBpAGwAdABlAHIAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEYAaQBsAHQAZQByAHMAIABhAG4AIABhAHIAcgBhAHkAIAAoADEARAAgAG8AcgAgADIARAApACAAYgB5ACAAcwBlAGwAZQBjAHQAaQBuAGcAIAByAG8AdwBzACAAdABoAGEAdAAgAGMAbwBuAHQAYQBpAG4AIABhAHQAIABsAGUAYQBzAHQAIABvAG4AZQBcAG4AIAAgACAAIAB2AGEAbAB1AGUAIABmAHIAbwBtACAAdABoAGUAIAAnAGkAbgBjAGwAdQBkAGUAJwAgAGMAcgBpAHQAZQByAGkAYQAuACAAUwBuAGEAcAC7AyAAaQBzACAAYQAgAHMAaQBtAHAAbABpAGYAaQBlAGQAIABhAGwAdABlAHIAbgBhAHQAaQB2AGUAIAB0AG8AXABuACAAIAAgACAARgBJAEwAVABFAFIAIAB3AGgAZQByAGUAIAB0AGgAZQAgAHUAcwBlAHIAIABzAHUAcABwAGwAaQBlAHMAIAB0AGgAZQAgAGkAbgBjAGwAdQBzAGkAbwBuACAAdgBhAGwAdQBlAHMAIABkAGkAcgBlAGMAdABsAHkAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AXABuACAAIAAgACAAYQAgAGIAbwBvAGwAZQBhAG4AIABtAGEAcwBrAC4AXABuAFwAbgAgACAAIAAgAFQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAYwBoAGUAYwBrAHMAIABlAGEAYwBoACAAcgBvAHcAIABmAG8AcgAgAHQAaABlACAAcAByAGUAcwBlAG4AYwBlACAAbwBmACAAYQBuAHkAIAB2AGEAbAB1AGUAIABpAG4AIAAnAGkAbgBjAGwAdQBkAGUAJwAuAFwAbgAgACAAIAAgAFIAbwB3AHMAIAB0AGgAYQB0ACAAYwBvAG4AdABhAGkAbgAgAHQAaABlACAAaQBuAGMAbAB1AHMAaQBvAG4AIABjAHIAaQB0AGUAcgBpAG8AbgAgAGEAcgBlACAAawBlAHAAdAA7ACAAYQBsAGwAIABvAHQAaABlAHIAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABmAGkAbAB0AGUAcgAuAFwAbgAgACAAIAAgAGkAbgBjAGwAdQBkAGUAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAG8AcgAgADEARAAgAGEAcgByAGEAeQAgAG8AZgAgAHYAYQBsAHUAZQBzACAAdABvACAAaQBuAGMAbAB1AGQAZQAuAFwAbgAgACAAIAAgAFsAaQBmAF8AZQBtAHAAdAB5AF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGEAbABsAGIAYQBjAGsAIAB2AGEAbAB1AGUAIAB3AGgAZQBuACAAbgBvACAAcgBvAHcAcwAgAHIAZQBtAGEAaQBuACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgADAAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEEAIAAyAEQAIABpAG4AYwBsAHUAZABlACAAYQByAHIAYQB5ACAAaQBzACAAaQBuAHYAYQBsAGkAZAAgAGEAbgBkACAAaABhAGwAdABzACAAdwBpAHQAaAAgAFwAIgAjADIARAAtAEkATgBDAEwAVQBEAEUAIQBcACIALgBcAG4AIAAgACAAIAAiICAATQBhAHQAYwBoAGkAbgBnACAAaQBzACAAcABlAHIAZgBvAHIAbQBlAGQAIAB1AHMAaQBuAGcAIABYAE0AQQBUAEMASAA7ACAAbgBvAG4AESBtAGEAdABjAGgAZQBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAegBlAHIAbwAuAFwAbgAgACAAIAAgACIgIABGAGkAbAB0AGUAcgBpAG4AZwAgAGkAcwAgAHIAbwB3ABEgdwBpAHMAZQA7ACAAYwBvAGwAdQBtAG4AcwAgAGEAcgBlACAAcAByAGUAcwBlAHIAdgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBuAGEAcAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABpAG4AYwBsAHUAZABlACwAXABuACAAIAAgACAAWwBpAGYAXwBlAG0AcAB0AHkAXQAsAFwAbgBcAG4ASQBGACgAQQBOAEQAKABSAE8AVwBTACgAaQBuAGMAbAB1AGQAZQApACAAPgAgADEALAAgAEMATwBMAFUATQBOAFMAKABpAG4AYwBsAHUAZABlACkAIAA+ACAAMQApACwAXAAiACMAMgBEAC0ASQBOAEMATABVAEQARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGEAbABsAGIAYQBjAGsAXABuACAAIAAgACAAaQBmAF8AZQBtAHAAdAB5ACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZgBfAGUAbQBwAHQAeQApACwAIAAwACwAIABpAGYAXwBlAG0AcAB0AHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAFIAVQBFACAAPQAgAGsAZQBlAHAAIAByAG8AdwAsACAARgBBAEwAUwBFACAAPQAgAGQAaQBzAGMAYQByAGQAIAByAG8AdwBcAG4AIAAgACAAIABrAGUAZQBwAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAEkARgBOAEEAKABYAE0AQQBUAEMASAAoAGEAcgByAGEAeQAsACAAaQBuAGMAbAB1AGQAZQApACwAIAAwACkALABPAFIAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYQByAHIAYQB5ACwAIABrAGUAZQBwAD8ALAAgAGkAZgBfAGUAbQBwAHQAeQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADAAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAGgAaQBmAHQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABSAG8AbABsAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABFAHgAcABsAG8AZABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGUAcgBmAG8AcgBtAHMAIABhACAAYwBpAHIAYwB1AGwAYQByACAAcwBoAGkAZgB0ACAAbwBuACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgAHQAdQBwAGwAZQAgACgAcwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACkALgBcAG4AIAAgACAAIABQAG8AcwBpAHQAaQB2AGUAIABzAGgAaQBmAHQAIAB2AGEAbAB1AGUAcwAgAHIAbwB0AGEAdABlACAAbABlAGYAdAA7ACAAbgBlAGcAYQB0AGkAdgBlACAAcwBoAGkAZgB0ACAAdgBhAGwAdQBlAHMAIAByAG8AdABhAHQAZQAgAHIAaQBnAGgAdAAuAFwAbgBcAG4AIAAgACAAIABFAHgAYQBtAHAAbABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgAD0AUwBoAGkAZgB0ALsDKAB7ADEALAAyACwAMwAsADQAfQAsACAAMgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIACSISAAewAzACwANAAsADEALAAyAH0AXABuAFwAbgAgACAAIAAgACAAIAAgACAAPQBTAGgAaQBmAHQAuwMoAHsAMQAsADIALAAzACwANAB9ACwAIAAtADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAkiEgAHsANAAsADEALAAyACwAMwB9AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAD0AUwBoAGkAZgB0ALsDKABcACIAMQAyADMANABcACIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAkiEgAHsAXAAiADIAXAAiADsAXAAiADMAXAAiADsAXAAiADQAXAAiADsAXAAiADEAXAAiAH0AXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAD0AUwBoAGkAZgB0ALsDKAB7ADEALAAyACwAMwAsADQAfQAsAHsAMQAsADIALAAzAH0AKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAkiEgAHsAMgAsADMALAA0ACwAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAzACwANAAsADEALAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADQALAAxACwAMgAsADMAfQBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAB0AHUAcABsAGUAIAAgACAAIAAgACAAIAAtACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYQByAGUAIABlAHgAcABsAG8AZABlAGQAIABpAG4AdABvACAAYwBoAGEAcgBhAGMAdABlAHIAIABhAHIAcgBhAHkAcwAgAHYAaQBhACAARQB4AHAAbABvAGQAZQC7Ay4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIAAyAEQAIABhAHIAcgBhAHkAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIAB3AGkAdABoACAAVABPAEMATwBMAC4AXABuAFwAbgAgACAAIAAgAFsAcwBoAGkAZgB0AF8AYgB5AF0AIAAgAC0AIABTAGgAaQBmAHQAIABjAG8AdQBuAHQAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAMQApAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABQAG8AcwBpAHQAaQB2AGUAIACSISAAbABlAGYAdAAgAHMAaABpAGYAdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIiAgAE4AZQBnAGEAdABpAHYAZQAgAJIhIAByAGkAZwBoAHQAIABzAGgAaQBmAHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABNAHUAbAB0AGkAESBzAGgAaQBmAHQAIABhAHIAcgBhAHkAcwAgAHAAcgBvAGQAdQBjAGUAIABhACAAYQByAHIAYQB5AF8AMgBEACAAbwBmACAAcwBoAGkAZgB0AGUAZAAgAHQAdQBwAGwAZQBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AIABtAGEAdABjAGgAZQBzACAAaQBuAHAAdQB0ADoAXABuACAAIAAgACAAIAAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByAHMAIACSISAAdgBlAHIAdABpAGMAYQBsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAC0AIABWAGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAcwAgAJIhIAB2AGUAcgB0AGkAYwBhAGwAXABuACAAIAAgACAAIAAgACAAIAAgACAALQAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAcwAgAJIhIABoAG8AcgBpAHoAbwBuAHQAYQBsAFwAbgAgACAAIAAgACIgIABNAHUAbAB0AGkAESBzAGgAaQBmAHQAIABpAG4AcAB1AHQAcwAgAHIAZQB0AHUAcgBuACAAYQAgAHMAdABhAGMAawBlAGQAIABhAHIAcgBhAHkAXwAyAEQAIABvAGYAIABzAGgAaQBmAHQAZQBkACAAcgBlAHMAdQBsAHQAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAGgAaQBmAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAdAB1AHAAbABlACwAXABuACAAIAAgACAAWwBzAGgAaQBmAHQAXwBiAHkAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAaABhAHAAZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHQAdQBwAGwAZQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAB0AHUAcABsAGUAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAdAB1AHAAbABlACAAkiEgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAB0AHUAcABsAGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALABFAHgAcABsAG8AZABlALsDKAB0AHUAcABsAGUAKQAsAHQAdQBwAGwAZQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABzAGgAaQBmAHQAXwBiAHkAIACSISAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAHMAaABpAGYAdABfAGIAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHMAaABpAGYAdABfAGIAeQApACwAIAAxACwAIABzAGgAaQBmAHQAXwBiAHkAKQApACwAXABuACAAIAAgACAASQBzAE0AdQBsAHQAaQBTAGgAaQBmAHQAPwAsACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAcwBoAGkAZgB0AF8AYgB5ACkAIAA+ACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAMQBFAGwAZQBtAGUAbgB0AD8ALAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKAB0AHUAcABsAGUAKQAgAD0AIAAxACwAXABuACAAIAAgACAASQBzAFQAZQB4AHQAUwBoAGkAZgB0AD8ALAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAcwBoAGkAZgB0AF8AYgB5ACkAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAMQBFAGwAZQBtAGUAbgB0AD8ALAAgAHQAdQBwAGwAZQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBUAGUAeAB0AFMAaABpAGYAdAA/ACwAIABcACIAIwBUAEUAWABUAC0AUwBIAEkARgBUACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFQAdQBwAGwAZQAgAGwAZQBuAGcAdABoAFwAbgAgACAAIAAgAG4ALAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAdAB1AHAAbABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAMAARIGIAYQBzAGUAZAAgAGkAbgBkAGUAeAAgAHMAZQBxAHUAZQBuAGMAZQBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAbgAsACAAMAAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAaQByAGMAdQBsAGEAcgAgAGkAbgBkAGUAeAAgAHMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgAE0ATwBEACgAaQAgACsAIABzAGgAaQBmAHQAXwBiAHkALAAgAG4AKQAgACsAIAAxACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAHMAaABpAGYAdABcAG4AIAAgACAAIABzAGgAaQBmAHQAZQBkACwAIAAgACAAIABJAE4ARABFAFgAKAB0AHUAcABsAGUALAAgAGkAZAB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIABJAEYAKABJAHMATQB1AGwAdABpAFMAaABpAGYAdAA/ACwAIABzAGgAaQBmAHQAZQBkACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABzAGgAaQBmAHQAZQBkACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBSAE8AVwAoAHMAaABpAGYAdABlAGQAKQApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAGgAaQBmAHQAUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFIAbwBsAGwAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAaABpAGYAdAC7AywAIABNAEcAcgBpAGQAuwMsACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFAAZQByAGYAbwByAG0AcwAgAGEAIABjAGkAcgBjAHUAbABhAHIAIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAcwBoAGkAZgB0ACAAbwBuACAAZQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAYQAgADIARAAgAGEAcgByAGEAeQAuACAAVABoAGUAIABzAGgAaQBmAHQAXwBiAHkAXABuACAAIAAgACAAdgBhAGwAdQBlACAAZABlAHQAZQByAG0AaQBuAGUAcwAgAGgAbwB3ACAAbQBhAG4AeQAgAHAAbwBzAGkAdABpAG8AbgBzACAAZQBhAGMAaAAgAHIAbwB3ACAAaQBzACAAcgBvAHQAYQB0AGUAZAA6AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFAAbwBzAGkAdABpAHYAZQAgAJIhIABzAGgAaQBmAHQAIABsAGUAZgB0AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAE4AZQBnAGEAdABpAHYAZQAgAJIhIABzAGgAaQBmAHQAIAByAGkAZwBoAHQAXABuAFwAbgAgACAAIAAgADEARAAgAGEAcgByAGEAeQBzACAAYQBuAGQAIABzAGMAYQBsAGEAcgBzACAAYQByAGUAIABkAGUAbABlAGcAYQB0AGUAZAAgAHQAbwAgAFMAaABpAGYAdAC7Ay4AXABuAFwAbgBFAHgAYQBtAHAAbABlAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAA9ACAAewBcACIAQgBvAGIAXAAiACwAXAAiAE0AYQB0AGgAXAAiACwAXAAiAEIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBiAFwAIgAsAFwAIgBQAGgAeQBzAGkAYwBzAFwAIgAsAFwAIgBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZQBcACIALABcACIASABpAHMAdABvAHIAeQBcACIALABcACIAQgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASgBvAGUAXAAiACwAXAAiAEMAaABlAG0AaQBzAHQAcgB5AFwAIgAsAFwAIgBDAFwAIgB9AFwAbgBcAG4AIAAgACAAIAA9AFMAaABpAGYAdABSAG8AdwBzALsDKABhAHIAcgBhAHkALAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgAJIhIAB7AFwAIgBNAGEAdABoAFwAIgAsAFwAIgBCAFwAIgAsAFwAIgBCAG8AYgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGgAeQBzAGkAYwBzAFwAIgAsAFwAIgBBAFwAIgAsAFwAIgBEAGUAYgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAcwB0AG8AcgB5AFwAIgAsAFwAIgBCAFwAIgAsAFwAIgBTAHUAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIALABcACIAQwBcACIALABcACIASgBvAGUAXAAiAH0AXABuAFwAbgAgACAAIAAgAD0AUwBoAGkAZgB0AFIAbwB3AHMAuwMoAGEAcgByAGEAeQAsACAALQAxACkAXABuACAAIAAgACAAIAAgACAAIACSISAAewBcACIAQgBcACIALABcACIAQgBvAGIAXAAiACwAXAAiAE0AYQB0AGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBcACIALABcACIARABlAGIAXAAiACwAXAAiAFAAaAB5AHMAaQBjAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBcACIALABcACIAUwB1AGUAXAAiACwAXAAiAEgAaQBzAHQAbwByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBcACIALABcACIASgBvAGUAXAAiACwAXAAiAEMAaABlAG0AaQBzAHQAcgB5AFwAIgB9AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAGgAaQBmAHQAUgBvAHcAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABbAHMAaABpAGYAdABfAGIAeQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADEARAAgAGEAcgByAGEAeQBzACAALwAgAHMAYwBhAGwAYQByAHMAIABoAGEAbgBkAGwAZQBkACAAYgB5ACAAUwBoAGkAZgB0ALsDXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsAFMAaABpAGYAdAC7AygAYQByAHIAYQB5AF8AMgBEACwAIABzAGgAaQBmAHQAXwBiAHkAKQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGkAbgBkAGkAYwBlAHMAIAByAGUAbQBhAGkAbgAgAGYAaQB4AGUAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgAE0ARwByAGkAZAC7AygAYQByAHIAYQB5AF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAYQByAGUAIABjAGkAcgBjAHUAbABhAHIAbAB5ACAAcwBoAGkAZgB0AGUAZABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDKABTAGgAaQBmAHQAuwMoAFMARQBRAFUARQBOAEMARQAoACwAIAB3ACkALAAgAHMAaABpAGYAdABfAGIAeQApACwAaAApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIABpACwAIABqACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBoAGkAZgB0AEMAbwBsAHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABSAG8AbABsAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABTAGgAaQBmAHQAuwMsACAATQBHAHIAaQBkALsDLAAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGUAcgBmAG8AcgBtAHMAIABhACAAYwBpAHIAYwB1AGwAYQByACAAdgBlAHIAdABpAGMAYQBsACAAcwBoAGkAZgB0ACAAbwBuACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAbwBmACAAYQAgADIARAAgAGEAcgByAGEAeQAuACAAVABoAGUAIABzAGgAaQBmAHQAXwBiAHkAXABuACAAIAAgACAAdgBhAGwAdQBlACAAZABlAHQAZQByAG0AaQBuAGUAcwAgAGgAbwB3ACAAbQBhAG4AeQAgAHAAbwBzAGkAdABpAG8AbgBzACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAaQBzACAAcgBvAHQAYQB0AGUAZAA6AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFAAbwBzAGkAdABpAHYAZQAgAJIhIABzAGgAaQBmAHQAIAB1AHAAXABuACAAIAAgACAAIAAgACAAIAAiICAATgBlAGcAYQB0AGkAdgBlACAAkiEgAHMAaABpAGYAdAAgAGQAbwB3AG4AXABuAFwAbgAgACAAIAAgADEARAAgAGEAcgByAGEAeQBzACAAYQBuAGQAIABzAGMAYQBsAGEAcgBzACAAYQByAGUAIABkAGUAbABlAGcAYQB0AGUAZAAgAHQAbwAgAFMAaABpAGYAdAC7Ay4AXABuAFwAbgBFAHgAYQBtAHAAbABlAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAA9ACAAewBcACIAQgBvAGIAXAAiACwAXAAiAE0AYQB0AGgAXAAiACwAXAAiAEIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBiAFwAIgAsAFwAIgBQAGgAeQBzAGkAYwBzAFwAIgAsAFwAIgBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZQBcACIALABcACIASABpAHMAdABvAHIAeQBcACIALABcACIAQgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASgBvAGUAXAAiACwAXAAiAEMAaABlAG0AaQBzAHQAcgB5AFwAIgAsAFwAIgBDAFwAIgB9AFwAbgBcAG4AIAAgACAAIAA9AFMAaABpAGYAdABDAG8AbABzALsDKABhAHIAcgBhAHkALAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgAJIhIAB7AFwAIgBEAGUAYgBcACIALABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZQBcACIALABcACIASABpAHMAdABvAHIAeQBcACIALABcACIAQgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAG8AZQBcACIALABcACIAQwBoAGUAbQBpAHMAdAByAHkAXAAiACwAXAAiAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBvAGIAXAAiACwAXAAiAE0AYQB0AGgAXAAiACwAXAAiAEIAXAAiAH0AXABuAFwAbgAgACAAIAAgAD0AUwBoAGkAZgB0AEMAbwBsAHMAuwMoAGEAcgByAGEAeQAsACAALQAxACkAXABuACAAIAAgACAAIAAgACAAIACSISAAewBcACIASgBvAGUAXAAiACwAXAAiAEMAaABlAG0AaQBzAHQAcgB5AFwAIgAsAFwAIgBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgAsAFwAIgBCAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBiAFwAIgAsAFwAIgBQAGgAeQBzAGkAYwBzAFwAIgAsAFwAIgBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBlAFwAIgAsAFwAIgBIAGkAcwB0AG8AcgB5AFwAIgAsAFwAIgBCAFwAIgB9AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAGgAaQBmAHQAQwBvAGwAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABbAHMAaABpAGYAdABfAGIAeQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADEARAAgAGEAcgByAGEAeQBzACAALwAgAHMAYwBhAGwAYQByAHMAIABoAGEAbgBkAGwAZQBkACAAYgB5ACAAUwBoAGkAZgB0ALsDXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsAFMAaABpAGYAdAC7AygAYQByAHIAYQB5AF8AMgBEACwAIABzAGgAaQBmAHQAXwBiAHkAKQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABDAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAIABhAHIAZQAgAGMAaQByAGMAdQBsAGEAcgBsAHkAIABzAGgAaQBmAHQAZQBkAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHMAaQB6AGUAuwMoAFMAaABpAGYAdAC7AygAUwBFAFEAVQBFAE4AQwBFACgAaAApACwAIABzAGgAaQBmAHQAXwBiAHkAKQAsACwAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3ACAAaQBuAGQAaQBjAGUAcwAgAHIAZQBtAGEAaQBuACAAZgBpAHgAZQBkAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkAXwAyAEQALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQBfADIARAAsACAAaQAsACAAagApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEUAbQBiAGUAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFMAZQBsAGUAYwB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAG0AYgBlAGQAcwAgAGEAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYQAgADIARAAgAGgAbwBzAHQAIABhAHIAcgBhAHkAIABhAHQAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgAGkAbgBkAGUAeAAuACAARQBtAGIAZQBkALsDIABzAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgBzACwAIAAxAEQAIABhAHIAcgBhAHkAcwAsACAAYQBuAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAuACAAVABoAGUAIABlAG0AYgBlAGQAZABlAGQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAaQBzACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQAgAGUAeABwAGEAbgBkAGUAZAAgAGEAcwAgAG4AZQBlAGQAZQBkACAAdABvACAAbQBhAGkAbgB0AGEAaQBuACAAcgBlAGMAdABhAG4AZwB1AGwAYQByAGkAdAB5ACAAYQBuAGQAIABhAHYAbwBpAGQAXABuACAAIAAgACAAagBhAGcAZwBlAGQAIAByAGUAcwB1AGwAdABzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAxAEQAIABvAHIAIAAyAEQAIABoAG8AcwB0ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACAAIAAgAC0AIABBAHIAcgBhAHkAIAB0AG8AIABlAG0AYgBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAaABvAHMAdAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAcgBvAHcAXwBpAG4AZABlAHgAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcgBvAHcAIABwAG8AcwBpAHQAaQBvAG4AIABmAG8AcgAgAGkAbgBzAGUAcgB0AGkAbwBuAC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABjAG8AbAB1AG0AbgAgAHAAbwBzAGkAdABpAG8AbgAgAGYAbwByACAAaQBuAHMAZQByAHQAaQBvAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABJAGYAIABiAG8AdABoACAAYQByAGUAIABzAHUAcABwAGwAaQBlAGQALAAgAHIAbwB3AF8AaQBuAGQAZQB4ACAAdABhAGsAZQBzACAAcAByAGUAYwBlAGQAZQBuAGMAZQAuAFwAbgBcAG4ATgB1AGEAbgBjAGUAcwA6AFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAZQB4AHAAYQBuAGQAIABoAG8AcgBpAHoAbwBuAHQAYQBsAGwAeQAgAHcAaABlAG4AIABpAG4AcwBlAHIAdABlAGQAIABiAHkAIAByAG8AdwBfAGkAbgBkAGUAeAAsACAAdgBlAHIAdABpAGMAYQBsAGwAeQAgAHcAaABlAG4AXABuACAAIAAgACAAIAAgAGkAbgBzAGUAcgB0AGUAZAAgAGIAeQAgAGMAbwBsAF8AaQBuAGQAZQB4AC4AXABuACAAIAAgACAAIiAgADEARAAvADIARAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQAgAGkAbgBwAHUAdABzACAAdABoAGEAdAAgAGQAbwAgAG4AbwB0ACAAbQBhAHQAYwBoACAAaABvAHMAdAAgAHcAaQBkAHQAaAAvAGgAZQBpAGcAaAB0ACAAYQByAGUAIABwAGEAZABkAGUAZABcAG4AIAAgACAAIAAgACAAdwBpAHQAaAAgAFwAIgBcACIAIAB0AG8AIABtAGEAaQBuAHQAYQBpAG4AIAByAGUAYwB0AGEAbgBnAHUAbABhAHIAaQB0AHkALgBcAG4AIAAgACAAIAAiICAAXAAiACMAUgBPAFcALwBDAE8ATAAtAEkATgBEAEUAWABcACIAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQAIABmAG8AcgAgAG4AbwBuABEgbgB1AG0AZQByAGkAYwAgAG8AcgAgAG8AdQB0ABEgbwBmABEgYgBvAHUAbgBkAHMAIABpAG4AZABpAGMAZQBzAC4AXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIABjAGEAbgBuAG8AdAAgAHMAZQByAHYAZQAgAGEAcwAgAGgAbwBzAHQAIABhAHIAcgBhAHkAcwA7ACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARQBtAGIAZQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAcgBvAHcAXwBpAG4AZABlAHgAXQAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEgAbwBzAHQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbQBiAGUAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaACCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABlAG0AYgBlAGQAXwBhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcAgiAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAHIAYQBtAGUAdABlAHIAIABwAHIAZQBzAGUAbgBjAGUAXABuACAAIAAgACAAUgBvAHcARQBtAGIAZQBkAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBfAGkAbgBkAGUAeAApACkALABcAG4AIAAgACAAIABDAG8AbABFAG0AYgBlAGQAPwAsACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkAKQAsAFwAbgAgACAAIAAgAFIAQwBFAG0AYgBlAGQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAFIAbwB3AEUAbQBiAGUAZAA/ACwAIABDAG8AbABFAG0AYgBlAGQAPwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgB2AGEAbABpAGQAIABlAG0AYgBlAGQAIABzAGkAegBlACAAKABlAG0AYgBlAGQAIABsAGEAcgBnAGUAcgAgAHQAaABhAG4AIABoAG8AcwB0ACkAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABFAG0AYgBlAGQAPwAsACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgAUgBvAHcARQBtAGIAZQBkAD8ALAAgAHcAgiAgAD4AIAB3ACkALAAgAFQAUgBVAEUALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABBAE4ARAAoAEMAbwBsAEUAbQBiAGUAZAA/ACwAIABoAIIgIAA+ACAAaAApACwAIABUAFIAVQBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABBAE4ARAAoAFIAQwBFAG0AYgBlAGQAPwAsACAATwBSACgAaACCICAAPgAgAGgALAAgAHcAgiAgAD4AIAB3ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFIAVQBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAQQBMAFMARQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQASQBkAHgAPwAsACAAIAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHIAbwB3AF8AaQBuAGQAZQB4ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABjAG8AbABfAGkAbgBkAGUAeAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AF8AaQBuAGQAZQB4ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKAByAG8AdwBfAGkAbgBkAGUAeAAgADwAIAAxACwAIAByAG8AdwBfAGkAbgBkAGUAeAAgAD4AIABoACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABjAG8AbABfAGkAbgBkAGUAeAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAYwBvAGwAXwBpAG4AZABlAHgAIAA8ACAAMQAsACAAYwBvAGwAXwBpAG4AZABlAHgAIAA+ACAAdwApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAG8AcwB0ACAAYwBhAG4AbgBvAHQAIABiAGUAIABzAGMAYQBsAGEAcgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQASQBkAHgAPwAsACAAXAAiACMAUgBPAFcALwBDAE8ATAAtAEkATgBEAEUAWABcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEUAbQBiAGUAZAA/ACwAIABcACIAIwBFAE0AQgBFAEQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABcACIAIwBTAEMAQQBMAEEAUgAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgA6ACAAdgBlAHIAdABpAGMAYQBsACAAaQBuAHMAZQByAHQAaQBvAG4AIAB1AG4AbABlAHMAcwAgAG8AbgBsAHkAIABjAG8AbABfAGkAbgBkAGUAeAAgAGkAcwAgAHAAcgBvAHYAaQBkAGUAZABcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAIAAgACAAIAAgACAATwBSACgATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AF8AaQBuAGQAZQB4ACkAKQAsACAASQBTAE8ATQBJAFQAVABFAEQAKABjAG8AbABfAGkAbgBkAGUAeAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAYwBrACAAZgB1AG4AYwB0AGkAbwBuAFwAbgAgACAAIAAgAFMAdABhAGMAawC7AywAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgAFYAUwBUAEEAQwBLACwAIABIAFMAVABBAEMASwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAZQBtAGIAZQBkAD8AXABuACAAIAAgACAASQBzAEkAbgBjAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgAEEATgBEACgAaACCICAAPQAgADEALAAgAHcAgiAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHMAZQByAHQAaQBvAG4AIABpAG4AZABlAHgAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAcgBvAHcAXwBpAG4AZABlAHgALAAgAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AIAAgACAAIABtAGEAeABfAGQAaQBtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQAgACsAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgAGgALAAgAHcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAbABpAHQAIABoAG8AcwB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAGIAbABvAGMAawBfAGEALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQByAHIAYQB5ACwAIABpAGQAeAAgAC0AIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQByAHIAYQB5ACwAIAAsACAAaQBkAHgAIAAtACAAMQApACkALABcAG4AXABuACAAIAAgACAAYgBsAG8AYwBrAF8AYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABhAHIAcgBhAHkALAAgAC0AKAAxACAAKwAgAGgAIAAtACAAaQBkAHgAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAGEAcgByAGEAeQAsACAALAAgAC0AKAAxACAAKwAgAHcAIAAtACAAaQBkAHgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAbgBkAGEAcgBkACAAaQBuAHMAZQByAHQAaQBvAG4AIAAoAHQAbwBwACAAbwByACAAYgBvAHQAdABvAG0AKQBcAG4AIAAgACAAIABJAHMAUwB0AGEAbgBkAGEAcgBkAD8ALAAgACAAIAAgACAAIAAgACAATwBSACgAaQBkAHgAIAA9ACAAMQAsACAAaQBkAHgAIAA9ACAAbQBhAHgAXwBkAGkAbQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBzAGkAbwBuACAAcgB1AGwAZQBzAFwAbgAgACAAIAAgAGUAeABwAF8AcwBjAGEAbABhAHIAXwB3AGkAZAB0AGgALAAgACAAIABFAFgAUABBAE4ARAAoAGUAbQBiAGUAZABfAGEAcgByAGEAeQAsACAALAAgAHcALAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAZQB4AHAAXwB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACwAIAAsACAAdwAsACAAXAAiAFwAIgApACwAXABuACAAIAAgACAAZQB4AHAAXwBzAGMAYQBsAGEAcgBfAGgAZQBpAGcAaAB0ACwAIAAgAEUAWABQAEEATgBEACgAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACwAIABoACwAIAAsACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABlAHgAcABfAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALAAgAGgALAAgACwAIABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAGQAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkAIAB0AG8AIABhAHYAbwBpAGQAIABkAGkAbQBlAG4AcwBpAG8AbgAgAG0AaQBzAG0AYQB0AGMAaABcAG4AIAAgACAAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACAAKgAgAEkAcwBJAG4AYwBTAGMAYQBsAGEAcgA/ACwAIABlAHgAcABfAHMAYwBhAGwAYQByAF8AdwBpAGQAdABoACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABlAHgAcABfAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAbgBjAFMAYwBhAGwAYQByAD8ALAAgAGUAeABwAF8AcwBjAGEAbABhAHIAXwBoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAcABfAGgAZQBpAGcAaAB0ACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAG4AZABhAHIAZAAgAHYAcwAgAG0AaQBkABEgYQByAHIAYQB5ACAAaQBuAHMAZQByAHQAaQBvAG4AXABuACAAIAAgACAAcwB0AGEAbgBkAGEAcgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGkAZAB4ACAAPQAgADEALABTAHQAYQBjAGsAuwMoAGUAbQBiAGUAZABfAGEAcgByAGEAeQAsACAAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAYQBjAGsAuwMoAGEAcgByAGEAeQAsACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACkAKQAsAFwAbgBcAG4AIAAgACAAIABzAHQAYQBjAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AGEAYwBrALsDKABiAGwAbwBjAGsAXwBhACwAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALAAgAGIAbABvAGMAawBfAGIAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAdABhAG4AZABhAHIAZAA/ACwAIABzAHQAYQBuAGQAYQByAGQALAAgAHMAdABhAGMAawApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABLAGUAZQBwAFIAbwB3AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABTAGUAbABlAGMAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUwB0AHIAZQBhAGsAuwMsACAAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQB0AGEAaQBuAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAGEAcwBlAGQAIABvAG4AIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AcwAuACAAQQAgAHAAbwBzAGkAdABpAHYAZQBcAG4AIAAgACAAIABrAGUAZQBwACAAdgBhAGwAdQBlACAAcgBlAHQAYQBpAG4AcwAgAHIAbwB3AHMAIABmAHIAbwBtACAAdABoAGUAIAB0AG8AcAAgAG8AZgAgAGUAYQBjAGgAIABzAHUAYgBnAHIAbwB1AHAAIAByAHUAbgA7ACAAYQAgAG4AZQBnAGEAdABpAHYAZQAgAGsAZQBlAHAAXABuACAAIAAgACAAdgBhAGwAdQBlACAAcgBlAHQAYQBpAG4AcwAgAHIAbwB3AHMAIABmAHIAbwBtACAAdABoAGUAIABiAG8AdAB0AG8AbQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGsAZQBlAHAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACAAaQBuAHQAZQBnAGUAcgA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPgAgADAAIACSISAAawBlAGUAcAAgAGYAcgBvAG0AIAB0AG8AcAAgAG8AZgAgAGUAYQBjAGgAIAByAHUAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADwAIAAwACAAkiEgAGsAZQBlAHAAIABmAHIAbwBtACAAYgBvAHQAdABvAG0AIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACAAIAAtACAAUwB1AGIAZwByAG8AdQBwACAAbABhAGIAZQBsAHMAIAAoAHMAYQBtAGUAIABoAGUAaQBnAGgAdAAgAGEAcwAgAGEAcgByAGEAeQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAbwBuAGwAeQAgAG8AbgBlACAAcwB1AGIAZwByAG8AdQBwACAAZQB4AGkAcwB0AHMALAAgAEQAUgBPAFAAKAApACAAaQBzACAAdQBzAGUAZAAgAGEAcwAgAGEAIABmAGEAcwB0ACAAcABhAHQAaAAuAFwAbgAgACAAIAAgACIgIABrAGUAZQBwACAAbQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgA7ACAAdABlAHgAdAAgAG8AcgAgAHYAZQBjAHQAbwByACAAaQBuAHAAdQB0AHMAIABoAGEAbAB0ACAAdwBpAHQAaAAgAGEAbgAgAGUAcgByAG8AcgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBLAGUAZQBwAFIAbwB3AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAawBlAGUAcAAsAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAdQBiAGcAcgBvAHUAcAAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAE8AbgBlAFMAdQBiAEcAcgBvAHUAcAA/ACwAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAFUATgBJAFEAVQBFACgAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkAKQAgAD0AIAAxACwAXABuACAAIAAgACAARABpAHMAYwBhAHIAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkAIAA8AD4AIABSAE8AVwBTACgAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkALABcAG4AIAAgACAAIABJAHMAVABlAHgAdAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABrAGUAZQBwACkALABcAG4AIAAgACAAIABOAG8AdABTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAE8AVAAoAEkAcwBUAGUAeAB0AD8AKQAsACAAQwBPAFUATgBUAEEAKABrAGUAZQBwACkAIAA+ACAAMQApACwAXABuACAAIAAgACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABJAHMAVABlAHgAdAA/ACwAIABOAG8AdABTAGMAYQBsAGEAcgA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQByAHIAbwByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAGgAYQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABzAGMAZQBuAGEAcgBpAG8AcwApACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgA7ACAAXAAiACMAVABFAFgAVAAhAFwAIgA7ACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIAfQAsAFwAbgAgACAAIAAgAGEAbABlAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAFIAUgBBAFkAVABPAFQARQBYAFQAKABGAEkATABUAEUAUgAoAGUAcgByAG8AcgBzACwAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAMAApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgATwBuAGUAUwB1AGIARwByAG8AdQBwAD8ALAAgAEQAaQBzAGMAYQByAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABoAGEAbAB0ACwAIABhAGwAZQByAHQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgACsAdABvAHAALAAgABMgYgBvAHQAdABvAG0AXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABrAGUAZQBwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgB1AG4AIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGEAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAcgBlAGEAawC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkALABcAG4AIAAgACAAIABkAGUAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAAawBlAGUAcAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAQgBTACgAawBlAGUAcAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAaQBuAGQAZQB4ACAAYgBhAHMAZQBkACAAbwBuACAAcwBpAGcAbgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcwAgAD0AIAAtADEALAAgAGQAZQBzAGMAZQBuAGQALAAgAGEAcwBjAGUAbgBkACkALABcAG4AXABuACAAIAAgACAALwAvACAASwBlAGUAcAAgAHIAbwB3AHMAIAB3AGgAZQByAGUAIABpAG4AZABlAHgAIABkIiAAawBlAGUAcABcAG4AIAAgACAAIABrAGUAZQBwAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBkAHgAIAA8AD0AIABrAGUAZQBwACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAawBlAGUAcAA/ACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABLAGUAZQBwAEMAbwBsAHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABTAGUAbABlAGMAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUwB0AHIAZQBhAGsAuwMsACAAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQB0AGEAaQBuAHMAIABjAG8AbAB1AG0AbgBzACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAGEAcwBlAGQAIABvAG4AIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AcwAuACAAQQAgAHAAbwBzAGkAdABpAHYAZQBcAG4AIAAgACAAIABrAGUAZQBwACAAdgBhAGwAdQBlACAAcgBlAHQAYQBpAG4AcwAgAGMAbwBsAHUAbQBuAHMAIABmAHIAbwBtACAAdABoAGUAIABsAGUAZgB0ACAAbwBmACAAZQBhAGMAaAAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuADsAIABhACAAbgBlAGcAYQB0AGkAdgBlAFwAbgAgACAAIAAgAGsAZQBlAHAAIAB2AGEAbAB1AGUAIAByAGUAdABhAGkAbgBzACAAYwBvAGwAdQBtAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAaQBnAGgAdAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGsAZQBlAHAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACAAaQBuAHQAZQBnAGUAcgA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPgAgADAAIACSISAAawBlAGUAcAAgAGYAcgBvAG0AIABsAGUAZgB0ACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPAAgADAAIACSISAAawBlAGUAcAAgAGYAcgBvAG0AIAByAGkAZwBoAHQAIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACAAIAAtACAAUwB1AGIAZwByAG8AdQBwACAAbABhAGIAZQBsAHMAIAAoAHMAYQBtAGUAIAB3AGkAZAB0AGgAIABhAHMAIABhAHIAcgBhAHkAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAG8AbgBsAHkAIABvAG4AZQAgAHMAdQBiAGcAcgBvAHUAcAAgAGUAeABpAHMAdABzACwAIABEAFIATwBQACgAKQAgAGkAcwAgAHUAcwBlAGQAIABhAHMAIABhACAAZgBhAHMAdAAgAHAAYQB0AGgALgBcAG4AIAAgACAAIAAiICAAawBlAGUAcAAgAG0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIAOwAgAHQAZQB4AHQAIABvAHIAIAB2AGUAYwB0AG8AcgAgAGkAbgBwAHUAdABzACAAaABhAGwAdAAgAHcAaQB0AGgAIABhAG4AIABlAHIAcgBvAHIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASwBlAGUAcABDAG8AbABzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGsAZQBlAHAALABcAG4AIAAgACAAIABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAHUAYgBnAHIAbwB1AHAAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABVAE4ASQBRAFUARQAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsACAAMQApACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEQAaQBzAGMAYQByAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAsACAAawBlAGUAcAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgADwAPgAgAEMATwBMAFUATQBOAFMAKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUAKQAsAFwAbgAgACAAIAAgAEkAcwBUAGUAeAB0AD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAGsAZQBlAHAAKQAsAFwAbgAgACAAIAAgAE4AbwB0AFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgASQBzAFQAZQB4AHQAPwApACwAIABDAE8AVQBOAFQAQQAoAGsAZQBlAHAAKQAgAD4AIAAxACkALABcAG4AIAAgACAAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgAEkAcwBUAGUAeAB0AD8ALAAgAE4AbwB0AFMAYwBhAGwAYQByAD8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHIAcgBvAHIAIABoAGEAbgBkAGwAaQBuAGcAXABuACAAIAAgACAAaABhAGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAHMAYwBlAG4AYQByAGkAbwBzACkALABcAG4AIAAgACAAIABlAHIAcgBvAHIAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAewBcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiADsAIABcACIAIwBUAEUAWABUACEAXAAiADsAIABcACIAIwBTAEMAQQBMAEEAUgAhAFwAIgB9ACwAXABuACAAIAAgACAAYQBsAGUAcgB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAUgBSAEEAWQBUAE8AVABFAFgAVAAoAEYASQBMAFQARQBSACgAZQByAHIAbwByAHMALAAgAHMAYwBlAG4AYQByAGkAbwBzACwAIAAwACkAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAARABpAHMAYwBhAHIAZAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGgAYQBsAHQALAAgAGEAbABlAHIAdAAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgA6ACAAKwBsAGUAZgB0ACwAIAATIHIAaQBnAGgAdABcAG4AIAAgACAAIABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAHUAbgAgAGkAbgBkAGkAYwBlAHMAIAAoAGgAbwByAGkAegBvAG4AdABhAGwAKQBcAG4AIAAgACAAIABhAHMAYwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AHIAZQBhAGsAuwMoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsACAAVABSAFUARQApACwAXABuACAAIAAgACAAZABlAHMAYwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMAbwB1AG4AdABkAG8AdwBuALsDKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALAAgAFQAUgBVAEUAKQAsAFwAbgAgACAAIAAgAGsAZQBlAHAALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAEIAUwAoAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGkAbgBkAGUAeAAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAIAA9ACAALQAxACwAIABkAGUAcwBjAGUAbgBkACwAIABhAHMAYwBlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQBlAHAAIABjAG8AbAB1AG0AbgBzACAAdwBoAGUAcgBlACAAaQBuAGQAZQB4ACAAZCIgAGsAZQBlAHAAXABuACAAIAAgACAAawBlAGUAcAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAZAB4ACAAPAA9ACAAawBlAGUAcAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbAB1AG0AbgARIHcAaQBzAGUAIABmAGkAbAB0AGUAcgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGsAZQBlAHAAPwApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAQgBsAG8AYwBrAE0AYQBwALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUwB0AHIAdQBjAHQAdQByAGEAbAAgAE0AYQBwAHAAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFYAYQBsAGkAZABhAHQAZQBCAGwAbwBjAGsATQBhAHAAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBzAGgAYQBwAGUAcwAgAGEAIABhAHIAcgBhAHkAXwAyAEQAIAByAG8AdwARIHcAaQBzAGUAIABvAHIAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIABpAG4AdABvACAAYgBsAG8AYwBrAHMAIABvAGYAIABzAGkAegBlAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAgANcAIAB3AGkAZAB0AGgALgAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIABhAGwAbABvAHcAIAByAGUAcwBoAGEAcABpAG4AZwAgAGIAeQAgAGMAbwBsAHUAbQBuACAAYQBuAGQAXABuACAAIAAgACAAdAByAGEAbgBzAHAAbwBzAGkAbgBnACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGcAcgBpAGQAcwAgAHUAcwBlAGQAIAB0AG8AIABnAGUAbgBlAHIAYQB0AGUAIABiAGwAbwBjAGsAIABpAG4AZABpAGMAZQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAXwAyAEQALgBcAG4AIAAgACAAIABkAGUAcAB0AGgAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASABlAGkAZwBoAHQAIABvAGYAIABlAGEAYwBoACAAYgBsAG8AYwBrAC4AXABuACAAIAAgACAAdwBpAGQAdABoACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAFcAaQBkAHQAaAAgAG8AZgAgAGUAYQBjAGgAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIABbAHIAZQBfAHMAaABhAHAAZQBfAGIAeQBfAGMAbwBsAHUAbQBuAD8AXQAtACAASQBmACAAVABSAFUARQAsACAAcgBlAHMAaABhAHAAZQAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQA7ACAAZQBsAHMAZQAgAHIAbwB3ABEgdwBpAHMAZQAuAFwAbgAgACAAIAAgAFsAdAByAGEAbgBzAHAAbwBzAGUAXwBhAG4AYwBoAG8AcgBzAD8AXQAgAC0AIABJAGYAIABUAFIAVQBFACwAIAB0AHIAYQBuAHMAcABvAHMAZQAgAHIAbwB3AC8AYwBvAGwAdQBtAG4AIABhAG4AYwBoAG8AcgAgAGcAcgBpAGQAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFYAYQBsAGkAZABhAHQAZQBCAGwAbwBjAGsATQBhAHAAuwMgAGUAbgBmAG8AcgBjAGUAcwAgAHMAdAByAGkAYwB0ACAAcwBoAGEAcABlACAAYwBvAG0AcABhAHQAaQBiAGkAbABpAHQAeQAuAFwAbgAgACAAIAAgACIgIABBAG4AYwBoAG8AcgBzACAAZABlAGYAaQBuAGUAIAB0AGgAZQAgAHQAbwBwABEgbABlAGYAdAAgAGMAbwByAG4AZQByACAAbwBmACAAZQBhAGMAaAAgAGIAbABvAGMAawAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGkAcwAgAGEAbAB3AGEAeQBzACAAcgBlAGMAdABhAG4AZwB1AGwAYQByACAAYQBuAGQAIABmAHUAbABsAHkAIAB0AGkAbABlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQgBsAG8AYwBrAE0AYQBwALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAsAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgAFsAcgBlAF8AcwBoAGEAcABlAF8AYgB5AF8AYwBvAGwAdQBtAG4APwBdACwAXABuACAAIAAgACAAWwB0AHIAYQBuAHMAcABvAHMAZQBfAGEAbgBjAGgAbwByAHMAPwBdACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAZQAgAGkAbgBwAHUAdABzACAAYgBlAGYAbwByAGUAIAByAGUAcwBoAGEAcABpAG4AZwBcAG4AIAAgACAAIABWAGEAbABpAGQAYQB0AGUAQgBsAG8AYwBrAE0AYQBwALsDKABhAHIAcgBhAHkAXwAyAEQALAAgAGQAZQBwAHQAaAAsACAAdwBpAGQAdABoACwAIAByAGUAXwBzAGgAYQBwAGUAXwBiAHkAXwBjAG8AbAB1AG0AbgA/ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEIAbABvAGMAawAgAGcAcgBpAGQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARABVAFAAKABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkAIAAvACAAZABlAHAAdABoACwAIAAwACkALAAgACAAIAAgACAALwAvACAAYgBsAG8AYwBrACAAcgBvAHcAcwBcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAVQBQACgAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACAALwAgAHcAaQBkAHQAaAAsACAAMAApACwAIAAgAC8ALwAgAGIAbABvAGMAawAgAGMAbwBsAHUAbQBuAHMAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAbgBjAGgAbwByACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAHgALAAgACwAIAAxACwAIABkAGUAcAB0AGgAKQAgACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHkALAAgADEALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAeQAsACAAMQAsACAAdwBpAGQAdABoACkAIAAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAHgALAAgACwAIAAxACwAIAAwACkALABcAG4AXABuACAAIAAgACAAcgBvAHcAXwBhAG4AYwBoAG8AcgAsACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB0AHIAYQBuAHMAcABvAHMAZQBfAGEAbgBjAGgAbwByAHMAPwApACwAIABpACwAIABUAFIAQQBOAFMAUABPAFMARQAoAGkAKQApACwAXABuACAAIAAgACAAYwBvAGwAXwBhAG4AYwBoAG8AcgAsACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB0AHIAYQBuAHMAcABvAHMAZQBfAGEAbgBjAGgAbwByAHMAPwApACwAIABqACwAIABUAFIAQQBOAFMAUABPAFMARQAoAGoAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3ACAAaQBuAGQAaQBjAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGIAbABvAGMAawBcAG4AIAAgACAAIAByAG8AdwBfAGkAbgBkAGkAYwBlAHMALAAgACAAIABUAE8AQwBPAEwAKAByAG8AdwBfAGEAbgBjAGgAbwByACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBUACgAUwBFAFEAVQBFAE4AQwBFACgALAAgAGQAZQBwAHQAaAAgACoAIAB3AGkAZAB0AGgALAAgADAALAAgADEAIAAvACAAdwBpAGQAdABoACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABiAGwAbwBjAGsAXABuACAAIAAgACAAYwBvAGwAXwBpAG4AZABpAGMAZQBzACwAIAAgACAAVABPAEMATwBMACgAYwBvAGwAXwBhAG4AYwBoAG8AcgApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AUgBPAFcAKABJAEYAUwAoAFMARQBRAFUARQBOAEMARQAoAGQAZQBwAHQAaAApACwAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIAAwACwAIAAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABiAGwAbwBjAGsAcwBcAG4AIAAgACAAIAByAGUAcwBoAGEAcABlAGQALAAgACAAIAAgACAAIABJAE4ARABFAFgAKABhAHIAcgBhAHkAXwAyAEQALAAgAHIAbwB3AF8AaQBuAGQAaQBjAGUAcwAsACAAYwBvAGwAXwBpAG4AZABpAGMAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAcgBlAHMAaABhAHAAZQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIABJAEYAKAByAGUAXwBzAGgAYQBwAGUAXwBiAHkAXwBjAG8AbAB1AG0AbgA/ACwAIABUAFIAQQBOAFMAUABPAFMARQAoAHIAZQBzAGgAYQBwAGUAZAApACwAIAByAGUAcwBoAGEAcABlAGQAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAESBDAE8AUgBFAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAEIAbABvAGMAawBNAGEAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEMAbwByAGUAIABWAGEAbABpAGQAYQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABWAGEAbABpAGQAYQB0AGUAcwAgAGkAbgBwAHUAdABzACAAZgBvAHIAIABCAGwAbwBjAGsATQBhAHAAuwMuACAARQBuAHMAdQByAGUAcwAgAHQAaABlACAAYQByAHIAYQB5AF8AMgBEACAAaQBzACAAdgBhAGwAaQBkACwAIABiAGwAbwBjAGsAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGEAcgBlACAAYwBvAG0AcABhAHQAaQBiAGwAZQAsACAAcgBlAHMAaABhAHAAaQBuAGcAIAB3AGkAbABsACAAbgBvAHQAIABzAHAAaQBsAGwALAAgAGEAbgBkACAAdABoAGUAIABiAGwAbwBjAGsAIABnAGUAbwBtAGUAdAByAHkAIAB0AGkAbABlAHMAIAB0AGgAZQBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQAIABjAGwAZQBhAG4AbAB5AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAXwAyAEQALgBcAG4AIAAgACAAIABkAGUAcAB0AGgAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAQgBsAG8AYwBrACAAaABlAGkAZwBoAHQALgBcAG4AIAAgACAAIAB3AGkAZAB0AGgAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAQgBsAG8AYwBrACAAdwBpAGQAdABoAC4AXABuACAAIAAgACAAcgBlAF8AcwBoAGEAcABlAF8AYgB5AF8AYwBvAGwAdQBtAG4APwAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAbABhAGcAIABmAG8AcgAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQAgAHIAZQBzAGgAYQBwAGUALgBcAG4AIAAgACAAIABvAG4AXwB2AGEAbABpAGQAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAARQB4AHAAcgBlAHMAcwBpAG8AbgAgAHQAbwAgAGUAdgBhAGwAdQBhAHQAZQAgAHcAaABlAG4AIAB2AGEAbABpAGQAYQB0AGkAbwBuACAAcABhAHMAcwBlAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABFAG4AcwB1AHIAZQBzACAAYQByAHIAYQB5AF8AMgBEACAAaQBzACAAYQAgAHAAcgBvAHAAZQByACAAYQByAHIAYQB5ACAAKABUAFkAUABFACAAPQAgADYANAApAC4AXABuACAAIAAgACAAIiAgAFAAcgBlAHYAZQBuAHQAcwAgAHMAcABpAGwAbAARIHIAaQBzAGsAIAB3AGgAZQBuACAAcgBlAHMAaABhAHAAaQBuAGcAIABiAHkAIABjAG8AbAB1AG0AbgAuAFwAbgAgACAAIAAgACIgIABFAG4AZgBvAHIAYwBlAHMAIABlAHgAYQBjAHQAIABkAGkAdgBpAHMAaQBiAGkAbABpAHQAeQAgAGIAeQAgAGIAbABvAGMAawAgAGQAaQBtAGUAbgBzAGkAbwBuAHMALgBcAG4AIAAgACAAIAAiICAAUgBlAGoAZQBjAHQAcwAgAGkAbgB2AGEAbABpAGQAIABvAHIAIAB0AGUAeAB0ACAAYgBsAG8AYwBrACAAcwBpAHoAZQBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBCAGwAbwBjAGsATQBhAHAAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAZABlAHAAdABoACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAXABuACAAIAAgACAAcgBlAF8AcwBoAGEAcABlAF8AYgB5AF8AYwBvAGwAdQBtAG4APwAsAFwAbgAgACAAIAAgAG8AbgBfAHYAYQBsAGkAZAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAHUAcwB0ACAAYgBlACAAYQBuACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAEkARgAoAE4ATwBUACgAVABZAFAARQAoAGEAcgByAGEAeQBfADIARAApACAAPQAgADYANAApACwAXAAiACMAYQByAHIAYQB5AF8AMgBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAcABpAGwAbAARIHIAaQBzAGsAIAB3AGgAZQBuACAAcgBlAHMAaABhAHAAaQBuAGcAIABiAHkAIABjAG8AbAB1AG0AbgBcAG4AIAAgACAAIABJAEYAKAAoAHIAZQBfAHMAaABhAHAAZQBfAGIAeQBfAGMAbwBsAHUAbQBuAD8AKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAoAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAgACoAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkAIAAvACAAKAB3AGkAZAB0AGgAIAAqACAAZABlAHAAdABoACkAXgAyACAAPgAgADEANgAzADgANAApACwAXAAiACMAUwBQAEkATABMAC0AUgBJAFMASwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAHUAcwB0ACAAdABpAGwAZQAgAGMAbABlAGEAbgBsAHkAXABuACAAIAAgACAASQBGACgAKABNAE8ARAAoAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsACAAZABlAHAAdABoACkAIAA8AD4AIAAwACkAIAArACgATQBPAEQAKABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkALAAgAHcAaQBkAHQAaAApACAAPAA+ACAAMAApACwAXAAiACMAQgBMAE8AQwBLACAATQBJAFMATQBBAFQAQwBIACEAXAAiACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbABvAGMAawAgAHMAaQB6AGUAIABtAHUAcwB0ACAAYgBlACAAdgBhAGwAaQBkAFwAbgAgACAAIAAgAEkARgAoAE8AUgAoAEEATgBEACgAdwBpAGQAdABoACAAPQAgADEALAAgAGQAZQBwAHQAaAAgAD0AIAAxACkALABkAGUAcAB0AGgAIAA+ACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB3AGkAZAB0AGgAIAA+ACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwASQBTAFQARQBYAFQAKAB3AGkAZAB0AGgAKQAsAEkAUwBUAEUAWABUACgAZABlAHAAdABoACkAKQAsAFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIALABcAG4AXABuACAAIAAgACAALwAvACAAQQBsAGwAIABjAGgAZQBjAGsAcwAgAHAAYQBzAHMAZQBkAFwAbgAgACAAIAAgAG8AbgBfAHYAYQBsAGkAZABcAG4AIAAgACAAIAApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAQwBvAG4AdgBvAGwAdgBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUwB0AHIAdQBjAHQAdQByAGEAbAAgAE0AYQBwAHAAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGUAcgBmAG8AcgBtAHMAIABhACAAcwBsAGkAZABpAG4AZwARIHcAaQBuAGQAbwB3ACAAYwBvAG4AdgBvAGwAdQB0AGkAbwBuACAAbwB2AGUAcgAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIAB1AHMAaQBuAGcAIABhACAAMgBEACAAawBlAHIAbgBlAGwALgBcAG4AIAAgACAAIABFAGEAYwBoACAAdwBpAG4AZABvAHcAIABlAHgAdAByAGEAYwB0AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGgAYQBzACAAdABoAGUAIABzAGEAbQBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGEAcwAgAHQAaABlAFwAbgAgACAAIAAgAGsAZQByAG4AZQBsAC4AIABBACAAcgBlAGQAdQBjAGUAcgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABlAGEAYwBoACAAdwBpAG4AZABvAHcAIAB0AG8AIABwAHIAbwBkAHUAYwBlACAAdABoAGUAIABvAHUAdABwAHUAdAAuAFwAbgBcAG4AIAAgACAAIABJAGYAIABuAG8AIAByAGUAZAB1AGMAZQByACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzACAAcwB1AHAAcABsAGkAZQBkACwAIABDAG8AbgB2AG8AbAB2AGUAuwMgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAGEAIABkAG8AdAARIHAAcgBvAGQAdQBjAHQAXABuACAAIAAgACAAcgBlAGQAdQBjAGUAcgA6ACAAUwBVAE0AKAB2ACAAKgAgAGsAZQByAG4AZQBsACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAdwBoAGkAYwBoACAAdABoAGUAIABrAGUAcgBuAGUAbAAgAGkAcwAgAGEAcABwAGwAaQBlAGQALgBcAG4AIAAgACAAIABrAGUAcgBuAGUAbAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAZABlAGYAaQBuAGkAbgBnACAAdABoAGUAIABzAGwAaQBkAGkAbgBnACAAdwBpAG4AZABvAHcAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHIAZQBkAHUAYwBlAHIAIABMAEEATQBCAEQAQQAgAGEAYwBjAGUAcAB0AGkAbgBnACAAYQAgAHMAaQBuAGcAbABlACAAYQByAHIAYQB5ACAAYQByAGcAdQBtAGUAbgB0AC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAFMAVQBNACgAdgAgACoAIABrAGUAcgBuAGUAbAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAEsARQBSAE4ARQBMACEAXAAiACAAaQBmACAAdABoAGUAIABrAGUAcgBuAGUAbAAgAGkAcwAgAGwAYQByAGcAZQByACAAdABoAGEAbgAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBGAFUATgBDAFQASQBPAE4AIQBcACIAIABpAGYAIAB0AGgAZQAgAHIAZQBkAHUAYwBlAHIAIABpAHMAIABuAG8AdAAgAGEAIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQAuAFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAMQDXADEAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAbQBhAHAAcABlAGQAIAB0AGgAcgBvAHUAZwBoACAAdABoAGUAIAByAGUAZAB1AGMAZQByAC4AXABuACAAIAAgACAAIiAgAFIAZQBkAHUAYwBlAHIAIABiAGUAaABhAHYAaQBvAHIAIABpAHMAIAB1AHMAZQByABEgZABlAGYAaQBuAGUAZAA7ACAAYQByAHIAYQB5AHMAIABuAGUAZQBkACAAbgBvAHQAIABiAGUAIABuAHUAbQBlAHIAaQBjAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEMAbwBuAHYAbwBsAHYAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABrAGUAcgBuAGUAbAAsAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABBAHIAcgBhAHkAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQByAG4AZQBsACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoAF8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGsAZQByAG4AZQBsACkALABcAG4AIAAgACAAIAB3AF8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGsAZQByAG4AZQBsACkALABcAG4AXABuACAAIAAgACAALwAvACAASwBlAHIAbgBlAGwAIABtAHUAcwB0ACAAZgBpAHQAIABpAG4AcwBpAGQAZQAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEsAZQByAG4AZQBsAD8ALAAgACAAIAAgACAATwBSACgAaABfACAAPgAgAGgALAAgAHcAXwAgAD4AIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGEAbABhAHIAIABoAGEAbgBkAGwAaQBuAGcAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgBLAGUAcgBuAGUAbAA/ACwAIAAgACAAIABBAE4ARAAoAGgAXwAgAD0AIAAxACwAIAB3AF8AIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAZAB1AGMAZQByACAAPQAgAGQAbwB0ACAAcAByAG8AZAB1AGMAdABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsAEwAQQBNAEIARABBACgAdgAsACAAUwBVAE0AKAB2ACAAKgAgAGsAZQByAG4AZQBsACkAKQAsAGYAdQBuAGMAdABpAG8AbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgAD0AIAAxADIAOAAgAJIhIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEYAbgA/ACwAIAAgACAAIAAgACAAIAAgACAAVABZAFAARQAoAGYAdQBuAGMAdABpAG8AbgApACAAPAA+ACAAMQAyADgALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGEAbABhAHIAIABvAHIAIABzAGMAYQBsAGEAcgARIGsAZQByAG4AZQBsACAAYwBhAHMAZQAgAJIhIABzAGkAbQBwAGwAZQAgAE0AQQBQAFwAbgAgACAAIAAgAFMAdABhAG4AZABhAHIAZABNAGEAcAAsACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAE0AQQBQACgAYQByAHIAYQB5ACwAIABmAHUAbgBjAHQAaQBvAG4AKQApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQASwBlAHIAbgBlAGwAPwAsACAAXAAiACMASwBFAFIATgBFAEwAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEYAbgA/ACwAIABcACIAIwBGAFUATgBDAFQASQBPAE4AIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoACgASQBzAFMAYwBhAGwAYQByAD8AKQAgACsAIAAoAEkAcwBTAGMAYQBsAGEAcgBLAGUAcgBuAGUAbAA/ACkALABTAHQAYQBuAGQAYQByAGQATQBhAHAAKAApACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEEAbgBjAGgAbwByACAAYwBvAHUAbgB0AHMAXABuACAAIAAgACAAYQBuAGMAaABfAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAIAAtACAAaABfACAAKwAgADEALABcAG4AIAAgACAAIABhAG4AYwBoAF8AYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwAgAC0AIAB3AF8AIAArACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABSAGUAcwBpAHoAZQC7AygAUwBFAFEAVQBFAE4AQwBFACgAYQBuAGMAaABfAHIAKQAsACAALAAgAGEAbgBjAGgAXwBjACkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsACAAYQBuAGMAaABfAGMAKQAsACAAYQBuAGMAaABfAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFcAaQBuAGQAbwB3ACAAcgBlAGQAdQBjAGUAcgBcAG4AIAAgACAAIABCAGwAbwBjAGsAQQBnAGcAuwMsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABpAF8ALAAgAGoAXwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsALAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgAGkAXwAgAC0AIAAxACwAIABqAF8AIAAtACAAMQApACwAIABoAF8ALAAgAHcAXwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AG8AdABhAGwALAAgACAAZgB1AG4AYwB0AGkAbwBuACgAYgBsAG8AYwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAbwB0AGEAbAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAcgBlAGQAdQBjAGUAcgAgAHQAbwAgAGUAYQBjAGgAIAB3AGkAbgBkAG8AdwBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABpACgAKQAsACAAagAoACkALAAgAEIAbABvAGMAawBBAGcAZwC7AykALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEAOABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEYAbwBsAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABTAHQAcgB1AGMAdAB1AHIAYQBsACAATQBhAHAAcABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQQBsAGkAZwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAZAB1AGMAZQBzACAAcgBlAGMAbwByAGQAcwAgAGkAbgAgAGEAbgAgAGEAcgByAGEAeQAgAGIAeQAgAGcAcgBvAHUAcABpAG4AZwAgAGkAZABlAG4AdABpAGMAYQBsACAAcgBvAHcAcwAgAGEAbgBkACAAYQBwAHAAbAB5AGkAbgBnACAAYQBuAFwAbgAgACAAIAAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAgAHQAbwAgAHQAaABlACAAYwBvAHIAcgBlAHMAcABvAG4AZABpAG4AZwAgAGUAbgB0AHIAaQBlAHMAIABpAG4AIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIABJAGYAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAgAGkAcwAgAG8AbQBpAHQAdABlAGQALAAgAEYAbwBsAGQAuwMgAHUAcwBlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGYAaQBlAGwAZAAgAG8AZgAgAGUAYQBjAGgAIAByAGUAYwBvAHIAZAAgAGEAcwBcAG4AIAAgACAAIAB0AGgAZQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAHYAZQBjAHQAbwByAC4AIABUAGgAaQBzACAAbQBvAGQAZQAgAGkAcwAgAGkAbgB0AGUAbgBkAGUAZAAgAGYAbwByACAAQwBPAFUATgBUAEEAOwAgAG8AdABoAGUAcgAgAHIAZQBkAHUAYwBlAHIAcwBcAG4AIAAgACAAIABtAGEAeQAgAHAAcgBvAGQAdQBjAGUAIAByAGUAcwB1AGwAdABzACAAYgB1AHQAIABhAHIAZQAgAG4AbwB0ACAAbQBlAGEAbgBpAG4AZwBmAHUAbAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAHIAbwB3AHMAIABkAGUAZgBpAG4AZQAgAGcAcgBvAHUAcABpAG4AZwAgAGsAZQB5AHMALgBcAG4AIAAgACAAIABbAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5AF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGEAZwBnAHIAZQBnAGEAdABlAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAAIAAgACAAIAAtACAAUgBlAGQAdQBjAGUAcgAgAEwAQQBNAEIARABBACAAYQBjAGMAZQBwAHQAaQBuAGcAIABhACAAMQBEACAAdgBlAGMAdABvAHIAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAQwBPAFUATgBUAEEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEYAbwBsAGQAuwMgAGgAYQBsAHQAcwAgAHcAaQB0AGgAIAAjAFYAQQBMAFUARQAhACAAaQBmACAAYQByAHIAYQB5ACAAYQBuAGQAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAgAGgAZQBpAGcAaAB0AHMAIABkAGkAZgBmAGUAcgAuAFwAbgAgACAAIAAgACIgIABGAG8AbABkALsDIABoAGEAbAB0AHMAIAB3AGkAdABoACAAIwBGAFUATgBDAFQASQBPAE4AIQAgAGkAZgAgAHIAZQBkAHUAYwBlAHIAIABpAHMAIABuAG8AdAAgAGEAIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQAuAFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4AuwMgAGMAYQBuAG8AbgBpAGMAYQBsAGkAegBlAHMAIAByAGUAYwBvAHIAZABzACAAcwBvACAAaQBkAGUAbgB0AGkAYwBhAGwAIAByAG8AdwBzACAAZwByAG8AdQBwACAAYwBsAGUAYQBuAGwAeQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBGAG8AbABkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAXQAsAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABlAGYAYQB1AGwAdAAgAHYAYQBsAHUAZQBzACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACwAVABBAEsARQAoAGEAcgByAGEAeQAsACAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAZAB1AGMAZQByAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsACAAIAAgACAASQBGACgATwBSACgASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsACAASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACkALABDAE8AVQBOAFQAQQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4ASQBGACgAQQBOAEQAKABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkAIAA8AD4AIABSAE8AVwBTACgAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQApACwAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEMAYQBuAG8AbgBpAGMAYQBsACAAZwByAG8AdQBwAGkAbgBnACAAawBlAHkAcwBcAG4AIAAgACAAIABhAGwAaQBnAG4AZQBkACwAIAAgACAAIAAgAEEAbABpAGcAbgC7AygAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBnAGcAcgBlAGcAYQB0AGkAbwBuAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAARwBSAE8AVQBQAEIAWQAoAGEAbABpAGcAbgBlAGQALAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgACwAIAAwACkALABcAG4AXABuACAAIAAgACAAYQBnAGcAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADkAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABKAG8AaQBuADIARAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABKAG8AaQBuAHMAIABhAGwAbAAgAG4AbwBuABEgZQBtAHAAdAB5ACAAdgBhAGwAdQBlAHMAIABhAGMAcgBvAHMAcwAgADIAIAB0AG8AIAA0ACAAaQBkAGUAbgB0AGkAYwBhAGwAbAB5ABEgcwBoAGEAcABlAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAgAHUAcwBpAG4AZwBcAG4AIAAgACAAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAIABkAGUAbABpAG0AaQB0AGUAcgAuACAAVABoAGUAIABvAHUAdABwAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIAB0AGgAZQAgAGkAbgBwAHUAdABzAC4AXABuAFwAbgAgACAAIAAgAEEAIABjAGUAbABsACAAaQBzACAAYwBvAG4AcwBpAGQAZQByAGUAZAAgABwgZQBtAHAAdAB5AB0gIABpAGYAIABpAHQAIABtAGEAdABjAGgAZQBzACAAQQBOAFkAIABvAGYAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABMAEUATgAoAGMAZQBsAGwAKQAgAD0AIAAwAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAGMAZQBsAGwAIAA9ACAARgBBAEwAUwBFAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAGMAZQBsAGwAIAA9ACAAaQBnAG4AbwByAGUAIAAoAHUAcwBlAHIAESBzAHAAZQBjAGkAZgBpAGUAZAApAFwAbgBcAG4AIAAgACAAIABKAG8AaQBuADIARAC7AyAAaQBzACAAYQBuACAAYQBsAHQAZQByAG4AYQB0AGkAdgBlACAAdABvACAAbgBlAHMAdABlAGQAIABNAEEAUAAgAGwAbwBnAGkAYwAgAGYAbwByACAAZQBsAGUAbQBlAG4AdAARIHcAaQBzAGUAIABqAG8AaQBuAGkAbgBnAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0AIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAZABlAGwAaQBtAGkAdABlAHIAXQAgAC0AIABEAGUAbABpAG0AaQB0AGUAcgAgAGYAbwByACAAagBvAGkAbgBpAG4AZwAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABcACIALAAgAFwAIgApAC4AXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACAAIAAgACAALQAgAFYAYQBsAHUAZQAgAHQAcgBlAGEAdABlAGQAIABhAHMAIABlAG0AcAB0AHkAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkAcwAgAG0AdQBzAHQAIABoAGEAdgBlACAAaQBkAGUAbgB0AGkAYwBhAGwAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAIiAgAEUAbQBwAHQAeQAgAGMAZQBsAGwAcwAgAGEAcgBlACAAcwBrAGkAcABwAGUAZAA7ACAAbgBvACAAdAByAGEAaQBsAGkAbgBnACAAZABlAGwAaQBtAGkAdABlAHIAIABpAHMAIABhAGQAZABlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASgBvAGkAbgAyAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8ANABdACwAXABuACAAIAAgACAAWwBkAGUAbABpAG0AaQB0AGUAcgBdACwAXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAASQBuAGMAbAB1AGQAZQAzAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkAKQAsAFwAbgAgACAAIAAgAEkAbgBjAGwAdQBkAGUANAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkALAAgAEYAQQBMAFMARQAsACAAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8ANAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACwAIABGAEEATABTAEUALAAgAGEAcgByAGEAeQBfADQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAbABpAG0AaQB0AGUAcgAgACsAIABpAGcAbgBvAHIAZQBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABkAGUAbABpAG0AaQB0AGUAcgApACwAIABcACIALAAgAFwAIgAsACAAZABlAGwAaQBtAGkAdABlAHIAKQAsAFwAbgAgACAAIAAgAGkAZwBuAG8AcgBlACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZwBuAG8AcgBlACkALAAgAFwAIgBcACIALAAgAGkAZwBuAG8AcgBlACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMQApACwAXABuAFwAbgAgACAAIAAgAGgAgiAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACwAXABuACAAIAAgACAAdwCCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AXABuACAAIAAgACAAaACDICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAzACkALABcAG4AIAAgACAAIAB3AIMgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADMAKQAsAFwAbgBcAG4AIAAgACAAIABoAIQgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADQAKQAsAFwAbgAgACAAIAAgAHcAhCAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuACAAYwBoAGUAYwBrAHMAXABuACAAIAAgACAAUwBfADIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGgAIAA8AD4AIABoAIIgLAAgAHcAIAA8AD4AIAB3AIIgKQAsAFwAbgAgACAAIAAgAFMAXwAzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAG4AYwBsAHUAZABlADMAPwAgACoAIABPAFIAKABoACAAPAA+ACAAaACDICwAIAB3ACAAPAA+ACAAdwCDICkALABcAG4AIAAgACAAIABTAF8ANAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAGMAbAB1AGQAZQA0AD8AIAAqACAATwBSACgAaAAgADwAPgAgAGgAhCAsACAAdwAgADwAPgAgAHcAhCApACwAXABuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABPAFIAKABTAF8AMgAsACAAUwBfADMALAAgAFMAXwA0ACkALABcAG4AXABuACAAIAAgACAASQBGACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AYwBjAHUAcABhAG4AYwB5ACAAcAByAGUAZABpAGMAYQB0AGUAXABuACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDLAAgACAATABBAE0AQgBEAEEAKABhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABhACAAPAA+ACAARgBBAEwAUwBFACkAIAAqACAAKABMAEUATgAoAGEAKQAgADwAPgAgADAAKQAgACoAIAAoAGEAIAA8AD4AIABpAGcAbgBvAHIAZQApACkALABcAG4AXABuACAAIAAgACAAbQBfADEALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwAxACkALABcAG4AIAAgACAAIABtAF8AMgAsACAAIAAgACAAIAAgACAAIABPAGMAYwB1AHAAaQBlAGQAuwMoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAG0AXwAzACwAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AygAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAbQBfADQALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASgBvAGkAbgAgAGkAbgAgAG8AcgBkAGUAcgAsACAAcwBrAGkAcABwAGkAbgBnACAAZQBtAHAAdABpAGUAcwBcAG4AIAAgACAAIABqAG8AaQBuAGUAZAAsACAAIAAgACAAIABJAEYAKABtAF8AMQAsACAAYQByAHIAYQB5AF8AMQAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACAAJgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8AMgAsACAAYQByAHIAYQB5AF8AMgAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACAAJgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG0AXwAzACwAIABhAHIAcgBhAHkAXwAzACAAJgAgAGQAZQBsAGkAbQBpAHQAZQByACwAIABcACIAXAAiACkAIAAmAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8ANAAsACAAYQByAHIAYQB5AF8ANAAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABqAG8AaQBuAGUAZAAsAGQAZQBsAGkAbQBpAHQAZQByACwALQAxACwAMQAsACwAagBvAGkAbgBlAGQAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAjACMAIAAwADUAIAAtACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAgACoALwBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVABoAGkAcwAgAHMAZQBjAHQAaQBvAG4AIABjAG8AbgB0AGEAaQBuAHMAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHQAaABhAHQAIAByAGUAcABsAGkAYwBhAHQAZQAgAGEAcgByAGEAeQBzACAAYQBsAG8AbgBnACAAcgBvAHcAcwAsACAAYwBvAGwAdQBtAG4AcwAsACAAbwByACAAYgBvAHQAaAAuAFwAbgBcAG4ARgB1AG4AYwB0AGkAbwBuAHMAOgBcAG4AIAAgACAAIAAiICAARQBjAGgAbwC7AyAAIAAgACAAIAAgACAAIAAgACAALQAgAFIAZQBwAGUAYQB0ACAAZQBhAGMAaAAgAGUAbABlAG0AZQBuAHQAIABpAG4AIABhACAAMQBEACAAYQByAHIAYQB5ACAAYgB5ACAAYwBvAHUAbgB0AC4AXABuACAAIAAgACAAIiAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMgACAAIAAgAC0AIABSAGUAcABlAGEAdAAgAGUAYQBjAGgAIAByAG8AdwAgAGIAeQAgAGEAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQALgBcAG4AIAAgACAAIAAiICAAUgBlAHAAZQBhAHQAQwBvAGwAcwC7AyAAIAAgACAALQAgAFIAZQBwAGUAYQB0ACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAYgB5ACAAYQAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdAAuAFwAbgAgACAAIAAgACIgIABUAGUAcwBzAGUAbABsAGEAdABlALsDIAAgACAAIAAtACAAVABpAGwAZQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AIABtAG8AZAB1AGwAYQByACAAZgBhAHMAaABpAG8AbgAsACAAcwB1AHAAcABvAHIAdABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABhAHIAdABpAGEAbAAgAHQAaQBsAGUAcwAgAHcAaABlAG4AIABvAHUAdABwAHUAdAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAG8AIABuAG8AdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAHYAaQBkAGUAIABlAHYAZQBuAGwAeQAuAFwAbgBcAG4AXABuAFwAbgBcACIAUAByAGUAcwBlAG4AdAAgAHMAdQBjAGMAZQBzAHMAIABpAHMAIABhAG4AIABlAGMAaABvACAAbwBmACAAYQAgAHAAYQBzAHQAIAB0AHIAaQB1AG0AcABoAC4AIABGAGEAaQBsAHUAcgBlACAAaQBzACAAcgBlAGQAdQBuAGQAYQBuAHQALgBcACIAIAAtACAAUgBlAHAAZQB0AHQAbwBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFIAUAAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABFAGMAaABvALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABSAGUAcABlAHQAaQB0AGkAbwBuAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHAAZQBhAHQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgADEARAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAXABuACAAIAAgACAAbgB1AG0AZQByAGkAYwAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwByACAAcwBjAGEAbABhAHIAIAB0AG8AIABiAGUAIABlAGMAaABvAGUAZAAuAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAKABuAHUAbQBlAHIAaQBjACwAIABlIiAAMQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgADEA1wAxACAAYQByAHIAYQB5AHMALgBcAG4AIAAgACAAIAAiICAASQBmACAAcgBlAHAAZQBhAHQAIABoAGEAcwAgAGEAIABkAGkAZgBmAGUAcgBlAG4AdAAgAGwAZQBuAGcAdABoACAAdABoAGEAbgAgAHYAZQBjAHQAbwByACwAIAB0AGgAZQAgAGwAYQBzAHQAIAByAGUAcABlAGEAdAAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAaQBzACAAZQB4AHQAZQBuAGQAZQBkACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIAB2AGUAYwB0AG8AcgAgAGwAZQBuAGcAdABoAC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAaQBzACAAYQBsAHcAYQB5AHMAIABhACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAYwBoAG8AuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAdgBlAGMAdABvAHIALABcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAByAGUAcABlAGEAdAApACwAIAByAGUAcABlAGEAdAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAKQAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAFYAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAZQBjAHQAbwByACkALABcAG4AIAAgACAAIABSAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIAAoAGUAeAB0AGUAbgBkACAAbABhAHMAdAAgAHYAYQBsAHUAZQAgAGkAZgAgAG4AZQBlAGQAZQBkACkAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABWAGgAIAA8AD4AIABSAGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAByAGUAcABlAGEAdAAsACAAVgBoACwAIAAsACAAQABUAEEASwBFACgAcgBlAHAAZQBhAHQALAAgAC0AMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGEAcwBlACAAaQBuAGQAZQB4AFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAUgBPAFcAUwAoAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4AGkAbQB1AG0AIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAdQBpAGwAZAAgAGkAbgBkAGUAeAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABUAE8AQwBPAEwAKABJAEYAKABTAEkARwBOACgAcgAgAC0AIABTAEUAUQBVAEUATgBDAEUAKAAsACAAbQAsACAAMAAsACAAKQApACAAPQAgADEALABpACwATgBBACgAKQApACwAMgApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB2AGUAYwB0AG8AcgAsACAAaQBkAHgAKAApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAMAAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBwAGUAYQB0AHMAIABlAGEAYwBoACAAcgBvAHcAIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5ACAAYQBjAGMAbwByAGQAaQBuAGcAIAB0AG8AIABhACAAdgBlAGMAdABvAHIAIABvAGYAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAuACAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHMAdQBwAHAAbwByAHQAZQBkAC4AIABSAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAbQB1AHMAdAAgAGIAZQAgAG4AdQBtAGUAcgBpAGMAXABuACAAIAAgACAAYQBuAGQAIABlIiAAMQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIAByAG8AdwBzACAAdwBpAGwAbAAgAGIAZQAgAHIAZQBwAGUAYQB0AGUAZAAuAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAKABuAHUAbQBlAHIAaQBjACwAIABlIiAAMQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAcgBlAHAAZQBhAHQAIABoAGEAcwAgAGYAZQB3AGUAcgAgAGUAbgB0AHIAaQBlAHMAIAB0AGgAYQBuACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMALAAgAHQAaABlACAAbABhAHMAdAAgAHIAZQBwAGUAYQB0AFwAbgAgACAAIAAgACAAIAB2AGEAbAB1AGUAIABpAHMAIABlAHgAdABlAG4AZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQAgAGEAcgByAGEAeQAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAcAByAGUAcwBlAHIAdgBlAHMAIAB0AGgAZQAgAGMAbwBsAHUAbQBuACAAcwB0AHIAdQBjAHQAdQByAGUAIABvAGYAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBSAGUAcABlAGEAdABSAG8AdwBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAXABuAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAHIAZQBwAGUAYQB0ACkALAAgAHIAZQBwAGUAYQB0ACAAPAA9ACAAMAApACwAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcgBlAHAAZQBhAHQAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABBAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAFIAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAZQBuAGQAIAByAGUAcABlAGEAdAAgAHYAZQBjAHQAbwByACAAaQBmACAAbgBlAGUAZABlAGQAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABBAGgAIAA8AD4AIABSAGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAByAGUAcABlAGEAdAAsACAAQQBoACwAIAAsACAAQABUAEEASwBFACgAcgBlAHAAZQBhAHQALAAgAC0AMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGEAcwBlACAAcgBvAHcAIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAUgBPAFcAUwAoAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4AGkAbQB1AG0AIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAdQBpAGwAZAAgAGkAbgBkAGUAeAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABUAE8AQwBPAEwAKABJAEYAKABTAEkARwBOACgAcgAgAC0AIABTAEUAUQBVAEUATgBDAEUAKAAsACAAbQAsACAAMAApACkAIAA9ACAAMQAsAGkALABOAEEAKAApACkALAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABhAHIAcgBhAHkALAAgAGkAZAB4ACgAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUgBQADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFIAZQBwAGUAYQB0AEMAbwBsAHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAFIAZQBwAGUAdABpAHQAaQBvAG4AXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcABlAGEAdABzACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAbwBmACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmACAAcgBlAHAAZQBhAHQAXABuACAAIAAgACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAIABuAHUAbQBlAHIAaQBjAFwAbgAgACAAIAAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAYwBvAGwAdQBtAG4AcwAgAHcAaQBsAGwAIABiAGUAIAByAGUAcABlAGEAdABlAGQALgBcAG4AIAAgACAAIAByAGUAcABlAGEAdAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgACgAbgB1AG0AZQByAGkAYwAsACAAZSIgADEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAHIAZQBwAGUAYQB0ACAAaABhAHMAIABmAGUAdwBlAHIAIABlAG4AdAByAGkAZQBzACAAdABoAGEAbgAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACwAIAB0AGgAZQAgAGwAYQBzAHQAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIAAgACAAdgBhAGwAdQBlACAAaQBzACAAZQB4AHQAZQBuAGQAZQBkACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABhAHIAcgBhAHkAIAB3AGkAZAB0AGgALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABwAHIAZQBzAGUAcgB2AGUAcwAgAHQAaABlACAAcgBvAHcAIABzAHQAcgB1AGMAdAB1AHIAZQAgAG8AZgAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBwAGUAYQB0AEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAcgBlAHAAZQBhAHQALABcAG4AXABuAEkARgAoAE8AUgAoAEkAUwBUAEUAWABUACgAcgBlAHAAZQBhAHQAKQAsACAAcgBlAHAAZQBhAHQAIAA8AD0AIAAwACkALABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIAByAGUAcABlAGEAdAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAEEAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAUgBoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdABlAG4AZAAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIABpAGYAIABuAGUAZQBkAGUAZABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEAdwAgADwAPgAgAFIAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAHIAZQBwAGUAYQB0ACwAIABBAHcALAAgACwAIABAAFQAQQBLAEUAKAByAGUAcABlAGEAdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAYQBzAGUAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKABSAE8AVwBTACgAYwApACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHgAaQBtAHUAbQAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgAG0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABjACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgB1AGkAbABkACAAaQBuAGQAZQB4ACAAdgBlAGMAdABvAHIAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFQATwBDAE8ATAAoAEkARgAoAFMASQBHAE4AKABjACAALQAgAFMARQBRAFUARQBOAEMARQAoACwAIABtACwAIAAwACkAKQAgAD0AIAAxACwAaQAsAE4AQQAoACkAKQAsADIAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAGEAcgByAGEAeQAsACAAaQBkAHgAKAApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVABlAHMAcwBlAGwAbABhAHQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFQARwByAGkAZAC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAbQBvAGQAdQBsAGEAcgAgAHQAZQBzAHMAZQBsAGwAYQB0AGkAbwBuACAAbwBmACAAYQAgADIARAAgAHAAYQB0AHQAZQByAG4AIABkAGUAZgBpAG4AZQBkACAAYgB5ACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAgANcAIABuAGUAdwBfAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgAFQAaABlACAAcABhAHQAdABlAHIAbgAgAGkAcwAgAHIAZQBwAGUAYQB0AGUAZAAgAHUAcwBpAG4AZwAgAG0AbwBkAHUAbABhAHIAIAByAG8AdwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AIABjAHkAYwBsAGUAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAdABoAGUAXABuACAAIAAgACAAcABhAHQAdABlAHIAbgAZIHMAIABvAHcAbgAgAGQAaQBtAGUAbgBzAGkAbwBuAHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgACgAMQBEACAAYQByAHIAYQB5AHMAIABhAGMAYwBlAHAAdABlAGQALAAgAHMAYwBhAGwAYQByAHMAIABhAHIAZQAgAGYAbwByAGIAaQBkAGQAZQBuACkALgBcAG4AIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGkAbgAgAHQAaABlACAAbwB1AHQAcAB1AHQAIAB0AGUAcwBzAGUAbABsAGEAdABpAG8AbgAuAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHQAZQBzAHMAZQBsAGwAYQB0AGkAbwBuAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUABlAHIAZgBvAHIAbQBzACAAbQBvAGQAdQBsAGEAcgAgAHIAZQBwAGUAdABpAHQAaQBvAG4AIAB1AHMAaQBuAGcAIABUAEcAcgBpAGQAuwMgAGYAbwByACAAcgBvAHcALwBjAG8AbAB1AG0AbgAgAGMAeQBjAGwAaQBuAGcALgBcAG4AIAAgACAAIAAiICAAUwB1AHAAcABvAHIAdABzACAAcABhAHIAdABpAGEAbAAgAHQAaQBsAGUAcwAgAHcAaABlAG4AIABuAGUAdwAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABhAHIAZQAgAG4AbwB0ACAAbQB1AGwAdABpAHAAbABlAHMAIABvAGYAXABuACAAIAAgACAAIAAgAHQAaABlACAAcABhAHQAdABlAHIAbgAgAHMAaQB6AGUALgBcAG4AIAAgACAAIAAiICAAUgBlAGoAZQBjAHQAcwAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVABlAHMAcwBlAGwAbABhAHQAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACwAXABuACAAIAAgACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUABhAHQAdABlAHIAbgAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcABhAHQAdABlAHIAbgApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAcABhAHQAdABlAHIAbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAZABlAHQAZQBjAHQAaQBvAG4AXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABuAGUAdwAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAIAAgACAAIABJAE4ARABFAFgAKABuAGUAdwBfAGgAZQBpAGcAaAB0ACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIABuAGUAdwBfAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAG4AZQB3AF8AdwBpAGQAdABoACwAIAAxACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAATgBvAEMAaABhAG4AZwBlAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAdwAgAD0AIABuAGUAdwBfAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQASABXAD8ALAAgACAAIAAgACAATwBSACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAgADwAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAIAA8AD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAG4AZQB3AF8AaABlAGkAZwBoAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABuAGUAdwBfAHcAaQBkAHQAaAApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AQwBoAGEAbgBnAGUAPwAsACAAcABhAHQAdABlAHIAbgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEgAVwA/ACwAIABcACIAIwBOAEUAVwAtAEgARQBJAEcASABUAC8AVwBJAEQAVABIACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AdQB0AHAAdQB0ACAAZwBlAG8AbQBlAHQAcgB5ACAAcABsAGEAYwBlAGgAbwBsAGQAZQByAFwAbgAgACAAIAAgAGUAeABwAF8AcwBoAGEAcABlACwAIAAgACAAIABFAFgAUABBAE4ARAAoADAALAAgAG4AZQB3AF8AaABlAGkAZwBoAHQALAAgAG4AZQB3AF8AdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBvAGQAdQBsAGEAcgAgAHIAbwB3AC8AYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEcAcgBpAGQAuwMoAGUAeABwAF8AcwBoAGEAcABlACwAIABoACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABHAHIAaQBkALsDKABlAHgAcABfAHMAaABhAHAAZQAsACAAdwAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAZQBzAHMAZQBsAGwAYQB0AGUAZAAgAG8AdQB0AHAAdQB0AFwAbgAgACAAIAAgAHQAZQBzAHMALAAgACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKABwAGEAdAB0AGUAcgBuACwAIABpACwAIABqACkALABcAG4AXABuACAAIAAgACAAdABlAHMAcwBcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAjACMAIAAwADYAIAAtACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACAAKgAvAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIABpAHMAIABhACAAYwBvAGwAbABlAGMAdABpAG8AbgAgAG8AZgAgAGYAdQBuAGMAdABpAG8AbgBzACAAZgBvAHIAIABlAGwAZQBnAGEAbgB0ACAAcwBlAHEAdQBlAG4AYwBpAG4AZwAsAFwAbgAgACAAIAAgAGMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAGEAbgBhAGwAeQBzAGkAcwAsACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAESBiAGEAcwBlAGQAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4ALAAgAGEAbgBkACAAcwB0AGEAdABpAHMAdABpAGMAcwAuAFwAbgAgACAAIAAgAFQAaABpAHMAIABtAG8AZAB1AGwAZQAgAGUAeAB0AGUAbgBkAHMAIAB0AGgAZQAgAGMAYQBwAGEAYgBpAGwAaQB0AGkAZQBzACAAbwBmACAAbgBhAHQAaQB2AGUAIABFAHgAYwBlAGwAIABmAHUAbgBjAHQAaQBvAG4AcwBcAG4AIAAgACAAIAAoAGUALgBnAC4ALAAgAE0AbwBkAGUAuwMgAGMAYQBuACAAcgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AbwBzAHQAIABmAHIAZQBxAHUAZQBuAHQAIABuAHUAbQBlAHIAaQBjAGEAbAAgAG8AcgAgAHQAZQB4AHQAIAB2AGEAbAB1AGUAcwApAC4AXABuAFwAbgAgACAAIAAgAFMAdQBiABEgYwBhAHQAZQBnAG8AcgBpAGUAcwA6AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABTAGUAcQB1AGUAbgBjAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AHIAZQBhAGsAuwMsACAAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgB5AEQAaQBhAGcAuwMsACAARABpAGEAZwBNAGEAcAC7AywAIABEAGkAYQBnAEkAbgBkAGUAeAC7AywAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwMsACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AywAIABRAHUAYQBkAHcAaQBzAGUAuwMsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwByAG8AdQBwAGIAeQBCAGkAbgC7AywAIABHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMsACAAUABpAHYAbwB0AGIAeQBDAGEAdAC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwByAGEAaQBuALsDLAAgAE0AbwBvAHIAZQBBAGcAZwC7AywAIABNAG8AbwByAGUAUwBlAGwAZQBjAHQAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUwB0AGEAdABpAHMAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAaQBzAHQAbwBnAHIAYQBtALsDLAAgAE0AbwBkAGUAuwMsACAAWgBvAG4AZQBTAHQAYQB0ALsDXABuACoALwBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFMAdAByAGUAYQBrALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAFMAZQBxAHUAZQBuAGMAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwBtAHAAdQB0AGUAcwAgAHMAdAByAGUAYQBrACAAYwBvAHUAbgB0AHMAIABvAGYAIABjAG8AbgBzAGUAYwB1AHQAaQB2AGUAIABpAGQAZQBuAHQAaQBjAGEAbAAgAHYAYQBsAHUAZQBzACAAaQBuACAAYQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFMAdAByAGUAYQBrAHMAIABpAG4AYwByAGUAbQBlAG4AdAAgAGYAbwByAHcAYQByAGQAIAAoADEALAAgADIALAAgADMALAAgACYgKQAgAHcAaABlAG4AZQB2AGUAcgAgAHQAaABlACAAYwB1AHIAcgBlAG4AdAAgAGUAbABlAG0AZQBuAHQAIABtAGEAdABjAGgAZQBzAFwAbgAgACAAIAAgAHQAaABlACAAcAByAGUAdgBpAG8AdQBzACAAbwBuAGUALgAgAEYAbwByACAAMgBEACAAYQByAHIAYQB5AHMALAAgAHMAdAByAGUAYQBrAHMAIABhAHIAZQAgAGMAbwBtAHAAdQB0AGUAZAAgAHIAbwB3ABEgbQBhAGoAbwByACAAYgB5ACAAZABlAGYAYQB1AGwAdAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAgACAAIAAgACAAIAAtACAARgBvAHIAIAAxAEQAIABhAHIAcgBhAHkAcwAsACAAYwBvAG0AcAB1AHQAZQAgAHMAdAByAGUAYQBrAHMAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIABpAG4AcwB0AGUAYQBkACAAbwBmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBvAHcAESB3AGkAcwBlAC4AIABJAGcAbgBvAHIAZQBkACAAZgBvAHIAIAAyAEQAIABhAHIAcgBhAHkAcwAuAFwAbgAgACAAIAAgAFsASQBuAGMAbAB1AGQAZQBfAFMAeQBtAGIAbwBsAD8AXQAgACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAGEAcABwAGUAbgBkACAAdABoAGUAIABzAHkAbQBiAG8AbAAgAHQAbwAgAHQAaABlACAAcwB0AHIAZQBhAGsAIABjAG8AdQBuAHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAGUALgBnAC4ALAAgAFcAtwAxACwAIABXALcAMgAsACAATAC3ADEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIAByAGUAdAB1AHIAbgAgAHQAaABlAG0AcwBlAGwAdgBlAHMALgBcAG4AIAAgACAAIAAiICAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAcgBvAHcAESBtAGEAagBvAHIALAAgAHAAcgBvAGMAZQBzAHMAZQBkACwAIAB0AGgAZQBuACAAcgBlAHMAdABvAHIAZQBkAC4AXABuACAAIAAgACAAIiAgAEgAbwByAGkAegBvAG4AdABhAGwAPwAgAG8AbgBsAHkAIABhAHAAcABsAGkAZQBzACAAdABvACAAMQBEACAAYQByAHIAYQB5AHMALgBcAG4AIAAgACAAIAAiICAASQBuAGMAbAB1AGQAZQBfAFMAeQBtAGIAbwBsAD8AIAB1AHMAZQBzACAAVQBOAEkAQwBIAEEAUgAoADEAOAAzACkAIAAoALcAKQAgAGEAcwAgAHQAaABlACAAcwBlAHAAYQByAGEAdABvAHIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwB0AHIAZQBhAGsAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAsAFwAbgAgACAAIAAgAFsASQBuAGMAbAB1AGQAZQBfAFMAeQBtAGIAbwBsAD8AXQAsAFwAbgBcAG4ASQBGACgAQQBOAEQAKABSAE8AVwBTACgAYQByAHIAYQB5ACkAIAA9ACAAMQAsACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACAAPQAgADEAKQAsAGEAcgByAGEAeQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABJAHMAMgBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPgAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAMgBEACAAkiEgADEARABcAG4AIAAgACAAIABhAHIAcgBhAHkALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAyAEQAPwAsACAAVABPAEMATwBMACgAYQByAHIAYQB5ACkALAAgAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuACAAKABvAG4AbAB5ACAAcgBlAGwAZQB2AGEAbgB0ACAAZgBvAHIAIAAxAEQAKQBcAG4AIAAgACAAIABOAG8ARABpAHIAPwAsACAAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgASABvAHIAaQB6AG8AbgB0AGEAbAA/ACkALABcAG4AIAAgACAAIABmAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBEAGkAcgA/ACwAIABWAFMAVABBAEMASwAsACAASABTAFQAQQBDAEsAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbQBwAGEAcgBlACAAdwBpAHQAaAAgAHAAcgBlAHYAaQBvAHUAcwAgAGUAbABlAG0AZQBuAHQAXABuACAAIAAgACAAawBlAHAAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8ARABpAHIAPwAsACAARABSAE8AUAAoAGEAcgByAGEAeQAsACAALQAxACkALAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgACwAIAAtADEAKQApACwAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIABhAHIAcgBhAHkAIAA9ACAAZgBuACgAXAAiAG8AbQBpAHQAXAAiACwAIABrAGUAcAB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBjAGMAdQBtAHUAbABhAHQAZQAgAHMAdAByAGUAYQBrACAAYwBvAHUAbgB0AHMAXABuACAAIAAgACAAYQBjAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEMAQQBOACgAMAAsAGIAbwBvAGwALABMAEEATQBCAEQAQQAoAGEALAAgAHYALABJAEYAKABhACAAPQAgADAALAAgADEALAAgAEkARgAoAHYALAAgAGEAIAArACAAMQAsACAAMQApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHMAeQBtAGIAbwBsACAAaQBuAGMAbAB1AHMAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEkAbgBjAGwAdQBkAGUAXwBTAHkAbQBiAG8AbAA/ACkALABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAHIAcgBhAHkAIAAmACAAVQBOAEkAQwBIAEEAUgAoADEAOAAzACkAIAAmACAAYQBjAGMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcwB0AG8AcgBlACAAMgBEACAAcwBoAGEAcABlACAAaQBmACAAbgBlAGUAZABlAGQAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMgBEAD8ALAAgAFcAUgBBAFAAUgBPAFcAUwAoAHIAZQBzAHUAbAB0ACwAIAB3ACkALAAgAHIAZQBzAHUAbAB0ACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAUwBlAHEAdQBlAG4AYwBpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABjAG8AdQBuAHQAZABvAHcAbgAgAGkAbgBkAGkAYwBlAHMAIABmAG8AcgAgAGMAbwBuAHQAaQBnAHUAbwB1AHMAIAByAHUAbgBzACAAaQBuACAAYQAgADEARAAgAGEAcgByAGEAeQAuACAARQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgAGMAbwB1AG4AdABzACAAZABvAHcAbgAgAGYAcgBvAG0AIABpAHQAcwAgAGwAZQBuAGcAdABoACAAdABvACAAMQAuACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMgAGkAcwAgAG0AbwBzAHQAIAB1AHMAZQBmAHUAbAAgAHcAaABlAG4AIAB3AG8AcgBrAGkAbgBnAFwAbgAgACAAIAAgAHcAaQB0AGgAIABzAG8AcgB0AGUAZAAgAHYAZQBjAHQAbwByAHMAIABhAG4AZAAgAGkAcwAgAHQAaABlACAAbgBhAHQAdQByAGEAbAAgAHIAZQB2AGUAcgBzAGUAIABvAGYAIABTAHQAcgBlAGEAawC7Ay4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAdgBlAGMAdABvAHIAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0AIAAgACAAIAAtACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAbwB1AHQAcAB1AHQAIABpAHMAIAB2AGUAcgB0AGkAYwBhAGwALgAgAEkAZgAgAFQAUgBVAEUALAAgAG8AdQB0AHAAdQB0ACAAaQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAdAB1AHIAbgBlAGQAIABoAG8AcgBpAHoAbwBuAHQAYQBsAGwAeQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEEAbAB3AGEAeQBzACAAZgBsAGEAdAB0AGUAbgBzACAAaQBuAHAAdQB0ACAAdABvACAAYQAgAHMAaQBuAGcAbABlACAAYwBvAGwAdQBtAG4AIABiAGUAZgBvAHIAZQAgAHAAcgBvAGMAZQBzAHMAaQBuAGcALgBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEMAbwB1AG4AdABkAG8AdwBuALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0ALABcAG4AXABuAEkARgAoAEEATgBEACgAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPQAgADEALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgAD0AIAAxACkALABhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA+ACAAMQAsACAAdwAgAD4AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgADIARAAgAJIhIAAxAEQAXABuACAAIAAgACAAYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMgBEAD8ALAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACwAIABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgAgACgAbwBuAGwAeQAgAHIAZQBsAGUAdgBhAG4AdAAgAGYAbwByACAAMQBEACkAXABuACAAIAAgACAATgBvAEQAaQByAD8ALAAgACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAEgAbwByAGkAegBvAG4AdABhAGwAPwApACwAXABuACAAIAAgACAAZgBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8ARABpAHIAPwAsACAAVgBTAFQAQQBDAEsALAAgAEgAUwBUAEEAQwBLACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AcABhAHIAZQAgAHcAaQB0AGgAIABwAHIAZQB2AGkAbwB1AHMAIABlAGwAZQBtAGUAbgB0AFwAbgAgACAAIAAgAGsAZQBwAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAEQAaQByAD8ALAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgAC0AMQApACwAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAYQByAHIAYQB5ACAAPQAgAGYAbgAoAFwAIgBvAG0AaQB0AFwAIgAsACAAawBlAHAAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAYwBjAHUAbQB1AGwAYQB0AGUAIABzAHQAcgBlAGEAawAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGEAYwBjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBDAEEATgAoADAALABiAG8AbwBsACwATABBAE0AQgBEAEEAKABhACwAIAB2ACwASQBGACgAYQAgAD0AIAAwACwAIAAxACwAIABJAEYAKAB2ACwAIABhACAAKwAgADEALAAgADEAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGgAYQBuAGcAZQAgAGcAcgBvAHUAcABzAFwAbgAgACAAIAAgAGMAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBDAEEATgAoADAALABOAE8AVAAoAGIAbwBvAGwAKQAsAFMAVQBNACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBvAHIAdAAgAGQAZQBzAGMAZQBuAGQAaQBuAGcAXABuACAAIAAgACAAcwBvAHIAdABlAGQALAAgACAAIAAgACAAIAAgACAAIABTAE8AUgBUAEIAWQAoAGEAYwBjACwAYwBnACwAMQAsAGEAYwBjACwALQAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgADIARAAgAHMAaABhAHAAZQAgAGkAZgAgAG4AZQBlAGQAZQBkAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgACAASQBGACgASQBzADIARAA/ACwAIABXAFIAQQBQAFIATwBXAFMAKABzAG8AcgB0AGUAZAAsACAAdwApACwAIABzAG8AcgB0AGUAZAApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEIAeQBEAGkAYQBnALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAcABwAGwAaQBlAHMAIABhAG4AIABFAFQAQQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AcgAgAEwAYQBtAGIAZABhACAAdABvACAAZQBhAGMAaAAgAGQAaQBhAGcAbwBuAGEAbAAgAG8AZgAgAGEAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABEAGkAYQBnAG8AbgBhAGwAcwAgAGEAcgBlACAAZQB4AHQAcgBhAGMAdABlAGQAIABmAHIAbwBtACAAdABvAHAAESBsAGUAZgB0ACAAdABvACAAYgBvAHQAdABvAG0AESByAGkAZwBoAHQALAAgAHcAaQB0AGgAIABlAGEAYwBoACAAZABpAGEAZwBvAG4AYQBsAFwAbgAgACAAIAAgAHIAZQBwAHIAZQBzAGUAbgB0AGUAZAAgAGEAcwAgAGEAIAByAG8AdwAgAGkAbgAgAHQAaABlACAAbwB1AHQAcAB1AHQALgAgAE8AcAB0AGkAbwBuAGEAbABsAHkALAAgAHIAZQBzAHUAbAB0AHMAIABtAGEAeQAgAGIAZQAgAHMAdABhAGMAawBlAGQAXABuACAAIAAgACAAcgBvAHcAESB3AGkAcwBlACAAKAB2AGUAcgB0AGkAYwBhAGwAKQAgAG8AcgAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQAgACgAaABvAHIAaQB6AG8AbgB0AGEAbAApAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAHMAYwBhAGwAYQByAHMAIABuAG8AdAAgAGEAYwBjAGUAcAB0AGUAZAApAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAAIAAgACAAIAAgACAAIAAgAC0AIABFAFQAQQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AcgAgAEwAYQBtAGIAZABhACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABkAGkAYQBnAG8AbgBhAGwALgBcAG4AIAAgACAAIABbAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/AF0AIAAgACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQBzAHUAbAB0AHMAIABhAHIAZQAgAHMAdABhAGMAawBlAGQAIAB2AGUAcgB0AGkAYwBhAGwAbAB5ADsAIABvAHQAaABlAHIAdwBpAHMAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAGEAZwBvAG4AYQBsAHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAgAGEAcwAgAGMAbwBsAHUAbQBuAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYQBuAGQAIAAxAEQAIABhAHIAcgBhAHkAcwAgAGEAcgBlACAAcgBlAGoAZQBjAHQAZQBkACAAYgB5ACAAVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwMuAFwAbgAgACAAIAAgACIgIABJAGYAIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAIABvAG0AaQB0AHQAZQBkACwAIAByAGEAdwAgAGQAaQBhAGcAbwBuAGEAbABzACAAYQByAGUAIAByAGUAdAB1AHIAbgBlAGQALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABzAGgAYQBwAGUAIABpAHMAIABrACAA1wAgAGoAIAB3AGgAZQByAGUAIABrACAAPQAgAE0ASQBOACgAcgBvAHcAcwAsACAAYwBvAGwAdQBtAG4AcwApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEIAeQBEAGkAYQBnALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AIAAgACAAIABbAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/AF0ALABcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBEAGkAYQBnALsDKABhAHIAcgBhAHkALAAgACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/ACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIABOAG8AXwBGAHUAbgBjAHQAaQBvAG4ALAAgACAAIAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgAgACAAIAAgAE4AbwBfAFIAbwB3AFMAdABhAGMAawAsACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBhAGcAbwBuAGEAbABzAFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAGgALAAgAHcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABpAG4AZABlAHgAIABnAGUAbgBlAHIAYQB0AG8AcgBzAFwAbgAgACAAIAAgAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGsAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwAsACAAMQAsACAAMAApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABrACkAIAArACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHcALAAgADAALAAgADEAKQApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgAeQAoACkAIAA+ACAAdwAsACAATgBBACgAKQAsACAAeQAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABkAGkAYQBnAG8AbgBhAGwAcwBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGAE4AQQAoAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAcgAoACkALAAgAGMAKAApACkALAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAcwBoAGEAcABlAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBfAFIAbwB3AFMAdABhAGMAawAsACAAcgBlAHMAdQBsAHQALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAcgBlAHMAdQBsAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAGYAdQBuAGMAdABpAG8AbgAgAGkAZgAgAHAAcgBvAHYAaQBkAGUAZABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAF8ARgB1AG4AYwB0AGkAbwBuACwAcwBoAGEAcABlAGQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AXwBSAG8AdwBTAHQAYQBjAGsALABCAFkAQwBPAEwAKABzAGgAYQBwAGUAZAAsACAAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKABzAGgAYQBwAGUAZAAsACAAZgB1AG4AYwB0AGkAbwBuACkAKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABpAGEAZwBNAGEAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEIAeQBEAGkAYQBnALsDLAAgAFYAYQBsAGkAZABhAHQAZQBEAGkAYQBnALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAbgBpAGUAbgBjAGUAIAB3AHIAYQBwAHAAZQByACAAZgBvAHIAIABCAHkARABpAGEAZwC7AyAAdABoAGEAdAAgAGUAeAB0AHIAYQBjAHQAcwAgAGEAbABsACAAZABpAGEAZwBvAG4AYQBsAHMAIABmAHIAbwBtACAAYQAgADIARABcAG4AIAAgACAAIABhAHIAcgBhAHkAIABhAG4AZAAgAHIAZQB0AHUAcgBuAHMAIAB0AGgAZQBtACAAYQBzACAAYQAgADIARAAgAGEAcgByAGEAeQBfADIARAAuACAATwBwAHQAaQBvAG4AYQBsACAAcgBvAHcAESB3AGkAcwBlACAAcwB0AGEAYwBrAGkAbgBnACAAaQBzAFwAbgAgACAAIAAgAHMAdQBwAHAAbwByAHQAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/AF0AIAAgACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAGQAaQBhAGcAbwBuAGEAbABzACAAYQByAGUAIABzAHQAYQBjAGsAZQBkACAAdgBlAHIAdABpAGMAYQBsAGwAeQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABjAGEAbABsAGkAbgBnACAAQgB5AEQAaQBhAGcAuwMoAGEAcgByAGEAeQAsACAALAAgAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/ACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABpAGEAZwBNAGEAcAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/AF0ALABcAG4AIAAgACAAIABCAHkARABpAGEAZwC7AygAYQByAHIAYQB5ACwAIAAsACAAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEQAaQBhAGcASQBuAGQAZQB4ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQgB5AEQAaQBhAGcAuwMsACAAVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAIABzAGkAbgBnAGwAZQAgAGQAaQBhAGcAbwBuAGEAbAAgAG8AcgAgAGEAbgB0AGkAESBkAGkAYQBnAG8AbgBhAGwAIAB2AGUAYwB0AG8AcgAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAUABvAHMAaQB0AGkAdgBlACAAYwBvAGwAXwBpAG4AZABlAHgAIABzAGUAbABlAGMAdABzACAAYQAgAHMAdABhAG4AZABhAHIAZAAgACgAUwBFABEgZABpAHIAZQBjAHQAaQBvAG4AKQAgAGQAaQBhAGcAbwBuAGEAbAAuAFwAbgAgACAAIAAgAE4AZQBnAGEAdABpAHYAZQAgAGMAbwBsAF8AaQBuAGQAZQB4ACAAcwBlAGwAZQBjAHQAcwAgAGEAbgAgAGEAbgB0AGkAESBkAGkAYQBnAG8AbgBhAGwAIAAoAFMAVwARIGQAaQByAGUAYwB0AGkAbwBuACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgBzACAAbgBvAHQAIABhAGMAYwBlAHAAdABlAGQAKQAuAFwAbgAgACAAIAAgAGMAbwBsAF8AaQBuAGQAZQB4ACAAIAAgAC0AIABTAHQAYQByAHQAaQBuAGcAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAuACAATgBlAGcAYQB0AGkAdgBlACAAdgBhAGwAdQBlAHMAIABpAG4AZABpAGMAYQB0AGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBuAHQAaQARIGQAaQBhAGcAbwBuAGEAbAAgAGUAeAB0AHIAYQBjAHQAaQBvAG4ALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGkAcwAgAGEAbAB3AGEAeQBzACAAYQAgADEARAAgAHYAZQBjAHQAbwByACAAbwBmACAAbABlAG4AZwB0AGgAIABrACAAPQAgAGQAaQBhAGcAbwBuAGEAbAAgAGwAZQBuAGcAdABoAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAaQBhAGcASQBuAGQAZQB4ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbwBsAF8AaQBuAGQAZQB4ACwAXABuAFwAbgBWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7AygAYQByAHIAYQB5ACwAIABjAG8AbABfAGkAbgBkAGUAeAAsACAALAAgACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuADoAIAArADEAIAA9ACAAUwBFACwAIAATIDEAIAA9ACAAUwBXAFwAbgAgACAAIAAgAHMALAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABjAG8AbABfAGkAbgBkAGUAeAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBhAGcAbwBuAGEAbAAgAGwAZQBuAGcAdABoAFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIAAgAEkARgAoAHMAIAA+ACAAMAAsAE0ASQBOACgAaAAsACAAdwAgACsAIAAxACAALQAgAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAGgALAAgAEEAQgBTACgAYwBvAGwAXwBpAG4AZABlAHgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAcgB0AGkAbgBnACAAYwBvAGwAdQBtAG4AXABuACAAIAAgACAAcwB0AGEAcgB0ACwAIAAgACAASQBGACgAcwAgADwAIAAwACwAIABBAEIAUwAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALAAgAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAaQBuAGQAZQB4ACAAZwBlAG4AZQByAGEAdABvAHIAcwBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGsAKQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABrACwAIAAsACAAcwB0AGEAcgB0ACwAIABzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAZABpAGEAZwBvAG4AYQBsAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAeAAoACkALAAgAHkAKAApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAESBDAE8AUgBFAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBvAHIAZQAgAFYAYQBsAGkAZABhAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBzACAAaQBuAHAAdQB0AHMAIABmAG8AcgAgAEIAeQBEAGkAYQBnALsDLAAgAEQAaQBhAGcATQBhAHAAuwMsACAAYQBuAGQAIABEAGkAYQBnAEkAbgBkAGUAeAC7Ay4AIABFAG4AcwB1AHIAZQBzACAAdABoAGEAdAAgAHQAaABlAFwAbgAgACAAIAAgAGEAcgByAGEAeQAgAGkAcwAgAGEAIAB2AGEAbABpAGQAIAAyAEQAIABzAHQAcgB1AGMAdAB1AHIAZQAsACAAdABoAGEAdAAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgACgAdwBoAGUAbgAgAHMAdQBwAHAAbABpAGUAZAApACAAYQByAGUAXABuACAAIAAgACAAdwBpAHQAaABpAG4AIABiAG8AdQBuAGQAcwAsACAAYQBuAGQAIAB0AGgAYQB0ACAAYQBuAHkAIABzAHUAcABwAGwAaQBlAGQAIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAIABhACAAdgBhAGwAaQBkACAATABBAE0AQgBEAEEALwBFAFQAQQBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAgACAAIAAgACAAIAAgACAAIAAtACAAUwB0AGEAcgB0AGkAbgBnACAAYwBvAGwAdQBtAG4AIABpAG4AZABlAHgAIAAoAEQAaQBhAGcASQBuAGQAZQB4ALsDIABvAG4AbAB5ACkALgBcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACAAIAAgACAAIAAgACAAIAAgACAALQAgAEUAVABBACAAbwByACAATABBAE0AQgBEAEEAIAAoAEIAeQBEAGkAYQBnALsDIABvAG4AbAB5ACkALgBcAG4AIAAgACAAIABbAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/AF0AIAAgACAALQAgAE8AcgBpAGUAbgB0AGEAdABpAG8AbgAgAGYAbABhAGcAIAAoAEIAeQBEAGkAYQBnALsDIAAvACAARABpAGEAZwBNAGEAcAC7AykALgBcAG4AIAAgACAAIABbAG8AbgBfAHYAYQBsAGkAZABdACAAIAAgACAAIAAgACAAIAAgACAALQAgAEUAeABwAHIAZQBzAHMAaQBvAG4AIAB0AG8AIABlAHYAYQBsAHUAYQB0AGUAIAB3AGgAZQBuACAAaQBuAHAAdQB0AHMAIABhAHIAZQAgAHYAYQBsAGkAZAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAG4AbwBuABEgYQByAHIAYQB5AHMAIABhAHIAZQAgAHIAZQBqAGUAYwB0AGUAZAAuAFwAbgAgACAAIAAgACIgIABjAG8AbABfAGkAbgBkAGUAeAAgAD0AIAAwACAAaQBzACAAaQBuAHYAYQBsAGkAZAAgAGIAeQAgAGQAZQBzAGkAZwBuAC4AXABuACAAIAAgACAAIiAgAEYAdQBuAGMAdABpAG8AbgAgAHYAYQBsAGkAZABhAHQAaQBvAG4AIAB1AHMAZQBzACAAYQAgAHMAYQBmAGUAIABUAFkAUABFABEgYgBhAHMAZQBkACAAaQBuAHYAbwBjAGEAdABpAG8AbgAgAHQAZQBzAHQALgBcAG4AIAAgACAAIAAiICAAUgBvAHUAdABpAG4AZwAgAGwAbwBnAGkAYwAgAGQAZQB0AGUAcgBtAGkAbgBlAHMAIAB3AGgAaQBjAGgAIABvAHAAZQByAGEAdABvAHIAIABpAHMAIABiAGUAaQBuAGcAIAB2AGEAbABpAGQAYQB0AGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGMAbwBsAF8AaQBuAGQAZQB4AF0ALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuACAAIAAgACAAWwByAG8AdwBfAHcAaQBzAGUAXwBzAHQAYQBjAGsAPwBdACwAXABuACAAIAAgACAAWwBvAG4AXwB2AGEAbABpAGQAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAQQByAHIAYQB5ACAAdgBhAGwAaQBkAGEAdABpAG8AbgAgAC0ALQAtAFwAbgAgACAAIAAgAEkAcwBBAHIAcgBhAHkAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABhAHIAcgBhAHkAKQAgAD0AIAA2ADQALABcAG4AIAAgACAAIABOAG8AdABfAEEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAcwBBAHIAcgBhAHkAPwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAQwBvAGwAdQBtAG4AIABpAG4AZABlAHgAIAB2AGEAbABpAGQAYQB0AGkAbwBuACAAKABEAGkAYQBnAEkAbgBkAGUAeAC7AyAAbwBuAGwAeQApACAALQAtAC0AXABuACAAIAAgACAATgBvAF8AQwBvAGwAXwBJAG4AZABlAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABjAG8AbABfAGkAbgBkAGUAeAApACwAXABuACAAIAAgACAAQwBvAGwASQBuAGQAZQB4AF8ASQBuAGMAbAB1AGQAZQBkACwAIAAgACAAIAAgACAATgBPAFQAKABOAG8AXwBDAG8AbABfAEkAbgBkAGUAeAApACwAXABuACAAIAAgACAATgBvAHQAXwBWAGEAbABpAGQAXwBDAG8AbABJAG4AZABlAHgAPwAsACAAIAAgACAATgBPAFQAKABBAE4ARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACAAPAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAEIAUwAoAGMAbwBsAF8AaQBuAGQAZQB4ACkAIAA8AD0AIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAARgB1AG4AYwB0AGkAbwBuACAAdgBhAGwAaQBkAGEAdABpAG8AbgAgACgAQgB5AEQAaQBhAGcAuwMgAG8AbgBsAHkAKQAgAC0ALQAtAFwAbgAgACAAIAAgAE4AbwBfAEYAdQBuAGMAdABpAG8AbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AIAAgACAAIABGAHUAbgBjAHQAaQBvAG4AXwBJAG4AYwBsAHUAZABlAGQALAAgACAAIAAgACAAIABOAE8AVAAoAE4AbwBfAEYAdQBuAGMAdABpAG8AbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYQBmAGUAIABmAHUAbgBjAHQAaQBvAG4AIAB2AGEAbABpAGQAYQB0AGkAbwBuADoAIABlAG4AcwB1AHIAZQAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGMAYQBsAGwAYQBiAGwAZQBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAF8ARgB1AG4AYwB0AGkAbwBuAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAEYAdQBuAGMAdABpAG8AbgBfAEkAbgBjAGwAdQBkAGUAZAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAEUAUgBSAE8AUgAoAEIAWQBSAE8AVwAoAHsAMQAsADEAfQAsACAAZgB1AG4AYwB0AGkAbwBuACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAZgBsAGEAZwAgACgARABpAGEAZwBNAGEAcAC7AyAALwAgAEIAeQBEAGkAYQBnALsDKQAgAC0ALQAtAFwAbgAgACAAIAAgAFIAbwB3AFcAaQBzAGUAUwB0AGEAYwBrAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBfAHcAaQBzAGUAXwBzAHQAYQBjAGsAPwApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABEAGUAdABlAHIAbQBpAG4AZQAgAHcAaABpAGMAaAAgAG8AcABlAHIAYQB0AG8AcgAgAGkAcwAgAGIAZQBpAG4AZwAgAHYAYQBsAGkAZABhAHQAZQBkACAALQAtAC0AXABuACAAIAAgACAASQBzAEQAaQBhAGcASQBuAGQAZQB4AD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAGwASQBuAGQAZQB4AF8ASQBuAGMAbAB1AGQAZQBkACwAXABuACAAIAAgACAASQBzAEIAeQBEAGkAYQBnAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAG8AXwBDAG8AbABfAEkAbgBkAGUAeAAsACAARgB1AG4AYwB0AGkAbwBuAF8ASQBuAGMAbAB1AGQAZQBkACkALABcAG4AIAAgACAAIABJAHMARABpAGEAZwBNAGEAcAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4AbwBfAEMAbwBsAF8ASQBuAGQAZQB4ACwAIABOAG8AXwBGAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAcwAgAC0ALQAtAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBhAGcASQBuAGQAZQB4ALsDXABuACAAIAAgACAAZwBhAHQAZQBfAEQAaQBhAGcASQBuAGQAZQB4ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAHQAXwBBAHIAcgBhAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMATgBPAFQALQBBAFIAUgBBAFkAIQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwB0AF8AVgBhAGwAaQBkAF8AQwBvAGwASQBuAGQAZQB4AD8ALAAgAFwAIgAjAEMATwBMAFUATQBOAC0ASQBOAEQARQBYACEAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AbgBfAHYAYQBsAGkAZAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgB5AEQAaQBhAGcAuwNcAG4AIAAgACAAIABnAGEAdABlAF8AQgB5AEQAaQBhAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AdABfAEEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8AVAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABfAEYAdQBuAGMAdABpAG8AbgA/ACwAIABcACIAIwBGAFUATgBDAFQASQBPAE4AIQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBuAF8AdgBhAGwAaQBkACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAYQBnAE0AYQBwALsDXABuACAAIAAgACAAZwBhAHQAZQBfAEQAaQBhAGcATQBhAHAALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAHQAXwBBAHIAcgBhAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMATgBPAFQALQBBAFIAUgBBAFkAIQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AbgBfAHYAYQBsAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAUgBvAHUAdABlACAAdABvACAAYwBvAHIAcgBlAGMAdAAgAGcAYQB0AGUAIAAtAC0ALQBcAG4AIAAgACAAIABkAGUAYwBpAGQAZQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARABpAGEAZwBJAG4AZABlAHgAPwAsACAAZwBhAHQAZQBfAEQAaQBhAGcASQBuAGQAZQB4ACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEQAaQBhAGcATQBhAHAAPwAsACAAZwBhAHQAZQBfAEQAaQBhAGcATQBhAHAALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBCAHkARABpAGEAZwA/ACwAIABnAGEAdABlAF8AQgB5AEQAaQBhAGcALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMAVQBOAFIATwBVAFQARQBEACEAXAAiACkAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBjAGkAZABlAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUABhAGkAcgB3AGkAcwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAARQBjAGgAbwC7AywAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwByAGUAYQB0AGUAcwAgAHYAZQByAHQAaQBjAGEAbAAgAHAAYQBpAHIAcwAgAGYAcgBvAG0AIAAxAEQAIABhAG4AZAAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMALgAgAEkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAXABuACAAIAAgACAAVABPAEMATwBMACAAdABvACAAbgBvAHIAbQBhAGwAaQB6AGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALgAgADIARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHQAcgBpAGMAdABsAHkAIABwAHIAbwBoAGkAYgBpAHQAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAdgBlAGMAdABvAHIAXwAxACAAIAAgACAALQAgADEARAAgAHYAZQBjAHQAbwByACAAbwByACAAcwBjAGEAbABhAHIALgBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgBfADIAIAAgACAAIAAtACAAMQBEACAAdgBlAGMAdABvAHIAIABvAHIAIABzAGMAYQBsAGEAcgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBQAGEAaQByAHcAaQBzAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMQAsAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAAdgAsACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAXwAxACkALABcAG4AIAAgACAAIAB2AIIgLAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKAB2AGUAYwB0AG8AcgBfADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAGwAZQBtAGUAbgB0ACAAYwBvAHUAbgB0AHMAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKAB2ACkALABcAG4AIAAgACAAIABrAIIgLAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHYAgiApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAMgBEAEkAbgBwAHUAdAA/ACwAIABPAFIAKABBAE4ARAAoAFIATwBXAFMAKAB2AGUAYwB0AG8AcgBfADEAKQA+ADEALAAgAEMATwBMAFUATQBOAFMAKAB2AGUAYwB0AG8AcgBfADEAKQA+ADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAUgBPAFcAUwAoAHYAZQBjAHQAbwByAF8AMgApAD4AMQAsACAAQwBPAEwAVQBNAE4AUwAoAHYAZQBjAHQAbwByAF8AMgApAD4AMQApACkALABcAG4AXABuACAAIAAgACAASQBzADIAQgBpAGcAPwAsACAAIAAgACAAawAgACoAIABrAIIgIAA+ACAAMQAwADAAMAAwADAAMAAsAFwAbgBcAG4ASQBGACgASQBzADIARABJAG4AcAB1AHQAPwAsACAAIAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwAyAEIAaQBnAD8ALAAgACAAIAAgACAAIwBOAFUATQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEMAYQByAHQAZQBzAGkAYQBuACAAZQB4AHAAYQBuAHMAaQBvAG4AXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEUAYwBoAG8AuwMoAHYALAAgAGsAgiApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDKAB2AIIgLAAgAGsAKQAsAFwAbgAgACAAIAAgAHAAYQBpAHIAcwAsACAAIABIAFMAVABBAEMASwAoAHgALAAgAHkAKQAsAFwAbgBcAG4AIAAgACAAIABwAGEAaQByAHMAXABuACAAIAAgACAAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAwADYAYQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFQAcgBpAHAAbABlAHcAaQBzAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABvAGYAIAAzACAAcwBlAHQAcwAuACAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIABhAG4AZABcAG4AIAAgACAAIAB0AGgAZQAgAHIAZQBzAHUAbAB0AGkAbgBnACAAdAByAGkAcABsAGUAcwAgAHAAcgBlAHMAZQByAHYAZQAgAHQAaABlACAAbwByAGQAZQByACAAbwBmACAAdABoAGUAIABzAHUAcABwAGwAaQBlAGQAIABzAGUAdABzAC4AXABuAFwAbgAgACAAIAAgAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMgAGUAeAB0AGUAbgBkAHMAIABQAGEAaQByAHcAaQBzAGUAuwMgAHQAbwAgAGEAIAAzABEgYQB4AGkAcwAgAGYAYQBiAHIAaQBjADoAXABuACAAIAAgACAAIAAgACAAIAAiICAAcwBlAHQAXwAxACAA1wAgAHMAZQB0AF8AMgAgANcAIABzAGUAdABfADMAXABuACAAIAAgACAAVABoAGUAIABvAHUAdABwAHUAdAAgAGkAcwAgAGEAIABzAHAAaQBsAGwAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAcgBvAHcAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABvAHIAZABlAHIAZQBkACAAdAByAGkAcABsAGUALgBcAG4AXABuAEYAbwByAG0AdQBsAGEAOgAgAD0AVAByAGkAcABsAGUAdwBpAHMAZQC7AygAewBcACIAZABvAGcAXAAiADsAXAAiAGMAYQB0AFwAIgA7AFwAIgBiAGkAcgBkAFwAIgB9ACwAewBcACIAYQBcACIAOwBcACIAYgBcACIAOwBcACIAYwBcACIAfQAsAHsAMQA7ADIAfQApAFwAbgBcAG4AUgBlAHMAdQBsAHQAOgBcAG4AIAAgACAAIAB7AFwAIgBkAG8AZwBcACIALABcACIAYQBcACIALAAxADsAXABuACAAIAAgACAAIABcACIAZABvAGcAXAAiACwAXAAiAGEAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGQAbwBnAFwAIgAsAFwAIgBiAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBkAG8AZwBcACIALABcACIAYgBcACIALAAyADsAXABuACAAIAAgACAAIABcACIAZABvAGcAXAAiACwAXAAiAGMAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGQAbwBnAFwAIgAsAFwAIgBjAFwAIgAsADIAOwBcAG4AIAAgACAAIAAgAFwAIgBjAGEAdABcACIALABcACIAYQBcACIALAAxADsAXABuACAAIAAgACAAIABcACIAYwBhAHQAXAAiACwAXAAiAGEAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGMAYQB0AFwAIgAsAFwAIgBiAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBjAGEAdABcACIALABcACIAYgBcACIALAAyADsAXABuACAAIAAgACAAIABcACIAYwBhAHQAXAAiACwAXAAiAGMAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGMAYQB0AFwAIgAsAFwAIgBjAFwAIgAsADIAOwBcAG4AIAAgACAAIAAgAFwAIgBiAGkAcgBkAFwAIgAsAFwAIgBhAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBiAGkAcgBkAFwAIgAsAFwAIgBhAFwAIgAsADIAOwBcAG4AIAAgACAAIAAgAFwAIgBiAGkAcgBkAFwAIgAsAFwAIgBiAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBiAGkAcgBkAFwAIgAsAFwAIgBiAFwAIgAsADIAOwBcAG4AIAAgACAAIAAgAFwAIgBiAGkAcgBkAFwAIgAsAFwAIgBjAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBiAGkAcgBkAFwAIgAsAFwAIgBjAFwAIgAsADIAfQBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABzAGUAdABfADEAIAAgACAAIABTAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgACgAMQBEACAAbwByACAAMgBEACkAIABhAHIAZQAgAGEAYwBjAGUAcAB0AGUAZAAuACAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQALgBcAG4AIAAgACAAIABzAGUAdABfADIAXABuACAAIAAgACAAcwBlAHQAXwAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBUAHIAaQBwAGwAZQB3AGkAcwBlALsDPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABzAGUAdABfADEALABcAG4AIAAgACAAIABzAGUAdABfADIALABcAG4AIAAgACAAIABzAGUAdABfADMALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAYQBsAGwAIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIABzAGUAdABfADEALAAgACAAIABUAE8AQwBPAEwAKABzAGUAdABfADEAKQAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMgAsACAAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMgApACwAXABuACAAIAAgACAAcwBlAHQAXwAzACwAIAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAzACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAHQAIABpAHQAZQBtACAAYwBvAHUAbgB0AHMAXABuACAAIAAgACAAawCBICwAIAAgACAAIAAgACAAUgBPAFcAUwAoAHMAZQB0AF8AMQApACwAXABuACAAIAAgACAAawCCICwAIAAgACAAIAAgACAAUgBPAFcAUwAoAHMAZQB0AF8AMgApACwAXABuACAAIAAgACAAawCDICwAIAAgACAAIAAgACAAUgBPAFcAUwAoAHMAZQB0AF8AMwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQB0AGUAcgBtAGkAbgBlACAAaQBmACAAcwBlAHQAXwAyACAAaQBzACAAcwBjAGEAbABhAHIAXABuACAAIAAgACAAcwB3AGEAcAA/ACwAIAAgACAAawCCICAAPQAgADEALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABDAHIAZQBhAHQAZQAgAHAAYQBpAHIAcwAgAGYAcgBvAG0AIABmAGkAcgBzAHQAIAB0AHcAbwAgAHMAZQB0AHMAXABuACAAIAAgACAAcABhAGkAcgBzACwAIAAgACAASQBGACgAcwB3AGEAcAA/ACwAIABQAGEAaQByAHcAaQBzAGUAuwMoAHMAZQB0AF8AMgAsAHMAZQB0AF8AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwMoAHMAZQB0AF8AMQAsAHMAZQB0AF8AMgApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABzAGUAdABzACAAZQB4AHAAYQBuAGQAZQBkAFwAbgAgACAAIAAgAGEALAAgACAAIAAgACAAIAAgAEkARgAoAHMAdwBhAHAAPwAsAFQAQQBLAEUAKABwAGEAaQByAHMALAAsAC0AMQApACwAVABBAEsARQAoAHAAYQBpAHIAcwAsACwAMQApACkALABcAG4AIAAgACAAIABiACwAIAAgACAAIAAgACAAIABJAEYAKABzAHcAYQBwAD8ALABUAEEASwBFACgAcABhAGkAcgBzACwALAAxACkALABUAEEASwBFACgAcABhAGkAcgBzACwALAAtADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBpAHIAcwAgAGYAcgBvAG0AIABzAGUAdABfADEAIABlAHgAcABhAG4AZABlAGQAIAArACAAcwBlAHQAXwAzAFwAbgAgACAAIAAgAHQAaAByAGkAYwBlACwAIAAgAEkARgAoAGsAgyAgADwAPgAgADEALAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAYQAsAHMAZQB0AF8AMwApACwAUABhAGkAcgB3AGkAcwBlALsDKABzAGUAdABfADMALABhACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGEAaQByAHMAIABmAHIAbwBtACAAcwBlAHQAXwAyACAAZQB4AHAAYQBuAGQAZQBkACAAKwAgAHMAZQB0AF8AMwBcAG4AIAAgACAAIAB0AGgAcgBpAGMAZQBfACwAIABJAEYAKABrAIMgIAA8AD4AIAAxACwAIABQAGEAaQByAHcAaQBzAGUAuwMoAGIALABzAGUAdABfADMAKQAsAFAAYQBpAHIAdwBpAHMAZQC7AygAcwBlAHQAXwAzACwAYgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAYwBvAGwAcwAsACAAIAAgACAASQBGACgAawCDICAAPQAgADEALAAxACwALQAxACkALABcAG4AIAAgACAAIABhAF8ALAAgACAAIAAgACAAIABEAFIATwBQACgAdABoAHIAaQBjAGUALAAsAGMAbwBsAHMAKQAsAFwAbgAgACAAIAAgAGIAXwAsACAAIAAgACAAIAAgAEQAUgBPAFAAKAB0AGgAcgBpAGMAZQBfACwALABjAG8AbABzACkALABcAG4AIAAgACAAIABjAF8ALAAgACAAIAAgACAAIABUAEEASwBFACgAdABoAHIAaQBjAGUALAAsAGMAbwBsAHMAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAHQAbwByAGUAIABvAHIAZABlAHIAIAB0AG8AIABtAGEAdABjAGgAIABpAG4AcAB1AHQAIABvAHIAZABlAHIAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAASABTAFQAQQBDAEsAKABhAF8ALABiAF8ALABjAF8AKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAANgBiAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUQB1AGEAZAB3AGkAcwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AywAIABSAGUAcwBpAHoAZQC7AywAIABUAHIAaQBwAGwAZQB3AGkAcwBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAHQAaABlACAAQwBhAHIAdABlAHMAaQBhAG4AIABwAHIAbwBkAHUAYwB0ACAAbwBmACAANAAgAHMAZQB0AHMALgAgAEEAbABsACAAaQBuAHAAdQB0AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAYQBuAGQAXABuACAAIAAgACAAdABoAGUAIAByAGUAcwB1AGwAdABpAG4AZwAgAHEAdQBhAGQAcgB1AHAAbABlAHMAIABwAHIAZQBzAGUAcgB2AGUAIAB0AGgAZQAgAG8AcgBkAGUAcgAgAG8AZgAgAHQAaABlACAAcwB1AHAAcABsAGkAZQBkACAAcwBlAHQAcwAuAFwAbgBcAG4AIAAgACAAIABRAHUAYQBkAHcAaQBzAGUAuwMgAGUAeAB0AGUAbgBkAHMAIABUAHIAaQBwAGwAZQB3AGkAcwBlALsDIAB0AG8AIABhACAANAARIGEAeABpAHMAIABmAGEAYgByAGkAYwA6AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAHMAZQB0AF8AMQAgANcAIABzAGUAdABfADIAIADXACAAcwBlAHQAXwAzACAA1wAgAHMAZQB0AF8ANABcAG4AIAAgACAAIABUAGgAZQAgAG8AdQB0AHAAdQB0ACAAaQBzACAAYQAgAHMAcABpAGwAbAAgAHIAYQBuAGcAZQAgAHcAaABlAHIAZQAgAGUAYQBjAGgAIAByAG8AdwAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQAgAG8AcgBkAGUAcgBlAGQAIABxAHUAYQBkAHIAdQBwAGwAZQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHMAZQB0AF8AMQAgACAAIAAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAKAAxAEQAIABvAHIAIAAyAEQAKQAgAGEAcgBlACAAYQBjAGMAZQBwAHQAZQBkAC4AIABBAGwAbAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAuAFwAbgAgACAAIAAgAHMAZQB0AF8AMgBcAG4AIAAgACAAIABzAGUAdABfADMAXABuACAAIAAgACAAcwBlAHQAXwA0AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBRAHUAYQBkAHcAaQBzAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHMAZQB0AF8AMQAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMgAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMwAsAFwAbgAgACAAIAAgAHMAZQB0AF8ANAAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABhAGwAbAAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAHMAZQB0AF8AMQAsACAAIABUAE8AQwBPAEwAKABzAGUAdABfADEAKQAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMgAsACAAIABUAE8AQwBPAEwAKABzAGUAdABfADIAKQAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMwAsACAAIABUAE8AQwBPAEwAKABzAGUAdABfADMAKQAsAFwAbgAgACAAIAAgAHMAZQB0AF8ANAAsACAAIABUAE8AQwBPAEwAKABzAGUAdABfADQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AcwBpAG8AbgAgAGMAbwB1AG4AdABcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAUgBPAFcAUwAoAHMAZQB0AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcwBlAHQAIAA0ACAAaQBmACAAcwBjAGEAbABhAHIAIAB0AG8AIABhAHYAbwBpAGQAIABUAE8AQwBPAEwAIABoAGEAbgBkAG8AZgBmACAAdABvACAAUgBlAHMAaQB6AGUAuwNcAG4AIAAgACAAIABkACwAIAAgACAAIAAgACAASQBGACgAawAgADwAPgAgADEALABzAGUAdABfADQALABJAE4ARABFAFgAKABzAGUAdABfADQALAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAHIAaQBwAGwAZQBzAFwAbgAgACAAIAAgAHQAaAByAGkAYwBlACwAIABUAHIAaQBwAGwAZQB3AGkAcwBlALsDKABzAGUAdABfADEALABzAGUAdABfADIALABzAGUAdABfADMAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBkACAAdAByAGkAcABsAGUAIAByAG8AdwBzACAAYgB5ACAAdABvAHQAYQBsACAAaQB0AGUAbQBzACAAaQBuACAAcwBlAHQAIAA0AFwAbgAgACAAIAAgAHQAaAByAGkAYwBlAF8ALABSAGUAcABlAGEAdABSAG8AdwBzALsDKAB0AGgAcgBpAGMAZQAsAGsAKQAsAFwAbgAgACAAIAAgAGsAgiAsACAAIAAgACAAIABSAE8AVwBTACgAdABoAHIAaQBjAGUAXwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBkACAAcwBlAHQAIAA0ACAAdABvACAAbQBhAHQAYwBoACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AHIAaQBwAGwAZQBcAG4AIAAgACAAIABmAG8AdQByACwAIAAgACAAUgBlAHMAaQB6AGUAuwMoAGQALABrAIIgIAAvACAAawApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAGMAawAgAGEAbgBkACAAZABpAHMAcABsAGEAeQBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAASABTAFQAQQBDAEsAKAB0AGgAcgBpAGMAZQBfACwAZgBvAHUAcgApACwAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgBcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEcAcgBvAHUAcABiAHkAQgBpAG4AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABBAGcAZwByAGUAZwBhAHQAZQBzACAAbwBuAGUAIABvAHIAIABtAG8AcgBlACAAdgBhAGwAdQBlACAAYQByAHIAYQB5AHMAIABpAG4AdABvACAAZgBpAHgAZQBkABEgdwBpAGQAdABoACAAYgBpAG4AcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAYQBcAG4AIAAgACAAIABuAHUAbQBlAHIAaQBjACAAZgBpAGUAbABkAC4AIABTAHUAcABwAG8AcgB0AHMAIABvAHAAdABpAG8AbgBhAGwAIABoAGUAYQBkAGUAcgBzACAAYQBuAGQAIABjAGgAYQByAHQAESByAGUAYQBkAHkAIABvAHUAdABwAHUAdAAuACAAQgBpAG4AcwAgAGEAcgBlAFwAbgAgACAAIAAgAGQAZQBmAGkAbgBlAGQAIABiAHkAIABhACAAbgB1AG0AZQByAGkAYwAgAGEAcgByAGEAeQAgAGEAbgBkACAAYQAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAIABiAGkAbgBfAHcAaQBkAHQAaAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAE4AdQBtAGUAcgBpAGMAIAAxAEQAIABhAHIAcgBhAHkAIAB1AHMAZQBkACAAdABvACAAZABlAGYAaQBuAGUAIABiAGkAbgAgAGIAbwB1AG4AZABhAHIAaQBlAHMALgBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAgACAAIAAgACAAIAAgACAAIAAgAC0AIABBAHIAcgBhAHkAKABzACkAIAB0AG8AIABiAGUAIABhAGcAZwByAGUAZwBhAHQAZQBkACAAKAAxAEQAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAGIAaQBuAF8AdwBpAGQAdABoACAAIAAgACAAIAAgACAALQAgAFAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAIABzAHAAZQBjAGkAZgB5AGkAbgBnACAAYgBpAG4AIAB3AGkAZAB0AGgAIAAoAGUiIAAxACkALgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AIAAgACAAIAAgACAAIAAgAC0AIABFAFQAQQARIGMAbwBtAHAAYQB0AGkAYgBsAGUAIABmAHUAbgBjAHQAaQBvAG4AIABvAHIAIABzAGkAbgBnAGwAZQARIHAAYQByAGEAbQBlAHQAZQByACAATABBAE0AQgBEAEEALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAXQAgACAALQAgAFQAUgBVAEUAIABpAGYAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAcwAgAGkAbgBjAGwAdQBkAGUAIABoAGUAYQBkAGUAcgBzACAAdABvACAAYgBlACAAYwBhAHIAcgBpAGUAZAAgAGYAbwByAHcAYQByAGQALgBcAG4AIAAgACAAIABbAGMAaABhAHIAdABfAHAAcgBlAHAAXQAgACAAIAAgAC0AIABUAFIAVQBFACAAdABvACAAcgBlAHQAdQByAG4AIABhACAAYwBvAG4AYwBpAHMAZQAgAGMAaABhAHIAdAARIHIAZQBhAGQAeQAgAGwAYQB5AG8AdQB0AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAYgBpAG4AXwB3AGkAZAB0AGgAIAA9ACAAMQAgAJIhIABiAGUAaABhAHYAZQBzACAAbABpAGsAZQAgAEcAUgBPAFUAUABCAFkAIAAoAG4AbwAgAGIAaQBuAG4AaQBuAGcAKQAuAFwAbgAgACAAIAAgACIgIABiAGkAbgBfAHcAaQBkAHQAaAAgAGUiIAAoAG0AYQB4ACAAEiIgAG0AaQBuACkAIACSISAAYwBvAGwAbABhAHAAcwBlAHMAIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABiAGkAbgAuAFwAbgAgACAAIAAgACIgIABDAGgAYQByAHQAIABtAG8AZABlACAAcgBlAHQAdQByAG4AcwAgAHsAXAAiAEIAaQBuAFwAIgAsAFwAIgBBAGcAZwByAGUAZwBhAHQAZQBcACIAfQAgAGYAbwByACAAZQBhAHMAeQAgAHAAbABvAHQAdABpAG4AZwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBHAHIAbwB1AHAAYgB5AEIAaQBuALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAYgBpAG4AXwB3AGkAZAB0AGgALABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABbAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAF0ALABcAG4AIAAgACAAIABbAGMAaABhAHIAdABfAHAAcgBlAHAAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABpAF8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAYQBsAHUAZQBzACkALABcAG4AIAAgACAAIABqAF8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAHYAYQBsAHUAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAASABlAGEAZABlAHIAIABmAGwAYQBnAFwAbgAgACAAIAAgAEgAZQBhAGQAZQByAHMAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABjAG8AbgBkAGkAdABpAG8AbgBzAFwAbgAgACAAIAAgAEkAcwAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGkAIAA+ACAAMQAsACAAagAgAD4AIAAxACkALABcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAAgACAAaQAgADwAPgAgAGkAXwAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAQgBpAG4APwAsACAAIAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAGIAaQBuAF8AdwBpAGQAdABoACkALAAgAGIAaQBuAF8AdwBpAGQAdABoACAAPAAgADEAKQAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARgBuAD8ALAAgACAAIAAgACAAIAAgACAAIABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA8AD4AIAAxADIAOAAsAFwAbgAgACAAIAAgAE4AbwBuAE4AdQBtAGUAcgBpAGMAPwAsACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEEATgBEACgASQBTAE4AVQBNAEIARQBSACgASQBGACgASABlAGEAZABlAHIAcwA/ACwAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAxACkALAAgAGEAcgByAGEAeQApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwAxAEQALQBBAFIAUgBBAFkAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgAFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBuAE4AdQBtAGUAcgBpAGMAPwAsACAAXAAiACMATgBVAE0AIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABCAGkAbgA/ACwAIABcACIAIwBCAEkATgAtAFcASQBEAFQASAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQARgBuAD8ALAAgAFwAIgAjAEkATgBWAEEATABJAEQALQBGAFUATgBDAFQASQBPAE4AIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBsAGEAZwBzAFwAbgAgACAAIAAgAE4AbwBDAGgAYQByAHQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGMAaABhAHIAdABfAHAAcgBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAcgBpAHAAIABoAGUAYQBkAGUAcgBzACAAaQBmACAAcAByAGUAcwBlAG4AdABcAG4AIAAgACAAIABhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASABlAGEAZABlAHIAcwA/ACwAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAxACkALAAgAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEgAZQBhAGQAZQByAHMAPwAsACAARABSAE8AUAAoAHYAYQBsAHUAZQBzACwAIAAxACkALAAgAHYAYQBsAHUAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAASABlAGEAZABlAHIAIABjAG8AbgBzAHQAcgB1AGMAdABpAG8AbgBcAG4AIAAgACAAIAByAG8AdwBfAGgAZQBhAGQAZQByACwAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABcACIAQgBpAG4AIABTAHQAYQByAHQAIABcACIAIAAmACAASQBGACgASABlAGEAZABlAHIAcwA/ACwAIABUAEEASwBFACgAYQByAHIAYQB5ACwAIAAxACkALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABWAGEAbAB1AGUAXAAiACwAXAAiAEIAaQBuACAARQBuAGQAXAAiACkALABcAG4AIAAgACAAIAB2AGEAbABfAGgAZQBhAGQAZQByACwAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKABJAEYAKABIAGUAYQBkAGUAcgBzAD8ALAAgAFQAQQBLAEUAKAB2AGEAbAB1AGUAcwAsACAAMQApACwAIABcACIAVABvAHQAYQBsAFwAIgApACwALABqAF8ALABcACIAXAAiACkALABcAG4AIAAgACAAIABoAGUAYQBkAGUAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKAByAG8AdwBfAGgAZQBhAGQAZQByACwAIAB2AGEAbABfAGgAZQBhAGQAZQByACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBpAG4AIABiAG8AdQBuAGQAYQByAGkAZQBzAFwAbgAgACAAIAAgAG0AaQBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAGEAcgByACkALABcAG4AIAAgACAAIABzAHQAYQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBMAE8ATwBSACgAbQBpAG4ALAAgAGIAaQBuAF8AdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAAbQBhAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAYQByAHIAKQAsAFwAbgAgACAAIAAgAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAbQBhAHgALAAgAGIAaQBuAF8AdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAZQBuAGQAIAAtACAAcwB0AGEAcgB0ACkAIAAvACAAYgBpAG4AXwB3AGkAZAB0AGgALABcAG4AXABuACAAIAAgACAAYgBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAGsAIAArACAAMQAsACAALAAgAHMAdABhAHIAdAAsACAAYgBpAG4AXwB3AGkAZAB0AGgAKQAsAFwAbgAgACAAIAAgAGIAaQBuAF8AcwB0AGEAcgB0ACwAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYgBpAG4ALAAgAC0AMQApACwAXABuACAAIAAgACAAYgBpAG4AXwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABiAGkAbgAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQBuACAAYQBzAHMAaQBnAG4AbQBlAG4AdABcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABhAHIAcgAsACAAYgBpAG4AXwBzAHQAYQByAHQALAAgAC0AMQApACwAXABuACAAIAAgACAAcgBvAHcAXwBzAHQAYQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGIAaQBuAF8AcwB0AGEAcgB0ACwAIABpAGQAeAApACwAXABuACAAIAAgACAAcgBvAHcAXwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGIAaQBuAF8AZQBuAGQALAAgAGkAZAB4ACkALABcAG4AIAAgACAAIAByAG8AdwBfAGYAaQBlAGwAZABzACwAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKAByAG8AdwBfAHMAdABhAHIAdAAsACAAcgBvAHcAXwBlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAZwBnAHIAZQBnAGEAdABpAG8AbgBcAG4AIAAgACAAIABhAGcAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwBSAE8AVQBQAEIAWQAoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgAHYAYQBsACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgAEgAZQBhAGQAZQByAHMAPwAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAaABhAHIAdAAgAHAAcgBlAHAAXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABhAGcAZwAsACAAMQApACAAJgAgAFwAIgAgAC0AIAA8AFwAIgAgACYAIABDAEgATwBPAFMARQBDAE8ATABTACgAYQBnAGcALAAgADIAKQAsAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYQBnAGcALAAgACwAIAAyACkALABcAG4AIAAgACAAIABjAGgAYQByAHQAXwBsAGEAYgBlAGwAcwAsACAAIAAgACAAIAAgACAAewBcACIAQgBpAG4AXAAiACwAIABcACIAQQBnAGcAcgBlAGcAYQB0AGUAXAAiAH0ALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIABtAG8AZABlAHMAXABuACAAIAAgACAAZABhAHQAYQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAaABlAGEAZABlAHIALAAgAGEAZwBnACkALABcAG4AIAAgACAAIABjAGgAYQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABjAGgAYQByAHQAXwBsAGEAYgBlAGwAcwAsACAASABTAFQAQQBDAEsAKABhACwAIABiACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAEMAaABhAHIAdAA/ACwAIABkAGEAdABhACwAIABjAGgAYQByAHQAKQAsAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAeQBcAG4AKQApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAAOABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEcAcgBvAHUAcABiAHkARABhAHQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFYAYQBsAGkAZABhAHQAZQBHAEQAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAZwBnAHIAZQBnAGEAdABlAHMAIAB2AGEAbAB1AGUAcwAgAGIAeQAgAHIAbwB3ACAAZgBpAGUAbABkAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAZABhAHQAZQBzACwAIAB1AHMAaQBuAGcAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAXABuACAAIAAgACAAZABhAHQAZQAvAHQAaQBtAGUAIABpAG4AdABlAHIAdgBhAGwAIAAoAG0AaQBuAHUAdABlACwAIABoAG8AdQByACwAIABkAGEAeQAsACAAdwBlAGUAawAsACAAZgBvAHIAdABuAGkAZwBoAHQALAAgAG0AbwBuAHQAaAAsACAAcQB1AGEAcgB0AGUAcgAsAFwAbgAgACAAIAAgAHkAZQBhAHIAKQAuACAAUwB1AHAAcABvAHIAdABzACAAbwBwAHQAaQBvAG4AYQBsACAAaABlAGEAZABlAHIAcwAsACAAYwB1AHMAdABvAG0AIABmAG8AcgBtAGEAdAB0AGkAbgBnACwAIABhAG4AZAAgAHIAbwB3ACAAZgBpAGwAdABlAHIAaQBuAGcALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAByAG8AdwBfAGYAaQBlAGwAZABzACAAIAAgACAAIAAgAC0AIABBAHIAcgBhAHkAIAAoADEARAAgAG8AcgAgADIARAApACAAdwBpAHQAaAAgAGQAYQB0AGUAcwAgAGkAbgAgAHQAaABlACAAbABlAGYAdABtAG8AcwB0ACAAYwBvAGwAdQBtAG4ALgBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAgACAAIAAgACAAIAAgACAAIAAgAC0AIABBAHIAcgBhAHkAIAAoADEARAAgAG8AcgAgADIARAApACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAHYAYQBsAHUAZQBzACAAZgBvAHIAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4ALgBcAG4AIAAgACAAIABpAG4AdABlAHIAdgBhAGwAIAAgACAAIAAgACAAIAAgAC0AIABEAGEAdABlAC8AdABpAG0AZQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGkAbgB0AGUAcgB2AGEAbAAgACgAbgB1AG0AYgBlAHIAIABvAHIAIAB0AGUAeAB0ACkALgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AIAAgACAAIAAgACAAIAAgAC0AIABFAFQAQQARIGMAbwBtAHAAYQB0AGkAYgBsAGUAIABmAHUAbgBjAHQAaQBvAG4AIABvAHIAIABzAGkAbgBnAGwAZQARIHAAYQByAGEAbQBlAHQAZQByACAATABBAE0AQgBEAEEALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAZgBvAHIAbQBhAHQAXQAgACAAIAAgACAAIAAgACAALQAgAEMAdQBzAHQAbwBtACAAZABhAHQAZQAvAHQAaQBtAGUAIABmAG8AcgBtAGEAdAAgAHMAdAByAGkAbgBnAC4AXABuACAAIAAgACAAWwBmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBzAF0AIAAtACAAVABSAFUARQAgAGkAZgAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQBzACAAaQBuAGMAbAB1AGQAZQAgAGgAZQBhAGQAZQByAHMALgBcAG4AIAAgACAAIABbAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5AF0AIAAgAC0AIABCAG8AbwBsAGUAYQBuACAAYQByAHIAYQB5ACAAdABvACAAZgBpAGwAdABlAHIAIAByAG8AdwBzACAAYgBlAGYAbwByAGUAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4ALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARwByAG8AdQBwAGIAeQBEAGEAdABlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMALABcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAsAFwAbgAgACAAIAAgAGkAbgB0AGUAcgB2AGEAbAAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAFsAZgBvAHIAbQBhAHQAXQAsAFwAbgAgACAAIAAgAFsAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAcwBdACwAXABuACAAIAAgACAAWwBmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQBdACwAXABuAFwAbgBWAGEAbABpAGQAYQB0AGUARwBEALsDKAByAG8AdwBfAGYAaQBlAGwAZABzACwAIAB2AGEAbAB1AGUAcwAsACAAaQBuAHQAZQByAHYAYQBsACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAHMALAAgAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEkAbgB0AGUAcgB2AGEAbAAgAG4AbwByAG0AYQBsAGkAegBhAHQAaQBvAG4AXABuACAAIAAgACAATgB1AG0ASQBuAHQAZQByAHYAYQBsAD8ALAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAFQARQBYAFQAKABpAG4AdABlAHIAdgBhAGwAKQApACwAXABuAFwAbgAgACAAIAAgAGMAbwBuAHMAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgBtAGkAbgB1AHQAZQBcACIAOwBcACIAaABvAHUAcgBcACIAOwBcACIAZABhAHkAXAAiADsAXAAiAHcAZQBlAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAbwByAHQAbgBpAGcAaAB0AFwAIgA7AFwAIgBtAG8AbgB0AGgAXAAiADsAXAAiAHEAdQBhAHIAdABlAHIAXAAiADsAXAAiAHkAZQBhAHIAXAAiAH0ALABcAG4AXABuACAAIAAgACAAaQBuAHQAZQByAHYAYQBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AdQBtAEkAbgB0AGUAcgB2AGEAbAA/ACwAaQBuAHQAZQByAHYAYQBsACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABMAE8AVwBFAFIAKABpAG4AdABlAHIAdgBhAGwAKQAgACYAIABcACIAKgBcACIALAAgAGMAbwBuAHMAdAAsACAAMgApACkALABcAG4AXABuACAAIAAgACAASQBuAGMAbAB1AGQAZQBzAF8AZQBuAGQAPwAsACAAIAAgACAAIAAgACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADQAKQAgACsAIAAoAGkAbgB0AGUAcgB2AGEAbAAgAD0AIAA1ACkALABcAG4AXABuACAAIAAgACAAdQBuAGkAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMASABPAE8AUwBFACgAaQBuAHQAZQByAHYAYQBsACwAIAAxADQANAAwACwAIAAyADQALAAgADEALAAgADEALAAgADEALAAgADEALAAgADEALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgAgACAAIAAgAE4AbwBGAG8AcgBtAGEAdAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGYAbwByAG0AYQB0ACkALABcAG4AIAAgACAAIABIAGUAYQBkAGUAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAHMAKQApACwAXABuACAAIAAgACAARgBpAGwAdABlAHIAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARABhAHQAZQAgAHYAZQBjAHQAbwByACAAZgByAG8AbQAgAHIAbwB3AF8AZgBpAGUAbABkAHMAXABuACAAIAAgACAAZABhAHQAZQBfAGMAbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEgAZQBhAGQAZQByAD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAVABBAEsARQAoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACwAIAAxACkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKAByAG8AdwBfAGYAaQBlAGwAZABzACwAIAAsACAAMQApACkALABcAG4AXABuACAAIAAgACAAZABhAHQAZQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGkAbgB0AGUAcgB2AGEAbAAgADwAIAAzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAZABhAHQAZQBfAGMAbwBsACAAKgAgAHUAbgBpAHQALAAgADAAKQAgAC8AIAB1AG4AaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBOAFQAKABkAGEAdABlAF8AYwBvAGwAKQApACwAXABuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzAF8AaABlAGEAZABlAHIALAAgACAAIAAgACAAIABUAEEASwBFACgAdgBhAGwAdQBlAHMALAAgADEAKQAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABIAGUAYQBkAGUAcgA/ACwAIABEAFIATwBQACgAdgBhAGwAdQBlAHMALAAgADEAKQAsACAAdgBhAGwAdQBlAHMAKQAsAFwAbgAgACAAIAAgAHIAbwB3AF8AZABlAHQAYQBpAGwAcwAsACAAIAAgACAAIAAgACAAIABEAFIATwBQACgARABSAE8AUAAoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACwAIAAxACkALAAgAEgAZQBhAGQAZQByAD8AKQAsAFwAbgAgACAAIAAgAGYAaQBsAHQAZQByAF8AdQBzAGUAZAAsACAAIAAgACAAIAAgACAAIABJAEYAKABIAGUAYQBkAGUAcgA/ACAAKgAgAEYAaQBsAHQAZQByAD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAVwBpAGQAdABoAHMAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAByAG8AdwBfAGYAaQBlAGwAZABzACkALABcAG4AIAAgACAAIAB3AF8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAHYAYQBsAHUAZQBzACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwAgACsAIAB3AF8ALABcAG4AXABuACAAIAAgACAALwAvACAARABhAHQAZQAgAGIAbwB1AG4AZABzAFwAbgAgACAAIAAgAG0AaQBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAE4AVAAoAE0ASQBOACgAZABhAHQAZQBzACkAKQAsAFwAbgAgACAAIAAgAG0AYQB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAE4AVAAoAE0AQQBYACgAZABhAHQAZQBzACkAKQAsAFwAbgAgACAAIAAgAG0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAE8ATgBUAEgAKABtAGkAbgApACwAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAQQBZACgAbQBpAG4AKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABZAEUAQQBSACgAbQBpAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAGkAbQBlACAAbwBmACAAZgBpAHIAcwB0ACAAZABhAHQAZQBcAG4AIAAgACAAIABmAGkAcgBzAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABkAGEAdABlAHMAKQAsAFwAbgAgACAAIAAgAGwAYQBzAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAGQAYQB0AGUAcwApACwAXABuACAAIAAgACAAaAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgATwBVAFIAKABmAGkAcgBzAHQAKQAsAFwAbgAgACAAIAAgAG0AbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgBVAFQARQAoAGYAaQByAHMAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAYQBuAGcAZQBzAFwAbgAgACAAIAAgAHMAZQBjAG8AbgBkAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAGwAYQBzAHQAIAAtACAAZgBpAHIAcwB0ACkAIAAqACAAOAA2ADQAMAAwACwAXABuACAAIAAgACAAbQBpAG4AdQB0AGUAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABzAGUAYwBvAG4AZABzACAALwAgADYAMAAsACAAMQApACwAXABuACAAIAAgACAAaABvAHUAcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AaQBuAHUAdABlAHMAIAAvACAANgAwACwAXABuACAAIAAgACAAZABhAHkAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4ACAALQAgAG0AaQBuACwAXABuACAAIAAgACAAdwBlAGUAawBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABkAGEAeQBzACAALwAgADcALAAgADEAKQAsAFwAbgAgACAAIAAgAGYAbwByAHQAbgBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAZABhAHkAcwAgAC8AIAAxADQALAAgADEAKQAsAFwAbgAgACAAIAAgAG0AbwBuAHQAaABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAEEAVABFAEQASQBGACgAbQBpAG4ALAAgAG0AYQB4ACwAIABcACIAbQBcACIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAHIAdABlAHIAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAbQBvAG4AdABoAHMAIAAvACAAMwAsACAAMQApACwAXABuACAAIAAgACAAeQBlAGEAcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABtAG8AbgB0AGgAcwAgAC8AIAAxADIALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAcwBwAGwAYQB5ACAAZgBvAHIAbQBhAHQAcwBcAG4AIAAgACAAIABoAF8AbQBtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZABhAHkAcwAgAD4AIAAxACwAIABcACIAbQAvAGQALwB5AHkAeQAgAGgAOgBtAG0AIABBAE0ALwBQAE0AXAAiACwAIABcACIAaAA6AG0AbQAgAEEATQAvAFAATQBcACIAKQAsAFwAbgAgACAAIAAgAG0AbQBtAG0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAbQBtAG0AbQAgAHkAeQB5AFwAIgAsAFwAbgAgACAAIAAgAGQAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAbQAvAGQALwB5AHkAeQBcACIALABcAG4AIAAgACAAIAB5AHkAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHkAeQB5AFwAIgAsAFwAbgBcAG4AIAAgACAAIABmAG0AdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAEYAbwByAG0AYQB0AD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFcASQBUAEMASAAoAGkAbgB0AGUAcgB2AGEAbAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxACwAIABoAF8AbQBtACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADIALAAgAGgAXwBtAG0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMwAsACAAZABhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAANAAsACAAZABhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAANQAsACAAZABhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAANgAsACAAbQBtAG0AbQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA3ACwAIABtAG0AbQBtACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADgALAAgAHkAeQB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AbQBtAG0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAbwByAG0AYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABhAHQAZQAvAHQAaQBtAGUAIABhAHIAcgBhAHkAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAbQBpAG4AXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAQABtAGkAbgB1AHQAZQBzACAAKwAgADEALAAgACwAIABmAGkAcgBzAHQALAAgADEAIAAvACAAMQA0ADQAMAApACkALABcAG4AIAAgACAAIABoAHIAcwBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABAAGgAbwB1AHIAcwAgACsAIAAxACwAIAAsACAAZgBpAHIAcwB0ACwAIAAxACAALwAgADIANAApACkALABcAG4AIAAgACAAIABkAGEAeQBzAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABkAGEAeQBzACAAKwAgADEALAAgACwAIABtAGkAbgAsACAAMQApACkALABcAG4AIAAgACAAIAB3AGUAZQBrAHMAXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABEAEEAVABFACgAeQAsACAAbQAsACAAUwBFAFEAVQBFAE4AQwBFACgAdwBlAGUAawBzACAAKwAgADEALAAgACwAIABkACwAIAA3ACkAKQApACwAXABuACAAIAAgACAAZgBvAHIAdABfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARABBAFQARQAoAHkALAAgAG0ALAAgAFMARQBRAFUARQBOAEMARQAoAGYAbwByAHQAbgBpAGcAaAB0ACAAKwAgADEALAAgACwAIABkACwAIAAxADQAKQApACkALABcAG4AIAAgACAAIABtAG8AbgB0AGgAXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABEAEEAVABFACgAeQAsACAAbQAgACsAIABTAEUAUQBVAEUATgBDAEUAKABtAG8AbgB0AGgAcwAgACsAIAAxACwAIAAsACAAMAApACwAIABkACkAKQAsAFwAbgAgACAAIAAgAHEAdAByAHMAXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEQAQQBUAEUAKAB5ACwAIABtACAAKwAgAFMARQBRAFUARQBOAEMARQAoAHEAdQBhAHIAdABlAHIAcwAgACsAIAAxACwAIAAsACAAMAAsACAAMwApACwAIABkACkAKQAsAFwAbgAgACAAIAAgAHkAcgBzAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEQAQQBUAEUAKAB5ACAAKwAgAFMARQBRAFUARQBOAEMARQAoAEAAeQBlAGEAcgBzACAAKwAgADEALAAgACwAIAAwACkALAAgAG0ALAAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgB0AGUAcgB2AGEAbAAgAHMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAGIAaQBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAGkAbgB0AGUAcgB2AGEAbAAgADwAIAAzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABDAEgATwBPAFMARQAoAGkAbgB0AGUAcgB2AGEAbAAsACAAbQBpAG4AXwBhAHIAcgAoACkALAAgAGgAcgBzAF8AYQByAHIAKAApACkAIAAqACAAdQBuAGkAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAwACkAIAAvACAAdQBuAGkAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBuAHQAZQByAHYAYQBsACAALQAgADIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABhAHkAcwBfAGEAcgByACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB3AGUAZQBrAHMAXwBhAHIAcgAoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBvAHIAdABfAGEAcgByACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAG8AbgB0AGgAXwBhAHIAcgAoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcQB0AHIAcwBfAGEAcgByACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB5AHIAcwBfAGEAcgByACgAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAGEAYgBlAGwAIABhAHMAcwBpAGcAbgBtAGUAbgB0AFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAGkAbgB0AGUAcgB2AGEAbAAgAD0AIAA4ACwAWABNAEEAVABDAEgAKABZAEUAQQBSACgAZABhAHQAZQBzACkALAAgAFkARQBBAFIAKABiAGkAbgAoACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAGQAYQB0AGUAcwAsACAAYgBpAG4AKAApACwAIAAtADEAKQApACkALABcAG4AXABuACAAIAAgACAAZABhAHQAZQBfAGYAaQBlAGwAZAAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBOAEQARQBYACgAYgBpAG4AKAApACwAIABpACgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBvAHcAIABsAGEAYgBlAGwAcwBcAG4AIAAgACAAIAByAG8AdwBfAGwAYQBiAGUAbABzACwAIAAgACAAIAAgACAAIAAgACAASQBGACgAdwAgAD0AIAAxACwAZABhAHQAZQBfAGYAaQBlAGwAZAAoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGQAYQB0AGUAXwBmAGkAZQBsAGQAKAApACwAIAByAG8AdwBfAGQAZQB0AGEAaQBsAHMAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAZQBhAGQAZQByAHMAXABuACAAIAAgACAAdABvAHQAYQBsAF8AbABhAGIAZQBsACwAIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAaQBuAHQAZQByAHYAYQBsACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQAsACAAXAAiAFQAbwB0AGEAbABzACAAYgB5ACAAbQBpAG4AdQB0AGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAsACAAXAAiAFQAbwB0AGEAbABzACAAYgB5ACAAaABvAHUAcgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAzACwAIABcACIAVABvAHQAYQBsAHMAIABiAHkAIABEAGEAeQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACwAIABcACIAVwBlAGUAawBsAHkAIABUAG8AdABhAGwAcwBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA1ACwAIABcACIAQgBpAHcAZQBlAGsAbAB5ACAAVABvAHQAYQBsAHMAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAANgAsACAAXAAiAE0AbwBuAHQAaABsAHkAIABUAG8AdABhAGwAcwBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA3ACwAIABcACIAVABvAHQAYQBsAHMAIABiAHkAIABRAHUAYQByAHQAZQByAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADgALAAgAFwAIgBZAGUAYQByAGwAeQAgAFQAbwB0AGEAbABzAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAB0AG8AdABhAGwAXwBoAGUAYQBkAGUAcgAsACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKABJAEYAKABPAFIAKABpAG4AdABlAHIAdgBhAGwAIAA9ACAANAAsACAAaQBuAHQAZQByAHYAYQBsACAAPQAgADUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKAB0AG8AdABhAGwAXwBsAGEAYgBlAGwALAAgAFwAIgBFAG4AZABpAG4AZwAgAEQAYQB0AGUAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAbwB0AGEAbABfAGwAYQBiAGUAbAApACwALAB3ACAAKwAgAEkAbgBjAGwAdQBkAGUAcwBfAGUAbgBkAD8ALABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAAYQBnAGcAXwBoAGUAYQBkAGUAcgAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEgAZQBhAGQAZQByAD8ALAB2AGEAbAB1AGUAcwBfAGgAZQBhAGQAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKABcACIAXAAiACwAIAAsACAAdwBfACwAIABcACIAXAAiACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAGcAZwByAGUAZwBhAHQAaQBvAG4AXABuACAAIAAgACAAbgBvAF8AZgBpAGwAdABlAHIALAAgACAAIAAgACAAIAAgACAAIAAgAEcAUgBPAFUAUABCAFkAKAByAG8AdwBfAGwAYQBiAGUAbABzACwAIAB2AGEAbAB1AGUAcwAsACAAZgB1AG4AYwB0AGkAbwBuACwAIABIAGUAYQBkAGUAcgA/ACkALABcAG4AIAAgACAAIABmAGkAbAB0AGUAcgBfAGkAbgBjACwAIAAgACAAIAAgACAAIAAgACAARwBSAE8AVQBQAEIAWQAoAHIAbwB3AF8AbABhAGIAZQBsAHMALAAgAHYAYQBsAHUAZQBzACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgAEgAZQBhAGQAZQByAD8ALAAgACwAIAAsACAAZgBpAGwAdABlAHIAXwB1AHMAZQBkACkALABcAG4AIAAgACAAIABhAGcAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgARgBpAGwAdABlAHIAPwAsACAAZgBpAGwAdABlAHIAXwBpAG4AYwAsACAAbgBvAF8AZgBpAGwAdABlAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGwAYQBiAGUAbAAgACgAdQBuAGYAbwByAG0AYQB0AHQAZQBkACkAIABhAG4AZAAgAGYAbwByAG0AYQB0AHQAZQBkAFwAbgAgACAAIAAgAHIAbwB3AF8AbABhAGIAZQBsACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFQAQQBLAEUAKABhAGcAZwAsACAALAAgADEAKQApACwAXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAVABFAFgAVAAoAHIAbwB3AF8AbABhAGIAZQBsACgAKQAsACAAZgBtAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbgBkAGkAbgBnACAAZABhAHQAZQBzACAAZgBvAHIAIAB3AGUAZQBrAGwAeQAgAC8AIABiAGkAdwBlAGUAawBsAHkAXABuACAAIAAgACAAYgBpAG4AXwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADQALABUAEUAWABUACgAYQAoACkAIAArACAANgAsACAAZgBtAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADUALAAgAFQARQBYAFQAKABhACgAKQAgACsAIAAxADMALAAgAGYAbQB0ACkALAAgADAAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAG0AYQBpAG4AaQBuAGcAIABjAG8AbAB1AG0AbgBzAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEQAUgBPAFAAKABhAGcAZwAsACAALAAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAGMAawBzAFwAbgAgACAAIAAgAHMAdABhAGMAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAEgAUwBUAEEAQwBLACgAdABvAHQAYQBsAF8AaABlAGEAZABlAHIALAAgAGEAZwBnAF8AaABlAGEAZABlAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAoACkALAAgAGIAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIABzAHQAYQBjAGsAXwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHQAbwB0AGEAbABfAGgAZQBhAGQAZQByACwAIABhAGcAZwBfAGgAZQBhAGQAZQByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAoACkALAAgAGIAaQBuAF8AZQBuAGQAKAApACwAIABiACgAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAGkAbgB0AGUAcgB2AGEAbAAgAD0AIAA0ACwAIABpAG4AdABlAHIAdgBhAGwAIAA9ACAANQApACwAIABzAHQAYQBjAGsAXwBlAG4AZAAsACAAcwB0AGEAYwBrACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgB5AFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgARIEMATwBSAEUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABWAGEAbABpAGQAYQB0AGUARwBEALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAbwByAGUAIABWAGEAbABpAGQAYQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABWAGEAbABpAGQAYQB0AGUAcwAgAGkAbgBwAHUAdABzACAAZgBvAHIAIABHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMuACAARQBuAHMAdQByAGUAcwAgAHQAaABhAHQAIAByAG8AdwBfAGYAaQBlAGwAZABzACAAYwBvAG4AdABhAGkAbgAgAHYAYQBsAGkAZABcAG4AIAAgACAAIABkAGEAdABlAHMALAAgAHQAaABhAHQAIABpAG4AdABlAHIAdgBhAGwAcwAgAGEAcgBlACAAcgBlAGMAbwBnAG4AaQB6AGUAZAAsACAAdABoAGEAdAAgAHYAYQBsAHUAZQBzACAAYQBuAGQAIABmAGkAbAB0AGUAcgBzACAAYQBsAGkAZwBuACAAaQBuAFwAbgAgACAAIAAgAHMAaABhAHAAZQAsACAAYQBuAGQAIAB0AGgAYQB0ACAAdABoAGUAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAIABjAGEAbABsAGEAYgBsAGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAByAG8AdwBfAGYAaQBlAGwAZABzACAAIAAgACAAIAAgAC0AIABBAHIAcgBhAHkAIAB3AGkAdABoACAAZABhAHQAZQBzACAAaQBuACAAdABoAGUAIABsAGUAZgB0AG0AbwBzAHQAIABjAG8AbAB1AG0AbgAuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAgAG8AZgAgAHYAYQBsAHUAZQBzACAAdABvACAAYQBnAGcAcgBlAGcAYQB0AGUALgBcAG4AIAAgACAAIABpAG4AdABlAHIAdgBhAGwAIAAgACAAIAAgACAAIAAgAC0AIABEAGEAdABlAC8AdABpAG0AZQAgAGkAbgB0AGUAcgB2AGEAbAAgACgAbgB1AG0AZQByAGkAYwAgAG8AcgAgAHQAZQB4AHQAKQAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgACAAIAAgACAALQAgAEUAVABBACAAbwByACAAcwBpAG4AZwBsAGUAESBwAGEAcgBhAG0AZQB0AGUAcgAgAEwAQQBNAEIARABBAC4AXABuACAAIAAgACAAWwBmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBzAF0AIAAtACAAVABSAFUARQAgAGkAZgAgAHIAbwB3AF8AZgBpAGUAbABkAHMALwB2AGEAbAB1AGUAcwAgAGkAbgBjAGwAdQBkAGUAIABoAGUAYQBkAGUAcgBzAC4AXABuACAAIAAgACAAWwBmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQBdACAAIAAtACAAQgBvAG8AbABlAGEAbgAgAGYAaQBsAHQAZQByACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBPAG4AXwBWAGEAbABpAGQAXQAgACAAIAAgACAAIAAtACAARQB4AHAAcgBlAHMAcwBpAG8AbgAgAHQAbwAgAGUAdgBhAGwAdQBhAHQAZQAgAHcAaABlAG4AIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAdgBhAGwAaQBkAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARABlAHQAZQBjAHQAcwAgAGkAbgB2AGEAbABpAGQAIABkAGEAdABlAHMALAAgAG0AaQBzAHMAaQBuAGcAIAB0AGkAbQBlACAAYwBvAG0AcABvAG4AZQBuAHQAcwAsACAAYQBuAGQAIABtAGEAbABmAG8AcgBtAGUAZAAgAGkAbgB0AGUAcgB2AGEAbABzAC4AXABuACAAIAAgACAAIiAgAEUAbgBzAHUAcgBlAHMAIAByAG8AdwBfAGYAaQBlAGwAZABzACwAIAB2AGEAbAB1AGUAcwAsACAAYQBuAGQAIABmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQAgAGgAYQB2AGUAIABtAGEAdABjAGgAaQBuAGcAIABoAGUAaQBnAGgAdABzAC4AXABuACAAIAAgACAAIiAgAEUAbgBzAHUAcgBlAHMAIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAIABjAGEAbABsAGEAYgBsAGUAIAB2AGkAYQAgAGEAIABzAGEAZgBlACAAQgBZAFIATwBXACAAdABlAHMAdAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBWAGEAbABpAGQAYQB0AGUARwBEALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMALABcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAsAFwAbgAgACAAIAAgAGkAbgB0AGUAcgB2AGEAbAAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAFsAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAcwBdACwAXABuACAAIAAgACAAWwBmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQBdACwAXABuACAAIAAgACAAWwBPAG4AXwBWAGEAbABpAGQAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAATwBwAHQAaQBvAG4AYQBsACAAZgBsAGEAZwBzACAALQAtAC0AXABuACAAIAAgACAATgBvAF8ARgBpAGUAbABkAF8ASABlAGEAZABlAHIAcwA/ACwAIAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBzACkALABcAG4AIAAgACAAIABGAGkAbAB0AGUAcgBJAG4AYwBsAHUAZABlAGQAPwAsACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAARQB4AHQAcgBhAGMAdAAgAGQAYQB0AGUAIABhAG4AZAAgAHYAYQBsAHUAZQAgAGMAbwBsAHUAbQBuAHMAIAAtAC0ALQBcAG4AIAAgACAAIABEAGEAdABlAF8AYwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AXwBGAGkAZQBsAGQAXwBIAGUAYQBkAGUAcgBzAD8ALABUAEEASwBFACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAFQAQQBLAEUAKAByAG8AdwBfAGYAaQBlAGwAZABzACwAIAAsACAAMQApACwAIAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABWAGEAbAB1AGUAcwBfAGMAbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AXwBGAGkAZQBsAGQAXwBIAGUAYQBkAGUAcgBzAD8ALABUAEEASwBFACgAdgBhAGwAdQBlAHMALAAgACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABUAEEASwBFACgAdgBhAGwAdQBlAHMALAAgACwAIAAxACkALAAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAARgBpAGwAdABlAHIAIABhAHIAcgBhAHkAIABuAG8AcgBtAGEAbABpAHoAYQB0AGkAbwBuACAALQAtAC0AXABuACAAIAAgACAAQgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEkARgAoAE4AbwBfAEYAaQBlAGwAZABfAEgAZQBhAGQAZQByAHMAPwAsAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQAsACAAMQApACAAKQAsADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEQAYQB0AGUAIAB2AGEAbABpAGQAaQB0AHkAIABjAGgAZQBjAGsAcwAgAC0ALQAtAFwAbgAgACAAIAAgAE4AbwBfAEQAYQB0AGUAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAEQAYQB0AGUAXwBjAG8AbAAgADwAIAAwACwARABhAHQAZQBfAGMAbwBsACAAPgAgADIAOQA1ADgANAA2ADUALABOAE8AVAAoAEEATgBEACgASQBTAE4AVQBNAEIARQBSACgARABhAHQAZQBfAGMAbwBsACkAKQApACkALABcAG4AXABuACAAIAAgACAATgBvAF8AVABpAG0AZQBzAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABEAGEAdABlAF8AYwBvAGwAIAAtACAASQBOAFQAKABEAGEAdABlAF8AYwBvAGwAKQAgAD0AIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABEAGkAbQBlAG4AcwBpAG8AbgAgAGMAaABlAGMAawBzACAALQAtAC0AXABuACAAIAAgACAAaQBfAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAEQAYQB0AGUAXwBjAG8AbAApACwAXABuACAAIAAgACAAaQBfAHYALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAFYAYQBsAHUAZQBzAF8AYwBvAGwAKQAsAFwAbgAgACAAIAAgAGkAXwBmACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEYAaQBsAHQAZQByAEkAbgBjAGwAdQBkAGUAZAA/ACwAIABSAE8AVwBTACgAQgBvAG8AbAApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABJAG4AdABlAHIAdgBhAGwAIAB2AGEAbABpAGQAYQB0AGkAbwBuACAALQAtAC0AXABuACAAIAAgACAAQwBvAG4AcwB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAewBcACIAbQBpAG4AdQB0AGUAXAAiADsAXAAiAGgAbwB1AHIAXAAiADsAXAAiAGQAYQB5AFwAIgA7AFwAIgB3AGUAZQBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAbwByAHQAbgBpAGcAaAB0AFwAIgA7AFwAIgBtAG8AbgB0AGgAXAAiADsAXAAiAHEAdQBhAHIAdABlAHIAXAAiADsAXAAiAHkAZQBhAHIAXAAiAH0ALABcAG4AXABuACAAIAAgACAAVABlAHgAdABJAG4AdABlAHIAdgBhAGwAPwAsACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABpAG4AdABlAHIAdgBhAGwAKQAsAFwAbgAgACAAIAAgAE4AdQBtAGUAcgBpAGMASQBuAHQAZQByAHYAYQBsAD8ALAAgACAAIAAgACAAIAAgAEkAUwBOAFUATQBCAEUAUgAoAGkAbgB0AGUAcgB2AGEAbAApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQASQBuAHQAZQByAHYAYQBsAD8ALAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgATgB1AG0AZQByAGkAYwBJAG4AdABlAHIAdgBhAGwAPwAsACAATwBSACgAaQBuAHQAZQByAHYAYQBsACAAPAAgADEALAAgAGkAbgB0AGUAcgB2AGEAbAAgAD4AIAA4ACkAKQAsAFQAUgBVAEUALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgAVABlAHgAdABJAG4AdABlAHIAdgBhAGwAPwAsACAASQBTAE4AQQAoAFgATQBBAFQAQwBIACgAaQBuAHQAZQByAHYAYQBsACAAJgAgAFwAIgAqAFwAIgAsACAAQwBvAG4AcwB0ACwAIAAyACkAKQApACwAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEEATABTAEUAKQApACwAXABuAFwAbgAgACAAIAAgAEkAcwBUAGkAbQBlAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgB0AGUAcgB2AGEAbAAgADwAIAAzACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAASABhAGwAdABpAG4AZwAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAAtAC0ALQBcAG4AIAAgACAAIABFAG0AcAB0AHkASQBuAHAAdQB0AHMAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AF8AZgBpAGUAbABkAHMAKQAsACAASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwApACkALABcAG4AXABuACAAIAAgACAASABhAGwAdABEAGEAdABlAHMAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABpAG4AdABlAHIAdgBhAGwAIAA+ACAAMgAsACAATgBvAF8ARABhAHQAZQBzAD8AKQAsAFwAbgAgACAAIAAgAEgAYQBsAHQAVABpAG0AZQA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgASQBzAFQAaQBtAGUAPwAsACAATgBvAF8AVABpAG0AZQBzAD8AKQAsAFwAbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAAgACAAIAAgACAAIABPAFIAKABpAF8AZAAgADwAPgAgAGkAXwB2ACwAQQBOAEQAKABGAGkAbAB0AGUAcgBJAG4AYwBsAHUAZABlAGQAPwAsACAAaQBfAGQAIAA8AD4AIABpAF8AZgApACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4APwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABZAFAARQAoAGYAdQBuAGMAdABpAG8AbgApACAAPAA+ACAAMQAyADgALABcAG4AXABuACAAIAAgACAARQBtAHAAdAB5AEYAaQBsAHQAZQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABGAGkAbAB0AGUAcgBJAG4AYwBsAHUAZABlAGQAPwAsACAATgBPAFQAKABPAFIAKABCAG8AbwBsACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAGwAZQBjAHQAIABhAGwAbAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAXABuACAAIAAgACAAYwBvAG4AZABpAHQAaQBvAG4AcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABFAG0AcAB0AHkASQBuAHAAdQB0AHMAPwAsAEgAYQBsAHQARABhAHQAZQBzAD8ALABIAGEAbAB0AFQAaQBtAGUAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwASQBuAHYAYQBsAGkAZABJAG4AdABlAHIAdgBhAGwAPwAsAEkAbgB2AGEAbABpAGQARgBuAD8ALABFAG0AcAB0AHkARgBpAGwAdABlAHIAPwApACwAXABuAFwAbgAgACAAIAAgAGgAYQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHIAcgBvAHIAIABtAGUAcwBzAGEAZwBlAHMAIAAoAGEAbABpAGcAbgBlAGQAIAB3AGkAdABoACAARwByAG8AdQBwAGIAeQBEAGEAdABlALsDKQBcAG4AIAAgACAAIABlAHIAcgBvAHIAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAEUATQBQAFQAWQAtAEkATgBQAFUAVAAhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMATgBPAC0ARABBAFQARQBTACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8ALQBUAEkATQBFAFMAIQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAEkATgBUAEUAUgBWAEEATAAhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMASQBOAFYAQQBMAEkARAAtAEYAVQBOAEMAVABJAE8ATgAhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMARQBNAFAAVABZAC0ARgBJAEwAVABFAFIAIQBcACIAfQAsAFwAbgBcAG4AIAAgACAAIABhAGwAZQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGUAcgByAG8AcgBzACwAIABjAG8AbgBkAGkAdABpAG8AbgBzACwAIABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABMAG8AZwBpAGMAIABnAGEAdABlACAALQAtAC0AXABuACAAIAAgACAASQBGACgAaABhAGwAdAAsACAAYQBsAGUAcgB0ACwAIABPAG4AXwBWAGEAbABpAGQAKQBcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAAOQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFAAaQB2AG8AdABiAHkAQwBhAHQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABTAHQAcgBlAGEAawC7AywAIABSAGUAcABlAGEAdABSAG8AdwBzALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGkAdgBvAHQAcwAgAGQAYQB0AGEAIABiAHkAIAByAG8AdwAgAGYAaQBlAGwAZABzACAAKABkAGUAdABhAGkAbAAgACsAIABkAGEAdABlACkALAAgAGMAYQB0AGUAZwBvAHIAaQBlAHMALAAgAGEAbgBkACAAdgBhAGwAdQBlAHMALgBcAG4AIAAgACAAIABDAGEAdABlAGcAbwByAGkAZQBzACAAYQByAGUAIABhAHMAcwB1AG0AZQBkACAAdABvACAAYgBlACAAcAByAGUAESBjAG8AbgBjAGEAdABlAG4AYQB0AGUAZAAgAHUAcwBpAG4AZwAgAGEAIABkAGUAbABpAG0AaQB0AGUAcgAuAFwAbgAgACAAIAAgAFMAdQBwAHAAbwByAHQAcwAgAG8AcAB0AGkAbwBuAGEAbAAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAgAGEAbgBkACAAZABhAHQAZQAgAGYAbwByAG0AYQB0AHQAaQBuAGcALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAByAG8AdwBfAGQAZQB0AGEAaQBsACAAIAAgACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIABuAG8AbgARIGQAYQB0AGUAIAByAG8AdwAgAGYAaQBlAGwAZABzAC4AXABuACAAIAAgACAAcgBvAHcAXwBkAGEAdABlAHMAIAAgACAAIAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAZABhAHQAZQBzAC4AXABuACAAIAAgACAAYwBhAHQAZQBnAG8AcgBpAGUAcwAgACAAIAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAZABlAGwAaQBtAGkAdABlAGQAIABjAGEAdABlAGcAbwByAHkAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAIAAgACAAdgBhAGwAdQBlAHMAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAHYAYQBsAHUAZQBzAC4AXABuACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIAIAAgACAAIAAgACAAIAAtACAARABlAGwAaQBtAGkAdABlAHIAIAB1AHMAZQBkACAAaQBuACAAdABoAGUAIABjAGEAdABlAGcAbwByAGkAZQBzACAAYQByAHIAYQB5AC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAGQAYQB0AGUAXwBmAG8AcgBtAGEAdABdACAAIAAgAC0AIABGAG8AcgBtAGEAdAAgAGMAbwBkAGUAIABmAG8AcgAgAGQAYQB0AGUAcwAgACgAZABlAGYAYQB1AGwAdAAgAFwAIgB5AHkAeQBcACIAKQAuAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0AIAAgACAAIAAgACAALQAgAEUAVABBACAAbwByACAATABBAE0AQgBEAEEAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABmAHUAbgBjAHQAaQBvAG4AIAAoAGQAZQBmAGEAdQBsAHQAIABTAFUATQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQwBhAHQAZQBnAG8AcgBpAGUAcwAgAGEAcgBlACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAG0AdQBsAHQAaQBwAGwAZQAgAHIAbwB3AHMAIAB1AHMAaQBuAGcAIABSAGUAcABlAGEAdABSAG8AdwBzALsDLgBcAG4AIAAgACAAIAAiICAARABhAHQAZQBzACAAYQByAGUAIABmAG8AcgBtAGEAdAB0AGUAZAAgAGEAbgBkACAAcwBvAHIAdABlAGQAIAB1AHMAaQBuAGcAIABhACAAbgB1AG0AZQByAGkAYwAgAHMAbwByAHQAIABrAGUAeQAuAFwAbgAgACAAIAAgACIgIABWAGEAbAB1AGUAcwAgAGEAcgBlACAAYQBwAHAAbwByAHQAaQBvAG4AZQBkACAAYQBjAHIAbwBzAHMAIAByAGUAcABlAGEAdABlAGQAIABjAGEAdABlAGcAbwByAHkAIAByAG8AdwBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFAAaQB2AG8AdABiAHkAQwBhAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcgBvAHcAXwBkAGUAdABhAGkAbAAsAFwAbgAgACAAIAAgAHIAbwB3AF8AZABhAHQAZQBzACwAXABuACAAIAAgACAAYwBhAHQAZQBnAG8AcgBpAGUAcwAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIALABcAG4AIAAgACAAIABbAGQAYQB0AGUAXwBmAG8AcgBtAGEAdABdACwAXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAIAAtAC0ALQBcAG4AIAAgACAAIAByAIEgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHIAbwB3AF8AZABlAHQAYQBpAGwAKQAsAFwAbgAgACAAIAAgAHIAgiAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcgBvAHcAXwBkAGEAdABlAHMAKQAsAFwAbgAgACAAIAAgAHIAgyAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYwBhAHQAZQBnAG8AcgBpAGUAcwApACwAXABuACAAIAAgACAAcgCEICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAB2AGEAbAB1AGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAASABhAGwAdABpAG4AZwAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAAtAC0ALQBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoACwAIAAgACAAIAAgACAATwBSACgAcgCBICAAPAA+ACAAcgCCICwAIAByAIEgIAA8AD4AIAByAIMgLAAgAHIAgSAgADwAPgAgAHIAhCApACwAXABuAFwAbgAgACAAIAAgAGQAYQB0AGUAXwBmAG8AcgBtAGEAdAAsACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGQAYQB0AGUAXwBmAG8AcgBtAGEAdAApACwAIABcACIAeQB5AHkAXAAiACwAIABkAGEAdABlAF8AZgBvAHIAbQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEQAYQB0AGUAcwAsACAAIAAgACAAIAAgACAATwBSACgAQQBOAEQAKABJAFMARQBSAFIATwBSACgARABBAFQARQBWAEEATABVAEUAKABUAEUAWABUACgAcgBvAHcAXwBkAGEAdABlAHMALAAgAGQAYQB0AGUAXwBmAG8AcgBtAGEAdAApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBFAFIAUgBPAFIAKABWAEEATABVAEUAKABUAEUAWABUACgAcgBvAHcAXwBkAGEAdABlAHMALAAgAGQAYQB0AGUAXwBmAG8AcgBtAGEAdAApACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKAByAG8AdwBfAGQAYQB0AGUAcwApACkAKQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARgBuACwAIAAgACAAIAAgACAAIAAgACAAIABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA8AD4AIAAxADIAOAAsAFwAbgBcAG4AIAAgACAAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoACwAIABJAG4AdgBhAGwAaQBkAEQAYQB0AGUAcwAsACAASQBuAHYAYQBsAGkAZABGAG4AKQAsAFwAbgBcAG4AIAAgACAAIABlAHIAcgBvAHIAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAewBcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMARABBAFQARQBTACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMASQBOAFYAQQBMAEkARAAtAEYAVQBOAEMAVABJAE8ATgAhAFwAIgB9ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAATABvAGcAaQBjACAAZwBhAHQAZQAgAC0ALQAtAFwAbgAgACAAIAAgAEYASQBMAFQARQBSACgAZQByAHIAbwByAHMALAAgAHMAYwBlAG4AYQByAGkAbwBzACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAIAAtAC0ALQBcAG4AIAAgACAAIABmAG4AuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsACAAUwBVAE0ALAAgAGYAdQBuAGMAdABpAG8AbgApACwAXABuAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEwAbwBjAGEAbAAgAGgAZQBsAHAAZQByAHMAIAAtAC0ALQBcAG4AIAAgACAAIABDAG8AdQBuAHQAQwBhAHQAuwMsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAVABFAFgAVABTAFAATABJAFQAKAByAG8AdwAsACAAZABlAGwAaQBtAGkAdABlAHIAKQApACkALABcAG4AXABuACAAIAAgACAAUABhAHIAcwBlALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAYQByAHIAYQB5ACwAIABpAG4AcwB0AGEAbgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUAEIARQBGAE8AUgBFACgAVABFAFgAVABBAEYAVABFAFIAKABkAGUAbABpAG0AaQB0AGUAcgAgACYAIABhAHIAcgBhAHkAIAAmACAAZABlAGwAaQBtAGkAdABlAHIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsAGkAbgBzAHQAYQBuAGMAZQAsACwALABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIALAAsACwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAYQB0AGUAZwBvAHIAaQBlAHMAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAQwBhAHQAZQBnAG8AcgB5ACAAZQB4AHAAYQBuAHMAaQBvAG4AIAAtAC0ALQBcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgBZAFIATwBXACgAYwBhAHQAZQBnAG8AcgBpAGUAcwAsACAAQwBvAHUAbgB0AEMAYQB0ALsDKQAsAFwAbgBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AygAUwBFAFEAVQBFAE4AQwBFACgAcgCBICkALAAgAGsAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAcgBlAGEAawC7AygAaQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAUgBvAHcAIABmAGkAZQBsAGQAcwAgAC0ALQAtAFwAbgAgACAAIAAgAGEALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDKAByAG8AdwBfAGQAZQB0AGEAaQBsACwAIABrACkALABcAG4AIAAgACAAIABkAGUAdABhAGkAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYQAgAD0AIAAwACwAIABcACIAVQBuAGsAbgBvAHcAbgBcACIALAAgAGEAKQAsAFwAbgBcAG4AIAAgACAAIABkAGEAdABlAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AygAVABFAFgAVAAoAHIAbwB3AF8AZABhAHQAZQBzACwAIABkAGEAdABlAF8AZgBvAHIAbQBhAHQAKQAsACAAawApACwAXABuACAAIAAgACAAcwBvAHIAdABfAGsAZQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABEAEEAVABFAFYAQQBMAFUARQAoAGQAYQB0AGUAcwApACwAIABWAEEATABVAEUAKABkAGEAdABlAHMAKQApACwAXABuAFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHMAbwByAHQAXwBrAGUAeQAsACAAZABlAHQAYQBpAGwALAAgAGQAYQB0AGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAQwBvAGwAdQBtAG4AIABmAGkAZQBsAGQAcwAgAC0ALQAtAFwAbgAgACAAIAAgAHUAbgBwAGEAYwBrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDKABjAGEAdABlAGcAbwByAGkAZQBzACwAIABrACkALABcAG4AIAAgACAAIABjAGEAdABlAGcAbwByAGkAZQBzACwAIAAgACAAIAAgACAAIAAgACAAUABhAHIAcwBlALsDKAB1AG4AcABhAGMAawAsACAAagApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAVgBhAGwAdQBlAHMAIAAoAGEAcABwAG8AcgB0AGkAbwBuAGUAZAApACAALQAtAC0AXABuACAAIAAgACAAdgBhAGwAdQBlAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMoAHYAYQBsAHUAZQBzACAALwAgAGsALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAC0ALQAtAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAUABJAFYATwBUAEIAWQAoAHIAbwB3AF8AZgBpAGUAbABkAHMALABjAGEAdABlAGcAbwByAGkAZQBzACwAdgBhAGwAdQBlAHMALABmAG4AuwMsACwAMAAsACwAMAApACwALAAxACkALABcAG4AXABuACAAIAAgACAAYQBnAGcAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMQAwAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARwByAGEAaQBuALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEQAbwB3AG4AcwBhAG0AcABsAGUAcwAgAGEAIABhAHIAcgBhAHkAXwAyAEQAIABiAHkAIABhAGcAZwByAGUAZwBhAHQAaQBuAGcAIABvAHYAZQByACAAbgBvAG4AESBvAHYAZQByAGwAYQBwAHAAaQBuAGcAIABzAHAAYQB0AGkAYQBsACAAYgBsAG8AYwBrAHMAXABuACAAIAAgACAAbwBmACAAcwBpAHoAZQAgAGQAZQBwAHQAaAAgANcAIAB3AGkAZAB0AGgALgAgAFAAYQByAHQAaQBhAGwAIABiAGwAbwBjAGsAcwAgAGEAdAAgAHQAaABlACAAZQBkAGcAZQBzACAAYQByAGUAIABpAG4AYwBsAHUAZABlAGQALgAgAFQAaABlAFwAbgAgACAAIAAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGkAcwAgAHAAZQByAGYAbwByAG0AZQBkACAAdQBzAGkAbgBnACAAYQBuACAARQBUAEEAESBjAG8AbQBwAGEAdABpAGIAbABlACAAZgB1AG4AYwB0AGkAbwBuACAAKABlAC4AZwAuACwAIABTAFUATQAsAFwAbgAgACAAIAAgAEEAVgBFAFIAQQBHAEUALAAgAE0AQQBYACwAIABNAEkATgAsACAATQBFAEQASQBBAE4ALAAgAG8AcgAgAGEAIABjAHUAcwB0AG8AbQAgAEwAQQBNAEIARABBACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQAIAAgACAAIAAgACAALQAgADIARAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQBfADIARAAuAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAgACAAIAAgACAAIAAgAC0AIABOAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIABwAGUAcgAgAGIAbABvAGMAawAuAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAgACAAIAAgACAAIAAgAC0AIABOAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABwAGUAcgAgAGIAbABvAGMAawAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgAC0AIABFAFQAQQAgAG8AcgAgAEwAQQBNAEIARABBACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABiAGwAbwBjAGsALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABSAGUAagBlAGMAdABzACAAbgBvAG4AESBhAHIAcgBhAHkAXwAyAEQAIABpAG4AcAB1AHQAcwAuAFwAbgAgACAAIAAgACIgIABSAGUAagBlAGMAdABzACAAaQBuAHYAYQBsAGkAZAAgAGIAbABvAGMAawAgAHMAaQB6AGUAcwAgAG8AcgAgAHQAZQB4AHQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAIiAgAFAAYQByAHQAaQBhAGwAIABiAGwAbwBjAGsAcwAgAGEAcgBlACAAaABhAG4AZABsAGUAZAAgAGEAdQB0AG8AbQBhAHQAaQBjAGEAbABsAHkAIAB2AGkAYQAgAEkATgBEAEUAWAAgACsAIABUAE8AQwBPAEwALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARwByAGEAaQBuALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAsAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgBcAG4ASQBGACgATgBPAFQAKABUAFkAUABFACgAYQByAHIAYQB5AF8AMgBEACkAIAA9ACAANgA0ACkALABcACIAIwBhAHIAcgBhAHkAXwAyAEQAIQBcACIALABcAG4AXABuACAAIAAgACAASQBGACgATwBSACgAZABlAHAAdABoACAAPgAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsACAAdwBpAGQAdABoACAAIAA+ACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwASQBTAFQARQBYAFQAKABkAGUAcAB0AGgAKQAsAEkAUwBUAEUAWABUACgAdwBpAGQAdABoACkAKQAsAFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA8AD4AIAAxADIAOAAsAFwAIgAjAEUAVABBACAARgBVAE4AQwBUAEkATwBOACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAHUAbQBiAGUAcgAgAG8AZgAgAGIAbABvAGMAawBzACAAKAByAG8AdQBuAGQAZQBkACAAdQBwACkAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAVQBQACgAaAAgAC8AIABkAGUAcAB0AGgALAAgADAAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEAFUAUAAoAHcAIAAvACAAdwBpAGQAdABoACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBsAG8AYwBrACAAYQBuAGMAaABvAHIAIABnAHIAaQBkAHMAIAAoAGQAZQBmAGUAcgByAGUAZAApAFwAbgAgACAAIAAgAGQAbwB3AG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAB4ACwAIAAsACAAMQAsACAAZABlAHAAdABoACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHkALAAgADEALAAgADAAKQApACwAXABuACAAIAAgACAAYQBjAHIAbwBzAHMALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoACwAIAB5ACwAIAAxACwAIAB3AGkAZAB0AGgAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwAIAAsACAAMQAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBsAG8AYwBrACAAYQBnAGcAcgBlAGcAYQB0AG8AcgBcAG4AIAAgACAAIABCAGwAbwBjAGsAcwC7AywAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsACAAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkALAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGQAZQBwAHQAaAAsACAALAAgAHIAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIAAxACwAIAAwACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoALAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoACwAIAB3AGkAZAB0AGgALAAgAGMAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgALAAgACwAIAAxACwAIAAwACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABvAGMAawAsACAAIABUAE8AQwBPAEwAKABJAE4ARABFAFgAKABhAHIAcgBhAHkAXwAyAEQALAAgAGkAKAApACwAIABqACgAKQApACwAIAAyACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcwB1AGwAdAAsACAAZgB1AG4AYwB0AGkAbwBuACgAYgBsAG8AYwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcwB1AGwAdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAdABvACAAZQBhAGMAaAAgAGIAbABvAGMAawBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAZABvAHcAbgAoACkALAAgAGEAYwByAG8AcwBzACgAKQAsACAAQgBsAG8AYwBrAHMAuwMpACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAxADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABNAG8AbwByAGUAQQBnAGcAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgATgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUABlAHIAZgBvAHIAbQBzACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAbwB2AGUAcgAgAE0AbwBvAHIAZQAgAG8AcgAgAHYAbwBuACAATgBlAHUAbQBhAG4AbgAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAIAB1AHMAaQBuAGcAIABhAG4AXABuACAAIAAgACAARQBUAEEAESBjAG8AbQBwAGEAdABpAGIAbABlACAAZgB1AG4AYwB0AGkAbwBuACAAKABTAFUATQAsACAAQQBWAEUAUgBBAEcARQAsACAATQBBAFgALAAgAE0ASQBOACwAIABNAEUARABJAEEATgAsACAAbwByACAAYQAgAGMAdQBzAHQAbwBtAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACkALgAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIABjAG8AbgB0AHIAbwBsACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAIAB0AHkAcABlACAAYQBuAGQAIABpAGYAIAB0AGgAZQBcAG4AIAAgACAAIABjAGUAbgB0AGUAcgAgAGMAZQBsAGwAIABpAHMAIAB0AG8AIABiAGUAIABpAG4AYwBsAHUAZABlAGQALgBcAG4AXABuAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAOgBcAG4AIAAgACAAIABNAG8AbwByAGUAIAAoADgAESBjAG8AbgBuAGUAYwB0AGUAZAApADoAIAAgACAAIAAgACAAIAAgAHYAbwBuACAATgBlAHUAbQBhAG4AbgAgACgANAARIGMAbwBuAG4AZQBjAHQAZQBkACkAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAgADIAIAAgADMAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgADQAIAAgAEMAIAAgADYAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAgACAAQwAgACAAMwBcAG4AIAAgACAAIAAgACAAIAAgADcAIAAgADgAIAAgADkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAANABcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMgBEACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AF8AMgBEAC4AXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACAAIAAgACAAIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABMAEEATQBCAEQAQQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAuAFwAbgAgACAAIAAgAFsASQBzAHYAbwBuAE4AZQB1AG0AYQBuAG4APwBdACAALQAgAFQAUgBVAEUAIACSISAAdQBzAGUAIAB2AG8AbgAgAE4AZQB1AG0AYQBuAG4AIABuAGUAaQBnAGgAYgBvAHIAaABvAG8AZAAuAFwAbgAgACAAIAAgAFsAbwBtAGkAdABfAGMAZQBuAHQAZQByAF0AIAAgACAALQAgAFQAUgBVAEUAIACSISAAZQB4AGMAbAB1AGQAZQAgAGMAZQBuAHQAZQByACAAYwBlAGwAbAAgAGYAcgBvAG0AIABhAGcAZwByAGUAZwBhAHQAaQBvAG4ALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ATQBvAG8AcgBlAEEAZwBnALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAFsASQBzAHYAbwBuAE4AZQB1AG0AYQBuAG4APwBdACwAXABuACAAIAAgACAAWwBvAG0AaQB0AF8AYwBlAG4AdABlAHIAXQAsAFwAbgBcAG4ASQBGACgAVABZAFAARQAoAGEAcgByAGEAeQBfADIARAApACAAPAA+ACAANgA0ACwAXAAiACMAYQByAHIAYQB5AF8AMgBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACAALABcACIAIwBFAFQAQQAgAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgAgACAAIAAgAEkAcwB2AG8AbgBOAGUAdQBtAGEAbgBuAD8ALAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgASQBzAHYAbwBuAE4AZQB1AG0AYQBuAG4APwApACkALABcAG4AIAAgACAAIABvAG0AaQB0AF8AYwBlAG4AdABlAHIALAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAG8AbQBpAHQAXwBjAGUAbgB0AGUAcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGEAZAAgAGEAcgByAGEAeQBfADIARAAgAHcAaQB0AGgAIABcACIAbwBtAGkAdABcACIAIAB0AG8AIABzAGEAZgBlAGwAeQAgAGQAcgBvAHAAIABlAGQAZwBlAHMAXABuACAAIAAgACAATQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXAAiAG8AbQBpAHQAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABcACIAbwBtAGkAdABcACIALAAgAGEAcgByAGEAeQBfADIARAAsACAAXAAiAG8AbQBpAHQAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBtAGkAdABcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgBhAGwAIAB2AGUAYwB0AG8AcgBzACAAKABmAGwAYQB0AHQAZQBuAGUAZAApAFwAbgAgACAAIAAgAGEALAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABEAFIATwBQACgATQAsACAALQAyACwAIAAtADIAKQApACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAFcAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAALAAgADEAKQAsACAAaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACkALAAgACAAIAAgACAAIAAgAC8ALwAgAE4AXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAALAAgADIAKQAsACAAaABlAGkAZwBoAHQAKQApACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAE4ARQBcAG4AIAAgACAAIABkACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAtADEAKQAsACAAaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACkALAAgACAAIAAgACAALwAvACAAVwBcAG4AIAAgACAAIABjAGUAbgB0AGUAcgAsACAAVABPAEMATwBMACgAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgAKQApACwAIAAgACAAIAAgACAALwAvACAAQwBcAG4AIAAgACAAIABmACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAAtAHcAaQBkAHQAaAApACkALAAgACAAIAAgACAALwAvACAARQBcAG4AIAAgACAAIABnACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAtADEAKQAsACAALQBoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACkAKQAsACAAIAAgACAALwAvACAAUwBXAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgADEALAAgAC0AMQApACwAIAAtAGgAZQBpAGcAaAB0ACwAIAAtAHcAaQBkAHQAaAApACkALAAgACAAIAAvAC8AIABTAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgADEALAAgADEAKQAsACAALQBoAGUAaQBnAGgAdAAsACAALQB3AGkAZAB0AGgAKQApACwAIAAgACAAIAAvAC8AIABTAEUAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAYQBzAHMAZQBtAGIAbABpAGUAcwBcAG4AIAAgACAAIABNAG8AbwByAGUAXwBuAG8AXwBjAGUAbgB0AGUAcgAsACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACwAYgAsAGMALABkACwAZgAsAGcALABoACwAaQApACwAXABuACAAIAAgACAATQBvAG8AcgBlAF8AdwBpAHQAaABfAGMAZQBuAHQAZQByACwAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsAGIALABjACwAZAAsAGMAZQBuAHQAZQByACwAZgAsAGcALABoACwAaQApACwAXABuAFwAbgAgACAAIAAgAHYAbwBuAF8AbgBvAF8AYwBlAG4AdABlAHIALAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGIALABkACwAZgAsAGgAKQAsAFwAbgAgACAAIAAgAHYAbwBuAF8AdwBpAHQAaABfAGMAZQBuAHQAZQByACwAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGIALABkACwAZgAsAGgALABjAGUAbgB0AGUAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAZwBnAHIAZQBnAGEAdABvAHIAXABuACAAIAAgACAAQQBnAGcAcgBlAGcAYQB0AGUAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAdgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAoAFQATwBDAE8ATAAoAEkARgBTACgAdgAsACAAdgApACwAMgApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AXABuACAAIAAgACAAYQBnAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwB2AG8AbgBOAGUAdQBtAGEAbgBuAD8ALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABvAG0AaQB0AF8AYwBlAG4AdABlAHIALABCAFkAUgBPAFcAKAB2AG8AbgBfAG4AbwBfAGMAZQBuAHQAZQByACwAIABBAGcAZwByAGUAZwBhAHQAZQC7AykALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAHYAbwBuAF8AdwBpAHQAaABfAGMAZQBuAHQAZQByACwAIABBAGcAZwByAGUAZwBhAHQAZQC7AykAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG8AbQBpAHQAXwBjAGUAbgB0AGUAcgAsAEIAWQBSAE8AVwAoAE0AbwBvAHIAZQBfAG4AbwBfAGMAZQBuAHQAZQByACwAIABBAGcAZwByAGUAZwBhAHQAZQC7AykALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAE0AbwBvAHIAZQBfAHcAaQB0AGgAXwBjAGUAbgB0AGUAcgAsACAAQQBnAGcAcgBlAGcAYQB0AGUAuwMpACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcwBoAGEAcABlACAAYgBhAGMAawAgAHQAbwAgAGEAcgByAGEAeQBfADIARABcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFcAUgBBAFAAUgBPAFcAUwAoAGEAZwBnACwAIAB3AGkAZAB0AGgAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMQAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBvAG8AcgBlAFMAZQBsAGUAYwB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAZQBsAGUAYwB0AHMAIABhACAAcwBwAGUAYwBpAGYAaQBjACAAbgBlAGkAZwBoAGIAbwByACAAKAAxABMgOQApACAAZgByAG8AbQAgAHQAaABlACAATQBvAG8AcgBlACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAIABmAG8AcgAgAGUAYQBjAGgAXABuACAAIAAgACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAGEAIABhAHIAcgBhAHkAXwAyAEQALgAgAE4AZQBpAGcAaABiAG8AcgAgAGkAbgBkAGUAeAAgADUAIAByAGUAdAB1AHIAbgBzACAAdABoAGUAIABjAGUAbgB0AGUAcgAgAGMAZQBsAGwALgBcAG4AXABuAE0AbwBvAHIAZQAgAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkADoAXABuACAAIAAgACAAIAAgACAAIAAxACAAIAAgADIAIAAgACAAMwBcAG4AIAAgACAAIAAgACAAIAAgADQAIAAgACAAQwAgACAAIAA2AFwAbgAgACAAIAAgACAAIAAgACAANwAgACAAIAA4ACAAIAAgADkAXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgACAAIAAgAC0AIAAyAEQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAXwAyAEQALgBcAG4AIAAgACAAIABuAGUAaQBnAGgAYgBvAHIAIAAgACAAIAAtACAASQBuAHQAZQBnAGUAcgAgADEAEyA5ACAAaQBuAGQAaQBjAGEAdABpAG4AZwAgAHcAaABpAGMAaAAgAG4AZQBpAGcAaABiAG8AcgAgAHQAbwAgAHIAZQB0AHUAcgBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0AbwBvAHIAZQBTAGUAbABlAGMAdAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABuAGUAaQBnAGgAYgBvAHIALABcAG4AXABuAEkARgAoAFQAWQBQAEUAKABhAHIAcgBhAHkAXwAyAEQAKQAgADwAPgAgADYANAAsAFwAIgAjAGEAcgByAGEAeQBfADIARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABOAE8AVAAoAEEATgBEACgAbgBlAGkAZwBoAGIAbwByACAAPgA9ACAAMQAsACAAbgBlAGkAZwBoAGIAbwByACAAPAA9ACAAOQAsACAATgBPAFQAKABJAFMAVABFAFgAVAAoAG4AZQBpAGcAaABiAG8AcgApACkAKQApACwAXAAiACMATgBFAEkARwBIAEIATwBSACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaABlAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAGQAIABhAHIAcgBhAHkAXwAyAEQAIAB3AGkAdABoACAAegBlAHIAbwBzACAAKABuAG8AIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABuAGUAZQBkAGUAZAApAFwAbgAgACAAIAAgAGgAcABhAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoADAALAAgACwAIAB3AGkAZAB0AGgAIAArACAAMgAsACAAMAApACwAXABuACAAIAAgACAAdgBwAGEAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAMAAsACAAaABlAGkAZwBoAHQALAAgACwAIAAwACkALABcAG4AIAAgACAAIABNACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABoAHAAYQBkACwAIABIAFMAVABBAEMASwAoAHYAcABhAGQALAAgAGEAcgByAGEAeQBfADIARAAsACAAdgBwAGEAZAApACwAIABoAHAAYQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBvAG8AcgBlACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAIABlAHgAdAByAGEAYwB0AGkAbwBuAFwAbgAgACAAIAAgAGEALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgATQAsACAALQAyACwAIAAtADIAKQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATgBXAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgACwAIAAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgAKQAsACAAIAAgACAAIAAgACAALwAvACAATgBcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAsACAAMgApACwAIABoAGUAaQBnAGgAdAApACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAE4ARQBcAG4AIAAgACAAIABkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAtADEAKQAsACAAaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACwAIAAgACAAIAAgAC8ALwAgAFcAXABuACAAIAAgACAAYwBlAG4AdABlAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAAMQApACwAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACkALAAgACAAIAAgACAAIAAvAC8AIABDAFwAbgAgACAAIAAgAGYALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgADEALAAgADEAKQAsACAAaABlAGkAZwBoAHQALAAgAC0AdwBpAGQAdABoACkALAAgACAAIAAgACAALwAvACAARQBcAG4AIAAgACAAIABnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAtADEAKQAsACAALQBoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACkALAAgACAAIAAgAC8ALwAgAFMAVwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAtADEAKQAsACAALQBoAGUAaQBnAGgAdAAsACAALQB3AGkAZAB0AGgAKQAsACAAIAAgAC8ALwAgAFMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAAMQApACwAIAAtAGgAZQBpAGcAaAB0ACwAIAAtAHcAaQBkAHQAaAApACwAIAAgACAAIAAvAC8AIABTAEUAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAGMAawAgAGEAbABsACAAOQAgAG4AZQBpAGcAaABiAG8AcgBzACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkAXABuACAAIAAgACAATQBvAG8AcgBlACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsACAAYgAsACAAYwAsACAAZAAsACAAYwBlAG4AdABlAHIALAAgAGYALAAgAGcALAAgAGgALAAgAGkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbQBwAHUAdABlACAAcwB0AGEAcgB0AGkAbgBnACAAYwBvAGwAdQBtAG4AIABmAG8AcgAgAHQAaABlACAAYwBoAG8AcwBlAG4AIABuAGUAaQBnAGgAYgBvAHIAXABuACAAIAAgACAAcwB0AGEAcgB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAbgBlAGkAZwBoAGIAbwByACAALQAgADEAKQAgACoAIAB3AGkAZAB0AGgAIAArACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAHQAaABlACAAbgBlAGkAZwBoAGIAbwByACAAYgBsAG8AYwBrAFwAbgAgACAAIAAgAHMAZQBsAGUAYwB0AF8AbgBlAGkAZwBoAGIAbwByACwAIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgATQBvAG8AcgBlACwAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIABzAHQAYQByAHQAKQApACwAXABuAFwAbgAgACAAIAAgAHMAZQBsAGUAYwB0AF8AbgBlAGkAZwBoAGIAbwByAFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADEAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEgAaQBzAHQAbwBnAHIAYQBtALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAFMAdABhAHQAaQBzAHQAaQBjAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAGgAaQBzAHQAbwBnAHIAYQBtACAAdQBzAGkAbgBnACAAYQB1AHQAbwBtAGEAdABpAGMAIABiAGkAbgBuAGkAbgBnACAAcgB1AGwAZQBzACAAKABTAHQAdQByAGcAZQBzACwAIABSAGkAYwBlACwAXABuACAAIAAgACAAUwBjAG8AdAB0ACwAIABGAHIAZQBlAGQAbQBhAG4AKQAgAGQAZQBwAGUAbgBkAGkAbgBnACAAbwBuACAAcwBhAG0AcABsAGUAIABzAGkAegBlACAAYQBuAGQAIABzAGsAZQB3AG4AZQBzAHMALgAgAFMAdQBwAHAAbwByAHQAcwAgAGEAbgBcAG4AIAAgACAAIABvAHAAdABpAG8AbgBhAGwAIABmAGkAeABlAGQAIABiAGkAbgAgAHcAaQBkAHQAaAAgAGEAbgBkACAAYQBuACAAbwBwAHQAaQBvAG4AYQBsACAAUABhAHIAZQB0AG8AIAAoAGMAdQBtAHUAbABhAHQAaQB2AGUAIAAlACkAIABjAG8AbAB1AG0AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAATgB1AG0AZQByAGkAYwAgAGEAcgByAGEAeQAgACgAMQBEACAAbwByACAAMgBEACkALgBcAG4AIAAgACAAIABbAGIAaQBuAF8AdwBpAGQAdABoAF0AIAAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQB4AGUAZAAgAGIAaQBuACAAdwBpAGQAdABoACAAKAAwACAAPAAgAHcAaQBkAHQAaAAgAGQiIAAxADAAMAAwACkALgBcAG4AIAAgACAAIABbAGkAbgBjAGwAdQBkAGUAXwBQAGEAcgBlAHQAbwBdACAALQAgAFQAUgBVAEUAIACSISAAaQBuAGMAbAB1AGQAZQAgAGMAdQBtAHUAbABhAHQAaQB2AGUAIAAlACAAYwBvAGwAdQBtAG4ALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABSAGUAdAB1AHIAbgBzACAAIwBWAEEATABVAEUAIQAgAGkAZgAgAGYAZQB3AGUAcgAgAHQAaABhAG4AIAAyACAAdgBhAGwAdQBlAHMAIABhAHIAZQAgAHMAdQBwAHAAbABpAGUAZAAuAFwAbgAgACAAIAAgACIgIABDAGEAcABzACAAdABvAHQAYQBsACAAYgBpAG4AcwAgAGEAdAAgADEAMAAwAC4AXABuACAAIAAgACAAIiAgAEkAZgAgAGIAaQBuAF8AdwBpAGQAdABoACAAaQBzACAAcwB1AHAAcABsAGkAZQBkACwAIABhAHUAdABvAG0AYQB0AGkAYwAgAHIAdQBsAGUAcwAgAGEAcgBlACAAYgB5AHAAYQBzAHMAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEgAaQBzAHQAbwBnAHIAYQBtALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAYgBpAG4AXwB3AGkAZAB0AGgAXQAsAFwAbgAgACAAIAAgAFsAaQBuAGMAbAB1AGQAZQBfAFAAYQByAGUAdABvAF0ALABcAG4AXABuAFwAbgBJAEYAKABDAE8AVQBOAFQAKABhAHIAcgBhAHkAKQAgADwAPQAgADEALAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEEATgBEACgATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGIAaQBuAF8AdwBpAGQAdABoACkAKQAsAE8AUgAoAGIAaQBuAF8AdwBpAGQAdABoACAAPAAgADAALAAgAGIAaQBuAF8AdwBpAGQAdABoACAAPgAgADEAMAAwADAAKQApACwAXAAiACMAQgBJAE4ALQBXAEkARABUAEgAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwBhAG0AcABsAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4AIAAgACAAIABuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVAAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAUwBtAGEAbABsAEQAYQB0AGEAPwAsACAAIAAgACAAIABuACAAPAAgADIAMAAwACwAXABuACAAIAAgACAAQQBkAGQAXwBQAGEAcgBlAHQAbwA/ACwAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAaQBuAGMAbAB1AGQAZQBfAFAAYQByAGUAdABvACkAKQAsAFwAbgBcAG4AIAAgACAAIABtAGkAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABtAGEAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAByAGEAbgBnAGUALAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4ACAALQAgAG0AaQBuACwAXABuACAAIAAgACAAaQBxAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABRAFUAQQBSAFQASQBMAEUAKABhAHIAcgBhAHkALAAgADMAKQAgAC0AIABRAFUAQQBSAFQASQBMAEUAKABhAHIAcgBhAHkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASwBFAFcAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGsAZQB3AGUAZAA/ACwAIAAgACAAIAAgACAASQBGACgAUwBtAGEAbABsAEQAYQB0AGEAPwAsACAARgBBAEwAUwBFACwAIABBAEIAUwAoAHMAKQAgAD4AIAAwAC4AMgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQB4AGUAZAAgAGIAaQBuACAAdwBpAGQAdABoAFwAbgAgACAAIAAgAEkAcwBGAGkAeABlAGQAPwAsACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGIAaQBuAF8AdwBpAGQAdABoACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHUAdABvAG0AYQB0AGkAYwAgAGIAaQBuAG4AaQBuAGcAIAByAHUAbABlAHMAXABuACAAIAAgACAAUwB0AHUAcgBnAGUALAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgATABPAEcAKABuACwAIAAyACkAIAArACAAMQAsACAAMQApACwAXABuACAAIAAgACAAUwBSAFIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAUwBRAFIAVAAoAG4AKQAsACAAMQApACwAXABuACAAIAAgACAAUgBpAGMAZQAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAMgAgACoAIABuAF4AKAAxAC8AMwApACwAIAAxACkALABcAG4AIAAgACAAIABTAGMAbwB0AHQALAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKAAzAC4ANQAgACoAIABTAFQARABFAFYALgBQACgAYQByAHIAYQB5ACkAIAAvACAAbgBeACgAMQAvADMAKQAsACAAMQApACwAXABuACAAIAAgACAARgByAGUAZQBkAG0AYQBuACwAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAMgAgACoAIABpAHEAcgAgAC8AIABuAF4AKAAxAC8AMwApACwAIAAxACkALABcAG4AXABuACAAIAAgACAAZgBpAHgAZQBkACwAIAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAcgBhAG4AZwBlACAALwAgAGIAaQBuAF8AdwBpAGQAdABoACwAIAAxACAALwAgAGIAaQBuAF8AdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBpAG4AIABjAG8AdQBuAHQAIABzAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBGAGkAeABlAGQAPwAsAGYAaQB4AGUAZAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABuACAAPAA9ACAAMwAwACwATQBBAFgAKABTAHQAdQByAGcAZQAsACAAUgBpAGMAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAawBlAHcAZQBkAD8ALABNAEkATgAoAEYAcgBlAGUAZABtAGEAbgAsACAAMQA1ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAUwBjAG8AdAB0ACwAIAAxADUAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHYAbwBpAGQAIABzAGkAbgBnAGwAZQAtAGIAaQBuACAAbwB1AHQAcAB1AHQAOwAgAGMAYQBwACAAYQB0ACAAMQAwADAAXABuACAAIAAgACAAawBfACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAEkARgAoAGsAIAA9ACAAMQAsACAANQAsACAAawApACwAIAAxADAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQBuACAAaQBuAHQAZQByAHYAYQBsAFwAbgAgACAAIAAgAGkAbgB0AGUAcgB2AGEAbAAsACAAIAAgACAAIAAgACAASQBGACgAcgBhAG4AZwBlACAAPQAgADAALAAgADEALAAgAE0AQQBYACgAcgBhAG4AZwBlACAALwAgAGsAXwAsACAAMAAuADEAKQApACwAXABuACAAIAAgACAAYgBpAG4AXwB1AHAAcABlAHIALAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAbQBhAHgALAAgAGkAbgB0AGUAcgB2AGEAbAApACwAXABuACAAIAAgACAAYgBpAG4AXwBsAG8AdwBlAHIALAAgACAAIAAgACAAIABGAEwATwBPAFIAKABtAGkAbgAsACAAaQBuAHQAZQByAHYAYQBsACkALABcAG4AXABuACAAIAAgACAAYgBpAG4AXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAxACAAKwAgACgAYgBpAG4AXwB1AHAAcABlAHIAIAAtACAAYgBpAG4AXwBsAG8AdwBlAHIAKQAgAC8AIABpAG4AdABlAHIAdgBhAGwALAAsAGIAaQBuAF8AbABvAHcAZQByACwAaQBuAHQAZQByAHYAYQBsACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBpAG4AIABsAGEAYgBlAGwAcwBcAG4AIAAgACAAIABiAGkAbgBfAHMAdABhAHIAdAAsACAAIAAgACAAIAAgAEQAUgBPAFAAKABiAGkAbgBfAGEAcgByACwAIAAtADEAKQAsAFwAbgAgACAAIAAgAGIAaQBuAF8AZQBuAGQALAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGIAaQBuAF8AYQByAHIALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABiAGkAbgBfAGgAZQBhAGQAZQByACwAIAAgACAAIAAgAHsAXAAiAFMAdABhAHIAdABcACIALAAgAFwAIgBFAG4AZABcACIALAAgAFwAIgBUAG8AdABhAGwAXAAiAH0ALABcAG4AIAAgACAAIABiAGkAbgBfAGwAYQBiAGUAbABzACwAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAVgBTAFQAQQBDAEsAKABcACIAPABcACIALAAgAGIAaQBuAF8AcwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABUAEEASwBFACgAYgBpAG4AXwBzAHQAYQByAHQALAAgADEAKQAsACAAYgBpAG4AXwBlAG4AZAApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgByAGUAcQB1AGUAbgBjAGkAZQBzACAAYQBuAGQAIABQAGEAcgBlAHQAbwBcAG4AIAAgACAAIABmAHIAZQBxACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABGAFIARQBRAFUARQBOAEMAWQAoAGEAcgByAGEAeQAsACAAYgBpAG4AXwBhAHIAcgApACwAIAAtADEAKQAsAFwAbgAgACAAIAAgAFAAYQByAGUAdABvACwAIAAgACAAIAAgACAAIAAgACAAQgBZAFIATwBXACgAZgByAGUAcQAsACAATABBAE0AQgBEAEEAKAB2ACwAIABQAEUAUgBDAEUATgBUAE8ARgAoAHYALAAgAGYAcgBlAHEAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBpAG4AYQBsACAAYQBzAHMAZQBtAGIAbAB5AFwAbgAgACAAIAAgAHMAdABhAGMAawAsACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABiAGkAbgBfAGgAZQBhAGQAZQByACwAIABIAFMAVABBAEMASwAoAGIAaQBuAF8AbABhAGIAZQBsAHMALAAgAGYAcgBlAHEAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgACAASQBGACgAQQBkAGQAXwBQAGEAcgBlAHQAbwA/ACwAUwBPAFIAVAAoAEgAUwBUAEEAQwBLACgAcwB0AGEAYwBrACwAVgBTAFQAQQBDAEsAKABcACIAQwB1AG0AdQBsAGEAdABpAHYAZQAgACUAXAAiACwAIABQAGEAcgBlAHQAbwApACkALAAzACwALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAYwBrACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAxADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABNAG8AZABlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAFMAdABhAHQAaQBzAHQAaQBjAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQB0AHUAcgBuAHMAIABhACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5ACAAbwBmACAAdABoAGUAIABtAG8AcwB0ACAAZgByAGUAcQB1AGUAbgB0AGwAeQAgAG8AYwBjAHUAcgByAGkAbgBnACAAdgBhAGwAdQBlAHMAIABvAHIAXABuACAAIAAgACAAdABlAHgAdAAgAGUAbgB0AHIAaQBlAHMAIABpAG4AIABhAG4AIABhAHIAcgBhAHkALgAgAFMAdQBwAHAAbwByAHQAcwAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAHQAbwB0AGEAbABzACAAYwBvAGwAdQBtAG4AIABzAGgAbwB3AGkAbgBnAFwAbgAgACAAIAAgAHQAaABlACAAYwBvAHUAbgB0ACAAbwBmACAAZQBhAGMAaAAgAG0AbwBkAGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABBAHIAcgBhAHkAIAAoADEARAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAWwBpAG4AYwBsAHUAZABlAF8AdABvAHQAYQBsAHMAXQAtACAAVABSAFUARQAgAJIhIABpAG4AYwBsAHUAZABlACAAYwBvAHUAbgB0AHMAIABvAGYAIABmAHIAZQBxAHUAZQBuAHQAIAB2AGEAbAB1AGUAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAHQAaABlACAAYQByAHIAYQB5ACAAYwBvAG4AdABhAGkAbgBzACAAbgBvACAAdABlAHgAdAAsACAATQBPAEQARQAuAE0AVQBMAFQAIABpAHMAIAB1AHMAZQBkACAAZgBvAHIAIABuAHUAbQBlAHIAaQBjACAAbQBvAGQAZQAuAFwAbgAgACAAIAAgACIgIABJAGYAIABuAG8AIAByAGUAcABlAGEAdABzACAAZQB4AGkAcwB0ACwAIAByAGUAdAB1AHIAbgBzACAAXAAiACMATgBPAC0AUgBFAFAARQBBAFQAUwAhAFwAIgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAG8AZABlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAaQBuAGMAbAB1AGQAZQBfAHQAbwB0AGEAbABzAF0ALABcAG4AXABuAEkARgAoAEMATwBVAE4AVAAoAC0ALQBJAFMAVABFAFgAVAAoAGEAcgByAGEAeQApACkAIAA9ACAAMAAsAE0ATwBEAEUALgBNAFUATABUACgAYQByAHIAYQB5ACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATQBlAHMAcwBhAGcAZQAgAGYAbwByACAAbgBvACAAcgBlAHAAZQBhAHQAcwBcAG4AIAAgACAAIABtAHMAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAE4ATwAtAFIARQBQAEUAQQBUAFMAIQBcACIALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdAAgAGEAbgBkACAAYwBvAG0AcAB1AHQAZQAgAG0AbwBkAGUAIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAFYALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ATwBEAEUALgBNAFUATABUACgAWABNAEEAVABDAEgAKABWACwAIABWACkAKQAsAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAUwBPAFIAVAAoAEkARgBFAFIAUgBPAFIAKABJAE4ARABFAFgAKABWACwAIABpACkALAAgAG0AcwBnACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AdABhAGwAcwAgAGYAbwByACAAcgBlAHAAZQBhAHQAZQBkACAAdgBhAGwAdQBlAHMAXABuACAAIAAgACAAawBlAGUAcAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMATgBVAE0AQgBFAFIAKABYAE0AQQBUAEMASAAoAFYALAAgAHIAZQBzAHUAbAB0ACkAKQAsAFwAbgAgACAAIAAgAHQAbwB0AGEAbABzACwAIAAgACAAIAAgACAAIAAgACAARwBSAE8AVQBQAEIAWQAoAFYALAAgAFYALAAgAEMATwBVAE4AVABBACwAIAAwACwAIAAwACwAIAAsACAAawBlAGUAcAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBsAGkAdgBlAHIAIAB0AG8AdABhAGwAcwAgAGkAZgAgAHIAZQBxAHUAZQBzAHQAZQBkAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABpAG4AYwBsAHUAZABlAF8AdABvAHQAYQBsAHMALAAgAHIAZQBzAHUAbAB0ACAAPAA+ACAAbQBzAGcAKQAsAHQAbwB0AGEAbABzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBzAHUAbAB0ACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMQA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAWgBvAG4AZQBTAHQAYQB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAFMAdABhAHQAaQBzAHQAaQBjAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEgAaQBzAHQAbwBnAHIAYQBtALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABBAGcAZwByAGUAZwBhAHQAZQBzACAAdgBhAGwAdQBlAHMAIABiAHkAIABcACIAegBvAG4AZQBzAFwAIgAgAGQAZQB0AGUAcgBtAGkAbgBlAGQAIABiAHkAIABIAGkAcwB0AG8AZwByAGEAbQC7Ay4AIABUAGgAZQAgAGIAaQBuACAAdwBpAGQAdABoACAAaQBzAFwAbgAgACAAIAAgAGMAbwBtAHAAdQB0AGUAZAAgAGEAcwAgADEAMABeAG0AIAB3AGgAZQByAGUAIABtACAAaQBzACAAdABoAGUAIABtAG8AcwB0ACAAZgByAGUAcQB1AGUAbgB0ACAAaQBuAHQAZQBnAGUAcgAgAEwATwBHACAAbQBhAGcAbgBpAHQAdQBkAGUAIABvAGYAXABuACAAIAAgACAAdABoAGUAIAB2AGEAbAB1AGUAcwAuACAAUwB1AHAAcABvAHIAdABzACAARQBUAEEAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGEAbgBkACAAYwB1AHMAdABvAG0AIABMAEEATQBCAEQAQQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAALQAgAE4AdQBtAGUAcgBpAGMAIABhAHIAcgBhAHkAIAAoADEARAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAALQAgAEUAVABBACAAbwByACAATABBAE0AQgBEAEEAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABmAHUAbgBjAHQAaQBvAG4AIAAoAGQAZQBmAGEAdQBsAHQAIABTAFUATQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAHIAZQB0AHUAcgBuACAAZgB1AG4AYwB0AGkAbwBuACgAZwByAGkAZAApAC4AXABuACAAIAAgACAAIiAgAE4AbwBuABEgbgB1AG0AZQByAGkAYwAgAGcAcgBpAGQAcwAgAHIAZQB0AHUAcgBuACAAIwBWAEEATABVAEUAIQAuAFwAbgAgACAAIAAgACIgIABaAG8AbgBlAHMAIABhAHIAZQAgAGEAcwBzAGkAZwBuAGUAZAAgAHYAaQBhACAASABpAHMAdABvAGcAcgBhAG0AuwMgAHUAcwBpAG4AZwAgAGEAdQB0AG8AbQBhAHQAaQBjACAAYgBpAG4AbgBpAG4AZwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBaAG8AbgBlAFMAdABhAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABlAGYAYQB1AGwAdAAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsACAAUwBVAE0ALAAgAGYAdQBuAGMAdABpAG8AbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAVgBhAGwAaQBkAGEAdABpAG8AbgAgAC0ALQAtAFwAbgAgACAAIAAgAEkAcwBOAG8AbgBOAHUAbQA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAEkAUwBUAEUAWABUACgAZwByAGkAZAApACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEYAbgA/ACwAIAAgACAAIAAgACAAIAAgACAAVABZAFAARQAoAGYAdQBuAGMAdABpAG8AbgApACAAPAA+ACAAMQAyADgALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABSAE8AVwBTACgAZwByAGkAZAApAD0AMQAsACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQA9ADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBOAG8AbgBOAHUAbQA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABGAG4APwAsACAAIAAgACAAIABcACIAIwBGAFUATgBDAFQASQBPAE4AIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgAGYAdQBuAGMAdABpAG8AbgAoAGcAcgBpAGQAKQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGUAdABlAHIAbQBpAG4AZQAgAGIAaQBuACAAdwBpAGQAdABoACAAZgByAG8AbQAgAG0AYQBnAG4AaQB0AHUAZABlAFwAbgAgACAAIAAgAG0AYQBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgATQBPAEQARQAoAEkATgBUACgATABPAEcAKABnAHIAaQBkACkAKQApACwAIAAxACkALABcAG4AIAAgACAAIABiAGkAbgBfAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAMQAwACAAXgAgAG0AYQBnACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAaQBzAHQAbwBnAHIAYQBtACAAYgBpAG4AcwAgACgAZgBpAHIAcwB0ACAAYwBvAGwAdQBtAG4AIABvAG4AbAB5ACkAXABuACAAIAAgACAAaABpAHMAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgASABpAHMAdABvAGcAcgBhAG0AuwMoAGcAcgBpAGQALAAgAGIAaQBuAF8AdwBpAGQAdABoACkALAAgADIAKQAsACAALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHMAcwBpAGcAbgAgAHoAbwBuAGUAcwBcAG4AIAAgACAAIAB6AG8AbgBlAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGAE4AQQAoAFgATQBBAFQAQwBIACgAZwByAGkAZAAsACAAaABpAHMAdAAsACAALQAxACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKAB6AG8AbgBlAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAGcAZwByAGUAZwBhAHQAZQAgAGIAeQAgAHoAbwBuAGUAXABuACAAIAAgACAAYQBnAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEcAUgBPAFUAUABCAFkAKAB6ACwAIABnACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgACwAIAAwACkALABcAG4AIAAgACAAIAB6AG8AbgBlAF8ASQBEAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAGEAZwBnACwAIAAsACAAMQApACwAXABuACAAIAAgACAAZwByAGkAZABfAHYAYQBsAHUAZQBzACwAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABhAGcAZwAsACAALAAgAC0AMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAcgBvAGEAZABjAGEAcwB0ACAAYQBnAGcAcgBlAGcAYQB0AGUAZAAgAHYAYQBsAHUAZQBzACAAYgBhAGMAawAgAHQAbwAgAGcAcgBpAGQAIABzAGgAYQBwAGUAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAB6AG8AbgBlAHMALAAgAHoAbwBuAGUAXwBJAEQAcwAsACAAZwByAGkAZABfAHYAYQBsAHUAZQBzACwAIAAwACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAFQAWABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAwADcAIAAUICAAVABlAHgAdABcAG4ALwAvACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABUAGgAaQBzACAAYwBhAHQAZQBnAG8AcgB5ACAAcAByAG8AdgBpAGQAZQBzACAAbwBwAGUAcgBhAHQAbwByAHMAIAB0AGgAYQB0ACAAbwB2AGUAcgBjAG8AbQBlACAAYwBvAG0AbQBvAG4AIABsAGkAbQBpAHQAYQB0AGkAbwBuAHMAIABpAG4AXABuACAAIAAgACAARQB4AGMAZQBsACcAcwAgAG4AYQB0AGkAdgBlACAAdABlAHgAdAAgAGUAbgBnAGkAbgBlACAAKABlAC4AZwAuACwAIABUAEUAWABUAFMAUABMAEkAVAAgAGMAYQBuAG4AbwB0ACAAcwBwAGkAbABsACAAMgBEACAAcgBlAHMAdQBsAHQAcwA7ACAAQgBZAFIATwBXAFwAbgAgACAAIAAgAGMAYQBuAG4AbwB0ACAAZABlAHAAbABvAHkAIABTAE8AUgBUACAAdABvACAAYQBsAGkAZwBuACAAYwBvAGwAdQBtAG4AcwApAC4AIABUAGgAZQBzAGUAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGUAbgBhAGIAbABlACAAcwB0AHIAdQBjAHQAdQByAGEAbABcAG4AIAAgACAAIABhAGwAaQBnAG4AbQBlAG4AdAAsACAAZQB4AHQAcgBhAGMAdABpAG8AbgAsACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBvAHIAbQBhAHQAaQBvAG4AIABvAGYAIAB0AGUAeAB0ACAAYQByAHIAYQB5AHMALAAgAGUAeAB0AGUAbgBkAGkAbgBnACAARQB4AGMAZQBsACcAcwBcAG4AIAAgACAAIABjAGEAcABhAGIAaQBsAGkAdABpAGUAcwAgAGYAbwByACAAYgBvAHQAaAAgADEARAAgAGEAbgBkACAAMgBEACAAaQBuAHAAdQB0AHMALgBcAG4AXABuAEYAdQBuAGMAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAEEAbABpAGcAbgC7A1wAbgAgACAAIAAgACAAIAAgACAAUwBvAHIAdABzACAAZQBhAGMAaAAgAHIAbwB3ACAAbwByACAAYwBvAGwAdQBtAG4AIABhAGwAcABoAGEAYgBlAHQAaQBjAGEAbABsAHkALgBcAG4AXABuACAAIAAgACAAIiAgAEEAbABpAGcAbgBEAGkAcwB0AGkAbgBjAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAYQBsAGwAcwAgAEEAbABpAGcAbgC7AyAAdABvACAAcwBvAHIAdAAgAGEAIAAyAEQAIABhAHIAcgBhAHkALAAgAHQAaABlAG4AIAByAGUAdAB1AHIAbgBzACAAZABpAHMAdABpAG4AYwB0ACAAdgBhAGwAdQBlAHMALgBcAG4AXABuACAAIAAgACAAIiAgAEEAbABpAGcAbgBVAG4AaQBxAHUAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAQwBhAGwAbABzACAAQQBsAGkAZwBuALsDIAB0AG8AIABzAG8AcgB0ACAAYQAgADIARAAgAGEAcgByAGEAeQAsACAAdABoAGUAbgAgAHIAZQB0AHUAcgBuAHMAIAB1AG4AaQBxAHUAZQAgAHYAYQBsAHUAZQBzAC4AXABuAFwAbgAgACAAIAAgACIgIABDAG8AYQBsAGUAcwBjAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAG4AbwBuABEgZQBtAHAAdAB5ACAAdgBhAGwAdQBlACAAYQBjAHIAbwBzAHMAIABtAHUAbAB0AGkAcABsAGUAIAAyAEQAIABhAHIAcgBhAHkAcwAgACgAMgAgAHQAbwAgADQAIABpAG4AcAB1AHQAcwApAC4AXABuAFwAbgAgACAAIAAgACIgIABFAHgAcABsAG8AZABlALsDXABuACAAIAAgACAAIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABhACAAcwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGEAbgAgAGUAeABwAGwAbwBkAGUAZAAgAGMAaABhAHIAYQBjAHQAZQByACAAYQByAHIAYQB5AC4AXABuAFwAbgAgACAAIAAgACIgIABOAHUAbQBiAGUAcgBzAE8AbgBsAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAG4AdQBtAGUAcgBpAGMAIAB2AGEAbAB1AGUAcwAgAGYAcgBvAG0AIABhACAAcwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AXABuAFwAbgAgACAAIAAgACIgIABUAGUAeAB0AE8AbgBsAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAHQAZQB4AHQAIAB2AGEAbAB1AGUAcwAgAGYAcgBvAG0AIABhACAAcwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AXABuAFwAbgAgACAAIAAgACIgIABTAHAAbABpAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgAFMAcABsAGkAdABzACAAMQBEACAAdABlAHgAdAAgAGEAcgByAGEAeQBzACAAdQBzAGkAbgBnACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAZABlAGwAaQBtAGkAdABlAHIALAAgAHcAaQB0AGgAIABmAHUAbABsACAAMgBEACAAcwBwAGkAbABsACAAcwB1AHAAcABvAHIAdAAuAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEEAbABpAGcAbgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAFMAcABsAGkAdAC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUwBvAHIAdABzACAAZQBhAGMAaAAgAHIAbwB3ACAAYQBsAHAAaABhAGIAZQB0AGkAYwBhAGwAbAB5ACAAKABkAGUAZgBhAHUAbAB0ACkAIABvAHIAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIAB3AGgAZQBuAFwAbgAgACAAIAAgAGIAeQBfAGMAbwBsACAAPQAgAFQAUgBVAEUALgAgAE8AcgBpAGUAbgB0AGEAdABpAG8AbgAgAGkAcwAgAG4AbwByAG0AYQBsAGkAegBlAGQAIABpAG4AdABlAHIAbgBhAGwAbAB5ACAAcwBvACAAdABoAGUAXABuACAAIAAgACAAcwBhAG0AZQAgAHAAaQBwAGUAbABpAG4AZQAgAGgAYQBuAGQAbABlAHMAIABiAG8AdABoACAAbQBvAGQAZQBzAC4AIABTAG8AcgB0AGkAbgBnACAAaQBzACAAbABlAHgAaQBjAG8AZwByAGEAcABoAGkAYwBcAG4AIAAgACAAIABhAG4AZAAgAGMAYQBzAGUAESBzAGUAbgBzAGkAdABpAHYAZQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABhAGwAaQBnAG4AZQBkAC4AXABuACAAIAAgACAAWwBiAHkAXwBjAG8AbABdACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAuACAAVABSAFUARQAgAJIhIABzAG8AcgB0ACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAdABvAHAAESB0AG8AESBiAG8AdAB0AG8AbQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAG0AaQB0AHQAZQBkACAAkiEgAHMAbwByAHQAIABlAGEAYwBoACAAcgBvAHcAIABsAGUAZgB0ABEgdABvABEgcgBpAGcAaAB0AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAFQARQBYAFQASgBPAEkATgAgACsAIABTAHAAbABpAHQAuwMgAGYAbwByACAAZgBhAHMAdAAgAHIAbwB3ABEgdwBpAHMAZQAgAGMAYQBuAG8AbgBpAGMAYQBsAGkAegBhAHQAaQBvAG4ALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQQBsAGkAZwBuALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAYgB5AF8AYwBvAGwAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGUAdABlAHIAbQBpAG4AZQAgAHMAbwByAHQAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAASQBzAFIAbwB3AFMAbwByAHQAPwAsACAASQBTAE8ATQBJAFQAVABFAEQAKABiAHkAXwBjAG8AbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuACAAKABhAGwAdwBhAHkAcwAgAHMAbwByAHQAIAByAG8AdwBzACkAXABuACAAIAAgACAAYQByAHIAYQB5ACwAIAAgACAAIAAgACAASQBGACgASQBzAFIAbwB3AFMAbwByAHQAPwAsACAAYQByAHIAYQB5ACwAIABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBvAHcAESB3AGkAcwBlACAAcwBvAHIAdAAgAJIhIABzAGMAYQBsAGEAcgAgAGoAbwBpAG4AIAB3AGkAdABoACAAaQBuAHYAaQBzAGkAYgBsAGUAIABzAGUAcABhAHIAYQB0AG8AcgBcAG4AIAAgACAAIABpAG4AdgBpAHMALAAgACAAIAAgACAAIABVAE4ASQBDAEgAQQBSACgAOAAyADkAMQApACwAXABuACAAIAAgACAAUgBvAHcAUwBvAHIAdAC7AywAIAAgACAATABBAE0AQgBEAEEAKAB2ACwAIABUAEUAWABUAEoATwBJAE4AKABpAG4AdgBpAHMALAAgACwAIABTAE8AUgBUACgAdgAsACAALAAgACwAIAAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBuAHYAZQByAHQAIABlAGEAYwBoACAAcgBvAHcAIAB0AG8AIABhACAAagBvAGkAbgBlAGQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIABqAG8AaQBuAGUAZAAsACAAIAAgACAAIABCAFkAUgBPAFcAKABhAHIAcgBhAHkALAAgAFIAbwB3AFMAbwByAHQAuwMpACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAcABsAGkAdAAgAGIAYQBjAGsAIABpAG4AdABvACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIABlAHgALAAgACAAIAAgACAAIAAgACAAIABTAHAAbABpAHQAuwMoAGoAbwBpAG4AZQBkACwAIABpAG4AdgBpAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcwB0AG8AcgBlACAAbwByAGkAZwBpAG4AYQBsACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBSAG8AdwBTAG8AcgB0AD8ALAAgAGUAeAAsACAAVABSAEEATgBTAFAATwBTAEUAKABlAHgAKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYADAAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEEAbABpAGcAbgBEAGkAcwB0AGkAbgBjAHQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABBAGwAaQBnAG4AuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAYQBsAGwAcwAgAEEAbABpAGcAbgC7AyAAdABvACAAYQBsAHAAaABhAGIAZQB0AGkAYwBhAGwAbAB5ACAAcwBvAHIAdAAgAGUAYQBjAGgAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACwAIAB0AGgAZQBuACAAcgBlAHQAdQByAG4AcwBcAG4AIAAgACAAIABkAGkAcwB0AGkAbgBjAHQAIAB2AGEAbAB1AGUAcwAgAGEAbABvAG4AZwAgAHQAaABlACAAcwBhAG0AZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABhAGwAaQBnAG4AZQBkACAAYQBuAGQAIABkAGUAZAB1AHAAbABpAGMAYQB0AGUAZAAuAFwAbgAgACAAIAAgAFsAYgB5AF8AYwBvAGwAXQAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwALgAgAFQAUgBVAEUAIACSISAAbwBwAGUAcgBhAHQAZQAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQAuACAATwBtAGkAdAB0AGUAZAAgAJIhIAByAG8AdwARIHcAaQBzAGUALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABEAEkAUwBUAEkATgBDAFQAIAByAGUAbQBvAHYAZQBzACAAZQB4AGEAYwB0ACAAZAB1AHAAbABpAGMAYQB0AGUAcwAuAFwAbgAgACAAIAAgACIgIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABpAHMAIABwAHIAZQBzAGUAcgB2AGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBBAGwAaQBnAG4ARABpAHMAdABpAG4AYwB0ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAYgB5AF8AYwBvAGwAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABmAGwAYQBnAFwAbgAgACAAIAAgAFMAbwByAHQAQgB5AEMAbwBsAD8ALAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABiAHkAXwBjAG8AbAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBsAGkAZwBuAG0AZQBuAHQAXABuACAAIAAgACAAYQBsAGkAZwBuAGUAZAAsACAAIAAgACAAQQBsAGkAZwBuALsDKABhAHIAcgBhAHkALAAgAGIAeQBfAGMAbwBsACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHMAdABpAG4AYwB0ACAAcgBlAG0AbwB2AGEAbABcAG4AIAAgACAAIAB1ACwAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAGEAbABpAGcAbgBlAGQALAAgAFMAbwByAHQAQgB5AEMAbwBsAD8ALAAgAFQAUgBVAEUAKQAsAFwAbgBcAG4AIAAgACAAIAB1AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQQBsAGkAZwBuAFUAbgBpAHEAdQBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAQQBsAGkAZwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAGEAbABsAHMAIABBAGwAaQBnAG4AuwMgAHQAbwAgAGEAbABwAGgAYQBiAGUAdABpAGMAYQBsAGwAeQAgAHMAbwByAHQAIABlAGEAYwBoACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAsACAAdABoAGUAbgAgAHIAZQB0AHUAcgBuAHMAXABuACAAIAAgACAAdQBuAGkAcQB1AGUAIAB2AGEAbAB1AGUAcwAgAGEAbABvAG4AZwAgAHQAaABlACAAcwBhAG0AZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABhAGwAaQBnAG4AZQBkACAAYQBuAGQAIABkAGUAZAB1AHAAbABpAGMAYQB0AGUAZAAuAFwAbgAgACAAIAAgAFsAYgB5AF8AYwBvAGwAXQAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwALgAgAFQAUgBVAEUAIACSISAAbwBwAGUAcgBhAHQAZQAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQAuACAATwBtAGkAdAB0AGUAZAAgAJIhIAByAG8AdwARIHcAaQBzAGUALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABVAE4ASQBRAFUARQAgAHIAZQBtAG8AdgBlAHMAIAByAGUAcABlAGEAdABlAGQAIAByAG8AdwBzAC8AYwBvAGwAdQBtAG4AcwAgAGIAdQB0ACAAcAByAGUAcwBlAHIAdgBlAHMAIABmAGkAcgBzAHQAIABvAGMAYwB1AHIAcgBlAG4AYwBlAHMALgBcAG4AIAAgACAAIAAiICAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQQBsAGkAZwBuAFUAbgBpAHEAdQBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAYgB5AF8AYwBvAGwAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABmAGwAYQBnAFwAbgAgACAAIAAgAFMAbwByAHQAQgB5AEMAbwBsAD8ALAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABiAHkAXwBjAG8AbAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBsAGkAZwBuAG0AZQBuAHQAXABuACAAIAAgACAAYQBsAGkAZwBuAGUAZAAsACAAIAAgACAAQQBsAGkAZwBuALsDKABhAHIAcgBhAHkALAAgAGIAeQBfAGMAbwBsACkALABcAG4AXABuACAAIAAgACAALwAvACAAVQBuAGkAcQB1AGUAIAByAGUAbQBvAHYAYQBsAFwAbgAgACAAIAAgAHUALAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAYQBsAGkAZwBuAGUAZAAsACAAUwBvAHIAdABCAHkAQwBvAGwAPwApACwAXABuAFwAbgAgACAAIAAgAHUAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABDAG8AYQBsAGUAcwBjAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABmAGkAcgBzAHQAIABuAG8AbgARIGUAbQBwAHQAeQAgAHYAYQBsAHUAZQAgAGEAYwByAG8AcwBzACAAbQB1AGwAdABpAHAAbABlACAAMgBEACAAYQByAHIAYQB5AHMAIAAoADIAIAB0AG8AIAA0ACAAaQBuAHAAdQB0AHMAKQAsAFwAbgAgACAAIAAgAGUAdgBhAGwAdQBhAHQAZQBkACAAaQBuACAAcAByAGkAbwByAGkAdAB5ACAAbwByAGQAZQByADoAXABuAFwAbgAgACAAIAAgACAAIAAgACAAYQByAHIAYQB5AF8AMQAgAJIhIABhAHIAcgBhAHkAXwAyACAAkiEgAGEAcgByAGEAeQBfADMAIACSISAAYQByAHIAYQB5AF8ANAAgAJIhIABmAGkAbABsAF8AdgBhAGwAdQBlAFwAbgBcAG4AIAAgACAAIABBACAAYwBlAGwAbAAgAGkAcwAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABcACIAZQBtAHAAdAB5AFwAIgAgAGkAZgAgAGkAdAAgAG0AYQB0AGMAaABlAHMAIABhAG4AeQAgAG8AZgAgAHQAaABlACAAZgBvAGwAbABvAHcAaQBuAGcAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABMAEUATgAoAGMAZQBsAGwAKQAgAD0AIAAwAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAGMAZQBsAGwAIAA9ACAARgBBAEwAUwBFAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAGMAZQBsAGwAIAA9ACAAaQBnAG4AbwByAGUAIAAgACAAKAB1AHMAZQByABEgcwBwAGUAYwBpAGYAaQBlAGQAKQBcAG4AXABuACAAIAAgACAARQBtAHAAdAB5ACAAYwBlAGwAbABzACAAYQByAGUAIABzAGsAaQBwAHAAZQBkACAAdwBoAGUAbgAgAGQAZQB0AGUAcgBtAGkAbgBpAG4AZwAgAHQAaABlACAAbwB1AHQAcAB1AHQAIAB2AGEAbAB1AGUALgAgAFQAaABpAHMAIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAXABuACAAIAAgACAAdQBzAGUAZgB1AGwAIABmAG8AcgAgAHIAZQBjAG8AbQBwAG8AcwBpAG4AZwAgAG0AYQBzAGsAZQBkACAAbwByACAAbABhAHkAZQByAGUAZAAgAGEAcgByAGEAeQBzACAAKABlAC4AZwAuACwAIAByAGkAbgBnAHMAKQAgAGkAbgB0AG8AIABhACAAcwBpAG4AZwBsAGUAXABuACAAIAAgACAAYwBvAGgAZQByAGUAbgB0ACAAZwByAGkAZAAgAGEAZgB0AGUAcgAgAHQAcgBhAG4AcwBmAG8AcgBtAGEAdABpAG8AbgBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAzAF0AIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAaQBnAG4AbwByAGUAXQAgACAAIAAgACAAIAAtACAAVgBhAGwAdQBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgAGUAbQBwAHQAeQAgAGQAdQByAGkAbgBnACAAbwBjAGMAdQBwAGEAbgBjAHkAIABlAHYAYQBsAHUAYQB0AGkAbwBuAC4AXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0AIAAgAC0AIABTAGMAYQBsAGEAcgAgAHUAcwBlAGQAIAB3AGgAZQBuACAAYQBsAGwAIABhAHIAcgBhAHkAcwAgAHMAdQBwAHAAbAB5ACAAYQBuACAAZQBtAHAAdAB5ACAAdgBhAGwAdQBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEMAbwBhAGwAZQBzAGMAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACwAIABhAHIAcgBhAHkAXwAyACwAIABbAGEAcgByAGEAeQBfADMAXQAsACAAWwBhAHIAcgBhAHkAXwA0AF0ALABcAG4AIAAgACAAIABbAGkAZwBuAG8AcgBlAF0ALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABhAHIAcgBhAHkAIABwAHIAZQBzAGUAbgBjAGUAXABuACAAIAAgACAASQBuAGMAbAB1AGQAZQAzACwAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMwApACkALABcAG4AIAAgACAAIABJAG4AYwBsAHUAZABlADQALAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwA0ACkAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADMALAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkALAAgAEYAQQBMAFMARQAsACAAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8ANAAsACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADQAKQAsACAARgBBAEwAUwBFACwAIABhAHIAcgBhAHkAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQBtAHAAdAB5ABEgdgBhAGwAdQBlACAAcgB1AGwAZQBzAFwAbgAgACAAIAAgAGkAZwBuAG8AcgBlACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABpAGcAbgBvAHIAZQApACwAIABcACIAXAAiACwAIABpAGcAbgBvAHIAZQApACwAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAXAAiAFwAIgAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMQApACwAIAAgACAAIAAgACAAdwAsACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAxACkALABcAG4AIAAgACAAIABoAIIgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyACkALAAgACAAIAAgACAAIAB3AIIgLAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGgAgyAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADMAKQAsACAAIAAgACAAIAAgAHcAgyAsACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAaACEICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8ANAApACwAIAAgACAAIAAgACAAdwCEICwAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AIABtAGkAcwBtAGEAdABjAGgAZQBzAFwAbgAgACAAIAAgAFMAXwAyACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAaAAgADwAPgAgAGgAgiAsACAAdwAgADwAPgAgAHcAgiApACwAXABuACAAIAAgACAAUwBfADMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAG4AYwBsAHUAZABlADMAIAAqACAATwBSACgAaAAgADwAPgAgAGgAgyAsACAAdwAgADwAPgAgAHcAgyApACwAXABuACAAIAAgACAAUwBfADQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAG4AYwBsAHUAZABlADQAIAAqACAATwBSACgAaAAgADwAPgAgAGgAhCAsACAAdwAgADwAPgAgAHcAhCApACwAXABuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAATwBSACgAUwBfADIALAAgAFMAXwAzACwAIABTAF8ANAApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsAFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBjAGMAdQBwAGEAbgBjAHkAIAB0AGUAcwB0AFwAbgAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AywAIAAgAEwAQQBNAEIARABBACgAYQByAHIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAKABhAHIAcgAgADwAPgAgAEYAQQBMAFMARQApACAAKgAoAEwARQBOACgAYQByAHIAKQAgADwAPgAgADAAKQAgACoAIAAoAGEAcgByACAAPAA+ACAAaQBnAG4AbwByAGUAKQApACkALABcAG4AXABuACAAIAAgACAAbQBfADEALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwAxACkALABcAG4AIAAgACAAIABtAF8AMgAsACAAIAAgACAAIAAgACAAIABPAGMAYwB1AHAAaQBlAGQAuwMoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAG0AXwAzACwAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AygAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAbQBfADQALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUAByAGkAbwByAGkAdAB5ACAAYwBoAGEAaQBuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAEkARgAoAG0AXwAxACgAKQAsACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBfADIAKAApACwAIABhAHIAcgBhAHkAXwAyACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG0AXwAzACgAKQAsACAAYQByAHIAYQB5AF8AMwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG0AXwA0ACgAKQAsACAAYQByAHIAYQB5AF8ANAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACkAKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAwADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABFAHgAcABsAG8AZABlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAATQBHAHIAaQBkALsDLAAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABhACAAcwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGEAbgAgAGUAeABwAGwAbwBkAGUAZAAgAGMAaABhAHIAYQBjAHQAZQByACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAARQB4AHAAbABvAHMAaQBvAG4AIABiAGUAaABhAHYAaQBvAHIAIABkAGUAcABlAG4AZABzACAAbwBuACAAdABoAGUAIABpAG4AcAB1AHQAIABzAGgAYQBwAGUAOgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGUAeABwAGwAbwBkAGUAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABWAGUAcgB0AGkAYwBhAGwAIAAxAEQAIABhAHIAcgBhAHkAcwAgAGUAeABwAGwAbwBkAGUAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABIAG8AcgBpAHoAbwBuAHQAYQBsACAAMQBEACAAYQByAHIAYQB5AHMAIABlAHgAcABsAG8AZABlACAAcgBvAHcAESB3AGkAcwBlAC4AXABuACAAIAAgACAAIAAgACAAIAAiICAAMgBEACAAYQByAHIAYQB5AHMAIABlAHgAcABsAG8AZABlACAAcgBvAHcAESB3AGkAcwBlACAAYgB5ACAAZABlAGYAYQB1AGwAdAAsACAAbwByACAAdwBpAGQAdABoABEgdwBpAHMAZQAgAHcAaABlAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAZQB4AHAAbABvAGQAZQBfADIARABfAGIAeQBjAG8AbAAgAD0AIABUAFIAVQBFAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABjAGEAbgAgAGIAZQAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAG8AcgAgADIARAAuAFwAbgAgACAAIAAgAFsAZQB4AHAAbABvAGQAZQBfADIARABfAGIAeQBjAG8AbABdACAAIAAtACAATwBwAHQAaQBvAG4AYQBsAC4AIABUAFIAVQBFACAAkiEgAGUAeABwAGwAbwBkAGUAIAAyAEQAIABhAHIAcgBhAHkAcwAgAHcAaQBkAHQAaAARIHcAaQBzAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AbQBpAHQAdABlAGQAIACSISAAZQB4AHAAbABvAGQAZQAgAHIAbwB3ABEgdwBpAHMAZQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEwARQBOACgAYQByAHIAYQB5ACkAIABkAGUAdABlAHIAbQBpAG4AZQBzACAAdABoAGUAIABtAGEAeABpAG0AdQBtACAAYwBoAGEAcgBhAGMAdABlAHIAIABjAG8AdQBuAHQAIABwAGUAcgAgAGMAZQBsAGwALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARQB4AHAAbABvAGQAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGUAeABwAGwAbwBkAGUAXwAyAEQAXwBiAHkAYwBvAGwAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwBlAG8AbQBlAHQAcgB5ACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAIAAgACAAaAAgAD4AIAB3ACwAXABuACAAIAAgACAASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAsACAAIAB3ACAAPgAgAGgALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPgAgADEALAAgAHcAIAA+ACAAMQApACwAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA+ACAAMQAsACAAdwAgAD4AIAAxACkALABcAG4AIAAgACAAIABEAGkAcgBPAG0AaQB0AHQAZQBkAD8ALAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAZQB4AHAAbABvAGQAZQBfADIARABfAGIAeQBjAG8AbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAZQB4AHAAbABvAHMAaQBvAG4AXABuACAAIAAgACAARQB4AHAAbABvAGQAZQBTAGMAYQBsAGEAcgAsACAAIABSAEUARwBFAFgARQBYAFQAUgBBAEMAVAAoAGEAcgByAGEAeQAsACAAXAAiAC4AXAAiACwAIAAxACkALABcAG4AXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALABFAHgAcABsAG8AZABlAFMAYwBhAGwAYQByACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4AGkAbQB1AG0AIABjAGgAYQByAGEAYwB0AGUAcgBzACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGMAZQBsAGwAcwBcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAEwARQBOACgAYQByAHIAYQB5ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgADEARAAgAGkAbgBkAGUAeABpAG4AZwAgAC0ALQAtAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAUwBFAFEAVQBFAE4AQwBFACgALAAgAG0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAbQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgADIARAAgAGkAbgBkAGUAeABpAG4AZwAgACgAdgBlAHIAdABpAGMAYQBsACAAZQB4AHAAbABvAHMAaQBvAG4AKQAgAC0ALQAtAFwAbgAgACAAIAAgAGkAXwAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAIABSAGUAcwBpAHoAZQC7AygAIABJAE4AVAAoAFMARQBRAFUARQBOAEMARQAoAG0AIAAqACAAaAAsACAALAAgACwAIAAxACAALwAgAG0AKQApACwAIAAsACAAdwAgACkAIAApACwAXABuACAAIAAgACAAagBfACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAAgAFIAZQBzAGkAegBlALsDKAAgAE0ARwByAGkAZAC7AygAYQByAHIAYQB5ACwAIAAxACkALAAgAG0AIAApACAAKQAsAFwAbgAgACAAIAAgAHMAdABhAHIAdABfAGEAdABfACwAIAAgAEwAQQBNAEIARABBACgAIABSAGUAcwBpAHoAZQC7AygAIABTAEUAUQBVAEUATgBDAEUAKABtACkALAAgAGgALAAgAHcAIAApACAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgADIARAAgAGkAbgBkAGUAeABpAG4AZwAgACgAaABvAHIAaQB6AG8AbgB0AGEAbAAgAGUAeABwAGwAbwBzAGkAbwBuACkAIAAtAC0ALQBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAUgBlAHMAaQB6AGUAuwMoACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkAKQAsACAALAAgAG0AIAApACAAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAIABSAGUAcwBpAHoAZQC7AygAIABJAE4AVAAoAFMARQBRAFUARQBOAEMARQAoACwAIABtACAAKgAgAHcALAAgACwAIAAxACAALwAgAG0AKQApACwAIABoACAAKQAgACkALABcAG4AIAAgACAAIABzAHQAYQByAHQAXwBhAHQALAAgACAAIABMAEEATQBCAEQAQQAoACAAUgBlAHMAaQB6AGUAuwMoACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG0AKQAsACAAaAAsACAAdwAgACkAIAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADEARAAgAGUAeABwAGwAbwBzAGkAbwBuAFwAbgAgACAAIAAgAGUAeAAxAEQALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAIABNAEkARAAoAGEAcgByAGEAeQAsACAAaQBkAHgAKAApACwAIAAxACkAIAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADIARAAgAGUAeABwAGwAbwBzAGkAbwBuACAAdgBhAHIAaQBhAG4AdABzAFwAbgAgACAAIAAgAGUAeAAyAEQAXwBWACwAIAAgACAAIAAgAEwAQQBNAEIARABBACgAIABNAEkARAAoAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAaQBfACgAKQAsACAAagBfACgAKQApACwAIABzAHQAYQByAHQAXwBhAHQAXwAoACkALAAgADEAKQAgACkALABcAG4AIAAgACAAIABlAHgAMgBEAF8ASAAsACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAATQBJAEQAKABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAGkAKAApACwAIAAgAGoAKAApACkALAAgAHMAdABhAHIAdABfAGEAdAAoACkALAAgACAAMQApACAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAyAEQAIABzAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIABlAHgAMgBEACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAEQAaQByAE8AbQBpAHQAdABlAGQAPwAsAGUAeAAyAEQAXwBWACgAKQAsAGUAeAAyAEQAXwBIACgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBpAG4AYQBsACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABlAHgAMQBEACgAKQAsACAAZQB4ADIARAAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAATgB1AG0AYgBlAHIAcwBPAG4AbAB5ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQB4AHAAbABvAGQAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAbgB1AG0AZQByAGkAYwAgAGMAaABhAHIAYQBjAHQAZQByAHMAIAAoADAAEyA5ACkAIABmAHIAbwBtACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABzAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABVAHMAZQBzACAARQB4AHAAbABvAGQAZQC7AyAAZgBvAHIAIABjAGgAYQByAGEAYwB0AGUAcgARIGwAZQB2AGUAbAAgAGUAeABwAGEAbgBzAGkAbwBuAC4AXABuACAAIAAgACAAIiAgAEMATwBEAEUAKAApACAAZgBpAGwAdABlAHIAaQBuAGcAIABlAG4AcwB1AHIAZQBzACAAcwB0AHIAaQBjAHQAIABkAGkAZwBpAHQAIABlAHgAdAByAGEAYwB0AGkAbwBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE4AdQBtAGIAZQByAHMATwBuAGwAeQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdAAgAGkAZgAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABhAHIAcgBhAHkALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABUAFkAUABFACgAYQByAHIAYQB5ACkAIAA8AD4AIAA2ADQALAAgAGEAcgByAGEAeQAsAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHAAbABvAGQAZQAgAHQAbwAgAGMAaABhAHIAYQBjAHQAZQByAHMAXABuACAAIAAgACAAZQB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQB4AHAAbABvAGQAZQC7AygAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAGcAaQB0ACAAbQBhAHMAawBcAG4AIAAgACAAIABLAGUAZQBwACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAKABDAE8ARABFACgAZQB4ACkAIAA+AD0AIAA0ADgAKQAgACoAIAAoAEMATwBEAEUAKABlAHgAKQAgADwAPQAgADUANwApACwAIABGAEEATABTAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAcwBrAGUAZAAgAHIAZQBzAHUAbAB0AFwAbgAgACAAIAAgAFIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEsAZQBlAHAALAAgAGUAeAAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADEARAAgAGMAbwBuAGMAYQB0AGUAbgBhAHQAZQBkACAAbwB1AHQAcAB1AHQAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEIAWQBSAE8AVwAoAFIAZQBzAHUAbAB0ACwAIABDAE8ATgBDAEEAVAApACAAKwAgADAALABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABPAG4AbAB5ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQB4AHAAbABvAGQAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAbgBvAG4AESBuAHUAbQBlAHIAaQBjACAAYwBoAGEAcgBhAGMAdABlAHIAcwAgAGYAcgBvAG0AIABhACAAcwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgAEkAbgBwAHUAdAAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABFAHgAcABsAG8AZABlALsDIABmAG8AcgAgAGMAaABhAHIAYQBjAHQAZQByABEgbABlAHYAZQBsACAAZQB4AHAAYQBuAHMAaQBvAG4ALgBcAG4AIAAgACAAIAAiICAAQwBvAG0AcABsAGUAbQBlAG4AdABzACAATgB1AG0AYgBlAHIAcwBPAG4AbAB5ALsDIABiAHkAIABzAGUAbABlAGMAdABpAG4AZwAgAGEAbABsACAAbgBvAG4AESBkAGkAZwBpAHQAIABjAGgAYQByAGEAYwB0AGUAcgBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAZQB4AHQATwBuAGwAeQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdAAgAGkAZgAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABhAHIAcgBhAHkALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABUAFkAUABFACgAYQByAHIAYQB5ACkAIAA8AD4AIAA2ADQALAAgAGEAcgByAGEAeQAsAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHAAbABvAGQAZQAgAHQAbwAgAGMAaABhAHIAYQBjAHQAZQByAHMAXABuACAAIAAgACAAZQB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQB4AHAAbABvAGQAZQC7AygAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAG4AESBkAGkAZwBpAHQAIABtAGEAcwBrAFwAbgAgACAAIAAgAEsAZQBlAHAALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAoAEMATwBEAEUAKABlAHgAKQAgADwAIAA0ADgAKQAgACsAIAAoAEMATwBEAEUAKABlAHgAKQAgAD4AIAA1ADcAKQAsACAARgBBAEwAUwBFACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHMAawBlAGQAIAByAGUAcwB1AGwAdABcAG4AIAAgACAAIABSAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIABJAEYAKABLAGUAZQBwACwAIABlAHgALAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABjAG8AbgBjAGEAdABlAG4AYQB0AGUAZAAgAG8AdQB0AHAAdQB0AFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABCAFkAUgBPAFcAKABSAGUAcwB1AGwAdAAsACAAQwBPAE4AQwBBAFQAKQAsAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAwADgAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABTAHAAbABpAHQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABSAGUAZwBlAHgAUwBhAGYAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUwBwAGwAaQB0AHMAIAAxAEQAIAB0AGUAeAB0ACAAYQByAHIAYQB5AHMAIABpAG4AdABvACAAdABvAGsAZQBuAHMAIAB1AHMAaQBuAGcAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAIABkAGUAbABpAG0AaQB0AGUAcgAuACAAVABoAGUAIABmAHUAbgBjAHQAaQBvAG4AXABuACAAIAAgACAAaQBzACAAcwBoAGEAcABlABEgYQB3AGEAcgBlACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAYQAgADIARAAgAHMAcABpAGwAbAAgAGEAbABpAGcAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAgAG8AZgAgAHQAaABlAFwAbgAgACAAIAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuACAAUwB1AHAAcABvAHIAdABzACAAbQB1AGwAdABpABEgYwBoAGEAcgBhAGMAdABlAHIAIABkAGUAbABpAG0AaQB0AGUAcgBzACAAYQBuAGQAIABmAHUAbABsACAAcgBlAGcAZQB4ABEgcwBhAGYAZQBcAG4AIAAgACAAIABlAHMAYwBhAHAAaQBuAGcALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAGEAcgByAGEAeQAgACgAdgBlAHIAdABpAGMAYQBsACAAbwByACAAaABvAHIAaQB6AG8AbgB0AGEAbAApAC4AIAAyAEQAIABhAHIAcgBhAHkAcwAgAGEAcgBlACAAbgBvAHQAIABzAHUAcABwAG8AcgB0AGUAZAAuAFwAbgAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByACAAIAAgAC0AIABEAGUAbABpAG0AaQB0AGUAcgAgAHUAcwBlAGQAIAB0AG8AIABzAHAAbABpAHQAIABlAGEAYwBoACAAdABlAHgAdAAgAGUAbABlAG0AZQBuAHQALgAgAFMAcABpAGwAbAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBzACAAaQBuAGYAZQByAHIAZQBkACAAZgByAG8AbQAgAHQAaABlACAAcwBoAGEAcABlACAAbwBmACAAYQByAHIAYQB5AC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkAF0AXABuACAAIAAgACAAIAAgACAAIABWAGEAbAB1AGUAIAByAGUAdAB1AHIAbgBlAGQAIAB3AGgAZQBuACAAYQAgAHQAZQB4AHQAIABlAGwAZQBtAGUAbgB0ACAAYwBvAG4AdABhAGkAbgBzACAAbgBvACAAZABlAGwAaQBtAGkAdABlAHIALgBcAG4AIAAgACAAIAAgACAAIAAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAFwAIgBcACIALgBcAG4AXABuACAAIAAgACAAWwB0AHIAZQBhAHQAXwBjAG8AbgBzAGUAYwB1AHQAaQB2AGUAXwBkAGUAbABpAG0AaQB0AGUAcgBzAF8AYQBzAF8AbwBuAGUAXQBcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBVAEUAIACSISAAYwBvAGwAbABhAHAAcwBlACAAcgB1AG4AcwAgAG8AZgAgAGMAbwBuAHMAZQBjAHUAdABpAHYAZQAgAGQAZQBsAGkAbQBpAHQAZQByAHMAIABiAGUAZgBvAHIAZQAgAHMAcABsAGkAdAB0AGkAbgBnAC4AXABuACAAIAAgACAAIAAgACAAIABVAHMAZQBmAHUAbAAgAGYAbwByACAAQwBTAFYAESBzAHQAeQBsAGUAIABuAG8AcgBtAGEAbABpAHoAYQB0AGkAbwBuAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQwBvAGwAbABhAHAAcwBlACAAbQBvAGQAZQAgAHAAZQByAGYAbwByAG0AcwAgAGEAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAgAHAAYQBzAHMAIAB3AGgAZQBuACAAYwBvAG4AcwBlAGMAdQB0AGkAdgBlACAAZABlAGwAaQBtAGkAdABlAHIAcwAgAGUAeABpAHMAdAAuAFwAbgAgACAAIAAgACAAIABGAG8AcgAgAHYAZQByAHkAIABsAGEAcgBnAGUAIABhAHIAcgBhAHkAcwAgAG8AcgAgAGgAaQBnAGgAIAB0AG8AawBlAG4AIABjAG8AdQBuAHQAcwAsACAAdABoAGkAcwAgAG0AYQB5ACAAaQBuAGMAcgBlAGEAcwBlACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuACAAdABpAG0AZQAuAFwAbgAgACAAIAAgACIgIABEAGUAbABpAG0AaQB0AGUAcgBzACAAYQByAGUAIABmAHUAbABsAHkAIAByAGUAZwBlAHgAESBlAHMAYwBhAHAAZQBkACAAdgBpAGEAIABSAGUAZwBlAHgAUwBhAGYAZQC7AywAIABhAGwAbABvAHcAaQBuAGcAIABsAGkAdABlAHIAYQBsACAAdQBzAGUAIABvAGYAXABuACAAIAAgACAAIAAgAG0AZQB0AGEAYwBoAGEAcgBhAGMAdABlAHIAcwAgACgAKgAsACAAPwAsACAAKwAsACAAfAAsACAAKAAsACAAKQAsACAAWwAsACAAXQAsACAAXgAsACAAJAAsACAAZQB0AGMALgApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAcABsAGkAdAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsAFwAbgAgACAAIAAgAFsAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAXQAsAFwAbgAgACAAIAAgAFsAdAByAGUAYQB0AF8AYwBvAG4AcwBlAGMAdQB0AGkAdgBlAF8AZABlAGwAaQBtAGkAdABlAHIAcwBfAGEAcwBfAG8AbgBlAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwAgAG8AZgAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABoACwAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAIABvAGYAIABkAGUAbABpAG0AaQB0AGUAcgBcAG4AIAAgACAAIABoAIIgLAAgAFIATwBXAFMAKABkAGUAbABpAG0AaQB0AGUAcgApACwAXABuACAAIAAgACAAdwCCICwAIABDAE8ATABVAE0ATgBTACgAZABlAGwAaQBtAGkAdABlAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABjAGgAZQBjAGsAcwBcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAIAAgAGgAIAA+ACAAdwAsAFwAbgAgACAAIAAgAEkAcwAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA+ACAAMQApACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAAsACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAKQAsACAAXAAiAFwAIgAsACAAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAKQAsAFwAbgAgACAAIAAgAEMAbwBsAGwAYQBwAHMAZQBEAGUAbABpAG0APwAsACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHQAcgBlAGEAdABfAGMAbwBuAHMAZQBjAHUAdABpAHYAZQBfAGQAZQBsAGkAbQBpAHQAZQByAHMAXwBhAHMAXwBvAG4AZQApACkALABcAG4AIAAgACAAIABNAHUAbAB0AGkAcABsAGUARABlAGwAaQBtAD8ALAAgAE8AUgAoAGgAgiAgAD4AIAAxACwAIAB3AIIgIAA+ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAASQBGACgASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjADIARAAtAEkATgBQAFUAVAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAE0AdQBsAHQAaQBwAGwAZQBEAGUAbABpAG0APwAsACAAXAAiACMARABFAEwASQBNAEkAVABFAFIALQBBAFIAUgBBAFkAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAVwByAGEAcAAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAdwBpAHQAaAAgAGQAZQBsAGkAbQBpAHQAZQByACAAbwBuACAAYgBvAHQAaAAgAHMAaQBkAGUAcwBcAG4AIAAgACAAIABqAG8AaQBuAGUAZAAsACAAIAAgACAAIAAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByACAAJgAgAGEAcgByAGEAeQAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAZwBlAHgAESBzAGEAZgBlACAAZABlAGwAaQBtAGkAdABlAHIAXABuACAAIAAgACAAZABlAGwAaQBtAF8AYgAsACAAIAAgACAAIAAgACAAIABSAGUAZwBlAHgAUwBhAGYAZQC7AygAZABlAGwAaQBtAGkAdABlAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAdABlAGMAdAAgAGMAbwBuAHMAZQBjAHUAdABpAHYAZQAgAGQAZQBsAGkAbQBpAHQAZQByAHMAXABuACAAIAAgACAASQBzAEMAbwBuAHMAZQBjAEQAZQBsAGkAbQA/ACwAIABPAFIAKABSAEUARwBFAFgAVABFAFMAVAAoAGoAbwBpAG4AZQBkACwAIABcACIAKABcACIAIAAmACAAZABlAGwAaQBtAF8AYgAgACYAIABcACIAKQB7ADIALAB9AFwAIgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAbABhAHAAcwBlACAAYwBvAG4AcwBlAGMAdQB0AGkAdgBlACAAZABlAGwAaQBtAGkAdABlAHIAcwAgAGkAZgAgAHIAZQBxAHUAZQBzAHQAZQBkAFwAbgAgACAAIAAgAHQAZQB4AHQAcwAsACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABDAG8AbABsAGEAcABzAGUARABlAGwAaQBtAD8ALAAgAEkAcwBDAG8AbgBzAGUAYwBEAGUAbABpAG0APwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIARQBHAEUAWABSAEUAUABMAEEAQwBFACgAagBvAGkAbgBlAGQALAAgAFwAIgAoAFwAIgAgACYAIABkAGUAbABpAG0AXwBiACAAJgAgAFwAIgApACsAXAAiACwAIABkAGUAbABpAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagBvAGkAbgBlAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AawBlAG4AIABjAG8AdQBuAHQAXABuACAAIAAgACAATAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUATgAoAGQAZQBsAGkAbQBpAHQAZQByACkALABcAG4AIAAgACAAIAB0AG8AawBlAG4ALAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgATABFAE4AKAB0AGUAeAB0AHMAKQAgAC0AIABMAEUATgAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKAB0AGUAeAB0AHMALAAgAGQAZQBsAGkAbQBpAHQAZQByACwAIABcACIAXAAiACkAKQApACAALwAgAEwAIAAtACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAaQBuAGcAIABmAG8AcgAgAFQARQBYAFQAQQBGAFQARQBSAC8AVABFAFgAVABCAEUARgBPAFIARQBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8AKQAgACsAIAAoAEkAcwBTAGMAYQBsAGEAcgA/ACkALABTAEUAUQBVAEUATgBDAEUAKAAsACAAdABvAGsAZQBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAB0AG8AawBlAG4AKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAHIAcwBlACAAdABvAGsAZQBuAHMAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABFAFgAVABCAEUARgBPAFIARQAoAFQARQBYAFQAQQBGAFQARQBSACgAdABlAHgAdABzACwAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAaQBkAHgAKAApACwAIAAsACAALAAgAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsACwAIAAsACAALAAgAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYAC0AQwBPAFIARQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFIAZQBnAGUAeABTAGEAZgBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0ACAAKABDAG8AcgBlACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHMAYwBhAHAAZQBzACAAcgBlAGcAZQB4ACAAbQBlAHQAYQBjAGgAYQByAGEAYwB0AGUAcgBzACAAaQBuACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgAGQAZQBsAGkAbQBpAHQAZQByACAAcwBvACAAaQB0ACAAYwBhAG4AIABiAGUAIAB1AHMAZQBkAFwAbgAgACAAIAAgAHMAYQBmAGUAbAB5ACAAaQBuACAAUgBFAEcARQBYAFQARQBTAFQALAAgAFIARQBHAEUAWABSAEUAUABMAEEAQwBFACwAIABhAG4AZAAgAFIARQBHAEUAWABFAFgAVABSAEEAQwBUACAAcABhAHQAdABlAHIAbgBzAC4AIABNAHUAbAB0AGkAESBcAG4AIAAgACAAIABjAGgAYQByAGEAYwB0AGUAcgAgAGQAZQBsAGkAbQBpAHQAZQByAHMAIABhAHIAZQAgAHAAcgBvAGMAZQBzAHMAZQBkACAAYwBoAGEAcgBhAGMAdABlAHIAESBiAHkAESBjAGgAYQByAGEAYwB0AGUAcgAsACAAYQBuAGQAIABvAG4AbAB5AFwAbgAgACAAIAAgAGMAaABhAHIAYQBjAHQAZQByAHMAIAB0AGgAYQB0ACAAcgBlAHEAdQBpAHIAZQAgAGUAcwBjAGEAcABpAG4AZwAgAGEAcgBlACAAcAByAGUAZgBpAHgAZQBkACAAdwBpAHQAaAAgAFwAIgBcAFwAXAAiAC4AXABuAFwAbgBFAHgAYQBtAHAAbABlADoAXABuACAAIAAgACAAPQBSAGUAZwBlAHgAUwBhAGYAZQC7AygAXAAiAHwAXAAiACkAXABuACAAIAAgACAAcgBlAHQAdQByAG4AcwA6ACAAXAAiAFwAXAB8AFwAIgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBlAGcAZQB4AFMAYQBmAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIAcwAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEMAaABhAHIAYQBjAHQAZQByAHMAIAByAGUAcQB1AGkAcgBpAG4AZwAgAGUAcwBjAGEAcABpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAnAHMAIABQAEMAUgBFADIAIABlAG4AZwBpAG4AZQBcAG4AIAAgACAAIABtAGUAdABhACwAIAAgACAAIAAgACAAIAB7AFwAIgBcAFwAXAAiACwAIABcACIAKwBcACIALAAgAFwAIgAqAFwAIgAsACAAXAAiAD8AXAAiACwAIABcACIAXgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAkAFwAIgAsACAAXAAiACgAXAAiACwAIABcACIAKQBcACIALAAgAFwAIgBbAFwAIgAsACAAXAAiAHwAXAAiAH0ALABcAG4AXABuACAAIAAgACAALwAvACAARQBuAHUAbQBlAHIAYQB0AGUAIABlAGEAYwBoACAAYwBoAGEAcgBhAGMAdABlAHIAIABvAGYAIAB0AGgAZQAgAGQAZQBsAGkAbQBpAHQAZQByAFwAbgAgACAAIAAgAGMAaABhAHIAcwAsACAAIAAgACAAIAAgAFIARQBHAEUAWABFAFgAVABSAEEAQwBUACgAZABlAGwAaQBtAGkAdABlAHIAcwAsAFwAIgAuAFwAIgAsADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAGQAZQBuAHQAaQBmAHkAIABtAGUAdABhAGMAaABhAHIAYQBjAHQAZQByAHMAXABuACAAIAAgACAASQBzAE0AZQB0AGEAPwAsACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgAWABNAEEAVABDAEgAKABjAGgAYQByAHMALAAgAG0AZQB0AGEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAcwBjAGEAcABlACAAbwBuAGwAeQAgAHQAaABvAHMAZQAgAHQAaABhAHQAIAByAGUAcQB1AGkAcgBlACAAaQB0AFwAbgAgACAAIAAgAHAAYQB0AHQAZQByAG4ALAAgACAAIAAgAEMATwBOAEMAQQBUACgASQBGACgASQBzAE0AZQB0AGEAPwAsACAAXAAiAFwAXABcACIAIAAmACAAYwBoAGEAcgBzACwAIABjAGgAYQByAHMAKQApACwAXABuAFwAbgAgACAAIAAgAHAAYQB0AHQAZQByAG4AXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAEUATgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAwADgAIAAUICAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgAvAC8AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFwAbgAvACoAXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFQAaABlACAARQBuAGcAaQBuAGUAZQByAGkAbgBnACAAYwBhAHQAZQBnAG8AcgB5ACAAcAByAG8AdgBpAGQAZQBzACAAYgBpAG4AYQByAHkALAAgAEcAcgBhAHkAESBjAG8AZABlACwAIABhAG4AZAAgAGIAaQB0ABEgbABlAHYAZQBsACAAdQB0AGkAbABpAHQAaQBlAHMAXABuACAAIAAgACAAZABlAHMAaQBnAG4AZQBkACAAdABvACAAbwBwAGUAcgBhAHQAZQAgAHcAZQBsAGwAIABiAGUAeQBvAG4AZAAgAEUAeABjAGUAbAAnAHMAIABuAGEAdABpAHYAZQAgAEQARQBDADIAQgBJAE4AIABsAGkAbQBpAHQAIABvAGYAIAA1ADEAMQAuACAAQQBsAGwAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuAHMAIABzAHUAcABwAG8AcgB0ACAAYwBvAG4AYwBpAHMAZQAgAGIAaQBuAGEAcgB5ACAAcwB0AHIAaQBuAGcAcwAgAGEAbgBkACAAcwBoAGEAcABlABEgcAByAGUAcwBlAHIAdgBpAG4AZwAgAGEAcgByAGEAeQAgAGIAZQBoAGEAdgBpAG8AcgAsAFwAbgAgACAAIAAgAHcAaQB0AGgAIABvAHAAdABpAG8AbgBhAGwAIAAyAEQAIABlAHgAcABsAG8AZABlAGQAIABiAGkAdAARIG0AYQB0AHIAaQBjAGUAcwAgAHcAaABlAHIAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUALgBcAG4AXABuAEYAdQBuAGMAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAEIAaQBuADIARABlAGMAuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAGMAbwBuAGMAaQBzAGUAIABiAGkAbgBhAHIAeQAgAGkAbgB0AG8AIABkAGUAYwBpAG0AYQBsACAAdgBhAGwAdQBlAHMALgBcAG4AXABuACAAIAAgACAAIiAgAEIAaQBuADIARwByAGEAeQC7A1wAbgAgACAAIAAgACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAYwBvAG4AYwBpAHMAZQAgAGIAaQBuAGEAcgB5ACAAaQBuAHQAbwAgAEcAcgBhAHkAESBjAG8AZABlACAAdgBhAGwAdQBlAHMALAAgAHcAaQB0AGgAIABvAHAAdABpAG8AbgBhAGwAIABlAHgAcABsAG8AZABlAGQAIABmAG8AcgBtAC4AXABuAFwAbgAgACAAIAAgACIgIABCAGkAdABDAG8AdQBuAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAGkAbgB0AGUAZwBlAHIAcwAgAHQAbwAgAGIAaQBuAGEAcgB5ACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAYgBpAHQAIABjAG8AdQBuAHQAcwAsACAAcAByAGUAcwBlAHIAdgBpAG4AZwAgAGkAbgBwAHUAdAAgAHMAaABhAHAAZQAuAFwAbgBcAG4AIAAgACAAIAAiICAARABlAGMAMgBCAGkAbgC7A1wAbgAgACAAIAAgACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAaQBuAHQAZQBnAGUAcgBzACAAaQBuAHQAbwAgAGIAaQBuAGEAcgB5ACAAdgBhAGwAdQBlAHMALAAgAHIAZQB0AHUAcgBuAGUAZAAgAGEAcwAgAGMAbwBuAGMAaQBzAGUAIABzAHQAcgBpAG4AZwBzACAAbwByAFwAbgAgACAAIAAgACAAIAAgACAAZQB4AHAAbABvAGQAZQBkACAAMgBEACAAYgBpAHQAESBhAHIAcgBhAHkAcwAuAFwAbgBcAG4AIAAgACAAIAAiICAARABlAGMAMgBHAHIAYQB5ALsDXABuACAAIAAgACAAIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABpAG4AdABlAGcAZQByAHMAIABpAG4AdABvACAARwByAGEAeQARIGMAbwBkAGUAIAB2AGEAbAB1AGUAcwAgACgAdwByAGEAcABwAGUAcgA6ACAARABlAGMAMgBCAGkAbgC7AyAAkiEgAEIAaQBuADIARwByAGEAeQC7AykALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABOAGUAZwBhAHQAaQB2AGUAIABuAHUAbQBiAGUAcgBzACAAYQByAGUAIABuAG8AdAAgAHMAdQBwAHAAbwByAHQAZQBkACAAZgBvAHIAIABEAGUAYwAyAEIAaQBuALsDIABvAHIAIABEAGUAYwAyAEcAcgBhAHkAuwMuAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARQBOADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEIAaQBuADIARABlAGMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAGMAbwBuAGMAaQBzAGUAIABiAGkAbgBhAHIAeQAgAGkAbgB0AG8AIABkAGUAYwBpAG0AYQBsACAAdgBhAGwAdQBlAHMALgAgAFMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAGEAbgBkACAAMgBEAFwAbgAgACAAIAAgAGkAbgBwAHUAdABzACAAdwBpAHQAaAAgAGYAdQBsAGwAIABzAGgAYQBwAGUAIABwAHIAZQBzAGUAcgB2AGEAdABpAG8AbgAuACAAQgBpAHQAESB3AGkAZAB0AGgAIABpAHMAIABpAG4AZgBlAHIAcgBlAGQAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5AFwAbgAgACAAIAAgAGEAbgBkACAAYQBsAGwAIAB2AGEAbAB1AGUAcwAgAGEAcgBlACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAGIAZQBmAG8AcgBlACAAZQB4AHAAbABvAHMAaQBvAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABiAGkAbgBhAHIAeQBcAG4AIAAgACAAIAAgACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABjAG8AbgBjAGkAcwBlACAAYgBpAG4AYQByAHkAIABzAHQAcgBpAG4AZwBzAC4AXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEMAbwBuAGMAaQBzAGUAIABmAG8AcgBtADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAwADEAMQBcACIALAAgAFwAIgAwADAAMAAxADEAMAAxADAAXAAiACwAIABlAHQAYwAuACAAIAAoAGEAbgB5ACAAcwBoAGEAcABlACkAXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABzAGgAYQBwAGUAIABtAGEAdABjAGgAZQBzACAAaQBuAHAAdQB0ACAAcwBoAGEAcABlACAAKABzAGMAYQBsAGEAcgAsACAAdgBlAHIAdABpAGMAYQBsACwAIABoAG8AcgBpAHoAbwBuAHQAYQBsACwAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgACIgIABTAHUAcABwAG8AcgB0AHMAIABiAGkAbgBhAHIAeQAgAHYAYQBsAHUAZQBzACAAZgBhAHIAIABiAGUAeQBvAG4AZAAgAEUAeABjAGUAbAAZIHMAIABuAGEAdABpAHYAZQAgADEANgARIGQAaQBnAGkAdAAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBpAHQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQgBpAG4AMgBEAGUAYwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABiAGkAbgBhAHIAeQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAaABhAHAAZQAgAG8AZgAgAGkAbgBwAHUAdABcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABiAGkAbgBhAHIAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYgBpAG4AYQByAHkAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIABBAE4ARAAoAGgAIAA+ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMASABvAHIAaQB6AG8AbgB0AGEAbAA/ACwAIAAgAEEATgBEACgAdwAgAD4AIAAxACwAIABoACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAGIAaQB0ABEgdwBpAGQAdABoACAAYQBuAGQAIABlAHgAcABsAG8AZABlAFwAbgAgACAAIAAgAGIAaQB0AHMALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABMAEUATgAoAGIAaQBuAGEAcgB5ACkAKQAsAFwAbgAgACAAIAAgAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABFAFgAVAAoAGIAaQBuAGEAcgB5ACwAIABSAEUAUABUACgAXAAiADAAXAAiACwAIABiAGkAdABzACkAKQAsAFwAbgAgACAAIAAgAGIAaQBuAGEAcgB5ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALABFAHgAcABsAG8AZABlALsDKABiAGkAbgBhAHIAeQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwMoAFQATwBDAE8ATAAoAGEAcgByACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB0AGgAXABuACAAIAAgACAAcABvAHcAZQByAHMALAAgAFMARQBRAFUARQBOAEMARQAoACwAIABiAGkAdABzACwAIABiAGkAdABzACAALQAgADEALAAgAC0AMQApACwAXABuACAAIAAgACAAcAAsACAAIAAgACAAIAAgAFAATwBXAEUAUgAoADIALAAgAHAAbwB3AGUAcgBzACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAJgAgAGQAZQBsAGkAdgBlAHIAeQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAQgBZAFIATwBXACgAYgBpAG4AYQByAHkAIAAqACAAcAAsACAAUwBVAE0AKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIABJAEYAKABPAFIAKABJAHMAUwBjAGEAbABhAHIAPwAsACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACkALAAgAHIAZQBzAHUAbAB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAsACAAVABSAEEATgBTAFAATwBTAEUAKAByAGUAcwB1AGwAdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABXAFIAQQBQAFIATwBXAFMAKAByAGUAcwB1AGwAdAAsACAAdwApACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEUATgAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABCAGkAbgAyAEcAcgBhAHkAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAGIAaQBuAGEAcgB5ACAAaQBuAHQAbwAgAEcAcgBhAHkAESBjAG8AZABlACAAdgBhAGwAdQBlAHMALgAgAFMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByACwAXABuACAAIAAgACAAMQBEACwAIABhAG4AZAAgADIARAAgAGkAbgBwAHUAdABzAC4AIABPAHUAdABwAHUAdAAgAGMAYQBuACAAYgBlACAAcgBlAHQAdQByAG4AZQBkACAAZQBpAHQAaABlAHIAIABhAHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAbwByACAAYQBzAFwAbgAgACAAIAAgAGMAbwBuAGMAaQBzAGUAIAByAG8AdwARIHcAaQBzAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYgBpAG4AYQByAHkAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAYgBpAG4AYQByAHkAIABkAGEAdABhAC4AXABuAFwAbgAgACAAIAAgAFsAYwBvAG4AYwBpAHMAZQBdAFwAbgAgACAAIAAgACAAIAAgACAATwBwAHQAaQBvAG4AYQBsAC4AIABUAFIAVQBFACAAkiEgAHIAZQB0AHUAcgBuACAARwByAGEAeQAgAGMAbwBkAGUAIABhAHMAIABjAG8AbgBjAGEAdABlAG4AYQB0AGUAZAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAgACAAIAAgACAAIAAgAE8AbQBpAHQAdABlAGQAIACSISAAcgBlAHQAdQByAG4AIAAyAEQAIABlAHgAcABsAG8AZABlAGQAIABHAHIAYQB5ABEgYwBvAGQAZQAgAGIAaQB0ACAAYQByAHIAYQB5AHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIAAyAEQAIABhAHIAcgBhAHkAcwAgAGEAcgBlACAAZABlAGwAaQB2AGUAcgBlAGQAIABpAG4AIABjAG8AbgBjAGkAcwBlACAAZgBvAHIAbQBhAHQALgBcAG4AIAAgACAAIAAiICAARwByAGEAeQAgAGMAbwBkAGUAIABpAHMAIABjAG8AbQBwAHUAdABlAGQAIABhAHMAOgAgACAAZwCAICAAPQAgAGIAgCAsACAAIABnAGIdIAA9ACAAYgBiHSAAWABPAFIAIABiAGIdiyCBIC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEIAaQBuADIARwByAGEAeQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABiAGkAbgBhAHIAeQAsAFwAbgAgACAAIAAgAFsAYwBvAG4AYwBpAHMAZQBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AdQB0AHAAdQB0ACAAbQBvAGQAZQBcAG4AIAAgACAAIABJAHMAMgBEAEcAcgBhAHkAPwAsACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAG4AYwBpAHMAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAaABhAHAAZQAgAG8AZgAgAGkAbgBwAHUAdABcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABiAGkAbgBhAHIAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYgBpAG4AYQByAHkAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIABBAE4ARAAoAGgAIAA+ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMASABvAHIAaQB6AG8AbgB0AGEAbAA/ACwAIAAgAEEATgBEACgAdwAgAD4AIAAxACwAIABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAYgBpAHQALQB3AGkAZAB0AGgAIABhAG4AZAAgAGUAeABwAGwAbwBkAGUAXABuACAAIAAgACAAYgBpAHQAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAEwARQBOACgAYgBpAG4AYQByAHkAKQApACwAXABuACAAIAAgACAAYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgAYgBpAG4AYQByAHkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGIAaQB0AHMAKQApACwAXABuACAAIAAgACAAYgBpAG4AYQByAHkALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsAEUAeABwAGwAbwBkAGUAuwMoAGIAaQBuAGEAcgB5ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQB4AHAAbABvAGQAZQC7AygAVABPAEMATwBMACgAYQByAHIAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBvAHMAdAAgAHMAaQBnAG4AaQBmAGkAYwBhAG4AdAAgAGIAaQB0AFwAbgAgACAAIAAgAG0AcwBiACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAGIAaQBuAGEAcgB5ACwAIAAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFgATwBSACAAbgBlAGkAZwBoAGIAbwByAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABCAEkAVABYAE8AUgAoAEQAUgBPAFAAKABiAGkAbgBhAHIAeQAsACAALAAgADEAKQAsACAARABSAE8AUAAoAGIAaQBuAGEAcgB5ACwAIAAsACAALQAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABHAHIAYQB5ACAAYwBvAGQAZQAgAGEAcgByAGEAeQBfADIARABcAG4AIAAgACAAIABnAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAbQBzAGIALAAgAHgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHUAdABwAHUAdAAgAGEAbgBkACAAZABlAGwAaQB2AGUAcgB5AFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABJAHMAMgBEAEcAcgBhAHkAPwAsAEkAcwAxAEQAPwApACwAIABnAHIAYQB5ACwAIABCAFkAUgBPAFcAKABnAHIAYQB5ACwAIABDAE8ATgBDAEEAVAApACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwASQBzAFYAZQByAHQAaQBjAGEAbAA/ACkALAByAGUAcwB1AGwAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASABvAHIAaQB6AG8AbgB0AGEAbAA/ACwAVABSAEEATgBTAFAATwBTAEUAKAByAGUAcwB1AGwAdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABXAFIAQQBQAFIATwBXAFMAKAByAGUAcwB1AGwAdAAsAHcAKQApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBFAE4AMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQgBpAHQAQwBvAHUAbgB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABFAG4AZwBpAG4AZQBlAHIAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AdQBuAHQAcwAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIAAxABEgYgBpAHQAcwAgAGkAbgAgAHQAaABlACAAYgBpAG4AYQByAHkAIAByAGUAcAByAGUAcwBlAG4AdABhAHQAaQBvAG4AIABvAGYAIABlAGEAYwBoACAAaQBuAHQAZQBnAGUAcgAuAFwAbgAgACAAIAAgAFMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAGEAbgBkACAAMgBEACAAaQBuAHAAdQB0AHMAIAB3AGkAdABoACAAZgB1AGwAbAAgAHMAaABhAHAAZQAgAHAAcgBlAHMAZQByAHYAYQB0AGkAbwBuAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAbgAgACAAIAAtACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AbwBuABEgbgBlAGcAYQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAEQAZQBjADIAQgBpAG4AuwMoAG4ALAAxACkAIAB0AG8AIABvAGIAdABhAGkAbgAgAGUAeABwAGwAbwBkAGUAZAAgAGIAaQB0ABEgbQBhAHQAcgBpAGMAZQBzAC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAcwBoAGEAcABlACAAbQBhAHQAYwBoAGUAcwAgAGkAbgBwAHUAdAAgAHMAaABhAHAAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBCAGkAdABDAG8AdQBuAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAbgAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAaABhAHAAZQBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAG4AKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAbgApACwAXABuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIABYAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAMgBEAD8ALAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA+ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAIABpAGYAIAAyAEQAXABuACAAIAAgACAAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsAG4ALABUAE8AQwBPAEwAKABuACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAHUAbgBjAHQAaQBvAG4AIAAoAGYAbwByACAAbgBvAG4ALQBzAGMAYQBsAGEAcgBzACkAXABuACAAIAAgACAAZgBuALsDLAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsAEkAcwAyAEQAPwApACwAQgBZAFIATwBXACwAQgBZAEMATwBMACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHAAbABvAGQAZQBkACAAYgBpAG4AYQByAHkAIABhAHIAcgBhAHkAXwAyAEQAXABuACAAIAAgACAAYgBpAHQAcwAsACAAIAAgACAAIAAgACAAIAAgAEQAZQBjADIAQgBpAG4AuwMoAG4ALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AdQBuAHQAIABiAGkAdABzAFwAbgAgACAAIAAgAGMAbwB1AG4AdABzACwAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAUwBVAE0AKABiAGkAdABzACkALABmAG4AuwMoAGIAaQB0AHMALABTAFUATQApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsAGMAbwB1AG4AdABzACwAVwBSAEEAUABSAE8AVwBTACgAYwBvAHUAbgB0AHMALAB3ACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEUATgAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABFAG4AZwBpAG4AZQBlAHIAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABuAG8AbgARIG4AZQBnAGEAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAgAGkAbgB0AG8AIABiAGkAbgBhAHIAeQAuACAAUwB1AHAAcABvAHIAdABzACAAcwBjAGEAbABhAHIALAAgADEARAAsACAAYQBuAGQAIAAyAEQAXABuACAAIAAgACAAaQBuAHAAdQB0AHMAIAB3AGkAdABoACAAZgB1AGwAbAAgAHMAaABhAHAAZQAgAHAAcgBlAHMAZQByAHYAYQB0AGkAbwBuAC4AIABSAGUAdAB1AHIAbgBzACAAZQBpAHQAaABlAHIAIABjAG8AbgBjAGkAcwBlACAAYgBpAG4AYQByAHkAIABzAHQAcgBpAG4AZwBzAFwAbgAgACAAIAAgAG8AcgAgAGUAeABwAGwAbwBkAGUAZAAgADIARAAgAGIAaQB0ABEgYQByAHIAYQB5AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABuAHUAbQBiAGUAcgBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAbgBvAG4AESBuAGUAZwBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMALgBcAG4AXABuACAAIAAgACAAWwBBAHIAcgBhAHkAXwBGAG8AcgBtAF8AMgBEAF0AXABuACAAIAAgACAAIAAgACAAIABPAHAAdABpAG8AbgBhAGwALgAgAFQAUgBVAEUAIACSISAAcgBlAHQAdQByAG4AIABlAHgAcABsAG8AZABlAGQAIAAyAEQAIABiAGkAdAARIGEAcgByAGEAeQBzAC4AXABuACAAIAAgACAAIAAgACAAIABPAG0AaQB0AHQAZQBkACAAkiEgAHIAZQB0AHUAcgBuACAAYwBvAG4AYwBpAHMAZQAgAGIAaQBuAGEAcgB5ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFMAdQBwAHAAbwByAHQAcwAgAGEAcgBiAGkAdAByAGEAcgBpAGwAeQAgAGwAYQByAGcAZQAgAGkAbgB0AGUAZwBlAHIAcwAgACgAYgBlAHkAbwBuAGQAIABFAHgAYwBlAGwAGSBzACAAbgBhAHQAaQB2AGUAIABCAEkATgAyAEQARQBDACAAbABpAG0AaQB0AHMAKQAuAFwAbgAgACAAIAAgACIgIABDAG8AbgBjAGkAcwBlACAAbwB1AHQAcAB1AHQAIABhAHYAbwBpAGQAcwAgAHMAYwBpAGUAbgB0AGkAZgBpAGMAIABuAG8AdABhAHQAaQBvAG4AIABhAG4AZAAgADEANgARIGQAaQBnAGkAdAAgAHAAcgBlAGMAaQBzAGkAbwBuACAAaQBzAHMAdQBlAHMALgBcAG4AIAAgACAAIAAiICAAMgBEACAAaQBuAHAAdQB0AHMAIABwAHIAZQBzAGUAcgB2AGUAIAB0AGgAZQBpAHIAIABvAHIAaQBnAGkAbgBhAGwAIABzAGgAYQBwAGUAIAB3AGgAZQBuACAAYwBvAG4AYwBpAHMAZQAgAG8AdQB0AHAAdQB0ACAAaQBzACAAcwBlAGwAZQBjAHQAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQBjADIAQgBpAG4AuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAG4AdQBtAGIAZQByAHMALABcAG4AIAAgACAAIABbAEEAcgByAGEAeQBfAEYAbwByAG0AXwAyAEQAXQAsAFwAbgBcAG4ALwAvAEMAaABlAGMAawAgAG4AdQBtAGIAZQByAHMAXABuAEkARgAoAE8AUgAoAEkAUwBUAEUAWABUACgAbgB1AG0AYgBlAHIAcwApACwAIABJAFMARQBSAFIATwBSACgALQAtAG4AdQBtAGIAZQByAHMAKQAsAG4AdQBtAGIAZQByAHMAIAA8ACAAMAApACwAIAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBwAHUAdAAgAHMAaABhAHAAZQBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAbgB1AG0AYgBlAHIAcwApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAG4AdQBtAGIAZQByAHMAKQAsAFwAbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAIABoACAAPgAgAHcALABcAG4AIAAgACAAIABJAHMAMgBEAD8ALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA+ACAAMQAsAHcAIAA+ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAXABuACAAIAAgACAAbgB1AG0AYgBlAHIAcwAsACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAbgB1AG0AYgBlAHIAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbwByAG0AXABuACAAIAAgACAASQBzAFYAZQBjAHQAbwByAD8ALAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABBAHIAcgBhAHkAXwBGAG8AcgBtAF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHgAIABiAGkAdABzACAAbgBlAGUAZABlAGQAIAB0AG8AIABlAHgAcAByAGUAcwBzACAAcgBlAHMAdQBsAHQAcwAgAGEAcwAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABiAGkAdABzACwAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAEkARgBFAFIAUgBPAFIAKABJAE4AVAAoAEwATwBHACgAbgB1AG0AYgBlAHIAcwAsADIAKQApACAAKwAgADEALAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAG8AcgBtAHMAIAAtACAAMgBEACAAYQByAHIAYQB5ACwAIABiAGkAbgAgAHYAZQBjAHQAbwByACAALQAgAGUAYQBnAGUAcgAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABkAGUAZgBlAHIAcgBlAGQAXABuACAAIAAgACAAYgBpAG4AXwBhAHIAcgAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAE8ARAAoAEIASQBUAFIAUwBIAEkARgBUACgAbgB1AG0AYgBlAHIAcwAsAFMARQBRAFUARQBOAEMARQAoACwAYgBpAHQAcwAsAGIAaQB0AHMAIAAtACAAMQAsAC0AMQApACkALAAyACkAKQAsAFwAbgAgACAAIAAgAGIAaQBuAF8AdgBlAGMAdABvAHIALAAgACAAIAAgAEwAQQBNAEIARABBACgAQgBZAFIATwBXACgAYgBpAG4AXwBhAHIAcgAoACkALABDAE8ATgBDAEEAVAApACkALABcAG4AIAAgACAAIABiAGkAbgBfAHIAZQBzAHUAbAB0ACwAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAEkAcwBWAGUAYwB0AG8AcgA/ACwAYgBpAG4AXwB2AGUAYwB0AG8AcgAoACkALABiAGkAbgBfAGEAcgByACgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAC0AcwBoAGEAcABpAG4AZwAgACYAIABkAGUAbABpAHYAZQByAHkAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAASQBGACgASQBzADIARAA/ACwAVwBSAEEAUABSAE8AVwBTACgAYgBpAG4AXwB2AGUAYwB0AG8AcgAoACkALAB3ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgASQBzAFMAYwBhAGwAYQByAD8ALABJAHMAVgBlAHIAdABpAGMAYQBsAD8AKQAsAGIAaQBuAF8AcgBlAHMAdQBsAHQAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAEEATgBTAFAATwBTAEUAKABiAGkAbgBfAHIAZQBzAHUAbAB0ACgAKQApACkAKQAsAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARQBOADAANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEQAZQBjADIARwByAGEAeQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARABlAGMAMgBCAGkAbgC7AywAIABCAGkAbgAyAEcAcgBhAHkAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAG4AbwBuABEgbgBlAGcAYQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgBzACAAaQBuAHQAbwAgAEcAcgBhAHkAESBjAG8AZABlACAAdgBhAGwAdQBlAHMALgAgAFMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByACwAIAAxAEQALABcAG4AIAAgACAAIABhAG4AZAAgADIARAAgAGkAbgBwAHUAdABzACAAdwBpAHQAaAAgAGYAdQBsAGwAIABzAGgAYQBwAGUAIABwAHIAZQBzAGUAcgB2AGEAdABpAG8AbgAuACAATwB1AHQAcAB1AHQAIABjAGEAbgAgAGIAZQAgAHIAZQB0AHUAcgBuAGUAZAAgAGUAaQB0AGgAZQByAFwAbgAgACAAIAAgAGEAcwAgAGMAbwBuAGMAaQBzAGUAIABHAHIAYQB5ABEgYwBvAGQAZQAgAHMAdAByAGkAbgBnAHMAIABvAHIAIABhAHMAIABlAHgAcABsAG8AZABlAGQAIAAyAEQAIABiAGkAdAARIGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAbgB1AG0AYgBlAHIAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIABuAG8AbgARIG4AZQBnAGEAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAuAFwAbgBcAG4AIAAgACAAIABbAGMAbwBuAGMAaQBzAGUAXQBcAG4AIAAgACAAIAAgACAAIAAgAE8AcAB0AGkAbwBuAGEAbAAuACAAVABSAFUARQAgAJIhIAByAGUAdAB1AHIAbgAgAEcAcgBhAHkAIABjAG8AZABlACAAYQBzACAAYwBvAG4AYwBhAHQAZQBuAGEAdABlAGQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAIAAgACAAIAAgACAAIABPAG0AaQB0AHQAZQBkACAAkiEgAHIAZQB0AHUAcgBuACAAZQB4AHAAbABvAGQAZQBkACAAMgBEACAARwByAGEAeQARIGMAbwBkAGUAIABiAGkAdAAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAEQAZQBjADIAQgBpAG4AuwMgAHQAbwAgAG8AYgB0AGEAaQBuACAAYgBpAG4AYQByAHkALAAgAHQAaABlAG4AIABCAGkAbgAyAEcAcgBhAHkAuwMgAHQAbwAgAGMAbwBuAHYAZQByAHQAIAB0AG8AIABHAHIAYQB5ACAAYwBvAGQAZQAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHMAaABhAHAAZQAgAG0AYQB0AGMAaABlAHMAIABpAG4AcAB1AHQAIABzAGgAYQBwAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABlAGMAMgBHAHIAYQB5ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAG4AdQBtAGIAZQByACwAXABuACAAIAAgACAAWwBjAG8AbgBjAGkAcwBlAF0ALABcAG4AIAAgACAAIABCAGkAbgAyAEcAcgBhAHkAuwMoAEQAZQBjADIAQgBpAG4AuwMoAG4AdQBtAGIAZQByACkALAAgAGMAbwBuAGMAaQBzAGUAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAEMAQgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAwADkAIAAUICAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4ALwAvACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABUAGgAZQAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAIABjAGEAdABlAGcAbwByAHkAIABwAHIAbwB2AGkAZABlAHMAIABoAGkAZwBoABEgcABlAHIAZgBvAHIAbQBhAG4AYwBlACAAZwBlAG4AZQByAGEAdABvAHIAcwAgAGYAbwByAFwAbgAgACAAIAAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgBzACwAIABjAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwAsACAAcwB1AGIAcwBlAHQAcwAsACAAYQBuAGQAIAByAGUAbABhAHQAZQBkACAAcwB0AHIAdQBjAHQAdQByAGUAcwAuAFwAbgBcAG4ARgB1AG4AYwB0AGkAbwBuAHMAOgBcAG4AIAAgACAAIAAiICAAUABlAHIAbQBSALsDXABuACAAIAAgACAAIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAgACgAawARIHQAdQBwAGwAZQBzACAAZAByAGEAdwBuACAAZgByAG8AbQAgAG4AIABpAHQAZQBtAHMAKQAuAFwAbgBcAG4AIAAgACAAIAAiICAAUABlAHIAbQC7A1wAbgAgACAAIAAgACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaQB0AGgAbwB1AHQAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQALgBcAG4AXABuACAAIAAgACAAIiAgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwNcAG4AIAAgACAAIAAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AC4AXABuAFwAbgAgACAAIAAgACIgIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7A1wAbgAgACAAIAAgACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABjAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwAgAHcAaQB0AGgAbwB1AHQAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQALgBcAG4AXABuACAAIAAgACAAIiAgAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDXABuACAAIAAgACAAIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgBzACAAdwBoAGUAcgBlACAAbgBvACAAZQBsAGUAbQBlAG4AdAAgAHIAZQBtAGEAaQBuAHMAIABpAG4AIABpAHQAcwAgAG8AcgBpAGcAaQBuAGEAbAAgAHAAbwBzAGkAdABpAG8AbgAuAFwAbgBcAG4AIAAgACAAIAAiICAASwBuAGEAcABTAGEAYwBrALsDXABuACAAIAAgACAAIAAgACAAIABTAG8AbAB2AGUAcwAgAHQAaABlACAAcwB1AGIAcwBlAHQAESBzAHUAbQAgAC8AIABrAG4AYQBwAHMAYQBjAGsAIABmAGUAYQBzAGkAYgBpAGwAaQB0AHkAIABwAHIAbwBiAGwAZQBtACAAdQBzAGkAbgBnACAAdgBlAGMAdABvAHIAaQB6AGUAZABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgB1AG0AZQByAGEAdABpAG8AbgAgAGEAbgBkACAAZgBpAGwAdABlAHIAaQBuAGcALgBcAG4AXABuACAAIAAgACAAIiAgAFMAdQBiAHMAZQB0AEcAZQBuALsDXABuACAAIAAgACAAIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAbABsACAAcwB1AGIAcwBlAHQAcwAgAG8AZgAgAGEAIABzAGUAdAAgACgAdABoAGUAIABwAG8AdwBlAHIAIABzAGUAdAApACwAIAByAGUAdAB1AHIAbgBlAGQAIABpAG4AIABiAGkAbgBhAHIAeQARIG0AYQBzAGsAXABuACAAIAAgACAAIAAgACAAIABvAHIAZABlAHIALgBcAG4AXABuACAAIAAgACAAIiAgAFMAdQBiAHMAZQB0AFMAdQBtALsDXABuACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBzACAAYQBsAGwAIABzAHUAYgBzAGUAdABzACAAdwBoAG8AcwBlACAAZQBsAGUAbQBlAG4AdABzACAAcwB1AG0AIAB0AG8AIABhACAAdABhAHIAZwBlAHQAIAB2AGEAbAB1AGUALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABBAGwAbAAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAHIAZQAgAHMAaABhAHAAZQARIHAAcgBlAHMAZQByAHYAaQBuAGcAIABhAG4AZAAgAHIAZQB0AHUAcgBuACAAMgBEACAAYQByAHIAYQB5AHMAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAcgBvAHcAXABuACAAIAAgACAAIAAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQAgAGMAbwBtAGIAaQBuAGEAdABvAHIAaQBhAGwAIABvAGIAagBlAGMAdAAuAFwAbgAgACAAIAAgACIgIABBAGwAbAAgAGYAdQBuAGMAdABpAG8AbgBzACAAbwBwAGUAcgBhAHQAZQAgAG8AbgAgAGEAcgByAGEAeQBzACAAbwBmACAAaQB0AGUAbQBzACwAIABuAG8AdAAgAGoAdQBzAHQAIABpAG4AdABlAGcAZQByAHMALgBcAG4AIAAgACAAIAAiICAAVABoAGUAIAB1AG4AZABlAHIAbAB5AGkAbgBnACAAYQByAGMAaABpAHQAZQBjAHQAdQByAGUAIAB1AHMAZQBzACAAYQAgAGYAdQBuAG4AZQBsACAAbQBvAGQAZQBsADoAIABsAGEAcgBnAGUAIABlAG4AdQBtAGUAcgBhAHQAaQBvAG4AcwAgAGEAcgBlAFwAbgAgACAAIAAgACAAIABnAGUAbgBlAHIAYQB0AGUAZAAgAG8AbgBjAGUAIABhAG4AZAAgAGYAaQBsAHQAZQByAGUAZAAgAGIAeQAgAG8AcgBkAGUAcgAsACAAdQBuAGkAcQB1AGUAbgBlAHMAcwAsACAAbwByACAAcABvAHMAaQB0AGkAbwBuAGEAbAAgAHAAcgBlAGQAaQBjAGEAdABlAHMALgBcAG4AXABuAEUAbgB1AG0AZQByAGEAdABlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEcAZQBuAGUAcgBhAHQAaQBuAGcAIABmAHUAbgBjAHQAaQBvAG4AKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUABlAHIAbQBSALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAGYAdQBsAGwAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaQB0AGgAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwMgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAZQByAG0AuwMgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAHIAYQBuAGcAZQBtAGUAbgB0AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACgAZgBpAGwAdABlAHIAIAByAGUAcABlAGEAdABzACkAIAAgACAAIAAgACAAIAAgACgAZgBpAGwAdABlAHIAIABiAHkAIABvAHIAZABlAHIAKQAgACAAIAAgACAAKABmAGkAbAB0AGUAcgAgAGIAeQAgAHAAbwBzAGkAdABpAG8AbgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHwAXABuACAAIAAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAuwNcAG4AIAAgACAAIAAgACgAZgBpAGwAdABlAHIAIAByAGUAcABlAGEAdABzACAAKwAgAG8AcgBkAGUAcgApAFwAbgBcAG4AXABuACoALwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBDAEIAESBDAE8AUgBFAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwByAGUAIABnAGUAbgBlAHIAYQB0AGkAbgBnACAAZgB1AG4AYwB0AGkAbwBuACAAZgBvAHIAIABhAGwAbAAgAGMAbwBtAGIAaQBuAGEAdABvAHIAaQBhAGwAIABvAHAAZQByAGEAdABvAHIAcwAgAGkAbgAgAHQAaABlACAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4AIAAgACAAIABjAGEAdABlAGcAbwByAHkALgAgAFAAcgBvAGQAdQBjAGUAcwAgAGkAbgBkAGUAeAAgAG0AYQB0AHIAaQBjAGUAcwAgAGYAbwByACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMALAAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACwAIABtAHUAbAB0AGkAcwBlAHQAcwAsAFwAbgAgACAAIAAgAGEAbgBkACAAZABlAHIAYQBuAGcAZQBtAGUAbgB0AHMAIAB1AHMAaQBuAGcAIABhACAAdgBlAGMAdABvAHIAaQB6AGUAZAAgAGYAdQBuAG4AZQBsACAAYQByAGMAaABpAHQAZQBjAHQAdQByAGUALgAgAEgAaQBnAGgAZQByABEgbABlAHYAZQBsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgBzACAAKABQAGUAcgBtAFIAuwMsACAAUABlAHIAbQC7AywAIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwBSALsDLAAgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzALsDLAAgAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDKQBcAG4AIAAgACAAIABhAHIAZQAgAHQAaABpAG4AIAB3AHIAYQBwAHAAZQByAHMAIABhAHIAbwB1AG4AZAAgAHQAaABpAHMAIABnAGUAbgBlAHIAYQB0AG8AcgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGkAdABlAG0AcwBcAG4AIAAgACAAIAAgACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAGkAdABlAG0AcwAuACAASQB0AGUAbQBzACAAbQBhAHkAIABiAGUAIABuAHUAbQBiAGUAcgBzACAAbwByACAAdABlAHgAdAAuAFwAbgBcAG4AIAAgACAAIABrAFwAbgAgACAAIAAgACAAIAAgACAATABlAG4AZwB0AGgAIABvAGYAIABlAGEAYwBoACAAdAB1AHAAbABlACAAKABrACAAZSIgADAAKQAuACAATQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4AIAAgACAAIAB0AHkAcABlAFwAbgAgACAAIAAgACAAIAAgACAAUwBlAGwAZQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBtAGIAaQBuAGEAdABvAHIAaQBhAGwAIABtAG8AZABlADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAIACSISAAUABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAyACAAkiEgAFAAZQByAG0AdQB0AGEAdABpAG8AbgBzACAAdwBpAHQAaABvAHUAdAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMwAgAJIhIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwAgAHcAaQB0AGgAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADQAIACSISAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAB3AGkAdABoAG8AdQB0ACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA1ACAAkiEgAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEEAbABsACAAcgBlAHMAdQBsAHQAcwAgAGEAcgBlACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAMgBEACAAYQByAHIAYQB5AHMAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAcgBvAHcAIABpAHMAIABvAG4AZQAgAHQAdQBwAGwAZQAuAFwAbgAgACAAIAAgACIgIABJAGYAIABpAHQAZQBtAHMAIABhAHIAZQAgAG4AdQBtAGUAcgBpAGMAIABhAG4AZAAgAGUAcQB1AGEAbAAgAHQAbwAgAFMARQBRAFUARQBOAEMARQAoAG4AKQAsACAAcgBhAHcAIABpAG4AZABpAGMAZQBzACAAYQByAGUAIAByAGUAdAB1AHIAbgBlAGQALgBcAG4AIAAgACAAIAAgACAATwB0AGgAZQByAHcAaQBzAGUALAAgAGkAdABlAG0AcwAgAGEAcgBlACAAcwB1AGIAcwB0AGkAdAB1AHQAZQBkACAAaQBuAHQAbwAgAHQAaABlACAAaQBuAGQAZQB4ACAAYQByAHIAYQB5AF8AMgBEAC4AXABuACAAIAAgACAAIiAgAE0AYQB4AGkAbQB1AG0AIABlAG4AdQBtAGUAcgBhAHQAaQBvAG4AIABzAGkAegBlACAAaQBzACAAYwBhAHAAcABlAGQAIABhAHQAIAAxACwAMAA0ADgALAA1ADcANgAgAHIAbwB3AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARQBuAHUAbQBlAHIAYQB0AGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQB0AGUAbQBzACwAXABuACAAIAAgACAAawAsAFwAbgAgACAAIAAgAHQAeQBwAGUALABcAG4AXABuAEkARgAoAE8AUgAoAEkAUwBUAEUAWABUACgAawApACwAIABrACAAPAAgADAALAAgAGsAIAA+ACAAQwBPAFUATgBUAEEAKABpAHQAZQBtAHMAKQApACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABDAE8AVQBOAFQAQQAoAGsAKQAgADwAPgAgADEALAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAQwBPAFUATgBUAEEAKABpAHQAZQBtAHMAKQAgAF4AIABrACAAPgAgADEAMAA0ADgANQA3ADYALAAjAE4AVQBNACEALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAdABlAG0AcwBcAG4AIAAgACAAIABsAGkAcwB0ACwAIAAgACAAIABUAE8AQwBPAEwAKABpAHQAZQBtAHMAKQAsAFwAbgAgACAAIAAgAG4ALAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAbABpAHMAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAHIAbwB3AHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAbgAgAF4AIABrACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAYQBzAGUAIABnAGUAbgBlAHIAYQB0AG8AcgA6ACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AFwAbgAgACAAIAAgAFAAXwByACwAIAAgACAAIAAgAEwAQQBNAEIARABBACgAMQAgACsAIABNAE8ARAAoAFEAVQBPAFQASQBFAE4AVAAoAFMARQBRAFUARQBOAEMARQAoAGkAKQAsAG4AIABeACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAGsALAAgAGsAIAAtACAAMQAsACAALQAxACkAKQAsAG4AKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAZQByAG0AdQB0AGEAdABpAG8AbgBzACAAKABuAG8AIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAKQBcAG4AIAAgACAAIABQACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEYASQBMAFQARQBSACgAUABfAHIAKAApACwASQBTAE4AQQAoAEIAWQBSAE8AVwAoAFAAXwByACgAKQAsACAATQBPAEQARQApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdABcAG4AIAAgACAAIABDAF8AcgAsACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEYASQBMAFQARQBSACgAUABfAHIAKAApACwAQgBZAFIATwBXACgAUABfAHIAKAApACwATABBAE0AQgBEAEEAKAByAG8AdwAsACAAQQBOAEQAKAByAG8AdwAgAD0AIABTAE8AUgBUACgAcgBvAHcALAAsACwAMQApACkAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwAgACgAbgBvACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0ACkAXABuACAAIAAgACAAQwAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAEMAXwByACgAKQAsAEkAUwBOAEEAKABCAFkAUgBPAFcAKABDAF8AcgAoACkALAAgAE0ATwBEAEUAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwBcAG4AIAAgACAAIABEACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEYASQBMAFQARQBSACgAUABfAHIAKAApACwAQgBZAFIATwBXACgAUABfAHIAKAApACwATABBAE0AQgBEAEEAKAByAG8AdwAsACAATgBPAFQAKABPAFIAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAawApACAAPQAgAHIAbwB3ACkAKQApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAZwBlAG4AZQByAGEAdABvAHIAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAATABBAE0AQgBEAEEAKABDAEgATwBPAFMARQAoAHQAeQBwAGUALAAgAFAAXwByACgAKQAsACAAUAAoACkALAAgAEMAXwByACgAKQAsACAAQwAoACkALAAgAEQAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHUAYgBzAHQAaQB0AHUAdABlACAAaQB0AGUAbQBzACAAdQBuAGwAZQBzAHMAIAB0AGgAZQB5ACAAYQByAGUAIABlAHgAYQBjAHQAbAB5ACAAMQAuAC4AbgBcAG4AIAAgACAAIABOAG8AdABJAG4AdAA/ACwAIABOAE8AVAAoAEEATgBEACgAUwBFAFEAVQBFAE4AQwBFACgAbgApACAAPQAgAGwAaQBzAHQAKQApACwAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAASQBGACgATgBvAHQASQBuAHQAPwAsACAASQBOAEQARQBYACgAbABpAHMAdAAsACAAaQBkAHgAKAApACkALAAgAGkAZAB4ACgAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEMAQgAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABQAGUAcgBtAFIAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaQB0AGgAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAIAAoAGsAESB0AHUAcABsAGUAcwAgAGQAcgBhAHcAbgAgAGYAcgBvAG0AIABuACAAaQB0AGUAbQBzACkALgBcAG4AIAAgACAAIABFAGEAYwBoACAAcgBvAHcAIABvAGYAIAB0AGgAZQAgAHIAZQBzAHUAbAB0ACAAcgBlAHAAcgBlAHMAZQBuAHQAcwAgAG8AbgBlACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuACAAbwBmACAAbABlAG4AZwB0AGgAIABrAC4AIABTAHUAcABwAG8AcgB0AHMAXABuACAAIAAgACAAcwBjAGEAbABhAHIALAAgADEARAAsACAAYQBuAGQAIAAyAEQAIABpAHQAZQBtACAAYQByAHIAYQB5AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIABpAHQAZQBtAHMALgAgAEkAdABlAG0AcwAgAG0AYQB5ACAAYgBlACAAbgB1AG0AYgBlAHIAcwAgAG8AcgAgAHQAZQB4AHQALgBcAG4AXABuACAAIAAgACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4AXABuACAAIAAgACAAIAAgACAAIABMAGUAbgBnAHQAaAAgAG8AZgAgAGUAYQBjAGgAIAB0AHUAcABsAGUAIAAoAGsAIABlIiAAMAApAC4AIABNAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAEUAbgB1AG0AZQByAGEAdABlALsDKABpAHQAZQBtAHMALAAgAGsALAAgADEAKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBQAGUAcgBtAFIAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQB0AGUAbQBzACwAXABuACAAIAAgACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALABcAG4AIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgAsACAAMQApAFwAbgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFAAZQByAG0AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaQB0AGgAbwB1AHQAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQALgAgAEUAYQBjAGgAIAByAG8AdwAgAG8AZgAgAHQAaABlACAAcgBlAHMAdQBsAHQAIAByAGUAcAByAGUAcwBlAG4AdABzAFwAbgAgACAAIAAgAG8AbgBlACAAawARIHQAdQBwAGwAZQAgAGQAcgBhAHcAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGkAdABlAG0AcwAsACAAdwBpAHQAaAAgAG4AbwAgAHIAZQBwAGUAYQB0AGUAZAAgAHAAbwBzAGkAdABpAG8AbgBzAC4AIABTAHUAcABwAG8AcgB0AHMAXABuACAAIAAgACAAcwBjAGEAbABhAHIALAAgADEARAAsACAAYQBuAGQAIAAyAEQAIABpAHQAZQBtACAAYQByAHIAYQB5AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIABpAHQAZQBtAHMALgAgAEkAdABlAG0AcwAgAG0AYQB5ACAAYgBlACAAbgB1AG0AYgBlAHIAcwAgAG8AcgAgAHQAZQB4AHQALgBcAG4AXABuACAAIAAgACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4AXABuACAAIAAgACAAIAAgACAAIABMAGUAbgBnAHQAaAAgAG8AZgAgAGUAYQBjAGgAIAB0AHUAcABsAGUAIAAoAGsAIABlIiAAMAApAC4AIABNAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAEUAbgB1AG0AZQByAGEAdABlALsDKABpAHQAZQBtAHMALAAgAGsALAAgADIAKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBQAGUAcgBtALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAXABuACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEMAQgAwADMAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwBSALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0ACAAKABtAHUAbAB0AGkAcwBlAHQAcwApAC4AIABFAGEAYwBoACAAcgBvAHcAIABvAGYAIAB0AGgAZQAgAHIAZQBzAHUAbAB0AFwAbgAgACAAIAAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQAgAGsAESBlAGwAZQBtAGUAbgB0ACAAbQB1AGwAdABpAHMAZQB0ACAAZAByAGEAdwBuACAAZgByAG8AbQAgAHQAaABlACAAaQBuAHAAdQB0ACAAaQB0AGUAbQBzACwAIAB3AGgAZQByAGUAIABvAHIAZABlAHIAXABuACAAIAAgACAAZABvAGUAcwAgAG4AbwB0ACAAbQBhAHQAdABlAHIAIABhAG4AZAAgAHIAZQBwAGUAYQB0AGUAZAAgAHMAZQBsAGUAYwB0AGkAbwBuAHMAIABhAHIAZQAgAGEAbABsAG8AdwBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIABpAHQAZQBtAHMALgAgAEkAdABlAG0AcwAgAG0AYQB5ACAAYgBlACAAbgB1AG0AYgBlAHIAcwAgAG8AcgAgAHQAZQB4AHQALgBcAG4AXABuACAAIAAgACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4AXABuACAAIAAgACAAIAAgACAAIABTAGkAegBlACAAbwBmACAAZQBhAGMAaAAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgACgAawAgAGUiIAAwACkALgAgAE0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABFAHEAdQBpAHYAYQBsAGUAbgB0ACAAdABvACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAawAsACAAMwApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQB0AGUAbQBzACwAXABuACAAIAAgACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALABcAG4AIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgAsACAAMwApAFwAbgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAANABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAB3AGkAdABoAG8AdQB0ACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AC4AIABFAGEAYwBoACAAcgBvAHcAIABvAGYAIAB0AGgAZQAgAHIAZQBzAHUAbAB0ACAAcgBlAHAAcgBlAHMAZQBuAHQAcwBcAG4AIAAgACAAIABvAG4AZQAgAGsAESBlAGwAZQBtAGUAbgB0ACAAcwB1AGIAcwBlAHQAIABkAHIAYQB3AG4AIABmAHIAbwBtACAAdABoAGUAIABpAG4AcAB1AHQAIABpAHQAZQBtAHMALAAgAHcAaABlAHIAZQAgAG8AcgBkAGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAG0AYQB0AHQAZQByAFwAbgAgACAAIAAgAGEAbgBkACAAcgBlAHAAZQBhAHQAZQBkACAAcwBlAGwAZQBjAHQAaQBvAG4AcwAgAGEAcgBlACAAbgBvAHQAIABhAGwAbABvAHcAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQBzAC4AIABJAHQAZQBtAHMAIABtAGEAeQAgAGIAZQAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0AC4AXABuAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAUwBpAHoAZQAgAG8AZgAgAGUAYQBjAGgAIABjAG8AbQBiAGkAbgBhAHQAaQBvAG4AIAAoAGsAIABlIiAAMAApAC4AIABNAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAEUAbgB1AG0AZQByAGEAdABlALsDKABpAHQAZQBtAHMALAAgAGsALAAgADQAKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABpAHQAZQBtAHMALABcAG4AIAAgACAAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgAsAFwAbgAgACAAIAAgAEUAbgB1AG0AZQByAGEAdABlALsDKABpAHQAZQBtAHMALAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAIAA0ACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBDAEIAMAA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARABlAHIAYQBuAGcAZQBtAGUAbgB0AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABkAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwAgAG8AZgAgAGwAZQBuAGcAdABoACAAawAuACAAQQAgAGQAZQByAGEAbgBnAGUAbQBlAG4AdAAgAGkAcwAgAGEAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AIABpAG4AIAB3AGgAaQBjAGgAXABuACAAIAAgACAAbgBvACAAZQBsAGUAbQBlAG4AdAAgAGEAcABwAGUAYQByAHMAIABpAG4AIABpAHQAcwAgAG8AcgBpAGcAaQBuAGEAbAAgAHAAbwBzAGkAdABpAG8AbgAuACAARQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIAByAGUAcwB1AGwAdABcAG4AIAAgACAAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABkAGUAcgBhAG4AZwBlAGQAIABrABEgdAB1AHAAbABlACAAZAByAGEAdwBuACAAZgByAG8AbQAgAHQAaABlACAAaQBuAHAAdQB0ACAAaQB0AGUAbQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQBzAC4AIABJAHQAZQBtAHMAIABtAGEAeQAgAGIAZQAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0AC4AXABuAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuAFwAbgAgACAAIAAgACAAIAAgACAATABlAG4AZwB0AGgAIABvAGYAIABlAGEAYwBoACAAdAB1AHAAbABlACAAKABrACAAZSIgADAAKQAuACAATQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABrACwAIAA1ACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABlAHIAYQBuAGcAZQBtAGUAbgB0AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQB0AGUAbQBzACwAXABuACAAIAAgACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALABcAG4AIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgAsACAANQApAFwAbgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEsAbgBhAHAAUwBhAGMAawC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEQAZQBjADIAQgBpAG4AuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAbwBsAHYAZQBzACAAdABoAGUAIAAwABEgMQAgAGsAbgBhAHAAcwBhAGMAawAgAHAAcgBvAGIAbABlAG0AIABiAHkAIABlAG4AdQBtAGUAcgBhAHQAaQBuAGcAIABhAGwAbAAgAHMAdQBiAHMAZQB0AHMAIABvAGYAIABpAHQAZQBtAHMAIABhAG4AZABcAG4AIAAgACAAIABzAGUAbABlAGMAdABpAG4AZwAgAHQAaABlACAAZgBlAGEAcwBpAGIAbABlACAAcABhAGMAawAoAHMAKQAgAHcAaQB0AGgAIABtAGEAeABpAG0AdQBtACAAdABvAHQAYQBsACAAdgBhAGwAdQBlAC4AIABVAHMAZQBzACAAYQAgAGIAcgB1AHQAZQARIGYAbwByAGMAZQAsAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAGkAegBlAGQAIABiAGkAdAARIG0AYQBzAGsAIABnAGUAbgBlAHIAYQB0AG8AcgAgAGEAbgBkACAAcwB1AHAAcABvAHIAdABzACAAYgBvAHQAaAAgAG4AdQBtAGUAcgBpAGMAIABhAG4AZAAgAHQAZQB4AHQAIABpAHQAZQBtACAAbABhAGIAZQBsAHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXABuACAAIAAgACAAIAAgACAAIABBAHIAcgBhAHkAIABvAGYAIABpAHQAZQBtACAAbABhAGIAZQBsAHMAIAAoAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0ACkALgBcAG4AXABuACAAIAAgACAAdgBhAGwAdQBlAF8AbwBmAF8AaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAHYAYQBsAHUAZQBzACAAYwBvAHIAcgBlAHMAcABvAG4AZABpAG4AZwAgAHQAbwAgAGUAYQBjAGgAIABpAHQAZQBtAC4AXABuAFwAbgAgACAAIAAgAHcAZQBpAGcAaAB0AHMAXABuACAAIAAgACAAIAAgACAAIABBAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAdwBlAGkAZwBoAHQAcwAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIAB0AG8AIABlAGEAYwBoACAAaQB0AGUAbQAuAFwAbgBcAG4AIAAgACAAIABjAGEAcABhAGMAaQB0AHkAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAgAG4AdQBtAGUAcgBpAGMAIAB3AGUAaQBnAGgAdAAgAGwAaQBtAGkAdAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAGkAdABlAG0AcwAsACAAdgBhAGwAdQBlAF8AbwBmAF8AaQB0AGUAbQBzACwAIABhAG4AZAAgAHcAZQBpAGcAaAB0AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAdwBpAHQAaAAgAFQATwBSAE8AVwAuAFwAbgAgACAAIAAgACIgIABjAGEAcABhAGMAaQB0AHkAIABpAHMAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAdABvACAAYQAgAHMAYwBhAGwAYQByACAAdwBpAHQAaAAgAEkATgBEAEUAWAAoAGMAYQBwAGEAYwBpAHQAeQAsADEALAAxACkALgBcAG4AIAAgACAAIAAiICAATQBhAHgAaQBtAHUAbQAgAGkAdABlAG0AIABjAG8AdQBuAHQAIABpAHMAIABjAGEAcABwAGUAZAAgAGEAdAAgADIAMAAgAHQAbwAgAGEAdgBvAGkAZAAgAGMAbwBtAGIAaQBuAGEAdABvAHIAaQBhAGwAIABlAHgAcABsAG8AcwBpAG8AbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBLAG4AYQBwAFMAYQBjAGsAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQB0AGUAbQBzACwAXABuACAAIAAgACAAdgBhAGwAdQBlAF8AbwBmAF8AaQB0AGUAbQBzACwAXABuACAAIAAgACAAdwBlAGkAZwBoAHQAcwAsAFwAbgAgACAAIAAgAGMAYQBwAGEAYwBpAHQAeQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABIAGEAbAB0AGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAAVABvAG8ATQBhAG4AeQBJAHQAZQBtAHMAPwAsACAAIAAgAFIATwBXAFMAKABpAHQAZQBtAHMAKQAgACoAIABDAE8ATABVAE0ATgBTACgAaQB0AGUAbQBzACkAIAA+ACAAMgAwACwAXABuACAAIAAgACAAVABlAHgAdABJAHQAZQBtAFYAYQBsAD8ALAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAdgBhAGwAdQBlAF8AbwBmAF8AaQB0AGUAbQBzACkAKQAsAFwAbgAgACAAIAAgAFQAZQB4AHQAVwBlAGkAZwBoAHQAcwA/ACwAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHcAZQBpAGcAaAB0AHMAKQApACwAXABuACAAIAAgACAAVABlAHgAdABDAGEAcABhAGMAaQB0AHkAPwAsACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYwBhAHAAYQBjAGkAdAB5ACkAKQAsAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBNAGEAdABjAGgAPwAsACAAIABPAFIAKABDAE8AVQBOAFQAQQAoAGkAdABlAG0AcwApACAAPAA+ACAAQwBPAFUATgBUAEEAKAB2AGEAbAB1AGUAXwBvAGYAXwBpAHQAZQBtAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAGkAdABlAG0AcwApACAAPAA+ACAAQwBPAFUATgBUAEEAKAB3AGUAaQBnAGgAdABzACkAKQAsAFwAbgBcAG4AIAAgACAAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABUAGUAeAB0AEkAdABlAG0AVgBhAGwAPwAsAFQAZQB4AHQAVwBlAGkAZwBoAHQAcwA/ACwAVABlAHgAdABDAGEAcABhAGMAaQB0AHkAPwAsAFMAaABhAHAAZQBNAGkAcwBNAGEAdABjAGgAPwApACwAXABuAFwAbgAgACAAIAAgAGUAeABpAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABzAGMAZQBuAGEAcgBpAG8AcwApACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMAVgBBAEwAVQBFAC0ASQBUAEUATQAhAFwAIgA7AFwAIgAjAFYAQQBMAFUARQAtAFcARQBJAEcASABUAFMAIQBcACIAOwBcACIAIwBWAEEATABVAEUALQBDAEEAUABBAEMASQBUAFkAIQBcACIAOwBcACIAIwBJAE4AUABVAFQALQBNAEkAUwBNAEEAVABDAEgAIQBcACIAfQAsAFwAbgBcAG4AIAAgACAAIABhAGwAZQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBSAFIAQQBZAFQATwBUAEUAWABUACgARgBJAEwAVABFAFIAKABlAHIAcgBvAHIAcwAsACAAcwBjAGUAbgBhAHIAaQBvAHMAKQApACwAXABuAFwAbgBJAEYAKABUAG8AbwBNAGEAbgB5AEkAdABlAG0AcwA/ACwAXAAiACMAVABPAE8ALQBNAEEATgBZAC0ASQBUAEUATQBTACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAGUAeABpAHQALABhAGwAZQByAHQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsACAAIAAgACAAIAAgACAAIAAgACAAVABPAFIATwBXACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAB2AGEAbAB1AGUAXwBvAGYAXwBpAHQAZQBtAHMALAAgAFQATwBSAE8AVwAoAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwApACwAXABuACAAIAAgACAAdwBlAGkAZwBoAHQAcwAsACAAIAAgACAAIAAgACAAIABUAE8AUgBPAFcAKAB3AGUAaQBnAGgAdABzACkALABcAG4AIAAgACAAIABjAGEAcABhAGMAaQB0AHkALAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGMAYQBwAGEAYwBpAHQAeQAsACAAMQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAYQBiAGUAbABzAFwAbgAgACAAIAAgAGwAYQBiAGUAbABzACwAIAAgACAAIAAgACAAIAAgACAAewBcACIASQB0AGUAbQBzAFwAIgA7ACAAXAAiAFYAYQBsAHUAZQBcACIAOwAgAFwAIgBXAGUAaQBnAGgAdABcACIAOwAgAFwAIgBQAGEAYwBrAFwAIgB9ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbgB1AG0AZQByAGEAdABpAG8AbgBcAG4AIAAgACAAIABuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIABDACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoADIAIABeACAAbgAgAC0AIAAxACkALABcAG4AIAAgACAAIABiAGkAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBjADIAQgBpAG4AuwMoAEMALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABXAGUAaQBnAGgAdAAgAGYAZQBhAHMAaQBiAGkAbABpAHQAeQBcAG4AIAAgACAAIAB3AF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgAGIAaQBuACAAKgAgAHcAZQBpAGcAaAB0AHMALABcAG4AIAAgACAAIABmAGUAYQBzAGkAYgBsAGUAPwAsACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAHcAXwBhAHIAcgAsACAAUwBVAE0AKQAgADwAPQAgAGMAYQBwAGEAYwBpAHQAeQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbAB1AGUAIABjAG8AbQBwAHUAdABhAHQAaQBvAG4AXABuACAAIAAgACAAdgBhAGwAXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGIAaQBuACAAKgAgAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwAsACAAZgBlAGEAcwBpAGIAbABlAD8ALAAgADAAKQAsAFwAbgAgACAAIAAgAHQAbwB0AGEAbABzACwAIAAgACAAIAAgACAAIAAgACAAQgBZAFIATwBXACgAdgBhAGwAXwBhAHIAcgAsACAAUwBVAE0AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAG8AcAB0AGkAbQBhAGwAIABwAGEAYwBrACgAcwApAFwAbgAgACAAIAAgAHAAYQBjAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAEYASQBMAFQARQBSACgAdgBhAGwAXwBhAHIAcgAsACAATQBBAFgAKAB0AG8AdABhAGwAcwApACAAPQAgAHQAbwB0AGEAbABzACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGkAbgBhAGwAIAB0AGEAYgBsAGUAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYATgBBACgASABTAFQAQQBDAEsAKABsAGEAYgBlAGwAcwAsACAAVgBTAFQAQQBDAEsAKABpAHQAZQBtAHMALAAgAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwAsACAAdwBlAGkAZwBoAHQAcwAsACAAcABhAGMAawApACkALABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBDAEIAMAA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUwB1AGIAcwBlAHQARwBlAG4AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAbABsACAAbgBvAG4AESBlAG0AcAB0AHkAIABzAHUAYgBzAGUAdABzACAAbwBmACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgAGwAaQBzAHQAIAB1AHMAaQBuAGcAIABiAHIAdQB0AGUAESBmAG8AcgBjAGUAXABuACAAIAAgACAAYgBpAHQAbQBhAHMAawBpAG4AZwAuACAARQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIAByAGUAcwB1AGwAdAAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQAgAHMAdQBiAHMAZQB0ACwAIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAXABuACAAIAAgACAAYwBvAG0AbQBhABEgcwBlAHAAYQByAGEAdABlAGQAIABzAHQAcgBpAG4AZwAuACAAUwB1AHAAcABvAHIAdABzACAAbgB1AG0AYgBlAHIAcwAgAG8AcgAgAHQAZQB4AHQAIABpAHQAZQBtAHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABzAGUAdABcAG4AIAAgACAAIAAgACAAIAAgAEEAcgByAGEAeQAgAG8AZgAgAGkAdABlAG0AcwAgACgAbgB1AG0AYgBlAHIAcwAgAG8AcgAgAHQAZQB4AHQAKQAuACAARgBsAGEAdAB0AGUAbgBlAGQAIAB3AGkAdABoACAAVABPAFIATwBXAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAATQBhAHgAaQBtAHUAbQAgAGkAdABlAG0AIABjAG8AdQBuAHQAIABpAHMAIABjAGEAcABwAGUAZAAgAGEAdAAgADIAMAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHUAYgBzAGUAdABHAGUAbgC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABzAGUAdAAsAFwAbgBcAG4ASQBGACgAUgBPAFcAUwAoAHMAZQB0ACkAIAAqACAAQwBPAEwAVQBNAE4AUwAoAHMAZQB0ACkAIAA+ACAAMgAwACwAXAAiACMAVABPAE8ALQBNAEEATgBZAC0ASQBUAEUATQBTACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAXABuACAAIAAgACAAcwBlAHQALAAgACAAIAAgAFQATwBSAE8AVwAoAHMAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgAG4ALAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHMAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBpAHQAIABtAGEAcwBrAHMAIAAoAGUAeABjAGwAdQBkAGUAIAAwACkAXABuACAAIAAgACAAQwAsACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoADIAIABeACAAbgAgAC0AIAAxACkALABcAG4AIAAgACAAIABiAGkAbgAsACAAIAAgACAARABlAGMAMgBCAGkAbgC7AygAQwAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAbQBhAHMAawBlAGQALAAgAEkARgAoAGIAaQBuACwAIABzAGUAdAAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBuAHYAZQByAHQAIABlAGEAYwBoACAAbQBhAHMAawBlAGQAIAByAG8AdwAgAGkAbgB0AG8AIABhACAAYwBvAG0AcABhAGMAdAAgAHMAdQBiAHMAZQB0ACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgAEIAWQBSAE8AVwAoAG0AYQBzAGsAZQBkACwAIABMAEEATQBCAEQAQQAoAHYALAAgAFQARQBYAFQASgBPAEkATgAoAFwAIgAsACAAXAAiACwAIAAxACwAIAB2ACkAKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBDAEIAMAA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUwB1AGIAcwBlAHQAUwB1AG0AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdAB1AHIAbgBzACAAYQBsAGwAIABzAHUAYgBzAGUAdABzACAAbwBmACAAYQAgAG4AdQBtAGUAcgBpAGMAIABzAGUAdAAgAHcAaABvAHMAZQAgAGUAbABlAG0AZQBuAHQAcwAgAHMAdQBtACAAZQB4AGEAYwB0AGwAeQAgAHQAbwAgAGEAIAB0AGEAcgBnAGUAdAAuAFwAbgAgACAAIAAgAFUAcwBlAHMAIABiAHIAdQB0AGUAESBmAG8AcgBjAGUAIABiAGkAdABtAGEAcwBrAGkAbgBnACAAKABuACAAZCIgADIAMAApAC4AIABFAGEAYwBoACAAcwB1AGIAcwBlAHQAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIABhACAAYwBvAG0AcABhAGMAdABcAG4AIAAgACAAIABjAG8AbQBtAGEAESBzAGUAcABhAHIAYQB0AGUAZAAgAHMAdAByAGkAbgBnAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAcwBlAHQAXABuACAAIAAgACAAIAAgACAAIABBAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAaQB0AGUAbQBzAC4AIABGAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AUgBPAFcALgAgAFQAZQB4AHQAIABpAHMAIABuAG8AdAAgAGEAbABsAG8AdwBlAGQALgBcAG4AXABuACAAIAAgACAAdABhAHIAZwBlAHQAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAgAG4AdQBtAGUAcgBpAGMAIAB0AGEAcgBnAGUAdAAgAHMAdQBtAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBtAHAAdAB5ACAAcwB1AGIAcwBlAHQAIABpAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABjAG8AbgBzAHQAcgB1AGMAdABpAG8AbgAgACgAYgBpAHQAbQBhAHMAawAgADAAIABvAG0AaQB0AHQAZQBkACkALgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAE4ATwAtAFMATwBMAFUAVABJAE8ATgAhAFwAIgAgAGkAZgAgAG4AbwAgAHMAdQBiAHMAZQB0AHMAIABtAGEAdABjAGgAIAB0AGgAZQAgAHQAYQByAGcAZQB0AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAdQBiAHMAZQB0AFMAdQBtALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHMAZQB0ACwAXABuACAAIAAgACAAdABhAHIAZwBlAHQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABzAGMAYQBsAGEAcgBcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAsACAASQBOAEQARQBYACgAdABhAHIAZwBlAHQALAAgADEALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGEAbAB0AGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAAVABvAG8ATQBhAG4AeQBJAHQAZQBtAHMAPwAsACAAUgBPAFcAUwAoAHMAZQB0ACkAIAAqACAAQwBPAEwAVQBNAE4AUwAoAHMAZQB0ACkAIAA+ACAAMgAwACwAXABuACAAIAAgACAAVABlAHgAdABTAGUAdAA/ACwAIAAgACAAIAAgACAATwBSACgASQBTAEUAUgBSAE8AUgAoAC0ALQBzAGUAdAApACkALABcAG4AIAAgACAAIABUAGUAeAB0AFQAYQByAGcAZQB0AD8ALAAgACAAIABJAFMARQBSAFIATwBSACgALQAtAHQAYQByAGcAZQB0ACkALABcAG4AXABuAEkARgAoAFQAbwBvAE0AYQBuAHkASQB0AGUAbQBzAD8ALAAgAFwAIgAjAFQATwBPAC0ATQBBAE4AWQAtAEkAVABFAE0AUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABUAGUAeAB0AFMAZQB0AD8ALAAgAFwAIgAjAFQARQBYAFQALQBTAEUAVAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAFQAZQB4AHQAVABhAHIAZwBlAHQAPwAsACAAXAAiACMAVABFAFgAVAAtAFQAQQBSAEcARQBUACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAXABuACAAIAAgACAAcwBlAHQALAAgACAAIAAgACAAIABUAE8AUgBPAFcAKAAtAC0AcwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABpAHQAZQBtAHMAXABuACAAIAAgACAAbgAsACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHMAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBpAHQAIABtAGEAcwBrAHMAIAAoAGUAeABjAGwAdQBkAGUAIAAwACkAXABuACAAIAAgACAAQwAsACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAyACAAXgAgAG4AIAAtACAAMQApACwAXABuACAAIAAgACAAYgBpAG4ALAAgACAAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDKABDACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAbQBhAHMAawBcAG4AIAAgACAAIAB2AGEAbABfAGEAcgByACwAIAAgAEkARgAoAGIAaQBuACwAIABzAGUAdAAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBjAGEAdABlACAAdABhAHIAZwBlAHQAIABzAHUAbQBcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAAIAAgAEIAWQBSAE8AVwAoAHYAYQBsAF8AYQByAHIALAAgAFMAVQBNACkAIAA9ACAAdABhAHIAZwBlAHQALABcAG4AIAAgACAAIABmAG8AdQBuAGQALAAgACAAIAAgAEYASQBMAFQARQBSACgAdgBhAGwAXwBhAHIAcgAsACAAYgBvAG8AbAAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBuAHYAZQByAHQAIABlAGEAYwBoACAAcwB1AGIAcwBlAHQAIAB0AG8AIABhACAAYwBvAG0AcABhAGMAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgAEMAbwBuAGMAaQBzAGUAuwMsACAATABBAE0AQgBEAEEAKAB2ACwAIABUAEUAWABUAEoATwBJAE4AKABcACIALAAgAFwAIgAsACAAMQAsACAAVABFAFgAVAAoAHYALAAgAFwAIgAwADsALQAwADsAOwBcACIAKQApACkALABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgAEIAWQBSAE8AVwAoAGYAbwB1AG4AZAAsACAAQwBvAG4AYwBpAHMAZQC7AykALABcAG4AXABuACAAIAAgACAALwAvACAASABhAG4AZABsAGUAIABuAG8AIABtAGEAdABjAGgAZQBzAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAASQBGACgAUwBVAE0AKABMAEUATgAoAHIAZQBzAHUAbAB0ACkAKQAgAD0AIAAwACwAIABcACIAIwBOAE8ALQBTAE8ATABVAFQASQBPAE4AIQBcACIALAAgAHIAZQBzAHUAbAB0ACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAEcARABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAxADAAIAAUICAARwByAGkAZAAgAEQAaQBhAGcAbgBvAHMAdABpAGMAcwBcAG4ALwAvACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAHIAaQBkACAARABpAGEAZwBuAG8AcwB0AGkAYwBzACAAYwBvAG4AdABhAGkAbgBzACAAZgB1AG4AYwB0AGkAbwBuAHMAIAB3AGgAbwBzAGUAIABwAHUAcgBwAG8AcwBlACAAaQBzACAAdABvACAAZQB4AHAAbwBzAGUALAAgAGEAbgBuAG8AdABhAHQAZQAsAFwAbgAgACAAIAAgAG8AcgAgAGUAeABwAGwAYQBpAG4AIAB0AGgAZQAgAGkAbgB0AGUAcgBuAGEAbAAgAHMAdAByAHUAYwB0AHUAcgBlACAAbwBmACAAYQAgAGcAcgBpAGQALgAgAEQAaQBhAGcAbgBvAHMAdABpAGMAcwAgAGYAdQBuAGMAdABpAG8AbgBzACAAYQByAGUAXABuACAAIAAgACAAdQBzAGUAZAAgAGYAbwByACAAZABlAGIAdQBnAGcAaQBuAGcALAAgAGkAbgB0AHIAbwBzAHAAZQBjAHQAaQBvAG4ALAAgAHYAaQBzAHUAYQBsAGkAegBhAHQAaQBvAG4ALAAgAGEAbgBkACAAcwB0AHIAdQBjAHQAdQByAGEAbAAgAGEAbgBhAGwAeQBzAGkAcwAuAFwAbgBcAG4ARgB1AG4AYwB0AGkAbwBuAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHYAZQBhAGwAuwNcAG4AIAAgACAAIAAgACAAIAAgAGkAbgBzAHAAZQBjAHQAcwAgAGEAIABhAHIAcgBhAHkAXwAyAEQAIABvAGYAIABkAGEAdABhACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAZQBpAHQAaABlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIiAgAEEAIAB0AG8AcAAtAGwAZQB2AGUAbAAgAHMAdQBtAG0AYQByAHkAIABvAGYAIABzAGUAbQBhAG4AdABpAGMAIABtAGUAdAByAGkAYwBzACAAKABOAHUAbQBiAGUAcgBzACwAIABUAGUAeAB0AHMALAAgAEUAcgByAG8AcgBzACwAIABlAHQAYwAuACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABBACAAdgBlAHIAYgBvAHMAZQAsACAAYwBlAGwAbAAtAGIAeQAtAGMAZQBsAGwAIABuAGEAcgByAGEAdABpAG8AbgAgAG8AZgAgAHQAYQBnAHMAIABwAGUAcgAgAGMAZQBsAGwAXABuACoALwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEQAMAAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUgBlAHYAZQBhAGwAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEcAcgBpAGQAIABEAGkAYQBnAG4AbwBzAHQAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdgBlAGEAbAC7AyAAaQBuAHMAcABlAGMAdABzACAAYQAgAGEAcgByAGEAeQBfADIARAAgAG8AZgAgAGQAYQB0AGEAIABhAG4AZAAgAHIAZQB0AHUAcgBuAHMAIABlAGkAdABoAGUAcgA6AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEEAIAB0AG8AcAAtAGwAZQB2AGUAbAAgAHMAdQBtAG0AYQByAHkAIABvAGYAIABzAGUAbQBhAG4AdABpAGMAIABtAGUAdAByAGkAYwBzACAAKABOAHUAbQBiAGUAcgBzACwAIABUAGUAeAB0AHMALAAgAEUAcgByAG8AcgBzACwAIABlAHQAYwAuACkAXABuACAAIAAgACAAIAAgACAAIAAiICAAQQAgAHYAZQByAGIAbwBzAGUALAAgAGMAZQBsAGwALQBiAHkALQBjAGUAbABsACAAbgBhAHIAcgBhAHQAaQBvAG4AIABvAGYAIAB0AGEAZwBzACAAcABlAHIAIABjAGUAbABsAFwAbgAgACAAIAAgAFMAdQBwAHAAbwByAHQAcwAgAG8AcAB0AGkAbwBuAGEAbAAgAGQAZQBsAGkAbQBpAHQAZQByACAAYwBvAG4AdAByAG8AbAAgAGEAbgBkACAAYgBsAGEAbgBrAC0AYQB3AGEAcgBlACAAbwBwAHQAaQBtAGkAegBhAHQAaQBvAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABkAGEAdABhAFwAbgAgACAAIAAgACAAIAAgACAARABhAHQAYQAgAHQAbwAgAGIAZQAgAGkAbgBzAHAAZQBjAHQAZQBkACAAKABhAG4AeQAgAHMAYwBhAGwAYQByACwAIAB2AGUAYwB0AG8AcgAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACkALgBcAG4AXABuACAAIAAgACAASQBzAFYAZQByAGIAbwBzAGUAPwAgACAAWwBvAHAAdABpAG8AbgBhAGwAXQBcAG4AIAAgACAAIAAgACAAIAAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuAHMAIABhACAAYQByAHIAYQB5AF8AMgBEACAAbwBmACAAbgBhAHIAcgBhAHQAYQBiAGwAZQAgAHQAYQBnAHMAIABwAGUAcgAgAGMAZQBsAGwALgBcAG4AIAAgACAAIAAgACAAIAAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHIAZQB0AHUAcgBuAHMAIABhACAAOQDXADIAIABzAHUAbQBtAGEAcgB5ACAAdABhAGIAbABlAC4AXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByACAAIAAgAFsAbwBwAHQAaQBvAG4AYQBsAF0AXABuACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAgAHUAcwBlAGQAIABpAG4AIAB2AGUAcgBiAG8AcwBlACAAbQBvAGQAZQAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAXAAiACwAIABcACIALgBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQB2AGUAYQBsALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGQAYQB0AGEALAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAWwBJAHMAVgBlAHIAYgBvAHMAZQA/AF0ALABcAG4AIAAgACAAIABbAGQAZQBsAGkAbQBpAHQAZQByAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGQAYQB0AGEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbABsACAAbQBlAHQAcgBpAGMAIABsAGEAYgBlAGwAcwBcAG4AIAAgACAAIABtAGUAdAByAGkAYwBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgBOAHUAbQBiAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHgAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgB1AG0AYgBlAHIALQBzAHQAbwByAGUAZAAtAGEAcwAtAHQAZQB4AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAcgByAG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG4AdABhAGkAbgBzACAAcwBwAGEAYwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBuAHQAYQBpAG4AcwAgAHMAcABlAGMAaQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBtAHUAbABhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBuAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBnAGkAYwBhAGwAXAAiAH0ALABcAG4AXABuACAAIAAgACAALwAvAC0ALQAgAEwAbwBjAGEAbAAgAGYAdQBuAGMAdABpAG8AbgBzACAALQAtAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAbQBhAHQAcgBpAGMAZQBzACAAYQBuAGQAIABlAG4AcwB1AHIAZQAgAGIAaQBuAGEAcgB5ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAQgBpAG4AuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAB2ACwAIABUAE8AQwBPAEwAKABJAEYARQBSAFIATwBSACgAdgAsACAAMAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAbQBvAHYAZQAgAGUAcgByAG8AcgBzACAAZgByAG8AbQAgAHMAYwBhAGwAYQByAHMALgBcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBOAEEAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALAAgAEkARgBOAEEAKAB2ACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABkAGUAbABpAG0AaQB0AGUAcgAgAGYAbwByACAAdgBlAHIAYgBvAHMAZQAgAHIAZQBwAG8AcgB0AC4AXABuACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABkAGUAbABpAG0AaQB0AGUAcgApACwAIABcACIALAAgAFwAIgAsACAAZABlAGwAaQBtAGkAdABlAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGUAcgBiAG8AcwBlACAAcgBlAHAAbwByAHQAIAAtACAAcgBlAHQAdQByAG4AcwAgAG4AYQByAHIAYQB0AGEAYgBsAGUAIAB0AGEAZwBzACAAYgB5ACAAYwBlAGwAbAAuACAAVABlAHIAbQBpAG4AYQB0AGUAcwAgAGUAYQByAGwAeQAgAGkAZgAgAGIAbABhAG4AawAuAFwAbgAgACAAIAAgAEcAZQB0AEQAZQB0AGEAaQBsAHMAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAYwAsACAAZAAsACAAZQAsACAAZgAsACAAZwAsACAAaAAsACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtACwAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhACwAIABiACwAIABjACwAIABkACwAIABSAGUAbQBvAHYAZQBOAEEAuwMoAGUAKQAsACAAUgBlAG0AbwB2AGUATgBBALsDKABmACkALAAgAGcALAAgAGgALAAgAGkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABlAHQAYQBpAGwALAAgAEkARgAoAGgALAAgAFwAIgBCAGwAYQBuAGsAXAAiACwAIABUAE8AQwBPAEwAKABJAEYAUwAoAG0ALAAgAG0AZQB0AHIAaQBjAHMAKQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoAbwBpAG4AZQBkACwAIABUAEUAWABUAEoATwBJAE4AKABkAGUAbABpAG0AaQB0AGUAcgAsACAAMQAsACAAZABlAHQAYQBpAGwAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagBvAGkAbgBlAGQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAZQBsAGwAcwAgAHcAaQB0AGgAOgBcAG4AIAAgACAAIABOAHUAbQBiAGUAcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAtAFQATwBDAE8ATAAoAEkAUwBOAFUATQBCAEUAUgAoAGQAYQB0AGEAKQApACwAXABuACAAIAAgACAAVABlAHgAdABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQBUAE8AQwBPAEwAKABJAFMAVABFAFgAVAAoAGQAYQB0AGEAKQApACwAXABuACAAIAAgACAATgB1AG0AYgBlAHIAcwBfAHMAdABvAHIAZQBkAF8AYQBzAF8AdABlAHgAdAAsACAAVABPAEMATwBMACgASQBTAE4AVQBNAEIARQBSACgASQBGAEUAUgBSAE8AUgAoAGQAYQB0AGEAIAArACAAMAAsACAAXAAiAFwAIgApACkAIAAqACAASQBTAFQARQBYAFQAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAEMAZQBsAGwAcwBfAHcAaQB0AGgAXwBlAHIAcgBvAHIAcwAsACAAIAAgACAAIAAtAC0AVABPAEMATwBMACgASQBTAEUAUgBSAE8AUgAoAGQAYQB0AGEAKQApACwAXABuACAAIAAgACAAUwBwAGEAYwBlAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQBCAGkAbgC7AygATABFAE4AKABUAFIASQBNACgAZABhAHQAYQApACkAIAA8AD4AIABMAEUATgAoAGQAYQB0AGEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQB0AHQAZQByAG4AIABtAGEAdABjAGgAZQBzACAAZgBvAHIAIABzAHAAZQBjAGkAYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAcwBcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFsAXgBBAC0AWgBhAC0AegAwAC0AOQAgAC4AXQB8AFsAXABcAHgAewAwADAAQQAwAH0AXABcAHgAewAyADAAMABCAH0ALQBcAFwAeAB7ADIAMAAwAEQAfQBdAHwAWwBcAFwAdABcAFwAbgBcAFwAcgBdAHwAWwBcAFwAeAB7ADEARgA2ADAAMAB9AC0AXABcAHgAewAxAEYANgA0AEYAfQBdAFwAIgAsAFwAbgAgACAAIAAgAFMAcABlAGMAaQBhAGwAXwBjAGgAYQByAGEAYwB0AGUAcgBzACwAIAAgACAAIAAtAC0AQgBpAG4AuwMoAFIARQBHAEUAWABUAEUAUwBUACgAZABhAHQAYQAsACAAcABhAHQAdABlAHIAbgApACkALABcAG4AXABuACAAIAAgACAARgBvAHIAbQB1AGwAYQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQBUAE8AQwBPAEwAKABJAFMARgBPAFIATQBVAEwAQQAoAGQAYQB0AGEAKQApACwAXABuACAAIAAgACAAQgBsAGEAbgBrAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQBUAE8AQwBPAEwAKABJAFMAQgBMAEEATgBLACgAZABhAHQAYQApACkALABcAG4AIAAgACAAIABMAG8AZwBpAGMAYQBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAtAFQATwBDAE8ATAAoAEkAUwBMAE8ARwBJAEMAQQBMACgAZABhAHQAYQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBlAHQAcgBpAGMAcwAgAGYAbABhAHQAdABlAG4AZQBkACAAcgBvAHcALQB3AGkAcwBlACAAYQBuAGQAIABzAHQAYQBjAGsAZQBkACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkALgBcAG4AIAAgACAAIABtAGUAdAByAGkAYwBfAHMAdABhAGMAawAsACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AdQBtAGIAZQByAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgB1AG0AYgBlAHIAcwBfAHMAdABvAHIAZQBkAF8AYQBzAF8AdABlAHgAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBlAGwAbABzAF8AdwBpAHQAaABfAGUAcgByAG8AcgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHAAYQBjAGUAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBwAGUAYwBpAGEAbABfAGMAaABhAHIAYQBjAHQAZQByAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAbwByAG0AdQBsAGEAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgBsAGEAbgBrAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAbwBnAGkAYwBhAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGUAdAByAGkAYwBzACAAcwB1AG0AbQBhAHIAaQB6AGUAZAAgAGEAbgBkACAAYwBvAG4AdgBlAHIAdABlAGQAIAB0AG8AIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIAB0AG8AdABhAGwAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABCAFkAQwBPAEwAKABtAGUAdAByAGkAYwBfAHMAdABhAGMAawAsACAAUwBVAE0AKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAtAC0AIABSAGUAcABvAHIAdABpAG4AZwAgAC0ALQBcAG4AXABuACAAIAAgACAALwAvACAAVABvAHAALQBsAGUAdgBlAGwAIAA5ANcAMgAgAHMAdQBtAG0AYQByAHkAIABvAGYAIABkAGEAdABhAC4AXABuACAAIAAgACAAUwB1AG0AbQBhAHIAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAE8AUgBUACgASABTAFQAQQBDAEsAKABtAGUAdAByAGkAYwBzACwAIAB0AG8AdABhAGwAcwApACwAIAAyACwAIAAtADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAZQBsAGwALQBiAHkALQBjAGUAbABsACAAcgBlAHAAbwByAHQAIABvAGYAIABkAGEAdABhAC4AXABuACAAIAAgACAAVgBlAHIAYgBvAHMAZQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVwBSAEEAUABSAE8AVwBTACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAUAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAHUAbQBiAGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAHUAbQBiAGUAcgBzAF8AcwB0AG8AcgBlAGQAXwBhAHMAXwB0AGUAeAB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMAZQBsAGwAcwBfAHcAaQB0AGgAXwBlAHIAcgBvAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHAAYQBjAGUAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHAAZQBjAGkAYQBsAF8AYwBoAGEAcgBhAGMAdABlAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAG8AcgBtAHUAbABhAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgBsAGEAbgBrAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABvAGcAaQBjAGEAbAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABHAGUAdABEAGUAdABhAGkAbABzALsDKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAAUgBlAHAAbwByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABJAHMAVgBlAHIAYgBvAHMAZQA/ACkALAAgAFMAdQBtAG0AYQByAHkAKAApACwAIABWAGUAcgBiAG8AcwBlACkALABcAG4AIAAgACAAIABSAGUAcABvAHIAdABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8ALwAgAC0ALQBFAG4AZAAgAG8AZgAgAEIAaQBnAFMAcABpAGwAbAAgAE0AbwBkAHUAbABlAC0ALQAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBEAEcAcgBpAGQAuwMiACwAIgBDAEcAcgBpAGQAuwMiACwAIgBNAEcAcgBpAGQAuwMiACwAIgBUAEcAcgBpAGQAuwMiACwAIgBQAG8AbABhAHIARwByAGkAZAC7AyIALAAiAEMAaQByAGMAbABlALsDIgAsACIARABpAGEAbQBvAG4AZAC7AyIALAAiAFAAbAB1AHMAuwMiACwAIgBQAHkAcgBhAG0AaQBkALsDIgAsACIAUgBpAG4AZwC7AyIALAAiAFMAcQB1AGEAcgBlALsDIgAsACIAVAByAGkAYQBuAGcAbABlALsDIgAsACIAUgBlAFMAaABhAHAAZQAyAEQAuwMiACwAIgBSAGUAcwBpAHoAZQC7AyIALAAiAFMAYwBhAG4AMgBEALsDIgAsACIAVAByAGEAdgBlAHIAcwBlALsDIgAsACIAVABhAGsAZQBCAGwAbwBjAGsAuwMiACwAIgBEAFMAdABhAGMAawC7AyIALAAiAFcAcgBhAHAAUgBvAHcAcwAyAEQAuwMiACwAIgBXAHIAYQBwAEMAbwBsAHMAMgBEALsDIgAsACIAUwB0AGEAaQByAGMAYQBzAGUAuwMiACwAIgBWAGEAbABpAGQAYQB0AGUAUwB0AGEAaQByAGMAYQBzAGUAuwMiACwAIgBVAG4AUABpAHYAbwB0ALsDIgAsACIAWgBpAHAAuwMiACwAIgBTAGwAaQBjAGUAQgB5AEQAZQBnALsDIgAsACIAUABhAGQAuwMiACwAIgBJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AyIALAAiAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDIgAsACIATQBhAGcAbgBpAGYAeQC7AyIALAAiAFoAbwBvAG0AuwMiACwAIgBEAGUAbABlAHQAZQBSAG8AdwBzALsDIgAsACIARABlAGwAZQB0AGUAQwBvAGwAcwC7AyIALAAiAEQAZQBsAGUAdABlAFcAaABlAHIAZQC7AyIALAAiAFAAaQBuAGMAaAC7AyIALAAiAFIAZQBtAG8AdgBlALsDIgAsACIAUwBxAHUAZQBlAHoAZQC7AyIALAAiAEsAcgBvAG4AZQBjAGsAZQByAFAAcgBvAGQAuwMiACwAIgBFAHgAYwBsAHUAZABlALsDIgAsACIAUwBuAGEAcAC7AyIALAAiAFMAaABpAGYAdAC7AyIALAAiAFMAaABpAGYAdABSAG8AdwBzALsDIgAsACIAUwBoAGkAZgB0AEMAbwBsAHMAuwMiACwAIgBFAG0AYgBlAGQAuwMiACwAIgBLAGUAZQBwAFIAbwB3AHMAuwMiACwAIgBLAGUAZQBwAEMAbwBsAHMAuwMiACwAIgBCAGwAbwBjAGsATQBhAHAAuwMiACwAIgBWAGEAbABpAGQAYQB0AGUAQgBsAG8AYwBrAE0AYQBwALsDIgAsACIAQwBvAG4AdgBvAGwAdgBlALsDIgAsACIARgBvAGwAZAC7AyIALAAiAEoAbwBpAG4AMgBEALsDIgAsACIARQBjAGgAbwC7AyIALAAiAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMiACwAIgBSAGUAcABlAGEAdABDAG8AbABzALsDIgAsACIAVABlAHMAcwBlAGwAbABhAHQAZQC7AyIALAAiAFMAdAByAGUAYQBrALsDIgAsACIAQwBvAHUAbgB0AGQAbwB3AG4AuwMiACwAIgBCAHkARABpAGEAZwC7AyIALAAiAEQAaQBhAGcATQBhAHAAuwMiACwAIgBEAGkAYQBnAEkAbgBkAGUAeAC7AyIALAAiAFYAYQBsAGkAZABhAHQAZQBEAGkAYQBnALsDIgAsACIAUABhAGkAcgB3AGkAcwBlALsDIgAsACIAVAByAGkAcABsAGUAdwBpAHMAZQC7AyIALAAiAFEAdQBhAGQAdwBpAHMAZQC7AyIALAAiAEcAcgBvAHUAcABiAHkAQgBpAG4AuwMiACwAIgBHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMiACwAIgBWAGEAbABpAGQAYQB0AGUARwBEALsDIgAsACIAUABpAHYAbwB0AGIAeQBDAGEAdAC7AyIALAAiAEcAcgBhAGkAbgC7AyIALAAiAE0AbwBvAHIAZQBBAGcAZwC7AyIALAAiAE0AbwBvAHIAZQBTAGUAbABlAGMAdAC7AyIALAAiAEgAaQBzAHQAbwBnAHIAYQBtALsDIgAsACIATQBvAGQAZQC7AyIALAAiAFoAbwBuAGUAUwB0AGEAdAC7AyIALAAiAEEAbABpAGcAbgC7AyIALAAiAEEAbABpAGcAbgBEAGkAcwB0AGkAbgBjAHQAuwMiACwAIgBBAGwAaQBnAG4AVQBuAGkAcQB1AGUAuwMiACwAIgBDAG8AYQBsAGUAcwBjAGUAuwMiACwAIgBFAHgAcABsAG8AZABlALsDIgAsACIATgB1AG0AYgBlAHIAcwBPAG4AbAB5ALsDIgAsACIAVABlAHgAdABPAG4AbAB5ALsDIgAsACIAUwBwAGwAaQB0ALsDIgAsACIAUgBlAGcAZQB4AFMAYQBmAGUAuwMiACwAIgBCAGkAbgAyAEQAZQBjALsDIgAsACIAQgBpAG4AMgBHAHIAYQB5ALsDIgAsACIAQgBpAHQAQwBvAHUAbgB0ALsDIgAsACIARABlAGMAMgBCAGkAbgC7AyIALAAiAEQAZQBjADIARwByAGEAeQC7AyIALAAiAEUAbgB1AG0AZQByAGEAdABlALsDIgAsACIAUABlAHIAbQBSALsDIgAsACIAUABlAHIAbQC7AyIALAAiAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwMiACwAIgBDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7AyIALAAiAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDIgAsACIASwBuAGEAcABTAGEAYwBrALsDIgAsACIAUwB1AGIAcwBlAHQARwBlAG4AuwMiACwAIgBTAHUAYgBzAGUAdABTAHUAbQC7AyIALAAiAFIAZQB2AGUAYQBsALsDIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBNAEQAWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuACAAIABfAF8AXwBfACAAIAAgACAAXwAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8AXwBfAF8AIAAgACAAIAAgACAAIAAgACAAIAAgAF8AIAAgACAAXwAgACAAIABfACAAXABuACAAfAAgACAAXwAgAFwAXAAgACAAKABfACkAIAAgACAAIAAgACAAIAAgACAAIAAvACAAXwBfAF8AXwB8ACAAIAAgACAAIAAgACAAIAAgACgAXwApACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAIABfACAAIAAgACAAXwBfACAAXwAgACAAfAAgACgAXwBfAF8AIAAgACAAIABfACAAXwBfACAAIAAgACAAXwAgACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAIABfACAAPAAgACAAfAAgAHwAIAAgAC8AIABfAGAAIAB8ACAAIABcAFwAXwBfAF8AIABcAFwAIAAgAHwAIAAnAF8AIABcAFwAIAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAfAAgAHwAIAB8ACAAKABfAHwAIAB8ACAAIABfAF8AXwBfACkAIAB8ACAAfAAgAHwAXwApACAAfAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8AF8AXwBfAF8ALwAgACAAfABfAHwAIAAgAFwAXABfAF8ALAAgAHwAIAB8AF8AXwBfAF8AXwAvACAAIAB8ACAALgBfAF8ALwAgACAAfABfAHwAIAB8AF8AfAAgAHwAXwB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8ALwAgAHwAIAAgACAAIAAgACAAIAAgACAAIAB8ACAAfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABfAF8AXwAvACAAIAAgACAAIAAgACAAIAAgACAAIAB8AF8AfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgBcAG4AdgAgADEALgAyAC4AMABcAG4AXABuAE0AbwBkAHUAbABlADoAIAAgAEIAaQBnAFMAcABpAGwAbABcAG4AUgBlAHAAbwA6ACAAIAAgACAAaAB0AHQAcABzADoALwAvAGcAaQB0AGgAdQBiAC4AYwBvAG0ALwBQAGEAdAByAGkAYwBrADIANwA4ADgALwBCAGkAZwBTAHAAaQBsAGwALQBFAHgAYwBlAGwALQBMAGEAbQBiAGQAYQAtAEwAaQBiAHIAYQByAHkAXABuAEwAaQBjAGUAbgBzAGUAOgAgAE0ASQBUACAAKABzAGUAZQAgAEwASQBDAEUATgBTAEUAIABmAGkAbABlACkAXABuAEEAdQB0AGgAbwByADoAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAEQAYQB0AGUAOgAgACAAIAAgADkALwAxADcALwAyADAAMgA2AFwAbgBcAG4AVgBlAHIAcwBpAG8AbgAgAGgAaQBzAHQAbwByAHkAOgBcAG4AIAAgACAAIAA3AC8ANgAvADIAMAAyADYAIAATICAAIABJAG4AaQB0AGkAYQBsACAAcgBlAGwAZQBhAHMAZQBcAG4AXABuACAAIAAgACAAOQAvADMALwAyADAAMgA2ACAAEyAgACAAQQBkAGQAZQBkACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AyAAYQBuAGQAIABRAHUAYQBkAHcAaQBzAGUAuwMgAHQAbwAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAHAAZABhAHQAZQBkACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAYwBhAHQAZQBnAG8AcgB5ACAAYgBsAG8AYwBrAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUAcABkAGEAdABlAGQAIABUAGUAcwBzAGUAbABsAGEAdABlALsDIAB0AG8AIABhAGMAYwBlAHAAdAAgADEARAAgAGEAcgByAGEAeQBzAFwAbgBcAG4AIAAgACAAIAA5AC8AMQA3AC8AMgAwADIANgAgABMgIABBAGQAZABlAGQAIABJAG4AcwB0AGEAbgBjAGUAuwMsACAAVwBhAHYAZQC7AywAIABHAHIAbwB1AHAASQBuAGQAZQB4ALsDLAAgAE8AYwBjAHUAcgByAGUAbgBjAGUAuwMsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAbgBkACAATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwMgAHQAbwAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAGkAeABlAGQAIAB2AHUAbABuAGUAcgBhAGIAaQBsAGkAdAB5ACAAaQBuACAAQwBvAG4AdgBvAGwAdgBlALsDIAB3AGkAdABoACAAMQBEACAAawBlAHIAbgBlAGwAcwBcAG4AXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAXABuACAAIAAgACAATgBvAG4AZQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwByAGUAIABtAG8AZAB1AGwAZQAgAGEAZwBnAHIAZQBnAGEAdABvAHIAIABmAG8AcgAgAGEAbABsACAAQgBpAGcAUwBwAGkAbABsACAAZgB1AG4AYwB0AGkAbwBuAHMALgBcAG4AXABuAFAAdQByAHAAbwBzAGUAOgBcAG4AIAAgACAAIABQAHIAbwB2AGkAZABlAHMAIABhACAAcwBpAG4AZwBsAGUAIABpAG0AcABvAHIAdAAgAHAAbwBpAG4AdAAgAGYAbwByACAAdABoAGUAIABlAG4AdABpAHIAZQAgAGwAaQBiAHIAYQByAHkALgBcAG4AXABuAEMAbwBuAHQAZQBuAHQAcwA6AFwAbgAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawAsACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQAsACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAsACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEALABcAG4AIAAgACAAIABSAGUAcABlAHQAaQB0AGkAbwBuACwAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMALAAgAFQAZQB4AHQALAAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwAsAFwAbgAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMALAAgAEQAaQBhAGcAbgBvAHMAdABpAGMAcwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4ALQAtAC0AVABhAGIAbABlACAAbwBmACAAQwBvAG4AdABlAG4AdABzAC0ALQAtAFwAbgBcAG4AIwAjACAAMAAxACAALQAgAFsARwBXAF0AIABHAHIAaQBkAHcAbwByAGsAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAVwAwADEAXQAgACAARABHAHIAaQBkALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBXADAAMgBdACAAIABDAEcAcgBpAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFcAMAAzAF0AIAAgAE0ARwByAGkAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAVwAwADQAXQAgACAAVABHAHIAaQBkALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBXADAANQBdACAAIABQAG8AbABhAHIARwByAGkAZAC7A1wAbgBcAG4AIwAjACAAMAAyACAALQAgAFsARwBHAF0AIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARwAwADEAXQAgACAAQwBpAHIAYwBsAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAAyAF0AIAAgAEQAaQBhAG0AbwBuAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAAzAF0AIAAgAFAAbAB1AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA0AF0AIAAgAFAAeQByAGEAbQBpAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA1AF0AIAAgAFIAaQBuAGcAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA2AF0AIAAgAFMAcQB1AGEAcgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBHADAANwBdACAAIABUAHIAaQBhAG4AZwBsAGUAuwNcAG4AXABuACMAIwAgADAAMwAgAC0AIABbAFMAQQBdACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAHIAZQAgAFMAaABhAHAAaQBuAGcAIABQAHIAaQBtAGkAdABpAHYAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADEAXQBcAHQAUgBlAFMAaABhAHAAZQAyAEQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMAAyAF0AXAB0AFIAZQBTAGkAegBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAAMwBdAFwAdABTAGMAYQBuADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADQAXQBcAHQAVAByAGEAdgBlAHIAcwBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAANQBdAFwAdABUAGEAawBlAEIAbABvAGMAawC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADYAXQBcAHQARABTAHQAYQBjAGsAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBmAGwAbwB3AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADcAXQBcAHQAVwByAGEAcABSAG8AdwBzADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADgAXQBcAHQAVwByAGEAcABDAG8AbABzADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADkAXQBcAHQAUwB0AGEAaQByAGMAYQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQAwAF0AXAB0AFUAbgBQAGkAdgBvAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQAxAF0AXAB0AFoAaQBwALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADEAMwBdAFwAdABTAGwAaQBjAGUAQgB5AEQAZQBnALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAxADQAXQBcAHQAUABhAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA1AF0AXAB0AEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADEANgBdAFwAdABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA3AF0AXAB0AE0AYQBnAG4AaQBmAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA4AF0AXAB0AFoAbwBvAG0AuwNcAG4AXABuACMAIwAgADAANAAgAC0AIABbAEcAQQBdACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAZQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADEAXQBcAHQARABlAGwAZQB0AGUAUgBvAHcAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADIAXQBcAHQARABlAGwAZQB0AGUAQwBvAGwAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADMAXQBcAHQARABlAGwAZQB0AGUAVwBoAGUAcgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAANABdAFwAdABQAGkAbgBjAGgAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMAA1AF0AXAB0AFIAZQBtAG8AdgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAANgBdAFwAdABTAHEAdQBlAGUAegBlALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAHgAcABhAG4AcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMAA3AF0AXAB0AEsAcgBvAG4AZQBjAGsAZQByAFAAcgBvAGQAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAaQBsAHQAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADgAXQBcAHQARQB4AGMAbAB1AGQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADkAXQBcAHQAUwBuAGEAcAC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBvAGwAbABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAwAF0AXAB0AFMAaABpAGYAdAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADEAXQBcAHQAUwBoAGkAZgB0AFIAbwB3AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAyAF0AXAB0AFMAaABpAGYAdABDAG8AbABzALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAzAF0AXAB0AEUAbQBiAGUAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADQAXQBcAHQASwBlAGUAcABSAG8AdwBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEANQBdAFwAdABLAGUAZQBwAEMAbwBsAHMAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADYAXQBcAHQAQgBsAG8AYwBrAE0AYQBwALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEANwBdAFwAdABDAG8AbgB2AG8AbAB2AGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQA4AF0AXAB0AEYAbwBsAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQA5AF0AXAB0AEoAbwBpAG4AMgBEALsDXABuAFwAbgAjACMAIAAwADUAIAAtACAAWwBSAFAAXQAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAxAF0AXAB0AEUAYwBoAG8AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAyAF0AXAB0AFIAZQBwAGUAYQB0AFIAbwB3AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAzAF0AXAB0AFIAZQBwAGUAYQB0AEMAbwBsAHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAA0AF0AXAB0AFQAZQBzAHMAZQBsAGwAYQB0AGUAuwNcAG4AXABuACMAIwAgADAANgAgAC0AIABbAEcAUgBdACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAZQBxAHUAZQBuAGMAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADAAMQBdAFwAdABTAHQAcgBlAGEAawC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADIAXQBcAHQAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXAB0AFwAdABcAHQAWwBHAFIAMQA2AF0AIAAgAEkAbgBzAHQAYQBuAGMAZQC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADcAXQBcAHQAVwBhAHYAZQC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADMAXQBcAHQAQgB5AEQAaQBhAGcAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA0AF0AXAB0AEQAaQBhAGcATQBhAHAAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA1AF0AXAB0AEQAaQBhAGcASQBuAGQAZQB4ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADAANgBdAFwAdABQAGEAaQByAHcAaQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA2AGEAXQBcAHQAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBcAHQAIAAgACAAIAAgACAAIAAgAFsARwBSADAANgBiAF0AIABRAHUAYQBkAHcAaQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA3AF0AXAB0AEcAcgBvAHUAcABiAHkAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA4AF0AXAB0AEcAcgBvAHUAcABiAHkARABhAHQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADkAXQBcAHQAUABpAHYAbwB0AGIAeQBDAGEAdAC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADgAXQBcAHQARwByAG8AdQBwAEkAbgBkAGUAeAC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADkAXQBcAHQATwBjAGMAdQByAHIAZQBuAGMAZQC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAyADAAXQBcAHQATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADEAMABdAFwAdABHAHIAYQBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQAxAF0AXAB0AE0AbwBvAHIAZQBBAGcAZwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADIAXQBcAHQATQBvAG8AcgBlAFMAZQBsAGUAYwB0ALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAYQB0AGkAcwB0AGkAYwBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADMAXQBcAHQASABpAHMAdABvAGcAcgBhAG0AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQA0AF0AXAB0AE0AbwBkAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQA1AF0AXAB0AFoAbwBuAGUAUwB0AGEAdAC7A1wAbgBcAG4AIwAjACAAMAA3ACAALQAgAFsAVABYAF0AIAAgAFQAZQB4AHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAAMQBdAFwAdABBAGwAaQBnAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAAyAF0AXAB0AEEAbABpAGcAbgBEAGkAcwB0AGkAbgBjAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAAzAF0AXAB0AEEAbABpAGcAbgBVAG4AaQBxAHUAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADQAXQBcAHQAQwBvAGEAbABlAHMAYwBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAANQBdAFwAdABFAHgAcABsAG8AZABlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAANgBdAFwAdABOAHUAbQBiAGUAcgBzAE8AbgBsAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAA3AF0AXAB0AFQAZQB4AHQATwBuAGwAeQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADgAXQBcAHQAUwBwAGwAaQB0ALsDXABuAFwAbgAjACMAIAAwADgAIAAtACAAWwBFAE4AXQAgACAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEUATgAwADEAXQBcAHQAQgBpAG4AMgBEAGUAYwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEUATgAwADIAXQBcAHQAQgBpAG4AMgBHAHIAYQB5ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARQBOADAAMwBdAFwAdABCAGkAdABDAG8AdQBuAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBFAE4AMAA0AF0AXAB0AEQAZQBjADIAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBFAE4AMAA1AF0AXAB0AEQAZQBjADIARwByAGEAeQC7A1wAbgBcAG4AIwAjACAAMAA5ACAALQAgAFsAQwBCAF0AIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAAMQBdAFwAdABQAGUAcgBtAFIAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAAyAF0AXAB0AFAAZQByAG0AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAAzAF0AXAB0AEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAA0AF0AXAB0AEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAANQBdAFwAdABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADYAXQBcAHQASwBuAGEAcABTAGEAYwBrALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAANwBdAFwAdABTAHUAYgBzAGUAdABHAGUAbgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADgAXQBcAHQAUwB1AGIAcwBlAHQAUwB1AG0AuwNcAG4AXABuACMAIwAgADEAMAAgAC0AIABbAEcARABdACAAIABHAHIAaQBkACAARABpAGEAZwBuAG8AcwB0AGkAYwBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARAAwADEAXQAgACAAUgBlAHYAZQBhAGwAuwNcAG4AXABuAFwAbgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAEcAVwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAwADEAIAAtACAARwByAGkAZAB3AG8AcgBrAFwAbgAvAC8AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFwAbgAvACoAXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawAgAGQAZQBmAGkAbgBlAHMAIAB0AGgAZQAgAGYAbwB1AG4AZABhAHQAaQBvAG4AYQBsACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAHMAeQBzAHQAZQBtAHMAIABmAG8AcgAgADIARAAgAGEAcgByAGEAeQBzAC4AIABFAGEAYwBoAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgAHAAcgBvAGQAdQBjAGUAcwAgAGEAIABjAGUAbgB0AGUAcgBlAGQALAAgAHMAeQBtAG0AZQB0AHIAaQBjAGEAbAAgAGcAZQBvAG0AZQB0AHIAaQBjACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAbwBmACAAdABoAGUAIABnAHIAaQBkAC4AXABuAFwAbgBGAHUAbgBjAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABEAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAARABpAHIAZQBjAHQAaQBvAG4AIABnAHIAaQBkACAAKAAwALAALQAzADYAMACwACkAIAB1AHMAaQBuAGcAIABjAGUAbgB0AGUAcgBlAGQAIABDAGEAcgB0AGUAcwBpAGEAbgAgAGEAeABlAHMAXABuAFwAbgAgACAAIAAgACIgIABDAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAAQwBhAHIAdABlAHMAaQBhAG4AIABnAHIAaQBkACAAKAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACwAIABjAGUAbgB0AGUAcgBlAGQAKQBcAG4AXABuACAAIAAgACAAIiAgAE0ARwByAGkAZAC7AyAAIAAgACAAIAAgAC0AIABNAGUAcwBoACAAZwByAGkAZAAgACgAMQARIGIAYQBzAGUAZAAgAHIAbwB3ACAAbwByACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACkAXABuAFwAbgAgACAAIAAgACIgIABUAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAAVABoAHIAZQBzAGgAbwBsAGQAZQBkACAAbQBlAHMAaAAgAGcAcgBpAGQAIAAoAGkAbgBkAGkAYwBlAHMAIAB3AHIAYQBwACAAYQBmAHQAZQByACAAYQAgAGwAaQBtAGkAdAApAFwAbgBcAG4AIAAgACAAIAAiICAAUABvAGwAYQByAEcAcgBpAGQAuwMgACAALQAgAFAAbwBsAGEAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAIAAgACAAEyAgAHIAYQBkAGkAYQBsACAAZABpAHMAdABhAG4AYwBlACAAZgByAG8AbQAgAGcAcgBpAGQAIABjAGUAbgB0AGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGgAaQAgABMgIABhAG4AZwBsAGUAIABpAG4AIAByAGEAZABpAGEAbgBzACAAdQBzAGkAbgBnACAAQQBUAEEATgAyACgAeQAsACAAeAApAFwAbgBcAG4AIAAgACAAIAAiICAAUgBlAHMAaQB6AGUAuwMgACAAIAAgACAALQAgAFUAdABpAGwAaQB0AHkAIABmAG8AcgAgAGIAcgBvAGEAZABjAGEAcwB0AGkAbgBnACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAHYAZQBjAHQAbwByAHMAIAB0AG8AIABnAHIAaQBkACAAcwBoAGEAcABlAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAQQBsAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGEAcgBlACAAcwBoAGEAcABlAC0AZAByAGkAdgBlAG4AOgAgAHQAaABlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAcwB1AHAAcABsAGkAZQBkACAAZwByAGkAZAAgAGQAZQB0AGUAcgBtAGkAbgBlAFwAbgAgACAAIAAgAHQAaABlACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGUAeAB0AGUAbgB0AHMALgBcAG4AXABuAEUAeABhAG0AcABsAGUAcwA6AFwAbgAgACAAIAAgAEcAcgBpAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAgACAAMgAgACAAIAAzACAAIAAgADQAIAAgACAANQBcAG4AIAAgACAAIAAgACAAIAAgADYAIAAgACAANwAgACAAIAA4ACAAIAAgADkAIAAgACAAMQAwAFwAbgAgACAAIAAgACAAIAAgACAAMQAxACAAIAAxADIAIAAgADEAMwAgACAAMQA0ACAAIAAxADUAXABuACAAIAAgACAAIAAgACAAIAAxADYAIAAgADEANwAgACAAMQA4ACAAIAAxADkAIAAgADIAMABcAG4AIAAgACAAIAAgACAAIAAgADIAMQAgACAAMgAyACAAIAAyADMAIAAgADIANAAgACAAMgA1AFwAbgBcAG4AIAAgACAAIABEAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQA6AFwAbgAgACAAIAAgACAAIAAgACAAMgAyADUALgAwADAAIAAyADAANgAuADUANwAgADEAOAAwAC4AMAAwACAAMQA1ADMALgA0ADMAIAAxADMANQAuADAAMABcAG4AIAAgACAAIAAgACAAIAAgADIANAAzAC4ANAAzACAAMgAyADUALgAwADAAIAAxADgAMAAuADAAMAAgADEAMwA1AC4AMAAwACAAMQAxADYALgA1ADcAXABuACAAIAAgACAAIAAgACAAIAAyADcAMAAuADAAMAAgADIANwAwAC4AMAAwACAAIAAgADAALgAwADAAIAAgADkAMAAuADAAMAAgACAAOQAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAAgACAAMgA5ADYALgA1ADcAIAAzADEANQAuADAAMAAgACAAIAAwAC4AMAAwACAAIAA0ADUALgAwADAAIAAgADYAMwAuADQAMwBcAG4AIAAgACAAIAAgACAAIAAgADMAMQA1AC4AMAAwACAAMwAzADMALgA0ADMAIAAgACAAMAAuADAAMAAgACAAMgA2AC4ANQA3ACAAIAA0ADUALgAwADAAXABuAFwAbgAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACAALQAgAHIAbwB3ACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAtADIAIAAtADIAIAAtADIAIAAtADIAIAAtADIAXABuACAAIAAgACAAIAAgACAAIAAtADEAIAAtADEAIAAtADEAIAAtADEAIAAtADEAXABuACAAIAAgACAAIAAgACAAIAAgADAAIAAgADAAIAAgADAAIAAgADAAIAAgADAAXABuACAAIAAgACAAIAAgACAAIAAgADEAIAAgADEAIAAgADEAIAAgADEAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAAgADIAIAAgADIAIAAgADIAIAAgADIAIAAgADIAXABuAFwAbgAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgBcAG4AIAAgACAAIABNAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAgAC0AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAxACAAMQAgADEAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAMgAgADIAIAAyACAAMgAgADIAXABuACAAIAAgACAAIAAgACAAIAAzACAAMwAgADMAIAAzACAAMwBcAG4AIAAgACAAIAAgACAAIAAgADQAIAA0ACAANAAgADQAIAA0AFwAbgAgACAAIAAgACAAIAAgACAANQAgADUAIAA1ACAANQAgADUAXABuAFwAbgAgACAAIAAgAE0ARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADQAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAANAAgADUAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAA0ACAANQBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADQAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAANAAgADUAXABuAFwAbgAgACAAIAAgAFQARwByAGkAZAC7AygAZwByAGkAZAAsADMAKQAgAC0AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALAAgAHQAaAByAGUAcwBoAG8AbABkACAAMwA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADEAIAAxACAAMQAgADEAXABuACAAIAAgACAAIAAgACAAIAAyACAAMgAgADIAIAAyACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADMAIAAzACAAMwAgADMAIAAzAFwAbgAgACAAIAAgACAAIAAgACAAMQAgADEAIAAxACAAMQAgADEAXABuACAAIAAgACAAIAAgACAAIAAyACAAMgAgADIAIAAyACAAMgBcAG4AXABuACAAIAAgACAAVABHAHIAaQBkALsDKABnAHIAaQBkACwAMwAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMALAAgAHQAaAByAGUAcwBoAG8AbABkACAAMwA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAAMQAgADIAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAAxACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADEAIAAyAFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAAMQAgADIAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAAxACAAMgBcAG4AXABuACAAIAAgACAAUABvAGwAYQByAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAgAC0AIAByADoAXABuACAAIAAgACAAIAAgACAAIAAyAC4AOAAzACAAMgAuADIANAAgADIALgAwADAAIAAyAC4AMgA0ACAAMgAuADgAMwBcAG4AIAAgACAAIAAgACAAIAAgADIALgAyADQAIAAxAC4ANAAxACAAMQAuADAAMAAgADEALgA0ADEAIAAyAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAMgAuADAAMAAgADEALgAwADAAIAAwAC4AMAAwACAAMQAuADAAMAAgADIALgAwADAAXABuACAAIAAgACAAIAAgACAAIAAyAC4AMgA0ACAAMQAuADQAMQAgADEALgAwADAAIAAxAC4ANAAxACAAMgAuADIANABcAG4AIAAgACAAIAAgACAAIAAgADIALgA4ADMAIAAyAC4AMgA0ACAAMgAuADAAMAAgADIALgAyADQAIAAyAC4AOAAzAFwAbgBcAG4AIAAgACAAIABQAG8AbABhAHIARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABwAGgAaQA6AFwAbgAgACAAIAAgACAAIAAgACAALQAyAC4AMwA2ACAALQAyAC4AMAAzACAALQAxAC4ANQA3ACAALQAxAC4AMQAxACAALQAwAC4ANwA5AFwAbgAgACAAIAAgACAAIAAgACAALQAyAC4ANgA4ACAALQAyAC4AMwA2ACAALQAxAC4ANQA3ACAALQAwAC4ANwA5ACAALQAwAC4ANAA2AFwAbgAgACAAIAAgACAAIAAgACAAIAAzAC4AMQA0ACAAIAAzAC4AMQA0ACAAIAAwAC4AMAAwACAAIAAwAC4AMAAwACAAIAAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAAgACAAIAAyAC4ANgA4ACAAIAAyAC4AMwA2ACAAIAAxAC4ANQA3ACAAIAAwAC4ANwA5ACAAIAAwAC4ANAA2AFwAbgAgACAAIAAgACAAIAAgACAAIAAyAC4AMwA2ACAAIAAyAC4AMAAzACAAIAAxAC4ANQA3ACAAIAAxAC4AMQAxACAAIAAwAC4ANwA5AFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADEAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEQARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQwBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABjAG8AdQBuAHQAZQByABEgYwBsAG8AYwBrAHcAaQBzAGUAIABkAGkAcgBlAGMAdABpAG8AbgAgAGcAcgBpAGQAIABpAG4AIABkAGUAZwByAGUAZQBzACAAKAAwALAAEyAzADYAMACwACkAIAB1AHMAaQBuAGcAXABuACAAIAAgACAAYwBlAG4AdABlAHIAZQBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIABmAHIAbwBtACAAQwBHAHIAaQBkALsDLgBcAG4AXABuACAAIAAgACAAQQBuAGcAbABlACAAYwBvAG4AdgBlAG4AdABpAG8AbgA6AFwAbgAgACAAIAAgACAAIAAgACAAMACwACAAIAAgAD0AIAArAFgAIABkAGkAcgBlAGMAdABpAG8AbgAgACgAcgBpAGcAaAB0ACkAXABuACAAIAAgACAAIAAgACAAIAA5ADAAsAAgACAAPQAgACsAWQAgAGQAaQByAGUAYwB0AGkAbwBuACAAKAB1AHAAKQBcAG4AIAAgACAAIAAgACAAIAAgADEAOAAwALAAIAA9ACAAEyBYACAAZABpAHIAZQBjAHQAaQBvAG4AIAAoAGwAZQBmAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgADIANwAwALAAIAA9ACAAEyBZACAAZABpAHIAZQBjAHQAaQBvAG4AIAAoAGQAbwB3AG4AKQBcAG4AXABuACAAIAAgACAAVABoAGUAIABjAGUAbgB0AGUAcgAgAGMAZQBsAGwAIAAoADAALAAwACkAIAByAGUAdAB1AHIAbgBzACAAMACwACAAdgBpAGEAIABJAEYARQBSAFIATwBSACAAZgBhAGwAbABiAGEAYwBrAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AIAAgACAAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABHAHIAaQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAGEAdwAgAGEAbgBnAGwAZQAgAGkAbgAgAGQAZQBnAHIAZQBlAHMAIAAoAG0AYQB5ACAAYgBlACAAbgBlAGcAYQB0AGkAdgBlACkAXABuACAAIAAgACAAdABoAGUAdABhACwAIABJAEYARQBSAFIATwBSACgARABFAEcAUgBFAEUAUwAoAEEAVABBAE4AMgAoAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAxACkAKQApACwAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAdABvACAAMACwABMgMwA2ADAAsABcAG4AIAAgACAAIABhAG4AZwBsAGUALAAgAE0ATwBEACgAdABoAGUAdABhACAAKwAgADMANgAwACwAIAAzADYAMAApACwAXABuAFwAbgAgACAAIAAgAGEAbgBnAGwAZQBcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADIAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEMARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBlAG4AdABlAHIAZQBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlACAAZwByAGkAZABzACAAYQBsAGkAZwBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBoAGEAcABlACAAbwBmACAAYQBcAG4AIAAgACAAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkALgAgAFIAZQB0AHUAcgBuAHMAIABlAGkAdABoAGUAcgAgAHIAbwB3ACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAbwByACAAYwBvAGwAdQBtAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMALgBcAG4AXABuACAAIAAgACAAQwBvAG8AcgBkAGkAbgBhAHQAZQAgAHIAYQBuAGcAZQBzACAAYQByAGUAIABjAGUAbgB0AGUAcgBlAGQAIABzAHUAYwBoACAAdABoAGEAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAUgBvAHcAOgAgACAALQAoAGgAIAAtACAAMQApACAALwAgADIAIAAgAC4ALgAuACAAIAArACgAaAAgAC0AIAAxACkAIAAvACAAMgBcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBsADoAIAAgAC0AKAB3ACAALQAgADEAKQAgAC8AIAAyACAAIAAuAC4ALgAgACAAKwAoAHcAIAAtACAAMQApACAALwAgADIAXABuAFwAbgAgACAAIAAgAFcAbwByAGsAcwAgAGYAbwByACAAYgBvAHQAaAAgADEARAAgAGEAbgBkACAAMgBEACAAYQByAHIAYQB5AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuACAAYwBvAGwAdQBtAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMALgAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHIAZQB0AHUAcgBuACAAcgBvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAcgB0AGkAbgBnACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAKABjAGUAbgB0AGUAcgBlAGQAKQBcAG4AIAAgACAAIABpAF8AcwB0AGEAcgB0ACwAIAAtACAAKABoACAALQAgADEAKQAgAC8AIAAyACwAXABuACAAIAAgACAAagBfAHMAdABhAHIAdAAsACAALQAgACgAdwAgAC0AIAAxACkAIAAvACAAMgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABjAG8AbwByAGQAaQBuAGEAdABlACAAZwBlAG4AZQByAGEAdABvAHIAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKABoACwALABpAF8AcwB0AGEAcgB0ACkALAAsAHcAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABSAGUAcwBpAHoAZQC7AygAUwBFAFEAVQBFAE4AQwBFACgALAB3ACwAagBfAHMAdABhAHIAdAApACwAaAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAEkARgAoAFIAbwB3AEkAZAB4AD8ALAAgAGkAKAApACwAIABqACgAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqAFsARwBXADAAMwBdAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBHAHIAaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkAHcAbwByAGsAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIAByAG8AdwARIGkAbgBkAGUAeAAgAG8AcgAgAGMAbwBsAHUAbQBuABEgaQBuAGQAZQB4ACAAZwByAGkAZABzACAAbQBhAHQAYwBoAGkAbgBnACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgAGEAcgByAGEAeQAuACAAVABoAGkAcwAgAGkAcwAgAHQAaABlACAARQB4AGMAZQBsACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAG8AZgAgAE0AQQBUAEwAQQBCABkgcwAgAG0AZQBzAGgAZwByAGkAZAAgAG8AcgAgAE4AdQBtAFAAeQAZIHMAIABpAG4AZABpAGMAZQBzAC4AXABuAFwAbgAgACAAIAAgAEIAeQAgAGQAZQBmAGEAdQBsAHQALAAgAE0ARwByAGkAZAC7AyAAcgBlAHQAdQByAG4AcwAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAuACAAVwBoAGUAbgAgAHQAaABlACAAbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAIABpAHMAIABUAFIAVQBFACwAXABuACAAIAAgACAAaQB0ACAAcgBlAHQAdQByAG4AcwAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAGkAbgBzAHQAZQBhAGQALgBcAG4AXABuACAAIAAgACAAVwBvAHIAawBzACAAZgBvAHIAIABiAG8AdABoACAAMQBEACAAYQBuAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAuACAATwB1AHQAcAB1AHQAIABhAGwAdwBhAHkAcwAgAG0AYQB0AGMAaABlAHMAIAB0AGgAZQAgAGcAZQBvAG0AZQB0AHIAeQAgAG8AZgAgAHQAaABlAFwAbgAgACAAIAAgAGkAbgBwAHUAdAAgAGcAcgBpAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzAC4AIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAByAGUAdAB1AHIAbgAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAaQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoAGgAKQAsACwAdwApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcAKQAsAGgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAWwBHAFcAMAA0AF0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABUAEcAcgBpAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAHIAbwB3ABEgaQBuAGQAZQB4ACAAbwByACAAYwBvAGwAdQBtAG4AESBpAG4AZABlAHgAIABnAHIAaQBkAHMAIAB3AGgAbwBzAGUAIAB2AGEAbAB1AGUAcwAgAHcAcgBhAHAAIAB3AGkAdABoAGkAbgAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZABcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAuACAASQBuAGQAaQBjAGUAcwAgAGMAeQBjAGwAZQAgAGYAcgBvAG0AIAAxACAAdABvACAAdABoAHIAZQBzAGgAbwBsAGQALAAgAHIAZQBwAGUAYQB0AGkAbgBnACAAYQBzACAAbgBlAGUAZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQBcAG4AIAAgACAAIABzAGgAYQBwAGUAIABvAGYAIAB0AGgAZQAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIABCAHkAIABkAGUAZgBhAHUAbAB0ACwAIABUAEcAcgBpAGQAuwMgAHIAZQB0AHUAcgBuAHMAIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALgAgAFcAaABlAG4AIAB0AGgAZQAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAVABSAFUARQAsAFwAbgAgACAAIAAgAGkAdAAgAHIAZQB0AHUAcgBuAHMAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAIABpAG4AcwB0AGUAYQBkAC4AXABuAFwAbgAgACAAIAAgAE4AbwBuABEgaQBuAHQAZQBnAGUAcgAgAHQAaAByAGUAcwBoAG8AbABkAHMAIABhAHIAZQAgAG4AbwByAG0AYQBsAGkAegBlAGQAIAB1AHMAaQBuAGcAIABJAE4AVAAoAHQAaAByAGUAcwBoAG8AbABkACkALgAgAFQAaAByAGUAcwBoAG8AbABkAHMAIABtAHUAcwB0ACAAYgBlAFwAbgAgACAAIAAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABBACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHMAaQB6AGUALgBcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAgACAAIAAtACAATQBhAHgAaQBtAHUAbQAgAGkAbgBkAGUAeAAgAHYAYQBsAHUAZQAgAGIAZQBmAG8AcgBlACAAdwByAGEAcABwAGkAbgBnACAAKABtAHUAcwB0ACAAYgBlACAAPgAgADAAKQAuAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAgAC0AIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAuACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAcgBlAHQAdQByAG4AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVABHAHIAaQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAB0AGgAcgBlAHMAaABvAGwAZAApACwAIAB0AGgAcgBlAHMAaABvAGwAZAAgADwAPQAgADAAKQAsAFwAIgAjAFQASABSAEUAUwBIAE8ATABEACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAdABoAHIAZQBzAGgAbwBsAGQAXABuACAAIAAgACAAdAAsACAAIAAgACAAIAAgACAASQBOAFQAKAB0AGgAcgBlAHMAaABvAGwAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAdwByAGEAcABwAGUAZAAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAMQAgACsAIABNAE8ARAAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKABoACwALAAwACkALAAsAHcAKQAsACAAdAApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAMQAgACsAIABNAE8ARAAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcALAAwACkALABoACkALAAgAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADUAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFAAbwBsAGEAcgBHAHIAaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkAHcAbwByAGsAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAGcAcgBpAGQAIABvAGYAIABwAG8AbABhAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIABhAGwAaQBnAG4AZQBkACAAdABvACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgAGEAcgByAGEAeQAuACAAQwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAYQByAGUAIABkAGUAcgBpAHYAZQBkACAAZgByAG8AbQAgAGMAZQBuAHQAZQByAGUAZAAgAEMAYQByAHQAZQBzAGkAYQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAcAByAG8AZAB1AGMAZQBkAFwAbgAgACAAIAAgAGIAeQAgAEMARwByAGkAZAC7Ay4AXABuAFwAbgAgACAAIAAgAFQAdwBvACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGYAaQBlAGwAZABzACAAYQByAGUAIABhAHYAYQBpAGwAYQBiAGwAZQA6AFwAbgAgACAAIAAgACAAIAAgACAAcgAgACAAIAAgAC0AIAByAGEAZABpAGEAbAAgAGQAaQBzAHQAYQBuAGMAZQAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAZQBuAHQAZQByAFwAbgAgACAAIAAgACAAIAAgACAAcABoAGkAIAAgAC0AIABhAG4AZwBsAGUAIABpAG4AIAByAGEAZABpAGEAbgBzACwAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAEEAVABBAE4AMgAoAHkALAAgAHgAKQAgAGMAbwBuAHYAZQBuAHQAaQBvAG4AXABuAFwAbgAgACAAIAAgAEkAZgAgAHAAaABpAF8AYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGkAcwAgAG8AbQBpAHQAdABlAGQALAAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAcgBlAHQAdQByAG4AcwAgAHQAaABlACAAcgBhAGQAaQBhAGwAIABkAGkAcwB0AGEAbgBjAGUAIABnAHIAaQBkAC4AXABuACAAIAAgACAASQBmACAAVABSAFUARQAsACAAdABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIAByAGUAdAB1AHIAbgBzACAAdABoAGUAIABhAG4AZwB1AGwAYQByACAAZwByAGkAZAAuAFwAbgBcAG4AIAAgACAAIABUAGgAZQAgAGMAZQBuAHQAZQByACAAYwBlAGwAbAAgACgAMAAsADAAKQAgAHIAZQB0AHUAcgBuAHMAIABwAGgAaQAgAD0AIAAwACAAdgBpAGEAIABJAEYARQBSAFIATwBSACAAZgBhAGwAbABiAGEAYwBrAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdwBoAGkAYwBoACAAdABvACAAZwBlAG4AZQByAGEAdABlACAAcABvAGwAYQByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAC4AXABuACAAIAAgACAAWwBwAGgAaQBfAGMAbwBvAHIAZABpAG4AYQB0AGUAXQAgAC0AIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgAgAHAAaABpADsAIABpAGYAIABvAG0AaQB0AHQAZQBkACwAIAByAGUAdAB1AHIAbgAgAHIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABvAGwAYQByAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAcABoAGkAXwBjAG8AbwByAGQAaQBuAGEAdABlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAG0AbwBkAGUAXABuACAAIAAgACAASQBzAFIAPwAsACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAcABoAGkAXwBjAG8AbwByAGQAaQBuAGEAdABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAG8AbABhAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgAFMAUQBSAFQAKAB4AF4AMgAgACsAIAB5AF4AMgApACwAXABuACAAIAAgACAAcABoAGkALAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABBAFQAQQBOADIAKAB5ACwAIAB4ACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAHIAIABvAHIAIABwAGgAaQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAASQBGACgASQBzAFIAPwAsACAAcgAsACAAcABoAGkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBHAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AIwAjACAAMAAyACAALQAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AIAAqAC8AXABuAFwAbgAvACoAXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFQAaABpAHMAIABtAG8AZAB1AGwAZQAgAGQAZQBmAGkAbgBlAHMAIABhACAAZgBhAG0AaQBsAHkAIABvAGYAIABnAGUAbwBtAGUAdAByAGkAYwAgAGUAeAB0AHIAYQBjAHQAaQBvAG4AIABvAHAAZQByAGEAdABvAHIAcwAgAGYAbwByACAAMgBEACAAYQByAHIAYQB5AHMALgBcAG4AIAAgACAAIABFAGEAYwBoACAAZgB1AG4AYwB0AGkAbwBuACAAcgBlAHQAdQByAG4AcwAgAGEAIAByAGUAZwBpAG8AbgAgAG8AZgAgAHQAaABlACAAZwByAGkAZAAgAGQAZQBmAGkAbgBlAGQAIABiAHkAIABhACAAcwBwAGUAYwBpAGYAaQBjACAAcwBoAGEAcABlACwAXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBpAG4AZwAgAHQAaABlACAAZwBlAG8AbQBlAHQAcgB5ACAAbwBmACAAdABoAGUAIABlAHgAdAByAGEAYwB0AGUAZAAgAGEAcgBlAGEALgAgAEMAZQBuAHQAZQByAHMAIABtAGEAeQAgAGIAZQAgAHMAcABlAGMAaQBmAGkAZQBkACAAYgB5AFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAgAG8AcgAgAGUAeABwAGwAaQBjAGkAdAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAsACAAYQBuAGQAIABvAHAAdABpAG8AbgBhAGwAIABmAGkAbABsACAAdgBhAGwAdQBlAHMAIABjAG8AbgB0AHIAbwBsACAAdwBoAGEAdABcAG4AIAAgACAAIABhAHAAcABlAGEAcgBzACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgAuAFwAbgBcAG4AIAAgACAAIABTAGgAYQBwAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEMAaQByAGMAbABlALsDIAAgACAALQAgACAAIABDAGkAcgBjAHUAbABhAHIAIAByAGUAZwBpAG8AbgAgAGIAeQAgAHQAYQByAGcAZQB0ACAAbwByACAAewByAG8AdwAsACAAYwBvAGwAfQAgAGMAZQBuAHQAZQByAC4AXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEQAaQBhAG0AbwBuAGQAuwMgACAALQAgACAAIABNAGEAbgBoAGEAdAB0AGEAbgARIHIAYQBkAGkAdQBzACAAZABpAGEAbQBvAG4AZAAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABQAGwAdQBzALsDIAAgACAAIAAgAC0AIAAgACAAQwByAG8AcwBzABEgcwBoAGEAcABlAGQAIAByAGUAZwBpAG8AbgAgACgAdgBvAG4AIABOAGUAdQBtAGEAbgBuACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAKQAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABQAHkAcgBhAG0AaQBkALsDIAAgAC0AIAAgACAARABpAHIAZQBjAHQAaQBvAG4AYQBsACAAaABhAGwAZgARIGQAaQBhAG0AbwBuAGQAIAAoAGYAbwB1AHIAIABwAGkAZQBjAGUAcwApAC4AXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFIAaQBuAGcAuwMgACAAIAAgACAALQAgACAAIABMAGEAeQBlAHIAESBiAGEAcwBlAGQAIABwAGUAcgBpAG0AZQB0AGUAcgAgAGUAeAB0AHIAYQBjAHQAaQBvAG4ALgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUwBxAHUAYQByAGUAuwMgACAAIAAtACAAIAAgAEMAaABlAGIAeQBzAGgAZQB2ABEgcgBhAGQAaQB1AHMAIABzAHEAdQBhAHIAZQAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABUAHIAaQBhAG4AZwBsAGUAuwMgAC0AIAAgACAARABpAHIAZQBjAHQAaQBvAG4AYQBsACAAdAByAGkAYQBuAGcAdQBsAGEAcgAgAHIAZQBnAGkAbwBuACAAKABhAGIAbwB2AGUAIABvAHIAIABiAGUAbABvAHcAKQAuAFwAbgBcAG4AIAAgACAAIABVAHQAaQBsAGkAdABpAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEMARwByAGkAZAC7AywAIABNAEcAcgBpAGQAuwMsACAAUgBlAHMAaQB6AGUAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4AIAAgACAAIABBAGwAbAAgAGYAdQBuAGMAdABpAG8AbgBzACAAYQByAGUAIABzAGgAYQBwAGUAESBkAHIAaQB2AGUAbgA6ACAAdABoAGUAIABpAG4AcAB1AHQAIABnAHIAaQBkACAAZABlAHQAZQByAG0AaQBuAGUAcwAgAHQAaABlACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBcAG4AIAAgACAAIABlAHgAdABlAG4AdABzACAAYQBuAGQAIAB0AGgAZQAgAGcAZQBvAG0AZQB0AHIAeQAgAG8AZgAgAHQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgAuAFwAbgAvACoAXABuAFwAbgAgACAAIAAgAEUAeABhAG0AcABsAGUAcwA6AFwAbgBcAG4AXABuAEcAcgBpAGQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuADEAXAB0ADIAXAB0ADMAXAB0ADQAXAB0ADUAXAB0ADYAXAB0ADcAXAB0ADgAXAB0ADkAXAB0ADEAMABcAG4AMQAxAFwAdAAxADIAXAB0ADEAMwBcAHQAMQA0AFwAdAAxADUAXAB0ADEANgBcAHQAMQA3AFwAdAAxADgAXAB0ADEAOQBcAHQAMgAwAFwAbgAyADEAXAB0ADIAMgBcAHQAMgAzAFwAdAAyADQAXAB0ADIANQBcAHQAMgA2AFwAdAAyADcAXAB0ADIAOABcAHQAMgA5AFwAdAAzADAAXABuADMAMQBcAHQAMwAyAFwAdAAzADMAXAB0ADMANABcAHQAMwA1AFwAdAAzADYAXAB0ADMANwBcAHQAMwA4AFwAdAAzADkAXAB0ADQAMABcAG4ANAAxAFwAdAA0ADIAXAB0ADQAMwBcAHQANAA0AFwAdAA0ADUAXAB0ADQANgBcAHQANAA3AFwAdAA0ADgAXAB0ADQAOQBcAHQANQAwAFwAbgA1ADEAXAB0ADUAMgBcAHQANQAzAFwAdAA1ADQAXAB0ADUANQBcAHQANQA2AFwAdAA1ADcAXAB0ADUAOABcAHQANQA5AFwAdAA2ADAAXABuADYAMQBcAHQANgAyAFwAdAA2ADMAXAB0ADYANABcAHQANgA1AFwAdAA2ADYAXAB0ADYANwBcAHQANgA4AFwAdAA2ADkAXAB0ADcAMABcAG4ANwAxAFwAdAA3ADIAXAB0ADcAMwBcAHQANwA0AFwAdAA3ADUAXAB0ADcANgBcAHQANwA3AFwAdAA3ADgAXAB0ADcAOQBcAHQAOAAwAFwAbgA4ADEAXAB0ADgAMgBcAHQAOAAzAFwAdAA4ADQAXAB0ADgANQBcAHQAOAA2AFwAdAA4ADcAXAB0ADgAOABcAHQAOAA5AFwAdAA5ADAAXABuADkAMQBcAHQAOQAyAFwAdAA5ADMAXAB0ADkANABcAHQAOQA1AFwAdAA5ADYAXAB0ADkANwBcAHQAOQA4AFwAdAA5ADkAXAB0ADEAMAAwAFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AQwBpAHIAYwBsAGUAuwMoAGcAcgBpAGQALAA0ADUALAA1ACwAXAAiAFwAIgApAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAMgBcAHQAMwBcAHQANABcAHQANQBcAHQANgBcAHQANwBcAHQAOABcAHQAXAB0AFwAbgAxADEAXAB0ADEAMgBcAHQAMQAzAFwAdAAxADQAXAB0ADEANQBcAHQAMQA2AFwAdAAxADcAXAB0ADEAOABcAHQAMQA5AFwAdABcAG4AMgAxAFwAdAAyADIAXAB0ADIAMwBcAHQAMgA0AFwAdAAyADUAXAB0ADIANgBcAHQAMgA3AFwAdAAyADgAXAB0ADIAOQBcAHQAXABuADMAMQBcAHQAMwAyAFwAdAAzADMAXAB0ADMANABcAHQAMwA1AFwAdAAzADYAXAB0ADMANwBcAHQAMwA4AFwAdAAzADkAXAB0AFwAbgA0ADEAXAB0ADQAMgBcAHQANAAzAFwAdAA0ADQAXAB0ADQANQBcAHQANAA2AFwAdAA0ADcAXAB0ADQAOABcAHQANAA5AFwAdAA1ADAAXABuADUAMQBcAHQANQAyAFwAdAA1ADMAXAB0ADUANABcAHQANQA1AFwAdAA1ADYAXAB0ADUANwBcAHQANQA4AFwAdAA1ADkAXAB0AFwAbgA2ADEAXAB0ADYAMgBcAHQANgAzAFwAdAA2ADQAXAB0ADYANQBcAHQANgA2AFwAdAA2ADcAXAB0ADYAOABcAHQANgA5AFwAdABcAG4ANwAxAFwAdAA3ADIAXAB0ADcAMwBcAHQANwA0AFwAdAA3ADUAXAB0ADcANgBcAHQANwA3AFwAdAA3ADgAXAB0ADcAOQBcAHQAXABuAFwAdAA4ADIAXAB0ADgAMwBcAHQAOAA0AFwAdAA4ADUAXAB0ADgANgBcAHQAOAA3AFwAdAA4ADgAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0ADkANQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4ARABpAGEAbQBvAG4AZAC7AygAZwByAGkAZAAsAHsANQAsADUAfQAsADMALABcACIAXAAiACkAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADEANQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdAAyADQAXAB0ADIANQBcAHQAMgA2AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdAAzADMAXAB0ADMANABcAHQAMwA1AFwAdAAzADYAXAB0ADMANwBcAHQAXAB0AFwAdABcAHQAXABuADQAMgBcAHQANAAzAFwAdAA0ADQAXAB0ADQANQBcAHQANAA2AFwAdAA0ADcAXAB0ADQAOABcAHQAXAB0AFwAdABcAG4AXAB0ADUAMwBcAHQANQA0AFwAdAA1ADUAXAB0ADUANgBcAHQANQA3AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdAA2ADQAXAB0ADYANQBcAHQANgA2AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADcANQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFAAbAB1AHMAuwMoAGcAcgBpAGQALAA1ADcALAAzACwAXAAiAFwAIgApAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdAAyADcAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADMANwBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQANAA3AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgA1ADQAXAB0ADUANQBcAHQANQA2AFwAdAA1ADcAXAB0ADUAOABcAHQANQA5AFwAdAA2ADAAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADYANwBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQANwA3AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdAA4ADcAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBQAHkAcgBhAG0AaQBkALsDKABnAHIAaQBkACwAMgAsAFwAIgB4AFwAIgApAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAAxADAAXABuAHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0ADEAOQBcAHQAMgAwAFwAbgB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAAyADgAXAB0ADIAOQBcAHQAMwAwAFwAbgB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAAzADcAXAB0ADMAOABcAHQAMwA5AFwAdAA0ADAAXABuAHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0ADQANgBcAHQANAA3AFwAdAA0ADgAXAB0ADQAOQBcAHQANQAwAFwAbgB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAA1ADUAXAB0ADUANgBcAHQANQA3AFwAdAA1ADgAXAB0ADUAOQBcAHQANgAwAFwAbgB4AFwAdAB4AFwAdAB4AFwAdAA2ADQAXAB0ADYANQBcAHQANgA2AFwAdAA2ADcAXAB0ADYAOABcAHQANgA5AFwAdAA3ADAAXABuAHgAXAB0AHgAXAB0ADcAMwBcAHQANwA0AFwAdAA3ADUAXAB0ADcANgBcAHQANwA3AFwAdAA3ADgAXAB0ADcAOQBcAHQAOAAwAFwAbgB4AFwAdAA4ADIAXAB0ADgAMwBcAHQAOAA0AFwAdAA4ADUAXAB0ADgANgBcAHQAOAA3AFwAdAA4ADgAXAB0ADgAOQBcAHQAOQAwAFwAbgA5ADEAXAB0ADkAMgBcAHQAOQAzAFwAdAA5ADQAXAB0ADkANQBcAHQAOQA2AFwAdAA5ADcAXAB0ADkAOABcAHQAOQA5AFwAdAAxADAAMABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFIAaQBuAGcAuwMoAGcAcgBpAGQALAAyACwAXAAiAC0AXAAiACkAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXABuAC0AXAB0ADEAMgBcAHQAMQAzAFwAdAAxADQAXAB0ADEANQBcAHQAMQA2AFwAdAAxADcAXAB0ADEAOABcAHQAMQA5AFwAdAAtAFwAbgAtAFwAdAAyADIAXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0ADIAOQBcAHQALQBcAG4ALQBcAHQAMwAyAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAzADkAXAB0AC0AXABuAC0AXAB0ADQAMgBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQANAA5AFwAdAAtAFwAbgAtAFwAdAA1ADIAXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0ADUAOQBcAHQALQBcAG4ALQBcAHQANgAyAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAA2ADkAXAB0AC0AXABuAC0AXAB0ADcAMgBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQANwA5AFwAdAAtAFwAbgAtAFwAdAA4ADIAXAB0ADgAMwBcAHQAOAA0AFwAdAA4ADUAXAB0ADgANgBcAHQAOAA3AFwAdAA4ADgAXAB0ADgAOQBcAHQALQBcAG4ALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFMAcQB1AGEAcgBlALsDKABnAHIAaQBkACwAMgA3ACwAMwAsAFwAIgBcACIAKQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4ANABcAHQANQBcAHQANgBcAHQANwBcAHQAOABcAHQAOQBcAHQAMQAwAFwAdABcAHQAXAB0AFwAbgAxADQAXAB0ADEANQBcAHQAMQA2AFwAdAAxADcAXAB0ADEAOABcAHQAMQA5AFwAdAAyADAAXAB0AFwAdABcAHQAXABuADIANABcAHQAMgA1AFwAdAAyADYAXAB0ADIANwBcAHQAMgA4AFwAdAAyADkAXAB0ADMAMABcAHQAXAB0AFwAdABcAG4AMwA0AFwAdAAzADUAXAB0ADMANgBcAHQAMwA3AFwAdAAzADgAXAB0ADMAOQBcAHQANAAwAFwAdABcAHQAXAB0AFwAbgA0ADQAXAB0ADQANQBcAHQANAA2AFwAdAA0ADcAXAB0ADQAOABcAHQANAA5AFwAdAA1ADAAXAB0AFwAdABcAHQAXABuADUANABcAHQANQA1AFwAdAA1ADYAXAB0ADUANwBcAHQANQA4AFwAdAA1ADkAXAB0ADYAMABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFQAcgBpAGEAbgBnAGwAZQC7AygAZwByAGkAZAAsADQANAAsADMALAAsAFwAIgBcACIAKQAgAC0AIABBAGIAbwB2AGUAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADEANABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdAAyADMAXAB0ADIANABcAHQAMgA1AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdAAzADIAXAB0ADMAMwBcAHQAMwA0AFwAdAAzADUAXAB0ADMANgBcAHQAXAB0AFwAdABcAHQAXABuADQAMQBcAHQANAAyAFwAdAA0ADMAXAB0ADQANABcAHQANAA1AFwAdAA0ADYAXAB0ADQANwBcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFQAcgBpAGEAbgBnAGwAZQC7AygAZwByAGkAZAAsADQANAAsADMALAAxACwAXAAiAFwAIgApACAALQAgAEIAZQBsAG8AdwBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4ANAAxAFwAdAA0ADIAXAB0ADQAMwBcAHQANAA0AFwAdAA0ADUAXAB0ADQANgBcAHQANAA3AFwAdABcAHQAXAB0AFwAbgBcAHQANQAyAFwAdAA1ADMAXAB0ADUANABcAHQANQA1AFwAdAA1ADYAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0ADYAMwBcAHQANgA0AFwAdAA2ADUAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQANwA0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABDAGkAcgBjAGwAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEMARwByAGkAZAC7AywAIABTAHEAdQBlAGUAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhACAAYwBpAHIAYwB1AGwAYQByACAAcgBlAGcAaQBvAG4AIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGIAeQAgAHMAcABlAGMAaQBmAHkAaQBuAGcAIAB0AGgAZQAgAGMAZQBuAHQAZQByACAAYQBuAGQAIABhAFwAbgAgACAAIAAgAHIAYQBkAGkAdQBzACAAKABlAHgAdABlAG4AZAApAC4AIABUAGgAZQAgAGMAZQBuAHQAZQByACAAbQBhAHkAIABiAGUAIABnAGkAdgBlAG4AIABhAHMAIABhACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGEAcwAgAGUAeABwAGwAaQBjAGkAdABcAG4AIAAgACAAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AIABUAGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkACAAcgBlAGcAaQBvAG4AIABwAHIAZQBzAGUAcgB2AGUAcwAgAGkAdABzACAAZwBlAG8AbQBlAHQAcgBpAGMAIABzAGgAYQBwAGUALABcAG4AIAAgACAAIABhAG4AZAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAG8AbgBsAHkAIABmAGkAbABsAF8AdgBhAGwAdQBlACAAYQByAGUAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAgACAAIAAgACAAIAAtACAAQwBlAG4AdABlAHIAIABvAGYAIAB0AGgAZQAgAGMAaQByAGMAbABlAC4AIABNAGEAeQAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAgAGMAcgBpAHQAZQByAGkAbwBuACAAbwByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIAB0AGgAZQAgAGYAbwByAG0AIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AXABuACAAIAAgACAAZQB4AHQAZQBuAGQAIAAgACAAIAAgACAALQAgAFIAYQBkAGkAdQBzACAAbwBmACAAdABoAGUAIABjAGkAcgBjAGwAZQAgACgAbQB1AHMAdAAgAGIAZQAgAGEAIABwAG8AcwBpAHQAaQB2AGUAIABpAG4AdABlAGcAZQByACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAYwBpAHIAYwBsAGUALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADAALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQwBpAHIAYwBsAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACwAXABuACAAIAAgACAAZQB4AHQAZQBuAGQALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAYQByAGcAZQB0ACAAaQBuAHQAZQByAHAAcgBlAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBJAF8ASgA/ACwAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUACgAdABhAHIAZwBlAHQAKQAgAD0AIAAyACwAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAFQAQQBLAEUAKAB0AGEAcgBnAGUAdAAsACAALQAxACwAIAAtADEAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAdABjAGgAIABmAG8AcgAgAHMAYwBhAGwAYQByACAAdABhAHIAZwBlAHQAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABnAHIAaQBkACAAPQAgAHQAYQByAGcAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHAAdQB0ACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABFAHgAdABlAG4AZAA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAGUAeAB0AGUAbgBkACkALAAgAGUAeAB0AGUAbgBkACAAPAAgADEAKQAsAFwAbgAgACAAIAAgAE4AbwBUAGEAcgBnAGUAdAA/ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEYAQQBMAFMARQAsACAATgBPAFQAKABPAFIAKABiAG8AbwBsACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAGwAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABFAHgAdABlAG4AZAA/ACwAIABcACIAIwBFAFgAVABFAE4ARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AVABhAHIAZwBlAHQAPwAsACAAXAAiACMAVABBAFIARwBFAFQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATQBlAHMAaAAgAGcAcgBpAGQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAZQBuAHQAZQByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAaQAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABpACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABqACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGoALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBpAHIAYwBsAGUAIABtAGEAcwBrAFwAbgAgACAAIAAgAG0AYQBzAGsALAAgACAAIAAoAGkAIAAtACAAeAApAF4AMgAgACsAIAAoAGoAIAAtACAAeQApAF4AMgAgADwAPQAgAGUAeAB0AGUAbgBkAF4AMgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYQBuAGQAIABzAHEAdQBlAGUAegBlAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIABTAHEAdQBlAGUAegBlALsDKABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABEAGkAYQBtAG8AbgBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQwBHAHIAaQBkALsDLAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAIABkAGkAYQBtAG8AbgBkABEgcwBoAGEAcABlAGQAIAByAGUAZwBpAG8AbgAgACgATQBhAG4AaABhAHQAdABhAG4AIAByAGEAZABpAHUAcwApACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAHkAXABuACAAIAAgACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAIABkAGkAcwB0AGEAbgBjAGUALgAgAFQAaABlACAAYwBlAG4AdABlAHIAIABtAGEAeQAgAGIAZQAgAGcAaQB2AGUAbgAgAGEAcwAgAGEAIABzAGMAYQBsAGEAcgBcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGEAcwAgAGUAeABwAGwAaQBjAGkAdAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgAgAFQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgBcAG4AIAAgACAAIABwAHIAZQBzAGUAcgB2AGUAcwAgAGkAdABzACAAZwBlAG8AbQBlAHQAcgBpAGMAIABzAGgAYQBwAGUALAAgAGEAbgBkACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAbwBuAGwAeQAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAXABuACAAIAAgACAAYQByAGUAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAgACAAIAAgACAAIAAtACAAQwBlAG4AdABlAHIAIABvAGYAIAB0AGgAZQAgAGQAaQBhAG0AbwBuAGQALgAgAE0AYQB5ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgBcAG4AIAAgACAAIABkAGkAcwB0AGEAbgBjAGUAIAAgACAAIAAtACAATQBhAG4AaABhAHQAdABhAG4AIAByAGEAZABpAHUAcwAgAG8AZgAgAHQAaABlACAAZABpAGEAbQBvAG4AZAAgACgAbQB1AHMAdAAgAGIAZQAgAGEAIABwAG8AcwBpAHQAaQB2AGUAIABpAG4AdABlAGcAZQByACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAZABpAGEAbQBvAG4AZAAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAGkAYQBtAG8AbgBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAsAFwAbgAgACAAIAAgAGQAaQBzAHQAYQBuAGMAZQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAGEAcgBnAGUAdAAgAGkAbgB0AGUAcgBwAHIAZQB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMASQBfAEoAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAKAB0AGEAcgBnAGUAdAApACAAPQAgADIALABcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABUAEEASwBFACgAdABhAHIAZwBlAHQALAAgAC0AMQAsACAALQAxACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAG8AbwBsAGUAYQBuACAAbQBhAHQAYwBoACAAZgBvAHIAIABzAGMAYQBsAGEAcgAgAHQAYQByAGcAZQB0AFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAGcAcgBpAGQAIAA9ACAAdABhAHIAZwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARABpAHMAdABhAG4AYwBlAD8ALAAgAE8AUgAoAEkAUwBUAEUAWABUACgAZABpAHMAdABhAG4AYwBlACkALAAgAGQAaQBzAHQAYQBuAGMAZQAgADwAIAAxACkALABcAG4AIAAgACAAIABOAG8AVABhAHIAZwBlAHQAPwAsACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABOAE8AVAAoAE8AUgAoAGIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAbABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABEAGkAcwB0AGEAbgBjAGUAPwAsACAAXAAiACMARABJAFMAVABBAE4AQwBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBUAGEAcgBnAGUAdAA/ACwAIABcACIAIwBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABpACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEkATgBEAEUAWAAoAGoALAAgAHIALAAgAGMAKQAsACAAVABPAEMATwBMACgASQBGACgAYgBvAG8AbAAsACAAagAsACAATgBBACgAKQApACwAIAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAYQBtAG8AbgBkACAAbQBhAHMAawAgACgATQBhAG4AaABhAHQAdABhAG4AIABkAGkAcwB0AGEAbgBjAGUAKQBcAG4AIAAgACAAIABtAGEAcwBrACwAIAAgACAAQQBCAFMAKABpACAALQAgAHgAKQAgACsAIABBAEIAUwAoAGoAIAAtACAAeQApACAAPAA9ACAAZABpAHMAdABhAG4AYwBlACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABhAG4AZAAgAHMAcQB1AGUAZQB6AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAFMAcQB1AGUAZQB6AGUAuwMoAEkARgAoAG0AYQBzAGsALAAgAGcAcgBpAGQALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBHADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFAAbAB1AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAHAAbAB1AHMAESBzAGgAYQBwAGUAZAAgAHIAZQBnAGkAbwBuACAAKABlAHgAdABlAG4AZABlAGQAIAB2AG8AbgAgAE4AZQB1AG0AYQBuAG4AIABuAGUAaQBnAGgAYgBvAHIAaABvAG8AZAApACAAZgByAG8AbQAgAGEAIAAyAEQAXABuACAAIAAgACAAYQByAHIAYQB5ACAAYgB5ACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAbgAgAGUAeAB0AGUAbgBkACAAdgBhAGwAdQBlAC4AIABUAGgAZQAgAGMAZQBuAHQAZQByACAAbQBhAHkAIABiAGUAIABnAGkAdgBlAG4AXABuACAAIAAgACAAYQBzACAAYQAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABhAHMAIABlAHgAcABsAGkAYwBpAHQAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AIABUAGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkAFwAbgAgACAAIAAgAHIAZQBnAGkAbwBuACAAcAByAGUAcwBlAHIAdgBlAHMAIABpAHQAcwAgAGcAZQBvAG0AZQB0AHIAaQBjACAAcwBoAGEAcABlACwAIABhAG4AZAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAG8AbgBsAHkAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAgAGEAcgBlACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAdABhAHIAZwBlAHQAIAAgACAAIAAgACAALQAgAEMAZQBuAHQAZQByACAAbwBmACAAdABoAGUAIABwAGwAdQBzAC4AIABNAGEAeQAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAgAGMAcgBpAHQAZQByAGkAbwBuACAAbwByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIAB0AGgAZQAgAGYAbwByAG0AIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AXABuACAAIAAgACAAZQB4AHQAZQBuAGQAIAAgACAAIAAgACAALQAgAFIAYQBkAGkAdQBzACAAbwBmACAAdABoAGUAIABwAGwAdQBzACAAYQByAG0AcwAgACgAbQB1AHMAdAAgAGIAZQAgAGEAIABwAG8AcwBpAHQAaQB2AGUAIABpAG4AdABlAGcAZQByACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAcABsAHUAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBQAGwAdQBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAsAFwAbgAgACAAIAAgAGUAeAB0AGUAbgBkACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAGEAcgBnAGUAdAAgAGkAbgB0AGUAcgBwAHIAZQB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMASQBfAEoAPwAsACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVAAoAHQAYQByAGcAZQB0ACkAIAA9ACAAMgAsAFwAbgAgACAAIAAgAHIALAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIAAgACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIAAgACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAtADEALAAgAC0AMQApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBvAG8AbABlAGEAbgAgAG0AYQB0AGMAaAAgAGYAbwByACAAcwBjAGEAbABhAHIAIAB0AGEAcgBnAGUAdABcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAGcAcgBpAGQAIAA9ACAAdABhAHIAZwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABYAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEUAeAB0AGUAbgBkAD8ALAAgAE8AUgAoAEkAUwBUAEUAWABUACgAZQB4AHQAZQBuAGQAKQAsACAAZQB4AHQAZQBuAGQAIAA8ACAAMQApACwAXABuACAAIAAgACAATgBvAFQAYQByAGcAZQB0AD8ALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABOAE8AVAAoAE8AUgAoAGIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAbABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIAAwACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAZwByAGkAZAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAXAAiACMAMQBEAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEUAeAB0AGUAbgBkAD8ALAAgAFwAIgAjAEUAWABUAEUATgBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBUAGEAcgBnAGUAdAA/ACwAIABcACIAIwBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABpACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEkATgBEAEUAWAAoAGoALAAgAHIALAAgAGMAKQAsACAAVABPAEMATwBMACgASQBGACgAYgBvAG8AbAAsACAAagAsACAATgBBACgAKQApACwAIAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGwAdQBzACAAbQBhAHMAawAgACgAaABvAHIAaQB6AG8AbgB0AGEAbAAgACsAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAbQBzACkAXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACgAaQAgAD0AIAB4ACkAIAAqACAAKABBAEIAUwAoAGoAIAAtACAAeQApACAAPAA9ACAAZQB4AHQAZQBuAGQAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAagAgAD0AIAB5ACkAIAAqACAAKABBAEIAUwAoAGkAIAAtACAAeAApACAAPAA9ACAAZQB4AHQAZQBuAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYQBuAGQAIABzAHEAdQBlAGUAegBlAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIABTAHEAdQBlAGUAegBlALsDKABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABQAHkAcgBhAG0AaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAATQBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABvAG4AZQAgAG8AZgAgAGYAbwB1AHIAIAB0AHIAaQBhAG4AZwB1AGwAYQByACAAXAAiAHAAeQByAGEAbQBpAGQAXAAiACAAcgBlAGcAaQBvAG4AcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAGkAbABlAFwAbgAgACAAIAAgAHAAcgBlAHMAZQByAHYAaQBuAGcAIABzAGgAYQBwAGUALgAgAFAAeQByAGEAbQBpAGQAIAByAGUAZwBpAG8AbgBzACAAYQByAGUAIABkAGUAZgBpAG4AZQBkACAAdQBzAGkAbgBnACAAcgBvAHcALwBjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABnAGUAbgBlAHIAYQB0AGUAZAAgAGIAeQAgAE0ARwByAGkAZAC7Ay4AIABBAG4AIABvAHAAdABpAG8AbgBhAGwAIABmAGkAbABsAF8AdgBhAGwAdQBlACAAYwBvAG4AdAByAG8AbABzACAAdwBoAGEAdAAgAGEAcABwAGUAYQByAHMAIABvAHUAdABzAGkAZABlACAAdABoAGUAXABuACAAIAAgACAAcwBlAGwAZQBjAHQAZQBkACAAcgBlAGcAaQBvAG4ALgBcAG4AXABuACAAIAAgACAAUAB5AHIAYQBtAGkAZAAgAHAAaQBlAGMAZQBzACAAKABjAGwAbwBjAGsAdwBpAHMAZQApADoAXABuACAAIAAgACAAIAAgACAAIAAxACAALQAgAFUAcABwAGUAcgAgAHIAaQBnAGgAdABcAG4AIAAgACAAIAAgACAAIAAgADIAIAAtACAATABvAHcAZQByACAAcgBpAGcAaAB0AFwAbgAgACAAIAAgACAAIAAgACAAMwAgAC0AIABMAG8AdwBlAHIAIABsAGUAZgB0AFwAbgAgACAAIAAgACAAIAAgACAANAAgAC0AIABVAHAAcABlAHIAIABsAGUAZgB0AFwAbgBcAG4AIAAgACAAIABQAHkAcgBhAG0AaQBkACAAZQB4AHQAcgBhAGMAdABpAG8AbgBzACAAYQByAGUAIABtAG8AcwB0ACAAbQBlAGEAbgBpAG4AZwBmAHUAbAAgAG8AbgAgAHMAcQB1AGEAcgBlACAAbwByACAAbgBlAGEAcgARIHMAcQB1AGEAcgBlACAAbQBhAHQAcgBpAGMAZQBzAC4AXABuACAAIAAgACAATwBuACAAdABhAGwAbAAgAG8AcgAgAG4AYQByAHIAbwB3ACAAbQBhAHQAcgBpAGMAZQBzACwAIAB0AGgAZQAgAHIAZQBzAHUAbAB0AGkAbgBnACAAcwBoAGEAcABlAHMAIABtAGEAeQAgAGIAZQAgAHYAaQBzAHUAYQBsAGwAeQAgAHMAawBlAHcAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAHQAbwAgAGUAeAB0AHIAYQBjAHQAIAB0AGgAZQAgAHIAZQBnAGkAbwBuAC4AXABuACAAIAAgACAAWwBwAGkAZQBjAGUAXQAgACAAIAAgACAAIAAtACAASQBuAHQAZQBnAGUAcgAgADEAEyA0ACAAcwBlAGwAZQBjAHQAaQBuAGcAIAB0AGgAZQAgAHAAeQByAGEAbQBpAGQAIAByAGUAZwBpAG8AbgAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACAALQAgAFMAYwBhAGwAYQByACAAdQBzAGUAZAAgAG8AdQB0AHMAaQBkAGUAIAB0AGgAZQAgAHIAZQBnAGkAbwBuAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABcACIAXAAiAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFAAeQByAGEAbQBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBwAGkAZQBjAGUAXQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABlACAAcABpAGUAYwBlAFwAbgAgACAAIAAgAHAAaQBlAGMAZQAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABpAGUAYwBlACkALAAgADEALAAgAHAAaQBlAGMAZQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABQAGkAZQBjAGUAPwAsACAATwBSACgAcABpAGUAYwBlACAAPAAgADEALAAgAHAAaQBlAGMAZQAgAD4AIAA0ACwAIABJAFMAVABFAFgAVAAoAHAAaQBlAGMAZQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAbABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAXAAiAFwAIgAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAUABpAGUAYwBlAD8ALAAgAFwAIgAjAFAASQBFAEMARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAHkAcgBhAG0AaQBkACAAbQBhAHMAawBzACAAKABjAGwAbwBjAGsAdwBpAHMAZQApAFwAbgAgACAAIAAgAHUAcABwAGUAcgBfAHIAaQBnAGgAdAAsACAAaQAgADwAPQAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgADEAXABuACAAIAAgACAAbABvAHcAZQByAF8AcgBpAGcAaAB0ACwAIABpACAAKwAgAGoAIAA+AD0AIABoACAAKwAgADEALAAgACAALwAvACAAMgBcAG4AIAAgACAAIABsAG8AdwBlAHIAXwBsAGUAZgB0ACwAIAAgAGkAIAA+AD0AIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAFwAbgAgACAAIAAgAHUAcABwAGUAcgBfAGwAZQBmAHQALAAgACAAaQAgACsAIABqACAAPAA9ACAAaAAgACsAIAAxACwAIAAgAC8ALwAgADQAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBlAGcAaQBvAG4AXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACAAIAAgACAAIABJAEYAKABwAGkAZQBjAGUAIAA9ACAAMQAsACAAdQBwAHAAZQByAF8AcgBpAGcAaAB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABwAGkAZQBjAGUAIAA9ACAAMgAsACAAbABvAHcAZQByAF8AcgBpAGcAaAB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHAAaQBlAGMAZQAgAD0AIAAzACwAIABsAG8AdwBlAHIAXwBsAGUAZgB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AHAAcABlAHIAXwBsAGUAZgB0ACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABJAEYAKABtAGEAcwBrACwAIABhAHIAcgBhAHkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGkAbgBnALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAATQBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhACAAcwBpAG4AZwBsAGUAIAByAGkAbgBnACAAKABsAGEAeQBlAHIAKQAgAGYAcgBvAG0AIABhACAAMgBEACAAZwByAGkAZAAgAHcAaABpAGwAZQAgAHAAcgBlAHMAZQByAHYAaQBuAGcAIAB0AGgAZQAgAG8AdgBlAHIAYQBsAGwAXABuACAAIAAgACAAcwBoAGEAcABlACAAbwBmACAAdABoAGUAIABnAHIAaQBkAC4AIABMAGEAeQBlAHIAIAAxACAAYwBvAHIAcgBlAHMAcABvAG4AZABzACAAdABvACAAdABoAGUAIABvAHUAdABlAHIAbQBvAHMAdAAgAHAAZQByAGkAbQBlAHQAZQByACwAIABhAG4AZAAgAGgAaQBnAGgAZQByAFwAbgAgACAAIAAgAGwAYQB5AGUAcgBzACAAbQBvAHYAZQAgAGkAbgB3AGEAcgBkAC4AIABUAGgAZQAgAG8AdQB0AHAAdQB0ACAAYQBsAHcAYQB5AHMAIABtAGEAdABjAGgAZQBzACAAdABoAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAbwBmACAAdABoAGUAIABpAG4AcAB1AHQAXABuACAAIAAgACAAZwByAGkAZAAsACAAdwBpAHQAaAAgAGEAbABsACAAbgBvAG4AESByAGkAbgBnACAAYwBlAGwAbABzACAAZgBpAGwAbABlAGQAIAB1AHMAaQBuAGcAIABmAGkAbABsAF8AdgBhAGwAdQBlAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAgAHIAZQBwAHIAZQBzAGUAbgB0AGkAbgBnACAAdABoAGUAIABmAHUAbABsACAAZwByAGkAZAAuAFwAbgAgACAAIAAgAGwAYQB5AGUAcgAgACAAIAAgACAAIAAgAC0AIABJAG4AdABlAGcAZQByACAAZSIgADEAIABzAHAAZQBjAGkAZgB5AGkAbgBnACAAdwBoAGkAYwBoACAAcgBpAG4AZwAgAHQAbwAgAGUAeAB0AHIAYQBjAHQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABhAHkAZQByAHMAIABlAHgAYwBlAGUAZABpAG4AZwAgAHQAaABlACAAaQBuAG4AZQByAG0AbwBzAHQAIAByAGkAbgBnACAAcgBlAHQAdQByAG4AIABcACIAIwBNAEEAWAAtAEwAQQBZAEUAUgA6ACAAbgBcACIALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAdABvACAAZgBpAGwAbAAgAG4AbwBuABEgcgBpAG4AZwAgAGMAZQBsAGwAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFQAaABpAHMAIABmAHUAbgBjAHQAaQBvAG4AIABwAGUAcgBmAG8AcgBtAHMAIABuAG8AIAByAG8AdABhAHQAaQBvAG4AOwAgAGkAdAAgAG8AbgBsAHkAIABlAHgAdAByAGEAYwB0AHMAIAB0AGgAZQAgAHIAaQBuAGcAIABtAGEAcwBrAC4AXABuACAAIAAgACAAIiAgAEQAZQBnAGUAbgBlAHIAYQB0AGUAIAByAGkAbgBnAHMAIAAoADEA1wBOACwAIABOANcAMQAsACAAMgDXAE4ALAAgAGUAdABjAC4AKQAgAGEAcgBlACAAcAByAGUAcwBlAHIAdgBlAGQAIABlAHgAYQBjAHQAbAB5AC4AXABuACAAIAAgACAAIiAgAFIAaQBuAGcAUgBvAHQAYQB0AGUAuwMgAGEAbgBkACAAUgBpAG4AZwBSAG8AdABhAHQAZQBSAGUAdgC7AyAAcgBlAGwAeQAgAG8AbgAgAFIAaQBuAGcAuwMgAHQAbwAgAGkAZABlAG4AdABpAGYAeQAgAHIAaQBuAGcAIABiAG8AdQBuAGQAYQByAGkAZQBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAaQBuAGcAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAGwAYQB5AGUAcgAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEwAYQB5AGUAcgA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAGwAYQB5AGUAcgApACwAIABsAGEAeQBlAHIAIAA8AD0AIAAwACkALABcAG4AIAAgACAAIABNAGEAeABMAGEAeQBlAHIALAAgACAAIAAgACAAIABJAE4AVAAoACgATQBJAE4AKABoACwAIAB3ACkAIAArACAAMQApACAALwAgADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABnAHIAaQBkACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABcACIAIwAxAEQALQBBAFIAUgBBAFkAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQATABhAHkAZQByAD8ALAAgAFwAIgAjAEwAQQBZAEUAUgAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGEAeQBlAHIAIAA+ACAATQBhAHgATABhAHkAZQByACwAIABcACIAIwBNAEEAWAAtAEwAQQBZAEUAUgA6ACAAXAAiACAAJgAgAE0AYQB4AEwAYQB5AGUAcgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAbABsAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgADAALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBpAG4AZwAgAGUAZABnAGUAcwBcAG4AIAAgACAAIAB0AG8AcAAsACAAIAAgACAAIAAgACAAIAAgACgAKABpACAAPQAgAGwAYQB5AGUAcgApACAAKwAgACgAaQAgAD0AIAAxACAAKwAgAGgAIAAtACAAbABhAHkAZQByACkAKQAgACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoACgAagAgAD4AIABsAGEAeQBlAHIAIAAtACAAMQApACAAKgAgACgAagAgADwAPQAgADEAIAArACAAdwAgAC0AIABsAGEAeQBlAHIAKQApACwAXABuAFwAbgAgACAAIAAgAHMAaQBkAGUALAAgACAAIAAgACAAIAAgACAAKAAoAGoAIAA9ACAAbABhAHkAZQByACkAIAArACAAKABqACAAPQAgADEAIAArACAAdwAgAC0AIABsAGEAeQBlAHIAKQApACAAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAKABpACAAPgAgAGwAYQB5AGUAcgAgAC0AIAAxACkAIAAqACAAKABpACAAPAA9ACAAMQAgACsAIABoACAALQAgAGwAYQB5AGUAcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AYgBpAG4AZQBkACAAcgBpAG4AZwAgAG0AYQBzAGsAXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAdABvAHAAIAArACAAcwBpAGQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEcAMAA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBxAHUAYQByAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAHMAcQB1AGEAcgBlABEgcwBoAGEAcABlAGQAIAByAGUAZwBpAG8AbgAgACgAQwBoAGUAYgB5AHMAaABlAHYAIAByAGEAZABpAHUAcwApACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAHkAXABuACAAIAAgACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAbgAgAGUAeAB0AGUAbgBkACAAdgBhAGwAdQBlAC4AIABUAGgAZQAgAGMAZQBuAHQAZQByACAAbQBhAHkAIABiAGUAIABnAGkAdgBlAG4AIABhAHMAIABhAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABhAHMAIABlAHgAcABsAGkAYwBpAHQAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AIABUAGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkACAAcgBlAGcAaQBvAG4AXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBlAHMAIABpAHQAcwAgAGcAZQBvAG0AZQB0AHIAaQBjACAAcwBoAGEAcABlACwAIABhAG4AZAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAG8AbgBsAHkAIABmAGkAbABsAF8AdgBhAGwAdQBlAFwAbgAgACAAIAAgAGEAcgBlACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAdABhAHIAZwBlAHQAIAAgACAAIAAgACAALQAgAEMAZQBuAHQAZQByACAAbwBmACAAdABoAGUAIABzAHEAdQBhAHIAZQAuACAATQBhAHkAIABiAGUAIABhACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBmACAAdABoAGUAIABmAG8AcgBtACAAewByAG8AdwAsACAAYwBvAGwAfQAuAFwAbgAgACAAIAAgAGUAeAB0AGUAbgBkACAAIAAgACAAIAAgAC0AIABDAGgAZQBiAHkAcwBoAGUAdgAgAHIAYQBkAGkAdQBzACAAbwBmACAAdABoAGUAIABzAHEAdQBhAHIAZQAgACgAbQB1AHMAdAAgAGIAZQAgAGEAIABwAG8AcwBpAHQAaQB2AGUAIABpAG4AdABlAGcAZQByACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAcwBxAHUAYQByAGUALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADAALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBxAHUAYQByAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACwAXABuACAAIAAgACAAZQB4AHQAZQBuAGQALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAYQByAGcAZQB0ACAAaQBuAHQAZQByAHAAcgBlAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBJAF8ASgA/ACwAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUACgAdABhAHIAZwBlAHQAKQAgAD0AIAAyACwAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAFQAQQBLAEUAKAB0AGEAcgBnAGUAdAAsACAALQAxACwAIAAtADEAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAdABjAGgAIABmAG8AcgAgAHMAYwBhAGwAYQByACAAdABhAHIAZwBlAHQAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABnAHIAaQBkACAAPQAgAHQAYQByAGcAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHAAdQB0ACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABFAHgAdABlAG4AZAA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAGUAeAB0AGUAbgBkACkALAAgAGUAeAB0AGUAbgBkACAAPAAgADEAKQAsAFwAbgAgACAAIAAgAE4AbwBUAGEAcgBnAGUAdAA/ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEYAQQBMAFMARQAsACAATgBPAFQAKABPAFIAKABiAG8AbwBsACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAGwAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABFAHgAdABlAG4AZAA/ACwAIABcACIAIwBFAFgAVABFAE4ARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AVABhAHIAZwBlAHQAPwAsACAAXAAiACMAVABBAFIARwBFAFQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATQBlAHMAaAAgAGcAcgBpAGQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAaQAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABpACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAagAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABqACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAcQB1AGEAcgBlACAAbQBhAHMAawAgACgAQwBoAGUAYgB5AHMAaABlAHYAIABkAGkAcwB0AGEAbgBjAGUAKQBcAG4AIAAgACAAIABtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgACgAQQBCAFMAKABpACAALQAgAHgAKQAgADwAPQAgAGUAeAB0AGUAbgBkACkAIAAqACAAKABBAEIAUwAoAGoAIAAtACAAeQApACAAPAA9ACAAZQB4AHQAZQBuAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYQBuAGQAIABzAHEAdQBlAGUAegBlAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAUwBxAHUAZQBlAHoAZQC7AygASQBGACgAbQBhAHMAawAsACAAZwByAGkAZAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEcAMAA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVAByAGkAYQBuAGcAbABlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQwBHAHIAaQBkALsDLAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAIABkAGkAcgBlAGMAdABpAG8AbgBhAGwAIAB0AHIAaQBhAG4AZwB1AGwAYQByACAAcgBlAGcAaQBvAG4AIAAoAHUAcABwAGUAcgAgAG8AcgAgAGwAbwB3AGUAcgApACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAHkAXABuACAAIAAgACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAIABNAGEAbgBoAGEAdAB0AGEAbgAgAHIAYQBkAGkAdQBzAC4AIABUAGgAZQAgAGMAZQBuAHQAZQByACAAbQBhAHkAIABiAGUAIABnAGkAdgBlAG4AIABhAHMAIABhAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABhAHMAIABlAHgAcABsAGkAYwBpAHQAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AIABUAGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkACAAcgBlAGcAaQBvAG4AXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBlAHMAIABpAHQAcwAgAGcAZQBvAG0AZQB0AHIAaQBjACAAcwBoAGEAcABlACwAIABhAG4AZAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAG8AbgBsAHkAIABmAGkAbABsAF8AdgBhAGwAdQBlAFwAbgAgACAAIAAgAGEAcgBlACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAdABhAHIAZwBlAHQAIAAgACAAIAAgACAALQAgAEMAZQBuAHQAZQByACAAbwBmACAAdABoAGUAIAB0AHIAaQBhAG4AZwBsAGUALgAgAE0AYQB5ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgBcAG4AIAAgACAAIAByAGEAZABpAHUAcwAgACAAIAAgACAAIAAtACAATQBhAG4AaABhAHQAdABhAG4AIAByAGEAZABpAHUAcwAgAG8AZgAgAHQAaABlACAAdAByAGkAYQBuAGcAbABlACAAKABtAHUAcwB0ACAAYgBlACAAYQAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAKQAuAFwAbgAgACAAIAAgAFsAYgBlAGwAbwB3AF0AIAAgACAAIAAgAC0AIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgBzACAAdABoAGUAIABsAG8AdwBlAHIAIAB0AHIAaQBhAG4AZwBsAGUAOwAgAGkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHIAZQB0AHUAcgBuAHMAIAB1AHAAcABlAHIALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdAByAGkAYQBuAGcAbABlAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAwAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAcgBpAGEAbgBnAGwAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAdABhAHIAZwBlAHQALABcAG4AIAAgACAAIAByAGEAZABpAHUAcwAsAFwAbgAgACAAIAAgAFsAYgBlAGwAbwB3AF0ALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAYQByAGcAZQB0ACAAaQBuAHQAZQByAHAAcgBlAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBJAF8ASgA/ACwAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUACgAdABhAHIAZwBlAHQAKQAgAD0AIAAyACwAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAFQAQQBLAEUAKAB0AGEAcgBnAGUAdAAsACAALQAxACwAIAAtADEAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAdABjAGgAIABmAG8AcgAgAHMAYwBhAGwAYQByACAAdABhAHIAZwBlAHQAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABnAHIAaQBkACAAPQAgAHQAYQByAGcAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHAAdQB0ACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABSAGEAZABpAHUAcwA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAHIAYQBkAGkAdQBzACkALAAgAHIAYQBkAGkAdQBzACAAPAAgADEAKQAsAFwAbgAgACAAIAAgAE4AbwBUAGEAcgBnAGUAdAA/ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEYAQQBMAFMARQAsACAATgBPAFQAKABPAFIAKABiAG8AbwBsACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuACAAIAAgACAASQBzAEEAYgBvAHYAZQA/ACwAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGIAZQBsAG8AdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABSAGEAZABpAHUAcwA/ACwAIABcACIAIwBSAEEARABJAFUAUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AVABhAHIAZwBlAHQAPwAsACAAXAAiACMAVABBAFIARwBFAFQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATQBlAHMAaAAgAGcAcgBpAGQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAaQAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABpACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAagAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABqACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuACAAbQBhAHMAawBcAG4AIAAgACAAIABkAGkAcgAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBBAGIAbwB2AGUAPwAsACAAKABpACAAPAA9ACAAeAApACwAIAAoAGkAIAA+AD0AIAB4ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAHIAaQBhAG4AZwBsAGUAIABtAGEAcwBrACAAKABNAGEAbgBoAGEAdAB0AGEAbgAgAGQAaQBzAHQAYQBuAGMAZQAgACsAIABkAGkAcgBlAGMAdABpAG8AbgApAFwAbgAgACAAIAAgAG0AYQBzAGsALAAgACAAIAAgACAAIAAgACAAKABBAEIAUwAoAGkAIAAtACAAeAApACAAKwAgAEEAQgBTACgAagAgAC0AIAB5ACkAIAA8AD0AIAByAGEAZABpAHUAcwApACAAKgAgAGQAaQByACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABhAG4AZAAgAHMAcQB1AGUAZQB6AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABTAHEAdQBlAGUAegBlALsDKABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACMAIwAgADAAMwAgAC0AIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACAAKgAvAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGgAYQBwAGkAbgBnACAAZgB1AG4AYwB0AGkAbwBuAHMAIAByAGUAcwBoAGEAcABlACwAIAByAGUAcwBpAHoAZQAsACAAdwByAGEAcAAsACAAcABhAGQALAAgAHQAcgBhAHYAZQByAHMAZQAsACAAbwByACAAcgBlAGYAbABvAHcAIABnAHIAaQBkAHMAIAB3AGgAaQBsAGUAXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBpAG4AZwAgAHQAaABlACAAcwB0AHIAdQBjAHQAdQByAGUAIABvAGYAIAB0AGgAZQAgAHUAbgBkAGUAcgBsAHkAaQBuAGcAIABkAGEAdABhAC4AXABuAFwAbgAgACAAIAAgAFMAdQBiACAAYwBhAHQAZQBnAG8AcgBpAGUAcwA6AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABDAG8AcgBlACAAUwBoAGEAcABpAG4AZwAgAFAAcgBpAG0AaQB0AGkAdgBlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAUwBoAGEAcABlADIARAC7AywAIABSAGUAcwBpAHoAZQC7AywAIABTAGMAYQBuADIARAC7AywAIABUAHIAYQB2AGUAcgBzAGUAuwMsACAAVABhAGsAZQBCAGwAbwBjAGsAuwMsACAARABTAHQAYQBjAGsAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUgBlAGYAbABvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABXAHIAYQBwAFIAbwB3AHMAMgBEALsDLAAgAFcAcgBhAHAAQwBvAGwAcwAyAEQAuwMsACAAUwB0AGEAaQByAGMAYQBzAGUAuwMsACAAVQBuAFAAaQB2AG8AdAC7AywAIABaAGkAcAC7AywAIABTAGwAaQBjAGUAQgB5AEQAZQBnALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAZAC7AywAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AywAIABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABJAG4AdABlAHIAcABvAGwAYQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBhAGcAbgBpAGYAeQC7AywAIABaAG8AbwBtALsDXABuAFwAbgAgACAAIAAgAEEAbABsACAAcwBoAGEAcABpAG4AZwAgAGYAdQBuAGMAdABpAG8AbgBzACAAcAByAGUAcwBlAHIAdgBlACAAMgBEACAAZwBlAG8AbQBlAHQAcgB5ACAAYQBuAGQAIAByAGUAdAB1AHIAbgAgAGEAcgByAGEAeQBzACAAdwBoAG8AcwBlACAAcwB0AHIAdQBjAHQAdQByAGUAXABuACAAIAAgACAAaQBzACAAZQB4AHAAbABpAGMAaQB0AGwAeQAgAGQAZQBmAGkAbgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBhAG4AcwBmAG8AcgBtAGEAdABpAG8AbgAgAHIAdQBsAGUAcwAuAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8ALwAgACAAQwBvAHIAZQAgAFMAaABhAHAAaQBuAGcAIABQAHIAaQBtAGkAdABpAHYAZQBzAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGUAUwBoAGEAcABlADIARAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBzAGgAYQBwAGUAcwAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYQAgAG4AZQB3ACAAYwBvAGwAdQBtAG4AIAB3AGkAZAB0AGgAIAB1AHMAaQBuAGcAIAByAG8AdwARIG0AYQBqAG8AcgAgAG8AcgBkAGUAcgAuACAAQQBsAGwAIAB2AGEAbAB1AGUAcwBcAG4AIAAgACAAIABhAHIAZQAgAHAAcgBlAHMAZQByAHYAZQBkACAAaQBuACAAcgBlAGEAZABpAG4AZwAgAG8AcgBkAGUAcgAsACAAYQBuAGQAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAGIAbABvAGMAawAgAGkAcwAgAHAAYQBkAGQAZQBkACAAaQBmACAAbgBlAGUAZABlAGQALgBcAG4AIAAgACAAIABPAG4AZQARIGQAaQBtAGUAbgBzAGkAbwBuAGEAbAAgAGEAcgByAGEAeQBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQALgBcAG4AXABuAEUAeABhAG0AcABsAGUAOgBcAG4AIAAgACAAIABJAG4AcAB1AHQAOgBcAG4AIAAgACAAIAAgACAAIAAgAHsAMQAsADIALAAzACwANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAA1ACwANgAsADcALAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgADkALAAxADAALAAxADEALAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMQAzACwAMQA0ACwAMQA1ACwAMQA2AH0AXABuAFwAbgAgACAAIAAgAD0AUgBlAFMAaABhAHAAZQAyAEQAuwMoAGEAcgByAGEAeQAsACAAMgApAFwAbgBcAG4AIAAgACAAIABPAHUAdABwAHUAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAewAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAzACwANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAA1ACwANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAA3ACwAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAA5ACwAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgADEAMQAsADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAxADMALAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMQA1ACwAMQA2AH0AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAcgBlAHMAaABhAHAAZQAuACAATwBuAGUAESBkAGkAbQBlAG4AcwBpAG8AbgBhAGwAIABhAHIAcgBhAHkAcwAgAGEAcgBlACAAcgBlAGoAZQBjAHQAZQBkAC4AXABuACAAIAAgACAAbgBlAHcAXwB3AGkAZAB0AGgAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIAByAGUAcwBoAGEAcABlAGQAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0AIAAgACAALQAgAFMAYwBhAGwAYQByACAAdQBzAGUAZAAgAHQAbwAgAGYAaQBsAGwAIABpAG4AYwBvAG0AcABsAGUAdABlACAAZgBpAG4AYQBsACAAcgBvAHcAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAATgBBACgAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQBzAGgAYQBwAGkAbgBnACAAaQBzACAAcABlAHIAZgBvAHIAbQBlAGQAIABzAHQAcgBpAGMAdABsAHkAIABpAG4AIAByAG8AdwARIG0AYQBqAG8AcgAgAG8AcgBkAGUAcgAuAFwAbgAgACAAIAAgACIgIABuAGUAdwBfAHcAaQBkAHQAaAAgAG0AdQBzAHQAIABiAGUAIABsAGUAcwBzACAAdABoAGEAbgAgAG8AcgAgAGUAcQB1AGEAbAAgAHQAbwAgAHQAaABlACAAbwByAGkAZwBpAG4AYQBsACAAdwBpAGQAdABoAC4AXABuACAAIAAgACAAIiAgAFQAaABpAHMAIABmAHUAbgBjAHQAaQBvAG4AIABkAG8AZQBzACAAbgBvAHQAIABmAGwAYQB0AHQAZQBuACAAbwByACAAcgBlABEgdwByAGEAcAAgADEARAAgAGEAcgByAGEAeQBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBTAGgAYQBwAGUAMgBEALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACwAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABDAE8AVQBOAFQAQQAoAGEAcgByAGEAeQApACAALwAgAG4AZQB3AF8AdwBpAGQAdABoACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAGQAZABpAG4AZwBcAG4AIAAgACAAIABwAGEAZABfAHcAaQB0AGgALAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABhAGQAXwB3AGkAdABoACkALAAgAE4AQQAoACkALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAVwBpAGQAdABoACwAIAAgACAAbgBlAHcAXwB3AGkAZAB0AGgAIAA+ACAAdwAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAZQBjAHQAbwByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIABoACAAPgAgAHcALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAYQByAHIAYQB5ACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAVwBpAGQAdABoACwAIABcACIAIwBXAEkARABUAEgAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAQwBFAEkATABJAE4ARwAoAFMARQBRAFUARQBOAEMARQAoAG4AZQB3AF8AaABlAGkAZwBoAHQALAAgAG4AZQB3AF8AdwBpAGQAdABoACkAIAAvACAAdwAsACAAMQApACkALABcAG4AXABuACAAIAAgACAAbQBvAGQAdQBsAG8ALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAE0ATwBEACgAUwBFAFEAVQBFAE4AQwBFACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAbgBlAHcAXwB3AGkAZAB0AGgAKQAsACAAdwApACkALABcAG4AXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAG0AbwBkAHUAbABvACgAKQAgAD0AIAAwACwAIAB3ACwAIABtAG8AZAB1AGwAbwAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAcgBlAHMAZQBuAHQAXABuACAAIAAgACAAcgBlAHMAaABhAHAAZQBkACwAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpACgAKQAsACAAagAoACkAKQAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAaABhAHAAZQBkAFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGUAcwBpAHoAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBwAGUAYQB0AHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAdgBlAHIAdABpAGMAYQBsAGwAeQAgAGEAbgBkAC8AbwByACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkAIABiAHkAIABpAG4AdABlAGcAZQByACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAuAFwAbgAgACAAIAAgAFUAcwBlAHIAcwAgAG0AYQB5ACAAcwBwAGUAYwBpAGYAeQAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgALAAgAG8AcgAgAGIAbwB0AGgALgAgAEkAZgAgAGUAaQB0AGgAZQByACAAcABhAHIAYQBtAGUAdABlAHIAIABpAHMAIABvAG0AaQB0AHQAZQBkACwAXABuACAAIAAgACAAdABoAGUAIABvAG0AaQB0AHQAZQBkACAAZABpAG0AZQBuAHMAaQBvAG4AIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAxAC4AIABHAGUAbwBtAGUAdAByAHkAIABpAHMAIABwAHIAZQBzAGUAcgB2AGUAZAA7ACAAbgBvACAAZgBsAGEAdAB0AGUAbgBpAG4AZwBcAG4AIAAgACAAIABvAGMAYwB1AHIAcwAuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQA6AFwAbgAgACAAIAAgAEkAbgBwAHUAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAewAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAzACwANAB9AFwAbgBcAG4AIAAgACAAIAA9AFIAZQBzAGkAegBlALsDKABhAHIAcgBhAHkALAAgADIALAAgADMAKQBcAG4AXABuACAAIAAgACAATwB1AHQAcAB1AHQAOgBcAG4AIAAgACAAIAAgACAAIAAgAHsAMQAsADIALAAxACwAMgAsADEALAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgADMALAA0ACwAMwAsADQALAAzACwANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAxACwAMgAsADEALAAyACwAMQAsADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMwAsADQALAAzACwANAAsADMALAA0AH0AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAYgBlACAAcgBlAHAAZQBhAHQAZQBkAC4AXABuACAAIAAgACAAWwBoAGUAaQBnAGgAdABdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAdgBlAHIAdABpAGMAYQBsACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADEALgBcAG4AIAAgACAAIABbAHcAaQBkAHQAaABdACAAIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADEALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABSAGUAcABlAHQAaQB0AGkAbwBuACAAaQBzACAAcABlAHIAZgBvAHIAbQBlAGQAIAB2AGkAYQAgAGkAbgBkAGUAeAAgAHIAZQBtAGEAcABwAGkAbgBnAC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAZwBlAG8AbQBlAHQAcgB5ACAAaQBzACAAKABoACAA1wAgAGgAZQBpAGcAaAB0ACkAIABiAHkAIAAoAHcAIADXACAAdwBpAGQAdABoACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBlAHMAaQB6AGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBoAGUAaQBnAGgAdABdACwAXABuACAAIAAgACAAWwB3AGkAZAB0AGgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBtAGkAcwBzAGkAbwBuACAAYwBoAGUAYwBrAHMAXABuACAAIAAgACAASABlAGkAZwBoAHQATwBtAGkAdAB0AGUAZAA/ACwAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAaABlAGkAZwBoAHQAKQAsAFwAbgAgACAAIAAgAFcAaQBkAHQAaABPAG0AaQB0AHQAZQBkAD8ALAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAHcAaQBkAHQAaAApACwAXABuACAAIAAgACAATgBvAEgAVwBJAG4AcAB1AHQAPwAsACAAIAAgACAAIAAgAEgAZQBpAGcAaAB0AE8AbQBpAHQAdABlAGQAPwAgACsAIABXAGkAZAB0AGgATwBtAGkAdAB0AGUAZAA/ACAAPQAgADIALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAYQB1AGwAdAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMAXABuACAAIAAgACAAaABlAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAE4AbwBIAFcASQBuAHAAdQB0AD8ALAAgAEgAZQBpAGcAaAB0AE8AbQBpAHQAdABlAGQAPwApACwAIAAxACwAIABoAGUAaQBnAGgAdAApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAE4AbwBIAFcASQBuAHAAdQB0AD8ALAAgAFcAaQBkAHQAaABPAG0AaQB0AHQAZQBkAD8AKQAsACAAMQAsACAAdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAATgBvAFIAZQBwAGUAYQB0AD8ALAAgACAAIAAgACAAIAAgAEEATgBEACgAaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABFAHgAcABhAG4AZABTAGMAYQBsAGEAcgAsACAAIAAgACAARQBYAFAAQQBOAEQAKABhAHIAcgBhAHkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgALAAgAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAUgBlAHAAZQBhAHQAPwAsACAAIABPAFIAKABJAFMAVABFAFgAVAAoAGgAZQBpAGcAaAB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKAB3AGkAZAB0AGgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABBAE4ARAAoAEkAUwBOAFUATQBCAEUAUgAoAGgAZQBpAGcAaAB0ACkALAAgAGgAZQBpAGcAaAB0ACAAPAA9ACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgASQBTAE4AVQBNAEIARQBSACgAdwBpAGQAdABoACkALAAgACAAdwBpAGQAdABoACAAPAA9ACAAMAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAE4AbwBSAGUAcABlAGEAdAA/ACwAIABhAHIAcgBhAHkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAARQB4AHAAYQBuAGQAUwBjAGEAbABhAHIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAUgBlAHAAZQBhAHQAPwAsACAAYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBkAGUAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAIAAqACAAaABlAGkAZwBoAHQALABcAG4AIAAgACAAIABrAIIgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwAgACoAIAB3AGkAZAB0AGgALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAaQBjAGUAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAMQAgACsAIABNAE8ARAAoAFMARQBRAFUARQBOAEMARQAoAGsALAAsADAALAApACwAIABoACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAGsAgiAsACAAMQAsACAAMAApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAAxACAAKwAgAE0ATwBEACgAUwBFAFEAVQBFAE4AQwBFACgALAAgAGsAgiAsACAAMAApACwAIAB3ACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAawAsACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgBzAHQAcgB1AGMAdAAgAHIAZQBwAGUAYQB0AGUAZAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpACgAKQAsACAAagAoACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBjAGEAbgAyAEQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAUwBoAGEAcABlADIARAC7AywAIABUAHIAYQB2AGUAcgBzAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAIAB0AHIAYQB2AGUAcgBzAGEAbAARIGEAdwBhAHIAZQAgADIARAAgAHMAYwBhAG4AbgBpAG4AZwAgAG8AcABlAHIAYQB0AG8AcgAgAHQAaABhAHQAIABlAHgAdABlAG4AZABzACAARQB4AGMAZQBsABkgcwAgAG4AYQB0AGkAdgBlACAAUwBDAEEATgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALgAgAFMAYwBhAG4AMgBEALsDIABzAHUAcABwAG8AcgB0AHMAIABmAGkAdgBlACAAdAByAGEAdgBlAHIAcwBhAGwAIABtAG8AZABlAHMALAAgAGEAbABsAG8AdwBpAG4AZwAgAGEAYwBjAHUAbQB1AGwAYQB0AGkAbwBuACAAdABvAFwAbgAgACAAIAAgAGIAZQBnAGkAbgAgAGEAdAAgAGQAaQBmAGYAZQByAGUAbgB0ACAAYwBvAHIAbgBlAHIAcwAgAGEAbgBkACAAcAByAG8AYwBlAGUAZAAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAbwByAGQAZQByAHMALgAgAEYAbwByACAAMgBEACAAYQByAHIAYQB5AHMALABcAG4AIAAgACAAIABnAGUAbwBtAGUAdAByAHkAIABpAHMAIABwAHIAZQBzAGUAcgB2AGUAZAAuAFwAbgBcAG4AIAAgACAAIABGAG8AcgAgADEARAAgAGEAcgByAGEAeQBzACwAIABTAGMAYQBuADIARAC7AyAAYgBlAGgAYQB2AGUAcwAgAGwAaQBrAGUAIABuAGEAdABpAHYAZQAgAFMAQwBBAE4ALAAgAHcAaQB0AGgAIABvAHAAdABpAG8AbgBhAGwAIAByAGUAdgBlAHIAcwBlAFwAbgAgACAAIAAgAG8AcgBkAGUAcgAgAHcAaABlAG4AIABkAGkAcgBlAGMAdABpAG8AbgAgAD0AIAAtADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACAAIAAtACAAUwBhAG0AZQAgAG0AZQBhAG4AaQBuAGcAIABhAHMAIABuAGEAdABpAHYAZQAgAFMAQwBBAE4ALgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AIABTAGMAYQBsAGEAcgBzACAAYQBuAGQAIAAxAEQAIAB2AGUAYwB0AG8AcgBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAgAHcAaQB0AGgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBzAHQAcgBpAGMAdABlAGQAIABkAGkAcgBlAGMAdABpAG8AbgAgAHMAZQBtAGEAbgB0AGkAYwBzAC4AXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACAAIAAgACAAIAAgACAALQAgAFMAYQBtAGUAIABtAGUAYQBuAGkAbgBnACAAYQBzACAAbgBhAHQAaQB2AGUAIABTAEMAQQBOAC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAGQAaQByAGUAYwB0AGkAbwBuAF0AIAAgACAAIAAtACAAVAByAGEAdgBlAHIAcwBhAGwAIABjAG8AZABlAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAwACAAKABzAHQAYQBuAGQAYQByAGQAIAByAG8AdwARIG0AYQBqAG8AcgApAC4AXABuAFwAbgBEAGkAcgBlAGMAdABpAG8AbgAgAEMAbwBkAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAMAAgACAAIAAtACAAUwB0AGEAbgBkAGEAcgBkACAAcgBvAHcAESBtAGEAagBvAHIAIAAoAGwAZQBmAHQAIACSISAAcgBpAGcAaAB0ACwAIAB0AG8AcAAgAJIhIABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgAC0AMQAgACAAIAAtACAAQwBvAGwAdQBtAG4AESBtAGEAagBvAHIAIABmAHIAbwBtACAATgBXACAAYwBvAHIAbgBlAHIAIAAoAHQAbwBwACAAkiEgAGIAbwB0AHQAbwBtACwAIABsAGUAZgB0ACAAkiEgAHIAaQBnAGgAdAApAFwAbgAgACAAIAAgACAAIAAgACAAMQAgACAAIAAtACAATgBFACAAdAByAGEAdgBlAHIAcwBhAGwAIAAoAGMAbwBsAHUAbQBuABEgbQBhAGoAbwByACkAXABuACAAIAAgACAAIAAgACAAIAAyACAAIAAgAC0AIABTAEUAIAB0AHIAYQB2AGUAcgBzAGEAbAAgACgAYwBvAGwAdQBtAG4AESBtAGEAagBvAHIALAAgAGIAbwB0AHQAbwBtACAAkiEgAHQAbwBwACkAXABuACAAIAAgACAAIAAgACAAIAAzACAAIAAgAC0AIABTAFcAIAB0AHIAYQB2AGUAcgBzAGEAbAAgACgAcgBvAHcAESBtAGEAagBvAHIALAAgAHIAaQBnAGgAdAAgAJIhIABsAGUAZgB0ACkAXABuAFwAbgBFAHIAcgBvAHIAIABDAG8AbgBkAGkAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAFwAIgAjAGQAaQByAGUAYwB0AGkAbwBuACEAXAAiACAALQAgAEkAbgB2AGEAbABpAGQAIABkAGkAcgBlAGMAdABpAG8AbgAgAGYAbwByACAAMQBEACAAYQByAHIAYQB5AHMAIABvAHIAIAB1AG4AcgBlAGMAbwBnAG4AaQB6AGUAZAAgAGMAbwBkAGUALgBcAG4AIAAgACAAIAAiICAAMQBEACAAYQByAHIAYQB5AHMAIABvAG4AbAB5ACAAcwB1AHAAcABvAHIAdAAgAGQAaQByAGUAYwB0AGkAbwBuACAAPQAgADAAIAAoAGYAbwByAHcAYQByAGQAKQAgAG8AcgAgAC0AMQAgACgAcgBlAHYAZQByAHMAZQApAC4AXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIABiAHkAcABhAHMAcwAgAHQAcgBhAHYAZQByAHMAYQBsACAAYQBuAGQAIAB1AHMAZQAgAG4AYQB0AGkAdgBlACAAUwBDAEEATgAgAGQAaQByAGUAYwB0AGwAeQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgADIARAAgAHQAcgBhAHYAZQByAHMAYQBsACAAdQBzAGUAcwAgAFQAcgBhAHYAZQByAHMAZQC7AyAAdABvACAAcgBlAG8AcgBkAGUAcgAgAHQAaABlACAAYQByAHIAYQB5ACwAIABTAEMAQQBOACAAdABvACAAYQBjAGMAdQBtAHUAbABhAHQAZQAsAFwAbgAgACAAIAAgACAAIABhAG4AZAAgAFIAZQBTAGgAYQBwAGUAMgBEALsDIAB0AG8AIAByAGUAcwB0AG8AcgBlACAAbwByAGkAZwBpAG4AYQBsACAAZwBlAG8AbQBlAHQAcgB5AC4AXABuACAAIAAgACAAIiAgAE4AbwAgAGYAbABhAHQAdABlAG4AaQBuAGcAIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAA7ACAAZwBlAG8AbQBlAHQAcgB5ACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBjAGEAbgAyAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHYAYQBsAHUAZQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAFsAZABpAHIAZQBjAHQAaQBvAG4AXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgADAAKQBcAG4AIAAgACAAIABkAGkAcgBlAGMAdABpAG8AbgAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZABpAHIAZQBjAHQAaQBvAG4AKQAsACAAMAAsACAAZABpAHIAZQBjAHQAaQBvAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAG4AESAyAEQAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAMQBEAEQAaQByAD8ALAAgACAAIAAgACAAQQBOAEQAKABJAHMAMQBEAD8ALAAgAGQAaQByAGUAYwB0AGkAbwBuACAAPAA+ACAAMAAsACAAZABpAHIAZQBjAHQAaQBvAG4AIAA8AD4AIAAtADEAKQAsAFwAbgAgACAAIAAgAEkAcwBSAGUAdgBlAHIAcwBlAD8ALAAgACAAIAAgACAAIAAgACAAZABpAHIAZQBjAHQAaQBvAG4AIAA9ACAALQAxACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAEkAcwAxAEQAPwAsACAAaAAgAD4AIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAMQBEACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABoACwAIAB3ACkALABcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAGUALAAsACAAZQAsACAALQAxACkALABcAG4AIAAgACAAIAByAGUAdgBfAGEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpAGQAeAApACwAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAsACAAaQBkAHgAKQApACwAXABuACAAIAAgACAAdgBlAGMAdABvAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUgBlAHYAZQByAHMAZQA/ACwAIAByAGUAdgBfAGEAcgByAGEAeQAsACAAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAUwBDAEEATgAoAGkAbgBpAHQAaQBhAGwAXwB2AGEAbAB1AGUALAAgAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkADEARABEAGkAcgA/ACwAIABcACIAIwBkAGkAcgBlAGMAdABpAG8AbgAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABTAEMAQQBOACgAaQBuAGkAdABpAGEAbABfAHYAYQBsAHUAZQAsACAAdgBlAGMAdABvAHIALAAgAGYAdQBuAGMAdABpAG8AbgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBOAEEAKABYAE0AQQBUAEMASAAoAGQAaQByAGUAYwB0AGkAbwBuACwAIAB7AC0AMQA7ADAAOwAxADsAMgA7ADMAOwBcACIATgBFAFwAIgA7AFwAIgBTAEUAXAAiADsAXAAiAFMAVwBcACIAfQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAGQAaQByAGUAYwB0AGkAbwBuACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgADIARAAgAHMAYwBhAG4AIABtAG8AZABlAHMAXABuACAAIAAgACAAcwB0AGEAbgBkAGEAcgBkACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMAQwBBAE4AKABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACwAIABhAHIAcgBhAHkALAAgAGYAdQBuAGMAdABpAG8AbgApACkALAAgAC8ALwAgADAAXABuAFwAbgAgACAAIAAgAHMAdABhAG4AZABhAHIAZABfAGIAeQBjAG8AbAAsACAAIAAgACAATABBAE0AQgBEAEEAKABUAFIAQQBOAFMAUABPAFMARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAQwBBAE4AKABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACwAIABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQApACwAIABmAHUAbgBjAHQAaQBvAG4AKQApACkALAAgAC8ALwAgAC0AMQBcAG4AXABuACAAIAAgACAAdAByAGEAdgBlAHIAcwBhAGwALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBTAGgAYQBwAGUAMgBEALsDKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEMAQQBOACgAaQBuAGkAdABpAGEAbABfAHYAYQBsAHUAZQAsAFQAcgBhAHYAZQByAHMAZQC7AygAYQByAHIAYQB5ACwAIABkAGkAcgBlAGMAdABpAG8AbgApACwAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB3ACkAKQAsACAALwAvACAAMQAsACAAMgAsACAAMwBcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABtAG8AZABlAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZABpAHIAZQBjAHQAaQBvAG4AIAA9ACAAMAAsACAAIABzAHQAYQBuAGQAYQByAGQAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGQAaQByAGUAYwB0AGkAbwBuACAAPQAgAC0AMQAsACAAcwB0AGEAbgBkAGEAcgBkAF8AYgB5AGMAbwBsACgAKQAsACAAdAByAGEAdgBlAHIAcwBhAGwAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABUAHIAYQB2AGUAcgBzAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAbQBhAHAAcwAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYQAgAG4AZQB3ACAAdAByAGEAdgBlAHIAcwBhAGwAIABvAHIAZABlAHIAIABiAHkAIAByAG8AdABhAHQAaQBuAGcAIAB0AGgAZQAgAHQAcgBhAHYAZQByAHMAYQBsACAAYQB4AGkAcwBcAG4AIAAgACAAIAB0AG8AIABvAG4AZQAgAG8AZgAgAHQAaAByAGUAZQAgAGQAaQBhAGcAbwBuAGEAbAAgAGQAaQByAGUAYwB0AGkAbwBuAHMALgAgAFQAaABlACAAcwBlAGwAZQBjAHQAZQBkACAAYQB4AGkAcwAgAGkAcwAgAHIAZQBtAGEAcABwAGUAZAAgAHQAbwAgAGEAXABuACAAIAAgACAAdABvAHAAESBsAGUAZgB0ABMgYQBuAGMAaABvAHIAZQBkACAAdAByAGEAdgBlAHIAcwBhAGwAIABvAHIAZABlAHIALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgADEARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQALgBcAG4AXABuAEEAYwBjAGUAcAB0AGUAZAAgAEQAaQByAGUAYwB0AGkAbwBuAHMAOgBcAG4AIAAgACAAIAAgACAAXAAiAE4ARQBcACIAIABvAHIAIAAxACAAIACSISAATgBvAHIAdABoAGUAYQBzAHQAIAAgACgAlyEpAFwAbgAgACAAIAAgACAAIABcACIAUwBFAFwAIgAgAG8AcgAgADIAIAAgAJIhIABTAG8AdQB0AGgAZQBhAHMAdAAgACAAKACYISkAXABuACAAIAAgACAAIAAgAFwAIgBTAFcAXAAiACAAbwByACAAMwAgACAAkiEgAFMAbwB1AHQAaAB3AGUAcwB0ACAAIAAoAJkhKQBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAG4AZQB3AF8AYQB4AGkAcwAgACAAIAAtACAARABpAHIAZQBjAHQAaQBvAG4AIABjAG8AZABlACAAKABcACIATgBFAFwAIgAsAFwAIgBTAEUAXAAiACwAXAAiAFMAVwBcACIAKQAgAG8AcgAgAGkAbgB0AGUAZwBlAHIAIAAxABMgMwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEcAZQBvAG0AZQB0AHIAeQAgAGkAcwAgAHAAcgBlAHMAZQByAHYAZQBkADsAIABvAG4AbAB5ACAAdAByAGEAdgBlAHIAcwBhAGwAIABvAHIAZABlAHIAIABjAGgAYQBuAGcAZQBzAC4AXABuACAAIAAgACAAIiAgAEkAbgB2AGEAbABpAGQAIABkAGkAcgBlAGMAdABpAG8AbgAgAGMAbwBkAGUAcwAgAHIAZQB0AHUAcgBuACAAXAAiACMAQQBYAEkAUwAhAFwAIgAuAFwAbgAgACAAIAAgACIgIAAxAEQAIABhAHIAcgBhAHkAcwAgAHIAZQB0AHUAcgBuACAAXAAiACMAMgBEAC0AQQBSAFIAQQBZACEAXAAiAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAcgBhAHYAZQByAHMAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABuAGUAdwBfAGEAeABpAHMALABcAG4AXABuAEkARgAoAE8AUgAoAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgAD0AIAAxACwAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAA9ACAAMQApACwAXAAiACMAMgBEAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEEATgBEACgASQBTAE4AVQBNAEIARQBSACgAbgBlAHcAXwBhAHgAaQBzACkALAAgAE8AUgAoAG4AZQB3AF8AYQB4AGkAcwAgADwAPQAgADAALAAgAG4AZQB3AF8AYQB4AGkAcwAgAD4AIAAzACkAKQAsAFwAIgAjAEEAWABJAFMAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQB4AGkAcwAgAHQAcgBhAHYAZQByAHMAYQBsACAAaQBuAGQAaQBjAGUAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAeABfAE4ARQAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAB3ACwALAAxACwAMAApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAaAApACkALABcAG4AIAAgACAAIAB5AF8ATgBFACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAHcALAAsAHcALAAtADEAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsAGgALAAxACwAMAApACkALABcAG4AXABuACAAIAAgACAAeABfAFMARQAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABoACwALABoACwALQAxACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAB3ACwAMQAsADAAKQApACwAXABuACAAIAAgACAAeQBfAFMARQAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABoACwALAB3ACwAMAApACAAKwAgAFMARQBRAFUARQBOAEMARQAoACwAdwAsADAALAAtADEAKQApACwAXABuAFwAbgAgACAAIAAgAHgAXwBTAFcALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAdwAsACwAaAAsADAAKQAgACsAIABTAEUAUQBVAEUATgBDAEUAKAAsAGgALAAwACwALQAxACkAKQAsAFwAbgAgACAAIAAgAHkAXwBTAFcALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAdwAsACwAMQApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAaAAsADEALAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHgAaQBzACAAbQBvAGQAZQAgAHMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAG0AbwBkAGUALAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAG4AZQB3AF8AYQB4AGkAcwApACwAbgBlAHcAXwBhAHgAaQBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFcASQBUAEMASAAoAG4AZQB3AF8AYQB4AGkAcwAsACAAXAAiAE4ARQBcACIALAAxACwAIABcACIAUwBFAFwAIgAsADIALAAgAFwAIgBTAFcAXAAiACwAMwAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKABtAG8AZABlACwAIAB4AF8ATgBFACwAIAB4AF8AUwBFACwAIAB4AF8AUwBXACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAG0AbwBkAGUALAAgAHkAXwBOAEUALAAgAHkAXwBTAEUALAAgAHkAXwBTAFcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAbQBhAHAAIABhAHIAcgBhAHkAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIAB4ACgAKQAsACAAeQAoACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABUAGEAawBlAEIAbABvAGMAawC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAE0ARwByAGkAZAC7AywAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAHIAZQBjAHQAYQBuAGcAdQBsAGEAcgAgAGIAbABvAGMAawAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgB5ACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAGEAbgAgAGEAbgBjAGgAbwByACAAdgBhAGwAdQBlAFwAbgAgACAAIAAgACgAcwB0AGEAcgB0AF8AYQB0ACkAIABhAG4AZAAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAHMAdABvAHAAcABpAG4AZwAgAHYAYQBsAHUAZQAgACgAcwB0AG8AcABfAHcAaABlAG4AKQAuACAAVABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIABsAG8AYwBhAHQAZQBzAFwAbgAgACAAIAAgAHQAaABlACAAZgBpAHIAcwB0ACAAbwBjAGMAdQByAHIAZQBuAGMAZQAgAG8AZgAgAHMAdABhAHIAdABfAGEAdAAsACAAdABoAGUAbgAgAHIAZQB0AHUAcgBuAHMAIABhAGwAbAAgAHIAbwB3AHMAIABmAHIAbwBtACAAdABoAGEAdAAgAHAAbwBpAG4AdABcAG4AIAAgACAAIABkAG8AdwBuAHcAYQByAGQAIABhAG4AZAAgAGEAbABsACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAHQAaABlACAAcgBpAGcAaAB0ACwAIABzAHQAbwBwAHAAaQBuAGcAIABlAGkAdABoAGUAcgAgAGEAdAAgAHQAaABlACAAZgBpAHIAcwB0AFwAbgAgACAAIAAgAG8AYwBjAHUAcgByAGUAbgBjAGUAIABvAGYAIABzAHQAbwBwAF8AdwBoAGUAbgAgAG8AcgAgAGEAdAAgAHQAaABlACAAZQBuAGQAIABvAGYAIAB0AGgAZQAgAGQAYQB0AGEALgBcAG4AXABuACAAIAAgACAAQgBvAHQAaAAgAHMAdABhAHIAdABfAGEAdAAgAGEAbgBkACAAcwB0AG8AcABfAHcAaABlAG4AIAByAGUAbAB5ACAAbwBuACAARQB4AGMAZQBsACcAcwAgAG4AYQB0AGkAdgBlACAAZQBxAHUAYQBsAGkAdAB5ACAAYwBvAG0AcABhAHIAaQBzAG8AbgBcAG4AIAAgACAAIAAoAGEAcgByAGEAeQAgAD0AIAB0AGUAcgBtACkALgAgAFQAaABpAHMAIABwAHIAbwB2AGkAZABlAHMAIABmAGEAcwB0ACwAIAB2AGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAYwBoAGkAbgBnACAAYgB1AHQAIABkAG8AZQBzACAAbgBvAHQAIABzAHUAcABwAG8AcgB0AFwAbgAgACAAIAAgAHcAaQBsAGQAYwBhAHIAZABzACAAbwByACAAcgBlAGcAdQBsAGEAcgAgAGUAeABwAHIAZQBzAHMAaQBvAG4AcwAuACAASQBmACAAcwB0AG8AcABfAHcAaABlAG4AIABpAHMAIABvAG0AaQB0AHQAZQBkACwAIAB0AGgAZQAgAGIAbABvAGMAawAgAGUAeAB0AGUAbgBkAHMAXABuACAAIAAgACAAdABvACAAdABoAGUAIABiAG8AdAB0AG8AbQAgAG8AZgAgAHQAaABlACAAYQByAHIAYQB5AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAcwB0AGEAcgB0AF8AYQB0ACAAIAAgACAAIAAtACAAQQBuAGMAaABvAHIAIAB2AGEAbAB1AGUAIABtAGEAcgBrAGkAbgBnACAAdABoAGUAIABmAGkAcgBzAHQAIAByAG8AdwAgAG8AZgAgAHQAaABlACAAYgBsAG8AYwBrAC4AXABuACAAIAAgACAAWwBzAHQAbwBwAF8AdwBoAGUAbgBdACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcwB0AG8AcABwAGkAbgBnACAAdgBhAGwAdQBlAC4AIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAB0AGgAZQAgAGIAbABvAGMAawAgAGMAbwBuAHQAaQBuAHUAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAbwAgAHQAaABlACAAZQBuAGQAIABvAGYAIAB0AGgAZQAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEcAZQBvAG0AZQB0AHIAeQAgAGkAcwAgAHAAcgBlAHMAZQByAHYAZQBkADsAIABuAG8AIABmAGwAYQB0AHQAZQBuAGkAbgBnACAAbwBjAGMAdQByAHMALgBcAG4AIAAgACAAIAAiICAASQBmACAAcwB0AGEAcgB0AF8AYQB0ACAAaQBzACAAbgBvAHQAIABmAG8AdQBuAGQALAAgAHIAZQB0AHUAcgBuAHMAIABcACIAIwBOAE8ALQBBAE4AQwBIAE8AUgAhAFwAIgAuAFwAbgAgACAAIAAgACIgIABJAGYAIABzAHQAbwBwAF8AdwBoAGUAbgAgAG8AYwBjAHUAcgBzACAAYgBlAGYAbwByAGUAIABzAHQAYQByAHQAXwBhAHQALAAgAHIAZQB0AHUAcgBuAHMAIABcACIAIwBOAE8ALQBTAEwASQBDAEUAIQBcACIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVABhAGsAZQBCAGwAbwBjAGsAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAcwB0AGEAcgB0AF8AYQB0ACwAXABuACAAIAAgACAAWwBzAHQAbwBwAF8AdwBoAGUAbgBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcwB0AG8AcABwAGkAbgBnACAAcABvAGkAbgB0AFwAbgAgACAAIAAgAEQAbwBOAG8AdABTAHQAbwBwAD8ALAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABzAHQAbwBwAF8AdwBoAGUAbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AYwBhAGwAIABoAGUAbABwAGUAcgBzAFwAbgAgACAAIAAgAEEAbgBjAGgAbwByALsDLAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABhAHIAcgAsACAAYwBvAG4AZABpAHQAaQBvAG4ALAAgAGkAZAB4ACwAIABOACgAYQByAHIAIAA9ACAAYwBvAG4AZABpAHQAaQBvAG4AKQAgACoAIABpAGQAeAApACwAXABuACAAIAAgACAASQBEAFgAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAGEAcgByACwAIABNAEkATgAoAEkARgAoAGEAcgByACAAPAA+ACAAMAAsACAAYQByAHIAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBuAGMAaABvAHIAIABwAG8AcwBpAHQAaQBvAG4AcwBcAG4AIAAgACAAIAByAG8AdwBfAHMAdABhAHIAdAAsACAAIAAgACAAIAAgAEEAbgBjAGgAbwByALsDKABhAHIAcgBhAHkALAAgAHMAdABhAHIAdABfAGEAdAAsACAAaQApACwAXABuACAAIAAgACAAYwBvAGwAXwBzAHQAYQByAHQALAAgACAAIAAgACAAIABBAG4AYwBoAG8AcgC7AygAYQByAHIAYQB5ACwAIABzAHQAYQByAHQAXwBhAHQALAAgAGoAKQAsAFwAbgBcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARABYALsDKAByAG8AdwBfAHMAdABhAHIAdAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEQAWAC7AygAYwBvAGwAXwBzAHQAYQByAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAbwBwAHAAaQBuAGcAIABwAG8AcwBpAHQAaQBvAG4AcwBcAG4AIAAgACAAIAByAG8AdwBfAHMAdABvAHAALAAgACAAIAAgACAAIAAgAEkARgAoAEQAbwBOAG8AdABTAHQAbwBwAD8ALAAgADAALAAgAEEAbgBjAGgAbwByALsDKABhAHIAcgBhAHkALAAgAHMAdABvAHAAXwB3AGgAZQBuACwAIABpACkAKQAsAFwAbgAgACAAIAAgAG4AbwBfAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAE0AKAByAG8AdwBfAHMAdABvAHAAKQAgAD0AIAAwACwAXABuACAAIAAgACAAcgBfACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABEAG8ATgBvAHQAUwB0AG8AcAA/ACwAIABuAG8AXwByACkALAAgAGgALAAgAEkARABYALsDKAByAG8AdwBfAHMAdABvAHAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABjAG8AbgBkAGkAdABpAG8AbgBzAFwAbgAgACAAIAAgAFcAaABlAHIAZQBOAG8AdABGAG8AdQBuAGQAPwAsACAAQQBOAEQAKAByACAAPQAgADAALAAgAGMAIAA9ACAAMAApACwAXABuACAAIAAgACAATgBvAFMAbABpAGMAZQA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgAbgBvAF8AcgApACwAIAByAF8AIAA8AD0AIAByACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABXAGgAZQByAGUATgBvAHQARgBvAHUAbgBkAD8ALAAgAFwAIgAjAE4ATwAtAEEATgBDAEgATwBSACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATgBvAFMAbABpAGMAZQA/ACwAIABcACIAIwBOAE8ALQBTAEwASQBDAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwB1AHQAcAB1AHQAIABnAGUAbwBtAGUAdAByAHkAXABuACAAIAAgACAAcgBvAHcAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AXwByACwAIABoACAALQAgAHIAIAArACAAMQAsACAAcgBfACAALQAgAHIAKQAsAFwAbgAgACAAIAAgAGMAbwBsAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAdwAgAC0AIABjACAAKwAgADEALABcAG4AXABuACAAIAAgACAALwAvACAAUgBvAHcAIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcgBvAHcAcwAgAD0AIAAxACwAcgAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAYwBvAGwAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAByAG8AdwBzACwALAAgAHIAKQAsACwAIABjAG8AbABzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbABzACAAPQAgADEALABTAEUAUQBVAEUATgBDAEUAKAByAG8AdwBzACwALAAgAGMALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAcwBpAHoAZQC7AygAUwBFAFEAVQBFAE4AQwBFACgALAAgAGMAbwBsAHMALAAgAGMAKQAsACAAcgBvAHcAcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAGIAbABvAGMAawBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAeAAsACAAeQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMAA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABTAHQAYQBjAGsAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABBAHAAcAByAG8AeABpAG0AYQB0AGUAcwAgAE4AdQBtAFAAeQAnAHMAIABkAHMAdABhAGMAawAgAGYAbwByACAARQB4AGMAZQBsACcAcwAgADIARAAgAGEAcgByAGEAeQAgAG0AbwBkAGUAbAAuACAARABTAHQAYQBjAGsAuwMgAHMAdABhAGMAawBzAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAZQAgADIARAAgAGEAcgByAGEAeQBzACAAYQBsAG8AbgBnACAAYQAgAFwAIgBkAGUAcAB0AGgAXAAiACAAZABpAG0AZQBuAHMAaQBvAG4AIABiAHkAIAB0AHIAYQBuAHMAcABvAHMAaQBuAGcAIABlAGEAYwBoACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAGEAbgBkACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkAIABjAG8AbgBjAGEAdABlAG4AYQB0AGkAbgBnACAAdABoAGUAIABsAGEAeQBlAHIAcwAuACAAVQBwACAAdABvACAAZgBvAHUAcgAgAGEAcgByAGEAeQBzACAAbQBhAHkAIABiAGUAXABuACAAIAAgACAAcwB1AHAAcABsAGkAZQBkAC4AIABNAGkAcwBzAGkAbgBnACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGkAZwBuAG8AcgBlAGQALgBcAG4AXABuACAAIAAgACAAQQBsAGwAIABhAHIAcgBhAHkAcwAgAG0AdQBzAHQAIABiAGUAIABuAG8AbgARIHMAYwBhAGwAYQByACAAYQBuAGQAIABuAG8AbgARIGUAbQBwAHQAeQAuACAARwBlAG8AbQBlAHQAcgB5ACAAbQB1AHMAdAAgAG0AYQB0AGMAaAAgAGEAYwByAG8AcwBzAFwAbgAgACAAIAAgAGEAbABsACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5AHMAIAAoAHMAYQBtAGUAIABoAGUAaQBnAGgAdAAgANcAIAB3AGkAZAB0AGgAKQAuACAATQBpAHMAbQBhAHQAYwBoAGUAZAAgAGUAbABlAG0AZQBuAHQAcwAgAGEAcgBlACAAcABhAGQAZABlAGQAXABuACAAIAAgACAAdQBzAGkAbgBnACAAcABhAGQAXwB3AGkAdABoAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgAGIAYQBzAGUAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADIAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcwBlAGMAbwBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAdABoAGkAcgBkACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0AIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAbwB1AHIAdABoACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAALQAgAEYAaQBsAGwAIAB2AGEAbAB1AGUAIABmAG8AcgAgAG0AaQBzAG0AYQB0AGMAaABlAGQAIABvAHIAIABtAGkAcwBzAGkAbgBnACAAZQBsAGUAbQBlAG4AdABzAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABOAEEAKAApAC4AXABuAFwAbgBCAGUAaABhAHYAaQBvAHIAOgBcAG4AIAAgACAAIAAiICAAVAB3AG8AIABhAHIAcgBhAHkAcwAgACAAkiEgAGQAZQBwAHQAaAAgAD0AIAAyAFwAbgAgACAAIAAgACIgIABUAGgAcgBlAGUAIABhAHIAcgBhAHkAcwAgAJIhIABkAGUAcAB0AGgAIAA9ACAAMwBcAG4AIAAgACAAIAAiICAARgBvAHUAcgAgAGEAcgByAGEAeQBzACAAIACSISAAZABlAHAAdABoACAAPQAgADQAXABuACAAIAAgACAAIiAgAEUAYQBjAGgAIABhAHIAcgBhAHkAIABpAHMAIAB0AHIAYQBuAHMAcABvAHMAZQBkACAAcwBvACAAZABlAHAAdABoACAAYgBlAGMAbwBtAGUAcwAgAHcAaQBkAHQAaAAsACAAdABoAGUAbgAgAEgAUwBUAEEAQwBLAGUAZAAuAFwAbgBcAG4ARQByAHIAbwByACAAQwBvAG4AZABpAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABcACIAIwBFAE0AUABUAFkALQBBAFIAUgBBAFkAIQBcACIAIAAgACAALQAgAE8AbgBlACAAcgBlAHEAdQBpAHIAZQBkACAAYQByAHIAYQB5ACAAaQBzACAAZQBtAHAAdAB5ACAAdwBoAGkAbABlACAAdABoAGUAIABvAHQAaABlAHIAIABpAHMAIABuAG8AdAAuAFwAbgAgACAAIAAgACIgIABcACIAIwBTAEMAQQBMAEEAUgAtAEUAUgBSAE8AUgAhAFwAIgAgACAALQAgAEEAbgB5ACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBzACAAcwBjAGEAbABhAHIALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABUAGgAaQBzACAAaQBzACAAYQAgADIARAAgAGEAcABwAHIAbwB4AGkAbQBhAHQAaQBvAG4AIABvAGYAIABkAGUAcAB0AGgAIABzAHQAYQBjAGsAaQBuAGcALgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABhAHIAcgBhAHkAcwAgAG0AdQBzAHQAIABzAGgAYQByAGUAIABnAGUAbwBtAGUAdAByAHkAIABvAHIAIABwAGEAZABkAGkAbgBnACAAdwBpAGwAbAAgAGIAZQAgAGEAcABwAGwAaQBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABTAHQAYQBjAGsAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMgBdACwAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAzAF0ALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAGUAcQB1AGkAcgBlAGQAIABhAHIAcgBhAHkAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADIAKQAsACAAMAAsACAAQwBPAFUATgBUAEEAKABhAHIAcgBhAHkAXwAyACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABhAHIAcgBhAHkAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMwApACwAIAAwACwAIABDAE8AVQBOAFQAQQAoAGEAcgByAGEAeQBfADMAKQApACwAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADQAKQAsACAAMAAsACAAQwBPAFUATgBUAEEAKABhAHIAcgBhAHkAXwA0ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAaQBuAGcAIABtAG8AZABlAHMAXABuACAAIAAgACAAcgBlAHEALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGMAIAA9ACAAMAAsACAAZAAgAD0AIAAwACkALABcAG4AIAAgACAAIABDAF8AbwBuAGwAeQAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAYwAgADwAPgAgADAALAAgAGQAIAA9ACAAMAApACwAXABuACAAIAAgACAARABfAG8AbgBsAHkALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGMAIAA9ACAAMAAsACAAZAAgADwAPgAgADAAKQAsAFwAbgAgACAAIAAgAEEAbABsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABjACAAPAA+ACAAMAAsACAAZAAgADwAPgAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGEAbAB0AGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAARQBtAHAAdAB5AEEAcgByAD8ALAAgACAAIAAgACAAIABPAFIAKABhACAAPQAgADAALAAgAGIAIAA9ACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABDAGwAYQBtAHAAuwMsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcABhAHIAYQBtACwAIABBAE4ARAAoAHAAYQByAGEAbQAgAD0AIAAxACwAIABJAFMARQBSAFIATwBSACgAcABhAHIAYQBtACkAKQApACwAXABuACAAIAAgACAAUwBjAGEAbABhAHIARQByAHIAPwAsACAAIAAgACAAIABPAFIAKABDAGwAYQBtAHAAuwMoAGEAKQAsACAAQwBsAGEAbQBwALsDKABiACkALAAgAEMAbABhAG0AcAC7AygAYwApACwAIABDAGwAYQBtAHAAuwMoAGQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgARQBtAHAAdAB5AEEAcgByAD8ALAAgAFwAIgAjAEUATQBQAFQAWQAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAFMAYwBhAGwAYQByAEUAcgByAD8ALAAgAFwAIgAjAFMAQwBBAEwAQQBSAC0ARQBSAFIATwBSACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAcABhAGQAXwB3AGkAdABoACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHAAYQBkAF8AdwBpAHQAaAApACwAIABOAEEAKAApACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAHIAYQBuAHMAcABvAHMAZQBkACAAbABhAHkAZQByAHMAXABuACAAIAAgACAAYQBAHSwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGIAQB0sACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAEEATgBTAFAATwBTAEUAKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIABjAEAdLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGMALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYQByAHIAYQB5AF8AMwApACwAIAAwACkALABcAG4AIAAgACAAIABkAEAdLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGQALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYQByAHIAYQB5AF8ANAApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAYwBrACAAdgBhAHIAaQBhAG4AdABzAFwAbgAgACAAIAAgAHIAZQBxAF8AcwB0AGEAYwBrACwAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhAEAdLAAgAGIAQB0pACwAXABuACAAIAAgACAAQwBfAG8AbgBsAHkAXwBzAHQAYQBjAGsALAAgACAAIABIAFMAVABBAEMASwAoAGEAQB0sACAAYgBAHSwAIABjAEAdKQAsAFwAbgAgACAAIAAgAEQAXwBvAG4AbAB5AF8AcwB0AGEAYwBrACwAIAAgACAASABTAFQAQQBDAEsAKABhAEAdLAAgAGIAQB0sACAAZABAHSkALABcAG4AIAAgACAAIABhAGwAbABfAHMAdABhAGMAawAsACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQBAHSwAIABiAEAdLAAgAGMAQB0sACAAZABAHSkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABmAGkAbgBhAGwAIABzAHQAYQBjAGsAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHIAZQBxACwAcgBlAHEAXwBzAHQAYQBjAGsALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABDAF8AbwBuAGwAeQAsAEMAXwBvAG4AbAB5AF8AcwB0AGEAYwBrACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABEAF8AbwBuAGwAeQAsAEQAXwBvAG4AbAB5AF8AcwB0AGEAYwBrACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEAbABsACwAYQBsAGwAXwBzAHQAYQBjAGsALAAgAEYAQQBMAFMARQApACkAKQApACwAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABXAHIAYQBwAFIAbwB3AHMAMgBEALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAARQBjAGgAbwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVwByAGEAcABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIAByAG8AdwAgAGIAbABvAGMAawBzACAAbwBmACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAaABlAGkAZwBoAHQAIAB3AGgAaQBsAGUAIABwAHIAZQBzAGUAcgB2AGkAbgBnAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuACAAdwBpAGQAdABoAC4AIABUAGgAZQAgAHcAcgBhAHAAcABlAGQAIABiAGwAbwBjAGsAcwAgAGEAcgBlACAAcwB0AGEAYwBrAGUAZAAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5ACAAaQBuACAAdABoAGUAIABvAHUAdABwAHUAdAAuAFwAbgAgACAAIAAgAEoAYQBnAGcAZQBkACAAbwByACAAaQBuAGMAbwBtAHAAbABlAHQAZQAgAGYAaQBuAGEAbAAgAGIAbABvAGMAawBzACAAYQByAGUAIABwAGEAZABkAGUAZAAgAHcAaQB0AGgAIABOAEEAKAApACAAdQBuAGwAZQBzAHMAIABhACAAZgBpAGwAbABcAG4AIAAgACAAIAB2AGEAbAB1AGUAIABpAHMAIABzAHUAcABwAGwAaQBlAGQAIAB2AGkAYQAgAHAAYQBkAF8AdwBpAHQAaAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAgACgAMQBEACAAYQByAHIAYQB5AHMAIABuAG8AdAAgAHMAdQBwAHAAbwByAHQAZQBkACkALgBcAG4AIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAIAAgAC0AIABOAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIABpAG4AIABlAGEAYwBoACAAdwByAGEAcABwAGUAZAAgAGIAbABvAGMAawAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAtACAARgBpAGwAbAAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIAB0AG8AIABwAGEAZAAgAGkAbgBjAG8AbQBwAGwAZQB0AGUAIABiAGwAbwBjAGsAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAATgBBACgAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAdwBpAGQAdABoACAAPQAgAGIAbABvAGMAawBzACAA1wAgAG8AcgBpAGcAaQBuAGEAbAAgAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgACIgIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAbQB1AHMAdAAgAGIAZQAgAHMAdAByAGkAYwB0AGwAeQAgAGwAZQBzAHMAIAB0AGgAYQBuACAAdABoAGUAIABhAHIAcgBhAHkAIABoAGUAaQBnAGgAdAAuAFwAbgAgACAAIAAgACIgIABTAHAAaQBsAGwAIAByAGkAcwBrACAAaQBzACAAYwBoAGUAYwBrAGUAZAAgAGEAZwBhAGkAbgBzAHQAIABFAHgAYwBlAGwAGSBzACAAMQA2ACwAMwA4ADQAESBjAG8AbAB1AG0AbgAgAGwAaQBtAGkAdAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBXAHIAYQBwAFIAbwB3AHMAMgBEALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG4AZQB3AF8AaABlAGkAZwBoAHQALABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwBoAGEAcABlAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABiAGwAbwBjAGsAcwAsACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABoACAALwAgAG4AZQB3AF8AaABlAGkAZwBoAHQALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgAHAAYQBkAF8AdwBpAHQAaAAsACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGEAZABfAHcAaQB0AGgAKQAsACAATgBBACgAKQAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAbwB1AHQAcAB1AHQAIAB3AGkAZAB0AGgAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsAcwAgACoAIAB3ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABEAGkAbQA/ACwAIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAPgA9ACAAaAAsAFwAbgAgACAAIAAgAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgACAAIAAgACAAYwAgAD4AIAAxADYAMwA4ADQALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQARABpAG0APwAsACAAXAAiACMASABFAEkARwBIAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAXAAiACMATgBVAE0AIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASQBuAGQAaQBjAGUAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFQATwBSAE8AVwAoAEUAYwBoAG8AuwMoAFMARQBRAFUARQBOAEMARQAoACwAIABiAGwAbwBjAGsAcwAsACAAMQAsACAAbgBlAHcAXwBoAGUAaQBnAGgAdAApACwAIAB3ACkAKQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAArACAAUwBFAFEAVQBFAE4AQwBFACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACwAIAAwACwAIAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABtAG8AZAB1AGwAbwAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgATQBPAEQAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwAgACoAIABiAGwAbwBjAGsAcwApACwAIAB3ACkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABtAG8AZAB1AGwAbwAoACkAIAA9ACAAMAAsACAAdwAsACAAbQBvAGQAdQBsAG8AKAApACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABXAHIAYQBwAHAAZQBkACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAaQAoACkALAAgAGoAKAApACkALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADAAOABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFcAcgBhAHAAQwBvAGwAcwAyAEQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABFAGMAaABvALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABXAHIAYQBwAHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGMAbwBsAHUAbQBuACAAYgBsAG8AYwBrAHMAIABvAGYAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAIAB3AGkAZAB0AGgAIAB3AGgAaQBsAGUAIABwAHIAZQBzAGUAcgB2AGkAbgBnAFwAbgAgACAAIAAgAHIAbwB3ACAAaABlAGkAZwBoAHQALgAgAFQAaABlACAAdwByAGEAcABwAGUAZAAgAGIAbABvAGMAawBzACAAYQByAGUAIABzAHQAYQBjAGsAZQBkACAAdgBlAHIAdABpAGMAYQBsAGwAeQAgAGkAbgAgAHQAaABlACAAbwB1AHQAcAB1AHQALgBcAG4AIAAgACAAIABKAGEAZwBnAGUAZAAgAG8AcgAgAGkAbgBjAG8AbQBwAGwAZQB0AGUAIABmAGkAbgBhAGwAIABiAGwAbwBjAGsAcwAgAGEAcgBlACAAcABhAGQAZABlAGQAIAB3AGkAdABoACAATgBBACgAKQAgAHUAbgBsAGUAcwBzACAAYQAgAGYAaQBsAGwAXABuACAAIAAgACAAdgBhAGwAdQBlACAAaQBzACAAcwB1AHAAcABsAGkAZQBkACAAdgBpAGEAIABwAGEAZABfAHcAaQB0AGgALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAKAAxAEQAIABhAHIAcgBhAHkAcwAgAG4AbwB0ACAAcwB1AHAAcABvAHIAdABlAGQAKQAuAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAIAAgAC0AIABOAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABpAG4AIABlAGEAYwBoACAAdwByAGEAcABwAGUAZAAgAGIAbABvAGMAawAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAALQAgAEYAaQBsAGwAIAB2AGEAbAB1AGUAIAB1AHMAZQBkACAAdABvACAAcABhAGQAIABpAG4AYwBvAG0AcABsAGUAdABlACAAYgBsAG8AYwBrAHMALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAE4AQQAoACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGgAZQBpAGcAaAB0ACAAPQAgAGIAbABvAGMAawBzACAA1wAgAG8AcgBpAGcAaQBuAGEAbAAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAIiAgAG4AZQB3AF8AdwBpAGQAdABoACAAbQB1AHMAdAAgAGIAZQAgAHMAdAByAGkAYwB0AGwAeQAgAGwAZQBzAHMAIAB0AGgAYQBuACAAdABoAGUAIABhAHIAcgBhAHkAIAB3AGkAZAB0AGgALgBcAG4AIAAgACAAIAAiICAAUwBwAGkAbABsACAAcgBpAHMAawAgAGkAcwAgAGMAaABlAGMAawBlAGQAIABhAGcAYQBpAG4AcwB0ACAARQB4AGMAZQBsABkgcwAgADEALAAwADQAOAAsADUANwA2ABEgcgBvAHcAIABsAGkAbQBpAHQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVwByAGEAcABDAG8AbABzADIARAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABuAGUAdwBfAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGIAbABvAGMAawBzACwAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAHcAIAAvACAAbgBlAHcAXwB3AGkAZAB0AGgALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgAHAAYQBkAF8AdwBpAHQAaAAsACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGEAZABfAHcAaQB0AGgAKQAsACAATgBBACgAKQAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAbwB1AHQAcAB1AHQAIABoAGUAaQBnAGgAdABcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABvAGMAawBzACAAKgAgAGgALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEQAaQBtAD8ALAAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAPgA9ACAAdwAsAFwAbgAgACAAIAAgAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgACAAIAAgACAAcgAgAD4AIAAxADAANAA4ADUANwA2ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEQAaQBtAD8ALAAgAFwAIgAjAFcASQBEAFQASAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABTAHAAaQBsAGwAUgBpAHMAawA/ACwAIABcACIAIwBOAFUATQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIABtAG8AZAB1AGwAbwAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgATQBPAEQAKABTAEUAUQBVAEUATgBDAEUAKAByACkALAAgAGgAKQApACwAXABuAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABtAG8AZAB1AGwAbwAoACkAIAA9ACAAMAAsACAAaAAsACAAbQBvAGQAdQBsAG8AKAApACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG4AZQB3AF8AdwBpAGQAdABoACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARQBjAGgAbwC7AygAUwBFAFEAVQBFAE4AQwBFACgAcgAgAC8AIABoACwALAAgADEALAAgAG4AZQB3AF8AdwBpAGQAdABoACkALAAgAGgAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKwAgAFMARQBRAFUARQBOAEMARQAoACwAIABuAGUAdwBfAHcAaQBkAHQAaAAsACAAMAAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAVwByAGEAcABwAGUAZAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAGkAKAApACwAIABqACgAKQApACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADkAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAHQAYQBpAHIAYwBhAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFYAYQBsAGkAZABhAHQAZQBTAHQAYQBpAHIAYwBhAHMAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG4AcwB0AHIAdQBjAHQAcwAgAGQAaQBhAGcAbwBuAGEAbAAgAHMAdABhAGkAcgBjAGEAcwBlACAAcABhAHQAdABlAHIAbgBzACAAZgByAG8AbQAgAGEAIAB2AGUAYwB0AG8AcgAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuACAAVABoAGUAIABpAG4AcAB1AHQAXABuACAAIAAgACAAYQByAHIAYQB5ACAAaQBzACAAZgBsAGEAdAB0AGUAbgBlAGQAIAByAG8AdwARIHcAaQBzAGUALAAgAHAAYQByAHQAaQB0AGkAbwBuAGUAZAAgAGkAbgB0AG8AIABiAGwAbwBjAGsAcwAgAG8AZgAgAHMAaQB6AGUAIABiAGwAbwBjAGsAXwBzAGkAegBlACwAIABhAG4AZABcAG4AIAAgACAAIABhAHIAcgBhAG4AZwBlAGQAIABpAG4AdABvACAAZABpAGEAZwBvAG4AYQBsACAAXAAiAHMAdABlAHAAcwBcACIALgAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIABjAG8AbgB0AHIAbwBsACAAYgBsAG8AYwBrACAAcwBwAGEAYwBpAG4AZwAsAFwAbgAgACAAIAAgAGgAbwByAGkAegBvAG4AdABhAGwALwB2AGUAcgB0AGkAYwBhAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALAAgAGEAbgBkACAAYQBuAHQAaQARIGQAaQBhAGcAbwBuAGEAbAAgAGwAYQB5AG8AdQB0AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABmAGwAYQB0AHQAZQBuAGUAZAAgAHIAbwB3ABEgdwBpAHMAZQApAC4AXABuACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAgACAAIAAgACAAIAAtACAAUgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABpAG4AIABlAGEAYwBoACAAcwB0AGEAaQByAGMAYQBzAGUAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIABbAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0AF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABzAHAAYQBjAGkAbgBnACAAYgBlAHQAdwBlAGUAbgAgAHMAdABhAGkAcgBjAGEAcwBlACAAYgBsAG8AYwBrAHMALgBcAG4AIAAgACAAIABbAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAB0AG8AZwBnAGwAZQAgAGYAbwByACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuAC4AXABuACAAIAAgACAAWwBJAHMAQQBuAHQAaQBEAGkAYQBnAD8AXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAdABvAGcAZwBsAGUAIABmAG8AcgAgAGEAbgB0AGkAESBkAGkAYQBnAG8AbgBhAGwAIABsAGEAeQBvAHUAdAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAbgBwAHUAdAAgAGkAcwAgAGYAbABhAHQAdABlAG4AZQBkACAAdQBzAGkAbgBnACAAVABPAEMATwBMAC4AXABuACAAIAAgACAAIiAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgAgACAAIAAgACIgIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAB2AGUAcgB0AGkAYwBhAGwAIAB1AG4AbABlAHMAcwAgAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AIABpAHMAIABwAHIAbwB2AGkAZABlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwB0AGEAaQByAGMAYQBzAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAsAFwAbgAgACAAIAAgAFsAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAXQAsAFwAbgAgACAAIAAgAFsASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACwAXABuACAAIAAgACAAWwBJAHMAQQBuAHQAaQBEAGkAYQBnAD8AXQAsAFwAbgBcAG4AVgBhAGwAaQBkAGEAdABlAFMAdABhAGkAcgBjAGEAcwBlALsDKABhAHIAcgBhAHkALAAgAGIAbABvAGMAawBfAHMAaQB6AGUALAAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAXABuACAAIAAgACAATgBvAE8AZgBmAHMAZQB0AD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAKQAsAFwAbgAgACAAIAAgAFoAZQByAG8ATwBmAGYAcwBlAHQAPwAsACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAAgAD0AIAAwACwAXABuACAAIAAgACAAYwBvAGwAXwBvAGYAZgBzAGUAdAAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBPAGYAZgBzAGUAdAA/ACwAIAAwACwAIABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQAsAFwAbgAgACAAIAAgAE4AbwBBAG4AdABpAEQAaQBhAGcAPwAsACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAEkAcwBBAG4AdABpAEQAaQBhAGcAPwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAXABuACAAIAAgACAAZgBsAGEAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAZgBsAGEAdAApACwAXABuACAAIAAgACAAcwBlAHEALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAawApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAHIAdABpAHQAaQBvAG4AIABpAG4AdABvACAAYgBsAG8AYwBrAHMAXABuACAAIAAgACAAVgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBSAE8AVwAoAEUAWABQAEEATgBEACgAVwBSAEEAUABSAE8AVwBTACgAcwBlAHEAKAApACwAIABiAGwAbwBjAGsAXwBzAGkAegBlACkALAAsAGIAbABvAGMAawBfAHMAaQB6AGUAIAArACAAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQALAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAFYAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgBzACAAYQBuAGQAIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGIAbABvAGMAawBfAHMAaQB6AGUAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIABjAG8AbABfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AQQBuAHQAaQBEAGkAYQBnAD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIAB3AGkAZAB0AGgALAAgAC0AMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAE8ARAAoAGMAbwBsAF8AYQByAHIAKAApACwAIABiAGwAbwBjAGsAXwBzAGkAegBlACAAKwAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACkAKQAsAFwAbgBcAG4AIAAgACAAIABqAF8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABPAFIAKABOAG8ATwBmAGYAcwBlAHQAPwAsACAAWgBlAHIAbwBPAGYAZgBzAGUAdAA/ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGoAKAApACAAPQAgADAALAAgAGIAbABvAGMAawBfAHMAaQB6AGUALAAgAGoAKAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABpACgAKQAgAD0AIABqAF8AKAApACwAIABWACwAIABOAEEAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAcwB0AGEAaQByAGMAYQBzAGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABJAEYATgBBACgASQBOAEQARQBYACgAZgBsAGEAdAAsACAAaQBkAHgAKAApACkALAAgAFwAIgBcACIAKQAsACwAIAAtAGMAbwBsAF8AbwBmAGYAcwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABUAFIAQQBOAFMAUABPAFMARQAoAHIAZQBzAHUAbAB0ACkALAAgAHIAZQBzAHUAbAB0ACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAtAEMATwBSAEUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBTAHQAYQBpAHIAYwBhAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAgACgAVgBhAGwAaQBkAGEAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVgBhAGwAaQBkAGEAdABpAG8AbgAgAGgAZQBsAHAAZQByACAAZgBvAHIAIABTAHQAYQBpAHIAYwBhAHMAZQC7Ay4AIABFAG4AcwB1AHIAZQBzACAAYQByAHIAYQB5ACAAaQBzACAAdgBhAGwAaQBkACwAIABiAGwAbwBjAGsAXwBzAGkAegBlACAAaQBzAFwAbgAgACAAIAAgAHAAbwBzAGkAdABpAHYAZQAgAGEAbgBkACAAZABvAGUAcwAgAG4AbwB0ACAAZQB4AGMAZQBlAGQAIABhAHIAcgBhAHkAIABsAGUAbgBnAHQAaAAsACAAYQBuAGQAIABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAAgAGkAcwAgAG4AbwBuABEgbgBlAGcAYQB0AGkAdgBlAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAYgBsAG8AYwBrACAAcwBpAHoAZQAuAFwAbgAgACAAIAAgAFsAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHMAcABhAGMAaQBuAGcAIABiAGUAdAB3AGUAZQBuACAAYgBsAG8AYwBrAHMALgBcAG4AIAAgACAAIABbAG8AbgBfAHYAYQBsAGkAZABdACAAIAAgACAAIAAgAC0AIABFAHgAcAByAGUAcwBzAGkAbwBuACAAdABvACAAZQB2AGEAbAB1AGEAdABlACAAdwBoAGUAbgAgAHYAYQBsAGkAZABhAHQAaQBvAG4AIABwAGEAcwBzAGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBWAGEAbABpAGQAYQB0AGUAUwB0AGEAaQByAGMAYQBzAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAsAFwAbgAgACAAIAAgAFsAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAXQAsAFwAbgAgACAAIAAgAFsAbwBuAF8AdgBhAGwAaQBkAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAcwBcAG4AIAAgACAAIABOAG8AdABBAHIAcgBhAHkAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFkAUABFACgAYQByAHIAYQB5ACkAIAA8AD4AIAA2ADQALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABCAGwAbwBjAGsAUwBpAHoAZQA/ACwAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKABiAGwAbwBjAGsAXwBzAGkAegBlACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsAXwBzAGkAegBlACAAPAA9ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABvAGMAawBfAHMAaQB6AGUAIAA+ACAAQwBPAFUATgBUAEEAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAQgBsAG8AYwBrAE8AZgBmAHMAZQB0AD8ALAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAKQAsAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACAAPAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAE4AbwB0AEEAcgByAGEAeQA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8AVAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAQgBsAG8AYwBrAFMAaQB6AGUAPwAsACAAIABcACIAIwBCAEwATwBDAEsALQBTAEkAWgBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEIAbABvAGMAawBPAGYAZgBzAGUAdAA/ACwAIABcACIAIwBCAEwATwBDAEsALQBPAEYARgBTAEUAVAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAG4AXwB2AGEAbABpAGQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADAAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABVAG4AUABpAHYAbwB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AywAIABSAGUAcwBpAHoAZQC7AywAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAYQAgAGEAcgByAGEAeQBfADIARAAgAGkAbgB0AG8AIABhACAAZgBsAGEAdAB0AGUAbgBlAGQAIAByAG8AdwARIHcAaQBzAGUAIAB0AGEAYgBsAGUAIABiAHkAIABwAHIAbwB2AGkAZABpAG4AZwAgAHIAbwB3ACAAbABhAGIAZQBsAHMALABcAG4AIAAgACAAIABjAG8AbAB1AG0AbgAgAGwAYQBiAGUAbABzACwAIABhAG4AZAAgAGEAIAB2AGEAbAB1AGUAIABhAHIAcgBhAHkAXwAyAEQALgAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAHQAZQByAGkAbgBnACAAcgBlAG0AbwB2AGUAcwAgAGIAbABhAG4AawBzACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgAGEAbgBkACAAegBlAHIAbwBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAcgBvAHcAcwAgACAAIAAgACAAIAAgACAALQAgAFYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAHIAbwB3ACAAbABhAGIAZQBsAHMALgBcAG4AIAAgACAAIABjAG8AbAB1AG0AbgBzACAAIAAgACAAIAAtACAASABvAHIAaQB6AG8AbgB0AGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAGMAbwBsAHUAbQBuACAAbABhAGIAZQBsAHMALgBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAgACAAIAAgACAAIAAtACAAYQByAHIAYQB5AF8AMgBEACAAbwBmACAAdgBhAGwAdQBlAHMAIAB0AG8AIAB1AG4AcABpAHYAbwB0AC4AXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAA6ACAAaQBmACAAVABSAFUARQAsACAAcgBlAG0AbwB2AGUAIABiAGwAYQBuAGsAcwAsACAAZQByAHIAbwByAHMALAAgAGEAbgBkACAAegBlAHIAbwBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAcgBvAHcAcwAgAG0AdQBzAHQAIABtAGEAdABjAGgAIAB0AGgAZQAgAGgAZQBpAGcAaAB0ACAAbwBmACAAdgBhAGwAdQBlAHMALgBcAG4AIAAgACAAIAAiICAAYwBvAGwAdQBtAG4AcwAgAG0AdQBzAHQAIABtAGEAdABjAGgAIAB0AGgAZQAgAHcAaQBkAHQAaAAgAG8AZgAgAHYAYQBsAHUAZQBzAC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAaQBzACAAYQAgADMAESBjAG8AbAB1AG0AbgAgAHQAYQBiAGwAZQA6ACAAewByAG8AdwBfAGwAYQBiAGUAbAAsACAAYwBvAGwAdQBtAG4AXwBsAGEAYgBlAGwALAAgAHYAYQBsAHUAZQB9AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFUAbgBQAGkAdgBvAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcgBvAHcAcwAsAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAHMALABcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAsAFwAbgAgACAAIAAgAFsAaQBnAG4AbwByAGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcgBvAHcAcwApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYwBvAGwAdQBtAG4AcwApACwAXABuAFwAbgAgACAAIAAgAGgAXwB2ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAYQBsAHUAZQBzACkALABcAG4AIAAgACAAIAB3AF8AdgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAB2AGEAbAB1AGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQAsACAAaABfAHYAIAA9ACAAMQAsACAAdwBfAHYAIAA9ACAAMQApACwAXABuACAAIAAgACAATgBvAFAAaQB2AG8AdAA/ACwAIAAgACAAIAAgACAAIAB3AF8AdgAgAD0AIAAxACwAXABuAFwAbgAgACAAIAAgAFIAbwB3AE0AaQBzAG0AYQB0AGMAaAA/ACwAIAAgACAAaAAgADwAPgAgAGgAXwB2ACwAXABuACAAIAAgACAAQwBvAGwATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAB3ACAAPAA+ACAAdwBfAHYALABcAG4AXABuACAAIAAgACAAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAIAAgACAAIABoAF8AdgAgACoAIAB3AF8AdgAgAD4AIAAxADAANAA4ADUANwA2ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAcABhAHMAcwB0AGgAcgBvAHUAZwBoAFwAbgAgACAAIAAgAE8AcgBpAGcARABhAHQAYQAsACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKAByAG8AdwBzACwAIABjAG8AbAB1AG0AbgBzACwAIAB2AGEAbAB1AGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADEAESBjAG8AbAB1AG0AbgAgAHAAYQBzAHMAdABoAHIAbwB1AGcAaABcAG4AIAAgACAAIABPAHIAaQBnAEQAYQB0AGEAUABhAGQALAAgACAAIAAgAEgAUwBUAEEAQwBLACgASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMoAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFYAUwBUAEEAQwBLACgAYwBvAGwAdQBtAG4AcwAsACAAdgBhAGwAdQBlAHMAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAE8AcgBpAGcARABhAHQAYQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBQAGkAdgBvAHQAPwAsACAATwByAGkAZwBEAGEAdABhAFAAYQBkACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABSAG8AdwBNAGkAcwBtAGEAdABjAGgAPwAsACAAXAAiACMARABJAE0ALQBSAE8AVwBTAC8AVgBBAEwAVQBFAFMAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQwBvAGwATQBpAHMAbQBhAHQAYwBoAD8ALAAgAFwAIgAjAEQASQBNAC0AQwBPAEwALwBWAEEATABVAEUAUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgAFwAIgAjAFIATwBXAC0ATABJAE0ASQBUACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEIAcgBvAGEAZABjAGEAcwB0ACAAcgBvAHcAIABsAGEAYgBlAGwAcwAgACgAcgBlAHAAZQBhAHQAIABlAGEAYwBoACAAcgBvAHcAIABsAGEAYgBlAGwAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwBvAGwAdQBtAG4AcwApAFwAbgAgACAAIAAgAHIAbwB3AF8AbABhAGIAZQBsAHMALAAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AygAcgBvAHcAcwAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAcgBvAGEAZABjAGEAcwB0ACAAYwBvAGwAdQBtAG4AIABsAGEAYgBlAGwAcwAgACgAcgBlAHAAZQBhAHQAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIABsAGEAYgBlAGwAIABkAG8AdwBuACAAYQBsAGwAIAByAG8AdwBzACkAXABuACAAIAAgACAAYQB0AHQAcgBpAGIAdQB0AGUALAAgACAAIAAgACAAIABSAGUAcwBpAHoAZQC7AygAVABSAEEATgBTAFAATwBTAEUAKABjAG8AbAB1AG0AbgBzACkALABoACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgAGYAbABhAHQAXwB2AGEAbAB1AGUAcwAsACAAIAAgACAAVABPAEMATwBMACgAdgBhAGwAdQBlAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAIABpAG4AdABvACAAMwARIGMAbwBsAHUAbQBuACAAdABhAGIAbABlAFwAbgAgACAAIAAgAHMAdABhAGMAawAsACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKAByAG8AdwBfAGwAYQBiAGUAbABzACwAIABhAHQAdAByAGkAYgB1AHQAZQAsACAAZgBsAGEAdABfAHYAYQBsAHUAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBpAGwAdABlAHIAaQBuAGcAXABuACAAIAAgACAAawBlAGUAcABfAG0AYQBzAGsALAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBCAEwAQQBOAEsAKABmAGwAYQB0AF8AdgBhAGwAdQBlAHMAKQAgACsAIAAoAEkARgBFAFIAUgBPAFIAKABmAGwAYQB0AF8AdgBhAGwAdQBlAHMALAAgADAAKQAgAD0AIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbAB0AGUAcgBlAGQALAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAcwB0AGEAYwBrACwAIABrAGUAZQBwAF8AbQBhAHMAawApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABpAGcAbgBvAHIAZQApACwAIABzAHQAYQBjAGsALAAgAGYAaQBsAHQAZQByAGUAZAApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAWgBpAHAAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABaAGkAcABzACAAdABvAGcAZQB0AGgAZQByACAAMQATIDQAIABhAHIAcgBhAHkAcwAgAGIAeQAgAGYAbABhAHQAdABlAG4AaQBuAGcAIABlAGEAYwBoACAAaQBuAHAAdQB0ACAAdwBpAHQAaAAgAFQATwBDAE8ATAAgAGEAbgBkACAAYQBsAGkAZwBuAGkAbgBnAFwAbgAgACAAIAAgAHQAaABlAG0AIABiAHkAIABsAGUAbgBnAHQAaAAuACAAQgB5ACAAZABlAGYAYQB1AGwAdAAsACAAWgBpAHAAuwMgAHAAZQByAGYAbwByAG0AcwAgAGEAIABzAHQAcgBpAGMAdAAgAHoAaQBwACwAIABwAGEAaQByAGkAbgBnACAAZQBsAGUAbQBlAG4AdABzAFwAbgAgACAAIAAgAG8AbgBsAHkAIAB1AHAAIAB0AG8AIAB0AGgAZQAgAGwAZQBuAGcAdABoACAAbwBmACAAdABoAGUAIABzAGgAbwByAHQAZQBzAHQAIABhAHIAcgBhAHkALgAgAEkAZgAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAAgAD0AIABUAFIAVQBFACwAIABaAGkAcAC7A1wAbgAgACAAIAAgAGMAbwBuAHQAaQBuAHUAZQBzACAAdQBuAHQAaQBsACAAdABoAGUAIABsAG8AbgBnAGUAcwB0ACAAYQByAHIAYQB5ACAAaQBzACAAYwBvAG4AcwB1AG0AZQBkACwAIABwAGEAZABkAGkAbgBnACAAcwBoAG8AcgB0AGUAcgAgAGEAcgByAGEAeQBzACAAdwBpAHQAaABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACAAKABkAGUAZgBhAHUAbAB0ADoAIAAjAE4ALwBBACkALgBcAG4AXABuACAAIAAgACAAVABoAGUAIAByAGUAcwB1AGwAdAAgAGkAcwAgAGEAIABoAG8AcgBpAHoAbwBuAHQAYQBsAGwAeQAgAHMAdABhAGMAawBlAGQAIAB0AGEAYgBsAGUAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAXABuACAAIAAgACAAegBpAHAAcABlAGQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALAAgAG4AbwByAG0AYQBsAGkAegBlAGQAIAB0AG8AIABhACAAYwBvAG0AbQBvAG4AIABsAGUAbgBnAHQAaAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEAIAAgACAAIAAgACAAIAAtACAARgBpAHIAcwB0ACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMgBdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcwBlAGMAbwBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHQAaABpAHIAZAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8ANABdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAZgBvAHUAcgB0AGgAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAHoAaQBwAF8AbABvAG4AZwBlAHMAdABdACAALQAgAFQAUgBVAEUAIAB0AG8AIAB6AGkAcAAgAHUAbgB0AGkAbAAgAHQAaABlACAAbABvAG4AZwBlAHMAdAAgAGEAcgByAGEAeQAgAGkAcwAgAGMAbwBuAHMAdQBtAGUAZAAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAWgBpAHAAuwMgAHUAcwBlAHMAIABzAHQAcgBpAGMAdAAgAG0AbwBkAGUAIAAoAHMAaABvAHIAdABlAHMAdAAgAGEAcgByAGEAeQApAC4AXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0AIAAgAC0AIABWAGEAbAB1AGUAIAB1AHMAZQBkACAAdABvACAAcABhAGQAIABzAGgAbwByAHQAZQByACAAYQByAHIAYQB5AHMAIAB3AGgAZQBuACAAegBpAHAAXwBsAG8AbgBnAGUAcwB0ACAAPQAgAFQAUgBVAEUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AWgBpAHAAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADIAXQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMwBdACwAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0ALABcAG4AIAAgACAAIABbAHoAaQBwAF8AbABvAG4AZwBlAHMAdABdACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwBlAHQAIAB6AGkAcAAgAG0AbwBkAGUAXABuACAAIAAgACAAWgBpAHAATABvAG4AZwA/ACwAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHoAaQBwAF8AbABvAG4AZwBlAHMAdAApACwAIABGAEEATABTAEUALAAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQB0ACAAZgB1AG4AYwB0AGkAbwBuACAAZgBvAHIAIABkAGUAdABlAHIAbQBpAG4AaQBuAGcAIABsAGUAbgBnAHQAaAAgAG8AZgAgAHoAaQBwAFwAbgAgACAAIAAgAGYAbgC7AywAIAAgACAAIAAgACAAIAAgACAASQBGACgAWgBpAHAATABvAG4AZwA/ACwATQBBAFgALABNAEkATgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQB0ACAAZgBpAGwAbABfAHYAYQBsAHUAZQBcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgAEkARgAoAFoAaQBwAEwAbwBuAGcAPwAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAE4AQQAoACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAATgBBACgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAeQBzACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgAFQAdwBvACwAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADIAKQApACwAXABuACAAIAAgACAAVABoAHIAZQBlACwAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMwApACkALABcAG4AIAAgACAAIABGAG8AdQByACwAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwA0ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABhAHIAcgBhAHkAcwAgAHMAdQBwAHAAbABpAGUAZABcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEYAbwB1AHIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAVABoAHIAZQBlACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAVAB3AG8ALAAgADIALAAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACwAIAAgACAAIAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIALAAgACAAIAAgACAASQBGACgAbQAgAD4APQAgADIALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAXwAyACkALABGAEEATABTAEUAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADMALAAgACAAIAAgACAASQBGACgAbQAgAD4APQAgADMALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAXwAzACkALABGAEEATABTAEUAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADQALAAgACAAIAAgACAASQBGACgAbQAgAD0AIAAgADQALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAXwA0ACkALABGAEEATABTAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAGUAbgBnAHQAaAAgAG8AZgAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAGsAgSAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsACAAIAAgAGsAgiAsACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIABrAIMgLAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAzACkALAAgACAAIABrAIQgLAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAZQBuAGcAdABoACAAbwBmACAAegBpAHAAXABuACAAIAAgACAATABaACwAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAG0ALABrAIEgLABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAbgC7AygAawCBICwAawCCICkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAbgC7AygAawCBICwAawCCICwAawCDICkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAbgC7AygAawCBICwAawCCICwAawCDICwAawCEICkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHIAcgBhAHkAcwAgAC0AIABuAG8AcgBtAGEAbABpAHoAZQBkACAAZgBvAHIAIAB6AGkAcAAgAG0AbwBkAGUAXABuACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMsACAAIABMAEEATQBCAEQAQQAoAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABaAGkAcABMAG8AbgBnAD8ALABFAFgAUABBAE4ARAAoAGEAcgByAGEAeQAsAEwAWgAsACwAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQByAHIAYQB5ACwATABaACkAKQApACwAXABuAFwAbgAgACAAIAAgAGEALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADMAKQAsAFwAbgAgACAAIAAgAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADQAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAbgBnAGUAbQBlAG4AdABcAG4AIAAgACAAIAB6AGkAcABwAGUAZAAsACAAIAAgACAAIAAgAEMASABPAE8AUwBFACgAbQAsAGEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACwAYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsAGIALABjACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACwAYgAsAGMALABkACkAKQAsAFwAbgAgACAAIAAgAHoAaQBwAHAAZQBkAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBsAGkAYwBlAEIAeQBEAGUAZwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEQARwByAGkAZAC7AywAIABEAGUAbABlAHQAZQBXAGgAZQByAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAbgAgAGEAbgBnAHUAbABhAHIAIABzAGwAaQBjAGUAIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAgAHUAcwBpAG4AZwAgAGQAZQBnAHIAZQBlACAAYgBvAHUAbgBkAHMAIABpAG4AIABhACAAMACwACAALQAgADMANgAwALAAXABuACAAIAAgACAAYwBpAHIAYwB1AGwAYQByACAAcwB5AHMAdABlAG0ALgAgAFQAaABlACAAcwBsAGkAYwBlACAAcAByAGUAcwBlAHIAdgBlAHMAIAB0AGgAZQAgAG8AcgBpAGcAaQBuAGEAbAAgAGcAZQBvAG0AZQB0AHIAeQAuACAASQBmACAAbQBhAHgAXwBkAGUAZwByAGUAZQAgAGkAcwBcAG4AIAAgACAAIABvAG0AaQB0AHQAZQBkACwAIABpAHQAIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAzADYAMACwAC4AXABuAFwAbgAgACAAIAAgAFcAcgBhAHAAESBhAHIAbwB1AG4AZAAgAGkAcwAgAHMAdQBwAHAAbwByAHQAZQBkADoAXABuACAAIAAgACAAIAAgACAAIAAiICAASQBmACAAbQBpAG4AXwBkAGUAZwByAGUAZQAgADwAPQAgAG0AYQB4AF8AZABlAGcAcgBlAGUAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAbABpAGMAZQAgAD0AIABbAG0AaQBuAF8AZABlAGcAcgBlAGUALAAgAG0AYQB4AF8AZABlAGcAcgBlAGUAXQBcAG4AIAAgACAAIAAgACAAIAAgACIgIABJAGYAIABtAGkAbgBfAGQAZQBnAHIAZQBlACAAPgAgAG0AYQB4AF8AZABlAGcAcgBlAGUAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAbABpAGMAZQAgAGMAcgBvAHMAcwBlAHMAIAAzADYAMACwACAAkiEgADAAsAAgAGEAbgBkACAAaQBuAGMAbAB1AGQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAbgBnAGwAZQBzACAAPgA9ACAAbQBpAG4AXwBkAGUAZwByAGUAZQAgACAATwBSACAAIABhAG4AZwBsAGUAcwAgADwAPQAgAG0AYQB4AF8AZABlAGcAcgBlAGUAXABuAFwAbgAgACAAIAAgAFYAYQBsAHUAZQBzACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAcwBsAGkAYwBlACAAYQByAGUAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAZgBpAGwAbABfAHYAYQBsAHUAZQAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABcACIAXAAiACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAHMAbABpAGMAZQAuAFwAbgAgACAAIAAgAG0AaQBuAF8AZABlAGcAcgBlAGUAIAAgACAAIAAtACAAUwB0AGEAcgB0AGkAbgBnACAAZABlAGcAcgBlAGUAIAAoADAALQAzADYAMAApAC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAG0AYQB4AF8AZABlAGcAcgBlAGUAXQAgACAALQAgAEUAbgBkAGkAbgBnACAAZABlAGcAcgBlAGUAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAMwA2ADAAKQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACAAIAAtACAARgBpAGwAbAAgAHYAYQBsAHUAZQAgAGYAbwByACAAbwB1AHQAESBvAGYAESBzAGwAaQBjAGUAIABjAGUAbABsAHMAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAEQARwByAGkAZAC7AyAAdABvACAAYwBvAG0AcAB1AHQAZQAgAHAAZQByABEgYwBlAGwAbAAgAGEAbgBnAGwAZQBzAC4AXABuACAAIAAgACAAIiAgAEQAZQBsAGUAdABlAFcAaABlAHIAZQC7AyAAcgBlAG0AbwB2AGUAcwAgAE4AQQAoACkAIAB3AGgAaQBsAGUAIABwAHIAZQBzAGUAcgB2AGkAbgBnACAAcwBoAGEAcABlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAbABpAGMAZQBCAHkARABlAGcAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAG0AaQBuAF8AZABlAGcAcgBlAGUALABcAG4AIAAgACAAIABbAG0AYQB4AF8AZABlAGcAcgBlAGUAXQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIABtAGEAeABfAGQAZQBnAHIAZQBlACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBkAGUAZwByAGUAZQApACwAIAAzADYAMAAsACAAbQBhAHgAXwBkAGUAZwByAGUAZQApACwAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAXAAiAFwAIgAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABEAGUAZwA/ACwAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAG0AaQBuAF8AZABlAGcAcgBlAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABtAGEAeABfAGQAZQBnAHIAZQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AaQBuAF8AZABlAGcAcgBlAGUAIAA8ACAAMAAsACAAbQBpAG4AXwBkAGUAZwByAGUAZQAgAD4AIAAzADYAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBkAGUAZwByAGUAZQAgADwAIAAwACwAIABtAGEAeABfAGQAZQBnAHIAZQBlACAAPgAgADMANgAwACkALABcAG4AXABuACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABEAGUAZwA/ACwAIABcACIAIwBEAEUARwBSAEUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABBAG4AZwBsAGUAIABmAGkAZQBsAGQAIAAoADAAEyAzADYAMAApAFwAbgAgACAAIAAgAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABHAHIAaQBkALsDKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAVwByAGEAcAARIGEAdwBhAHIAZQAgAG0AYQBzAGsAXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGkAbgBfAGQAZQBnAHIAZQBlACAAPAA9ACAAbQBhAHgAXwBkAGUAZwByAGUAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAGQAIAA+AD0AIABtAGkAbgBfAGQAZQBnAHIAZQBlACkAIAAqACAAKABkACAAPAA9ACAAbQBhAHgAXwBkAGUAZwByAGUAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAZAAgAD4APQAgAG0AaQBuAF8AZABlAGcAcgBlAGUAKQAgACsAIAAoAGQAIAA8AD0AIABtAGEAeABfAGQAZQBnAHIAZQBlACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABtAGEAcwBrAFwAbgAgACAAIAAgAG0AYQBzAGsAZQBkACwAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAHMAawAsACAAZwByAGkAZAAsACAATgBBACgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBtAG8AdgBlACAATgBBACAAYgB1AHQAIABwAHIAZQBzAGUAcgB2AGUAIABzAGgAYQBwAGUAXABuACAAIAAgACAAYwBsAGUAYQBuAGUAZAAsACAAIAAgACAAIAAgACAAIABEAGUAbABlAHQAZQBXAGgAZQByAGUAuwMoAG0AYQBzAGsAZQBkACwAIABMAEEATQBCAEQAQQAoAHYALAAgAEEATgBEACgASQBTAE4AQQAoAHYAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcABsAGEAYwBlACAAcgBlAG0AbwB2AGUAZAAgAHYAYQBsAHUAZQBzACAAdwBpAHQAaAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABJAEYATgBBACgAYwBsAGUAYQBuAGUAZAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADEANABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFAAYQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMsACAASQBuAHMAdQBsAGEAdABlAEMAbwBsAHMAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAcABwAGwAaQBlAHMAIAByAG8AdwAgAGEAbgBkAC8AbwByACAAYwBvAGwAdQBtAG4AIABwAGEAZABkAGkAbgBnACAAdABvACAAYQBuAHkAIABhAHIAcgBhAHkALgAgAFAAYQBkALsDIABnAGUAbgBlAHIAYQBsAGkAegBlAHMAIAB0AGgAZQAgAGIAZQBoAGEAdgBpAG8AcgBcAG4AIAAgACAAIABvAGYAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AyAAYQBuAGQAIABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7AyAAYgB5ACAAYQBsAGwAbwB3AGkAbgBnACAAYQBsAGwAIABmAG8AdQByACAAcwBpAGQAZQBzACAAbwBmACAAYQBuACAAYQByAHIAYQB5ACAAdABvAFwAbgAgACAAIAAgAGIAZQAgAHAAYQBkAGQAZQBkACAAaQBuACAAYQAgAHMAaQBuAGcAbABlACAAbwBwAGUAcgBhAHQAaQBvAG4ALgAgAFAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwAgAG0AYQB5ACAAYgBlACAAcwB1AHAAcABsAGkAZQBkACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0AGwAeQBcAG4AIAAgACAAIABvAHIAIABvAG0AaQB0AHQAZQBkACAAZgBvAHIAIABjAG8AbgB2AGUAbgBpAGUAbgBjAGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgACAAIAAgAC0AIABSAG8AdwBzACAAdABvACAAcABhAGQAIABhAGIAbwB2AGUAIAB0AGgAZQAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwByAG8AdwBzAF8AYQBmAHQAZQByAF0AIAAgACAALQAgAFIAbwB3AHMAIAB0AG8AIABwAGEAZAAgAGIAZQBsAG8AdwAgACgAZABlAGYAYQB1AGwAdABzACAAdABvACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkALgBcAG4AIAAgACAAIABbAGMAbwBsAHMAXwBiAGUAZgBvAHIAZQBdACAAIAAtACAAQwBvAGwAdQBtAG4AcwAgAHQAbwAgAHAAYQBkACAAbABlAGYAdAAgACgAZABlAGYAYQB1AGwAdABzACAAdABvACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkALgBcAG4AIAAgACAAIABbAGMAbwBsAHMAXwBhAGYAdABlAHIAXQAgACAAIAAtACAAQwBvAGwAdQBtAG4AcwAgAHQAbwAgAHAAYQBkACAAcgBpAGcAaAB0ACAAKABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAKQAuAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0AIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAHAAYQBkAGQAaQBuAGcAIAB2AGEAbAB1AGUAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBuAHkAIABvAG0AaQB0AHQAZQBkACAAcABhAGQAZABpAG4AZwAgAGMAbwB1AG4AdAAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQBcAG4AIAAgACAAIAAgACAAKABUAGgAaQBzACAAYQBsAGwAbwB3AHMAIABmAG8AcgAgAGUAYQBzAHkAIABwAGEAZABkAGkAbgBnADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAD0AUABhAGQAuwMoAGEAcgByAGEAeQAsADMAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBkAGQAcwAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAIABvAGYAIAAzACAAYQBsAGwAIABhAHIAbwB1AG4AZAAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACkAXABuACAAIAAgACAAIiAgAE4AZQBnAGEAdABpAHYAZQAgAG8AcgAgAHQAZQB4AHQAIABwAGEAZABkAGkAbgBnACAAYwBvAHUAbgB0AHMAIAByAGUAdAB1AHIAbgAgAFwAIgAjAFQARQBYAFQALQBQAEEARAAhAFwAIgAuAFwAbgAgACAAIAAgACIgIABEAGUAbABlAGcAYQB0AGUAcwAgAHIAbwB3ACAAcABhAGQAZABpAG4AZwAgAHQAbwAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAcABhAGQAZABpAG4AZwAgAHQAbwAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDLgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABhAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAXABuACAAIAAgACAAWwByAG8AdwBzAF8AYQBmAHQAZQByAF0ALABcAG4AIAAgACAAIABbAGMAbwBsAHMAXwBiAGUAZgBvAHIAZQBdACwAXABuACAAIAAgACAAWwBjAG8AbABzAF8AYQBmAHQAZQByAF0ALABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwBjAGEAbABhAHIAaQB6AGUAIABhAG4AeQAgAGEAcgByAGEAeQAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAEkAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHgALAAgAEkATgBEAEUAWAAoAHgALAAgADEALAAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAG8AbAB2AGUAIABwAGEAZABkAGkAbgBnACAAYwBvAHUAbgB0AHMAIAAoAG8AbQBpAHQAdABlAGQAIACSISAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkAXABuACAAIAAgACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIAAgACAAIAAgACAAIAAgAEkAuwMoAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQApACwAXABuACAAIAAgACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAsACAAIAAgACAAIAAgACAAIAAgAEkAuwMoAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAcwBfAGEAZgB0AGUAcgApACwAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUALAAgAHIAbwB3AHMAXwBhAGYAdABlAHIAKQApACwAXABuACAAIAAgACAAYwBvAGwAcwBfAGIAZQBmAG8AcgBlACwAIAAgACAAIAAgACAAIAAgAEkAuwMoAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAcwBfAGIAZQBmAG8AcgBlACkALAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAsACAAYwBvAGwAcwBfAGIAZQBmAG8AcgBlACkAKQAsAFwAbgAgACAAIAAgAGMAbwBsAHMAXwBhAGYAdABlAHIALAAgACAAIAAgACAAIAAgACAAIABJALsDKABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAHMAXwBhAGYAdABlAHIAKQAsACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIABjAG8AbABzAF8AYQBmAHQAZQByACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGUAIABwAGEAZABkAGkAbgBnACAAYwBvAHUAbgB0AHMAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABJAG4AcwA/ACwAIAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKAByAG8AdwBzAF8AYQBmAHQAZQByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABjAG8AbABzAF8AYgBlAGYAbwByAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAGMAbwBsAHMAXwBhAGYAdABlAHIAKQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQASQBuAHMAPwAsACAAXAAiACMAVABFAFgAVAAtAFAAQQBEACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAHIAbwB3ACAAcABhAGQAZABpAG4AZwBcAG4AIAAgACAAIABwAGEAZABkAGUAZABfAHIAbwB3AHMALAAgACAAIAAgACAAIAAgACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMoAGEAcgByAGEAeQAsACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIAByAG8AdwBzAF8AYQBmAHQAZQByACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABjAG8AbAB1AG0AbgAgAHAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAcABhAGQAZABlAGQAXwBhAGwAbAAsACAAIAAgACAAIAAgACAAIAAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDKABwAGEAZABkAGUAZABfAHIAbwB3AHMALAAgAGMAbwBsAHMAXwBiAGUAZgBvAHIAZQAsACAAYwBvAGwAcwBfAGEAZgB0AGUAcgAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAAcABhAGQAZABlAGQAXwBhAGwAbABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnACAAKABQAGEAZABkAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABBAGQAZABzACAAcgBvAHcAcwAgAG8AZgAgAHAAYQBkAGQAaQBuAGcAIABiAGUAZgBvAHIAZQAgAGEAbgBkAC8AbwByACAAYQBmAHQAZQByACAAYQBuACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7A1wAbgAgACAAIAAgAGcAZQBuAGUAcgBhAGwAaQB6AGUAcwAgAEUAWABQAEEATgBEACAAYgB5ACAAcwB1AHAAcABvAHIAdABpAG4AZwAgAHMAeQBtAG0AZQB0AHIAaQBjAGEAbAAgAHAAYQBkAGQAaQBuAGcALAAgAHoAZQByAG8AESBwAGEAZABkAGkAbgBnACAAbwBuACAAZQBpAHQAaABlAHIAXABuACAAIAAgACAAcwBpAGQAZQAsACAAYQBuAGQAIABzAGMAYQBsAGEAcgBpAHoAZQBkACAAcABhAGQAZABpAG4AZwAgAHYAYQBsAHUAZQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAIAAgAC0AIABSAG8AdwBzACAAdABvACAAcABhAGQAIABhAGIAbwB2AGUAIAB0AGgAZQAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwByAG8AdwBzAF8AYQBmAHQAZQByAF0AIAAgAC0AIABSAG8AdwBzACAAdABvACAAcABhAGQAIABiAGUAbABvAHcAIAAoAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQApAC4AXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAHAAYQBkAGQAaQBuAGcAIAB2AGEAbAB1AGUAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAYgBvAHQAaAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgAGEAbgBkACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAgAD0AIAAwACwAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgAgACAAIAAgACIgIAByAG8AdwBzAF8AYQBmAHQAZQByACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAdQBuAGwAZQBzAHMAIABlAHgAcABsAGkAYwBpAHQAbAB5ACAAcwBlAHQAIAB0AG8AIAAwAC4AXABuACAAIAAgACAAIiAgAHAAYQBkAF8AdwBpAHQAaAAgAGkAcwAgAHMAYwBhAGwAYQByAGkAegBlAGQAIAB0AG8AIABhACAAMQDXADEAIAB2AGEAbAB1AGUALgBcAG4AIAAgACAAIAAiICAATgBlAGcAYQB0AGkAdgBlACAAbwByACAAdABlAHgAdAAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwAgAHIAZQB0AHUAcgBuACAAXAAiACMAUgBPAFcAUwAtAEIARQBGAE8AUgBFAC8AQQBGAFQARQBSACEAXAAiAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAsAFwAbgAgACAAIAAgAFsAcgBvAHcAcwBfAGEAZgB0AGUAcgBdACwAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIAByAG8AdwBzAF8AYQBmAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBzAF8AYQBmAHQAZQByACkALAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgApACwAXABuACAAIAAgACAAcABhAGQAXwB3AGkAdABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABhAGQAXwB3AGkAdABoACkALAAgAFwAIgBcACIALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAIAAxACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAFAAYQBkAEMAbwB1AG4AdAA/ACwAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAByAG8AdwBzAF8AYgBlAGYAbwByAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAHIAbwB3AHMAXwBhAGYAdABlAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAIAA8ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAPAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AESBwAGEAZABkAGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAFwAbgAgACAAIAAgAE4AbwBQAGEAZABkAGkAbgBnAD8ALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgAD0AIAAwACwAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAPQAgADAAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFAAYQBkAEMAbwB1AG4AdAA/ACwAIABcACIAIwBSAE8AVwBTAC0AQgBFAEYATwBSAEUALwBBAEYAVABFAFIAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AUABhAGQAZABpAG4AZwA/ACwAIABhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUABhAGQAZABpAG4AZwAgAGIAbABvAGMAawBzAFwAbgAgACAAIAAgAHAAYQBkAF8AYgBlAGYAbwByAGUALAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAHAAYQBkAF8AdwBpAHQAaAAsACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIAB3ACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgAgACAAIAAgAHAAYQBkAF8AYQBmAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAHAAYQBkAF8AdwBpAHQAaAAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAsACAAdwAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAAYgBlAGYAbwByAGUAXwBvAG4AbAB5AD8ALAAgACAAIAAgACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAPAA+ACAAMAAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAgAD0AIAAwACkALABcAG4AIAAgACAAIABhAGYAdABlAHIAXwBvAG4AbAB5AD8ALAAgACAAIAAgACAAIAAgACAAQQBOAEQAKAByAG8AdwBzAF8AYgBlAGYAbwByAGUAIAA9ACAAMAAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAgADwAPgAgADAAKQAsAFwAbgAgACAAIAAgAGYAdQBsAGwAeQBfAGkAbgBzAHUAbABhAHQAZQBkAD8ALAAgACAAIABBAE4ARAAoAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgADwAPgAgADAALAAgAHIAbwB3AHMAXwBhAGYAdABlAHIAIAA8AD4AIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAbgBkAGEAcgBkACAARQBYAFAAQQBOAEQAIABmAG8AcgAgAGEAZgB0AGUAcgARIG8AbgBsAHkAIABjAGEAcwBlAFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAKwAgAGgALABcAG4AIAAgACAAIABlAHgAcABhAG4AZABfAG8AbgBsAHkALAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKABhAHIAcgBhAHkALAAgAGsALAAgAHcALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAbgBnAGUAbQBlAG4AdABzAFwAbgAgACAAIAAgAGkAbgBzAHUAbABhAHQAZQBfAGIAZQBmAG8AcgBlACwAIAAgACAAIABWAFMAVABBAEMASwAoAHAAYQBkAF8AYgBlAGYAbwByAGUALAAgAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAaQBuAHMAdQBsAGEAdABlAF8AYQBsAGwALAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAcABhAGQAXwBiAGUAZgBvAHIAZQAsACAAYQByAHIAYQB5ACwAIABwAGEAZABfAGEAZgB0AGUAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAHUAbABsAHkAXwBpAG4AcwB1AGwAYQB0AGUAZAA/ACwAIABpAG4AcwB1AGwAYQB0AGUAXwBhAGwAbAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGIAZQBmAG8AcgBlAF8AbwBuAGwAeQA/ACwAIAAgACAAaQBuAHMAdQBsAGEAdABlAF8AYgBlAGYAbwByAGUALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAcABhAG4AZABfAG8AbgBsAHkAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAgACgAUABhAGQAZABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAZABkAHMAIABjAG8AbAB1AG0AbgBzACAAbwBmACAAcABhAGQAZABpAG4AZwAgAGIAZQBmAG8AcgBlACAAYQBuAGQALwBvAHIAIABhAGYAdABlAHIAIABhAG4AIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDIABpAHMAXABuACAAIAAgACAAdABoAGUAIABjAG8AbAB1AG0AbgARIG8AcgBpAGUAbgB0AGUAZAAgAGMAbwB1AG4AdABlAHIAcABhAHIAdAAgAHQAbwAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDLgAgAFQAaABlACAAYQByAHIAYQB5ACAAaQBzACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAHQAbwBcAG4AIAAgACAAIAB2AGUAcgB0AGkAYwBhAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALAAgAHAAYQBkAGQAZQBkACAAdgBpAGEAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AywAIABhAG4AZAAgAHIAZQBzAHQAbwByAGUAZAAgAHQAbwAgAGkAdABzACAAbwByAGkAZwBpAG4AYQBsAFwAbgAgACAAIAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAHMAXwBiAGUAZgBvAHIAZQAgACAAIAAtACAAQwBvAGwAdQBtAG4AcwAgAHQAbwAgAHAAYQBkACAAdABvACAAdABoAGUAIABsAGUAZgB0AC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAGMAbwBsAHUAbQBuAHMAXwBhAGYAdABlAHIAXQAgACAALQAgAEMAbwBsAHUAbQBuAHMAIAB0AG8AIABwAGEAZAAgAHQAbwAgAHQAaABlACAAcgBpAGcAaAB0ACAAKABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABjAG8AbAB1AG0AbgBzAF8AYgBlAGYAbwByAGUAKQAuAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0AIAAgACAAIAAgACAAIAAtACAAUwBjAGEAbABhAHIAIABwAGEAZABkAGkAbgBnACAAdgBhAGwAdQBlACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgAFwAIgBcACIAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAGIAbwB0AGgAIABjAG8AbAB1AG0AbgBzAF8AYgBlAGYAbwByAGUAIABhAG4AZAAgAGMAbwBsAHUAbQBuAHMAXwBhAGYAdABlAHIAIAA9ACAAMAAsACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQALgBcAG4AIAAgACAAIAAiICAAYwBvAGwAdQBtAG4AcwBfAGEAZgB0AGUAcgAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAGMAbwBsAHUAbQBuAHMAXwBiAGUAZgBvAHIAZQAgAHUAbgBsAGUAcwBzACAAZQB4AHAAbABpAGMAaQB0AGwAeQAgAHMAZQB0ACAAdABvACAAMAAuAFwAbgAgACAAIAAgACIgIABwAGEAZABfAHcAaQB0AGgAIABpAHMAIABzAGMAYQBsAGEAcgBpAHoAZQBkACAAdABvACAAYQAgADEA1wAxACAAdgBhAGwAdQBlAC4AXABuACAAIAAgACAAIiAgAE4AZQBnAGEAdABpAHYAZQAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwAgAGgAYQBsAHQAIABpAG4AcwBpAGQAZQAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDLgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASQBuAHMAdQBsAGEAdABlAEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBvAGwAdQBtAG4AcwBfAGIAZQBmAG8AcgBlACwAXABuACAAIAAgACAAWwBjAG8AbAB1AG0AbgBzAF8AYQBmAHQAZQByAF0ALABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIAB0AG8AIAB2AGUAcgB0AGkAYwBhAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAYQByAHIAYQB5AF8AdgAsACAAIAAgACAAIAAgACAAIABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAHIAbwB3ABEgcABhAGQAZABpAG4AZwAgAGkAbgAgAHYAZQByAHQAaQBjAGEAbAAgAHMAcABhAGMAZQBcAG4AIAAgACAAIABwAGEAZABkAGUAZABfAHYALAAgACAAIAAgACAAIAAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDKABhAHIAcgBhAHkAXwB2ACwAIABjAG8AbAB1AG0AbgBzAF8AYgBlAGYAbwByAGUALAAgAGMAbwBsAHUAbQBuAHMAXwBhAGYAdABlAHIALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAHQAbwByAGUAIABvAHIAaQBnAGkAbgBhAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABUAFIAQQBOAFMAUABPAFMARQAoAHAAYQBkAGQAZQBkAF8AdgApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBhAGcAbgBpAGYAeQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAgACgASQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHAAYQBuAGQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAbwBmACAAYQBuACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGEAIABiAGwAbwBjAGsAIABvAGYAIABzAHAAZQBjAGkAZgBpAGUAZAAgAGgAZQBpAGcAaAB0ACAAYQBuAGQAXABuACAAIAAgACAAdwBpAGQAdABoACAAdQBzAGkAbgBnACAAbgBlAGEAcgBlAHMAdAARIG4AZQBpAGcAaABiAG8AcgAgAGkAbgB0AGUAcgBwAG8AbABhAHQAaQBvAG4ALgAgAFMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByAHMALAAgADEARAAgAGEAcgByAGEAeQBzACwAIABhAG4AZABcAG4AIAAgACAAIAAyAEQAIABhAHIAcgBhAHkAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAIAB0AG8AIABtAGEAZwBuAGkAZgB5AC4AXABuACAAIAAgACAAaABlAGkAZwBoAHQAIAAgACAAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGYAbwByACAAZQBhAGMAaAAgAG0AYQBnAG4AaQBmAGkAZQBkACAAZQBsAGUAbQBlAG4AdAAgACgAcABvAHMAaQB0AGkAdgBlACAAcwBjAGEAbABhAHIAKQAuAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAgACAAIAAgACAAIAAgAC0AIABOAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABtAGEAZwBuAGkAZgBpAGUAZAAgAGUAbABlAG0AZQBuAHQAIAAoAHAAbwBzAGkAdABpAHYAZQAgAHMAYwBhAGwAYQByACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABoAGUAaQBnAGgAdAAgAGEAbgBkACAAdwBpAGQAdABoACAAbQB1AHMAdAAgAGIAZQAgAHMAYwBhAGwAYQByACwAIABuAHUAbQBlAHIAaQBjACwAIABhAG4AZAAgAD4AIAAwAC4AXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAZQB4AHAAYQBuAHMAaQBvAG4AIAB2AGkAYQAgAGkAbgBkAGUAeAAgAHIAZQBwAGwAaQBjAGEAdABpAG8AbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAGEAZwBuAGkAZgB5ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgBJAEYAKABPAFIAKABDAE8AVQBOAFQAKABoAGUAaQBnAGgAdAApACAAPAA+ACAAMQAsACAAQwBPAFUATgBUACgAdwBpAGQAdABoACkAIAA8AD4AIAAxACkALABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuACAAIAAgACAASQBGACgATwBSACgASQBTAFQARQBYAFQAKABoAGUAaQBnAGgAdAApACwAIABJAFMAVABFAFgAVAAoAHcAaQBkAHQAaAApACkALABcACIAIwBUAEUAWABUACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgAaABlAGkAZwBoAHQAIAA8AD0AIAAwACwAIAB3AGkAZAB0AGgAIAA8AD0AIAAwACkALABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwAgAG8AZgAgAG0AYQBnAG4AaQBmAGkAZQBkACAAbwB1AHQAcAB1AHQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgACoAIABoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAAqACAAdwBpAGQAdABoACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AZQBzAGgAIABnAHIAaQBkACAAZgBvAHIAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAcgBlAHAAbABpAGMAYQB0AGkAbwBuAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkATgBUACgAUwBFAFEAVQBFAE4AQwBFACgAaQAsACwALAAgADEAIAAvACAAaABlAGkAZwBoAHQAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAGoALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkATgBUACgAUwBFAFEAVQBFAE4AQwBFACgALAAgAGoALAAsACAAMQAgAC8AIAB3AGkAZAB0AGgAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAaQAsACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABlAHYAYQBsAHUAYQB0AGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAHgAKAApACwAIAB5ACgAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAWgBvAG8AbQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAgACgASwBlAHIAbgBlAGwAIABFAHgAcABhAG4AcwBpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeABwAGEAbgBkAHMAIABlAGEAYwBoACAAZQBsAGUAbQBlAG4AdAAgAG8AZgAgAGEAbgAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABhACAAYgBsAG8AYwBrACAAdwBoAG8AcwBlACAAcwBpAHoAZQAgAG0AYQB0AGMAaABlAHMAIAB0AGgAZQBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAgANcAIAB3AGkAZAB0AGgAIABvAGYAIAB6AG8AbwBtAF8AawBlAHIAbgBlAGwALgAgAEUAYQBjAGgAIABlAHgAcABhAG4AZABlAGQAIABiAGwAbwBjAGsAIABpAHMAIABmAG8AcgBtAGUAZAAgAGIAeQAgAGEAZABkAGkAbgBnACAAdABoAGUAXABuACAAIAAgACAAZQBsAGUAbQBlAG4AdAAgAHYAYQBsAHUAZQAgAHQAbwAgAHQAaABlACAAegBvAG8AbQBfAGsAZQByAG4AZQBsAC4AIABJAG4AdABlAG4AZABlAGQAIABzAHQAcgBpAGMAdABsAHkAIABmAG8AcgAgAG4AdQBtAGUAcgBpAGMAIABhAHIAcgBhAHkAcwAgAGEAbgBkAFwAbgAgACAAIAAgAG4AdQBtAGUAcgBpAGMAIABrAGUAcgBuAGUAbABzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAbgB1AG0AZQByAGkAYwAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIAcwAgAGEAbABsAG8AdwBlAGQAKQAuAFwAbgAgACAAIAAgAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAgACAALQAgAE4AdQBtAGUAcgBpAGMAIABrAGUAcgBuAGUAbAAgAGQAZQBmAGkAbgBpAG4AZwAgAGUAeABwAGEAbgBzAGkAbwBuACAAaABlAGkAZwBoAHQAIABhAG4AZAAgAHcAaQBkAHQAaAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBBAFIAUgBBAFkAIQBcACIAIABpAGYAIABhAG4AeQAgAGEAcgByAGEAeQAgAGUAbABlAG0AZQBuAHQAcwAgAGEAcgBlACAAbgBvAG4AESBuAHUAbQBlAHIAaQBjAC4AXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBLAEUAUgBOAEUATAAhAFwAIgAgAGkAZgAgAGEAbgB5ACAAawBlAHIAbgBlAGwAIABlAGwAZQBtAGUAbgB0AHMAIABhAHIAZQAgAG4AbwBuABEgbgB1AG0AZQByAGkAYwAuAFwAbgAgACAAIAAgACIgIABJAGYAIAB6AG8AbwBtAF8AawBlAHIAbgBlAGwAIABpAHMAIAAxANcAMQAsACAAWgBvAG8AbQC7AyAAcgBlAGQAdQBjAGUAcwAgAHQAbwAgAGEAcgByAGEAeQAgACsAIABzAGMAYQBsAGEAcgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBaAG8AbwBtALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEsAZQByAG4AZQBsACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAB6AG8AbwBtAF8AawBlAHIAbgBlAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAVABlAHgAdABLAGUAcgBuAGUAbAA/ACwAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAB6AG8AbwBtAF8AawBlAHIAbgBlAGwAKQApACwAXABuACAAIAAgACAASQBzAFQAZQB4AHQAQQByAHIAYQB5AD8ALAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYQByAHIAYQB5ACkAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgBLAGUAcgBuAGUAbAA/ACwAIAAgACAAIABBAE4ARAAoAGgAZQBpAGcAaAB0ACAAPQAgADEALAAgAHcAaQBkAHQAaAAgAD0AIAAxACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFQAZQB4AHQASwBlAHIAbgBlAGwAPwAsACAAXAAiACMASwBFAFIATgBFAEwAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVABlAHgAdABBAHIAcgBhAHkAPwAsACAAXAAiACMAQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIASwBlAHIAbgBlAGwAPwAsACAAYQByAHIAYQB5ACAAKwAgAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHUAdABwAHUAdAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAKgAgAGgAZQBpAGcAaAB0ACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACAAKgAgAHcAaQBkAHQAaAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZAAgAGYAbwByACAAbgBlAGEAcgBlAHMAdAARIG4AZQBpAGcAaABiAG8AcgAgAGUAeABwAGEAbgBzAGkAbwBuAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKABpACwALAAsACAAMQAgAC8AIABoAGUAaQBnAGgAdAApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAGoALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAagAsACwAIAAxACAALwAgAHcAaQBkAHQAaAApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAaQAsACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AZABlAGQAIABhAHIAcgBhAHkAIAAoAG4AZQBhAHIAZQBzAHQAESBuAGUAaQBnAGgAYgBvAHIAKQBcAG4AIAAgACAAIAB6AG8AbwBtAGUAZAAsACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAeAAoACkALAAgAHkAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcwBpAHoAZQAgAGsAZQByAG4AZQBsACAAdABvACAAbQBhAHQAYwBoACAAegBvAG8AbQBlAGQAIABiAGwAbwBjAGsAIABzAHQAcgB1AGMAdAB1AHIAZQBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAegBvAG8AbQBlAGQAKAApACkAIAAvACAAaABlAGkAZwBoAHQALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAegBvAG8AbQBlAGQAKAApACkAIAAvACAAdwBpAGQAdABoACwAXABuACAAIAAgACAAawBlAHIAbgBlAGwAXwBtAGEAZwAsACAAUgBlAHMAaQB6AGUAuwMoAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAsACAAaAAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAHoAbwBvAG0AZQBkACAAbwB1AHQAcAB1AHQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHoAbwBvAG0AZQBkACgAKQAgACsAIABrAGUAcgBuAGUAbABfAG0AYQBnACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAEcAQQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAwADQAIAAtACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHAAcgBvAHYAaQBkAGUAIABhACAAdABvAG8AbABrAGkAdAAgAGYAbwByACAAcwB0AHIAdQBjAHQAdQByAGEAbAAgAGUAZABpAHQAaQBuAGcAIABvAGYAXABuACAAIAAgACAAMgBEACAAYQByAHIAYQB5AHMALgAgAFQAaABlAHMAZQAgAG8AcABlAHIAYQB0AG8AcgBzACAAcwB1AHAAcABvAHIAdAAgAGQAZQBsAGUAdABpAG8AbgAsACAAcwBlAGwAZQBjAHQAaQBvAG4ALAAgAGYAaQBsAHQAZQByAGkAbgBnACwAIAByAG8AbABsAGkAbgBnACwAXABuACAAIAAgACAAZQB4AHAAYQBuAHMAaQBvAG4ALAAgAGEAbgBkACAAcwB0AHIAdQBjAHQAdQByAGEAbAAgAG0AYQBwAHAAaQBuAGcALgBcAG4AXABuACAAIAAgACAAUwB1AGIAESBjAGEAdABlAGcAbwByAGkAZQBzADoAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEQAZQBsAGUAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGUAdABlAFIAbwB3AHMAuwMsACAARABlAGwAZQB0AGUAQwBvAGwAcwC7AywAIABEAGUAbABlAHQAZQBXAGgAZQByAGUAuwMsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUABpAG4AYwBoALsDLAAgAFIAZQBtAG8AdgBlALsDLAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAARQB4AHAAYQBuAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABLAHIAbwBuAGUAYwBrAGUAcgBQAHIAbwBkALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEYAaQBsAHQAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQB4AGMAbAB1AGQAZQC7AywAIABTAG4AYQBwALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFIAbwBsAGwAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAGgAaQBmAHQAuwMsACAAUwBoAGkAZgB0AFIAbwB3AHMAuwMsACAAUwBoAGkAZgB0AEMAbwBsAHMAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAG0AYgBlAGQAuwMsACAASwBlAGUAcABSAG8AdwBzALsDLAAgAEsAZQBlAHAAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABTAHQAcgB1AGMAdAB1AHIAYQBsACAATQBhAHAAcABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAbABvAGMAawBNAGEAcAC7AywAIABDAG8AbgB2AG8AbAB2AGUAuwMsACAARgBvAGwAZAC7AywAIABKAG8AaQBuADIARAC7A1wAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEQAZQBsAGUAdABlAFIAbwB3AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABEAGUAbABlAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAdAByAGUAYQBrALsDLAAgAEMAbwB1AG4AdABkAG8AdwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABEAGUAbABlAHQAZQBzACAAcgBvAHcAcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgBhAHMAZQBkACAAbwBuACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuAHMALgAgAEEAIABwAG8AcwBpAHQAaQB2AGUAXABuACAAIAAgACAAZABlAGwAZQB0AGUAIAB2AGEAbAB1AGUAIAB0AHIAaQBtAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAHQAaABlACAAdABvAHAAIABvAGYAIABlAGEAYwBoACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AOwAgAGEAIABuAGUAZwBhAHQAaQB2AGUAIABkAGUAbABlAHQAZQBcAG4AIAAgACAAIAB2AGEAbAB1AGUAIAB0AHIAaQBtAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAHQAaABlACAAYgBvAHQAdABvAG0ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABkAGUAbABlAHQAZQAgACAAIAAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAGkAbgB0AGUAZwBlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAD4AIAAwACAAkiEgAHQAcgBpAG0AIABmAHIAbwBtACAAdABvAHAAIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA8ACAAMAAgAJIhIAB0AHIAaQBtACAAZgByAG8AbQAgAGIAbwB0AHQAbwBtACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAgACAALQAgAFMAdQBiAGcAcgBvAHUAcAAgAGwAYQBiAGUAbABzACAAKABzAGEAbQBlACAAaABlAGkAZwBoAHQAIABhAHMAIABhAHIAcgBhAHkAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAG8AbgBsAHkAIABvAG4AZQAgAHMAdQBiAGcAcgBvAHUAcAAgAGUAeABpAHMAdABzACwAIABEAFIATwBQACgAKQAgAGkAcwAgAHUAcwBlAGQAIABhAHMAIABhACAAZgBhAHMAdAAgAHAAYQB0AGgALgBcAG4AIAAgACAAIAAiICAAZABlAGwAZQB0AGUAIABtAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByADsAIAB0AGUAeAB0ACAAbwByACAAdgBlAGMAdABvAHIAIABpAG4AcAB1AHQAcwAgAGgAYQBsAHQAIAB3AGkAdABoACAAYQBuACAAZQByAHIAbwByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQBsAGUAdABlAFIAbwB3AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAZABlAGwAZQB0AGUALABcAG4AIAAgACAAIABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAHUAYgBnAHIAbwB1AHAAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABVAE4ASQBRAFUARQAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEQAaQBzAGMAYQByAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIABAAGQAZQBsAGUAdABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPAA+ACAAUgBPAFcAUwAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAASQBzAFQAZQB4AHQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAZABlAGwAZQB0AGUAKQAsAFwAbgAgACAAIAAgAE4AbwB0AFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgASQBzAFQAZQB4AHQAPwApACwAIABDAE8AVQBOAFQAQQAoAGQAZQBsAGUAdABlACkAIAA+ACAAMQApACwAXABuACAAIAAgACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABJAHMAVABlAHgAdAA/ACwAIABOAG8AdABTAGMAYQBsAGEAcgA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQByAHIAbwByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAGgAYQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABzAGMAZQBuAGEAcgBpAG8AcwApACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgA7ACAAXAAiACMAVABFAFgAVAAhAFwAIgA7ACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIAfQAsAFwAbgAgACAAIAAgAGEAbABlAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAFIAUgBBAFkAVABPAFQARQBYAFQAKABGAEkATABUAEUAUgAoAGUAcgByAG8AcgBzACwAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAMAApACkALABcAG4AXABuACAAIAAgACAASQBGACgATwBuAGUAUwB1AGIARwByAG8AdQBwAD8ALAAgAEQAaQBzAGMAYQByAGQALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGgAYQBsAHQALAAgAGEAbABlAHIAdAAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgA6ACAAKwB0AG8AcAAsACAAEyBiAG8AdAB0AG8AbQBcAG4AIAAgACAAIABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGQAZQBsAGUAdABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgB1AG4AIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGEAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAcgBlAGEAawC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkALABcAG4AIAAgACAAIABkAGUAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAAZABlAGwAZQB0AGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAQgBTACgAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGkAbgBkAGUAeAAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAIAA9ACAALQAxACwAIABkAGUAcwBjAGUAbgBkACwAIABhAHMAYwBlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQBlAHAAIAByAG8AdwBzACAAdwBoAGUAcgBlACAAaQBuAGQAZQB4ACAAPgAgAGQAZQBsAGUAdABlAFwAbgAgACAAIAAgAGsAZQBlAHAAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAGkAZAB4ACAAPAA9ACAAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGsAZQBlAHAAPwApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABlAGwAZQB0AGUAQwBvAGwAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEQAZQBsAGUAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUwB0AHIAZQBhAGsAuwMsACAAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEQAZQBsAGUAdABlAHMAIABjAG8AbAB1AG0AbgBzACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAGEAcwBlAGQAIABvAG4AIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AcwAuACAAQQAgAHAAbwBzAGkAdABpAHYAZQBcAG4AIAAgACAAIABkAGUAbABlAHQAZQAgAHYAYQBsAHUAZQAgAHQAcgBpAG0AcwAgAGMAbwBsAHUAbQBuAHMAIABmAHIAbwBtACAAdABoAGUAIABsAGUAZgB0ACAAbwBmACAAZQBhAGMAaAAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuADsAIABhACAAbgBlAGcAYQB0AGkAdgBlAFwAbgAgACAAIAAgAGQAZQBsAGUAdABlACAAdgBhAGwAdQBlACAAdAByAGkAbQBzACAAYwBvAGwAdQBtAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAaQBnAGgAdAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGQAZQBsAGUAdABlACAAIAAgACAAIAAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACAAaQBuAHQAZQBnAGUAcgA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPgAgADAAIACSISAAdAByAGkAbQAgAGYAcgBvAG0AIABsAGUAZgB0ACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPAAgADAAIACSISAAdAByAGkAbQAgAGYAcgBvAG0AIAByAGkAZwBoAHQAIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACAAIAAtACAAUwB1AGIAZwByAG8AdQBwACAAbABhAGIAZQBsAHMAIAAoAHMAYQBtAGUAIAB3AGkAZAB0AGgAIABhAHMAIABhAHIAcgBhAHkAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAG8AbgBsAHkAIABvAG4AZQAgAHMAdQBiAGcAcgBvAHUAcAAgAGUAeABpAHMAdABzACwAIABEAFIATwBQACgAKQAgAGkAcwAgAHUAcwBlAGQAIABhAHMAIABhACAAZgBhAHMAdAAgAHAAYQB0AGgALgBcAG4AIAAgACAAIAAiICAAZABlAGwAZQB0AGUAIABtAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByADsAIAB0AGUAeAB0ACAAbwByACAAdgBlAGMAdABvAHIAIABpAG4AcAB1AHQAcwAgAGgAYQBsAHQAIAB3AGkAdABoACAAYQBuACAAZQByAHIAbwByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQBsAGUAdABlAEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAZABlAGwAZQB0AGUALABcAG4AIAAgACAAIABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAHUAYgBnAHIAbwB1AHAAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABVAE4ASQBRAFUARQAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsACAAMQApACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEQAaQBzAGMAYQByAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAsACAAQABkAGUAbABlAHQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgADwAPgAgAEMATwBMAFUATQBOAFMAKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUAKQAsAFwAbgAgACAAIAAgAEkAcwBUAGUAeAB0AD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAGQAZQBsAGUAdABlACkALABcAG4AIAAgACAAIABOAG8AdABTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAE8AVAAoAEkAcwBUAGUAeAB0AD8AKQAsACAAQwBPAFUATgBUAEEAKABkAGUAbABlAHQAZQApACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAHMAYwBlAG4AYQByAGkAbwBzACwAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAASQBzAFQAZQB4AHQAPwAsACAATgBvAHQAUwBjAGEAbABhAHIAPwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAcgByAG8AcgAgAGgAYQBuAGQAbABpAG4AZwBcAG4AIAAgACAAIABoAGEAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAcwBjAGUAbgBhAHIAaQBvAHMAKQAsAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIAOwAgAFwAIgAjAFQARQBYAFQAIQBcACIAOwAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiAH0ALABcAG4AIAAgACAAIABhAGwAZQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBSAFIAQQBZAFQATwBUAEUAWABUACgARgBJAEwAVABFAFIAKABlAHIAcgBvAHIAcwAsACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAE8AbgBlAFMAdQBiAEcAcgBvAHUAcAA/ACwAIABEAGkAcwBjAGEAcgBkACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABoAGEAbAB0ACwAIABhAGwAZQByAHQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgACsAbABlAGYAdAAsACAAEyByAGkAZwBoAHQAXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABkAGUAbABlAHQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAdQBuACAAaQBuAGQAaQBjAGUAcwAgACgAaABvAHIAaQB6AG8AbgB0AGEAbAApAFwAbgAgACAAIAAgAGEAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAcgBlAGEAawC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACwAIABUAFIAVQBFACkALABcAG4AIAAgACAAIABkAGUAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsACAAVABSAFUARQApACwAXABuACAAIAAgACAAZABlAGwAZQB0AGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAQgBTACgAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGkAbgBkAGUAeAAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAIAA9ACAALQAxACwAIABkAGUAcwBjAGUAbgBkACwAIABhAHMAYwBlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQBlAHAAIABjAG8AbAB1AG0AbgBzACAAdwBoAGUAcgBlACAAaQBuAGQAZQB4ACAAPgAgAGQAZQBsAGUAdABlAFwAbgAgACAAIAAgAGsAZQBlAHAAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAGkAZAB4ACAAPAA9ACAAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbAB1AG0AbgARIHcAaQBzAGUAIABmAGkAbAB0AGUAcgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGsAZQBlAHAAPwApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABlAGwAZQB0AGUAVwBoAGUAcgBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARABlAGwAZQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBzACAAdgBlAHIAdABpAGMAYQBsACAAYQBuAGQAIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAdgBlAGMAdABvAHIAcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgBhAHMAZQBkACAAbwBuACAAYQAgAHAAcgBlAGQAaQBjAGEAdABlAFwAbgAgACAAIAAgAEwAYQBtAGIAZABhAC4AIABUAGgAZQAgAHAAcgBlAGQAaQBjAGEAdABlACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAGUAYQBjAGgAIAByAG8AdwAgAGEAbgBkACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuADsAIABhAG4AeQAgAHYAZQBjAHQAbwByACAAZgBvAHIAXABuACAAIAAgACAAdwBoAGkAYwBoACAAdABoAGUAIABwAHIAZQBkAGkAYwBhAHQAZQAgAHIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBzACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AIAAgACAAIAAtACAATABhAG0AYgBkAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAZQBhAGMAaAAgAHIAbwB3ACAAYQBuAGQAIABjAG8AbAB1AG0AbgAgAHYAZQBjAHQAbwByAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVABoAGUAIABwAHIAZQBkAGkAYwBhAHQAZQAgAGkAcwAgAGUAdgBhAGwAdQBhAHQAZQBkACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0AGwAeQAgAGYAbwByACAAcgBvAHcAcwAgACgAQgBZAFIATwBXACkAIABhAG4AZAAgAGMAbwBsAHUAbQBuAHMAIAAoAEIAWQBDAE8ATAApAC4AXABuACAAIAAgACAAIiAgAEkAZgAgAG4AbwAgAHIAbwB3AHMAIABvAHIAIABjAG8AbAB1AG0AbgBzACAAYQByAGUAIAByAGUAbQBvAHYAZQBkACwAIABcACIAIwBFAE0AUABUAFkALQBBAFIAUgBBAFkAIQBcACIAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABlAGwAZQB0AGUAVwBoAGUAcgBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGUAeAAgAHMAZQBxAHUAZQBuAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAFIATwBXAFMAKABhAHIAcgBhAHkAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AZQBnAGEAdABlAGQAIABwAHIAZQBkAGkAYwBhAHQAZQAgACgAVABSAFUARQAgAD0AIABrAGUAZQBwACkAXABuACAAIAAgACAAZgBuACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAB2ACwAIABOAE8AVAAoAGYAdQBuAGMAdABpAG8AbgAoAHYAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBvAHcAIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAHQAbwAgAGsAZQBlAHAAXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgASQBGACgAQgBZAFIATwBXACgAYQByAHIAYQB5ACwAIABmAG4AKQAsACAAaQAsACAATgBBACgAKQApACwAIAAyACkALABcAG4AIAAgACAAIABiACwAIAAgACAAIAAgACAAIAAgACAAIABUAE8AUgBPAFcAKABJAEYAKABCAFkAQwBPAEwAKABhAHIAcgBhAHkALAAgAGYAbgApACwAIABqACwAIABOAEEAKAApACkALAAgADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AIAByAGUAbQBvAHYAYQBsAHMAPwBcAG4AIAAgACAAIABJAHMARQBtAHAAdAB5AD8ALAAgACAAIABBAE4ARAAoAEkAUwBFAFIAUgBPAFIAKABhACkALAAgAEkAUwBFAFIAUgBPAFIAKABiACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAGUAdwAgAHMAaABhAHAAZQBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAYQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAeQAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAYgAgACoAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwAIAAsACAAMQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgAEkARgAoAEkAcwBFAG0AcAB0AHkAPwAsACAAXAAiACMARQBNAFAAVABZAC0AQQBSAFIAQQBZACEAXAAiACwAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAHIALAAgAGMAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUABpAG4AYwBoALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARABlAGwAZQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBzACAAYQBuAHkAIABmAHUAbABsACAAcgBvAHcAcwAgAG8AcgAgAGMAbwBsAHUAbQBuAHMAIAB3AGgAbwBzAGUAIABjAGUAbABsAHMAIABhAGwAbAAgAGgAYQB2AGUAIABMAEUATgAoAGMAZQBsAGwAKQAgAD0AIAAwAC4AIABSAG8AdwBzACAAbwByAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAbwBuAGwAeQAgAGUAbQBwAHQAeQAgAHMAdAByAGkAbgBnAHMAIABvAHIAIABlAHIAcgBvAHIAcwAgAGEAcgBlACAAZABpAHMAYwBhAHIAZABlAGQALgAgAFAAaQBuAGMAaAC7AyAAaQBzACAAYQBcAG4AIAAgACAAIABzAHQAcgB1AGMAdAB1AHIAYQBsACAAYwBsAGUAYQBuAHUAcAAgAG8AcABlAHIAYQB0AG8AcgAgAGYAbwByACAAdAByAGkAbQBtAGkAbgBnACAAdwBoAGkAdABlAHMAcABhAGMAZQARIG8AbgBsAHkAIABvAHIAIABuAHUAbABsACAAcgBlAGcAaQBvAG4AcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAGUAbQBwAHQAeQAgAHIAbwB3AHMAIABhAG4AZAAgAGMAbwBsAHUAbQBuAHMAIABhAHIAZQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGkAcwAgAGUAbQBwAHQAeQAsACAAUABpAG4AYwBoALsDIAByAGUAdAB1AHIAbgBzACAAMAAuAFwAbgAgACAAIAAgACIgIABFAHIAcgBvAHIAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgAG4AbwBuABEgZQBtAHAAdAB5ADsAIABvAG4AbAB5ACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIAB3AGgAZQByAGUAIABMAEUATgAoAGMAZQBsAGwAKQAgAD0AIAAwACAAZgBvAHIAXABuACAAIAAgACAAIAAgAGEAbABsACAAYwBlAGwAbABzACAAYQByAGUAIAByAGUAbQBvAHYAZQBkAC4AXABuACAAIAAgACAAIiAgAFAAaQBuAGMAaAC7AyAAcAByAGUAcwBlAHIAdgBlAHMAIAB0AGgAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAGEAbABpAHQAeQAgAG8AZgAgAG4AbwBuABEgZQBtAHAAdAB5ACAAcgBlAGcAaQBvAG4AcwAgAGEAbgBkACAAZABvAGUAcwAgAG4AbwB0ACAAYQBsAHQAZQByAFwAbgAgACAAIAAgACAAIABpAG4AdABlAHIAbgBhAGwAIABjAG8AbgB0AGUAbgB0AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFAAaQBuAGMAaAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AXABuAEkARgAoAEMATwBVAE4AVABBACgAYQByAHIAYQB5ACkAIAA9ACAAMAAsADAALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAG4AESBlAG0AcAB0AHkAIABtAGEAcwBrAFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUATgAoAGEAcgByAGEAeQApACAAPAA+ACAAMAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAvAGMAbwBsAHUAbQBuACAAawBlAGUAcAAgAGYAbABhAGcAcwBcAG4AIAAgACAAIABPAFIAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAB2ACwAIABJAEYARQBSAFIATwBSACgATwBSACgAVABPAEMATwBMACgAdgAsACAAMgApACkALAAgAEYAQQBMAFMARQApACkALABcAG4AIAAgACAAIABtAGEAcgBrAF8AcgBvAHcAcwAsACAAIAAgACAAIAAgACAAIAAgACAAQgBZAFIATwBXACgAYgBvAG8AbAAsACAATwBSALsDKQAsAFwAbgAgACAAIAAgAG0AYQByAGsAXwBjAG8AbABzACwAIAAgACAAIAAgACAAIAAgACAAIABCAFkAQwBPAEwAKABiAG8AbwBsACwAIABPAFIAuwMpACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBtAG8AdgBlACAAZQBtAHAAdAB5ACAAcgBvAHcAcwBcAG4AIAAgACAAIABmAGkAcgBzAHQAXwBwAGEAcwBzACwAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAG0AYQByAGsAXwByAG8AdwBzACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAG0AbwB2AGUAIABlAG0AcAB0AHkAIABjAG8AbAB1AG0AbgBzAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGYAaQByAHMAdABfAHAAYQBzAHMALAAgAG0AYQByAGsAXwBjAG8AbABzACwAIAAwACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADAANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFIAZQBtAG8AdgBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARABlAGwAZQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBzACAAcwBwAGUAYwBpAGYAaQBjACAAcgBvAHcAcwAgAGEAbgBkAC8AbwByACAAYwBvAGwAdQBtAG4AcwAgAGYAcgBvAG0AIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5AC4AIABSAGUAbQBvAHYAZQC7AyAAcwB1AHAAcABvAHIAdABzAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByAHMALAAgADEARAAgAGEAcgByAGEAeQBzACwAIABhAG4AZAAgADIARAAgAGEAcgByAGEAeQBzACAAZgBvAHIAIABiAG8AdABoACAAcgBvAHcAIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAaQBuAHAAdQB0AHMALgAgAEEAbABsAFwAbgAgACAAIAAgAGkAbgBkAGUAeAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAGIAZQBmAG8AcgBlACAAZQB2AGEAbAB1AGEAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAHIAbwB3AHMAIABhAG4AZAAvAG8AcgAgAGMAbwBsAHUAbQBuAHMAIABhAHIAZQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AIAAgACAAIABbAHIAbwB3AHMAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHIAbwB3ACAAaQBuAGQAZQB4ACAAbwByACAAYQByAHIAYQB5ACAAbwBmACAAaQBuAGQAaQBjAGUAcwAgAHQAbwAgAHIAZQBtAG8AdgBlAC4AXABuACAAIAAgACAAWwBjAG8AbABzAF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAGkAbgBkAGkAYwBlAHMAIAB0AG8AIAByAGUAbQBvAHYAZQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBJAE4AVgBBAEwASQBEAC0AUgBPAFcAIQBcACIAIABpAGYAIABhAG4AeQAgAHIAbwB3ACAAaQBuAGQAZQB4ACAAaQBzACAAbwB1AHQAIABvAGYAIABiAG8AdQBuAGQAcwAuAFwAbgAgACAAIAAgACIgIABSAGUAdAB1AHIAbgBzACAAXAAiACMASQBOAFYAQQBMAEkARAAtAEMATwBMACEAXAAiACAAaQBmACAAYQBuAHkAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGkAcwAgAG8AdQB0ACAAbwBmACAAYgBvAHUAbgBkAHMALgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAcgBlAHQAdQByAG4AZQBkACAAdQBuAGMAaABhAG4AZwBlAGQALgBcAG4AIAAgACAAIAAiICAAUgBvAHcALwBjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AQwBPAEwAIABmAG8AcgAgAGMAbwBuAHMAaQBzAHQAZQBuAGMAeQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBSAGUAbQBvAHYAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAHIAbwB3AHMAXQAsAFwAbgAgACAAIAAgAFsAYwBvAGwAcwBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgAgAHAAcgBlAHMAZQBuAGMAZQBcAG4AIAAgACAAIAByAG8AdwBzAF8AaQBuAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AHMAKQApACwAXABuACAAIAAgACAAYwBvAGwAcwBfAGkAbgBjACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABjAG8AbABzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAbQBvAHYAYQBsACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAAUgBlAG0AbwB2AGUAUgBvAHcAcwA/ACwAIAAgACAAIAAgACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGkAbgBjACwAIABOAE8AVAAoAGMAbwBsAHMAXwBpAG4AYwApACkALABcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBDAG8AbABzAD8ALAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABjAG8AbABzAF8AaQBuAGMALAAgAE4ATwBUACgAcgBvAHcAcwBfAGkAbgBjACkAKQAsAFwAbgAgACAAIAAgAFIAZQBtAG8AdgBlAFIAQwA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAHIAbwB3AHMAXwBpAG4AYwAsACAAYwBvAGwAcwBfAGkAbgBjACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABUAGUAeAB0AFIAbwB3AHMAPwAsACAAIAAgACAAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAByAG8AdwBzACkAKQAsAFwAbgAgACAAIAAgAFQAZQB4AHQAQwBvAGwAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAGMAbwBsAHMAKQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAUgBvAHcAPwAsACAAIAAgACAAIAAgACAAIABJAEYAKABUAGUAeAB0AFIAbwB3AHMAPwAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGkAbgBjACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABNAEkATgAoAHIAbwB3AHMAKQAgADwAIAAxACwAIABNAEEAWAAoAHIAbwB3AHMAKQAgAD4AIABoACkAKQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAQwBvAGwAPwAsACAAIAAgACAAIAAgACAAIABJAEYAKABUAGUAeAB0AEMAbwBsAHMAPwAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAYwBvAGwAcwBfAGkAbgBjACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABNAEkATgAoAGMAbwBsAHMAKQAgADwAIAAxACwAIABNAEEAWAAoAGMAbwBsAHMAKQAgAD4AIAB3ACkAKQApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABhAHIAcgBhAHkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFIAbwB3AD8ALAAgAFwAIgAjAEkATgBWAEEATABJAEQALQBSAE8AVwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABDAG8AbAA/ACwAIABcACIAIwBJAE4AVgBBAEwASQBEAC0AQwBPAEwAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUgBvAHcALwBjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAHYAZQBjAHQAbwByAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAGgAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAcwBrAHMAXABuACAAIAAgACAAcgBtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBTAE4AQQAoAFgATQBBAFQAQwBIACgAcgAsACAAVABPAEMATwBMACgAcgBvAHcAcwApACkAKQApACwAXABuACAAIAAgACAAYwBtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBTAE4AQQAoAFgATQBBAFQAQwBIACgAYwAsACAAVABPAEMATwBMACgAYwBvAGwAcwApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3AC0AbwBuAGwAeQAgAHIAZQBtAG8AdgBhAGwAXABuACAAIAAgACAAcgBvAHcAcwBfAG8AbgBsAHkALAAgACAAIAAgAEwAQQBNAEIARABBACgARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAHIAbQBhAHMAawAoACkALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAHUAbQBuAC0AbwBuAGwAeQAgAHIAZQBtAG8AdgBhAGwAXABuACAAIAAgACAAYwBvAGwAcwBfAG8AbgBsAHkALAAgACAAIAAgAEwAQQBNAEIARABBACgARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGMAbQBhAHMAawAoACkALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwB0AGgAIAByAG8AdwBzACAAYQBuAGQAIABjAG8AbAB1AG0AbgBzAFwAbgAgACAAIAAgAFIAQwBfAHIALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEYASQBMAFQARQBSACgAYQByAHIAYQB5ACwAIAByAG0AYQBzAGsAKAApACwAIAAwACkAKQAsAFwAbgAgACAAIAAgAFIAQwAsACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEYASQBMAFQARQBSACgAUgBDAF8AcgAoACkALAAgAGMAbQBhAHMAawAoACkALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIABJAEYAKABSAGUAbQBvAHYAZQBSAG8AdwBzAD8ALAAgAHIAbwB3AHMAXwBvAG4AbAB5ACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABSAGUAbQBvAHYAZQBDAG8AbABzAD8ALAAgAGMAbwBsAHMAXwBvAG4AbAB5ACgAKQAsACAAUgBDACgAKQApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADAANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABEAGUAbABlAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBtAG8AdgBlAHMAIABuAHUAbABsACAAYQBuAGQAIABzAHQAcgBhAGkAZwBoAHQAESB6AGUAcgBvACAAdgBlAHIAdABpAGMAYQBsACAAbwByACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgAHYAZQBjAHQAbwByAHMAIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFMAdQBwAHAAbwByAHQAcwAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAGMAdQBzAHQAbwBtACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAGYAbwByACAAcgBlAG0AbwB2AGEAbAAuACAAUwBxAHUAZQBlAHoAZQC7AyAAYwBhAG4AIABhAGwAcwBvAFwAbgAgACAAIAAgAG8AcAB0AGkAbwBuAGEAbABsAHkAIABzAHUAcABwAHIAZQBzAHMAIAB6AGUAcgBvAHMAIABpAG4AIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYgB5ACAAcgBlAHAAbABhAGMAaQBuAGcAIAB0AGgAZQBtACAAdwBpAHQAaAAgAFwAIgBcACIALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAGYAcgBvAG0AIAB3AGgAaQBjAGgAIAByAG8AdwBzAC8AYwBvAGwAdQBtAG4AcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAuAFwAbgAgACAAIAAgAFsAYwB1AHMAdABvAG0AXwBjAHIAaQB0AGUAcgBpAGEAXQAtACAATwBwAHQAaQBvAG4AYQBsACAAcwBjAGEAbABhAHIAIAB1AHMAZQBkACAAYQBzACAAdABoAGUAIAByAGUAbQBvAHYAYQBsACAAYwByAGkAdABlAHIAaQBvAG4ALgBcAG4AIAAgACAAIABbAHMAdQBwAHAAcgBlAHMAcwBfAHoAZQByAG8AcwBdACAALQAgAEkAZgAgAHAAcgBvAHYAaQBkAGUAZAAsACAAegBlAHIAbwBzACAAaQBuACAAdABoAGUAIABmAGkAbgBhAGwAIAByAGUAcwB1AGwAdAAgAGEAcgBlACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAFwAIgBcACIALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIABiAG8AdABoACAAcgBvAHcAIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAdgBlAGMAdABvAHIAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAsACAAdABoAGUAIAByAGUAcwB1AGwAdAAgAG0AYQB5ACAAcwBoAHIAaQBuAGsAIABpAG4AIABiAG8AdABoAFwAbgAgACAAIAAgACAAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAIiAgAEkAZgAgAG4AbwAgAHIAbwB3AHMAIABvAHIAIABjAG8AbAB1AG0AbgBzACAAcgBlAG0AYQBpAG4ALAAgAFwAIgAjAEUATQBQAFQAWQAtAEEAUgBSAEEAWQAhAFwAIgAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgAgACAAIAAgACIgIABzAHUAcABwAHIAZQBzAHMAXwB6AGUAcgBvAHMAIABvAG4AbAB5ACAAYQBmAGYAZQBjAHQAcwAgAHQAaABlACAAKgBvAHUAdABwAHUAdAAqACwAIABuAG8AdAAgAHQAaABlACAAcgBlAG0AbwB2AGEAbAAgAGwAbwBnAGkAYwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHEAdQBlAGUAegBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAYwB1AHMAdABvAG0AXwBjAHIAaQB0AGUAcgBpAGEAXQAsAFwAbgAgACAAIAAgAFsAcwB1AHAAcAByAGUAcwBzAF8AegBlAHIAbwBzAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABaAGUAcgBvABEgcwB1AHAAcAByAGUAcwBzAGkAbwBuACAAZgBsAGEAZwBcAG4AIAAgACAAIABIAGkAZABlAFoAZQByAG8APwAsACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHMAdQBwAHAAcgBlAHMAcwBfAHoAZQByAG8AcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAcwBlAHEAdQBlAG4AYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAFIATwBXAFMAKABhAHIAcgBhAHkAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBhAHUAbAB0ACAAcgBlAG0AbwB2AGEAbAA6ACAAcgBlAG0AbwB2AGUAIABhAGwAbAARIHoAZQByAG8AIAB2AGUAYwB0AG8AcgBzAFwAbgAgACAAIAAgAEsAZQBlAHAAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALAAgAE4ATwBUACgAQQBOAEQAKABUAE8AQwBPAEwAKAB2ACwAIAAyACkAIAA9ACAAMAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAHUAcwB0AG8AbQAgAHIAZQBtAG8AdgBhAGwAOgAgAHIAZQBtAG8AdgBlACAAdgBlAGMAdABvAHIAcwAgAGUAcQB1AGEAbAAgAHQAbwAgAGMAdQBzAHQAbwBtAF8AYwByAGkAdABlAHIAaQBhAFwAbgAgACAAIAAgAEMAdQBzAHQAbwBtALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALAAgAE4ATwBUACgAQQBOAEQAKABUAE8AQwBPAEwAKAB2ACwAIAAyACkAIAA9ACAAYwB1AHMAdABvAG0AXwBjAHIAaQB0AGUAcgBpAGEAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABwAHIAZQBkAGkAYwBhAHQAZQBcAG4AIAAgACAAIABmAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABjAHUAcwB0AG8AbQBfAGMAcgBpAHQAZQByAGkAYQApACwAIABLAGUAZQBwALsDLAAgAEMAdQBzAHQAbwBtALsDKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAvAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAHQAbwAgAGsAZQBlAHAAXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAEkARgAoAEIAWQBSAE8AVwAoAGEAcgByAGEAeQAsACAAZgBuACkALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACwAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBSAE8AVwAoAEkARgAoAEIAWQBDAE8ATAAoAGEAcgByAGEAeQAsACAAZgBuACkALAAgAGoALAAgAE4AQQAoACkAKQAsACAAMgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwAgAHIAbwB3AHMAIABvAHIAIABjAG8AbAB1AG0AbgBzACAAcgBlAG0AYQBpAG4APwBcAG4AIAAgACAAIABJAHMARQBtAHAAdAB5AD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAFMARQBSAFIATwBSACgAYQApACwAIABJAFMARQBSAFIATwBSACgAYgApACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBlAHcAIABzAGgAYQBwAGUAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHkALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiACAAKgAgAFMARQBRAFUARQBOAEMARQAoAHgALAAgACwAIAAxACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAHIAZQBzAHUAbAB0AFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAHIALAAgAGMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIAB6AGUAcgBvACAAcwB1AHAAcAByAGUAcwBzAGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AF8AYgAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAByAGUAcwB1AGwAdAAgAD0AIAAwACwAIABcACIAXAAiACwAIAByAGUAcwB1AGwAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0AFwAbgAgACAAIAAgAG8AdQB0AHAAdQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARQBtAHAAdAB5AD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBFAE0AUABUAFkALQBBAFIAUgBBAFkAIQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABIAGkAZABlAFoAZQByAG8APwAsACAAcgBlAHMAdQBsAHQAXwBiACwAIAByAGUAcwB1AGwAdAApACkALABcAG4AXABuACAAIAAgACAAbwB1AHQAcAB1AHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAwADcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABLAHIAbwBuAGUAYwBrAGUAcgBQAHIAbwBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARQB4AHAAYQBuAHMAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAE0AYQBnAG4AaQBmAHkAuwMsACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAASwByAG8AbgBlAGMAawBlAHIAIABwAHIAbwBkAHUAYwB0ACAAbwBmACAAdAB3AG8AIABhAHIAcgBhAHkAcwAuACAAVABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIABpAHMAIABlAHgAcABhAG4AZABlAGQAXABuACAAIAAgACAAdQBzAGkAbgBnACAATQBhAGcAbgBpAGYAeQC7AyAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABoAGUAaQBnAGgAdAAgAGEAbgBkACAAdwBpAGQAdABoACAAbwBmACAAYQByAHIAYQB5AF8AMgAsACAAdwBoAGkAbABlACAAYQByAHIAYQB5AF8AMgAgAGkAcwBcAG4AIAAgACAAIAByAGUAcwBpAHoAZQBkACAAdQBzAGkAbgBnACAAUgBlAHMAaQB6AGUAuwMgAHQAbwAgAG0AYQB0AGMAaAAgAHQAaABlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAG8AZgAgAGEAcgByAGEAeQBfADEALgAgAFQAaABlAGkAcgAgAGUAbABlAG0AZQBuAHQAESB3AGkAcwBlAFwAbgAgACAAIAAgAHAAcgBvAGQAdQBjAHQAIAB5AGkAZQBsAGQAcwAgAHQAaABlACAAZgB1AGwAbAAgAEsAcgBvAG4AZQBjAGsAZQByACAAZQB4AHAAYQBuAHMAaQBvAG4ALgBcAG4AXABuACAAIAAgACAAQQBsAHQAaABvAHUAZwBoACAASwByAG8AbgBlAGMAawBlAHIAIABwAHIAbwBkAHUAYwB0AHMAIABhAHIAZQAgAHQAcgBhAGQAaQB0AGkAbwBuAGEAbABsAHkAIABkAGUAZgBpAG4AZQBkACAAZgBvAHIAIABtAGEAdAByAGkAYwBlAHMALAAgAHQAaABpAHMAXABuACAAIAAgACAAaQBtAHAAbABlAG0AZQBuAHQAYQB0AGkAbwBuACAAYQBsAHMAbwAgAHMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByAHMAIABhAG4AZAAgADEARAAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIAcwAgAGEAYwBjAGUAcAB0AGUAZAApAC4AXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIAcwAgAGEAYwBjAGUAcAB0AGUAZAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQgByAG8AYQBkAGMAYQBzAHQAaQBuAGcAIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAAgAHYAaQBhACAAbgBlAGEAcgBlAHMAdAARIG4AZQBpAGcAaABiAG8AcgAgAGUAeABwAGEAbgBzAGkAbwBuAC4AXABuACAAIAAgACAAIiAgAFQAaABlACAAbwB1AHQAcAB1AHQAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAYQByAGUAIAAoAFIATwBXAFMAKABhAHIAcgBhAHkAXwAxACkAKgBSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACkAIADXAFwAbgAgACAAIAAgACAAIAAoAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAxACkAKgBDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgApACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASwByAG8AbgBlAGMAawBlAHIAUAByAG8AZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAxACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGgAgiAsACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACwAXABuACAAIAAgACAAdwCCICwAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgByAG8AYQBkAGMAYQBzAHQAIABhAHIAcgBhAHkAXwAxACAAYgB5ACAAbQBhAGcAbgBpAGYAeQBpAG4AZwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuAHQAbwAgAGEAbgAgAGgAgiAgANcAIAB3AIIgIABiAGwAbwBjAGsAXABuACAAIAAgACAAQQAsACAAIAAgACAAIAAgAE0AYQBnAG4AaQBmAHkAuwMoAGEAcgByAGEAeQBfADEALAAgAGgAgiAsACAAdwCCICkALABcAG4AXABuACAAIAAgACAALwAvACAAQgByAG8AYQBkAGMAYQBzAHQAIABhAHIAcgBhAHkAXwAyACAAYgB5ACAAcgBlAHMAaQB6AGkAbgBnACAAaQB0ACAAdABvACAAbQBhAHQAYwBoACAAYQByAHIAYQB5AF8AMQAZIHMAIABzAHQAcgB1AGMAdAB1AHIAZQBcAG4AIAAgACAAIABCACwAIAAgACAAIAAgACAAUgBlAHMAaQB6AGUAuwMoAGEAcgByAGEAeQBfADIALAAgAGgALAAgAHcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAGwAZQBtAGUAbgB0ABEgdwBpAHMAZQAgAHAAcgBvAGQAdQBjAHQAIAB5AGkAZQBsAGQAcwAgAHQAaABlACAASwByAG8AbgBlAGMAawBlAHIAIABlAHgAcABhAG4AcwBpAG8AbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAQQAgACoAIABCACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARQB4AGMAbAB1AGQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEYAaQBsAHQAZQByAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABGAGkAbAB0AGUAcgBzACAAYQBuACAAYQByAHIAYQB5ACAAKAAxAEQAIABvAHIAIAAyAEQAKQAgAGIAeQAgAGUAeABjAGwAdQBkAGkAbgBnACAAYQBuAHkAIAByAG8AdwAgAHQAaABhAHQAIABjAG8AbgB0AGEAaQBuAHMAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBvAG4ALgAgAEUAeABjAGwAdQBkAGUAuwMgAGkAcwAgAGEAIABzAGkAbQBwAGwAaQBmAGkAZQBkACAAYQBsAHQAZQByAG4AYQB0AGkAdgBlACAAdABvACAARgBJAEwAVABFAFIAIAB3AGgAZQByAGUAIAB0AGgAZQAgAHUAcwBlAHIAXABuACAAIAAgACAAcwB1AHAAcABsAGkAZQBzACAAdABoAGUAIABlAHgAYwBsAHUAcwBpAG8AbgAgAHYAYQBsAHUAZQBzACAAZABpAHIAZQBjAHQAbAB5ACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAYQAgAGIAbwBvAGwAZQBhAG4AIABtAGEAcwBrAC4AXABuAFwAbgAgACAAIAAgAFQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAYwBoAGUAYwBrAHMAIABlAGEAYwBoACAAcgBvAHcAIABmAG8AcgAgAHQAaABlACAAcAByAGUAcwBlAG4AYwBlACAAbwBmACAAYQBuAHkAIAB2AGEAbAB1AGUAIABpAG4AIAAnAGUAeABjAGwAdQBkAGUAJwAuAFwAbgAgACAAIAAgAFIAbwB3AHMAIAB0AGgAYQB0ACAAYwBvAG4AdABhAGkAbgAgAHQAaABlACAAZQB4AGMAbAB1AHMAaQBvAG4AIABjAHIAaQB0AGUAcgBpAG8AbgAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAA7ACAAYQBsAGwAIABvAHQAaABlAHIAcwAgAGEAcgBlACAAawBlAHAAdAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABmAGkAbAB0AGUAcgAuAFwAbgAgACAAIAAgAGUAeABjAGwAdQBkAGUAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAG8AcgAgADEARAAgAGEAcgByAGEAeQAgAG8AZgAgAHYAYQBsAHUAZQBzACAAdABvACAAbwBtAGkAdAAuAFwAbgAgACAAIAAgAFsAaQBmAF8AZQBtAHAAdAB5AF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGEAbABsAGIAYQBjAGsAIAB2AGEAbAB1AGUAIAB3AGgAZQBuACAAbgBvACAAcgBvAHcAcwAgAHIAZQBtAGEAaQBuACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgADAAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEEAIAAyAEQAIABlAHgAYwBsAHUAZABlACAAYQByAHIAYQB5ACAAaQBzACAAaQBuAHYAYQBsAGkAZAAgAGEAbgBkACAAaABhAGwAdABzACAAdwBpAHQAaAAgAFwAIgAjADIARAAtAEUAWABDAEwAVQBEAEUAIQBcACIALgBcAG4AIAAgACAAIAAiICAATQBhAHQAYwBoAGkAbgBnACAAaQBzACAAcABlAHIAZgBvAHIAbQBlAGQAIAB1AHMAaQBuAGcAIABYAE0AQQBUAEMASAA7ACAAbgBvAG4AESBtAGEAdABjAGgAZQBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAegBlAHIAbwAuAFwAbgAgACAAIAAgACIgIABGAGkAbAB0AGUAcgBpAG4AZwAgAGkAcwAgAHIAbwB3ABEgdwBpAHMAZQA7ACAAYwBvAGwAdQBtAG4AcwAgAGEAcgBlACAAcAByAGUAcwBlAHIAdgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARQB4AGMAbAB1AGQAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABlAHgAYwBsAHUAZABlACwAXABuACAAIAAgACAAWwBpAGYAXwBlAG0AcAB0AHkAXQAsAFwAbgBcAG4ASQBGACgAQQBOAEQAKABSAE8AVwBTACgAZQB4AGMAbAB1AGQAZQApACAAPgAgADEALAAgAEMATwBMAFUATQBOAFMAKABlAHgAYwBsAHUAZABlACkAIAA+ACAAMQApACwAXAAiACMAMgBEAC0ARQBYAEMATABVAEQARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGEAbABsAGIAYQBjAGsAXABuACAAIAAgACAAaQBmAF8AZQBtAHAAdAB5ACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZgBfAGUAbQBwAHQAeQApACwAIAAwACwAIABpAGYAXwBlAG0AcAB0AHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAFIAVQBFACAAPQAgAGsAZQBlAHAAIAByAG8AdwAsACAARgBBAEwAUwBFACAAPQAgAGUAeABjAGwAdQBkAGUAIAByAG8AdwBcAG4AIAAgACAAIABrAGUAZQBwAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgAQgBZAFIATwBXACgASQBGAE4AQQAoAFgATQBBAFQAQwBIACgAYQByAHIAYQB5ACwAIABlAHgAYwBsAHUAZABlACkALAAgADAAKQAsAE8AUgApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAawBlAGUAcAA/ACwAIABpAGYAXwBlAG0AcAB0AHkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAA5AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBuAGEAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEYAaQBsAHQAZQByAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABGAGkAbAB0AGUAcgBzACAAYQBuACAAYQByAHIAYQB5ACAAKAAxAEQAIABvAHIAIAAyAEQAKQAgAGIAeQAgAHMAZQBsAGUAYwB0AGkAbgBnACAAcgBvAHcAcwAgAHQAaABhAHQAIABjAG8AbgB0AGEAaQBuACAAYQB0ACAAbABlAGEAcwB0ACAAbwBuAGUAXABuACAAIAAgACAAdgBhAGwAdQBlACAAZgByAG8AbQAgAHQAaABlACAAJwBpAG4AYwBsAHUAZABlACcAIABjAHIAaQB0AGUAcgBpAGEALgAgAFMAbgBhAHAAuwMgAGkAcwAgAGEAIABzAGkAbQBwAGwAaQBmAGkAZQBkACAAYQBsAHQAZQByAG4AYQB0AGkAdgBlACAAdABvAFwAbgAgACAAIAAgAEYASQBMAFQARQBSACAAdwBoAGUAcgBlACAAdABoAGUAIAB1AHMAZQByACAAcwB1AHAAcABsAGkAZQBzACAAdABoAGUAIABpAG4AYwBsAHUAcwBpAG8AbgAgAHYAYQBsAHUAZQBzACAAZABpAHIAZQBjAHQAbAB5ACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuAFwAbgAgACAAIAAgAGEAIABiAG8AbwBsAGUAYQBuACAAbQBhAHMAawAuAFwAbgBcAG4AIAAgACAAIABUAGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAGMAaABlAGMAawBzACAAZQBhAGMAaAAgAHIAbwB3ACAAZgBvAHIAIAB0AGgAZQAgAHAAcgBlAHMAZQBuAGMAZQAgAG8AZgAgAGEAbgB5ACAAdgBhAGwAdQBlACAAaQBuACAAJwBpAG4AYwBsAHUAZABlACcALgBcAG4AIAAgACAAIABSAG8AdwBzACAAdABoAGEAdAAgAGMAbwBuAHQAYQBpAG4AIAB0AGgAZQAgAGkAbgBjAGwAdQBzAGkAbwBuACAAYwByAGkAdABlAHIAaQBvAG4AIABhAHIAZQAgAGsAZQBwAHQAOwAgAGEAbABsACAAbwB0AGgAZQByAHMAIABhAHIAZQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAZgBpAGwAdABlAHIALgBcAG4AIAAgACAAIABpAG4AYwBsAHUAZABlACAAIAAgACAAIAAtACAAUwBjAGEAbABhAHIAIABvAHIAIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGkAbgBjAGwAdQBkAGUALgBcAG4AIAAgACAAIABbAGkAZgBfAGUAbQBwAHQAeQBdACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAZgBhAGwAbABiAGEAYwBrACAAdgBhAGwAdQBlACAAdwBoAGUAbgAgAG4AbwAgAHIAbwB3AHMAIAByAGUAbQBhAGkAbgAgACgAZABlAGYAYQB1AGwAdAAgAD0AIAAwACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABBACAAMgBEACAAaQBuAGMAbAB1AGQAZQAgAGEAcgByAGEAeQAgAGkAcwAgAGkAbgB2AGEAbABpAGQAIABhAG4AZAAgAGgAYQBsAHQAcwAgAHcAaQB0AGgAIABcACIAIwAyAEQALQBJAE4AQwBMAFUARABFACEAXAAiAC4AXABuACAAIAAgACAAIiAgAE0AYQB0AGMAaABpAG4AZwAgAGkAcwAgAHAAZQByAGYAbwByAG0AZQBkACAAdQBzAGkAbgBnACAAWABNAEEAVABDAEgAOwAgAG4AbwBuABEgbQBhAHQAYwBoAGUAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgAHoAZQByAG8ALgBcAG4AIAAgACAAIAAiICAARgBpAGwAdABlAHIAaQBuAGcAIABpAHMAIAByAG8AdwARIHcAaQBzAGUAOwAgAGMAbwBsAHUAbQBuAHMAIABhAHIAZQAgAHAAcgBlAHMAZQByAHYAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAbgBhAHAAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAaQBuAGMAbAB1AGQAZQAsAFwAbgAgACAAIAAgAFsAaQBmAF8AZQBtAHAAdAB5AF0ALABcAG4AXABuAEkARgAoAEEATgBEACgAUgBPAFcAUwAoAGkAbgBjAGwAdQBkAGUAKQAgAD4AIAAxACwAIABDAE8ATABVAE0ATgBTACgAaQBuAGMAbAB1AGQAZQApACAAPgAgADEAKQAsAFwAIgAjADIARAAtAEkATgBDAEwAVQBEAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBhAGwAbABiAGEAYwBrAFwAbgAgACAAIAAgAGkAZgBfAGUAbQBwAHQAeQAsACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABpAGYAXwBlAG0AcAB0AHkAKQAsACAAMAAsACAAaQBmAF8AZQBtAHAAdAB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABSAFUARQAgAD0AIABrAGUAZQBwACAAcgBvAHcALAAgAEYAQQBMAFMARQAgAD0AIABkAGkAcwBjAGEAcgBkACAAcgBvAHcAXABuACAAIAAgACAAawBlAGUAcAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKABJAEYATgBBACgAWABNAEEAVABDAEgAKABhAHIAcgBhAHkALAAgAGkAbgBjAGwAdQBkAGUAKQAsACAAMAApACwATwBSACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAawBlAGUAcAA/ACwAIABpAGYAXwBlAG0AcAB0AHkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQAwAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBoAGkAZgB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUgBvAGwAbABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAARQB4AHAAbABvAGQAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUABlAHIAZgBvAHIAbQBzACAAYQAgAGMAaQByAGMAdQBsAGEAcgAgAHMAaABpAGYAdAAgAG8AbgAgAGEAIABzAHUAcABwAGwAaQBlAGQAIAB0AHUAcABsAGUAIAAoAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQApAC4AXABuACAAIAAgACAAUABvAHMAaQB0AGkAdgBlACAAcwBoAGkAZgB0ACAAdgBhAGwAdQBlAHMAIAByAG8AdABhAHQAZQAgAGwAZQBmAHQAOwAgAG4AZQBnAGEAdABpAHYAZQAgAHMAaABpAGYAdAAgAHYAYQBsAHUAZQBzACAAcgBvAHQAYQB0AGUAIAByAGkAZwBoAHQALgBcAG4AXABuACAAIAAgACAARQB4AGEAbQBwAGwAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAA9AFMAaABpAGYAdAC7AygAewAxACwAMgAsADMALAA0AH0ALAAgADIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAkiEgAHsAMwAsADQALAAxACwAMgB9AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAD0AUwBoAGkAZgB0ALsDKAB7ADEALAAyACwAMwAsADQAfQAsACAALQAxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAJIhIAB7ADQALAAxACwAMgAsADMAfQBcAG4AXABuACAAIAAgACAAIAAgACAAIAA9AFMAaABpAGYAdAC7AygAXAAiADEAMgAzADQAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAJIhIAB7AFwAIgAyAFwAIgA7AFwAIgAzAFwAIgA7AFwAIgA0AFwAIgA7AFwAIgAxAFwAIgB9AFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAA9AFMAaABpAGYAdAC7AygAewAxACwAMgAsADMALAA0AH0ALAB7ADEALAAyACwAMwB9ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAJIhIAB7ADIALAAzACwANAAsADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMwAsADQALAAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACwAMQAsADIALAAzAH0AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAdAB1AHAAbABlACAAIAAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAZQB4AHAAbABvAGQAZQBkACAAaQBuAHQAbwAgAGMAaABhAHIAYQBjAHQAZQByACAAYQByAHIAYQB5AHMAIAB2AGkAYQAgAEUAeABwAGwAbwBkAGUAuwMuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAdwBpAHQAaAAgAFQATwBDAE8ATAAuAFwAbgBcAG4AIAAgACAAIABbAHMAaABpAGYAdABfAGIAeQBdACAAIAAtACAAUwBoAGkAZgB0ACAAYwBvAHUAbgB0ACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgADEAKQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAAUABvAHMAaQB0AGkAdgBlACAAkiEgAGwAZQBmAHQAIABzAGgAaQBmAHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABOAGUAZwBhAHQAaQB2AGUAIACSISAAcgBpAGcAaAB0ACAAcwBoAGkAZgB0AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAATQB1AGwAdABpABEgcwBoAGkAZgB0ACAAYQByAHIAYQB5AHMAIABwAHIAbwBkAHUAYwBlACAAYQAgAGEAcgByAGEAeQBfADIARAAgAG8AZgAgAHMAaABpAGYAdABlAGQAIAB0AHUAcABsAGUAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuACAAbQBhAHQAYwBoAGUAcwAgAGkAbgBwAHUAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgBzACAAkiEgAHYAZQByAHQAaQBjAGEAbABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAtACAAVgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5AHMAIACSISAAdgBlAHIAdABpAGMAYQBsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAC0AIABIAG8AcgBpAHoAbwBuAHQAYQBsACAAYQByAHIAYQB5AHMAIACSISAAaABvAHIAaQB6AG8AbgB0AGEAbABcAG4AIAAgACAAIAAiICAATQB1AGwAdABpABEgcwBoAGkAZgB0ACAAaQBuAHAAdQB0AHMAIAByAGUAdAB1AHIAbgAgAGEAIABzAHQAYQBjAGsAZQBkACAAYQByAHIAYQB5AF8AMgBEACAAbwBmACAAcwBoAGkAZgB0AGUAZAAgAHIAZQBzAHUAbAB0AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBoAGkAZgB0ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHQAdQBwAGwAZQAsAFwAbgAgACAAIAAgAFsAcwBoAGkAZgB0AF8AYgB5AF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAB0AHUAcABsAGUAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAdAB1AHAAbABlACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHQAdQBwAGwAZQAgAJIhIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAXABuACAAIAAgACAAdAB1AHAAbABlACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwARQB4AHAAbABvAGQAZQC7AygAdAB1AHAAbABlACkALAB0AHUAcABsAGUAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcwBoAGkAZgB0AF8AYgB5ACAAkiEgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABzAGgAaQBmAHQAXwBiAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABzAGgAaQBmAHQAXwBiAHkAKQAsACAAMQAsACAAcwBoAGkAZgB0AF8AYgB5ACkAKQAsAFwAbgAgACAAIAAgAEkAcwBNAHUAbAB0AGkAUwBoAGkAZgB0AD8ALAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHMAaABpAGYAdABfAGIAeQApACAAPgAgADEALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAASQBzADEARQBsAGUAbQBlAG4AdAA/ACwAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAdAB1AHAAbABlACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEkAcwBUAGUAeAB0AFMAaABpAGYAdAA/ACwAIAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHMAaABpAGYAdABfAGIAeQApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzADEARQBsAGUAbQBlAG4AdAA/ACwAIAB0AHUAcABsAGUALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVABlAHgAdABTAGgAaQBmAHQAPwAsACAAXAAiACMAVABFAFgAVAAtAFMASABJAEYAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABUAHUAcABsAGUAIABsAGUAbgBnAHQAaABcAG4AIAAgACAAIABuACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHQAdQBwAGwAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADAAESBiAGEAcwBlAGQAIABpAG4AZABlAHgAIABzAGUAcQB1AGUAbgBjAGUAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG4ALAAgADAALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGkAcgBjAHUAbABhAHIAIABpAG4AZABlAHgAIABzAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIABNAE8ARAAoAGkAIAArACAAcwBoAGkAZgB0AF8AYgB5ACwAIABuACkAIAArACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABzAGgAaQBmAHQAXABuACAAIAAgACAAcwBoAGkAZgB0AGUAZAAsACAAIAAgACAASQBOAEQARQBYACgAdAB1AHAAbABlACwAIABpAGQAeAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAHQAbwByAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAASQBGACgASQBzAE0AdQBsAHQAaQBTAGgAaQBmAHQAPwAsACAAcwBoAGkAZgB0AGUAZAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAcwBoAGkAZgB0AGUAZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AUgBPAFcAKABzAGgAaQBmAHQAZQBkACkAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBoAGkAZgB0AFIAbwB3AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABSAG8AbABsAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABTAGgAaQBmAHQAuwMsACAATQBHAHIAaQBkALsDLAAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGUAcgBmAG8AcgBtAHMAIABhACAAYwBpAHIAYwB1AGwAYQByACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgAHMAaABpAGYAdAAgAG8AbgAgAGUAYQBjAGgAIAByAG8AdwAgAG8AZgAgAGEAIAAyAEQAIABhAHIAcgBhAHkALgAgAFQAaABlACAAcwBoAGkAZgB0AF8AYgB5AFwAbgAgACAAIAAgAHYAYQBsAHUAZQAgAGQAZQB0AGUAcgBtAGkAbgBlAHMAIABoAG8AdwAgAG0AYQBuAHkAIABwAG8AcwBpAHQAaQBvAG4AcwAgAGUAYQBjAGgAIAByAG8AdwAgAGkAcwAgAHIAbwB0AGEAdABlAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABQAG8AcwBpAHQAaQB2AGUAIACSISAAcwBoAGkAZgB0ACAAbABlAGYAdABcAG4AIAAgACAAIAAgACAAIAAgACIgIABOAGUAZwBhAHQAaQB2AGUAIACSISAAcwBoAGkAZgB0ACAAcgBpAGcAaAB0AFwAbgBcAG4AIAAgACAAIAAxAEQAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAcwBjAGEAbABhAHIAcwAgAGEAcgBlACAAZABlAGwAZQBnAGEAdABlAGQAIAB0AG8AIABTAGgAaQBmAHQAuwMuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAPQAgAHsAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgAsAFwAIgBCAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYgBcACIALABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGUAXAAiACwAXAAiAEgAaQBzAHQAbwByAHkAXAAiACwAXAAiAEIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAbwBlAFwAIgAsAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIALABcACIAQwBcACIAfQBcAG4AXABuACAAIAAgACAAPQBTAGgAaQBmAHQAUgBvAHcAcwC7AygAYQByAHIAYQB5ACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIACSISAAewBcACIATQBhAHQAaABcACIALABcACIAQgBcACIALABcACIAQgBvAGIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIALABcACIARABlAGIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAHMAdABvAHIAeQBcACIALABcACIAQgBcACIALABcACIAUwB1AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGUAbQBpAHMAdAByAHkAXAAiACwAXAAiAEMAXAAiACwAXAAiAEoAbwBlAFwAIgB9AFwAbgBcAG4AIAAgACAAIAA9AFMAaABpAGYAdABSAG8AdwBzALsDKABhAHIAcgBhAHkALAAgAC0AMQApAFwAbgAgACAAIAAgACAAIAAgACAAkiEgAHsAXAAiAEIAXAAiACwAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAXAAiACwAXAAiAEQAZQBiAFwAIgAsAFwAIgBQAGgAeQBzAGkAYwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAXAAiACwAXAAiAFMAdQBlAFwAIgAsAFwAIgBIAGkAcwB0AG8AcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXAAiACwAXAAiAEoAbwBlAFwAIgAsAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIAfQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBoAGkAZgB0AFIAbwB3AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAWwBzAGgAaQBmAHQAXwBiAHkAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABhAHIAcgBhAHkAcwAgAC8AIABzAGMAYQBsAGEAcgBzACAAaABhAG4AZABsAGUAZAAgAGIAeQAgAFMAaABpAGYAdAC7A1wAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALABTAGgAaQBmAHQAuwMoAGEAcgByAGEAeQBfADIARAAsACAAcwBoAGkAZgB0AF8AYgB5ACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUgBvAHcAIABpAG4AZABpAGMAZQBzACAAcgBlAG0AYQBpAG4AIABmAGkAeABlAGQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGEAcgByAGEAeQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAGEAcgBlACAAYwBpAHIAYwB1AGwAYQByAGwAeQAgAHMAaABpAGYAdABlAGQAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIABSAGUAcwBpAHoAZQC7AygAUwBoAGkAZgB0ALsDKABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwApACwAIABzAGgAaQBmAHQAXwBiAHkAKQAsAGgAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQBfADIARAAsACAAaQAsACAAagApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFMAaABpAGYAdABDAG8AbABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUgBvAGwAbABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUwBoAGkAZgB0ALsDLAAgAE0ARwByAGkAZAC7AywAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUABlAHIAZgBvAHIAbQBzACAAYQAgAGMAaQByAGMAdQBsAGEAcgAgAHYAZQByAHQAaQBjAGEAbAAgAHMAaABpAGYAdAAgAG8AbgAgAGUAYQBjAGgAIABjAG8AbAB1AG0AbgAgAG8AZgAgAGEAIAAyAEQAIABhAHIAcgBhAHkALgAgAFQAaABlACAAcwBoAGkAZgB0AF8AYgB5AFwAbgAgACAAIAAgAHYAYQBsAHUAZQAgAGQAZQB0AGUAcgBtAGkAbgBlAHMAIABoAG8AdwAgAG0AYQBuAHkAIABwAG8AcwBpAHQAaQBvAG4AcwAgAGUAYQBjAGgAIABjAG8AbAB1AG0AbgAgAGkAcwAgAHIAbwB0AGEAdABlAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABQAG8AcwBpAHQAaQB2AGUAIACSISAAcwBoAGkAZgB0ACAAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAE4AZQBnAGEAdABpAHYAZQAgAJIhIABzAGgAaQBmAHQAIABkAG8AdwBuAFwAbgBcAG4AIAAgACAAIAAxAEQAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAcwBjAGEAbABhAHIAcwAgAGEAcgBlACAAZABlAGwAZQBnAGEAdABlAGQAIAB0AG8AIABTAGgAaQBmAHQAuwMuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAPQAgAHsAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgAsAFwAIgBCAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYgBcACIALABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGUAXAAiACwAXAAiAEgAaQBzAHQAbwByAHkAXAAiACwAXAAiAEIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAbwBlAFwAIgAsAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIALABcACIAQwBcACIAfQBcAG4AXABuACAAIAAgACAAPQBTAGgAaQBmAHQAQwBvAGwAcwC7AygAYQByAHIAYQB5ACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIACSISAAewBcACIARABlAGIAXAAiACwAXAAiAFAAaAB5AHMAaQBjAHMAXAAiACwAXAAiAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGUAXAAiACwAXAAiAEgAaQBzAHQAbwByAHkAXAAiACwAXAAiAEIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASgBvAGUAXAAiACwAXAAiAEMAaABlAG0AaQBzAHQAcgB5AFwAIgAsAFwAIgBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgAsAFwAIgBCAFwAIgB9AFwAbgBcAG4AIAAgACAAIAA9AFMAaABpAGYAdABDAG8AbABzALsDKABhAHIAcgBhAHkALAAgAC0AMQApAFwAbgAgACAAIAAgACAAIAAgACAAkiEgAHsAXAAiAEoAbwBlAFwAIgAsAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIALABcACIAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAG8AYgBcACIALABcACIATQBhAHQAaABcACIALABcACIAQgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYgBcACIALABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZQBcACIALABcACIASABpAHMAdABvAHIAeQBcACIALABcACIAQgBcACIAfQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBoAGkAZgB0AEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAWwBzAGgAaQBmAHQAXwBiAHkAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABhAHIAcgBhAHkAcwAgAC8AIABzAGMAYQBsAGEAcgBzACAAaABhAG4AZABsAGUAZAAgAGIAeQAgAFMAaABpAGYAdAC7A1wAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALABTAGgAaQBmAHQAuwMoAGEAcgByAGEAeQBfADIARAAsACAAcwBoAGkAZgB0AF8AYgB5ACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAYQByAGUAIABjAGkAcgBjAHUAbABhAHIAbAB5ACAAcwBoAGkAZgB0AGUAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDKABTAGgAaQBmAHQAuwMoAFMARQBRAFUARQBOAEMARQAoAGgAKQAsACAAcwBoAGkAZgB0AF8AYgB5ACkALAAsAHcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGkAbgBkAGkAYwBlAHMAIAByAGUAbQBhAGkAbgAgAGYAaQB4AGUAZABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ARwByAGkAZAC7AygAYQByAHIAYQB5AF8AMgBEACwAIAAxACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABJAE4ARABFAFgAKABhAHIAcgBhAHkAXwAyAEQALAAgAGkALAAgAGoAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADMAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABFAG0AYgBlAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABTAGUAbABlAGMAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQBtAGIAZQBkAHMAIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGEAIAAyAEQAIABoAG8AcwB0ACAAYQByAHIAYQB5ACAAYQB0ACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgBcAG4AIAAgACAAIABpAG4AZABlAHgALgAgAEUAbQBiAGUAZAC7AyAAcwB1AHAAcABvAHIAdABzACAAcwBjAGEAbABhAHIAcwAsACAAMQBEACAAYQByAHIAYQB5AHMALAAgAGEAbgBkACAAMgBEACAAYQByAHIAYQB5AHMALgAgAFQAaABlACAAZQBtAGIAZQBkAGQAZQBkACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAGkAcwAgAGEAdQB0AG8AbQBhAHQAaQBjAGEAbABsAHkAIABlAHgAcABhAG4AZABlAGQAIABhAHMAIABuAGUAZQBkAGUAZAAgAHQAbwAgAG0AYQBpAG4AdABhAGkAbgAgAHIAZQBjAHQAYQBuAGcAdQBsAGEAcgBpAHQAeQAgAGEAbgBkACAAYQB2AG8AaQBkAFwAbgAgACAAIAAgAGoAYQBnAGcAZQBkACAAcgBlAHMAdQBsAHQAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMQBEACAAbwByACAAMgBEACAAaABvAHMAdAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQAgACAAIAAtACAAQQByAHIAYQB5ACAAdABvACAAZQBtAGIAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGgAbwBzAHQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAHIAbwB3AF8AaQBuAGQAZQB4AF0AIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHIAbwB3ACAAcABvAHMAaQB0AGkAbwBuACAAZgBvAHIAIABpAG4AcwBlAHIAdABpAG8AbgAuAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAYwBvAGwAdQBtAG4AIABwAG8AcwBpAHQAaQBvAG4AIABmAG8AcgAgAGkAbgBzAGUAcgB0AGkAbwBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAASQBmACAAYgBvAHQAaAAgAGEAcgBlACAAcwB1AHAAcABsAGkAZQBkACwAIAByAG8AdwBfAGkAbgBkAGUAeAAgAHQAYQBrAGUAcwAgAHAAcgBlAGMAZQBkAGUAbgBjAGUALgBcAG4AXABuAE4AdQBhAG4AYwBlAHMAOgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGUAeABwAGEAbgBkACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkAIAB3AGgAZQBuACAAaQBuAHMAZQByAHQAZQBkACAAYgB5ACAAcgBvAHcAXwBpAG4AZABlAHgALAAgAHYAZQByAHQAaQBjAGEAbABsAHkAIAB3AGgAZQBuAFwAbgAgACAAIAAgACAAIABpAG4AcwBlAHIAdABlAGQAIABiAHkAIABjAG8AbABfAGkAbgBkAGUAeAAuAFwAbgAgACAAIAAgACIgIAAxAEQALwAyAEQAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkAIABpAG4AcAB1AHQAcwAgAHQAaABhAHQAIABkAG8AIABuAG8AdAAgAG0AYQB0AGMAaAAgAGgAbwBzAHQAIAB3AGkAZAB0AGgALwBoAGUAaQBnAGgAdAAgAGEAcgBlACAAcABhAGQAZABlAGQAXABuACAAIAAgACAAIAAgAHcAaQB0AGgAIABcACIAXAAiACAAdABvACAAbQBhAGkAbgB0AGEAaQBuACAAcgBlAGMAdABhAG4AZwB1AGwAYQByAGkAdAB5AC4AXABuACAAIAAgACAAIiAgAFwAIgAjAFIATwBXAC8AQwBPAEwALQBJAE4ARABFAFgAXAAiACAAaQBzACAAcgBlAHQAdQByAG4AZQBkACAAZgBvAHIAIABuAG8AbgARIG4AdQBtAGUAcgBpAGMAIABvAHIAIABvAHUAdAARIG8AZgARIGIAbwB1AG4AZABzACAAaQBuAGQAaQBjAGUAcwAuAFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYwBhAG4AbgBvAHQAIABzAGUAcgB2AGUAIABhAHMAIABoAG8AcwB0ACAAYQByAHIAYQB5AHMAOwAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiACAAaQBzACAAcgBlAHQAdQByAG4AZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAbQBiAGUAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAHIAbwB3AF8AaQBuAGQAZQB4AF0ALABcAG4AIAAgACAAIABbAGMAbwBsAF8AaQBuAGQAZQB4AF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABIAG8AcwB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAG0AYgBlAGQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAgiAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3AIIgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGUAbQBiAGUAZABfAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQByAGEAbQBlAHQAZQByACAAcAByAGUAcwBlAG4AYwBlAFwAbgAgACAAIAAgAFIAbwB3AEUAbQBiAGUAZAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAXwBpAG4AZABlAHgAKQApACwAXABuACAAIAAgACAAQwBvAGwARQBtAGIAZQBkAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABjAG8AbABfAGkAbgBkAGUAeAApACkALABcAG4AIAAgACAAIABSAEMARQBtAGIAZQBkAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABSAG8AdwBFAG0AYgBlAGQAPwAsACAAQwBvAGwARQBtAGIAZQBkAD8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AdgBhAGwAaQBkACAAZQBtAGIAZQBkACAAcwBpAHoAZQAgACgAZQBtAGIAZQBkACAAbABhAHIAZwBlAHIAIAB0AGgAYQBuACAAaABvAHMAdAApAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARQBtAGIAZQBkAD8ALAAgACAAIAAgACAAIABJAEYAKABBAE4ARAAoAFIAbwB3AEUAbQBiAGUAZAA/ACwAIAB3AIIgIAA+ACAAdwApACwAIABUAFIAVQBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABDAG8AbABFAG0AYgBlAGQAPwAsACAAaACCICAAPgAgAGgAKQAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABSAEMARQBtAGIAZQBkAD8ALAAgAE8AUgAoAGgAgiAgAD4AIABoACwAIAB3AIIgIAA+ACAAdwApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEEATABTAEUAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEkAZAB4AD8ALAAgACAAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAByAG8AdwBfAGkAbgBkAGUAeAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBfAGkAbgBkAGUAeAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAcgBvAHcAXwBpAG4AZABlAHgAIAA8ACAAMQAsACAAcgBvAHcAXwBpAG4AZABlAHgAIAA+ACAAaAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAXwBpAG4AZABlAHgAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGMAbwBsAF8AaQBuAGQAZQB4ACAAPAAgADEALAAgAGMAbwBsAF8AaQBuAGQAZQB4ACAAPgAgAHcAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAASABvAHMAdAAgAGMAYQBuAG4AbwB0ACAAYgBlACAAcwBjAGEAbABhAHIAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEkAZAB4AD8ALAAgAFwAIgAjAFIATwBXAC8AQwBPAEwALQBJAE4ARABFAFgAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABFAG0AYgBlAGQAPwAsACAAXAAiACMARQBNAEIARQBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgAHYAZQByAHQAaQBjAGEAbAAgAGkAbgBzAGUAcgB0AGkAbwBuACAAdQBuAGwAZQBzAHMAIABvAG4AbAB5ACAAYwBvAGwAXwBpAG4AZABlAHgAIABpAHMAIABwAHIAbwB2AGkAZABlAGQAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAAIAAgAE8AUgAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBfAGkAbgBkAGUAeAApACkALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAXwBpAG4AZABlAHgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAGMAawAgAGYAdQBuAGMAdABpAG8AbgBcAG4AIAAgACAAIABTAHQAYQBjAGsAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABWAFMAVABBAEMASwAsACAASABTAFQAQQBDAEsAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAYQBsAGEAcgAgAGUAbQBiAGUAZAA/AFwAbgAgACAAIAAgAEkAcwBJAG4AYwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAgiAgAD0AIAAxACwAIAB3AIIgIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBzAGUAcgB0AGkAbwBuACAAaQBuAGQAZQB4AFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgAHIAbwB3AF8AaQBuAGQAZQB4ACwAIABjAG8AbABfAGkAbgBkAGUAeAApACwAXABuACAAIAAgACAAbQBhAHgAXwBkAGkAbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAIAArACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABoACwAIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBwAGwAaQB0ACAAaABvAHMAdAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABiAGwAbwBjAGsAXwBhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAGEAcgByAGEAeQAsACAAaQBkAHgAIAAtACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAGEAcgByAGEAeQAsACAALAAgAGkAZAB4ACAALQAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAGIAbABvAGMAawBfAGIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQByAHIAYQB5ACwAIAAtACgAMQAgACsAIABoACAALQAgAGkAZAB4ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABhAHIAcgBhAHkALAAgACwAIAAtACgAMQAgACsAIAB3ACAALQAgAGkAZAB4ACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAG4AZABhAHIAZAAgAGkAbgBzAGUAcgB0AGkAbwBuACAAKAB0AG8AcAAgAG8AcgAgAGIAbwB0AHQAbwBtACkAXABuACAAIAAgACAASQBzAFMAdABhAG4AZABhAHIAZAA/ACwAIAAgACAAIAAgACAAIAAgAE8AUgAoAGkAZAB4ACAAPQAgADEALAAgAGkAZAB4ACAAPQAgAG0AYQB4AF8AZABpAG0AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AcwBpAG8AbgAgAHIAdQBsAGUAcwBcAG4AIAAgACAAIABlAHgAcABfAHMAYwBhAGwAYQByAF8AdwBpAGQAdABoACwAIAAgACAARQBYAFAAQQBOAEQAKABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALAAgACwAIAB3ACwAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGUAeABwAF8AdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAGUAbQBiAGUAZABfAGEAcgByAGEAeQAsACAALAAgAHcALAAgAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgAGUAeABwAF8AcwBjAGEAbABhAHIAXwBoAGUAaQBnAGgAdAAsACAAIABFAFgAUABBAE4ARAAoAGUAbQBiAGUAZABfAGEAcgByAGEAeQAsACAAaAAsACAALAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAZQB4AHAAXwBoAGUAaQBnAGgAdAAsACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACwAIABoACwAIAAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBkACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACAAdABvACAAYQB2AG8AaQBkACAAZABpAG0AZQBuAHMAaQBvAG4AIABtAGkAcwBtAGEAdABjAGgAXABuACAAIAAgACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAgACoAIABJAHMASQBuAGMAUwBjAGEAbABhAHIAPwAsACAAZQB4AHAAXwBzAGMAYQBsAGEAcgBfAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAZQB4AHAAXwB3AGkAZAB0AGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAG4AYwBTAGMAYQBsAGEAcgA/ACwAIABlAHgAcABfAHMAYwBhAGwAYQByAF8AaABlAGkAZwBoAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZQB4AHAAXwBoAGUAaQBnAGgAdAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBuAGQAYQByAGQAIAB2AHMAIABtAGkAZAARIGEAcgByAGEAeQAgAGkAbgBzAGUAcgB0AGkAbwBuAFwAbgAgACAAIAAgAHMAdABhAG4AZABhAHIAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABpAGQAeAAgAD0AIAAxACwAUwB0AGEAYwBrALsDKABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALAAgAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AGEAYwBrALsDKABhAHIAcgBhAHkALAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAAcwB0AGEAYwBrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdABhAGMAawC7AygAYgBsAG8AYwBrAF8AYQAsACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACwAIABiAGwAbwBjAGsAXwBiACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAHQAYQBuAGQAYQByAGQAPwAsACAAcwB0AGEAbgBkAGEAcgBkACwAIABzAHQAYQBjAGsAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAASwBlAGUAcABSAG8AdwBzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUwBlAGwAZQBjAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAdAByAGUAYQBrALsDLAAgAEMAbwB1AG4AdABkAG8AdwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdABhAGkAbgBzACAAcgBvAHcAcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgBhAHMAZQBkACAAbwBuACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuAHMALgAgAEEAIABwAG8AcwBpAHQAaQB2AGUAXABuACAAIAAgACAAawBlAGUAcAAgAHYAYQBsAHUAZQAgAHIAZQB0AGEAaQBuAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAHQAaABlACAAdABvAHAAIABvAGYAIABlAGEAYwBoACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AOwAgAGEAIABuAGUAZwBhAHQAaQB2AGUAIABrAGUAZQBwAFwAbgAgACAAIAAgAHYAYQBsAHUAZQAgAHIAZQB0AGEAaQBuAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAHQAaABlACAAYgBvAHQAdABvAG0ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABrAGUAZQBwACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAGkAbgB0AGUAZwBlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAD4AIAAwACAAkiEgAGsAZQBlAHAAIABmAHIAbwBtACAAdABvAHAAIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA8ACAAMAAgAJIhIABrAGUAZQBwACAAZgByAG8AbQAgAGIAbwB0AHQAbwBtACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAgACAALQAgAFMAdQBiAGcAcgBvAHUAcAAgAGwAYQBiAGUAbABzACAAKABzAGEAbQBlACAAaABlAGkAZwBoAHQAIABhAHMAIABhAHIAcgBhAHkAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAG8AbgBsAHkAIABvAG4AZQAgAHMAdQBiAGcAcgBvAHUAcAAgAGUAeABpAHMAdABzACwAIABEAFIATwBQACgAKQAgAGkAcwAgAHUAcwBlAGQAIABhAHMAIABhACAAZgBhAHMAdAAgAHAAYQB0AGgALgBcAG4AIAAgACAAIAAiICAAawBlAGUAcAAgAG0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIAOwAgAHQAZQB4AHQAIABvAHIAIAB2AGUAYwB0AG8AcgAgAGkAbgBwAHUAdABzACAAaABhAGwAdAAgAHcAaQB0AGgAIABhAG4AIABlAHIAcgBvAHIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASwBlAGUAcABSAG8AdwBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGsAZQBlAHAALABcAG4AIAAgACAAIABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAHUAYgBnAHIAbwB1AHAAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABVAE4ASQBRAFUARQAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEQAaQBzAGMAYQByAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIABrAGUAZQBwACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPAA+ACAAUgBPAFcAUwAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAASQBzAFQAZQB4AHQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAawBlAGUAcAApACwAXABuACAAIAAgACAATgBvAHQAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgATgBPAFQAKABJAHMAVABlAHgAdAA/ACkALAAgAEMATwBVAE4AVABBACgAawBlAGUAcAApACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAHMAYwBlAG4AYQByAGkAbwBzACwAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAASQBzAFQAZQB4AHQAPwAsACAATgBvAHQAUwBjAGEAbABhAHIAPwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAcgByAG8AcgAgAGgAYQBuAGQAbABpAG4AZwBcAG4AIAAgACAAIABoAGEAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAcwBjAGUAbgBhAHIAaQBvAHMAKQAsAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIAOwAgAFwAIgAjAFQARQBYAFQAIQBcACIAOwAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiAH0ALABcAG4AIAAgACAAIABhAGwAZQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBSAFIAQQBZAFQATwBUAEUAWABUACgARgBJAEwAVABFAFIAKABlAHIAcgBvAHIAcwAsACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgADAAKQApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAE8AbgBlAFMAdQBiAEcAcgBvAHUAcAA/ACwAIABEAGkAcwBjAGEAcgBkACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAaABhAGwAdAAsACAAYQBsAGUAcgB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuADoAIAArAHQAbwBwACwAIAATIGIAbwB0AHQAbwBtAFwAbgAgACAAIAAgAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAawBlAGUAcAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAdQBuACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABhAHMAYwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AHIAZQBhAGsAuwMoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAAZABlAHMAYwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMAbwB1AG4AdABkAG8AdwBuALsDKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUAKQAsAFwAbgAgACAAIAAgAGsAZQBlAHAALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAEIAUwAoAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGkAbgBkAGUAeAAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAIAA9ACAALQAxACwAIABkAGUAcwBjAGUAbgBkACwAIABhAHMAYwBlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQBlAHAAIAByAG8AdwBzACAAdwBoAGUAcgBlACAAaQBuAGQAZQB4ACAAZCIgAGsAZQBlAHAAXABuACAAIAAgACAAawBlAGUAcAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAZAB4ACAAPAA9ACAAawBlAGUAcAAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGsAZQBlAHAAPwApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAASwBlAGUAcABDAG8AbABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUwBlAGwAZQBjAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAdAByAGUAYQBrALsDLAAgAEMAbwB1AG4AdABkAG8AdwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdABhAGkAbgBzACAAYwBvAGwAdQBtAG4AcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgBhAHMAZQBkACAAbwBuACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuAHMALgAgAEEAIABwAG8AcwBpAHQAaQB2AGUAXABuACAAIAAgACAAawBlAGUAcAAgAHYAYQBsAHUAZQAgAHIAZQB0AGEAaQBuAHMAIABjAG8AbAB1AG0AbgBzACAAZgByAG8AbQAgAHQAaABlACAAbABlAGYAdAAgAG8AZgAgAGUAYQBjAGgAIABzAHUAYgBnAHIAbwB1AHAAIAByAHUAbgA7ACAAYQAgAG4AZQBnAGEAdABpAHYAZQBcAG4AIAAgACAAIABrAGUAZQBwACAAdgBhAGwAdQBlACAAcgBlAHQAYQBpAG4AcwAgAGMAbwBsAHUAbQBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGkAZwBoAHQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABrAGUAZQBwACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAGkAbgB0AGUAZwBlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAD4AIAAwACAAkiEgAGsAZQBlAHAAIABmAHIAbwBtACAAbABlAGYAdAAgAG8AZgAgAGUAYQBjAGgAIAByAHUAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADwAIAAwACAAkiEgAGsAZQBlAHAAIABmAHIAbwBtACAAcgBpAGcAaAB0ACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAgACAALQAgAFMAdQBiAGcAcgBvAHUAcAAgAGwAYQBiAGUAbABzACAAKABzAGEAbQBlACAAdwBpAGQAdABoACAAYQBzACAAYQByAHIAYQB5ACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIABvAG4AbAB5ACAAbwBuAGUAIABzAHUAYgBnAHIAbwB1AHAAIABlAHgAaQBzAHQAcwAsACAARABSAE8AUAAoACkAIABpAHMAIAB1AHMAZQBkACAAYQBzACAAYQAgAGYAYQBzAHQAIABwAGEAdABoAC4AXABuACAAIAAgACAAIiAgAGsAZQBlAHAAIABtAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByADsAIAB0AGUAeAB0ACAAbwByACAAdgBlAGMAdABvAHIAIABpAG4AcAB1AHQAcwAgAGgAYQBsAHQAIAB3AGkAdABoACAAYQBuACAAZQByAHIAbwByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEsAZQBlAHAAQwBvAGwAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABrAGUAZQBwACwAXABuACAAIAAgACAAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwB1AGIAZwByAG8AdQBwACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAATwBuAGUAUwB1AGIARwByAG8AdQBwAD8ALAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAVQBOAEkAUQBVAEUAKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALAAgADEAKQApACAAPQAgADEALABcAG4AIAAgACAAIABEAGkAcwBjAGEAcgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGEAcgByAGEAeQAsACAALAAgAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAA8AD4AIABDAE8ATABVAE0ATgBTACgAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkALABcAG4AIAAgACAAIABJAHMAVABlAHgAdAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABrAGUAZQBwACkALABcAG4AIAAgACAAIABOAG8AdABTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAE8AVAAoAEkAcwBUAGUAeAB0AD8AKQAsACAAQwBPAFUATgBUAEEAKABrAGUAZQBwACkAIAA+ACAAMQApACwAXABuACAAIAAgACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABJAHMAVABlAHgAdAA/ACwAIABOAG8AdABTAGMAYQBsAGEAcgA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQByAHIAbwByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAGgAYQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABzAGMAZQBuAGEAcgBpAG8AcwApACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgA7ACAAXAAiACMAVABFAFgAVAAhAFwAIgA7ACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIAfQAsAFwAbgAgACAAIAAgAGEAbABlAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAFIAUgBBAFkAVABPAFQARQBYAFQAKABGAEkATABUAEUAUgAoAGUAcgByAG8AcgBzACwAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAMAApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgATwBuAGUAUwB1AGIARwByAG8AdQBwAD8ALAAgAEQAaQBzAGMAYQByAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABoAGEAbAB0ACwAIABhAGwAZQByAHQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgACsAbABlAGYAdAAsACAAEyByAGkAZwBoAHQAXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABrAGUAZQBwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgB1AG4AIABpAG4AZABpAGMAZQBzACAAKABoAG8AcgBpAHoAbwBuAHQAYQBsACkAXABuACAAIAAgACAAYQBzAGMAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAGUAYQBrALsDKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALAAgAFQAUgBVAEUAKQAsAFwAbgAgACAAIAAgAGQAZQBzAGMAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAG8AdQBuAHQAZABvAHcAbgC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACwAIABUAFIAVQBFACkALABcAG4AIAAgACAAIABrAGUAZQBwACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBCAFMAKABrAGUAZQBwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABpAG4AZABlAHgAIABiAGEAcwBlAGQAIABvAG4AIABzAGkAZwBuAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABzACAAPQAgAC0AMQAsACAAZABlAHMAYwBlAG4AZAAsACAAYQBzAGMAZQBuAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABLAGUAZQBwACAAYwBvAGwAdQBtAG4AcwAgAHcAaABlAHIAZQAgAGkAbgBkAGUAeAAgAGQiIABrAGUAZQBwAFwAbgAgACAAIAAgAGsAZQBlAHAAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAGQAeAAgADwAPQAgAGsAZQBlAHAALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAdQBtAG4AESB3AGkAcwBlACAAZgBpAGwAdABlAHIAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYQByAHIAYQB5ACwAIABrAGUAZQBwAD8AKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEIAbABvAGMAawBNAGEAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABWAGEAbABpAGQAYQB0AGUAQgBsAG8AYwBrAE0AYQBwALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcwBoAGEAcABlAHMAIABhACAAYQByAHIAYQB5AF8AMgBEACAAcgBvAHcAESB3AGkAcwBlACAAbwByACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAaQBuAHQAbwAgAGIAbABvAGMAawBzACAAbwBmACAAcwBpAHoAZQBcAG4AIAAgACAAIABkAGUAcAB0AGgAIADXACAAdwBpAGQAdABoAC4AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzACAAYQBsAGwAbwB3ACAAcgBlAHMAaABhAHAAaQBuAGcAIABiAHkAIABjAG8AbAB1AG0AbgAgAGEAbgBkAFwAbgAgACAAIAAgAHQAcgBhAG4AcwBwAG8AcwBpAG4AZwAgAHQAaABlACAAYQBuAGMAaABvAHIAIABnAHIAaQBkAHMAIAB1AHMAZQBkACAAdABvACAAZwBlAG4AZQByAGEAdABlACAAYgBsAG8AYwBrACAAaQBuAGQAaQBjAGUAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5AF8AMgBEAC4AXABuACAAIAAgACAAZABlAHAAdABoACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAEgAZQBpAGcAaAB0ACAAbwBmACAAZQBhAGMAaAAgAGIAbABvAGMAawAuAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABXAGkAZAB0AGgAIABvAGYAIABlAGEAYwBoACAAYgBsAG8AYwBrAC4AXABuACAAIAAgACAAWwByAGUAXwBzAGgAYQBwAGUAXwBiAHkAXwBjAG8AbAB1AG0AbgA/AF0ALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQBzAGgAYQBwAGUAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAOwAgAGUAbABzAGUAIAByAG8AdwARIHcAaQBzAGUALgBcAG4AIAAgACAAIABbAHQAcgBhAG4AcwBwAG8AcwBlAF8AYQBuAGMAaABvAHIAcwA/AF0AIAAtACAASQBmACAAVABSAFUARQAsACAAdAByAGEAbgBzAHAAbwBzAGUAIAByAG8AdwAvAGMAbwBsAHUAbQBuACAAYQBuAGMAaABvAHIAIABnAHIAaQBkAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABWAGEAbABpAGQAYQB0AGUAQgBsAG8AYwBrAE0AYQBwALsDIABlAG4AZgBvAHIAYwBlAHMAIABzAHQAcgBpAGMAdAAgAHMAaABhAHAAZQAgAGMAbwBtAHAAYQB0AGkAYgBpAGwAaQB0AHkALgBcAG4AIAAgACAAIAAiICAAQQBuAGMAaABvAHIAcwAgAGQAZQBmAGkAbgBlACAAdABoAGUAIAB0AG8AcAARIGwAZQBmAHQAIABjAG8AcgBuAGUAcgAgAG8AZgAgAGUAYQBjAGgAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhAGwAdwBhAHkAcwAgAHIAZQBjAHQAYQBuAGcAdQBsAGEAcgAgAGEAbgBkACAAZgB1AGwAbAB5ACAAdABpAGwAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEIAbABvAGMAawBNAGEAcAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABkAGUAcAB0AGgALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALABcAG4AIAAgACAAIABbAHIAZQBfAHMAaABhAHAAZQBfAGIAeQBfAGMAbwBsAHUAbQBuAD8AXQAsAFwAbgAgACAAIAAgAFsAdAByAGEAbgBzAHAAbwBzAGUAXwBhAG4AYwBoAG8AcgBzAD8AXQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGUAIABpAG4AcAB1AHQAcwAgAGIAZQBmAG8AcgBlACAAcgBlAHMAaABhAHAAaQBuAGcAXABuACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAEIAbABvAGMAawBNAGEAcAC7AygAYQByAHIAYQB5AF8AMgBEACwAIABkAGUAcAB0AGgALAAgAHcAaQBkAHQAaAAsACAAcgBlAF8AcwBoAGEAcABlAF8AYgB5AF8AYwBvAGwAdQBtAG4APwAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABCAGwAbwBjAGsAIABnAHIAaQBkACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAVQBQACgAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIARAApACAALwAgAGQAZQBwAHQAaAAsACAAMAApACwAIAAgACAAIAAgAC8ALwAgAGIAbABvAGMAawAgAHIAbwB3AHMAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEAFUAUAAoAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAgAC8AIAB3AGkAZAB0AGgALAAgADAAKQAsACAAIAAvAC8AIABiAGwAbwBjAGsAIABjAG8AbAB1AG0AbgBzAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwAIAAsACAAMQAsACAAZABlAHAAdABoACkAIAAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAIAB5ACwAIAAxACwAIAAwACkALABcAG4AXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHkALAAgADEALAAgAHcAaQBkAHQAaAApACAAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwAIAAsACAAMQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAHIAbwB3AF8AYQBuAGMAaABvAHIALAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAdAByAGEAbgBzAHAAbwBzAGUAXwBhAG4AYwBoAG8AcgBzAD8AKQAsACAAaQAsACAAVABSAEEATgBTAFAATwBTAEUAKABpACkAKQAsAFwAbgAgACAAIAAgAGMAbwBsAF8AYQBuAGMAaABvAHIALAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAdAByAGEAbgBzAHAAbwBzAGUAXwBhAG4AYwBoAG8AcgBzAD8AKQAsACAAagAsACAAVABSAEEATgBTAFAATwBTAEUAKABqACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGkAbgBkAGkAYwBlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABiAGwAbwBjAGsAXABuACAAIAAgACAAcgBvAHcAXwBpAG4AZABpAGMAZQBzACwAIAAgACAAVABPAEMATwBMACgAcgBvAHcAXwBhAG4AYwBoAG8AcgApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAE4AVAAoAFMARQBRAFUARQBOAEMARQAoACwAIABkAGUAcAB0AGgAIAAqACAAdwBpAGQAdABoACwAIAAwACwAIAAxACAALwAgAHcAaQBkAHQAaAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAYgBsAG8AYwBrAFwAbgAgACAAIAAgAGMAbwBsAF8AaQBuAGQAaQBjAGUAcwAsACAAIAAgAFQATwBDAE8ATAAoAGMAbwBsAF8AYQBuAGMAaABvAHIAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAFIATwBXACgASQBGAFMAKABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgAKQAsACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHcAaQBkAHQAaAAsACAAMAAsACAAMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYgBsAG8AYwBrAHMAXABuACAAIAAgACAAcgBlAHMAaABhAHAAZQBkACwAIAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIAByAG8AdwBfAGkAbgBkAGkAYwBlAHMALAAgAGMAbwBsAF8AaQBuAGQAaQBjAGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQAgAHIAZQBzAGgAYQBwAGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAASQBGACgAcgBlAF8AcwBoAGEAcABlAF8AYgB5AF8AYwBvAGwAdQBtAG4APwAsACAAVABSAEEATgBTAFAATwBTAEUAKAByAGUAcwBoAGEAcABlAGQAKQAsACAAcgBlAHMAaABhAHAAZQBkACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBABEgQwBPAFIARQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBCAGwAbwBjAGsATQBhAHAAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABDAG8AcgBlACAAVgBhAGwAaQBkAGEAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAHMAIABpAG4AcAB1AHQAcwAgAGYAbwByACAAQgBsAG8AYwBrAE0AYQBwALsDLgAgAEUAbgBzAHUAcgBlAHMAIAB0AGgAZQAgAGEAcgByAGEAeQBfADIARAAgAGkAcwAgAHYAYQBsAGkAZAAsACAAYgBsAG8AYwBrACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABhAHIAZQAgAGMAbwBtAHAAYQB0AGkAYgBsAGUALAAgAHIAZQBzAGgAYQBwAGkAbgBnACAAdwBpAGwAbAAgAG4AbwB0ACAAcwBwAGkAbABsACwAIABhAG4AZAAgAHQAaABlACAAYgBsAG8AYwBrACAAZwBlAG8AbQBlAHQAcgB5ACAAdABpAGwAZQBzACAAdABoAGUAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAYwBsAGUAYQBuAGwAeQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5AF8AMgBEAC4AXABuACAAIAAgACAAZABlAHAAdABoACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAEIAbABvAGMAawAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAdwBpAGQAdABoACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAEIAbABvAGMAawAgAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgAHIAZQBfAHMAaABhAHAAZQBfAGIAeQBfAGMAbwBsAHUAbQBuAD8AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGwAYQBnACAAZgBvAHIAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIAByAGUAcwBoAGEAcABlAC4AXABuACAAIAAgACAAbwBuAF8AdgBhAGwAaQBkACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAEUAeABwAHIAZQBzAHMAaQBvAG4AIAB0AG8AIABlAHYAYQBsAHUAYQB0AGUAIAB3AGgAZQBuACAAdgBhAGwAaQBkAGEAdABpAG8AbgAgAHAAYQBzAHMAZQBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBuAHMAdQByAGUAcwAgAGEAcgByAGEAeQBfADIARAAgAGkAcwAgAGEAIABwAHIAbwBwAGUAcgAgAGEAcgByAGEAeQAgACgAVABZAFAARQAgAD0AIAA2ADQAKQAuAFwAbgAgACAAIAAgACIgIABQAHIAZQB2AGUAbgB0AHMAIABzAHAAaQBsAGwAESByAGkAcwBrACAAdwBoAGUAbgAgAHIAZQBzAGgAYQBwAGkAbgBnACAAYgB5ACAAYwBvAGwAdQBtAG4ALgBcAG4AIAAgACAAIAAiICAARQBuAGYAbwByAGMAZQBzACAAZQB4AGEAYwB0ACAAZABpAHYAaQBzAGkAYgBpAGwAaQB0AHkAIABiAHkAIABiAGwAbwBjAGsAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAIiAgAFIAZQBqAGUAYwB0AHMAIABpAG4AdgBhAGwAaQBkACAAbwByACAAdABlAHgAdAAgAGIAbABvAGMAawAgAHMAaQB6AGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBWAGEAbABpAGQAYQB0AGUAQgBsAG8AYwBrAE0AYQBwALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAsAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgAHIAZQBfAHMAaABhAHAAZQBfAGIAeQBfAGMAbwBsAHUAbQBuAD8ALABcAG4AIAAgACAAIABvAG4AXwB2AGEAbABpAGQALABcAG4AXABuACAAIAAgACAALwAvACAATQB1AHMAdAAgAGIAZQAgAGEAbgAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABJAEYAKABOAE8AVAAoAFQAWQBQAEUAKABhAHIAcgBhAHkAXwAyAEQAKQAgAD0AIAA2ADQAKQAsAFwAIgAjAGEAcgByAGEAeQBfADIARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAaQBsAGwAESByAGkAcwBrACAAdwBoAGUAbgAgAHIAZQBzAGgAYQBwAGkAbgBnACAAYgB5ACAAYwBvAGwAdQBtAG4AXABuACAAIAAgACAASQBGACgAKAByAGUAXwBzAGgAYQBwAGUAXwBiAHkAXwBjAG8AbAB1AG0AbgA/ACkAIAAqACAAXABuACAAIAAgACAAIAAgACAAKABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkAIAAqACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACAALwAgACgAdwBpAGQAdABoACAAKgAgAGQAZQBwAHQAaAApAF4AMgAgAD4AIAAxADYAMwA4ADQAKQAsAFwAIgAjAFMAUABJAEwATAAtAFIASQBTAEsAIQBcACIALABcAG4AXABuACAAIAAgACAALwAvACAATQB1AHMAdAAgAHQAaQBsAGUAIABjAGwAZQBhAG4AbAB5AFwAbgAgACAAIAAgAEkARgAoACgATQBPAEQAKABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALAAgAGQAZQBwAHQAaAApACAAPAA+ACAAMAApACAAKwAoAE0ATwBEACgAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwAIAB3AGkAZAB0AGgAKQAgADwAPgAgADAAKQAsAFwAIgAjAEIATABPAEMASwAgAE0ASQBTAE0AQQBUAEMASAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGwAbwBjAGsAIABzAGkAegBlACAAbQB1AHMAdAAgAGIAZQAgAHYAYQBsAGkAZABcAG4AIAAgACAAIABJAEYAKABPAFIAKABBAE4ARAAoAHcAaQBkAHQAaAAgAD0AIAAxACwAIABkAGUAcAB0AGgAIAA9ACAAMQApACwAZABlAHAAdABoACAAPgAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwBpAGQAdABoACAAPgAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAEkAUwBUAEUAWABUACgAdwBpAGQAdABoACkALABJAFMAVABFAFgAVAAoAGQAZQBwAHQAaAApACkALABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAbABsACAAYwBoAGUAYwBrAHMAIABwAGEAcwBzAGUAZABcAG4AIAAgACAAIABvAG4AXwB2AGEAbABpAGQAXABuACAAIAAgACAAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEMAbwBuAHYAbwBsAHYAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADIAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUABlAHIAZgBvAHIAbQBzACAAYQAgAHMAbABpAGQAaQBuAGcAESB3AGkAbgBkAG8AdwAgAGMAbwBuAHYAbwBsAHUAdABpAG8AbgAgAG8AdgBlAHIAIABhACAAMgBEACAAYQByAHIAYQB5ACAAdQBzAGkAbgBnACAAYQAgADIARAAgAGsAZQByAG4AZQBsAC4AXABuACAAIAAgACAARQBhAGMAaAAgAHcAaQBuAGQAbwB3ACAAZQB4AHQAcgBhAGMAdABlAGQAIABmAHIAbwBtACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABoAGEAcwAgAHQAaABlACAAcwBhAG0AZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABhAHMAIAB0AGgAZQBcAG4AIAAgACAAIABrAGUAcgBuAGUAbAAuACAAQQAgAHIAZQBkAHUAYwBlAHIAIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAZQBhAGMAaAAgAHcAaQBuAGQAbwB3ACAAdABvACAAcAByAG8AZAB1AGMAZQAgAHQAaABlACAAbwB1AHQAcAB1AHQALgBcAG4AXABuACAAIAAgACAASQBmACAAbgBvACAAcgBlAGQAdQBjAGUAcgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAHMAdQBwAHAAbABpAGUAZAAsACAAQwBvAG4AdgBvAGwAdgBlALsDIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABhACAAZABvAHQAESBwAHIAbwBkAHUAYwB0AFwAbgAgACAAIAAgAHIAZQBkAHUAYwBlAHIAOgAgAFMAVQBNACgAdgAgACoAIABrAGUAcgBuAGUAbAApAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAHcAaABpAGMAaAAgAHQAaABlACAAawBlAHIAbgBlAGwAIABpAHMAIABhAHAAcABsAGkAZQBkAC4AXABuACAAIAAgACAAawBlAHIAbgBlAGwAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAGQAZQBmAGkAbgBpAG4AZwAgAHQAaABlACAAcwBsAGkAZABpAG4AZwAgAHcAaQBuAGQAbwB3ACAAZABpAG0AZQBuAHMAaQBvAG4AcwAuAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAByAGUAZAB1AGMAZQByACAATABBAE0AQgBEAEEAIABhAGMAYwBlAHAAdABpAG4AZwAgAGEAIABzAGkAbgBnAGwAZQAgAGEAcgByAGEAeQAgAGEAcgBnAHUAbQBlAG4AdAAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABTAFUATQAoAHYAIAAqACAAawBlAHIAbgBlAGwAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBLAEUAUgBOAEUATAAhAFwAIgAgAGkAZgAgAHQAaABlACAAawBlAHIAbgBlAGwAIABpAHMAIABsAGEAcgBnAGUAcgAgAHQAaABhAG4AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgACIgIABSAGUAdAB1AHIAbgBzACAAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACAAaQBmACAAdABoAGUAIAByAGUAZAB1AGMAZQByACAAaQBzACAAbgBvAHQAIABhACAAdgBhAGwAaQBkACAATABBAE0AQgBEAEEALgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgADEA1wAxACAAYQByAHIAYQB5AHMAIABhAG4AZAAgAG0AYQBwAHAAZQBkACAAdABoAHIAbwB1AGcAaAAgAHQAaABlACAAcgBlAGQAdQBjAGUAcgAuAFwAbgAgACAAIAAgACIgIABSAGUAZAB1AGMAZQByACAAYgBlAGgAYQB2AGkAbwByACAAaQBzACAAdQBzAGUAcgARIGQAZQBmAGkAbgBlAGQAOwAgAGEAcgByAGEAeQBzACAAbgBlAGUAZAAgAG4AbwB0ACAAYgBlACAAbgB1AG0AZQByAGkAYwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AbgB2AG8AbAB2AGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQQByAHIAYQB5ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABLAGUAcgBuAGUAbAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaABfACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABrAGUAcgBuAGUAbAApACwAXABuACAAIAAgACAAdwBfACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABrAGUAcgBuAGUAbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQByAG4AZQBsACAAbQB1AHMAdAAgAGYAaQB0ACAAaQBuAHMAaQBkAGUAIABhAHIAcgBhAHkAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABLAGUAcgBuAGUAbAA/ACwAIAAgACAAIAAgAE8AUgAoAGgAXwAgAD4AIABoACwAIAB3AF8AIAA+ACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIASwBlAHIAbgBlAGwAPwAsACAAIAAgACAAQQBOAEQAKABoAF8AIAA9ACAAMQAsACAAdwBfACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBhAHUAbAB0ACAAcgBlAGQAdQBjAGUAcgAgAD0AIABkAG8AdAAgAHAAcgBvAGQAdQBjAHQAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgB1AG4AYwB0AGkAbwBuACkALABMAEEATQBCAEQAQQAoAHYALAAgAFMAVQBNACgAdgAgACoAIABrAGUAcgBuAGUAbAApACkALABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA9ACAAMQAyADgAIACSISAAdgBhAGwAaQBkACAATABBAE0AQgBEAEEAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4APwAsACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAbwByACAAcwBjAGEAbABhAHIAESBrAGUAcgBuAGUAbAAgAGMAYQBzAGUAIACSISAAcwBpAG0AcABsAGUAIABNAEEAUABcAG4AIAAgACAAIABTAHQAYQBuAGQAYQByAGQATQBhAHAALAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAEEAUAAoAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACkAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEsAZQByAG4AZQBsAD8ALAAgAFwAIgAjAEsARQBSAE4ARQBMACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABGAG4APwAsACAAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAAoAEkAcwBTAGMAYQBsAGEAcgA/ACkAIAArACAAKABJAHMAUwBjAGEAbABhAHIASwBlAHIAbgBlAGwAPwApACwAUwB0AGEAbgBkAGEAcgBkAE0AYQBwACgAKQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGEAbgBjAGgAXwByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABoACAALQAgAGgAXwAgACsAIAAxACwAXABuACAAIAAgACAAYQBuAGMAaABfAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAIAAtACAAdwBfACAAKwAgADEALABcAG4AXABuACAAIAAgACAALwAvACAAQQBuAGMAaABvAHIAIABpAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAEkARgAoAGEAbgBjAGgAXwByACAAPQAgADEALAAgADEALABTAEUAUQBVAEUATgBDAEUAKABhAG4AYwBoAF8AcgApACkALAAgACwAIABhAG4AYwBoAF8AYwApACkALAAgACAAIAAgAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABJAEYAKABhAG4AYwBoAF8AYwAgAD0AIAAxACwAIAAxACwAIABTAEUAUQBVAEUATgBDAEUAKAAsAGEAbgBjAGgAXwBjACkAKQAsACAAYQBuAGMAaABfAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFcAaQBuAGQAbwB3ACAAcgBlAGQAdQBjAGUAcgBcAG4AIAAgACAAIABCAGwAbwBjAGsAQQBnAGcAuwMsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABpAF8ALAAgAGoAXwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsALAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgAGkAXwAgAC0AIAAxACwAIABqAF8AIAAtACAAMQApACwAIABoAF8ALAAgAHcAXwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AG8AdABhAGwALAAgACAAZgB1AG4AYwB0AGkAbwBuACgAYgBsAG8AYwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAbwB0AGEAbAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAcgBlAGQAdQBjAGUAcgAgAHQAbwAgAGUAYQBjAGgAIAB3AGkAbgBkAG8AdwBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABpACgAKQAsACAAagAoACkALAAgAEIAbABvAGMAawBBAGcAZwC7AykALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEAOABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEYAbwBsAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABTAHQAcgB1AGMAdAB1AHIAYQBsACAATQBhAHAAcABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQQBsAGkAZwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAZAB1AGMAZQBzACAAcgBlAGMAbwByAGQAcwAgAGkAbgAgAGEAbgAgAGEAcgByAGEAeQAgAGIAeQAgAGcAcgBvAHUAcABpAG4AZwAgAGkAZABlAG4AdABpAGMAYQBsACAAcgBvAHcAcwAgAGEAbgBkACAAYQBwAHAAbAB5AGkAbgBnACAAYQBuAFwAbgAgACAAIAAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAgAHQAbwAgAHQAaABlACAAYwBvAHIAcgBlAHMAcABvAG4AZABpAG4AZwAgAGUAbgB0AHIAaQBlAHMAIABpAG4AIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIABJAGYAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAgAGkAcwAgAG8AbQBpAHQAdABlAGQALAAgAEYAbwBsAGQAuwMgAHUAcwBlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGYAaQBlAGwAZAAgAG8AZgAgAGUAYQBjAGgAIAByAGUAYwBvAHIAZAAgAGEAcwBcAG4AIAAgACAAIAB0AGgAZQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAHYAZQBjAHQAbwByAC4AIABUAGgAaQBzACAAbQBvAGQAZQAgAGkAcwAgAGkAbgB0AGUAbgBkAGUAZAAgAGYAbwByACAAQwBPAFUATgBUAEEAOwAgAG8AdABoAGUAcgAgAHIAZQBkAHUAYwBlAHIAcwBcAG4AIAAgACAAIABtAGEAeQAgAHAAcgBvAGQAdQBjAGUAIAByAGUAcwB1AGwAdABzACAAYgB1AHQAIABhAHIAZQAgAG4AbwB0ACAAbQBlAGEAbgBpAG4AZwBmAHUAbAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAHIAbwB3AHMAIABkAGUAZgBpAG4AZQAgAGcAcgBvAHUAcABpAG4AZwAgAGsAZQB5AHMALgBcAG4AIAAgACAAIABbAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5AF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGEAZwBnAHIAZQBnAGEAdABlAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAAIAAgACAAIAAtACAAUgBlAGQAdQBjAGUAcgAgAEwAQQBNAEIARABBACAAYQBjAGMAZQBwAHQAaQBuAGcAIABhACAAMQBEACAAdgBlAGMAdABvAHIAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAQwBPAFUATgBUAEEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEYAbwBsAGQAuwMgAGgAYQBsAHQAcwAgAHcAaQB0AGgAIAAjAFYAQQBMAFUARQAhACAAaQBmACAAYQByAHIAYQB5ACAAYQBuAGQAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAgAGgAZQBpAGcAaAB0AHMAIABkAGkAZgBmAGUAcgAuAFwAbgAgACAAIAAgACIgIABGAG8AbABkALsDIABoAGEAbAB0AHMAIAB3AGkAdABoACAAIwBGAFUATgBDAFQASQBPAE4AIQAgAGkAZgAgAHIAZQBkAHUAYwBlAHIAIABpAHMAIABuAG8AdAAgAGEAIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQAuAFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4AuwMgAGMAYQBuAG8AbgBpAGMAYQBsAGkAegBlAHMAIAByAGUAYwBvAHIAZABzACAAcwBvACAAaQBkAGUAbgB0AGkAYwBhAGwAIAByAG8AdwBzACAAZwByAG8AdQBwACAAYwBsAGUAYQBuAGwAeQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBGAG8AbABkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAXQAsAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABlAGYAYQB1AGwAdAAgAHYAYQBsAHUAZQBzACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACwAVABBAEsARQAoAGEAcgByAGEAeQAsACAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAZAB1AGMAZQByAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsACAAIAAgACAASQBGACgATwBSACgASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsACAASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACkALABDAE8AVQBOAFQAQQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4ASQBGACgAQQBOAEQAKABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkAIAA8AD4AIABSAE8AVwBTACgAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQApACwAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEMAYQBuAG8AbgBpAGMAYQBsACAAZwByAG8AdQBwAGkAbgBnACAAawBlAHkAcwBcAG4AIAAgACAAIABhAGwAaQBnAG4AZQBkACwAIAAgACAAIAAgAEEAbABpAGcAbgC7AygAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBnAGcAcgBlAGcAYQB0AGkAbwBuAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAARwBSAE8AVQBQAEIAWQAoAGEAbABpAGcAbgBlAGQALAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgACwAIAAwACkALABcAG4AXABuACAAIAAgACAAYQBnAGcAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADkAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABKAG8AaQBuADIARAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABKAG8AaQBuAHMAIABhAGwAbAAgAG4AbwBuABEgZQBtAHAAdAB5ACAAdgBhAGwAdQBlAHMAIABhAGMAcgBvAHMAcwAgADIAIAB0AG8AIAA0ACAAaQBkAGUAbgB0AGkAYwBhAGwAbAB5ABEgcwBoAGEAcABlAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAgAHUAcwBpAG4AZwBcAG4AIAAgACAAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAIABkAGUAbABpAG0AaQB0AGUAcgAuACAAVABoAGUAIABvAHUAdABwAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIAB0AGgAZQAgAGkAbgBwAHUAdABzAC4AXABuAFwAbgAgACAAIAAgAEEAIABjAGUAbABsACAAaQBzACAAYwBvAG4AcwBpAGQAZQByAGUAZAAgABwgZQBtAHAAdAB5AB0gIABpAGYAIABpAHQAIABtAGEAdABjAGgAZQBzACAAQQBOAFkAIABvAGYAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABMAEUATgAoAGMAZQBsAGwAKQAgAD0AIAAwAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAGMAZQBsAGwAIAA9ACAARgBBAEwAUwBFAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAGMAZQBsAGwAIAA9ACAAaQBnAG4AbwByAGUAIAAoAHUAcwBlAHIAESBzAHAAZQBjAGkAZgBpAGUAZAApAFwAbgBcAG4AIAAgACAAIABKAG8AaQBuADIARAC7AyAAaQBzACAAYQBuACAAYQBsAHQAZQByAG4AYQB0AGkAdgBlACAAdABvACAAbgBlAHMAdABlAGQAIABNAEEAUAAgAGwAbwBnAGkAYwAgAGYAbwByACAAZQBsAGUAbQBlAG4AdAARIHcAaQBzAGUAIABqAG8AaQBuAGkAbgBnAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0AIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAZABlAGwAaQBtAGkAdABlAHIAXQAgAC0AIABEAGUAbABpAG0AaQB0AGUAcgAgAGYAbwByACAAagBvAGkAbgBpAG4AZwAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABcACIALAAgAFwAIgApAC4AXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACAAIAAgACAALQAgAFYAYQBsAHUAZQAgAHQAcgBlAGEAdABlAGQAIABhAHMAIABlAG0AcAB0AHkAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkAcwAgAG0AdQBzAHQAIABoAGEAdgBlACAAaQBkAGUAbgB0AGkAYwBhAGwAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAIiAgAEUAbQBwAHQAeQAgAGMAZQBsAGwAcwAgAGEAcgBlACAAcwBrAGkAcABwAGUAZAA7ACAAbgBvACAAdAByAGEAaQBsAGkAbgBnACAAZABlAGwAaQBtAGkAdABlAHIAIABpAHMAIABhAGQAZABlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASgBvAGkAbgAyAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8ANABdACwAXABuACAAIAAgACAAWwBkAGUAbABpAG0AaQB0AGUAcgBdACwAXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAASQBuAGMAbAB1AGQAZQAzAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkAKQAsAFwAbgAgACAAIAAgAEkAbgBjAGwAdQBkAGUANAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkALAAgAEYAQQBMAFMARQAsACAAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8ANAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACwAIABGAEEATABTAEUALAAgAGEAcgByAGEAeQBfADQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAbABpAG0AaQB0AGUAcgAgACsAIABpAGcAbgBvAHIAZQBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABkAGUAbABpAG0AaQB0AGUAcgApACwAIABcACIALAAgAFwAIgAsACAAZABlAGwAaQBtAGkAdABlAHIAKQAsAFwAbgAgACAAIAAgAGkAZwBuAG8AcgBlACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZwBuAG8AcgBlACkALAAgAFwAIgBcACIALAAgAGkAZwBuAG8AcgBlACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMQApACwAXABuAFwAbgAgACAAIAAgAGgAgiAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACwAXABuACAAIAAgACAAdwCCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AXABuACAAIAAgACAAaACDICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAzACkALABcAG4AIAAgACAAIAB3AIMgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADMAKQAsAFwAbgBcAG4AIAAgACAAIABoAIQgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADQAKQAsAFwAbgAgACAAIAAgAHcAhCAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuACAAYwBoAGUAYwBrAHMAXABuACAAIAAgACAAUwBfADIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGgAIAA8AD4AIABoAIIgLAAgAHcAIAA8AD4AIAB3AIIgKQAsAFwAbgAgACAAIAAgAFMAXwAzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAG4AYwBsAHUAZABlADMAPwAgACoAIABPAFIAKABoACAAPAA+ACAAaACDICwAIAB3ACAAPAA+ACAAdwCDICkALABcAG4AIAAgACAAIABTAF8ANAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAGMAbAB1AGQAZQA0AD8AIAAqACAATwBSACgAaAAgADwAPgAgAGgAhCAsACAAdwAgADwAPgAgAHcAhCApACwAXABuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABPAFIAKABTAF8AMgAsACAAUwBfADMALAAgAFMAXwA0ACkALABcAG4AXABuACAAIAAgACAASQBGACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AYwBjAHUAcABhAG4AYwB5ACAAcAByAGUAZABpAGMAYQB0AGUAXABuACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDLAAgACAATABBAE0AQgBEAEEAKABhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABhACAAPAA+ACAARgBBAEwAUwBFACkAIAAqACAAKABMAEUATgAoAGEAKQAgADwAPgAgADAAKQAgACoAIAAoAGEAIAA8AD4AIABpAGcAbgBvAHIAZQApACkALABcAG4AXABuACAAIAAgACAAbQBfADEALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwAxACkALABcAG4AIAAgACAAIABtAF8AMgAsACAAIAAgACAAIAAgACAAIABPAGMAYwB1AHAAaQBlAGQAuwMoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAG0AXwAzACwAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AygAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAbQBfADQALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASgBvAGkAbgAgAGkAbgAgAG8AcgBkAGUAcgAsACAAcwBrAGkAcABwAGkAbgBnACAAZQBtAHAAdABpAGUAcwBcAG4AIAAgACAAIABqAG8AaQBuAGUAZAAsACAAIAAgACAAIABJAEYAKABtAF8AMQAsACAAYQByAHIAYQB5AF8AMQAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACAAJgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8AMgAsACAAYQByAHIAYQB5AF8AMgAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACAAJgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG0AXwAzACwAIABhAHIAcgBhAHkAXwAzACAAJgAgAGQAZQBsAGkAbQBpAHQAZQByACwAIABcACIAXAAiACkAIAAmAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8ANAAsACAAYQByAHIAYQB5AF8ANAAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABqAG8AaQBuAGUAZAAsAGQAZQBsAGkAbQBpAHQAZQByACwALQAxACwAMQAsACwAagBvAGkAbgBlAGQAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAjACMAIAAwADUAIAAtACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAgACoALwBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVABoAGkAcwAgAHMAZQBjAHQAaQBvAG4AIABjAG8AbgB0AGEAaQBuAHMAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHQAaABhAHQAIAByAGUAcABsAGkAYwBhAHQAZQAgAGEAcgByAGEAeQBzACAAYQBsAG8AbgBnACAAcgBvAHcAcwAsACAAYwBvAGwAdQBtAG4AcwAsACAAbwByACAAYgBvAHQAaAAuAFwAbgBcAG4ARgB1AG4AYwB0AGkAbwBuAHMAOgBcAG4AIAAgACAAIAAiICAARQBjAGgAbwC7AyAAIAAgACAAIAAgACAAIAAgACAALQAgAFIAZQBwAGUAYQB0ACAAZQBhAGMAaAAgAGUAbABlAG0AZQBuAHQAIABpAG4AIABhACAAMQBEACAAYQByAHIAYQB5ACAAYgB5ACAAYwBvAHUAbgB0AC4AXABuACAAIAAgACAAIiAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMgACAAIAAgAC0AIABSAGUAcABlAGEAdAAgAGUAYQBjAGgAIAByAG8AdwAgAGIAeQAgAGEAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQALgBcAG4AIAAgACAAIAAiICAAUgBlAHAAZQBhAHQAQwBvAGwAcwC7AyAAIAAgACAALQAgAFIAZQBwAGUAYQB0ACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAYgB5ACAAYQAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdAAuAFwAbgAgACAAIAAgACIgIABUAGUAcwBzAGUAbABsAGEAdABlALsDIAAgACAAIAAtACAAVABpAGwAZQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AIABtAG8AZAB1AGwAYQByACAAZgBhAHMAaABpAG8AbgAsACAAcwB1AHAAcABvAHIAdABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABhAHIAdABpAGEAbAAgAHQAaQBsAGUAcwAgAHcAaABlAG4AIABvAHUAdABwAHUAdAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAG8AIABuAG8AdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAHYAaQBkAGUAIABlAHYAZQBuAGwAeQAuAFwAbgBcAG4AXABuAFwAbgBcACIAUAByAGUAcwBlAG4AdAAgAHMAdQBjAGMAZQBzAHMAIABpAHMAIABhAG4AIABlAGMAaABvACAAbwBmACAAYQAgAHAAYQBzAHQAIAB0AHIAaQB1AG0AcABoAC4AIABGAGEAaQBsAHUAcgBlACAAaQBzACAAcgBlAGQAdQBuAGQAYQBuAHQALgBcACIAIAAtACAAUgBlAHAAZQB0AHQAbwBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFIAUAAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABFAGMAaABvALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABSAGUAcABlAHQAaQB0AGkAbwBuAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHAAZQBhAHQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgADEARAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAXABuACAAIAAgACAAbgB1AG0AZQByAGkAYwAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwByACAAcwBjAGEAbABhAHIAIAB0AG8AIABiAGUAIABlAGMAaABvAGUAZAAuAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAKABuAHUAbQBlAHIAaQBjACwAIABlIiAAMQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgADEA1wAxACAAYQByAHIAYQB5AHMALgBcAG4AIAAgACAAIAAiICAASQBmACAAcgBlAHAAZQBhAHQAIABoAGEAcwAgAGEAIABkAGkAZgBmAGUAcgBlAG4AdAAgAGwAZQBuAGcAdABoACAAdABoAGEAbgAgAHYAZQBjAHQAbwByACwAIAB0AGgAZQAgAGwAYQBzAHQAIAByAGUAcABlAGEAdAAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAaQBzACAAZQB4AHQAZQBuAGQAZQBkACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIAB2AGUAYwB0AG8AcgAgAGwAZQBuAGcAdABoAC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAaQBzACAAYQBsAHcAYQB5AHMAIABhACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAYwBoAG8AuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAdgBlAGMAdABvAHIALABcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAByAGUAcABlAGEAdAApACwAIAByAGUAcABlAGEAdAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAKQAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAFYAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAZQBjAHQAbwByACkALABcAG4AIAAgACAAIABSAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIAAoAGUAeAB0AGUAbgBkACAAbABhAHMAdAAgAHYAYQBsAHUAZQAgAGkAZgAgAG4AZQBlAGQAZQBkACkAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABWAGgAIAA8AD4AIABSAGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAByAGUAcABlAGEAdAAsACAAVgBoACwAIAAsACAAQABUAEEASwBFACgAcgBlAHAAZQBhAHQALAAgAC0AMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGEAcwBlACAAaQBuAGQAZQB4AFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAUgBPAFcAUwAoAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4AGkAbQB1AG0AIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAdQBpAGwAZAAgAGkAbgBkAGUAeAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABUAE8AQwBPAEwAKABJAEYAKABTAEkARwBOACgAcgAgAC0AIABTAEUAUQBVAEUATgBDAEUAKAAsACAAbQAsACAAMAAsACAAKQApACAAPQAgADEALABpACwATgBBACgAKQApACwAMgApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB2AGUAYwB0AG8AcgAsACAAaQBkAHgAKAApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAMAAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBwAGUAYQB0AHMAIABlAGEAYwBoACAAcgBvAHcAIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5ACAAYQBjAGMAbwByAGQAaQBuAGcAIAB0AG8AIABhACAAdgBlAGMAdABvAHIAIABvAGYAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAuACAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHMAdQBwAHAAbwByAHQAZQBkAC4AIABSAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAbQB1AHMAdAAgAGIAZQAgAG4AdQBtAGUAcgBpAGMAXABuACAAIAAgACAAYQBuAGQAIABlIiAAMQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIAByAG8AdwBzACAAdwBpAGwAbAAgAGIAZQAgAHIAZQBwAGUAYQB0AGUAZAAuAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAKABuAHUAbQBlAHIAaQBjACwAIABlIiAAMQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAcgBlAHAAZQBhAHQAIABoAGEAcwAgAGYAZQB3AGUAcgAgAGUAbgB0AHIAaQBlAHMAIAB0AGgAYQBuACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMALAAgAHQAaABlACAAbABhAHMAdAAgAHIAZQBwAGUAYQB0AFwAbgAgACAAIAAgACAAIAB2AGEAbAB1AGUAIABpAHMAIABlAHgAdABlAG4AZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQAgAGEAcgByAGEAeQAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAcAByAGUAcwBlAHIAdgBlAHMAIAB0AGgAZQAgAGMAbwBsAHUAbQBuACAAcwB0AHIAdQBjAHQAdQByAGUAIABvAGYAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBSAGUAcABlAGEAdABSAG8AdwBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAXABuAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAHIAZQBwAGUAYQB0ACkALAAgAHIAZQBwAGUAYQB0ACAAPAA9ACAAMAApACwAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcgBlAHAAZQBhAHQAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABBAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAFIAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAZQBuAGQAIAByAGUAcABlAGEAdAAgAHYAZQBjAHQAbwByACAAaQBmACAAbgBlAGUAZABlAGQAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABBAGgAIAA8AD4AIABSAGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAByAGUAcABlAGEAdAAsACAAQQBoACwAIAAsACAAQABUAEEASwBFACgAcgBlAHAAZQBhAHQALAAgAC0AMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGEAcwBlACAAcgBvAHcAIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAUgBPAFcAUwAoAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4AGkAbQB1AG0AIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAdQBpAGwAZAAgAGkAbgBkAGUAeAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABUAE8AQwBPAEwAKABJAEYAKABTAEkARwBOACgAcgAgAC0AIABTAEUAUQBVAEUATgBDAEUAKAAsACAAbQAsACAAMAApACkAIAA9ACAAMQAsAGkALABOAEEAKAApACkALAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABhAHIAcgBhAHkALAAgAGkAZAB4ACgAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUgBQADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFIAZQBwAGUAYQB0AEMAbwBsAHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAFIAZQBwAGUAdABpAHQAaQBvAG4AXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcABlAGEAdABzACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAbwBmACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmACAAcgBlAHAAZQBhAHQAXABuACAAIAAgACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAIABuAHUAbQBlAHIAaQBjAFwAbgAgACAAIAAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAYwBvAGwAdQBtAG4AcwAgAHcAaQBsAGwAIABiAGUAIAByAGUAcABlAGEAdABlAGQALgBcAG4AIAAgACAAIAByAGUAcABlAGEAdAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgACgAbgB1AG0AZQByAGkAYwAsACAAZSIgADEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAHIAZQBwAGUAYQB0ACAAaABhAHMAIABmAGUAdwBlAHIAIABlAG4AdAByAGkAZQBzACAAdABoAGEAbgAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACwAIAB0AGgAZQAgAGwAYQBzAHQAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIAAgACAAdgBhAGwAdQBlACAAaQBzACAAZQB4AHQAZQBuAGQAZQBkACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABhAHIAcgBhAHkAIAB3AGkAZAB0AGgALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABwAHIAZQBzAGUAcgB2AGUAcwAgAHQAaABlACAAcgBvAHcAIABzAHQAcgB1AGMAdAB1AHIAZQAgAG8AZgAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBwAGUAYQB0AEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAcgBlAHAAZQBhAHQALABcAG4AXABuAEkARgAoAE8AUgAoAEkAUwBUAEUAWABUACgAcgBlAHAAZQBhAHQAKQAsACAAcgBlAHAAZQBhAHQAIAA8AD0AIAAwACkALABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIAByAGUAcABlAGEAdAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAEEAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAUgBoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdABlAG4AZAAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIABpAGYAIABuAGUAZQBkAGUAZABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEAdwAgADwAPgAgAFIAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAHIAZQBwAGUAYQB0ACwAIABBAHcALAAgACwAIABAAFQAQQBLAEUAKAByAGUAcABlAGEAdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAYQBzAGUAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKABSAE8AVwBTACgAYwApACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHgAaQBtAHUAbQAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgAG0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABjACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgB1AGkAbABkACAAaQBuAGQAZQB4ACAAdgBlAGMAdABvAHIAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFQATwBDAE8ATAAoAEkARgAoAFMASQBHAE4AKABjACAALQAgAFMARQBRAFUARQBOAEMARQAoACwAIABtACwAIAAwACkAKQAgAD0AIAAxACwAaQAsAE4AQQAoACkAKQAsADIAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAGEAcgByAGEAeQAsACAAaQBkAHgAKAApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVABlAHMAcwBlAGwAbABhAHQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFQARwByAGkAZAC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAbQBvAGQAdQBsAGEAcgAgAHQAZQBzAHMAZQBsAGwAYQB0AGkAbwBuACAAbwBmACAAYQAgADIARAAgAHAAYQB0AHQAZQByAG4AIABkAGUAZgBpAG4AZQBkACAAYgB5ACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAgANcAIABuAGUAdwBfAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgAFQAaABlACAAcABhAHQAdABlAHIAbgAgAGkAcwAgAHIAZQBwAGUAYQB0AGUAZAAgAHUAcwBpAG4AZwAgAG0AbwBkAHUAbABhAHIAIAByAG8AdwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AIABjAHkAYwBsAGUAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAdABoAGUAXABuACAAIAAgACAAcABhAHQAdABlAHIAbgAZIHMAIABvAHcAbgAgAGQAaQBtAGUAbgBzAGkAbwBuAHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgACgAMQBEACAAYQByAHIAYQB5AHMAIABhAGMAYwBlAHAAdABlAGQALAAgAHMAYwBhAGwAYQByAHMAIABhAHIAZQAgAGYAbwByAGIAaQBkAGQAZQBuACkALgBcAG4AIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGkAbgAgAHQAaABlACAAbwB1AHQAcAB1AHQAIAB0AGUAcwBzAGUAbABsAGEAdABpAG8AbgAuAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHQAZQBzAHMAZQBsAGwAYQB0AGkAbwBuAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUABlAHIAZgBvAHIAbQBzACAAbQBvAGQAdQBsAGEAcgAgAHIAZQBwAGUAdABpAHQAaQBvAG4AIAB1AHMAaQBuAGcAIABUAEcAcgBpAGQAuwMgAGYAbwByACAAcgBvAHcALwBjAG8AbAB1AG0AbgAgAGMAeQBjAGwAaQBuAGcALgBcAG4AIAAgACAAIAAiICAAUwB1AHAAcABvAHIAdABzACAAcABhAHIAdABpAGEAbAAgAHQAaQBsAGUAcwAgAHcAaABlAG4AIABuAGUAdwAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABhAHIAZQAgAG4AbwB0ACAAbQB1AGwAdABpAHAAbABlAHMAIABvAGYAXABuACAAIAAgACAAIAAgAHQAaABlACAAcABhAHQAdABlAHIAbgAgAHMAaQB6AGUALgBcAG4AIAAgACAAIAAiICAAUgBlAGoAZQBjAHQAcwAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVABlAHMAcwBlAGwAbABhAHQAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACwAXABuACAAIAAgACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUABhAHQAdABlAHIAbgAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcABhAHQAdABlAHIAbgApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAcABhAHQAdABlAHIAbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAZABlAHQAZQBjAHQAaQBvAG4AXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABuAGUAdwAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAIAAgACAAIABJAE4ARABFAFgAKABuAGUAdwBfAGgAZQBpAGcAaAB0ACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIABuAGUAdwBfAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAG4AZQB3AF8AdwBpAGQAdABoACwAIAAxACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAATgBvAEMAaABhAG4AZwBlAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAdwAgAD0AIABuAGUAdwBfAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQASABXAD8ALAAgACAAIAAgACAATwBSACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAgADwAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAIAA8AD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAG4AZQB3AF8AaABlAGkAZwBoAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABuAGUAdwBfAHcAaQBkAHQAaAApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AQwBoAGEAbgBnAGUAPwAsACAAcABhAHQAdABlAHIAbgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEgAVwA/ACwAIABcACIAIwBOAEUAVwAtAEgARQBJAEcASABUAC8AVwBJAEQAVABIACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AdQB0AHAAdQB0ACAAZwBlAG8AbQBlAHQAcgB5ACAAcABsAGEAYwBlAGgAbwBsAGQAZQByAFwAbgAgACAAIAAgAGUAeABwAF8AcwBoAGEAcABlACwAIAAgACAAIABFAFgAUABBAE4ARAAoADAALAAgAG4AZQB3AF8AaABlAGkAZwBoAHQALAAgAG4AZQB3AF8AdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBvAGQAdQBsAGEAcgAgAHIAbwB3AC8AYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEcAcgBpAGQAuwMoAGUAeABwAF8AcwBoAGEAcABlACwAIABoACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABHAHIAaQBkALsDKABlAHgAcABfAHMAaABhAHAAZQAsACAAdwAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAZQBzAHMAZQBsAGwAYQB0AGUAZAAgAG8AdQB0AHAAdQB0AFwAbgAgACAAIAAgAHQAZQBzAHMALAAgACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKABwAGEAdAB0AGUAcgBuACwAIABpACwAIABqACkALABcAG4AXABuACAAIAAgACAAdABlAHMAcwBcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAjACMAIAAwADYAIAAtACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACAAKgAvAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIABpAHMAIABhACAAYwBvAGwAbABlAGMAdABpAG8AbgAgAG8AZgAgAGYAdQBuAGMAdABpAG8AbgBzACAAZgBvAHIAIABlAGwAZQBnAGEAbgB0ACAAcwBlAHEAdQBlAG4AYwBpAG4AZwAsAFwAbgAgACAAIAAgAGMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAGEAbgBhAGwAeQBzAGkAcwAsACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAESBiAGEAcwBlAGQAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4ALAAgAGEAbgBkACAAcwB0AGEAdABpAHMAdABpAGMAcwAuAFwAbgAgACAAIAAgAFQAaABpAHMAIABtAG8AZAB1AGwAZQAgAGUAeAB0AGUAbgBkAHMAIAB0AGgAZQAgAGMAYQBwAGEAYgBpAGwAaQB0AGkAZQBzACAAbwBmACAAbgBhAHQAaQB2AGUAIABFAHgAYwBlAGwAIABmAHUAbgBjAHQAaQBvAG4AcwBcAG4AIAAgACAAIAAoAGUALgBnAC4ALAAgAE0AbwBkAGUAuwMgAGMAYQBuACAAcgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AbwBzAHQAIABmAHIAZQBxAHUAZQBuAHQAIABuAHUAbQBlAHIAaQBjAGEAbAAgAG8AcgAgAHQAZQB4AHQAIAB2AGEAbAB1AGUAcwApAC4AXABuAFwAbgAgACAAIAAgAFMAdQBiABEgYwBhAHQAZQBnAG8AcgBpAGUAcwA6AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABTAGUAcQB1AGUAbgBjAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AHIAZQBhAGsAuwMsACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMsACAASQBuAHMAdABhAG4AYwBlALsDLAAgAFcAYQB2AGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgB5AEQAaQBhAGcAuwMsACAARABpAGEAZwBNAGEAcAC7AywAIABEAGkAYQBnAEkAbgBkAGUAeAC7AywAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwMsACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AywAIABRAHUAYQBkAHcAaQBzAGUAuwMsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwByAG8AdQBwAGIAeQBCAGkAbgC7AywAIABHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMsACAAUABpAHYAbwB0AGIAeQBDAGEAdAC7AywAXABuAFwAdABcAHQAXAB0ACAAIABHAHIAbwB1AHAASQBuAGQAZQB4ALsDLAAgAE8AYwBjAHUAcgByAGUAbgBjAGUAuwMsACAATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAATgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEcAcgBhAGkAbgC7AywAIABNAG8AbwByAGUAQQBnAGcAuwMsACAATQBvAG8AcgBlAFMAZQBsAGUAYwB0ALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFMAdABhAHQAaQBzAHQAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAGkAcwB0AG8AZwByAGEAbQC7AywAIABNAG8AZABlALsDLAAgAFoAbwBuAGUAUwB0AGEAdAC7A1wAbgAqAC8AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAHQAcgBlAGEAawC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABTAGUAcQB1AGUAbgBjAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbQBwAHUAdABlAHMAIABzAHQAcgBlAGEAawAgAGMAbwB1AG4AdABzACAAbwBmACAAYwBvAG4AcwBlAGMAdQB0AGkAdgBlACAAaQBkAGUAbgB0AGkAYwBhAGwAIAB2AGEAbAB1AGUAcwAgAGkAbgAgAGEAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABTAHQAcgBlAGEAawBzACAAaQBuAGMAcgBlAG0AZQBuAHQAIABmAG8AcgB3AGEAcgBkACAAKAAxACwAIAAyACwAIAAzACwAIAAmICkAIAB3AGgAZQBuAGUAdgBlAHIAIAB0AGgAZQAgAGMAdQByAHIAZQBuAHQAIABlAGwAZQBtAGUAbgB0ACAAbQBhAHQAYwBoAGUAcwBcAG4AIAAgACAAIAB0AGgAZQAgAHAAcgBlAHYAaQBvAHUAcwAgAG8AbgBlAC4AIABGAG8AcgAgADIARAAgAGEAcgByAGEAeQBzACwAIABzAHQAcgBlAGEAawBzACAAYQByAGUAIABjAG8AbQBwAHUAdABlAGQAIAByAG8AdwARIG0AYQBqAG8AcgAgAGIAeQAgAGQAZQBmAGEAdQBsAHQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0AIAAgACAAIAAgACAALQAgAEYAbwByACAAMQBEACAAYQByAHIAYQB5AHMALAAgAGMAbwBtAHAAdQB0AGUAIABzAHQAcgBlAGEAawBzACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAaQBuAHMAdABlAGEAZAAgAG8AZgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAbwB3ABEgdwBpAHMAZQAuACAASQBnAG4AbwByAGUAZAAgAGYAbwByACAAMgBEACAAYQByAHIAYQB5AHMALgBcAG4AIAAgACAAIABbAEkAbgBjAGwAdQBkAGUAXwBTAHkAbQBiAG8AbAA/AF0AIAAgAC0AIABJAGYAIABUAFIAVQBFACwAIABhAHAAcABlAG4AZAAgAHQAaABlACAAcwB5AG0AYgBvAGwAIAB0AG8AIAB0AGgAZQAgAHMAdAByAGUAYQBrACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABlAC4AZwAuACwAIABXALcAMQAsACAAVwC3ADIALAAgAEwAtwAxACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAcgBlAHQAdQByAG4AIAB0AGgAZQBtAHMAZQBsAHYAZQBzAC4AXABuACAAIAAgACAAIiAgADIARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHIAbwB3ABEgbQBhAGoAbwByACwAIABwAHIAbwBjAGUAcwBzAGUAZAAsACAAdABoAGUAbgAgAHIAZQBzAHQAbwByAGUAZAAuAFwAbgAgACAAIAAgACIgIABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AIABvAG4AbAB5ACAAYQBwAHAAbABpAGUAcwAgAHQAbwAgADEARAAgAGEAcgByAGEAeQBzAC4AXABuACAAIAAgACAAIiAgAEkAbgBjAGwAdQBkAGUAXwBTAHkAbQBiAG8AbAA/ACAAdQBzAGUAcwAgAFUATgBJAEMASABBAFIAKAAxADgAMwApACAAKAC3ACkAIABhAHMAIAB0AGgAZQAgAHMAZQBwAGEAcgBhAHQAbwByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAdAByAGUAYQBrALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0ALABcAG4AIAAgACAAIABbAEkAbgBjAGwAdQBkAGUAXwBTAHkAbQBiAG8AbAA/AF0ALABcAG4AXABuAEkARgAoAEEATgBEACgAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPQAgADEALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgAD0AIAAxACkALABhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA+ACAAMQAsACAAdwAgAD4AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgADIARAAgAJIhIAAxAEQAXABuACAAIAAgACAAYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMgBEAD8ALAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACwAIABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgAgACgAbwBuAGwAeQAgAHIAZQBsAGUAdgBhAG4AdAAgAGYAbwByACAAMQBEACkAXABuACAAIAAgACAATgBvAEQAaQByAD8ALAAgACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAEgAbwByAGkAegBvAG4AdABhAGwAPwApACwAXABuACAAIAAgACAAZgBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8ARABpAHIAPwAsACAAVgBTAFQAQQBDAEsALAAgAEgAUwBUAEEAQwBLACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AcABhAHIAZQAgAHcAaQB0AGgAIABwAHIAZQB2AGkAbwB1AHMAIABlAGwAZQBtAGUAbgB0AFwAbgAgACAAIAAgAGsAZQBwAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAEQAaQByAD8ALAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgAC0AMQApACwAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAYQByAHIAYQB5ACAAPQAgAGYAbgAoAFwAIgBvAG0AaQB0AFwAIgAsACAAawBlAHAAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAYwBjAHUAbQB1AGwAYQB0AGUAIABzAHQAcgBlAGEAawAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGEAYwBjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBDAEEATgAoADAALABiAG8AbwBsACwATABBAE0AQgBEAEEAKABhACwAIAB2ACwASQBGACgAYQAgAD0AIAAwACwAIAAxACwAIABJAEYAKAB2ACwAIABhACAAKwAgADEALAAgADEAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABzAHkAbQBiAG8AbAAgAGkAbgBjAGwAdQBzAGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABJAG4AYwBsAHUAZABlAF8AUwB5AG0AYgBvAGwAPwApACwAYQBjAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQByAHIAYQB5ACAAJgAgAFUATgBJAEMASABBAFIAKAAxADgAMwApACAAJgAgAGEAYwBjACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgADIARAAgAHMAaABhAHAAZQAgAGkAZgAgAG4AZQBlAGQAZQBkAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgACAASQBGACgASQBzADIARAA/ACwAIABXAFIAQQBQAFIATwBXAFMAKAByAGUAcwB1AGwAdAAsACAAdwApACwAIAByAGUAcwB1AGwAdAApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEMAbwB1AG4AdABkAG8AdwBuALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAFMAZQBxAHUAZQBuAGMAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBvAHUAbgB0AGQAbwB3AG4AIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgB1AG4AcwAgAGkAbgAgAGEAIAAxAEQAIABhAHIAcgBhAHkALgAgAEUAYQBjAGgAIAByAHUAbgBcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAgAGQAbwB3AG4AIABmAHIAbwBtACAAaQB0AHMAIABsAGUAbgBnAHQAaAAgAHQAbwAgADEALgAgAEMAbwB1AG4AdABkAG8AdwBuALsDIABpAHMAIABtAG8AcwB0ACAAdQBzAGUAZgB1AGwAIAB3AGgAZQBuACAAdwBvAHIAawBpAG4AZwBcAG4AIAAgACAAIAB3AGkAdABoACAAcwBvAHIAdABlAGQAIAB2AGUAYwB0AG8AcgBzACAAYQBuAGQAIABpAHMAIAB0AGgAZQAgAG4AYQB0AHUAcgBhAGwAIAByAGUAdgBlAHIAcwBlACAAbwBmACAAUwB0AHIAZQBhAGsAuwMuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5AC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACAAIAAgACAALQAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAG8AdQB0AHAAdQB0ACAAaQBzACAAdgBlAHIAdABpAGMAYQBsAC4AIABJAGYAIABUAFIAVQBFACwAIABvAHUAdABwAHUAdAAgAGkAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHQAdQByAG4AZQBkACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABBAGwAdwBhAHkAcwAgAGYAbABhAHQAdABlAG4AcwAgAGkAbgBwAHUAdAAgAHQAbwAgAGEAIABzAGkAbgBnAGwAZQAgAGMAbwBsAHUAbQBuACAAYgBlAGYAbwByAGUAIABwAHIAbwBjAGUAcwBzAGkAbgBnAC4AXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AdQBuAHQAZABvAHcAbgC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACwAXABuAFwAbgBJAEYAKABBAE4ARAAoAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgAD0AIAAxACwAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAA9ACAAMQApACwAYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAEkAcwAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA+ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIAAyAEQAIACSISAAMQBEAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzADIARAA/ACwAIABUAE8AQwBPAEwAKABhAHIAcgBhAHkAKQAsACAAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AIAAoAG8AbgBsAHkAIAByAGUAbABlAHYAYQBuAHQAIABmAG8AcgAgADEARAApAFwAbgAgACAAIAAgAE4AbwBEAGkAcgA/ACwAIAAgACAAIAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQAsAFwAbgAgACAAIAAgAGYAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAEQAaQByAD8ALAAgAFYAUwBUAEEAQwBLACwAIABIAFMAVABBAEMASwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBtAHAAYQByAGUAIAB3AGkAdABoACAAcAByAGUAdgBpAG8AdQBzACAAZQBsAGUAbQBlAG4AdABcAG4AIAAgACAAIABrAGUAcAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBEAGkAcgA/ACwAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAtADEAKQAsACAARABSAE8AUAAoAGEAcgByAGEAeQAsACAALAAgAC0AMQApACkALABcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAcgByAGEAeQAgAD0AIABmAG4AKABcACIAbwBtAGkAdABcACIALAAgAGsAZQBwAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAGMAYwB1AG0AdQBsAGEAdABlACAAcwB0AHIAZQBhAGsAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABhAGMAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAQwBBAE4AKAAwACwAYgBvAG8AbAAsAEwAQQBNAEIARABBACgAYQAsACAAdgAsAEkARgAoAGEAIAA9ACAAMAAsACAAMQAsACAASQBGACgAdgAsACAAYQAgACsAIAAxACwAIAAxACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBoAGEAbgBnAGUAIABnAHIAbwB1AHAAcwBcAG4AIAAgACAAIABjAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAQwBBAE4AKAAwACwATgBPAFQAKABiAG8AbwBsACkALABTAFUATQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAbwByAHQAIABkAGUAcwBjAGUAbgBkAGkAbgBnAFwAbgAgACAAIAAgAHMAbwByAHQAZQBkACwAIAAgACAAIAAgACAAIAAgACAAUwBPAFIAVABCAFkAKABhAGMAYwAsAGMAZwAsADEALABhAGMAYwAsAC0AMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAHQAbwByAGUAIAAyAEQAIABzAGgAYQBwAGUAIABpAGYAIABuAGUAZQBkAGUAZABcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAyAEQAPwAsACAAVwBSAEEAUABSAE8AVwBTACgAcwBvAHIAdABlAGQALAAgAHcAKQAsACAAcwBvAHIAdABlAGQAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADEANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEkAbgBzAHQAYQBuAGMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAWwBHAFIAMAAzAF0AIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAUwBlAHEAdQBlAG4AYwBpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMsACAATQBHAHIAaQBkALsDLAAgAFMAdAByAGUAYQBrALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABPAGIAdABhAGkAbgAgAHQAaABlACAAaQBuAHMAdABhAG4AYwBlACAAbgB1AG0AYgBlAHIAcwAgAGYAbwByACAAdQBuAHMAbwByAHQAZQBkACAAdgBhAGwAdQBlAHMAIABpAG4AIABhACAAMQBEACAAYQByAHIAYQB5ACAAdwBpAHQAaAAgAG8AcAB0AGkAbwBuAHMAXABuACAAIAAgACAAZgBvAHIAIAByAGUAdAB1AHIAbgBpAG4AZwAgAGkAbgBzAHQAYQBuAGMAZQBzACAAZgBvAHIAIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAdgBlAGMAdABvAHIAcwAsACAAYQBuAGQAIABkAGkAcwBwAGwAYQB5AGkAbgBnACAAaQBuAHMAdABhAG4AYwBlAHMAIABpAG4AXABuACAAIAAgACAAZABlAHMAYwBlAG4AZABpAG4AZwAgAG8AcgBkAGUAcgAuAFwAbgAgACAAIAAgAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACAAIAAgACAAIAAgACAAIAAgACAALQAgACAAIAAxAEQAIABhAHIAcgBhAHkAIABpAG4AcAB1AHQAIAAoADIARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAApAFwAbgAgACAAIAAgAFsASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0AIAAgACAALQAgACAAIABJAGYAIABUAFIAVQBFACwAIABvAGIAdABhAGkAbgAgAGkAbgBzAHQAYQBuAGMAZQAgAG4AdQBtAGIAZQByAHMAIABmAG8AcgAgAGgAbwByAGkAegBvAG4AdABhAGwAIAB2AGUAYwB0AG8AcgBzAFwAbgAgACAAIAAgAFsARABlAHMAYwBlAG4AZAA/AF0AIAAgACAAIAAgACAALQAgACAAIABJAGYAIABUAFIAVQBFACwAIABkAGkAcwBwAGwAYQB5ACAAaQBuAHMAdABhAG4AYwBlAHMAIABpAG4AIABkAGUAcwBjAGUAbgBkAGkAbgBnACAAbwByAGQAZQByAFwAbgAgACAAIAAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBJAG4AcwB0AGEAbgBjAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACwAXABuACAAIAAgACAAWwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAsAFwAbgAgACAAIAAgAFsARABlAHMAYwBlAG4AZAA/AF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAIABvAGYAIAAxAEQAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAsACAAIAAgACAAIAAgAFIATwBXAFMAKAB2AGUAYwB0AG8AcgApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAdgBlAGMAdABvAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAASQBTAE8ATQBJAFQAVABFAEQAKABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQAsAFwAbgAgACAAIAAgAEkAcwBEAGUAcwBjAGUAbgBkAD8ALAAgACAAQQBOAEQAKABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgARABlAHMAYwBlAG4AZAA/ACkAKQAsACAARABlAHMAYwBlAG4AZAA/ACAAPQAgAFQAUgBVAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgAEEATgBEACgAaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAaABlAGkAZwBoAHQAIAA+ACAAMQAwADQAOAA1ADcANgAsAGgAZQBpAGcAaAB0ACAAPgAgADEANgAzADgANAApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAdgBlAGMAdABvAHIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABTAHAAaQBsAGwAUgBpAHMAawA/ACwAIwBOAFUATQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFQAeQBwAGUAIABvAGYAIABpAG4AZABlAHgAXABuACAAIAAgACAAaQBkAHgAuwMsACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARABlAHMAYwBlAG4AZAA/ACwAIABDAG8AdQBuAHQAZABvAHcAbgC7AywAIABTAHQAcgBlAGEAawC7AykALABcAG4AXABuACAAIAAgACAALwAvACAAUwBvAHIAdAAgAGsAZQB5AFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKAB2AGUAYwB0AG8AcgApACwAXABuACAAIAAgACAAXABuACAAIAAgACAALwAvACAAUwBvAHIAdAAgAGEAcwAgADIARAAgAGEAcgByAGEAeQAsACAAbwBiAHQAYQBpAG4AIABzAHQAcgBlAGEAawBcAG4AIAAgACAAIABzAG8AcgB0AGUAZAAsACAAIAAgACAAIAAgAFMATwBSAFQAKABIAFMAVABBAEMASwAoAGkALAB2AGUAYwB0AG8AcgApACwAMgApACwAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIABpAGQAeAC7AygAVABBAEsARQAoAHMAbwByAHQAZQBkACwALAAtADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAbgBnAGUAIABuAGUAdwAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABuAGUAdwBfAGEAcgByACwAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAcwBvAHIAdABlAGQALABpAGQAeAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAbwByAHQAIABiAHkAIABrAGUAeQAsACAAbwBiAHQAYQBpAG4AIABpAG4AcwB0AGEAbgBjAGUAIABuAHUAbQBiAGUAcgBcAG4AIAAgACAAIABpAG4AcwB0ACwAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABTAE8AUgBUACgAbgBlAHcAXwBhAHIAcgApACwALAAtADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUALQBzAGgAYQBwAGUALAAgAGkAZgAgAG4AZQBlAGQAZQBkACAAYQBuAGQAIAByAGUAdAB1AHIAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsAGkAbgBzAHQALABUAE8AUgBPAFcAKABpAG4AcwB0ACkAKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAxADcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAVwBhAHYAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAUwBlAHEAdQBlAG4AYwBpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAARQBjAGgAbwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHQAdQByAG4AcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIAAxAEQAIABcACIAdwBhAHYAZQAgAGEAcgByAGEAeQBcACIAIABiAHkAIABzAHUAcABwAGwAeQBpAG4AZwAgAGEAIABjAHIAZQBzAHQAIAAoAG0AYQB4ACAAdgBhAGwAdQBlACkAIABhAG4AZAAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAHIAZQBwAF8AYwBvAHUAbgB0AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYwByAGUAcwB0ACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAgACAAbQBhAHgAIAB2AGEAbAB1AGUAIABpAG4AIAAxAEQAIAB3AGEAdgBlACAAYQByAHIAYQB5AFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAFsAcgBlAHAAXwBjAG8AdQBuAHQAXQAgACAAIAAgACAAIAAtACAAIAAgAG4AdQBtAGIAZQByACAAbwBmACAAdABpAG0AZQBzACAAdABvACAAcgBlAHAAZQBhAHQAIABlAGEAYwBoACAAaQBuAHQAZQBnAGUAcgAgAGkAbgAgAHcAYQB2AGUAIABhAHIAcgBhAHkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAbgBvACAAcgBlAHAAZQB0AGkAdABpAG8AbgAuAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBXAGEAdgBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAcgBlAHMAdAAsAFwAbgAgACAAIAAgAFsAcgBlAHAAXwBjAG8AdQBuAHQAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFcAYQB2AGUAIABtAG8AZABlAFwAbgAgACAAIAAgAFMAdABhAG4AZABhAHIAZAA/ACwAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAcgBlAHAAXwBjAG8AdQBuAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIAByAGUAcABlAHQAaQB0AGkAbwBuAFwAbgAgACAAIAAgAHIAZQBwAF8AYwBvAHUAbgB0ACwAIAAgAEkARgAoAFMAdABhAG4AZABhAHIAZAA/ACwAMQAsAEkATgBEAEUAWAAoAHIAZQBwAF8AYwBvAHUAbgB0ACwAMQAsADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAYwByAGUAcwB0AFwAbgAgACAAIAAgAGMAcgBlAHMAdAAsACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGMAcgBlAHMAdAAsADEALAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQATgA/ACwAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYwByAGUAcwB0ACkALAAgAGMAcgBlAHMAdAAgADwAIAAwACkALABcAG4AIAAgACAAIABTAHAAaQBsAGwAUgBpAHMAawA/ACwAIAByAGUAcABfAGMAbwB1AG4AdAAgACoAIAAoAGMAcgBlAHMAdAAgACoAIAAyACAALQAgADEAKQAgAD4AIAAxADAANAA4ADUANwA2ACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQATgA/ACwAIAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAIwBOAFUATQAhACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATABlAG4AZwB0AGgAIABvAGYAIABzAGUAcQB1AGUAbgBjAGUAIAAoAGIAZQBmAG8AcgBlACAAYQBuAHkAIAByAGUAcABlAHQAaQB0AGkAbwBuACAAaQBzACAAYQBkAGQAZQBkACkAXABuACAAIAAgACAAawAsACAAIAAgACAAYwByAGUAcwB0ACAAKgAgADIAIAAtACAAMQAsAFwAbgAgACAAIAAgAHMAZQBxACwAIAAgAFMARQBRAFUARQBOAEMARQAoAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAeAAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAbQAsACAAIAAgACAATQBBAFgAKABzAGUAcQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBxAHUAZQBuAGMAZQAgAGEAZABqAHUAcwB0AG0AZQBuAHQAXABuACAAIAAgACAAdwAsACAAIAAgACAASQBGACgAcwBlAHEAIAA+ACAAYwByAGUAcwB0ACwAIABtACAALQAgAHMAZQBxACAAKwAgADEALAAgAHMAZQBxACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHMAcABsAGEAeQAgAHcAYQB2AGUAIABzAGUAcQB1AGUAbgBjAGUAIAB3AGkAdABoACAAbwBwAHQAaQBvAG4AYQBsACAAZQBjAGgAbwBpAG4AZwBcAG4AIAAgACAAIABmAGkAbgBhAGwALABJAEYAKABTAHQAYQBuAGQAYQByAGQAPwAsAHcALABFAGMAaABvALsDKAB3ACwAcgBlAHAAXwBjAG8AdQBuAHQAKQApACwAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAQgB5AEQAaQBhAGcAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQBwAHAAbABpAGUAcwAgAGEAbgAgAEUAVABBACAAZgB1AG4AYwB0AGkAbwBuACAAbwByACAATABhAG0AYgBkAGEAIAB0AG8AIABlAGEAYwBoACAAZABpAGEAZwBvAG4AYQBsACAAbwBmACAAYQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAEQAaQBhAGcAbwBuAGEAbABzACAAYQByAGUAIABlAHgAdAByAGEAYwB0AGUAZAAgAGYAcgBvAG0AIAB0AG8AcAARIGwAZQBmAHQAIAB0AG8AIABiAG8AdAB0AG8AbQARIHIAaQBnAGgAdAAsACAAdwBpAHQAaAAgAGUAYQBjAGgAIABkAGkAYQBnAG8AbgBhAGwAXABuACAAIAAgACAAcgBlAHAAcgBlAHMAZQBuAHQAZQBkACAAYQBzACAAYQAgAHIAbwB3ACAAaQBuACAAdABoAGUAIABvAHUAdABwAHUAdAAuACAATwBwAHQAaQBvAG4AYQBsAGwAeQAsACAAcgBlAHMAdQBsAHQAcwAgAG0AYQB5ACAAYgBlACAAcwB0AGEAYwBrAGUAZABcAG4AIAAgACAAIAByAG8AdwARIHcAaQBzAGUAIAAoAHYAZQByAHQAaQBjAGEAbAApACAAbwByACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAKABoAG8AcgBpAHoAbwBuAHQAYQBsACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIAcwAgAG4AbwB0ACAAYQBjAGMAZQBwAHQAZQBkACkALgBcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACAAIAAgACAAIAAgACAAIAAgACAALQAgAEUAVABBACAAZgB1AG4AYwB0AGkAbwBuACAAbwByACAATABhAG0AYgBkAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAZQBhAGMAaAAgAGQAaQBhAGcAbwBuAGEAbAAuAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAgACAAIAAtACAASQBmACAAVABSAFUARQAsACAAcgBlAHMAdQBsAHQAcwAgAGEAcgBlACAAcwB0AGEAYwBrAGUAZAAgAHYAZQByAHQAaQBjAGEAbABsAHkAOwAgAG8AdABoAGUAcgB3AGkAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAYQBnAG8AbgBhAGwAcwAgAGEAcgBlACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAYwBvAGwAdQBtAG4AcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgADEARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQAIABiAHkAIABWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7Ay4AXABuACAAIAAgACAAIiAgAEkAZgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAG8AbQBpAHQAdABlAGQALAAgAHIAYQB3ACAAZABpAGEAZwBvAG4AYQBsAHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHMAaABhAHAAZQAgAGkAcwAgAGsAIADXACAAagAgAHcAaABlAHIAZQAgAGsAIAA9ACAATQBJAE4AKAByAG8AdwBzACwAIABjAG8AbAB1AG0AbgBzACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQgB5AEQAaQBhAGcAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAsAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAsAFwAbgBcAG4AVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwMoAGEAcgByAGEAeQAsACAALAAgAGYAdQBuAGMAdABpAG8AbgAsACAAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgAgACAAIAAgAE4AbwBfAEYAdQBuAGMAdABpAG8AbgAsACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGYAdQBuAGMAdABpAG8AbgApACwAXABuACAAIAAgACAATgBvAF8AUgBvAHcAUwB0AGEAYwBrACwAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AdQBtAGIAZQByACAAbwBmACAAZABpAGEAZwBvAG4AYQBsAHMAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAaAAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGUAcgByAGUAZAAgAGkAbgBkAGUAeAAgAGcAZQBuAGUAcgBhAHQAbwByAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAawApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIAB3ACwAIAAxACwAIAAwACkAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGsAKQAgACsAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwAsACAAMAAsACAAMQApACkALABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKAB5ACgAKQAgAD4AIAB3ACwAIABOAEEAKAApACwAIAB5ACgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAGQAaQBhAGcAbwBuAGEAbABzAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYATgBBACgASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIAByACgAKQAsACAAYwAoACkAKQAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcgBpAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABzAGgAYQBwAGUAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAF8AUgBvAHcAUwB0AGEAYwBrACwAIAByAGUAcwB1AGwAdAAsACAAVABSAEEATgBTAFAATwBTAEUAKAByAGUAcwB1AGwAdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAZgB1AG4AYwB0AGkAbwBuACAAaQBmACAAcAByAG8AdgBpAGQAZQBkAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AXwBGAHUAbgBjAHQAaQBvAG4ALABzAGgAYQBwAGUAZAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBfAFIAbwB3AFMAdABhAGMAawAsAEIAWQBDAE8ATAAoAHMAaABhAHAAZQBkACwAIABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAHMAaABhAHAAZQBkACwAIABmAHUAbgBjAHQAaQBvAG4AKQApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABEAGkAYQBnAE0AYQBwALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQgB5AEQAaQBhAGcAuwMsACAAVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwBuAHYAZQBuAGkAZQBuAGMAZQAgAHcAcgBhAHAAcABlAHIAIABmAG8AcgAgAEIAeQBEAGkAYQBnALsDIAB0AGgAYQB0ACAAZQB4AHQAcgBhAGMAdABzACAAYQBsAGwAIABkAGkAYQBnAG8AbgBhAGwAcwAgAGYAcgBvAG0AIABhACAAMgBEAFwAbgAgACAAIAAgAGEAcgByAGEAeQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAHQAaABlAG0AIABhAHMAIABhACAAMgBEACAAYQByAHIAYQB5AF8AMgBEAC4AIABPAHAAdABpAG8AbgBhAGwAIAByAG8AdwARIHcAaQBzAGUAIABzAHQAYQBjAGsAaQBuAGcAIABpAHMAXABuACAAIAAgACAAcwB1AHAAcABvAHIAdABlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAgACAAIAAtACAASQBmACAAVABSAFUARQAsACAAZABpAGEAZwBvAG4AYQBsAHMAIABhAHIAZQAgAHMAdABhAGMAawBlAGQAIAB2AGUAcgB0AGkAYwBhAGwAbAB5AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAGMAYQBsAGwAaQBuAGcAIABCAHkARABpAGEAZwC7AygAYQByAHIAYQB5ACwAIAAsACAAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAGkAYQBnAE0AYQBwALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAsAFwAbgAgACAAIAAgAEIAeQBEAGkAYQBnALsDKABhAHIAcgBhAHkALAAgACwAIAByAG8AdwBfAHcAaQBzAGUAXwBzAHQAYQBjAGsAPwApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABpAGEAZwBJAG4AZABlAHgAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABCAHkARABpAGEAZwC7AywAIABWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAHMAaQBuAGcAbABlACAAZABpAGEAZwBvAG4AYQBsACAAbwByACAAYQBuAHQAaQARIGQAaQBhAGcAbwBuAGEAbAAgAHYAZQBjAHQAbwByACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABQAG8AcwBpAHQAaQB2AGUAIABjAG8AbABfAGkAbgBkAGUAeAAgAHMAZQBsAGUAYwB0AHMAIABhACAAcwB0AGEAbgBkAGEAcgBkACAAKABTAEUAESBkAGkAcgBlAGMAdABpAG8AbgApACAAZABpAGEAZwBvAG4AYQBsAC4AXABuACAAIAAgACAATgBlAGcAYQB0AGkAdgBlACAAYwBvAGwAXwBpAG4AZABlAHgAIABzAGUAbABlAGMAdABzACAAYQBuACAAYQBuAHQAaQARIGQAaQBhAGcAbwBuAGEAbAAgACgAUwBXABEgZABpAHIAZQBjAHQAaQBvAG4AKQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAHMAYwBhAGwAYQByAHMAIABuAG8AdAAgAGEAYwBjAGUAcAB0AGUAZAApAC4AXABuACAAIAAgACAAYwBvAGwAXwBpAG4AZABlAHgAIAAgACAALQAgAFMAdABhAHIAdABpAG4AZwAgAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4AC4AIABOAGUAZwBhAHQAaQB2AGUAIAB2AGEAbAB1AGUAcwAgAGkAbgBkAGkAYwBhAHQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAG4AdABpABEgZABpAGEAZwBvAG4AYQBsACAAZQB4AHQAcgBhAGMAdABpAG8AbgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAaQBzACAAYQBsAHcAYQB5AHMAIABhACAAMQBEACAAdgBlAGMAdABvAHIAIABvAGYAIABsAGUAbgBnAHQAaAAgAGsAIAA9ACAAZABpAGEAZwBvAG4AYQBsACAAbABlAG4AZwB0AGgALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABpAGEAZwBJAG4AZABlAHgAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBvAGwAXwBpAG4AZABlAHgALABcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBEAGkAYQBnALsDKABhAHIAcgBhAHkALAAgAGMAbwBsAF8AaQBuAGQAZQB4ACwAIAAsACAALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgACsAMQAgAD0AIABTAEUALAAgABMgMQAgAD0AIABTAFcAXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAGEAZwBvAG4AYQBsACAAbABlAG4AZwB0AGgAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAASQBGACgAcwAgAD4AIAAwACwATQBJAE4AKABoACwAIAB3ACAAKwAgADEAIAAtACAAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAaAAsACAAQQBCAFMAKABjAG8AbABfAGkAbgBkAGUAeAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQByAHQAaQBuAGcAIABjAG8AbAB1AG0AbgBcAG4AIAAgACAAIABzAHQAYQByAHQALAAgACAAIABJAEYAKABzACAAPAAgADAALAAgAEEAQgBTACgAYwBvAGwAXwBpAG4AZABlAHgAKQAsACAAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABpAG4AZABlAHgAIABnAGUAbgBlAHIAYQB0AG8AcgBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAawApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGsALAAgACwAIABzAHQAYQByAHQALAAgAHMAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABkAGkAYQBnAG8AbgBhAGwAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIAB4ACgAKQAsACAAeQAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgARIEMATwBSAEUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAG8AcgBlACAAVgBhAGwAaQBkAGEAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAHMAIABpAG4AcAB1AHQAcwAgAGYAbwByACAAQgB5AEQAaQBhAGcAuwMsACAARABpAGEAZwBNAGEAcAC7AywAIABhAG4AZAAgAEQAaQBhAGcASQBuAGQAZQB4ALsDLgAgAEUAbgBzAHUAcgBlAHMAIAB0AGgAYQB0ACAAdABoAGUAXABuACAAIAAgACAAYQByAHIAYQB5ACAAaQBzACAAYQAgAHYAYQBsAGkAZAAgADIARAAgAHMAdAByAHUAYwB0AHUAcgBlACwAIAB0AGgAYQB0ACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAKAB3AGgAZQBuACAAcwB1AHAAcABsAGkAZQBkACkAIABhAHIAZQBcAG4AIAAgACAAIAB3AGkAdABoAGkAbgAgAGIAbwB1AG4AZABzACwAIABhAG4AZAAgAHQAaABhAHQAIABhAG4AeQAgAHMAdQBwAHAAbABpAGUAZAAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGEAIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQAvAEUAVABBAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMgBEACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAAIAAgACAAIAAgACAAIAAgAC0AIABTAHQAYQByAHQAaQBuAGcAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgACgARABpAGEAZwBJAG4AZABlAHgAuwMgAG8AbgBsAHkAKQAuAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0AIAAgACAAIAAgACAAIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABMAEEATQBCAEQAQQAgACgAQgB5AEQAaQBhAGcAuwMgAG8AbgBsAHkAKQAuAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAgACAAIAAtACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAZgBsAGEAZwAgACgAQgB5AEQAaQBhAGcAuwMgAC8AIABEAGkAYQBnAE0AYQBwALsDKQAuAFwAbgAgACAAIAAgAFsAbwBuAF8AdgBhAGwAaQBkAF0AIAAgACAAIAAgACAAIAAgACAAIAAtACAARQB4AHAAcgBlAHMAcwBpAG8AbgAgAHQAbwAgAGUAdgBhAGwAdQBhAHQAZQAgAHcAaABlAG4AIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAdgBhAGwAaQBkAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAbgBvAG4AESBhAHIAcgBhAHkAcwAgAGEAcgBlACAAcgBlAGoAZQBjAHQAZQBkAC4AXABuACAAIAAgACAAIiAgAGMAbwBsAF8AaQBuAGQAZQB4ACAAPQAgADAAIABpAHMAIABpAG4AdgBhAGwAaQBkACAAYgB5ACAAZABlAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAiICAARgB1AG4AYwB0AGkAbwBuACAAdgBhAGwAaQBkAGEAdABpAG8AbgAgAHUAcwBlAHMAIABhACAAcwBhAGYAZQAgAFQAWQBQAEUAESBiAGEAcwBlAGQAIABpAG4AdgBvAGMAYQB0AGkAbwBuACAAdABlAHMAdAAuAFwAbgAgACAAIAAgACIgIABSAG8AdQB0AGkAbgBnACAAbABvAGcAaQBjACAAZABlAHQAZQByAG0AaQBuAGUAcwAgAHcAaABpAGMAaAAgAG8AcABlAHIAYQB0AG8AcgAgAGkAcwAgAGIAZQBpAG4AZwAgAHYAYQBsAGkAZABhAHQAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBEAGkAYQBnALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AIAAgACAAIABbAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/AF0ALABcAG4AIAAgACAAIABbAG8AbgBfAHYAYQBsAGkAZABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAALQAtAC0AIABBAHIAcgBhAHkAIAB2AGEAbABpAGQAYQB0AGkAbwBuACAALQAtAC0AXABuACAAIAAgACAASQBzAEEAcgByAGEAeQA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABZAFAARQAoAGEAcgByAGEAeQApACAAPQAgADYANAAsAFwAbgAgACAAIAAgAE4AbwB0AF8AQQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBzAEEAcgByAGEAeQA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABDAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAHYAYQBsAGkAZABhAHQAaQBvAG4AIAAoAEQAaQBhAGcASQBuAGQAZQB4ALsDIABvAG4AbAB5ACkAIAAtAC0ALQBcAG4AIAAgACAAIABOAG8AXwBDAG8AbABfAEkAbgBkAGUAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AIAAgACAAIABDAG8AbABJAG4AZABlAHgAXwBJAG4AYwBsAHUAZABlAGQALAAgACAAIAAgACAAIABOAE8AVAAoAE4AbwBfAEMAbwBsAF8ASQBuAGQAZQB4ACkALABcAG4AIAAgACAAIABOAG8AdABfAFYAYQBsAGkAZABfAEMAbwBsAEkAbgBkAGUAeAA/ACwAIAAgACAAIABOAE8AVAAoAEEATgBEACgAYwBvAGwAXwBpAG4AZABlAHgAIAA8AD4AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAQgBTACgAYwBvAGwAXwBpAG4AZABlAHgAKQAgADwAPQAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABGAHUAbgBjAHQAaQBvAG4AIAB2AGEAbABpAGQAYQB0AGkAbwBuACAAKABCAHkARABpAGEAZwC7AyAAbwBuAGwAeQApACAALQAtAC0AXABuACAAIAAgACAATgBvAF8ARgB1AG4AYwB0AGkAbwBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgAgACAAIAAgAEYAdQBuAGMAdABpAG8AbgBfAEkAbgBjAGwAdQBkAGUAZAAsACAAIAAgACAAIAAgAE4ATwBUACgATgBvAF8ARgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBhAGYAZQAgAGYAdQBuAGMAdABpAG8AbgAgAHYAYQBsAGkAZABhAHQAaQBvAG4AOgAgAGUAbgBzAHUAcgBlACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzACAAYwBhAGwAbABhAGIAbABlAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAXwBGAHUAbgBjAHQAaQBvAG4APwAsACAAIAAgACAAIAAgAEEATgBEACgARgB1AG4AYwB0AGkAbwBuAF8ASQBuAGMAbAB1AGQAZQBkACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMARQBSAFIATwBSACgAQgBZAFIATwBXACgAewAxACwAMQB9ACwAIABmAHUAbgBjAHQAaQBvAG4AKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABmAGwAYQBnACAAKABEAGkAYQBnAE0AYQBwALsDIAAvACAAQgB5AEQAaQBhAGcAuwMpACAALQAtAC0AXABuACAAIAAgACAAUgBvAHcAVwBpAHMAZQBTAHQAYQBjAGsAPwAsACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEQAZQB0AGUAcgBtAGkAbgBlACAAdwBoAGkAYwBoACAAbwBwAGUAcgBhAHQAbwByACAAaQBzACAAYgBlAGkAbgBnACAAdgBhAGwAaQBkAGEAdABlAGQAIAAtAC0ALQBcAG4AIAAgACAAIABJAHMARABpAGEAZwBJAG4AZABlAHgAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAG8AbABJAG4AZABlAHgAXwBJAG4AYwBsAHUAZABlAGQALABcAG4AIAAgACAAIABJAHMAQgB5AEQAaQBhAGcAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4AbwBfAEMAbwBsAF8ASQBuAGQAZQB4ACwAIABGAHUAbgBjAHQAaQBvAG4AXwBJAG4AYwBsAHUAZABlAGQAKQAsAFwAbgAgACAAIAAgAEkAcwBEAGkAYQBnAE0AYQBwAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgATgBvAF8AQwBvAGwAXwBJAG4AZABlAHgALAAgAE4AbwBfAEYAdQBuAGMAdABpAG8AbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAATABvAGcAaQBjACAAZwBhAHQAZQBzACAALQAtAC0AXABuACAAIAAgACAALwAvACAARABpAGEAZwBJAG4AZABlAHgAuwNcAG4AIAAgACAAIABnAGEAdABlAF8ARABpAGEAZwBJAG4AZABlAHgALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AdABfAEEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8AVAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAHQAXwBWAGEAbABpAGQAXwBDAG8AbABJAG4AZABlAHgAPwAsACAAXAAiACMAQwBPAEwAVQBNAE4ALQBJAE4ARABFAFgAIQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBuAF8AdgBhAGwAaQBkACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHkARABpAGEAZwC7A1wAbgAgACAAIAAgAGcAYQB0AGUAXwBCAHkARABpAGEAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwB0AF8AQQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAE4ATwBUAC0AQQBSAFIAQQBZACEAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAF8ARgB1AG4AYwB0AGkAbwBuAD8ALAAgAFwAIgAjAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAG4AXwB2AGEAbABpAGQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBhAGcATQBhAHAAuwNcAG4AIAAgACAAIABnAGEAdABlAF8ARABpAGEAZwBNAGEAcAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AdABfAEEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8AVAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBuAF8AdgBhAGwAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABSAG8AdQB0AGUAIAB0AG8AIABjAG8AcgByAGUAYwB0ACAAZwBhAHQAZQAgAC0ALQAtAFwAbgAgACAAIAAgAGQAZQBjAGkAZABlACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBEAGkAYQBnAEkAbgBkAGUAeAA/ACwAIABnAGEAdABlAF8ARABpAGEAZwBJAG4AZABlAHgALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARABpAGEAZwBNAGEAcAA/ACwAIABnAGEAdABlAF8ARABpAGEAZwBNAGEAcAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEIAeQBEAGkAYQBnAD8ALAAgAGcAYQB0AGUAXwBCAHkARABpAGEAZwAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBVAE4AUgBPAFUAVABFAEQAIQBcACIAKQApACkALABcAG4AXABuACAAIAAgACAAZABlAGMAaQBkAGUAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAwADYAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABFAGMAaABvALsDLAAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAHIAZQBhAHQAZQBzACAAdgBlAHIAdABpAGMAYQBsACAAcABhAGkAcgBzACAAZgByAG8AbQAgADEARAAgAGEAbgBkACAAcwBjAGEAbABhAHIAIABpAG4AcAB1AHQAcwAuACAASQBuAHAAdQB0AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAdwBpAHQAaABcAG4AIAAgACAAIABUAE8AQwBPAEwAIAB0AG8AIABuAG8AcgBtAGEAbABpAHoAZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAuACAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHMAdAByAGkAYwB0AGwAeQAgAHAAcgBvAGgAaQBiAGkAdABlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgBfADEAIAAgACAAIAAtACAAMQBEACAAdgBlAGMAdABvAHIAIABvAHIAIABzAGMAYQBsAGEAcgAuAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMgAgACAAIAAgAC0AIAAxAEQAIAB2AGUAYwB0AG8AcgAgAG8AcgAgAHMAYwBhAGwAYQByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFAAYQBpAHIAdwBpAHMAZQC7Az0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAdgBlAGMAdABvAHIAXwAxACwAXABuACAAIAAgACAAdgBlAGMAdABvAHIAXwAyACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIAB2ACwAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKAB2AGUAYwB0AG8AcgBfADEAKQAsAFwAbgAgACAAIAAgAHYAgiAsACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAHYAZQBjAHQAbwByAF8AMgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbABlAG0AZQBuAHQAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHYAKQAsAFwAbgAgACAAIAAgAGsAgiAsACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAdgCCICkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwAyAEQASQBuAHAAdQB0AD8ALAAgAE8AUgAoAEEATgBEACgAUgBPAFcAUwAoAHYAZQBjAHQAbwByAF8AMQApAD4AMQAsACAAQwBPAEwAVQBNAE4AUwAoAHYAZQBjAHQAbwByAF8AMQApAD4AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABSAE8AVwBTACgAdgBlAGMAdABvAHIAXwAyACkAPgAxACwAIABDAE8ATABVAE0ATgBTACgAdgBlAGMAdABvAHIAXwAyACkAPgAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABJAHMAMgBCAGkAZwA/ACwAIAAgACAAIABrACAAKgAgAGsAgiAgAD4AIAAxADAAMAAwADAAMAAwACwAXABuAFwAbgBJAEYAKABJAHMAMgBEAEkAbgBwAHUAdAA/ACwAIAAgACMAVgBBAEwAVQBFACEALABcAG4AXABuACAAIAAgACAASQBGACgASQBzADIAQgBpAGcAPwAsACAAIAAgACAAIAAjAE4AVQBNACEALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQwBhAHIAdABlAHMAaQBhAG4AIABlAHgAcABhAG4AcwBpAG8AbgBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAARQBjAGgAbwC7AygAdgAsACAAawCCICkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAUgBlAHMAaQB6AGUAuwMoAHYAgiAsACAAawApACwAXABuACAAIAAgACAAcABhAGkAcgBzACwAIAAgAEgAUwBUAEEAQwBLACgAeAAsACAAeQApACwAXABuAFwAbgAgACAAIAAgAHAAYQBpAHIAcwBcAG4AIAAgACAAIABcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAANgBhAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAFAAYQBpAHIAdwBpAHMAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIAB0AGgAZQAgAEMAYQByAHQAZQBzAGkAYQBuACAAcAByAG8AZAB1AGMAdAAgAG8AZgAgADMAIABzAGUAdABzAC4AIABBAGwAbAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAGEAbgBkAFwAbgAgACAAIAAgAHQAaABlACAAcgBlAHMAdQBsAHQAaQBuAGcAIAB0AHIAaQBwAGwAZQBzACAAcAByAGUAcwBlAHIAdgBlACAAdABoAGUAIABvAHIAZABlAHIAIABvAGYAIAB0AGgAZQAgAHMAdQBwAHAAbABpAGUAZAAgAHMAZQB0AHMALgBcAG4AXABuACAAIAAgACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AyAAZQB4AHQAZQBuAGQAcwAgAFAAYQBpAHIAdwBpAHMAZQC7AyAAdABvACAAYQAgADMAESBhAHgAaQBzACAAZgBhAGIAcgBpAGMAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABzAGUAdABfADEAIADXACAAcwBlAHQAXwAyACAA1wAgAHMAZQB0AF8AMwBcAG4AIAAgACAAIABUAGgAZQAgAG8AdQB0AHAAdQB0ACAAaQBzACAAYQAgAHMAcABpAGwAbAAgAHcAaABlAHIAZQAgAGUAYQBjAGgAIAByAG8AdwAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQAgAG8AcgBkAGUAcgBlAGQAIAB0AHIAaQBwAGwAZQAuAFwAbgBcAG4ARgBvAHIAbQB1AGwAYQA6ACAAPQBUAHIAaQBwAGwAZQB3AGkAcwBlALsDKAB7AFwAIgBkAG8AZwBcACIAOwBcACIAYwBhAHQAXAAiADsAXAAiAGIAaQByAGQAXAAiAH0ALAB7AFwAIgBhAFwAIgA7AFwAIgBiAFwAIgA7AFwAIgBjAFwAIgB9ACwAewAxADsAMgB9ACkAXABuAFwAbgBSAGUAcwB1AGwAdAA6AFwAbgAgACAAIAAgAHsAXAAiAGQAbwBnAFwAIgAsAFwAIgBhAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBkAG8AZwBcACIALABcACIAYQBcACIALAAyADsAXABuACAAIAAgACAAIABcACIAZABvAGcAXAAiACwAXAAiAGIAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGQAbwBnAFwAIgAsAFwAIgBiAFwAIgAsADIAOwBcAG4AIAAgACAAIAAgAFwAIgBkAG8AZwBcACIALABcACIAYwBcACIALAAxADsAXABuACAAIAAgACAAIABcACIAZABvAGcAXAAiACwAXAAiAGMAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGMAYQB0AFwAIgAsAFwAIgBhAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBjAGEAdABcACIALABcACIAYQBcACIALAAyADsAXABuACAAIAAgACAAIABcACIAYwBhAHQAXAAiACwAXAAiAGIAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGMAYQB0AFwAIgAsAFwAIgBiAFwAIgAsADIAOwBcAG4AIAAgACAAIAAgAFwAIgBjAGEAdABcACIALABcACIAYwBcACIALAAxADsAXABuACAAIAAgACAAIABcACIAYwBhAHQAXAAiACwAXAAiAGMAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGEAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGEAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGIAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGIAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGMAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGMAXAAiACwAMgB9AFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHMAZQB0AF8AMQAgACAAIAAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAKAAxAEQAIABvAHIAIAAyAEQAKQAgAGEAcgBlACAAYQBjAGMAZQBwAHQAZQBkAC4AIABBAGwAbAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAuAFwAbgAgACAAIAAgAHMAZQB0AF8AMgBcAG4AIAAgACAAIABzAGUAdABfADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAcgBpAHAAbABlAHcAaQBzAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHMAZQB0AF8AMQAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMgAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMwAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABhAGwAbAAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAHMAZQB0AF8AMQAsACAAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMQApACwAXABuACAAIAAgACAAcwBlAHQAXwAyACwAIAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAyACkALABcAG4AIAAgACAAIABzAGUAdABfADMALAAgACAAIABUAE8AQwBPAEwAKABzAGUAdABfADMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAdAAgAGkAdABlAG0AIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABrAIEgLAAgACAAIAAgACAAIABSAE8AVwBTACgAcwBlAHQAXwAxACkALABcAG4AIAAgACAAIABrAIIgLAAgACAAIAAgACAAIABSAE8AVwBTACgAcwBlAHQAXwAyACkALABcAG4AIAAgACAAIABrAIMgLAAgACAAIAAgACAAIABSAE8AVwBTACgAcwBlAHQAXwAzACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIABpAGYAIABzAGUAdABfADIAIABpAHMAIABzAGMAYQBsAGEAcgBcAG4AIAAgACAAIABzAHcAYQBwAD8ALAAgACAAIABrAIIgIAA9ACAAMQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAcABhAGkAcgBzACAAZgByAG8AbQAgAGYAaQByAHMAdAAgAHQAdwBvACAAcwBlAHQAcwBcAG4AIAAgACAAIABwAGEAaQByAHMALAAgACAAIABJAEYAKABzAHcAYQBwAD8ALAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAcwBlAHQAXwAyACwAcwBlAHQAXwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAcwBlAHQAXwAxACwAcwBlAHQAXwAyACkAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAHMAZQB0AHMAIABlAHgAcABhAG4AZABlAGQAXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAASQBGACgAcwB3AGEAcAA/ACwAVABBAEsARQAoAHAAYQBpAHIAcwAsACwALQAxACkALABUAEEASwBFACgAcABhAGkAcgBzACwALAAxACkAKQAsAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIAAgAEkARgAoAHMAdwBhAHAAPwAsAFQAQQBLAEUAKABwAGEAaQByAHMALAAsADEAKQAsAFQAQQBLAEUAKABwAGEAaQByAHMALAAsAC0AMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAGkAcgBzACAAZgByAG8AbQAgAHMAZQB0AF8AMQAgAGUAeABwAGEAbgBkAGUAZAAgACsAIABzAGUAdABfADMAXABuACAAIAAgACAAdABoAHIAaQBjAGUALAAgACAASQBGACgAawCDICAAPAA+ACAAMQAsACAAUABhAGkAcgB3AGkAcwBlALsDKABhACwAcwBlAHQAXwAzACkALABQAGEAaQByAHcAaQBzAGUAuwMoAHMAZQB0AF8AMwAsAGEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBpAHIAcwAgAGYAcgBvAG0AIABzAGUAdABfADIAIABlAHgAcABhAG4AZABlAGQAIAArACAAcwBlAHQAXwAzAFwAbgAgACAAIAAgAHQAaAByAGkAYwBlAF8ALAAgAEkARgAoAGsAgyAgADwAPgAgADEALAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAYgAsAHMAZQB0AF8AMwApACwAUABhAGkAcgB3AGkAcwBlALsDKABzAGUAdABfADMALABiACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIABjAG8AbABzACwAIAAgACAAIABJAEYAKABrAIMgIAA9ACAAMQAsADEALAAtADEAKQAsAFwAbgAgACAAIAAgAGEAXwAsACAAIAAgACAAIAAgAEQAUgBPAFAAKAB0AGgAcgBpAGMAZQAsACwAYwBvAGwAcwApACwAXABuACAAIAAgACAAYgBfACwAIAAgACAAIAAgACAARABSAE8AUAAoAHQAaAByAGkAYwBlAF8ALAAsAGMAbwBsAHMAKQAsAFwAbgAgACAAIAAgAGMAXwAsACAAIAAgACAAIAAgAFQAQQBLAEUAKAB0AGgAcgBpAGMAZQAsACwAYwBvAGwAcwApACwAXABuACAAIAAgACAAXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgAG8AcgBkAGUAcgAgAHQAbwAgAG0AYQB0AGMAaAAgAGkAbgBwAHUAdAAgAG8AcgBkAGUAcgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIABIAFMAVABBAEMASwAoAGEAXwAsAGIAXwAsAGMAXwApACwAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA2AGIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABRAHUAYQBkAHcAaQBzAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDLAAgAFIAZQBzAGkAegBlALsDLAAgAFQAcgBpAHAAbABlAHcAaQBzAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABvAGYAIAA0ACAAcwBlAHQAcwAuACAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIABhAG4AZABcAG4AIAAgACAAIAB0AGgAZQAgAHIAZQBzAHUAbAB0AGkAbgBnACAAcQB1AGEAZAByAHUAcABsAGUAcwAgAHAAcgBlAHMAZQByAHYAZQAgAHQAaABlACAAbwByAGQAZQByACAAbwBmACAAdABoAGUAIABzAHUAcABwAGwAaQBlAGQAIABzAGUAdABzAC4AXABuAFwAbgAgACAAIAAgAFEAdQBhAGQAdwBpAHMAZQC7AyAAZQB4AHQAZQBuAGQAcwAgAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMgAHQAbwAgAGEAIAA0ABEgYQB4AGkAcwAgAGYAYQBiAHIAaQBjADoAXABuACAAIAAgACAAIAAgACAAIAAiICAAcwBlAHQAXwAxACAA1wAgAHMAZQB0AF8AMgAgANcAIABzAGUAdABfADMAIADXACAAcwBlAHQAXwA0AFwAbgAgACAAIAAgAFQAaABlACAAbwB1AHQAcAB1AHQAIABpAHMAIABhACAAcwBwAGkAbABsACAAcgBhAG4AZwBlACAAdwBoAGUAcgBlACAAZQBhAGMAaAAgAHIAbwB3ACAAcgBlAHAAcgBlAHMAZQBuAHQAcwAgAG8AbgBlACAAbwByAGQAZQByAGUAZAAgAHEAdQBhAGQAcgB1AHAAbABlAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAcwBlAHQAXwAxACAAIAAgACAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAYQByAHIAYQB5AHMAIAAoADEARAAgAG8AcgAgADIARAApACAAYQByAGUAIABhAGMAYwBlAHAAdABlAGQALgAgAEEAbABsACAAaQBuAHAAdQB0AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkAC4AXABuACAAIAAgACAAcwBlAHQAXwAyAFwAbgAgACAAIAAgAHMAZQB0AF8AMwBcAG4AIAAgACAAIABzAGUAdABfADQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFEAdQBhAGQAdwBpAHMAZQC7Az0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcwBlAHQAXwAxACwAXABuACAAIAAgACAAcwBlAHQAXwAyACwAXABuACAAIAAgACAAcwBlAHQAXwAzACwAXABuACAAIAAgACAAcwBlAHQAXwA0ACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGEAbABsACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAAcwBlAHQAXwAxACwAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMQApACwAXABuACAAIAAgACAAcwBlAHQAXwAyACwAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMgApACwAXABuACAAIAAgACAAcwBlAHQAXwAzACwAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMwApACwAXABuACAAIAAgACAAcwBlAHQAXwA0ACwAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBzAGkAbwBuACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIABSAE8AVwBTACgAcwBlAHQAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABzAGUAdAAgADQAIABpAGYAIABzAGMAYQBsAGEAcgAgAHQAbwAgAGEAdgBvAGkAZAAgAFQATwBDAE8ATAAgAGgAYQBuAGQAbwBmAGYAIAB0AG8AIABSAGUAcwBpAHoAZQC7A1wAbgAgACAAIAAgAGQALAAgACAAIAAgACAAIABJAEYAKABrACAAPAA+ACAAMQAsAHMAZQB0AF8ANAAsAEkATgBEAEUAWAAoAHMAZQB0AF8ANAAsADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAcgBpAHAAbABlAHMAXABuACAAIAAgACAAdABoAHIAaQBjAGUALAAgAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMoAHMAZQB0AF8AMQAsAHMAZQB0AF8AMgAsAHMAZQB0AF8AMwApACwAXABuACAAIAAgACAAXABuACAAIAAgACAALwAvACAARQB4AHAAYQBuAGQAIAB0AHIAaQBwAGwAZQAgAHIAbwB3AHMAIABiAHkAIAB0AG8AdABhAGwAIABpAHQAZQBtAHMAIABpAG4AIABzAGUAdAAgADQAXABuACAAIAAgACAAdABoAHIAaQBjAGUAXwAsAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMoAHQAaAByAGkAYwBlACwAawApACwAXABuACAAIAAgACAAawCCICwAIAAgACAAIAAgAFIATwBXAFMAKAB0AGgAcgBpAGMAZQBfACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHAAYQBuAGQAIABzAGUAdAAgADQAIAB0AG8AIABtAGEAdABjAGgAIABsAGUAbgBnAHQAaAAgAG8AZgAgAHQAcgBpAHAAbABlAFwAbgAgACAAIAAgAGYAbwB1AHIALAAgACAAIABSAGUAcwBpAHoAZQC7AygAZAAsAGsAgiAgAC8AIABrACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAYwBrACAAYQBuAGQAIABkAGkAcwBwAGwAYQB5AFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIABIAFMAVABBAEMASwAoAHQAaAByAGkAYwBlAF8ALABmAG8AdQByACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARwByAG8AdQBwAGIAeQBCAGkAbgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAZwBnAHIAZQBnAGEAdABlAHMAIABvAG4AZQAgAG8AcgAgAG0AbwByAGUAIAB2AGEAbAB1AGUAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABmAGkAeABlAGQAESB3AGkAZAB0AGgAIABiAGkAbgBzACAAZABlAHIAaQB2AGUAZAAgAGYAcgBvAG0AIABhAFwAbgAgACAAIAAgAG4AdQBtAGUAcgBpAGMAIABmAGkAZQBsAGQALgAgAFMAdQBwAHAAbwByAHQAcwAgAG8AcAB0AGkAbwBuAGEAbAAgAGgAZQBhAGQAZQByAHMAIABhAG4AZAAgAGMAaABhAHIAdAARIHIAZQBhAGQAeQAgAG8AdQB0AHAAdQB0AC4AIABCAGkAbgBzACAAYQByAGUAXABuACAAIAAgACAAZABlAGYAaQBuAGUAZAAgAGIAeQAgAGEAIABuAHUAbQBlAHIAaQBjACAAYQByAHIAYQB5ACAAYQBuAGQAIABhACAAcABvAHMAaQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgAgAGIAaQBuAF8AdwBpAGQAdABoAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAATgB1AG0AZQByAGkAYwAgADEARAAgAGEAcgByAGEAeQAgAHUAcwBlAGQAIAB0AG8AIABkAGUAZgBpAG4AZQAgAGIAaQBuACAAYgBvAHUAbgBkAGEAcgBpAGUAcwAuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAoAHMAKQAgAHQAbwAgAGIAZQAgAGEAZwBnAHIAZQBnAGEAdABlAGQAIAAoADEARAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAYgBpAG4AXwB3AGkAZAB0AGgAIAAgACAAIAAgACAAIAAtACAAUABvAHMAaQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgAgAHMAcABlAGMAaQBmAHkAaQBuAGcAIABiAGkAbgAgAHcAaQBkAHQAaAAgACgAZSIgADEAKQAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgACAAIAAgACAALQAgAEUAVABBABEgYwBvAG0AcABhAHQAaQBiAGwAZQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AcgAgAHMAaQBuAGcAbABlABEgcABhAHIAYQBtAGUAdABlAHIAIABMAEEATQBCAEQAQQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBdACAAIAAtACAAVABSAFUARQAgAGkAZgAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQBzACAAaQBuAGMAbAB1AGQAZQAgAGgAZQBhAGQAZQByAHMAIAB0AG8AIABiAGUAIABjAGEAcgByAGkAZQBkACAAZgBvAHIAdwBhAHIAZAAuAFwAbgAgACAAIAAgAFsAYwBoAGEAcgB0AF8AcAByAGUAcABdACAAIAAgACAALQAgAFQAUgBVAEUAIAB0AG8AIAByAGUAdAB1AHIAbgAgAGEAIABjAG8AbgBjAGkAcwBlACAAYwBoAGEAcgB0ABEgcgBlAGEAZAB5ACAAbABhAHkAbwB1AHQALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABiAGkAbgBfAHcAaQBkAHQAaAAgAD0AIAAxACAAkiEgAGIAZQBoAGEAdgBlAHMAIABsAGkAawBlACAARwBSAE8AVQBQAEIAWQAgACgAbgBvACAAYgBpAG4AbgBpAG4AZwApAC4AXABuACAAIAAgACAAIiAgAGIAaQBuAF8AdwBpAGQAdABoACAAZSIgACgAbQBhAHgAIAASIiAAbQBpAG4AKQAgAJIhIABjAG8AbABsAGEAcABzAGUAcwAgAHQAbwAgAGEAIABzAGkAbgBnAGwAZQAgAGIAaQBuAC4AXABuACAAIAAgACAAIiAgAEMAaABhAHIAdAAgAG0AbwBkAGUAIAByAGUAdAB1AHIAbgBzACAAewBcACIAQgBpAG4AXAAiACwAXAAiAEEAZwBnAHIAZQBnAGEAdABlAFwAIgB9ACAAZgBvAHIAIABlAGEAcwB5ACAAcABsAG8AdAB0AGkAbgBnAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEcAcgBvAHUAcABiAHkAQgBpAG4AuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAdgBhAGwAdQBlAHMALABcAG4AIAAgACAAIABiAGkAbgBfAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAFsAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAXQAsAFwAbgAgACAAIAAgAFsAYwBoAGEAcgB0AF8AcAByAGUAcABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGkAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAdgBhAGwAdQBlAHMAKQAsAFwAbgAgACAAIAAgAGoAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAdgBhAGwAdQBlAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGUAYQBkAGUAcgAgAGYAbABhAGcAXABuACAAIAAgACAASABlAGEAZABlAHIAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaQAgAD4AIAAxACwAIABqACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABpACAAPAA+ACAAaQBfACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABCAGkAbgA/ACwAIAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYgBpAG4AXwB3AGkAZAB0AGgAKQAsACAAYgBpAG4AXwB3AGkAZAB0AGgAIAA8ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4APwAsACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuACAAIAAgACAATgBvAG4ATgB1AG0AZQByAGkAYwA/ACwAIAAgACAAIAAgACAAIAAgAE4ATwBUACgAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKABJAEYAKABIAGUAYQBkAGUAcgBzAD8ALAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgADEAKQAsACAAYQByAHIAYQB5ACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAMgBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAG4ATgB1AG0AZQByAGkAYwA/ACwAIABcACIAIwBOAFUATQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEIAaQBuAD8ALAAgAFwAIgAjAEIASQBOAC0AVwBJAEQAVABIACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABGAG4APwAsACAAXAAiACMASQBOAFYAQQBMAEkARAAtAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGwAYQBnAHMAXABuACAAIAAgACAATgBvAEMAaABhAHIAdAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYwBoAGEAcgB0AF8AcAByAGUAcAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdAByAGkAcAAgAGgAZQBhAGQAZQByAHMAIABpAGYAIABwAHIAZQBzAGUAbgB0AFwAbgAgACAAIAAgAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABIAGUAYQBkAGUAcgBzAD8ALAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgADEAKQAsACAAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB2AGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASABlAGEAZABlAHIAcwA/ACwAIABEAFIATwBQACgAdgBhAGwAdQBlAHMALAAgADEAKQAsACAAdgBhAGwAdQBlAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGUAYQBkAGUAcgAgAGMAbwBuAHMAdAByAHUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAHIAbwB3AF8AaABlAGEAZABlAHIALAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAFwAIgBCAGkAbgAgAFMAdABhAHIAdAAgAFwAIgAgACYAIABJAEYAKABIAGUAYQBkAGUAcgBzAD8ALAAgAFQAQQBLAEUAKABhAHIAcgBhAHkALAAgADEAKQAsACAAXAAiAFwAIgApACAAJgAgAFwAIgAgAFYAYQBsAHUAZQBcACIALABcACIAQgBpAG4AIABFAG4AZABcACIAKQAsAFwAbgAgACAAIAAgAHYAYQBsAF8AaABlAGEAZABlAHIALAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAEkARgAoAEgAZQBhAGQAZQByAHMAPwAsACAAVABBAEsARQAoAHYAYQBsAHUAZQBzACwAIAAxACkALAAgAFwAIgBUAG8AdABhAGwAXAAiACkALAAsAGoAXwAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgAGgAZQBhAGQAZQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHIAbwB3AF8AaABlAGEAZABlAHIALAAgAHYAYQBsAF8AaABlAGEAZABlAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGkAbgAgAGIAbwB1AG4AZABhAHIAaQBlAHMAXABuACAAIAAgACAAbQBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAYQByAHIAKQAsAFwAbgAgACAAIAAgAHMAdABhAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEwATwBPAFIAKABtAGkAbgAsACAAYgBpAG4AXwB3AGkAZAB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIABtAGEAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABhAHIAcgApACwAXABuACAAIAAgACAAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABtAGEAeAAsACAAYgBpAG4AXwB3AGkAZAB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABlAG4AZAAgAC0AIABzAHQAYQByAHQAKQAgAC8AIABiAGkAbgBfAHcAaQBkAHQAaAAsAFwAbgBcAG4AIAAgACAAIABiAGkAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAawAgACsAIAAxACwAIAAsACAAcwB0AGEAcgB0ACwAIABiAGkAbgBfAHcAaQBkAHQAaAApACwAXABuACAAIAAgACAAYgBpAG4AXwBzAHQAYQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABiAGkAbgAsACAALQAxACkALABcAG4AIAAgACAAIABiAGkAbgBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGIAaQBuACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBpAG4AIABhAHMAcwBpAGcAbgBtAGUAbgB0AFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAGEAcgByACwAIABiAGkAbgBfAHMAdABhAHIAdAAsACAALQAxACkALABcAG4AIAAgACAAIAByAG8AdwBfAHMAdABhAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYgBpAG4AXwBzAHQAYQByAHQALAAgAGkAZAB4ACkALABcAG4AIAAgACAAIAByAG8AdwBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYgBpAG4AXwBlAG4AZAAsACAAaQBkAHgAKQAsAFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHIAbwB3AF8AcwB0AGEAcgB0ACwAIAByAG8AdwBfAGUAbgBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBnAGcAcgBlAGcAYQB0AGkAbwBuAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABHAFIATwBVAFAAQgBZACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAAdgBhAGwALAAgAGYAdQBuAGMAdABpAG8AbgAsACAASABlAGEAZABlAHIAcwA/ACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBoAGEAcgB0ACAAcAByAGUAcABcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAGEAZwBnACwAIAAxACkAIAAmACAAXAAiACAALQAgADwAXAAiACAAJgAgAEMASABPAE8AUwBFAEMATwBMAFMAKABhAGcAZwAsACAAMgApACwAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABhAGcAZwAsACAALAAgADIAKQAsAFwAbgAgACAAIAAgAGMAaABhAHIAdABfAGwAYQBiAGUAbABzACwAIAAgACAAIAAgACAAIAB7AFwAIgBCAGkAbgBcACIALAAgAFwAIgBBAGcAZwByAGUAZwBhAHQAZQBcACIAfQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAG0AbwBkAGUAcwBcAG4AIAAgACAAIABkAGEAdABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABoAGUAYQBkAGUAcgAsACAAYQBnAGcAKQAsAFwAbgAgACAAIAAgAGMAaABhAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGMAaABhAHIAdABfAGwAYQBiAGUAbABzACwAIABIAFMAVABBAEMASwAoAGEALAAgAGIAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AQwBoAGEAcgB0AD8ALAAgAGQAYQB0AGEALAAgAGMAaABhAHIAdAApACwAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgB5AFwAbgApACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARwByAG8AdQBwAGIAeQBEAGEAdABlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAVgBhAGwAaQBkAGEAdABlAEcARAC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQBnAGcAcgBlAGcAYQB0AGUAcwAgAHYAYQBsAHUAZQBzACAAYgB5ACAAcgBvAHcAIABmAGkAZQBsAGQAcwAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABkAGEAdABlAHMALAAgAHUAcwBpAG4AZwAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZABcAG4AIAAgACAAIABkAGEAdABlAC8AdABpAG0AZQAgAGkAbgB0AGUAcgB2AGEAbAAgACgAbQBpAG4AdQB0AGUALAAgAGgAbwB1AHIALAAgAGQAYQB5ACwAIAB3AGUAZQBrACwAIABmAG8AcgB0AG4AaQBnAGgAdAAsACAAbQBvAG4AdABoACwAIABxAHUAYQByAHQAZQByACwAXABuACAAIAAgACAAeQBlAGEAcgApAC4AIABTAHUAcABwAG8AcgB0AHMAIABvAHAAdABpAG8AbgBhAGwAIABoAGUAYQBkAGUAcgBzACwAIABjAHUAcwB0AG8AbQAgAGYAbwByAG0AYQB0AHQAaQBuAGcALAAgAGEAbgBkACAAcgBvAHcAIABmAGkAbAB0AGUAcgBpAG4AZwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAgACgAMQBEACAAbwByACAAMgBEACkAIAB3AGkAdABoACAAZABhAHQAZQBzACAAaQBuACAAdABoAGUAIABsAGUAZgB0AG0AbwBzAHQAIABjAG8AbAB1AG0AbgAuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAgACgAMQBEACAAbwByACAAMgBEACkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAuAFwAbgAgACAAIAAgAGkAbgB0AGUAcgB2AGEAbAAgACAAIAAgACAAIAAgACAALQAgAEQAYQB0AGUALwB0AGkAbQBlACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAaQBuAHQAZQByAHYAYQBsACAAKABuAHUAbQBiAGUAcgAgAG8AcgAgAHQAZQB4AHQAKQAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgACAAIAAgACAALQAgAEUAVABBABEgYwBvAG0AcABhAHQAaQBiAGwAZQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AcgAgAHMAaQBuAGcAbABlABEgcABhAHIAYQBtAGUAdABlAHIAIABMAEEATQBCAEQAQQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBmAG8AcgBtAGEAdABdACAAIAAgACAAIAAgACAAIAAtACAAQwB1AHMAdABvAG0AIABkAGEAdABlAC8AdABpAG0AZQAgAGYAbwByAG0AYQB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAgACAAIABbAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAHMAXQAgAC0AIABUAFIAVQBFACAAaQBmACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AHMAIABpAG4AYwBsAHUAZABlACAAaABlAGEAZABlAHIAcwAuAFwAbgAgACAAIAAgAFsAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkAXQAgACAALQAgAEIAbwBvAGwAZQBhAG4AIABhAHIAcgBhAHkAIAB0AG8AIABmAGkAbAB0AGUAcgAgAHIAbwB3AHMAIABiAGUAZgBvAHIAZQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcgBvAHcAXwBmAGkAZQBsAGQAcwAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAaQBuAHQAZQByAHYAYQBsACwAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAXABuACAAIAAgACAAWwBmAG8AcgBtAGEAdABdACwAXABuACAAIAAgACAAWwBmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBzAF0ALABcAG4AIAAgACAAIABbAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5AF0ALABcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBHAEQAuwMoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgAHYAYQBsAHUAZQBzACwAIABpAG4AdABlAHIAdgBhAGwALAAgAGYAdQBuAGMAdABpAG8AbgAsACAAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAcwAsACAAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASQBuAHQAZQByAHYAYQBsACAAbgBvAHIAbQBhAGwAaQB6AGEAdABpAG8AbgBcAG4AIAAgACAAIABOAHUAbQBJAG4AdABlAHIAdgBhAGwAPwAsACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMAVABFAFgAVAAoAGkAbgB0AGUAcgB2AGEAbAApACkALABcAG4AXABuACAAIAAgACAAYwBvAG4AcwB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiAG0AaQBuAHUAdABlAFwAIgA7AFwAIgBoAG8AdQByAFwAIgA7AFwAIgBkAGEAeQBcACIAOwBcACIAdwBlAGUAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBvAHIAdABuAGkAZwBoAHQAXAAiADsAXAAiAG0AbwBuAHQAaABcACIAOwBcACIAcQB1AGEAcgB0AGUAcgBcACIAOwBcACIAeQBlAGEAcgBcACIAfQAsAFwAbgBcAG4AIAAgACAAIABpAG4AdABlAHIAdgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgB1AG0ASQBuAHQAZQByAHYAYQBsAD8ALABpAG4AdABlAHIAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAEwATwBXAEUAUgAoAGkAbgB0AGUAcgB2AGEAbAApACAAJgAgAFwAIgAqAFwAIgAsACAAYwBvAG4AcwB0ACwAIAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIABJAG4AYwBsAHUAZABlAHMAXwBlAG4AZAA/ACwAIAAgACAAIAAgACAAKABpAG4AdABlAHIAdgBhAGwAIAA9ACAANAApACAAKwAgACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADUAKQAsAFwAbgBcAG4AIAAgACAAIAB1AG4AaQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKABpAG4AdABlAHIAdgBhAGwALAAgADEANAA0ADAALAAgADIANAAsACAAMQAsACAAMQAsACAAMQAsACAAMQAsACAAMQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAXABuACAAIAAgACAATgBvAEYAbwByAG0AYQB0AD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAZgBvAHIAbQBhAHQAKQAsAFwAbgAgACAAIAAgAEgAZQBhAGQAZQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAcwApACkALABcAG4AIAAgACAAIABGAGkAbAB0AGUAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGEAdABlACAAdgBlAGMAdABvAHIAIABmAHIAbwBtACAAcgBvAHcAXwBmAGkAZQBsAGQAcwBcAG4AIAAgACAAIABkAGEAdABlAF8AYwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASABlAGEAZABlAHIAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABUAEEASwBFACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAALAAgADEAKQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACwAIAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGEAdABlAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBuAHQAZQByAHYAYQBsACAAPAAgADMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABkAGEAdABlAF8AYwBvAGwAIAAqACAAdQBuAGkAdAAsACAAMAApACAALwAgAHUAbgBpAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAE4AVAAoAGQAYQB0AGUAXwBjAG8AbAApACkALABcAG4AXABuACAAIAAgACAAdgBhAGwAdQBlAHMAXwBoAGUAYQBkAGUAcgAsACAAIAAgACAAIAAgAFQAQQBLAEUAKAB2AGEAbAB1AGUAcwAsACAAMQApACwAXABuACAAIAAgACAAdgBhAGwAdQBlAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEgAZQBhAGQAZQByAD8ALAAgAEQAUgBPAFAAKAB2AGEAbAB1AGUAcwAsACAAMQApACwAIAB2AGEAbAB1AGUAcwApACwAXABuACAAIAAgACAAcgBvAHcAXwBkAGUAdABhAGkAbABzACwAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABEAFIATwBQACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAALAAgADEAKQAsACAASABlAGEAZABlAHIAPwApACwAXABuACAAIAAgACAAZgBpAGwAdABlAHIAXwB1AHMAZQBkACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEgAZQBhAGQAZQByAD8AIAAqACAARgBpAGwAdABlAHIAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABXAGkAZAB0AGgAcwBcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAHIAbwB3AF8AZgBpAGUAbABkAHMAKQAsAFwAbgAgACAAIAAgAHcAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAdgBhAGwAdQBlAHMAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB3ACAAKwAgAHcAXwAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGEAdABlACAAYgBvAHUAbgBkAHMAXABuACAAIAAgACAAbQBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBUACgATQBJAE4AKABkAGEAdABlAHMAKQApACwAXABuACAAIAAgACAAbQBhAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBUACgATQBBAFgAKABkAGEAdABlAHMAKQApACwAXABuACAAIAAgACAAbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ATwBOAFQASAAoAG0AaQBuACkALABcAG4AIAAgACAAIABkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABBAFkAKABtAGkAbgApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFkARQBBAFIAKABtAGkAbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAaQBtAGUAIABvAGYAIABmAGkAcgBzAHQAIABkAGEAdABlAFwAbgAgACAAIAAgAGYAaQByAHMAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAGQAYQB0AGUAcwApACwAXABuACAAIAAgACAAbABhAHMAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAZABhAHQAZQBzACkALABcAG4AIAAgACAAIABoAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABPAFUAUgAoAGYAaQByAHMAdAApACwAXABuACAAIAAgACAAbQBtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOAFUAVABFACgAZgBpAHIAcwB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBhAG4AZwBlAHMAXABuACAAIAAgACAAcwBlAGMAbwBuAGQAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAbABhAHMAdAAgAC0AIABmAGkAcgBzAHQAKQAgACoAIAA4ADYANAAwADAALABcAG4AIAAgACAAIABtAGkAbgB1AHQAZQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAHMAZQBjAG8AbgBkAHMAIAAvACAANgAwACwAIAAxACkALABcAG4AIAAgACAAIABoAG8AdQByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBpAG4AdQB0AGUAcwAgAC8AIAA2ADAALABcAG4AIAAgACAAIABkAGEAeQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAIAAtACAAbQBpAG4ALABcAG4AIAAgACAAIAB3AGUAZQBrAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAGQAYQB5AHMAIAAvACAANwAsACAAMQApACwAXABuACAAIAAgACAAZgBvAHIAdABuAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABkAGEAeQBzACAALwAgADEANAAsACAAMQApACwAXABuACAAIAAgACAAbQBvAG4AdABoAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAQQBUAEUARABJAEYAKABtAGkAbgAsACAAbQBhAHgALAAgAFwAIgBtAFwAIgApACwAXABuACAAIAAgACAAcQB1AGEAcgB0AGUAcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABtAG8AbgB0AGgAcwAgAC8AIAAzACwAIAAxACkALABcAG4AIAAgACAAIAB5AGUAYQByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAG0AbwBuAHQAaABzACAALwAgADEAMgAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBzAHAAbABhAHkAIABmAG8AcgBtAGEAdABzAFwAbgAgACAAIAAgAGgAXwBtAG0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABkAGEAeQBzACAAPgAgADEALAAgAFwAIgBtAC8AZAAvAHkAeQB5ACAAaAA6AG0AbQAgAEEATQAvAFAATQBcACIALAAgAFwAIgBoADoAbQBtACAAQQBNAC8AUABNAFwAIgApACwAXABuACAAIAAgACAAbQBtAG0AbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAG0AbQBtACAAeQB5AHkAXAAiACwAXABuACAAIAAgACAAZABhAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAC8AZAAvAHkAeQB5AFwAIgAsAFwAbgAgACAAIAAgAHkAeQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAeQB5AHkAXAAiACwAXABuAFwAbgAgACAAIAAgAGYAbQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8ARgBvAHIAbQBhAHQAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAaQBuAHQAZQByAHYAYQBsACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEALAAgAGgAXwBtAG0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAsACAAaABfAG0AbQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAzACwAIABkAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACwAIABkAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA1ACwAIABkAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA2ACwAIABtAG0AbQBtACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADcALAAgAG0AbQBtAG0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAOAAsACAAeQB5AHkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBtAG0AbQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBvAHIAbQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGEAdABlAC8AdABpAG0AZQAgAGEAcgByAGEAeQBzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIABtAGkAbgBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABAAG0AaQBuAHUAdABlAHMAIAArACAAMQAsACAALAAgAGYAaQByAHMAdAAsACAAMQAgAC8AIAAxADQANAAwACkAKQAsAFwAbgAgACAAIAAgAGgAcgBzAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAEAAaABvAHUAcgBzACAAKwAgADEALAAgACwAIABmAGkAcgBzAHQALAAgADEAIAAvACAAMgA0ACkAKQAsAFwAbgAgACAAIAAgAGQAYQB5AHMAXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGQAYQB5AHMAIAArACAAMQAsACAALAAgAG0AaQBuACwAIAAxACkAKQAsAFwAbgAgACAAIAAgAHcAZQBlAGsAcwBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEQAQQBUAEUAKAB5ACwAIABtACwAIABTAEUAUQBVAEUATgBDAEUAKAB3AGUAZQBrAHMAIAArACAAMQAsACAALAAgAGQALAAgADcAKQApACkALABcAG4AIAAgACAAIABmAG8AcgB0AF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABEAEEAVABFACgAeQAsACAAbQAsACAAUwBFAFEAVQBFAE4AQwBFACgAZgBvAHIAdABuAGkAZwBoAHQAIAArACAAMQAsACAALAAgAGQALAAgADEANAApACkAKQAsAFwAbgAgACAAIAAgAG0AbwBuAHQAaABfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEQAQQBUAEUAKAB5ACwAIABtACAAKwAgAFMARQBRAFUARQBOAEMARQAoAG0AbwBuAHQAaABzACAAKwAgADEALAAgACwAIAAwACkALAAgAGQAKQApACwAXABuACAAIAAgACAAcQB0AHIAcwBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARABBAFQARQAoAHkALAAgAG0AIAArACAAUwBFAFEAVQBFAE4AQwBFACgAcQB1AGEAcgB0AGUAcgBzACAAKwAgADEALAAgACwAIAAwACwAIAAzACkALAAgAGQAKQApACwAXABuACAAIAAgACAAeQByAHMAXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARABBAFQARQAoAHkAIAArACAAUwBFAFEAVQBFAE4AQwBFACgAQAB5AGUAYQByAHMAIAArACAAMQAsACAALAAgADAAKQAsACAAbQAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHQAZQByAHYAYQBsACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAYgBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgAaQBuAHQAZQByAHYAYQBsACAAPAAgADMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAEMASABPAE8AUwBFACgAaQBuAHQAZQByAHYAYQBsACwAIABtAGkAbgBfAGEAcgByACgAKQAsACAAaAByAHMAXwBhAHIAcgAoACkAKQAgACoAIAB1AG4AaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADAAKQAgAC8AIAB1AG4AaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAG4AdABlAHIAdgBhAGwAIAAtACAAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGEAeQBzAF8AYQByAHIAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAZQBlAGsAcwBfAGEAcgByACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAG8AcgB0AF8AYQByAHIAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AbwBuAHQAaABfAGEAcgByACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHQAcgBzAF8AYQByAHIAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHkAcgBzAF8AYQByAHIAKAApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAYQBiAGUAbAAgAGEAcwBzAGkAZwBuAG0AZQBuAHQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADgALABYAE0AQQBUAEMASAAoAFkARQBBAFIAKABkAGEAdABlAHMAKQAsACAAWQBFAEEAUgAoAGIAaQBuACgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATQBBAFQAQwBIACgAZABhAHQAZQBzACwAIABiAGkAbgAoACkALAAgAC0AMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGEAdABlAF8AZgBpAGUAbABkACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAE4ARABFAFgAKABiAGkAbgAoACkALAAgAGkAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGwAYQBiAGUAbABzAFwAbgAgACAAIAAgAHIAbwB3AF8AbABhAGIAZQBsAHMALAAgACAAIAAgACAAIAAgACAAIABJAEYAKAB3ACAAPQAgADEALABkAGEAdABlAF8AZgBpAGUAbABkACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAZABhAHQAZQBfAGYAaQBlAGwAZAAoACkALAAgAHIAbwB3AF8AZABlAHQAYQBpAGwAcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAASABlAGEAZABlAHIAcwBcAG4AIAAgACAAIAB0AG8AdABhAGwAXwBsAGEAYgBlAGwALAAgACAAIAAgACAAIAAgACAAUwBXAEkAVABDAEgAKABpAG4AdABlAHIAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxACwAIABcACIAVABvAHQAYQBsAHMAIABiAHkAIABtAGkAbgB1AHQAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAyACwAIABcACIAVABvAHQAYQBsAHMAIABiAHkAIABoAG8AdQByAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADMALAAgAFwAIgBUAG8AdABhAGwAcwAgAGIAeQAgAEQAYQB5AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADQALAAgAFwAIgBXAGUAZQBrAGwAeQAgAFQAbwB0AGEAbABzAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADUALAAgAFwAIgBCAGkAdwBlAGUAawBsAHkAIABUAG8AdABhAGwAcwBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA2ACwAIABcACIATQBvAG4AdABoAGwAeQAgAFQAbwB0AGEAbABzAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADcALAAgAFwAIgBUAG8AdABhAGwAcwAgAGIAeQAgAFEAdQBhAHIAdABlAHIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAOAAsACAAXAAiAFkAZQBhAHIAbAB5ACAAVABvAHQAYQBsAHMAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAHQAbwB0AGEAbABfAGgAZQBhAGQAZQByACwAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAEkARgAoAE8AUgAoAGkAbgB0AGUAcgB2AGEAbAAgAD0AIAA0ACwAIABpAG4AdABlAHIAdgBhAGwAIAA9ACAANQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHQAbwB0AGEAbABfAGwAYQBiAGUAbAAsACAAXAAiAEUAbgBkAGkAbgBnACAARABhAHQAZQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABvAHQAYQBsAF8AbABhAGIAZQBsACkALAAsAHcAIAArACAASQBuAGMAbAB1AGQAZQBzAF8AZQBuAGQAPwAsAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIABhAGcAZwBfAGgAZQBhAGQAZQByACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASABlAGEAZABlAHIAPwAsAHYAYQBsAHUAZQBzAF8AaABlAGEAZABlAHIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAFwAIgBcACIALAAgACwAIAB3AF8ALAAgAFwAIgBcACIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAZwBnAHIAZQBnAGEAdABpAG8AbgBcAG4AIAAgACAAIABuAG8AXwBmAGkAbAB0AGUAcgAsACAAIAAgACAAIAAgACAAIAAgACAARwBSAE8AVQBQAEIAWQAoAHIAbwB3AF8AbABhAGIAZQBsAHMALAAgAHYAYQBsAHUAZQBzACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgAEgAZQBhAGQAZQByAD8AKQAsAFwAbgAgACAAIAAgAGYAaQBsAHQAZQByAF8AaQBuAGMALAAgACAAIAAgACAAIAAgACAAIABHAFIATwBVAFAAQgBZACgAcgBvAHcAXwBsAGEAYgBlAGwAcwAsACAAdgBhAGwAdQBlAHMALAAgAGYAdQBuAGMAdABpAG8AbgAsACAASABlAGEAZABlAHIAPwAsACAALAAgACwAIABmAGkAbAB0AGUAcgBfAHUAcwBlAGQAKQAsAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABGAGkAbAB0AGUAcgA/ACwAIABmAGkAbAB0AGUAcgBfAGkAbgBjACwAIABuAG8AXwBmAGkAbAB0AGUAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3ACAAbABhAGIAZQBsACAAKAB1AG4AZgBvAHIAbQBhAHQAdABlAGQAKQAgAGEAbgBkACAAZgBvAHIAbQBhAHQAdABlAGQAXABuACAAIAAgACAAcgBvAHcAXwBsAGEAYgBlAGwALAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAVABBAEsARQAoAGEAZwBnACwAIAAsACAAMQApACkALABcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABUAEUAWABUACgAcgBvAHcAXwBsAGEAYgBlAGwAKAApACwAIABmAG0AdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAARQBuAGQAaQBuAGcAIABkAGEAdABlAHMAIABmAG8AcgAgAHcAZQBlAGsAbAB5ACAALwAgAGIAaQB3AGUAZQBrAGwAeQBcAG4AIAAgACAAIABiAGkAbgBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABpAG4AdABlAHIAdgBhAGwAIAA9ACAANAAsAFQARQBYAFQAKABhACgAKQAgACsAIAA2ACwAIABmAG0AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABpAG4AdABlAHIAdgBhAGwAIAA9ACAANQAsACAAVABFAFgAVAAoAGEAKAApACAAKwAgADEAMwAsACAAZgBtAHQAKQAsACAAMAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAbQBhAGkAbgBpAG4AZwAgAGMAbwBsAHUAbQBuAHMAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARABSAE8AUAAoAGEAZwBnACwAIAAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAYwBrAHMAXABuACAAIAAgACAAcwB0AGEAYwBrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgASABTAFQAQQBDAEsAKAB0AG8AdABhAGwAXwBoAGUAYQBkAGUAcgAsACAAYQBnAGcAXwBoAGUAYQBkAGUAcgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACgAKQAsACAAYgAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAHMAdABhAGMAawBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAdABvAHQAYQBsAF8AaABlAGEAZABlAHIALAAgAGEAZwBnAF8AaABlAGEAZABlAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACgAKQAsACAAYgBpAG4AXwBlAG4AZAAoACkALAAgAGIAKAApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADQALAAgAGkAbgB0AGUAcgB2AGEAbAAgAD0AIAA1ACkALAAgAHMAdABhAGMAawBfAGUAbgBkACwAIABzAHQAYQBjAGsAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAHkAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSABEgQwBPAFIARQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBHAEQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBvAHIAZQAgAFYAYQBsAGkAZABhAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBzACAAaQBuAHAAdQB0AHMAIABmAG8AcgAgAEcAcgBvAHUAcABiAHkARABhAHQAZQC7Ay4AIABFAG4AcwB1AHIAZQBzACAAdABoAGEAdAAgAHIAbwB3AF8AZgBpAGUAbABkAHMAIABjAG8AbgB0AGEAaQBuACAAdgBhAGwAaQBkAFwAbgAgACAAIAAgAGQAYQB0AGUAcwAsACAAdABoAGEAdAAgAGkAbgB0AGUAcgB2AGEAbABzACAAYQByAGUAIAByAGUAYwBvAGcAbgBpAHoAZQBkACwAIAB0AGgAYQB0ACAAdgBhAGwAdQBlAHMAIABhAG4AZAAgAGYAaQBsAHQAZQByAHMAIABhAGwAaQBnAG4AIABpAG4AXABuACAAIAAgACAAcwBoAGEAcABlACwAIABhAG4AZAAgAHQAaABhAHQAIAB0AGgAZQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGMAYQBsAGwAYQBiAGwAZQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAgAHcAaQB0AGgAIABkAGEAdABlAHMAIABpAG4AIAB0AGgAZQAgAGwAZQBmAHQAbQBvAHMAdAAgAGMAbwBsAHUAbQBuAC4AXABuACAAIAAgACAAdgBhAGwAdQBlAHMAIAAgACAAIAAgACAAIAAgACAAIAAtACAAQQByAHIAYQB5ACAAbwBmACAAdgBhAGwAdQBlAHMAIAB0AG8AIABhAGcAZwByAGUAZwBhAHQAZQAuAFwAbgAgACAAIAAgAGkAbgB0AGUAcgB2AGEAbAAgACAAIAAgACAAIAAgACAALQAgAEQAYQB0AGUALwB0AGkAbQBlACAAaQBuAHQAZQByAHYAYQBsACAAKABuAHUAbQBlAHIAaQBjACAAbwByACAAdABlAHgAdAApAC4AXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACAAIAAgACAAIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABzAGkAbgBnAGwAZQARIHAAYQByAGEAbQBlAHQAZQByACAATABBAE0AQgBEAEEALgBcAG4AIAAgACAAIABbAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAHMAXQAgAC0AIABUAFIAVQBFACAAaQBmACAAcgBvAHcAXwBmAGkAZQBsAGQAcwAvAHYAYQBsAHUAZQBzACAAaQBuAGMAbAB1AGQAZQAgAGgAZQBhAGQAZQByAHMALgBcAG4AIAAgACAAIABbAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5AF0AIAAgAC0AIABCAG8AbwBsAGUAYQBuACAAZgBpAGwAdABlAHIAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAE8AbgBfAFYAYQBsAGkAZABdACAAIAAgACAAIAAgAC0AIABFAHgAcAByAGUAcwBzAGkAbwBuACAAdABvACAAZQB2AGEAbAB1AGEAdABlACAAdwBoAGUAbgAgAGkAbgBwAHUAdABzACAAYQByAGUAIAB2AGEAbABpAGQALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABEAGUAdABlAGMAdABzACAAaQBuAHYAYQBsAGkAZAAgAGQAYQB0AGUAcwAsACAAbQBpAHMAcwBpAG4AZwAgAHQAaQBtAGUAIABjAG8AbQBwAG8AbgBlAG4AdABzACwAIABhAG4AZAAgAG0AYQBsAGYAbwByAG0AZQBkACAAaQBuAHQAZQByAHYAYQBsAHMALgBcAG4AIAAgACAAIAAiICAARQBuAHMAdQByAGUAcwAgAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgAHYAYQBsAHUAZQBzACwAIABhAG4AZAAgAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACAAaABhAHYAZQAgAG0AYQB0AGMAaABpAG4AZwAgAGgAZQBpAGcAaAB0AHMALgBcAG4AIAAgACAAIAAiICAARQBuAHMAdQByAGUAcwAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGMAYQBsAGwAYQBiAGwAZQAgAHYAaQBhACAAYQAgAHMAYQBmAGUAIABCAFkAUgBPAFcAIAB0AGUAcwB0AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBHAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcgBvAHcAXwBmAGkAZQBsAGQAcwAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAaQBuAHQAZQByAHYAYQBsACwAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAXABuACAAIAAgACAAWwBmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBzAF0ALABcAG4AIAAgACAAIABbAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5AF0ALABcAG4AIAAgACAAIABbAE8AbgBfAFYAYQBsAGkAZABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAALQAtAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGwAYQBnAHMAIAAtAC0ALQBcAG4AIAAgACAAIABOAG8AXwBGAGkAZQBsAGQAXwBIAGUAYQBkAGUAcgBzAD8ALAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAHMAKQAsAFwAbgAgACAAIAAgAEYAaQBsAHQAZQByAEkAbgBjAGwAdQBkAGUAZAA/ACwAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABFAHgAdAByAGEAYwB0ACAAZABhAHQAZQAgAGEAbgBkACAAdgBhAGwAdQBlACAAYwBvAGwAdQBtAG4AcwAgAC0ALQAtAFwAbgAgACAAIAAgAEQAYQB0AGUAXwBjAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBfAEYAaQBlAGwAZABfAEgAZQBhAGQAZQByAHMAPwAsAFQAQQBLAEUAKAByAG8AdwBfAGYAaQBlAGwAZABzACwAIAAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAVABBAEsARQAoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACwAIAAxACkALAAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAFYAYQBsAHUAZQBzAF8AYwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBfAEYAaQBlAGwAZABfAEgAZQBhAGQAZQByAHMAPwAsAFQAQQBLAEUAKAB2AGEAbAB1AGUAcwAsACAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAFQAQQBLAEUAKAB2AGEAbAB1AGUAcwAsACAALAAgADEAKQAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABGAGkAbAB0AGUAcgAgAGEAcgByAGEAeQAgAG4AbwByAG0AYQBsAGkAegBhAHQAaQBvAG4AIAAtAC0ALQBcAG4AIAAgACAAIABCAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgASQBGACgATgBvAF8ARgBpAGUAbABkAF8ASABlAGEAZABlAHIAcwA/ACwAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACwAIAAxACkAIAApACwAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAARABhAHQAZQAgAHYAYQBsAGkAZABpAHQAeQAgAGMAaABlAGMAawBzACAALQAtAC0AXABuACAAIAAgACAATgBvAF8ARABhAHQAZQBzAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgARABhAHQAZQBfAGMAbwBsACAAPAAgADAALABEAGEAdABlAF8AYwBvAGwAIAA+ACAAMgA5ADUAOAA0ADYANQAsAE4ATwBUACgAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKABEAGEAdABlAF8AYwBvAGwAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIABOAG8AXwBUAGkAbQBlAHMAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAEQAYQB0AGUAXwBjAG8AbAAgAC0AIABJAE4AVAAoAEQAYQB0AGUAXwBjAG8AbAApACAAPQAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEQAaQBtAGUAbgBzAGkAbwBuACAAYwBoAGUAYwBrAHMAIAAtAC0ALQBcAG4AIAAgACAAIABpAF8AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgARABhAHQAZQBfAGMAbwBsACkALABcAG4AIAAgACAAIABpAF8AdgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAVgBhAGwAdQBlAHMAXwBjAG8AbAApACwAXABuACAAIAAgACAAaQBfAGYALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgARgBpAGwAdABlAHIASQBuAGMAbAB1AGQAZQBkAD8ALAAgAFIATwBXAFMAKABCAG8AbwBsACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEkAbgB0AGUAcgB2AGEAbAAgAHYAYQBsAGkAZABhAHQAaQBvAG4AIAAtAC0ALQBcAG4AIAAgACAAIABDAG8AbgBzAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgBtAGkAbgB1AHQAZQBcACIAOwBcACIAaABvAHUAcgBcACIAOwBcACIAZABhAHkAXAAiADsAXAAiAHcAZQBlAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBvAHIAdABuAGkAZwBoAHQAXAAiADsAXAAiAG0AbwBuAHQAaABcACIAOwBcACIAcQB1AGEAcgB0AGUAcgBcACIAOwBcACIAeQBlAGEAcgBcACIAfQAsAFwAbgBcAG4AIAAgACAAIABUAGUAeAB0AEkAbgB0AGUAcgB2AGEAbAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAGkAbgB0AGUAcgB2AGEAbAApACwAXABuACAAIAAgACAATgB1AG0AZQByAGkAYwBJAG4AdABlAHIAdgBhAGwAPwAsACAAIAAgACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgAaQBuAHQAZQByAHYAYQBsACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABJAG4AdABlAHIAdgBhAGwAPwAsACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABOAHUAbQBlAHIAaQBjAEkAbgB0AGUAcgB2AGEAbAA/ACwAIABPAFIAKABpAG4AdABlAHIAdgBhAGwAIAA8ACAAMQAsACAAaQBuAHQAZQByAHYAYQBsACAAPgAgADgAKQApACwAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABUAGUAeAB0AEkAbgB0AGUAcgB2AGEAbAA/ACwAIABJAFMATgBBACgAWABNAEEAVABDAEgAKABpAG4AdABlAHIAdgBhAGwAIAAmACAAXAAiACoAXAAiACwAIABDAG8AbgBzAHQALAAgADIAKQApACkALABUAFIAVQBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAQQBMAFMARQApACkALABcAG4AXABuACAAIAAgACAASQBzAFQAaQBtAGUAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBuAHQAZQByAHYAYQBsACAAPAAgADMALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABIAGEAbAB0AGkAbgBnACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAC0ALQAtAFwAbgAgACAAIAAgAEUAbQBwAHQAeQBJAG4AcAB1AHQAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAXwBmAGkAZQBsAGQAcwApACwAIABJAFMATwBNAEkAVABUAEUARAAoAHYAYQBsAHUAZQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIABIAGEAbAB0AEQAYQB0AGUAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGkAbgB0AGUAcgB2AGEAbAAgAD4AIAAyACwAIABOAG8AXwBEAGEAdABlAHMAPwApACwAXABuACAAIAAgACAASABhAGwAdABUAGkAbQBlAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAHMAVABpAG0AZQA/ACwAIABOAG8AXwBUAGkAbQBlAHMAPwApACwAXABuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGkAXwBkACAAPAA+ACAAaQBfAHYALABBAE4ARAAoAEYAaQBsAHQAZQByAEkAbgBjAGwAdQBkAGUAZAA/ACwAIABpAF8AZAAgADwAPgAgAGkAXwBmACkAKQAsAFwAbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEYAbgA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA8AD4AIAAxADIAOAAsAFwAbgBcAG4AIAAgACAAIABFAG0AcAB0AHkARgBpAGwAdABlAHIAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAEYAaQBsAHQAZQByAEkAbgBjAGwAdQBkAGUAZAA/ACwAIABOAE8AVAAoAE8AUgAoAEIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAbABlAGMAdAAgAGEAbABsACAAYwBvAG4AZABpAHQAaQBvAG4AcwBcAG4AIAAgACAAIABjAG8AbgBkAGkAdABpAG8AbgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAEUAbQBwAHQAeQBJAG4AcAB1AHQAcwA/ACwASABhAGwAdABEAGEAdABlAHMAPwAsAEgAYQBsAHQAVABpAG0AZQA/ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALABJAG4AdgBhAGwAaQBkAEkAbgB0AGUAcgB2AGEAbAA/ACwASQBuAHYAYQBsAGkAZABGAG4APwAsAEUAbQBwAHQAeQBGAGkAbAB0AGUAcgA/ACkALABcAG4AXABuACAAIAAgACAAaABhAGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAYwBvAG4AZABpAHQAaQBvAG4AcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAcwAgACgAYQBsAGkAZwBuAGUAZAAgAHcAaQB0AGgAIABHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMpAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMARQBNAFAAVABZAC0ASQBOAFAAVQBUACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8ALQBEAEEAVABFAFMAIQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAE4ATwAtAFQASQBNAEUAUwAhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMASQBOAFQARQBSAFYAQQBMACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBJAE4AVgBBAEwASQBEAC0ARgBVAE4AQwBUAEkATwBOACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBFAE0AUABUAFkALQBGAEkATABUAEUAUgAhAFwAIgB9ACwAXABuAFwAbgAgACAAIAAgAGEAbABlAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAZQByAHIAbwByAHMALAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMALAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAIAAtAC0ALQBcAG4AIAAgACAAIABJAEYAKABoAGEAbAB0ACwAIABhAGwAZQByAHQALAAgAE8AbgBfAFYAYQBsAGkAZAApAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA5AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUABpAHYAbwB0AGIAeQBDAGEAdAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAdAByAGUAYQBrALsDLAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFAAaQB2AG8AdABzACAAZABhAHQAYQAgAGIAeQAgAHIAbwB3ACAAZgBpAGUAbABkAHMAIAAoAGQAZQB0AGEAaQBsACAAKwAgAGQAYQB0AGUAKQAsACAAYwBhAHQAZQBnAG8AcgBpAGUAcwAsACAAYQBuAGQAIAB2AGEAbAB1AGUAcwAuAFwAbgAgACAAIAAgAEMAYQB0AGUAZwBvAHIAaQBlAHMAIABhAHIAZQAgAGEAcwBzAHUAbQBlAGQAIAB0AG8AIABiAGUAIABwAHIAZQARIGMAbwBuAGMAYQB0AGUAbgBhAHQAZQBkACAAdQBzAGkAbgBnACAAYQAgAGQAZQBsAGkAbQBpAHQAZQByAC4AXABuACAAIAAgACAAUwB1AHAAcABvAHIAdABzACAAbwBwAHQAaQBvAG4AYQBsACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAZgB1AG4AYwB0AGkAbwBuACAAYQBuAGQAIABkAGEAdABlACAAZgBvAHIAbQBhAHQAdABpAG4AZwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHIAbwB3AF8AZABlAHQAYQBpAGwAIAAgACAAIAAgACAALQAgADEARAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AbwBuABEgZABhAHQAZQAgAHIAbwB3ACAAZgBpAGUAbABkAHMALgBcAG4AIAAgACAAIAByAG8AdwBfAGQAYQB0AGUAcwAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIABkAGEAdABlAHMALgBcAG4AIAAgACAAIABjAGEAdABlAGcAbwByAGkAZQBzACAAIAAgACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIABkAGUAbABpAG0AaQB0AGUAZAAgAGMAYQB0AGUAZwBvAHIAeQAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAdgBhAGwAdQBlAHMALgBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAgACAAIAAgACAAIAAgAC0AIABEAGUAbABpAG0AaQB0AGUAcgAgAHUAcwBlAGQAIABpAG4AIAB0AGgAZQAgAGMAYQB0AGUAZwBvAHIAaQBlAHMAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAZABhAHQAZQBfAGYAbwByAG0AYQB0AF0AIAAgACAALQAgAEYAbwByAG0AYQB0ACAAYwBvAGQAZQAgAGYAbwByACAAZABhAHQAZQBzACAAKABkAGUAZgBhAHUAbAB0ACAAXAAiAHkAeQB5AFwAIgApAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAAIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABMAEEATQBCAEQAQQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAgACgAZABlAGYAYQB1AGwAdAAgAFMAVQBNACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABDAGEAdABlAGcAbwByAGkAZQBzACAAYQByAGUAIABzAHAAbABpAHQAIABpAG4AdABvACAAbQB1AGwAdABpAHAAbABlACAAcgBvAHcAcwAgAHUAcwBpAG4AZwAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMuAFwAbgAgACAAIAAgACIgIABEAGEAdABlAHMAIABhAHIAZQAgAGYAbwByAG0AYQB0AHQAZQBkACAAYQBuAGQAIABzAG8AcgB0AGUAZAAgAHUAcwBpAG4AZwAgAGEAIABuAHUAbQBlAHIAaQBjACAAcwBvAHIAdAAgAGsAZQB5AC4AXABuACAAIAAgACAAIiAgAFYAYQBsAHUAZQBzACAAYQByAGUAIABhAHAAcABvAHIAdABpAG8AbgBlAGQAIABhAGMAcgBvAHMAcwAgAHIAZQBwAGUAYQB0AGUAZAAgAGMAYQB0AGUAZwBvAHIAeQAgAHIAbwB3AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABpAHYAbwB0AGIAeQBDAGEAdAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAByAG8AdwBfAGQAZQB0AGEAaQBsACwAXABuACAAIAAgACAAcgBvAHcAXwBkAGEAdABlAHMALABcAG4AIAAgACAAIABjAGEAdABlAGcAbwByAGkAZQBzACwAXABuACAAIAAgACAAdgBhAGwAdQBlAHMALABcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsAFwAbgAgACAAIAAgAFsAZABhAHQAZQBfAGYAbwByAG0AYQB0AF0ALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAARABpAG0AZQBuAHMAaQBvAG4AcwAgAC0ALQAtAFwAbgAgACAAIAAgAHIAgSAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcgBvAHcAXwBkAGUAdABhAGkAbAApACwAXABuACAAIAAgACAAcgCCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAG8AdwBfAGQAYQB0AGUAcwApACwAXABuACAAIAAgACAAcgCDICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABjAGEAdABlAGcAbwByAGkAZQBzACkALABcAG4AIAAgACAAIAByAIQgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAYQBsAHUAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABIAGEAbAB0AGkAbgBnACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAC0ALQAtAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgALAAgACAAIAAgACAAIABPAFIAKAByAIEgIAA8AD4AIAByAIIgLAAgAHIAgSAgADwAPgAgAHIAgyAsACAAcgCBICAAPAA+ACAAcgCEICkALABcAG4AXABuACAAIAAgACAAZABhAHQAZQBfAGYAbwByAG0AYQB0ACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZABhAHQAZQBfAGYAbwByAG0AYQB0ACkALAAgAFwAIgB5AHkAeQBcACIALAAgAGQAYQB0AGUAXwBmAG8AcgBtAGEAdAApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARABhAHQAZQBzACwAIAAgACAAIAAgACAAIABPAFIAKABBAE4ARAAoAEkAUwBFAFIAUgBPAFIAKABEAEEAVABFAFYAQQBMAFUARQAoAFQARQBYAFQAKAByAG8AdwBfAGQAYQB0AGUAcwAsACAAZABhAHQAZQBfAGYAbwByAG0AYQB0ACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAEUAUgBSAE8AUgAoAFYAQQBMAFUARQAoAFQARQBYAFQAKAByAG8AdwBfAGQAYQB0AGUAcwAsACAAZABhAHQAZQBfAGYAbwByAG0AYQB0ACkAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABBAE4ARAAoAEkAUwBOAFUATQBCAEUAUgAoAHIAbwB3AF8AZABhAHQAZQBzACkAKQApACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4ALAAgACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuAFwAbgAgACAAIAAgAHMAYwBlAG4AYQByAGkAbwBzACwAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgALAAgAEkAbgB2AGEAbABpAGQARABhAHQAZQBzACwAIABJAG4AdgBhAGwAaQBkAEYAbgApACwAXABuAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBEAEEAVABFAFMAIQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBJAE4AVgBBAEwASQBEAC0ARgBVAE4AQwBUAEkATwBOACEAXAAiAH0ALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABMAG8AZwBpAGMAIABnAGEAdABlACAALQAtAC0AXABuACAAIAAgACAARgBJAEwAVABFAFIAKABlAHIAcgBvAHIAcwAsACAAcwBjAGUAbgBhAHIAaQBvAHMALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAALQAtAC0AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgAgAC0ALQAtAFwAbgAgACAAIAAgAGYAbgC7AywAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAdQBuAGMAdABpAG8AbgApACwAIABTAFUATQAsACAAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAATABvAGMAYQBsACAAaABlAGwAcABlAHIAcwAgAC0ALQAtAFwAbgAgACAAIAAgAEMAbwB1AG4AdABDAGEAdAC7AywAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIAbwB3ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABUAEUAWABUAFMAUABMAEkAVAAoAHIAbwB3ACwAIABkAGUAbABpAG0AaQB0AGUAcgApACkAKQAsAFwAbgBcAG4AIAAgACAAIABQAGEAcgBzAGUAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABhAHIAcgBhAHkALAAgAGkAbgBzAHQAYQBuAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABUAEUAWABUAEEARgBUAEUAUgAoAGQAZQBsAGkAbQBpAHQAZQByACAAJgAgAGEAcgByAGEAeQAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByACwAaQBuAHMAdABhAG4AYwBlACwALAAsAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsACwALAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBhAHQAZQBnAG8AcgBpAGUAcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABDAGEAdABlAGcAbwByAHkAIABlAHgAcABhAG4AcwBpAG8AbgAgAC0ALQAtAFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKABjAGEAdABlAGcAbwByAGkAZQBzACwAIABDAG8AdQBuAHQAQwBhAHQAuwMpACwAXABuAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDKABTAEUAUQBVAEUATgBDAEUAKAByAIEgKQAsACAAawApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAGUAYQBrALsDKABpACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABSAG8AdwAgAGYAaQBlAGwAZABzACAALQAtAC0AXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMoAHIAbwB3AF8AZABlAHQAYQBpAGwALAAgAGsAKQAsAFwAbgAgACAAIAAgAGQAZQB0AGEAaQBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABhACAAPQAgADAALAAgAFwAIgBVAG4AawBuAG8AdwBuAFwAIgAsACAAYQApACwAXABuAFwAbgAgACAAIAAgAGQAYQB0AGUAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDKABUAEUAWABUACgAcgBvAHcAXwBkAGEAdABlAHMALAAgAGQAYQB0AGUAXwBmAG8AcgBtAGEAdAApACwAIABrACkALABcAG4AIAAgACAAIABzAG8AcgB0AF8AawBlAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEQAQQBUAEUAVgBBAEwAVQBFACgAZABhAHQAZQBzACkALAAgAFYAQQBMAFUARQAoAGQAYQB0AGUAcwApACkALABcAG4AXABuACAAIAAgACAAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAcwBvAHIAdABfAGsAZQB5ACwAIABkAGUAdABhAGkAbAAsACAAZABhAHQAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABDAG8AbAB1AG0AbgAgAGYAaQBlAGwAZABzACAALQAtAC0AXABuACAAIAAgACAAdQBuAHAAYQBjAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMoAGMAYQB0AGUAZwBvAHIAaQBlAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgAGMAYQB0AGUAZwBvAHIAaQBlAHMALAAgACAAIAAgACAAIAAgACAAIABQAGEAcgBzAGUAuwMoAHUAbgBwAGEAYwBrACwAIABqACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABWAGEAbAB1AGUAcwAgACgAYQBwAHAAbwByAHQAaQBvAG4AZQBkACkAIAAtAC0ALQBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AygAdgBhAGwAdQBlAHMAIAAvACAAawAsACAAawApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAQQBnAGcAcgBlAGcAYQB0AGkAbwBuACAALQAtAC0AXABuACAAIAAgACAAYQBnAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABQAEkAVgBPAFQAQgBZACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsAGMAYQB0AGUAZwBvAHIAaQBlAHMALAB2AGEAbAB1AGUAcwAsAGYAbgC7AywALAAwACwALAAwACkALAAsADEAKQAsAFwAbgBcAG4AIAAgACAAIABhAGcAZwBcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgACAAWwBHAFIAMQA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARwByAG8AdQBwAEkAbgBkAGUAeAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAcwBzAGkAZwBuACAAbgB1AG0AZQByAGkAYwBhAGwAIABnAHIAbwB1AHAAIABpAG4AZABpAGMAZQBzACAAdABvACAAYQAgADEARAAgAGEAcgByAGEAeQAgACgAaABvAHIAaQB6AG8AbgB0AGEAbAAgAG8AcgAgAHYAZQByAHQAaQBjAGEAbAApAC4AXABuACAAIAAgACAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAdgBlAHIAdABpAGMAYQBsAGwAeQAgAGIAZQBmAG8AcgBlACAAaQBuAGQAaQBjAGUAcwAgAGEAcgBlACAAYQBzAHMAaQBnAG4AZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAdgBlAGMAdABvAHIAIAAgACAAIAAgACAAIAAgACAALQAgACAAIAAxAEQAIABhAHIAcgBhAHkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAdgBhAGwAdQBlAHMAIAB0AG8AIABiAGUAIABwAGwAYQBjAGUAZAAgAGkAbgAgAG4AdQBtAGUAcgBpAGMAYQBsACAAZwByAG8AdQBwAHMAXABuACAAIAAgACAAWwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAgACAALQAgACAAIABUAFIAVQBFACAAPQAgAGgAbwByAGkAegBvAG4AdABhAGwAIABvAHUAdABwAHUAdAA7ACAAbwBtAGkAdAB0AGUAZAAgAD0AIAB2AGUAcgB0AGkAYwBhAGwAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AIAAqAC8AXABuAEcAcgBvAHUAcABJAG4AZABlAHgAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAdgBlAGMAdABvAHIALABcAG4AIAAgACAAIABbAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdABcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAHYAZQBjAHQAbwByACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBoAGEAcABlAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAZQBjAHQAbwByACkALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAB2AGUAYwB0AG8AcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAASQBTAE8ATQBJAFQAVABFAEQAKABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgAEEATgBEACgAaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAaABlAGkAZwBoAHQAIAA+ACAAMQAwADQAOAA1ADcANgAsAGgAZQBpAGcAaAB0ACAAPgAgADEANgAzADgANAApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAB2AGUAYwB0AG8AcgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAIwBOAFUATQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEcAcgBvAHUAcAAgAGkAbgBkAGUAeAAgAD0AIABwAG8AcwBpAHQAaQBvAG4AIABvAGYAIABmAGkAcgBzAHQAIABvAGMAYwB1AHIAcgBlAG4AYwBlAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAWABNAEEAVABDAEgAKAB2AGUAYwB0AG8AcgAsACAAVQBOAEkAUQBVAEUAKAB2AGUAYwB0AG8AcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAaABhAHAAZQBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAaQBkAHgALAAgAFQATwBSAE8AVwAoAGkAZAB4ACkAKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAxADkAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABPAGMAYwB1AHIAcgBlAG4AYwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAASQBuAHMAdABhAG4AYwBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGUAbABlAGMAdABzACAAdABoAGUAIABOAEAdNB1fAG8AYwBjAHUAcgByAGUAbgBjAGUAcwAgAG8AZgAgAHIAbwB3AHMAIABmAHIAbwBtACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAYgB5ACAAbABvAGMAYQB0AGkAbgBnACAAdABoAGUAIABOAEAdNB0gAGkAbgBzAHQAYQBuAGMAZQBcAG4AIAAgACAAIABmAHIAbwBtACAAYQAgAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgAuACAAIABSAGUAcwB1AGwAdABzACAAYQByAGUAIAByAGUAdAB1AHIAbgBlAGQAIABpAG4AIABvAHIAZABlAHIAIABvAGYAIABhAHAAcABlAGEAcgBhAG4AYwBlACAAYQBuAGQAIABuAG8AdAAgAHMAbwByAHQAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAIAAgADIARAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABjAHIAaQB0AF8AdgBlAGMAdABvAHIAIAAgACAAIAAgAC0AIAAgACAAMQBEACAAYQByAHIAYQB5ACAAZABlAGYAaQBuAGkAbgBnACAAdABoAGUAIABzAHQAcgB1AGMAdAB1AHIAZQBcAG4AIAAgACAAIABOAEAdNB1fAG8AYwBjAHUAcgByAGUAbgBjAGUALAAgAC0AIAAgACAASQBuAHQAZQBnAGUAcgAgAG8AZgAgAHMAZQBsAGUAYwB0AGUAZAAgAG8AYwBjAHUAcgByAGUAbgBjAGUAcwAgACgAZQAuAGcALgAgADEALQBuACkAXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAE8AYwBjAHUAcgByAGUAbgBjAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgAsAFwAbgAgACAAIAAgAE4AQB00HV8AbwBjAGMAdQByAHIAZQBuAGMAZQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAaABhAHAAZQBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAaABlAGkAZwBoAHQAXwAsAFIATwBXAFMAKABjAHIAaQB0AF8AdgBlAGMAdABvAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGEAbAB0AGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAAaABlAGkAZwBoAHQAXwBtAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgAGgAZQBpAGcAaAB0ACAAPAA+ACAAaABlAGkAZwBoAHQAXwAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQATwBjAGMAdQByAHIAZQBuAGMAZQA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAE4AQB00HV8AbwBjAGMAdQByAHIAZQBuAGMAZQApACwATgBAHTQdXwBvAGMAYwB1AHIAcgBlAG4AYwBlACAAPQAgADAAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABoAGUAaQBnAGgAdABfAG0AaQBzAG0AYQB0AGMAaAA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABPAGMAYwB1AHIAcgBlAG4AYwBlAD8ALAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0AGkAbwBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABEAGUAcwBjAGUAbgBkAD8ALAAgACAAIABTAEkARwBOACgATgBAHTQdXwBvAGMAYwB1AHIAcgBlAG4AYwBlACkAIAA9ACAALQAxACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAZABlAG4AdABpAGYAeQAgAE4AdABoACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzAFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgAEkAbgBzAHQAYQBuAGMAZQC7AygAYwByAGkAdABfAHYAZQBjAHQAbwByACwALABEAGUAcwBjAGUAbgBkAD8AKQAgAD0AIABBAEIAUwAoAE4AQB00HV8AbwBjAGMAdQByAHIAZQBuAGMAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAZABhAHQAYQBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsAGIAbwBvAGwALAAwACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACAAIAAgACAAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADIAMABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcgByAGUAbgBjAGUAUgBhAG4AZwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAASQBuAHMAdABhAG4AYwBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGUAbABlAGMAdABzACAAYQAgAHIAYQBuAGcAZQAgAG8AZgAgAG8AYwBjAHUAcgByAGUAbgBjAGUAcwAgAG8AZgAgAHIAbwB3AHMAIABmAHIAbwBtACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAYgB5ACAAbABvAGMAYQB0AGkAbgBnACAAdABoAGUAIABOAEAdNB0gAGkAbgBzAHQAYQBuAGMAZQBzAFwAbgAgACAAIAAgAGYAcgBvAG0AIABhACAAYwByAGkAdABfAHYAZQBjAHQAbwByAC4AIABOAGUAZwBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMAIABhAHIAZQAgAHIAZQBqAGUAYwB0AGUAZAAgAGYAbwByACAAcwB0AGEAcgB0ACAAYQBuAGQAIABlAG4AZAAgAG8AYwBjAHUAcgByAGUAbgBjAGUAcwAuAFwAbgAgACAAIAAgAFIAZQBzAHUAbAB0AHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAgAGkAbgAgAG8AcgBkAGUAcgAgAG8AZgAgAGEAcABwAGUAYQByAGEAbgBjAGUAIABhAG4AZAAgAG4AbwB0ACAAcwBvAHIAdABlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAIAAgADIARAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABjAHIAaQB0AF8AdgBlAGMAdABvAHIAIAAgACAAIAAgACAAIAAtACAAIAAgADEARAAgAGEAcgByAGEAeQAgAGQAZQBmAGkAbgBpAG4AZwAgAHQAaABlACAAcwB0AHIAdQBjAHQAdQByAGUAXABuACAAIAAgACAAcwB0AGEAcgB0AF8AbwBjAGMAdQByAHIAZQBuAGMAZQAsACAALQAgACAAIABTAHQAYQByAHQAaQBuAGcAIABpAG4AdABlAGcAZQByACAAbwBmACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzAFwAbgAgACAAIAAgAFsAZQBuAGQAXwBvAGMAYwB1AHIAcgBlAG4AYwBlAF0AIAAgAC0AIAAgACAARQBuAGQAaQBuAGcAIABpAG4AdABlAGcAZQByACAAbwBmACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzAC4AIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAB0AGgAZQAgAHMAZQBsAGUAYwB0AGkAbwBuACAAbwBmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBmACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzACAAPQAgAHMAdABhAHIAdABfAG8AYwBjAHUAcgByAGUAbgBjAGUAIAB+ACAAZQBuAGQAIABvAGYAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACAAIAAgACAAIAAtACAAIAAgAFQAUgBVAEUAIAA9ACAAcwBlAGwAZQBjAHQAIABvAGMAYwB1AHIAcgBlAG4AYwBlACAAcgBhAG4AZwBlACAAZgByAG8AbQAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5ACAAYQByAHIAYQBuAGcAZQBkACAAZABhAHQAYQBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4ATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgAsAFwAbgAgACAAIAAgAHMAdABhAHIAdABfAG8AYwBjAHUAcgByAGUAbgBjAGUALABcAG4AIAAgACAAIABbAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQBdACwAXABuACAAIAAgACAAWwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAATgBPAFQAKABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQApACwAIABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AIAA9ACAAVABSAFUARQApACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABhAHIAcgBhAHkALABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQApACkALABcAG4AIAAgACAAIABjAHIAaQB0AF8AdgBlAGMAdABvAHIALAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABjAHIAaQB0AF8AdgBlAGMAdABvAHIALABUAFIAQQBOAFMAUABPAFMARQAoAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsAFwAbgAgACAAIAAgAEkAbgBjAGwAdQBkAGUARQBuAGQAPwAsACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABlAG4AZABfAG8AYwBjAHUAcgByAGUAbgBjAGUAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcwB0AGEAcgB0AC8AcwB0AG8AcABcAG4AIAAgACAAIABzAHQAYQByAHQAXwBvAGMAYwB1AHIAcgBlAG4AYwBlACwAIABJAE4ARABFAFgAKABzAHQAYQByAHQAXwBvAGMAYwB1AHIAcgBlAG4AYwBlACwAMQAsADEAKQAsAFwAbgAgACAAIAAgAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQAsACAAIAAgAEkARgAoAEkAbgBjAGwAdQBkAGUARQBuAGQAPwAsAEkATgBEAEUAWAAoAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQAsADEALAAxACkALABGAEEATABTAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAXABuACAAIAAgACAAaABlAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAaABlAGkAZwBoAHQAXwAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABoAGUAaQBnAGgAdABfAG0AaQBzAG0AYQB0AGMAaAA/ACwAIAAgACAAaABlAGkAZwBoAHQAIAA8AD4AIABoAGUAaQBnAGgAdABfACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQATwBjAGMAdQByAHIAZQBuAGMAZQA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAHMAdABhAHIAdABfAG8AYwBjAHUAcgByAGUAbgBjAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAXwBvAGMAYwB1AHIAcgBlAG4AYwBlACAAPAAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAG4AYwBsAHUAZABlAEUAbgBkAD8ALABJAFMAVABFAFgAVAAoAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAG4AYwBsAHUAZABlAEUAbgBkAD8ALABlAG4AZABfAG8AYwBjAHUAcgByAGUAbgBjAGUAIAA8ACAAcwB0AGEAcgB0AF8AbwBjAGMAdQByAHIAZQBuAGMAZQApACkALABcAG4AXABuACAAIAAgACAASQBGACgAaABlAGkAZwBoAHQAXwBtAGkAcwBtAGEAdABjAGgAPwAsACMAVgBBAEwAVQBFACEALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQATwBjAGMAdQByAHIAZQBuAGMAZQA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABJAGQAZQBuAHQAaQBmAHkAIABOAHQAaAAgAG8AYwBjAHUAcgByAGUAbgBjAGUAcwBcAG4AIAAgACAAIABpAG4AcwB0ACwAIAAgACAASQBuAHMAdABhAG4AYwBlALsDKABjAHIAaQB0AF8AdgBlAGMAdABvAHIAKQAsAFwAbgBcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAASQBGACgASQBuAGMAbAB1AGQAZQBFAG4AZAA/ACwAKABpAG4AcwB0ACAAPgA9ACAAcwB0AGEAcgB0AF8AbwBjAGMAdQByAHIAZQBuAGMAZQApACAAKgAgACgAaQBuAHMAdAAgADwAPQAgAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAaQBuAHMAdAAgAD4APQAgAHMAdABhAHIAdABfAG8AYwBjAHUAcgByAGUAbgBjAGUAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAZABhAHQAYQAgAGEAbgBkACAAdAByAGEAbgBwAG8AcwBlACAAaQBmACAAaABvAHIAaQB6AG8AbgB0AGEAbABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsAGIAbwBvAGwALAAwACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAByAGUAcwB1AGwAdAAsAFQAUgBBAE4AUwBQAE8AUwBFACgAcgBlAHMAdQBsAHQAKQApACwAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgAgACAAIAAgACkAKQApACkAKQA7AFwAbgBcAG4AXABuACAAIAAgACAAXABuAC8AKgAgAFsARwBSADEAMABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEcAcgBhAGkAbgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABEAG8AdwBuAHMAYQBtAHAAbABlAHMAIABhACAAYQByAHIAYQB5AF8AMgBEACAAYgB5ACAAYQBnAGcAcgBlAGcAYQB0AGkAbgBnACAAbwB2AGUAcgAgAG4AbwBuABEgbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAcwBwAGEAdABpAGEAbAAgAGIAbABvAGMAawBzAFwAbgAgACAAIAAgAG8AZgAgAHMAaQB6AGUAIABkAGUAcAB0AGgAIADXACAAdwBpAGQAdABoAC4AIABQAGEAcgB0AGkAYQBsACAAYgBsAG8AYwBrAHMAIABhAHQAIAB0AGgAZQAgAGUAZABnAGUAcwAgAGEAcgBlACAAaQBuAGMAbAB1AGQAZQBkAC4AIABUAGgAZQBcAG4AIAAgACAAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAAgAHUAcwBpAG4AZwAgAGEAbgAgAEUAVABBABEgYwBvAG0AcABhAHQAaQBiAGwAZQAgAGYAdQBuAGMAdABpAG8AbgAgACgAZQAuAGcALgAsACAAUwBVAE0ALABcAG4AIAAgACAAIABBAFYARQBSAEEARwBFACwAIABNAEEAWAAsACAATQBJAE4ALAAgAE0ARQBEAEkAQQBOACwAIABvAHIAIABhACAAYwB1AHMAdABvAG0AIABMAEEATQBCAEQAQQApAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgACAAIAAgAC0AIAAyAEQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAXwAyAEQALgBcAG4AIAAgACAAIABkAGUAcAB0AGgAIAAgACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwBzACAAcABlAHIAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIAB3AGkAZAB0AGgAIAAgACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAcABlAHIAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABMAEEATQBCAEQAQQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABlAGEAYwBoACAAYgBsAG8AYwBrAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAGoAZQBjAHQAcwAgAG4AbwBuABEgYQByAHIAYQB5AF8AMgBEACAAaQBuAHAAdQB0AHMALgBcAG4AIAAgACAAIAAiICAAUgBlAGoAZQBjAHQAcwAgAGkAbgB2AGEAbABpAGQAIABiAGwAbwBjAGsAIABzAGkAegBlAHMAIABvAHIAIAB0AGUAeAB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwAuAFwAbgAgACAAIAAgACIgIABQAGEAcgB0AGkAYQBsACAAYgBsAG8AYwBrAHMAIABhAHIAZQAgAGgAYQBuAGQAbABlAGQAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAdgBpAGEAIABJAE4ARABFAFgAIAArACAAVABPAEMATwBMAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEcAcgBhAGkAbgC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABkAGUAcAB0AGgALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALABcAG4AXABuAEkARgAoAE4ATwBUACgAVABZAFAARQAoAGEAcgByAGEAeQBfADIARAApACAAPQAgADYANAApACwAXAAiACMAYQByAHIAYQB5AF8AMgBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAE8AUgAoAGQAZQBwAHQAaAAgAD4AIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALAAgAHcAaQBkAHQAaAAgACAAPgAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAEkAUwBUAEUAWABUACgAZABlAHAAdABoACkALABJAFMAVABFAFgAVAAoAHcAaQBkAHQAaAApACkALABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAVABZAFAARQAoAGYAdQBuAGMAdABpAG8AbgApACAAPAA+ACAAMQAyADgALABcACIAIwBFAFQAQQAgAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAATgB1AG0AYgBlAHIAIABvAGYAIABiAGwAbwBjAGsAcwAgACgAcgBvAHUAbgBkAGUAZAAgAHUAcAApAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEAFUAUAAoAGgAIAAvACAAZABlAHAAdABoACwAIAAwACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARABVAFAAKAB3ACAALwAgAHcAaQBkAHQAaAAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbABvAGMAawAgAGEAbgBjAGgAbwByACAAZwByAGkAZABzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIABkAG8AdwBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAeAAsACAALAAgADEALAAgAGQAZQBwAHQAaAApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIAB5ACwAIAAxACwAIAAwACkAKQAsAFwAbgAgACAAIAAgAGEAYwByAG8AcwBzACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAeQAsACAAMQAsACAAdwBpAGQAdABoACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAeAAsACAALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbABvAGMAawAgAGEAZwBnAHIAZQBnAGEAdABvAHIAXABuACAAIAAgACAAQgBsAG8AYwBrAHMAuwMsACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpACwAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgALAAgACwAIAByACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHcAaQBkAHQAaAAsACAAMQAsACAAMAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABqACwAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIABjACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAZABlAHAAdABoACwAIAAsACAAMQAsACAAMAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsALAAgACAAVABPAEMATwBMACgASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIABpACgAKQAsACAAagAoACkAKQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAGYAdQBuAGMAdABpAG8AbgAoAGIAbABvAGMAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHMAdQBsAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAHQAbwAgAGUAYQBjAGgAIABiAGwAbwBjAGsAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABNAEEAUAAoAGQAbwB3AG4AKAApACwAIABhAGMAcgBvAHMAcwAoACkALAAgAEIAbABvAGMAawBzALsDKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMQAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBvAG8AcgBlAEEAZwBnALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFAAZQByAGYAbwByAG0AcwAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAG8AdgBlAHIAIABNAG8AbwByAGUAIABvAHIAIAB2AG8AbgAgAE4AZQB1AG0AYQBuAG4AIABuAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzACAAdQBzAGkAbgBnACAAYQBuAFwAbgAgACAAIAAgAEUAVABBABEgYwBvAG0AcABhAHQAaQBiAGwAZQAgAGYAdQBuAGMAdABpAG8AbgAgACgAUwBVAE0ALAAgAEEAVgBFAFIAQQBHAEUALAAgAE0AQQBYACwAIABNAEkATgAsACAATQBFAEQASQBBAE4ALAAgAG8AcgAgAGEAIABjAHUAcwB0AG8AbQBcAG4AIAAgACAAIABMAEEATQBCAEQAQQApAC4AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzACAAYwBvAG4AdAByAG8AbAAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAdAB5AHAAZQAgAGEAbgBkACAAaQBmACAAdABoAGUAXABuACAAIAAgACAAYwBlAG4AdABlAHIAIABjAGUAbABsACAAaQBzACAAdABvACAAYgBlACAAaQBuAGMAbAB1AGQAZQBkAC4AXABuAFwAbgBOAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzADoAXABuACAAIAAgACAATQBvAG8AcgBlACAAKAA4ABEgYwBvAG4AbgBlAGMAdABlAGQAKQA6ACAAIAAgACAAIAAgACAAIAB2AG8AbgAgAE4AZQB1AG0AYQBuAG4AIAAoADQAESBjAG8AbgBuAGUAYwB0AGUAZAApADoAXABuACAAIAAgACAAIAAgACAAIAAxACAAIAAyACAAIAAzACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAA0ACAAIABDACAAIAA2ACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADIAIAAgAEMAIAAgADMAXABuACAAIAAgACAAIAAgACAAIAA3ACAAIAA4ACAAIAA5ACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADQAXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQBfADIARAAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgACAAIAAgACAALQAgAEUAVABBACAAbwByACAATABBAE0AQgBEAEEAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABmAHUAbgBjAHQAaQBvAG4ALgBcAG4AIAAgACAAIABbAEkAcwB2AG8AbgBOAGUAdQBtAGEAbgBuAD8AXQAgAC0AIABUAFIAVQBFACAAkiEgAHUAcwBlACAAdgBvAG4AIABOAGUAdQBtAGEAbgBuACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQALgBcAG4AIAAgACAAIABbAG8AbQBpAHQAXwBjAGUAbgB0AGUAcgBdACAAIAAgAC0AIABUAFIAVQBFACAAkiEgAGUAeABjAGwAdQBkAGUAIABjAGUAbgB0AGUAcgAgAGMAZQBsAGwAIABmAHIAbwBtACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0AbwBvAHIAZQBBAGcAZwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABbAEkAcwB2AG8AbgBOAGUAdQBtAGEAbgBuAD8AXQAsAFwAbgAgACAAIAAgAFsAbwBtAGkAdABfAGMAZQBuAHQAZQByAF0ALABcAG4AXABuAEkARgAoAFQAWQBQAEUAKABhAHIAcgBhAHkAXwAyAEQAKQAgADwAPgAgADYANAAsAFwAIgAjAGEAcgByAGEAeQBfADIARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA8AD4AIAAxADIAOAAgACwAXAAiACMARQBUAEEAIABGAFUATgBDAFQASQBPAE4AIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIABJAHMAdgBvAG4ATgBlAHUAbQBhAG4AbgA/ACwAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAEkAcwB2AG8AbgBOAGUAdQBtAGEAbgBuAD8AKQApACwAXABuACAAIAAgACAAbwBtAGkAdABfAGMAZQBuAHQAZQByACwAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABvAG0AaQB0AF8AYwBlAG4AdABlAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaABlAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAGQAIABhAHIAcgBhAHkAXwAyAEQAIAB3AGkAdABoACAAXAAiAG8AbQBpAHQAXAAiACAAdABvACAAcwBhAGYAZQBsAHkAIABkAHIAbwBwACAAZQBkAGcAZQBzAFwAbgAgACAAIAAgAE0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFwAIgBvAG0AaQB0AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAXAAiAG8AbQBpAHQAXAAiACwAIABhAHIAcgBhAHkAXwAyAEQALAAgAFwAIgBvAG0AaQB0AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AbQBpAHQAXAAiACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AYQBsACAAdgBlAGMAdABvAHIAcwAgACgAZgBsAGEAdAB0AGUAbgBlAGQAKQBcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAVABPAEMATwBMACgARABSAE8AUAAoAE0ALAAgAC0AMgAsACAALQAyACkAKQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATgBXAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgACwAIAAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgAKQApACwAIAAgACAAIAAgACAAIAAvAC8AIABOAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgACwAIAAyACkALAAgAGgAZQBpAGcAaAB0ACkAKQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAEUAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgAKQApACwAIAAgACAAIAAgAC8ALwAgAFcAXABuACAAIAAgACAAYwBlAG4AdABlAHIALAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAAMQApACwAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACkAKQAsACAAIAAgACAAIAAgAC8ALwAgAEMAXABuACAAIAAgACAAZgAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAAMQApACwAIABoAGUAaQBnAGgAdAAsACAALQB3AGkAZAB0AGgAKQApACwAIAAgACAAIAAgAC8ALwAgAEUAXABuACAAIAAgACAAZwAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAC0AaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACkALAAgACAAIAAgAC8ALwAgAFMAVwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAtADEAKQAsACAALQBoAGUAaQBnAGgAdAAsACAALQB3AGkAZAB0AGgAKQApACwAIAAgACAALwAvACAAUwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAxACkALAAgAC0AaABlAGkAZwBoAHQALAAgAC0AdwBpAGQAdABoACkAKQAsACAAIAAgACAALwAvACAAUwBFAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZAAgAGEAcwBzAGUAbQBiAGwAaQBlAHMAXABuACAAIAAgACAATQBvAG8AcgBlAF8AbgBvAF8AYwBlAG4AdABlAHIALAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsAGIALABjACwAZAAsAGYALABnACwAaAAsAGkAKQAsAFwAbgAgACAAIAAgAE0AbwBvAHIAZQBfAHcAaQB0AGgAXwBjAGUAbgB0AGUAcgAsACAAIAAgACAAIABIAFMAVABBAEMASwAoAGEALABiACwAYwAsAGQALABjAGUAbgB0AGUAcgAsAGYALABnACwAaAAsAGkAKQAsAFwAbgBcAG4AIAAgACAAIAB2AG8AbgBfAG4AbwBfAGMAZQBuAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABiACwAZAAsAGYALABoACkALABcAG4AIAAgACAAIAB2AG8AbgBfAHcAaQB0AGgAXwBjAGUAbgB0AGUAcgAsACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABiACwAZAAsAGYALABoACwAYwBlAG4AdABlAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAGcAZwByAGUAZwBhAHQAbwByAFwAbgAgACAAIAAgAEEAZwBnAHIAZQBnAGEAdABlALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AKABUAE8AQwBPAEwAKABJAEYAUwAoAHYALAAgAHYAKQAsADIAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAdgBvAG4ATgBlAHUAbQBhAG4AbgA/ACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbwBtAGkAdABfAGMAZQBuAHQAZQByACwAQgBZAFIATwBXACgAdgBvAG4AXwBuAG8AXwBjAGUAbgB0AGUAcgAsACAAQQBnAGcAcgBlAGcAYQB0AGUAuwMpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKAB2AG8AbgBfAHcAaQB0AGgAXwBjAGUAbgB0AGUAcgAsACAAQQBnAGcAcgBlAGcAYQB0AGUAuwMpACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABvAG0AaQB0AF8AYwBlAG4AdABlAHIALABCAFkAUgBPAFcAKABNAG8AbwByAGUAXwBuAG8AXwBjAGUAbgB0AGUAcgAsACAAQQBnAGcAcgBlAGcAYQB0AGUAuwMpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKABNAG8AbwByAGUAXwB3AGkAdABoAF8AYwBlAG4AdABlAHIALAAgAEEAZwBnAHIAZQBnAGEAdABlALsDKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAaABhAHAAZQAgAGIAYQBjAGsAIAB0AG8AIABhAHIAcgBhAHkAXwAyAEQAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABXAFIAQQBQAFIATwBXAFMAKABhAGcAZwAsACAAdwBpAGQAdABoACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADEAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAE0AbwBvAHIAZQBTAGUAbABlAGMAdAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGUAbABlAGMAdABzACAAYQAgAHMAcABlAGMAaQBmAGkAYwAgAG4AZQBpAGcAaABiAG8AcgAgACgAMQATIDkAKQAgAGYAcgBvAG0AIAB0AGgAZQAgAE0AbwBvAHIAZQAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAZgBvAHIAIABlAGEAYwBoAFwAbgAgACAAIAAgAGUAbABlAG0AZQBuAHQAIABpAG4AIABhACAAYQByAHIAYQB5AF8AMgBEAC4AIABOAGUAaQBnAGgAYgBvAHIAIABpAG4AZABlAHgAIAA1ACAAcgBlAHQAdQByAG4AcwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABjAGUAbABsAC4AXABuAFwAbgBNAG8AbwByAGUAIABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZAA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgACAAIAAyACAAIAAgADMAXABuACAAIAAgACAAIAAgACAAIAA0ACAAIAAgAEMAIAAgACAANgBcAG4AIAAgACAAIAAgACAAIAAgADcAIAAgACAAOAAgACAAIAA5AFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAAIAAtACAAMgBEACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AF8AMgBEAC4AXABuACAAIAAgACAAbgBlAGkAZwBoAGIAbwByACAAIAAgACAALQAgAEkAbgB0AGUAZwBlAHIAIAAxABMgOQAgAGkAbgBkAGkAYwBhAHQAaQBuAGcAIAB3AGgAaQBjAGgAIABuAGUAaQBnAGgAYgBvAHIAIAB0AG8AIAByAGUAdAB1AHIAbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAG8AbwByAGUAUwBlAGwAZQBjAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAbgBlAGkAZwBoAGIAbwByACwAXABuAFwAbgBJAEYAKABUAFkAUABFACgAYQByAHIAYQB5AF8AMgBEACkAIAA8AD4AIAA2ADQALABcACIAIwBhAHIAcgBhAHkAXwAyAEQAIQBcACIALABcAG4AXABuACAAIAAgACAASQBGACgATgBPAFQAKABBAE4ARAAoAG4AZQBpAGcAaABiAG8AcgAgAD4APQAgADEALAAgAG4AZQBpAGcAaABiAG8AcgAgADwAPQAgADkALAAgAE4ATwBUACgASQBTAFQARQBYAFQAKABuAGUAaQBnAGgAYgBvAHIAKQApACkAKQAsAFwAIgAjAE4ARQBJAEcASABCAE8AUgAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBkACAAYQByAHIAYQB5AF8AMgBEACAAdwBpAHQAaAAgAHoAZQByAG8AcwAgACgAbgBvACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAbgBlAGUAZABlAGQAKQBcAG4AIAAgACAAIABoAHAAYQBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAAwACwAIAAsACAAdwBpAGQAdABoACAAKwAgADIALAAgADAAKQAsAFwAbgAgACAAIAAgAHYAcABhAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoADAALAAgAGgAZQBpAGcAaAB0ACwAIAAsACAAMAApACwAXABuACAAIAAgACAATQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAaABwAGEAZAAsACAASABTAFQAQQBDAEsAKAB2AHAAYQBkACwAIABhAHIAcgBhAHkAXwAyAEQALAAgAHYAcABhAGQAKQAsACAAaABwAGEAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AbwBvAHIAZQAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAZQB4AHQAcgBhAGMAdABpAG8AbgBcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAE0ALAAgAC0AMgAsACAALQAyACkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAE4AVwBcAG4AIAAgACAAIABiACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAsACAAMQApACwAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACkALAAgACAAIAAgACAAIAAgAC8ALwAgAE4AXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAALAAgADIAKQAsACAAaABlAGkAZwBoAHQAKQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAEUAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgAKQAsACAAIAAgACAAIAAvAC8AIABXAFwAbgAgACAAIAAgAGMAZQBuAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgADEALAAgADEAKQAsACAAaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACwAIAAgACAAIAAgACAALwAvACAAQwBcAG4AIAAgACAAIABmACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAAtAHcAaQBkAHQAaAApACwAIAAgACAAIAAgAC8ALwAgAEUAXABuACAAIAAgACAAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAC0AaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACwAIAAgACAAIAAvAC8AIABTAFcAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAC0AaABlAGkAZwBoAHQALAAgAC0AdwBpAGQAdABoACkALAAgACAAIAAvAC8AIABTAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgADEALAAgADEAKQAsACAALQBoAGUAaQBnAGgAdAAsACAALQB3AGkAZAB0AGgAKQAsACAAIAAgACAALwAvACAAUwBFAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAIABhAGwAbAAgADkAIABuAGUAaQBnAGgAYgBvAHIAcwAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5AFwAbgAgACAAIAAgAE0AbwBvAHIAZQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGEALAAgAGIALAAgAGMALAAgAGQALAAgAGMAZQBuAHQAZQByACwAIABmACwAIABnACwAIABoACwAIABpACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AcAB1AHQAZQAgAHMAdABhAHIAdABpAG4AZwAgAGMAbwBsAHUAbQBuACAAZgBvAHIAIAB0AGgAZQAgAGMAaABvAHMAZQBuACAAbgBlAGkAZwBoAGIAbwByAFwAbgAgACAAIAAgAHMAdABhAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAG4AZQBpAGcAaABiAG8AcgAgAC0AIAAxACkAIAAqACAAdwBpAGQAdABoACAAKwAgADEALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIAB0AGgAZQAgAG4AZQBpAGcAaABiAG8AcgAgAGIAbABvAGMAawBcAG4AIAAgACAAIABzAGUAbABlAGMAdABfAG4AZQBpAGcAaABiAG8AcgAsACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAE0AbwBvAHIAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHcAaQBkAHQAaAAsACAAcwB0AGEAcgB0ACkAKQAsAFwAbgBcAG4AIAAgACAAIABzAGUAbABlAGMAdABfAG4AZQBpAGcAaABiAG8AcgBcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAxADMAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABIAGkAcwB0AG8AZwByAGEAbQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABTAHQAYQB0AGkAcwB0AGkAYwBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABoAGkAcwB0AG8AZwByAGEAbQAgAHUAcwBpAG4AZwAgAGEAdQB0AG8AbQBhAHQAaQBjACAAYgBpAG4AbgBpAG4AZwAgAHIAdQBsAGUAcwAgACgAUwB0AHUAcgBnAGUAcwAsACAAUgBpAGMAZQAsAFwAbgAgACAAIAAgAFMAYwBvAHQAdAAsACAARgByAGUAZQBkAG0AYQBuACkAIABkAGUAcABlAG4AZABpAG4AZwAgAG8AbgAgAHMAYQBtAHAAbABlACAAcwBpAHoAZQAgAGEAbgBkACAAcwBrAGUAdwBuAGUAcwBzAC4AIABTAHUAcABwAG8AcgB0AHMAIABhAG4AXABuACAAIAAgACAAbwBwAHQAaQBvAG4AYQBsACAAZgBpAHgAZQBkACAAYgBpAG4AIAB3AGkAZAB0AGgAIABhAG4AZAAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAFAAYQByAGUAdABvACAAKABjAHUAbQB1AGwAYQB0AGkAdgBlACAAJQApACAAYwBvAGwAdQBtAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAE4AdQBtAGUAcgBpAGMAIABhAHIAcgBhAHkAIAAoADEARAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAWwBiAGkAbgBfAHcAaQBkAHQAaABdACAAIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAeABlAGQAIABiAGkAbgAgAHcAaQBkAHQAaAAgACgAMAAgADwAIAB3AGkAZAB0AGgAIABkIiAAMQAwADAAMAApAC4AXABuACAAIAAgACAAWwBpAG4AYwBsAHUAZABlAF8AUABhAHIAZQB0AG8AXQAgAC0AIABUAFIAVQBFACAAkiEgAGkAbgBjAGwAdQBkAGUAIABjAHUAbQB1AGwAYQB0AGkAdgBlACAAJQAgAGMAbwBsAHUAbQBuAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgACMAVgBBAEwAVQBFACEAIABpAGYAIABmAGUAdwBlAHIAIAB0AGgAYQBuACAAMgAgAHYAYQBsAHUAZQBzACAAYQByAGUAIABzAHUAcABwAGwAaQBlAGQALgBcAG4AIAAgACAAIAAiICAAQwBhAHAAcwAgAHQAbwB0AGEAbAAgAGIAaQBuAHMAIABhAHQAIAAxADAAMAAuAFwAbgAgACAAIAAgACIgIABJAGYAIABiAGkAbgBfAHcAaQBkAHQAaAAgAGkAcwAgAHMAdQBwAHAAbABpAGUAZAAsACAAYQB1AHQAbwBtAGEAdABpAGMAIAByAHUAbABlAHMAIABhAHIAZQAgAGIAeQBwAGEAcwBzAGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBIAGkAcwB0AG8AZwByAGEAbQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGIAaQBuAF8AdwBpAGQAdABoAF0ALABcAG4AIAAgACAAIABbAGkAbgBjAGwAdQBkAGUAXwBQAGEAcgBlAHQAbwBdACwAXABuAFwAbgBcAG4ASQBGACgAQwBPAFUATgBUACgAYQByAHIAYQB5ACkAIAA8AD0AIAAxACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABiAGkAbgBfAHcAaQBkAHQAaAApACkALABPAFIAKABiAGkAbgBfAHcAaQBkAHQAaAAgADwAIAAwACwAIABiAGkAbgBfAHcAaQBkAHQAaAAgAD4AIAAxADAAMAAwACkAKQAsAFwAIgAjAEIASQBOAC0AVwBJAEQAVABIACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAYQBtAHAAbABlACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuACAAIAAgACAAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAFMAbQBhAGwAbABEAGEAdABhAD8ALAAgACAAIAAgACAAbgAgADwAIAAyADAAMAAsAFwAbgAgACAAIAAgAEEAZABkAF8AUABhAHIAZQB0AG8APwAsACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGkAbgBjAGwAdQBkAGUAXwBQAGEAcgBlAHQAbwApACkALABcAG4AXABuACAAIAAgACAAbQBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAbQBhAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAcgBhAG4AZwBlACwAIAAgACAAIAAgACAAIAAgACAAIABtAGEAeAAgAC0AIABtAGkAbgAsAFwAbgAgACAAIAAgAGkAcQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUQBVAEEAUgBUAEkATABFACgAYQByAHIAYQB5ACwAIAAzACkAIAAtACAAUQBVAEEAUgBUAEkATABFACgAYQByAHIAYQB5ACwAIAAxACkALABcAG4AXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEsARQBXACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABJAHMAUwBrAGUAdwBlAGQAPwAsACAAIAAgACAAIAAgAEkARgAoAFMAbQBhAGwAbABEAGEAdABhAD8ALAAgAEYAQQBMAFMARQAsACAAQQBCAFMAKABzACkAIAA+ACAAMAAuADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAeABlAGQAIABiAGkAbgAgAHcAaQBkAHQAaABcAG4AIAAgACAAIABJAHMARgBpAHgAZQBkAD8ALAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABiAGkAbgBfAHcAaQBkAHQAaAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQB1AHQAbwBtAGEAdABpAGMAIABiAGkAbgBuAGkAbgBnACAAcgB1AGwAZQBzAFwAbgAgACAAIAAgAFMAdAB1AHIAZwBlACwAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAEwATwBHACgAbgAsACAAMgApACAAKwAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgAFMAUgBSACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAFMAUQBSAFQAKABuACkALAAgADEAKQAsAFwAbgAgACAAIAAgAFIAaQBjAGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoADIAIAAqACAAbgBeACgAMQAvADMAKQAsACAAMQApACwAXABuACAAIAAgACAAUwBjAG8AdAB0ACwAIAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAMwAuADUAIAAqACAAUwBUAEQARQBWAC4AUAAoAGEAcgByAGEAeQApACAALwAgAG4AXgAoADEALwAzACkALAAgADEAKQAsAFwAbgAgACAAIAAgAEYAcgBlAGUAZABtAGEAbgAsACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoADIAIAAqACAAaQBxAHIAIAAvACAAbgBeACgAMQAvADMAKQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAGYAaQB4AGUAZAAsACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAHIAYQBuAGcAZQAgAC8AIABiAGkAbgBfAHcAaQBkAHQAaAAsACAAMQAgAC8AIABiAGkAbgBfAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQBuACAAYwBvAHUAbgB0ACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARgBpAHgAZQBkAD8ALABmAGkAeABlAGQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbgAgADwAPQAgADMAMAAsAE0AQQBYACgAUwB0AHUAcgBnAGUALAAgAFIAaQBjAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAGsAZQB3AGUAZAA/ACwATQBJAE4AKABGAHIAZQBlAGQAbQBhAG4ALAAgADEANQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFMAYwBvAHQAdAAsACAAMQA1ACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQB2AG8AaQBkACAAcwBpAG4AZwBsAGUALQBiAGkAbgAgAG8AdQB0AHAAdQB0ADsAIABjAGEAcAAgAGEAdAAgADEAMAAwAFwAbgAgACAAIAAgAGsAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABJAEYAKABrACAAPQAgADEALAAgADUALAAgAGsAKQAsACAAMQAwADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGkAbgAgAGkAbgB0AGUAcgB2AGEAbABcAG4AIAAgACAAIABpAG4AdABlAHIAdgBhAGwALAAgACAAIAAgACAAIAAgAEkARgAoAHIAYQBuAGcAZQAgAD0AIAAwACwAIAAxACwAIABNAEEAWAAoAHIAYQBuAGcAZQAgAC8AIABrAF8ALAAgADAALgAxACkAKQAsAFwAbgAgACAAIAAgAGIAaQBuAF8AdQBwAHAAZQByACwAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAG0AYQB4ACwAIABpAG4AdABlAHIAdgBhAGwAKQAsAFwAbgAgACAAIAAgAGIAaQBuAF8AbABvAHcAZQByACwAIAAgACAAIAAgACAARgBMAE8ATwBSACgAbQBpAG4ALAAgAGkAbgB0AGUAcgB2AGEAbAApACwAXABuAFwAbgAgACAAIAAgAGIAaQBuAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAMQAgACsAIAAoAGIAaQBuAF8AdQBwAHAAZQByACAALQAgAGIAaQBuAF8AbABvAHcAZQByACkAIAAvACAAaQBuAHQAZQByAHYAYQBsACwALABiAGkAbgBfAGwAbwB3AGUAcgAsAGkAbgB0AGUAcgB2AGEAbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQBuACAAbABhAGIAZQBsAHMAXABuACAAIAAgACAAYgBpAG4AXwBzAHQAYQByAHQALAAgACAAIAAgACAAIABEAFIATwBQACgAYgBpAG4AXwBhAHIAcgAsACAALQAxACkALABcAG4AIAAgACAAIABiAGkAbgBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABiAGkAbgBfAGEAcgByACwAIAAxACkALABcAG4AXABuACAAIAAgACAAYgBpAG4AXwBoAGUAYQBkAGUAcgAsACAAIAAgACAAIAB7AFwAIgBTAHQAYQByAHQAXAAiACwAIABcACIARQBuAGQAXAAiACwAIABcACIAVABvAHQAYQBsAFwAIgB9ACwAXABuACAAIAAgACAAYgBpAG4AXwBsAGEAYgBlAGwAcwAsACAAIAAgACAAIABIAFMAVABBAEMASwAoAFYAUwBUAEEAQwBLACgAXAAiADwAXAAiACwAIABiAGkAbgBfAHMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVABBAEsARQAoAGIAaQBuAF8AcwB0AGEAcgB0ACwAIAAxACkALAAgAGIAaQBuAF8AZQBuAGQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAcgBlAHEAdQBlAG4AYwBpAGUAcwAgAGEAbgBkACAAUABhAHIAZQB0AG8AXABuACAAIAAgACAAZgByAGUAcQAsACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgARgBSAEUAUQBVAEUATgBDAFkAKABhAHIAcgBhAHkALAAgAGIAaQBuAF8AYQByAHIAKQAsACAALQAxACkALABcAG4AIAAgACAAIABQAGEAcgBlAHQAbwAsACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAGYAcgBlAHEALAAgAEwAQQBNAEIARABBACgAdgAsACAAUABFAFIAQwBFAE4AVABPAEYAKAB2ACwAIABmAHIAZQBxACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAGEAcwBzAGUAbQBiAGwAeQBcAG4AIAAgACAAIABzAHQAYQBjAGsALAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAYgBpAG4AXwBoAGUAYQBkAGUAcgAsACAASABTAFQAQQBDAEsAKABiAGkAbgBfAGwAYQBiAGUAbABzACwAIABmAHIAZQBxACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEEAZABkAF8AUABhAHIAZQB0AG8APwAsAFMATwBSAFQAKABIAFMAVABBAEMASwAoAHMAdABhAGMAawAsAFYAUwBUAEEAQwBLACgAXAAiAEMAdQBtAHUAbABhAHQAaQB2AGUAIAAlAFwAIgAsACAAUABhAHIAZQB0AG8AKQApACwAMwAsAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAGMAawApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMQA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBvAGQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABTAHQAYQB0AGkAcwB0AGkAYwBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdAB1AHIAbgBzACAAYQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAHQAaABlACAAbQBvAHMAdAAgAGYAcgBlAHEAdQBlAG4AdABsAHkAIABvAGMAYwB1AHIAcgBpAG4AZwAgAHYAYQBsAHUAZQBzACAAbwByAFwAbgAgACAAIAAgAHQAZQB4AHQAIABlAG4AdAByAGkAZQBzACAAaQBuACAAYQBuACAAYQByAHIAYQB5AC4AIABTAHUAcABwAG8AcgB0AHMAIABhAG4AIABvAHAAdABpAG8AbgBhAGwAIAB0AG8AdABhAGwAcwAgAGMAbwBsAHUAbQBuACAAcwBoAG8AdwBpAG4AZwBcAG4AIAAgACAAIAB0AGgAZQAgAGMAbwB1AG4AdAAgAG8AZgAgAGUAYQBjAGgAIABtAG8AZABlAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAQQByAHIAYQB5ACAAKAAxAEQAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAFsAaQBuAGMAbAB1AGQAZQBfAHQAbwB0AGEAbABzAF0ALQAgAFQAUgBVAEUAIACSISAAaQBuAGMAbAB1AGQAZQAgAGMAbwB1AG4AdABzACAAbwBmACAAZgByAGUAcQB1AGUAbgB0ACAAdgBhAGwAdQBlAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIAB0AGgAZQAgAGEAcgByAGEAeQAgAGMAbwBuAHQAYQBpAG4AcwAgAG4AbwAgAHQAZQB4AHQALAAgAE0ATwBEAEUALgBNAFUATABUACAAaQBzACAAdQBzAGUAZAAgAGYAbwByACAAbgB1AG0AZQByAGkAYwAgAG0AbwBkAGUALgBcAG4AIAAgACAAIAAiICAASQBmACAAbgBvACAAcgBlAHAAZQBhAHQAcwAgAGUAeABpAHMAdAAsACAAcgBlAHQAdQByAG4AcwAgAFwAIgAjAE4ATwAtAFIARQBQAEUAQQBUAFMAIQBcACIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ATQBvAGQAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGkAbgBjAGwAdQBkAGUAXwB0AG8AdABhAGwAcwBdACwAXABuAFwAbgBJAEYAKABDAE8AVQBOAFQAKAAtAC0ASQBTAFQARQBYAFQAKABhAHIAcgBhAHkAKQApACAAPQAgADAALABNAE8ARABFAC4ATQBVAEwAVAAoAGEAcgByAGEAeQApACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE0AZQBzAHMAYQBnAGUAIABmAG8AcgAgAG4AbwAgAHIAZQBwAGUAYQB0AHMAXABuACAAIAAgACAAbQBzAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8ALQBSAEUAUABFAEEAVABTACEAXAAiACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAIABhAG4AZAAgAGMAbwBtAHAAdQB0AGUAIABtAG8AZABlACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABWACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAE8ARABFAC4ATQBVAEwAVAAoAFgATQBBAFQAQwBIACgAVgAsACAAVgApACkALABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAFMATwBSAFQAKABJAEYARQBSAFIATwBSACgASQBOAEQARQBYACgAVgAsACAAaQApACwAIABtAHMAZwApACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsAHMAIABmAG8AcgAgAHIAZQBwAGUAYQB0AGUAZAAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgAGsAZQBlAHAALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgAWABNAEEAVABDAEgAKABWACwAIAByAGUAcwB1AGwAdAApACkALABcAG4AIAAgACAAIAB0AG8AdABhAGwAcwAsACAAIAAgACAAIAAgACAAIAAgAEcAUgBPAFUAUABCAFkAKABWACwAIABWACwAIABDAE8AVQBOAFQAQQAsACAAMAAsACAAMAAsACAALAAgAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAbABpAHYAZQByACAAdABvAHQAYQBsAHMAIABpAGYAIAByAGUAcQB1AGUAcwB0AGUAZABcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgAaQBuAGMAbAB1AGQAZQBfAHQAbwB0AGEAbABzACwAIAByAGUAcwB1AGwAdAAgADwAPgAgAG0AcwBnACkALAB0AG8AdABhAGwAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcwB1AGwAdAApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADEANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFoAbwBuAGUAUwB0AGEAdAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABTAHQAYQB0AGkAcwB0AGkAYwBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABIAGkAcwB0AG8AZwByAGEAbQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQBnAGcAcgBlAGcAYQB0AGUAcwAgAHYAYQBsAHUAZQBzACAAYgB5ACAAXAAiAHoAbwBuAGUAcwBcACIAIABkAGUAdABlAHIAbQBpAG4AZQBkACAAYgB5ACAASABpAHMAdABvAGcAcgBhAG0AuwMuACAAVABoAGUAIABiAGkAbgAgAHcAaQBkAHQAaAAgAGkAcwBcAG4AIAAgACAAIABjAG8AbQBwAHUAdABlAGQAIABhAHMAIAAxADAAXgBtACAAdwBoAGUAcgBlACAAbQAgAGkAcwAgAHQAaABlACAAbQBvAHMAdAAgAGYAcgBlAHEAdQBlAG4AdAAgAGkAbgB0AGUAZwBlAHIAIABMAE8ARwAgAG0AYQBnAG4AaQB0AHUAZABlACAAbwBmAFwAbgAgACAAIAAgAHQAaABlACAAdgBhAGwAdQBlAHMALgAgAFMAdQBwAHAAbwByAHQAcwAgAEUAVABBACAAZgB1AG4AYwB0AGkAbwBuAHMAIABhAG4AZAAgAGMAdQBzAHQAbwBtACAATABBAE0AQgBEAEEAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABOAHUAbQBlAHIAaQBjACAAYQByAHIAYQB5ACAAKAAxAEQAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0AIAAgAC0AIABFAFQAQQAgAG8AcgAgAEwAQQBNAEIARABBACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAZgB1AG4AYwB0AGkAbwBuACAAKABkAGUAZgBhAHUAbAB0ACAAUwBVAE0AKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIAByAGUAdAB1AHIAbgAgAGYAdQBuAGMAdABpAG8AbgAoAGcAcgBpAGQAKQAuAFwAbgAgACAAIAAgACIgIABOAG8AbgARIG4AdQBtAGUAcgBpAGMAIABnAHIAaQBkAHMAIAByAGUAdAB1AHIAbgAgACMAVgBBAEwAVQBFACEALgBcAG4AIAAgACAAIAAiICAAWgBvAG4AZQBzACAAYQByAGUAIABhAHMAcwBpAGcAbgBlAGQAIAB2AGkAYQAgAEgAaQBzAHQAbwBnAHIAYQBtALsDIAB1AHMAaQBuAGcAIABhAHUAdABvAG0AYQB0AGkAYwAgAGIAaQBuAG4AaQBuAGcALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AWgBvAG4AZQBTAHQAYQB0ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABmAHUAbgBjAHQAaQBvAG4AXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgB1AG4AYwB0AGkAbwBuACkALAAgAFMAVQBNACwAIABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAFYAYQBsAGkAZABhAHQAaQBvAG4AIAAtAC0ALQBcAG4AIAAgACAAIABJAHMATgBvAG4ATgB1AG0APwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAFMAVABFAFgAVAAoAGcAcgBpAGQAKQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4APwAsACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAUgBPAFcAUwAoAGcAcgBpAGQAKQA9ADEALAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkAPQAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMATgBvAG4ATgB1AG0APwAsACAAIAAgACAAIAAgACAAIAAgACAAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQARgBuAD8ALAAgACAAIAAgACAAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAIABmAHUAbgBjAHQAaQBvAG4AKABnAHIAaQBkACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIABiAGkAbgAgAHcAaQBkAHQAaAAgAGYAcgBvAG0AIABtAGEAZwBuAGkAdAB1AGQAZQBcAG4AIAAgACAAIABtAGEAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAE0ATwBEAEUAKABJAE4AVAAoAEwATwBHACgAZwByAGkAZAApACkAKQAsACAAMQApACwAXABuACAAIAAgACAAYgBpAG4AXwB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgADEAMAAgAF4AIABtAGEAZwAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGkAcwB0AG8AZwByAGEAbQAgAGIAaQBuAHMAIAAoAGYAaQByAHMAdAAgAGMAbwBsAHUAbQBuACAAbwBuAGwAeQApAFwAbgAgACAAIAAgAGgAaQBzAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgARABSAE8AUAAoAEgAaQBzAHQAbwBnAHIAYQBtALsDKABnAHIAaQBkACwAIABiAGkAbgBfAHcAaQBkAHQAaAApACwAIAAyACkALAAgACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBzAHMAaQBnAG4AIAB6AG8AbgBlAHMAXABuACAAIAAgACAAegBvAG4AZQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBOAEEAKABYAE0AQQBUAEMASAAoAGcAcgBpAGQALAAgAGgAaQBzAHQALAAgAC0AMQApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABnAHIAaQBkACkALABcAG4AIAAgACAAIAB6ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAegBvAG4AZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBnAGcAcgBlAGcAYQB0AGUAIABiAHkAIAB6AG8AbgBlAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABHAFIATwBVAFAAQgBZACgAegAsACAAZwAsACAAZgB1AG4AYwB0AGkAbwBuACwAIAAsACAAMAApACwAXABuACAAIAAgACAAegBvAG4AZQBfAEkARABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABhAGcAZwAsACAALAAgADEAKQAsAFwAbgAgACAAIAAgAGcAcgBpAGQAXwB2AGEAbAB1AGUAcwAsACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQBnAGcALAAgACwAIAAtADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHIAbwBhAGQAYwBhAHMAdAAgAGEAZwBnAHIAZQBnAGEAdABlAGQAIAB2AGEAbAB1AGUAcwAgAGIAYQBjAGsAIAB0AG8AIABnAHIAaQBkACAAcwBoAGEAcABlAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAegBvAG4AZQBzACwAIAB6AG8AbgBlAF8ASQBEAHMALAAgAGcAcgBpAGQAXwB2AGEAbAB1AGUAcwAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAvACAAWwBUAFgAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ALwAvACAALQAtAC0AIwAjACAAMAA3ACAAFCAgAFQAZQB4AHQAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVABoAGkAcwAgAGMAYQB0AGUAZwBvAHIAeQAgAHAAcgBvAHYAaQBkAGUAcwAgAG8AcABlAHIAYQB0AG8AcgBzACAAdABoAGEAdAAgAG8AdgBlAHIAYwBvAG0AZQAgAGMAbwBtAG0AbwBuACAAbABpAG0AaQB0AGEAdABpAG8AbgBzACAAaQBuAFwAbgAgACAAIAAgAEUAeABjAGUAbAAnAHMAIABuAGEAdABpAHYAZQAgAHQAZQB4AHQAIABlAG4AZwBpAG4AZQAgACgAZQAuAGcALgAsACAAVABFAFgAVABTAFAATABJAFQAIABjAGEAbgBuAG8AdAAgAHMAcABpAGwAbAAgADIARAAgAHIAZQBzAHUAbAB0AHMAOwAgAEIAWQBSAE8AVwBcAG4AIAAgACAAIABjAGEAbgBuAG8AdAAgAGQAZQBwAGwAbwB5ACAAUwBPAFIAVAAgAHQAbwAgAGEAbABpAGcAbgAgAGMAbwBsAHUAbQBuAHMAKQAuACAAVABoAGUAcwBlACAAZgB1AG4AYwB0AGkAbwBuAHMAIABlAG4AYQBiAGwAZQAgAHMAdAByAHUAYwB0AHUAcgBhAGwAXABuACAAIAAgACAAYQBsAGkAZwBuAG0AZQBuAHQALAAgAGUAeAB0AHIAYQBjAHQAaQBvAG4ALAAgAGEAbgBkACAAdAByAGEAbgBzAGYAbwByAG0AYQB0AGkAbwBuACAAbwBmACAAdABlAHgAdAAgAGEAcgByAGEAeQBzACwAIABlAHgAdABlAG4AZABpAG4AZwAgAEUAeABjAGUAbAAnAHMAXABuACAAIAAgACAAYwBhAHAAYQBiAGkAbABpAHQAaQBlAHMAIABmAG8AcgAgAGIAbwB0AGgAIAAxAEQAIABhAG4AZAAgADIARAAgAGkAbgBwAHUAdABzAC4AXABuAFwAbgBGAHUAbgBjAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgAFMAbwByAHQAcwAgAGUAYQBjAGgAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAYQBsAHAAaABhAGIAZQB0AGkAYwBhAGwAbAB5AC4AXABuAFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4ARABpAHMAdABpAG4AYwB0ALsDXABuACAAIAAgACAAIAAgACAAIABDAGEAbABsAHMAIABBAGwAaQBnAG4AuwMgAHQAbwAgAHMAbwByAHQAIABhACAAMgBEACAAYQByAHIAYQB5ACwAIAB0AGgAZQBuACAAcgBlAHQAdQByAG4AcwAgAGQAaQBzAHQAaQBuAGMAdAAgAHYAYQBsAHUAZQBzAC4AXABuAFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4AVQBuAGkAcQB1AGUAuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAYQBsAGwAcwAgAEEAbABpAGcAbgC7AyAAdABvACAAcwBvAHIAdAAgAGEAIAAyAEQAIABhAHIAcgBhAHkALAAgAHQAaABlAG4AIAByAGUAdAB1AHIAbgBzACAAdQBuAGkAcQB1AGUAIAB2AGEAbAB1AGUAcwAuAFwAbgBcAG4AIAAgACAAIAAiICAAQwBvAGEAbABlAHMAYwBlALsDXABuACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABmAGkAcgBzAHQAIABuAG8AbgARIGUAbQBwAHQAeQAgAHYAYQBsAHUAZQAgAGEAYwByAG8AcwBzACAAbQB1AGwAdABpAHAAbABlACAAMgBEACAAYQByAHIAYQB5AHMAIAAoADIAIAB0AG8AIAA0ACAAaQBuAHAAdQB0AHMAKQAuAFwAbgBcAG4AIAAgACAAIAAiICAARQB4AHAAbABvAGQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABhAG4AIABlAHgAcABsAG8AZABlAGQAIABjAGgAYQByAGEAYwB0AGUAcgAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIAAiICAATgB1AG0AYgBlAHIAcwBPAG4AbAB5ALsDXABuACAAIAAgACAAIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABuAHUAbQBlAHIAaQBjACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIAAiICAAVABlAHgAdABPAG4AbAB5ALsDXABuACAAIAAgACAAIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIAB0AGUAeAB0ACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIAAiICAAUwBwAGwAaQB0ALsDXABuACAAIAAgACAAIAAgACAAIABTAHAAbABpAHQAcwAgADEARAAgAHQAZQB4AHQAIABhAHIAcgBhAHkAcwAgAHUAcwBpAG4AZwAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZAAgAGQAZQBsAGkAbQBpAHQAZQByACwAIAB3AGkAdABoACAAZgB1AGwAbAAgADIARAAgAHMAcABpAGwAbAAgAHMAdQBwAHAAbwByAHQALgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABBAGwAaQBnAG4AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABTAHAAbABpAHQAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAbwByAHQAcwAgAGUAYQBjAGgAIAByAG8AdwAgAGEAbABwAGgAYQBiAGUAdABpAGMAYQBsAGwAeQAgACgAZABlAGYAYQB1AGwAdAApACAAbwByACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAdwBoAGUAbgBcAG4AIAAgACAAIABiAHkAXwBjAG8AbAAgAD0AIABUAFIAVQBFAC4AIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABpAHMAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAaQBuAHQAZQByAG4AYQBsAGwAeQAgAHMAbwAgAHQAaABlAFwAbgAgACAAIAAgAHMAYQBtAGUAIABwAGkAcABlAGwAaQBuAGUAIABoAGEAbgBkAGwAZQBzACAAYgBvAHQAaAAgAG0AbwBkAGUAcwAuACAAUwBvAHIAdABpAG4AZwAgAGkAcwAgAGwAZQB4AGkAYwBvAGcAcgBhAHAAaABpAGMAXABuACAAIAAgACAAYQBuAGQAIABjAGEAcwBlABEgcwBlAG4AcwBpAHQAaQB2AGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAYgBlACAAYQBsAGkAZwBuAGUAZAAuAFwAbgAgACAAIAAgAFsAYgB5AF8AYwBvAGwAXQAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwALgAgAFQAUgBVAEUAIACSISAAcwBvAHIAdAAgAGUAYQBjAGgAIABjAG8AbAB1AG0AbgAgAHQAbwBwABEgdABvABEgYgBvAHQAdABvAG0ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBtAGkAdAB0AGUAZAAgAJIhIABzAG8AcgB0ACAAZQBhAGMAaAAgAHIAbwB3ACAAbABlAGYAdAARIHQAbwARIHIAaQBnAGgAdAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABUAEUAWABUAEoATwBJAE4AIAArACAAUwBwAGwAaQB0ALsDIABmAG8AcgAgAGYAYQBzAHQAIAByAG8AdwARIHcAaQBzAGUAIABjAGEAbgBvAG4AaQBjAGEAbABpAHoAYQB0AGkAbwBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEEAbABpAGcAbgC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIABzAG8AcgB0ACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBSAG8AdwBTAG8AcgB0AD8ALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYgB5AF8AYwBvAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAgACgAYQBsAHcAYQB5AHMAIABzAG8AcgB0ACAAcgBvAHcAcwApAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBSAG8AdwBTAG8AcgB0AD8ALAAgAGEAcgByAGEAeQAsACAAVABSAEEATgBTAFAATwBTAEUAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3ABEgdwBpAHMAZQAgAHMAbwByAHQAIACSISAAcwBjAGEAbABhAHIAIABqAG8AaQBuACAAdwBpAHQAaAAgAGkAbgB2AGkAcwBpAGIAbABlACAAcwBlAHAAYQByAGEAdABvAHIAXABuACAAIAAgACAAaQBuAHYAaQBzACwAIAAgACAAIAAgACAAVQBOAEkAQwBIAEEAUgAoADgAMgA5ADEAKQAsAFwAbgAgACAAIAAgAFIAbwB3AFMAbwByAHQAuwMsACAAIAAgAEwAQQBNAEIARABBACgAdgAsACAAVABFAFgAVABKAE8ASQBOACgAaQBuAHYAaQBzACwAIAAsACAAUwBPAFIAVAAoAHYALAAgACwAIAAsACAAMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgB2AGUAcgB0ACAAZQBhAGMAaAAgAHIAbwB3ACAAdABvACAAYQAgAGoAbwBpAG4AZQBkACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAagBvAGkAbgBlAGQALAAgACAAIAAgACAAQgBZAFIATwBXACgAYQByAHIAYQB5ACwAIABSAG8AdwBTAG8AcgB0ALsDKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAbABpAHQAIABiAGEAYwBrACAAaQBuAHQAbwAgAGMAbwBsAHUAbQBuAHMAXABuACAAIAAgACAAZQB4ACwAIAAgACAAIAAgACAAIAAgACAAUwBwAGwAaQB0ALsDKABqAG8AaQBuAGUAZAAsACAAaQBuAHYAaQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgAG8AcgBpAGcAaQBuAGEAbAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIABJAEYAKABJAHMAUgBvAHcAUwBvAHIAdAA/ACwAIABlAHgALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAZQB4ACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABBAGwAaQBnAG4ARABpAHMAdABpAG4AYwB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAQQBsAGkAZwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAGEAbABsAHMAIABBAGwAaQBnAG4AuwMgAHQAbwAgAGEAbABwAGgAYQBiAGUAdABpAGMAYQBsAGwAeQAgAHMAbwByAHQAIABlAGEAYwBoACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAsACAAdABoAGUAbgAgAHIAZQB0AHUAcgBuAHMAXABuACAAIAAgACAAZABpAHMAdABpAG4AYwB0ACAAdgBhAGwAdQBlAHMAIABhAGwAbwBuAGcAIAB0AGgAZQAgAHMAYQBtAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAYgBlACAAYQBsAGkAZwBuAGUAZAAgAGEAbgBkACAAZABlAGQAdQBwAGwAaQBjAGEAdABlAGQALgBcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0AIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsAC4AIABUAFIAVQBFACAAkiEgAG8AcABlAHIAYQB0AGUAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUALgAgAE8AbQBpAHQAdABlAGQAIACSISAAcgBvAHcAESB3AGkAcwBlAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARABJAFMAVABJAE4AQwBUACAAcgBlAG0AbwB2AGUAcwAgAGUAeABhAGMAdAAgAGQAdQBwAGwAaQBjAGEAdABlAHMALgBcAG4AIAAgACAAIAAiICAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQQBsAGkAZwBuAEQAaQBzAHQAaQBuAGMAdAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAZgBsAGEAZwBcAG4AIAAgACAAIABTAG8AcgB0AEIAeQBDAG8AbAA/ACwAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgB5AF8AYwBvAGwAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAbABpAGcAbgBtAGUAbgB0AFwAbgAgACAAIAAgAGEAbABpAGcAbgBlAGQALAAgACAAIAAgAEEAbABpAGcAbgC7AygAYQByAHIAYQB5ACwAIABiAHkAXwBjAG8AbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBzAHQAaQBuAGMAdAAgAHIAZQBtAG8AdgBhAGwAXABuACAAIAAgACAAdQAsACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABhAGwAaQBnAG4AZQBkACwAIABTAG8AcgB0AEIAeQBDAG8AbAA/ACwAIABUAFIAVQBFACkALABcAG4AXABuACAAIAAgACAAdQBcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEEAbABpAGcAbgBVAG4AaQBxAHUAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEEAbABpAGcAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBhAGwAbABzACAAQQBsAGkAZwBuALsDIAB0AG8AIABhAGwAcABoAGEAYgBlAHQAaQBjAGEAbABsAHkAIABzAG8AcgB0ACAAZQBhAGMAaAAgAHIAbwB3ACAAbwByACAAYwBvAGwAdQBtAG4ALAAgAHQAaABlAG4AIAByAGUAdAB1AHIAbgBzAFwAbgAgACAAIAAgAHUAbgBpAHEAdQBlACAAdgBhAGwAdQBlAHMAIABhAGwAbwBuAGcAIAB0AGgAZQAgAHMAYQBtAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAYgBlACAAYQBsAGkAZwBuAGUAZAAgAGEAbgBkACAAZABlAGQAdQBwAGwAaQBjAGEAdABlAGQALgBcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0AIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsAC4AIABUAFIAVQBFACAAkiEgAG8AcABlAHIAYQB0AGUAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUALgAgAE8AbQBpAHQAdABlAGQAIACSISAAcgBvAHcAESB3AGkAcwBlAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBOAEkAUQBVAEUAIAByAGUAbQBvAHYAZQBzACAAcgBlAHAAZQBhAHQAZQBkACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABiAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAZgBpAHIAcwB0ACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzAC4AXABuACAAIAAgACAAIiAgAE8AcgBpAGUAbgB0AGEAdABpAG8AbgAgAGkAcwAgAHAAcgBlAHMAZQByAHYAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEEAbABpAGcAbgBVAG4AaQBxAHUAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAZgBsAGEAZwBcAG4AIAAgACAAIABTAG8AcgB0AEIAeQBDAG8AbAA/ACwAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgB5AF8AYwBvAGwAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAbABpAGcAbgBtAGUAbgB0AFwAbgAgACAAIAAgAGEAbABpAGcAbgBlAGQALAAgACAAIAAgAEEAbABpAGcAbgC7AygAYQByAHIAYQB5ACwAIABiAHkAXwBjAG8AbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFUAbgBpAHEAdQBlACAAcgBlAG0AbwB2AGEAbABcAG4AIAAgACAAIAB1ACwAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAGEAbABpAGcAbgBlAGQALAAgAFMAbwByAHQAQgB5AEMAbwBsAD8AKQAsAFwAbgBcAG4AIAAgACAAIAB1AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQwBvAGEAbABlAHMAYwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAZgBpAHIAcwB0ACAAbgBvAG4AESBlAG0AcAB0AHkAIAB2AGEAbAB1AGUAIABhAGMAcgBvAHMAcwAgAG0AdQBsAHQAaQBwAGwAZQAgADIARAAgAGEAcgByAGEAeQBzACAAKAAyACAAdABvACAANAAgAGkAbgBwAHUAdABzACkALABcAG4AIAAgACAAIABlAHYAYQBsAHUAYQB0AGUAZAAgAGkAbgAgAHAAcgBpAG8AcgBpAHQAeQAgAG8AcgBkAGUAcgA6AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGEAcgByAGEAeQBfADEAIACSISAAYQByAHIAYQB5AF8AMgAgAJIhIABhAHIAcgBhAHkAXwAzACAAkiEgAGEAcgByAGEAeQBfADQAIACSISAAZgBpAGwAbABfAHYAYQBsAHUAZQBcAG4AXABuACAAIAAgACAAQQAgAGMAZQBsAGwAIABpAHMAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAXAAiAGUAbQBwAHQAeQBcACIAIABpAGYAIABpAHQAIABtAGEAdABjAGgAZQBzACAAYQBuAHkAIABvAGYAIAB0AGgAZQAgAGYAbwBsAGwAbwB3AGkAbgBnADoAXABuACAAIAAgACAAIAAgACAAIAAiICAATABFAE4AKABjAGUAbABsACkAIAA9ACAAMABcAG4AIAAgACAAIAAgACAAIAAgACIgIABjAGUAbABsACAAPQAgAEYAQQBMAFMARQBcAG4AIAAgACAAIAAgACAAIAAgACIgIABjAGUAbABsACAAPQAgAGkAZwBuAG8AcgBlACAAIAAgACgAdQBzAGUAcgARIHMAcABlAGMAaQBmAGkAZQBkACkAXABuAFwAbgAgACAAIAAgAEUAbQBwAHQAeQAgAGMAZQBsAGwAcwAgAGEAcgBlACAAcwBrAGkAcABwAGUAZAAgAHcAaABlAG4AIABkAGUAdABlAHIAbQBpAG4AaQBuAGcAIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAdgBhAGwAdQBlAC4AIABUAGgAaQBzACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzAFwAbgAgACAAIAAgAHUAcwBlAGYAdQBsACAAZgBvAHIAIAByAGUAYwBvAG0AcABvAHMAaQBuAGcAIABtAGEAcwBrAGUAZAAgAG8AcgAgAGwAYQB5AGUAcgBlAGQAIABhAHIAcgBhAHkAcwAgACgAZQAuAGcALgAsACAAcgBpAG4AZwBzACkAIABpAG4AdABvACAAYQAgAHMAaQBuAGcAbABlAFwAbgAgACAAIAAgAGMAbwBoAGUAcgBlAG4AdAAgAGcAcgBpAGQAIABhAGYAdABlAHIAIAB0AHIAYQBuAHMAZgBvAHIAbQBhAHQAaQBvAG4AcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMwBdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0AIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGkAZwBuAG8AcgBlAF0AIAAgACAAIAAgACAALQAgAFYAYQBsAHUAZQAgAHQAcgBlAGEAdABlAGQAIABhAHMAIABlAG0AcAB0AHkAIABkAHUAcgBpAG4AZwAgAG8AYwBjAHUAcABhAG4AYwB5ACAAZQB2AGEAbAB1AGEAdABpAG8AbgAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACAAIAAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAdwBoAGUAbgAgAGEAbABsACAAYQByAHIAYQB5AHMAIABzAHUAcABwAGwAeQAgAGEAbgAgAGUAbQBwAHQAeQAgAHYAYQBsAHUAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AYQBsAGUAcwBjAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsACAAYQByAHIAYQB5AF8AMgAsACAAWwBhAHIAcgBhAHkAXwAzAF0ALAAgAFsAYQByAHIAYQB5AF8ANABdACwAXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAYQByAHIAYQB5ACAAcAByAGUAcwBlAG4AYwBlAFwAbgAgACAAIAAgAEkAbgBjAGwAdQBkAGUAMwAsACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADMAKQApACwAXABuACAAIAAgACAASQBuAGMAbAB1AGQAZQA0ACwAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAzACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMwApACwAIABGAEEATABTAEUALAAgAGEAcgByAGEAeQBfADMAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADQALAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwA0ACkALAAgAEYAQQBMAFMARQAsACAAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbQBwAHQAeQARIHYAYQBsAHUAZQAgAHIAdQBsAGUAcwBcAG4AIAAgACAAIABpAGcAbgBvAHIAZQAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAaQBnAG4AbwByAGUAKQAsACAAXAAiAFwAIgAsACAAaQBnAG4AbwByAGUAKQAsAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAFwAIgBcACIALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsACAAIAAgACAAIAAgAHcALAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAaACCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACwAIAAgACAAIAAgACAAdwCCICwAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIABoAIMgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAzACkALAAgACAAIAAgACAAIAB3AIMgLAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADMAKQAsAFwAbgAgACAAIAAgAGgAhCAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADQAKQAsACAAIAAgACAAIAAgAHcAhCAsACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuACAAbQBpAHMAbQBhAHQAYwBoAGUAcwBcAG4AIAAgACAAIABTAF8AMgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGgAIAA8AD4AIABoAIIgLAAgAHcAIAA8AD4AIAB3AIIgKQAsAFwAbgAgACAAIAAgAFMAXwAzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAGMAbAB1AGQAZQAzACAAKgAgAE8AUgAoAGgAIAA8AD4AIABoAIMgLAAgAHcAIAA8AD4AIAB3AIMgKQAsAFwAbgAgACAAIAAgAFMAXwA0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAGMAbAB1AGQAZQA0ACAAKgAgAE8AUgAoAGgAIAA8AD4AIABoAIQgLAAgAHcAIAA8AD4AIAB3AIQgKQAsAFwAbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgAE8AUgAoAFMAXwAyACwAIABTAF8AMwAsACAAUwBfADQAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AYwBjAHUAcABhAG4AYwB5ACAAdABlAHMAdABcAG4AIAAgACAAIABPAGMAYwB1AHAAaQBlAGQAuwMsACAAIABMAEEATQBCAEQAQQAoAGEAcgByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACgAYQByAHIAIAA8AD4AIABGAEEATABTAEUAKQAgACoAKABMAEUATgAoAGEAcgByACkAIAA8AD4AIAAwACkAIAAqACAAKABhAHIAcgAgADwAPgAgAGkAZwBuAG8AcgBlACkAKQApACwAXABuAFwAbgAgACAAIAAgAG0AXwAxACwAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AygAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAbQBfADIALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIABtAF8AMwAsACAAIAAgACAAIAAgACAAIABPAGMAYwB1AHAAaQBlAGQAuwMoAGEAcgByAGEAeQBfADMAKQAsAFwAbgAgACAAIAAgAG0AXwA0ACwAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AygAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAcgBpAG8AcgBpAHQAeQAgAGMAaABhAGkAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIABJAEYAKABtAF8AMQAoACkALAAgAGEAcgByAGEAeQBfADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG0AXwAyACgAKQAsACAAYQByAHIAYQB5AF8AMgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8AMwAoACkALAAgAGEAcgByAGEAeQBfADMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8ANAAoACkALAAgAGEAcgByAGEAeQBfADQALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARQB4AHAAbABvAGQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAE0ARwByAGkAZAC7AywAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABhAG4AIABlAHgAcABsAG8AZABlAGQAIABjAGgAYQByAGEAYwB0AGUAcgAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAEUAeABwAGwAbwBzAGkAbwBuACAAYgBlAGgAYQB2AGkAbwByACAAZABlAHAAZQBuAGQAcwAgAG8AbgAgAHQAaABlACAAaQBuAHAAdQB0ACAAcwBoAGEAcABlADoAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIABlAHgAcABsAG8AZABlACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlAC4AXABuACAAIAAgACAAIAAgACAAIAAiICAAVgBlAHIAdABpAGMAYQBsACAAMQBEACAAYQByAHIAYQB5AHMAIABlAHgAcABsAG8AZABlACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlAC4AXABuACAAIAAgACAAIAAgACAAIAAiICAASABvAHIAaQB6AG8AbgB0AGEAbAAgADEARAAgAGEAcgByAGEAeQBzACAAZQB4AHAAbABvAGQAZQAgAHIAbwB3ABEgdwBpAHMAZQAuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgADIARAAgAGEAcgByAGEAeQBzACAAZQB4AHAAbABvAGQAZQAgAHIAbwB3ABEgdwBpAHMAZQAgAGIAeQAgAGQAZQBmAGEAdQBsAHQALAAgAG8AcgAgAHcAaQBkAHQAaAARIHcAaQBzAGUAIAB3AGgAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAGUAeABwAGwAbwBkAGUAXwAyAEQAXwBiAHkAYwBvAGwAIAA9ACAAVABSAFUARQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYwBhAG4AIABiAGUAIABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABvAHIAIAAyAEQALgBcAG4AIAAgACAAIABbAGUAeABwAGwAbwBkAGUAXwAyAEQAXwBiAHkAYwBvAGwAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAuACAAVABSAFUARQAgAJIhIABlAHgAcABsAG8AZABlACAAMgBEACAAYQByAHIAYQB5AHMAIAB3AGkAZAB0AGgAESB3AGkAcwBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAG0AaQB0AHQAZQBkACAAkiEgAGUAeABwAGwAbwBkAGUAIAByAG8AdwARIHcAaQBzAGUALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABMAEUATgAoAGEAcgByAGEAeQApACAAZABlAHQAZQByAG0AaQBuAGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAGMAaABhAHIAYQBjAHQAZQByACAAYwBvAHUAbgB0ACAAcABlAHIAIABjAGUAbABsAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAeABwAGwAbwBkAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBlAHgAcABsAG8AZABlAF8AMgBEAF8AYgB5AGMAbwBsAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEcAZQBvAG0AZQB0AHIAeQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAIAAgAGgAIAA+ACAAdwAsAFwAbgAgACAAIAAgAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8ALAAgACAAdwAgAD4AIABoACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAMQBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAFgATwBSACgAaAAgAD4AIAAxACwAIAB3ACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA+ACAAMQApACwAXABuACAAIAAgACAARABpAHIATwBtAGkAdAB0AGUAZAA/ACwAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGUAeABwAGwAbwBkAGUAXwAyAEQAXwBiAHkAYwBvAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAYQBsAGEAcgAgAGUAeABwAGwAbwBzAGkAbwBuAFwAbgAgACAAIAAgAEUAeABwAGwAbwBkAGUAUwBjAGEAbABhAHIALAAgACAAUgBFAEcARQBYAEUAWABUAFIAQQBDAFQAKABhAHIAcgBhAHkALAAgAFwAIgAuAFwAIgAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwARQB4AHAAbABvAGQAZQBTAGMAYQBsAGEAcgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGEAeABpAG0AdQBtACAAYwBoAGEAcgBhAGMAdABlAHIAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAGUAbABsAHMAXABuACAAIAAgACAAbQAsACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABMAEUATgAoAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIAAxAEQAIABpAG4AZABlAHgAaQBuAGcAIAAtAC0ALQBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsAFMARQBRAFUARQBOAEMARQAoACwAIABtACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAG0AKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIAAyAEQAIABpAG4AZABlAHgAaQBuAGcAIAAoAHYAZQByAHQAaQBjAGEAbAAgAGUAeABwAGwAbwBzAGkAbwBuACkAIAAtAC0ALQBcAG4AIAAgACAAIABpAF8ALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAUgBlAHMAaQB6AGUAuwMoACAASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKABtACAAKgAgAGgALAAgACwAIAAsACAAMQAgAC8AIABtACkAKQAsACAALAAgAHcAIAApACAAKQAsAFwAbgAgACAAIAAgAGoAXwAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAIABSAGUAcwBpAHoAZQC7AygAIABNAEcAcgBpAGQAuwMoAGEAcgByAGEAeQAsACAAMQApACwAIABtACAAKQAgACkALABcAG4AIAAgACAAIABzAHQAYQByAHQAXwBhAHQAXwAsACAAIABMAEEATQBCAEQAQQAoACAAUgBlAHMAaQB6AGUAuwMoACAAUwBFAFEAVQBFAE4AQwBFACgAbQApACwAIABoACwAIAB3ACAAKQAgACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIAAyAEQAIABpAG4AZABlAHgAaQBuAGcAIAAoAGgAbwByAGkAegBvAG4AdABhAGwAIABlAHgAcABsAG8AcwBpAG8AbgApACAALQAtAC0AXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAAgAFIAZQBzAGkAegBlALsDKAAgAE0ARwByAGkAZAC7AygAYQByAHIAYQB5ACkALAAgACwAIABtACAAKQAgACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAUgBlAHMAaQB6AGUAuwMoACAASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAbQAgACoAIAB3ACwAIAAsACAAMQAgAC8AIABtACkAKQAsACAAaAAgACkAIAApACwAXABuACAAIAAgACAAcwB0AGEAcgB0AF8AYQB0ACwAIAAgACAATABBAE0AQgBEAEEAKAAgAFIAZQBzAGkAegBlALsDKAAgAFMARQBRAFUARQBOAEMARQAoACwAIABtACkALAAgAGgALAAgAHcAIAApACAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABlAHgAcABsAG8AcwBpAG8AbgBcAG4AIAAgACAAIABlAHgAMQBEACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAATQBJAEQAKABhAHIAcgBhAHkALAAgAGkAZAB4ACgAKQAsACAAMQApACAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAyAEQAIABlAHgAcABsAG8AcwBpAG8AbgAgAHYAYQByAGkAYQBuAHQAcwBcAG4AIAAgACAAIABlAHgAMgBEAF8AVgAsACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAATQBJAEQAKABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAGkAXwAoACkALAAgAGoAXwAoACkAKQAsACAAcwB0AGEAcgB0AF8AYQB0AF8AKAApACwAIAAxACkAIAApACwAXABuACAAIAAgACAAZQB4ADIARABfAEgALAAgACAAIAAgACAATABBAE0AQgBEAEEAKAAgAE0ASQBEACgASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpACgAKQAsACAAIABqACgAKQApACwAIABzAHQAYQByAHQAXwBhAHQAKAApACwAIAAgADEAKQAgACkALABcAG4AXABuACAAIAAgACAALwAvACAAMgBEACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAZQB4ADIARAAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABEAGkAcgBPAG0AaQB0AHQAZQBkAD8ALABlAHgAMgBEAF8AVgAoACkALABlAHgAMgBEAF8ASAAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAHMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAZQB4ADEARAAoACkALAAgAGUAeAAyAEQAKAApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYADAANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAE4AdQBtAGIAZQByAHMATwBuAGwAeQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAG4AdQBtAGUAcgBpAGMAIABjAGgAYQByAGEAYwB0AGUAcgBzACAAKAAwABMgOQApACAAZgByAG8AbQAgAGEAIABzAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAcwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAEUAeABwAGwAbwBkAGUAuwMgAGYAbwByACAAYwBoAGEAcgBhAGMAdABlAHIAESBsAGUAdgBlAGwAIABlAHgAcABhAG4AcwBpAG8AbgAuAFwAbgAgACAAIAAgACIgIABDAE8ARABFACgAKQAgAGYAaQBsAHQAZQByAGkAbgBnACAAZQBuAHMAdQByAGUAcwAgAHMAdAByAGkAYwB0ACAAZABpAGcAaQB0ACAAZQB4AHQAcgBhAGMAdABpAG8AbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBOAHUAbQBiAGUAcgBzAE8AbgBsAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAIABpAGYAIABhAHIAcgBhAHkAXABuACAAIAAgACAAYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgAVABZAFAARQAoAGEAcgByAGEAeQApACAAPAA+ACAANgA0ACwAIABhAHIAcgBhAHkALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGwAbwBkAGUAIAB0AG8AIABjAGgAYQByAGEAYwB0AGUAcgBzAFwAbgAgACAAIAAgAGUAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwMoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBnAGkAdAAgAG0AYQBzAGsAXABuACAAIAAgACAASwBlAGUAcAAsACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoACgAQwBPAEQARQAoAGUAeAApACAAPgA9ACAANAA4ACkAIAAqACAAKABDAE8ARABFACgAZQB4ACkAIAA8AD0AIAA1ADcAKQAsACAARgBBAEwAUwBFACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHMAawBlAGQAIAByAGUAcwB1AGwAdABcAG4AIAAgACAAIABSAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIABJAEYAKABLAGUAZQBwACwAIABlAHgALAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABjAG8AbgBjAGEAdABlAG4AYQB0AGUAZAAgAG8AdQB0AHAAdQB0AFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABCAFkAUgBPAFcAKABSAGUAcwB1AGwAdAAsACAAQwBPAE4AQwBBAFQAKQAgACsAIAAwACwAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYADAANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQATwBuAGwAeQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAG4AbwBuABEgbgB1AG0AZQByAGkAYwAgAGMAaABhAHIAYQBjAHQAZQByAHMAIABmAHIAbwBtACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABzAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABVAHMAZQBzACAARQB4AHAAbABvAGQAZQC7AyAAZgBvAHIAIABjAGgAYQByAGEAYwB0AGUAcgARIGwAZQB2AGUAbAAgAGUAeABwAGEAbgBzAGkAbwBuAC4AXABuACAAIAAgACAAIiAgAEMAbwBtAHAAbABlAG0AZQBuAHQAcwAgAE4AdQBtAGIAZQByAHMATwBuAGwAeQC7AyAAYgB5ACAAcwBlAGwAZQBjAHQAaQBuAGcAIABhAGwAbAAgAG4AbwBuABEgZABpAGcAaQB0ACAAYwBoAGEAcgBhAGMAdABlAHIAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBUAGUAeAB0AE8AbgBsAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAIABpAGYAIABhAHIAcgBhAHkAXABuACAAIAAgACAAYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgAVABZAFAARQAoAGEAcgByAGEAeQApACAAPAA+ACAANgA0ACwAIABhAHIAcgBhAHkALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGwAbwBkAGUAIAB0AG8AIABjAGgAYQByAGEAYwB0AGUAcgBzAFwAbgAgACAAIAAgAGUAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwMoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwBuABEgZABpAGcAaQB0ACAAbQBhAHMAawBcAG4AIAAgACAAIABLAGUAZQBwACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAKABDAE8ARABFACgAZQB4ACkAIAA8ACAANAA4ACkAIAArACAAKABDAE8ARABFACgAZQB4ACkAIAA+ACAANQA3ACkALAAgAEYAQQBMAFMARQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQBzAGsAZQBkACAAcgBlAHMAdQBsAHQAXABuACAAIAAgACAAUgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAASQBGACgASwBlAGUAcAAsACAAZQB4ACwAIABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAALwAvACAAMQBEACAAYwBvAG4AYwBhAHQAZQBuAGEAdABlAGQAIABvAHUAdABwAHUAdABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAQgBZAFIATwBXACgAUgBlAHMAdQBsAHQALAAgAEMATwBOAEMAQQBUACkALABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUwBwAGwAaQB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAUgBlAGcAZQB4AFMAYQBmAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAcABsAGkAdABzACAAMQBEACAAdABlAHgAdAAgAGEAcgByAGEAeQBzACAAaQBuAHQAbwAgAHQAbwBrAGUAbgBzACAAdQBzAGkAbgBnACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAZABlAGwAaQBtAGkAdABlAHIALgAgAFQAaABlACAAZgB1AG4AYwB0AGkAbwBuAFwAbgAgACAAIAAgAGkAcwAgAHMAaABhAHAAZQARIGEAdwBhAHIAZQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAGEAIAAyAEQAIABzAHAAaQBsAGwAIABhAGwAaQBnAG4AZQBkACAAdABvACAAdABoAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AIABvAGYAIAB0AGgAZQBcAG4AIAAgACAAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgAgAFMAdQBwAHAAbwByAHQAcwAgAG0AdQBsAHQAaQARIGMAaABhAHIAYQBjAHQAZQByACAAZABlAGwAaQBtAGkAdABlAHIAcwAgAGEAbgBkACAAZgB1AGwAbAAgAHIAZQBnAGUAeAARIHMAYQBmAGUAXABuACAAIAAgACAAZQBzAGMAYQBwAGkAbgBnAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgAEEAIAAxAEQAIABhAHIAcgBhAHkAIAAoAHYAZQByAHQAaQBjAGEAbAAgAG8AcgAgAGgAbwByAGkAegBvAG4AdABhAGwAKQAuACAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAG4AbwB0ACAAcwB1AHAAcABvAHIAdABlAGQALgBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAgACAAIAAtACAARABlAGwAaQBtAGkAdABlAHIAIAB1AHMAZQBkACAAdABvACAAcwBwAGwAaQB0ACAAZQBhAGMAaAAgAHQAZQB4AHQAIABlAGwAZQBtAGUAbgB0AC4AIABTAHAAaQBsAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAcwAgAGkAbgBmAGUAcgByAGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAaABhAHAAZQAgAG8AZgAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBpAGYAXwBuAG8AdABfAGYAbwB1AG4AZABdAFwAbgAgACAAIAAgACAAIAAgACAAVgBhAGwAdQBlACAAcgBlAHQAdQByAG4AZQBkACAAdwBoAGUAbgAgAGEAIAB0AGUAeAB0ACAAZQBsAGUAbQBlAG4AdAAgAGMAbwBuAHQAYQBpAG4AcwAgAG4AbwAgAGQAZQBsAGkAbQBpAHQAZQByAC4AXABuACAAIAAgACAAIAAgACAAIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABcACIAXAAiAC4AXABuAFwAbgAgACAAIAAgAFsAdAByAGUAYQB0AF8AYwBvAG4AcwBlAGMAdQB0AGkAdgBlAF8AZABlAGwAaQBtAGkAdABlAHIAcwBfAGEAcwBfAG8AbgBlAF0AXABuACAAIAAgACAAIAAgACAAIABUAFIAVQBFACAAkiEgAGMAbwBsAGwAYQBwAHMAZQAgAHIAdQBuAHMAIABvAGYAIABjAG8AbgBzAGUAYwB1AHQAaQB2AGUAIABkAGUAbABpAG0AaQB0AGUAcgBzACAAYgBlAGYAbwByAGUAIABzAHAAbABpAHQAdABpAG4AZwAuAFwAbgAgACAAIAAgACAAIAAgACAAVQBzAGUAZgB1AGwAIABmAG8AcgAgAEMAUwBWABEgcwB0AHkAbABlACAAbgBvAHIAbQBhAGwAaQB6AGEAdABpAG8AbgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEMAbwBsAGwAYQBwAHMAZQAgAG0AbwBkAGUAIABwAGUAcgBmAG8AcgBtAHMAIABhACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAIABwAGEAcwBzACAAdwBoAGUAbgAgAGMAbwBuAHMAZQBjAHUAdABpAHYAZQAgAGQAZQBsAGkAbQBpAHQAZQByAHMAIABlAHgAaQBzAHQALgBcAG4AIAAgACAAIAAgACAARgBvAHIAIAB2AGUAcgB5ACAAbABhAHIAZwBlACAAYQByAHIAYQB5AHMAIABvAHIAIABoAGkAZwBoACAAdABvAGsAZQBuACAAYwBvAHUAbgB0AHMALAAgAHQAaABpAHMAIABtAGEAeQAgAGkAbgBjAHIAZQBhAHMAZQAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAgAHQAaQBtAGUALgBcAG4AIAAgACAAIAAiICAARABlAGwAaQBtAGkAdABlAHIAcwAgAGEAcgBlACAAZgB1AGwAbAB5ACAAcgBlAGcAZQB4ABEgZQBzAGMAYQBwAGUAZAAgAHYAaQBhACAAUgBlAGcAZQB4AFMAYQBmAGUAuwMsACAAYQBsAGwAbwB3AGkAbgBnACAAbABpAHQAZQByAGEAbAAgAHUAcwBlACAAbwBmAFwAbgAgACAAIAAgACAAIABtAGUAdABhAGMAaABhAHIAYQBjAHQAZQByAHMAIAAoACoALAAgAD8ALAAgACsALAAgAHwALAAgACgALAAgACkALAAgAFsALAAgAF0ALAAgAF4ALAAgACQALAAgAGUAdABjAC4AKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHAAbABpAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIALABcAG4AIAAgACAAIABbAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkAF0ALABcAG4AIAAgACAAIABbAHQAcgBlAGEAdABfAGMAbwBuAHMAZQBjAHUAdABpAHYAZQBfAGQAZQBsAGkAbQBpAHQAZQByAHMAXwBhAHMAXwBvAG4AZQBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAIABvAGYAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAaAAsACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzACAAbwBmACAAZABlAGwAaQBtAGkAdABlAHIAXABuACAAIAAgACAAaACCICwAIABSAE8AVwBTACgAZABlAGwAaQBtAGkAdABlAHIAKQAsAFwAbgAgACAAIAAgAHcAgiAsACAAQwBPAEwAVQBNAE4AUwAoAGQAZQBsAGkAbQBpAHQAZQByACkALABcAG4AXABuACAAIAAgACAALwAvACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAYwBoAGUAYwBrAHMAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIABoACAAPgAgAHcALABcAG4AIAAgACAAIABJAHMAMgBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAXABuACAAIAAgACAAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQALAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkALAAgAFwAIgBcACIALAAgAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkALABcAG4AIAAgACAAIABDAG8AbABsAGEAcABzAGUARABlAGwAaQBtAD8ALAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAB0AHIAZQBhAHQAXwBjAG8AbgBzAGUAYwB1AHQAaQB2AGUAXwBkAGUAbABpAG0AaQB0AGUAcgBzAF8AYQBzAF8AbwBuAGUAKQApACwAXABuACAAIAAgACAATQB1AGwAdABpAHAAbABlAEQAZQBsAGkAbQA/ACwAIABPAFIAKABoAIIgIAA+ACAAMQAsACAAdwCCICAAPgAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkARgAoAEkAcwAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwAyAEQALQBJAE4AUABVAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABNAHUAbAB0AGkAcABsAGUARABlAGwAaQBtAD8ALAAgAFwAIgAjAEQARQBMAEkATQBJAFQARQBSAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFcAcgBhAHAAIABlAGEAYwBoACAAZQBsAGUAbQBlAG4AdAAgAHcAaQB0AGgAIABkAGUAbABpAG0AaQB0AGUAcgAgAG8AbgAgAGIAbwB0AGgAIABzAGkAZABlAHMAXABuACAAIAAgACAAagBvAGkAbgBlAGQALAAgACAAIAAgACAAIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAgACYAIABhAHIAcgBhAHkAIAAmACAAZABlAGwAaQBtAGkAdABlAHIALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAGcAZQB4ABEgcwBhAGYAZQAgAGQAZQBsAGkAbQBpAHQAZQByAFwAbgAgACAAIAAgAGQAZQBsAGkAbQBfAGIALAAgACAAIAAgACAAIAAgACAAUgBlAGcAZQB4AFMAYQBmAGUAuwMoAGQAZQBsAGkAbQBpAHQAZQByACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAHQAZQBjAHQAIABjAG8AbgBzAGUAYwB1AHQAaQB2AGUAIABkAGUAbABpAG0AaQB0AGUAcgBzAFwAbgAgACAAIAAgAEkAcwBDAG8AbgBzAGUAYwBEAGUAbABpAG0APwAsACAATwBSACgAUgBFAEcARQBYAFQARQBTAFQAKABqAG8AaQBuAGUAZAAsACAAXAAiACgAXAAiACAAJgAgAGQAZQBsAGkAbQBfAGIAIAAmACAAXAAiACkAewAyACwAfQBcACIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAGwAYQBwAHMAZQAgAGMAbwBuAHMAZQBjAHUAdABpAHYAZQAgAGQAZQBsAGkAbQBpAHQAZQByAHMAIABpAGYAIAByAGUAcQB1AGUAcwB0AGUAZABcAG4AIAAgACAAIAB0AGUAeAB0AHMALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgAQwBvAGwAbABhAHAAcwBlAEQAZQBsAGkAbQA/ACwAIABJAHMAQwBvAG4AcwBlAGMARABlAGwAaQBtAD8AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAoAGoAbwBpAG4AZQBkACwAIABcACIAKABcACIAIAAmACAAZABlAGwAaQBtAF8AYgAgACYAIABcACIAKQArAFwAIgAsACAAZABlAGwAaQBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoAbwBpAG4AZQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAGsAZQBuACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgAEwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAE4AKABkAGUAbABpAG0AaQB0AGUAcgApACwAXABuACAAIAAgACAAdABvAGsAZQBuACwAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAEwARQBOACgAdABlAHgAdABzACkAIAAtACAATABFAE4AKABTAFUAQgBTAFQASQBUAFUAVABFACgAdABlAHgAdABzACwAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACkAKQAgAC8AIABMACAALQAgADEALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4AGkAbgBnACAAZgBvAHIAIABUAEUAWABUAEEARgBUAEUAUgAvAFQARQBYAFQAQgBFAEYATwBSAEUAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACkAIAArACAAKABJAHMAUwBjAGEAbABhAHIAPwApACwAUwBFAFEAVQBFAE4AQwBFACgALAAgAHQAbwBrAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAdABvAGsAZQBuACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQByAHMAZQAgAHQAbwBrAGUAbgBzAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABUAEUAWABUAEEARgBUAEUAUgAoAHQAZQB4AHQAcwAsACAAZABlAGwAaQBtAGkAdABlAHIALAAgAGkAZAB4ACgAKQAsACAALAAgACwAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIALAAsACAALAAgACwAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAtAEMATwBSAEUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABSAGUAZwBlAHgAUwBhAGYAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdAAgACgAQwBvAHIAZQApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQBzAGMAYQBwAGUAcwAgAHIAZQBnAGUAeAAgAG0AZQB0AGEAYwBoAGEAcgBhAGMAdABlAHIAcwAgAGkAbgAgAGEAIABzAHUAcABwAGwAaQBlAGQAIABkAGUAbABpAG0AaQB0AGUAcgAgAHMAbwAgAGkAdAAgAGMAYQBuACAAYgBlACAAdQBzAGUAZABcAG4AIAAgACAAIABzAGEAZgBlAGwAeQAgAGkAbgAgAFIARQBHAEUAWABUAEUAUwBUACwAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAsACAAYQBuAGQAIABSAEUARwBFAFgARQBYAFQAUgBBAEMAVAAgAHAAYQB0AHQAZQByAG4AcwAuACAATQB1AGwAdABpABEgXABuACAAIAAgACAAYwBoAGEAcgBhAGMAdABlAHIAIABkAGUAbABpAG0AaQB0AGUAcgBzACAAYQByAGUAIABwAHIAbwBjAGUAcwBzAGUAZAAgAGMAaABhAHIAYQBjAHQAZQByABEgYgB5ABEgYwBoAGEAcgBhAGMAdABlAHIALAAgAGEAbgBkACAAbwBuAGwAeQBcAG4AIAAgACAAIABjAGgAYQByAGEAYwB0AGUAcgBzACAAdABoAGEAdAAgAHIAZQBxAHUAaQByAGUAIABlAHMAYwBhAHAAaQBuAGcAIABhAHIAZQAgAHAAcgBlAGYAaQB4AGUAZAAgAHcAaQB0AGgAIABcACIAXABcAFwAIgAuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQA6AFwAbgAgACAAIAAgAD0AUgBlAGcAZQB4AFMAYQBmAGUAuwMoAFwAIgB8AFwAIgApAFwAbgAgACAAIAAgAHIAZQB0AHUAcgBuAHMAOgAgAFwAIgBcAFwAfABcACIAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBnAGUAeABTAGEAZgBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByAHMALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABDAGgAYQByAGEAYwB0AGUAcgBzACAAcgBlAHEAdQBpAHIAaQBuAGcAIABlAHMAYwBhAHAAaQBuAGcAIABpAG4AIABFAHgAYwBlAGwAJwBzACAAUABDAFIARQAyACAAZQBuAGcAaQBuAGUAXABuACAAIAAgACAAbQBlAHQAYQAsACAAIAAgACAAIAAgACAAewBcACIAXABcAFwAIgAsACAAXAAiACsAXAAiACwAIABcACIAKgBcACIALAAgAFwAIgA/AFwAIgAsACAAXAAiAF4AXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAJABcACIALAAgAFwAIgAoAFwAIgAsACAAXAAiACkAXAAiACwAIABcACIAWwBcACIALAAgAFwAIgB8AFwAIgB9ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbgB1AG0AZQByAGEAdABlACAAZQBhAGMAaAAgAGMAaABhAHIAYQBjAHQAZQByACAAbwBmACAAdABoAGUAIABkAGUAbABpAG0AaQB0AGUAcgBcAG4AIAAgACAAIABjAGgAYQByAHMALAAgACAAIAAgACAAIABSAEUARwBFAFgARQBYAFQAUgBBAEMAVAAoAGQAZQBsAGkAbQBpAHQAZQByAHMALABcACIALgBcACIALAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBkAGUAbgB0AGkAZgB5ACAAbQBlAHQAYQBjAGgAYQByAGEAYwB0AGUAcgBzAFwAbgAgACAAIAAgAEkAcwBNAGUAdABhAD8ALAAgACAAIAAgAEkAUwBOAFUATQBCAEUAUgAoAFgATQBBAFQAQwBIACgAYwBoAGEAcgBzACwAIABtAGUAdABhACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHMAYwBhAHAAZQAgAG8AbgBsAHkAIAB0AGgAbwBzAGUAIAB0AGgAYQB0ACAAcgBlAHEAdQBpAHIAZQAgAGkAdABcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACwAIAAgACAAIABDAE8ATgBDAEEAVAAoAEkARgAoAEkAcwBNAGUAdABhAD8ALAAgAFwAIgBcAFwAXAAiACAAJgAgAGMAaABhAHIAcwAsACAAYwBoAGEAcgBzACkAKQAsAFwAbgBcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAvACAAWwBFAE4AXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ALwAvACAALQAtAC0AIwAjACAAMAA4ACAAFCAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwBcAG4ALwAvACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABUAGgAZQAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwAgAGMAYQB0AGUAZwBvAHIAeQAgAHAAcgBvAHYAaQBkAGUAcwAgAGIAaQBuAGEAcgB5ACwAIABHAHIAYQB5ABEgYwBvAGQAZQAsACAAYQBuAGQAIABiAGkAdAARIGwAZQB2AGUAbAAgAHUAdABpAGwAaQB0AGkAZQBzAFwAbgAgACAAIAAgAGQAZQBzAGkAZwBuAGUAZAAgAHQAbwAgAG8AcABlAHIAYQB0AGUAIAB3AGUAbABsACAAYgBlAHkAbwBuAGQAIABFAHgAYwBlAGwAJwBzACAAbgBhAHQAaQB2AGUAIABEAEUAQwAyAEIASQBOACAAbABpAG0AaQB0ACAAbwBmACAANQAxADEALgAgAEEAbABsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgBzACAAcwB1AHAAcABvAHIAdAAgAGMAbwBuAGMAaQBzAGUAIABiAGkAbgBhAHIAeQAgAHMAdAByAGkAbgBnAHMAIABhAG4AZAAgAHMAaABhAHAAZQARIHAAcgBlAHMAZQByAHYAaQBuAGcAIABhAHIAcgBhAHkAIABiAGUAaABhAHYAaQBvAHIALABcAG4AIAAgACAAIAB3AGkAdABoACAAbwBwAHQAaQBvAG4AYQBsACAAMgBEACAAZQB4AHAAbABvAGQAZQBkACAAYgBpAHQAESBtAGEAdAByAGkAYwBlAHMAIAB3AGgAZQByAGUAIABhAHAAcABsAGkAYwBhAGIAbABlAC4AXABuAFwAbgBGAHUAbgBjAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABCAGkAbgAyAEQAZQBjALsDXABuACAAIAAgACAAIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABjAG8AbgBjAGkAcwBlACAAYgBpAG4AYQByAHkAIABpAG4AdABvACAAZABlAGMAaQBtAGEAbAAgAHYAYQBsAHUAZQBzAC4AXABuAFwAbgAgACAAIAAgACIgIABCAGkAbgAyAEcAcgBhAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAGMAbwBuAGMAaQBzAGUAIABiAGkAbgBhAHIAeQAgAGkAbgB0AG8AIABHAHIAYQB5ABEgYwBvAGQAZQAgAHYAYQBsAHUAZQBzACwAIAB3AGkAdABoACAAbwBwAHQAaQBvAG4AYQBsACAAZQB4AHAAbABvAGQAZQBkACAAZgBvAHIAbQAuAFwAbgBcAG4AIAAgACAAIAAiICAAQgBpAHQAQwBvAHUAbgB0ALsDXABuACAAIAAgACAAIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABpAG4AdABlAGcAZQByAHMAIAB0AG8AIABiAGkAbgBhAHIAeQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAGIAaQB0ACAAYwBvAHUAbgB0AHMALAAgAHAAcgBlAHMAZQByAHYAaQBuAGcAIABpAG4AcAB1AHQAIABzAGgAYQBwAGUALgBcAG4AXABuACAAIAAgACAAIiAgAEQAZQBjADIAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAGkAbgB0AGUAZwBlAHIAcwAgAGkAbgB0AG8AIABiAGkAbgBhAHIAeQAgAHYAYQBsAHUAZQBzACwAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIABjAG8AbgBjAGkAcwBlACAAcwB0AHIAaQBuAGcAcwAgAG8AcgBcAG4AIAAgACAAIAAgACAAIAAgAGUAeABwAGwAbwBkAGUAZAAgADIARAAgAGIAaQB0ABEgYQByAHIAYQB5AHMALgBcAG4AXABuACAAIAAgACAAIiAgAEQAZQBjADIARwByAGEAeQC7A1wAbgAgACAAIAAgACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAaQBuAHQAZQBnAGUAcgBzACAAaQBuAHQAbwAgAEcAcgBhAHkAESBjAG8AZABlACAAdgBhAGwAdQBlAHMAIAAoAHcAcgBhAHAAcABlAHIAOgAgAEQAZQBjADIAQgBpAG4AuwMgAJIhIABCAGkAbgAyAEcAcgBhAHkAuwMpAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAATgBlAGcAYQB0AGkAdgBlACAAbgB1AG0AYgBlAHIAcwAgAGEAcgBlACAAbgBvAHQAIABzAHUAcABwAG8AcgB0AGUAZAAgAGYAbwByACAARABlAGMAMgBCAGkAbgC7AyAAbwByACAARABlAGMAMgBHAHIAYQB5ALsDLgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEUATgAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABCAGkAbgAyAEQAZQBjALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABFAG4AZwBpAG4AZQBlAHIAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABFAHgAcABsAG8AZABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABjAG8AbgBjAGkAcwBlACAAYgBpAG4AYQByAHkAIABpAG4AdABvACAAZABlAGMAaQBtAGEAbAAgAHYAYQBsAHUAZQBzAC4AIABTAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABhAG4AZAAgADIARABcAG4AIAAgACAAIABpAG4AcAB1AHQAcwAgAHcAaQB0AGgAIABmAHUAbABsACAAcwBoAGEAcABlACAAcAByAGUAcwBlAHIAdgBhAHQAaQBvAG4ALgAgAEIAaQB0ABEgdwBpAGQAdABoACAAaQBzACAAaQBuAGYAZQByAHIAZQBkACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQBcAG4AIAAgACAAIABhAG4AZAAgAGEAbABsACAAdgBhAGwAdQBlAHMAIABhAHIAZQAgAG4AbwByAG0AYQBsAGkAegBlAGQAIABiAGUAZgBvAHIAZQAgAGUAeABwAGwAbwBzAGkAbwBuAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYgBpAG4AYQByAHkAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAYwBvAG4AYwBpAHMAZQAgAGIAaQBuAGEAcgB5ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABDAG8AbgBjAGkAcwBlACAAZgBvAHIAbQA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMAAxADEAXAAiACwAIABcACIAMAAwADAAMQAxADAAMQAwAFwAIgAsACAAZQB0AGMALgAgACAAKABhAG4AeQAgAHMAaABhAHAAZQApAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAcwBoAGEAcABlACAAbQBhAHQAYwBoAGUAcwAgAGkAbgBwAHUAdAAgAHMAaABhAHAAZQAgACgAcwBjAGEAbABhAHIALAAgAHYAZQByAHQAaQBjAGEAbAAsACAAaABvAHIAaQB6AG8AbgB0AGEAbAAsACAAbwByACAAMgBEACkALgBcAG4AIAAgACAAIAAiICAAUwB1AHAAcABvAHIAdABzACAAYgBpAG4AYQByAHkAIAB2AGEAbAB1AGUAcwAgAGYAYQByACAAYgBlAHkAbwBuAGQAIABFAHgAYwBlAGwAGSBzACAAbgBhAHQAaQB2AGUAIAAxADYAESBkAGkAZwBpAHQAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AaQB0AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEIAaQBuADIARABlAGMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYgBpAG4AYQByAHkALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAIABvAGYAIABpAG4AcAB1AHQAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYgBpAG4AYQByAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGIAaQBuAGEAcgB5ACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAsACAAIABBAE4ARAAoAHcAIAA+ACAAMQAsACAAaAAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABiAGkAdAARIHcAaQBkAHQAaAAgAGEAbgBkACAAZQB4AHAAbABvAGQAZQBcAG4AIAAgACAAIABiAGkAdABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgATABFAE4AKABiAGkAbgBhAHIAeQApACkALABcAG4AIAAgACAAIABhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQARQBYAFQAKABiAGkAbgBhAHIAeQAsACAAUgBFAFAAVAAoAFwAIgAwAFwAIgAsACAAYgBpAHQAcwApACkALABcAG4AIAAgACAAIABiAGkAbgBhAHIAeQAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwARQB4AHAAbABvAGQAZQC7AygAYgBpAG4AYQByAHkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAHgAcABsAG8AZABlALsDKABUAE8AQwBPAEwAKABhAHIAcgApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAdABoAFwAbgAgACAAIAAgAHAAbwB3AGUAcgBzACwAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAYgBpAHQAcwAsACAAYgBpAHQAcwAgAC0AIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgAHAALAAgACAAIAAgACAAIABQAE8AVwBFAFIAKAAyACwAIABwAG8AdwBlAHIAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAZwBnAHIAZQBnAGEAdABpAG8AbgAgACYAIABkAGUAbABpAHYAZQByAHkAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAEIAWQBSAE8AVwAoAGIAaQBuAGEAcgB5ACAAKgAgAHAALAAgAFMAVQBNACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAASQBGACgATwBSACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwApACwAIAByAGUAcwB1AGwAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8ALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAcgBlAHMAdQBsAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVwBSAEEAUABSAE8AVwBTACgAcgBlAHMAdQBsAHQALAAgAHcAKQApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBFAE4AMAAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQgBpAG4AMgBHAHIAYQB5ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABFAG4AZwBpAG4AZQBlAHIAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABFAHgAcABsAG8AZABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABiAGkAbgBhAHIAeQAgAGkAbgB0AG8AIABHAHIAYQB5ABEgYwBvAGQAZQAgAHYAYQBsAHUAZQBzAC4AIABTAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAsAFwAbgAgACAAIAAgADEARAAsACAAYQBuAGQAIAAyAEQAIABpAG4AcAB1AHQAcwAuACAATwB1AHQAcAB1AHQAIABjAGEAbgAgAGIAZQAgAHIAZQB0AHUAcgBuAGUAZAAgAGUAaQB0AGgAZQByACAAYQBzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAG8AcgAgAGEAcwBcAG4AIAAgACAAIABjAG8AbgBjAGkAcwBlACAAcgBvAHcAESB3AGkAcwBlACAAcwB0AHIAaQBuAGcAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGIAaQBuAGEAcgB5AFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAGIAaQBuAGEAcgB5ACAAZABhAHQAYQAuAFwAbgBcAG4AIAAgACAAIABbAGMAbwBuAGMAaQBzAGUAXQBcAG4AIAAgACAAIAAgACAAIAAgAE8AcAB0AGkAbwBuAGEAbAAuACAAVABSAFUARQAgAJIhIAByAGUAdAB1AHIAbgAgAEcAcgBhAHkAIABjAG8AZABlACAAYQBzACAAYwBvAG4AYwBhAHQAZQBuAGEAdABlAGQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAIAAgACAAIAAgACAAIABPAG0AaQB0AHQAZQBkACAAkiEgAHIAZQB0AHUAcgBuACAAMgBEACAAZQB4AHAAbABvAGQAZQBkACAARwByAGEAeQARIGMAbwBkAGUAIABiAGkAdAAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGQAZQBsAGkAdgBlAHIAZQBkACAAaQBuACAAYwBvAG4AYwBpAHMAZQAgAGYAbwByAG0AYQB0AC4AXABuACAAIAAgACAAIiAgAEcAcgBhAHkAIABjAG8AZABlACAAaQBzACAAYwBvAG0AcAB1AHQAZQBkACAAYQBzADoAIAAgAGcAgCAgAD0AIABiAIAgLAAgACAAZwBiHSAAPQAgAGIAYh0gAFgATwBSACAAYgBiHYsggSAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBCAGkAbgAyAEcAcgBhAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYgBpAG4AYQByAHkALABcAG4AIAAgACAAIABbAGMAbwBuAGMAaQBzAGUAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHUAdABwAHUAdAAgAG0AbwBkAGUAXABuACAAIAAgACAASQBzADIARABHAHIAYQB5AD8ALAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBuAGMAaQBzAGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAIABvAGYAIABpAG4AcAB1AHQAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYgBpAG4AYQByAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGIAaQBuAGEAcgB5ACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAsACAAIABBAE4ARAAoAHcAIAA+ACAAMQAsACAAaAAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAMQBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAFgATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAGIAaQB0AC0AdwBpAGQAdABoACAAYQBuAGQAIABlAHgAcABsAG8AZABlAFwAbgAgACAAIAAgAGIAaQB0AHMALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABMAEUATgAoAGIAaQBuAGEAcgB5ACkAKQAsAFwAbgAgACAAIAAgAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABFAFgAVAAoAGIAaQBuAGEAcgB5ACwAIABSAEUAUABUACgAXAAiADAAXAAiACwAIABiAGkAdABzACkAKQAsAFwAbgAgACAAIAAgAGIAaQBuAGEAcgB5ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALABFAHgAcABsAG8AZABlALsDKABiAGkAbgBhAHIAeQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwMoAFQATwBDAE8ATAAoAGEAcgByACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AbwBzAHQAIABzAGkAZwBuAGkAZgBpAGMAYQBuAHQAIABiAGkAdABcAG4AIAAgACAAIABtAHMAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABiAGkAbgBhAHIAeQAsACAALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABYAE8AUgAgAG4AZQBpAGcAaABiAG8AcgBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgBJAFQAWABPAFIAKABEAFIATwBQACgAYgBpAG4AYQByAHkALAAgACwAIAAxACkALAAgAEQAUgBPAFAAKABiAGkAbgBhAHIAeQAsACAALAAgAC0AMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGEAeQAgAGMAbwBkAGUAIABhAHIAcgBhAHkAXwAyAEQAXABuACAAIAAgACAAZwByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAG0AcwBiACwAIAB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAATwB1AHQAcAB1AHQAIABhAG4AZAAgAGQAZQBsAGkAdgBlAHIAeQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgASQBzADIARABHAHIAYQB5AD8ALABJAHMAMQBEAD8AKQAsACAAZwByAGEAeQAsACAAQgBZAFIATwBXACgAZwByAGEAeQAsACAAQwBPAE4AQwBBAFQAKQApACwAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAHMAUwBjAGEAbABhAHIAPwAsAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwApACwAcgBlAHMAdQBsAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAsAFQAUgBBAE4AUwBQAE8AUwBFACgAcgBlAHMAdQBsAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVwBSAEEAUABSAE8AVwBTACgAcgBlAHMAdQBsAHQALAB3ACkAKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARQBOADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEIAaQB0AEMAbwB1AG4AdAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARABlAGMAMgBCAGkAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAHUAbgB0AHMAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAMQARIGIAaQB0AHMAIABpAG4AIAB0AGgAZQAgAGIAaQBuAGEAcgB5ACAAcgBlAHAAcgBlAHMAZQBuAHQAYQB0AGkAbwBuACAAbwBmACAAZQBhAGMAaAAgAGkAbgB0AGUAZwBlAHIALgBcAG4AIAAgACAAIABTAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABhAG4AZAAgADIARAAgAGkAbgBwAHUAdABzACAAdwBpAHQAaAAgAGYAdQBsAGwAIABzAGgAYQBwAGUAIABwAHIAZQBzAGUAcgB2AGEAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAG4AIAAgACAALQAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIABuAG8AbgARIG4AZQBnAGEAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABEAGUAYwAyAEIAaQBuALsDKABuACwAMQApACAAdABvACAAbwBiAHQAYQBpAG4AIABlAHgAcABsAG8AZABlAGQAIABiAGkAdAARIG0AYQB0AHIAaQBjAGUAcwAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHMAaABhAHAAZQAgAG0AYQB0AGMAaABlAHMAIABpAG4AcAB1AHQAIABzAGgAYQBwAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQgBpAHQAQwBvAHUAbgB0ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAG4ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABuACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAG4AKQAsAFwAbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABJAHMAMQBEAD8ALAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPgAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0ACAAaQBmACAAMgBEAFwAbgAgACAAIAAgAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALABuACwAVABPAEMATwBMACgAbgApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgB1AG4AYwB0AGkAbwBuACAAKABmAG8AcgAgAG4AbwBuAC0AcwBjAGEAbABhAHIAcwApAFwAbgAgACAAIAAgAGYAbgC7AywAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABJAHMAMgBEAD8AKQAsAEIAWQBSAE8AVwAsAEIAWQBDAE8ATAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGwAbwBkAGUAZAAgAGIAaQBuAGEAcgB5ACAAYQByAHIAYQB5AF8AMgBEAFwAbgAgACAAIAAgAGIAaQB0AHMALAAgACAAIAAgACAAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDKABuACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAHUAbgB0ACAAYgBpAHQAcwBcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAsACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAFMAVQBNACgAYgBpAHQAcwApACwAZgBuALsDKABiAGkAdABzACwAUwBVAE0AKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALABjAG8AdQBuAHQAcwAsAFcAUgBBAFAAUgBPAFcAUwAoAGMAbwB1AG4AdABzACwAdwApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBFAE4AMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARABlAGMAMgBCAGkAbgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAbgBvAG4AESBuAGUAZwBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMAIABpAG4AdABvACAAYgBpAG4AYQByAHkALgAgAFMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAGEAbgBkACAAMgBEAFwAbgAgACAAIAAgAGkAbgBwAHUAdABzACAAdwBpAHQAaAAgAGYAdQBsAGwAIABzAGgAYQBwAGUAIABwAHIAZQBzAGUAcgB2AGEAdABpAG8AbgAuACAAUgBlAHQAdQByAG4AcwAgAGUAaQB0AGgAZQByACAAYwBvAG4AYwBpAHMAZQAgAGIAaQBuAGEAcgB5ACAAcwB0AHIAaQBuAGcAcwBcAG4AIAAgACAAIABvAHIAIABlAHgAcABsAG8AZABlAGQAIAAyAEQAIABiAGkAdAARIGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAbgB1AG0AYgBlAHIAcwBcAG4AIAAgACAAIAAgACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AbwBuABEgbgBlAGcAYQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgBzAC4AXABuAFwAbgAgACAAIAAgAFsAQQByAHIAYQB5AF8ARgBvAHIAbQBfADIARABdAFwAbgAgACAAIAAgACAAIAAgACAATwBwAHQAaQBvAG4AYQBsAC4AIABUAFIAVQBFACAAkiEgAHIAZQB0AHUAcgBuACAAZQB4AHAAbABvAGQAZQBkACAAMgBEACAAYgBpAHQAESBhAHIAcgBhAHkAcwAuAFwAbgAgACAAIAAgACAAIAAgACAATwBtAGkAdAB0AGUAZAAgAJIhIAByAGUAdAB1AHIAbgAgAGMAbwBuAGMAaQBzAGUAIABiAGkAbgBhAHIAeQAgAHMAdAByAGkAbgBnAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABTAHUAcABwAG8AcgB0AHMAIABhAHIAYgBpAHQAcgBhAHIAaQBsAHkAIABsAGEAcgBnAGUAIABpAG4AdABlAGcAZQByAHMAIAAoAGIAZQB5AG8AbgBkACAARQB4AGMAZQBsABkgcwAgAG4AYQB0AGkAdgBlACAAQgBJAE4AMgBEAEUAQwAgAGwAaQBtAGkAdABzACkALgBcAG4AIAAgACAAIAAiICAAQwBvAG4AYwBpAHMAZQAgAG8AdQB0AHAAdQB0ACAAYQB2AG8AaQBkAHMAIABzAGMAaQBlAG4AdABpAGYAaQBjACAAbgBvAHQAYQB0AGkAbwBuACAAYQBuAGQAIAAxADYAESBkAGkAZwBpAHQAIABwAHIAZQBjAGkAcwBpAG8AbgAgAGkAcwBzAHUAZQBzAC4AXABuACAAIAAgACAAIiAgADIARAAgAGkAbgBwAHUAdABzACAAcAByAGUAcwBlAHIAdgBlACAAdABoAGUAaQByACAAbwByAGkAZwBpAG4AYQBsACAAcwBoAGEAcABlACAAdwBoAGUAbgAgAGMAbwBuAGMAaQBzAGUAIABvAHUAdABwAHUAdAAgAGkAcwAgAHMAZQBsAGUAYwB0AGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAGUAYwAyAEIAaQBuALsDPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABuAHUAbQBiAGUAcgBzACwAXABuACAAIAAgACAAWwBBAHIAcgBhAHkAXwBGAG8AcgBtAF8AMgBEAF0ALABcAG4AXABuAC8ALwBDAGgAZQBjAGsAIABuAHUAbQBiAGUAcgBzAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAG4AdQBtAGIAZQByAHMAKQAsACAASQBTAEUAUgBSAE8AUgAoAC0ALQBuAHUAbQBiAGUAcgBzACkALABuAHUAbQBiAGUAcgBzACAAPAAgADAAKQAsACAAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIABzAGgAYQBwAGUAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAG4AdQBtAGIAZQByAHMAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABuAHUAbQBiAGUAcgBzACkALABcAG4AXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAaAAgAD4AIAB3ACwAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAB3ACAAPgAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAG4AdQBtAGIAZQByAHMALAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAG4AdQBtAGIAZQByAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAG8AcgBtAFwAbgAgACAAIAAgAEkAcwBWAGUAYwB0AG8AcgA/ACwAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAQQByAHIAYQB5AF8ARgBvAHIAbQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4ACAAYgBpAHQAcwAgAG4AZQBlAGQAZQBkACAAdABvACAAZQB4AHAAcgBlAHMAcwAgAHIAZQBzAHUAbAB0AHMAIABhAHMAIABhAHIAcgBhAHkAXABuACAAIAAgACAAYgBpAHQAcwAsACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABJAEYARQBSAFIATwBSACgASQBOAFQAKABMAE8ARwAoAG4AdQBtAGIAZQByAHMALAAyACkAKQAgACsAIAAxACwAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBvAHIAbQBzACAALQAgADIARAAgAGEAcgByAGEAeQAsACAAYgBpAG4AIAB2AGUAYwB0AG8AcgAgAC0AIABlAGEAZwBlAHIAIABlAHYAYQBsAHUAYQB0AGkAbwBuACAAZABlAGYAZQByAHIAZQBkAFwAbgAgACAAIAAgAGIAaQBuAF8AYQByAHIALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgATQBPAEQAKABCAEkAVABSAFMASABJAEYAVAAoAG4AdQBtAGIAZQByAHMALABTAEUAUQBVAEUATgBDAEUAKAAsAGIAaQB0AHMALABiAGkAdABzACAALQAgADEALAAtADEAKQApACwAMgApACkALABcAG4AIAAgACAAIABiAGkAbgBfAHYAZQBjAHQAbwByACwAIAAgACAAIABMAEEATQBCAEQAQQAoAEIAWQBSAE8AVwAoAGIAaQBuAF8AYQByAHIAKAApACwAQwBPAE4AQwBBAFQAKQApACwAXABuACAAIAAgACAAYgBpAG4AXwByAGUAcwB1AGwAdAAsACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABJAHMAVgBlAGMAdABvAHIAPwAsAGIAaQBuAF8AdgBlAGMAdABvAHIAKAApACwAYgBpAG4AXwBhAHIAcgAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQAtAHMAaABhAHAAaQBuAGcAIAAmACAAZABlAGwAaQB2AGUAcgB5AFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAyAEQAPwAsAFcAUgBBAFAAUgBPAFcAUwAoAGIAaQBuAF8AdgBlAGMAdABvAHIAKAApACwAdwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwASQBzAFYAZQByAHQAaQBjAGEAbAA/ACkALABiAGkAbgBfAHIAZQBzAHUAbAB0ACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYgBpAG4AXwByAGUAcwB1AGwAdAAoACkAKQApACkALABcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEUATgAwADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABEAGUAYwAyAEcAcgBhAHkAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEQAZQBjADIAQgBpAG4AuwMsACAAQgBpAG4AMgBHAHIAYQB5ALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABuAG8AbgARIG4AZQBnAGEAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAgAGkAbgB0AG8AIABHAHIAYQB5ABEgYwBvAGQAZQAgAHYAYQBsAHUAZQBzAC4AIABTAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAsACAAMQBEACwAXABuACAAIAAgACAAYQBuAGQAIAAyAEQAIABpAG4AcAB1AHQAcwAgAHcAaQB0AGgAIABmAHUAbABsACAAcwBoAGEAcABlACAAcAByAGUAcwBlAHIAdgBhAHQAaQBvAG4ALgAgAE8AdQB0AHAAdQB0ACAAYwBhAG4AIABiAGUAIAByAGUAdAB1AHIAbgBlAGQAIABlAGkAdABoAGUAcgBcAG4AIAAgACAAIABhAHMAIABjAG8AbgBjAGkAcwBlACAARwByAGEAeQARIGMAbwBkAGUAIABzAHQAcgBpAG4AZwBzACAAbwByACAAYQBzACAAZQB4AHAAbABvAGQAZQBkACAAMgBEACAAYgBpAHQAESBhAHIAcgBhAHkAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAG4AdQBtAGIAZQByAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAbgBvAG4AESBuAGUAZwBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMALgBcAG4AXABuACAAIAAgACAAWwBjAG8AbgBjAGkAcwBlAF0AXABuACAAIAAgACAAIAAgACAAIABPAHAAdABpAG8AbgBhAGwALgAgAFQAUgBVAEUAIACSISAAcgBlAHQAdQByAG4AIABHAHIAYQB5ACAAYwBvAGQAZQAgAGEAcwAgAGMAbwBuAGMAYQB0AGUAbgBhAHQAZQBkACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACAAIAAgACAAIAAgACAATwBtAGkAdAB0AGUAZAAgAJIhIAByAGUAdAB1AHIAbgAgAGUAeABwAGwAbwBkAGUAZAAgADIARAAgAEcAcgBhAHkAESBjAG8AZABlACAAYgBpAHQAIABhAHIAcgBhAHkAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABEAGUAYwAyAEIAaQBuALsDIAB0AG8AIABvAGIAdABhAGkAbgAgAGIAaQBuAGEAcgB5ACwAIAB0AGgAZQBuACAAQgBpAG4AMgBHAHIAYQB5ALsDIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAdABvACAARwByAGEAeQAgAGMAbwBkAGUALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABzAGgAYQBwAGUAIABtAGEAdABjAGgAZQBzACAAaQBuAHAAdQB0ACAAcwBoAGEAcABlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQBjADIARwByAGEAeQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABuAHUAbQBiAGUAcgAsAFwAbgAgACAAIAAgAFsAYwBvAG4AYwBpAHMAZQBdACwAXABuACAAIAAgACAAQgBpAG4AMgBHAHIAYQB5ALsDKABEAGUAYwAyAEIAaQBuALsDKABuAHUAbQBiAGUAcgApACwAIABjAG8AbgBjAGkAcwBlACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4ALwAvACAAWwBDAEIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ALwAvACAALQAtAC0AIwAjACAAMAA5ACAAFCAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVABoAGUAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzACAAYwBhAHQAZQBnAG8AcgB5ACAAcAByAG8AdgBpAGQAZQBzACAAaABpAGcAaAARIHAAZQByAGYAbwByAG0AYQBuAGMAZQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABmAG8AcgBcAG4AIAAgACAAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAsACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMALAAgAHMAdQBiAHMAZQB0AHMALAAgAGEAbgBkACAAcgBlAGwAYQB0AGUAZAAgAHMAdAByAHUAYwB0AHUAcgBlAHMALgBcAG4AXABuAEYAdQBuAGMAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAFAAZQByAG0AUgC7A1wAbgAgACAAIAAgACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaQB0AGgAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAIAAoAGsAESB0AHUAcABsAGUAcwAgAGQAcgBhAHcAbgAgAGYAcgBvAG0AIABuACAAaQB0AGUAbQBzACkALgBcAG4AXABuACAAIAAgACAAIiAgAFAAZQByAG0AuwNcAG4AIAAgACAAIAAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoAG8AdQB0ACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AC4AXABuAFwAbgAgACAAIAAgACIgIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwBSALsDXABuACAAIAAgACAAIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAuAFwAbgBcAG4AIAAgACAAIAAiICAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAuwNcAG4AIAAgACAAIAAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAB3AGkAdABoAG8AdQB0ACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AC4AXABuAFwAbgAgACAAIAAgACIgIABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwC7A1wAbgAgACAAIAAgACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaABlAHIAZQAgAG4AbwAgAGUAbABlAG0AZQBuAHQAIAByAGUAbQBhAGkAbgBzACAAaQBuACAAaQB0AHMAIABvAHIAaQBnAGkAbgBhAGwAIABwAG8AcwBpAHQAaQBvAG4ALgBcAG4AXABuACAAIAAgACAAIiAgAEsAbgBhAHAAUwBhAGMAawC7A1wAbgAgACAAIAAgACAAIAAgACAAUwBvAGwAdgBlAHMAIAB0AGgAZQAgAHMAdQBiAHMAZQB0ABEgcwB1AG0AIAAvACAAawBuAGEAcABzAGEAYwBrACAAZgBlAGEAcwBpAGIAaQBsAGkAdAB5ACAAcAByAG8AYgBsAGUAbQAgAHUAcwBpAG4AZwAgAHYAZQBjAHQAbwByAGkAegBlAGQAXABuACAAIAAgACAAIAAgACAAIABlAG4AdQBtAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGYAaQBsAHQAZQByAGkAbgBnAC4AXABuAFwAbgAgACAAIAAgACIgIABTAHUAYgBzAGUAdABHAGUAbgC7A1wAbgAgACAAIAAgACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABhAGwAbAAgAHMAdQBiAHMAZQB0AHMAIABvAGYAIABhACAAcwBlAHQAIAAoAHQAaABlACAAcABvAHcAZQByACAAcwBlAHQAKQAsACAAcgBlAHQAdQByAG4AZQBkACAAaQBuACAAYgBpAG4AYQByAHkAESBtAGEAcwBrAFwAbgAgACAAIAAgACAAIAAgACAAbwByAGQAZQByAC4AXABuAFwAbgAgACAAIAAgACIgIABTAHUAYgBzAGUAdABTAHUAbQC7A1wAbgAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AcwAgAGEAbABsACAAcwB1AGIAcwBlAHQAcwAgAHcAaABvAHMAZQAgAGUAbABlAG0AZQBuAHQAcwAgAHMAdQBtACAAdABvACAAYQAgAHQAYQByAGcAZQB0ACAAdgBhAGwAdQBlAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQByAGUAIABzAGgAYQBwAGUAESBwAHIAZQBzAGUAcgB2AGkAbgBnACAAYQBuAGQAIAByAGUAdAB1AHIAbgAgADIARAAgAGEAcgByAGEAeQBzACAAdwBoAGUAcgBlACAAZQBhAGMAaAAgAHIAbwB3AFwAbgAgACAAIAAgACAAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABjAG8AbQBiAGkAbgBhAHQAbwByAGkAYQBsACAAbwBiAGoAZQBjAHQALgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAG8AcABlAHIAYQB0AGUAIABvAG4AIABhAHIAcgBhAHkAcwAgAG8AZgAgAGkAdABlAG0AcwAsACAAbgBvAHQAIABqAHUAcwB0ACAAaQBuAHQAZQBnAGUAcgBzAC4AXABuACAAIAAgACAAIiAgAFQAaABlACAAdQBuAGQAZQByAGwAeQBpAG4AZwAgAGEAcgBjAGgAaQB0AGUAYwB0AHUAcgBlACAAdQBzAGUAcwAgAGEAIABmAHUAbgBuAGUAbAAgAG0AbwBkAGUAbAA6ACAAbABhAHIAZwBlACAAZQBuAHUAbQBlAHIAYQB0AGkAbwBuAHMAIABhAHIAZQBcAG4AIAAgACAAIAAgACAAZwBlAG4AZQByAGEAdABlAGQAIABvAG4AYwBlACAAYQBuAGQAIABmAGkAbAB0AGUAcgBlAGQAIABiAHkAIABvAHIAZABlAHIALAAgAHUAbgBpAHEAdQBlAG4AZQBzAHMALAAgAG8AcgAgAHAAbwBzAGkAdABpAG8AbgBhAGwAIABwAHIAZQBkAGkAYwBhAHQAZQBzAC4AXABuAFwAbgBFAG4AdQBtAGUAcgBhAHQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABHAGUAbgBlAHIAYQB0AGkAbgBnACAAZgB1AG4AYwB0AGkAbwBuACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAZQByAG0AUgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABmAHUAbABsACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHwAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwBSALsDIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGUAcgBtALsDIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDXABuACAAIAAgACAAIAAgACAAIAAoAGYAaQBsAHQAZQByACAAcgBlAHAAZQBhAHQAcwApACAAIAAgACAAIAAgACAAIAAoAGYAaQBsAHQAZQByACAAYgB5ACAAbwByAGQAZQByACkAIAAgACAAIAAgACgAZgBpAGwAdABlAHIAIABiAHkAIABwAG8AcwBpAHQAaQBvAG4AKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzALsDXABuACAAIAAgACAAIAAoAGYAaQBsAHQAZQByACAAcgBlAHAAZQBhAHQAcwAgACsAIABvAHIAZABlAHIAKQBcAG4AXABuAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCABEgQwBPAFIARQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AcgBlACAAZwBlAG4AZQByAGEAdABpAG4AZwAgAGYAdQBuAGMAdABpAG8AbgAgAGYAbwByACAAYQBsAGwAIABjAG8AbQBiAGkAbgBhAHQAbwByAGkAYQBsACAAbwBwAGUAcgBhAHQAbwByAHMAIABpAG4AIAB0AGgAZQAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuACAAIAAgACAAYwBhAHQAZQBnAG8AcgB5AC4AIABQAHIAbwBkAHUAYwBlAHMAIABpAG4AZABlAHgAIABtAGEAdAByAGkAYwBlAHMAIABmAG8AcgAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgBzACwAIABjAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwAsACAAbQB1AGwAdABpAHMAZQB0AHMALABcAG4AIAAgACAAIABhAG4AZAAgAGQAZQByAGEAbgBnAGUAbQBlAG4AdABzACAAdQBzAGkAbgBnACAAYQAgAHYAZQBjAHQAbwByAGkAegBlAGQAIABmAHUAbgBuAGUAbAAgAGEAcgBjAGgAaQB0AGUAYwB0AHUAcgBlAC4AIABIAGkAZwBoAGUAcgARIGwAZQB2AGUAbABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AcwAgACgAUABlAHIAbQBSALsDLAAgAFAAZQByAG0AuwMsACAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAUgC7AywAIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7AywAIABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwC7AykAXABuACAAIAAgACAAYQByAGUAIAB0AGgAaQBuACAAdwByAGEAcABwAGUAcgBzACAAYQByAG8AdQBuAGQAIAB0AGgAaQBzACAAZwBlAG4AZQByAGEAdABvAHIALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIABpAHQAZQBtAHMALgAgAEkAdABlAG0AcwAgAG0AYQB5ACAAYgBlACAAbgB1AG0AYgBlAHIAcwAgAG8AcgAgAHQAZQB4AHQALgBcAG4AXABuACAAIAAgACAAawBcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBuAGcAdABoACAAbwBmACAAZQBhAGMAaAAgAHQAdQBwAGwAZQAgACgAawAgAGUiIAAwACkALgAgAE0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIALgBcAG4AXABuACAAIAAgACAAdAB5AHAAZQBcAG4AIAAgACAAIAAgACAAIAAgAFMAZQBsAGUAYwB0AG8AcgAgAGYAbwByACAAdABoAGUAIABjAG8AbQBiAGkAbgBhAHQAbwByAGkAYQBsACAAbQBvAGQAZQA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxACAAkiEgAFAAZQByAG0AdQB0AGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAgAJIhIABQAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaQB0AGgAbwB1AHQAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADMAIACSISAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACAAkiEgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaABvAHUAdAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAANQAgAJIhIABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABBAGwAbAAgAHIAZQBzAHUAbAB0AHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAgAGEAcwAgADIARAAgAGEAcgByAGEAeQBzACAAdwBoAGUAcgBlACAAZQBhAGMAaAAgAHIAbwB3ACAAaQBzACAAbwBuAGUAIAB0AHUAcABsAGUALgBcAG4AIAAgACAAIAAiICAASQBmACAAaQB0AGUAbQBzACAAYQByAGUAIABuAHUAbQBlAHIAaQBjACAAYQBuAGQAIABlAHEAdQBhAGwAIAB0AG8AIABTAEUAUQBVAEUATgBDAEUAKABuACkALAAgAHIAYQB3ACAAaQBuAGQAaQBjAGUAcwAgAGEAcgBlACAAcgBlAHQAdQByAG4AZQBkAC4AXABuACAAIAAgACAAIAAgAE8AdABoAGUAcgB3AGkAcwBlACwAIABpAHQAZQBtAHMAIABhAHIAZQAgAHMAdQBiAHMAdABpAHQAdQB0AGUAZAAgAGkAbgB0AG8AIAB0AGgAZQAgAGkAbgBkAGUAeAAgAGEAcgByAGEAeQBfADIARAAuAFwAbgAgACAAIAAgACIgIABNAGEAeABpAG0AdQBtACAAZQBuAHUAbQBlAHIAYQB0AGkAbwBuACAAcwBpAHoAZQAgAGkAcwAgAGMAYQBwAHAAZQBkACAAYQB0ACAAMQAsADAANAA4ACwANQA3ADYAIAByAG8AdwBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAbgB1AG0AZQByAGEAdABlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGsALABcAG4AIAAgACAAIAB0AHkAcABlACwAXABuAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAGsAKQAsACAAawAgADwAIAAwACwAIABrACAAPgAgAEMATwBVAE4AVABBACgAaQB0AGUAbQBzACkAKQAsACMAVgBBAEwAVQBFACEALABcAG4AXABuACAAIAAgACAASQBGACgAQwBPAFUATgBUAEEAKABrACkAIAA8AD4AIAAxACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEMATwBVAE4AVABBACgAaQB0AGUAbQBzACkAIABeACAAawAgAD4AIAAxADAANAA4ADUANwA2ACwAIwBOAFUATQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAHQAZQBtAHMAXABuACAAIAAgACAAbABpAHMAdAAsACAAIAAgACAAVABPAEMATwBMACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIABuACwAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAGwAaQBzAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIAByAG8AdwBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAG4AIABeACAAawAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGEAcwBlACAAZwBlAG4AZQByAGEAdABvAHIAOgAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdABcAG4AIAAgACAAIABQAF8AcgAsACAAIAAgACAAIABMAEEATQBCAEQAQQAoADEAIAArACAATQBPAEQAKABRAFUATwBUAEkARQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKABpACkALABuACAAXgAgAFMARQBRAFUARQBOAEMARQAoACwAIABrACwAIABrACAALQAgADEALAAgAC0AMQApACkALABuACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgACgAbgBvACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0ACkAXABuACAAIAAgACAAUAAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAFAAXwByACgAKQAsAEkAUwBOAEEAKABCAFkAUgBPAFcAKABQAF8AcgAoACkALAAgAE0ATwBEAEUAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwAgAHcAaQB0AGgAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAXABuACAAIAAgACAAQwBfAHIALAAgACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAFAAXwByACgAKQAsAEIAWQBSAE8AVwAoAFAAXwByACgAKQAsAEwAQQBNAEIARABBACgAcgBvAHcALAAgAEEATgBEACgAcgBvAHcAIAA9ACAAUwBPAFIAVAAoAHIAbwB3ACwALAAsADEAKQApACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAAoAG4AbwAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAApAFwAbgAgACAAIAAgAEMALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARgBJAEwAVABFAFIAKABDAF8AcgAoACkALABJAFMATgBBACgAQgBZAFIATwBXACgAQwBfAHIAKAApACwAIABNAE8ARABFACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAHIAYQBuAGcAZQBtAGUAbgB0AHMAXABuACAAIAAgACAARAAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAFAAXwByACgAKQAsAEIAWQBSAE8AVwAoAFAAXwByACgAKQAsAEwAQQBNAEIARABBACgAcgBvAHcALAAgAE4ATwBUACgATwBSACgAUwBFAFEAVQBFAE4AQwBFACgALAAgAGsAKQAgAD0AIAByAG8AdwApACkAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGcAZQBuAGUAcgBhAHQAbwByAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgAEwAQQBNAEIARABBACgAQwBIAE8ATwBTAEUAKAB0AHkAcABlACwAIABQAF8AcgAoACkALAAgAFAAKAApACwAIABDAF8AcgAoACkALAAgAEMAKAApACwAIABEACgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB1AGIAcwB0AGkAdAB1AHQAZQAgAGkAdABlAG0AcwAgAHUAbgBsAGUAcwBzACAAdABoAGUAeQAgAGEAcgBlACAAZQB4AGEAYwB0AGwAeQAgADEALgAuAG4AXABuACAAIAAgACAATgBvAHQASQBuAHQAPwAsACAATgBPAFQAKABBAE4ARAAoAFMARQBRAFUARQBOAEMARQAoAG4AKQAgAD0AIABsAGkAcwB0ACkAKQAsAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgAEkARgAoAE4AbwB0AEkAbgB0AD8ALAAgAEkATgBEAEUAWAAoAGwAaQBzAHQALAAgAGkAZAB4ACgAKQApACwAIABpAGQAeAAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBDAEIAMAAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUABlAHIAbQBSALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0ACAAKABrABEgdAB1AHAAbABlAHMAIABkAHIAYQB3AG4AIABmAHIAbwBtACAAbgAgAGkAdABlAG0AcwApAC4AXABuACAAIAAgACAARQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIAByAGUAcwB1AGwAdAAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoACAAawAuACAAUwB1AHAAcABvAHIAdABzAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAGEAbgBkACAAMgBEACAAaQB0AGUAbQAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQBzAC4AIABJAHQAZQBtAHMAIABtAGEAeQAgAGIAZQAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0AC4AXABuAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuAFwAbgAgACAAIAAgACAAIAAgACAATABlAG4AZwB0AGgAIABvAGYAIABlAGEAYwBoACAAdAB1AHAAbABlACAAKABrACAAZSIgADAAKQAuACAATQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABrACwAIAAxACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABlAHIAbQBSALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAXABuACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALAAgADEAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEMAQgAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABQAGUAcgBtALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoAG8AdQB0ACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AC4AIABFAGEAYwBoACAAcgBvAHcAIABvAGYAIAB0AGgAZQAgAHIAZQBzAHUAbAB0ACAAcgBlAHAAcgBlAHMAZQBuAHQAcwBcAG4AIAAgACAAIABvAG4AZQAgAGsAESB0AHUAcABsAGUAIABkAHIAYQB3AG4AIABmAHIAbwBtACAAdABoAGUAIABpAG4AcAB1AHQAIABpAHQAZQBtAHMALAAgAHcAaQB0AGgAIABuAG8AIAByAGUAcABlAGEAdABlAGQAIABwAG8AcwBpAHQAaQBvAG4AcwAuACAAUwB1AHAAcABvAHIAdABzAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAGEAbgBkACAAMgBEACAAaQB0AGUAbQAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQBzAC4AIABJAHQAZQBtAHMAIABtAGEAeQAgAGIAZQAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0AC4AXABuAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuAFwAbgAgACAAIAAgACAAIAAgACAATABlAG4AZwB0AGgAIABvAGYAIABlAGEAYwBoACAAdAB1AHAAbABlACAAKABrACAAZSIgADAAKQAuACAATQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABrACwAIAAyACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABlAHIAbQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABpAHQAZQBtAHMALABcAG4AIAAgACAAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgAsAFwAbgAgACAAIAAgAEUAbgB1AG0AZQByAGEAdABlALsDKABpAHQAZQBtAHMALAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAIAAyACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBDAEIAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAUgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAbgB1AG0AZQByAGEAdABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAgACgAbQB1AGwAdABpAHMAZQB0AHMAKQAuACAARQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIAByAGUAcwB1AGwAdABcAG4AIAAgACAAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABrABEgZQBsAGUAbQBlAG4AdAAgAG0AdQBsAHQAaQBzAGUAdAAgAGQAcgBhAHcAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGkAdABlAG0AcwAsACAAdwBoAGUAcgBlACAAbwByAGQAZQByAFwAbgAgACAAIAAgAGQAbwBlAHMAIABuAG8AdAAgAG0AYQB0AHQAZQByACAAYQBuAGQAIAByAGUAcABlAGEAdABlAGQAIABzAGUAbABlAGMAdABpAG8AbgBzACAAYQByAGUAIABhAGwAbABvAHcAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQBzAC4AIABJAHQAZQBtAHMAIABtAGEAeQAgAGIAZQAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0AC4AXABuAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAUwBpAHoAZQAgAG8AZgAgAGUAYQBjAGgAIABjAG8AbQBiAGkAbgBhAHQAaQBvAG4AIAAoAGsAIABlIiAAMAApAC4AIABNAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAEUAbgB1AG0AZQByAGEAdABlALsDKABpAHQAZQBtAHMALAAgAGsALAAgADMAKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwBSALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAXABuACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALAAgADMAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEMAQgAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAbgB1AG0AZQByAGEAdABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaABvAHUAdAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAuACAARQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIAByAGUAcwB1AGwAdAAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAXABuACAAIAAgACAAbwBuAGUAIABrABEgZQBsAGUAbQBlAG4AdAAgAHMAdQBiAHMAZQB0ACAAZAByAGEAdwBuACAAZgByAG8AbQAgAHQAaABlACAAaQBuAHAAdQB0ACAAaQB0AGUAbQBzACwAIAB3AGgAZQByAGUAIABvAHIAZABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABtAGEAdAB0AGUAcgBcAG4AIAAgACAAIABhAG4AZAAgAHIAZQBwAGUAYQB0AGUAZAAgAHMAZQBsAGUAYwB0AGkAbwBuAHMAIABhAHIAZQAgAG4AbwB0ACAAYQBsAGwAbwB3AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGkAdABlAG0AcwBcAG4AIAAgACAAIAAgACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAGkAdABlAG0AcwAuACAASQB0AGUAbQBzACAAbQBhAHkAIABiAGUAIABuAHUAbQBiAGUAcgBzACAAbwByACAAdABlAHgAdAAuAFwAbgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAaQB6AGUAIABvAGYAIABlAGEAYwBoACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuACAAKABrACAAZSIgADAAKQAuACAATQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABrACwAIAA0ACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQB0AGUAbQBzACwAXABuACAAIAAgACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALABcAG4AIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgAsACAANAApAFwAbgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAZABlAHIAYQBuAGcAZQBtAGUAbgB0AHMAIABvAGYAIABsAGUAbgBnAHQAaAAgAGsALgAgAEEAIABkAGUAcgBhAG4AZwBlAG0AZQBuAHQAIABpAHMAIABhACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuACAAaQBuACAAdwBoAGkAYwBoAFwAbgAgACAAIAAgAG4AbwAgAGUAbABlAG0AZQBuAHQAIABhAHAAcABlAGEAcgBzACAAaQBuACAAaQB0AHMAIABvAHIAaQBnAGkAbgBhAGwAIABwAG8AcwBpAHQAaQBvAG4ALgAgAEUAYQBjAGgAIAByAG8AdwAgAG8AZgAgAHQAaABlACAAcgBlAHMAdQBsAHQAXABuACAAIAAgACAAcgBlAHAAcgBlAHMAZQBuAHQAcwAgAG8AbgBlACAAZABlAHIAYQBuAGcAZQBkACAAawARIHQAdQBwAGwAZQAgAGQAcgBhAHcAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGkAdABlAG0AcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGkAdABlAG0AcwBcAG4AIAAgACAAIAAgACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAGkAdABlAG0AcwAuACAASQB0AGUAbQBzACAAbQBhAHkAIABiAGUAIABuAHUAbQBiAGUAcgBzACAAbwByACAAdABlAHgAdAAuAFwAbgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgBcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBuAGcAdABoACAAbwBmACAAZQBhAGMAaAAgAHQAdQBwAGwAZQAgACgAawAgAGUiIAAwACkALgAgAE0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABFAHEAdQBpAHYAYQBsAGUAbgB0ACAAdABvACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAawAsACAANQApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAXABuACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALAAgADUAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEMAQgAwADYAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABLAG4AYQBwAFMAYQBjAGsAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAG8AbAB2AGUAcwAgAHQAaABlACAAMAARIDEAIABrAG4AYQBwAHMAYQBjAGsAIABwAHIAbwBiAGwAZQBtACAAYgB5ACAAZQBuAHUAbQBlAHIAYQB0AGkAbgBnACAAYQBsAGwAIABzAHUAYgBzAGUAdABzACAAbwBmACAAaQB0AGUAbQBzACAAYQBuAGQAXABuACAAIAAgACAAcwBlAGwAZQBjAHQAaQBuAGcAIAB0AGgAZQAgAGYAZQBhAHMAaQBiAGwAZQAgAHAAYQBjAGsAKABzACkAIAB3AGkAdABoACAAbQBhAHgAaQBtAHUAbQAgAHQAbwB0AGEAbAAgAHYAYQBsAHUAZQAuACAAVQBzAGUAcwAgAGEAIABiAHIAdQB0AGUAESBmAG8AcgBjAGUALABcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgBpAHoAZQBkACAAYgBpAHQAESBtAGEAcwBrACAAZwBlAG4AZQByAGEAdABvAHIAIABhAG4AZAAgAHMAdQBwAHAAbwByAHQAcwAgAGIAbwB0AGgAIABuAHUAbQBlAHIAaQBjACAAYQBuAGQAIAB0AGUAeAB0ACAAaQB0AGUAbQAgAGwAYQBiAGUAbABzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQAgAGwAYQBiAGUAbABzACAAKABuAHUAbQBiAGUAcgBzACAAbwByACAAdABlAHgAdAApAC4AXABuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwBcAG4AIAAgACAAIAAgACAAIAAgAEEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIAB2AGEAbAB1AGUAcwAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIAB0AG8AIABlAGEAYwBoACAAaQB0AGUAbQAuAFwAbgBcAG4AIAAgACAAIAB3AGUAaQBnAGgAdABzAFwAbgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAHcAZQBpAGcAaAB0AHMAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAdABvACAAZQBhAGMAaAAgAGkAdABlAG0ALgBcAG4AXABuACAAIAAgACAAYwBhAHAAYQBjAGkAdAB5AFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIAIABuAHUAbQBlAHIAaQBjACAAdwBlAGkAZwBoAHQAIABsAGkAbQBpAHQALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABpAHQAZQBtAHMALAAgAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwAsACAAYQBuAGQAIAB3AGUAaQBnAGgAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AUgBPAFcALgBcAG4AIAAgACAAIAAiICAAYwBhAHAAYQBjAGkAdAB5ACAAaQBzACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAHQAbwAgAGEAIABzAGMAYQBsAGEAcgAgAHcAaQB0AGgAIABJAE4ARABFAFgAKABjAGEAcABhAGMAaQB0AHkALAAxACwAMQApAC4AXABuACAAIAAgACAAIiAgAE0AYQB4AGkAbQB1AG0AIABpAHQAZQBtACAAYwBvAHUAbgB0ACAAaQBzACAAYwBhAHAAcABlAGQAIABhAHQAIAAyADAAIAB0AG8AIABhAHYAbwBpAGQAIABjAG8AbQBiAGkAbgBhAHQAbwByAGkAYQBsACAAZQB4AHAAbABvAHMAaQBvAG4ALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASwBuAGEAcABTAGEAYwBrALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAHcAZQBpAGcAaAB0AHMALABcAG4AIAAgACAAIABjAGEAcABhAGMAaQB0AHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAFQAbwBvAE0AYQBuAHkASQB0AGUAbQBzAD8ALAAgACAAIABSAE8AVwBTACgAaQB0AGUAbQBzACkAIAAqACAAQwBPAEwAVQBNAE4AUwAoAGkAdABlAG0AcwApACAAPgAgADIAMAAsAFwAbgAgACAAIAAgAFQAZQB4AHQASQB0AGUAbQBWAGEAbAA/ACwAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwApACkALABcAG4AIAAgACAAIABUAGUAeAB0AFcAZQBpAGcAaAB0AHMAPwAsACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAB3AGUAaQBnAGgAdABzACkAKQAsAFwAbgAgACAAIAAgAFQAZQB4AHQAQwBhAHAAYQBjAGkAdAB5AD8ALAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAGMAYQBwAGEAYwBpAHQAeQApACkALABcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMATQBhAHQAYwBoAD8ALAAgACAATwBSACgAQwBPAFUATgBUAEEAKABpAHQAZQBtAHMAKQAgADwAPgAgAEMATwBVAE4AVABBACgAdgBhAGwAdQBlAF8AbwBmAF8AaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABpAHQAZQBtAHMAKQAgADwAPgAgAEMATwBVAE4AVABBACgAdwBlAGkAZwBoAHQAcwApACkALABcAG4AXABuACAAIAAgACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVABlAHgAdABJAHQAZQBtAFYAYQBsAD8ALABUAGUAeAB0AFcAZQBpAGcAaAB0AHMAPwAsAFQAZQB4AHQAQwBhAHAAYQBjAGkAdAB5AD8ALABTAGgAYQBwAGUATQBpAHMATQBhAHQAYwBoAD8AKQAsAFwAbgBcAG4AIAAgACAAIABlAHgAaQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAcwBjAGUAbgBhAHIAaQBvAHMAKQAsAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAFYAQQBMAFUARQAtAEkAVABFAE0AIQBcACIAOwBcACIAIwBWAEEATABVAEUALQBXAEUASQBHAEgAVABTACEAXAAiADsAXAAiACMAVgBBAEwAVQBFAC0AQwBBAFAAQQBDAEkAVABZACEAXAAiADsAXAAiACMASQBOAFAAVQBUAC0ATQBJAFMATQBBAFQAQwBIACEAXAAiAH0ALABcAG4AXABuACAAIAAgACAAYQBsAGUAcgB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAUgBSAEEAWQBUAE8AVABFAFgAVAAoAEYASQBMAFQARQBSACgAZQByAHIAbwByAHMALAAgAHMAYwBlAG4AYQByAGkAbwBzACkAKQAsAFwAbgBcAG4ASQBGACgAVABvAG8ATQBhAG4AeQBJAHQAZQBtAHMAPwAsAFwAIgAjAFQATwBPAC0ATQBBAE4AWQAtAEkAVABFAE0AUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABlAHgAaQB0ACwAYQBsAGUAcgB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIABpAHQAZQBtAHMALAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBSAE8AVwAoAGkAdABlAG0AcwApACwAXABuACAAIAAgACAAdgBhAGwAdQBlAF8AbwBmAF8AaQB0AGUAbQBzACwAIABUAE8AUgBPAFcAKAB2AGEAbAB1AGUAXwBvAGYAXwBpAHQAZQBtAHMAKQAsAFwAbgAgACAAIAAgAHcAZQBpAGcAaAB0AHMALAAgACAAIAAgACAAIAAgACAAVABPAFIATwBXACgAdwBlAGkAZwBoAHQAcwApACwAXABuACAAIAAgACAAYwBhAHAAYQBjAGkAdAB5ACwAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKABjAGEAcABhAGMAaQB0AHkALAAgADEALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAGEAYgBlAGwAcwBcAG4AIAAgACAAIABsAGEAYgBlAGwAcwAsACAAIAAgACAAIAAgACAAIAAgAHsAXAAiAEkAdABlAG0AcwBcACIAOwAgAFwAIgBWAGEAbAB1AGUAXAAiADsAIABcACIAVwBlAGkAZwBoAHQAXAAiADsAIABcACIAUABhAGMAawBcACIAfQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAG4AdQBtAGUAcgBhAHQAaQBvAG4AXABuACAAIAAgACAAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAGkAdABlAG0AcwApACwAXABuACAAIAAgACAAQwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAyACAAXgAgAG4AIAAtACAAMQApACwAXABuACAAIAAgACAAYgBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDKABDACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAVwBlAGkAZwBoAHQAIABmAGUAYQBzAGkAYgBpAGwAaQB0AHkAXABuACAAIAAgACAAdwBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIABiAGkAbgAgACoAIAB3AGUAaQBnAGgAdABzACwAXABuACAAIAAgACAAZgBlAGEAcwBpAGIAbABlAD8ALAAgACAAIAAgACAAIABCAFkAUgBPAFcAKAB3AF8AYQByAHIALAAgAFMAVQBNACkAIAA8AD0AIABjAGEAcABhAGMAaQB0AHkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAdQBlACAAYwBvAG0AcAB1AHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAHYAYQBsAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABiAGkAbgAgACoAIAB2AGEAbAB1AGUAXwBvAGYAXwBpAHQAZQBtAHMALAAgAGYAZQBhAHMAaQBiAGwAZQA/ACwAIAAwACkALABcAG4AIAAgACAAIAB0AG8AdABhAGwAcwAsACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAHYAYQBsAF8AYQByAHIALAAgAFMAVQBNACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABvAHAAdABpAG0AYQBsACAAcABhAGMAawAoAHMAKQBcAG4AIAAgACAAIABwAGEAYwBrACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABGAEkATABUAEUAUgAoAHYAYQBsAF8AYQByAHIALAAgAE0AQQBYACgAdABvAHQAYQBsAHMAKQAgAD0AIAB0AG8AdABhAGwAcwAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBpAG4AYQBsACAAdABhAGIAbABlAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAASQBGAE4AQQAoAEgAUwBUAEEAQwBLACgAbABhAGIAZQBsAHMALAAgAFYAUwBUAEEAQwBLACgAaQB0AGUAbQBzACwAIAB2AGEAbAB1AGUAXwBvAGYAXwBpAHQAZQBtAHMALAAgAHcAZQBpAGcAaAB0AHMALAAgAHAAYQBjAGsAKQApACwAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFMAdQBiAHMAZQB0AEcAZQBuALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARABlAGMAMgBCAGkAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABhAGwAbAAgAG4AbwBuABEgZQBtAHAAdAB5ACAAcwB1AGIAcwBlAHQAcwAgAG8AZgAgAGEAIABzAHUAcABwAGwAaQBlAGQAIABsAGkAcwB0ACAAdQBzAGkAbgBnACAAYgByAHUAdABlABEgZgBvAHIAYwBlAFwAbgAgACAAIAAgAGIAaQB0AG0AYQBzAGsAaQBuAGcALgAgAEUAYQBjAGgAIAByAG8AdwAgAG8AZgAgAHQAaABlACAAcgBlAHMAdQBsAHQAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABzAHUAYgBzAGUAdAAsACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhAFwAbgAgACAAIAAgAGMAbwBtAG0AYQARIHMAZQBwAGEAcgBhAHQAZQBkACAAcwB0AHIAaQBuAGcALgAgAFMAdQBwAHAAbwByAHQAcwAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0ACAAaQB0AGUAbQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAcwBlAHQAXABuACAAIAAgACAAIAAgACAAIABBAHIAcgBhAHkAIABvAGYAIABpAHQAZQBtAHMAIAAoAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0ACkALgAgAEYAbABhAHQAdABlAG4AZQBkACAAdwBpAHQAaAAgAFQATwBSAE8AVwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE0AYQB4AGkAbQB1AG0AIABpAHQAZQBtACAAYwBvAHUAbgB0ACAAaQBzACAAYwBhAHAAcABlAGQAIABhAHQAIAAyADAALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwB1AGIAcwBlAHQARwBlAG4AuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcwBlAHQALABcAG4AXABuAEkARgAoAFIATwBXAFMAKABzAGUAdAApACAAKgAgAEMATwBMAFUATQBOAFMAKABzAGUAdAApACAAPgAgADIAMAAsAFwAIgAjAFQATwBPAC0ATQBBAE4AWQAtAEkAVABFAE0AUwAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAHMAZQB0ACwAIAAgACAAIABUAE8AUgBPAFcAKABzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGkAdABlAG0AcwBcAG4AIAAgACAAIABuACwAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQB0ACAAbQBhAHMAawBzACAAKABlAHgAYwBsAHUAZABlACAAMAApAFwAbgAgACAAIAAgAEMALAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAyACAAXgAgAG4AIAAtACAAMQApACwAXABuACAAIAAgACAAYgBpAG4ALAAgACAAIAAgAEQAZQBjADIAQgBpAG4AuwMoAEMALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABtAGEAcwBrAFwAbgAgACAAIAAgAG0AYQBzAGsAZQBkACwAIABJAEYAKABiAGkAbgAsACAAcwBlAHQALAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgB2AGUAcgB0ACAAZQBhAGMAaAAgAG0AYQBzAGsAZQBkACAAcgBvAHcAIABpAG4AdABvACAAYQAgAGMAbwBtAHAAYQBjAHQAIABzAHUAYgBzAGUAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIABCAFkAUgBPAFcAKABtAGEAcwBrAGUAZAAsACAATABBAE0AQgBEAEEAKAB2ACwAIABUAEUAWABUAEoATwBJAE4AKABcACIALAAgAFwAIgAsACAAMQAsACAAdgApACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAAOABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFMAdQBiAHMAZQB0AFMAdQBtALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARABlAGMAMgBCAGkAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHQAdQByAG4AcwAgAGEAbABsACAAcwB1AGIAcwBlAHQAcwAgAG8AZgAgAGEAIABuAHUAbQBlAHIAaQBjACAAcwBlAHQAIAB3AGgAbwBzAGUAIABlAGwAZQBtAGUAbgB0AHMAIABzAHUAbQAgAGUAeABhAGMAdABsAHkAIAB0AG8AIABhACAAdABhAHIAZwBlAHQALgBcAG4AIAAgACAAIABVAHMAZQBzACAAYgByAHUAdABlABEgZgBvAHIAYwBlACAAYgBpAHQAbQBhAHMAawBpAG4AZwAgACgAbgAgAGQiIAAyADAAKQAuACAARQBhAGMAaAAgAHMAdQBiAHMAZQB0ACAAaQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAYQAgAGMAbwBtAHAAYQBjAHQAXABuACAAIAAgACAAYwBvAG0AbQBhABEgcwBlAHAAYQByAGEAdABlAGQAIABzAHQAcgBpAG4AZwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHMAZQB0AFwAbgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGkAdABlAG0AcwAuACAARgBsAGEAdAB0AGUAbgBlAGQAIAB3AGkAdABoACAAVABPAFIATwBXAC4AIABUAGUAeAB0ACAAaQBzACAAbgBvAHQAIABhAGwAbABvAHcAZQBkAC4AXABuAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0AFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIAIABuAHUAbQBlAHIAaQBjACAAdABhAHIAZwBlAHQAIABzAHUAbQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAbQBwAHQAeQAgAHMAdQBiAHMAZQB0ACAAaQBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAYwBvAG4AcwB0AHIAdQBjAHQAaQBvAG4AIAAoAGIAaQB0AG0AYQBzAGsAIAAwACAAbwBtAGkAdAB0AGUAZAApAC4AXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBOAE8ALQBTAE8ATABVAFQASQBPAE4AIQBcACIAIABpAGYAIABuAG8AIABzAHUAYgBzAGUAdABzACAAbQBhAHQAYwBoACAAdABoAGUAIAB0AGEAcgBnAGUAdAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHUAYgBzAGUAdABTAHUAbQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABzAGUAdAAsAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcwBjAGEAbABhAHIAXABuACAAIAAgACAAdABhAHIAZwBlAHQALAAgAEkATgBEAEUAWAAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAFQAbwBvAE0AYQBuAHkASQB0AGUAbQBzAD8ALAAgAFIATwBXAFMAKABzAGUAdAApACAAKgAgAEMATwBMAFUATQBOAFMAKABzAGUAdAApACAAPgAgADIAMAAsAFwAbgAgACAAIAAgAFQAZQB4AHQAUwBlAHQAPwAsACAAIAAgACAAIAAgAE8AUgAoAEkAUwBFAFIAUgBPAFIAKAAtAC0AcwBlAHQAKQApACwAXABuACAAIAAgACAAVABlAHgAdABUAGEAcgBnAGUAdAA/ACwAIAAgACAASQBTAEUAUgBSAE8AUgAoAC0ALQB0AGEAcgBnAGUAdAApACwAXABuAFwAbgBJAEYAKABUAG8AbwBNAGEAbgB5AEkAdABlAG0AcwA/ACwAIABcACIAIwBUAE8ATwAtAE0AQQBOAFkALQBJAFQARQBNAFMAIQBcACIALABcAG4AXABuACAAIAAgACAASQBGACgAVABlAHgAdABTAGUAdAA/ACwAIABcACIAIwBUAEUAWABUAC0AUwBFAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABUAGUAeAB0AFQAYQByAGcAZQB0AD8ALAAgAFwAIgAjAFQARQBYAFQALQBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAHMAZQB0ACwAIAAgACAAIAAgACAAVABPAFIATwBXACgALQAtAHMAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgAG4ALAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQB0ACAAbQBhAHMAawBzACAAKABlAHgAYwBsAHUAZABlACAAMAApAFwAbgAgACAAIAAgAEMALAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAMgAgAF4AIABuACAALQAgADEAKQAsAFwAbgAgACAAIAAgAGIAaQBuACwAIAAgACAAIAAgACAARABlAGMAMgBCAGkAbgC7AygAQwAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAdgBhAGwAXwBhAHIAcgAsACAAIABJAEYAKABiAGkAbgAsACAAcwBlAHQALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AYwBhAHQAZQAgAHQAYQByAGcAZQB0ACAAcwB1AG0AXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIABCAFkAUgBPAFcAKAB2AGEAbABfAGEAcgByACwAIABTAFUATQApACAAPQAgAHQAYQByAGcAZQB0ACwAXABuACAAIAAgACAAZgBvAHUAbgBkACwAIAAgACAAIABGAEkATABUAEUAUgAoAHYAYQBsAF8AYQByAHIALAAgAGIAbwBvAGwALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgB2AGUAcgB0ACAAZQBhAGMAaAAgAHMAdQBiAHMAZQB0ACAAdABvACAAYQAgAGMAbwBtAHAAYQBjAHQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIABDAG8AbgBjAGkAcwBlALsDLAAgAEwAQQBNAEIARABBACgAdgAsACAAVABFAFgAVABKAE8ASQBOACgAXAAiACwAIABcACIALAAgADEALAAgAFQARQBYAFQAKAB2ACwAIABcACIAMAA7AC0AMAA7ADsAXAAiACkAKQApACwAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIABCAFkAUgBPAFcAKABmAG8AdQBuAGQALAAgAEMAbwBuAGMAaQBzAGUAuwMpACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBuAGQAbABlACAAbgBvACAAbQBhAHQAYwBoAGUAcwBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgAEkARgAoAFMAVQBNACgATABFAE4AKAByAGUAcwB1AGwAdAApACkAIAA9ACAAMAAsACAAXAAiACMATgBPAC0AUwBPAEwAVQBUAEkATwBOACEAXAAiACwAIAByAGUAcwB1AGwAdAApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAvACAAWwBHAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ALwAvACAALQAtAC0AIwAjACAAMQAwACAAFCAgAEcAcgBpAGQAIABEAGkAYQBnAG4AbwBzAHQAaQBjAHMAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwByAGkAZAAgAEQAaQBhAGcAbgBvAHMAdABpAGMAcwAgAGMAbwBuAHQAYQBpAG4AcwAgAGYAdQBuAGMAdABpAG8AbgBzACAAdwBoAG8AcwBlACAAcAB1AHIAcABvAHMAZQAgAGkAcwAgAHQAbwAgAGUAeABwAG8AcwBlACwAIABhAG4AbgBvAHQAYQB0AGUALABcAG4AIAAgACAAIABvAHIAIABlAHgAcABsAGEAaQBuACAAdABoAGUAIABpAG4AdABlAHIAbgBhAGwAIABzAHQAcgB1AGMAdAB1AHIAZQAgAG8AZgAgAGEAIABnAHIAaQBkAC4AIABEAGkAYQBnAG4AbwBzAHQAaQBjAHMAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGEAcgBlAFwAbgAgACAAIAAgAHUAcwBlAGQAIABmAG8AcgAgAGQAZQBiAHUAZwBnAGkAbgBnACwAIABpAG4AdAByAG8AcwBwAGUAYwB0AGkAbwBuACwAIAB2AGkAcwB1AGEAbABpAHoAYQB0AGkAbwBuACwAIABhAG4AZAAgAHMAdAByAHUAYwB0AHUAcgBhAGwAIABhAG4AYQBsAHkAcwBpAHMALgBcAG4AXABuAEYAdQBuAGMAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAFIAZQB2AGUAYQBsALsDXABuACAAIAAgACAAIAAgACAAIABpAG4AcwBwAGUAYwB0AHMAIABhACAAYQByAHIAYQB5AF8AMgBEACAAbwBmACAAZABhAHQAYQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAGUAaQB0AGgAZQByADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABBACAAdABvAHAALQBsAGUAdgBlAGwAIABzAHUAbQBtAGEAcgB5ACAAbwBmACAAcwBlAG0AYQBuAHQAaQBjACAAbQBlAHQAcgBpAGMAcwAgACgATgB1AG0AYgBlAHIAcwAsACAAVABlAHgAdABzACwAIABFAHIAcgBvAHIAcwAsACAAZQB0AGMALgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAAQQAgAHYAZQByAGIAbwBzAGUALAAgAGMAZQBsAGwALQBiAHkALQBjAGUAbABsACAAbgBhAHIAcgBhAHQAaQBvAG4AIABvAGYAIAB0AGEAZwBzACAAcABlAHIAIABjAGUAbABsAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBEADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFIAZQB2AGUAYQBsALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABHAHIAaQBkACAARABpAGEAZwBuAG8AcwB0AGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHYAZQBhAGwAuwMgAGkAbgBzAHAAZQBjAHQAcwAgAGEAIABhAHIAcgBhAHkAXwAyAEQAIABvAGYAIABkAGEAdABhACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAZQBpAHQAaABlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABBACAAdABvAHAALQBsAGUAdgBlAGwAIABzAHUAbQBtAGEAcgB5ACAAbwBmACAAcwBlAG0AYQBuAHQAaQBjACAAbQBlAHQAcgBpAGMAcwAgACgATgB1AG0AYgBlAHIAcwAsACAAVABlAHgAdABzACwAIABFAHIAcgBvAHIAcwAsACAAZQB0AGMALgApAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEEAIAB2AGUAcgBiAG8AcwBlACwAIABjAGUAbABsAC0AYgB5AC0AYwBlAGwAbAAgAG4AYQByAHIAYQB0AGkAbwBuACAAbwBmACAAdABhAGcAcwAgAHAAZQByACAAYwBlAGwAbABcAG4AIAAgACAAIABTAHUAcABwAG8AcgB0AHMAIABvAHAAdABpAG8AbgBhAGwAIABkAGUAbABpAG0AaQB0AGUAcgAgAGMAbwBuAHQAcgBvAGwAIABhAG4AZAAgAGIAbABhAG4AawAtAGEAdwBhAHIAZQAgAG8AcAB0AGkAbQBpAHoAYQB0AGkAbwBuAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZABhAHQAYQBcAG4AIAAgACAAIAAgACAAIAAgAEQAYQB0AGEAIAB0AG8AIABiAGUAIABpAG4AcwBwAGUAYwB0AGUAZAAgACgAYQBuAHkAIABzAGMAYQBsAGEAcgAsACAAdgBlAGMAdABvAHIALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQApAC4AXABuAFwAbgAgACAAIAAgAEkAcwBWAGUAcgBiAG8AcwBlAD8AIAAgAFsAbwBwAHQAaQBvAG4AYQBsAF0AXABuACAAIAAgACAAIAAgACAAIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgBzACAAYQAgAGEAcgByAGEAeQBfADIARAAgAG8AZgAgAG4AYQByAHIAYQB0AGEAYgBsAGUAIAB0AGEAZwBzACAAcABlAHIAIABjAGUAbABsAC4AXABuACAAIAAgACAAIAAgACAAIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAByAGUAdAB1AHIAbgBzACAAYQAgADkA1wAyACAAcwB1AG0AbQBhAHIAeQAgAHQAYQBiAGwAZQAuAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAgACAAIABbAG8AcAB0AGkAbwBuAGEAbABdAFwAbgAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIAIAB1AHMAZQBkACAAaQBuACAAdgBlAHIAYgBvAHMAZQAgAG0AbwBkAGUALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAFwAIgAsACAAXAAiAC4AXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBSAGUAdgBlAGEAbAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABkAGEAdABhACwAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgAFsASQBzAFYAZQByAGIAbwBzAGUAPwBdACwAXABuACAAIAAgACAAWwBkAGUAbABpAG0AaQB0AGUAcgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABkAGEAdABhACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAGwAbAAgAG0AZQB0AHIAaQBjACAAbABhAGIAZQBsAHMAXABuACAAIAAgACAAbQBlAHQAcgBpAGMAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAewBcACIATgB1AG0AYgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQB4AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AdQBtAGIAZQByAC0AcwB0AG8AcgBlAGQALQBhAHMALQB0AGUAeAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHIAcgBvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBuAHQAYQBpAG4AcwAgAHMAcABhAGMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbgB0AGEAaQBuAHMAIABzAHAAZQBjAGkAYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAbQB1AGwAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBsAGEAbgBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AZwBpAGMAYQBsAFwAIgB9ACwAXABuAFwAbgAgACAAIAAgAC8ALwAtAC0AIABMAG8AYwBhAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAC0ALQBcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAG0AYQB0AHIAaQBjAGUAcwAgAGEAbgBkACAAZQBuAHMAdQByAGUAIABiAGkAbgBhAHIAeQAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAEIAaQBuALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAdgAsACAAVABPAEMATwBMACgASQBGAEUAUgBSAE8AUgAoAHYALAAgADAAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAG0AbwB2AGUAIABlAHIAcgBvAHIAcwAgAGYAcgBvAG0AIABzAGMAYQBsAGEAcgBzAC4AXABuACAAIAAgACAAUgBlAG0AbwB2AGUATgBBALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAB2ACwAIABJAEYATgBBACgAdgAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZABlAGwAaQBtAGkAdABlAHIAIABmAG8AcgAgAHYAZQByAGIAbwBzAGUAIAByAGUAcABvAHIAdAAuAFwAbgAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZABlAGwAaQBtAGkAdABlAHIAKQAsACAAXAAiACwAIABcACIALAAgAGQAZQBsAGkAbQBpAHQAZQByACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBlAHIAYgBvAHMAZQAgAHIAZQBwAG8AcgB0ACAALQAgAHIAZQB0AHUAcgBuAHMAIABuAGEAcgByAGEAdABhAGIAbABlACAAdABhAGcAcwAgAGIAeQAgAGMAZQBsAGwALgAgAFQAZQByAG0AaQBuAGEAdABlAHMAIABlAGEAcgBsAHkAIABpAGYAIABiAGwAYQBuAGsALgBcAG4AIAAgACAAIABHAGUAdABEAGUAdABhAGkAbABzALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAGEALAAgAGIALAAgAGMALAAgAGQALAAgAGUALAAgAGYALAAgAGcALAAgAGgALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQAsACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAYQAsACAAYgAsACAAYwAsACAAZAAsACAAUgBlAG0AbwB2AGUATgBBALsDKABlACkALAAgAFIAZQBtAG8AdgBlAE4AQQC7AygAZgApACwAIABnACwAIABoACwAIABpACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAZQB0AGEAaQBsACwAIABJAEYAKABoACwAIABcACIAQgBsAGEAbgBrAFwAIgAsACAAVABPAEMATwBMACgASQBGAFMAKABtACwAIABtAGUAdAByAGkAYwBzACkALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABqAG8AaQBuAGUAZAAsACAAVABFAFgAVABKAE8ASQBOACgAZABlAGwAaQBtAGkAdABlAHIALAAgADEALAAgAGQAZQB0AGEAaQBsACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoAbwBpAG4AZQBkACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbABsAHMAIAB3AGkAdABoADoAXABuACAAIAAgACAATgB1AG0AYgBlAHIAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQBUAE8AQwBPAEwAKABJAFMATgBVAE0AQgBFAFIAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAFQAZQB4AHQAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AVABPAEMATwBMACgASQBTAFQARQBYAFQAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAE4AdQBtAGIAZQByAHMAXwBzAHQAbwByAGUAZABfAGEAcwBfAHQAZQB4AHQALAAgAFQATwBDAE8ATAAoAEkAUwBOAFUATQBCAEUAUgAoAEkARgBFAFIAUgBPAFIAKABkAGEAdABhACAAKwAgADAALAAgAFwAIgBcACIAKQApACAAKgAgAEkAUwBUAEUAWABUACgAZABhAHQAYQApACkALABcAG4AIAAgACAAIABDAGUAbABsAHMAXwB3AGkAdABoAF8AZQByAHIAbwByAHMALAAgACAAIAAgACAALQAtAFQATwBDAE8ATAAoAEkAUwBFAFIAUgBPAFIAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAFMAcABhAGMAZQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AQgBpAG4AuwMoAEwARQBOACgAVABSAEkATQAoAGQAYQB0AGEAKQApACAAPAA+ACAATABFAE4AKABkAGEAdABhACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGEAdAB0AGUAcgBuACAAbQBhAHQAYwBoAGUAcwAgAGYAbwByACAAcwBwAGUAYwBpAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAHMAXABuACAAIAAgACAAcABhAHQAdABlAHIAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBbAF4AQQAtAFoAYQAtAHoAMAAtADkAIAAuAF0AfABbAFwAXAB4AHsAMAAwAEEAMAB9AFwAXAB4AHsAMgAwADAAQgB9AC0AXABcAHgAewAyADAAMABEAH0AXQB8AFsAXABcAHQAXABcAG4AXABcAHIAXQB8AFsAXABcAHgAewAxAEYANgAwADAAfQAtAFwAXAB4AHsAMQBGADYANABGAH0AXQBcACIALABcAG4AIAAgACAAIABTAHAAZQBjAGkAYQBsAF8AYwBoAGEAcgBhAGMAdABlAHIAcwAsACAAIAAgACAALQAtAEIAaQBuALsDKABSAEUARwBFAFgAVABFAFMAVAAoAGQAYQB0AGEALAAgAHAAYQB0AHQAZQByAG4AKQApACwAXABuAFwAbgAgACAAIAAgAEYAbwByAG0AdQBsAGEAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AVABPAEMATwBMACgASQBTAEYATwBSAE0AVQBMAEEAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAEIAbABhAG4AawBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AVABPAEMATwBMACgASQBTAEIATABBAE4ASwAoAGQAYQB0AGEAKQApACwAXABuACAAIAAgACAATABvAGcAaQBjAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQBUAE8AQwBPAEwAKABJAFMATABPAEcASQBDAEEATAAoAGQAYQB0AGEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AZQB0AHIAaQBjAHMAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHIAbwB3AC0AdwBpAHMAZQAgAGEAbgBkACAAcwB0AGEAYwBrAGUAZAAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5AC4AXABuACAAIAAgACAAbQBlAHQAcgBpAGMAXwBzAHQAYQBjAGsALAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAHUAbQBiAGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAeAB0AHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AdQBtAGIAZQByAHMAXwBzAHQAbwByAGUAZABfAGEAcwBfAHQAZQB4AHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMAZQBsAGwAcwBfAHcAaQB0AGgAXwBlAHIAcgBvAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBwAGEAYwBlAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAcABlAGMAaQBhAGwAXwBjAGgAYQByAGEAYwB0AGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAG8AcgBtAHUAbABhAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAbABhAG4AawBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAG8AZwBpAGMAYQBsACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBlAHQAcgBpAGMAcwAgAHMAdQBtAG0AYQByAGkAegBlAGQAIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAdABvAHQAYQBsAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAQgBZAEMATwBMACgAbQBlAHQAcgBpAGMAXwBzAHQAYQBjAGsALAAgAFMAVQBNACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8ALQAtACAAUgBlAHAAbwByAHQAaQBuAGcAIAAtAC0AXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAbwBwAC0AbABlAHYAZQBsACAAOQDXADIAIABzAHUAbQBtAGEAcgB5ACAAbwBmACAAZABhAHQAYQAuAFwAbgAgACAAIAAgAFMAdQBtAG0AYQByAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBPAFIAVAAoAEgAUwBUAEEAQwBLACgAbQBlAHQAcgBpAGMAcwAsACAAdABvAHQAYQBsAHMAKQAsACAAMgAsACAALQAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbABsAC0AYgB5AC0AYwBlAGwAbAAgAHIAZQBwAG8AcgB0ACAAbwBmACAAZABhAHQAYQAuAFwAbgAgACAAIAAgAFYAZQByAGIAbwBzAGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFcAUgBBAFAAUgBPAFcAUwAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgB1AG0AYgBlAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAeAB0AHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgB1AG0AYgBlAHIAcwBfAHMAdABvAHIAZQBkAF8AYQBzAF8AdABlAHgAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAGUAbABsAHMAXwB3AGkAdABoAF8AZQByAHIAbwByAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBwAGEAYwBlAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBwAGUAYwBpAGEAbABfAGMAaABhAHIAYQBjAHQAZQByAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBvAHIAbQB1AGwAYQBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAbABhAG4AawBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAbwBnAGkAYwBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwBlAHQARABlAHQAYQBpAGwAcwC7AykALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAFIAZQBwAG8AcgB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgASQBzAFYAZQByAGIAbwBzAGUAPwApACwAIABTAHUAbQBtAGEAcgB5ACgAKQAsACAAVgBlAHIAYgBvAHMAZQApACwAXABuACAAIAAgACAAUgBlAHAAbwByAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvAC8AIAAtAC0ARQBuAGQAIABvAGYAIABCAGkAZwBTAHAAaQBsAGwAIABNAG8AZAB1AGwAZQAtAC0AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIARABHAHIAaQBkALsDIgAsACIAQwBHAHIAaQBkALsDIgAsACIATQBHAHIAaQBkALsDIgAsACIAVABHAHIAaQBkALsDIgAsACIAUABvAGwAYQByAEcAcgBpAGQAuwMiACwAIgBDAGkAcgBjAGwAZQC7AyIALAAiAEQAaQBhAG0AbwBuAGQAuwMiACwAIgBQAGwAdQBzALsDIgAsACIAUAB5AHIAYQBtAGkAZAC7AyIALAAiAFIAaQBuAGcAuwMiACwAIgBTAHEAdQBhAHIAZQC7AyIALAAiAFQAcgBpAGEAbgBnAGwAZQC7AyIALAAiAFIAZQBTAGgAYQBwAGUAMgBEALsDIgAsACIAUgBlAHMAaQB6AGUAuwMiACwAIgBTAGMAYQBuADIARAC7AyIALAAiAFQAcgBhAHYAZQByAHMAZQC7AyIALAAiAFQAYQBrAGUAQgBsAG8AYwBrALsDIgAsACIARABTAHQAYQBjAGsAuwMiACwAIgBXAHIAYQBwAFIAbwB3AHMAMgBEALsDIgAsACIAVwByAGEAcABDAG8AbABzADIARAC7AyIALAAiAFMAdABhAGkAcgBjAGEAcwBlALsDIgAsACIAVgBhAGwAaQBkAGEAdABlAFMAdABhAGkAcgBjAGEAcwBlALsDIgAsACIAVQBuAFAAaQB2AG8AdAC7AyIALAAiAFoAaQBwALsDIgAsACIAUwBsAGkAYwBlAEIAeQBEAGUAZwC7AyIALAAiAFAAYQBkALsDIgAsACIASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMiACwAIgBJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7AyIALAAiAE0AYQBnAG4AaQBmAHkAuwMiACwAIgBaAG8AbwBtALsDIgAsACIARABlAGwAZQB0AGUAUgBvAHcAcwC7AyIALAAiAEQAZQBsAGUAdABlAEMAbwBsAHMAuwMiACwAIgBEAGUAbABlAHQAZQBXAGgAZQByAGUAuwMiACwAIgBQAGkAbgBjAGgAuwMiACwAIgBSAGUAbQBvAHYAZQC7AyIALAAiAFMAcQB1AGUAZQB6AGUAuwMiACwAIgBLAHIAbwBuAGUAYwBrAGUAcgBQAHIAbwBkALsDIgAsACIARQB4AGMAbAB1AGQAZQC7AyIALAAiAFMAbgBhAHAAuwMiACwAIgBTAGgAaQBmAHQAuwMiACwAIgBTAGgAaQBmAHQAUgBvAHcAcwC7AyIALAAiAFMAaABpAGYAdABDAG8AbABzALsDIgAsACIARQBtAGIAZQBkALsDIgAsACIASwBlAGUAcABSAG8AdwBzALsDIgAsACIASwBlAGUAcABDAG8AbABzALsDIgAsACIAQgBsAG8AYwBrAE0AYQBwALsDIgAsACIAVgBhAGwAaQBkAGEAdABlAEIAbABvAGMAawBNAGEAcAC7AyIALAAiAEMAbwBuAHYAbwBsAHYAZQC7AyIALAAiAEYAbwBsAGQAuwMiACwAIgBKAG8AaQBuADIARAC7AyIALAAiAEUAYwBoAG8AuwMiACwAIgBSAGUAcABlAGEAdABSAG8AdwBzALsDIgAsACIAUgBlAHAAZQBhAHQAQwBvAGwAcwC7AyIALAAiAFQAZQBzAHMAZQBsAGwAYQB0AGUAuwMiACwAIgBTAHQAcgBlAGEAawC7AyIALAAiAEMAbwB1AG4AdABkAG8AdwBuALsDIgAsACIASQBuAHMAdABhAG4AYwBlALsDIgAsACIAVwBhAHYAZQC7AyIALAAiAEIAeQBEAGkAYQBnALsDIgAsACIARABpAGEAZwBNAGEAcAC7AyIALAAiAEQAaQBhAGcASQBuAGQAZQB4ALsDIgAsACIAVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwMiACwAIgBQAGEAaQByAHcAaQBzAGUAuwMiACwAIgBUAHIAaQBwAGwAZQB3AGkAcwBlALsDIgAsACIAUQB1AGEAZAB3AGkAcwBlALsDIgAsACIARwByAG8AdQBwAGIAeQBCAGkAbgC7AyIALAAiAEcAcgBvAHUAcABiAHkARABhAHQAZQC7AyIALAAiAFYAYQBsAGkAZABhAHQAZQBHAEQAuwMiACwAIgBQAGkAdgBvAHQAYgB5AEMAYQB0ALsDIgAsACIARwByAG8AdQBwAEkAbgBkAGUAeAC7AyIALAAiAE8AYwBjAHUAcgByAGUAbgBjAGUAuwMiACwAIgBPAGMAYwB1AHIAcgBlAG4AYwBlAFIAYQBuAGcAZQC7AyIALAAiAEcAcgBhAGkAbgC7AyIALAAiAE0AbwBvAHIAZQBBAGcAZwC7AyIALAAiAE0AbwBvAHIAZQBTAGUAbABlAGMAdAC7AyIALAAiAEgAaQBzAHQAbwBnAHIAYQBtALsDIgAsACIATQBvAGQAZQC7AyIALAAiAFoAbwBuAGUAUwB0AGEAdAC7AyIALAAiAEEAbABpAGcAbgC7AyIALAAiAEEAbABpAGcAbgBEAGkAcwB0AGkAbgBjAHQAuwMiACwAIgBBAGwAaQBnAG4AVQBuAGkAcQB1AGUAuwMiACwAIgBDAG8AYQBsAGUAcwBjAGUAuwMiACwAIgBFAHgAcABsAG8AZABlALsDIgAsACIATgB1AG0AYgBlAHIAcwBPAG4AbAB5ALsDIgAsACIAVABlAHgAdABPAG4AbAB5ALsDIgAsACIAUwBwAGwAaQB0ALsDIgAsACIAUgBlAGcAZQB4AFMAYQBmAGUAuwMiACwAIgBCAGkAbgAyAEQAZQBjALsDIgAsACIAQgBpAG4AMgBHAHIAYQB5ALsDIgAsACIAQgBpAHQAQwBvAHUAbgB0ALsDIgAsACIARABlAGMAMgBCAGkAbgC7AyIALAAiAEQAZQBjADIARwByAGEAeQC7AyIALAAiAEUAbgB1AG0AZQByAGEAdABlALsDIgAsACIAUABlAHIAbQBSALsDIgAsACIAUABlAHIAbQC7AyIALAAiAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwMiACwAIgBDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7AyIALAAiAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDIgAsACIASwBuAGEAcABTAGEAYwBrALsDIgAsACIAUwB1AGIAcwBlAHQARwBlAG4AuwMiACwAIgBTAHUAYgBzAGUAdABTAHUAbQC7AyIALAAiAFIAZQB2AGUAYQBsALsDIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBNAEQAWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/onboarding/01. BigSpill - Gridwork and Grid Geometry.xlsx
+++ b/onboarding/01. BigSpill - Gridwork and Grid Geometry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PatrickHogan\Downloads\BigSpill\ready\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82171C58-A494-466A-B2A1-904096EA6B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAEEDF4-A0E3-45DB-BD19-C0B97163146B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC51E23B-0A7B-48A2-94F9-79121C6422FB}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{DC51E23B-0A7B-48A2-94F9-79121C6422FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <definedName name="MGridλ">_xlfn.LAMBDA(_xlpm.grid,_xlop.col_index, _xlfn.LET(_xlpm.RowIdx?, _xlfn.ISOMITTED(_xlpm.col_index), _xlpm.h, ROWS(_xlpm.grid), _xlpm.w, COLUMNS(_xlpm.grid), _xlpm.i, _xlfn.LAMBDA(Resizeλ(_xlfn.SEQUENCE(_xlpm.h), , _xlpm.w)), _xlpm.j, _xlfn.LAMBDA(Resizeλ(_xlfn.SEQUENCE(, _xlpm.w), _xlpm.h)), _xlpm.result, IF(_xlpm.RowIdx?, _xlpm.i(), _xlpm.j()), _xlpm.result))</definedName>
     <definedName name="Modeλ">_xlfn.LAMBDA(_xlpm.array,_xlop.include_totals, IF(COUNT(--ISTEXT(_xlpm.array)) = 0, _xlfn.MODE.MULT(_xlpm.array), _xlfn.LET(_xlpm.msg, "#NO-REPEATS!", _xlpm.V, _xlfn.TOCOL(_xlpm.array), _xlpm.i, _xlfn.MODE.MULT(_xlfn.XMATCH(_xlpm.V, _xlpm.V)), _xlpm.result, _xlfn._xlws.SORT(IFERROR(INDEX(_xlpm.V, _xlpm.i), _xlpm.msg)), _xlpm.keep, ISNUMBER(_xlfn.XMATCH(_xlpm.V, _xlpm.result)), _xlpm.totals, _xlfn.GROUPBY(_xlpm.V, _xlpm.V, _xleta.COUNTA, 0, 0, , _xlpm.keep), _xlpm.deliver, IF(AND(_xlpm.include_totals, _xlpm.result &lt;&gt; _xlpm.msg), _xlpm.totals, _xlpm.result), _xlpm.deliver)))</definedName>
     <definedName name="MooreAggλ">_xlfn.LAMBDA(_xlpm.array_2D,_xlpm.function,_xlop.IsvonNeumann?,_xlop.omit_center, IF(TYPE(_xlpm.array_2D) &lt;&gt; 64, "#array_2D!", IF(TYPE(_xlpm.function) &lt;&gt; 128, "#ETA FUNCTION!", _xlfn.LET(_xlpm.IsvonNeumann?, NOT(_xlfn.ISOMITTED(_xlpm.IsvonNeumann?)), _xlpm.omit_center, NOT(_xlfn.ISOMITTED(_xlpm.omit_center)), _xlpm.height, ROWS(_xlpm.array_2D), _xlpm.width, COLUMNS(_xlpm.array_2D), _xlpm.M, _xlfn.VSTACK("omit", _xlfn.HSTACK("omit", _xlpm.array_2D, "omit"), "omit"), _xlpm.a, _xlfn.TOCOL(_xlfn.DROP(_xlpm.M, -2, -2)), _xlpm.b, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 1), _xlpm.height, _xlpm.width)), _xlpm.c, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 2), _xlpm.height)), _xlpm.d, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), _xlpm.height, _xlpm.width)), _xlpm.center, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, _xlpm.width)), _xlpm.f, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, -_xlpm.width)), _xlpm.g, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, _xlpm.width)), _xlpm.h, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, -_xlpm.width)), _xlpm.i, _xlfn.TOCOL(_xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), -_xlpm.height, -_xlpm.width)), _xlpm.Moore_no_center, _xlfn.HSTACK(_xlpm.a, _xlpm.b, _xlpm.c, _xlpm.d, _xlpm.f, _xlpm.g, _xlpm.h, _xlpm.i), _xlpm.Moore_with_center, _xlfn.HSTACK(_xlpm.a, _xlpm.b, _xlpm.c, _xlpm.d, _xlpm.center, _xlpm.f, _xlpm.g, _xlpm.h, _xlpm.i), _xlpm.von_no_center, _xlfn.HSTACK(_xlpm.b, _xlpm.d, _xlpm.f, _xlpm.h), _xlpm.von_with_center, _xlfn.HSTACK(_xlpm.b, _xlpm.d, _xlpm.f, _xlpm.h, _xlpm.center), _xlpm.Aggregateλ, _xlfn.LAMBDA(_xlpm.v, _xlpm.function(_xlfn.TOCOL(_xlfn.IFS(_xlpm.v, _xlpm.v), 2))), _xlpm.agg, IF(_xlpm.IsvonNeumann?, IF(_xlpm.omit_center, _xlfn.BYROW(_xlpm.von_no_center, _xlpm.Aggregateλ), _xlfn.BYROW(_xlpm.von_with_center, _xlpm.Aggregateλ)), IF(_xlpm.omit_center, _xlfn.BYROW(_xlpm.Moore_no_center, _xlpm.Aggregateλ), _xlfn.BYROW(_xlpm.Moore_with_center, _xlpm.Aggregateλ))), _xlpm.deliver, IFERROR(_xlfn.WRAPROWS(_xlpm.agg, _xlpm.width), 0), _xlpm.deliver))))</definedName>
-    <definedName name="MooreSelectλ">_xlfn.LAMBDA(_xlpm.array_2D,_xlpm.neighbor, IF(TYPE(_xlpm.array_2D) &lt;&gt; 64, "#array_2D!", IF(NOT(AND(_xlpm.neighbor &gt;= 1, _xlpm.neighbor &lt;= 9, NOT(ISTEXT(_xlpm.neighbor)))), "#NEIGHBOR!", _xlfn.LET(_xlpm.height, ROWS(_xlpm.array_2D), _xlpm.width, COLUMNS(_xlpm.array_2D), _xlpm.hpad, _xlfn.EXPAND(0, , _xlpm.width + 2, 0), _xlpm.vpad, _xlfn.EXPAND(0, _xlpm.height, , 0), _xlpm.M, _xlfn.VSTACK(_xlpm.hpad, _xlfn.HSTACK(_xlpm.vpad, _xlpm.array_2D, _xlpm.vpad), _xlpm.hpad), _xlpm.a, _xlfn.DROP(_xlpm.M, -2, -2), _xlpm.b, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 1), _xlpm.height, _xlpm.width), _xlpm.c, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 2), _xlpm.height), _xlpm.d, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), _xlpm.height, _xlpm.width), _xlpm.center, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, _xlpm.width), _xlpm.f, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, -_xlpm.width), _xlpm.g, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, _xlpm.width), _xlpm.h, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, -_xlpm.width), _xlpm.i, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), -_xlpm.height, -_xlpm.width), _xlpm.Moore, _xlfn.HSTACK(_xlpm.a, _xlpm.b, _xlpm.c, _xlpm.d, _xlpm.center, _xlpm.f, _xlpm.g, _xlpm.h, _xlpm.i), _xlpm.start, (_xlpm.neighbor - 1) * _xlpm.width + 1, _xlpm.select_neighbor, _xlfn.CHOOSECOLS(_xlpm.Moore, _xlfn.SEQUENCE(, _xlpm.width, _xlpm.start)), _xlpm.select_neighbor))))</definedName>
+    <definedName name="MooreSelectλ">_xlfn.LAMBDA(_xlpm.array_2D,_xlpm.neighbor, IF(TYPE(_xlpm.array_2D) &lt;&gt; 64, "#array_2D!", IF(NOT(AND(_xlpm.neighbor &gt;= 1, _xlpm.neighbor &lt;= 9, NOT(ISTEXT(_xlpm.neighbor)))), "#NEIGHBOR!", _xlfn.LET(_xlpm.height, ROWS(_xlpm.array_2D), _xlpm.width, COLUMNS(_xlpm.array_2D), _xlpm.hpad, _xlfn.EXPAND(0, , _xlpm.width + 2, 0), _xlpm.vpad, _xlfn.EXPAND(0, _xlpm.height, , 0), _xlpm.M, _xlfn.VSTACK(_xlpm.hpad, _xlfn.HSTACK(_xlpm.vpad, _xlpm.array_2D, _xlpm.vpad), _xlpm.hpad), _xlpm.a, _xlfn.DROP(_xlpm.M, -2, -2), _xlpm.b, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 1), _xlpm.height, _xlpm.width), _xlpm.c, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, , 2), _xlpm.height), _xlpm.d, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), _xlpm.height, _xlpm.width), _xlpm.center, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, _xlpm.width), _xlpm.f, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), _xlpm.height, -_xlpm.width), _xlpm.g, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, _xlpm.width), _xlpm.h, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, -1), -_xlpm.height, -_xlpm.width), _xlpm.i, _xlfn.TAKE(_xlfn.DROP(_xlpm.M, 1, 1), -_xlpm.height, -_xlpm.width), _xlpm.select_neighbor, CHOOSE(_xlpm.neighbor, _xlpm.a, _xlpm.b, _xlpm.c, _xlpm.d, _xlpm.center, _xlpm.f, _xlpm.g, _xlpm.h, _xlpm.i), _xlpm.select_neighbor))))</definedName>
     <definedName name="NumbersOnlyλ">_xlfn.LAMBDA(_xlpm.array, _xlfn.LET(_xlpm.array, IF(TYPE(_xlpm.array) &lt;&gt; 64, _xlpm.array, _xlfn.TOCOL(_xlpm.array)), _xlpm.ex, Explodeλ(_xlpm.array), _xlpm.Keep, IFERROR((CODE(_xlpm.ex) &gt;= 48) * (CODE(_xlpm.ex) &lt;= 57), FALSE), _xlpm.Result, IF(_xlpm.Keep, _xlpm.ex, ""), _xlpm.final, IFERROR(_xlfn.BYROW(_xlpm.Result, _xleta.CONCAT) + 0, ""), _xlpm.final))</definedName>
     <definedName name="OccurrenceRangeλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.crit_vector,_xlpm.start_occurrence,_xlop.end_occurrence,_xlop.Horizontal?, _xlfn.LET(_xlpm.IsVertical?, NOT(AND(NOT(_xlfn.ISOMITTED(_xlpm.Horizontal?)), _xlpm.Horizontal? = TRUE)), _xlpm.array, IF(_xlpm.IsVertical?, _xlpm.array, TRANSPOSE(_xlpm.array)), _xlpm.crit_vector, IF(_xlpm.IsVertical?, _xlpm.crit_vector, TRANSPOSE(_xlpm.crit_vector)), _xlpm.IncludeEnd?, NOT(_xlfn.ISOMITTED(_xlpm.end_occurrence)), _xlpm.start_occurrence, INDEX(_xlpm.start_occurrence, 1, 1), _xlpm.end_occurrence, IF(_xlpm.IncludeEnd?, INDEX(_xlpm.end_occurrence, 1, 1), FALSE), _xlpm.height, ROWS(_xlpm.array), _xlpm.height_, ROWS(_xlpm.crit_vector), _xlpm.height_mismatch?, _xlpm.height &lt;&gt; _xlpm.height_, _xlpm.InvalidOccurrence?, OR(ISTEXT(_xlpm.start_occurrence), _xlpm.start_occurrence &lt; 1, AND(_xlpm.IncludeEnd?, ISTEXT(_xlpm.end_occurrence)), AND(_xlpm.IncludeEnd?, _xlpm.end_occurrence &lt; _xlpm.start_occurrence)), IF(_xlpm.height_mismatch?, #VALUE!, IF(_xlpm.InvalidOccurrence?, #VALUE!, _xlfn.LET(_xlpm.inst, Instanceλ(_xlpm.crit_vector), _xlpm.bool, IF(_xlpm.IncludeEnd?, (_xlpm.inst &gt;= _xlpm.start_occurrence) * (_xlpm.inst &lt;= _xlpm.end_occurrence), (_xlpm.inst &gt;= _xlpm.start_occurrence)), _xlpm.result, _xlfn._xlws.FILTER(_xlpm.array, _xlpm.bool, 0), _xlpm.final, IF(_xlpm.IsVertical?, _xlpm.result, TRANSPOSE(_xlpm.result)), _xlpm.final)))))</definedName>
     <definedName name="Occurrenceλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.crit_vector,_xlpm.Nᵀᴴ_occurrence, _xlfn.LET(_xlpm.height, ROWS(_xlpm.array), _xlpm.height_, ROWS(_xlpm.crit_vector), _xlpm.height_mismatch?, _xlpm.height &lt;&gt; _xlpm.height_, _xlpm.InvalidOccurrence?, OR(ISTEXT(_xlpm.Nᵀᴴ_occurrence), _xlpm.Nᵀᴴ_occurrence = 0), IF(_xlpm.height_mismatch?, #VALUE!, IF(_xlpm.InvalidOccurrence?, #VALUE!, _xlfn.LET(_xlpm.Descend?, SIGN(_xlpm.Nᵀᴴ_occurrence) = -1, _xlpm.bool, Instanceλ(_xlpm.crit_vector, , _xlpm.Descend?) = ABS(_xlpm.Nᵀᴴ_occurrence), _xlpm.final, _xlfn._xlws.FILTER(_xlpm.array, _xlpm.bool, 0), _xlpm.final)))))</definedName>
@@ -1422,7 +1422,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="976" row="9">
+  <wetp:taskpane dockstate="right" visibility="0" width="875" row="8">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1455,14 +1455,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530863C0-84AB-413A-8878-41E8E2A541E8}">
   <dimension ref="A6:G31"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.9"/>
   <cols>
-    <col min="1" max="3" width="8.6640625" style="1" customWidth="1"/>
+    <col min="1" max="3" width="8.6484375" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="52" style="56" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.6640625" style="1" hidden="1"/>
+    <col min="6" max="6" width="8.6484375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.84765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.6484375" style="1" hidden="1"/>
   </cols>
   <sheetData>
     <row r="6" spans="3:5">
@@ -1637,12 +1637,12 @@
     <tabColor rgb="FFD0F0C0"/>
   </sheetPr>
   <dimension ref="B2:BE56"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="8.6484375" defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
-    <col min="2" max="25" width="4.58203125" style="1" customWidth="1"/>
+    <col min="2" max="25" width="4.59765625" style="1" customWidth="1"/>
     <col min="26" max="46" width="4" style="1" customWidth="1"/>
-    <col min="47" max="16384" width="8.6640625" style="1"/>
+    <col min="47" max="16384" width="8.6484375" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:44">
@@ -5157,23 +5157,23 @@
     <tabColor rgb="FFFED8B1"/>
   </sheetPr>
   <dimension ref="B2:CC45"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="8.6484375" defaultRowHeight="12.3"/>
   <cols>
     <col min="1" max="1" width="5.5" style="20" customWidth="1"/>
     <col min="2" max="32" width="4.5" style="20" customWidth="1"/>
     <col min="33" max="45" width="4.5" style="21" customWidth="1"/>
     <col min="46" max="54" width="4.5" style="20" customWidth="1"/>
     <col min="55" max="65" width="3.5" style="20" customWidth="1"/>
-    <col min="66" max="77" width="3.83203125" style="20" customWidth="1"/>
-    <col min="78" max="16384" width="8.6640625" style="20"/>
+    <col min="66" max="77" width="3.84765625" style="20" customWidth="1"/>
+    <col min="78" max="16384" width="8.6484375" style="20"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:81" ht="15">
+    <row r="2" spans="2:81" ht="14.4">
       <c r="B2" s="23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:81" ht="15">
+    <row r="4" spans="2:81" ht="14.4">
       <c r="R4" s="24"/>
       <c r="S4" s="25"/>
       <c r="T4" s="25"/>
@@ -5216,7 +5216,7 @@
       <c r="BA4" s="25"/>
       <c r="BB4" s="37"/>
     </row>
-    <row r="5" spans="2:81" ht="15">
+    <row r="5" spans="2:81" ht="14.4">
       <c r="B5" s="23" t="s">
         <v>31</v>
       </c>
@@ -5244,7 +5244,7 @@
       <c r="CB5" s="21"/>
       <c r="CC5" s="21"/>
     </row>
-    <row r="6" spans="2:81" ht="14">
+    <row r="6" spans="2:81" ht="13.8">
       <c r="B6" s="71">
         <v>1</v>
       </c>
@@ -5391,7 +5391,7 @@
       <c r="CB6" s="21"/>
       <c r="CC6" s="21"/>
     </row>
-    <row r="7" spans="2:81" ht="14">
+    <row r="7" spans="2:81" ht="13.8">
       <c r="B7" s="71">
         <v>16</v>
       </c>
@@ -5536,7 +5536,7 @@
       <c r="CB7" s="21"/>
       <c r="CC7" s="21"/>
     </row>
-    <row r="8" spans="2:81" ht="14">
+    <row r="8" spans="2:81" ht="13.8">
       <c r="B8" s="71">
         <v>31</v>
       </c>
@@ -5681,7 +5681,7 @@
       <c r="CB8" s="21"/>
       <c r="CC8" s="21"/>
     </row>
-    <row r="9" spans="2:81" ht="14">
+    <row r="9" spans="2:81" ht="13.8">
       <c r="B9" s="71">
         <v>46</v>
       </c>
@@ -5826,7 +5826,7 @@
       <c r="CB9" s="21"/>
       <c r="CC9" s="21"/>
     </row>
-    <row r="10" spans="2:81" ht="14">
+    <row r="10" spans="2:81" ht="13.8">
       <c r="B10" s="71">
         <v>61</v>
       </c>
@@ -5971,7 +5971,7 @@
       <c r="CB10" s="21"/>
       <c r="CC10" s="21"/>
     </row>
-    <row r="11" spans="2:81" ht="14">
+    <row r="11" spans="2:81" ht="13.8">
       <c r="B11" s="71">
         <v>76</v>
       </c>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="BB11" s="40"/>
     </row>
-    <row r="12" spans="2:81" ht="14">
+    <row r="12" spans="2:81" ht="13.8">
       <c r="B12" s="71">
         <v>91</v>
       </c>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="BB12" s="40"/>
     </row>
-    <row r="13" spans="2:81" ht="14">
+    <row r="13" spans="2:81" ht="13.8">
       <c r="B13" s="71">
         <v>106</v>
       </c>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BB13" s="40"/>
     </row>
-    <row r="14" spans="2:81" ht="14">
+    <row r="14" spans="2:81" ht="13.8">
       <c r="B14" s="71">
         <v>121</v>
       </c>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="BB14" s="40"/>
     </row>
-    <row r="15" spans="2:81" ht="14">
+    <row r="15" spans="2:81" ht="13.8">
       <c r="B15" s="71">
         <v>136</v>
       </c>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="BB15" s="40"/>
     </row>
-    <row r="16" spans="2:81" ht="14">
+    <row r="16" spans="2:81" ht="13.8">
       <c r="B16" s="71">
         <v>151</v>
       </c>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="BB16" s="40"/>
     </row>
-    <row r="17" spans="2:54" ht="14">
+    <row r="17" spans="2:54" ht="13.8">
       <c r="B17" s="71">
         <v>166</v>
       </c>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="BB17" s="40"/>
     </row>
-    <row r="18" spans="2:54" ht="14">
+    <row r="18" spans="2:54" ht="13.8">
       <c r="B18" s="71">
         <v>181</v>
       </c>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="BB18" s="40"/>
     </row>
-    <row r="19" spans="2:54" ht="14">
+    <row r="19" spans="2:54" ht="13.8">
       <c r="B19" s="71">
         <v>196</v>
       </c>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="BB19" s="40"/>
     </row>
-    <row r="20" spans="2:54" ht="14">
+    <row r="20" spans="2:54" ht="13.8">
       <c r="B20" s="71">
         <v>211</v>
       </c>
@@ -7420,7 +7420,7 @@
       <c r="BA21" s="33"/>
       <c r="BB21" s="43"/>
     </row>
-    <row r="22" spans="2:54" ht="15">
+    <row r="22" spans="2:54" ht="14.4">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="26" t="s">
@@ -7480,7 +7480,7 @@
       <c r="BA22" s="25"/>
       <c r="BB22" s="37"/>
     </row>
-    <row r="23" spans="2:54" ht="15">
+    <row r="23" spans="2:54" ht="14.4">
       <c r="B23" s="29" t="s">
         <v>36</v>
       </c>
@@ -7505,7 +7505,7 @@
       <c r="AS23" s="20"/>
       <c r="BB23" s="40"/>
     </row>
-    <row r="24" spans="2:54" ht="14">
+    <row r="24" spans="2:54" ht="13.8">
       <c r="B24" s="73" t="str" cm="1">
         <f t="array" ref="B24:N34">Plusλ(GeoGrid,158,6,"")</f>
         <v/>
@@ -7608,7 +7608,7 @@
       <c r="AS24" s="20"/>
       <c r="BB24" s="40"/>
     </row>
-    <row r="25" spans="2:54" ht="14">
+    <row r="25" spans="2:54" ht="13.8">
       <c r="B25" s="73" t="str">
         <v/>
       </c>
@@ -7708,7 +7708,7 @@
       <c r="AS25" s="20"/>
       <c r="BB25" s="40"/>
     </row>
-    <row r="26" spans="2:54" ht="14">
+    <row r="26" spans="2:54" ht="13.8">
       <c r="B26" s="73" t="str">
         <v/>
       </c>
@@ -7808,7 +7808,7 @@
       <c r="AS26" s="20"/>
       <c r="BB26" s="40"/>
     </row>
-    <row r="27" spans="2:54" ht="14">
+    <row r="27" spans="2:54" ht="13.8">
       <c r="B27" s="73" t="str">
         <v/>
       </c>
@@ -7908,7 +7908,7 @@
       <c r="AS27" s="20"/>
       <c r="BB27" s="40"/>
     </row>
-    <row r="28" spans="2:54" ht="14">
+    <row r="28" spans="2:54" ht="13.8">
       <c r="B28" s="73" t="str">
         <v/>
       </c>
@@ -8008,7 +8008,7 @@
       <c r="AS28" s="20"/>
       <c r="BB28" s="40"/>
     </row>
-    <row r="29" spans="2:54" ht="14">
+    <row r="29" spans="2:54" ht="13.8">
       <c r="B29" s="73" t="str">
         <v/>
       </c>
@@ -8087,7 +8087,7 @@
       <c r="BA29" s="33"/>
       <c r="BB29" s="43"/>
     </row>
-    <row r="30" spans="2:54" ht="15">
+    <row r="30" spans="2:54" ht="14.7">
       <c r="B30" s="73">
         <v>152</v>
       </c>
@@ -8172,7 +8172,7 @@
       <c r="BA30" s="25"/>
       <c r="BB30" s="37"/>
     </row>
-    <row r="31" spans="2:54" ht="15">
+    <row r="31" spans="2:54" ht="14.7">
       <c r="B31" s="73" t="str">
         <v/>
       </c>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="BB31" s="40"/>
     </row>
-    <row r="32" spans="2:54" ht="14">
+    <row r="32" spans="2:54" ht="13.8">
       <c r="B32" s="73" t="str">
         <v/>
       </c>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="BB32" s="40"/>
     </row>
-    <row r="33" spans="2:54" ht="14">
+    <row r="33" spans="2:54" ht="13.8">
       <c r="B33" s="73" t="str">
         <v/>
       </c>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BB33" s="40"/>
     </row>
-    <row r="34" spans="2:54" ht="14">
+    <row r="34" spans="2:54" ht="13.8">
       <c r="B34" s="73" t="str">
         <v/>
       </c>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="BB34" s="40"/>
     </row>
-    <row r="35" spans="2:54" ht="14">
+    <row r="35" spans="2:54" ht="13.8">
       <c r="B35" s="32"/>
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="BB35" s="40"/>
     </row>
-    <row r="36" spans="2:54" ht="14">
+    <row r="36" spans="2:54" ht="13.8">
       <c r="R36" s="78" t="str">
         <v/>
       </c>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="BB36" s="40"/>
     </row>
-    <row r="37" spans="2:54" ht="14">
+    <row r="37" spans="2:54" ht="13.8">
       <c r="R37" s="78" t="str">
         <v/>
       </c>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="BB37" s="40"/>
     </row>
-    <row r="38" spans="2:54" ht="14">
+    <row r="38" spans="2:54" ht="13.8">
       <c r="R38" s="78">
         <v>92</v>
       </c>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="BB38" s="40"/>
     </row>
-    <row r="39" spans="2:54" ht="14">
+    <row r="39" spans="2:54" ht="13.8">
       <c r="R39" s="78" t="str">
         <v/>
       </c>
@@ -9176,7 +9176,7 @@
       <c r="AT39" s="31"/>
       <c r="BB39" s="40"/>
     </row>
-    <row r="40" spans="2:54" ht="14">
+    <row r="40" spans="2:54" ht="13.8">
       <c r="R40" s="78" t="str">
         <v/>
       </c>
@@ -9260,7 +9260,7 @@
       <c r="AT40" s="31"/>
       <c r="BB40" s="40"/>
     </row>
-    <row r="41" spans="2:54" ht="14">
+    <row r="41" spans="2:54" ht="13.8">
       <c r="R41" s="78" t="str">
         <v/>
       </c>
@@ -9344,7 +9344,7 @@
       <c r="AT41" s="31"/>
       <c r="BB41" s="40"/>
     </row>
-    <row r="42" spans="2:54" ht="14">
+    <row r="42" spans="2:54" ht="13.8">
       <c r="R42" s="78" t="str">
         <v/>
       </c>
@@ -9428,7 +9428,7 @@
       <c r="AT42" s="31"/>
       <c r="BB42" s="40"/>
     </row>
-    <row r="43" spans="2:54" ht="14">
+    <row r="43" spans="2:54" ht="13.8">
       <c r="R43" s="78" t="str">
         <v/>
       </c>
@@ -9512,7 +9512,7 @@
       <c r="AT43" s="31"/>
       <c r="BB43" s="40"/>
     </row>
-    <row r="44" spans="2:54" ht="14">
+    <row r="44" spans="2:54" ht="13.8">
       <c r="R44" s="78" t="str">
         <v/>
       </c>
@@ -9647,26 +9647,26 @@
     <tabColor theme="3" tint="0.89999084444715716"/>
   </sheetPr>
   <dimension ref="B2:AI42"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="8.6484375" defaultRowHeight="12.3"/>
   <cols>
     <col min="1" max="1" width="5" style="20" customWidth="1"/>
     <col min="2" max="2" width="3.5" style="20" customWidth="1"/>
     <col min="3" max="12" width="3.5" style="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.6640625" style="20" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" style="20"/>
+    <col min="13" max="13" width="4.6484375" style="20" customWidth="1"/>
+    <col min="14" max="14" width="8.6484375" style="20"/>
     <col min="15" max="15" width="4.25" style="20" customWidth="1"/>
     <col min="16" max="29" width="3.5" style="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.9140625" style="20" customWidth="1"/>
+    <col min="30" max="30" width="3.8984375" style="20" customWidth="1"/>
     <col min="31" max="45" width="3.5" style="20" bestFit="1" customWidth="1"/>
-    <col min="46" max="16384" width="8.6640625" style="20"/>
+    <col min="46" max="16384" width="8.6484375" style="20"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:35" ht="15">
+    <row r="2" spans="2:35" ht="14.4">
       <c r="B2" s="107" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="2:35" ht="15">
+    <row r="4" spans="2:35" ht="14.4">
       <c r="O4" s="63"/>
       <c r="P4" s="64"/>
       <c r="Q4" s="26" t="s">
@@ -9691,7 +9691,7 @@
       <c r="AH4" s="25"/>
       <c r="AI4" s="37"/>
     </row>
-    <row r="5" spans="2:35" ht="15">
+    <row r="5" spans="2:35" ht="14.4">
       <c r="B5" s="23" t="s">
         <v>75</v>
       </c>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="AI5" s="40"/>
     </row>
-    <row r="6" spans="2:35" ht="14">
+    <row r="6" spans="2:35" ht="13.8">
       <c r="B6" s="87">
         <v>1</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:35" ht="14">
+    <row r="7" spans="2:35" ht="13.8">
       <c r="B7" s="87">
         <v>16</v>
       </c>
@@ -9905,7 +9905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="2:35" ht="14">
+    <row r="8" spans="2:35" ht="13.8">
       <c r="B8" s="87">
         <v>31</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:35" ht="14">
+    <row r="9" spans="2:35" ht="13.8">
       <c r="B9" s="87">
         <v>46</v>
       </c>
@@ -10095,7 +10095,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="2:35" ht="14">
+    <row r="10" spans="2:35" ht="13.8">
       <c r="B10" s="87">
         <v>61</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="2:35" ht="14">
+    <row r="11" spans="2:35" ht="13.8">
       <c r="B11" s="87">
         <v>76</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="2:35" ht="14">
+    <row r="12" spans="2:35" ht="13.8">
       <c r="B12" s="87">
         <v>91</v>
       </c>
@@ -10380,7 +10380,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="2:35" ht="14">
+    <row r="13" spans="2:35" ht="13.8">
       <c r="B13" s="87">
         <v>106</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="2:35" ht="14">
+    <row r="14" spans="2:35" ht="13.8">
       <c r="B14" s="87">
         <v>121</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="2:35" ht="14">
+    <row r="15" spans="2:35" ht="13.8">
       <c r="B15" s="87">
         <v>136</v>
       </c>
@@ -10665,7 +10665,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="2:35" ht="14">
+    <row r="16" spans="2:35" ht="13.8">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -10700,7 +10700,7 @@
       <c r="AH16" s="21"/>
       <c r="AI16" s="30"/>
     </row>
-    <row r="17" spans="2:35" ht="15">
+    <row r="17" spans="2:35" ht="14.4">
       <c r="B17" s="66" t="s">
         <v>63</v>
       </c>
@@ -10741,7 +10741,7 @@
       <c r="AH17" s="21"/>
       <c r="AI17" s="30"/>
     </row>
-    <row r="18" spans="2:35" ht="15">
+    <row r="18" spans="2:35" ht="14.4">
       <c r="B18" s="44" t="s">
         <v>65</v>
       </c>
@@ -11561,7 +11561,7 @@
       <c r="AH28" s="33"/>
       <c r="AI28" s="43"/>
     </row>
-    <row r="29" spans="2:35" ht="15">
+    <row r="29" spans="2:35" ht="14.4">
       <c r="B29" s="44" t="s">
         <v>64</v>
       </c>
@@ -11588,7 +11588,7 @@
       <c r="AH29" s="25"/>
       <c r="AI29" s="37"/>
     </row>
-    <row r="30" spans="2:35" ht="15">
+    <row r="30" spans="2:35" ht="14.4">
       <c r="B30" s="93" t="str" cm="1">
         <f t="array" ref="B30:J38">Plusλ(SeqGrid,{3,3},6,"")</f>
         <v/>
@@ -12522,7 +12522,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuACAAIABfAF8AXwBfACAAIAAgACAAXwAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8AXwBfAF8AIAAgACAAIAAgACAAIAAgACAAIAAgAF8AIAAgACAAXwAgACAAIABfACAAXABuACAAfAAgACAAXwAgAFwAXAAgACAAKABfACkAIAAgACAAIAAgACAAIAAgACAAIAAvACAAXwBfAF8AXwB8ACAAIAAgACAAIAAgACAAIAAgACgAXwApACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAIABfACAAIAAgACAAXwBfACAAXwAgACAAfAAgACgAXwBfAF8AIAAgACAAIABfACAAXwBfACAAIAAgACAAXwAgACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAIABfACAAPAAgACAAfAAgAHwAIAAgAC8AIABfAGAAIAB8ACAAIABcAFwAXwBfAF8AIABcAFwAIAAgAHwAIAAnAF8AIABcAFwAIAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAfAAgAHwAIAB8ACAAKABfAHwAIAB8ACAAIABfAF8AXwBfACkAIAB8ACAAfAAgAHwAXwApACAAfAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8AF8AXwBfAF8ALwAgACAAfABfAHwAIAAgAFwAXABfAF8ALAAgAHwAIAB8AF8AXwBfAF8AXwAvACAAIAB8ACAALgBfAF8ALwAgACAAfABfAHwAIAB8AF8AfAAgAHwAXwB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8ALwAgAHwAIAAgACAAIAAgACAAIAAgACAAIAB8ACAAfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABfAF8AXwAvACAAIAAgACAAIAAgACAAIAAgACAAIAB8AF8AfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgBcAG4AdgAgADEALgAyAC4AMABcAG4AXABuAE0AbwBkAHUAbABlADoAIAAgAEIAaQBnAFMAcABpAGwAbABcAG4AUgBlAHAAbwA6ACAAIAAgACAAaAB0AHQAcABzADoALwAvAGcAaQB0AGgAdQBiAC4AYwBvAG0ALwBQAGEAdAByAGkAYwBrADIANwA4ADgALwBCAGkAZwBTAHAAaQBsAGwALQBFAHgAYwBlAGwALQBMAGEAbQBiAGQAYQAtAEwAaQBiAHIAYQByAHkAXABuAEwAaQBjAGUAbgBzAGUAOgAgAE0ASQBUACAAKABzAGUAZQAgAEwASQBDAEUATgBTAEUAIABmAGkAbABlACkAXABuAEEAdQB0AGgAbwByADoAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAEQAYQB0AGUAOgAgACAAIAAgADkALwAxADcALwAyADAAMgA2AFwAbgBcAG4AVgBlAHIAcwBpAG8AbgAgAGgAaQBzAHQAbwByAHkAOgBcAG4AIAAgACAAIAA3AC8ANgAvADIAMAAyADYAIAATICAAIABJAG4AaQB0AGkAYQBsACAAcgBlAGwAZQBhAHMAZQBcAG4AXABuACAAIAAgACAAOQAvADMALwAyADAAMgA2ACAAEyAgACAAQQBkAGQAZQBkACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AyAAYQBuAGQAIABRAHUAYQBkAHcAaQBzAGUAuwMgAHQAbwAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAHAAZABhAHQAZQBkACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAYwBhAHQAZQBnAG8AcgB5ACAAYgBsAG8AYwBrAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUAcABkAGEAdABlAGQAIABUAGUAcwBzAGUAbABsAGEAdABlALsDIAB0AG8AIABhAGMAYwBlAHAAdAAgADEARAAgAGEAcgByAGEAeQBzAFwAbgBcAG4AIAAgACAAIAA5AC8AMQA3AC8AMgAwADIANgAgABMgIABBAGQAZABlAGQAIABJAG4AcwB0AGEAbgBjAGUAuwMsACAAVwBhAHYAZQC7AywAIABHAHIAbwB1AHAASQBuAGQAZQB4ALsDLAAgAE8AYwBjAHUAcgByAGUAbgBjAGUAuwMsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAbgBkACAATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwMgAHQAbwAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAGkAeABlAGQAIAB2AHUAbABuAGUAcgBhAGIAaQBsAGkAdAB5ACAAaQBuACAAQwBvAG4AdgBvAGwAdgBlALsDIAB3AGkAdABoACAAMQBEACAAawBlAHIAbgBlAGwAcwBcAG4AXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAXABuACAAIAAgACAATgBvAG4AZQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwByAGUAIABtAG8AZAB1AGwAZQAgAGEAZwBnAHIAZQBnAGEAdABvAHIAIABmAG8AcgAgAGEAbABsACAAQgBpAGcAUwBwAGkAbABsACAAZgB1AG4AYwB0AGkAbwBuAHMALgBcAG4AXABuAFAAdQByAHAAbwBzAGUAOgBcAG4AIAAgACAAIABQAHIAbwB2AGkAZABlAHMAIABhACAAcwBpAG4AZwBsAGUAIABpAG0AcABvAHIAdAAgAHAAbwBpAG4AdAAgAGYAbwByACAAdABoAGUAIABlAG4AdABpAHIAZQAgAGwAaQBiAHIAYQByAHkALgBcAG4AXABuAEMAbwBuAHQAZQBuAHQAcwA6AFwAbgAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawAsACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQAsACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAsACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEALABcAG4AIAAgACAAIABSAGUAcABlAHQAaQB0AGkAbwBuACwAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMALAAgAFQAZQB4AHQALAAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwAsAFwAbgAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMALAAgAEQAaQBhAGcAbgBvAHMAdABpAGMAcwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4ALQAtAC0AVABhAGIAbABlACAAbwBmACAAQwBvAG4AdABlAG4AdABzAC0ALQAtAFwAbgBcAG4AIwAjACAAMAAxACAALQAgAFsARwBXAF0AIABHAHIAaQBkAHcAbwByAGsAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAVwAwADEAXQAgACAARABHAHIAaQBkALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBXADAAMgBdACAAIABDAEcAcgBpAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFcAMAAzAF0AIAAgAE0ARwByAGkAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAVwAwADQAXQAgACAAVABHAHIAaQBkALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBXADAANQBdACAAIABQAG8AbABhAHIARwByAGkAZAC7A1wAbgBcAG4AIwAjACAAMAAyACAALQAgAFsARwBHAF0AIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARwAwADEAXQAgACAAQwBpAHIAYwBsAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAAyAF0AIAAgAEQAaQBhAG0AbwBuAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAAzAF0AIAAgAFAAbAB1AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA0AF0AIAAgAFAAeQByAGEAbQBpAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA1AF0AIAAgAFIAaQBuAGcAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA2AF0AIAAgAFMAcQB1AGEAcgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBHADAANwBdACAAIABUAHIAaQBhAG4AZwBsAGUAuwNcAG4AXABuACMAIwAgADAAMwAgAC0AIABbAFMAQQBdACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAHIAZQAgAFMAaABhAHAAaQBuAGcAIABQAHIAaQBtAGkAdABpAHYAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADEAXQBcAHQAUgBlAFMAaABhAHAAZQAyAEQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMAAyAF0AXAB0AFIAZQBTAGkAegBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAAMwBdAFwAdABTAGMAYQBuADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADQAXQBcAHQAVAByAGEAdgBlAHIAcwBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAANQBdAFwAdABUAGEAawBlAEIAbABvAGMAawC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADYAXQBcAHQARABTAHQAYQBjAGsAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBmAGwAbwB3AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADcAXQBcAHQAVwByAGEAcABSAG8AdwBzADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADgAXQBcAHQAVwByAGEAcABDAG8AbABzADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADkAXQBcAHQAUwB0AGEAaQByAGMAYQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQAwAF0AXAB0AFUAbgBQAGkAdgBvAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQAxAF0AXAB0AFoAaQBwALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADEAMwBdAFwAdABTAGwAaQBjAGUAQgB5AEQAZQBnALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAxADQAXQBcAHQAUABhAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA1AF0AXAB0AEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADEANgBdAFwAdABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA3AF0AXAB0AE0AYQBnAG4AaQBmAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA4AF0AXAB0AFoAbwBvAG0AuwNcAG4AXABuACMAIwAgADAANAAgAC0AIABbAEcAQQBdACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAZQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADEAXQBcAHQARABlAGwAZQB0AGUAUgBvAHcAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADIAXQBcAHQARABlAGwAZQB0AGUAQwBvAGwAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADMAXQBcAHQARABlAGwAZQB0AGUAVwBoAGUAcgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAANABdAFwAdABQAGkAbgBjAGgAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMAA1AF0AXAB0AFIAZQBtAG8AdgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAANgBdAFwAdABTAHEAdQBlAGUAegBlALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAHgAcABhAG4AcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMAA3AF0AXAB0AEsAcgBvAG4AZQBjAGsAZQByAFAAcgBvAGQAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAaQBsAHQAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADgAXQBcAHQARQB4AGMAbAB1AGQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADkAXQBcAHQAUwBuAGEAcAC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBvAGwAbABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAwAF0AXAB0AFMAaABpAGYAdAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADEAXQBcAHQAUwBoAGkAZgB0AFIAbwB3AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAyAF0AXAB0AFMAaABpAGYAdABDAG8AbABzALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAzAF0AXAB0AEUAbQBiAGUAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADQAXQBcAHQASwBlAGUAcABSAG8AdwBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEANQBdAFwAdABLAGUAZQBwAEMAbwBsAHMAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADYAXQBcAHQAQgBsAG8AYwBrAE0AYQBwALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEANwBdAFwAdABDAG8AbgB2AG8AbAB2AGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQA4AF0AXAB0AEYAbwBsAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQA5AF0AXAB0AEoAbwBpAG4AMgBEALsDXABuAFwAbgAjACMAIAAwADUAIAAtACAAWwBSAFAAXQAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAxAF0AXAB0AEUAYwBoAG8AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAyAF0AXAB0AFIAZQBwAGUAYQB0AFIAbwB3AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAzAF0AXAB0AFIAZQBwAGUAYQB0AEMAbwBsAHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAA0AF0AXAB0AFQAZQBzAHMAZQBsAGwAYQB0AGUAuwNcAG4AXABuACMAIwAgADAANgAgAC0AIABbAEcAUgBdACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAZQBxAHUAZQBuAGMAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADAAMQBdAFwAdABTAHQAcgBlAGEAawC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADIAXQBcAHQAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXAB0AFwAdABcAHQAWwBHAFIAMQA2AF0AIAAgAEkAbgBzAHQAYQBuAGMAZQC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADcAXQBcAHQAVwBhAHYAZQC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADMAXQBcAHQAQgB5AEQAaQBhAGcAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA0AF0AXAB0AEQAaQBhAGcATQBhAHAAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA1AF0AXAB0AEQAaQBhAGcASQBuAGQAZQB4ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADAANgBdAFwAdABQAGEAaQByAHcAaQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA2AGEAXQBcAHQAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBcAHQAIAAgACAAIAAgACAAIAAgAFsARwBSADAANgBiAF0AIABRAHUAYQBkAHcAaQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA3AF0AXAB0AEcAcgBvAHUAcABiAHkAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA4AF0AXAB0AEcAcgBvAHUAcABiAHkARABhAHQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADkAXQBcAHQAUABpAHYAbwB0AGIAeQBDAGEAdAC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADgAXQBcAHQARwByAG8AdQBwAEkAbgBkAGUAeAC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADkAXQBcAHQATwBjAGMAdQByAHIAZQBuAGMAZQC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAyADAAXQBcAHQATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADEAMABdAFwAdABHAHIAYQBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQAxAF0AXAB0AE0AbwBvAHIAZQBBAGcAZwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADIAXQBcAHQATQBvAG8AcgBlAFMAZQBsAGUAYwB0ALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAYQB0AGkAcwB0AGkAYwBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADMAXQBcAHQASABpAHMAdABvAGcAcgBhAG0AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQA0AF0AXAB0AE0AbwBkAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQA1AF0AXAB0AFoAbwBuAGUAUwB0AGEAdAC7A1wAbgBcAG4AIwAjACAAMAA3ACAALQAgAFsAVABYAF0AIAAgAFQAZQB4AHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAAMQBdAFwAdABBAGwAaQBnAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAAyAF0AXAB0AEEAbABpAGcAbgBEAGkAcwB0AGkAbgBjAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAAzAF0AXAB0AEEAbABpAGcAbgBVAG4AaQBxAHUAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADQAXQBcAHQAQwBvAGEAbABlAHMAYwBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAANQBdAFwAdABFAHgAcABsAG8AZABlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAANgBdAFwAdABOAHUAbQBiAGUAcgBzAE8AbgBsAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAA3AF0AXAB0AFQAZQB4AHQATwBuAGwAeQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADgAXQBcAHQAUwBwAGwAaQB0ALsDXABuAFwAbgAjACMAIAAwADgAIAAtACAAWwBFAE4AXQAgACAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEUATgAwADEAXQBcAHQAQgBpAG4AMgBEAGUAYwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEUATgAwADIAXQBcAHQAQgBpAG4AMgBHAHIAYQB5ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARQBOADAAMwBdAFwAdABCAGkAdABDAG8AdQBuAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBFAE4AMAA0AF0AXAB0AEQAZQBjADIAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBFAE4AMAA1AF0AXAB0AEQAZQBjADIARwByAGEAeQC7A1wAbgBcAG4AIwAjACAAMAA5ACAALQAgAFsAQwBCAF0AIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAAMQBdAFwAdABQAGUAcgBtAFIAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAAyAF0AXAB0AFAAZQByAG0AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAAzAF0AXAB0AEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAA0AF0AXAB0AEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAANQBdAFwAdABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADYAXQBcAHQASwBuAGEAcABTAGEAYwBrALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAANwBdAFwAdABTAHUAYgBzAGUAdABHAGUAbgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADgAXQBcAHQAUwB1AGIAcwBlAHQAUwB1AG0AuwNcAG4AXABuACMAIwAgADEAMAAgAC0AIABbAEcARABdACAAIABHAHIAaQBkACAARABpAGEAZwBuAG8AcwB0AGkAYwBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARAAwADEAXQAgACAAUgBlAHYAZQBhAGwAuwNcAG4AXABuAFwAbgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAEcAVwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAwADEAIAAtACAARwByAGkAZAB3AG8AcgBrAFwAbgAvAC8AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFwAbgAvACoAXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawAgAGQAZQBmAGkAbgBlAHMAIAB0AGgAZQAgAGYAbwB1AG4AZABhAHQAaQBvAG4AYQBsACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAHMAeQBzAHQAZQBtAHMAIABmAG8AcgAgADIARAAgAGEAcgByAGEAeQBzAC4AIABFAGEAYwBoAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgAHAAcgBvAGQAdQBjAGUAcwAgAGEAIABjAGUAbgB0AGUAcgBlAGQALAAgAHMAeQBtAG0AZQB0AHIAaQBjAGEAbAAgAGcAZQBvAG0AZQB0AHIAaQBjACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAbwBmACAAdABoAGUAIABnAHIAaQBkAC4AXABuAFwAbgBGAHUAbgBjAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABEAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAARABpAHIAZQBjAHQAaQBvAG4AIABnAHIAaQBkACAAKAAwALAALQAzADYAMACwACkAIAB1AHMAaQBuAGcAIABjAGUAbgB0AGUAcgBlAGQAIABDAGEAcgB0AGUAcwBpAGEAbgAgAGEAeABlAHMAXABuAFwAbgAgACAAIAAgACIgIABDAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAAQwBhAHIAdABlAHMAaQBhAG4AIABnAHIAaQBkACAAKAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACwAIABjAGUAbgB0AGUAcgBlAGQAKQBcAG4AXABuACAAIAAgACAAIiAgAE0ARwByAGkAZAC7AyAAIAAgACAAIAAgAC0AIABNAGUAcwBoACAAZwByAGkAZAAgACgAMQARIGIAYQBzAGUAZAAgAHIAbwB3ACAAbwByACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACkAXABuAFwAbgAgACAAIAAgACIgIABUAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAAVABoAHIAZQBzAGgAbwBsAGQAZQBkACAAbQBlAHMAaAAgAGcAcgBpAGQAIAAoAGkAbgBkAGkAYwBlAHMAIAB3AHIAYQBwACAAYQBmAHQAZQByACAAYQAgAGwAaQBtAGkAdAApAFwAbgBcAG4AIAAgACAAIAAiICAAUABvAGwAYQByAEcAcgBpAGQAuwMgACAALQAgAFAAbwBsAGEAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAIAAgACAAEyAgAHIAYQBkAGkAYQBsACAAZABpAHMAdABhAG4AYwBlACAAZgByAG8AbQAgAGcAcgBpAGQAIABjAGUAbgB0AGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGgAaQAgABMgIABhAG4AZwBsAGUAIABpAG4AIAByAGEAZABpAGEAbgBzACAAdQBzAGkAbgBnACAAQQBUAEEATgAyACgAeQAsACAAeAApAFwAbgBcAG4AIAAgACAAIAAiICAAUgBlAHMAaQB6AGUAuwMgACAAIAAgACAALQAgAFUAdABpAGwAaQB0AHkAIABmAG8AcgAgAGIAcgBvAGEAZABjAGEAcwB0AGkAbgBnACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAHYAZQBjAHQAbwByAHMAIAB0AG8AIABnAHIAaQBkACAAcwBoAGEAcABlAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAQQBsAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGEAcgBlACAAcwBoAGEAcABlAC0AZAByAGkAdgBlAG4AOgAgAHQAaABlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAcwB1AHAAcABsAGkAZQBkACAAZwByAGkAZAAgAGQAZQB0AGUAcgBtAGkAbgBlAFwAbgAgACAAIAAgAHQAaABlACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGUAeAB0AGUAbgB0AHMALgBcAG4AXABuAEUAeABhAG0AcABsAGUAcwA6AFwAbgAgACAAIAAgAEcAcgBpAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAgACAAMgAgACAAIAAzACAAIAAgADQAIAAgACAANQBcAG4AIAAgACAAIAAgACAAIAAgADYAIAAgACAANwAgACAAIAA4ACAAIAAgADkAIAAgACAAMQAwAFwAbgAgACAAIAAgACAAIAAgACAAMQAxACAAIAAxADIAIAAgADEAMwAgACAAMQA0ACAAIAAxADUAXABuACAAIAAgACAAIAAgACAAIAAxADYAIAAgADEANwAgACAAMQA4ACAAIAAxADkAIAAgADIAMABcAG4AIAAgACAAIAAgACAAIAAgADIAMQAgACAAMgAyACAAIAAyADMAIAAgADIANAAgACAAMgA1AFwAbgBcAG4AIAAgACAAIABEAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQA6AFwAbgAgACAAIAAgACAAIAAgACAAMgAyADUALgAwADAAIAAyADAANgAuADUANwAgADEAOAAwAC4AMAAwACAAMQA1ADMALgA0ADMAIAAxADMANQAuADAAMABcAG4AIAAgACAAIAAgACAAIAAgADIANAAzAC4ANAAzACAAMgAyADUALgAwADAAIAAxADgAMAAuADAAMAAgADEAMwA1AC4AMAAwACAAMQAxADYALgA1ADcAXABuACAAIAAgACAAIAAgACAAIAAyADcAMAAuADAAMAAgADIANwAwAC4AMAAwACAAIAAgADAALgAwADAAIAAgADkAMAAuADAAMAAgACAAOQAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAAgACAAMgA5ADYALgA1ADcAIAAzADEANQAuADAAMAAgACAAIAAwAC4AMAAwACAAIAA0ADUALgAwADAAIAAgADYAMwAuADQAMwBcAG4AIAAgACAAIAAgACAAIAAgADMAMQA1AC4AMAAwACAAMwAzADMALgA0ADMAIAAgACAAMAAuADAAMAAgACAAMgA2AC4ANQA3ACAAIAA0ADUALgAwADAAXABuAFwAbgAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACAALQAgAHIAbwB3ACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAtADIAIAAtADIAIAAtADIAIAAtADIAIAAtADIAXABuACAAIAAgACAAIAAgACAAIAAtADEAIAAtADEAIAAtADEAIAAtADEAIAAtADEAXABuACAAIAAgACAAIAAgACAAIAAgADAAIAAgADAAIAAgADAAIAAgADAAIAAgADAAXABuACAAIAAgACAAIAAgACAAIAAgADEAIAAgADEAIAAgADEAIAAgADEAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAAgADIAIAAgADIAIAAgADIAIAAgADIAIAAgADIAXABuAFwAbgAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgBcAG4AIAAgACAAIABNAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAgAC0AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAxACAAMQAgADEAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAMgAgADIAIAAyACAAMgAgADIAXABuACAAIAAgACAAIAAgACAAIAAzACAAMwAgADMAIAAzACAAMwBcAG4AIAAgACAAIAAgACAAIAAgADQAIAA0ACAANAAgADQAIAA0AFwAbgAgACAAIAAgACAAIAAgACAANQAgADUAIAA1ACAANQAgADUAXABuAFwAbgAgACAAIAAgAE0ARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADQAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAANAAgADUAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAA0ACAANQBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADQAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAANAAgADUAXABuAFwAbgAgACAAIAAgAFQARwByAGkAZAC7AygAZwByAGkAZAAsADMAKQAgAC0AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALAAgAHQAaAByAGUAcwBoAG8AbABkACAAMwA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADEAIAAxACAAMQAgADEAXABuACAAIAAgACAAIAAgACAAIAAyACAAMgAgADIAIAAyACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADMAIAAzACAAMwAgADMAIAAzAFwAbgAgACAAIAAgACAAIAAgACAAMQAgADEAIAAxACAAMQAgADEAXABuACAAIAAgACAAIAAgACAAIAAyACAAMgAgADIAIAAyACAAMgBcAG4AXABuACAAIAAgACAAVABHAHIAaQBkALsDKABnAHIAaQBkACwAMwAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMALAAgAHQAaAByAGUAcwBoAG8AbABkACAAMwA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAAMQAgADIAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAAxACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADEAIAAyAFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAAMQAgADIAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAAxACAAMgBcAG4AXABuACAAIAAgACAAUABvAGwAYQByAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAgAC0AIAByADoAXABuACAAIAAgACAAIAAgACAAIAAyAC4AOAAzACAAMgAuADIANAAgADIALgAwADAAIAAyAC4AMgA0ACAAMgAuADgAMwBcAG4AIAAgACAAIAAgACAAIAAgADIALgAyADQAIAAxAC4ANAAxACAAMQAuADAAMAAgADEALgA0ADEAIAAyAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAMgAuADAAMAAgADEALgAwADAAIAAwAC4AMAAwACAAMQAuADAAMAAgADIALgAwADAAXABuACAAIAAgACAAIAAgACAAIAAyAC4AMgA0ACAAMQAuADQAMQAgADEALgAwADAAIAAxAC4ANAAxACAAMgAuADIANABcAG4AIAAgACAAIAAgACAAIAAgADIALgA4ADMAIAAyAC4AMgA0ACAAMgAuADAAMAAgADIALgAyADQAIAAyAC4AOAAzAFwAbgBcAG4AIAAgACAAIABQAG8AbABhAHIARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABwAGgAaQA6AFwAbgAgACAAIAAgACAAIAAgACAALQAyAC4AMwA2ACAALQAyAC4AMAAzACAALQAxAC4ANQA3ACAALQAxAC4AMQAxACAALQAwAC4ANwA5AFwAbgAgACAAIAAgACAAIAAgACAALQAyAC4ANgA4ACAALQAyAC4AMwA2ACAALQAxAC4ANQA3ACAALQAwAC4ANwA5ACAALQAwAC4ANAA2AFwAbgAgACAAIAAgACAAIAAgACAAIAAzAC4AMQA0ACAAIAAzAC4AMQA0ACAAIAAwAC4AMAAwACAAIAAwAC4AMAAwACAAIAAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAAgACAAIAAyAC4ANgA4ACAAIAAyAC4AMwA2ACAAIAAxAC4ANQA3ACAAIAAwAC4ANwA5ACAAIAAwAC4ANAA2AFwAbgAgACAAIAAgACAAIAAgACAAIAAyAC4AMwA2ACAAIAAyAC4AMAAzACAAIAAxAC4ANQA3ACAAIAAxAC4AMQAxACAAIAAwAC4ANwA5AFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADEAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEQARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQwBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABjAG8AdQBuAHQAZQByABEgYwBsAG8AYwBrAHcAaQBzAGUAIABkAGkAcgBlAGMAdABpAG8AbgAgAGcAcgBpAGQAIABpAG4AIABkAGUAZwByAGUAZQBzACAAKAAwALAAEyAzADYAMACwACkAIAB1AHMAaQBuAGcAXABuACAAIAAgACAAYwBlAG4AdABlAHIAZQBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIABmAHIAbwBtACAAQwBHAHIAaQBkALsDLgBcAG4AXABuACAAIAAgACAAQQBuAGcAbABlACAAYwBvAG4AdgBlAG4AdABpAG8AbgA6AFwAbgAgACAAIAAgACAAIAAgACAAMACwACAAIAAgAD0AIAArAFgAIABkAGkAcgBlAGMAdABpAG8AbgAgACgAcgBpAGcAaAB0ACkAXABuACAAIAAgACAAIAAgACAAIAA5ADAAsAAgACAAPQAgACsAWQAgAGQAaQByAGUAYwB0AGkAbwBuACAAKAB1AHAAKQBcAG4AIAAgACAAIAAgACAAIAAgADEAOAAwALAAIAA9ACAAEyBYACAAZABpAHIAZQBjAHQAaQBvAG4AIAAoAGwAZQBmAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgADIANwAwALAAIAA9ACAAEyBZACAAZABpAHIAZQBjAHQAaQBvAG4AIAAoAGQAbwB3AG4AKQBcAG4AXABuACAAIAAgACAAVABoAGUAIABjAGUAbgB0AGUAcgAgAGMAZQBsAGwAIAAoADAALAAwACkAIAByAGUAdAB1AHIAbgBzACAAMACwACAAdgBpAGEAIABJAEYARQBSAFIATwBSACAAZgBhAGwAbABiAGEAYwBrAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AIAAgACAAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABHAHIAaQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAGEAdwAgAGEAbgBnAGwAZQAgAGkAbgAgAGQAZQBnAHIAZQBlAHMAIAAoAG0AYQB5ACAAYgBlACAAbgBlAGcAYQB0AGkAdgBlACkAXABuACAAIAAgACAAdABoAGUAdABhACwAIABJAEYARQBSAFIATwBSACgARABFAEcAUgBFAEUAUwAoAEEAVABBAE4AMgAoAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAxACkAKQApACwAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAdABvACAAMACwABMgMwA2ADAAsABcAG4AIAAgACAAIABhAG4AZwBsAGUALAAgAE0ATwBEACgAdABoAGUAdABhACAAKwAgADMANgAwACwAIAAzADYAMAApACwAXABuAFwAbgAgACAAIAAgAGEAbgBnAGwAZQBcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADIAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEMARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBlAG4AdABlAHIAZQBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlACAAZwByAGkAZABzACAAYQBsAGkAZwBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBoAGEAcABlACAAbwBmACAAYQBcAG4AIAAgACAAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkALgAgAFIAZQB0AHUAcgBuAHMAIABlAGkAdABoAGUAcgAgAHIAbwB3ACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAbwByACAAYwBvAGwAdQBtAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMALgBcAG4AXABuACAAIAAgACAAQwBvAG8AcgBkAGkAbgBhAHQAZQAgAHIAYQBuAGcAZQBzACAAYQByAGUAIABjAGUAbgB0AGUAcgBlAGQAIABzAHUAYwBoACAAdABoAGEAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAUgBvAHcAOgAgACAALQAoAGgAIAAtACAAMQApACAALwAgADIAIAAgAC4ALgAuACAAIAArACgAaAAgAC0AIAAxACkAIAAvACAAMgBcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBsADoAIAAgAC0AKAB3ACAALQAgADEAKQAgAC8AIAAyACAAIAAuAC4ALgAgACAAKwAoAHcAIAAtACAAMQApACAALwAgADIAXABuAFwAbgAgACAAIAAgAFcAbwByAGsAcwAgAGYAbwByACAAYgBvAHQAaAAgADEARAAgAGEAbgBkACAAMgBEACAAYQByAHIAYQB5AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuACAAYwBvAGwAdQBtAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMALgAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHIAZQB0AHUAcgBuACAAcgBvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAcgB0AGkAbgBnACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAKABjAGUAbgB0AGUAcgBlAGQAKQBcAG4AIAAgACAAIABpAF8AcwB0AGEAcgB0ACwAIAAtACAAKABoACAALQAgADEAKQAgAC8AIAAyACwAXABuACAAIAAgACAAagBfAHMAdABhAHIAdAAsACAALQAgACgAdwAgAC0AIAAxACkAIAAvACAAMgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABjAG8AbwByAGQAaQBuAGEAdABlACAAZwBlAG4AZQByAGEAdABvAHIAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKABoACwALABpAF8AcwB0AGEAcgB0ACkALAAsAHcAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABSAGUAcwBpAHoAZQC7AygAUwBFAFEAVQBFAE4AQwBFACgALAB3ACwAagBfAHMAdABhAHIAdAApACwAaAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAEkARgAoAFIAbwB3AEkAZAB4AD8ALAAgAGkAKAApACwAIABqACgAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqAFsARwBXADAAMwBdAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBHAHIAaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkAHcAbwByAGsAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIAByAG8AdwARIGkAbgBkAGUAeAAgAG8AcgAgAGMAbwBsAHUAbQBuABEgaQBuAGQAZQB4ACAAZwByAGkAZABzACAAbQBhAHQAYwBoAGkAbgBnACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgAGEAcgByAGEAeQAuACAAVABoAGkAcwAgAGkAcwAgAHQAaABlACAARQB4AGMAZQBsACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAG8AZgAgAE0AQQBUAEwAQQBCABkgcwAgAG0AZQBzAGgAZwByAGkAZAAgAG8AcgAgAE4AdQBtAFAAeQAZIHMAIABpAG4AZABpAGMAZQBzAC4AXABuAFwAbgAgACAAIAAgAEIAeQAgAGQAZQBmAGEAdQBsAHQALAAgAE0ARwByAGkAZAC7AyAAcgBlAHQAdQByAG4AcwAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAuACAAVwBoAGUAbgAgAHQAaABlACAAbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAIABpAHMAIABUAFIAVQBFACwAXABuACAAIAAgACAAaQB0ACAAcgBlAHQAdQByAG4AcwAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAGkAbgBzAHQAZQBhAGQALgBcAG4AXABuACAAIAAgACAAVwBvAHIAawBzACAAZgBvAHIAIABiAG8AdABoACAAMQBEACAAYQBuAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAuACAATwB1AHQAcAB1AHQAIABhAGwAdwBhAHkAcwAgAG0AYQB0AGMAaABlAHMAIAB0AGgAZQAgAGcAZQBvAG0AZQB0AHIAeQAgAG8AZgAgAHQAaABlAFwAbgAgACAAIAAgAGkAbgBwAHUAdAAgAGcAcgBpAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzAC4AIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAByAGUAdAB1AHIAbgAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAaQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoAGgAKQAsACwAdwApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcAKQAsAGgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAWwBHAFcAMAA0AF0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABUAEcAcgBpAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAHIAbwB3ABEgaQBuAGQAZQB4ACAAbwByACAAYwBvAGwAdQBtAG4AESBpAG4AZABlAHgAIABnAHIAaQBkAHMAIAB3AGgAbwBzAGUAIAB2AGEAbAB1AGUAcwAgAHcAcgBhAHAAIAB3AGkAdABoAGkAbgAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZABcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAuACAASQBuAGQAaQBjAGUAcwAgAGMAeQBjAGwAZQAgAGYAcgBvAG0AIAAxACAAdABvACAAdABoAHIAZQBzAGgAbwBsAGQALAAgAHIAZQBwAGUAYQB0AGkAbgBnACAAYQBzACAAbgBlAGUAZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQBcAG4AIAAgACAAIABzAGgAYQBwAGUAIABvAGYAIAB0AGgAZQAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIABCAHkAIABkAGUAZgBhAHUAbAB0ACwAIABUAEcAcgBpAGQAuwMgAHIAZQB0AHUAcgBuAHMAIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALgAgAFcAaABlAG4AIAB0AGgAZQAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAVABSAFUARQAsAFwAbgAgACAAIAAgAGkAdAAgAHIAZQB0AHUAcgBuAHMAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAIABpAG4AcwB0AGUAYQBkAC4AXABuAFwAbgAgACAAIAAgAE4AbwBuABEgaQBuAHQAZQBnAGUAcgAgAHQAaAByAGUAcwBoAG8AbABkAHMAIABhAHIAZQAgAG4AbwByAG0AYQBsAGkAegBlAGQAIAB1AHMAaQBuAGcAIABJAE4AVAAoAHQAaAByAGUAcwBoAG8AbABkACkALgAgAFQAaAByAGUAcwBoAG8AbABkAHMAIABtAHUAcwB0ACAAYgBlAFwAbgAgACAAIAAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABBACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHMAaQB6AGUALgBcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAgACAAIAAtACAATQBhAHgAaQBtAHUAbQAgAGkAbgBkAGUAeAAgAHYAYQBsAHUAZQAgAGIAZQBmAG8AcgBlACAAdwByAGEAcABwAGkAbgBnACAAKABtAHUAcwB0ACAAYgBlACAAPgAgADAAKQAuAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAgAC0AIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAuACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAcgBlAHQAdQByAG4AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVABHAHIAaQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAB0AGgAcgBlAHMAaABvAGwAZAApACwAIAB0AGgAcgBlAHMAaABvAGwAZAAgADwAPQAgADAAKQAsAFwAIgAjAFQASABSAEUAUwBIAE8ATABEACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAdABoAHIAZQBzAGgAbwBsAGQAXABuACAAIAAgACAAdAAsACAAIAAgACAAIAAgACAASQBOAFQAKAB0AGgAcgBlAHMAaABvAGwAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAdwByAGEAcABwAGUAZAAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAMQAgACsAIABNAE8ARAAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKABoACwALAAwACkALAAsAHcAKQAsACAAdAApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAMQAgACsAIABNAE8ARAAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcALAAwACkALABoACkALAAgAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADUAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFAAbwBsAGEAcgBHAHIAaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkAHcAbwByAGsAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAGcAcgBpAGQAIABvAGYAIABwAG8AbABhAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIABhAGwAaQBnAG4AZQBkACAAdABvACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgAGEAcgByAGEAeQAuACAAQwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAYQByAGUAIABkAGUAcgBpAHYAZQBkACAAZgByAG8AbQAgAGMAZQBuAHQAZQByAGUAZAAgAEMAYQByAHQAZQBzAGkAYQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAcAByAG8AZAB1AGMAZQBkAFwAbgAgACAAIAAgAGIAeQAgAEMARwByAGkAZAC7Ay4AXABuAFwAbgAgACAAIAAgAFQAdwBvACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGYAaQBlAGwAZABzACAAYQByAGUAIABhAHYAYQBpAGwAYQBiAGwAZQA6AFwAbgAgACAAIAAgACAAIAAgACAAcgAgACAAIAAgAC0AIAByAGEAZABpAGEAbAAgAGQAaQBzAHQAYQBuAGMAZQAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAZQBuAHQAZQByAFwAbgAgACAAIAAgACAAIAAgACAAcABoAGkAIAAgAC0AIABhAG4AZwBsAGUAIABpAG4AIAByAGEAZABpAGEAbgBzACwAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAEEAVABBAE4AMgAoAHkALAAgAHgAKQAgAGMAbwBuAHYAZQBuAHQAaQBvAG4AXABuAFwAbgAgACAAIAAgAEkAZgAgAHAAaABpAF8AYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGkAcwAgAG8AbQBpAHQAdABlAGQALAAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAcgBlAHQAdQByAG4AcwAgAHQAaABlACAAcgBhAGQAaQBhAGwAIABkAGkAcwB0AGEAbgBjAGUAIABnAHIAaQBkAC4AXABuACAAIAAgACAASQBmACAAVABSAFUARQAsACAAdABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIAByAGUAdAB1AHIAbgBzACAAdABoAGUAIABhAG4AZwB1AGwAYQByACAAZwByAGkAZAAuAFwAbgBcAG4AIAAgACAAIABUAGgAZQAgAGMAZQBuAHQAZQByACAAYwBlAGwAbAAgACgAMAAsADAAKQAgAHIAZQB0AHUAcgBuAHMAIABwAGgAaQAgAD0AIAAwACAAdgBpAGEAIABJAEYARQBSAFIATwBSACAAZgBhAGwAbABiAGEAYwBrAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdwBoAGkAYwBoACAAdABvACAAZwBlAG4AZQByAGEAdABlACAAcABvAGwAYQByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAC4AXABuACAAIAAgACAAWwBwAGgAaQBfAGMAbwBvAHIAZABpAG4AYQB0AGUAXQAgAC0AIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgAgAHAAaABpADsAIABpAGYAIABvAG0AaQB0AHQAZQBkACwAIAByAGUAdAB1AHIAbgAgAHIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABvAGwAYQByAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAcABoAGkAXwBjAG8AbwByAGQAaQBuAGEAdABlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAG0AbwBkAGUAXABuACAAIAAgACAASQBzAFIAPwAsACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAcABoAGkAXwBjAG8AbwByAGQAaQBuAGEAdABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAG8AbABhAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgAFMAUQBSAFQAKAB4AF4AMgAgACsAIAB5AF4AMgApACwAXABuACAAIAAgACAAcABoAGkALAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABBAFQAQQBOADIAKAB5ACwAIAB4ACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAHIAIABvAHIAIABwAGgAaQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAASQBGACgASQBzAFIAPwAsACAAcgAsACAAcABoAGkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBHAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AIwAjACAAMAAyACAALQAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AIAAqAC8AXABuAFwAbgAvACoAXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFQAaABpAHMAIABtAG8AZAB1AGwAZQAgAGQAZQBmAGkAbgBlAHMAIABhACAAZgBhAG0AaQBsAHkAIABvAGYAIABnAGUAbwBtAGUAdAByAGkAYwAgAGUAeAB0AHIAYQBjAHQAaQBvAG4AIABvAHAAZQByAGEAdABvAHIAcwAgAGYAbwByACAAMgBEACAAYQByAHIAYQB5AHMALgBcAG4AIAAgACAAIABFAGEAYwBoACAAZgB1AG4AYwB0AGkAbwBuACAAcgBlAHQAdQByAG4AcwAgAGEAIAByAGUAZwBpAG8AbgAgAG8AZgAgAHQAaABlACAAZwByAGkAZAAgAGQAZQBmAGkAbgBlAGQAIABiAHkAIABhACAAcwBwAGUAYwBpAGYAaQBjACAAcwBoAGEAcABlACwAXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBpAG4AZwAgAHQAaABlACAAZwBlAG8AbQBlAHQAcgB5ACAAbwBmACAAdABoAGUAIABlAHgAdAByAGEAYwB0AGUAZAAgAGEAcgBlAGEALgAgAEMAZQBuAHQAZQByAHMAIABtAGEAeQAgAGIAZQAgAHMAcABlAGMAaQBmAGkAZQBkACAAYgB5AFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAgAG8AcgAgAGUAeABwAGwAaQBjAGkAdAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAsACAAYQBuAGQAIABvAHAAdABpAG8AbgBhAGwAIABmAGkAbABsACAAdgBhAGwAdQBlAHMAIABjAG8AbgB0AHIAbwBsACAAdwBoAGEAdABcAG4AIAAgACAAIABhAHAAcABlAGEAcgBzACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgAuAFwAbgBcAG4AIAAgACAAIABTAGgAYQBwAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEMAaQByAGMAbABlALsDIAAgACAALQAgACAAIABDAGkAcgBjAHUAbABhAHIAIAByAGUAZwBpAG8AbgAgAGIAeQAgAHQAYQByAGcAZQB0ACAAbwByACAAewByAG8AdwAsACAAYwBvAGwAfQAgAGMAZQBuAHQAZQByAC4AXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEQAaQBhAG0AbwBuAGQAuwMgACAALQAgACAAIABNAGEAbgBoAGEAdAB0AGEAbgARIHIAYQBkAGkAdQBzACAAZABpAGEAbQBvAG4AZAAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABQAGwAdQBzALsDIAAgACAAIAAgAC0AIAAgACAAQwByAG8AcwBzABEgcwBoAGEAcABlAGQAIAByAGUAZwBpAG8AbgAgACgAdgBvAG4AIABOAGUAdQBtAGEAbgBuACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAKQAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABQAHkAcgBhAG0AaQBkALsDIAAgAC0AIAAgACAARABpAHIAZQBjAHQAaQBvAG4AYQBsACAAaABhAGwAZgARIGQAaQBhAG0AbwBuAGQAIAAoAGYAbwB1AHIAIABwAGkAZQBjAGUAcwApAC4AXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFIAaQBuAGcAuwMgACAAIAAgACAALQAgACAAIABMAGEAeQBlAHIAESBiAGEAcwBlAGQAIABwAGUAcgBpAG0AZQB0AGUAcgAgAGUAeAB0AHIAYQBjAHQAaQBvAG4ALgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUwBxAHUAYQByAGUAuwMgACAAIAAtACAAIAAgAEMAaABlAGIAeQBzAGgAZQB2ABEgcgBhAGQAaQB1AHMAIABzAHEAdQBhAHIAZQAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABUAHIAaQBhAG4AZwBsAGUAuwMgAC0AIAAgACAARABpAHIAZQBjAHQAaQBvAG4AYQBsACAAdAByAGkAYQBuAGcAdQBsAGEAcgAgAHIAZQBnAGkAbwBuACAAKABhAGIAbwB2AGUAIABvAHIAIABiAGUAbABvAHcAKQAuAFwAbgBcAG4AIAAgACAAIABVAHQAaQBsAGkAdABpAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEMARwByAGkAZAC7AywAIABNAEcAcgBpAGQAuwMsACAAUgBlAHMAaQB6AGUAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4AIAAgACAAIABBAGwAbAAgAGYAdQBuAGMAdABpAG8AbgBzACAAYQByAGUAIABzAGgAYQBwAGUAESBkAHIAaQB2AGUAbgA6ACAAdABoAGUAIABpAG4AcAB1AHQAIABnAHIAaQBkACAAZABlAHQAZQByAG0AaQBuAGUAcwAgAHQAaABlACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBcAG4AIAAgACAAIABlAHgAdABlAG4AdABzACAAYQBuAGQAIAB0AGgAZQAgAGcAZQBvAG0AZQB0AHIAeQAgAG8AZgAgAHQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgAuAFwAbgAvACoAXABuAFwAbgAgACAAIAAgAEUAeABhAG0AcABsAGUAcwA6AFwAbgBcAG4AXABuAEcAcgBpAGQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuADEAXAB0ADIAXAB0ADMAXAB0ADQAXAB0ADUAXAB0ADYAXAB0ADcAXAB0ADgAXAB0ADkAXAB0ADEAMABcAG4AMQAxAFwAdAAxADIAXAB0ADEAMwBcAHQAMQA0AFwAdAAxADUAXAB0ADEANgBcAHQAMQA3AFwAdAAxADgAXAB0ADEAOQBcAHQAMgAwAFwAbgAyADEAXAB0ADIAMgBcAHQAMgAzAFwAdAAyADQAXAB0ADIANQBcAHQAMgA2AFwAdAAyADcAXAB0ADIAOABcAHQAMgA5AFwAdAAzADAAXABuADMAMQBcAHQAMwAyAFwAdAAzADMAXAB0ADMANABcAHQAMwA1AFwAdAAzADYAXAB0ADMANwBcAHQAMwA4AFwAdAAzADkAXAB0ADQAMABcAG4ANAAxAFwAdAA0ADIAXAB0ADQAMwBcAHQANAA0AFwAdAA0ADUAXAB0ADQANgBcAHQANAA3AFwAdAA0ADgAXAB0ADQAOQBcAHQANQAwAFwAbgA1ADEAXAB0ADUAMgBcAHQANQAzAFwAdAA1ADQAXAB0ADUANQBcAHQANQA2AFwAdAA1ADcAXAB0ADUAOABcAHQANQA5AFwAdAA2ADAAXABuADYAMQBcAHQANgAyAFwAdAA2ADMAXAB0ADYANABcAHQANgA1AFwAdAA2ADYAXAB0ADYANwBcAHQANgA4AFwAdAA2ADkAXAB0ADcAMABcAG4ANwAxAFwAdAA3ADIAXAB0ADcAMwBcAHQANwA0AFwAdAA3ADUAXAB0ADcANgBcAHQANwA3AFwAdAA3ADgAXAB0ADcAOQBcAHQAOAAwAFwAbgA4ADEAXAB0ADgAMgBcAHQAOAAzAFwAdAA4ADQAXAB0ADgANQBcAHQAOAA2AFwAdAA4ADcAXAB0ADgAOABcAHQAOAA5AFwAdAA5ADAAXABuADkAMQBcAHQAOQAyAFwAdAA5ADMAXAB0ADkANABcAHQAOQA1AFwAdAA5ADYAXAB0ADkANwBcAHQAOQA4AFwAdAA5ADkAXAB0ADEAMAAwAFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AQwBpAHIAYwBsAGUAuwMoAGcAcgBpAGQALAA0ADUALAA1ACwAXAAiAFwAIgApAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAMgBcAHQAMwBcAHQANABcAHQANQBcAHQANgBcAHQANwBcAHQAOABcAHQAXAB0AFwAbgAxADEAXAB0ADEAMgBcAHQAMQAzAFwAdAAxADQAXAB0ADEANQBcAHQAMQA2AFwAdAAxADcAXAB0ADEAOABcAHQAMQA5AFwAdABcAG4AMgAxAFwAdAAyADIAXAB0ADIAMwBcAHQAMgA0AFwAdAAyADUAXAB0ADIANgBcAHQAMgA3AFwAdAAyADgAXAB0ADIAOQBcAHQAXABuADMAMQBcAHQAMwAyAFwAdAAzADMAXAB0ADMANABcAHQAMwA1AFwAdAAzADYAXAB0ADMANwBcAHQAMwA4AFwAdAAzADkAXAB0AFwAbgA0ADEAXAB0ADQAMgBcAHQANAAzAFwAdAA0ADQAXAB0ADQANQBcAHQANAA2AFwAdAA0ADcAXAB0ADQAOABcAHQANAA5AFwAdAA1ADAAXABuADUAMQBcAHQANQAyAFwAdAA1ADMAXAB0ADUANABcAHQANQA1AFwAdAA1ADYAXAB0ADUANwBcAHQANQA4AFwAdAA1ADkAXAB0AFwAbgA2ADEAXAB0ADYAMgBcAHQANgAzAFwAdAA2ADQAXAB0ADYANQBcAHQANgA2AFwAdAA2ADcAXAB0ADYAOABcAHQANgA5AFwAdABcAG4ANwAxAFwAdAA3ADIAXAB0ADcAMwBcAHQANwA0AFwAdAA3ADUAXAB0ADcANgBcAHQANwA3AFwAdAA3ADgAXAB0ADcAOQBcAHQAXABuAFwAdAA4ADIAXAB0ADgAMwBcAHQAOAA0AFwAdAA4ADUAXAB0ADgANgBcAHQAOAA3AFwAdAA4ADgAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0ADkANQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4ARABpAGEAbQBvAG4AZAC7AygAZwByAGkAZAAsAHsANQAsADUAfQAsADMALABcACIAXAAiACkAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADEANQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdAAyADQAXAB0ADIANQBcAHQAMgA2AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdAAzADMAXAB0ADMANABcAHQAMwA1AFwAdAAzADYAXAB0ADMANwBcAHQAXAB0AFwAdABcAHQAXABuADQAMgBcAHQANAAzAFwAdAA0ADQAXAB0ADQANQBcAHQANAA2AFwAdAA0ADcAXAB0ADQAOABcAHQAXAB0AFwAdABcAG4AXAB0ADUAMwBcAHQANQA0AFwAdAA1ADUAXAB0ADUANgBcAHQANQA3AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdAA2ADQAXAB0ADYANQBcAHQANgA2AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADcANQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFAAbAB1AHMAuwMoAGcAcgBpAGQALAA1ADcALAAzACwAXAAiAFwAIgApAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdAAyADcAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADMANwBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQANAA3AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgA1ADQAXAB0ADUANQBcAHQANQA2AFwAdAA1ADcAXAB0ADUAOABcAHQANQA5AFwAdAA2ADAAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADYANwBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQANwA3AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0AFwAdAA4ADcAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBQAHkAcgBhAG0AaQBkALsDKABnAHIAaQBkACwAMgAsAFwAIgB4AFwAIgApAFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAAxADAAXABuAHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0ADEAOQBcAHQAMgAwAFwAbgB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAAyADgAXAB0ADIAOQBcAHQAMwAwAFwAbgB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAAzADcAXAB0ADMAOABcAHQAMwA5AFwAdAA0ADAAXABuAHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0AHgAXAB0ADQANgBcAHQANAA3AFwAdAA0ADgAXAB0ADQAOQBcAHQANQAwAFwAbgB4AFwAdAB4AFwAdAB4AFwAdAB4AFwAdAA1ADUAXAB0ADUANgBcAHQANQA3AFwAdAA1ADgAXAB0ADUAOQBcAHQANgAwAFwAbgB4AFwAdAB4AFwAdAB4AFwAdAA2ADQAXAB0ADYANQBcAHQANgA2AFwAdAA2ADcAXAB0ADYAOABcAHQANgA5AFwAdAA3ADAAXABuAHgAXAB0AHgAXAB0ADcAMwBcAHQANwA0AFwAdAA3ADUAXAB0ADcANgBcAHQANwA3AFwAdAA3ADgAXAB0ADcAOQBcAHQAOAAwAFwAbgB4AFwAdAA4ADIAXAB0ADgAMwBcAHQAOAA0AFwAdAA4ADUAXAB0ADgANgBcAHQAOAA3AFwAdAA4ADgAXAB0ADgAOQBcAHQAOQAwAFwAbgA5ADEAXAB0ADkAMgBcAHQAOQAzAFwAdAA5ADQAXAB0ADkANQBcAHQAOQA2AFwAdAA5ADcAXAB0ADkAOABcAHQAOQA5AFwAdAAxADAAMABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFIAaQBuAGcAuwMoAGcAcgBpAGQALAAyACwAXAAiAC0AXAAiACkAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXABuAC0AXAB0ADEAMgBcAHQAMQAzAFwAdAAxADQAXAB0ADEANQBcAHQAMQA2AFwAdAAxADcAXAB0ADEAOABcAHQAMQA5AFwAdAAtAFwAbgAtAFwAdAAyADIAXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0ADIAOQBcAHQALQBcAG4ALQBcAHQAMwAyAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAzADkAXAB0AC0AXABuAC0AXAB0ADQAMgBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQANAA5AFwAdAAtAFwAbgAtAFwAdAA1ADIAXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0AC0AXAB0ADUAOQBcAHQALQBcAG4ALQBcAHQANgAyAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAAtAFwAdAA2ADkAXAB0AC0AXABuAC0AXAB0ADcAMgBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQANwA5AFwAdAAtAFwAbgAtAFwAdAA4ADIAXAB0ADgAMwBcAHQAOAA0AFwAdAA4ADUAXAB0ADgANgBcAHQAOAA3AFwAdAA4ADgAXAB0ADgAOQBcAHQALQBcAG4ALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAHQALQBcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFMAcQB1AGEAcgBlALsDKABnAHIAaQBkACwAMgA3ACwAMwAsAFwAIgBcACIAKQBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4ANABcAHQANQBcAHQANgBcAHQANwBcAHQAOABcAHQAOQBcAHQAMQAwAFwAdABcAHQAXAB0AFwAbgAxADQAXAB0ADEANQBcAHQAMQA2AFwAdAAxADcAXAB0ADEAOABcAHQAMQA5AFwAdAAyADAAXAB0AFwAdABcAHQAXABuADIANABcAHQAMgA1AFwAdAAyADYAXAB0ADIANwBcAHQAMgA4AFwAdAAyADkAXAB0ADMAMABcAHQAXAB0AFwAdABcAG4AMwA0AFwAdAAzADUAXAB0ADMANgBcAHQAMwA3AFwAdAAzADgAXAB0ADMAOQBcAHQANAAwAFwAdABcAHQAXAB0AFwAbgA0ADQAXAB0ADQANQBcAHQANAA2AFwAdAA0ADcAXAB0ADQAOABcAHQANAA5AFwAdAA1ADAAXAB0AFwAdABcAHQAXABuADUANABcAHQANQA1AFwAdAA1ADYAXAB0ADUANwBcAHQANQA4AFwAdAA1ADkAXAB0ADYAMABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFQAcgBpAGEAbgBnAGwAZQC7AygAZwByAGkAZAAsADQANAAsADMALAAsAFwAIgBcACIAKQAgAC0AIABBAGIAbwB2AGUAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdABcAHQAXAB0ADEANABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdAAyADMAXAB0ADIANABcAHQAMgA1AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFwAdAAzADIAXAB0ADMAMwBcAHQAMwA0AFwAdAAzADUAXAB0ADMANgBcAHQAXAB0AFwAdABcAHQAXABuADQAMQBcAHQANAAyAFwAdAA0ADMAXAB0ADQANABcAHQANAA1AFwAdAA0ADYAXAB0ADQANwBcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXABuAFQAcgBpAGEAbgBnAGwAZQC7AygAZwByAGkAZAAsADQANAAsADMALAAxACwAXAAiAFwAIgApACAALQAgAEIAZQBsAG8AdwBcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4ANAAxAFwAdAA0ADIAXAB0ADQAMwBcAHQANAA0AFwAdAA0ADUAXAB0ADQANgBcAHQANAA3AFwAdABcAHQAXAB0AFwAbgBcAHQANQAyAFwAdAA1ADMAXAB0ADUANABcAHQANQA1AFwAdAA1ADYAXAB0AFwAdABcAHQAXAB0AFwAbgBcAHQAXAB0ADYAMwBcAHQANgA0AFwAdAA2ADUAXAB0AFwAdABcAHQAXAB0AFwAdABcAG4AXAB0AFwAdABcAHQANwA0AFwAdABcAHQAXAB0AFwAdABcAHQAXAB0AFwAbgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABDAGkAcgBjAGwAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEMARwByAGkAZAC7AywAIABTAHEAdQBlAGUAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhACAAYwBpAHIAYwB1AGwAYQByACAAcgBlAGcAaQBvAG4AIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGIAeQAgAHMAcABlAGMAaQBmAHkAaQBuAGcAIAB0AGgAZQAgAGMAZQBuAHQAZQByACAAYQBuAGQAIABhAFwAbgAgACAAIAAgAHIAYQBkAGkAdQBzACAAKABlAHgAdABlAG4AZAApAC4AIABUAGgAZQAgAGMAZQBuAHQAZQByACAAbQBhAHkAIABiAGUAIABnAGkAdgBlAG4AIABhAHMAIABhACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGEAcwAgAGUAeABwAGwAaQBjAGkAdABcAG4AIAAgACAAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AIABUAGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkACAAcgBlAGcAaQBvAG4AIABwAHIAZQBzAGUAcgB2AGUAcwAgAGkAdABzACAAZwBlAG8AbQBlAHQAcgBpAGMAIABzAGgAYQBwAGUALABcAG4AIAAgACAAIABhAG4AZAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAG8AbgBsAHkAIABmAGkAbABsAF8AdgBhAGwAdQBlACAAYQByAGUAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAgACAAIAAgACAAIAAtACAAQwBlAG4AdABlAHIAIABvAGYAIAB0AGgAZQAgAGMAaQByAGMAbABlAC4AIABNAGEAeQAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAgAGMAcgBpAHQAZQByAGkAbwBuACAAbwByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIAB0AGgAZQAgAGYAbwByAG0AIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AXABuACAAIAAgACAAZQB4AHQAZQBuAGQAIAAgACAAIAAgACAALQAgAFIAYQBkAGkAdQBzACAAbwBmACAAdABoAGUAIABjAGkAcgBjAGwAZQAgACgAbQB1AHMAdAAgAGIAZQAgAGEAIABwAG8AcwBpAHQAaQB2AGUAIABpAG4AdABlAGcAZQByACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAYwBpAHIAYwBsAGUALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADAALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQwBpAHIAYwBsAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACwAXABuACAAIAAgACAAZQB4AHQAZQBuAGQALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAYQByAGcAZQB0ACAAaQBuAHQAZQByAHAAcgBlAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBJAF8ASgA/ACwAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUACgAdABhAHIAZwBlAHQAKQAgAD0AIAAyACwAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAFQAQQBLAEUAKAB0AGEAcgBnAGUAdAAsACAALQAxACwAIAAtADEAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAdABjAGgAIABmAG8AcgAgAHMAYwBhAGwAYQByACAAdABhAHIAZwBlAHQAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABnAHIAaQBkACAAPQAgAHQAYQByAGcAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHAAdQB0ACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABFAHgAdABlAG4AZAA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAGUAeAB0AGUAbgBkACkALAAgAGUAeAB0AGUAbgBkACAAPAAgADEAKQAsAFwAbgAgACAAIAAgAE4AbwBUAGEAcgBnAGUAdAA/ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEYAQQBMAFMARQAsACAATgBPAFQAKABPAFIAKABiAG8AbwBsACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAGwAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABFAHgAdABlAG4AZAA/ACwAIABcACIAIwBFAFgAVABFAE4ARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AVABhAHIAZwBlAHQAPwAsACAAXAAiACMAVABBAFIARwBFAFQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATQBlAHMAaAAgAGcAcgBpAGQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAZQBuAHQAZQByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAaQAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABpACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABqACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGoALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBpAHIAYwBsAGUAIABtAGEAcwBrAFwAbgAgACAAIAAgAG0AYQBzAGsALAAgACAAIAAoAGkAIAAtACAAeAApAF4AMgAgACsAIAAoAGoAIAAtACAAeQApAF4AMgAgADwAPQAgAGUAeAB0AGUAbgBkAF4AMgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYQBuAGQAIABzAHEAdQBlAGUAegBlAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIABTAHEAdQBlAGUAegBlALsDKABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABEAGkAYQBtAG8AbgBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQwBHAHIAaQBkALsDLAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAIABkAGkAYQBtAG8AbgBkABEgcwBoAGEAcABlAGQAIAByAGUAZwBpAG8AbgAgACgATQBhAG4AaABhAHQAdABhAG4AIAByAGEAZABpAHUAcwApACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAHkAXABuACAAIAAgACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAIABkAGkAcwB0AGEAbgBjAGUALgAgAFQAaABlACAAYwBlAG4AdABlAHIAIABtAGEAeQAgAGIAZQAgAGcAaQB2AGUAbgAgAGEAcwAgAGEAIABzAGMAYQBsAGEAcgBcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGEAcwAgAGUAeABwAGwAaQBjAGkAdAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgAgAFQAaABlACAAZQB4AHQAcgBhAGMAdABlAGQAIAByAGUAZwBpAG8AbgBcAG4AIAAgACAAIABwAHIAZQBzAGUAcgB2AGUAcwAgAGkAdABzACAAZwBlAG8AbQBlAHQAcgBpAGMAIABzAGgAYQBwAGUALAAgAGEAbgBkACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAbwBuAGwAeQAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAXABuACAAIAAgACAAYQByAGUAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAgACAAIAAgACAAIAAtACAAQwBlAG4AdABlAHIAIABvAGYAIAB0AGgAZQAgAGQAaQBhAG0AbwBuAGQALgAgAE0AYQB5ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgBcAG4AIAAgACAAIABkAGkAcwB0AGEAbgBjAGUAIAAgACAAIAAtACAATQBhAG4AaABhAHQAdABhAG4AIAByAGEAZABpAHUAcwAgAG8AZgAgAHQAaABlACAAZABpAGEAbQBvAG4AZAAgACgAbQB1AHMAdAAgAGIAZQAgAGEAIABwAG8AcwBpAHQAaQB2AGUAIABpAG4AdABlAGcAZQByACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAZABpAGEAbQBvAG4AZAAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAGkAYQBtAG8AbgBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAsAFwAbgAgACAAIAAgAGQAaQBzAHQAYQBuAGMAZQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAGEAcgBnAGUAdAAgAGkAbgB0AGUAcgBwAHIAZQB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMASQBfAEoAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAKAB0AGEAcgBnAGUAdAApACAAPQAgADIALABcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABUAEEASwBFACgAdABhAHIAZwBlAHQALAAgAC0AMQAsACAALQAxACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAG8AbwBsAGUAYQBuACAAbQBhAHQAYwBoACAAZgBvAHIAIABzAGMAYQBsAGEAcgAgAHQAYQByAGcAZQB0AFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAGcAcgBpAGQAIAA9ACAAdABhAHIAZwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARABpAHMAdABhAG4AYwBlAD8ALAAgAE8AUgAoAEkAUwBUAEUAWABUACgAZABpAHMAdABhAG4AYwBlACkALAAgAGQAaQBzAHQAYQBuAGMAZQAgADwAIAAxACkALABcAG4AIAAgACAAIABOAG8AVABhAHIAZwBlAHQAPwAsACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABOAE8AVAAoAE8AUgAoAGIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAbABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABEAGkAcwB0AGEAbgBjAGUAPwAsACAAXAAiACMARABJAFMAVABBAE4AQwBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBUAGEAcgBnAGUAdAA/ACwAIABcACIAIwBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABpACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEkATgBEAEUAWAAoAGoALAAgAHIALAAgAGMAKQAsACAAVABPAEMATwBMACgASQBGACgAYgBvAG8AbAAsACAAagAsACAATgBBACgAKQApACwAIAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAYQBtAG8AbgBkACAAbQBhAHMAawAgACgATQBhAG4AaABhAHQAdABhAG4AIABkAGkAcwB0AGEAbgBjAGUAKQBcAG4AIAAgACAAIABtAGEAcwBrACwAIAAgACAAQQBCAFMAKABpACAALQAgAHgAKQAgACsAIABBAEIAUwAoAGoAIAAtACAAeQApACAAPAA9ACAAZABpAHMAdABhAG4AYwBlACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABhAG4AZAAgAHMAcQB1AGUAZQB6AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAFMAcQB1AGUAZQB6AGUAuwMoAEkARgAoAG0AYQBzAGsALAAgAGcAcgBpAGQALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBHADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFAAbAB1AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAHAAbAB1AHMAESBzAGgAYQBwAGUAZAAgAHIAZQBnAGkAbwBuACAAKABlAHgAdABlAG4AZABlAGQAIAB2AG8AbgAgAE4AZQB1AG0AYQBuAG4AIABuAGUAaQBnAGgAYgBvAHIAaABvAG8AZAApACAAZgByAG8AbQAgAGEAIAAyAEQAXABuACAAIAAgACAAYQByAHIAYQB5ACAAYgB5ACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAbgAgAGUAeAB0AGUAbgBkACAAdgBhAGwAdQBlAC4AIABUAGgAZQAgAGMAZQBuAHQAZQByACAAbQBhAHkAIABiAGUAIABnAGkAdgBlAG4AXABuACAAIAAgACAAYQBzACAAYQAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABhAHMAIABlAHgAcABsAGkAYwBpAHQAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AIABUAGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkAFwAbgAgACAAIAAgAHIAZQBnAGkAbwBuACAAcAByAGUAcwBlAHIAdgBlAHMAIABpAHQAcwAgAGcAZQBvAG0AZQB0AHIAaQBjACAAcwBoAGEAcABlACwAIABhAG4AZAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAG8AbgBsAHkAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAgAGEAcgBlACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAdABhAHIAZwBlAHQAIAAgACAAIAAgACAALQAgAEMAZQBuAHQAZQByACAAbwBmACAAdABoAGUAIABwAGwAdQBzAC4AIABNAGEAeQAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAgAGMAcgBpAHQAZQByAGkAbwBuACAAbwByACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIAB0AGgAZQAgAGYAbwByAG0AIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AXABuACAAIAAgACAAZQB4AHQAZQBuAGQAIAAgACAAIAAgACAALQAgAFIAYQBkAGkAdQBzACAAbwBmACAAdABoAGUAIABwAGwAdQBzACAAYQByAG0AcwAgACgAbQB1AHMAdAAgAGIAZQAgAGEAIABwAG8AcwBpAHQAaQB2AGUAIABpAG4AdABlAGcAZQByACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAcABsAHUAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBQAGwAdQBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIAB0AGEAcgBnAGUAdAAsAFwAbgAgACAAIAAgAGUAeAB0AGUAbgBkACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAGEAcgBnAGUAdAAgAGkAbgB0AGUAcgBwAHIAZQB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMASQBfAEoAPwAsACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVAAoAHQAYQByAGcAZQB0ACkAIAA9ACAAMgAsAFwAbgAgACAAIAAgAHIALAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIAAgACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIAAgACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAtADEALAAgAC0AMQApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBvAG8AbABlAGEAbgAgAG0AYQB0AGMAaAAgAGYAbwByACAAcwBjAGEAbABhAHIAIAB0AGEAcgBnAGUAdABcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABGAEEATABTAEUALAAgAGcAcgBpAGQAIAA9ACAAdABhAHIAZwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIAB2AGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABYAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEUAeAB0AGUAbgBkAD8ALAAgAE8AUgAoAEkAUwBUAEUAWABUACgAZQB4AHQAZQBuAGQAKQAsACAAZQB4AHQAZQBuAGQAIAA8ACAAMQApACwAXABuACAAIAAgACAATgBvAFQAYQByAGcAZQB0AD8ALAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABOAE8AVAAoAE8AUgAoAGIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAbABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIAAwACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAZwByAGkAZAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAXAAiACMAMQBEAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEUAeAB0AGUAbgBkAD8ALAAgAFwAIgAjAEUAWABUAEUATgBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBUAGEAcgBnAGUAdAA/ACwAIABcACIAIwBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAF8ASgA/ACwAIABJAE4ARABFAFgAKABpACwAIAByACwAIABjACkALAAgAFQATwBDAE8ATAAoAEkARgAoAGIAbwBvAGwALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEkATgBEAEUAWAAoAGoALAAgAHIALAAgAGMAKQAsACAAVABPAEMATwBMACgASQBGACgAYgBvAG8AbAAsACAAagAsACAATgBBACgAKQApACwAIAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGwAdQBzACAAbQBhAHMAawAgACgAaABvAHIAaQB6AG8AbgB0AGEAbAAgACsAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAbQBzACkAXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACgAaQAgAD0AIAB4ACkAIAAqACAAKABBAEIAUwAoAGoAIAAtACAAeQApACAAPAA9ACAAZQB4AHQAZQBuAGQAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAagAgAD0AIAB5ACkAIAAqACAAKABBAEIAUwAoAGkAIAAtACAAeAApACAAPAA9ACAAZQB4AHQAZQBuAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYQBuAGQAIABzAHEAdQBlAGUAegBlAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIABTAHEAdQBlAGUAegBlALsDKABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABQAHkAcgBhAG0AaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAATQBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABvAG4AZQAgAG8AZgAgAGYAbwB1AHIAIAB0AHIAaQBhAG4AZwB1AGwAYQByACAAXAAiAHAAeQByAGEAbQBpAGQAXAAiACAAcgBlAGcAaQBvAG4AcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAGkAbABlAFwAbgAgACAAIAAgAHAAcgBlAHMAZQByAHYAaQBuAGcAIABzAGgAYQBwAGUALgAgAFAAeQByAGEAbQBpAGQAIAByAGUAZwBpAG8AbgBzACAAYQByAGUAIABkAGUAZgBpAG4AZQBkACAAdQBzAGkAbgBnACAAcgBvAHcALwBjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABnAGUAbgBlAHIAYQB0AGUAZAAgAGIAeQAgAE0ARwByAGkAZAC7Ay4AIABBAG4AIABvAHAAdABpAG8AbgBhAGwAIABmAGkAbABsAF8AdgBhAGwAdQBlACAAYwBvAG4AdAByAG8AbABzACAAdwBoAGEAdAAgAGEAcABwAGUAYQByAHMAIABvAHUAdABzAGkAZABlACAAdABoAGUAXABuACAAIAAgACAAcwBlAGwAZQBjAHQAZQBkACAAcgBlAGcAaQBvAG4ALgBcAG4AXABuACAAIAAgACAAUAB5AHIAYQBtAGkAZAAgAHAAaQBlAGMAZQBzACAAKABjAGwAbwBjAGsAdwBpAHMAZQApADoAXABuACAAIAAgACAAIAAgACAAIAAxACAALQAgAFUAcABwAGUAcgAgAHIAaQBnAGgAdABcAG4AIAAgACAAIAAgACAAIAAgADIAIAAtACAATABvAHcAZQByACAAcgBpAGcAaAB0AFwAbgAgACAAIAAgACAAIAAgACAAMwAgAC0AIABMAG8AdwBlAHIAIABsAGUAZgB0AFwAbgAgACAAIAAgACAAIAAgACAANAAgAC0AIABVAHAAcABlAHIAIABsAGUAZgB0AFwAbgBcAG4AIAAgACAAIABQAHkAcgBhAG0AaQBkACAAZQB4AHQAcgBhAGMAdABpAG8AbgBzACAAYQByAGUAIABtAG8AcwB0ACAAbQBlAGEAbgBpAG4AZwBmAHUAbAAgAG8AbgAgAHMAcQB1AGEAcgBlACAAbwByACAAbgBlAGEAcgARIHMAcQB1AGEAcgBlACAAbQBhAHQAcgBpAGMAZQBzAC4AXABuACAAIAAgACAATwBuACAAdABhAGwAbAAgAG8AcgAgAG4AYQByAHIAbwB3ACAAbQBhAHQAcgBpAGMAZQBzACwAIAB0AGgAZQAgAHIAZQBzAHUAbAB0AGkAbgBnACAAcwBoAGEAcABlAHMAIABtAGEAeQAgAGIAZQAgAHYAaQBzAHUAYQBsAGwAeQAgAHMAawBlAHcAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAHQAbwAgAGUAeAB0AHIAYQBjAHQAIAB0AGgAZQAgAHIAZQBnAGkAbwBuAC4AXABuACAAIAAgACAAWwBwAGkAZQBjAGUAXQAgACAAIAAgACAAIAAtACAASQBuAHQAZQBnAGUAcgAgADEAEyA0ACAAcwBlAGwAZQBjAHQAaQBuAGcAIAB0AGgAZQAgAHAAeQByAGEAbQBpAGQAIAByAGUAZwBpAG8AbgAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACAALQAgAFMAYwBhAGwAYQByACAAdQBzAGUAZAAgAG8AdQB0AHMAaQBkAGUAIAB0AGgAZQAgAHIAZQBnAGkAbwBuAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABcACIAXAAiAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFAAeQByAGEAbQBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBwAGkAZQBjAGUAXQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABlACAAcABpAGUAYwBlAFwAbgAgACAAIAAgAHAAaQBlAGMAZQAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABpAGUAYwBlACkALAAgADEALAAgAHAAaQBlAGMAZQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABQAGkAZQBjAGUAPwAsACAATwBSACgAcABpAGUAYwBlACAAPAAgADEALAAgAHAAaQBlAGMAZQAgAD4AIAA0ACwAIABJAFMAVABFAFgAVAAoAHAAaQBlAGMAZQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAbABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAXAAiAFwAIgAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAUABpAGUAYwBlAD8ALAAgAFwAIgAjAFAASQBFAEMARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAHkAcgBhAG0AaQBkACAAbQBhAHMAawBzACAAKABjAGwAbwBjAGsAdwBpAHMAZQApAFwAbgAgACAAIAAgAHUAcABwAGUAcgBfAHIAaQBnAGgAdAAsACAAaQAgADwAPQAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgADEAXABuACAAIAAgACAAbABvAHcAZQByAF8AcgBpAGcAaAB0ACwAIABpACAAKwAgAGoAIAA+AD0AIABoACAAKwAgADEALAAgACAALwAvACAAMgBcAG4AIAAgACAAIABsAG8AdwBlAHIAXwBsAGUAZgB0ACwAIAAgAGkAIAA+AD0AIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAFwAbgAgACAAIAAgAHUAcABwAGUAcgBfAGwAZQBmAHQALAAgACAAaQAgACsAIABqACAAPAA9ACAAaAAgACsAIAAxACwAIAAgAC8ALwAgADQAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBlAGcAaQBvAG4AXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACAAIAAgACAAIABJAEYAKABwAGkAZQBjAGUAIAA9ACAAMQAsACAAdQBwAHAAZQByAF8AcgBpAGcAaAB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABwAGkAZQBjAGUAIAA9ACAAMgAsACAAbABvAHcAZQByAF8AcgBpAGcAaAB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHAAaQBlAGMAZQAgAD0AIAAzACwAIABsAG8AdwBlAHIAXwBsAGUAZgB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AHAAcABlAHIAXwBsAGUAZgB0ACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABJAEYAKABtAGEAcwBrACwAIABhAHIAcgBhAHkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcARwAwADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGkAbgBnALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAATQBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhACAAcwBpAG4AZwBsAGUAIAByAGkAbgBnACAAKABsAGEAeQBlAHIAKQAgAGYAcgBvAG0AIABhACAAMgBEACAAZwByAGkAZAAgAHcAaABpAGwAZQAgAHAAcgBlAHMAZQByAHYAaQBuAGcAIAB0AGgAZQAgAG8AdgBlAHIAYQBsAGwAXABuACAAIAAgACAAcwBoAGEAcABlACAAbwBmACAAdABoAGUAIABnAHIAaQBkAC4AIABMAGEAeQBlAHIAIAAxACAAYwBvAHIAcgBlAHMAcABvAG4AZABzACAAdABvACAAdABoAGUAIABvAHUAdABlAHIAbQBvAHMAdAAgAHAAZQByAGkAbQBlAHQAZQByACwAIABhAG4AZAAgAGgAaQBnAGgAZQByAFwAbgAgACAAIAAgAGwAYQB5AGUAcgBzACAAbQBvAHYAZQAgAGkAbgB3AGEAcgBkAC4AIABUAGgAZQAgAG8AdQB0AHAAdQB0ACAAYQBsAHcAYQB5AHMAIABtAGEAdABjAGgAZQBzACAAdABoAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAbwBmACAAdABoAGUAIABpAG4AcAB1AHQAXABuACAAIAAgACAAZwByAGkAZAAsACAAdwBpAHQAaAAgAGEAbABsACAAbgBvAG4AESByAGkAbgBnACAAYwBlAGwAbABzACAAZgBpAGwAbABlAGQAIAB1AHMAaQBuAGcAIABmAGkAbABsAF8AdgBhAGwAdQBlAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAgAHIAZQBwAHIAZQBzAGUAbgB0AGkAbgBnACAAdABoAGUAIABmAHUAbABsACAAZwByAGkAZAAuAFwAbgAgACAAIAAgAGwAYQB5AGUAcgAgACAAIAAgACAAIAAgAC0AIABJAG4AdABlAGcAZQByACAAZSIgADEAIABzAHAAZQBjAGkAZgB5AGkAbgBnACAAdwBoAGkAYwBoACAAcgBpAG4AZwAgAHQAbwAgAGUAeAB0AHIAYQBjAHQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABhAHkAZQByAHMAIABlAHgAYwBlAGUAZABpAG4AZwAgAHQAaABlACAAaQBuAG4AZQByAG0AbwBzAHQAIAByAGkAbgBnACAAcgBlAHQAdQByAG4AIABcACIAIwBNAEEAWAAtAEwAQQBZAEUAUgA6ACAAbgBcACIALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAdABvACAAZgBpAGwAbAAgAG4AbwBuABEgcgBpAG4AZwAgAGMAZQBsAGwAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFQAaABpAHMAIABmAHUAbgBjAHQAaQBvAG4AIABwAGUAcgBmAG8AcgBtAHMAIABuAG8AIAByAG8AdABhAHQAaQBvAG4AOwAgAGkAdAAgAG8AbgBsAHkAIABlAHgAdAByAGEAYwB0AHMAIAB0AGgAZQAgAHIAaQBuAGcAIABtAGEAcwBrAC4AXABuACAAIAAgACAAIiAgAEQAZQBnAGUAbgBlAHIAYQB0AGUAIAByAGkAbgBnAHMAIAAoADEA1wBOACwAIABOANcAMQAsACAAMgDXAE4ALAAgAGUAdABjAC4AKQAgAGEAcgBlACAAcAByAGUAcwBlAHIAdgBlAGQAIABlAHgAYQBjAHQAbAB5AC4AXABuACAAIAAgACAAIiAgAFIAaQBuAGcAUgBvAHQAYQB0AGUAuwMgAGEAbgBkACAAUgBpAG4AZwBSAG8AdABhAHQAZQBSAGUAdgC7AyAAcgBlAGwAeQAgAG8AbgAgAFIAaQBuAGcAuwMgAHQAbwAgAGkAZABlAG4AdABpAGYAeQAgAHIAaQBuAGcAIABiAG8AdQBuAGQAYQByAGkAZQBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAaQBuAGcAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAGwAYQB5AGUAcgAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGcAcgBpAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEwAYQB5AGUAcgA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAGwAYQB5AGUAcgApACwAIABsAGEAeQBlAHIAIAA8AD0AIAAwACkALABcAG4AIAAgACAAIABNAGEAeABMAGEAeQBlAHIALAAgACAAIAAgACAAIABJAE4AVAAoACgATQBJAE4AKABoACwAIAB3ACkAIAArACAAMQApACAALwAgADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABnAHIAaQBkACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABcACIAIwAxAEQALQBBAFIAUgBBAFkAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQATABhAHkAZQByAD8ALAAgAFwAIgAjAEwAQQBZAEUAUgAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGEAeQBlAHIAIAA+ACAATQBhAHgATABhAHkAZQByACwAIABcACIAIwBNAEEAWAAtAEwAQQBZAEUAUgA6ACAAXAAiACAAJgAgAE0AYQB4AEwAYQB5AGUAcgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAbABsAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgADAALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBpAG4AZwAgAGUAZABnAGUAcwBcAG4AIAAgACAAIAB0AG8AcAAsACAAIAAgACAAIAAgACAAIAAgACgAKABpACAAPQAgAGwAYQB5AGUAcgApACAAKwAgACgAaQAgAD0AIAAxACAAKwAgAGgAIAAtACAAbABhAHkAZQByACkAKQAgACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoACgAagAgAD4AIABsAGEAeQBlAHIAIAAtACAAMQApACAAKgAgACgAagAgADwAPQAgADEAIAArACAAdwAgAC0AIABsAGEAeQBlAHIAKQApACwAXABuAFwAbgAgACAAIAAgAHMAaQBkAGUALAAgACAAIAAgACAAIAAgACAAKAAoAGoAIAA9ACAAbABhAHkAZQByACkAIAArACAAKABqACAAPQAgADEAIAArACAAdwAgAC0AIABsAGEAeQBlAHIAKQApACAAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAKABpACAAPgAgAGwAYQB5AGUAcgAgAC0AIAAxACkAIAAqACAAKABpACAAPAA9ACAAMQAgACsAIABoACAALQAgAGwAYQB5AGUAcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AYgBpAG4AZQBkACAAcgBpAG4AZwAgAG0AYQBzAGsAXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAdABvAHAAIAArACAAcwBpAGQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEcAMAA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBxAHUAYQByAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABDAEcAcgBpAGQAuwMsACAAUwBxAHUAZQBlAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAHMAcQB1AGEAcgBlABEgcwBoAGEAcABlAGQAIAByAGUAZwBpAG8AbgAgACgAQwBoAGUAYgB5AHMAaABlAHYAIAByAGEAZABpAHUAcwApACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAHkAXABuACAAIAAgACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAbgAgAGUAeAB0AGUAbgBkACAAdgBhAGwAdQBlAC4AIABUAGgAZQAgAGMAZQBuAHQAZQByACAAbQBhAHkAIABiAGUAIABnAGkAdgBlAG4AIABhAHMAIABhAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABhAHMAIABlAHgAcABsAGkAYwBpAHQAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AIABUAGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkACAAcgBlAGcAaQBvAG4AXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBlAHMAIABpAHQAcwAgAGcAZQBvAG0AZQB0AHIAaQBjACAAcwBoAGEAcABlACwAIABhAG4AZAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAG8AbgBsAHkAIABmAGkAbABsAF8AdgBhAGwAdQBlAFwAbgAgACAAIAAgAGEAcgBlACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAdABhAHIAZwBlAHQAIAAgACAAIAAgACAALQAgAEMAZQBuAHQAZQByACAAbwBmACAAdABoAGUAIABzAHEAdQBhAHIAZQAuACAATQBhAHkAIABiAGUAIABhACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAG8AcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBmACAAdABoAGUAIABmAG8AcgBtACAAewByAG8AdwAsACAAYwBvAGwAfQAuAFwAbgAgACAAIAAgAGUAeAB0AGUAbgBkACAAIAAgACAAIAAgAC0AIABDAGgAZQBiAHkAcwBoAGUAdgAgAHIAYQBkAGkAdQBzACAAbwBmACAAdABoAGUAIABzAHEAdQBhAHIAZQAgACgAbQB1AHMAdAAgAGIAZQAgAGEAIABwAG8AcwBpAHQAaQB2AGUAIABpAG4AdABlAGcAZQByACkALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAcwBxAHUAYQByAGUALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADAALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBxAHUAYQByAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACwAXABuACAAIAAgACAAZQB4AHQAZQBuAGQALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAYQByAGcAZQB0ACAAaQBuAHQAZQByAHAAcgBlAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBJAF8ASgA/ACwAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUACgAdABhAHIAZwBlAHQAKQAgAD0AIAAyACwAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAFQAQQBLAEUAKAB0AGEAcgBnAGUAdAAsACAALQAxACwAIAAtADEAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAdABjAGgAIABmAG8AcgAgAHMAYwBhAGwAYQByACAAdABhAHIAZwBlAHQAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABnAHIAaQBkACAAPQAgAHQAYQByAGcAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHAAdQB0ACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABFAHgAdABlAG4AZAA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAGUAeAB0AGUAbgBkACkALAAgAGUAeAB0AGUAbgBkACAAPAAgADEAKQAsAFwAbgAgACAAIAAgAE4AbwBUAGEAcgBnAGUAdAA/ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEYAQQBMAFMARQAsACAATgBPAFQAKABPAFIAKABiAG8AbwBsACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAGwAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABFAHgAdABlAG4AZAA/ACwAIABcACIAIwBFAFgAVABFAE4ARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AVABhAHIAZwBlAHQAPwAsACAAXAAiACMAVABBAFIARwBFAFQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATQBlAHMAaAAgAGcAcgBpAGQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAaQAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABpACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAagAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABqACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAcQB1AGEAcgBlACAAbQBhAHMAawAgACgAQwBoAGUAYgB5AHMAaABlAHYAIABkAGkAcwB0AGEAbgBjAGUAKQBcAG4AIAAgACAAIABtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgACgAQQBCAFMAKABpACAALQAgAHgAKQAgADwAPQAgAGUAeAB0AGUAbgBkACkAIAAqACAAKABBAEIAUwAoAGoAIAAtACAAeQApACAAPAA9ACAAZQB4AHQAZQBuAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYQBuAGQAIABzAHEAdQBlAGUAegBlAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAUwBxAHUAZQBlAHoAZQC7AygASQBGACgAbQBhAHMAawAsACAAZwByAGkAZAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEcAMAA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVAByAGkAYQBuAGcAbABlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAARwBlAG8AbQBlAHQAcgB5AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQwBHAHIAaQBkALsDLAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAIABkAGkAcgBlAGMAdABpAG8AbgBhAGwAIAB0AHIAaQBhAG4AZwB1AGwAYQByACAAcgBlAGcAaQBvAG4AIAAoAHUAcABwAGUAcgAgAG8AcgAgAGwAbwB3AGUAcgApACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAHkAXABuACAAIAAgACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABhAG4AZAAgAGEAIABNAGEAbgBoAGEAdAB0AGEAbgAgAHIAYQBkAGkAdQBzAC4AIABUAGgAZQAgAGMAZQBuAHQAZQByACAAbQBhAHkAIABiAGUAIABnAGkAdgBlAG4AIABhAHMAIABhAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABhAHMAIABlAHgAcABsAGkAYwBpAHQAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIAB7AHIAbwB3ACwAIABjAG8AbAB9AC4AIABUAGgAZQAgAGUAeAB0AHIAYQBjAHQAZQBkACAAcgBlAGcAaQBvAG4AXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBlAHMAIABpAHQAcwAgAGcAZQBvAG0AZQB0AHIAaQBjACAAcwBoAGEAcABlACwAIABhAG4AZAAgAHIAbwB3AHMALwBjAG8AbAB1AG0AbgBzACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAG8AbgBsAHkAIABmAGkAbABsAF8AdgBhAGwAdQBlAFwAbgAgACAAIAAgAGEAcgBlACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAdABhAHIAZwBlAHQAIAAgACAAIAAgACAALQAgAEMAZQBuAHQAZQByACAAbwBmACAAdABoAGUAIAB0AHIAaQBhAG4AZwBsAGUALgAgAE0AYQB5ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByACAAYwByAGkAdABlAHIAaQBvAG4AIABvAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQAgAHsAcgBvAHcALAAgAGMAbwBsAH0ALgBcAG4AIAAgACAAIAByAGEAZABpAHUAcwAgACAAIAAgACAAIAAtACAATQBhAG4AaABhAHQAdABhAG4AIAByAGEAZABpAHUAcwAgAG8AZgAgAHQAaABlACAAdAByAGkAYQBuAGcAbABlACAAKABtAHUAcwB0ACAAYgBlACAAYQAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAKQAuAFwAbgAgACAAIAAgAFsAYgBlAGwAbwB3AF0AIAAgACAAIAAgAC0AIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgBzACAAdABoAGUAIABsAG8AdwBlAHIAIAB0AHIAaQBhAG4AZwBsAGUAOwAgAGkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHIAZQB0AHUAcgBuAHMAIAB1AHAAcABlAHIALgBcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdAByAGkAYQBuAGcAbABlAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAwAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAcgBpAGEAbgBnAGwAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABnAHIAaQBkACwAXABuACAAIAAgACAAdABhAHIAZwBlAHQALABcAG4AIAAgACAAIAByAGEAZABpAHUAcwAsAFwAbgAgACAAIAAgAFsAYgBlAGwAbwB3AF0ALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZwByAGkAZAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAZwByAGkAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAYQByAGcAZQB0ACAAaQBuAHQAZQByAHAAcgBlAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBJAF8ASgA/ACwAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUACgAdABhAHIAZwBlAHQAKQAgAD0AIAAyACwAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAAVABBAEsARQAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAFQAQQBLAEUAKAB0AGEAcgBnAGUAdAAsACAALQAxACwAIAAtADEAKQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAdABjAGgAIABmAG8AcgAgAHMAYwBhAGwAYQByACAAdABhAHIAZwBlAHQAXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAARgBBAEwAUwBFACwAIABnAHIAaQBkACAAPQAgAHQAYQByAGcAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHAAdQB0ACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABSAGEAZABpAHUAcwA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAHIAYQBkAGkAdQBzACkALAAgAHIAYQBkAGkAdQBzACAAPAAgADEAKQAsAFwAbgAgACAAIAAgAE4AbwBUAGEAcgBnAGUAdAA/ACwAIAAgACAAIAAgACAASQBGACgASQBzAEkAXwBKAD8ALAAgAEYAQQBMAFMARQAsACAATgBPAFQAKABPAFIAKABiAG8AbwBsACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAMAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuACAAIAAgACAASQBzAEEAYgBvAHYAZQA/ACwAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGIAZQBsAG8AdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAGcAcgBpAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABSAGEAZABpAHUAcwA/ACwAIABcACIAIwBSAEEARABJAFUAUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AVABhAHIAZwBlAHQAPwAsACAAXAAiACMAVABBAFIARwBFAFQAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATQBlAHMAaAAgAGcAcgBpAGQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBHAHIAaQBkALsDKABnAHIAaQBkACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAG4AdABlAHIAIABjAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAaQAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABpACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMASQBfAEoAPwAsACAASQBOAEQARQBYACgAagAsACAAcgAsACAAYwApACwAIABUAE8AQwBPAEwAKABJAEYAKABiAG8AbwBsACwAIABqACwAIABOAEEAKAApACkALAAgADIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuACAAbQBhAHMAawBcAG4AIAAgACAAIABkAGkAcgAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBBAGIAbwB2AGUAPwAsACAAKABpACAAPAA9ACAAeAApACwAIAAoAGkAIAA+AD0AIAB4ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAHIAaQBhAG4AZwBsAGUAIABtAGEAcwBrACAAKABNAGEAbgBoAGEAdAB0AGEAbgAgAGQAaQBzAHQAYQBuAGMAZQAgACsAIABkAGkAcgBlAGMAdABpAG8AbgApAFwAbgAgACAAIAAgAG0AYQBzAGsALAAgACAAIAAgACAAIAAgACAAKABBAEIAUwAoAGkAIAAtACAAeAApACAAKwAgAEEAQgBTACgAagAgAC0AIAB5ACkAIAA8AD0AIAByAGEAZABpAHUAcwApACAAKgAgAGQAaQByACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABhAG4AZAAgAHMAcQB1AGUAZQB6AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABTAHEAdQBlAGUAegBlALsDKABJAEYAKABtAGEAcwBrACwAIABnAHIAaQBkACwAIABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACMAIwAgADAAMwAgAC0AIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACAAKgAvAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGgAYQBwAGkAbgBnACAAZgB1AG4AYwB0AGkAbwBuAHMAIAByAGUAcwBoAGEAcABlACwAIAByAGUAcwBpAHoAZQAsACAAdwByAGEAcAAsACAAcABhAGQALAAgAHQAcgBhAHYAZQByAHMAZQAsACAAbwByACAAcgBlAGYAbABvAHcAIABnAHIAaQBkAHMAIAB3AGgAaQBsAGUAXABuACAAIAAgACAAcAByAGUAcwBlAHIAdgBpAG4AZwAgAHQAaABlACAAcwB0AHIAdQBjAHQAdQByAGUAIABvAGYAIAB0AGgAZQAgAHUAbgBkAGUAcgBsAHkAaQBuAGcAIABkAGEAdABhAC4AXABuAFwAbgAgACAAIAAgAFMAdQBiACAAYwBhAHQAZQBnAG8AcgBpAGUAcwA6AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABDAG8AcgBlACAAUwBoAGEAcABpAG4AZwAgAFAAcgBpAG0AaQB0AGkAdgBlAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAUwBoAGEAcABlADIARAC7AywAIABSAGUAcwBpAHoAZQC7AywAIABTAGMAYQBuADIARAC7AywAIABUAHIAYQB2AGUAcgBzAGUAuwMsACAAVABhAGsAZQBCAGwAbwBjAGsAuwMsACAARABTAHQAYQBjAGsAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUgBlAGYAbABvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABXAHIAYQBwAFIAbwB3AHMAMgBEALsDLAAgAFcAcgBhAHAAQwBvAGwAcwAyAEQAuwMsACAAUwB0AGEAaQByAGMAYQBzAGUAuwMsACAAVQBuAFAAaQB2AG8AdAC7AywAIABaAGkAcAC7AywAIABTAGwAaQBjAGUAQgB5AEQAZQBnALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAZAC7AywAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AywAIABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABJAG4AdABlAHIAcABvAGwAYQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBhAGcAbgBpAGYAeQC7AywAIABaAG8AbwBtALsDXABuAFwAbgAgACAAIAAgAEEAbABsACAAcwBoAGEAcABpAG4AZwAgAGYAdQBuAGMAdABpAG8AbgBzACAAcAByAGUAcwBlAHIAdgBlACAAMgBEACAAZwBlAG8AbQBlAHQAcgB5ACAAYQBuAGQAIAByAGUAdAB1AHIAbgAgAGEAcgByAGEAeQBzACAAdwBoAG8AcwBlACAAcwB0AHIAdQBjAHQAdQByAGUAXABuACAAIAAgACAAaQBzACAAZQB4AHAAbABpAGMAaQB0AGwAeQAgAGQAZQBmAGkAbgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBhAG4AcwBmAG8AcgBtAGEAdABpAG8AbgAgAHIAdQBsAGUAcwAuAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8ALwAgACAAQwBvAHIAZQAgAFMAaABhAHAAaQBuAGcAIABQAHIAaQBtAGkAdABpAHYAZQBzAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGUAUwBoAGEAcABlADIARAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBzAGgAYQBwAGUAcwAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYQAgAG4AZQB3ACAAYwBvAGwAdQBtAG4AIAB3AGkAZAB0AGgAIAB1AHMAaQBuAGcAIAByAG8AdwARIG0AYQBqAG8AcgAgAG8AcgBkAGUAcgAuACAAQQBsAGwAIAB2AGEAbAB1AGUAcwBcAG4AIAAgACAAIABhAHIAZQAgAHAAcgBlAHMAZQByAHYAZQBkACAAaQBuACAAcgBlAGEAZABpAG4AZwAgAG8AcgBkAGUAcgAsACAAYQBuAGQAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAGIAbABvAGMAawAgAGkAcwAgAHAAYQBkAGQAZQBkACAAaQBmACAAbgBlAGUAZABlAGQALgBcAG4AIAAgACAAIABPAG4AZQARIGQAaQBtAGUAbgBzAGkAbwBuAGEAbAAgAGEAcgByAGEAeQBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQALgBcAG4AXABuAEUAeABhAG0AcABsAGUAOgBcAG4AIAAgACAAIABJAG4AcAB1AHQAOgBcAG4AIAAgACAAIAAgACAAIAAgAHsAMQAsADIALAAzACwANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAA1ACwANgAsADcALAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgADkALAAxADAALAAxADEALAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMQAzACwAMQA0ACwAMQA1ACwAMQA2AH0AXABuAFwAbgAgACAAIAAgAD0AUgBlAFMAaABhAHAAZQAyAEQAuwMoAGEAcgByAGEAeQAsACAAMgApAFwAbgBcAG4AIAAgACAAIABPAHUAdABwAHUAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAewAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAzACwANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAA1ACwANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAA3ACwAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAA5ACwAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgADEAMQAsADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAxADMALAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMQA1ACwAMQA2AH0AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAcgBlAHMAaABhAHAAZQAuACAATwBuAGUAESBkAGkAbQBlAG4AcwBpAG8AbgBhAGwAIABhAHIAcgBhAHkAcwAgAGEAcgBlACAAcgBlAGoAZQBjAHQAZQBkAC4AXABuACAAIAAgACAAbgBlAHcAXwB3AGkAZAB0AGgAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIAByAGUAcwBoAGEAcABlAGQAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0AIAAgACAALQAgAFMAYwBhAGwAYQByACAAdQBzAGUAZAAgAHQAbwAgAGYAaQBsAGwAIABpAG4AYwBvAG0AcABsAGUAdABlACAAZgBpAG4AYQBsACAAcgBvAHcAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAATgBBACgAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQBzAGgAYQBwAGkAbgBnACAAaQBzACAAcABlAHIAZgBvAHIAbQBlAGQAIABzAHQAcgBpAGMAdABsAHkAIABpAG4AIAByAG8AdwARIG0AYQBqAG8AcgAgAG8AcgBkAGUAcgAuAFwAbgAgACAAIAAgACIgIABuAGUAdwBfAHcAaQBkAHQAaAAgAG0AdQBzAHQAIABiAGUAIABsAGUAcwBzACAAdABoAGEAbgAgAG8AcgAgAGUAcQB1AGEAbAAgAHQAbwAgAHQAaABlACAAbwByAGkAZwBpAG4AYQBsACAAdwBpAGQAdABoAC4AXABuACAAIAAgACAAIiAgAFQAaABpAHMAIABmAHUAbgBjAHQAaQBvAG4AIABkAG8AZQBzACAAbgBvAHQAIABmAGwAYQB0AHQAZQBuACAAbwByACAAcgBlABEgdwByAGEAcAAgADEARAAgAGEAcgByAGEAeQBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBTAGgAYQBwAGUAMgBEALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACwAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABDAE8AVQBOAFQAQQAoAGEAcgByAGEAeQApACAALwAgAG4AZQB3AF8AdwBpAGQAdABoACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAGQAZABpAG4AZwBcAG4AIAAgACAAIABwAGEAZABfAHcAaQB0AGgALAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABhAGQAXwB3AGkAdABoACkALAAgAE4AQQAoACkALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAVwBpAGQAdABoACwAIAAgACAAbgBlAHcAXwB3AGkAZAB0AGgAIAA+ACAAdwAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAZQBjAHQAbwByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIABoACAAPgAgAHcALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAYQByAHIAYQB5ACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAVwBpAGQAdABoACwAIABcACIAIwBXAEkARABUAEgAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAQwBFAEkATABJAE4ARwAoAFMARQBRAFUARQBOAEMARQAoAG4AZQB3AF8AaABlAGkAZwBoAHQALAAgAG4AZQB3AF8AdwBpAGQAdABoACkAIAAvACAAdwAsACAAMQApACkALABcAG4AXABuACAAIAAgACAAbQBvAGQAdQBsAG8ALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAE0ATwBEACgAUwBFAFEAVQBFAE4AQwBFACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAbgBlAHcAXwB3AGkAZAB0AGgAKQAsACAAdwApACkALABcAG4AXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAG0AbwBkAHUAbABvACgAKQAgAD0AIAAwACwAIAB3ACwAIABtAG8AZAB1AGwAbwAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAcgBlAHMAZQBuAHQAXABuACAAIAAgACAAcgBlAHMAaABhAHAAZQBkACwAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpACgAKQAsACAAagAoACkAKQAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAaABhAHAAZQBkAFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGUAcwBpAHoAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBwAGUAYQB0AHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAdgBlAHIAdABpAGMAYQBsAGwAeQAgAGEAbgBkAC8AbwByACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkAIABiAHkAIABpAG4AdABlAGcAZQByACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAuAFwAbgAgACAAIAAgAFUAcwBlAHIAcwAgAG0AYQB5ACAAcwBwAGUAYwBpAGYAeQAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgALAAgAG8AcgAgAGIAbwB0AGgALgAgAEkAZgAgAGUAaQB0AGgAZQByACAAcABhAHIAYQBtAGUAdABlAHIAIABpAHMAIABvAG0AaQB0AHQAZQBkACwAXABuACAAIAAgACAAdABoAGUAIABvAG0AaQB0AHQAZQBkACAAZABpAG0AZQBuAHMAaQBvAG4AIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAxAC4AIABHAGUAbwBtAGUAdAByAHkAIABpAHMAIABwAHIAZQBzAGUAcgB2AGUAZAA7ACAAbgBvACAAZgBsAGEAdAB0AGUAbgBpAG4AZwBcAG4AIAAgACAAIABvAGMAYwB1AHIAcwAuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQA6AFwAbgAgACAAIAAgAEkAbgBwAHUAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAewAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAzACwANAB9AFwAbgBcAG4AIAAgACAAIAA9AFIAZQBzAGkAegBlALsDKABhAHIAcgBhAHkALAAgADIALAAgADMAKQBcAG4AXABuACAAIAAgACAATwB1AHQAcAB1AHQAOgBcAG4AIAAgACAAIAAgACAAIAAgAHsAMQAsADIALAAxACwAMgAsADEALAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgADMALAA0ACwAMwAsADQALAAzACwANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAxACwAMgAsADEALAAyACwAMQAsADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMwAsADQALAAzACwANAAsADMALAA0AH0AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAYgBlACAAcgBlAHAAZQBhAHQAZQBkAC4AXABuACAAIAAgACAAWwBoAGUAaQBnAGgAdABdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAdgBlAHIAdABpAGMAYQBsACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADEALgBcAG4AIAAgACAAIABbAHcAaQBkAHQAaABdACAAIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgADEALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABSAGUAcABlAHQAaQB0AGkAbwBuACAAaQBzACAAcABlAHIAZgBvAHIAbQBlAGQAIAB2AGkAYQAgAGkAbgBkAGUAeAAgAHIAZQBtAGEAcABwAGkAbgBnAC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAZwBlAG8AbQBlAHQAcgB5ACAAaQBzACAAKABoACAA1wAgAGgAZQBpAGcAaAB0ACkAIABiAHkAIAAoAHcAIADXACAAdwBpAGQAdABoACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBlAHMAaQB6AGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBoAGUAaQBnAGgAdABdACwAXABuACAAIAAgACAAWwB3AGkAZAB0AGgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBtAGkAcwBzAGkAbwBuACAAYwBoAGUAYwBrAHMAXABuACAAIAAgACAASABlAGkAZwBoAHQATwBtAGkAdAB0AGUAZAA/ACwAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAaABlAGkAZwBoAHQAKQAsAFwAbgAgACAAIAAgAFcAaQBkAHQAaABPAG0AaQB0AHQAZQBkAD8ALAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAHcAaQBkAHQAaAApACwAXABuACAAIAAgACAATgBvAEgAVwBJAG4AcAB1AHQAPwAsACAAIAAgACAAIAAgAEgAZQBpAGcAaAB0AE8AbQBpAHQAdABlAGQAPwAgACsAIABXAGkAZAB0AGgATwBtAGkAdAB0AGUAZAA/ACAAPQAgADIALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAYQB1AGwAdAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMAXABuACAAIAAgACAAaABlAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAE4AbwBIAFcASQBuAHAAdQB0AD8ALAAgAEgAZQBpAGcAaAB0AE8AbQBpAHQAdABlAGQAPwApACwAIAAxACwAIABoAGUAaQBnAGgAdAApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAE4AbwBIAFcASQBuAHAAdQB0AD8ALAAgAFcAaQBkAHQAaABPAG0AaQB0AHQAZQBkAD8AKQAsACAAMQAsACAAdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAATgBvAFIAZQBwAGUAYQB0AD8ALAAgACAAIAAgACAAIAAgAEEATgBEACgAaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABFAHgAcABhAG4AZABTAGMAYQBsAGEAcgAsACAAIAAgACAARQBYAFAAQQBOAEQAKABhAHIAcgBhAHkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgALAAgAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAUgBlAHAAZQBhAHQAPwAsACAAIABPAFIAKABJAFMAVABFAFgAVAAoAGgAZQBpAGcAaAB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKAB3AGkAZAB0AGgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABBAE4ARAAoAEkAUwBOAFUATQBCAEUAUgAoAGgAZQBpAGcAaAB0ACkALAAgAGgAZQBpAGcAaAB0ACAAPAA9ACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgASQBTAE4AVQBNAEIARQBSACgAdwBpAGQAdABoACkALAAgACAAdwBpAGQAdABoACAAPAA9ACAAMAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAE4AbwBSAGUAcABlAGEAdAA/ACwAIABhAHIAcgBhAHkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAARQB4AHAAYQBuAGQAUwBjAGEAbABhAHIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAUgBlAHAAZQBhAHQAPwAsACAAYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBkAGUAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAIAAqACAAaABlAGkAZwBoAHQALABcAG4AIAAgACAAIABrAIIgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwAgACoAIAB3AGkAZAB0AGgALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAaQBjAGUAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAMQAgACsAIABNAE8ARAAoAFMARQBRAFUARQBOAEMARQAoAGsALAAsADAALAApACwAIABoACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAGsAgiAsACAAMQAsACAAMAApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAAxACAAKwAgAE0ATwBEACgAUwBFAFEAVQBFAE4AQwBFACgALAAgAGsAgiAsACAAMAApACwAIAB3ACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAawAsACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgBzAHQAcgB1AGMAdAAgAHIAZQBwAGUAYQB0AGUAZAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpACgAKQAsACAAagAoACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBjAGEAbgAyAEQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAUwBoAGEAcABlADIARAC7AywAIABUAHIAYQB2AGUAcgBzAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAIAB0AHIAYQB2AGUAcgBzAGEAbAARIGEAdwBhAHIAZQAgADIARAAgAHMAYwBhAG4AbgBpAG4AZwAgAG8AcABlAHIAYQB0AG8AcgAgAHQAaABhAHQAIABlAHgAdABlAG4AZABzACAARQB4AGMAZQBsABkgcwAgAG4AYQB0AGkAdgBlACAAUwBDAEEATgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALgAgAFMAYwBhAG4AMgBEALsDIABzAHUAcABwAG8AcgB0AHMAIABmAGkAdgBlACAAdAByAGEAdgBlAHIAcwBhAGwAIABtAG8AZABlAHMALAAgAGEAbABsAG8AdwBpAG4AZwAgAGEAYwBjAHUAbQB1AGwAYQB0AGkAbwBuACAAdABvAFwAbgAgACAAIAAgAGIAZQBnAGkAbgAgAGEAdAAgAGQAaQBmAGYAZQByAGUAbgB0ACAAYwBvAHIAbgBlAHIAcwAgAGEAbgBkACAAcAByAG8AYwBlAGUAZAAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAbwByAGQAZQByAHMALgAgAEYAbwByACAAMgBEACAAYQByAHIAYQB5AHMALABcAG4AIAAgACAAIABnAGUAbwBtAGUAdAByAHkAIABpAHMAIABwAHIAZQBzAGUAcgB2AGUAZAAuAFwAbgBcAG4AIAAgACAAIABGAG8AcgAgADEARAAgAGEAcgByAGEAeQBzACwAIABTAGMAYQBuADIARAC7AyAAYgBlAGgAYQB2AGUAcwAgAGwAaQBrAGUAIABuAGEAdABpAHYAZQAgAFMAQwBBAE4ALAAgAHcAaQB0AGgAIABvAHAAdABpAG8AbgBhAGwAIAByAGUAdgBlAHIAcwBlAFwAbgAgACAAIAAgAG8AcgBkAGUAcgAgAHcAaABlAG4AIABkAGkAcgBlAGMAdABpAG8AbgAgAD0AIAAtADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACAAIAAtACAAUwBhAG0AZQAgAG0AZQBhAG4AaQBuAGcAIABhAHMAIABuAGEAdABpAHYAZQAgAFMAQwBBAE4ALgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AIABTAGMAYQBsAGEAcgBzACAAYQBuAGQAIAAxAEQAIAB2AGUAYwB0AG8AcgBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAgAHcAaQB0AGgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBzAHQAcgBpAGMAdABlAGQAIABkAGkAcgBlAGMAdABpAG8AbgAgAHMAZQBtAGEAbgB0AGkAYwBzAC4AXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACAAIAAgACAAIAAgACAALQAgAFMAYQBtAGUAIABtAGUAYQBuAGkAbgBnACAAYQBzACAAbgBhAHQAaQB2AGUAIABTAEMAQQBOAC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAGQAaQByAGUAYwB0AGkAbwBuAF0AIAAgACAAIAAtACAAVAByAGEAdgBlAHIAcwBhAGwAIABjAG8AZABlAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAwACAAKABzAHQAYQBuAGQAYQByAGQAIAByAG8AdwARIG0AYQBqAG8AcgApAC4AXABuAFwAbgBEAGkAcgBlAGMAdABpAG8AbgAgAEMAbwBkAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAMAAgACAAIAAtACAAUwB0AGEAbgBkAGEAcgBkACAAcgBvAHcAESBtAGEAagBvAHIAIAAoAGwAZQBmAHQAIACSISAAcgBpAGcAaAB0ACwAIAB0AG8AcAAgAJIhIABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgAC0AMQAgACAAIAAtACAAQwBvAGwAdQBtAG4AESBtAGEAagBvAHIAIABmAHIAbwBtACAATgBXACAAYwBvAHIAbgBlAHIAIAAoAHQAbwBwACAAkiEgAGIAbwB0AHQAbwBtACwAIABsAGUAZgB0ACAAkiEgAHIAaQBnAGgAdAApAFwAbgAgACAAIAAgACAAIAAgACAAMQAgACAAIAAtACAATgBFACAAdAByAGEAdgBlAHIAcwBhAGwAIAAoAGMAbwBsAHUAbQBuABEgbQBhAGoAbwByACkAXABuACAAIAAgACAAIAAgACAAIAAyACAAIAAgAC0AIABTAEUAIAB0AHIAYQB2AGUAcgBzAGEAbAAgACgAYwBvAGwAdQBtAG4AESBtAGEAagBvAHIALAAgAGIAbwB0AHQAbwBtACAAkiEgAHQAbwBwACkAXABuACAAIAAgACAAIAAgACAAIAAzACAAIAAgAC0AIABTAFcAIAB0AHIAYQB2AGUAcgBzAGEAbAAgACgAcgBvAHcAESBtAGEAagBvAHIALAAgAHIAaQBnAGgAdAAgAJIhIABsAGUAZgB0ACkAXABuAFwAbgBFAHIAcgBvAHIAIABDAG8AbgBkAGkAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAFwAIgAjAGQAaQByAGUAYwB0AGkAbwBuACEAXAAiACAALQAgAEkAbgB2AGEAbABpAGQAIABkAGkAcgBlAGMAdABpAG8AbgAgAGYAbwByACAAMQBEACAAYQByAHIAYQB5AHMAIABvAHIAIAB1AG4AcgBlAGMAbwBnAG4AaQB6AGUAZAAgAGMAbwBkAGUALgBcAG4AIAAgACAAIAAiICAAMQBEACAAYQByAHIAYQB5AHMAIABvAG4AbAB5ACAAcwB1AHAAcABvAHIAdAAgAGQAaQByAGUAYwB0AGkAbwBuACAAPQAgADAAIAAoAGYAbwByAHcAYQByAGQAKQAgAG8AcgAgAC0AMQAgACgAcgBlAHYAZQByAHMAZQApAC4AXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIABiAHkAcABhAHMAcwAgAHQAcgBhAHYAZQByAHMAYQBsACAAYQBuAGQAIAB1AHMAZQAgAG4AYQB0AGkAdgBlACAAUwBDAEEATgAgAGQAaQByAGUAYwB0AGwAeQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgADIARAAgAHQAcgBhAHYAZQByAHMAYQBsACAAdQBzAGUAcwAgAFQAcgBhAHYAZQByAHMAZQC7AyAAdABvACAAcgBlAG8AcgBkAGUAcgAgAHQAaABlACAAYQByAHIAYQB5ACwAIABTAEMAQQBOACAAdABvACAAYQBjAGMAdQBtAHUAbABhAHQAZQAsAFwAbgAgACAAIAAgACAAIABhAG4AZAAgAFIAZQBTAGgAYQBwAGUAMgBEALsDIAB0AG8AIAByAGUAcwB0AG8AcgBlACAAbwByAGkAZwBpAG4AYQBsACAAZwBlAG8AbQBlAHQAcgB5AC4AXABuACAAIAAgACAAIiAgAE4AbwAgAGYAbABhAHQAdABlAG4AaQBuAGcAIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAA7ACAAZwBlAG8AbQBlAHQAcgB5ACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBjAGEAbgAyAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHYAYQBsAHUAZQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAFsAZABpAHIAZQBjAHQAaQBvAG4AXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgADAAKQBcAG4AIAAgACAAIABkAGkAcgBlAGMAdABpAG8AbgAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZABpAHIAZQBjAHQAaQBvAG4AKQAsACAAMAAsACAAZABpAHIAZQBjAHQAaQBvAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAG4AESAyAEQAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAMQBEAEQAaQByAD8ALAAgACAAIAAgACAAQQBOAEQAKABJAHMAMQBEAD8ALAAgAGQAaQByAGUAYwB0AGkAbwBuACAAPAA+ACAAMAAsACAAZABpAHIAZQBjAHQAaQBvAG4AIAA8AD4AIAAtADEAKQAsAFwAbgAgACAAIAAgAEkAcwBSAGUAdgBlAHIAcwBlAD8ALAAgACAAIAAgACAAIAAgACAAZABpAHIAZQBjAHQAaQBvAG4AIAA9ACAALQAxACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAEkAcwAxAEQAPwAsACAAaAAgAD4AIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAMQBEACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABoACwAIAB3ACkALABcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAGUALAAsACAAZQAsACAALQAxACkALABcAG4AIAAgACAAIAByAGUAdgBfAGEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpAGQAeAApACwAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAsACAAaQBkAHgAKQApACwAXABuACAAIAAgACAAdgBlAGMAdABvAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUgBlAHYAZQByAHMAZQA/ACwAIAByAGUAdgBfAGEAcgByAGEAeQAsACAAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAUwBDAEEATgAoAGkAbgBpAHQAaQBhAGwAXwB2AGEAbAB1AGUALAAgAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkADEARABEAGkAcgA/ACwAIABcACIAIwBkAGkAcgBlAGMAdABpAG8AbgAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABTAEMAQQBOACgAaQBuAGkAdABpAGEAbABfAHYAYQBsAHUAZQAsACAAdgBlAGMAdABvAHIALAAgAGYAdQBuAGMAdABpAG8AbgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBOAEEAKABYAE0AQQBUAEMASAAoAGQAaQByAGUAYwB0AGkAbwBuACwAIAB7AC0AMQA7ADAAOwAxADsAMgA7ADMAOwBcACIATgBFAFwAIgA7AFwAIgBTAEUAXAAiADsAXAAiAFMAVwBcACIAfQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAGQAaQByAGUAYwB0AGkAbwBuACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgADIARAAgAHMAYwBhAG4AIABtAG8AZABlAHMAXABuACAAIAAgACAAcwB0AGEAbgBkAGEAcgBkACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMAQwBBAE4AKABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACwAIABhAHIAcgBhAHkALAAgAGYAdQBuAGMAdABpAG8AbgApACkALAAgAC8ALwAgADAAXABuAFwAbgAgACAAIAAgAHMAdABhAG4AZABhAHIAZABfAGIAeQBjAG8AbAAsACAAIAAgACAATABBAE0AQgBEAEEAKABUAFIAQQBOAFMAUABPAFMARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAQwBBAE4AKABpAG4AaQB0AGkAYQBsAF8AdgBhAGwAdQBlACwAIABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQApACwAIABmAHUAbgBjAHQAaQBvAG4AKQApACkALAAgAC8ALwAgAC0AMQBcAG4AXABuACAAIAAgACAAdAByAGEAdgBlAHIAcwBhAGwALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBTAGgAYQBwAGUAMgBEALsDKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEMAQQBOACgAaQBuAGkAdABpAGEAbABfAHYAYQBsAHUAZQAsAFQAcgBhAHYAZQByAHMAZQC7AygAYQByAHIAYQB5ACwAIABkAGkAcgBlAGMAdABpAG8AbgApACwAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB3ACkAKQAsACAALwAvACAAMQAsACAAMgAsACAAMwBcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABtAG8AZABlAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZABpAHIAZQBjAHQAaQBvAG4AIAA9ACAAMAAsACAAIABzAHQAYQBuAGQAYQByAGQAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGQAaQByAGUAYwB0AGkAbwBuACAAPQAgAC0AMQAsACAAcwB0AGEAbgBkAGEAcgBkAF8AYgB5AGMAbwBsACgAKQAsACAAdAByAGEAdgBlAHIAcwBhAGwAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABUAHIAYQB2AGUAcgBzAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAbQBhAHAAcwAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYQAgAG4AZQB3ACAAdAByAGEAdgBlAHIAcwBhAGwAIABvAHIAZABlAHIAIABiAHkAIAByAG8AdABhAHQAaQBuAGcAIAB0AGgAZQAgAHQAcgBhAHYAZQByAHMAYQBsACAAYQB4AGkAcwBcAG4AIAAgACAAIAB0AG8AIABvAG4AZQAgAG8AZgAgAHQAaAByAGUAZQAgAGQAaQBhAGcAbwBuAGEAbAAgAGQAaQByAGUAYwB0AGkAbwBuAHMALgAgAFQAaABlACAAcwBlAGwAZQBjAHQAZQBkACAAYQB4AGkAcwAgAGkAcwAgAHIAZQBtAGEAcABwAGUAZAAgAHQAbwAgAGEAXABuACAAIAAgACAAdABvAHAAESBsAGUAZgB0ABMgYQBuAGMAaABvAHIAZQBkACAAdAByAGEAdgBlAHIAcwBhAGwAIABvAHIAZABlAHIALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgADEARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQALgBcAG4AXABuAEEAYwBjAGUAcAB0AGUAZAAgAEQAaQByAGUAYwB0AGkAbwBuAHMAOgBcAG4AIAAgACAAIAAgACAAXAAiAE4ARQBcACIAIABvAHIAIAAxACAAIACSISAATgBvAHIAdABoAGUAYQBzAHQAIAAgACgAlyEpAFwAbgAgACAAIAAgACAAIABcACIAUwBFAFwAIgAgAG8AcgAgADIAIAAgAJIhIABTAG8AdQB0AGgAZQBhAHMAdAAgACAAKACYISkAXABuACAAIAAgACAAIAAgAFwAIgBTAFcAXAAiACAAbwByACAAMwAgACAAkiEgAFMAbwB1AHQAaAB3AGUAcwB0ACAAIAAoAJkhKQBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAG4AZQB3AF8AYQB4AGkAcwAgACAAIAAtACAARABpAHIAZQBjAHQAaQBvAG4AIABjAG8AZABlACAAKABcACIATgBFAFwAIgAsAFwAIgBTAEUAXAAiACwAXAAiAFMAVwBcACIAKQAgAG8AcgAgAGkAbgB0AGUAZwBlAHIAIAAxABMgMwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEcAZQBvAG0AZQB0AHIAeQAgAGkAcwAgAHAAcgBlAHMAZQByAHYAZQBkADsAIABvAG4AbAB5ACAAdAByAGEAdgBlAHIAcwBhAGwAIABvAHIAZABlAHIAIABjAGgAYQBuAGcAZQBzAC4AXABuACAAIAAgACAAIiAgAEkAbgB2AGEAbABpAGQAIABkAGkAcgBlAGMAdABpAG8AbgAgAGMAbwBkAGUAcwAgAHIAZQB0AHUAcgBuACAAXAAiACMAQQBYAEkAUwAhAFwAIgAuAFwAbgAgACAAIAAgACIgIAAxAEQAIABhAHIAcgBhAHkAcwAgAHIAZQB0AHUAcgBuACAAXAAiACMAMgBEAC0AQQBSAFIAQQBZACEAXAAiAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAcgBhAHYAZQByAHMAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABuAGUAdwBfAGEAeABpAHMALABcAG4AXABuAEkARgAoAE8AUgAoAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgAD0AIAAxACwAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAA9ACAAMQApACwAXAAiACMAMgBEAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEEATgBEACgASQBTAE4AVQBNAEIARQBSACgAbgBlAHcAXwBhAHgAaQBzACkALAAgAE8AUgAoAG4AZQB3AF8AYQB4AGkAcwAgADwAPQAgADAALAAgAG4AZQB3AF8AYQB4AGkAcwAgAD4AIAAzACkAKQAsAFwAIgAjAEEAWABJAFMAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQB4AGkAcwAgAHQAcgBhAHYAZQByAHMAYQBsACAAaQBuAGQAaQBjAGUAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAeABfAE4ARQAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAB3ACwALAAxACwAMAApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAaAApACkALABcAG4AIAAgACAAIAB5AF8ATgBFACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAHcALAAsAHcALAAtADEAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsAGgALAAxACwAMAApACkALABcAG4AXABuACAAIAAgACAAeABfAFMARQAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABoACwALABoACwALQAxACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAB3ACwAMQAsADAAKQApACwAXABuACAAIAAgACAAeQBfAFMARQAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABoACwALAB3ACwAMAApACAAKwAgAFMARQBRAFUARQBOAEMARQAoACwAdwAsADAALAAtADEAKQApACwAXABuAFwAbgAgACAAIAAgAHgAXwBTAFcALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAdwAsACwAaAAsADAAKQAgACsAIABTAEUAUQBVAEUATgBDAEUAKAAsAGgALAAwACwALQAxACkAKQAsAFwAbgAgACAAIAAgAHkAXwBTAFcALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAdwAsACwAMQApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAaAAsADEALAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHgAaQBzACAAbQBvAGQAZQAgAHMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAG0AbwBkAGUALAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAG4AZQB3AF8AYQB4AGkAcwApACwAbgBlAHcAXwBhAHgAaQBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFcASQBUAEMASAAoAG4AZQB3AF8AYQB4AGkAcwAsACAAXAAiAE4ARQBcACIALAAxACwAIABcACIAUwBFAFwAIgAsADIALAAgAFwAIgBTAFcAXAAiACwAMwAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKABtAG8AZABlACwAIAB4AF8ATgBFACwAIAB4AF8AUwBFACwAIAB4AF8AUwBXACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAG0AbwBkAGUALAAgAHkAXwBOAEUALAAgAHkAXwBTAEUALAAgAHkAXwBTAFcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAbQBhAHAAIABhAHIAcgBhAHkAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIAB4ACgAKQAsACAAeQAoACkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABUAGEAawBlAEIAbABvAGMAawC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAE0ARwByAGkAZAC7AywAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAHIAZQBjAHQAYQBuAGcAdQBsAGEAcgAgAGIAbABvAGMAawAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgB5ACAAcwBwAGUAYwBpAGYAeQBpAG4AZwAgAGEAbgAgAGEAbgBjAGgAbwByACAAdgBhAGwAdQBlAFwAbgAgACAAIAAgACgAcwB0AGEAcgB0AF8AYQB0ACkAIABhAG4AZAAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAHMAdABvAHAAcABpAG4AZwAgAHYAYQBsAHUAZQAgACgAcwB0AG8AcABfAHcAaABlAG4AKQAuACAAVABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIABsAG8AYwBhAHQAZQBzAFwAbgAgACAAIAAgAHQAaABlACAAZgBpAHIAcwB0ACAAbwBjAGMAdQByAHIAZQBuAGMAZQAgAG8AZgAgAHMAdABhAHIAdABfAGEAdAAsACAAdABoAGUAbgAgAHIAZQB0AHUAcgBuAHMAIABhAGwAbAAgAHIAbwB3AHMAIABmAHIAbwBtACAAdABoAGEAdAAgAHAAbwBpAG4AdABcAG4AIAAgACAAIABkAG8AdwBuAHcAYQByAGQAIABhAG4AZAAgAGEAbABsACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAHQAaABlACAAcgBpAGcAaAB0ACwAIABzAHQAbwBwAHAAaQBuAGcAIABlAGkAdABoAGUAcgAgAGEAdAAgAHQAaABlACAAZgBpAHIAcwB0AFwAbgAgACAAIAAgAG8AYwBjAHUAcgByAGUAbgBjAGUAIABvAGYAIABzAHQAbwBwAF8AdwBoAGUAbgAgAG8AcgAgAGEAdAAgAHQAaABlACAAZQBuAGQAIABvAGYAIAB0AGgAZQAgAGQAYQB0AGEALgBcAG4AXABuACAAIAAgACAAQgBvAHQAaAAgAHMAdABhAHIAdABfAGEAdAAgAGEAbgBkACAAcwB0AG8AcABfAHcAaABlAG4AIAByAGUAbAB5ACAAbwBuACAARQB4AGMAZQBsACcAcwAgAG4AYQB0AGkAdgBlACAAZQBxAHUAYQBsAGkAdAB5ACAAYwBvAG0AcABhAHIAaQBzAG8AbgBcAG4AIAAgACAAIAAoAGEAcgByAGEAeQAgAD0AIAB0AGUAcgBtACkALgAgAFQAaABpAHMAIABwAHIAbwB2AGkAZABlAHMAIABmAGEAcwB0ACwAIAB2AGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAYwBoAGkAbgBnACAAYgB1AHQAIABkAG8AZQBzACAAbgBvAHQAIABzAHUAcABwAG8AcgB0AFwAbgAgACAAIAAgAHcAaQBsAGQAYwBhAHIAZABzACAAbwByACAAcgBlAGcAdQBsAGEAcgAgAGUAeABwAHIAZQBzAHMAaQBvAG4AcwAuACAASQBmACAAcwB0AG8AcABfAHcAaABlAG4AIABpAHMAIABvAG0AaQB0AHQAZQBkACwAIAB0AGgAZQAgAGIAbABvAGMAawAgAGUAeAB0AGUAbgBkAHMAXABuACAAIAAgACAAdABvACAAdABoAGUAIABiAG8AdAB0AG8AbQAgAG8AZgAgAHQAaABlACAAYQByAHIAYQB5AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAcwB0AGEAcgB0AF8AYQB0ACAAIAAgACAAIAAtACAAQQBuAGMAaABvAHIAIAB2AGEAbAB1AGUAIABtAGEAcgBrAGkAbgBnACAAdABoAGUAIABmAGkAcgBzAHQAIAByAG8AdwAgAG8AZgAgAHQAaABlACAAYgBsAG8AYwBrAC4AXABuACAAIAAgACAAWwBzAHQAbwBwAF8AdwBoAGUAbgBdACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcwB0AG8AcABwAGkAbgBnACAAdgBhAGwAdQBlAC4AIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAB0AGgAZQAgAGIAbABvAGMAawAgAGMAbwBuAHQAaQBuAHUAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAbwAgAHQAaABlACAAZQBuAGQAIABvAGYAIAB0AGgAZQAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEcAZQBvAG0AZQB0AHIAeQAgAGkAcwAgAHAAcgBlAHMAZQByAHYAZQBkADsAIABuAG8AIABmAGwAYQB0AHQAZQBuAGkAbgBnACAAbwBjAGMAdQByAHMALgBcAG4AIAAgACAAIAAiICAASQBmACAAcwB0AGEAcgB0AF8AYQB0ACAAaQBzACAAbgBvAHQAIABmAG8AdQBuAGQALAAgAHIAZQB0AHUAcgBuAHMAIABcACIAIwBOAE8ALQBBAE4AQwBIAE8AUgAhAFwAIgAuAFwAbgAgACAAIAAgACIgIABJAGYAIABzAHQAbwBwAF8AdwBoAGUAbgAgAG8AYwBjAHUAcgBzACAAYgBlAGYAbwByAGUAIABzAHQAYQByAHQAXwBhAHQALAAgAHIAZQB0AHUAcgBuAHMAIABcACIAIwBOAE8ALQBTAEwASQBDAEUAIQBcACIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVABhAGsAZQBCAGwAbwBjAGsAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAcwB0AGEAcgB0AF8AYQB0ACwAXABuACAAIAAgACAAWwBzAHQAbwBwAF8AdwBoAGUAbgBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcwB0AG8AcABwAGkAbgBnACAAcABvAGkAbgB0AFwAbgAgACAAIAAgAEQAbwBOAG8AdABTAHQAbwBwAD8ALAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABzAHQAbwBwAF8AdwBoAGUAbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKABhAHIAcgBhAHkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AYwBhAGwAIABoAGUAbABwAGUAcgBzAFwAbgAgACAAIAAgAEEAbgBjAGgAbwByALsDLAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABhAHIAcgAsACAAYwBvAG4AZABpAHQAaQBvAG4ALAAgAGkAZAB4ACwAIABOACgAYQByAHIAIAA9ACAAYwBvAG4AZABpAHQAaQBvAG4AKQAgACoAIABpAGQAeAApACwAXABuACAAIAAgACAASQBEAFgAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAGEAcgByACwAIABNAEkATgAoAEkARgAoAGEAcgByACAAPAA+ACAAMAAsACAAYQByAHIAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBuAGMAaABvAHIAIABwAG8AcwBpAHQAaQBvAG4AcwBcAG4AIAAgACAAIAByAG8AdwBfAHMAdABhAHIAdAAsACAAIAAgACAAIAAgAEEAbgBjAGgAbwByALsDKABhAHIAcgBhAHkALAAgAHMAdABhAHIAdABfAGEAdAAsACAAaQApACwAXABuACAAIAAgACAAYwBvAGwAXwBzAHQAYQByAHQALAAgACAAIAAgACAAIABBAG4AYwBoAG8AcgC7AygAYQByAHIAYQB5ACwAIABzAHQAYQByAHQAXwBhAHQALAAgAGoAKQAsAFwAbgBcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARABYALsDKAByAG8AdwBfAHMAdABhAHIAdAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEQAWAC7AygAYwBvAGwAXwBzAHQAYQByAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAbwBwAHAAaQBuAGcAIABwAG8AcwBpAHQAaQBvAG4AcwBcAG4AIAAgACAAIAByAG8AdwBfAHMAdABvAHAALAAgACAAIAAgACAAIAAgAEkARgAoAEQAbwBOAG8AdABTAHQAbwBwAD8ALAAgADAALAAgAEEAbgBjAGgAbwByALsDKABhAHIAcgBhAHkALAAgAHMAdABvAHAAXwB3AGgAZQBuACwAIABpACkAKQAsAFwAbgAgACAAIAAgAG4AbwBfAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAE0AKAByAG8AdwBfAHMAdABvAHAAKQAgAD0AIAAwACwAXABuACAAIAAgACAAcgBfACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABEAG8ATgBvAHQAUwB0AG8AcAA/ACwAIABuAG8AXwByACkALAAgAGgALAAgAEkARABYALsDKAByAG8AdwBfAHMAdABvAHAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABjAG8AbgBkAGkAdABpAG8AbgBzAFwAbgAgACAAIAAgAFcAaABlAHIAZQBOAG8AdABGAG8AdQBuAGQAPwAsACAAQQBOAEQAKAByACAAPQAgADAALAAgAGMAIAA9ACAAMAApACwAXABuACAAIAAgACAATgBvAFMAbABpAGMAZQA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgAbgBvAF8AcgApACwAIAByAF8AIAA8AD0AIAByACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABXAGgAZQByAGUATgBvAHQARgBvAHUAbgBkAD8ALAAgAFwAIgAjAE4ATwAtAEEATgBDAEgATwBSACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATgBvAFMAbABpAGMAZQA/ACwAIABcACIAIwBOAE8ALQBTAEwASQBDAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwB1AHQAcAB1AHQAIABnAGUAbwBtAGUAdAByAHkAXABuACAAIAAgACAAcgBvAHcAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AXwByACwAIABoACAALQAgAHIAIAArACAAMQAsACAAcgBfACAALQAgAHIAKQAsAFwAbgAgACAAIAAgAGMAbwBsAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAdwAgAC0AIABjACAAKwAgADEALABcAG4AXABuACAAIAAgACAALwAvACAAUgBvAHcAIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcgBvAHcAcwAgAD0AIAAxACwAcgAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAYwBvAGwAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAByAG8AdwBzACwALAAgAHIAKQAsACwAIABjAG8AbABzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbABzACAAPQAgADEALABTAEUAUQBVAEUATgBDAEUAKAByAG8AdwBzACwALAAgAGMALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAcwBpAHoAZQC7AygAUwBFAFEAVQBFAE4AQwBFACgALAAgAGMAbwBsAHMALAAgAGMAKQAsACAAcgBvAHcAcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAGIAbABvAGMAawBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAeAAsACAAeQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMAA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABTAHQAYQBjAGsAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABBAHAAcAByAG8AeABpAG0AYQB0AGUAcwAgAE4AdQBtAFAAeQAnAHMAIABkAHMAdABhAGMAawAgAGYAbwByACAARQB4AGMAZQBsACcAcwAgADIARAAgAGEAcgByAGEAeQAgAG0AbwBkAGUAbAAuACAARABTAHQAYQBjAGsAuwMgAHMAdABhAGMAawBzAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAZQAgADIARAAgAGEAcgByAGEAeQBzACAAYQBsAG8AbgBnACAAYQAgAFwAIgBkAGUAcAB0AGgAXAAiACAAZABpAG0AZQBuAHMAaQBvAG4AIABiAHkAIAB0AHIAYQBuAHMAcABvAHMAaQBuAGcAIABlAGEAYwBoACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAGEAbgBkACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkAIABjAG8AbgBjAGEAdABlAG4AYQB0AGkAbgBnACAAdABoAGUAIABsAGEAeQBlAHIAcwAuACAAVQBwACAAdABvACAAZgBvAHUAcgAgAGEAcgByAGEAeQBzACAAbQBhAHkAIABiAGUAXABuACAAIAAgACAAcwB1AHAAcABsAGkAZQBkAC4AIABNAGkAcwBzAGkAbgBnACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGkAZwBuAG8AcgBlAGQALgBcAG4AXABuACAAIAAgACAAQQBsAGwAIABhAHIAcgBhAHkAcwAgAG0AdQBzAHQAIABiAGUAIABuAG8AbgARIHMAYwBhAGwAYQByACAAYQBuAGQAIABuAG8AbgARIGUAbQBwAHQAeQAuACAARwBlAG8AbQBlAHQAcgB5ACAAbQB1AHMAdAAgAG0AYQB0AGMAaAAgAGEAYwByAG8AcwBzAFwAbgAgACAAIAAgAGEAbABsACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5AHMAIAAoAHMAYQBtAGUAIABoAGUAaQBnAGgAdAAgANcAIAB3AGkAZAB0AGgAKQAuACAATQBpAHMAbQBhAHQAYwBoAGUAZAAgAGUAbABlAG0AZQBuAHQAcwAgAGEAcgBlACAAcABhAGQAZABlAGQAXABuACAAIAAgACAAdQBzAGkAbgBnACAAcABhAGQAXwB3AGkAdABoAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgAGIAYQBzAGUAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADIAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcwBlAGMAbwBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAdABoAGkAcgBkACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0AIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAbwB1AHIAdABoACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAALQAgAEYAaQBsAGwAIAB2AGEAbAB1AGUAIABmAG8AcgAgAG0AaQBzAG0AYQB0AGMAaABlAGQAIABvAHIAIABtAGkAcwBzAGkAbgBnACAAZQBsAGUAbQBlAG4AdABzAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABOAEEAKAApAC4AXABuAFwAbgBCAGUAaABhAHYAaQBvAHIAOgBcAG4AIAAgACAAIAAiICAAVAB3AG8AIABhAHIAcgBhAHkAcwAgACAAkiEgAGQAZQBwAHQAaAAgAD0AIAAyAFwAbgAgACAAIAAgACIgIABUAGgAcgBlAGUAIABhAHIAcgBhAHkAcwAgAJIhIABkAGUAcAB0AGgAIAA9ACAAMwBcAG4AIAAgACAAIAAiICAARgBvAHUAcgAgAGEAcgByAGEAeQBzACAAIACSISAAZABlAHAAdABoACAAPQAgADQAXABuACAAIAAgACAAIiAgAEUAYQBjAGgAIABhAHIAcgBhAHkAIABpAHMAIAB0AHIAYQBuAHMAcABvAHMAZQBkACAAcwBvACAAZABlAHAAdABoACAAYgBlAGMAbwBtAGUAcwAgAHcAaQBkAHQAaAAsACAAdABoAGUAbgAgAEgAUwBUAEEAQwBLAGUAZAAuAFwAbgBcAG4ARQByAHIAbwByACAAQwBvAG4AZABpAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABcACIAIwBFAE0AUABUAFkALQBBAFIAUgBBAFkAIQBcACIAIAAgACAALQAgAE8AbgBlACAAcgBlAHEAdQBpAHIAZQBkACAAYQByAHIAYQB5ACAAaQBzACAAZQBtAHAAdAB5ACAAdwBoAGkAbABlACAAdABoAGUAIABvAHQAaABlAHIAIABpAHMAIABuAG8AdAAuAFwAbgAgACAAIAAgACIgIABcACIAIwBTAEMAQQBMAEEAUgAtAEUAUgBSAE8AUgAhAFwAIgAgACAALQAgAEEAbgB5ACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBzACAAcwBjAGEAbABhAHIALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABUAGgAaQBzACAAaQBzACAAYQAgADIARAAgAGEAcABwAHIAbwB4AGkAbQBhAHQAaQBvAG4AIABvAGYAIABkAGUAcAB0AGgAIABzAHQAYQBjAGsAaQBuAGcALgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABhAHIAcgBhAHkAcwAgAG0AdQBzAHQAIABzAGgAYQByAGUAIABnAGUAbwBtAGUAdAByAHkAIABvAHIAIABwAGEAZABkAGkAbgBnACAAdwBpAGwAbAAgAGIAZQAgAGEAcABwAGwAaQBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABTAHQAYQBjAGsAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMgBdACwAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAzAF0ALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAGUAcQB1AGkAcgBlAGQAIABhAHIAcgBhAHkAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADIAKQAsACAAMAAsACAAQwBPAFUATgBUAEEAKABhAHIAcgBhAHkAXwAyACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABhAHIAcgBhAHkAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMwApACwAIAAwACwAIABDAE8AVQBOAFQAQQAoAGEAcgByAGEAeQBfADMAKQApACwAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADQAKQAsACAAMAAsACAAQwBPAFUATgBUAEEAKABhAHIAcgBhAHkAXwA0ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAaQBuAGcAIABtAG8AZABlAHMAXABuACAAIAAgACAAcgBlAHEALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGMAIAA9ACAAMAAsACAAZAAgAD0AIAAwACkALABcAG4AIAAgACAAIABDAF8AbwBuAGwAeQAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAYwAgADwAPgAgADAALAAgAGQAIAA9ACAAMAApACwAXABuACAAIAAgACAARABfAG8AbgBsAHkALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGMAIAA9ACAAMAAsACAAZAAgADwAPgAgADAAKQAsAFwAbgAgACAAIAAgAEEAbABsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABjACAAPAA+ACAAMAAsACAAZAAgADwAPgAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGEAbAB0AGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAARQBtAHAAdAB5AEEAcgByAD8ALAAgACAAIAAgACAAIABPAFIAKABhACAAPQAgADAALAAgAGIAIAA9ACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABDAGwAYQBtAHAAuwMsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcABhAHIAYQBtACwAIABBAE4ARAAoAHAAYQByAGEAbQAgAD0AIAAxACwAIABJAFMARQBSAFIATwBSACgAcABhAHIAYQBtACkAKQApACwAXABuACAAIAAgACAAUwBjAGEAbABhAHIARQByAHIAPwAsACAAIAAgACAAIABPAFIAKABDAGwAYQBtAHAAuwMoAGEAKQAsACAAQwBsAGEAbQBwALsDKABiACkALAAgAEMAbABhAG0AcAC7AygAYwApACwAIABDAGwAYQBtAHAAuwMoAGQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgARQBtAHAAdAB5AEEAcgByAD8ALAAgAFwAIgAjAEUATQBQAFQAWQAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAFMAYwBhAGwAYQByAEUAcgByAD8ALAAgAFwAIgAjAFMAQwBBAEwAQQBSAC0ARQBSAFIATwBSACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAcABhAGQAXwB3AGkAdABoACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHAAYQBkAF8AdwBpAHQAaAApACwAIABOAEEAKAApACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAHIAYQBuAHMAcABvAHMAZQBkACAAbABhAHkAZQByAHMAXABuACAAIAAgACAAYQBAHSwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGIAQB0sACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAEEATgBTAFAATwBTAEUAKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIABjAEAdLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGMALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYQByAHIAYQB5AF8AMwApACwAIAAwACkALABcAG4AIAAgACAAIABkAEAdLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGQALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYQByAHIAYQB5AF8ANAApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAYwBrACAAdgBhAHIAaQBhAG4AdABzAFwAbgAgACAAIAAgAHIAZQBxAF8AcwB0AGEAYwBrACwAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhAEAdLAAgAGIAQB0pACwAXABuACAAIAAgACAAQwBfAG8AbgBsAHkAXwBzAHQAYQBjAGsALAAgACAAIABIAFMAVABBAEMASwAoAGEAQB0sACAAYgBAHSwAIABjAEAdKQAsAFwAbgAgACAAIAAgAEQAXwBvAG4AbAB5AF8AcwB0AGEAYwBrACwAIAAgACAASABTAFQAQQBDAEsAKABhAEAdLAAgAGIAQB0sACAAZABAHSkALABcAG4AIAAgACAAIABhAGwAbABfAHMAdABhAGMAawAsACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQBAHSwAIABiAEAdLAAgAGMAQB0sACAAZABAHSkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABmAGkAbgBhAGwAIABzAHQAYQBjAGsAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHIAZQBxACwAcgBlAHEAXwBzAHQAYQBjAGsALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABDAF8AbwBuAGwAeQAsAEMAXwBvAG4AbAB5AF8AcwB0AGEAYwBrACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABEAF8AbwBuAGwAeQAsAEQAXwBvAG4AbAB5AF8AcwB0AGEAYwBrACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEAbABsACwAYQBsAGwAXwBzAHQAYQBjAGsALAAgAEYAQQBMAFMARQApACkAKQApACwAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABXAHIAYQBwAFIAbwB3AHMAMgBEALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAARQBjAGgAbwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVwByAGEAcABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIAByAG8AdwAgAGIAbABvAGMAawBzACAAbwBmACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAaABlAGkAZwBoAHQAIAB3AGgAaQBsAGUAIABwAHIAZQBzAGUAcgB2AGkAbgBnAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuACAAdwBpAGQAdABoAC4AIABUAGgAZQAgAHcAcgBhAHAAcABlAGQAIABiAGwAbwBjAGsAcwAgAGEAcgBlACAAcwB0AGEAYwBrAGUAZAAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5ACAAaQBuACAAdABoAGUAIABvAHUAdABwAHUAdAAuAFwAbgAgACAAIAAgAEoAYQBnAGcAZQBkACAAbwByACAAaQBuAGMAbwBtAHAAbABlAHQAZQAgAGYAaQBuAGEAbAAgAGIAbABvAGMAawBzACAAYQByAGUAIABwAGEAZABkAGUAZAAgAHcAaQB0AGgAIABOAEEAKAApACAAdQBuAGwAZQBzAHMAIABhACAAZgBpAGwAbABcAG4AIAAgACAAIAB2AGEAbAB1AGUAIABpAHMAIABzAHUAcABwAGwAaQBlAGQAIAB2AGkAYQAgAHAAYQBkAF8AdwBpAHQAaAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAgACgAMQBEACAAYQByAHIAYQB5AHMAIABuAG8AdAAgAHMAdQBwAHAAbwByAHQAZQBkACkALgBcAG4AIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAIAAgAC0AIABOAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIABpAG4AIABlAGEAYwBoACAAdwByAGEAcABwAGUAZAAgAGIAbABvAGMAawAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAtACAARgBpAGwAbAAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIAB0AG8AIABwAGEAZAAgAGkAbgBjAG8AbQBwAGwAZQB0AGUAIABiAGwAbwBjAGsAcwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAATgBBACgAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAdwBpAGQAdABoACAAPQAgAGIAbABvAGMAawBzACAA1wAgAG8AcgBpAGcAaQBuAGEAbAAgAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgACIgIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAbQB1AHMAdAAgAGIAZQAgAHMAdAByAGkAYwB0AGwAeQAgAGwAZQBzAHMAIAB0AGgAYQBuACAAdABoAGUAIABhAHIAcgBhAHkAIABoAGUAaQBnAGgAdAAuAFwAbgAgACAAIAAgACIgIABTAHAAaQBsAGwAIAByAGkAcwBrACAAaQBzACAAYwBoAGUAYwBrAGUAZAAgAGEAZwBhAGkAbgBzAHQAIABFAHgAYwBlAGwAGSBzACAAMQA2ACwAMwA4ADQAESBjAG8AbAB1AG0AbgAgAGwAaQBtAGkAdAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBXAHIAYQBwAFIAbwB3AHMAMgBEALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG4AZQB3AF8AaABlAGkAZwBoAHQALABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwBoAGEAcABlAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABiAGwAbwBjAGsAcwAsACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABoACAALwAgAG4AZQB3AF8AaABlAGkAZwBoAHQALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgAHAAYQBkAF8AdwBpAHQAaAAsACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGEAZABfAHcAaQB0AGgAKQAsACAATgBBACgAKQAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAbwB1AHQAcAB1AHQAIAB3AGkAZAB0AGgAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsAcwAgACoAIAB3ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABEAGkAbQA/ACwAIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAPgA9ACAAaAAsAFwAbgAgACAAIAAgAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgACAAIAAgACAAYwAgAD4AIAAxADYAMwA4ADQALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzADEARAA/ACwAIABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQARABpAG0APwAsACAAXAAiACMASABFAEkARwBIAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAXAAiACMATgBVAE0AIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASQBuAGQAaQBjAGUAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFQATwBSAE8AVwAoAEUAYwBoAG8AuwMoAFMARQBRAFUARQBOAEMARQAoACwAIABiAGwAbwBjAGsAcwAsACAAMQAsACAAbgBlAHcAXwBoAGUAaQBnAGgAdAApACwAIAB3ACkAKQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAArACAAUwBFAFEAVQBFAE4AQwBFACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACwAIAAwACwAIAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABtAG8AZAB1AGwAbwAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgATQBPAEQAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwAgACoAIABiAGwAbwBjAGsAcwApACwAIAB3ACkAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABtAG8AZAB1AGwAbwAoACkAIAA9ACAAMAAsACAAdwAsACAAbQBvAGQAdQBsAG8AKAApACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABXAHIAYQBwAHAAZQBkACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAaQAoACkALAAgAGoAKAApACkALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADAAOABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFcAcgBhAHAAQwBvAGwAcwAyAEQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABFAGMAaABvALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABXAHIAYQBwAHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGMAbwBsAHUAbQBuACAAYgBsAG8AYwBrAHMAIABvAGYAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAIAB3AGkAZAB0AGgAIAB3AGgAaQBsAGUAIABwAHIAZQBzAGUAcgB2AGkAbgBnAFwAbgAgACAAIAAgAHIAbwB3ACAAaABlAGkAZwBoAHQALgAgAFQAaABlACAAdwByAGEAcABwAGUAZAAgAGIAbABvAGMAawBzACAAYQByAGUAIABzAHQAYQBjAGsAZQBkACAAdgBlAHIAdABpAGMAYQBsAGwAeQAgAGkAbgAgAHQAaABlACAAbwB1AHQAcAB1AHQALgBcAG4AIAAgACAAIABKAGEAZwBnAGUAZAAgAG8AcgAgAGkAbgBjAG8AbQBwAGwAZQB0AGUAIABmAGkAbgBhAGwAIABiAGwAbwBjAGsAcwAgAGEAcgBlACAAcABhAGQAZABlAGQAIAB3AGkAdABoACAATgBBACgAKQAgAHUAbgBsAGUAcwBzACAAYQAgAGYAaQBsAGwAXABuACAAIAAgACAAdgBhAGwAdQBlACAAaQBzACAAcwB1AHAAcABsAGkAZQBkACAAdgBpAGEAIABwAGEAZABfAHcAaQB0AGgALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAKAAxAEQAIABhAHIAcgBhAHkAcwAgAG4AbwB0ACAAcwB1AHAAcABvAHIAdABlAGQAKQAuAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAIAAgAC0AIABOAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABpAG4AIABlAGEAYwBoACAAdwByAGEAcABwAGUAZAAgAGIAbABvAGMAawAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAALQAgAEYAaQBsAGwAIAB2AGEAbAB1AGUAIAB1AHMAZQBkACAAdABvACAAcABhAGQAIABpAG4AYwBvAG0AcABsAGUAdABlACAAYgBsAG8AYwBrAHMALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAE4AQQAoACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGgAZQBpAGcAaAB0ACAAPQAgAGIAbABvAGMAawBzACAA1wAgAG8AcgBpAGcAaQBuAGEAbAAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAIiAgAG4AZQB3AF8AdwBpAGQAdABoACAAbQB1AHMAdAAgAGIAZQAgAHMAdAByAGkAYwB0AGwAeQAgAGwAZQBzAHMAIAB0AGgAYQBuACAAdABoAGUAIABhAHIAcgBhAHkAIAB3AGkAZAB0AGgALgBcAG4AIAAgACAAIAAiICAAUwBwAGkAbABsACAAcgBpAHMAawAgAGkAcwAgAGMAaABlAGMAawBlAGQAIABhAGcAYQBpAG4AcwB0ACAARQB4AGMAZQBsABkgcwAgADEALAAwADQAOAAsADUANwA2ABEgcgBvAHcAIABsAGkAbQBpAHQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVwByAGEAcABDAG8AbABzADIARAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABuAGUAdwBfAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGIAbABvAGMAawBzACwAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAHcAIAAvACAAbgBlAHcAXwB3AGkAZAB0AGgALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgAHAAYQBkAF8AdwBpAHQAaAAsACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGEAZABfAHcAaQB0AGgAKQAsACAATgBBACgAKQAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAbwB1AHQAcAB1AHQAIABoAGUAaQBnAGgAdABcAG4AIAAgACAAIAByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABvAGMAawBzACAAKgAgAGgALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAASQBzADEARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEQAaQBtAD8ALAAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAPgA9ACAAdwAsAFwAbgAgACAAIAAgAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgACAAIAAgACAAcgAgAD4AIAAxADAANAA4ADUANwA2ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEQAaQBtAD8ALAAgAFwAIgAjAFcASQBEAFQASAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABTAHAAaQBsAGwAUgBpAHMAawA/ACwAIABcACIAIwBOAFUATQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIABtAG8AZAB1AGwAbwAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgATQBPAEQAKABTAEUAUQBVAEUATgBDAEUAKAByACkALAAgAGgAKQApACwAXABuAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABtAG8AZAB1AGwAbwAoACkAIAA9ACAAMAAsACAAaAAsACAAbQBvAGQAdQBsAG8AKAApACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG4AZQB3AF8AdwBpAGQAdABoACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARQBjAGgAbwC7AygAUwBFAFEAVQBFAE4AQwBFACgAcgAgAC8AIABoACwALAAgADEALAAgAG4AZQB3AF8AdwBpAGQAdABoACkALAAgAGgAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKwAgAFMARQBRAFUARQBOAEMARQAoACwAIABuAGUAdwBfAHcAaQBkAHQAaAAsACAAMAAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAVwByAGEAcABwAGUAZAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAGkAKAApACwAIABqACgAKQApACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAwADkAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAHQAYQBpAHIAYwBhAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFYAYQBsAGkAZABhAHQAZQBTAHQAYQBpAHIAYwBhAHMAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG4AcwB0AHIAdQBjAHQAcwAgAGQAaQBhAGcAbwBuAGEAbAAgAHMAdABhAGkAcgBjAGEAcwBlACAAcABhAHQAdABlAHIAbgBzACAAZgByAG8AbQAgAGEAIAB2AGUAYwB0AG8AcgAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuACAAVABoAGUAIABpAG4AcAB1AHQAXABuACAAIAAgACAAYQByAHIAYQB5ACAAaQBzACAAZgBsAGEAdAB0AGUAbgBlAGQAIAByAG8AdwARIHcAaQBzAGUALAAgAHAAYQByAHQAaQB0AGkAbwBuAGUAZAAgAGkAbgB0AG8AIABiAGwAbwBjAGsAcwAgAG8AZgAgAHMAaQB6AGUAIABiAGwAbwBjAGsAXwBzAGkAegBlACwAIABhAG4AZABcAG4AIAAgACAAIABhAHIAcgBhAG4AZwBlAGQAIABpAG4AdABvACAAZABpAGEAZwBvAG4AYQBsACAAXAAiAHMAdABlAHAAcwBcACIALgAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIABjAG8AbgB0AHIAbwBsACAAYgBsAG8AYwBrACAAcwBwAGEAYwBpAG4AZwAsAFwAbgAgACAAIAAgAGgAbwByAGkAegBvAG4AdABhAGwALwB2AGUAcgB0AGkAYwBhAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALAAgAGEAbgBkACAAYQBuAHQAaQARIGQAaQBhAGcAbwBuAGEAbAAgAGwAYQB5AG8AdQB0AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABmAGwAYQB0AHQAZQBuAGUAZAAgAHIAbwB3ABEgdwBpAHMAZQApAC4AXABuACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAgACAAIAAgACAAIAAtACAAUgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABpAG4AIABlAGEAYwBoACAAcwB0AGEAaQByAGMAYQBzAGUAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIABbAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0AF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABzAHAAYQBjAGkAbgBnACAAYgBlAHQAdwBlAGUAbgAgAHMAdABhAGkAcgBjAGEAcwBlACAAYgBsAG8AYwBrAHMALgBcAG4AIAAgACAAIABbAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAB0AG8AZwBnAGwAZQAgAGYAbwByACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuAC4AXABuACAAIAAgACAAWwBJAHMAQQBuAHQAaQBEAGkAYQBnAD8AXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAdABvAGcAZwBsAGUAIABmAG8AcgAgAGEAbgB0AGkAESBkAGkAYQBnAG8AbgBhAGwAIABsAGEAeQBvAHUAdAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAbgBwAHUAdAAgAGkAcwAgAGYAbABhAHQAdABlAG4AZQBkACAAdQBzAGkAbgBnACAAVABPAEMATwBMAC4AXABuACAAIAAgACAAIiAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAMAAuAFwAbgAgACAAIAAgACIgIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAB2AGUAcgB0AGkAYwBhAGwAIAB1AG4AbABlAHMAcwAgAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AIABpAHMAIABwAHIAbwB2AGkAZABlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwB0AGEAaQByAGMAYQBzAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAsAFwAbgAgACAAIAAgAFsAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAXQAsAFwAbgAgACAAIAAgAFsASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACwAXABuACAAIAAgACAAWwBJAHMAQQBuAHQAaQBEAGkAYQBnAD8AXQAsAFwAbgBcAG4AVgBhAGwAaQBkAGEAdABlAFMAdABhAGkAcgBjAGEAcwBlALsDKABhAHIAcgBhAHkALAAgAGIAbABvAGMAawBfAHMAaQB6AGUALAAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAXABuACAAIAAgACAATgBvAE8AZgBmAHMAZQB0AD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAKQAsAFwAbgAgACAAIAAgAFoAZQByAG8ATwBmAGYAcwBlAHQAPwAsACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAAgAD0AIAAwACwAXABuACAAIAAgACAAYwBvAGwAXwBvAGYAZgBzAGUAdAAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBPAGYAZgBzAGUAdAA/ACwAIAAwACwAIABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQAsAFwAbgAgACAAIAAgAE4AbwBBAG4AdABpAEQAaQBhAGcAPwAsACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAEkAcwBBAG4AdABpAEQAaQBhAGcAPwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAXABuACAAIAAgACAAZgBsAGEAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAZgBsAGEAdAApACwAXABuACAAIAAgACAAcwBlAHEALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAawApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAHIAdABpAHQAaQBvAG4AIABpAG4AdABvACAAYgBsAG8AYwBrAHMAXABuACAAIAAgACAAVgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBSAE8AVwAoAEUAWABQAEEATgBEACgAVwBSAEEAUABSAE8AVwBTACgAcwBlAHEAKAApACwAIABiAGwAbwBjAGsAXwBzAGkAegBlACkALAAsAGIAbABvAGMAawBfAHMAaQB6AGUAIAArACAAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQALAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAFYAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgBzACAAYQBuAGQAIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGIAbABvAGMAawBfAHMAaQB6AGUAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIABjAG8AbABfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AQQBuAHQAaQBEAGkAYQBnAD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIAB3AGkAZAB0AGgALAAgAC0AMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAE8ARAAoAGMAbwBsAF8AYQByAHIAKAApACwAIABiAGwAbwBjAGsAXwBzAGkAegBlACAAKwAgAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACkAKQAsAFwAbgBcAG4AIAAgACAAIABqAF8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABPAFIAKABOAG8ATwBmAGYAcwBlAHQAPwAsACAAWgBlAHIAbwBPAGYAZgBzAGUAdAA/ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGoAKAApACAAPQAgADAALAAgAGIAbABvAGMAawBfAHMAaQB6AGUALAAgAGoAKAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABpACgAKQAgAD0AIABqAF8AKAApACwAIABWACwAIABOAEEAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAcwB0AGEAaQByAGMAYQBzAGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABJAEYATgBBACgASQBOAEQARQBYACgAZgBsAGEAdAAsACAAaQBkAHgAKAApACkALAAgAFwAIgBcACIAKQAsACwAIAAtAGMAbwBsAF8AbwBmAGYAcwBlAHQAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABUAFIAQQBOAFMAUABPAFMARQAoAHIAZQBzAHUAbAB0ACkALAAgAHIAZQBzAHUAbAB0ACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAtAEMATwBSAEUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBTAHQAYQBpAHIAYwBhAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAgACgAVgBhAGwAaQBkAGEAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVgBhAGwAaQBkAGEAdABpAG8AbgAgAGgAZQBsAHAAZQByACAAZgBvAHIAIABTAHQAYQBpAHIAYwBhAHMAZQC7Ay4AIABFAG4AcwB1AHIAZQBzACAAYQByAHIAYQB5ACAAaQBzACAAdgBhAGwAaQBkACwAIABiAGwAbwBjAGsAXwBzAGkAegBlACAAaQBzAFwAbgAgACAAIAAgAHAAbwBzAGkAdABpAHYAZQAgAGEAbgBkACAAZABvAGUAcwAgAG4AbwB0ACAAZQB4AGMAZQBlAGQAIABhAHIAcgBhAHkAIABsAGUAbgBnAHQAaAAsACAAYQBuAGQAIABiAGwAbwBjAGsAXwBvAGYAZgBzAGUAdAAgAGkAcwAgAG4AbwBuABEgbgBlAGcAYQB0AGkAdgBlAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAYgBsAG8AYwBrACAAcwBpAHoAZQAuAFwAbgAgACAAIAAgAFsAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHMAcABhAGMAaQBuAGcAIABiAGUAdAB3AGUAZQBuACAAYgBsAG8AYwBrAHMALgBcAG4AIAAgACAAIABbAG8AbgBfAHYAYQBsAGkAZABdACAAIAAgACAAIAAgAC0AIABFAHgAcAByAGUAcwBzAGkAbwBuACAAdABvACAAZQB2AGEAbAB1AGEAdABlACAAdwBoAGUAbgAgAHYAYQBsAGkAZABhAHQAaQBvAG4AIABwAGEAcwBzAGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBWAGEAbABpAGQAYQB0AGUAUwB0AGEAaQByAGMAYQBzAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAYgBsAG8AYwBrAF8AcwBpAHoAZQAsAFwAbgAgACAAIAAgAFsAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAXQAsAFwAbgAgACAAIAAgAFsAbwBuAF8AdgBhAGwAaQBkAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAcwBcAG4AIAAgACAAIABOAG8AdABBAHIAcgBhAHkAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFkAUABFACgAYQByAHIAYQB5ACkAIAA8AD4AIAA2ADQALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABCAGwAbwBjAGsAUwBpAHoAZQA/ACwAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKABiAGwAbwBjAGsAXwBzAGkAegBlACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsAXwBzAGkAegBlACAAPAA9ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABvAGMAawBfAHMAaQB6AGUAIAA+ACAAQwBPAFUATgBUAEEAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAQgBsAG8AYwBrAE8AZgBmAHMAZQB0AD8ALAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYgBsAG8AYwBrAF8AbwBmAGYAcwBlAHQAKQAsAGIAbABvAGMAawBfAG8AZgBmAHMAZQB0ACAAPAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAE4AbwB0AEEAcgByAGEAeQA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8AVAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQAQgBsAG8AYwBrAFMAaQB6AGUAPwAsACAAIABcACIAIwBCAEwATwBDAEsALQBTAEkAWgBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEIAbABvAGMAawBPAGYAZgBzAGUAdAA/ACwAIABcACIAIwBCAEwATwBDAEsALQBPAEYARgBTAEUAVAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAG4AXwB2AGEAbABpAGQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADAAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABVAG4AUABpAHYAbwB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AywAIABSAGUAcwBpAHoAZQC7AywAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAYQAgAGEAcgByAGEAeQBfADIARAAgAGkAbgB0AG8AIABhACAAZgBsAGEAdAB0AGUAbgBlAGQAIAByAG8AdwARIHcAaQBzAGUAIAB0AGEAYgBsAGUAIABiAHkAIABwAHIAbwB2AGkAZABpAG4AZwAgAHIAbwB3ACAAbABhAGIAZQBsAHMALABcAG4AIAAgACAAIABjAG8AbAB1AG0AbgAgAGwAYQBiAGUAbABzACwAIABhAG4AZAAgAGEAIAB2AGEAbAB1AGUAIABhAHIAcgBhAHkAXwAyAEQALgAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAHQAZQByAGkAbgBnACAAcgBlAG0AbwB2AGUAcwAgAGIAbABhAG4AawBzACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgAGEAbgBkACAAegBlAHIAbwBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAcgBvAHcAcwAgACAAIAAgACAAIAAgACAALQAgAFYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAHIAbwB3ACAAbABhAGIAZQBsAHMALgBcAG4AIAAgACAAIABjAG8AbAB1AG0AbgBzACAAIAAgACAAIAAtACAASABvAHIAaQB6AG8AbgB0AGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAGMAbwBsAHUAbQBuACAAbABhAGIAZQBsAHMALgBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAgACAAIAAgACAAIAAtACAAYQByAHIAYQB5AF8AMgBEACAAbwBmACAAdgBhAGwAdQBlAHMAIAB0AG8AIAB1AG4AcABpAHYAbwB0AC4AXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAA6ACAAaQBmACAAVABSAFUARQAsACAAcgBlAG0AbwB2AGUAIABiAGwAYQBuAGsAcwAsACAAZQByAHIAbwByAHMALAAgAGEAbgBkACAAegBlAHIAbwBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAcgBvAHcAcwAgAG0AdQBzAHQAIABtAGEAdABjAGgAIAB0AGgAZQAgAGgAZQBpAGcAaAB0ACAAbwBmACAAdgBhAGwAdQBlAHMALgBcAG4AIAAgACAAIAAiICAAYwBvAGwAdQBtAG4AcwAgAG0AdQBzAHQAIABtAGEAdABjAGgAIAB0AGgAZQAgAHcAaQBkAHQAaAAgAG8AZgAgAHYAYQBsAHUAZQBzAC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAaQBzACAAYQAgADMAESBjAG8AbAB1AG0AbgAgAHQAYQBiAGwAZQA6ACAAewByAG8AdwBfAGwAYQBiAGUAbAAsACAAYwBvAGwAdQBtAG4AXwBsAGEAYgBlAGwALAAgAHYAYQBsAHUAZQB9AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFUAbgBQAGkAdgBvAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcgBvAHcAcwAsAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAHMALABcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAsAFwAbgAgACAAIAAgAFsAaQBnAG4AbwByAGUAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcgBvAHcAcwApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYwBvAGwAdQBtAG4AcwApACwAXABuAFwAbgAgACAAIAAgAGgAXwB2ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAYQBsAHUAZQBzACkALABcAG4AIAAgACAAIAB3AF8AdgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAB2AGEAbAB1AGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQAsACAAaABfAHYAIAA9ACAAMQAsACAAdwBfAHYAIAA9ACAAMQApACwAXABuACAAIAAgACAATgBvAFAAaQB2AG8AdAA/ACwAIAAgACAAIAAgACAAIAB3AF8AdgAgAD0AIAAxACwAXABuAFwAbgAgACAAIAAgAFIAbwB3AE0AaQBzAG0AYQB0AGMAaAA/ACwAIAAgACAAaAAgADwAPgAgAGgAXwB2ACwAXABuACAAIAAgACAAQwBvAGwATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAB3ACAAPAA+ACAAdwBfAHYALABcAG4AXABuACAAIAAgACAAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAIAAgACAAIABoAF8AdgAgACoAIAB3AF8AdgAgAD4AIAAxADAANAA4ADUANwA2ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAcABhAHMAcwB0AGgAcgBvAHUAZwBoAFwAbgAgACAAIAAgAE8AcgBpAGcARABhAHQAYQAsACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKAByAG8AdwBzACwAIABjAG8AbAB1AG0AbgBzACwAIAB2AGEAbAB1AGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADEAESBjAG8AbAB1AG0AbgAgAHAAYQBzAHMAdABoAHIAbwB1AGcAaABcAG4AIAAgACAAIABPAHIAaQBnAEQAYQB0AGEAUABhAGQALAAgACAAIAAgAEgAUwBUAEEAQwBLACgASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMoAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFYAUwBUAEEAQwBLACgAYwBvAGwAdQBtAG4AcwAsACAAdgBhAGwAdQBlAHMAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAE8AcgBpAGcARABhAHQAYQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBQAGkAdgBvAHQAPwAsACAATwByAGkAZwBEAGEAdABhAFAAYQBkACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABSAG8AdwBNAGkAcwBtAGEAdABjAGgAPwAsACAAXAAiACMARABJAE0ALQBSAE8AVwBTAC8AVgBBAEwAVQBFAFMAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQwBvAGwATQBpAHMAbQBhAHQAYwBoAD8ALAAgAFwAIgAjAEQASQBNAC0AQwBPAEwALwBWAEEATABVAEUAUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgAFwAIgAjAFIATwBXAC0ATABJAE0ASQBUACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEIAcgBvAGEAZABjAGEAcwB0ACAAcgBvAHcAIABsAGEAYgBlAGwAcwAgACgAcgBlAHAAZQBhAHQAIABlAGEAYwBoACAAcgBvAHcAIABsAGEAYgBlAGwAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwBvAGwAdQBtAG4AcwApAFwAbgAgACAAIAAgAHIAbwB3AF8AbABhAGIAZQBsAHMALAAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AygAcgBvAHcAcwAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAcgBvAGEAZABjAGEAcwB0ACAAYwBvAGwAdQBtAG4AIABsAGEAYgBlAGwAcwAgACgAcgBlAHAAZQBhAHQAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIABsAGEAYgBlAGwAIABkAG8AdwBuACAAYQBsAGwAIAByAG8AdwBzACkAXABuACAAIAAgACAAYQB0AHQAcgBpAGIAdQB0AGUALAAgACAAIAAgACAAIABSAGUAcwBpAHoAZQC7AygAVABSAEEATgBTAFAATwBTAEUAKABjAG8AbAB1AG0AbgBzACkALABoACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgAGYAbABhAHQAXwB2AGEAbAB1AGUAcwAsACAAIAAgACAAVABPAEMATwBMACgAdgBhAGwAdQBlAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAIABpAG4AdABvACAAMwARIGMAbwBsAHUAbQBuACAAdABhAGIAbABlAFwAbgAgACAAIAAgAHMAdABhAGMAawAsACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKAByAG8AdwBfAGwAYQBiAGUAbABzACwAIABhAHQAdAByAGkAYgB1AHQAZQAsACAAZgBsAGEAdABfAHYAYQBsAHUAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBpAGwAdABlAHIAaQBuAGcAXABuACAAIAAgACAAawBlAGUAcABfAG0AYQBzAGsALAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBCAEwAQQBOAEsAKABmAGwAYQB0AF8AdgBhAGwAdQBlAHMAKQAgACsAIAAoAEkARgBFAFIAUgBPAFIAKABmAGwAYQB0AF8AdgBhAGwAdQBlAHMALAAgADAAKQAgAD0AIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbAB0AGUAcgBlAGQALAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAcwB0AGEAYwBrACwAIABrAGUAZQBwAF8AbQBhAHMAawApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABpAGcAbgBvAHIAZQApACwAIABzAHQAYQBjAGsALAAgAGYAaQBsAHQAZQByAGUAZAApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAWgBpAHAAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgADIARAAgAEEAcgByAGEAeQAgAFMAaABhAHAAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABaAGkAcABzACAAdABvAGcAZQB0AGgAZQByACAAMQATIDQAIABhAHIAcgBhAHkAcwAgAGIAeQAgAGYAbABhAHQAdABlAG4AaQBuAGcAIABlAGEAYwBoACAAaQBuAHAAdQB0ACAAdwBpAHQAaAAgAFQATwBDAE8ATAAgAGEAbgBkACAAYQBsAGkAZwBuAGkAbgBnAFwAbgAgACAAIAAgAHQAaABlAG0AIABiAHkAIABsAGUAbgBnAHQAaAAuACAAQgB5ACAAZABlAGYAYQB1AGwAdAAsACAAWgBpAHAAuwMgAHAAZQByAGYAbwByAG0AcwAgAGEAIABzAHQAcgBpAGMAdAAgAHoAaQBwACwAIABwAGEAaQByAGkAbgBnACAAZQBsAGUAbQBlAG4AdABzAFwAbgAgACAAIAAgAG8AbgBsAHkAIAB1AHAAIAB0AG8AIAB0AGgAZQAgAGwAZQBuAGcAdABoACAAbwBmACAAdABoAGUAIABzAGgAbwByAHQAZQBzAHQAIABhAHIAcgBhAHkALgAgAEkAZgAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAAgAD0AIABUAFIAVQBFACwAIABaAGkAcAC7A1wAbgAgACAAIAAgAGMAbwBuAHQAaQBuAHUAZQBzACAAdQBuAHQAaQBsACAAdABoAGUAIABsAG8AbgBnAGUAcwB0ACAAYQByAHIAYQB5ACAAaQBzACAAYwBvAG4AcwB1AG0AZQBkACwAIABwAGEAZABkAGkAbgBnACAAcwBoAG8AcgB0AGUAcgAgAGEAcgByAGEAeQBzACAAdwBpAHQAaABcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACAAKABkAGUAZgBhAHUAbAB0ADoAIAAjAE4ALwBBACkALgBcAG4AXABuACAAIAAgACAAVABoAGUAIAByAGUAcwB1AGwAdAAgAGkAcwAgAGEAIABoAG8AcgBpAHoAbwBuAHQAYQBsAGwAeQAgAHMAdABhAGMAawBlAGQAIAB0AGEAYgBsAGUAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAXABuACAAIAAgACAAegBpAHAAcABlAGQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALAAgAG4AbwByAG0AYQBsAGkAegBlAGQAIAB0AG8AIABhACAAYwBvAG0AbQBvAG4AIABsAGUAbgBnAHQAaAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEAIAAgACAAIAAgACAAIAAtACAARgBpAHIAcwB0ACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMgBdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAcwBlAGMAbwBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHQAaABpAHIAZAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8ANABdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAZgBvAHUAcgB0AGgAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAHoAaQBwAF8AbABvAG4AZwBlAHMAdABdACAALQAgAFQAUgBVAEUAIAB0AG8AIAB6AGkAcAAgAHUAbgB0AGkAbAAgAHQAaABlACAAbABvAG4AZwBlAHMAdAAgAGEAcgByAGEAeQAgAGkAcwAgAGMAbwBuAHMAdQBtAGUAZAAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAWgBpAHAAuwMgAHUAcwBlAHMAIABzAHQAcgBpAGMAdAAgAG0AbwBkAGUAIAAoAHMAaABvAHIAdABlAHMAdAAgAGEAcgByAGEAeQApAC4AXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0AIAAgAC0AIABWAGEAbAB1AGUAIAB1AHMAZQBkACAAdABvACAAcABhAGQAIABzAGgAbwByAHQAZQByACAAYQByAHIAYQB5AHMAIAB3AGgAZQBuACAAegBpAHAAXwBsAG8AbgBnAGUAcwB0ACAAPQAgAFQAUgBVAEUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AWgBpAHAAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADIAXQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMwBdACwAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0ALABcAG4AIAAgACAAIABbAHoAaQBwAF8AbABvAG4AZwBlAHMAdABdACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwBlAHQAIAB6AGkAcAAgAG0AbwBkAGUAXABuACAAIAAgACAAWgBpAHAATABvAG4AZwA/ACwAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHoAaQBwAF8AbABvAG4AZwBlAHMAdAApACwAIABGAEEATABTAEUALAAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQB0ACAAZgB1AG4AYwB0AGkAbwBuACAAZgBvAHIAIABkAGUAdABlAHIAbQBpAG4AaQBuAGcAIABsAGUAbgBnAHQAaAAgAG8AZgAgAHoAaQBwAFwAbgAgACAAIAAgAGYAbgC7AywAIAAgACAAIAAgACAAIAAgACAASQBGACgAWgBpAHAATABvAG4AZwA/ACwATQBBAFgALABNAEkATgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQB0ACAAZgBpAGwAbABfAHYAYQBsAHUAZQBcAG4AIAAgACAAIABmAGkAbABsAF8AdgBhAGwAdQBlACwAIAAgAEkARgAoAFoAaQBwAEwAbwBuAGcAPwAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAE4AQQAoACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAATgBBACgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAeQBzACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgAFQAdwBvACwAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADIAKQApACwAXABuACAAIAAgACAAVABoAHIAZQBlACwAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMwApACkALABcAG4AIAAgACAAIABGAG8AdQByACwAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwA0ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABhAHIAcgBhAHkAcwAgAHMAdQBwAHAAbABpAGUAZABcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEYAbwB1AHIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAVABoAHIAZQBlACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAVAB3AG8ALAAgADIALAAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACwAIAAgACAAIAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIALAAgACAAIAAgACAASQBGACgAbQAgAD4APQAgADIALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAXwAyACkALABGAEEATABTAEUAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADMALAAgACAAIAAgACAASQBGACgAbQAgAD4APQAgADMALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAXwAzACkALABGAEEATABTAEUAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADQALAAgACAAIAAgACAASQBGACgAbQAgAD0AIAAgADQALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAXwA0ACkALABGAEEATABTAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAGUAbgBnAHQAaAAgAG8AZgAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAGsAgSAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsACAAIAAgAGsAgiAsACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIABrAIMgLAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAzACkALAAgACAAIABrAIQgLAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAZQBuAGcAdABoACAAbwBmACAAegBpAHAAXABuACAAIAAgACAATABaACwAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAG0ALABrAIEgLABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAbgC7AygAawCBICwAawCCICkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAbgC7AygAawCBICwAawCCICwAawCDICkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAbgC7AygAawCBICwAawCCICwAawCDICwAawCEICkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHIAcgBhAHkAcwAgAC0AIABuAG8AcgBtAGEAbABpAHoAZQBkACAAZgBvAHIAIAB6AGkAcAAgAG0AbwBkAGUAXABuACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMsACAAIABMAEEATQBCAEQAQQAoAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABaAGkAcABMAG8AbgBnAD8ALABFAFgAUABBAE4ARAAoAGEAcgByAGEAeQAsAEwAWgAsACwAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQByAHIAYQB5ACwATABaACkAKQApACwAXABuAFwAbgAgACAAIAAgAGEALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADMAKQAsAFwAbgAgACAAIAAgAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADQAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAbgBnAGUAbQBlAG4AdABcAG4AIAAgACAAIAB6AGkAcABwAGUAZAAsACAAIAAgACAAIAAgAEMASABPAE8AUwBFACgAbQAsAGEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACwAYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsAGIALABjACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACwAYgAsAGMALABkACkAKQAsAFwAbgAgACAAIAAgAHoAaQBwAHAAZQBkAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBsAGkAYwBlAEIAeQBEAGUAZwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAEQARwByAGkAZAC7AywAIABEAGUAbABlAHQAZQBXAGgAZQByAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAGEAbgAgAGEAbgBnAHUAbABhAHIAIABzAGwAaQBjAGUAIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAgAHUAcwBpAG4AZwAgAGQAZQBnAHIAZQBlACAAYgBvAHUAbgBkAHMAIABpAG4AIABhACAAMACwACAALQAgADMANgAwALAAXABuACAAIAAgACAAYwBpAHIAYwB1AGwAYQByACAAcwB5AHMAdABlAG0ALgAgAFQAaABlACAAcwBsAGkAYwBlACAAcAByAGUAcwBlAHIAdgBlAHMAIAB0AGgAZQAgAG8AcgBpAGcAaQBuAGEAbAAgAGcAZQBvAG0AZQB0AHIAeQAuACAASQBmACAAbQBhAHgAXwBkAGUAZwByAGUAZQAgAGkAcwBcAG4AIAAgACAAIABvAG0AaQB0AHQAZQBkACwAIABpAHQAIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAzADYAMACwAC4AXABuAFwAbgAgACAAIAAgAFcAcgBhAHAAESBhAHIAbwB1AG4AZAAgAGkAcwAgAHMAdQBwAHAAbwByAHQAZQBkADoAXABuACAAIAAgACAAIAAgACAAIAAiICAASQBmACAAbQBpAG4AXwBkAGUAZwByAGUAZQAgADwAPQAgAG0AYQB4AF8AZABlAGcAcgBlAGUAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAbABpAGMAZQAgAD0AIABbAG0AaQBuAF8AZABlAGcAcgBlAGUALAAgAG0AYQB4AF8AZABlAGcAcgBlAGUAXQBcAG4AIAAgACAAIAAgACAAIAAgACIgIABJAGYAIABtAGkAbgBfAGQAZQBnAHIAZQBlACAAPgAgAG0AYQB4AF8AZABlAGcAcgBlAGUAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAbABpAGMAZQAgAGMAcgBvAHMAcwBlAHMAIAAzADYAMACwACAAkiEgADAAsAAgAGEAbgBkACAAaQBuAGMAbAB1AGQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAbgBnAGwAZQBzACAAPgA9ACAAbQBpAG4AXwBkAGUAZwByAGUAZQAgACAATwBSACAAIABhAG4AZwBsAGUAcwAgADwAPQAgAG0AYQB4AF8AZABlAGcAcgBlAGUAXABuAFwAbgAgACAAIAAgAFYAYQBsAHUAZQBzACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAcwBsAGkAYwBlACAAYQByAGUAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAZgBpAGwAbABfAHYAYQBsAHUAZQAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABcACIAXAAiACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAHMAbABpAGMAZQAuAFwAbgAgACAAIAAgAG0AaQBuAF8AZABlAGcAcgBlAGUAIAAgACAAIAAtACAAUwB0AGEAcgB0AGkAbgBnACAAZABlAGcAcgBlAGUAIAAoADAALQAzADYAMAApAC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAG0AYQB4AF8AZABlAGcAcgBlAGUAXQAgACAALQAgAEUAbgBkAGkAbgBnACAAZABlAGcAcgBlAGUAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAMwA2ADAAKQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACAAIAAtACAARgBpAGwAbAAgAHYAYQBsAHUAZQAgAGYAbwByACAAbwB1AHQAESBvAGYAESBzAGwAaQBjAGUAIABjAGUAbABsAHMAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAEQARwByAGkAZAC7AyAAdABvACAAYwBvAG0AcAB1AHQAZQAgAHAAZQByABEgYwBlAGwAbAAgAGEAbgBnAGwAZQBzAC4AXABuACAAIAAgACAAIiAgAEQAZQBsAGUAdABlAFcAaABlAHIAZQC7AyAAcgBlAG0AbwB2AGUAcwAgAE4AQQAoACkAIAB3AGgAaQBsAGUAIABwAHIAZQBzAGUAcgB2AGkAbgBnACAAcwBoAGEAcABlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAbABpAGMAZQBCAHkARABlAGcAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAG0AaQBuAF8AZABlAGcAcgBlAGUALABcAG4AIAAgACAAIABbAG0AYQB4AF8AZABlAGcAcgBlAGUAXQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIABtAGEAeABfAGQAZQBnAHIAZQBlACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBkAGUAZwByAGUAZQApACwAIAAzADYAMAAsACAAbQBhAHgAXwBkAGUAZwByAGUAZQApACwAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsACAAXAAiAFwAIgAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABEAGUAZwA/ACwAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAG0AaQBuAF8AZABlAGcAcgBlAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABtAGEAeABfAGQAZQBnAHIAZQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AaQBuAF8AZABlAGcAcgBlAGUAIAA8ACAAMAAsACAAbQBpAG4AXwBkAGUAZwByAGUAZQAgAD4AIAAzADYAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBkAGUAZwByAGUAZQAgADwAIAAwACwAIABtAGEAeABfAGQAZQBnAHIAZQBlACAAPgAgADMANgAwACkALABcAG4AXABuACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABEAGUAZwA/ACwAIABcACIAIwBEAEUARwBSAEUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABBAG4AZwBsAGUAIABmAGkAZQBsAGQAIAAoADAAEyAzADYAMAApAFwAbgAgACAAIAAgAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABHAHIAaQBkALsDKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAVwByAGEAcAARIGEAdwBhAHIAZQAgAG0AYQBzAGsAXABuACAAIAAgACAAbQBhAHMAawAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGkAbgBfAGQAZQBnAHIAZQBlACAAPAA9ACAAbQBhAHgAXwBkAGUAZwByAGUAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAGQAIAA+AD0AIABtAGkAbgBfAGQAZQBnAHIAZQBlACkAIAAqACAAKABkACAAPAA9ACAAbQBhAHgAXwBkAGUAZwByAGUAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAZAAgAD4APQAgAG0AaQBuAF8AZABlAGcAcgBlAGUAKQAgACsAIAAoAGQAIAA8AD0AIABtAGEAeABfAGQAZQBnAHIAZQBlACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABtAGEAcwBrAFwAbgAgACAAIAAgAG0AYQBzAGsAZQBkACwAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAHMAawAsACAAZwByAGkAZAAsACAATgBBACgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBtAG8AdgBlACAATgBBACAAYgB1AHQAIABwAHIAZQBzAGUAcgB2AGUAIABzAGgAYQBwAGUAXABuACAAIAAgACAAYwBsAGUAYQBuAGUAZAAsACAAIAAgACAAIAAgACAAIABEAGUAbABlAHQAZQBXAGgAZQByAGUAuwMoAG0AYQBzAGsAZQBkACwAIABMAEEATQBCAEQAQQAoAHYALAAgAEEATgBEACgASQBTAE4AQQAoAHYAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcABsAGEAYwBlACAAcgBlAG0AbwB2AGUAZAAgAHYAYQBsAHUAZQBzACAAdwBpAHQAaAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABJAEYATgBBACgAYwBsAGUAYQBuAGUAZAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUwBBADEANABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFAAYQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMsACAASQBuAHMAdQBsAGEAdABlAEMAbwBsAHMAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAcABwAGwAaQBlAHMAIAByAG8AdwAgAGEAbgBkAC8AbwByACAAYwBvAGwAdQBtAG4AIABwAGEAZABkAGkAbgBnACAAdABvACAAYQBuAHkAIABhAHIAcgBhAHkALgAgAFAAYQBkALsDIABnAGUAbgBlAHIAYQBsAGkAegBlAHMAIAB0AGgAZQAgAGIAZQBoAGEAdgBpAG8AcgBcAG4AIAAgACAAIABvAGYAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AyAAYQBuAGQAIABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7AyAAYgB5ACAAYQBsAGwAbwB3AGkAbgBnACAAYQBsAGwAIABmAG8AdQByACAAcwBpAGQAZQBzACAAbwBmACAAYQBuACAAYQByAHIAYQB5ACAAdABvAFwAbgAgACAAIAAgAGIAZQAgAHAAYQBkAGQAZQBkACAAaQBuACAAYQAgAHMAaQBuAGcAbABlACAAbwBwAGUAcgBhAHQAaQBvAG4ALgAgAFAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwAgAG0AYQB5ACAAYgBlACAAcwB1AHAAcABsAGkAZQBkACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0AGwAeQBcAG4AIAAgACAAIABvAHIAIABvAG0AaQB0AHQAZQBkACAAZgBvAHIAIABjAG8AbgB2AGUAbgBpAGUAbgBjAGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgACAAIAAgAC0AIABSAG8AdwBzACAAdABvACAAcABhAGQAIABhAGIAbwB2AGUAIAB0AGgAZQAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwByAG8AdwBzAF8AYQBmAHQAZQByAF0AIAAgACAALQAgAFIAbwB3AHMAIAB0AG8AIABwAGEAZAAgAGIAZQBsAG8AdwAgACgAZABlAGYAYQB1AGwAdABzACAAdABvACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkALgBcAG4AIAAgACAAIABbAGMAbwBsAHMAXwBiAGUAZgBvAHIAZQBdACAAIAAtACAAQwBvAGwAdQBtAG4AcwAgAHQAbwAgAHAAYQBkACAAbABlAGYAdAAgACgAZABlAGYAYQB1AGwAdABzACAAdABvACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkALgBcAG4AIAAgACAAIABbAGMAbwBsAHMAXwBhAGYAdABlAHIAXQAgACAAIAAtACAAQwBvAGwAdQBtAG4AcwAgAHQAbwAgAHAAYQBkACAAcgBpAGcAaAB0ACAAKABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAKQAuAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0AIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAHAAYQBkAGQAaQBuAGcAIAB2AGEAbAB1AGUAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBuAHkAIABvAG0AaQB0AHQAZQBkACAAcABhAGQAZABpAG4AZwAgAGMAbwB1AG4AdAAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQBcAG4AIAAgACAAIAAgACAAKABUAGgAaQBzACAAYQBsAGwAbwB3AHMAIABmAG8AcgAgAGUAYQBzAHkAIABwAGEAZABkAGkAbgBnADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAD0AUABhAGQAuwMoAGEAcgByAGEAeQAsADMAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBkAGQAcwAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAIABvAGYAIAAzACAAYQBsAGwAIABhAHIAbwB1AG4AZAAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACkAXABuACAAIAAgACAAIiAgAE4AZQBnAGEAdABpAHYAZQAgAG8AcgAgAHQAZQB4AHQAIABwAGEAZABkAGkAbgBnACAAYwBvAHUAbgB0AHMAIAByAGUAdAB1AHIAbgAgAFwAIgAjAFQARQBYAFQALQBQAEEARAAhAFwAIgAuAFwAbgAgACAAIAAgACIgIABEAGUAbABlAGcAYQB0AGUAcwAgAHIAbwB3ACAAcABhAGQAZABpAG4AZwAgAHQAbwAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAcABhAGQAZABpAG4AZwAgAHQAbwAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDLgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABhAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAXABuACAAIAAgACAAWwByAG8AdwBzAF8AYQBmAHQAZQByAF0ALABcAG4AIAAgACAAIABbAGMAbwBsAHMAXwBiAGUAZgBvAHIAZQBdACwAXABuACAAIAAgACAAWwBjAG8AbABzAF8AYQBmAHQAZQByAF0ALABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwBjAGEAbABhAHIAaQB6AGUAIABhAG4AeQAgAGEAcgByAGEAeQAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAEkAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHgALAAgAEkATgBEAEUAWAAoAHgALAAgADEALAAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAG8AbAB2AGUAIABwAGEAZABkAGkAbgBnACAAYwBvAHUAbgB0AHMAIAAoAG8AbQBpAHQAdABlAGQAIACSISAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkAXABuACAAIAAgACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIAAgACAAIAAgACAAIAAgAEkAuwMoAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQApACwAXABuACAAIAAgACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAsACAAIAAgACAAIAAgACAAIAAgAEkAuwMoAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAcwBfAGEAZgB0AGUAcgApACwAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUALAAgAHIAbwB3AHMAXwBhAGYAdABlAHIAKQApACwAXABuACAAIAAgACAAYwBvAGwAcwBfAGIAZQBmAG8AcgBlACwAIAAgACAAIAAgACAAIAAgAEkAuwMoAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAcwBfAGIAZQBmAG8AcgBlACkALAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAsACAAYwBvAGwAcwBfAGIAZQBmAG8AcgBlACkAKQAsAFwAbgAgACAAIAAgAGMAbwBsAHMAXwBhAGYAdABlAHIALAAgACAAIAAgACAAIAAgACAAIABJALsDKABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAHMAXwBhAGYAdABlAHIAKQAsACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIABjAG8AbABzAF8AYQBmAHQAZQByACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGUAIABwAGEAZABkAGkAbgBnACAAYwBvAHUAbgB0AHMAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABJAG4AcwA/ACwAIAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKAByAG8AdwBzAF8AYQBmAHQAZQByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABjAG8AbABzAF8AYgBlAGYAbwByAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAGMAbwBsAHMAXwBhAGYAdABlAHIAKQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQASQBuAHMAPwAsACAAXAAiACMAVABFAFgAVAAtAFAAQQBEACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAHIAbwB3ACAAcABhAGQAZABpAG4AZwBcAG4AIAAgACAAIABwAGEAZABkAGUAZABfAHIAbwB3AHMALAAgACAAIAAgACAAIAAgACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMoAGEAcgByAGEAeQAsACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIAByAG8AdwBzAF8AYQBmAHQAZQByACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABjAG8AbAB1AG0AbgAgAHAAYQBkAGQAaQBuAGcAXABuACAAIAAgACAAcABhAGQAZABlAGQAXwBhAGwAbAAsACAAIAAgACAAIAAgACAAIAAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDKABwAGEAZABkAGUAZABfAHIAbwB3AHMALAAgAGMAbwBsAHMAXwBiAGUAZgBvAHIAZQAsACAAYwBvAGwAcwBfAGEAZgB0AGUAcgAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAAcABhAGQAZABlAGQAXwBhAGwAbABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFMAQQAxADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnACAAKABQAGEAZABkAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABBAGQAZABzACAAcgBvAHcAcwAgAG8AZgAgAHAAYQBkAGQAaQBuAGcAIABiAGUAZgBvAHIAZQAgAGEAbgBkAC8AbwByACAAYQBmAHQAZQByACAAYQBuACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7A1wAbgAgACAAIAAgAGcAZQBuAGUAcgBhAGwAaQB6AGUAcwAgAEUAWABQAEEATgBEACAAYgB5ACAAcwB1AHAAcABvAHIAdABpAG4AZwAgAHMAeQBtAG0AZQB0AHIAaQBjAGEAbAAgAHAAYQBkAGQAaQBuAGcALAAgAHoAZQByAG8AESBwAGEAZABkAGkAbgBnACAAbwBuACAAZQBpAHQAaABlAHIAXABuACAAIAAgACAAcwBpAGQAZQAsACAAYQBuAGQAIABzAGMAYQBsAGEAcgBpAHoAZQBkACAAcABhAGQAZABpAG4AZwAgAHYAYQBsAHUAZQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAIAAgAC0AIABSAG8AdwBzACAAdABvACAAcABhAGQAIABhAGIAbwB2AGUAIAB0AGgAZQAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwByAG8AdwBzAF8AYQBmAHQAZQByAF0AIAAgAC0AIABSAG8AdwBzACAAdABvACAAcABhAGQAIABiAGUAbABvAHcAIAAoAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQApAC4AXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAHAAYQBkAGQAaQBuAGcAIAB2AGEAbAB1AGUAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAYgBvAHQAaAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgAGEAbgBkACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAgAD0AIAAwACwAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgAgACAAIAAgACIgIAByAG8AdwBzAF8AYQBmAHQAZQByACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAdQBuAGwAZQBzAHMAIABlAHgAcABsAGkAYwBpAHQAbAB5ACAAcwBlAHQAIAB0AG8AIAAwAC4AXABuACAAIAAgACAAIiAgAHAAYQBkAF8AdwBpAHQAaAAgAGkAcwAgAHMAYwBhAGwAYQByAGkAegBlAGQAIAB0AG8AIABhACAAMQDXADEAIAB2AGEAbAB1AGUALgBcAG4AIAAgACAAIAAiICAATgBlAGcAYQB0AGkAdgBlACAAbwByACAAdABlAHgAdAAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwAgAHIAZQB0AHUAcgBuACAAXAAiACMAUgBPAFcAUwAtAEIARQBGAE8AUgBFAC8AQQBGAFQARQBSACEAXAAiAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAsAFwAbgAgACAAIAAgAFsAcgBvAHcAcwBfAGEAZgB0AGUAcgBdACwAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIAByAG8AdwBzAF8AYQBmAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBzAF8AYQBmAHQAZQByACkALAAgAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgApACwAXABuACAAIAAgACAAcABhAGQAXwB3AGkAdABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABhAGQAXwB3AGkAdABoACkALAAgAFwAIgBcACIALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAIAAxACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAFAAYQBkAEMAbwB1AG4AdAA/ACwAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAByAG8AdwBzAF8AYgBlAGYAbwByAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAHIAbwB3AHMAXwBhAGYAdABlAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdwBzAF8AYgBlAGYAbwByAGUAIAA8ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAPAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AESBwAGEAZABkAGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAFwAbgAgACAAIAAgAE4AbwBQAGEAZABkAGkAbgBnAD8ALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgAD0AIAAwACwAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAPQAgADAAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFAAYQBkAEMAbwB1AG4AdAA/ACwAIABcACIAIwBSAE8AVwBTAC0AQgBFAEYATwBSAEUALwBBAEYAVABFAFIAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AUABhAGQAZABpAG4AZwA/ACwAIABhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUABhAGQAZABpAG4AZwAgAGIAbABvAGMAawBzAFwAbgAgACAAIAAgAHAAYQBkAF8AYgBlAGYAbwByAGUALAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAHAAYQBkAF8AdwBpAHQAaAAsACAAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACwAIAB3ACwAIABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgAgACAAIAAgAHAAYQBkAF8AYQBmAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAHAAYQBkAF8AdwBpAHQAaAAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAsACAAdwAsACAAcABhAGQAXwB3AGkAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAAYgBlAGYAbwByAGUAXwBvAG4AbAB5AD8ALAAgACAAIAAgACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGIAZQBmAG8AcgBlACAAPAA+ACAAMAAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAgAD0AIAAwACkALABcAG4AIAAgACAAIABhAGYAdABlAHIAXwBvAG4AbAB5AD8ALAAgACAAIAAgACAAIAAgACAAQQBOAEQAKAByAG8AdwBzAF8AYgBlAGYAbwByAGUAIAA9ACAAMAAsACAAcgBvAHcAcwBfAGEAZgB0AGUAcgAgADwAPgAgADAAKQAsAFwAbgAgACAAIAAgAGYAdQBsAGwAeQBfAGkAbgBzAHUAbABhAHQAZQBkAD8ALAAgACAAIABBAE4ARAAoAHIAbwB3AHMAXwBiAGUAZgBvAHIAZQAgADwAPgAgADAALAAgAHIAbwB3AHMAXwBhAGYAdABlAHIAIAA8AD4AIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAbgBkAGEAcgBkACAARQBYAFAAQQBOAEQAIABmAG8AcgAgAGEAZgB0AGUAcgARIG8AbgBsAHkAIABjAGEAcwBlAFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdwBzAF8AYQBmAHQAZQByACAAKwAgAGgALABcAG4AIAAgACAAIABlAHgAcABhAG4AZABfAG8AbgBsAHkALAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKABhAHIAcgBhAHkALAAgAGsALAAgAHcALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAbgBnAGUAbQBlAG4AdABzAFwAbgAgACAAIAAgAGkAbgBzAHUAbABhAHQAZQBfAGIAZQBmAG8AcgBlACwAIAAgACAAIABWAFMAVABBAEMASwAoAHAAYQBkAF8AYgBlAGYAbwByAGUALAAgAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAaQBuAHMAdQBsAGEAdABlAF8AYQBsAGwALAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAcABhAGQAXwBiAGUAZgBvAHIAZQAsACAAYQByAHIAYQB5ACwAIABwAGEAZABfAGEAZgB0AGUAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAHUAbABsAHkAXwBpAG4AcwB1AGwAYQB0AGUAZAA/ACwAIABpAG4AcwB1AGwAYQB0AGUAXwBhAGwAbAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGIAZQBmAG8AcgBlAF8AbwBuAGwAeQA/ACwAIAAgACAAaQBuAHMAdQBsAGEAdABlAF8AYgBlAGYAbwByAGUALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAcABhAG4AZABfAG8AbgBsAHkAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQA2AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAgACgAUABhAGQAZABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAZABkAHMAIABjAG8AbAB1AG0AbgBzACAAbwBmACAAcABhAGQAZABpAG4AZwAgAGIAZQBmAG8AcgBlACAAYQBuAGQALwBvAHIAIABhAGYAdABlAHIAIABhAG4AIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgAgAEkAbgBzAHUAbABhAHQAZQBDAG8AbABzALsDIABpAHMAXABuACAAIAAgACAAdABoAGUAIABjAG8AbAB1AG0AbgARIG8AcgBpAGUAbgB0AGUAZAAgAGMAbwB1AG4AdABlAHIAcABhAHIAdAAgAHQAbwAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDLgAgAFQAaABlACAAYQByAHIAYQB5ACAAaQBzACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAHQAbwBcAG4AIAAgACAAIAB2AGUAcgB0AGkAYwBhAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALAAgAHAAYQBkAGQAZQBkACAAdgBpAGEAIABJAG4AcwB1AGwAYQB0AGUAUgBvAHcAcwC7AywAIABhAG4AZAAgAHIAZQBzAHQAbwByAGUAZAAgAHQAbwAgAGkAdABzACAAbwByAGkAZwBpAG4AYQBsAFwAbgAgACAAIAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAKABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAHMAXwBiAGUAZgBvAHIAZQAgACAAIAAtACAAQwBvAGwAdQBtAG4AcwAgAHQAbwAgAHAAYQBkACAAdABvACAAdABoAGUAIABsAGUAZgB0AC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAGMAbwBsAHUAbQBuAHMAXwBhAGYAdABlAHIAXQAgACAALQAgAEMAbwBsAHUAbQBuAHMAIAB0AG8AIABwAGEAZAAgAHQAbwAgAHQAaABlACAAcgBpAGcAaAB0ACAAKABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABjAG8AbAB1AG0AbgBzAF8AYgBlAGYAbwByAGUAKQAuAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0AIAAgACAAIAAgACAAIAAtACAAUwBjAGEAbABhAHIAIABwAGEAZABkAGkAbgBnACAAdgBhAGwAdQBlACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgAFwAIgBcACIAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAGIAbwB0AGgAIABjAG8AbAB1AG0AbgBzAF8AYgBlAGYAbwByAGUAIABhAG4AZAAgAGMAbwBsAHUAbQBuAHMAXwBhAGYAdABlAHIAIAA9ACAAMAAsACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQALgBcAG4AIAAgACAAIAAiICAAYwBvAGwAdQBtAG4AcwBfAGEAZgB0AGUAcgAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAGMAbwBsAHUAbQBuAHMAXwBiAGUAZgBvAHIAZQAgAHUAbgBsAGUAcwBzACAAZQB4AHAAbABpAGMAaQB0AGwAeQAgAHMAZQB0ACAAdABvACAAMAAuAFwAbgAgACAAIAAgACIgIABwAGEAZABfAHcAaQB0AGgAIABpAHMAIABzAGMAYQBsAGEAcgBpAHoAZQBkACAAdABvACAAYQAgADEA1wAxACAAdgBhAGwAdQBlAC4AXABuACAAIAAgACAAIiAgAE4AZQBnAGEAdABpAHYAZQAgAHAAYQBkAGQAaQBuAGcAIABjAG8AdQBuAHQAcwAgAGgAYQBsAHQAIABpAG4AcwBpAGQAZQAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDLgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASQBuAHMAdQBsAGEAdABlAEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBvAGwAdQBtAG4AcwBfAGIAZQBmAG8AcgBlACwAXABuACAAIAAgACAAWwBjAG8AbAB1AG0AbgBzAF8AYQBmAHQAZQByAF0ALABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIAB0AG8AIAB2AGUAcgB0AGkAYwBhAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAYQByAHIAYQB5AF8AdgAsACAAIAAgACAAIAAgACAAIABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAHIAbwB3ABEgcABhAGQAZABpAG4AZwAgAGkAbgAgAHYAZQByAHQAaQBjAGEAbAAgAHMAcABhAGMAZQBcAG4AIAAgACAAIABwAGEAZABkAGUAZABfAHYALAAgACAAIAAgACAAIAAgAEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDKABhAHIAcgBhAHkAXwB2ACwAIABjAG8AbAB1AG0AbgBzAF8AYgBlAGYAbwByAGUALAAgAGMAbwBsAHUAbQBuAHMAXwBhAGYAdABlAHIALAAgAHAAYQBkAF8AdwBpAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAHQAbwByAGUAIABvAHIAaQBnAGkAbgBhAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABUAFIAQQBOAFMAUABPAFMARQAoAHAAYQBkAGQAZQBkAF8AdgApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBhAGcAbgBpAGYAeQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAgACgASQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHAAYQBuAGQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAbwBmACAAYQBuACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGEAIABiAGwAbwBjAGsAIABvAGYAIABzAHAAZQBjAGkAZgBpAGUAZAAgAGgAZQBpAGcAaAB0ACAAYQBuAGQAXABuACAAIAAgACAAdwBpAGQAdABoACAAdQBzAGkAbgBnACAAbgBlAGEAcgBlAHMAdAARIG4AZQBpAGcAaABiAG8AcgAgAGkAbgB0AGUAcgBwAG8AbABhAHQAaQBvAG4ALgAgAFMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByAHMALAAgADEARAAgAGEAcgByAGEAeQBzACwAIABhAG4AZABcAG4AIAAgACAAIAAyAEQAIABhAHIAcgBhAHkAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABhAHIAcgBhAHkAIAB0AG8AIABtAGEAZwBuAGkAZgB5AC4AXABuACAAIAAgACAAaABlAGkAZwBoAHQAIAAgACAAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGYAbwByACAAZQBhAGMAaAAgAG0AYQBnAG4AaQBmAGkAZQBkACAAZQBsAGUAbQBlAG4AdAAgACgAcABvAHMAaQB0AGkAdgBlACAAcwBjAGEAbABhAHIAKQAuAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAgACAAIAAgACAAIAAgAC0AIABOAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABtAGEAZwBuAGkAZgBpAGUAZAAgAGUAbABlAG0AZQBuAHQAIAAoAHAAbwBzAGkAdABpAHYAZQAgAHMAYwBhAGwAYQByACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABoAGUAaQBnAGgAdAAgAGEAbgBkACAAdwBpAGQAdABoACAAbQB1AHMAdAAgAGIAZQAgAHMAYwBhAGwAYQByACwAIABuAHUAbQBlAHIAaQBjACwAIABhAG4AZAAgAD4AIAAwAC4AXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAZQB4AHAAYQBuAHMAaQBvAG4AIAB2AGkAYQAgAGkAbgBkAGUAeAAgAHIAZQBwAGwAaQBjAGEAdABpAG8AbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAGEAZwBuAGkAZgB5ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgBJAEYAKABPAFIAKABDAE8AVQBOAFQAKABoAGUAaQBnAGgAdAApACAAPAA+ACAAMQAsACAAQwBPAFUATgBUACgAdwBpAGQAdABoACkAIAA8AD4AIAAxACkALABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuACAAIAAgACAASQBGACgATwBSACgASQBTAFQARQBYAFQAKABoAGUAaQBnAGgAdAApACwAIABJAFMAVABFAFgAVAAoAHcAaQBkAHQAaAApACkALABcACIAIwBUAEUAWABUACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgAaABlAGkAZwBoAHQAIAA8AD0AIAAwACwAIAB3AGkAZAB0AGgAIAA8AD0AIAAwACkALABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwAgAG8AZgAgAG0AYQBnAG4AaQBmAGkAZQBkACAAbwB1AHQAcAB1AHQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgACoAIABoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAAqACAAdwBpAGQAdABoACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AZQBzAGgAIABnAHIAaQBkACAAZgBvAHIAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAcgBlAHAAbABpAGMAYQB0AGkAbwBuAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkATgBUACgAUwBFAFEAVQBFAE4AQwBFACgAaQAsACwALAAgADEAIAAvACAAaABlAGkAZwBoAHQAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAGoALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkATgBUACgAUwBFAFEAVQBFAE4AQwBFACgALAAgAGoALAAsACAAMQAgAC8AIAB3AGkAZAB0AGgAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAaQAsACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABlAHYAYQBsAHUAYQB0AGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAHgAKAApACwAIAB5ACgAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBTAEEAMQA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAWgBvAG8AbQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAgACgASwBlAHIAbgBlAGwAIABFAHgAcABhAG4AcwBpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeABwAGEAbgBkAHMAIABlAGEAYwBoACAAZQBsAGUAbQBlAG4AdAAgAG8AZgAgAGEAbgAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABhACAAYgBsAG8AYwBrACAAdwBoAG8AcwBlACAAcwBpAHoAZQAgAG0AYQB0AGMAaABlAHMAIAB0AGgAZQBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAgANcAIAB3AGkAZAB0AGgAIABvAGYAIAB6AG8AbwBtAF8AawBlAHIAbgBlAGwALgAgAEUAYQBjAGgAIABlAHgAcABhAG4AZABlAGQAIABiAGwAbwBjAGsAIABpAHMAIABmAG8AcgBtAGUAZAAgAGIAeQAgAGEAZABkAGkAbgBnACAAdABoAGUAXABuACAAIAAgACAAZQBsAGUAbQBlAG4AdAAgAHYAYQBsAHUAZQAgAHQAbwAgAHQAaABlACAAegBvAG8AbQBfAGsAZQByAG4AZQBsAC4AIABJAG4AdABlAG4AZABlAGQAIABzAHQAcgBpAGMAdABsAHkAIABmAG8AcgAgAG4AdQBtAGUAcgBpAGMAIABhAHIAcgBhAHkAcwAgAGEAbgBkAFwAbgAgACAAIAAgAG4AdQBtAGUAcgBpAGMAIABrAGUAcgBuAGUAbABzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAbgB1AG0AZQByAGkAYwAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIAcwAgAGEAbABsAG8AdwBlAGQAKQAuAFwAbgAgACAAIAAgAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAgACAALQAgAE4AdQBtAGUAcgBpAGMAIABrAGUAcgBuAGUAbAAgAGQAZQBmAGkAbgBpAG4AZwAgAGUAeABwAGEAbgBzAGkAbwBuACAAaABlAGkAZwBoAHQAIABhAG4AZAAgAHcAaQBkAHQAaAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBBAFIAUgBBAFkAIQBcACIAIABpAGYAIABhAG4AeQAgAGEAcgByAGEAeQAgAGUAbABlAG0AZQBuAHQAcwAgAGEAcgBlACAAbgBvAG4AESBuAHUAbQBlAHIAaQBjAC4AXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBLAEUAUgBOAEUATAAhAFwAIgAgAGkAZgAgAGEAbgB5ACAAawBlAHIAbgBlAGwAIABlAGwAZQBtAGUAbgB0AHMAIABhAHIAZQAgAG4AbwBuABEgbgB1AG0AZQByAGkAYwAuAFwAbgAgACAAIAAgACIgIABJAGYAIAB6AG8AbwBtAF8AawBlAHIAbgBlAGwAIABpAHMAIAAxANcAMQAsACAAWgBvAG8AbQC7AyAAcgBlAGQAdQBjAGUAcwAgAHQAbwAgAGEAcgByAGEAeQAgACsAIABzAGMAYQBsAGEAcgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBaAG8AbwBtALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEsAZQByAG4AZQBsACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAB6AG8AbwBtAF8AawBlAHIAbgBlAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAVABlAHgAdABLAGUAcgBuAGUAbAA/ACwAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAB6AG8AbwBtAF8AawBlAHIAbgBlAGwAKQApACwAXABuACAAIAAgACAASQBzAFQAZQB4AHQAQQByAHIAYQB5AD8ALAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYQByAHIAYQB5ACkAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgBLAGUAcgBuAGUAbAA/ACwAIAAgACAAIABBAE4ARAAoAGgAZQBpAGcAaAB0ACAAPQAgADEALAAgAHcAaQBkAHQAaAAgAD0AIAAxACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFQAZQB4AHQASwBlAHIAbgBlAGwAPwAsACAAXAAiACMASwBFAFIATgBFAEwAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVABlAHgAdABBAHIAcgBhAHkAPwAsACAAXAAiACMAQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIASwBlAHIAbgBlAGwAPwAsACAAYQByAHIAYQB5ACAAKwAgAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHUAdABwAHUAdAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAKgAgAGgAZQBpAGcAaAB0ACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACAAKgAgAHcAaQBkAHQAaAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZAAgAGYAbwByACAAbgBlAGEAcgBlAHMAdAARIG4AZQBpAGcAaABiAG8AcgAgAGUAeABwAGEAbgBzAGkAbwBuAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKABpACwALAAsACAAMQAgAC8AIABoAGUAaQBnAGgAdAApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAGoALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAagAsACwAIAAxACAALwAgAHcAaQBkAHQAaAApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAaQAsACwAIAAxACwAIAAwACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AZABlAGQAIABhAHIAcgBhAHkAIAAoAG4AZQBhAHIAZQBzAHQAESBuAGUAaQBnAGgAYgBvAHIAKQBcAG4AIAAgACAAIAB6AG8AbwBtAGUAZAAsACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAeAAoACkALAAgAHkAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcwBpAHoAZQAgAGsAZQByAG4AZQBsACAAdABvACAAbQBhAHQAYwBoACAAegBvAG8AbQBlAGQAIABiAGwAbwBjAGsAIABzAHQAcgB1AGMAdAB1AHIAZQBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAegBvAG8AbQBlAGQAKAApACkAIAAvACAAaABlAGkAZwBoAHQALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAegBvAG8AbQBlAGQAKAApACkAIAAvACAAdwBpAGQAdABoACwAXABuACAAIAAgACAAawBlAHIAbgBlAGwAXwBtAGEAZwAsACAAUgBlAHMAaQB6AGUAuwMoAHoAbwBvAG0AXwBrAGUAcgBuAGUAbAAsACAAaAAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAHoAbwBvAG0AZQBkACAAbwB1AHQAcAB1AHQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHoAbwBvAG0AZQBkACgAKQAgACsAIABrAGUAcgBuAGUAbABfAG0AYQBnACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAEcAQQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAwADQAIAAtACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHAAcgBvAHYAaQBkAGUAIABhACAAdABvAG8AbABrAGkAdAAgAGYAbwByACAAcwB0AHIAdQBjAHQAdQByAGEAbAAgAGUAZABpAHQAaQBuAGcAIABvAGYAXABuACAAIAAgACAAMgBEACAAYQByAHIAYQB5AHMALgAgAFQAaABlAHMAZQAgAG8AcABlAHIAYQB0AG8AcgBzACAAcwB1AHAAcABvAHIAdAAgAGQAZQBsAGUAdABpAG8AbgAsACAAcwBlAGwAZQBjAHQAaQBvAG4ALAAgAGYAaQBsAHQAZQByAGkAbgBnACwAIAByAG8AbABsAGkAbgBnACwAXABuACAAIAAgACAAZQB4AHAAYQBuAHMAaQBvAG4ALAAgAGEAbgBkACAAcwB0AHIAdQBjAHQAdQByAGEAbAAgAG0AYQBwAHAAaQBuAGcALgBcAG4AXABuACAAIAAgACAAUwB1AGIAESBjAGEAdABlAGcAbwByAGkAZQBzADoAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEQAZQBsAGUAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGUAdABlAFIAbwB3AHMAuwMsACAARABlAGwAZQB0AGUAQwBvAGwAcwC7AywAIABEAGUAbABlAHQAZQBXAGgAZQByAGUAuwMsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUABpAG4AYwBoALsDLAAgAFIAZQBtAG8AdgBlALsDLAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAARQB4AHAAYQBuAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABLAHIAbwBuAGUAYwBrAGUAcgBQAHIAbwBkALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEYAaQBsAHQAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQB4AGMAbAB1AGQAZQC7AywAIABTAG4AYQBwALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFIAbwBsAGwAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAGgAaQBmAHQAuwMsACAAUwBoAGkAZgB0AFIAbwB3AHMAuwMsACAAUwBoAGkAZgB0AEMAbwBsAHMAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAUwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAG0AYgBlAGQAuwMsACAASwBlAGUAcABSAG8AdwBzALsDLAAgAEsAZQBlAHAAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABTAHQAcgB1AGMAdAB1AHIAYQBsACAATQBhAHAAcABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAbABvAGMAawBNAGEAcAC7AywAIABDAG8AbgB2AG8AbAB2AGUAuwMsACAARgBvAGwAZAC7AywAIABKAG8AaQBuADIARAC7A1wAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEQAZQBsAGUAdABlAFIAbwB3AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABEAGUAbABlAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAdAByAGUAYQBrALsDLAAgAEMAbwB1AG4AdABkAG8AdwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABEAGUAbABlAHQAZQBzACAAcgBvAHcAcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgBhAHMAZQBkACAAbwBuACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuAHMALgAgAEEAIABwAG8AcwBpAHQAaQB2AGUAXABuACAAIAAgACAAZABlAGwAZQB0AGUAIAB2AGEAbAB1AGUAIAB0AHIAaQBtAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAHQAaABlACAAdABvAHAAIABvAGYAIABlAGEAYwBoACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AOwAgAGEAIABuAGUAZwBhAHQAaQB2AGUAIABkAGUAbABlAHQAZQBcAG4AIAAgACAAIAB2AGEAbAB1AGUAIAB0AHIAaQBtAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAHQAaABlACAAYgBvAHQAdABvAG0ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABkAGUAbABlAHQAZQAgACAAIAAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAGkAbgB0AGUAZwBlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAD4AIAAwACAAkiEgAHQAcgBpAG0AIABmAHIAbwBtACAAdABvAHAAIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA8ACAAMAAgAJIhIAB0AHIAaQBtACAAZgByAG8AbQAgAGIAbwB0AHQAbwBtACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAgACAALQAgAFMAdQBiAGcAcgBvAHUAcAAgAGwAYQBiAGUAbABzACAAKABzAGEAbQBlACAAaABlAGkAZwBoAHQAIABhAHMAIABhAHIAcgBhAHkAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAG8AbgBsAHkAIABvAG4AZQAgAHMAdQBiAGcAcgBvAHUAcAAgAGUAeABpAHMAdABzACwAIABEAFIATwBQACgAKQAgAGkAcwAgAHUAcwBlAGQAIABhAHMAIABhACAAZgBhAHMAdAAgAHAAYQB0AGgALgBcAG4AIAAgACAAIAAiICAAZABlAGwAZQB0AGUAIABtAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByADsAIAB0AGUAeAB0ACAAbwByACAAdgBlAGMAdABvAHIAIABpAG4AcAB1AHQAcwAgAGgAYQBsAHQAIAB3AGkAdABoACAAYQBuACAAZQByAHIAbwByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQBsAGUAdABlAFIAbwB3AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAZABlAGwAZQB0AGUALABcAG4AIAAgACAAIABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAHUAYgBnAHIAbwB1AHAAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABVAE4ASQBRAFUARQAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEQAaQBzAGMAYQByAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIABAAGQAZQBsAGUAdABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPAA+ACAAUgBPAFcAUwAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAASQBzAFQAZQB4AHQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAZABlAGwAZQB0AGUAKQAsAFwAbgAgACAAIAAgAE4AbwB0AFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgASQBzAFQAZQB4AHQAPwApACwAIABDAE8AVQBOAFQAQQAoAGQAZQBsAGUAdABlACkAIAA+ACAAMQApACwAXABuACAAIAAgACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABJAHMAVABlAHgAdAA/ACwAIABOAG8AdABTAGMAYQBsAGEAcgA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQByAHIAbwByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAGgAYQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABzAGMAZQBuAGEAcgBpAG8AcwApACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgA7ACAAXAAiACMAVABFAFgAVAAhAFwAIgA7ACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIAfQAsAFwAbgAgACAAIAAgAGEAbABlAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAFIAUgBBAFkAVABPAFQARQBYAFQAKABGAEkATABUAEUAUgAoAGUAcgByAG8AcgBzACwAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAMAApACkALABcAG4AXABuACAAIAAgACAASQBGACgATwBuAGUAUwB1AGIARwByAG8AdQBwAD8ALAAgAEQAaQBzAGMAYQByAGQALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGgAYQBsAHQALAAgAGEAbABlAHIAdAAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgA6ACAAKwB0AG8AcAAsACAAEyBiAG8AdAB0AG8AbQBcAG4AIAAgACAAIABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGQAZQBsAGUAdABlACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgB1AG4AIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGEAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAcgBlAGEAawC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkALABcAG4AIAAgACAAIABkAGUAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAAZABlAGwAZQB0AGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAQgBTACgAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGkAbgBkAGUAeAAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAIAA9ACAALQAxACwAIABkAGUAcwBjAGUAbgBkACwAIABhAHMAYwBlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQBlAHAAIAByAG8AdwBzACAAdwBoAGUAcgBlACAAaQBuAGQAZQB4ACAAPgAgAGQAZQBsAGUAdABlAFwAbgAgACAAIAAgAGsAZQBlAHAAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAGkAZAB4ACAAPAA9ACAAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGsAZQBlAHAAPwApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABlAGwAZQB0AGUAQwBvAGwAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEQAZQBsAGUAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUwB0AHIAZQBhAGsAuwMsACAAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEQAZQBsAGUAdABlAHMAIABjAG8AbAB1AG0AbgBzACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABiAGEAcwBlAGQAIABvAG4AIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AcwAuACAAQQAgAHAAbwBzAGkAdABpAHYAZQBcAG4AIAAgACAAIABkAGUAbABlAHQAZQAgAHYAYQBsAHUAZQAgAHQAcgBpAG0AcwAgAGMAbwBsAHUAbQBuAHMAIABmAHIAbwBtACAAdABoAGUAIABsAGUAZgB0ACAAbwBmACAAZQBhAGMAaAAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuADsAIABhACAAbgBlAGcAYQB0AGkAdgBlAFwAbgAgACAAIAAgAGQAZQBsAGUAdABlACAAdgBhAGwAdQBlACAAdAByAGkAbQBzACAAYwBvAGwAdQBtAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAaQBnAGgAdAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGQAZQBsAGUAdABlACAAIAAgACAAIAAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACAAaQBuAHQAZQBnAGUAcgA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPgAgADAAIACSISAAdAByAGkAbQAgAGYAcgBvAG0AIABsAGUAZgB0ACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAPAAgADAAIACSISAAdAByAGkAbQAgAGYAcgBvAG0AIAByAGkAZwBoAHQAIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACAAIAAtACAAUwB1AGIAZwByAG8AdQBwACAAbABhAGIAZQBsAHMAIAAoAHMAYQBtAGUAIAB3AGkAZAB0AGgAIABhAHMAIABhAHIAcgBhAHkAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAG8AbgBsAHkAIABvAG4AZQAgAHMAdQBiAGcAcgBvAHUAcAAgAGUAeABpAHMAdABzACwAIABEAFIATwBQACgAKQAgAGkAcwAgAHUAcwBlAGQAIABhAHMAIABhACAAZgBhAHMAdAAgAHAAYQB0AGgALgBcAG4AIAAgACAAIAAiICAAZABlAGwAZQB0AGUAIABtAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByADsAIAB0AGUAeAB0ACAAbwByACAAdgBlAGMAdABvAHIAIABpAG4AcAB1AHQAcwAgAGgAYQBsAHQAIAB3AGkAdABoACAAYQBuACAAZQByAHIAbwByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQBsAGUAdABlAEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAZABlAGwAZQB0AGUALABcAG4AIAAgACAAIABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAHUAYgBnAHIAbwB1AHAAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABVAE4ASQBRAFUARQAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsACAAMQApACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEQAaQBzAGMAYQByAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAsACAAQABkAGUAbABlAHQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFYAYQBsAGkAZABhAHQAaQBvAG4AXABuACAAIAAgACAAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgADwAPgAgAEMATwBMAFUATQBOAFMAKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUAKQAsAFwAbgAgACAAIAAgAEkAcwBUAGUAeAB0AD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAGQAZQBsAGUAdABlACkALABcAG4AIAAgACAAIABOAG8AdABTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAE8AVAAoAEkAcwBUAGUAeAB0AD8AKQAsACAAQwBPAFUATgBUAEEAKABkAGUAbABlAHQAZQApACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAHMAYwBlAG4AYQByAGkAbwBzACwAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAASQBzAFQAZQB4AHQAPwAsACAATgBvAHQAUwBjAGEAbABhAHIAPwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAcgByAG8AcgAgAGgAYQBuAGQAbABpAG4AZwBcAG4AIAAgACAAIABoAGEAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAcwBjAGUAbgBhAHIAaQBvAHMAKQAsAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIAOwAgAFwAIgAjAFQARQBYAFQAIQBcACIAOwAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiAH0ALABcAG4AIAAgACAAIABhAGwAZQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBSAFIAQQBZAFQATwBUAEUAWABUACgARgBJAEwAVABFAFIAKABlAHIAcgBvAHIAcwAsACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAE8AbgBlAFMAdQBiAEcAcgBvAHUAcAA/ACwAIABEAGkAcwBjAGEAcgBkACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABoAGEAbAB0ACwAIABhAGwAZQByAHQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgACsAbABlAGYAdAAsACAAEyByAGkAZwBoAHQAXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABkAGUAbABlAHQAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAdQBuACAAaQBuAGQAaQBjAGUAcwAgACgAaABvAHIAaQB6AG8AbgB0AGEAbAApAFwAbgAgACAAIAAgAGEAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAcgBlAGEAawC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACwAIABUAFIAVQBFACkALABcAG4AIAAgACAAIABkAGUAcwBjAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAsACAAVABSAFUARQApACwAXABuACAAIAAgACAAZABlAGwAZQB0AGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAQgBTACgAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGkAbgBkAGUAeAAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAIAA9ACAALQAxACwAIABkAGUAcwBjAGUAbgBkACwAIABhAHMAYwBlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQBlAHAAIABjAG8AbAB1AG0AbgBzACAAdwBoAGUAcgBlACAAaQBuAGQAZQB4ACAAPgAgAGQAZQBsAGUAdABlAFwAbgAgACAAIAAgAGsAZQBlAHAAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAGkAZAB4ACAAPAA9ACAAZABlAGwAZQB0AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbAB1AG0AbgARIHcAaQBzAGUAIABmAGkAbAB0AGUAcgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGsAZQBlAHAAPwApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABlAGwAZQB0AGUAVwBoAGUAcgBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARABlAGwAZQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBzACAAdgBlAHIAdABpAGMAYQBsACAAYQBuAGQAIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAdgBlAGMAdABvAHIAcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgBhAHMAZQBkACAAbwBuACAAYQAgAHAAcgBlAGQAaQBjAGEAdABlAFwAbgAgACAAIAAgAEwAYQBtAGIAZABhAC4AIABUAGgAZQAgAHAAcgBlAGQAaQBjAGEAdABlACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAGUAYQBjAGgAIAByAG8AdwAgAGEAbgBkACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuADsAIABhAG4AeQAgAHYAZQBjAHQAbwByACAAZgBvAHIAXABuACAAIAAgACAAdwBoAGkAYwBoACAAdABoAGUAIABwAHIAZQBkAGkAYwBhAHQAZQAgAHIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBzACAAcgBlAG0AbwB2AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AIAAgACAAIAAtACAATABhAG0AYgBkAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAZQBhAGMAaAAgAHIAbwB3ACAAYQBuAGQAIABjAG8AbAB1AG0AbgAgAHYAZQBjAHQAbwByAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVABoAGUAIABwAHIAZQBkAGkAYwBhAHQAZQAgAGkAcwAgAGUAdgBhAGwAdQBhAHQAZQBkACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0AGwAeQAgAGYAbwByACAAcgBvAHcAcwAgACgAQgBZAFIATwBXACkAIABhAG4AZAAgAGMAbwBsAHUAbQBuAHMAIAAoAEIAWQBDAE8ATAApAC4AXABuACAAIAAgACAAIiAgAEkAZgAgAG4AbwAgAHIAbwB3AHMAIABvAHIAIABjAG8AbAB1AG0AbgBzACAAYQByAGUAIAByAGUAbQBvAHYAZQBkACwAIABcACIAIwBFAE0AUABUAFkALQBBAFIAUgBBAFkAIQBcACIAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABlAGwAZQB0AGUAVwBoAGUAcgBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGUAeAAgAHMAZQBxAHUAZQBuAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAFIATwBXAFMAKABhAHIAcgBhAHkAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AZQBnAGEAdABlAGQAIABwAHIAZQBkAGkAYwBhAHQAZQAgACgAVABSAFUARQAgAD0AIABrAGUAZQBwACkAXABuACAAIAAgACAAZgBuACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAB2ACwAIABOAE8AVAAoAGYAdQBuAGMAdABpAG8AbgAoAHYAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBvAHcAIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAHQAbwAgAGsAZQBlAHAAXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgASQBGACgAQgBZAFIATwBXACgAYQByAHIAYQB5ACwAIABmAG4AKQAsACAAaQAsACAATgBBACgAKQApACwAIAAyACkALABcAG4AIAAgACAAIABiACwAIAAgACAAIAAgACAAIAAgACAAIABUAE8AUgBPAFcAKABJAEYAKABCAFkAQwBPAEwAKABhAHIAcgBhAHkALAAgAGYAbgApACwAIABqACwAIABOAEEAKAApACkALAAgADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AIAByAGUAbQBvAHYAYQBsAHMAPwBcAG4AIAAgACAAIABJAHMARQBtAHAAdAB5AD8ALAAgACAAIABBAE4ARAAoAEkAUwBFAFIAUgBPAFIAKABhACkALAAgAEkAUwBFAFIAUgBPAFIAKABiACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAGUAdwAgAHMAaABhAHAAZQBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAYQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAeQAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAYgAgACoAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwAIAAsACAAMQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgAEkARgAoAEkAcwBFAG0AcAB0AHkAPwAsACAAXAAiACMARQBNAFAAVABZAC0AQQBSAFIAQQBZACEAXAAiACwAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAHIALAAgAGMAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUABpAG4AYwBoALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARABlAGwAZQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBzACAAYQBuAHkAIABmAHUAbABsACAAcgBvAHcAcwAgAG8AcgAgAGMAbwBsAHUAbQBuAHMAIAB3AGgAbwBzAGUAIABjAGUAbABsAHMAIABhAGwAbAAgAGgAYQB2AGUAIABMAEUATgAoAGMAZQBsAGwAKQAgAD0AIAAwAC4AIABSAG8AdwBzACAAbwByAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAHMAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAbwBuAGwAeQAgAGUAbQBwAHQAeQAgAHMAdAByAGkAbgBnAHMAIABvAHIAIABlAHIAcgBvAHIAcwAgAGEAcgBlACAAZABpAHMAYwBhAHIAZABlAGQALgAgAFAAaQBuAGMAaAC7AyAAaQBzACAAYQBcAG4AIAAgACAAIABzAHQAcgB1AGMAdAB1AHIAYQBsACAAYwBsAGUAYQBuAHUAcAAgAG8AcABlAHIAYQB0AG8AcgAgAGYAbwByACAAdAByAGkAbQBtAGkAbgBnACAAdwBoAGkAdABlAHMAcABhAGMAZQARIG8AbgBsAHkAIABvAHIAIABuAHUAbABsACAAcgBlAGcAaQBvAG4AcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAGUAbQBwAHQAeQAgAHIAbwB3AHMAIABhAG4AZAAgAGMAbwBsAHUAbQBuAHMAIABhAHIAZQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGkAcwAgAGUAbQBwAHQAeQAsACAAUABpAG4AYwBoALsDIAByAGUAdAB1AHIAbgBzACAAMAAuAFwAbgAgACAAIAAgACIgIABFAHIAcgBvAHIAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgAG4AbwBuABEgZQBtAHAAdAB5ADsAIABvAG4AbAB5ACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIAB3AGgAZQByAGUAIABMAEUATgAoAGMAZQBsAGwAKQAgAD0AIAAwACAAZgBvAHIAXABuACAAIAAgACAAIAAgAGEAbABsACAAYwBlAGwAbABzACAAYQByAGUAIAByAGUAbQBvAHYAZQBkAC4AXABuACAAIAAgACAAIiAgAFAAaQBuAGMAaAC7AyAAcAByAGUAcwBlAHIAdgBlAHMAIAB0AGgAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAGEAbABpAHQAeQAgAG8AZgAgAG4AbwBuABEgZQBtAHAAdAB5ACAAcgBlAGcAaQBvAG4AcwAgAGEAbgBkACAAZABvAGUAcwAgAG4AbwB0ACAAYQBsAHQAZQByAFwAbgAgACAAIAAgACAAIABpAG4AdABlAHIAbgBhAGwAIABjAG8AbgB0AGUAbgB0AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFAAaQBuAGMAaAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AXABuAEkARgAoAEMATwBVAE4AVABBACgAYQByAHIAYQB5ACkAIAA9ACAAMAAsADAALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAG4AESBlAG0AcAB0AHkAIABtAGEAcwBrAFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUATgAoAGEAcgByAGEAeQApACAAPAA+ACAAMAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAvAGMAbwBsAHUAbQBuACAAawBlAGUAcAAgAGYAbABhAGcAcwBcAG4AIAAgACAAIABPAFIAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAB2ACwAIABJAEYARQBSAFIATwBSACgATwBSACgAVABPAEMATwBMACgAdgAsACAAMgApACkALAAgAEYAQQBMAFMARQApACkALABcAG4AIAAgACAAIABtAGEAcgBrAF8AcgBvAHcAcwAsACAAIAAgACAAIAAgACAAIAAgACAAQgBZAFIATwBXACgAYgBvAG8AbAAsACAATwBSALsDKQAsAFwAbgAgACAAIAAgAG0AYQByAGsAXwBjAG8AbABzACwAIAAgACAAIAAgACAAIAAgACAAIABCAFkAQwBPAEwAKABiAG8AbwBsACwAIABPAFIAuwMpACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBtAG8AdgBlACAAZQBtAHAAdAB5ACAAcgBvAHcAcwBcAG4AIAAgACAAIABmAGkAcgBzAHQAXwBwAGEAcwBzACwAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAG0AYQByAGsAXwByAG8AdwBzACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAG0AbwB2AGUAIABlAG0AcAB0AHkAIABjAG8AbAB1AG0AbgBzAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGYAaQByAHMAdABfAHAAYQBzAHMALAAgAG0AYQByAGsAXwBjAG8AbABzACwAIAAwACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADAANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFIAZQBtAG8AdgBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARABlAGwAZQB0AGkAbwBuACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBzACAAcwBwAGUAYwBpAGYAaQBjACAAcgBvAHcAcwAgAGEAbgBkAC8AbwByACAAYwBvAGwAdQBtAG4AcwAgAGYAcgBvAG0AIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5AC4AIABSAGUAbQBvAHYAZQC7AyAAcwB1AHAAcABvAHIAdABzAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByAHMALAAgADEARAAgAGEAcgByAGEAeQBzACwAIABhAG4AZAAgADIARAAgAGEAcgByAGEAeQBzACAAZgBvAHIAIABiAG8AdABoACAAcgBvAHcAIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4ACAAaQBuAHAAdQB0AHMALgAgAEEAbABsAFwAbgAgACAAIAAgAGkAbgBkAGUAeAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAGIAZQBmAG8AcgBlACAAZQB2AGEAbAB1AGEAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAHIAbwB3AHMAIABhAG4AZAAvAG8AcgAgAGMAbwBsAHUAbQBuAHMAIABhAHIAZQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AIAAgACAAIABbAHIAbwB3AHMAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHIAbwB3ACAAaQBuAGQAZQB4ACAAbwByACAAYQByAHIAYQB5ACAAbwBmACAAaQBuAGQAaQBjAGUAcwAgAHQAbwAgAHIAZQBtAG8AdgBlAC4AXABuACAAIAAgACAAWwBjAG8AbABzAF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAGkAbgBkAGkAYwBlAHMAIAB0AG8AIAByAGUAbQBvAHYAZQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBJAE4AVgBBAEwASQBEAC0AUgBPAFcAIQBcACIAIABpAGYAIABhAG4AeQAgAHIAbwB3ACAAaQBuAGQAZQB4ACAAaQBzACAAbwB1AHQAIABvAGYAIABiAG8AdQBuAGQAcwAuAFwAbgAgACAAIAAgACIgIABSAGUAdAB1AHIAbgBzACAAXAAiACMASQBOAFYAQQBMAEkARAAtAEMATwBMACEAXAAiACAAaQBmACAAYQBuAHkAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGkAcwAgAG8AdQB0ACAAbwBmACAAYgBvAHUAbgBkAHMALgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAcgBlAHQAdQByAG4AZQBkACAAdQBuAGMAaABhAG4AZwBlAGQALgBcAG4AIAAgACAAIAAiICAAUgBvAHcALwBjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AQwBPAEwAIABmAG8AcgAgAGMAbwBuAHMAaQBzAHQAZQBuAGMAeQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBSAGUAbQBvAHYAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAHIAbwB3AHMAXQAsAFwAbgAgACAAIAAgAFsAYwBvAGwAcwBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgAgAHAAcgBlAHMAZQBuAGMAZQBcAG4AIAAgACAAIAByAG8AdwBzAF8AaQBuAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AHMAKQApACwAXABuACAAIAAgACAAYwBvAGwAcwBfAGkAbgBjACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABjAG8AbABzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAbQBvAHYAYQBsACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAAUgBlAG0AbwB2AGUAUgBvAHcAcwA/ACwAIAAgACAAIAAgACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGkAbgBjACwAIABOAE8AVAAoAGMAbwBsAHMAXwBpAG4AYwApACkALABcAG4AIAAgACAAIABSAGUAbQBvAHYAZQBDAG8AbABzAD8ALAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABjAG8AbABzAF8AaQBuAGMALAAgAE4ATwBUACgAcgBvAHcAcwBfAGkAbgBjACkAKQAsAFwAbgAgACAAIAAgAFIAZQBtAG8AdgBlAFIAQwA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAHIAbwB3AHMAXwBpAG4AYwAsACAAYwBvAGwAcwBfAGkAbgBjACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABUAGUAeAB0AFIAbwB3AHMAPwAsACAAIAAgACAAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAByAG8AdwBzACkAKQAsAFwAbgAgACAAIAAgAFQAZQB4AHQAQwBvAGwAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAGMAbwBsAHMAKQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAUgBvAHcAPwAsACAAIAAgACAAIAAgACAAIABJAEYAKABUAGUAeAB0AFIAbwB3AHMAPwAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAcgBvAHcAcwBfAGkAbgBjACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABNAEkATgAoAHIAbwB3AHMAKQAgADwAIAAxACwAIABNAEEAWAAoAHIAbwB3AHMAKQAgAD4AIABoACkAKQApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAQwBvAGwAPwAsACAAIAAgACAAIAAgACAAIABJAEYAKABUAGUAeAB0AEMAbwBsAHMAPwAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAYwBvAGwAcwBfAGkAbgBjACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABNAEkATgAoAGMAbwBsAHMAKQAgADwAIAAxACwAIABNAEEAWAAoAGMAbwBsAHMAKQAgAD4AIAB3ACkAKQApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABhAHIAcgBhAHkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFIAbwB3AD8ALAAgAFwAIgAjAEkATgBWAEEATABJAEQALQBSAE8AVwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABDAG8AbAA/ACwAIABcACIAIwBJAE4AVgBBAEwASQBEAC0AQwBPAEwAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUgBvAHcALwBjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAHYAZQBjAHQAbwByAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAGgAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwBvAGwAZQBhAG4AIABtAGEAcwBrAHMAXABuACAAIAAgACAAcgBtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBTAE4AQQAoAFgATQBBAFQAQwBIACgAcgAsACAAVABPAEMATwBMACgAcgBvAHcAcwApACkAKQApACwAXABuACAAIAAgACAAYwBtAGEAcwBrACwAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBTAE4AQQAoAFgATQBBAFQAQwBIACgAYwAsACAAVABPAEMATwBMACgAYwBvAGwAcwApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3AC0AbwBuAGwAeQAgAHIAZQBtAG8AdgBhAGwAXABuACAAIAAgACAAcgBvAHcAcwBfAG8AbgBsAHkALAAgACAAIAAgAEwAQQBNAEIARABBACgARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAHIAbQBhAHMAawAoACkALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAHUAbQBuAC0AbwBuAGwAeQAgAHIAZQBtAG8AdgBhAGwAXABuACAAIAAgACAAYwBvAGwAcwBfAG8AbgBsAHkALAAgACAAIAAgAEwAQQBNAEIARABBACgARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGMAbQBhAHMAawAoACkALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbwB0AGgAIAByAG8AdwBzACAAYQBuAGQAIABjAG8AbAB1AG0AbgBzAFwAbgAgACAAIAAgAFIAQwBfAHIALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEYASQBMAFQARQBSACgAYQByAHIAYQB5ACwAIAByAG0AYQBzAGsAKAApACwAIAAwACkAKQAsAFwAbgAgACAAIAAgAFIAQwAsACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEYASQBMAFQARQBSACgAUgBDAF8AcgAoACkALAAgAGMAbQBhAHMAawAoACkALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIABJAEYAKABSAGUAbQBvAHYAZQBSAG8AdwBzAD8ALAAgAHIAbwB3AHMAXwBvAG4AbAB5ACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABSAGUAbQBvAHYAZQBDAG8AbABzAD8ALAAgAGMAbwBsAHMAXwBvAG4AbAB5ACgAKQAsACAAUgBDACgAKQApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADAANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFMAcQB1AGUAZQB6AGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABEAGUAbABlAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBtAG8AdgBlAHMAIABuAHUAbABsACAAYQBuAGQAIABzAHQAcgBhAGkAZwBoAHQAESB6AGUAcgBvACAAdgBlAHIAdABpAGMAYQBsACAAbwByACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgAHYAZQBjAHQAbwByAHMAIABmAHIAbwBtACAAYQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFMAdQBwAHAAbwByAHQAcwAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAGMAdQBzAHQAbwBtACAAcwBjAGEAbABhAHIAIABjAHIAaQB0AGUAcgBpAG8AbgAgAGYAbwByACAAcgBlAG0AbwB2AGEAbAAuACAAUwBxAHUAZQBlAHoAZQC7AyAAYwBhAG4AIABhAGwAcwBvAFwAbgAgACAAIAAgAG8AcAB0AGkAbwBuAGEAbABsAHkAIABzAHUAcABwAHIAZQBzAHMAIAB6AGUAcgBvAHMAIABpAG4AIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYgB5ACAAcgBlAHAAbABhAGMAaQBuAGcAIAB0AGgAZQBtACAAdwBpAHQAaAAgAFwAIgBcACIALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAGYAcgBvAG0AIAB3AGgAaQBjAGgAIAByAG8AdwBzAC8AYwBvAGwAdQBtAG4AcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAuAFwAbgAgACAAIAAgAFsAYwB1AHMAdABvAG0AXwBjAHIAaQB0AGUAcgBpAGEAXQAtACAATwBwAHQAaQBvAG4AYQBsACAAcwBjAGEAbABhAHIAIAB1AHMAZQBkACAAYQBzACAAdABoAGUAIAByAGUAbQBvAHYAYQBsACAAYwByAGkAdABlAHIAaQBvAG4ALgBcAG4AIAAgACAAIABbAHMAdQBwAHAAcgBlAHMAcwBfAHoAZQByAG8AcwBdACAALQAgAEkAZgAgAHAAcgBvAHYAaQBkAGUAZAAsACAAegBlAHIAbwBzACAAaQBuACAAdABoAGUAIABmAGkAbgBhAGwAIAByAGUAcwB1AGwAdAAgAGEAcgBlACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAFwAIgBcACIALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIABiAG8AdABoACAAcgBvAHcAIABhAG4AZAAgAGMAbwBsAHUAbQBuACAAdgBlAGMAdABvAHIAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAsACAAdABoAGUAIAByAGUAcwB1AGwAdAAgAG0AYQB5ACAAcwBoAHIAaQBuAGsAIABpAG4AIABiAG8AdABoAFwAbgAgACAAIAAgACAAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAIiAgAEkAZgAgAG4AbwAgAHIAbwB3AHMAIABvAHIAIABjAG8AbAB1AG0AbgBzACAAcgBlAG0AYQBpAG4ALAAgAFwAIgAjAEUATQBQAFQAWQAtAEEAUgBSAEEAWQAhAFwAIgAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgAgACAAIAAgACIgIABzAHUAcABwAHIAZQBzAHMAXwB6AGUAcgBvAHMAIABvAG4AbAB5ACAAYQBmAGYAZQBjAHQAcwAgAHQAaABlACAAKgBvAHUAdABwAHUAdAAqACwAIABuAG8AdAAgAHQAaABlACAAcgBlAG0AbwB2AGEAbAAgAGwAbwBnAGkAYwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHEAdQBlAGUAegBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAYwB1AHMAdABvAG0AXwBjAHIAaQB0AGUAcgBpAGEAXQAsAFwAbgAgACAAIAAgAFsAcwB1AHAAcAByAGUAcwBzAF8AegBlAHIAbwBzAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABaAGUAcgBvABEgcwB1AHAAcAByAGUAcwBzAGkAbwBuACAAZgBsAGEAZwBcAG4AIAAgACAAIABIAGkAZABlAFoAZQByAG8APwAsACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHMAdQBwAHAAcgBlAHMAcwBfAHoAZQByAG8AcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAcwBlAHEAdQBlAG4AYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAFIATwBXAFMAKABhAHIAcgBhAHkAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBhAHUAbAB0ACAAcgBlAG0AbwB2AGEAbAA6ACAAcgBlAG0AbwB2AGUAIABhAGwAbAARIHoAZQByAG8AIAB2AGUAYwB0AG8AcgBzAFwAbgAgACAAIAAgAEsAZQBlAHAAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALAAgAE4ATwBUACgAQQBOAEQAKABUAE8AQwBPAEwAKAB2ACwAIAAyACkAIAA9ACAAMAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAHUAcwB0AG8AbQAgAHIAZQBtAG8AdgBhAGwAOgAgAHIAZQBtAG8AdgBlACAAdgBlAGMAdABvAHIAcwAgAGUAcQB1AGEAbAAgAHQAbwAgAGMAdQBzAHQAbwBtAF8AYwByAGkAdABlAHIAaQBhAFwAbgAgACAAIAAgAEMAdQBzAHQAbwBtALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALAAgAE4ATwBUACgAQQBOAEQAKABUAE8AQwBPAEwAKAB2ACwAIAAyACkAIAA9ACAAYwB1AHMAdABvAG0AXwBjAHIAaQB0AGUAcgBpAGEAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABwAHIAZQBkAGkAYwBhAHQAZQBcAG4AIAAgACAAIABmAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABjAHUAcwB0AG8AbQBfAGMAcgBpAHQAZQByAGkAYQApACwAIABLAGUAZQBwALsDLAAgAEMAdQBzAHQAbwBtALsDKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAvAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAHQAbwAgAGsAZQBlAHAAXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAEkARgAoAEIAWQBSAE8AVwAoAGEAcgByAGEAeQAsACAAZgBuACkALAAgAGkALAAgAE4AQQAoACkAKQAsACAAMgApACwAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBSAE8AVwAoAEkARgAoAEIAWQBDAE8ATAAoAGEAcgByAGEAeQAsACAAZgBuACkALAAgAGoALAAgAE4AQQAoACkAKQAsACAAMgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwAgAHIAbwB3AHMAIABvAHIAIABjAG8AbAB1AG0AbgBzACAAcgBlAG0AYQBpAG4APwBcAG4AIAAgACAAIABJAHMARQBtAHAAdAB5AD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAFMARQBSAFIATwBSACgAYQApACwAIABJAFMARQBSAFIATwBSACgAYgApACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBlAHcAIABzAGgAYQBwAGUAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHkALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiACAAKgAgAFMARQBRAFUARQBOAEMARQAoAHgALAAgACwAIAAxACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAHIAZQBzAHUAbAB0AFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAHIALAAgAGMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIAB6AGUAcgBvACAAcwB1AHAAcAByAGUAcwBzAGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AF8AYgAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAByAGUAcwB1AGwAdAAgAD0AIAAwACwAIABcACIAXAAiACwAIAByAGUAcwB1AGwAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0AFwAbgAgACAAIAAgAG8AdQB0AHAAdQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARQBtAHAAdAB5AD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBFAE0AUABUAFkALQBBAFIAUgBBAFkAIQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABIAGkAZABlAFoAZQByAG8APwAsACAAcgBlAHMAdQBsAHQAXwBiACwAIAByAGUAcwB1AGwAdAApACkALABcAG4AXABuACAAIAAgACAAbwB1AHQAcAB1AHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAwADcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABLAHIAbwBuAGUAYwBrAGUAcgBQAHIAbwBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgARQB4AHAAYQBuAHMAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAE0AYQBnAG4AaQBmAHkAuwMsACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAASwByAG8AbgBlAGMAawBlAHIAIABwAHIAbwBkAHUAYwB0ACAAbwBmACAAdAB3AG8AIABhAHIAcgBhAHkAcwAuACAAVABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIABpAHMAIABlAHgAcABhAG4AZABlAGQAXABuACAAIAAgACAAdQBzAGkAbgBnACAATQBhAGcAbgBpAGYAeQC7AyAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABoAGUAaQBnAGgAdAAgAGEAbgBkACAAdwBpAGQAdABoACAAbwBmACAAYQByAHIAYQB5AF8AMgAsACAAdwBoAGkAbABlACAAYQByAHIAYQB5AF8AMgAgAGkAcwBcAG4AIAAgACAAIAByAGUAcwBpAHoAZQBkACAAdQBzAGkAbgBnACAAUgBlAHMAaQB6AGUAuwMgAHQAbwAgAG0AYQB0AGMAaAAgAHQAaABlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAG8AZgAgAGEAcgByAGEAeQBfADEALgAgAFQAaABlAGkAcgAgAGUAbABlAG0AZQBuAHQAESB3AGkAcwBlAFwAbgAgACAAIAAgAHAAcgBvAGQAdQBjAHQAIAB5AGkAZQBsAGQAcwAgAHQAaABlACAAZgB1AGwAbAAgAEsAcgBvAG4AZQBjAGsAZQByACAAZQB4AHAAYQBuAHMAaQBvAG4ALgBcAG4AXABuACAAIAAgACAAQQBsAHQAaABvAHUAZwBoACAASwByAG8AbgBlAGMAawBlAHIAIABwAHIAbwBkAHUAYwB0AHMAIABhAHIAZQAgAHQAcgBhAGQAaQB0AGkAbwBuAGEAbABsAHkAIABkAGUAZgBpAG4AZQBkACAAZgBvAHIAIABtAGEAdAByAGkAYwBlAHMALAAgAHQAaABpAHMAXABuACAAIAAgACAAaQBtAHAAbABlAG0AZQBuAHQAYQB0AGkAbwBuACAAYQBsAHMAbwAgAHMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByAHMAIABhAG4AZAAgADEARAAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIAcwAgAGEAYwBjAGUAcAB0AGUAZAApAC4AXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIAcwAgAGEAYwBjAGUAcAB0AGUAZAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQgByAG8AYQBkAGMAYQBzAHQAaQBuAGcAIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAAgAHYAaQBhACAAbgBlAGEAcgBlAHMAdAARIG4AZQBpAGcAaABiAG8AcgAgAGUAeABwAGEAbgBzAGkAbwBuAC4AXABuACAAIAAgACAAIiAgAFQAaABlACAAbwB1AHQAcAB1AHQAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAYQByAGUAIAAoAFIATwBXAFMAKABhAHIAcgBhAHkAXwAxACkAKgBSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACkAIADXAFwAbgAgACAAIAAgACAAIAAoAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAxACkAKgBDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgApACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASwByAG8AbgBlAGMAawBlAHIAUAByAG8AZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAxACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGgAgiAsACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACwAXABuACAAIAAgACAAdwCCICwAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgByAG8AYQBkAGMAYQBzAHQAIABhAHIAcgBhAHkAXwAxACAAYgB5ACAAbQBhAGcAbgBpAGYAeQBpAG4AZwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuAHQAbwAgAGEAbgAgAGgAgiAgANcAIAB3AIIgIABiAGwAbwBjAGsAXABuACAAIAAgACAAQQAsACAAIAAgACAAIAAgAE0AYQBnAG4AaQBmAHkAuwMoAGEAcgByAGEAeQBfADEALAAgAGgAgiAsACAAdwCCICkALABcAG4AXABuACAAIAAgACAALwAvACAAQgByAG8AYQBkAGMAYQBzAHQAIABhAHIAcgBhAHkAXwAyACAAYgB5ACAAcgBlAHMAaQB6AGkAbgBnACAAaQB0ACAAdABvACAAbQBhAHQAYwBoACAAYQByAHIAYQB5AF8AMQAZIHMAIABzAHQAcgB1AGMAdAB1AHIAZQBcAG4AIAAgACAAIABCACwAIAAgACAAIAAgACAAUgBlAHMAaQB6AGUAuwMoAGEAcgByAGEAeQBfADIALAAgAGgALAAgAHcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAGwAZQBtAGUAbgB0ABEgdwBpAHMAZQAgAHAAcgBvAGQAdQBjAHQAIAB5AGkAZQBsAGQAcwAgAHQAaABlACAASwByAG8AbgBlAGMAawBlAHIAIABlAHgAcABhAG4AcwBpAG8AbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAQQAgACoAIABCACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARQB4AGMAbAB1AGQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEYAaQBsAHQAZQByAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABGAGkAbAB0AGUAcgBzACAAYQBuACAAYQByAHIAYQB5ACAAKAAxAEQAIABvAHIAIAAyAEQAKQAgAGIAeQAgAGUAeABjAGwAdQBkAGkAbgBnACAAYQBuAHkAIAByAG8AdwAgAHQAaABhAHQAIABjAG8AbgB0AGEAaQBuAHMAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBvAG4ALgAgAEUAeABjAGwAdQBkAGUAuwMgAGkAcwAgAGEAIABzAGkAbQBwAGwAaQBmAGkAZQBkACAAYQBsAHQAZQByAG4AYQB0AGkAdgBlACAAdABvACAARgBJAEwAVABFAFIAIAB3AGgAZQByAGUAIAB0AGgAZQAgAHUAcwBlAHIAXABuACAAIAAgACAAcwB1AHAAcABsAGkAZQBzACAAdABoAGUAIABlAHgAYwBsAHUAcwBpAG8AbgAgAHYAYQBsAHUAZQBzACAAZABpAHIAZQBjAHQAbAB5ACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAYQAgAGIAbwBvAGwAZQBhAG4AIABtAGEAcwBrAC4AXABuAFwAbgAgACAAIAAgAFQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAYwBoAGUAYwBrAHMAIABlAGEAYwBoACAAcgBvAHcAIABmAG8AcgAgAHQAaABlACAAcAByAGUAcwBlAG4AYwBlACAAbwBmACAAYQBuAHkAIAB2AGEAbAB1AGUAIABpAG4AIAAnAGUAeABjAGwAdQBkAGUAJwAuAFwAbgAgACAAIAAgAFIAbwB3AHMAIAB0AGgAYQB0ACAAYwBvAG4AdABhAGkAbgAgAHQAaABlACAAZQB4AGMAbAB1AHMAaQBvAG4AIABjAHIAaQB0AGUAcgBpAG8AbgAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAA7ACAAYQBsAGwAIABvAHQAaABlAHIAcwAgAGEAcgBlACAAawBlAHAAdAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABmAGkAbAB0AGUAcgAuAFwAbgAgACAAIAAgAGUAeABjAGwAdQBkAGUAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAG8AcgAgADEARAAgAGEAcgByAGEAeQAgAG8AZgAgAHYAYQBsAHUAZQBzACAAdABvACAAbwBtAGkAdAAuAFwAbgAgACAAIAAgAFsAaQBmAF8AZQBtAHAAdAB5AF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGEAbABsAGIAYQBjAGsAIAB2AGEAbAB1AGUAIAB3AGgAZQBuACAAbgBvACAAcgBvAHcAcwAgAHIAZQBtAGEAaQBuACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgADAAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEEAIAAyAEQAIABlAHgAYwBsAHUAZABlACAAYQByAHIAYQB5ACAAaQBzACAAaQBuAHYAYQBsAGkAZAAgAGEAbgBkACAAaABhAGwAdABzACAAdwBpAHQAaAAgAFwAIgAjADIARAAtAEUAWABDAEwAVQBEAEUAIQBcACIALgBcAG4AIAAgACAAIAAiICAATQBhAHQAYwBoAGkAbgBnACAAaQBzACAAcABlAHIAZgBvAHIAbQBlAGQAIAB1AHMAaQBuAGcAIABYAE0AQQBUAEMASAA7ACAAbgBvAG4AESBtAGEAdABjAGgAZQBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAegBlAHIAbwAuAFwAbgAgACAAIAAgACIgIABGAGkAbAB0AGUAcgBpAG4AZwAgAGkAcwAgAHIAbwB3ABEgdwBpAHMAZQA7ACAAYwBvAGwAdQBtAG4AcwAgAGEAcgBlACAAcAByAGUAcwBlAHIAdgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARQB4AGMAbAB1AGQAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABlAHgAYwBsAHUAZABlACwAXABuACAAIAAgACAAWwBpAGYAXwBlAG0AcAB0AHkAXQAsAFwAbgBcAG4ASQBGACgAQQBOAEQAKABSAE8AVwBTACgAZQB4AGMAbAB1AGQAZQApACAAPgAgADEALAAgAEMATwBMAFUATQBOAFMAKABlAHgAYwBsAHUAZABlACkAIAA+ACAAMQApACwAXAAiACMAMgBEAC0ARQBYAEMATABVAEQARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGEAbABsAGIAYQBjAGsAXABuACAAIAAgACAAaQBmAF8AZQBtAHAAdAB5ACwAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZgBfAGUAbQBwAHQAeQApACwAIAAwACwAIABpAGYAXwBlAG0AcAB0AHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAFIAVQBFACAAPQAgAGsAZQBlAHAAIAByAG8AdwAsACAARgBBAEwAUwBFACAAPQAgAGUAeABjAGwAdQBkAGUAIAByAG8AdwBcAG4AIAAgACAAIABrAGUAZQBwAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgAQgBZAFIATwBXACgASQBGAE4AQQAoAFgATQBBAFQAQwBIACgAYQByAHIAYQB5ACwAIABlAHgAYwBsAHUAZABlACkALAAgADAAKQAsAE8AUgApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAawBlAGUAcAA/ACwAIABpAGYAXwBlAG0AcAB0AHkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMAA5AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBuAGEAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAEYAaQBsAHQAZQByAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABGAGkAbAB0AGUAcgBzACAAYQBuACAAYQByAHIAYQB5ACAAKAAxAEQAIABvAHIAIAAyAEQAKQAgAGIAeQAgAHMAZQBsAGUAYwB0AGkAbgBnACAAcgBvAHcAcwAgAHQAaABhAHQAIABjAG8AbgB0AGEAaQBuACAAYQB0ACAAbABlAGEAcwB0ACAAbwBuAGUAXABuACAAIAAgACAAdgBhAGwAdQBlACAAZgByAG8AbQAgAHQAaABlACAAJwBpAG4AYwBsAHUAZABlACcAIABjAHIAaQB0AGUAcgBpAGEALgAgAFMAbgBhAHAAuwMgAGkAcwAgAGEAIABzAGkAbQBwAGwAaQBmAGkAZQBkACAAYQBsAHQAZQByAG4AYQB0AGkAdgBlACAAdABvAFwAbgAgACAAIAAgAEYASQBMAFQARQBSACAAdwBoAGUAcgBlACAAdABoAGUAIAB1AHMAZQByACAAcwB1AHAAcABsAGkAZQBzACAAdABoAGUAIABpAG4AYwBsAHUAcwBpAG8AbgAgAHYAYQBsAHUAZQBzACAAZABpAHIAZQBjAHQAbAB5ACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuAFwAbgAgACAAIAAgAGEAIABiAG8AbwBsAGUAYQBuACAAbQBhAHMAawAuAFwAbgBcAG4AIAAgACAAIABUAGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAGMAaABlAGMAawBzACAAZQBhAGMAaAAgAHIAbwB3ACAAZgBvAHIAIAB0AGgAZQAgAHAAcgBlAHMAZQBuAGMAZQAgAG8AZgAgAGEAbgB5ACAAdgBhAGwAdQBlACAAaQBuACAAJwBpAG4AYwBsAHUAZABlACcALgBcAG4AIAAgACAAIABSAG8AdwBzACAAdABoAGEAdAAgAGMAbwBuAHQAYQBpAG4AIAB0AGgAZQAgAGkAbgBjAGwAdQBzAGkAbwBuACAAYwByAGkAdABlAHIAaQBvAG4AIABhAHIAZQAgAGsAZQBwAHQAOwAgAGEAbABsACAAbwB0AGgAZQByAHMAIABhAHIAZQAgAHIAZQBtAG8AdgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAZgBpAGwAdABlAHIALgBcAG4AIAAgACAAIABpAG4AYwBsAHUAZABlACAAIAAgACAAIAAtACAAUwBjAGEAbABhAHIAIABvAHIAIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGkAbgBjAGwAdQBkAGUALgBcAG4AIAAgACAAIABbAGkAZgBfAGUAbQBwAHQAeQBdACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAZgBhAGwAbABiAGEAYwBrACAAdgBhAGwAdQBlACAAdwBoAGUAbgAgAG4AbwAgAHIAbwB3AHMAIAByAGUAbQBhAGkAbgAgACgAZABlAGYAYQB1AGwAdAAgAD0AIAAwACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABBACAAMgBEACAAaQBuAGMAbAB1AGQAZQAgAGEAcgByAGEAeQAgAGkAcwAgAGkAbgB2AGEAbABpAGQAIABhAG4AZAAgAGgAYQBsAHQAcwAgAHcAaQB0AGgAIABcACIAIwAyAEQALQBJAE4AQwBMAFUARABFACEAXAAiAC4AXABuACAAIAAgACAAIiAgAE0AYQB0AGMAaABpAG4AZwAgAGkAcwAgAHAAZQByAGYAbwByAG0AZQBkACAAdQBzAGkAbgBnACAAWABNAEEAVABDAEgAOwAgAG4AbwBuABEgbQBhAHQAYwBoAGUAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgAHoAZQByAG8ALgBcAG4AIAAgACAAIAAiICAARgBpAGwAdABlAHIAaQBuAGcAIABpAHMAIAByAG8AdwARIHcAaQBzAGUAOwAgAGMAbwBsAHUAbQBuAHMAIABhAHIAZQAgAHAAcgBlAHMAZQByAHYAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAbgBhAHAAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAaQBuAGMAbAB1AGQAZQAsAFwAbgAgACAAIAAgAFsAaQBmAF8AZQBtAHAAdAB5AF0ALABcAG4AXABuAEkARgAoAEEATgBEACgAUgBPAFcAUwAoAGkAbgBjAGwAdQBkAGUAKQAgAD4AIAAxACwAIABDAE8ATABVAE0ATgBTACgAaQBuAGMAbAB1AGQAZQApACAAPgAgADEAKQAsAFwAIgAjADIARAAtAEkATgBDAEwAVQBEAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZgBhAGwAbABiAGEAYwBrAFwAbgAgACAAIAAgAGkAZgBfAGUAbQBwAHQAeQAsACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABpAGYAXwBlAG0AcAB0AHkAKQAsACAAMAAsACAAaQBmAF8AZQBtAHAAdAB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABSAFUARQAgAD0AIABrAGUAZQBwACAAcgBvAHcALAAgAEYAQQBMAFMARQAgAD0AIABkAGkAcwBjAGEAcgBkACAAcgBvAHcAXABuACAAIAAgACAAawBlAGUAcAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKABJAEYATgBBACgAWABNAEEAVABDAEgAKABhAHIAcgBhAHkALAAgAGkAbgBjAGwAdQBkAGUAKQAsACAAMAApACwATwBSACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsACAAawBlAGUAcAA/ACwAIABpAGYAXwBlAG0AcAB0AHkAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQAwAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBoAGkAZgB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUgBvAGwAbABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAARQB4AHAAbABvAGQAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUABlAHIAZgBvAHIAbQBzACAAYQAgAGMAaQByAGMAdQBsAGEAcgAgAHMAaABpAGYAdAAgAG8AbgAgAGEAIABzAHUAcABwAGwAaQBlAGQAIAB0AHUAcABsAGUAIAAoAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQApAC4AXABuACAAIAAgACAAUABvAHMAaQB0AGkAdgBlACAAcwBoAGkAZgB0ACAAdgBhAGwAdQBlAHMAIAByAG8AdABhAHQAZQAgAGwAZQBmAHQAOwAgAG4AZQBnAGEAdABpAHYAZQAgAHMAaABpAGYAdAAgAHYAYQBsAHUAZQBzACAAcgBvAHQAYQB0AGUAIAByAGkAZwBoAHQALgBcAG4AXABuACAAIAAgACAARQB4AGEAbQBwAGwAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAA9AFMAaABpAGYAdAC7AygAewAxACwAMgAsADMALAA0AH0ALAAgADIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAkiEgAHsAMwAsADQALAAxACwAMgB9AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAD0AUwBoAGkAZgB0ALsDKAB7ADEALAAyACwAMwAsADQAfQAsACAALQAxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAJIhIAB7ADQALAAxACwAMgAsADMAfQBcAG4AXABuACAAIAAgACAAIAAgACAAIAA9AFMAaABpAGYAdAC7AygAXAAiADEAMgAzADQAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAJIhIAB7AFwAIgAyAFwAIgA7AFwAIgAzAFwAIgA7AFwAIgA0AFwAIgA7AFwAIgAxAFwAIgB9AFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAA9AFMAaABpAGYAdAC7AygAewAxACwAMgAsADMALAA0AH0ALAB7ADEALAAyACwAMwB9ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAJIhIAB7ADIALAAzACwANAAsADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMwAsADQALAAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACwAMQAsADIALAAzAH0AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAdAB1AHAAbABlACAAIAAgACAAIAAgACAALQAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAZQB4AHAAbABvAGQAZQBkACAAaQBuAHQAbwAgAGMAaABhAHIAYQBjAHQAZQByACAAYQByAHIAYQB5AHMAIAB2AGkAYQAgAEUAeABwAGwAbwBkAGUAuwMuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAdwBpAHQAaAAgAFQATwBDAE8ATAAuAFwAbgBcAG4AIAAgACAAIABbAHMAaABpAGYAdABfAGIAeQBdACAAIAAtACAAUwBoAGkAZgB0ACAAYwBvAHUAbgB0ACAAKABkAGUAZgBhAHUAbAB0ACAAPQAgADEAKQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAAUABvAHMAaQB0AGkAdgBlACAAkiEgAGwAZQBmAHQAIABzAGgAaQBmAHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABOAGUAZwBhAHQAaQB2AGUAIACSISAAcgBpAGcAaAB0ACAAcwBoAGkAZgB0AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAATQB1AGwAdABpABEgcwBoAGkAZgB0ACAAYQByAHIAYQB5AHMAIABwAHIAbwBkAHUAYwBlACAAYQAgAGEAcgByAGEAeQBfADIARAAgAG8AZgAgAHMAaABpAGYAdABlAGQAIAB0AHUAcABsAGUAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuACAAbQBhAHQAYwBoAGUAcwAgAGkAbgBwAHUAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgBzACAAkiEgAHYAZQByAHQAaQBjAGEAbABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAtACAAVgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5AHMAIACSISAAdgBlAHIAdABpAGMAYQBsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAC0AIABIAG8AcgBpAHoAbwBuAHQAYQBsACAAYQByAHIAYQB5AHMAIACSISAAaABvAHIAaQB6AG8AbgB0AGEAbABcAG4AIAAgACAAIAAiICAATQB1AGwAdABpABEgcwBoAGkAZgB0ACAAaQBuAHAAdQB0AHMAIAByAGUAdAB1AHIAbgAgAGEAIABzAHQAYQBjAGsAZQBkACAAYQByAHIAYQB5AF8AMgBEACAAbwBmACAAcwBoAGkAZgB0AGUAZAAgAHIAZQBzAHUAbAB0AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBoAGkAZgB0ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHQAdQBwAGwAZQAsAFwAbgAgACAAIAAgAFsAcwBoAGkAZgB0AF8AYgB5AF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAB0AHUAcABsAGUAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAdAB1AHAAbABlACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHQAdQBwAGwAZQAgAJIhIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAXABuACAAIAAgACAAdAB1AHAAbABlACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwARQB4AHAAbABvAGQAZQC7AygAdAB1AHAAbABlACkALAB0AHUAcABsAGUAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcwBoAGkAZgB0AF8AYgB5ACAAkiEgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABzAGgAaQBmAHQAXwBiAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABzAGgAaQBmAHQAXwBiAHkAKQAsACAAMQAsACAAcwBoAGkAZgB0AF8AYgB5ACkAKQAsAFwAbgAgACAAIAAgAEkAcwBNAHUAbAB0AGkAUwBoAGkAZgB0AD8ALAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHMAaABpAGYAdABfAGIAeQApACAAPgAgADEALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAASQBzADEARQBsAGUAbQBlAG4AdAA/ACwAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAdAB1AHAAbABlACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEkAcwBUAGUAeAB0AFMAaABpAGYAdAA/ACwAIAAgACAAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHMAaABpAGYAdABfAGIAeQApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzADEARQBsAGUAbQBlAG4AdAA/ACwAIAB0AHUAcABsAGUALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVABlAHgAdABTAGgAaQBmAHQAPwAsACAAXAAiACMAVABFAFgAVAAtAFMASABJAEYAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABUAHUAcABsAGUAIABsAGUAbgBnAHQAaABcAG4AIAAgACAAIABuACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHQAdQBwAGwAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgADAAESBiAGEAcwBlAGQAIABpAG4AZABlAHgAIABzAGUAcQB1AGUAbgBjAGUAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG4ALAAgADAALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGkAcgBjAHUAbABhAHIAIABpAG4AZABlAHgAIABzAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIABNAE8ARAAoAGkAIAArACAAcwBoAGkAZgB0AF8AYgB5ACwAIABuACkAIAArACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABzAGgAaQBmAHQAXABuACAAIAAgACAAcwBoAGkAZgB0AGUAZAAsACAAIAAgACAASQBOAEQARQBYACgAdAB1AHAAbABlACwAIABpAGQAeAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAHQAbwByAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAASQBGACgASQBzAE0AdQBsAHQAaQBTAGgAaQBmAHQAPwAsACAAcwBoAGkAZgB0AGUAZAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAcwBoAGkAZgB0AGUAZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AUgBPAFcAKABzAGgAaQBmAHQAZQBkACkAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUwBoAGkAZgB0AFIAbwB3AHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABSAG8AbABsAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABTAGgAaQBmAHQAuwMsACAATQBHAHIAaQBkALsDLAAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGUAcgBmAG8AcgBtAHMAIABhACAAYwBpAHIAYwB1AGwAYQByACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgAHMAaABpAGYAdAAgAG8AbgAgAGUAYQBjAGgAIAByAG8AdwAgAG8AZgAgAGEAIAAyAEQAIABhAHIAcgBhAHkALgAgAFQAaABlACAAcwBoAGkAZgB0AF8AYgB5AFwAbgAgACAAIAAgAHYAYQBsAHUAZQAgAGQAZQB0AGUAcgBtAGkAbgBlAHMAIABoAG8AdwAgAG0AYQBuAHkAIABwAG8AcwBpAHQAaQBvAG4AcwAgAGUAYQBjAGgAIAByAG8AdwAgAGkAcwAgAHIAbwB0AGEAdABlAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABQAG8AcwBpAHQAaQB2AGUAIACSISAAcwBoAGkAZgB0ACAAbABlAGYAdABcAG4AIAAgACAAIAAgACAAIAAgACIgIABOAGUAZwBhAHQAaQB2AGUAIACSISAAcwBoAGkAZgB0ACAAcgBpAGcAaAB0AFwAbgBcAG4AIAAgACAAIAAxAEQAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAcwBjAGEAbABhAHIAcwAgAGEAcgBlACAAZABlAGwAZQBnAGEAdABlAGQAIAB0AG8AIABTAGgAaQBmAHQAuwMuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAPQAgAHsAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgAsAFwAIgBCAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYgBcACIALABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGUAXAAiACwAXAAiAEgAaQBzAHQAbwByAHkAXAAiACwAXAAiAEIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAbwBlAFwAIgAsAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIALABcACIAQwBcACIAfQBcAG4AXABuACAAIAAgACAAPQBTAGgAaQBmAHQAUgBvAHcAcwC7AygAYQByAHIAYQB5ACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIACSISAAewBcACIATQBhAHQAaABcACIALABcACIAQgBcACIALABcACIAQgBvAGIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIALABcACIARABlAGIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAHMAdABvAHIAeQBcACIALABcACIAQgBcACIALABcACIAUwB1AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGUAbQBpAHMAdAByAHkAXAAiACwAXAAiAEMAXAAiACwAXAAiAEoAbwBlAFwAIgB9AFwAbgBcAG4AIAAgACAAIAA9AFMAaABpAGYAdABSAG8AdwBzALsDKABhAHIAcgBhAHkALAAgAC0AMQApAFwAbgAgACAAIAAgACAAIAAgACAAkiEgAHsAXAAiAEIAXAAiACwAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAXAAiACwAXAAiAEQAZQBiAFwAIgAsAFwAIgBQAGgAeQBzAGkAYwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAXAAiACwAXAAiAFMAdQBlAFwAIgAsAFwAIgBIAGkAcwB0AG8AcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXAAiACwAXAAiAEoAbwBlAFwAIgAsAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIAfQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBoAGkAZgB0AFIAbwB3AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAWwBzAGgAaQBmAHQAXwBiAHkAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABhAHIAcgBhAHkAcwAgAC8AIABzAGMAYQBsAGEAcgBzACAAaABhAG4AZABsAGUAZAAgAGIAeQAgAFMAaABpAGYAdAC7A1wAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALABTAGgAaQBmAHQAuwMoAGEAcgByAGEAeQBfADIARAAsACAAcwBoAGkAZgB0AF8AYgB5ACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUgBvAHcAIABpAG4AZABpAGMAZQBzACAAcgBlAG0AYQBpAG4AIABmAGkAeABlAGQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIABNAEcAcgBpAGQAuwMoAGEAcgByAGEAeQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAGEAcgBlACAAYwBpAHIAYwB1AGwAYQByAGwAeQAgAHMAaABpAGYAdABlAGQAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIABSAGUAcwBpAHoAZQC7AygAUwBoAGkAZgB0ALsDKABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwApACwAIABzAGgAaQBmAHQAXwBiAHkAKQAsAGgAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQBfADIARAAsACAAaQAsACAAagApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFMAaABpAGYAdABDAG8AbABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUgBvAGwAbABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUwBoAGkAZgB0ALsDLAAgAE0ARwByAGkAZAC7AywAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUABlAHIAZgBvAHIAbQBzACAAYQAgAGMAaQByAGMAdQBsAGEAcgAgAHYAZQByAHQAaQBjAGEAbAAgAHMAaABpAGYAdAAgAG8AbgAgAGUAYQBjAGgAIABjAG8AbAB1AG0AbgAgAG8AZgAgAGEAIAAyAEQAIABhAHIAcgBhAHkALgAgAFQAaABlACAAcwBoAGkAZgB0AF8AYgB5AFwAbgAgACAAIAAgAHYAYQBsAHUAZQAgAGQAZQB0AGUAcgBtAGkAbgBlAHMAIABoAG8AdwAgAG0AYQBuAHkAIABwAG8AcwBpAHQAaQBvAG4AcwAgAGUAYQBjAGgAIABjAG8AbAB1AG0AbgAgAGkAcwAgAHIAbwB0AGEAdABlAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABQAG8AcwBpAHQAaQB2AGUAIACSISAAcwBoAGkAZgB0ACAAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAE4AZQBnAGEAdABpAHYAZQAgAJIhIABzAGgAaQBmAHQAIABkAG8AdwBuAFwAbgBcAG4AIAAgACAAIAAxAEQAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAcwBjAGEAbABhAHIAcwAgAGEAcgBlACAAZABlAGwAZQBnAGEAdABlAGQAIAB0AG8AIABTAGgAaQBmAHQAuwMuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAPQAgAHsAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgAsAFwAIgBCAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYgBcACIALABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGUAXAAiACwAXAAiAEgAaQBzAHQAbwByAHkAXAAiACwAXAAiAEIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAbwBlAFwAIgAsAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIALABcACIAQwBcACIAfQBcAG4AXABuACAAIAAgACAAPQBTAGgAaQBmAHQAQwBvAGwAcwC7AygAYQByAHIAYQB5ACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIACSISAAewBcACIARABlAGIAXAAiACwAXAAiAFAAaAB5AHMAaQBjAHMAXAAiACwAXAAiAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGUAXAAiACwAXAAiAEgAaQBzAHQAbwByAHkAXAAiACwAXAAiAEIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASgBvAGUAXAAiACwAXAAiAEMAaABlAG0AaQBzAHQAcgB5AFwAIgAsAFwAIgBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBiAFwAIgAsAFwAIgBNAGEAdABoAFwAIgAsAFwAIgBCAFwAIgB9AFwAbgBcAG4AIAAgACAAIAA9AFMAaABpAGYAdABDAG8AbABzALsDKABhAHIAcgBhAHkALAAgAC0AMQApAFwAbgAgACAAIAAgACAAIAAgACAAkiEgAHsAXAAiAEoAbwBlAFwAIgAsAFwAIgBDAGgAZQBtAGkAcwB0AHIAeQBcACIALABcACIAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAG8AYgBcACIALABcACIATQBhAHQAaABcACIALABcACIAQgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYgBcACIALABcACIAUABoAHkAcwBpAGMAcwBcACIALABcACIAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZQBcACIALABcACIASABpAHMAdABvAHIAeQBcACIALABcACIAQgBcACIAfQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwBoAGkAZgB0AEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAWwBzAGgAaQBmAHQAXwBiAHkAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABhAHIAcgBhAHkAcwAgAC8AIABzAGMAYQBsAGEAcgBzACAAaABhAG4AZABsAGUAZAAgAGIAeQAgAFMAaABpAGYAdAC7A1wAbgAgACAAIAAgAEkAcwAxAEQAPwAsACAAIAAgACAAIAAgACAATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALABTAGgAaQBmAHQAuwMoAGEAcgByAGEAeQBfADIARAAsACAAcwBoAGkAZgB0AF8AYgB5ACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAYQByAGUAIABjAGkAcgBjAHUAbABhAHIAbAB5ACAAcwBoAGkAZgB0AGUAZABcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBzAGkAegBlALsDKABTAGgAaQBmAHQAuwMoAFMARQBRAFUARQBOAEMARQAoAGgAKQAsACAAcwBoAGkAZgB0AF8AYgB5ACkALAAsAHcAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGkAbgBkAGkAYwBlAHMAIAByAGUAbQBhAGkAbgAgAGYAaQB4AGUAZABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ARwByAGkAZAC7AygAYQByAHIAYQB5AF8AMgBEACwAIAAxACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIABJAE4ARABFAFgAKABhAHIAcgBhAHkAXwAyAEQALAAgAGkALAAgAGoAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADMAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABFAG0AYgBlAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABTAGUAbABlAGMAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQBtAGIAZQBkAHMAIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAGEAIAAyAEQAIABoAG8AcwB0ACAAYQByAHIAYQB5ACAAYQB0ACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgBcAG4AIAAgACAAIABpAG4AZABlAHgALgAgAEUAbQBiAGUAZAC7AyAAcwB1AHAAcABvAHIAdABzACAAcwBjAGEAbABhAHIAcwAsACAAMQBEACAAYQByAHIAYQB5AHMALAAgAGEAbgBkACAAMgBEACAAYQByAHIAYQB5AHMALgAgAFQAaABlACAAZQBtAGIAZQBkAGQAZQBkACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAGkAcwAgAGEAdQB0AG8AbQBhAHQAaQBjAGEAbABsAHkAIABlAHgAcABhAG4AZABlAGQAIABhAHMAIABuAGUAZQBkAGUAZAAgAHQAbwAgAG0AYQBpAG4AdABhAGkAbgAgAHIAZQBjAHQAYQBuAGcAdQBsAGEAcgBpAHQAeQAgAGEAbgBkACAAYQB2AG8AaQBkAFwAbgAgACAAIAAgAGoAYQBnAGcAZQBkACAAcgBlAHMAdQBsAHQAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMQBEACAAbwByACAAMgBEACAAaABvAHMAdAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQAgACAAIAAtACAAQQByAHIAYQB5ACAAdABvACAAZQBtAGIAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGgAbwBzAHQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAHIAbwB3AF8AaQBuAGQAZQB4AF0AIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHIAbwB3ACAAcABvAHMAaQB0AGkAbwBuACAAZgBvAHIAIABpAG4AcwBlAHIAdABpAG8AbgAuAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAYwBvAGwAdQBtAG4AIABwAG8AcwBpAHQAaQBvAG4AIABmAG8AcgAgAGkAbgBzAGUAcgB0AGkAbwBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAASQBmACAAYgBvAHQAaAAgAGEAcgBlACAAcwB1AHAAcABsAGkAZQBkACwAIAByAG8AdwBfAGkAbgBkAGUAeAAgAHQAYQBrAGUAcwAgAHAAcgBlAGMAZQBkAGUAbgBjAGUALgBcAG4AXABuAE4AdQBhAG4AYwBlAHMAOgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGUAeABwAGEAbgBkACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkAIAB3AGgAZQBuACAAaQBuAHMAZQByAHQAZQBkACAAYgB5ACAAcgBvAHcAXwBpAG4AZABlAHgALAAgAHYAZQByAHQAaQBjAGEAbABsAHkAIAB3AGgAZQBuAFwAbgAgACAAIAAgACAAIABpAG4AcwBlAHIAdABlAGQAIABiAHkAIABjAG8AbABfAGkAbgBkAGUAeAAuAFwAbgAgACAAIAAgACIgIAAxAEQALwAyAEQAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkAIABpAG4AcAB1AHQAcwAgAHQAaABhAHQAIABkAG8AIABuAG8AdAAgAG0AYQB0AGMAaAAgAGgAbwBzAHQAIAB3AGkAZAB0AGgALwBoAGUAaQBnAGgAdAAgAGEAcgBlACAAcABhAGQAZABlAGQAXABuACAAIAAgACAAIAAgAHcAaQB0AGgAIABcACIAXAAiACAAdABvACAAbQBhAGkAbgB0AGEAaQBuACAAcgBlAGMAdABhAG4AZwB1AGwAYQByAGkAdAB5AC4AXABuACAAIAAgACAAIiAgAFwAIgAjAFIATwBXAC8AQwBPAEwALQBJAE4ARABFAFgAXAAiACAAaQBzACAAcgBlAHQAdQByAG4AZQBkACAAZgBvAHIAIABuAG8AbgARIG4AdQBtAGUAcgBpAGMAIABvAHIAIABvAHUAdAARIG8AZgARIGIAbwB1AG4AZABzACAAaQBuAGQAaQBjAGUAcwAuAFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYwBhAG4AbgBvAHQAIABzAGUAcgB2AGUAIABhAHMAIABoAG8AcwB0ACAAYQByAHIAYQB5AHMAOwAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiACAAaQBzACAAcgBlAHQAdQByAG4AZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAbQBiAGUAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAHIAbwB3AF8AaQBuAGQAZQB4AF0ALABcAG4AIAAgACAAIABbAGMAbwBsAF8AaQBuAGQAZQB4AF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABIAG8AcwB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAG0AYgBlAGQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAgiAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3AIIgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGUAbQBiAGUAZABfAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQByAGEAbQBlAHQAZQByACAAcAByAGUAcwBlAG4AYwBlAFwAbgAgACAAIAAgAFIAbwB3AEUAbQBiAGUAZAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAXwBpAG4AZABlAHgAKQApACwAXABuACAAIAAgACAAQwBvAGwARQBtAGIAZQBkAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABjAG8AbABfAGkAbgBkAGUAeAApACkALABcAG4AIAAgACAAIABSAEMARQBtAGIAZQBkAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABSAG8AdwBFAG0AYgBlAGQAPwAsACAAQwBvAGwARQBtAGIAZQBkAD8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AdgBhAGwAaQBkACAAZQBtAGIAZQBkACAAcwBpAHoAZQAgACgAZQBtAGIAZQBkACAAbABhAHIAZwBlAHIAIAB0AGgAYQBuACAAaABvAHMAdAApAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARQBtAGIAZQBkAD8ALAAgACAAIAAgACAAIABJAEYAKABBAE4ARAAoAFIAbwB3AEUAbQBiAGUAZAA/ACwAIAB3AIIgIAA+ACAAdwApACwAIABUAFIAVQBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABDAG8AbABFAG0AYgBlAGQAPwAsACAAaACCICAAPgAgAGgAKQAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABSAEMARQBtAGIAZQBkAD8ALAAgAE8AUgAoAGgAgiAgAD4AIABoACwAIAB3AIIgIAA+ACAAdwApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEEATABTAEUAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4ACAAdgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEkAZAB4AD8ALAAgACAAIAAgACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAByAG8AdwBfAGkAbgBkAGUAeAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBfAGkAbgBkAGUAeAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAcgBvAHcAXwBpAG4AZABlAHgAIAA8ACAAMQAsACAAcgBvAHcAXwBpAG4AZABlAHgAIAA+ACAAaAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAXwBpAG4AZABlAHgAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGMAbwBsAF8AaQBuAGQAZQB4ACAAPAAgADEALAAgAGMAbwBsAF8AaQBuAGQAZQB4ACAAPgAgAHcAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAASABvAHMAdAAgAGMAYQBuAG4AbwB0ACAAYgBlACAAcwBjAGEAbABhAHIAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEkAZAB4AD8ALAAgAFwAIgAjAFIATwBXAC8AQwBPAEwALQBJAE4ARABFAFgAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABFAG0AYgBlAGQAPwAsACAAXAAiACMARQBNAEIARQBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgAHYAZQByAHQAaQBjAGEAbAAgAGkAbgBzAGUAcgB0AGkAbwBuACAAdQBuAGwAZQBzAHMAIABvAG4AbAB5ACAAYwBvAGwAXwBpAG4AZABlAHgAIABpAHMAIABwAHIAbwB2AGkAZABlAGQAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAAIAAgAE8AUgAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAByAG8AdwBfAGkAbgBkAGUAeAApACkALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYwBvAGwAXwBpAG4AZABlAHgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAGMAawAgAGYAdQBuAGMAdABpAG8AbgBcAG4AIAAgACAAIABTAHQAYQBjAGsAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABWAFMAVABBAEMASwAsACAASABTAFQAQQBDAEsAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAYQBsAGEAcgAgAGUAbQBiAGUAZAA/AFwAbgAgACAAIAAgAEkAcwBJAG4AYwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAgiAgAD0AIAAxACwAIAB3AIIgIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBzAGUAcgB0AGkAbwBuACAAaQBuAGQAZQB4AFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgAHIAbwB3AF8AaQBuAGQAZQB4ACwAIABjAG8AbABfAGkAbgBkAGUAeAApACwAXABuACAAIAAgACAAbQBhAHgAXwBkAGkAbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAIAArACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIABoACwAIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBwAGwAaQB0ACAAaABvAHMAdAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABiAGwAbwBjAGsAXwBhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAGEAcgByAGEAeQAsACAAaQBkAHgAIAAtACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAGEAcgByAGEAeQAsACAALAAgAGkAZAB4ACAALQAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAGIAbABvAGMAawBfAGIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQByAHIAYQB5ACwAIAAtACgAMQAgACsAIABoACAALQAgAGkAZAB4ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABhAHIAcgBhAHkALAAgACwAIAAtACgAMQAgACsAIAB3ACAALQAgAGkAZAB4ACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdABhAG4AZABhAHIAZAAgAGkAbgBzAGUAcgB0AGkAbwBuACAAKAB0AG8AcAAgAG8AcgAgAGIAbwB0AHQAbwBtACkAXABuACAAIAAgACAASQBzAFMAdABhAG4AZABhAHIAZAA/ACwAIAAgACAAIAAgACAAIAAgAE8AUgAoAGkAZAB4ACAAPQAgADEALAAgAGkAZAB4ACAAPQAgAG0AYQB4AF8AZABpAG0AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AcwBpAG8AbgAgAHIAdQBsAGUAcwBcAG4AIAAgACAAIABlAHgAcABfAHMAYwBhAGwAYQByAF8AdwBpAGQAdABoACwAIAAgACAARQBYAFAAQQBOAEQAKABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALAAgACwAIAB3ACwAIABlAG0AYgBlAGQAXwBhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGUAeABwAF8AdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAGUAbQBiAGUAZABfAGEAcgByAGEAeQAsACAALAAgAHcALAAgAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgAGUAeABwAF8AcwBjAGEAbABhAHIAXwBoAGUAaQBnAGgAdAAsACAAIABFAFgAUABBAE4ARAAoAGUAbQBiAGUAZABfAGEAcgByAGEAeQAsACAAaAAsACAALAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAZQB4AHAAXwBoAGUAaQBnAGgAdAAsACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACwAIABoACwAIAAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBkACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACAAdABvACAAYQB2AG8AaQBkACAAZABpAG0AZQBuAHMAaQBvAG4AIABtAGkAcwBtAGEAdABjAGgAXABuACAAIAAgACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAgACoAIABJAHMASQBuAGMAUwBjAGEAbABhAHIAPwAsACAAZQB4AHAAXwBzAGMAYQBsAGEAcgBfAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAZQB4AHAAXwB3AGkAZAB0AGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBJAG4AYwBTAGMAYQBsAGEAcgA/ACwAIABlAHgAcABfAHMAYwBhAGwAYQByAF8AaABlAGkAZwBoAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZQB4AHAAXwBoAGUAaQBnAGgAdAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBuAGQAYQByAGQAIAB2AHMAIABtAGkAZAARIGEAcgByAGEAeQAgAGkAbgBzAGUAcgB0AGkAbwBuAFwAbgAgACAAIAAgAHMAdABhAG4AZABhAHIAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABpAGQAeAAgAD0AIAAxACwAUwB0AGEAYwBrALsDKABlAG0AYgBlAGQAXwBhAHIAcgBhAHkALAAgAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AGEAYwBrALsDKABhAHIAcgBhAHkALAAgAGUAbQBiAGUAZABfAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAAcwB0AGEAYwBrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdABhAGMAawC7AygAYgBsAG8AYwBrAF8AYQAsACAAZQBtAGIAZQBkAF8AYQByAHIAYQB5ACwAIABiAGwAbwBjAGsAXwBiACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAHQAYQBuAGQAYQByAGQAPwAsACAAcwB0AGEAbgBkAGEAcgBkACwAIABzAHQAYQBjAGsAKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAASwBlAGUAcABSAG8AdwBzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUwBlAGwAZQBjAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAdAByAGUAYQBrALsDLAAgAEMAbwB1AG4AdABkAG8AdwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdABhAGkAbgBzACAAcgBvAHcAcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgBhAHMAZQBkACAAbwBuACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuAHMALgAgAEEAIABwAG8AcwBpAHQAaQB2AGUAXABuACAAIAAgACAAawBlAGUAcAAgAHYAYQBsAHUAZQAgAHIAZQB0AGEAaQBuAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAHQAaABlACAAdABvAHAAIABvAGYAIABlAGEAYwBoACAAcwB1AGIAZwByAG8AdQBwACAAcgB1AG4AOwAgAGEAIABuAGUAZwBhAHQAaQB2AGUAIABrAGUAZQBwAFwAbgAgACAAIAAgAHYAYQBsAHUAZQAgAHIAZQB0AGEAaQBuAHMAIAByAG8AdwBzACAAZgByAG8AbQAgAHQAaABlACAAYgBvAHQAdABvAG0ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABrAGUAZQBwACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAGkAbgB0AGUAZwBlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAD4AIAAwACAAkiEgAGsAZQBlAHAAIABmAHIAbwBtACAAdABvAHAAIABvAGYAIABlAGEAYwBoACAAcgB1AG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA8ACAAMAAgAJIhIABrAGUAZQBwACAAZgByAG8AbQAgAGIAbwB0AHQAbwBtACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAgACAALQAgAFMAdQBiAGcAcgBvAHUAcAAgAGwAYQBiAGUAbABzACAAKABzAGEAbQBlACAAaABlAGkAZwBoAHQAIABhAHMAIABhAHIAcgBhAHkAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAG8AbgBsAHkAIABvAG4AZQAgAHMAdQBiAGcAcgBvAHUAcAAgAGUAeABpAHMAdABzACwAIABEAFIATwBQACgAKQAgAGkAcwAgAHUAcwBlAGQAIABhAHMAIABhACAAZgBhAHMAdAAgAHAAYQB0AGgALgBcAG4AIAAgACAAIAAiICAAawBlAGUAcAAgAG0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIAOwAgAHQAZQB4AHQAIABvAHIAIAB2AGUAYwB0AG8AcgAgAGkAbgBwAHUAdABzACAAaABhAGwAdAAgAHcAaQB0AGgAIABhAG4AIABlAHIAcgBvAHIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASwBlAGUAcABSAG8AdwBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGsAZQBlAHAALABcAG4AIAAgACAAIABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAHUAYgBnAHIAbwB1AHAAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABPAG4AZQBTAHUAYgBHAHIAbwB1AHAAPwAsACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABVAE4ASQBRAFUARQAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACkAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEQAaQBzAGMAYQByAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIABrAGUAZQBwACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPAA+ACAAUgBPAFcAUwAoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAASQBzAFQAZQB4AHQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAawBlAGUAcAApACwAXABuACAAIAAgACAATgBvAHQAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgATgBPAFQAKABJAHMAVABlAHgAdAA/ACkALAAgAEMATwBVAE4AVABBACgAawBlAGUAcAApACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAHMAYwBlAG4AYQByAGkAbwBzACwAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAASQBzAFQAZQB4AHQAPwAsACAATgBvAHQAUwBjAGEAbABhAHIAPwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAcgByAG8AcgAgAGgAYQBuAGQAbABpAG4AZwBcAG4AIAAgACAAIABoAGEAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAcwBjAGUAbgBhAHIAaQBvAHMAKQAsAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIAOwAgAFwAIgAjAFQARQBYAFQAIQBcACIAOwAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiAH0ALABcAG4AIAAgACAAIABhAGwAZQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBSAFIAQQBZAFQATwBUAEUAWABUACgARgBJAEwAVABFAFIAKABlAHIAcgBvAHIAcwAsACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgADAAKQApACwAXABuAFwAbgAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAE8AbgBlAFMAdQBiAEcAcgBvAHUAcAA/ACwAIABEAGkAcwBjAGEAcgBkACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAaABhAGwAdAAsACAAYQBsAGUAcgB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQByAGUAYwB0AGkAbwBuADoAIAArAHQAbwBwACwAIAATIGIAbwB0AHQAbwBtAFwAbgAgACAAIAAgAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAawBlAGUAcAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAdQBuACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABhAHMAYwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AHIAZQBhAGsAuwMoAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQApACwAXABuACAAIAAgACAAZABlAHMAYwBlAG4AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMAbwB1AG4AdABkAG8AdwBuALsDKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUAKQAsAFwAbgAgACAAIAAgAGsAZQBlAHAALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAEIAUwAoAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGkAbgBkAGUAeAAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAIAA9ACAALQAxACwAIABkAGUAcwBjAGUAbgBkACwAIABhAHMAYwBlAG4AZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQBlAHAAIAByAG8AdwBzACAAdwBoAGUAcgBlACAAaQBuAGQAZQB4ACAAZCIgAGsAZQBlAHAAXABuACAAIAAgACAAawBlAGUAcAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAZAB4ACAAPAA9ACAAawBlAGUAcAAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABhAHIAcgBhAHkALAAgAGsAZQBlAHAAPwApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAEEAMQA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAASwBlAGUAcABDAG8AbABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQAgACgAUwBlAGwAZQBjAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAdAByAGUAYQBrALsDLAAgAEMAbwB1AG4AdABkAG8AdwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdABhAGkAbgBzACAAYwBvAGwAdQBtAG4AcwAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYgBhAHMAZQBkACAAbwBuACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHMAdQBiAGcAcgBvAHUAcAAgAHIAdQBuAHMALgAgAEEAIABwAG8AcwBpAHQAaQB2AGUAXABuACAAIAAgACAAawBlAGUAcAAgAHYAYQBsAHUAZQAgAHIAZQB0AGEAaQBuAHMAIABjAG8AbAB1AG0AbgBzACAAZgByAG8AbQAgAHQAaABlACAAbABlAGYAdAAgAG8AZgAgAGUAYQBjAGgAIABzAHUAYgBnAHIAbwB1AHAAIAByAHUAbgA7ACAAYQAgAG4AZQBnAGEAdABpAHYAZQBcAG4AIAAgACAAIABrAGUAZQBwACAAdgBhAGwAdQBlACAAcgBlAHQAYQBpAG4AcwAgAGMAbwBsAHUAbQBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGkAZwBoAHQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABrAGUAZQBwACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAgAGkAbgB0AGUAZwBlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAD4AIAAwACAAkiEgAGsAZQBlAHAAIABmAHIAbwBtACAAbABlAGYAdAAgAG8AZgAgAGUAYQBjAGgAIAByAHUAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADwAIAAwACAAkiEgAGsAZQBlAHAAIABmAHIAbwBtACAAcgBpAGcAaAB0ACAAbwBmACAAZQBhAGMAaAAgAHIAdQBuAFwAbgAgACAAIAAgAGEAdABfAGUAYQBjAGgAXwBjAGgAYQBuAGcAZQAgACAALQAgAFMAdQBiAGcAcgBvAHUAcAAgAGwAYQBiAGUAbABzACAAKABzAGEAbQBlACAAdwBpAGQAdABoACAAYQBzACAAYQByAHIAYQB5ACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIABvAG4AbAB5ACAAbwBuAGUAIABzAHUAYgBnAHIAbwB1AHAAIABlAHgAaQBzAHQAcwAsACAARABSAE8AUAAoACkAIABpAHMAIAB1AHMAZQBkACAAYQBzACAAYQAgAGYAYQBzAHQAIABwAGEAdABoAC4AXABuACAAIAAgACAAIiAgAGsAZQBlAHAAIABtAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByADsAIAB0AGUAeAB0ACAAbwByACAAdgBlAGMAdABvAHIAIABpAG4AcAB1AHQAcwAgAGgAYQBsAHQAIAB3AGkAdABoACAAYQBuACAAZQByAHIAbwByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEsAZQBlAHAAQwBvAGwAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABrAGUAZQBwACwAXABuACAAIAAgACAAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUwB1AGIAZwByAG8AdQBwACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAATwBuAGUAUwB1AGIARwByAG8AdQBwAD8ALAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAVQBOAEkAUQBVAEUAKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALAAgADEAKQApACAAPQAgADEALABcAG4AIAAgACAAIABEAGkAcwBjAGEAcgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGEAcgByAGEAeQAsACAALAAgAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAA8AD4AIABDAE8ATABVAE0ATgBTACgAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACkALABcAG4AIAAgACAAIABJAHMAVABlAHgAdAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABrAGUAZQBwACkALABcAG4AIAAgACAAIABOAG8AdABTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAE8AVAAoAEkAcwBUAGUAeAB0AD8AKQAsACAAQwBPAFUATgBUAEEAKABrAGUAZQBwACkAIAA+ACAAMQApACwAXABuACAAIAAgACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABJAHMAVABlAHgAdAA/ACwAIABOAG8AdABTAGMAYQBsAGEAcgA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQByAHIAbwByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAGgAYQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKABzAGMAZQBuAGEAcgBpAG8AcwApACwAXABuACAAIAAgACAAZQByAHIAbwByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgA7ACAAXAAiACMAVABFAFgAVAAhAFwAIgA7ACAAXAAiACMAUwBDAEEATABBAFIAIQBcACIAfQAsAFwAbgAgACAAIAAgAGEAbABlAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAFIAUgBBAFkAVABPAFQARQBYAFQAKABGAEkATABUAEUAUgAoAGUAcgByAG8AcgBzACwAIABzAGMAZQBuAGEAcgBpAG8AcwAsACAAMAApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgATwBuAGUAUwB1AGIARwByAG8AdQBwAD8ALAAgAEQAaQBzAGMAYQByAGQALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABoAGEAbAB0ACwAIABhAGwAZQByAHQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgACsAbABlAGYAdAAsACAAEyByAGkAZwBoAHQAXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABrAGUAZQBwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgB1AG4AIABpAG4AZABpAGMAZQBzACAAKABoAG8AcgBpAHoAbwBuAHQAYQBsACkAXABuACAAIAAgACAAYQBzAGMAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAGUAYQBrALsDKABhAHQAXwBlAGEAYwBoAF8AYwBoAGEAbgBnAGUALAAgAFQAUgBVAEUAKQAsAFwAbgAgACAAIAAgAGQAZQBzAGMAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAG8AdQBuAHQAZABvAHcAbgC7AygAYQB0AF8AZQBhAGMAaABfAGMAaABhAG4AZwBlACwAIABUAFIAVQBFACkALABcAG4AIAAgACAAIABrAGUAZQBwACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBCAFMAKABrAGUAZQBwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABpAG4AZABlAHgAIABiAGEAcwBlAGQAIABvAG4AIABzAGkAZwBuAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABzACAAPQAgAC0AMQAsACAAZABlAHMAYwBlAG4AZAAsACAAYQBzAGMAZQBuAGQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABLAGUAZQBwACAAYwBvAGwAdQBtAG4AcwAgAHcAaABlAHIAZQAgAGkAbgBkAGUAeAAgAGQiIABrAGUAZQBwAFwAbgAgACAAIAAgAGsAZQBlAHAAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAGQAeAAgADwAPQAgAGsAZQBlAHAALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAdQBtAG4AESB3AGkAcwBlACAAZgBpAGwAdABlAHIAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYQByAHIAYQB5ACwAIABrAGUAZQBwAD8AKQAsAFwAbgBcAG4AIAAgACAAIAByAGUAcwB1AGwAdABcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEIAbABvAGMAawBNAGEAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABWAGEAbABpAGQAYQB0AGUAQgBsAG8AYwBrAE0AYQBwALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcwBoAGEAcABlAHMAIABhACAAYQByAHIAYQB5AF8AMgBEACAAcgBvAHcAESB3AGkAcwBlACAAbwByACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAaQBuAHQAbwAgAGIAbABvAGMAawBzACAAbwBmACAAcwBpAHoAZQBcAG4AIAAgACAAIABkAGUAcAB0AGgAIADXACAAdwBpAGQAdABoAC4AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzACAAYQBsAGwAbwB3ACAAcgBlAHMAaABhAHAAaQBuAGcAIABiAHkAIABjAG8AbAB1AG0AbgAgAGEAbgBkAFwAbgAgACAAIAAgAHQAcgBhAG4AcwBwAG8AcwBpAG4AZwAgAHQAaABlACAAYQBuAGMAaABvAHIAIABnAHIAaQBkAHMAIAB1AHMAZQBkACAAdABvACAAZwBlAG4AZQByAGEAdABlACAAYgBsAG8AYwBrACAAaQBuAGQAaQBjAGUAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5AF8AMgBEAC4AXABuACAAIAAgACAAZABlAHAAdABoACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAEgAZQBpAGcAaAB0ACAAbwBmACAAZQBhAGMAaAAgAGIAbABvAGMAawAuAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIABXAGkAZAB0AGgAIABvAGYAIABlAGEAYwBoACAAYgBsAG8AYwBrAC4AXABuACAAIAAgACAAWwByAGUAXwBzAGgAYQBwAGUAXwBiAHkAXwBjAG8AbAB1AG0AbgA/AF0ALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQBzAGgAYQBwAGUAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAOwAgAGUAbABzAGUAIAByAG8AdwARIHcAaQBzAGUALgBcAG4AIAAgACAAIABbAHQAcgBhAG4AcwBwAG8AcwBlAF8AYQBuAGMAaABvAHIAcwA/AF0AIAAtACAASQBmACAAVABSAFUARQAsACAAdAByAGEAbgBzAHAAbwBzAGUAIAByAG8AdwAvAGMAbwBsAHUAbQBuACAAYQBuAGMAaABvAHIAIABnAHIAaQBkAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABWAGEAbABpAGQAYQB0AGUAQgBsAG8AYwBrAE0AYQBwALsDIABlAG4AZgBvAHIAYwBlAHMAIABzAHQAcgBpAGMAdAAgAHMAaABhAHAAZQAgAGMAbwBtAHAAYQB0AGkAYgBpAGwAaQB0AHkALgBcAG4AIAAgACAAIAAiICAAQQBuAGMAaABvAHIAcwAgAGQAZQBmAGkAbgBlACAAdABoAGUAIAB0AG8AcAARIGwAZQBmAHQAIABjAG8AcgBuAGUAcgAgAG8AZgAgAGUAYQBjAGgAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhAGwAdwBhAHkAcwAgAHIAZQBjAHQAYQBuAGcAdQBsAGEAcgAgAGEAbgBkACAAZgB1AGwAbAB5ACAAdABpAGwAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEIAbABvAGMAawBNAGEAcAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABkAGUAcAB0AGgALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALABcAG4AIAAgACAAIABbAHIAZQBfAHMAaABhAHAAZQBfAGIAeQBfAGMAbwBsAHUAbQBuAD8AXQAsAFwAbgAgACAAIAAgAFsAdAByAGEAbgBzAHAAbwBzAGUAXwBhAG4AYwBoAG8AcgBzAD8AXQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGUAIABpAG4AcAB1AHQAcwAgAGIAZQBmAG8AcgBlACAAcgBlAHMAaABhAHAAaQBuAGcAXABuACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAEIAbABvAGMAawBNAGEAcAC7AygAYQByAHIAYQB5AF8AMgBEACwAIABkAGUAcAB0AGgALAAgAHcAaQBkAHQAaAAsACAAcgBlAF8AcwBoAGEAcABlAF8AYgB5AF8AYwBvAGwAdQBtAG4APwAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABCAGwAbwBjAGsAIABnAHIAaQBkACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAVQBQACgAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIARAApACAALwAgAGQAZQBwAHQAaAAsACAAMAApACwAIAAgACAAIAAgAC8ALwAgAGIAbABvAGMAawAgAHIAbwB3AHMAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEAFUAUAAoAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAgAC8AIAB3AGkAZAB0AGgALAAgADAAKQAsACAAIAAvAC8AIABiAGwAbwBjAGsAIABjAG8AbAB1AG0AbgBzAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwAIAAsACAAMQAsACAAZABlAHAAdABoACkAIAAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAIAB5ACwAIAAxACwAIAAwACkALABcAG4AXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHkALAAgADEALAAgAHcAaQBkAHQAaAApACAAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwAIAAsACAAMQAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAHIAbwB3AF8AYQBuAGMAaABvAHIALAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAdAByAGEAbgBzAHAAbwBzAGUAXwBhAG4AYwBoAG8AcgBzAD8AKQAsACAAaQAsACAAVABSAEEATgBTAFAATwBTAEUAKABpACkAKQAsAFwAbgAgACAAIAAgAGMAbwBsAF8AYQBuAGMAaABvAHIALAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAdAByAGEAbgBzAHAAbwBzAGUAXwBhAG4AYwBoAG8AcgBzAD8AKQAsACAAagAsACAAVABSAEEATgBTAFAATwBTAEUAKABqACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGkAbgBkAGkAYwBlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABiAGwAbwBjAGsAXABuACAAIAAgACAAcgBvAHcAXwBpAG4AZABpAGMAZQBzACwAIAAgACAAVABPAEMATwBMACgAcgBvAHcAXwBhAG4AYwBoAG8AcgApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAE4AVAAoAFMARQBRAFUARQBOAEMARQAoACwAIABkAGUAcAB0AGgAIAAqACAAdwBpAGQAdABoACwAIAAwACwAIAAxACAALwAgAHcAaQBkAHQAaAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAYgBsAG8AYwBrAFwAbgAgACAAIAAgAGMAbwBsAF8AaQBuAGQAaQBjAGUAcwAsACAAIAAgAFQATwBDAE8ATAAoAGMAbwBsAF8AYQBuAGMAaABvAHIAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAFIATwBXACgASQBGAFMAKABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgAKQAsACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHcAaQBkAHQAaAAsACAAMAAsACAAMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYgBsAG8AYwBrAHMAXABuACAAIAAgACAAcgBlAHMAaABhAHAAZQBkACwAIAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIAByAG8AdwBfAGkAbgBkAGkAYwBlAHMALAAgAGMAbwBsAF8AaQBuAGQAaQBjAGUAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQAgAHIAZQBzAGgAYQBwAGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAASQBGACgAcgBlAF8AcwBoAGEAcABlAF8AYgB5AF8AYwBvAGwAdQBtAG4APwAsACAAVABSAEEATgBTAFAATwBTAEUAKAByAGUAcwBoAGEAcABlAGQAKQAsACAAcgBlAHMAaABhAHAAZQBkACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBABEgQwBPAFIARQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBCAGwAbwBjAGsATQBhAHAAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABDAG8AcgBlACAAVgBhAGwAaQBkAGEAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAHMAIABpAG4AcAB1AHQAcwAgAGYAbwByACAAQgBsAG8AYwBrAE0AYQBwALsDLgAgAEUAbgBzAHUAcgBlAHMAIAB0AGgAZQAgAGEAcgByAGEAeQBfADIARAAgAGkAcwAgAHYAYQBsAGkAZAAsACAAYgBsAG8AYwBrACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABhAHIAZQAgAGMAbwBtAHAAYQB0AGkAYgBsAGUALAAgAHIAZQBzAGgAYQBwAGkAbgBnACAAdwBpAGwAbAAgAG4AbwB0ACAAcwBwAGkAbABsACwAIABhAG4AZAAgAHQAaABlACAAYgBsAG8AYwBrACAAZwBlAG8AbQBlAHQAcgB5ACAAdABpAGwAZQBzACAAdABoAGUAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAYwBsAGUAYQBuAGwAeQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYQByAHIAYQB5AF8AMgBEAC4AXABuACAAIAAgACAAZABlAHAAdABoACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAEIAbABvAGMAawAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAdwBpAGQAdABoACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAEIAbABvAGMAawAgAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgAHIAZQBfAHMAaABhAHAAZQBfAGIAeQBfAGMAbwBsAHUAbQBuAD8AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGwAYQBnACAAZgBvAHIAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIAByAGUAcwBoAGEAcABlAC4AXABuACAAIAAgACAAbwBuAF8AdgBhAGwAaQBkACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAEUAeABwAHIAZQBzAHMAaQBvAG4AIAB0AG8AIABlAHYAYQBsAHUAYQB0AGUAIAB3AGgAZQBuACAAdgBhAGwAaQBkAGEAdABpAG8AbgAgAHAAYQBzAHMAZQBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBuAHMAdQByAGUAcwAgAGEAcgByAGEAeQBfADIARAAgAGkAcwAgAGEAIABwAHIAbwBwAGUAcgAgAGEAcgByAGEAeQAgACgAVABZAFAARQAgAD0AIAA2ADQAKQAuAFwAbgAgACAAIAAgACIgIABQAHIAZQB2AGUAbgB0AHMAIABzAHAAaQBsAGwAESByAGkAcwBrACAAdwBoAGUAbgAgAHIAZQBzAGgAYQBwAGkAbgBnACAAYgB5ACAAYwBvAGwAdQBtAG4ALgBcAG4AIAAgACAAIAAiICAARQBuAGYAbwByAGMAZQBzACAAZQB4AGEAYwB0ACAAZABpAHYAaQBzAGkAYgBpAGwAaQB0AHkAIABiAHkAIABiAGwAbwBjAGsAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAIiAgAFIAZQBqAGUAYwB0AHMAIABpAG4AdgBhAGwAaQBkACAAbwByACAAdABlAHgAdAAgAGIAbABvAGMAawAgAHMAaQB6AGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBWAGEAbABpAGQAYQB0AGUAQgBsAG8AYwBrAE0AYQBwALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAsAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgAHIAZQBfAHMAaABhAHAAZQBfAGIAeQBfAGMAbwBsAHUAbQBuAD8ALABcAG4AIAAgACAAIABvAG4AXwB2AGEAbABpAGQALABcAG4AXABuACAAIAAgACAALwAvACAATQB1AHMAdAAgAGIAZQAgAGEAbgAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABJAEYAKABOAE8AVAAoAFQAWQBQAEUAKABhAHIAcgBhAHkAXwAyAEQAKQAgAD0AIAA2ADQAKQAsAFwAIgAjAGEAcgByAGEAeQBfADIARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAaQBsAGwAESByAGkAcwBrACAAdwBoAGUAbgAgAHIAZQBzAGgAYQBwAGkAbgBnACAAYgB5ACAAYwBvAGwAdQBtAG4AXABuACAAIAAgACAASQBGACgAKAByAGUAXwBzAGgAYQBwAGUAXwBiAHkAXwBjAG8AbAB1AG0AbgA/ACkAIAAqACAAXABuACAAIAAgACAAIAAgACAAKABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkAIAAqACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACAALwAgACgAdwBpAGQAdABoACAAKgAgAGQAZQBwAHQAaAApAF4AMgAgAD4AIAAxADYAMwA4ADQAKQAsAFwAIgAjAFMAUABJAEwATAAtAFIASQBTAEsAIQBcACIALABcAG4AXABuACAAIAAgACAALwAvACAATQB1AHMAdAAgAHQAaQBsAGUAIABjAGwAZQBhAG4AbAB5AFwAbgAgACAAIAAgAEkARgAoACgATQBPAEQAKABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALAAgAGQAZQBwAHQAaAApACAAPAA+ACAAMAApACAAKwAoAE0ATwBEACgAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwAIAB3AGkAZAB0AGgAKQAgADwAPgAgADAAKQAsAFwAIgAjAEIATABPAEMASwAgAE0ASQBTAE0AQQBUAEMASAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGwAbwBjAGsAIABzAGkAegBlACAAbQB1AHMAdAAgAGIAZQAgAHYAYQBsAGkAZABcAG4AIAAgACAAIABJAEYAKABPAFIAKABBAE4ARAAoAHcAaQBkAHQAaAAgAD0AIAAxACwAIABkAGUAcAB0AGgAIAA9ACAAMQApACwAZABlAHAAdABoACAAPgAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwBpAGQAdABoACAAPgAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAEkAUwBUAEUAWABUACgAdwBpAGQAdABoACkALABJAFMAVABFAFgAVAAoAGQAZQBwAHQAaAApACkALABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAbABsACAAYwBoAGUAYwBrAHMAIABwAGEAcwBzAGUAZABcAG4AIAAgACAAIABvAG4AXwB2AGEAbABpAGQAXABuACAAIAAgACAAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEMAbwBuAHYAbwBsAHYAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADIAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUABlAHIAZgBvAHIAbQBzACAAYQAgAHMAbABpAGQAaQBuAGcAESB3AGkAbgBkAG8AdwAgAGMAbwBuAHYAbwBsAHUAdABpAG8AbgAgAG8AdgBlAHIAIABhACAAMgBEACAAYQByAHIAYQB5ACAAdQBzAGkAbgBnACAAYQAgADIARAAgAGsAZQByAG4AZQBsAC4AXABuACAAIAAgACAARQBhAGMAaAAgAHcAaQBuAGQAbwB3ACAAZQB4AHQAcgBhAGMAdABlAGQAIABmAHIAbwBtACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABoAGEAcwAgAHQAaABlACAAcwBhAG0AZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABhAHMAIAB0AGgAZQBcAG4AIAAgACAAIABrAGUAcgBuAGUAbAAuACAAQQAgAHIAZQBkAHUAYwBlAHIAIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAZQBhAGMAaAAgAHcAaQBuAGQAbwB3ACAAdABvACAAcAByAG8AZAB1AGMAZQAgAHQAaABlACAAbwB1AHQAcAB1AHQALgBcAG4AXABuACAAIAAgACAASQBmACAAbgBvACAAcgBlAGQAdQBjAGUAcgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAHMAdQBwAHAAbABpAGUAZAAsACAAQwBvAG4AdgBvAGwAdgBlALsDIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABhACAAZABvAHQAESBwAHIAbwBkAHUAYwB0AFwAbgAgACAAIAAgAHIAZQBkAHUAYwBlAHIAOgAgAFMAVQBNACgAdgAgACoAIABrAGUAcgBuAGUAbAApAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAHcAaABpAGMAaAAgAHQAaABlACAAawBlAHIAbgBlAGwAIABpAHMAIABhAHAAcABsAGkAZQBkAC4AXABuACAAIAAgACAAawBlAHIAbgBlAGwAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAGQAZQBmAGkAbgBpAG4AZwAgAHQAaABlACAAcwBsAGkAZABpAG4AZwAgAHcAaQBuAGQAbwB3ACAAZABpAG0AZQBuAHMAaQBvAG4AcwAuAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAByAGUAZAB1AGMAZQByACAATABBAE0AQgBEAEEAIABhAGMAYwBlAHAAdABpAG4AZwAgAGEAIABzAGkAbgBnAGwAZQAgAGEAcgByAGEAeQAgAGEAcgBnAHUAbQBlAG4AdAAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABTAFUATQAoAHYAIAAqACAAawBlAHIAbgBlAGwAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBLAEUAUgBOAEUATAAhAFwAIgAgAGkAZgAgAHQAaABlACAAawBlAHIAbgBlAGwAIABpAHMAIABsAGEAcgBnAGUAcgAgAHQAaABhAG4AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgACIgIABSAGUAdAB1AHIAbgBzACAAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACAAaQBmACAAdABoAGUAIAByAGUAZAB1AGMAZQByACAAaQBzACAAbgBvAHQAIABhACAAdgBhAGwAaQBkACAATABBAE0AQgBEAEEALgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgADEA1wAxACAAYQByAHIAYQB5AHMAIABhAG4AZAAgAG0AYQBwAHAAZQBkACAAdABoAHIAbwB1AGcAaAAgAHQAaABlACAAcgBlAGQAdQBjAGUAcgAuAFwAbgAgACAAIAAgACIgIABSAGUAZAB1AGMAZQByACAAYgBlAGgAYQB2AGkAbwByACAAaQBzACAAdQBzAGUAcgARIGQAZQBmAGkAbgBlAGQAOwAgAGEAcgByAGEAeQBzACAAbgBlAGUAZAAgAG4AbwB0ACAAYgBlACAAbgB1AG0AZQByAGkAYwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AbgB2AG8AbAB2AGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQQByAHIAYQB5ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABLAGUAcgBuAGUAbAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaABfACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABrAGUAcgBuAGUAbAApACwAXABuACAAIAAgACAAdwBfACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABrAGUAcgBuAGUAbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQByAG4AZQBsACAAbQB1AHMAdAAgAGYAaQB0ACAAaQBuAHMAaQBkAGUAIABhAHIAcgBhAHkAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABLAGUAcgBuAGUAbAA/ACwAIAAgACAAIAAgAE8AUgAoAGgAXwAgAD4AIABoACwAIAB3AF8AIAA+ACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAaABhAG4AZABsAGkAbgBnAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIASwBlAHIAbgBlAGwAPwAsACAAIAAgACAAQQBOAEQAKABoAF8AIAA9ACAAMQAsACAAdwBfACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBhAHUAbAB0ACAAcgBlAGQAdQBjAGUAcgAgAD0AIABkAG8AdAAgAHAAcgBvAGQAdQBjAHQAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgB1AG4AYwB0AGkAbwBuACkALABMAEEATQBCAEQAQQAoAHYALAAgAFMAVQBNACgAdgAgACoAIABrAGUAcgBuAGUAbAApACkALABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA9ACAAMQAyADgAIACSISAAdgBhAGwAaQBkACAATABBAE0AQgBEAEEAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4APwAsACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAbwByACAAcwBjAGEAbABhAHIAESBrAGUAcgBuAGUAbAAgAGMAYQBzAGUAIACSISAAcwBpAG0AcABsAGUAIABNAEEAUABcAG4AIAAgACAAIABTAHQAYQBuAGQAYQByAGQATQBhAHAALAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAEEAUAAoAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACkAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEsAZQByAG4AZQBsAD8ALAAgAFwAIgAjAEsARQBSAE4ARQBMACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABGAG4APwAsACAAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAAoAEkAcwBTAGMAYQBsAGEAcgA/ACkAIAArACAAKABJAHMAUwBjAGEAbABhAHIASwBlAHIAbgBlAGwAPwApACwAUwB0AGEAbgBkAGEAcgBkAE0AYQBwACgAKQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGEAbgBjAGgAXwByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABoACAALQAgAGgAXwAgACsAIAAxACwAXABuACAAIAAgACAAYQBuAGMAaABfAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAIAAtACAAdwBfACAAKwAgADEALABcAG4AXABuACAAIAAgACAALwAvACAAQQBuAGMAaABvAHIAIABpAG4AZABlAHgAIABnAHIAaQBkAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAEkARgAoAGEAbgBjAGgAXwByACAAPQAgADEALAAgADEALABTAEUAUQBVAEUATgBDAEUAKABhAG4AYwBoAF8AcgApACkALAAgACwAIABhAG4AYwBoAF8AYwApACkALAAgACAAIAAgAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABJAEYAKABhAG4AYwBoAF8AYwAgAD0AIAAxACwAIAAxACwAIABTAEUAUQBVAEUATgBDAEUAKAAsAGEAbgBjAGgAXwBjACkAKQAsACAAYQBuAGMAaABfAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFcAaQBuAGQAbwB3ACAAcgBlAGQAdQBjAGUAcgBcAG4AIAAgACAAIABCAGwAbwBjAGsAQQBnAGcAuwMsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABpAF8ALAAgAGoAXwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsALAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgAGkAXwAgAC0AIAAxACwAIABqAF8AIAAtACAAMQApACwAIABoAF8ALAAgAHcAXwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AG8AdABhAGwALAAgACAAZgB1AG4AYwB0AGkAbwBuACgAYgBsAG8AYwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAbwB0AGEAbAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAcgBlAGQAdQBjAGUAcgAgAHQAbwAgAGUAYQBjAGgAIAB3AGkAbgBkAG8AdwBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABpACgAKQAsACAAagAoACkALAAgAEIAbABvAGMAawBBAGcAZwC7AykALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBBADEAOABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEYAbwBsAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAGwAZwBlAGIAcgBhACAAKABTAHQAcgB1AGMAdAB1AHIAYQBsACAATQBhAHAAcABpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQQBsAGkAZwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAZAB1AGMAZQBzACAAcgBlAGMAbwByAGQAcwAgAGkAbgAgAGEAbgAgAGEAcgByAGEAeQAgAGIAeQAgAGcAcgBvAHUAcABpAG4AZwAgAGkAZABlAG4AdABpAGMAYQBsACAAcgBvAHcAcwAgAGEAbgBkACAAYQBwAHAAbAB5AGkAbgBnACAAYQBuAFwAbgAgACAAIAAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAgAHQAbwAgAHQAaABlACAAYwBvAHIAcgBlAHMAcABvAG4AZABpAG4AZwAgAGUAbgB0AHIAaQBlAHMAIABpAG4AIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIABJAGYAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAgAGkAcwAgAG8AbQBpAHQAdABlAGQALAAgAEYAbwBsAGQAuwMgAHUAcwBlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGYAaQBlAGwAZAAgAG8AZgAgAGUAYQBjAGgAIAByAGUAYwBvAHIAZAAgAGEAcwBcAG4AIAAgACAAIAB0AGgAZQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAHYAZQBjAHQAbwByAC4AIABUAGgAaQBzACAAbQBvAGQAZQAgAGkAcwAgAGkAbgB0AGUAbgBkAGUAZAAgAGYAbwByACAAQwBPAFUATgBUAEEAOwAgAG8AdABoAGUAcgAgAHIAZQBkAHUAYwBlAHIAcwBcAG4AIAAgACAAIABtAGEAeQAgAHAAcgBvAGQAdQBjAGUAIAByAGUAcwB1AGwAdABzACAAYgB1AHQAIABhAHIAZQAgAG4AbwB0ACAAbQBlAGEAbgBpAG4AZwBmAHUAbAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAHIAbwB3AHMAIABkAGUAZgBpAG4AZQAgAGcAcgBvAHUAcABpAG4AZwAgAGsAZQB5AHMALgBcAG4AIAAgACAAIABbAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5AF0AIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGEAZwBnAHIAZQBnAGEAdABlAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAAIAAgACAAIAAtACAAUgBlAGQAdQBjAGUAcgAgAEwAQQBNAEIARABBACAAYQBjAGMAZQBwAHQAaQBuAGcAIABhACAAMQBEACAAdgBlAGMAdABvAHIAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAQwBPAFUATgBUAEEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEYAbwBsAGQAuwMgAGgAYQBsAHQAcwAgAHcAaQB0AGgAIAAjAFYAQQBMAFUARQAhACAAaQBmACAAYQByAHIAYQB5ACAAYQBuAGQAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAgAGgAZQBpAGcAaAB0AHMAIABkAGkAZgBmAGUAcgAuAFwAbgAgACAAIAAgACIgIABGAG8AbABkALsDIABoAGEAbAB0AHMAIAB3AGkAdABoACAAIwBGAFUATgBDAFQASQBPAE4AIQAgAGkAZgAgAHIAZQBkAHUAYwBlAHIAIABpAHMAIABuAG8AdAAgAGEAIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQAuAFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4AuwMgAGMAYQBuAG8AbgBpAGMAYQBsAGkAegBlAHMAIAByAGUAYwBvAHIAZABzACAAcwBvACAAaQBkAGUAbgB0AGkAYwBhAGwAIAByAG8AdwBzACAAZwByAG8AdQBwACAAYwBsAGUAYQBuAGwAeQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBGAG8AbABkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAXQAsAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABlAGYAYQB1AGwAdAAgAHYAYQBsAHUAZQBzACAAYQByAHIAYQB5AFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACwAVABBAEsARQAoAGEAcgByAGEAeQAsACAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAZAB1AGMAZQByAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsACAAIAAgACAASQBGACgATwBSACgASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsACAASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACkALABDAE8AVQBOAFQAQQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4ASQBGACgAQQBOAEQAKABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkAIAA8AD4AIABSAE8AVwBTACgAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQApACwAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEMAYQBuAG8AbgBpAGMAYQBsACAAZwByAG8AdQBwAGkAbgBnACAAawBlAHkAcwBcAG4AIAAgACAAIABhAGwAaQBnAG4AZQBkACwAIAAgACAAIAAgAEEAbABpAGcAbgC7AygAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBnAGcAcgBlAGcAYQB0AGkAbwBuAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAARwBSAE8AVQBQAEIAWQAoAGEAbABpAGcAbgBlAGQALAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgACwAIAAwACkALABcAG4AXABuACAAIAAgACAAYQBnAGcAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAQQAxADkAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABKAG8AaQBuADIARAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEAIAAoAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABKAG8AaQBuAHMAIABhAGwAbAAgAG4AbwBuABEgZQBtAHAAdAB5ACAAdgBhAGwAdQBlAHMAIABhAGMAcgBvAHMAcwAgADIAIAB0AG8AIAA0ACAAaQBkAGUAbgB0AGkAYwBhAGwAbAB5ABEgcwBoAGEAcABlAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAgAHUAcwBpAG4AZwBcAG4AIAAgACAAIABhACAAcwBwAGUAYwBpAGYAaQBlAGQAIABkAGUAbABpAG0AaQB0AGUAcgAuACAAVABoAGUAIABvAHUAdABwAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIAB0AGgAZQAgAGkAbgBwAHUAdABzAC4AXABuAFwAbgAgACAAIAAgAEEAIABjAGUAbABsACAAaQBzACAAYwBvAG4AcwBpAGQAZQByAGUAZAAgABwgZQBtAHAAdAB5AB0gIABpAGYAIABpAHQAIABtAGEAdABjAGgAZQBzACAAQQBOAFkAIABvAGYAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABMAEUATgAoAGMAZQBsAGwAKQAgAD0AIAAwAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAGMAZQBsAGwAIAA9ACAARgBBAEwAUwBFAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAGMAZQBsAGwAIAA9ACAAaQBnAG4AbwByAGUAIAAoAHUAcwBlAHIAESBzAHAAZQBjAGkAZgBpAGUAZAApAFwAbgBcAG4AIAAgACAAIABKAG8AaQBuADIARAC7AyAAaQBzACAAYQBuACAAYQBsAHQAZQByAG4AYQB0AGkAdgBlACAAdABvACAAbgBlAHMAdABlAGQAIABNAEEAUAAgAGwAbwBnAGkAYwAgAGYAbwByACAAZQBsAGUAbQBlAG4AdAARIHcAaQBzAGUAIABqAG8AaQBuAGkAbgBnAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0AIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAZABlAGwAaQBtAGkAdABlAHIAXQAgAC0AIABEAGUAbABpAG0AaQB0AGUAcgAgAGYAbwByACAAagBvAGkAbgBpAG4AZwAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABcACIALAAgAFwAIgApAC4AXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACAAIAAgACAALQAgAFYAYQBsAHUAZQAgAHQAcgBlAGEAdABlAGQAIABhAHMAIABlAG0AcAB0AHkAIAAoAGQAZQBmAGEAdQBsAHQAIAA9ACAAXAAiAFwAIgApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkAcwAgAG0AdQBzAHQAIABoAGEAdgBlACAAaQBkAGUAbgB0AGkAYwBhAGwAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAIiAgAEUAbQBwAHQAeQAgAGMAZQBsAGwAcwAgAGEAcgBlACAAcwBrAGkAcABwAGUAZAA7ACAAbgBvACAAdAByAGEAaQBsAGkAbgBnACAAZABlAGwAaQBtAGkAdABlAHIAIABpAHMAIABhAGQAZABlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASgBvAGkAbgAyAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADMAXQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8ANABdACwAXABuACAAIAAgACAAWwBkAGUAbABpAG0AaQB0AGUAcgBdACwAXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAASQBuAGMAbAB1AGQAZQAzAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkAKQAsAFwAbgAgACAAIAAgAEkAbgBjAGwAdQBkAGUANAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAzACkALAAgAEYAQQBMAFMARQAsACAAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8ANAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACwAIABGAEEATABTAEUALAAgAGEAcgByAGEAeQBfADQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAbABpAG0AaQB0AGUAcgAgACsAIABpAGcAbgBvAHIAZQBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABkAGUAbABpAG0AaQB0AGUAcgApACwAIABcACIALAAgAFwAIgAsACAAZABlAGwAaQBtAGkAdABlAHIAKQAsAFwAbgAgACAAIAAgAGkAZwBuAG8AcgBlACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZwBuAG8AcgBlACkALAAgAFwAIgBcACIALAAgAGkAZwBuAG8AcgBlACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMQApACwAXABuAFwAbgAgACAAIAAgAGgAgiAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACwAXABuACAAIAAgACAAdwCCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AXABuACAAIAAgACAAaACDICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAzACkALABcAG4AIAAgACAAIAB3AIMgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADMAKQAsAFwAbgBcAG4AIAAgACAAIABoAIQgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADQAKQAsAFwAbgAgACAAIAAgAHcAhCAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuACAAYwBoAGUAYwBrAHMAXABuACAAIAAgACAAUwBfADIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGgAIAA8AD4AIABoAIIgLAAgAHcAIAA8AD4AIAB3AIIgKQAsAFwAbgAgACAAIAAgAFMAXwAzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAG4AYwBsAHUAZABlADMAPwAgACoAIABPAFIAKABoACAAPAA+ACAAaACDICwAIAB3ACAAPAA+ACAAdwCDICkALABcAG4AIAAgACAAIABTAF8ANAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAGMAbAB1AGQAZQA0AD8AIAAqACAATwBSACgAaAAgADwAPgAgAGgAhCAsACAAdwAgADwAPgAgAHcAhCApACwAXABuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABPAFIAKABTAF8AMgAsACAAUwBfADMALAAgAFMAXwA0ACkALABcAG4AXABuACAAIAAgACAASQBGACgAUwBoAGEAcABlAE0AaQBzAG0AYQB0AGMAaAA/ACwAIABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AYwBjAHUAcABhAG4AYwB5ACAAcAByAGUAZABpAGMAYQB0AGUAXABuACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDLAAgACAATABBAE0AQgBEAEEAKABhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABhACAAPAA+ACAARgBBAEwAUwBFACkAIAAqACAAKABMAEUATgAoAGEAKQAgADwAPgAgADAAKQAgACoAIAAoAGEAIAA8AD4AIABpAGcAbgBvAHIAZQApACkALABcAG4AXABuACAAIAAgACAAbQBfADEALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwAxACkALABcAG4AIAAgACAAIABtAF8AMgAsACAAIAAgACAAIAAgACAAIABPAGMAYwB1AHAAaQBlAGQAuwMoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAG0AXwAzACwAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AygAYQByAHIAYQB5AF8AMwApACwAXABuACAAIAAgACAAbQBfADQALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAASgBvAGkAbgAgAGkAbgAgAG8AcgBkAGUAcgAsACAAcwBrAGkAcABwAGkAbgBnACAAZQBtAHAAdABpAGUAcwBcAG4AIAAgACAAIABqAG8AaQBuAGUAZAAsACAAIAAgACAAIABJAEYAKABtAF8AMQAsACAAYQByAHIAYQB5AF8AMQAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACAAJgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8AMgAsACAAYQByAHIAYQB5AF8AMgAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACAAJgBcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG0AXwAzACwAIABhAHIAcgBhAHkAXwAzACAAJgAgAGQAZQBsAGkAbQBpAHQAZQByACwAIABcACIAXAAiACkAIAAmAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8ANAAsACAAYQByAHIAYQB5AF8ANAAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABqAG8AaQBuAGUAZAAsAGQAZQBsAGkAbQBpAHQAZQByACwALQAxACwAMQAsACwAagBvAGkAbgBlAGQAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAjACMAIAAwADUAIAAtACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAgACoALwBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVABoAGkAcwAgAHMAZQBjAHQAaQBvAG4AIABjAG8AbgB0AGEAaQBuAHMAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHQAaABhAHQAIAByAGUAcABsAGkAYwBhAHQAZQAgAGEAcgByAGEAeQBzACAAYQBsAG8AbgBnACAAcgBvAHcAcwAsACAAYwBvAGwAdQBtAG4AcwAsACAAbwByACAAYgBvAHQAaAAuAFwAbgBcAG4ARgB1AG4AYwB0AGkAbwBuAHMAOgBcAG4AIAAgACAAIAAiICAARQBjAGgAbwC7AyAAIAAgACAAIAAgACAAIAAgACAALQAgAFIAZQBwAGUAYQB0ACAAZQBhAGMAaAAgAGUAbABlAG0AZQBuAHQAIABpAG4AIABhACAAMQBEACAAYQByAHIAYQB5ACAAYgB5ACAAYwBvAHUAbgB0AC4AXABuACAAIAAgACAAIiAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMgACAAIAAgAC0AIABSAGUAcABlAGEAdAAgAGUAYQBjAGgAIAByAG8AdwAgAGIAeQAgAGEAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQALgBcAG4AIAAgACAAIAAiICAAUgBlAHAAZQBhAHQAQwBvAGwAcwC7AyAAIAAgACAALQAgAFIAZQBwAGUAYQB0ACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAYgB5ACAAYQAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdAAuAFwAbgAgACAAIAAgACIgIABUAGUAcwBzAGUAbABsAGEAdABlALsDIAAgACAAIAAtACAAVABpAGwAZQAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AIABtAG8AZAB1AGwAYQByACAAZgBhAHMAaABpAG8AbgAsACAAcwB1AHAAcABvAHIAdABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABhAHIAdABpAGEAbAAgAHQAaQBsAGUAcwAgAHcAaABlAG4AIABvAHUAdABwAHUAdAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAG8AIABuAG8AdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAHYAaQBkAGUAIABlAHYAZQBuAGwAeQAuAFwAbgBcAG4AXABuAFwAbgBcACIAUAByAGUAcwBlAG4AdAAgAHMAdQBjAGMAZQBzAHMAIABpAHMAIABhAG4AIABlAGMAaABvACAAbwBmACAAYQAgAHAAYQBzAHQAIAB0AHIAaQB1AG0AcABoAC4AIABGAGEAaQBsAHUAcgBlACAAaQBzACAAcgBlAGQAdQBuAGQAYQBuAHQALgBcACIAIAAtACAAUgBlAHAAZQB0AHQAbwBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFIAUAAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABFAGMAaABvALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABSAGUAcABlAHQAaQB0AGkAbwBuAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHAAZQBhAHQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgADEARAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAXABuACAAIAAgACAAbgB1AG0AZQByAGkAYwAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwByACAAcwBjAGEAbABhAHIAIAB0AG8AIABiAGUAIABlAGMAaABvAGUAZAAuAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAKABuAHUAbQBlAHIAaQBjACwAIABlIiAAMQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAcgBlACAAdAByAGUAYQB0AGUAZAAgAGEAcwAgADEA1wAxACAAYQByAHIAYQB5AHMALgBcAG4AIAAgACAAIAAiICAASQBmACAAcgBlAHAAZQBhAHQAIABoAGEAcwAgAGEAIABkAGkAZgBmAGUAcgBlAG4AdAAgAGwAZQBuAGcAdABoACAAdABoAGEAbgAgAHYAZQBjAHQAbwByACwAIAB0AGgAZQAgAGwAYQBzAHQAIAByAGUAcABlAGEAdAAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAaQBzACAAZQB4AHQAZQBuAGQAZQBkACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIAB2AGUAYwB0AG8AcgAgAGwAZQBuAGcAdABoAC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAaQBzACAAYQBsAHcAYQB5AHMAIABhACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAYwBoAG8AuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAdgBlAGMAdABvAHIALABcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAByAGUAcABlAGEAdAApACwAIAByAGUAcABlAGEAdAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAKQAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAFYAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAZQBjAHQAbwByACkALABcAG4AIAAgACAAIABSAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIAAoAGUAeAB0AGUAbgBkACAAbABhAHMAdAAgAHYAYQBsAHUAZQAgAGkAZgAgAG4AZQBlAGQAZQBkACkAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABWAGgAIAA8AD4AIABSAGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAByAGUAcABlAGEAdAAsACAAVgBoACwAIAAsACAAQABUAEEASwBFACgAcgBlAHAAZQBhAHQALAAgAC0AMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGEAcwBlACAAaQBuAGQAZQB4AFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAUgBPAFcAUwAoAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4AGkAbQB1AG0AIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAdQBpAGwAZAAgAGkAbgBkAGUAeAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABUAE8AQwBPAEwAKABJAEYAKABTAEkARwBOACgAcgAgAC0AIABTAEUAUQBVAEUATgBDAEUAKAAsACAAbQAsACAAMAAsACAAKQApACAAPQAgADEALABpACwATgBBACgAKQApACwAMgApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB2AGUAYwB0AG8AcgAsACAAaQBkAHgAKAApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAMAAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBwAGUAYQB0AHMAIABlAGEAYwBoACAAcgBvAHcAIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5ACAAYQBjAGMAbwByAGQAaQBuAGcAIAB0AG8AIABhACAAdgBlAGMAdABvAHIAIABvAGYAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAuACAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHMAdQBwAHAAbwByAHQAZQBkAC4AIABSAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAbQB1AHMAdAAgAGIAZQAgAG4AdQBtAGUAcgBpAGMAXABuACAAIAAgACAAYQBuAGQAIABlIiAAMQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIAByAG8AdwBzACAAdwBpAGwAbAAgAGIAZQAgAHIAZQBwAGUAYQB0AGUAZAAuAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAKABuAHUAbQBlAHIAaQBjACwAIABlIiAAMQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAcgBlAHAAZQBhAHQAIABoAGEAcwAgAGYAZQB3AGUAcgAgAGUAbgB0AHIAaQBlAHMAIAB0AGgAYQBuACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMALAAgAHQAaABlACAAbABhAHMAdAAgAHIAZQBwAGUAYQB0AFwAbgAgACAAIAAgACAAIAB2AGEAbAB1AGUAIABpAHMAIABlAHgAdABlAG4AZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQAgAGEAcgByAGEAeQAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAcAByAGUAcwBlAHIAdgBlAHMAIAB0AGgAZQAgAGMAbwBsAHUAbQBuACAAcwB0AHIAdQBjAHQAdQByAGUAIABvAGYAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBSAGUAcABlAGEAdABSAG8AdwBzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAXABuAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAHIAZQBwAGUAYQB0ACkALAAgAHIAZQBwAGUAYQB0ACAAPAA9ACAAMAApACwAXAAiACMAVgBBAEwAVQBFACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcgBlAHAAZQBhAHQAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABBAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAFIAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAZQBuAGQAIAByAGUAcABlAGEAdAAgAHYAZQBjAHQAbwByACAAaQBmACAAbgBlAGUAZABlAGQAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABBAGgAIAA8AD4AIABSAGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAByAGUAcABlAGEAdAAsACAAQQBoACwAIAAsACAAQABUAEEASwBFACgAcgBlAHAAZQBhAHQALAAgAC0AMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGEAcwBlACAAcgBvAHcAIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAUgBPAFcAUwAoAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4AGkAbQB1AG0AIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABcAG4AIAAgACAAIABtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAdQBpAGwAZAAgAGkAbgBkAGUAeAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABUAE8AQwBPAEwAKABJAEYAKABTAEkARwBOACgAcgAgAC0AIABTAEUAUQBVAEUATgBDAEUAKAAsACAAbQAsACAAMAApACkAIAA9ACAAMQAsAGkALABOAEEAKAApACkALAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABhAHIAcgBhAHkALAAgAGkAZAB4ACgAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAUgBQADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFIAZQBwAGUAYQB0AEMAbwBsAHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAFIAZQBwAGUAdABpAHQAaQBvAG4AXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcABlAGEAdABzACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAbwBmACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmACAAcgBlAHAAZQBhAHQAXABuACAAIAAgACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAIABuAHUAbQBlAHIAaQBjAFwAbgAgACAAIAAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAYwBvAGwAdQBtAG4AcwAgAHcAaQBsAGwAIABiAGUAIAByAGUAcABlAGEAdABlAGQALgBcAG4AIAAgACAAIAByAGUAcABlAGEAdAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgACgAbgB1AG0AZQByAGkAYwAsACAAZSIgADEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAHIAZQBwAGUAYQB0ACAAaABhAHMAIABmAGUAdwBlAHIAIABlAG4AdAByAGkAZQBzACAAdABoAGEAbgAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACwAIAB0AGgAZQAgAGwAYQBzAHQAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIAAgACAAdgBhAGwAdQBlACAAaQBzACAAZQB4AHQAZQBuAGQAZQBkACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABhAHIAcgBhAHkAIAB3AGkAZAB0AGgALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABwAHIAZQBzAGUAcgB2AGUAcwAgAHQAaABlACAAcgBvAHcAIABzAHQAcgB1AGMAdAB1AHIAZQAgAG8AZgAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBwAGUAYQB0AEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAcgBlAHAAZQBhAHQALABcAG4AXABuAEkARgAoAE8AUgAoAEkAUwBUAEUAWABUACgAcgBlAHAAZQBhAHQAKQAsACAAcgBlAHAAZQBhAHQAIAA8AD0AIAAwACkALABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIAByAGUAcABlAGEAdAAgAHYAZQBjAHQAbwByAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAEEAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAUgBoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdABlAG4AZAAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIABpAGYAIABuAGUAZQBkAGUAZABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEAdwAgADwAPgAgAFIAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAHIAZQBwAGUAYQB0ACwAIABBAHcALAAgACwAIABAAFQAQQBLAEUAKAByAGUAcABlAGEAdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAYQBzAGUAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKABSAE8AVwBTACgAYwApACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHgAaQBtAHUAbQAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgAG0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABjACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgB1AGkAbABkACAAaQBuAGQAZQB4ACAAdgBlAGMAdABvAHIAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFQATwBDAE8ATAAoAEkARgAoAFMASQBHAE4AKABjACAALQAgAFMARQBRAFUARQBOAEMARQAoACwAIABtACwAIAAwACkAKQAgAD0AIAAxACwAaQAsAE4AQQAoACkAKQAsADIAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAGEAcgByAGEAeQAsACAAaQBkAHgAKAApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBSAFAAMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAVABlAHMAcwBlAGwAbABhAHQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFQARwByAGkAZAC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAbQBvAGQAdQBsAGEAcgAgAHQAZQBzAHMAZQBsAGwAYQB0AGkAbwBuACAAbwBmACAAYQAgADIARAAgAHAAYQB0AHQAZQByAG4AIABkAGUAZgBpAG4AZQBkACAAYgB5ACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAgANcAIABuAGUAdwBfAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgAFQAaABlACAAcABhAHQAdABlAHIAbgAgAGkAcwAgAHIAZQBwAGUAYQB0AGUAZAAgAHUAcwBpAG4AZwAgAG0AbwBkAHUAbABhAHIAIAByAG8AdwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AIABjAHkAYwBsAGUAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAdABoAGUAXABuACAAIAAgACAAcABhAHQAdABlAHIAbgAZIHMAIABvAHcAbgAgAGQAaQBtAGUAbgBzAGkAbwBuAHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACAAIAAgACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgACgAMQBEACAAYQByAHIAYQB5AHMAIABhAGMAYwBlAHAAdABlAGQALAAgAHMAYwBhAGwAYQByAHMAIABhAHIAZQAgAGYAbwByAGIAaQBkAGQAZQBuACkALgBcAG4AIAAgACAAIABuAGUAdwBfAGgAZQBpAGcAaAB0ACAAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGkAbgAgAHQAaABlACAAbwB1AHQAcAB1AHQAIAB0AGUAcwBzAGUAbABsAGEAdABpAG8AbgAuAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHQAZQBzAHMAZQBsAGwAYQB0AGkAbwBuAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUABlAHIAZgBvAHIAbQBzACAAbQBvAGQAdQBsAGEAcgAgAHIAZQBwAGUAdABpAHQAaQBvAG4AIAB1AHMAaQBuAGcAIABUAEcAcgBpAGQAuwMgAGYAbwByACAAcgBvAHcALwBjAG8AbAB1AG0AbgAgAGMAeQBjAGwAaQBuAGcALgBcAG4AIAAgACAAIAAiICAAUwB1AHAAcABvAHIAdABzACAAcABhAHIAdABpAGEAbAAgAHQAaQBsAGUAcwAgAHcAaABlAG4AIABuAGUAdwAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABhAHIAZQAgAG4AbwB0ACAAbQB1AGwAdABpAHAAbABlAHMAIABvAGYAXABuACAAIAAgACAAIAAgAHQAaABlACAAcABhAHQAdABlAHIAbgAgAHMAaQB6AGUALgBcAG4AIAAgACAAIAAiICAAUgBlAGoAZQBjAHQAcwAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVABlAHMAcwBlAGwAbABhAHQAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACwAXABuACAAIAAgACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsAFwAbgAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAUABhAHQAdABlAHIAbgAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcABhAHQAdABlAHIAbgApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAcABhAHQAdABlAHIAbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAZABlAHQAZQBjAHQAaQBvAG4AXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABuAGUAdwAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAIAAgACAAIABJAE4ARABFAFgAKABuAGUAdwBfAGgAZQBpAGcAaAB0ACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIABuAGUAdwBfAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAG4AZQB3AF8AdwBpAGQAdABoACwAIAAxACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAATgBvAEMAaABhAG4AZwBlAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAbgBlAHcAXwBoAGUAaQBnAGgAdAAsACAAdwAgAD0AIABuAGUAdwBfAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQASABXAD8ALAAgACAAIAAgACAATwBSACgAbgBlAHcAXwBoAGUAaQBnAGgAdAAgADwAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB3AF8AdwBpAGQAdABoACAAIAA8AD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAG4AZQB3AF8AaABlAGkAZwBoAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAFQARQBYAFQAKABuAGUAdwBfAHcAaQBkAHQAaAApACkALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAFwAIgAjAFMAQwBBAEwAQQBSACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AQwBoAGEAbgBnAGUAPwAsACAAcABhAHQAdABlAHIAbgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEgAVwA/ACwAIABcACIAIwBOAEUAVwAtAEgARQBJAEcASABUAC8AVwBJAEQAVABIACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AdQB0AHAAdQB0ACAAZwBlAG8AbQBlAHQAcgB5ACAAcABsAGEAYwBlAGgAbwBsAGQAZQByAFwAbgAgACAAIAAgAGUAeABwAF8AcwBoAGEAcABlACwAIAAgACAAIABFAFgAUABBAE4ARAAoADAALAAgAG4AZQB3AF8AaABlAGkAZwBoAHQALAAgAG4AZQB3AF8AdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBvAGQAdQBsAGEAcgAgAHIAbwB3AC8AYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEcAcgBpAGQAuwMoAGUAeABwAF8AcwBoAGEAcABlACwAIABoACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABHAHIAaQBkALsDKABlAHgAcABfAHMAaABhAHAAZQAsACAAdwAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAZQBzAHMAZQBsAGwAYQB0AGUAZAAgAG8AdQB0AHAAdQB0AFwAbgAgACAAIAAgAHQAZQBzAHMALAAgACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKABwAGEAdAB0AGUAcgBuACwAIABpACwAIABqACkALABcAG4AXABuACAAIAAgACAAdABlAHMAcwBcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAjACMAIAAwADYAIAAtACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACAAKgAvAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIABpAHMAIABhACAAYwBvAGwAbABlAGMAdABpAG8AbgAgAG8AZgAgAGYAdQBuAGMAdABpAG8AbgBzACAAZgBvAHIAIABlAGwAZQBnAGEAbgB0ACAAcwBlAHEAdQBlAG4AYwBpAG4AZwAsAFwAbgAgACAAIAAgAGMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAGEAbgBhAGwAeQBzAGkAcwAsACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAESBiAGEAcwBlAGQAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4ALAAgAGEAbgBkACAAcwB0AGEAdABpAHMAdABpAGMAcwAuAFwAbgAgACAAIAAgAFQAaABpAHMAIABtAG8AZAB1AGwAZQAgAGUAeAB0AGUAbgBkAHMAIAB0AGgAZQAgAGMAYQBwAGEAYgBpAGwAaQB0AGkAZQBzACAAbwBmACAAbgBhAHQAaQB2AGUAIABFAHgAYwBlAGwAIABmAHUAbgBjAHQAaQBvAG4AcwBcAG4AIAAgACAAIAAoAGUALgBnAC4ALAAgAE0AbwBkAGUAuwMgAGMAYQBuACAAcgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AbwBzAHQAIABmAHIAZQBxAHUAZQBuAHQAIABuAHUAbQBlAHIAaQBjAGEAbAAgAG8AcgAgAHQAZQB4AHQAIAB2AGEAbAB1AGUAcwApAC4AXABuAFwAbgAgACAAIAAgAFMAdQBiABEgYwBhAHQAZQBnAG8AcgBpAGUAcwA6AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABTAGUAcQB1AGUAbgBjAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwB0AHIAZQBhAGsAuwMsACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMsACAASQBuAHMAdABhAG4AYwBlALsDLAAgAFcAYQB2AGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgB5AEQAaQBhAGcAuwMsACAARABpAGEAZwBNAGEAcAC7AywAIABEAGkAYQBnAEkAbgBkAGUAeAC7AywAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwMsACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AywAIABRAHUAYQBkAHcAaQBzAGUAuwMsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwByAG8AdQBwAGIAeQBCAGkAbgC7AywAIABHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMsACAAUABpAHYAbwB0AGIAeQBDAGEAdAC7AywAXABuAFwAdABcAHQAXAB0ACAAIABHAHIAbwB1AHAASQBuAGQAZQB4ALsDLAAgAE8AYwBjAHUAcgByAGUAbgBjAGUAuwMsACAATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAiICAATgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEcAcgBhAGkAbgC7AywAIABNAG8AbwByAGUAQQBnAGcAuwMsACAATQBvAG8AcgBlAFMAZQBsAGUAYwB0ALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFMAdABhAHQAaQBzAHQAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAGkAcwB0AG8AZwByAGEAbQC7AywAIABNAG8AZABlALsDLAAgAFoAbwBuAGUAUwB0AGEAdAC7A1wAbgAqAC8AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABTAHQAcgBlAGEAawC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABTAGUAcQB1AGUAbgBjAGkAbgBnACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbQBwAHUAdABlAHMAIABzAHQAcgBlAGEAawAgAGMAbwB1AG4AdABzACAAbwBmACAAYwBvAG4AcwBlAGMAdQB0AGkAdgBlACAAaQBkAGUAbgB0AGkAYwBhAGwAIAB2AGEAbAB1AGUAcwAgAGkAbgAgAGEAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABTAHQAcgBlAGEAawBzACAAaQBuAGMAcgBlAG0AZQBuAHQAIABmAG8AcgB3AGEAcgBkACAAKAAxACwAIAAyACwAIAAzACwAIAAmICkAIAB3AGgAZQBuAGUAdgBlAHIAIAB0AGgAZQAgAGMAdQByAHIAZQBuAHQAIABlAGwAZQBtAGUAbgB0ACAAbQBhAHQAYwBoAGUAcwBcAG4AIAAgACAAIAB0AGgAZQAgAHAAcgBlAHYAaQBvAHUAcwAgAG8AbgBlAC4AIABGAG8AcgAgADIARAAgAGEAcgByAGEAeQBzACwAIABzAHQAcgBlAGEAawBzACAAYQByAGUAIABjAG8AbQBwAHUAdABlAGQAIAByAG8AdwARIG0AYQBqAG8AcgAgAGIAeQAgAGQAZQBmAGEAdQBsAHQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0AIAAgACAAIAAgACAALQAgAEYAbwByACAAMQBEACAAYQByAHIAYQB5AHMALAAgAGMAbwBtAHAAdQB0AGUAIABzAHQAcgBlAGEAawBzACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAaQBuAHMAdABlAGEAZAAgAG8AZgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAbwB3ABEgdwBpAHMAZQAuACAASQBnAG4AbwByAGUAZAAgAGYAbwByACAAMgBEACAAYQByAHIAYQB5AHMALgBcAG4AIAAgACAAIABbAEkAbgBjAGwAdQBkAGUAXwBTAHkAbQBiAG8AbAA/AF0AIAAgAC0AIABJAGYAIABUAFIAVQBFACwAIABhAHAAcABlAG4AZAAgAHQAaABlACAAcwB5AG0AYgBvAGwAIAB0AG8AIAB0AGgAZQAgAHMAdAByAGUAYQBrACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABlAC4AZwAuACwAIABXALcAMQAsACAAVwC3ADIALAAgAEwAtwAxACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAcgBlAHQAdQByAG4AIAB0AGgAZQBtAHMAZQBsAHYAZQBzAC4AXABuACAAIAAgACAAIiAgADIARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHIAbwB3ABEgbQBhAGoAbwByACwAIABwAHIAbwBjAGUAcwBzAGUAZAAsACAAdABoAGUAbgAgAHIAZQBzAHQAbwByAGUAZAAuAFwAbgAgACAAIAAgACIgIABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AIABvAG4AbAB5ACAAYQBwAHAAbABpAGUAcwAgAHQAbwAgADEARAAgAGEAcgByAGEAeQBzAC4AXABuACAAIAAgACAAIiAgAEkAbgBjAGwAdQBkAGUAXwBTAHkAbQBiAG8AbAA/ACAAdQBzAGUAcwAgAFUATgBJAEMASABBAFIAKAAxADgAMwApACAAKAC3ACkAIABhAHMAIAB0AGgAZQAgAHMAZQBwAGEAcgBhAHQAbwByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFMAdAByAGUAYQBrALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0ALABcAG4AIAAgACAAIABbAEkAbgBjAGwAdQBkAGUAXwBTAHkAbQBiAG8AbAA/AF0ALABcAG4AXABuAEkARgAoAEEATgBEACgAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPQAgADEALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgAD0AIAAxACkALABhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA+ACAAMQAsACAAdwAgAD4AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgADIARAAgAJIhIAAxAEQAXABuACAAIAAgACAAYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMgBEAD8ALAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACwAIABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAcgBlAGMAdABpAG8AbgAgACgAbwBuAGwAeQAgAHIAZQBsAGUAdgBhAG4AdAAgAGYAbwByACAAMQBEACkAXABuACAAIAAgACAATgBvAEQAaQByAD8ALAAgACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAEgAbwByAGkAegBvAG4AdABhAGwAPwApACwAXABuACAAIAAgACAAZgBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8ARABpAHIAPwAsACAAVgBTAFQAQQBDAEsALAAgAEgAUwBUAEEAQwBLACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AcABhAHIAZQAgAHcAaQB0AGgAIABwAHIAZQB2AGkAbwB1AHMAIABlAGwAZQBtAGUAbgB0AFwAbgAgACAAIAAgAGsAZQBwAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAEQAaQByAD8ALAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgAC0AMQApACwAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAYQByAHIAYQB5ACAAPQAgAGYAbgAoAFwAIgBvAG0AaQB0AFwAIgAsACAAawBlAHAAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAYwBjAHUAbQB1AGwAYQB0AGUAIABzAHQAcgBlAGEAawAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGEAYwBjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBDAEEATgAoADAALABiAG8AbwBsACwATABBAE0AQgBEAEEAKABhACwAIAB2ACwASQBGACgAYQAgAD0AIAAwACwAIAAxACwAIABJAEYAKAB2ACwAIABhACAAKwAgADEALAAgADEAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABzAHkAbQBiAG8AbAAgAGkAbgBjAGwAdQBzAGkAbwBuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABJAG4AYwBsAHUAZABlAF8AUwB5AG0AYgBvAGwAPwApACwAYQBjAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQByAHIAYQB5ACAAJgAgAFUATgBJAEMASABBAFIAKAAxADgAMwApACAAJgAgAGEAYwBjACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgADIARAAgAHMAaABhAHAAZQAgAGkAZgAgAG4AZQBlAGQAZQBkAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgACAASQBGACgASQBzADIARAA/ACwAIABXAFIAQQBQAFIATwBXAFMAKAByAGUAcwB1AGwAdAAsACAAdwApACwAIAByAGUAcwB1AGwAdAApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEMAbwB1AG4AdABkAG8AdwBuALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAFMAZQBxAHUAZQBuAGMAaQBuAGcAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBvAHUAbgB0AGQAbwB3AG4AIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgB1AG4AcwAgAGkAbgAgAGEAIAAxAEQAIABhAHIAcgBhAHkALgAgAEUAYQBjAGgAIAByAHUAbgBcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAgAGQAbwB3AG4AIABmAHIAbwBtACAAaQB0AHMAIABsAGUAbgBnAHQAaAAgAHQAbwAgADEALgAgAEMAbwB1AG4AdABkAG8AdwBuALsDIABpAHMAIABtAG8AcwB0ACAAdQBzAGUAZgB1AGwAIAB3AGgAZQBuACAAdwBvAHIAawBpAG4AZwBcAG4AIAAgACAAIAB3AGkAdABoACAAcwBvAHIAdABlAGQAIAB2AGUAYwB0AG8AcgBzACAAYQBuAGQAIABpAHMAIAB0AGgAZQAgAG4AYQB0AHUAcgBhAGwAIAByAGUAdgBlAHIAcwBlACAAbwBmACAAUwB0AHIAZQBhAGsAuwMuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5AC4AXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAOgBcAG4AIAAgACAAIABbAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACAAIAAgACAALQAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAG8AdQB0AHAAdQB0ACAAaQBzACAAdgBlAHIAdABpAGMAYQBsAC4AIABJAGYAIABUAFIAVQBFACwAIABvAHUAdABwAHUAdAAgAGkAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHQAdQByAG4AZQBkACAAaABvAHIAaQB6AG8AbgB0AGEAbABsAHkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABBAGwAdwBhAHkAcwAgAGYAbABhAHQAdABlAG4AcwAgAGkAbgBwAHUAdAAgAHQAbwAgAGEAIABzAGkAbgBnAGwAZQAgAGMAbwBsAHUAbQBuACAAYgBlAGYAbwByAGUAIABwAHIAbwBjAGUAcwBzAGkAbgBnAC4AXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AdQBuAHQAZABvAHcAbgC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACwAXABuAFwAbgBJAEYAKABBAE4ARAAoAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgAD0AIAAxACwAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkAIAA9ACAAMQApACwAYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAEkAcwAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA+ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIAAyAEQAIACSISAAMQBEAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzADIARAA/ACwAIABUAE8AQwBPAEwAKABhAHIAcgBhAHkAKQAsACAAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AIAAoAG8AbgBsAHkAIAByAGUAbABlAHYAYQBuAHQAIABmAG8AcgAgADEARAApAFwAbgAgACAAIAAgAE4AbwBEAGkAcgA/ACwAIAAgACAAIAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQAsAFwAbgAgACAAIAAgAGYAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAEQAaQByAD8ALAAgAFYAUwBUAEEAQwBLACwAIABIAFMAVABBAEMASwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBtAHAAYQByAGUAIAB3AGkAdABoACAAcAByAGUAdgBpAG8AdQBzACAAZQBsAGUAbQBlAG4AdABcAG4AIAAgACAAIABrAGUAcAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBEAGkAcgA/ACwAIABEAFIATwBQACgAYQByAHIAYQB5ACwAIAAtADEAKQAsACAARABSAE8AUAAoAGEAcgByAGEAeQAsACAALAAgAC0AMQApACkALABcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAcgByAGEAeQAgAD0AIABmAG4AKABcACIAbwBtAGkAdABcACIALAAgAGsAZQBwAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAGMAYwB1AG0AdQBsAGEAdABlACAAcwB0AHIAZQBhAGsAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABhAGMAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAQwBBAE4AKAAwACwAYgBvAG8AbAAsAEwAQQBNAEIARABBACgAYQAsACAAdgAsAEkARgAoAGEAIAA9ACAAMAAsACAAMQAsACAASQBGACgAdgAsACAAYQAgACsAIAAxACwAIAAxACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBoAGEAbgBnAGUAIABnAHIAbwB1AHAAcwBcAG4AIAAgACAAIABjAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAQwBBAE4AKAAwACwATgBPAFQAKABiAG8AbwBsACkALABTAFUATQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAbwByAHQAIABkAGUAcwBjAGUAbgBkAGkAbgBnAFwAbgAgACAAIAAgAHMAbwByAHQAZQBkACwAIAAgACAAIAAgACAAIAAgACAAUwBPAFIAVABCAFkAKABhAGMAYwAsAGMAZwAsADEALABhAGMAYwAsAC0AMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBzAHQAbwByAGUAIAAyAEQAIABzAGgAYQBwAGUAIABpAGYAIABuAGUAZQBkAGUAZABcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAyAEQAPwAsACAAVwBSAEEAUABSAE8AVwBTACgAcwBvAHIAdABlAGQALAAgAHcAKQAsACAAcwBvAHIAdABlAGQAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADEANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEkAbgBzAHQAYQBuAGMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAWwBHAFIAMAAzAF0AIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAUwBlAHEAdQBlAG4AYwBpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAQwBvAHUAbgB0AGQAbwB3AG4AuwMsACAATQBHAHIAaQBkALsDLAAgAFMAdAByAGUAYQBrALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABPAGIAdABhAGkAbgAgAHQAaABlACAAaQBuAHMAdABhAG4AYwBlACAAbgB1AG0AYgBlAHIAcwAgAGYAbwByACAAdQBuAHMAbwByAHQAZQBkACAAdgBhAGwAdQBlAHMAIABpAG4AIABhACAAMQBEACAAYQByAHIAYQB5ACAAdwBpAHQAaAAgAG8AcAB0AGkAbwBuAHMAXABuACAAIAAgACAAZgBvAHIAIAByAGUAdAB1AHIAbgBpAG4AZwAgAGkAbgBzAHQAYQBuAGMAZQBzACAAZgBvAHIAIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAdgBlAGMAdABvAHIAcwAsACAAYQBuAGQAIABkAGkAcwBwAGwAYQB5AGkAbgBnACAAaQBuAHMAdABhAG4AYwBlAHMAIABpAG4AXABuACAAIAAgACAAZABlAHMAYwBlAG4AZABpAG4AZwAgAG8AcgBkAGUAcgAuAFwAbgAgACAAIAAgAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACAAIAAgACAAIAAgACAAIAAgACAALQAgACAAIAAxAEQAIABhAHIAcgBhAHkAIABpAG4AcAB1AHQAIAAoADIARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAApAFwAbgAgACAAIAAgAFsASABvAHIAaQB6AG8AbgB0AGEAbAA/AF0AIAAgACAALQAgACAAIABJAGYAIABUAFIAVQBFACwAIABvAGIAdABhAGkAbgAgAGkAbgBzAHQAYQBuAGMAZQAgAG4AdQBtAGIAZQByAHMAIABmAG8AcgAgAGgAbwByAGkAegBvAG4AdABhAGwAIAB2AGUAYwB0AG8AcgBzAFwAbgAgACAAIAAgAFsARABlAHMAYwBlAG4AZAA/AF0AIAAgACAAIAAgACAALQAgACAAIABJAGYAIABUAFIAVQBFACwAIABkAGkAcwBwAGwAYQB5ACAAaQBuAHMAdABhAG4AYwBlAHMAIABpAG4AIABkAGUAcwBjAGUAbgBkAGkAbgBnACAAbwByAGQAZQByAFwAbgAgACAAIAAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBJAG4AcwB0AGEAbgBjAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACwAXABuACAAIAAgACAAWwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAsAFwAbgAgACAAIAAgAFsARABlAHMAYwBlAG4AZAA/AF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAHYAZQBjAHQAbwByACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAIABvAGYAIAAxAEQAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAsACAAIAAgACAAIAAgAFIATwBXAFMAKAB2AGUAYwB0AG8AcgApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAdgBlAGMAdABvAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAASQBTAE8ATQBJAFQAVABFAEQAKABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQAsAFwAbgAgACAAIAAgAEkAcwBEAGUAcwBjAGUAbgBkAD8ALAAgACAAQQBOAEQAKABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgARABlAHMAYwBlAG4AZAA/ACkAKQAsACAARABlAHMAYwBlAG4AZAA/ACAAPQAgAFQAUgBVAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgAEEATgBEACgAaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAaABlAGkAZwBoAHQAIAA+ACAAMQAwADQAOAA1ADcANgAsAGgAZQBpAGcAaAB0ACAAPgAgADEANgAzADgANAApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAdgBlAGMAdABvAHIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABTAHAAaQBsAGwAUgBpAHMAawA/ACwAIwBOAFUATQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFQAeQBwAGUAIABvAGYAIABpAG4AZABlAHgAXABuACAAIAAgACAAaQBkAHgAuwMsACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARABlAHMAYwBlAG4AZAA/ACwAIABDAG8AdQBuAHQAZABvAHcAbgC7AywAIABTAHQAcgBlAGEAawC7AykALABcAG4AXABuACAAIAAgACAALwAvACAAUwBvAHIAdAAgAGsAZQB5AFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBHAHIAaQBkALsDKAB2AGUAYwB0AG8AcgApACwAXABuACAAIAAgACAAXABuACAAIAAgACAALwAvACAAUwBvAHIAdAAgAGEAcwAgADIARAAgAGEAcgByAGEAeQAsACAAbwBiAHQAYQBpAG4AIABzAHQAcgBlAGEAawBcAG4AIAAgACAAIABzAG8AcgB0AGUAZAAsACAAIAAgACAAIAAgAFMATwBSAFQAKABIAFMAVABBAEMASwAoAGkALAB2AGUAYwB0AG8AcgApACwAMgApACwAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIABpAGQAeAC7AygAVABBAEsARQAoAHMAbwByAHQAZQBkACwALAAtADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAbgBnAGUAIABuAGUAdwAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABuAGUAdwBfAGEAcgByACwAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAcwBvAHIAdABlAGQALABpAGQAeAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAbwByAHQAIABiAHkAIABrAGUAeQAsACAAbwBiAHQAYQBpAG4AIABpAG4AcwB0AGEAbgBjAGUAIABuAHUAbQBiAGUAcgBcAG4AIAAgACAAIABpAG4AcwB0ACwAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABTAE8AUgBUACgAbgBlAHcAXwBhAHIAcgApACwALAAtADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUALQBzAGgAYQBwAGUALAAgAGkAZgAgAG4AZQBlAGQAZQBkACAAYQBuAGQAIAByAGUAdAB1AHIAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsAGkAbgBzAHQALABUAE8AUgBPAFcAKABpAG4AcwB0ACkAKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAxADcAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAVwBhAHYAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAUwBlAHEAdQBlAG4AYwBpAG4AZwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAARQBjAGgAbwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHQAdQByAG4AcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIAAxAEQAIABcACIAdwBhAHYAZQAgAGEAcgByAGEAeQBcACIAIABiAHkAIABzAHUAcABwAGwAeQBpAG4AZwAgAGEAIABjAHIAZQBzAHQAIAAoAG0AYQB4ACAAdgBhAGwAdQBlACkAIABhAG4AZAAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAHIAZQBwAF8AYwBvAHUAbgB0AC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYwByAGUAcwB0ACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAgACAAbQBhAHgAIAB2AGEAbAB1AGUAIABpAG4AIAAxAEQAIAB3AGEAdgBlACAAYQByAHIAYQB5AFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAFsAcgBlAHAAXwBjAG8AdQBuAHQAXQAgACAAIAAgACAAIAAtACAAIAAgAG4AdQBtAGIAZQByACAAbwBmACAAdABpAG0AZQBzACAAdABvACAAcgBlAHAAZQBhAHQAIABlAGEAYwBoACAAaQBuAHQAZQBnAGUAcgAgAGkAbgAgAHcAYQB2AGUAIABhAHIAcgBhAHkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAbgBvACAAcgBlAHAAZQB0AGkAdABpAG8AbgAuAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBXAGEAdgBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAcgBlAHMAdAAsAFwAbgAgACAAIAAgAFsAcgBlAHAAXwBjAG8AdQBuAHQAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFcAYQB2AGUAIABtAG8AZABlAFwAbgAgACAAIAAgAFMAdABhAG4AZABhAHIAZAA/ACwAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAcgBlAHAAXwBjAG8AdQBuAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIAByAGUAcABlAHQAaQB0AGkAbwBuAFwAbgAgACAAIAAgAHIAZQBwAF8AYwBvAHUAbgB0ACwAIAAgAEkARgAoAFMAdABhAG4AZABhAHIAZAA/ACwAMQAsAEkATgBEAEUAWAAoAHIAZQBwAF8AYwBvAHUAbgB0ACwAMQAsADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAYwByAGUAcwB0AFwAbgAgACAAIAAgAGMAcgBlAHMAdAAsACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGMAcgBlAHMAdAAsADEALAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQATgA/ACwAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYwByAGUAcwB0ACkALAAgAGMAcgBlAHMAdAAgADwAIAAwACkALABcAG4AIAAgACAAIABTAHAAaQBsAGwAUgBpAHMAawA/ACwAIAByAGUAcABfAGMAbwB1AG4AdAAgACoAIAAoAGMAcgBlAHMAdAAgACoAIAAyACAALQAgADEAKQAgAD4AIAAxADAANAA4ADUANwA2ACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQATgA/ACwAIAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAIwBOAFUATQAhACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATABlAG4AZwB0AGgAIABvAGYAIABzAGUAcQB1AGUAbgBjAGUAIAAoAGIAZQBmAG8AcgBlACAAYQBuAHkAIAByAGUAcABlAHQAaQB0AGkAbwBuACAAaQBzACAAYQBkAGQAZQBkACkAXABuACAAIAAgACAAawAsACAAIAAgACAAYwByAGUAcwB0ACAAKgAgADIAIAAtACAAMQAsAFwAbgAgACAAIAAgAHMAZQBxACwAIAAgAFMARQBRAFUARQBOAEMARQAoAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAeAAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAbQAsACAAIAAgACAATQBBAFgAKABzAGUAcQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBxAHUAZQBuAGMAZQAgAGEAZABqAHUAcwB0AG0AZQBuAHQAXABuACAAIAAgACAAdwAsACAAIAAgACAASQBGACgAcwBlAHEAIAA+ACAAYwByAGUAcwB0ACwAIABtACAALQAgAHMAZQBxACAAKwAgADEALAAgAHMAZQBxACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHMAcABsAGEAeQAgAHcAYQB2AGUAIABzAGUAcQB1AGUAbgBjAGUAIAB3AGkAdABoACAAbwBwAHQAaQBvAG4AYQBsACAAZQBjAGgAbwBpAG4AZwBcAG4AIAAgACAAIABmAGkAbgBhAGwALABJAEYAKABTAHQAYQBuAGQAYQByAGQAPwAsAHcALABFAGMAaABvALsDKAB3ACwAcgBlAHAAXwBjAG8AdQBuAHQAKQApACwAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAQgB5AEQAaQBhAGcAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQBwAHAAbABpAGUAcwAgAGEAbgAgAEUAVABBACAAZgB1AG4AYwB0AGkAbwBuACAAbwByACAATABhAG0AYgBkAGEAIAB0AG8AIABlAGEAYwBoACAAZABpAGEAZwBvAG4AYQBsACAAbwBmACAAYQAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAEQAaQBhAGcAbwBuAGEAbABzACAAYQByAGUAIABlAHgAdAByAGEAYwB0AGUAZAAgAGYAcgBvAG0AIAB0AG8AcAARIGwAZQBmAHQAIAB0AG8AIABiAG8AdAB0AG8AbQARIHIAaQBnAGgAdAAsACAAdwBpAHQAaAAgAGUAYQBjAGgAIABkAGkAYQBnAG8AbgBhAGwAXABuACAAIAAgACAAcgBlAHAAcgBlAHMAZQBuAHQAZQBkACAAYQBzACAAYQAgAHIAbwB3ACAAaQBuACAAdABoAGUAIABvAHUAdABwAHUAdAAuACAATwBwAHQAaQBvAG4AYQBsAGwAeQAsACAAcgBlAHMAdQBsAHQAcwAgAG0AYQB5ACAAYgBlACAAcwB0AGEAYwBrAGUAZABcAG4AIAAgACAAIAByAG8AdwARIHcAaQBzAGUAIAAoAHYAZQByAHQAaQBjAGEAbAApACAAbwByACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlACAAKABoAG8AcgBpAHoAbwBuAHQAYQBsACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIAcwAgAG4AbwB0ACAAYQBjAGMAZQBwAHQAZQBkACkALgBcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACAAIAAgACAAIAAgACAAIAAgACAALQAgAEUAVABBACAAZgB1AG4AYwB0AGkAbwBuACAAbwByACAATABhAG0AYgBkAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAZQBhAGMAaAAgAGQAaQBhAGcAbwBuAGEAbAAuAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAgACAAIAAtACAASQBmACAAVABSAFUARQAsACAAcgBlAHMAdQBsAHQAcwAgAGEAcgBlACAAcwB0AGEAYwBrAGUAZAAgAHYAZQByAHQAaQBjAGEAbABsAHkAOwAgAG8AdABoAGUAcgB3AGkAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAYQBnAG8AbgBhAGwAcwAgAGEAcgBlACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAYwBvAGwAdQBtAG4AcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgADEARAAgAGEAcgByAGEAeQBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQAIABiAHkAIABWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7Ay4AXABuACAAIAAgACAAIiAgAEkAZgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAG8AbQBpAHQAdABlAGQALAAgAHIAYQB3ACAAZABpAGEAZwBvAG4AYQBsAHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHMAaABhAHAAZQAgAGkAcwAgAGsAIADXACAAagAgAHcAaABlAHIAZQAgAGsAIAA9ACAATQBJAE4AKAByAG8AdwBzACwAIABjAG8AbAB1AG0AbgBzACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQgB5AEQAaQBhAGcAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAsAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAsAFwAbgBcAG4AVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwMoAGEAcgByAGEAeQAsACAALAAgAGYAdQBuAGMAdABpAG8AbgAsACAAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgAgACAAIAAgAE4AbwBfAEYAdQBuAGMAdABpAG8AbgAsACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGYAdQBuAGMAdABpAG8AbgApACwAXABuACAAIAAgACAATgBvAF8AUgBvAHcAUwB0AGEAYwBrACwAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AdQBtAGIAZQByACAAbwBmACAAZABpAGEAZwBvAG4AYQBsAHMAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAaAAsACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGUAcgByAGUAZAAgAGkAbgBkAGUAeAAgAGcAZQBuAGUAcgBhAHQAbwByAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAawApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIAB3ACwAIAAxACwAIAAwACkAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGsAKQAgACsAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwAsACAAMAAsACAAMQApACkALABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKAB5ACgAKQAgAD4AIAB3ACwAIABOAEEAKAApACwAIAB5ACgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAGQAaQBhAGcAbwBuAGEAbABzAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYATgBBACgASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIAByACgAKQAsACAAYwAoACkAKQAsACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcgBpAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABzAGgAYQBwAGUAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAF8AUgBvAHcAUwB0AGEAYwBrACwAIAByAGUAcwB1AGwAdAAsACAAVABSAEEATgBTAFAATwBTAEUAKAByAGUAcwB1AGwAdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAZgB1AG4AYwB0AGkAbwBuACAAaQBmACAAcAByAG8AdgBpAGQAZQBkAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AXwBGAHUAbgBjAHQAaQBvAG4ALABzAGgAYQBwAGUAZAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBfAFIAbwB3AFMAdABhAGMAawAsAEIAWQBDAE8ATAAoAHMAaABhAHAAZQBkACwAIABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAHMAaABhAHAAZQBkACwAIABmAHUAbgBjAHQAaQBvAG4AKQApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABEAGkAYQBnAE0AYQBwALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQgB5AEQAaQBhAGcAuwMsACAAVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwBuAHYAZQBuAGkAZQBuAGMAZQAgAHcAcgBhAHAAcABlAHIAIABmAG8AcgAgAEIAeQBEAGkAYQBnALsDIAB0AGgAYQB0ACAAZQB4AHQAcgBhAGMAdABzACAAYQBsAGwAIABkAGkAYQBnAG8AbgBhAGwAcwAgAGYAcgBvAG0AIABhACAAMgBEAFwAbgAgACAAIAAgAGEAcgByAGEAeQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAHQAaABlAG0AIABhAHMAIABhACAAMgBEACAAYQByAHIAYQB5AF8AMgBEAC4AIABPAHAAdABpAG8AbgBhAGwAIAByAG8AdwARIHcAaQBzAGUAIABzAHQAYQBjAGsAaQBuAGcAIABpAHMAXABuACAAIAAgACAAcwB1AHAAcABvAHIAdABlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAgACAAIAAtACAASQBmACAAVABSAFUARQAsACAAZABpAGEAZwBvAG4AYQBsAHMAIABhAHIAZQAgAHMAdABhAGMAawBlAGQAIAB2AGUAcgB0AGkAYwBhAGwAbAB5AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAGMAYQBsAGwAaQBuAGcAIABCAHkARABpAGEAZwC7AygAYQByAHIAYQB5ACwAIAAsACAAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAGkAYQBnAE0AYQBwALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAsAFwAbgAgACAAIAAgAEIAeQBEAGkAYQBnALsDKABhAHIAcgBhAHkALAAgACwAIAByAG8AdwBfAHcAaQBzAGUAXwBzAHQAYQBjAGsAPwApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARABpAGEAZwBJAG4AZABlAHgAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABCAHkARABpAGEAZwC7AywAIABWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQB4AHQAcgBhAGMAdABzACAAYQAgAHMAaQBuAGcAbABlACAAZABpAGEAZwBvAG4AYQBsACAAbwByACAAYQBuAHQAaQARIGQAaQBhAGcAbwBuAGEAbAAgAHYAZQBjAHQAbwByACAAZgByAG8AbQAgAGEAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABQAG8AcwBpAHQAaQB2AGUAIABjAG8AbABfAGkAbgBkAGUAeAAgAHMAZQBsAGUAYwB0AHMAIABhACAAcwB0AGEAbgBkAGEAcgBkACAAKABTAEUAESBkAGkAcgBlAGMAdABpAG8AbgApACAAZABpAGEAZwBvAG4AYQBsAC4AXABuACAAIAAgACAATgBlAGcAYQB0AGkAdgBlACAAYwBvAGwAXwBpAG4AZABlAHgAIABzAGUAbABlAGMAdABzACAAYQBuACAAYQBuAHQAaQARIGQAaQBhAGcAbwBuAGEAbAAgACgAUwBXABEgZABpAHIAZQBjAHQAaQBvAG4AKQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIAAoAHMAYwBhAGwAYQByAHMAIABuAG8AdAAgAGEAYwBjAGUAcAB0AGUAZAApAC4AXABuACAAIAAgACAAYwBvAGwAXwBpAG4AZABlAHgAIAAgACAALQAgAFMAdABhAHIAdABpAG4AZwAgAGMAbwBsAHUAbQBuACAAaQBuAGQAZQB4AC4AIABOAGUAZwBhAHQAaQB2AGUAIAB2AGEAbAB1AGUAcwAgAGkAbgBkAGkAYwBhAHQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAG4AdABpABEgZABpAGEAZwBvAG4AYQBsACAAZQB4AHQAcgBhAGMAdABpAG8AbgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAaQBzACAAYQBsAHcAYQB5AHMAIABhACAAMQBEACAAdgBlAGMAdABvAHIAIABvAGYAIABsAGUAbgBnAHQAaAAgAGsAIAA9ACAAZABpAGEAZwBvAG4AYQBsACAAbABlAG4AZwB0AGgALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABpAGEAZwBJAG4AZABlAHgAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBvAGwAXwBpAG4AZABlAHgALABcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBEAGkAYQBnALsDKABhAHIAcgBhAHkALAAgAGMAbwBsAF8AaQBuAGQAZQB4ACwAIAAsACAALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AOgAgACsAMQAgAD0AIABTAEUALAAgABMgMQAgAD0AIABTAFcAXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAGEAZwBvAG4AYQBsACAAbABlAG4AZwB0AGgAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAASQBGACgAcwAgAD4AIAAwACwATQBJAE4AKABoACwAIAB3ACAAKwAgADEAIAAtACAAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAaAAsACAAQQBCAFMAKABjAG8AbABfAGkAbgBkAGUAeAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQByAHQAaQBuAGcAIABjAG8AbAB1AG0AbgBcAG4AIAAgACAAIABzAHQAYQByAHQALAAgACAAIABJAEYAKABzACAAPAAgADAALAAgAEEAQgBTACgAYwBvAGwAXwBpAG4AZABlAHgAKQAsACAAYwBvAGwAXwBpAG4AZABlAHgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABpAG4AZABlAHgAIABnAGUAbgBlAHIAYQB0AG8AcgBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAawApACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGsALAAgACwAIABzAHQAYQByAHQALAAgAHMAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABkAGkAYQBnAG8AbgBhAGwAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIAB4ACgAKQAsACAAeQAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgARIEMATwBSAEUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABWAGEAbABpAGQAYQB0AGUARABpAGEAZwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAG8AcgBlACAAVgBhAGwAaQBkAGEAdABpAG8AbgApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVgBhAGwAaQBkAGEAdABlAHMAIABpAG4AcAB1AHQAcwAgAGYAbwByACAAQgB5AEQAaQBhAGcAuwMsACAARABpAGEAZwBNAGEAcAC7AywAIABhAG4AZAAgAEQAaQBhAGcASQBuAGQAZQB4ALsDLgAgAEUAbgBzAHUAcgBlAHMAIAB0AGgAYQB0ACAAdABoAGUAXABuACAAIAAgACAAYQByAHIAYQB5ACAAaQBzACAAYQAgAHYAYQBsAGkAZAAgADIARAAgAHMAdAByAHUAYwB0AHUAcgBlACwAIAB0AGgAYQB0ACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACAAKAB3AGgAZQBuACAAcwB1AHAAcABsAGkAZQBkACkAIABhAHIAZQBcAG4AIAAgACAAIAB3AGkAdABoAGkAbgAgAGIAbwB1AG4AZABzACwAIABhAG4AZAAgAHQAaABhAHQAIABhAG4AeQAgAHMAdQBwAHAAbABpAGUAZAAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGEAIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQAvAEUAVABBAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMgBEACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAAIAAgACAAIAAgACAAIAAgAC0AIABTAHQAYQByAHQAaQBuAGcAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgACgARABpAGEAZwBJAG4AZABlAHgAuwMgAG8AbgBsAHkAKQAuAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0AIAAgACAAIAAgACAAIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABMAEEATQBCAEQAQQAgACgAQgB5AEQAaQBhAGcAuwMgAG8AbgBsAHkAKQAuAFwAbgAgACAAIAAgAFsAcgBvAHcAXwB3AGkAcwBlAF8AcwB0AGEAYwBrAD8AXQAgACAAIAAtACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAZgBsAGEAZwAgACgAQgB5AEQAaQBhAGcAuwMgAC8AIABEAGkAYQBnAE0AYQBwALsDKQAuAFwAbgAgACAAIAAgAFsAbwBuAF8AdgBhAGwAaQBkAF0AIAAgACAAIAAgACAAIAAgACAAIAAtACAARQB4AHAAcgBlAHMAcwBpAG8AbgAgAHQAbwAgAGUAdgBhAGwAdQBhAHQAZQAgAHcAaABlAG4AIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAdgBhAGwAaQBkAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAbgBvAG4AESBhAHIAcgBhAHkAcwAgAGEAcgBlACAAcgBlAGoAZQBjAHQAZQBkAC4AXABuACAAIAAgACAAIiAgAGMAbwBsAF8AaQBuAGQAZQB4ACAAPQAgADAAIABpAHMAIABpAG4AdgBhAGwAaQBkACAAYgB5ACAAZABlAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAiICAARgB1AG4AYwB0AGkAbwBuACAAdgBhAGwAaQBkAGEAdABpAG8AbgAgAHUAcwBlAHMAIABhACAAcwBhAGYAZQAgAFQAWQBQAEUAESBiAGEAcwBlAGQAIABpAG4AdgBvAGMAYQB0AGkAbwBuACAAdABlAHMAdAAuAFwAbgAgACAAIAAgACIgIABSAG8AdQB0AGkAbgBnACAAbABvAGcAaQBjACAAZABlAHQAZQByAG0AaQBuAGUAcwAgAHcAaABpAGMAaAAgAG8AcABlAHIAYQB0AG8AcgAgAGkAcwAgAGIAZQBpAG4AZwAgAHYAYQBsAGkAZABhAHQAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBEAGkAYQBnALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AIAAgACAAIABbAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/AF0ALABcAG4AIAAgACAAIABbAG8AbgBfAHYAYQBsAGkAZABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAALQAtAC0AIABBAHIAcgBhAHkAIAB2AGEAbABpAGQAYQB0AGkAbwBuACAALQAtAC0AXABuACAAIAAgACAASQBzAEEAcgByAGEAeQA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABZAFAARQAoAGEAcgByAGEAeQApACAAPQAgADYANAAsAFwAbgAgACAAIAAgAE4AbwB0AF8AQQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBzAEEAcgByAGEAeQA/ACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABDAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAHYAYQBsAGkAZABhAHQAaQBvAG4AIAAoAEQAaQBhAGcASQBuAGQAZQB4ALsDIABvAG4AbAB5ACkAIAAtAC0ALQBcAG4AIAAgACAAIABOAG8AXwBDAG8AbABfAEkAbgBkAGUAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AIAAgACAAIABDAG8AbABJAG4AZABlAHgAXwBJAG4AYwBsAHUAZABlAGQALAAgACAAIAAgACAAIABOAE8AVAAoAE4AbwBfAEMAbwBsAF8ASQBuAGQAZQB4ACkALABcAG4AIAAgACAAIABOAG8AdABfAFYAYQBsAGkAZABfAEMAbwBsAEkAbgBkAGUAeAA/ACwAIAAgACAAIABOAE8AVAAoAEEATgBEACgAYwBvAGwAXwBpAG4AZABlAHgAIAA8AD4AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAQgBTACgAYwBvAGwAXwBpAG4AZABlAHgAKQAgADwAPQAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABGAHUAbgBjAHQAaQBvAG4AIAB2AGEAbABpAGQAYQB0AGkAbwBuACAAKABCAHkARABpAGEAZwC7AyAAbwBuAGwAeQApACAALQAtAC0AXABuACAAIAAgACAATgBvAF8ARgB1AG4AYwB0AGkAbwBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgAgACAAIAAgAEYAdQBuAGMAdABpAG8AbgBfAEkAbgBjAGwAdQBkAGUAZAAsACAAIAAgACAAIAAgAE4ATwBUACgATgBvAF8ARgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBhAGYAZQAgAGYAdQBuAGMAdABpAG8AbgAgAHYAYQBsAGkAZABhAHQAaQBvAG4AOgAgAGUAbgBzAHUAcgBlACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzACAAYwBhAGwAbABhAGIAbABlAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAXwBGAHUAbgBjAHQAaQBvAG4APwAsACAAIAAgACAAIAAgAEEATgBEACgARgB1AG4AYwB0AGkAbwBuAF8ASQBuAGMAbAB1AGQAZQBkACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAFMARQBSAFIATwBSACgAQgBZAFIATwBXACgAewAxACwAMQB9ACwAIABmAHUAbgBjAHQAaQBvAG4AKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABmAGwAYQBnACAAKABEAGkAYQBnAE0AYQBwALsDIAAvACAAQgB5AEQAaQBhAGcAuwMpACAALQAtAC0AXABuACAAIAAgACAAUgBvAHcAVwBpAHMAZQBTAHQAYQBjAGsAPwAsACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAHIAbwB3AF8AdwBpAHMAZQBfAHMAdABhAGMAawA/ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEQAZQB0AGUAcgBtAGkAbgBlACAAdwBoAGkAYwBoACAAbwBwAGUAcgBhAHQAbwByACAAaQBzACAAYgBlAGkAbgBnACAAdgBhAGwAaQBkAGEAdABlAGQAIAAtAC0ALQBcAG4AIAAgACAAIABJAHMARABpAGEAZwBJAG4AZABlAHgAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABDAG8AbABJAG4AZABlAHgAXwBJAG4AYwBsAHUAZABlAGQALABcAG4AIAAgACAAIABJAHMAQgB5AEQAaQBhAGcAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAE4AbwBfAEMAbwBsAF8ASQBuAGQAZQB4ACwAIABGAHUAbgBjAHQAaQBvAG4AXwBJAG4AYwBsAHUAZABlAGQAKQAsAFwAbgAgACAAIAAgAEkAcwBEAGkAYQBnAE0AYQBwAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgATgBvAF8AQwBvAGwAXwBJAG4AZABlAHgALAAgAE4AbwBfAEYAdQBuAGMAdABpAG8AbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAATABvAGcAaQBjACAAZwBhAHQAZQBzACAALQAtAC0AXABuACAAIAAgACAALwAvACAARABpAGEAZwBJAG4AZABlAHgAuwNcAG4AIAAgACAAIABnAGEAdABlAF8ARABpAGEAZwBJAG4AZABlAHgALAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AdABfAEEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8AVAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAHQAXwBWAGEAbABpAGQAXwBDAG8AbABJAG4AZABlAHgAPwAsACAAXAAiACMAQwBPAEwAVQBNAE4ALQBJAE4ARABFAFgAIQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBuAF8AdgBhAGwAaQBkACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHkARABpAGEAZwC7A1wAbgAgACAAIAAgAGcAYQB0AGUAXwBCAHkARABpAGEAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwB0AF8AQQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAE4ATwBUAC0AQQBSAFIAQQBZACEAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAF8ARgB1AG4AYwB0AGkAbwBuAD8ALAAgAFwAIgAjAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAG4AXwB2AGEAbABpAGQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBhAGcATQBhAHAAuwNcAG4AIAAgACAAIABnAGEAdABlAF8ARABpAGEAZwBNAGEAcAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AdABfAEEAcgByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8AVAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBuAF8AdgBhAGwAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABSAG8AdQB0AGUAIAB0AG8AIABjAG8AcgByAGUAYwB0ACAAZwBhAHQAZQAgAC0ALQAtAFwAbgAgACAAIAAgAGQAZQBjAGkAZABlACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBEAGkAYQBnAEkAbgBkAGUAeAA/ACwAIABnAGEAdABlAF8ARABpAGEAZwBJAG4AZABlAHgALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARABpAGEAZwBNAGEAcAA/ACwAIABnAGEAdABlAF8ARABpAGEAZwBNAGEAcAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEIAeQBEAGkAYQBnAD8ALAAgAGcAYQB0AGUAXwBCAHkARABpAGEAZwAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBVAE4AUgBPAFUAVABFAEQAIQBcACIAKQApACkALABcAG4AXABuACAAIAAgACAAZABlAGMAaQBkAGUAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAwADYAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABFAGMAaABvALsDLAAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAHIAZQBhAHQAZQBzACAAdgBlAHIAdABpAGMAYQBsACAAcABhAGkAcgBzACAAZgByAG8AbQAgADEARAAgAGEAbgBkACAAcwBjAGEAbABhAHIAIABpAG4AcAB1AHQAcwAuACAASQBuAHAAdQB0AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAdwBpAHQAaABcAG4AIAAgACAAIABUAE8AQwBPAEwAIAB0AG8AIABuAG8AcgBtAGEAbABpAHoAZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAuACAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHMAdAByAGkAYwB0AGwAeQAgAHAAcgBvAGgAaQBiAGkAdABlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgBfADEAIAAgACAAIAAtACAAMQBEACAAdgBlAGMAdABvAHIAIABvAHIAIABzAGMAYQBsAGEAcgAuAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMgAgACAAIAAgAC0AIAAxAEQAIAB2AGUAYwB0AG8AcgAgAG8AcgAgAHMAYwBhAGwAYQByAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFAAYQBpAHIAdwBpAHMAZQC7Az0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAdgBlAGMAdABvAHIAXwAxACwAXABuACAAIAAgACAAdgBlAGMAdABvAHIAXwAyACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIAB2ACwAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKAB2AGUAYwB0AG8AcgBfADEAKQAsAFwAbgAgACAAIAAgAHYAgiAsACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAHYAZQBjAHQAbwByAF8AMgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbABlAG0AZQBuAHQAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAHYAKQAsAFwAbgAgACAAIAAgAGsAgiAsACAAIAAgACAAIAAgACAAIAAgAEMATwBVAE4AVABBACgAdgCCICkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwAyAEQASQBuAHAAdQB0AD8ALAAgAE8AUgAoAEEATgBEACgAUgBPAFcAUwAoAHYAZQBjAHQAbwByAF8AMQApAD4AMQAsACAAQwBPAEwAVQBNAE4AUwAoAHYAZQBjAHQAbwByAF8AMQApAD4AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABSAE8AVwBTACgAdgBlAGMAdABvAHIAXwAyACkAPgAxACwAIABDAE8ATABVAE0ATgBTACgAdgBlAGMAdABvAHIAXwAyACkAPgAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABJAHMAMgBCAGkAZwA/ACwAIAAgACAAIABrACAAKgAgAGsAgiAgAD4AIAAxADAAMAAwADAAMAAwACwAXABuAFwAbgBJAEYAKABJAHMAMgBEAEkAbgBwAHUAdAA/ACwAIAAgACMAVgBBAEwAVQBFACEALABcAG4AXABuACAAIAAgACAASQBGACgASQBzADIAQgBpAGcAPwAsACAAIAAgACAAIAAjAE4AVQBNACEALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQwBhAHIAdABlAHMAaQBhAG4AIABlAHgAcABhAG4AcwBpAG8AbgBcAG4AIAAgACAAIAB4ACwAIAAgACAAIAAgACAARQBjAGgAbwC7AygAdgAsACAAawCCICkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAUgBlAHMAaQB6AGUAuwMoAHYAgiAsACAAawApACwAXABuACAAIAAgACAAcABhAGkAcgBzACwAIAAgAEgAUwBUAEEAQwBLACgAeAAsACAAeQApACwAXABuAFwAbgAgACAAIAAgAHAAYQBpAHIAcwBcAG4AIAAgACAAIABcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADAANgBhAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAFAAYQBpAHIAdwBpAHMAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIAB0AGgAZQAgAEMAYQByAHQAZQBzAGkAYQBuACAAcAByAG8AZAB1AGMAdAAgAG8AZgAgADMAIABzAGUAdABzAC4AIABBAGwAbAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAGEAbgBkAFwAbgAgACAAIAAgAHQAaABlACAAcgBlAHMAdQBsAHQAaQBuAGcAIAB0AHIAaQBwAGwAZQBzACAAcAByAGUAcwBlAHIAdgBlACAAdABoAGUAIABvAHIAZABlAHIAIABvAGYAIAB0AGgAZQAgAHMAdQBwAHAAbABpAGUAZAAgAHMAZQB0AHMALgBcAG4AXABuACAAIAAgACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AyAAZQB4AHQAZQBuAGQAcwAgAFAAYQBpAHIAdwBpAHMAZQC7AyAAdABvACAAYQAgADMAESBhAHgAaQBzACAAZgBhAGIAcgBpAGMAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABzAGUAdABfADEAIADXACAAcwBlAHQAXwAyACAA1wAgAHMAZQB0AF8AMwBcAG4AIAAgACAAIABUAGgAZQAgAG8AdQB0AHAAdQB0ACAAaQBzACAAYQAgAHMAcABpAGwAbAAgAHcAaABlAHIAZQAgAGUAYQBjAGgAIAByAG8AdwAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQAgAG8AcgBkAGUAcgBlAGQAIAB0AHIAaQBwAGwAZQAuAFwAbgBcAG4ARgBvAHIAbQB1AGwAYQA6ACAAPQBUAHIAaQBwAGwAZQB3AGkAcwBlALsDKAB7AFwAIgBkAG8AZwBcACIAOwBcACIAYwBhAHQAXAAiADsAXAAiAGIAaQByAGQAXAAiAH0ALAB7AFwAIgBhAFwAIgA7AFwAIgBiAFwAIgA7AFwAIgBjAFwAIgB9ACwAewAxADsAMgB9ACkAXABuAFwAbgBSAGUAcwB1AGwAdAA6AFwAbgAgACAAIAAgAHsAXAAiAGQAbwBnAFwAIgAsAFwAIgBhAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBkAG8AZwBcACIALABcACIAYQBcACIALAAyADsAXABuACAAIAAgACAAIABcACIAZABvAGcAXAAiACwAXAAiAGIAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGQAbwBnAFwAIgAsAFwAIgBiAFwAIgAsADIAOwBcAG4AIAAgACAAIAAgAFwAIgBkAG8AZwBcACIALABcACIAYwBcACIALAAxADsAXABuACAAIAAgACAAIABcACIAZABvAGcAXAAiACwAXAAiAGMAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGMAYQB0AFwAIgAsAFwAIgBhAFwAIgAsADEAOwBcAG4AIAAgACAAIAAgAFwAIgBjAGEAdABcACIALABcACIAYQBcACIALAAyADsAXABuACAAIAAgACAAIABcACIAYwBhAHQAXAAiACwAXAAiAGIAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGMAYQB0AFwAIgAsAFwAIgBiAFwAIgAsADIAOwBcAG4AIAAgACAAIAAgAFwAIgBjAGEAdABcACIALABcACIAYwBcACIALAAxADsAXABuACAAIAAgACAAIABcACIAYwBhAHQAXAAiACwAXAAiAGMAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGEAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGEAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGIAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGIAXAAiACwAMgA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGMAXAAiACwAMQA7AFwAbgAgACAAIAAgACAAXAAiAGIAaQByAGQAXAAiACwAXAAiAGMAXAAiACwAMgB9AFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHMAZQB0AF8AMQAgACAAIAAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAKAAxAEQAIABvAHIAIAAyAEQAKQAgAGEAcgBlACAAYQBjAGMAZQBwAHQAZQBkAC4AIABBAGwAbAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAuAFwAbgAgACAAIAAgAHMAZQB0AF8AMgBcAG4AIAAgACAAIABzAGUAdABfADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAcgBpAHAAbABlAHcAaQBzAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHMAZQB0AF8AMQAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMgAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMwAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABhAGwAbAAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAHMAZQB0AF8AMQAsACAAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMQApACwAXABuACAAIAAgACAAcwBlAHQAXwAyACwAIAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAyACkALABcAG4AIAAgACAAIABzAGUAdABfADMALAAgACAAIABUAE8AQwBPAEwAKABzAGUAdABfADMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAdAAgAGkAdABlAG0AIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABrAIEgLAAgACAAIAAgACAAIABSAE8AVwBTACgAcwBlAHQAXwAxACkALABcAG4AIAAgACAAIABrAIIgLAAgACAAIAAgACAAIABSAE8AVwBTACgAcwBlAHQAXwAyACkALABcAG4AIAAgACAAIABrAIMgLAAgACAAIAAgACAAIABSAE8AVwBTACgAcwBlAHQAXwAzACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIABpAGYAIABzAGUAdABfADIAIABpAHMAIABzAGMAYQBsAGEAcgBcAG4AIAAgACAAIABzAHcAYQBwAD8ALAAgACAAIABrAIIgIAA9ACAAMQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAcABhAGkAcgBzACAAZgByAG8AbQAgAGYAaQByAHMAdAAgAHQAdwBvACAAcwBlAHQAcwBcAG4AIAAgACAAIABwAGEAaQByAHMALAAgACAAIABJAEYAKABzAHcAYQBwAD8ALAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAcwBlAHQAXwAyACwAcwBlAHQAXwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAcwBlAHQAXwAxACwAcwBlAHQAXwAyACkAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAHMAZQB0AHMAIABlAHgAcABhAG4AZABlAGQAXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAASQBGACgAcwB3AGEAcAA/ACwAVABBAEsARQAoAHAAYQBpAHIAcwAsACwALQAxACkALABUAEEASwBFACgAcABhAGkAcgBzACwALAAxACkAKQAsAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIAAgAEkARgAoAHMAdwBhAHAAPwAsAFQAQQBLAEUAKABwAGEAaQByAHMALAAsADEAKQAsAFQAQQBLAEUAKABwAGEAaQByAHMALAAsAC0AMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAGkAcgBzACAAZgByAG8AbQAgAHMAZQB0AF8AMQAgAGUAeABwAGEAbgBkAGUAZAAgACsAIABzAGUAdABfADMAXABuACAAIAAgACAAdABoAHIAaQBjAGUALAAgACAASQBGACgAawCDICAAPAA+ACAAMQAsACAAUABhAGkAcgB3AGkAcwBlALsDKABhACwAcwBlAHQAXwAzACkALABQAGEAaQByAHcAaQBzAGUAuwMoAHMAZQB0AF8AMwAsAGEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBpAHIAcwAgAGYAcgBvAG0AIABzAGUAdABfADIAIABlAHgAcABhAG4AZABlAGQAIAArACAAcwBlAHQAXwAzAFwAbgAgACAAIAAgAHQAaAByAGkAYwBlAF8ALAAgAEkARgAoAGsAgyAgADwAPgAgADEALAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAYgAsAHMAZQB0AF8AMwApACwAUABhAGkAcgB3AGkAcwBlALsDKABzAGUAdABfADMALABiACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIABjAG8AbABzACwAIAAgACAAIABJAEYAKABrAIMgIAA9ACAAMQAsADEALAAtADEAKQAsAFwAbgAgACAAIAAgAGEAXwAsACAAIAAgACAAIAAgAEQAUgBPAFAAKAB0AGgAcgBpAGMAZQAsACwAYwBvAGwAcwApACwAXABuACAAIAAgACAAYgBfACwAIAAgACAAIAAgACAARABSAE8AUAAoAHQAaAByAGkAYwBlAF8ALAAsAGMAbwBsAHMAKQAsAFwAbgAgACAAIAAgAGMAXwAsACAAIAAgACAAIAAgAFQAQQBLAEUAKAB0AGgAcgBpAGMAZQAsACwAYwBvAGwAcwApACwAXABuACAAIAAgACAAXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgAG8AcgBkAGUAcgAgAHQAbwAgAG0AYQB0AGMAaAAgAGkAbgBwAHUAdAAgAG8AcgBkAGUAcgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIABIAFMAVABBAEMASwAoAGEAXwAsAGIAXwAsAGMAXwApACwAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA2AGIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABRAHUAYQBkAHcAaQBzAGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDLAAgAFIAZQBzAGkAegBlALsDLAAgAFQAcgBpAHAAbABlAHcAaQBzAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABvAGYAIAA0ACAAcwBlAHQAcwAuACAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIABhAG4AZABcAG4AIAAgACAAIAB0AGgAZQAgAHIAZQBzAHUAbAB0AGkAbgBnACAAcQB1AGEAZAByAHUAcABsAGUAcwAgAHAAcgBlAHMAZQByAHYAZQAgAHQAaABlACAAbwByAGQAZQByACAAbwBmACAAdABoAGUAIABzAHUAcABwAGwAaQBlAGQAIABzAGUAdABzAC4AXABuAFwAbgAgACAAIAAgAFEAdQBhAGQAdwBpAHMAZQC7AyAAZQB4AHQAZQBuAGQAcwAgAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMgAHQAbwAgAGEAIAA0ABEgYQB4AGkAcwAgAGYAYQBiAHIAaQBjADoAXABuACAAIAAgACAAIAAgACAAIAAiICAAcwBlAHQAXwAxACAA1wAgAHMAZQB0AF8AMgAgANcAIABzAGUAdABfADMAIADXACAAcwBlAHQAXwA0AFwAbgAgACAAIAAgAFQAaABlACAAbwB1AHQAcAB1AHQAIABpAHMAIABhACAAcwBwAGkAbABsACAAcgBhAG4AZwBlACAAdwBoAGUAcgBlACAAZQBhAGMAaAAgAHIAbwB3ACAAcgBlAHAAcgBlAHMAZQBuAHQAcwAgAG8AbgBlACAAbwByAGQAZQByAGUAZAAgAHEAdQBhAGQAcgB1AHAAbABlAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAcwBlAHQAXwAxACAAIAAgACAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAYQByAHIAYQB5AHMAIAAoADEARAAgAG8AcgAgADIARAApACAAYQByAGUAIABhAGMAYwBlAHAAdABlAGQALgAgAEEAbABsACAAaQBuAHAAdQB0AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkAC4AXABuACAAIAAgACAAcwBlAHQAXwAyAFwAbgAgACAAIAAgAHMAZQB0AF8AMwBcAG4AIAAgACAAIABzAGUAdABfADQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFEAdQBhAGQAdwBpAHMAZQC7Az0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcwBlAHQAXwAxACwAXABuACAAIAAgACAAcwBlAHQAXwAyACwAXABuACAAIAAgACAAcwBlAHQAXwAzACwAXABuACAAIAAgACAAcwBlAHQAXwA0ACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGEAbABsACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAAcwBlAHQAXwAxACwAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMQApACwAXABuACAAIAAgACAAcwBlAHQAXwAyACwAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMgApACwAXABuACAAIAAgACAAcwBlAHQAXwAzACwAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMwApACwAXABuACAAIAAgACAAcwBlAHQAXwA0ACwAIAAgAFQATwBDAE8ATAAoAHMAZQB0AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBzAGkAbwBuACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIABSAE8AVwBTACgAcwBlAHQAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABzAGUAdAAgADQAIABpAGYAIABzAGMAYQBsAGEAcgAgAHQAbwAgAGEAdgBvAGkAZAAgAFQATwBDAE8ATAAgAGgAYQBuAGQAbwBmAGYAIAB0AG8AIABSAGUAcwBpAHoAZQC7A1wAbgAgACAAIAAgAGQALAAgACAAIAAgACAAIABJAEYAKABrACAAPAA+ACAAMQAsAHMAZQB0AF8ANAAsAEkATgBEAEUAWAAoAHMAZQB0AF8ANAAsADEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAcgBpAHAAbABlAHMAXABuACAAIAAgACAAdABoAHIAaQBjAGUALAAgAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMoAHMAZQB0AF8AMQAsAHMAZQB0AF8AMgAsAHMAZQB0AF8AMwApACwAXABuACAAIAAgACAAXABuACAAIAAgACAALwAvACAARQB4AHAAYQBuAGQAIAB0AHIAaQBwAGwAZQAgAHIAbwB3AHMAIABiAHkAIAB0AG8AdABhAGwAIABpAHQAZQBtAHMAIABpAG4AIABzAGUAdAAgADQAXABuACAAIAAgACAAdABoAHIAaQBjAGUAXwAsAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMoAHQAaAByAGkAYwBlACwAawApACwAXABuACAAIAAgACAAawCCICwAIAAgACAAIAAgAFIATwBXAFMAKAB0AGgAcgBpAGMAZQBfACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHAAYQBuAGQAIABzAGUAdAAgADQAIAB0AG8AIABtAGEAdABjAGgAIABsAGUAbgBnAHQAaAAgAG8AZgAgAHQAcgBpAHAAbABlAFwAbgAgACAAIAAgAGYAbwB1AHIALAAgACAAIABSAGUAcwBpAHoAZQC7AygAZAAsAGsAgiAgAC8AIABrACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAYwBrACAAYQBuAGQAIABkAGkAcwBwAGwAYQB5AFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIABIAFMAVABBAEMASwAoAHQAaAByAGkAYwBlAF8ALABmAG8AdQByACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA3AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARwByAG8AdQBwAGIAeQBCAGkAbgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAZwBnAHIAZQBnAGEAdABlAHMAIABvAG4AZQAgAG8AcgAgAG0AbwByAGUAIAB2AGEAbAB1AGUAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABmAGkAeABlAGQAESB3AGkAZAB0AGgAIABiAGkAbgBzACAAZABlAHIAaQB2AGUAZAAgAGYAcgBvAG0AIABhAFwAbgAgACAAIAAgAG4AdQBtAGUAcgBpAGMAIABmAGkAZQBsAGQALgAgAFMAdQBwAHAAbwByAHQAcwAgAG8AcAB0AGkAbwBuAGEAbAAgAGgAZQBhAGQAZQByAHMAIABhAG4AZAAgAGMAaABhAHIAdAARIHIAZQBhAGQAeQAgAG8AdQB0AHAAdQB0AC4AIABCAGkAbgBzACAAYQByAGUAXABuACAAIAAgACAAZABlAGYAaQBuAGUAZAAgAGIAeQAgAGEAIABuAHUAbQBlAHIAaQBjACAAYQByAHIAYQB5ACAAYQBuAGQAIABhACAAcABvAHMAaQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgAgAGIAaQBuAF8AdwBpAGQAdABoAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAATgB1AG0AZQByAGkAYwAgADEARAAgAGEAcgByAGEAeQAgAHUAcwBlAGQAIAB0AG8AIABkAGUAZgBpAG4AZQAgAGIAaQBuACAAYgBvAHUAbgBkAGEAcgBpAGUAcwAuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAoAHMAKQAgAHQAbwAgAGIAZQAgAGEAZwBnAHIAZQBnAGEAdABlAGQAIAAoADEARAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAYgBpAG4AXwB3AGkAZAB0AGgAIAAgACAAIAAgACAAIAAtACAAUABvAHMAaQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgAgAHMAcABlAGMAaQBmAHkAaQBuAGcAIABiAGkAbgAgAHcAaQBkAHQAaAAgACgAZSIgADEAKQAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgACAAIAAgACAALQAgAEUAVABBABEgYwBvAG0AcABhAHQAaQBiAGwAZQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AcgAgAHMAaQBuAGcAbABlABEgcABhAHIAYQBtAGUAdABlAHIAIABMAEEATQBCAEQAQQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBdACAAIAAtACAAVABSAFUARQAgAGkAZgAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQBzACAAaQBuAGMAbAB1AGQAZQAgAGgAZQBhAGQAZQByAHMAIAB0AG8AIABiAGUAIABjAGEAcgByAGkAZQBkACAAZgBvAHIAdwBhAHIAZAAuAFwAbgAgACAAIAAgAFsAYwBoAGEAcgB0AF8AcAByAGUAcABdACAAIAAgACAALQAgAFQAUgBVAEUAIAB0AG8AIAByAGUAdAB1AHIAbgAgAGEAIABjAG8AbgBjAGkAcwBlACAAYwBoAGEAcgB0ABEgcgBlAGEAZAB5ACAAbABhAHkAbwB1AHQALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABiAGkAbgBfAHcAaQBkAHQAaAAgAD0AIAAxACAAkiEgAGIAZQBoAGEAdgBlAHMAIABsAGkAawBlACAARwBSAE8AVQBQAEIAWQAgACgAbgBvACAAYgBpAG4AbgBpAG4AZwApAC4AXABuACAAIAAgACAAIiAgAGIAaQBuAF8AdwBpAGQAdABoACAAZSIgACgAbQBhAHgAIAASIiAAbQBpAG4AKQAgAJIhIABjAG8AbABsAGEAcABzAGUAcwAgAHQAbwAgAGEAIABzAGkAbgBnAGwAZQAgAGIAaQBuAC4AXABuACAAIAAgACAAIiAgAEMAaABhAHIAdAAgAG0AbwBkAGUAIAByAGUAdAB1AHIAbgBzACAAewBcACIAQgBpAG4AXAAiACwAXAAiAEEAZwBnAHIAZQBnAGEAdABlAFwAIgB9ACAAZgBvAHIAIABlAGEAcwB5ACAAcABsAG8AdAB0AGkAbgBnAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEcAcgBvAHUAcABiAHkAQgBpAG4AuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAdgBhAGwAdQBlAHMALABcAG4AIAAgACAAIABiAGkAbgBfAHcAaQBkAHQAaAAsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAFsAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAXQAsAFwAbgAgACAAIAAgAFsAYwBoAGEAcgB0AF8AcAByAGUAcABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGkAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAdgBhAGwAdQBlAHMAKQAsAFwAbgAgACAAIAAgAGoAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAdgBhAGwAdQBlAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGUAYQBkAGUAcgAgAGYAbABhAGcAXABuACAAIAAgACAASABlAGEAZABlAHIAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaQAgAD4AIAAxACwAIABqACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIABpACAAPAA+ACAAaQBfACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABCAGkAbgA/ACwAIAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAYgBpAG4AXwB3AGkAZAB0AGgAKQAsACAAYgBpAG4AXwB3AGkAZAB0AGgAIAA8ACAAMQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4APwAsACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuACAAIAAgACAATgBvAG4ATgB1AG0AZQByAGkAYwA/ACwAIAAgACAAIAAgACAAIAAgAE4ATwBUACgAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKABJAEYAKABIAGUAYQBkAGUAcgBzAD8ALAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgADEAKQAsACAAYQByAHIAYQB5ACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMAMgBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjADEARAAtAEEAUgBSAEEAWQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAG4ATgB1AG0AZQByAGkAYwA/ACwAIABcACIAIwBOAFUATQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEIAaQBuAD8ALAAgAFwAIgAjAEIASQBOAC0AVwBJAEQAVABIACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABGAG4APwAsACAAXAAiACMASQBOAFYAQQBMAEkARAAtAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGwAYQBnAHMAXABuACAAIAAgACAATgBvAEMAaABhAHIAdAA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYwBoAGEAcgB0AF8AcAByAGUAcAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAdAByAGkAcAAgAGgAZQBhAGQAZQByAHMAIABpAGYAIABwAHIAZQBzAGUAbgB0AFwAbgAgACAAIAAgAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABIAGUAYQBkAGUAcgBzAD8ALAAgAEQAUgBPAFAAKABhAHIAcgBhAHkALAAgADEAKQAsACAAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB2AGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASABlAGEAZABlAHIAcwA/ACwAIABEAFIATwBQACgAdgBhAGwAdQBlAHMALAAgADEAKQAsACAAdgBhAGwAdQBlAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGUAYQBkAGUAcgAgAGMAbwBuAHMAdAByAHUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAHIAbwB3AF8AaABlAGEAZABlAHIALAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAFwAIgBCAGkAbgAgAFMAdABhAHIAdAAgAFwAIgAgACYAIABJAEYAKABIAGUAYQBkAGUAcgBzAD8ALAAgAFQAQQBLAEUAKABhAHIAcgBhAHkALAAgADEAKQAsACAAXAAiAFwAIgApACAAJgAgAFwAIgAgAFYAYQBsAHUAZQBcACIALABcACIAQgBpAG4AIABFAG4AZABcACIAKQAsAFwAbgAgACAAIAAgAHYAYQBsAF8AaABlAGEAZABlAHIALAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAEkARgAoAEgAZQBhAGQAZQByAHMAPwAsACAAVABBAEsARQAoAHYAYQBsAHUAZQBzACwAIAAxACkALAAgAFwAIgBUAG8AdABhAGwAXAAiACkALAAsAGoAXwAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgAGgAZQBhAGQAZQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHIAbwB3AF8AaABlAGEAZABlAHIALAAgAHYAYQBsAF8AaABlAGEAZABlAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGkAbgAgAGIAbwB1AG4AZABhAHIAaQBlAHMAXABuACAAIAAgACAAbQBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAYQByAHIAKQAsAFwAbgAgACAAIAAgAHMAdABhAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEwATwBPAFIAKABtAGkAbgAsACAAYgBpAG4AXwB3AGkAZAB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIABtAGEAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABhAHIAcgApACwAXABuACAAIAAgACAAZQBuAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABtAGEAeAAsACAAYgBpAG4AXwB3AGkAZAB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIABrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABlAG4AZAAgAC0AIABzAHQAYQByAHQAKQAgAC8AIABiAGkAbgBfAHcAaQBkAHQAaAAsAFwAbgBcAG4AIAAgACAAIABiAGkAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAawAgACsAIAAxACwAIAAsACAAcwB0AGEAcgB0ACwAIABiAGkAbgBfAHcAaQBkAHQAaAApACwAXABuACAAIAAgACAAYgBpAG4AXwBzAHQAYQByAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABiAGkAbgAsACAALQAxACkALABcAG4AIAAgACAAIABiAGkAbgBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGIAaQBuACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBpAG4AIABhAHMAcwBpAGcAbgBtAGUAbgB0AFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAGEAcgByACwAIABiAGkAbgBfAHMAdABhAHIAdAAsACAALQAxACkALABcAG4AIAAgACAAIAByAG8AdwBfAHMAdABhAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYgBpAG4AXwBzAHQAYQByAHQALAAgAGkAZAB4ACkALABcAG4AIAAgACAAIAByAG8AdwBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYgBpAG4AXwBlAG4AZAAsACAAaQBkAHgAKQAsAFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHIAbwB3AF8AcwB0AGEAcgB0ACwAIAByAG8AdwBfAGUAbgBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBnAGcAcgBlAGcAYQB0AGkAbwBuAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABHAFIATwBVAFAAQgBZACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAAdgBhAGwALAAgAGYAdQBuAGMAdABpAG8AbgAsACAASABlAGEAZABlAHIAcwA/ACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBoAGEAcgB0ACAAcAByAGUAcABcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAGEAZwBnACwAIAAxACkAIAAmACAAXAAiACAALQAgADwAXAAiACAAJgAgAEMASABPAE8AUwBFAEMATwBMAFMAKABhAGcAZwAsACAAMgApACwAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABhAGcAZwAsACAALAAgADIAKQAsAFwAbgAgACAAIAAgAGMAaABhAHIAdABfAGwAYQBiAGUAbABzACwAIAAgACAAIAAgACAAIAB7AFwAIgBCAGkAbgBcACIALAAgAFwAIgBBAGcAZwByAGUAZwBhAHQAZQBcACIAfQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAG0AbwBkAGUAcwBcAG4AIAAgACAAIABkAGEAdABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABoAGUAYQBkAGUAcgAsACAAYQBnAGcAKQAsAFwAbgAgACAAIAAgAGMAaABhAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGMAaABhAHIAdABfAGwAYQBiAGUAbABzACwAIABIAFMAVABBAEMASwAoAGEALAAgAGIAKQApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AQwBoAGEAcgB0AD8ALAAgAGQAYQB0AGEALAAgAGMAaABhAHIAdAApACwAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgB5AFwAbgApACkAKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAARwByAG8AdQBwAGIAeQBEAGEAdABlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAVgBhAGwAaQBkAGEAdABlAEcARAC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQBnAGcAcgBlAGcAYQB0AGUAcwAgAHYAYQBsAHUAZQBzACAAYgB5ACAAcgBvAHcAIABmAGkAZQBsAGQAcwAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABkAGEAdABlAHMALAAgAHUAcwBpAG4AZwAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZABcAG4AIAAgACAAIABkAGEAdABlAC8AdABpAG0AZQAgAGkAbgB0AGUAcgB2AGEAbAAgACgAbQBpAG4AdQB0AGUALAAgAGgAbwB1AHIALAAgAGQAYQB5ACwAIAB3AGUAZQBrACwAIABmAG8AcgB0AG4AaQBnAGgAdAAsACAAbQBvAG4AdABoACwAIABxAHUAYQByAHQAZQByACwAXABuACAAIAAgACAAeQBlAGEAcgApAC4AIABTAHUAcABwAG8AcgB0AHMAIABvAHAAdABpAG8AbgBhAGwAIABoAGUAYQBkAGUAcgBzACwAIABjAHUAcwB0AG8AbQAgAGYAbwByAG0AYQB0AHQAaQBuAGcALAAgAGEAbgBkACAAcgBvAHcAIABmAGkAbAB0AGUAcgBpAG4AZwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAgACgAMQBEACAAbwByACAAMgBEACkAIAB3AGkAdABoACAAZABhAHQAZQBzACAAaQBuACAAdABoAGUAIABsAGUAZgB0AG0AbwBzAHQAIABjAG8AbAB1AG0AbgAuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAgACgAMQBEACAAbwByACAAMgBEACkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAuAFwAbgAgACAAIAAgAGkAbgB0AGUAcgB2AGEAbAAgACAAIAAgACAAIAAgACAALQAgAEQAYQB0AGUALwB0AGkAbQBlACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAaQBuAHQAZQByAHYAYQBsACAAKABuAHUAbQBiAGUAcgAgAG8AcgAgAHQAZQB4AHQAKQAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgACAAIAAgACAALQAgAEUAVABBABEgYwBvAG0AcABhAHQAaQBiAGwAZQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AcgAgAHMAaQBuAGcAbABlABEgcABhAHIAYQBtAGUAdABlAHIAIABMAEEATQBCAEQAQQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBmAG8AcgBtAGEAdABdACAAIAAgACAAIAAgACAAIAAtACAAQwB1AHMAdABvAG0AIABkAGEAdABlAC8AdABpAG0AZQAgAGYAbwByAG0AYQB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAgACAAIABbAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAHMAXQAgAC0AIABUAFIAVQBFACAAaQBmACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AHMAIABpAG4AYwBsAHUAZABlACAAaABlAGEAZABlAHIAcwAuAFwAbgAgACAAIAAgAFsAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkAXQAgACAALQAgAEIAbwBvAGwAZQBhAG4AIABhAHIAcgBhAHkAIAB0AG8AIABmAGkAbAB0AGUAcgAgAHIAbwB3AHMAIABiAGUAZgBvAHIAZQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcgBvAHcAXwBmAGkAZQBsAGQAcwAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAaQBuAHQAZQByAHYAYQBsACwAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAXABuACAAIAAgACAAWwBmAG8AcgBtAGEAdABdACwAXABuACAAIAAgACAAWwBmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBzAF0ALABcAG4AIAAgACAAIABbAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5AF0ALABcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBHAEQAuwMoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgAHYAYQBsAHUAZQBzACwAIABpAG4AdABlAHIAdgBhAGwALAAgAGYAdQBuAGMAdABpAG8AbgAsACAAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAcwAsACAAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASQBuAHQAZQByAHYAYQBsACAAbgBvAHIAbQBhAGwAaQB6AGEAdABpAG8AbgBcAG4AIAAgACAAIABOAHUAbQBJAG4AdABlAHIAdgBhAGwAPwAsACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMAVABFAFgAVAAoAGkAbgB0AGUAcgB2AGEAbAApACkALABcAG4AXABuACAAIAAgACAAYwBvAG4AcwB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiAG0AaQBuAHUAdABlAFwAIgA7AFwAIgBoAG8AdQByAFwAIgA7AFwAIgBkAGEAeQBcACIAOwBcACIAdwBlAGUAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBvAHIAdABuAGkAZwBoAHQAXAAiADsAXAAiAG0AbwBuAHQAaABcACIAOwBcACIAcQB1AGEAcgB0AGUAcgBcACIAOwBcACIAeQBlAGEAcgBcACIAfQAsAFwAbgBcAG4AIAAgACAAIABpAG4AdABlAHIAdgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgB1AG0ASQBuAHQAZQByAHYAYQBsAD8ALABpAG4AdABlAHIAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAEwATwBXAEUAUgAoAGkAbgB0AGUAcgB2AGEAbAApACAAJgAgAFwAIgAqAFwAIgAsACAAYwBvAG4AcwB0ACwAIAAyACkAKQAsAFwAbgBcAG4AIAAgACAAIABJAG4AYwBsAHUAZABlAHMAXwBlAG4AZAA/ACwAIAAgACAAIAAgACAAKABpAG4AdABlAHIAdgBhAGwAIAA9ACAANAApACAAKwAgACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADUAKQAsAFwAbgBcAG4AIAAgACAAIAB1AG4AaQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKABpAG4AdABlAHIAdgBhAGwALAAgADEANAA0ADAALAAgADIANAAsACAAMQAsACAAMQAsACAAMQAsACAAMQAsACAAMQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAXABuACAAIAAgACAATgBvAEYAbwByAG0AYQB0AD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAZgBvAHIAbQBhAHQAKQAsAFwAbgAgACAAIAAgAEgAZQBhAGQAZQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgBpAGUAbABkAF8AaABlAGEAZABlAHIAcwApACkALABcAG4AIAAgACAAIABGAGkAbAB0AGUAcgA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGEAdABlACAAdgBlAGMAdABvAHIAIABmAHIAbwBtACAAcgBvAHcAXwBmAGkAZQBsAGQAcwBcAG4AIAAgACAAIABkAGEAdABlAF8AYwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASABlAGEAZABlAHIAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABUAEEASwBFACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAALAAgADEAKQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACwAIAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGEAdABlAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBuAHQAZQByAHYAYQBsACAAPAAgADMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABkAGEAdABlAF8AYwBvAGwAIAAqACAAdQBuAGkAdAAsACAAMAApACAALwAgAHUAbgBpAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAE4AVAAoAGQAYQB0AGUAXwBjAG8AbAApACkALABcAG4AXABuACAAIAAgACAAdgBhAGwAdQBlAHMAXwBoAGUAYQBkAGUAcgAsACAAIAAgACAAIAAgAFQAQQBLAEUAKAB2AGEAbAB1AGUAcwAsACAAMQApACwAXABuACAAIAAgACAAdgBhAGwAdQBlAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEgAZQBhAGQAZQByAD8ALAAgAEQAUgBPAFAAKAB2AGEAbAB1AGUAcwAsACAAMQApACwAIAB2AGEAbAB1AGUAcwApACwAXABuACAAIAAgACAAcgBvAHcAXwBkAGUAdABhAGkAbABzACwAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABEAFIATwBQACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAALAAgADEAKQAsACAASABlAGEAZABlAHIAPwApACwAXABuACAAIAAgACAAZgBpAGwAdABlAHIAXwB1AHMAZQBkACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEgAZQBhAGQAZQByAD8AIAAqACAARgBpAGwAdABlAHIAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABXAGkAZAB0AGgAcwBcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAHIAbwB3AF8AZgBpAGUAbABkAHMAKQAsAFwAbgAgACAAIAAgAHcAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAdgBhAGwAdQBlAHMAKQAsAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB3ACAAKwAgAHcAXwAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGEAdABlACAAYgBvAHUAbgBkAHMAXABuACAAIAAgACAAbQBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBUACgATQBJAE4AKABkAGEAdABlAHMAKQApACwAXABuACAAIAAgACAAbQBhAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBUACgATQBBAFgAKABkAGEAdABlAHMAKQApACwAXABuACAAIAAgACAAbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ATwBOAFQASAAoAG0AaQBuACkALABcAG4AIAAgACAAIABkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABBAFkAKABtAGkAbgApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFkARQBBAFIAKABtAGkAbgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAaQBtAGUAIABvAGYAIABmAGkAcgBzAHQAIABkAGEAdABlAFwAbgAgACAAIAAgAGYAaQByAHMAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAGQAYQB0AGUAcwApACwAXABuACAAIAAgACAAbABhAHMAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAZABhAHQAZQBzACkALABcAG4AIAAgACAAIABoAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABPAFUAUgAoAGYAaQByAHMAdAApACwAXABuACAAIAAgACAAbQBtACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOAFUAVABFACgAZgBpAHIAcwB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBhAG4AZwBlAHMAXABuACAAIAAgACAAcwBlAGMAbwBuAGQAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAbABhAHMAdAAgAC0AIABmAGkAcgBzAHQAKQAgACoAIAA4ADYANAAwADAALABcAG4AIAAgACAAIABtAGkAbgB1AHQAZQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAHMAZQBjAG8AbgBkAHMAIAAvACAANgAwACwAIAAxACkALABcAG4AIAAgACAAIABoAG8AdQByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBpAG4AdQB0AGUAcwAgAC8AIAA2ADAALABcAG4AIAAgACAAIABkAGEAeQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAIAAtACAAbQBpAG4ALABcAG4AIAAgACAAIAB3AGUAZQBrAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAGQAYQB5AHMAIAAvACAANwAsACAAMQApACwAXABuACAAIAAgACAAZgBvAHIAdABuAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABkAGEAeQBzACAALwAgADEANAAsACAAMQApACwAXABuACAAIAAgACAAbQBvAG4AdABoAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAQQBUAEUARABJAEYAKABtAGkAbgAsACAAbQBhAHgALAAgAFwAIgBtAFwAIgApACwAXABuACAAIAAgACAAcQB1AGEAcgB0AGUAcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEMARQBJAEwASQBOAEcAKABtAG8AbgB0AGgAcwAgAC8AIAAzACwAIAAxACkALABcAG4AIAAgACAAIAB5AGUAYQByAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAG0AbwBuAHQAaABzACAALwAgADEAMgAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBzAHAAbABhAHkAIABmAG8AcgBtAGEAdABzAFwAbgAgACAAIAAgAGgAXwBtAG0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABkAGEAeQBzACAAPgAgADEALAAgAFwAIgBtAC8AZAAvAHkAeQB5ACAAaAA6AG0AbQAgAEEATQAvAFAATQBcACIALAAgAFwAIgBoADoAbQBtACAAQQBNAC8AUABNAFwAIgApACwAXABuACAAIAAgACAAbQBtAG0AbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAG0AbQBtACAAeQB5AHkAXAAiACwAXABuACAAIAAgACAAZABhAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAC8AZAAvAHkAeQB5AFwAIgAsAFwAbgAgACAAIAAgAHkAeQB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAeQB5AHkAXAAiACwAXABuAFwAbgAgACAAIAAgAGYAbQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8ARgBvAHIAbQBhAHQAPwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAaQBuAHQAZQByAHYAYQBsACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEALAAgAGgAXwBtAG0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAsACAAaABfAG0AbQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAzACwAIABkAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACwAIABkAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA1ACwAIABkAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA2ACwAIABtAG0AbQBtACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADcALAAgAG0AbQBtAG0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAOAAsACAAeQB5AHkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBtAG0AbQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBvAHIAbQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGEAdABlAC8AdABpAG0AZQAgAGEAcgByAGEAeQBzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIABtAGkAbgBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABAAG0AaQBuAHUAdABlAHMAIAArACAAMQAsACAALAAgAGYAaQByAHMAdAAsACAAMQAgAC8AIAAxADQANAAwACkAKQAsAFwAbgAgACAAIAAgAGgAcgBzAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAEAAaABvAHUAcgBzACAAKwAgADEALAAgACwAIABmAGkAcgBzAHQALAAgADEAIAAvACAAMgA0ACkAKQAsAFwAbgAgACAAIAAgAGQAYQB5AHMAXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoAGQAYQB5AHMAIAArACAAMQAsACAALAAgAG0AaQBuACwAIAAxACkAKQAsAFwAbgAgACAAIAAgAHcAZQBlAGsAcwBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEQAQQBUAEUAKAB5ACwAIABtACwAIABTAEUAUQBVAEUATgBDAEUAKAB3AGUAZQBrAHMAIAArACAAMQAsACAALAAgAGQALAAgADcAKQApACkALABcAG4AIAAgACAAIABmAG8AcgB0AF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABEAEEAVABFACgAeQAsACAAbQAsACAAUwBFAFEAVQBFAE4AQwBFACgAZgBvAHIAdABuAGkAZwBoAHQAIAArACAAMQAsACAALAAgAGQALAAgADEANAApACkAKQAsAFwAbgAgACAAIAAgAG0AbwBuAHQAaABfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEQAQQBUAEUAKAB5ACwAIABtACAAKwAgAFMARQBRAFUARQBOAEMARQAoAG0AbwBuAHQAaABzACAAKwAgADEALAAgACwAIAAwACkALAAgAGQAKQApACwAXABuACAAIAAgACAAcQB0AHIAcwBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARABBAFQARQAoAHkALAAgAG0AIAArACAAUwBFAFEAVQBFAE4AQwBFACgAcQB1AGEAcgB0AGUAcgBzACAAKwAgADEALAAgACwAIAAwACwAIAAzACkALAAgAGQAKQApACwAXABuACAAIAAgACAAeQByAHMAXwBhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARABBAFQARQAoAHkAIAArACAAUwBFAFEAVQBFAE4AQwBFACgAQAB5AGUAYQByAHMAIAArACAAMQAsACAALAAgADAAKQAsACAAbQAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAHQAZQByAHYAYQBsACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAYgBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgAaQBuAHQAZQByAHYAYQBsACAAPAAgADMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAEMASABPAE8AUwBFACgAaQBuAHQAZQByAHYAYQBsACwAIABtAGkAbgBfAGEAcgByACgAKQAsACAAaAByAHMAXwBhAHIAcgAoACkAKQAgACoAIAB1AG4AaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADAAKQAgAC8AIAB1AG4AaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAG4AdABlAHIAdgBhAGwAIAAtACAAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGEAeQBzAF8AYQByAHIAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAZQBlAGsAcwBfAGEAcgByACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAG8AcgB0AF8AYQByAHIAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AbwBuAHQAaABfAGEAcgByACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHQAcgBzAF8AYQByAHIAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHkAcgBzAF8AYQByAHIAKAApACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAYQBiAGUAbAAgAGEAcwBzAGkAZwBuAG0AZQBuAHQAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgASQBGACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADgALABYAE0AQQBUAEMASAAoAFkARQBBAFIAKABkAGEAdABlAHMAKQAsACAAWQBFAEEAUgAoAGIAaQBuACgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATQBBAFQAQwBIACgAZABhAHQAZQBzACwAIABiAGkAbgAoACkALAAgAC0AMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGEAdABlAF8AZgBpAGUAbABkACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAE4ARABFAFgAKABiAGkAbgAoACkALAAgAGkAKAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAG8AdwAgAGwAYQBiAGUAbABzAFwAbgAgACAAIAAgAHIAbwB3AF8AbABhAGIAZQBsAHMALAAgACAAIAAgACAAIAAgACAAIABJAEYAKAB3ACAAPQAgADEALABkAGEAdABlAF8AZgBpAGUAbABkACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAZABhAHQAZQBfAGYAaQBlAGwAZAAoACkALAAgAHIAbwB3AF8AZABlAHQAYQBpAGwAcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAASABlAGEAZABlAHIAcwBcAG4AIAAgACAAIAB0AG8AdABhAGwAXwBsAGEAYgBlAGwALAAgACAAIAAgACAAIAAgACAAUwBXAEkAVABDAEgAKABpAG4AdABlAHIAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxACwAIABcACIAVABvAHQAYQBsAHMAIABiAHkAIABtAGkAbgB1AHQAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAyACwAIABcACIAVABvAHQAYQBsAHMAIABiAHkAIABoAG8AdQByAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADMALAAgAFwAIgBUAG8AdABhAGwAcwAgAGIAeQAgAEQAYQB5AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADQALAAgAFwAIgBXAGUAZQBrAGwAeQAgAFQAbwB0AGEAbABzAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADUALAAgAFwAIgBCAGkAdwBlAGUAawBsAHkAIABUAG8AdABhAGwAcwBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA2ACwAIABcACIATQBvAG4AdABoAGwAeQAgAFQAbwB0AGEAbABzAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADcALAAgAFwAIgBUAG8AdABhAGwAcwAgAGIAeQAgAFEAdQBhAHIAdABlAHIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAOAAsACAAXAAiAFkAZQBhAHIAbAB5ACAAVABvAHQAYQBsAHMAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAHQAbwB0AGEAbABfAGgAZQBhAGQAZQByACwAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAEkARgAoAE8AUgAoAGkAbgB0AGUAcgB2AGEAbAAgAD0AIAA0ACwAIABpAG4AdABlAHIAdgBhAGwAIAA9ACAANQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAHQAbwB0AGEAbABfAGwAYQBiAGUAbAAsACAAXAAiAEUAbgBkAGkAbgBnACAARABhAHQAZQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABvAHQAYQBsAF8AbABhAGIAZQBsACkALAAsAHcAIAArACAASQBuAGMAbAB1AGQAZQBzAF8AZQBuAGQAPwAsAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIABhAGcAZwBfAGgAZQBhAGQAZQByACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASABlAGEAZABlAHIAPwAsAHYAYQBsAHUAZQBzAF8AaABlAGEAZABlAHIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAFwAIgBcACIALAAgACwAIAB3AF8ALAAgAFwAIgBcACIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAZwBnAHIAZQBnAGEAdABpAG8AbgBcAG4AIAAgACAAIABuAG8AXwBmAGkAbAB0AGUAcgAsACAAIAAgACAAIAAgACAAIAAgACAARwBSAE8AVQBQAEIAWQAoAHIAbwB3AF8AbABhAGIAZQBsAHMALAAgAHYAYQBsAHUAZQBzACwAIABmAHUAbgBjAHQAaQBvAG4ALAAgAEgAZQBhAGQAZQByAD8AKQAsAFwAbgAgACAAIAAgAGYAaQBsAHQAZQByAF8AaQBuAGMALAAgACAAIAAgACAAIAAgACAAIABHAFIATwBVAFAAQgBZACgAcgBvAHcAXwBsAGEAYgBlAGwAcwAsACAAdgBhAGwAdQBlAHMALAAgAGYAdQBuAGMAdABpAG8AbgAsACAASABlAGEAZABlAHIAPwAsACAALAAgACwAIABmAGkAbAB0AGUAcgBfAHUAcwBlAGQAKQAsAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABGAGkAbAB0AGUAcgA/ACwAIABmAGkAbAB0AGUAcgBfAGkAbgBjACwAIABuAG8AXwBmAGkAbAB0AGUAcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3ACAAbABhAGIAZQBsACAAKAB1AG4AZgBvAHIAbQBhAHQAdABlAGQAKQAgAGEAbgBkACAAZgBvAHIAbQBhAHQAdABlAGQAXABuACAAIAAgACAAcgBvAHcAXwBsAGEAYgBlAGwALAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAVABBAEsARQAoAGEAZwBnACwAIAAsACAAMQApACkALABcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABUAEUAWABUACgAcgBvAHcAXwBsAGEAYgBlAGwAKAApACwAIABmAG0AdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAARQBuAGQAaQBuAGcAIABkAGEAdABlAHMAIABmAG8AcgAgAHcAZQBlAGsAbAB5ACAALwAgAGIAaQB3AGUAZQBrAGwAeQBcAG4AIAAgACAAIABiAGkAbgBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABpAG4AdABlAHIAdgBhAGwAIAA9ACAANAAsAFQARQBYAFQAKABhACgAKQAgACsAIAA2ACwAIABmAG0AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABpAG4AdABlAHIAdgBhAGwAIAA9ACAANQAsACAAVABFAFgAVAAoAGEAKAApACAAKwAgADEAMwAsACAAZgBtAHQAKQAsACAAMAApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAbQBhAGkAbgBpAG4AZwAgAGMAbwBsAHUAbQBuAHMAXABuACAAIAAgACAAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARABSAE8AUAAoAGEAZwBnACwAIAAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAYwBrAHMAXABuACAAIAAgACAAcwB0AGEAYwBrACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgASABTAFQAQQBDAEsAKAB0AG8AdABhAGwAXwBoAGUAYQBkAGUAcgAsACAAYQBnAGcAXwBoAGUAYQBkAGUAcgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACgAKQAsACAAYgAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAHMAdABhAGMAawBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAdABvAHQAYQBsAF8AaABlAGEAZABlAHIALAAgAGEAZwBnAF8AaABlAGEAZABlAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABhACgAKQAsACAAYgBpAG4AXwBlAG4AZAAoACkALAAgAGIAKAApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgAaQBuAHQAZQByAHYAYQBsACAAPQAgADQALAAgAGkAbgB0AGUAcgB2AGEAbAAgAD0AIAA1ACkALAAgAHMAdABhAGMAawBfAGUAbgBkACwAIABzAHQAYQBjAGsAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAHkAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSABEgQwBPAFIARQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBHAEQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwAgACgAQwBvAHIAZQAgAFYAYQBsAGkAZABhAHQAaQBvAG4AKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFYAYQBsAGkAZABhAHQAZQBzACAAaQBuAHAAdQB0AHMAIABmAG8AcgAgAEcAcgBvAHUAcABiAHkARABhAHQAZQC7Ay4AIABFAG4AcwB1AHIAZQBzACAAdABoAGEAdAAgAHIAbwB3AF8AZgBpAGUAbABkAHMAIABjAG8AbgB0AGEAaQBuACAAdgBhAGwAaQBkAFwAbgAgACAAIAAgAGQAYQB0AGUAcwAsACAAdABoAGEAdAAgAGkAbgB0AGUAcgB2AGEAbABzACAAYQByAGUAIAByAGUAYwBvAGcAbgBpAHoAZQBkACwAIAB0AGgAYQB0ACAAdgBhAGwAdQBlAHMAIABhAG4AZAAgAGYAaQBsAHQAZQByAHMAIABhAGwAaQBnAG4AIABpAG4AXABuACAAIAAgACAAcwBoAGEAcABlACwAIABhAG4AZAAgAHQAaABhAHQAIAB0AGgAZQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGMAYQBsAGwAYQBiAGwAZQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHIAbwB3AF8AZgBpAGUAbABkAHMAIAAgACAAIAAgACAALQAgAEEAcgByAGEAeQAgAHcAaQB0AGgAIABkAGEAdABlAHMAIABpAG4AIAB0AGgAZQAgAGwAZQBmAHQAbQBvAHMAdAAgAGMAbwBsAHUAbQBuAC4AXABuACAAIAAgACAAdgBhAGwAdQBlAHMAIAAgACAAIAAgACAAIAAgACAAIAAtACAAQQByAHIAYQB5ACAAbwBmACAAdgBhAGwAdQBlAHMAIAB0AG8AIABhAGcAZwByAGUAZwBhAHQAZQAuAFwAbgAgACAAIAAgAGkAbgB0AGUAcgB2AGEAbAAgACAAIAAgACAAIAAgACAALQAgAEQAYQB0AGUALwB0AGkAbQBlACAAaQBuAHQAZQByAHYAYQBsACAAKABuAHUAbQBlAHIAaQBjACAAbwByACAAdABlAHgAdAApAC4AXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACAAIAAgACAAIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABzAGkAbgBnAGwAZQARIHAAYQByAGEAbQBlAHQAZQByACAATABBAE0AQgBEAEEALgBcAG4AIAAgACAAIABbAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAHMAXQAgAC0AIABUAFIAVQBFACAAaQBmACAAcgBvAHcAXwBmAGkAZQBsAGQAcwAvAHYAYQBsAHUAZQBzACAAaQBuAGMAbAB1AGQAZQAgAGgAZQBhAGQAZQByAHMALgBcAG4AIAAgACAAIABbAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5AF0AIAAgAC0AIABCAG8AbwBsAGUAYQBuACAAZgBpAGwAdABlAHIAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAE8AbgBfAFYAYQBsAGkAZABdACAAIAAgACAAIAAgAC0AIABFAHgAcAByAGUAcwBzAGkAbwBuACAAdABvACAAZQB2AGEAbAB1AGEAdABlACAAdwBoAGUAbgAgAGkAbgBwAHUAdABzACAAYQByAGUAIAB2AGEAbABpAGQALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABEAGUAdABlAGMAdABzACAAaQBuAHYAYQBsAGkAZAAgAGQAYQB0AGUAcwAsACAAbQBpAHMAcwBpAG4AZwAgAHQAaQBtAGUAIABjAG8AbQBwAG8AbgBlAG4AdABzACwAIABhAG4AZAAgAG0AYQBsAGYAbwByAG0AZQBkACAAaQBuAHQAZQByAHYAYQBsAHMALgBcAG4AIAAgACAAIAAiICAARQBuAHMAdQByAGUAcwAgAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgAHYAYQBsAHUAZQBzACwAIABhAG4AZAAgAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACAAaABhAHYAZQAgAG0AYQB0AGMAaABpAG4AZwAgAGgAZQBpAGcAaAB0AHMALgBcAG4AIAAgACAAIAAiICAARQBuAHMAdQByAGUAcwAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGMAYQBsAGwAYQBiAGwAZQAgAHYAaQBhACAAYQAgAHMAYQBmAGUAIABCAFkAUgBPAFcAIAB0AGUAcwB0AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFYAYQBsAGkAZABhAHQAZQBHAEQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcgBvAHcAXwBmAGkAZQBsAGQAcwAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAaQBuAHQAZQByAHYAYQBsACwAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAXABuACAAIAAgACAAWwBmAGkAZQBsAGQAXwBoAGUAYQBkAGUAcgBzAF0ALABcAG4AIAAgACAAIABbAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5AF0ALABcAG4AIAAgACAAIABbAE8AbgBfAFYAYQBsAGkAZABdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAALQAtAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGwAYQBnAHMAIAAtAC0ALQBcAG4AIAAgACAAIABOAG8AXwBGAGkAZQBsAGQAXwBIAGUAYQBkAGUAcgBzAD8ALAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBlAGwAZABfAGgAZQBhAGQAZQByAHMAKQAsAFwAbgAgACAAIAAgAEYAaQBsAHQAZQByAEkAbgBjAGwAdQBkAGUAZAA/ACwAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbAB0AGUAcgBfAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABFAHgAdAByAGEAYwB0ACAAZABhAHQAZQAgAGEAbgBkACAAdgBhAGwAdQBlACAAYwBvAGwAdQBtAG4AcwAgAC0ALQAtAFwAbgAgACAAIAAgAEQAYQB0AGUAXwBjAG8AbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBfAEYAaQBlAGwAZABfAEgAZQBhAGQAZQByAHMAPwAsAFQAQQBLAEUAKAByAG8AdwBfAGYAaQBlAGwAZABzACwAIAAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAVABBAEsARQAoAHIAbwB3AF8AZgBpAGUAbABkAHMALAAgACwAIAAxACkALAAgADEAKQApACwAXABuAFwAbgAgACAAIAAgAFYAYQBsAHUAZQBzAF8AYwBvAGwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE4AbwBfAEYAaQBlAGwAZABfAEgAZQBhAGQAZQByAHMAPwAsAFQAQQBLAEUAKAB2AGEAbAB1AGUAcwAsACAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAFQAQQBLAEUAKAB2AGEAbAB1AGUAcwAsACAALAAgADEAKQAsACAAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABGAGkAbAB0AGUAcgAgAGEAcgByAGEAeQAgAG4AbwByAG0AYQBsAGkAegBhAHQAaQBvAG4AIAAtAC0ALQBcAG4AIAAgACAAIABCAG8AbwBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgASQBGACgATgBvAF8ARgBpAGUAbABkAF8ASABlAGEAZABlAHIAcwA/ACwAZgBpAGwAdABlAHIAXwBhAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGYAaQBsAHQAZQByAF8AYQByAHIAYQB5ACwAIAAxACkAIAApACwAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAARABhAHQAZQAgAHYAYQBsAGkAZABpAHQAeQAgAGMAaABlAGMAawBzACAALQAtAC0AXABuACAAIAAgACAATgBvAF8ARABhAHQAZQBzAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgARABhAHQAZQBfAGMAbwBsACAAPAAgADAALABEAGEAdABlAF8AYwBvAGwAIAA+ACAAMgA5ADUAOAA0ADYANQAsAE4ATwBUACgAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKABEAGEAdABlAF8AYwBvAGwAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIABOAG8AXwBUAGkAbQBlAHMAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAEQAYQB0AGUAXwBjAG8AbAAgAC0AIABJAE4AVAAoAEQAYQB0AGUAXwBjAG8AbAApACAAPQAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEQAaQBtAGUAbgBzAGkAbwBuACAAYwBoAGUAYwBrAHMAIAAtAC0ALQBcAG4AIAAgACAAIABpAF8AZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgARABhAHQAZQBfAGMAbwBsACkALABcAG4AIAAgACAAIABpAF8AdgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAVgBhAGwAdQBlAHMAXwBjAG8AbAApACwAXABuACAAIAAgACAAaQBfAGYALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgARgBpAGwAdABlAHIASQBuAGMAbAB1AGQAZQBkAD8ALAAgAFIATwBXAFMAKABCAG8AbwBsACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEkAbgB0AGUAcgB2AGEAbAAgAHYAYQBsAGkAZABhAHQAaQBvAG4AIAAtAC0ALQBcAG4AIAAgACAAIABDAG8AbgBzAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgBtAGkAbgB1AHQAZQBcACIAOwBcACIAaABvAHUAcgBcACIAOwBcACIAZABhAHkAXAAiADsAXAAiAHcAZQBlAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBvAHIAdABuAGkAZwBoAHQAXAAiADsAXAAiAG0AbwBuAHQAaABcACIAOwBcACIAcQB1AGEAcgB0AGUAcgBcACIAOwBcACIAeQBlAGEAcgBcACIAfQAsAFwAbgBcAG4AIAAgACAAIABUAGUAeAB0AEkAbgB0AGUAcgB2AGEAbAA/ACwAIAAgACAAIAAgACAAIAAgACAAIABJAFMAVABFAFgAVAAoAGkAbgB0AGUAcgB2AGEAbAApACwAXABuACAAIAAgACAATgB1AG0AZQByAGkAYwBJAG4AdABlAHIAdgBhAGwAPwAsACAAIAAgACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgAaQBuAHQAZQByAHYAYQBsACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABJAG4AdABlAHIAdgBhAGwAPwAsACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABOAHUAbQBlAHIAaQBjAEkAbgB0AGUAcgB2AGEAbAA/ACwAIABPAFIAKABpAG4AdABlAHIAdgBhAGwAIAA8ACAAMQAsACAAaQBuAHQAZQByAHYAYQBsACAAPgAgADgAKQApACwAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBOAEQAKABUAGUAeAB0AEkAbgB0AGUAcgB2AGEAbAA/ACwAIABJAFMATgBBACgAWABNAEEAVABDAEgAKABpAG4AdABlAHIAdgBhAGwAIAAmACAAXAAiACoAXAAiACwAIABDAG8AbgBzAHQALAAgADIAKQApACkALABUAFIAVQBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAQQBMAFMARQApACkALABcAG4AXABuACAAIAAgACAASQBzAFQAaQBtAGUAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBuAHQAZQByAHYAYQBsACAAPAAgADMALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABIAGEAbAB0AGkAbgBnACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAC0ALQAtAFwAbgAgACAAIAAgAEUAbQBwAHQAeQBJAG4AcAB1AHQAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcgBvAHcAXwBmAGkAZQBsAGQAcwApACwAIABJAFMATwBNAEkAVABUAEUARAAoAHYAYQBsAHUAZQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIABIAGEAbAB0AEQAYQB0AGUAcwA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAGkAbgB0AGUAcgB2AGEAbAAgAD4AIAAyACwAIABOAG8AXwBEAGEAdABlAHMAPwApACwAXABuACAAIAAgACAASABhAGwAdABUAGkAbQBlAD8ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAHMAVABpAG0AZQA/ACwAIABOAG8AXwBUAGkAbQBlAHMAPwApACwAXABuAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGkAXwBkACAAPAA+ACAAaQBfAHYALABBAE4ARAAoAEYAaQBsAHQAZQByAEkAbgBjAGwAdQBkAGUAZAA/ACwAIABpAF8AZAAgADwAPgAgAGkAXwBmACkAKQAsAFwAbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEYAbgA/ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA8AD4AIAAxADIAOAAsAFwAbgBcAG4AIAAgACAAIABFAG0AcAB0AHkARgBpAGwAdABlAHIAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAEYAaQBsAHQAZQByAEkAbgBjAGwAdQBkAGUAZAA/ACwAIABOAE8AVAAoAE8AUgAoAEIAbwBvAGwAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAGwAbABlAGMAdAAgAGEAbABsACAAYwBvAG4AZABpAHQAaQBvAG4AcwBcAG4AIAAgACAAIABjAG8AbgBkAGkAdABpAG8AbgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAEUAbQBwAHQAeQBJAG4AcAB1AHQAcwA/ACwASABhAGwAdABEAGEAdABlAHMAPwAsAEgAYQBsAHQAVABpAG0AZQA/ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALABJAG4AdgBhAGwAaQBkAEkAbgB0AGUAcgB2AGEAbAA/ACwASQBuAHYAYQBsAGkAZABGAG4APwAsAEUAbQBwAHQAeQBGAGkAbAB0AGUAcgA/ACkALABcAG4AXABuACAAIAAgACAAaABhAGwAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAYwBvAG4AZABpAHQAaQBvAG4AcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAcwAgACgAYQBsAGkAZwBuAGUAZAAgAHcAaQB0AGgAIABHAHIAbwB1AHAAYgB5AEQAYQB0AGUAuwMpAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAXAAiACMARQBNAFAAVABZAC0ASQBOAFAAVQBUACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8ALQBEAEEAVABFAFMAIQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAE4ATwAtAFQASQBNAEUAUwAhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMARABJAE0ARQBOAFMASQBPAE4AUwAhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMASQBOAFQARQBSAFYAQQBMACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBJAE4AVgBBAEwASQBEAC0ARgBVAE4AQwBUAEkATwBOACEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBFAE0AUABUAFkALQBGAEkATABUAEUAUgAhAFwAIgB9ACwAXABuAFwAbgAgACAAIAAgAGEAbABlAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAZQByAHIAbwByAHMALAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMALAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAIAAtAC0ALQBcAG4AIAAgACAAIABJAEYAKABoAGEAbAB0ACwAIABhAGwAZQByAHQALAAgAE8AbgBfAFYAYQBsAGkAZAApAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMAA5AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUABpAHYAbwB0AGIAeQBDAGEAdAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFMAdAByAGUAYQBrALsDLAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFAAaQB2AG8AdABzACAAZABhAHQAYQAgAGIAeQAgAHIAbwB3ACAAZgBpAGUAbABkAHMAIAAoAGQAZQB0AGEAaQBsACAAKwAgAGQAYQB0AGUAKQAsACAAYwBhAHQAZQBnAG8AcgBpAGUAcwAsACAAYQBuAGQAIAB2AGEAbAB1AGUAcwAuAFwAbgAgACAAIAAgAEMAYQB0AGUAZwBvAHIAaQBlAHMAIABhAHIAZQAgAGEAcwBzAHUAbQBlAGQAIAB0AG8AIABiAGUAIABwAHIAZQARIGMAbwBuAGMAYQB0AGUAbgBhAHQAZQBkACAAdQBzAGkAbgBnACAAYQAgAGQAZQBsAGkAbQBpAHQAZQByAC4AXABuACAAIAAgACAAUwB1AHAAcABvAHIAdABzACAAbwBwAHQAaQBvAG4AYQBsACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAZgB1AG4AYwB0AGkAbwBuACAAYQBuAGQAIABkAGEAdABlACAAZgBvAHIAbQBhAHQAdABpAG4AZwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHIAbwB3AF8AZABlAHQAYQBpAGwAIAAgACAAIAAgACAALQAgADEARAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AbwBuABEgZABhAHQAZQAgAHIAbwB3ACAAZgBpAGUAbABkAHMALgBcAG4AIAAgACAAIAByAG8AdwBfAGQAYQB0AGUAcwAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIABkAGEAdABlAHMALgBcAG4AIAAgACAAIABjAGEAdABlAGcAbwByAGkAZQBzACAAIAAgACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIABkAGUAbABpAG0AaQB0AGUAZAAgAGMAYQB0AGUAZwBvAHIAeQAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAgACAAIAAgACAAIAAgACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAdgBhAGwAdQBlAHMALgBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAgACAAIAAgACAAIAAgAC0AIABEAGUAbABpAG0AaQB0AGUAcgAgAHUAcwBlAGQAIABpAG4AIAB0AGgAZQAgAGMAYQB0AGUAZwBvAHIAaQBlAHMAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAZABhAHQAZQBfAGYAbwByAG0AYQB0AF0AIAAgACAALQAgAEYAbwByAG0AYQB0ACAAYwBvAGQAZQAgAGYAbwByACAAZABhAHQAZQBzACAAKABkAGUAZgBhAHUAbAB0ACAAXAAiAHkAeQB5AFwAIgApAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAAIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABMAEEATQBCAEQAQQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAGYAdQBuAGMAdABpAG8AbgAgACgAZABlAGYAYQB1AGwAdAAgAFMAVQBNACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABDAGEAdABlAGcAbwByAGkAZQBzACAAYQByAGUAIABzAHAAbABpAHQAIABpAG4AdABvACAAbQB1AGwAdABpAHAAbABlACAAcgBvAHcAcwAgAHUAcwBpAG4AZwAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMuAFwAbgAgACAAIAAgACIgIABEAGEAdABlAHMAIABhAHIAZQAgAGYAbwByAG0AYQB0AHQAZQBkACAAYQBuAGQAIABzAG8AcgB0AGUAZAAgAHUAcwBpAG4AZwAgAGEAIABuAHUAbQBlAHIAaQBjACAAcwBvAHIAdAAgAGsAZQB5AC4AXABuACAAIAAgACAAIiAgAFYAYQBsAHUAZQBzACAAYQByAGUAIABhAHAAcABvAHIAdABpAG8AbgBlAGQAIABhAGMAcgBvAHMAcwAgAHIAZQBwAGUAYQB0AGUAZAAgAGMAYQB0AGUAZwBvAHIAeQAgAHIAbwB3AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABpAHYAbwB0AGIAeQBDAGEAdAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAByAG8AdwBfAGQAZQB0AGEAaQBsACwAXABuACAAIAAgACAAcgBvAHcAXwBkAGEAdABlAHMALABcAG4AIAAgACAAIABjAGEAdABlAGcAbwByAGkAZQBzACwAXABuACAAIAAgACAAdgBhAGwAdQBlAHMALABcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsAFwAbgAgACAAIAAgAFsAZABhAHQAZQBfAGYAbwByAG0AYQB0AF0ALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAARABpAG0AZQBuAHMAaQBvAG4AcwAgAC0ALQAtAFwAbgAgACAAIAAgAHIAgSAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAcgBvAHcAXwBkAGUAdABhAGkAbAApACwAXABuACAAIAAgACAAcgCCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAG8AdwBfAGQAYQB0AGUAcwApACwAXABuACAAIAAgACAAcgCDICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABjAGEAdABlAGcAbwByAGkAZQBzACkALABcAG4AIAAgACAAIAByAIQgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAYQBsAHUAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABIAGEAbAB0AGkAbgBnACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAC0ALQAtAFwAbgAgACAAIAAgAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgALAAgACAAIAAgACAAIABPAFIAKAByAIEgIAA8AD4AIAByAIIgLAAgAHIAgSAgADwAPgAgAHIAgyAsACAAcgCBICAAPAA+ACAAcgCEICkALABcAG4AXABuACAAIAAgACAAZABhAHQAZQBfAGYAbwByAG0AYQB0ACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZABhAHQAZQBfAGYAbwByAG0AYQB0ACkALAAgAFwAIgB5AHkAeQBcACIALAAgAGQAYQB0AGUAXwBmAG8AcgBtAGEAdAApACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQARABhAHQAZQBzACwAIAAgACAAIAAgACAAIABPAFIAKABBAE4ARAAoAEkAUwBFAFIAUgBPAFIAKABEAEEAVABFAFYAQQBMAFUARQAoAFQARQBYAFQAKAByAG8AdwBfAGQAYQB0AGUAcwAsACAAZABhAHQAZQBfAGYAbwByAG0AYQB0ACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAEUAUgBSAE8AUgAoAFYAQQBMAFUARQAoAFQARQBYAFQAKAByAG8AdwBfAGQAYQB0AGUAcwAsACAAZABhAHQAZQBfAGYAbwByAG0AYQB0ACkAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABBAE4ARAAoAEkAUwBOAFUATQBCAEUAUgAoAHIAbwB3AF8AZABhAHQAZQBzACkAKQApACkALABcAG4AXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4ALAAgACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuAFwAbgAgACAAIAAgAHMAYwBlAG4AYQByAGkAbwBzACwAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFMAaABhAHAAZQBNAGkAcwBtAGEAdABjAGgALAAgAEkAbgB2AGEAbABpAGQARABhAHQAZQBzACwAIABJAG4AdgBhAGwAaQBkAEYAbgApACwAXABuAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAEQASQBNAEUATgBTAEkATwBOAFMAIQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBEAEEAVABFAFMAIQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBJAE4AVgBBAEwASQBEAC0ARgBVAE4AQwBUAEkATwBOACEAXAAiAH0ALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABMAG8AZwBpAGMAIABnAGEAdABlACAALQAtAC0AXABuACAAIAAgACAARgBJAEwAVABFAFIAKABlAHIAcgBvAHIAcwAsACAAcwBjAGUAbgBhAHIAaQBvAHMALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAALQAtAC0AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgAgAC0ALQAtAFwAbgAgACAAIAAgAGYAbgC7AywAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGYAdQBuAGMAdABpAG8AbgApACwAIABTAFUATQAsACAAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAATABvAGMAYQBsACAAaABlAGwAcABlAHIAcwAgAC0ALQAtAFwAbgAgACAAIAAgAEMAbwB1AG4AdABDAGEAdAC7AywAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIAbwB3ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABUAEUAWABUAFMAUABMAEkAVAAoAHIAbwB3ACwAIABkAGUAbABpAG0AaQB0AGUAcgApACkAKQAsAFwAbgBcAG4AIAAgACAAIABQAGEAcgBzAGUAuwMsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABhAHIAcgBhAHkALAAgAGkAbgBzAHQAYQBuAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABUAEUAWABUAEEARgBUAEUAUgAoAGQAZQBsAGkAbQBpAHQAZQByACAAJgAgAGEAcgByAGEAeQAgACYAIABkAGUAbABpAG0AaQB0AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByACwAaQBuAHMAdABhAG4AYwBlACwALAAsAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAsACwALAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBhAHQAZQBnAG8AcgBpAGUAcwApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABDAGEAdABlAGcAbwByAHkAIABlAHgAcABhAG4AcwBpAG8AbgAgAC0ALQAtAFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKABjAGEAdABlAGcAbwByAGkAZQBzACwAIABDAG8AdQBuAHQAQwBhAHQAuwMpACwAXABuAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDKABTAEUAUQBVAEUATgBDAEUAKAByAIEgKQAsACAAawApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAGUAYQBrALsDKABpACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABSAG8AdwAgAGYAaQBlAGwAZABzACAALQAtAC0AXABuACAAIAAgACAAYQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMoAHIAbwB3AF8AZABlAHQAYQBpAGwALAAgAGsAKQAsAFwAbgAgACAAIAAgAGQAZQB0AGEAaQBsACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABhACAAPQAgADAALAAgAFwAIgBVAG4AawBuAG8AdwBuAFwAIgAsACAAYQApACwAXABuAFwAbgAgACAAIAAgAGQAYQB0AGUAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAcABlAGEAdABSAG8AdwBzALsDKABUAEUAWABUACgAcgBvAHcAXwBkAGEAdABlAHMALAAgAGQAYQB0AGUAXwBmAG8AcgBtAGEAdAApACwAIABrACkALABcAG4AIAAgACAAIABzAG8AcgB0AF8AawBlAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEQAQQBUAEUAVgBBAEwAVQBFACgAZABhAHQAZQBzACkALAAgAFYAQQBMAFUARQAoAGQAYQB0AGUAcwApACkALABcAG4AXABuACAAIAAgACAAcgBvAHcAXwBmAGkAZQBsAGQAcwAsACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAcwBvAHIAdABfAGsAZQB5ACwAIABkAGUAdABhAGkAbAAsACAAZABhAHQAZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABDAG8AbAB1AG0AbgAgAGYAaQBlAGwAZABzACAALQAtAC0AXABuACAAIAAgACAAdQBuAHAAYQBjAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMoAGMAYQB0AGUAZwBvAHIAaQBlAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgAGMAYQB0AGUAZwBvAHIAaQBlAHMALAAgACAAIAAgACAAIAAgACAAIABQAGEAcgBzAGUAuwMoAHUAbgBwAGEAYwBrACwAIABqACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIABWAGEAbAB1AGUAcwAgACgAYQBwAHAAbwByAHQAaQBvAG4AZQBkACkAIAAtAC0ALQBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AygAdgBhAGwAdQBlAHMAIAAvACAAawAsACAAawApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAC0ALQAtACAAQQBnAGcAcgBlAGcAYQB0AGkAbwBuACAALQAtAC0AXABuACAAIAAgACAAYQBnAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABQAEkAVgBPAFQAQgBZACgAcgBvAHcAXwBmAGkAZQBsAGQAcwAsAGMAYQB0AGUAZwBvAHIAaQBlAHMALAB2AGEAbAB1AGUAcwAsAGYAbgC7AywALAAwACwALAAwACkALAAsADEAKQAsAFwAbgBcAG4AIAAgACAAIABhAGcAZwBcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgACAAWwBHAFIAMQA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARwByAG8AdQBwAEkAbgBkAGUAeAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABDAGEAdABlAGcAbwByAGkAYwBhAGwAIABBAG4AYQBsAHkAcwBpAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEEAcwBzAGkAZwBuACAAbgB1AG0AZQByAGkAYwBhAGwAIABnAHIAbwB1AHAAIABpAG4AZABpAGMAZQBzACAAdABvACAAYQAgADEARAAgAGEAcgByAGEAeQAgACgAaABvAHIAaQB6AG8AbgB0AGEAbAAgAG8AcgAgAHYAZQByAHQAaQBjAGEAbAApAC4AXABuACAAIAAgACAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGYAbABhAHQAdABlAG4AZQBkACAAdgBlAHIAdABpAGMAYQBsAGwAeQAgAGIAZQBmAG8AcgBlACAAaQBuAGQAaQBjAGUAcwAgAGEAcgBlACAAYQBzAHMAaQBnAG4AZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAdgBlAGMAdABvAHIAIAAgACAAIAAgACAAIAAgACAALQAgACAAIAAxAEQAIABhAHIAcgBhAHkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAdgBhAGwAdQBlAHMAIAB0AG8AIABiAGUAIABwAGwAYQBjAGUAZAAgAGkAbgAgAG4AdQBtAGUAcgBpAGMAYQBsACAAZwByAG8AdQBwAHMAXABuACAAIAAgACAAWwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAgACAALQAgACAAIABUAFIAVQBFACAAPQAgAGgAbwByAGkAegBvAG4AdABhAGwAIABvAHUAdABwAHUAdAA7ACAAbwBtAGkAdAB0AGUAZAAgAD0AIAB2AGUAcgB0AGkAYwBhAGwAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AIAAqAC8AXABuAEcAcgBvAHUAcABJAG4AZABlAHgAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAdgBlAGMAdABvAHIALABcAG4AIAAgACAAIABbAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdABcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAHYAZQBjAHQAbwByACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBoAGEAcABlAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAUgBPAFcAUwAoAHYAZQBjAHQAbwByACkALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKAB2AGUAYwB0AG8AcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAASQBTAE8ATQBJAFQAVABFAEQAKABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgAEEATgBEACgAaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAFMAcABpAGwAbABSAGkAcwBrAD8ALAAgACAASQBGACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAaABlAGkAZwBoAHQAIAA+ACAAMQAwADQAOAA1ADcANgAsAGgAZQBpAGcAaAB0ACAAPgAgADEANgAzADgANAApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAB2AGUAYwB0AG8AcgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAUwBwAGkAbABsAFIAaQBzAGsAPwAsACAAIwBOAFUATQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEcAcgBvAHUAcAAgAGkAbgBkAGUAeAAgAD0AIABwAG8AcwBpAHQAaQBvAG4AIABvAGYAIABmAGkAcgBzAHQAIABvAGMAYwB1AHIAcgBlAG4AYwBlAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgACAAIAAgACAAWABNAEEAVABDAEgAKAB2AGUAYwB0AG8AcgAsACAAVQBOAEkAUQBVAEUAKAB2AGUAYwB0AG8AcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAaABhAHAAZQBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAaQBkAHgALAAgAFQATwBSAE8AVwAoAGkAZAB4ACkAKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAxADkAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABPAGMAYwB1AHIAcgBlAG4AYwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAASQBuAHMAdABhAG4AYwBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGUAbABlAGMAdABzACAAdABoAGUAIABOAEAdNB1fAG8AYwBjAHUAcgByAGUAbgBjAGUAcwAgAG8AZgAgAHIAbwB3AHMAIABmAHIAbwBtACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAYgB5ACAAbABvAGMAYQB0AGkAbgBnACAAdABoAGUAIABOAEAdNB0gAGkAbgBzAHQAYQBuAGMAZQBcAG4AIAAgACAAIABmAHIAbwBtACAAYQAgAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgAuACAAIABSAGUAcwB1AGwAdABzACAAYQByAGUAIAByAGUAdAB1AHIAbgBlAGQAIABpAG4AIABvAHIAZABlAHIAIABvAGYAIABhAHAAcABlAGEAcgBhAG4AYwBlACAAYQBuAGQAIABuAG8AdAAgAHMAbwByAHQAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAIAAgADIARAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABjAHIAaQB0AF8AdgBlAGMAdABvAHIAIAAgACAAIAAgAC0AIAAgACAAMQBEACAAYQByAHIAYQB5ACAAZABlAGYAaQBuAGkAbgBnACAAdABoAGUAIABzAHQAcgB1AGMAdAB1AHIAZQBcAG4AIAAgACAAIABOAEAdNB1fAG8AYwBjAHUAcgByAGUAbgBjAGUALAAgAC0AIAAgACAASQBuAHQAZQBnAGUAcgAgAG8AZgAgAHMAZQBsAGUAYwB0AGUAZAAgAG8AYwBjAHUAcgByAGUAbgBjAGUAcwAgACgAZQAuAGcALgAgADEALQBuACkAXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAE8AYwBjAHUAcgByAGUAbgBjAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgAsAFwAbgAgACAAIAAgAE4AQB00HV8AbwBjAGMAdQByAHIAZQBuAGMAZQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAaABhAHAAZQBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAaABlAGkAZwBoAHQAXwAsAFIATwBXAFMAKABjAHIAaQB0AF8AdgBlAGMAdABvAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGEAbAB0AGkAbgBnACAAcwBjAGUAbgBhAHIAaQBvAHMAXABuACAAIAAgACAAaABlAGkAZwBoAHQAXwBtAGkAcwBtAGEAdABjAGgAPwAsACAAIAAgAGgAZQBpAGcAaAB0ACAAPAA+ACAAaABlAGkAZwBoAHQAXwAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQATwBjAGMAdQByAHIAZQBuAGMAZQA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAE4AQB00HV8AbwBjAGMAdQByAHIAZQBuAGMAZQApACwATgBAHTQdXwBvAGMAYwB1AHIAcgBlAG4AYwBlACAAPQAgADAAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABoAGUAaQBnAGgAdABfAG0AaQBzAG0AYQB0AGMAaAA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABPAGMAYwB1AHIAcgBlAG4AYwBlAD8ALAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0AGkAbwBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABEAGUAcwBjAGUAbgBkAD8ALAAgACAAIABTAEkARwBOACgATgBAHTQdXwBvAGMAYwB1AHIAcgBlAG4AYwBlACkAIAA9ACAALQAxACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAZABlAG4AdABpAGYAeQAgAE4AdABoACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzAFwAbgAgACAAIAAgAGIAbwBvAGwALAAgACAAIAAgACAAIAAgAEkAbgBzAHQAYQBuAGMAZQC7AygAYwByAGkAdABfAHYAZQBjAHQAbwByACwALABEAGUAcwBjAGUAbgBkAD8AKQAgAD0AIABBAEIAUwAoAE4AQB00HV8AbwBjAGMAdQByAHIAZQBuAGMAZQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAZABhAHQAYQBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsAGIAbwBvAGwALAAwACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACAAIAAgACAAKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADIAMABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcgByAGUAbgBjAGUAUgBhAG4AZwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAEMAYQB0AGUAZwBvAHIAaQBjAGEAbAAgAEEAbgBhAGwAeQBzAGkAcwApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAASQBuAHMAdABhAG4AYwBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGUAbABlAGMAdABzACAAYQAgAHIAYQBuAGcAZQAgAG8AZgAgAG8AYwBjAHUAcgByAGUAbgBjAGUAcwAgAG8AZgAgAHIAbwB3AHMAIABmAHIAbwBtACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAMgBEACAAYQByAHIAYQB5ACAAYgB5ACAAbABvAGMAYQB0AGkAbgBnACAAdABoAGUAIABOAEAdNB0gAGkAbgBzAHQAYQBuAGMAZQBzAFwAbgAgACAAIAAgAGYAcgBvAG0AIABhACAAYwByAGkAdABfAHYAZQBjAHQAbwByAC4AIABOAGUAZwBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMAIABhAHIAZQAgAHIAZQBqAGUAYwB0AGUAZAAgAGYAbwByACAAcwB0AGEAcgB0ACAAYQBuAGQAIABlAG4AZAAgAG8AYwBjAHUAcgByAGUAbgBjAGUAcwAuAFwAbgAgACAAIAAgAFIAZQBzAHUAbAB0AHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAgAGkAbgAgAG8AcgBkAGUAcgAgAG8AZgAgAGEAcABwAGUAYQByAGEAbgBjAGUAIABhAG4AZAAgAG4AbwB0ACAAcwBvAHIAdABlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAIAAgADIARAAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABjAHIAaQB0AF8AdgBlAGMAdABvAHIAIAAgACAAIAAgACAAIAAtACAAIAAgADEARAAgAGEAcgByAGEAeQAgAGQAZQBmAGkAbgBpAG4AZwAgAHQAaABlACAAcwB0AHIAdQBjAHQAdQByAGUAXABuACAAIAAgACAAcwB0AGEAcgB0AF8AbwBjAGMAdQByAHIAZQBuAGMAZQAsACAALQAgACAAIABTAHQAYQByAHQAaQBuAGcAIABpAG4AdABlAGcAZQByACAAbwBmACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzAFwAbgAgACAAIAAgAFsAZQBuAGQAXwBvAGMAYwB1AHIAcgBlAG4AYwBlAF0AIAAgAC0AIAAgACAARQBuAGQAaQBuAGcAIABpAG4AdABlAGcAZQByACAAbwBmACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzAC4AIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAB0AGgAZQAgAHMAZQBsAGUAYwB0AGkAbwBuACAAbwBmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbwBmACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzACAAPQAgAHMAdABhAHIAdABfAG8AYwBjAHUAcgByAGUAbgBjAGUAIAB+ACAAZQBuAGQAIABvAGYAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAEgAbwByAGkAegBvAG4AdABhAGwAPwBdACAAIAAgACAAIAAtACAAIAAgAFQAUgBVAEUAIAA9ACAAcwBlAGwAZQBjAHQAIABvAGMAYwB1AHIAcgBlAG4AYwBlACAAcgBhAG4AZwBlACAAZgByAG8AbQAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5ACAAYQByAHIAYQBuAGcAZQBkACAAZABhAHQAYQBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4ATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgAsAFwAbgAgACAAIAAgAHMAdABhAHIAdABfAG8AYwBjAHUAcgByAGUAbgBjAGUALABcAG4AIAAgACAAIABbAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQBdACwAXABuACAAIAAgACAAWwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8AXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIAAgACAATgBPAFQAKABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AKQApACwAIABIAG8AcgBpAHoAbwBuAHQAYQBsAD8AIAA9ACAAVABSAFUARQApACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABhAHIAcgBhAHkALABUAFIAQQBOAFMAUABPAFMARQAoAGEAcgByAGEAeQApACkALABcAG4AIAAgACAAIABjAHIAaQB0AF8AdgBlAGMAdABvAHIALAAgACAAIAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABjAHIAaQB0AF8AdgBlAGMAdABvAHIALABUAFIAQQBOAFMAUABPAFMARQAoAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsAFwAbgAgACAAIAAgAEkAbgBjAGwAdQBkAGUARQBuAGQAPwAsACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABlAG4AZABfAG8AYwBjAHUAcgByAGUAbgBjAGUAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcwB0AGEAcgB0AC8AcwB0AG8AcABcAG4AIAAgACAAIABzAHQAYQByAHQAXwBvAGMAYwB1AHIAcgBlAG4AYwBlACwAIABJAE4ARABFAFgAKABzAHQAYQByAHQAXwBvAGMAYwB1AHIAcgBlAG4AYwBlACwAMQAsADEAKQAsAFwAbgAgACAAIAAgAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQAsACAAIAAgAEkARgAoAEkAbgBjAGwAdQBkAGUARQBuAGQAPwAsAEkATgBEAEUAWAAoAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQAsADEALAAxACkALABGAEEATABTAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAXABuACAAIAAgACAAaABlAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAaABlAGkAZwBoAHQAXwAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGMAcgBpAHQAXwB2AGUAYwB0AG8AcgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABoAGUAaQBnAGgAdABfAG0AaQBzAG0AYQB0AGMAaAA/ACwAIAAgACAAaABlAGkAZwBoAHQAIAA8AD4AIABoAGUAaQBnAGgAdABfACwAXABuAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQATwBjAGMAdQByAHIAZQBuAGMAZQA/ACwAIABPAFIAKABJAFMAVABFAFgAVAAoAHMAdABhAHIAdABfAG8AYwBjAHUAcgByAGUAbgBjAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAXwBvAGMAYwB1AHIAcgBlAG4AYwBlACAAPAAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAG4AYwBsAHUAZABlAEUAbgBkAD8ALABJAFMAVABFAFgAVAAoAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAG4AYwBsAHUAZABlAEUAbgBkAD8ALABlAG4AZABfAG8AYwBjAHUAcgByAGUAbgBjAGUAIAA8ACAAcwB0AGEAcgB0AF8AbwBjAGMAdQByAHIAZQBuAGMAZQApACkALABcAG4AXABuACAAIAAgACAASQBGACgAaABlAGkAZwBoAHQAXwBtAGkAcwBtAGEAdABjAGgAPwAsACMAVgBBAEwAVQBFACEALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQATwBjAGMAdQByAHIAZQBuAGMAZQA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABJAGQAZQBuAHQAaQBmAHkAIABOAHQAaAAgAG8AYwBjAHUAcgByAGUAbgBjAGUAcwBcAG4AIAAgACAAIABpAG4AcwB0ACwAIAAgACAASQBuAHMAdABhAG4AYwBlALsDKABjAHIAaQB0AF8AdgBlAGMAdABvAHIAKQAsAFwAbgBcAG4AIAAgACAAIABiAG8AbwBsACwAIAAgACAASQBGACgASQBuAGMAbAB1AGQAZQBFAG4AZAA/ACwAKABpAG4AcwB0ACAAPgA9ACAAcwB0AGEAcgB0AF8AbwBjAGMAdQByAHIAZQBuAGMAZQApACAAKgAgACgAaQBuAHMAdAAgADwAPQAgAGUAbgBkAF8AbwBjAGMAdQByAHIAZQBuAGMAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAaQBuAHMAdAAgAD4APQAgAHMAdABhAHIAdABfAG8AYwBjAHUAcgByAGUAbgBjAGUAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAZABhAHQAYQAgAGEAbgBkACAAdAByAGEAbgBwAG8AcwBlACAAaQBmACAAaABvAHIAaQB6AG8AbgB0AGEAbABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIABGAEkATABUAEUAUgAoAGEAcgByAGEAeQAsAGIAbwBvAGwALAAwACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIABJAEYAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAByAGUAcwB1AGwAdAAsAFQAUgBBAE4AUwBQAE8AUwBFACgAcgBlAHMAdQBsAHQAKQApACwAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgAgACAAIAAgACkAKQApACkAKQA7AFwAbgBcAG4AXABuACAAIAAgACAAXABuAC8AKgAgAFsARwBSADEAMABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEcAcgBhAGkAbgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABEAG8AdwBuAHMAYQBtAHAAbABlAHMAIABhACAAYQByAHIAYQB5AF8AMgBEACAAYgB5ACAAYQBnAGcAcgBlAGcAYQB0AGkAbgBnACAAbwB2AGUAcgAgAG4AbwBuABEgbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAcwBwAGEAdABpAGEAbAAgAGIAbABvAGMAawBzAFwAbgAgACAAIAAgAG8AZgAgAHMAaQB6AGUAIABkAGUAcAB0AGgAIADXACAAdwBpAGQAdABoAC4AIABQAGEAcgB0AGkAYQBsACAAYgBsAG8AYwBrAHMAIABhAHQAIAB0AGgAZQAgAGUAZABnAGUAcwAgAGEAcgBlACAAaQBuAGMAbAB1AGQAZQBkAC4AIABUAGgAZQBcAG4AIAAgACAAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABpAHMAIABwAGUAcgBmAG8AcgBtAGUAZAAgAHUAcwBpAG4AZwAgAGEAbgAgAEUAVABBABEgYwBvAG0AcABhAHQAaQBiAGwAZQAgAGYAdQBuAGMAdABpAG8AbgAgACgAZQAuAGcALgAsACAAUwBVAE0ALABcAG4AIAAgACAAIABBAFYARQBSAEEARwBFACwAIABNAEEAWAAsACAATQBJAE4ALAAgAE0ARQBEAEkAQQBOACwAIABvAHIAIABhACAAYwB1AHMAdABvAG0AIABMAEEATQBCAEQAQQApAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgACAAIAAgAC0AIAAyAEQAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAXwAyAEQALgBcAG4AIAAgACAAIABkAGUAcAB0AGgAIAAgACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwBzACAAcABlAHIAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIAB3AGkAZAB0AGgAIAAgACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAcABlAHIAIABiAGwAbwBjAGsALgBcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AIAAgACAAIAAtACAARQBUAEEAIABvAHIAIABMAEEATQBCAEQAQQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABlAGEAYwBoACAAYgBsAG8AYwBrAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAGoAZQBjAHQAcwAgAG4AbwBuABEgYQByAHIAYQB5AF8AMgBEACAAaQBuAHAAdQB0AHMALgBcAG4AIAAgACAAIAAiICAAUgBlAGoAZQBjAHQAcwAgAGkAbgB2AGEAbABpAGQAIABiAGwAbwBjAGsAIABzAGkAegBlAHMAIABvAHIAIAB0AGUAeAB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwAuAFwAbgAgACAAIAAgACIgIABQAGEAcgB0AGkAYQBsACAAYgBsAG8AYwBrAHMAIABhAHIAZQAgAGgAYQBuAGQAbABlAGQAIABhAHUAdABvAG0AYQB0AGkAYwBhAGwAbAB5ACAAdgBpAGEAIABJAE4ARABFAFgAIAArACAAVABPAEMATwBMAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEcAcgBhAGkAbgC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABkAGUAcAB0AGgALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALABcAG4AXABuAEkARgAoAE4ATwBUACgAVABZAFAARQAoAGEAcgByAGEAeQBfADIARAApACAAPQAgADYANAApACwAXAAiACMAYQByAHIAYQB5AF8AMgBEACEAXAAiACwAXABuAFwAbgAgACAAIAAgAEkARgAoAE8AUgAoAGQAZQBwAHQAaAAgAD4AIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALAAgAHcAaQBkAHQAaAAgACAAPgAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAEkAUwBUAEUAWABUACgAZABlAHAAdABoACkALABJAFMAVABFAFgAVAAoAHcAaQBkAHQAaAApACkALABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAVABZAFAARQAoAGYAdQBuAGMAdABpAG8AbgApACAAPAA+ACAAMQAyADgALABcACIAIwBFAFQAQQAgAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAATgB1AG0AYgBlAHIAIABvAGYAIABiAGwAbwBjAGsAcwAgACgAcgBvAHUAbgBkAGUAZAAgAHUAcAApAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEAFUAUAAoAGgAIAAvACAAZABlAHAAdABoACwAIAAwACkALABcAG4AIAAgACAAIAB5ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARABVAFAAKAB3ACAALwAgAHcAaQBkAHQAaAAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbABvAGMAawAgAGEAbgBjAGgAbwByACAAZwByAGkAZABzACAAKABkAGUAZgBlAHIAcgBlAGQAKQBcAG4AIAAgACAAIABkAG8AdwBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAeAAsACAALAAgADEALAAgAGQAZQBwAHQAaAApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIAB5ACwAIAAxACwAIAAwACkAKQAsAFwAbgAgACAAIAAgAGEAYwByAG8AcwBzACwAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAeQAsACAAMQAsACAAdwBpAGQAdABoACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAeAAsACAALAAgADEALAAgADAAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAbABvAGMAawAgAGEAZwBnAHIAZQBnAGEAdABvAHIAXABuACAAIAAgACAAQgBsAG8AYwBrAHMAuwMsACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpACwAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgALAAgACwAIAByACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHcAaQBkAHQAaAAsACAAMQAsACAAMAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABqACwAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAdwBpAGQAdABoACwAIABjACkAIAAqACAAUwBFAFEAVQBFAE4AQwBFACgAZABlAHAAdABoACwAIAAsACAAMQAsACAAMAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsALAAgACAAVABPAEMATwBMACgASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIABpACgAKQAsACAAagAoACkAKQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAGYAdQBuAGMAdABpAG8AbgAoAGIAbABvAGMAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHMAdQBsAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAHQAbwAgAGUAYQBjAGgAIABiAGwAbwBjAGsAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABNAEEAUAAoAGQAbwB3AG4AKAApACwAIABhAGMAcgBvAHMAcwAoACkALAAgAEIAbABvAGMAawBzALsDKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMQAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBvAG8AcgBlAEEAZwBnALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAIAAoAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAKQBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFAAZQByAGYAbwByAG0AcwAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAG8AdgBlAHIAIABNAG8AbwByAGUAIABvAHIAIAB2AG8AbgAgAE4AZQB1AG0AYQBuAG4AIABuAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzACAAdQBzAGkAbgBnACAAYQBuAFwAbgAgACAAIAAgAEUAVABBABEgYwBvAG0AcABhAHQAaQBiAGwAZQAgAGYAdQBuAGMAdABpAG8AbgAgACgAUwBVAE0ALAAgAEEAVgBFAFIAQQBHAEUALAAgAE0AQQBYACwAIABNAEkATgAsACAATQBFAEQASQBBAE4ALAAgAG8AcgAgAGEAIABjAHUAcwB0AG8AbQBcAG4AIAAgACAAIABMAEEATQBCAEQAQQApAC4AIABPAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgBzACAAYwBvAG4AdAByAG8AbAAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAdAB5AHAAZQAgAGEAbgBkACAAaQBmACAAdABoAGUAXABuACAAIAAgACAAYwBlAG4AdABlAHIAIABjAGUAbABsACAAaQBzACAAdABvACAAYgBlACAAaQBuAGMAbAB1AGQAZQBkAC4AXABuAFwAbgBOAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzADoAXABuACAAIAAgACAATQBvAG8AcgBlACAAKAA4ABEgYwBvAG4AbgBlAGMAdABlAGQAKQA6ACAAIAAgACAAIAAgACAAIAB2AG8AbgAgAE4AZQB1AG0AYQBuAG4AIAAoADQAESBjAG8AbgBuAGUAYwB0AGUAZAApADoAXABuACAAIAAgACAAIAAgACAAIAAxACAAIAAyACAAIAAzACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAA0ACAAIABDACAAIAA2ACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADIAIAAgAEMAIAAgADMAXABuACAAIAAgACAAIAAgACAAIAA3ACAAIAA4ACAAIAA5ACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADQAXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgACAAIAAgACAAIAAgACAALQAgADIARAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQBfADIARAAuAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgACAAIAAgACAAIAAgACAALQAgAEUAVABBACAAbwByACAATABBAE0AQgBEAEEAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABmAHUAbgBjAHQAaQBvAG4ALgBcAG4AIAAgACAAIABbAEkAcwB2AG8AbgBOAGUAdQBtAGEAbgBuAD8AXQAgAC0AIABUAFIAVQBFACAAkiEgAHUAcwBlACAAdgBvAG4AIABOAGUAdQBtAGEAbgBuACAAbgBlAGkAZwBoAGIAbwByAGgAbwBvAGQALgBcAG4AIAAgACAAIABbAG8AbQBpAHQAXwBjAGUAbgB0AGUAcgBdACAAIAAgAC0AIABUAFIAVQBFACAAkiEgAGUAeABjAGwAdQBkAGUAIABjAGUAbgB0AGUAcgAgAGMAZQBsAGwAIABmAHIAbwBtACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0AbwBvAHIAZQBBAGcAZwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABbAEkAcwB2AG8AbgBOAGUAdQBtAGEAbgBuAD8AXQAsAFwAbgAgACAAIAAgAFsAbwBtAGkAdABfAGMAZQBuAHQAZQByAF0ALABcAG4AXABuAEkARgAoAFQAWQBQAEUAKABhAHIAcgBhAHkAXwAyAEQAKQAgADwAPgAgADYANAAsAFwAIgAjAGEAcgByAGEAeQBfADIARAAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABUAFkAUABFACgAZgB1AG4AYwB0AGkAbwBuACkAIAA8AD4AIAAxADIAOAAgACwAXAAiACMARQBUAEEAIABGAFUATgBDAFQASQBPAE4AIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIABJAHMAdgBvAG4ATgBlAHUAbQBhAG4AbgA/ACwAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAEkAcwB2AG8AbgBOAGUAdQBtAGEAbgBuAD8AKQApACwAXABuACAAIAAgACAAbwBtAGkAdABfAGMAZQBuAHQAZQByACwAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABvAG0AaQB0AF8AYwBlAG4AdABlAHIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaABlAGkAZwBoAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAAUABhAGQAIABhAHIAcgBhAHkAXwAyAEQAIAB3AGkAdABoACAAXAAiAG8AbQBpAHQAXAAiACAAdABvACAAcwBhAGYAZQBsAHkAIABkAHIAbwBwACAAZQBkAGcAZQBzAFwAbgAgACAAIAAgAE0ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFwAIgBvAG0AaQB0AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAXAAiAG8AbQBpAHQAXAAiACwAIABhAHIAcgBhAHkAXwAyAEQALAAgAFwAIgBvAG0AaQB0AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AbQBpAHQAXAAiACkALABcAG4AXABuACAAIAAgACAALwAvACAARABpAHIAZQBjAHQAaQBvAG4AYQBsACAAdgBlAGMAdABvAHIAcwAgACgAZgBsAGEAdAB0AGUAbgBlAGQAKQBcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAVABPAEMATwBMACgARABSAE8AUAAoAE0ALAAgAC0AMgAsACAALQAyACkAKQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATgBXAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgACwAIAAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgAKQApACwAIAAgACAAIAAgACAAIAAvAC8AIABOAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgACwAIAAyACkALAAgAGgAZQBpAGcAaAB0ACkAKQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAEUAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgAKQApACwAIAAgACAAIAAgAC8ALwAgAFcAXABuACAAIAAgACAAYwBlAG4AdABlAHIALAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAAMQApACwAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACkAKQAsACAAIAAgACAAIAAgAC8ALwAgAEMAXABuACAAIAAgACAAZgAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAAMQApACwAIABoAGUAaQBnAGgAdAAsACAALQB3AGkAZAB0AGgAKQApACwAIAAgACAAIAAgAC8ALwAgAEUAXABuACAAIAAgACAAZwAsACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAC0AaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACkALAAgACAAIAAgAC8ALwAgAFMAVwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAtADEAKQAsACAALQBoAGUAaQBnAGgAdAAsACAALQB3AGkAZAB0AGgAKQApACwAIAAgACAALwAvACAAUwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAVABPAEMATwBMACgAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAxACkALAAgAC0AaABlAGkAZwBoAHQALAAgAC0AdwBpAGQAdABoACkAKQAsACAAIAAgACAALwAvACAAUwBFAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZAAgAGEAcwBzAGUAbQBiAGwAaQBlAHMAXABuACAAIAAgACAATQBvAG8AcgBlAF8AbgBvAF8AYwBlAG4AdABlAHIALAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsAGIALABjACwAZAAsAGYALABnACwAaAAsAGkAKQAsAFwAbgAgACAAIAAgAE0AbwBvAHIAZQBfAHcAaQB0AGgAXwBjAGUAbgB0AGUAcgAsACAAIAAgACAAIABIAFMAVABBAEMASwAoAGEALABiACwAYwAsAGQALABjAGUAbgB0AGUAcgAsAGYALABnACwAaAAsAGkAKQAsAFwAbgBcAG4AIAAgACAAIAB2AG8AbgBfAG4AbwBfAGMAZQBuAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABiACwAZAAsAGYALABoACkALABcAG4AIAAgACAAIAB2AG8AbgBfAHcAaQB0AGgAXwBjAGUAbgB0AGUAcgAsACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABiACwAZAAsAGYALABoACwAYwBlAG4AdABlAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAGcAZwByAGUAZwBhAHQAbwByAFwAbgAgACAAIAAgAEEAZwBnAHIAZQBnAGEAdABlALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHYALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AKABUAE8AQwBPAEwAKABJAEYAUwAoAHYALAAgAHYAKQAsADIAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBwAHAAbAB5ACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAdgBvAG4ATgBlAHUAbQBhAG4AbgA/ACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbwBtAGkAdABfAGMAZQBuAHQAZQByACwAQgBZAFIATwBXACgAdgBvAG4AXwBuAG8AXwBjAGUAbgB0AGUAcgAsACAAQQBnAGcAcgBlAGcAYQB0AGUAuwMpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKAB2AG8AbgBfAHcAaQB0AGgAXwBjAGUAbgB0AGUAcgAsACAAQQBnAGcAcgBlAGcAYQB0AGUAuwMpACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABvAG0AaQB0AF8AYwBlAG4AdABlAHIALABCAFkAUgBPAFcAKABNAG8AbwByAGUAXwBuAG8AXwBjAGUAbgB0AGUAcgAsACAAQQBnAGcAcgBlAGcAYQB0AGUAuwMpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABCAFkAUgBPAFcAKABNAG8AbwByAGUAXwB3AGkAdABoAF8AYwBlAG4AdABlAHIALAAgAEEAZwBnAHIAZQBnAGEAdABlALsDKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAaABhAHAAZQAgAGIAYQBjAGsAIAB0AG8AIABhAHIAcgBhAHkAXwAyAEQAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABXAFIAQQBQAFIATwBXAFMAKABhAGcAZwAsACAAdwBpAGQAdABoACkALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADEAMgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAE0AbwBvAHIAZQBTAGUAbABlAGMAdAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZABzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGUAbABlAGMAdABzACAAYQAgAHMAcABlAGMAaQBmAGkAYwAgAG4AZQBpAGcAaABiAG8AcgAgACgAMQATIDkAKQAgAGYAcgBvAG0AIAB0AGgAZQAgAE0AbwBvAHIAZQAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAZgBvAHIAIABlAGEAYwBoAFwAbgAgACAAIAAgAGUAbABlAG0AZQBuAHQAIABpAG4AIABhACAAYQByAHIAYQB5AF8AMgBEAC4AIABOAGUAaQBnAGgAYgBvAHIAIABpAG4AZABlAHgAIAA1ACAAcgBlAHQAdQByAG4AcwAgAHQAaABlACAAYwBlAG4AdABlAHIAIABjAGUAbABsAC4AXABuAFwAbgBNAG8AbwByAGUAIABOAGUAaQBnAGgAYgBvAHIAaABvAG8AZAA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgACAAIAAyACAAIAAgADMAXABuACAAIAAgACAAIAAgACAAIAA0ACAAIAAgAEMAIAAgACAANgBcAG4AIAAgACAAIAAgACAAIAAgADcAIAAgACAAOAAgACAAIAA5AFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAAIAAtACAAMgBEACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AF8AMgBEAC4AXABuACAAIAAgACAAbgBlAGkAZwBoAGIAbwByACAAIAAgACAALQAgAEkAbgB0AGUAZwBlAHIAIAAxABMgOQAgAGkAbgBkAGkAYwBhAHQAaQBuAGcAIAB3AGgAaQBjAGgAIABuAGUAaQBnAGgAYgBvAHIAIAB0AG8AIAByAGUAdAB1AHIAbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAG8AbwByAGUAUwBlAGwAZQBjAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAbgBlAGkAZwBoAGIAbwByACwAXABuAFwAbgBJAEYAKABUAFkAUABFACgAYQByAHIAYQB5AF8AMgBEACkAIAA8AD4AIAA2ADQALABcACIAIwBhAHIAcgBhAHkAXwAyAEQAIQBcACIALABcAG4AXABuACAAIAAgACAASQBGACgATgBPAFQAKABBAE4ARAAoAG4AZQBpAGcAaABiAG8AcgAgAD4APQAgADEALAAgAG4AZQBpAGcAaABiAG8AcgAgADwAPQAgADkALAAgAE4ATwBUACgASQBTAFQARQBYAFQAKABuAGUAaQBnAGgAYgBvAHIAKQApACkAKQAsAFwAIgAjAE4ARQBJAEcASABCAE8AUgAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBkACAAYQByAHIAYQB5AF8AMgBEACAAdwBpAHQAaAAgAHoAZQByAG8AcwAgACgAbgBvACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAbgBlAGUAZABlAGQAKQBcAG4AIAAgACAAIABoAHAAYQBkACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAAwACwAIAAsACAAdwBpAGQAdABoACAAKwAgADIALAAgADAAKQAsAFwAbgAgACAAIAAgAHYAcABhAGQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoADAALAAgAGgAZQBpAGcAaAB0ACwAIAAsACAAMAApACwAXABuACAAIAAgACAATQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAaABwAGEAZAAsACAASABTAFQAQQBDAEsAKAB2AHAAYQBkACwAIABhAHIAcgBhAHkAXwAyAEQALAAgAHYAcABhAGQAKQAsACAAaABwAGEAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AbwBvAHIAZQAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAZQB4AHQAcgBhAGMAdABpAG8AbgBcAG4AIAAgACAAIABhACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAE0ALAAgAC0AMgAsACAALQAyACkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAE4AVwBcAG4AIAAgACAAIABiACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAsACAAMQApACwAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACkALAAgACAAIAAgACAAIAAgAC8ALwAgAE4AXABuACAAIAAgACAAYwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAALAAgADIAKQAsACAAaABlAGkAZwBoAHQAKQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAEUAXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAB3AGkAZAB0AGgAKQAsACAAIAAgACAAIAAvAC8AIABXAFwAbgAgACAAIAAgAGMAZQBuAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgADEALAAgADEAKQAsACAAaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACwAIAAgACAAIAAgACAALwAvACAAQwBcAG4AIAAgACAAIABmACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAEQAUgBPAFAAKABNACwAIAAxACwAIAAxACkALAAgAGgAZQBpAGcAaAB0ACwAIAAtAHcAaQBkAHQAaAApACwAIAAgACAAIAAgAC8ALwAgAEUAXABuACAAIAAgACAAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAC0AaABlAGkAZwBoAHQALAAgAHcAaQBkAHQAaAApACwAIAAgACAAIAAvAC8AIABTAFcAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABEAFIATwBQACgATQAsACAAMQAsACAALQAxACkALAAgAC0AaABlAGkAZwBoAHQALAAgAC0AdwBpAGQAdABoACkALAAgACAAIAAvAC8AIABTAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgARABSAE8AUAAoAE0ALAAgADEALAAgADEAKQAsACAALQBoAGUAaQBnAGgAdAAsACAALQB3AGkAZAB0AGgAKQAsACAAIAAgACAALwAvACAAUwBFAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAIABhAGwAbAAgADkAIABuAGUAaQBnAGgAYgBvAHIAcwAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5AFwAbgAgACAAIAAgAE0AbwBvAHIAZQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGEALAAgAGIALAAgAGMALAAgAGQALAAgAGMAZQBuAHQAZQByACwAIABmACwAIABnACwAIABoACwAIABpACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AcAB1AHQAZQAgAHMAdABhAHIAdABpAG4AZwAgAGMAbwBsAHUAbQBuACAAZgBvAHIAIAB0AGgAZQAgAGMAaABvAHMAZQBuACAAbgBlAGkAZwBoAGIAbwByAFwAbgAgACAAIAAgAHMAdABhAHIAdAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAG4AZQBpAGcAaABiAG8AcgAgAC0AIAAxACkAIAAqACAAdwBpAGQAdABoACAAKwAgADEALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIAB0AGgAZQAgAG4AZQBpAGcAaABiAG8AcgAgAGIAbABvAGMAawBcAG4AIAAgACAAIABzAGUAbABlAGMAdABfAG4AZQBpAGcAaABiAG8AcgAsACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAE0AbwBvAHIAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAHcAaQBkAHQAaAAsACAAcwB0AGEAcgB0ACkAKQAsAFwAbgBcAG4AIAAgACAAIABzAGUAbABlAGMAdABfAG4AZQBpAGcAaABiAG8AcgBcAG4AKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEcAUgAxADMAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABIAGkAcwB0AG8AZwByAGEAbQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABTAHQAYQB0AGkAcwB0AGkAYwBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABoAGkAcwB0AG8AZwByAGEAbQAgAHUAcwBpAG4AZwAgAGEAdQB0AG8AbQBhAHQAaQBjACAAYgBpAG4AbgBpAG4AZwAgAHIAdQBsAGUAcwAgACgAUwB0AHUAcgBnAGUAcwAsACAAUgBpAGMAZQAsAFwAbgAgACAAIAAgAFMAYwBvAHQAdAAsACAARgByAGUAZQBkAG0AYQBuACkAIABkAGUAcABlAG4AZABpAG4AZwAgAG8AbgAgAHMAYQBtAHAAbABlACAAcwBpAHoAZQAgAGEAbgBkACAAcwBrAGUAdwBuAGUAcwBzAC4AIABTAHUAcABwAG8AcgB0AHMAIABhAG4AXABuACAAIAAgACAAbwBwAHQAaQBvAG4AYQBsACAAZgBpAHgAZQBkACAAYgBpAG4AIAB3AGkAZAB0AGgAIABhAG4AZAAgAGEAbgAgAG8AcAB0AGkAbwBuAGEAbAAgAFAAYQByAGUAdABvACAAKABjAHUAbQB1AGwAYQB0AGkAdgBlACAAJQApACAAYwBvAGwAdQBtAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAgAE4AdQBtAGUAcgBpAGMAIABhAHIAcgBhAHkAIAAoADEARAAgAG8AcgAgADIARAApAC4AXABuACAAIAAgACAAWwBiAGkAbgBfAHcAaQBkAHQAaABdACAAIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAeABlAGQAIABiAGkAbgAgAHcAaQBkAHQAaAAgACgAMAAgADwAIAB3AGkAZAB0AGgAIABkIiAAMQAwADAAMAApAC4AXABuACAAIAAgACAAWwBpAG4AYwBsAHUAZABlAF8AUABhAHIAZQB0AG8AXQAgAC0AIABUAFIAVQBFACAAkiEgAGkAbgBjAGwAdQBkAGUAIABjAHUAbQB1AGwAYQB0AGkAdgBlACAAJQAgAGMAbwBsAHUAbQBuAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgACMAVgBBAEwAVQBFACEAIABpAGYAIABmAGUAdwBlAHIAIAB0AGgAYQBuACAAMgAgAHYAYQBsAHUAZQBzACAAYQByAGUAIABzAHUAcABwAGwAaQBlAGQALgBcAG4AIAAgACAAIAAiICAAQwBhAHAAcwAgAHQAbwB0AGEAbAAgAGIAaQBuAHMAIABhAHQAIAAxADAAMAAuAFwAbgAgACAAIAAgACIgIABJAGYAIABiAGkAbgBfAHcAaQBkAHQAaAAgAGkAcwAgAHMAdQBwAHAAbABpAGUAZAAsACAAYQB1AHQAbwBtAGEAdABpAGMAIAByAHUAbABlAHMAIABhAHIAZQAgAGIAeQBwAGEAcwBzAGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBIAGkAcwB0AG8AZwByAGEAbQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGIAaQBuAF8AdwBpAGQAdABoAF0ALABcAG4AIAAgACAAIABbAGkAbgBjAGwAdQBkAGUAXwBQAGEAcgBlAHQAbwBdACwAXABuAFwAbgBcAG4ASQBGACgAQwBPAFUATgBUACgAYQByAHIAYQB5ACkAIAA8AD0AIAAxACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABiAGkAbgBfAHcAaQBkAHQAaAApACkALABPAFIAKABiAGkAbgBfAHcAaQBkAHQAaAAgADwAIAAwACwAIABiAGkAbgBfAHcAaQBkAHQAaAAgAD4AIAAxADAAMAAwACkAKQAsAFwAIgAjAEIASQBOAC0AVwBJAEQAVABIACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFMAYQBtAHAAbABlACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuACAAIAAgACAAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAFMAbQBhAGwAbABEAGEAdABhAD8ALAAgACAAIAAgACAAbgAgADwAIAAyADAAMAAsAFwAbgAgACAAIAAgAEEAZABkAF8AUABhAHIAZQB0AG8APwAsACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGkAbgBjAGwAdQBkAGUAXwBQAGEAcgBlAHQAbwApACkALABcAG4AXABuACAAIAAgACAAbQBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAbQBhAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAcgBhAG4AZwBlACwAIAAgACAAIAAgACAAIAAgACAAIABtAGEAeAAgAC0AIABtAGkAbgAsAFwAbgAgACAAIAAgAGkAcQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUQBVAEEAUgBUAEkATABFACgAYQByAHIAYQB5ACwAIAAzACkAIAAtACAAUQBVAEEAUgBUAEkATABFACgAYQByAHIAYQB5ACwAIAAxACkALABcAG4AXABuACAAIAAgACAAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEsARQBXACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABJAHMAUwBrAGUAdwBlAGQAPwAsACAAIAAgACAAIAAgAEkARgAoAFMAbQBhAGwAbABEAGEAdABhAD8ALAAgAEYAQQBMAFMARQAsACAAQQBCAFMAKABzACkAIAA+ACAAMAAuADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIABmAGkAeABlAGQAIABiAGkAbgAgAHcAaQBkAHQAaABcAG4AIAAgACAAIABJAHMARgBpAHgAZQBkAD8ALAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABiAGkAbgBfAHcAaQBkAHQAaAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQB1AHQAbwBtAGEAdABpAGMAIABiAGkAbgBuAGkAbgBnACAAcgB1AGwAZQBzAFwAbgAgACAAIAAgAFMAdAB1AHIAZwBlACwAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAEwATwBHACgAbgAsACAAMgApACAAKwAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgAFMAUgBSACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAFMAUQBSAFQAKABuACkALAAgADEAKQAsAFwAbgAgACAAIAAgAFIAaQBjAGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoADIAIAAqACAAbgBeACgAMQAvADMAKQAsACAAMQApACwAXABuACAAIAAgACAAUwBjAG8AdAB0ACwAIAAgACAAIAAgACAAIAAgACAAIABDAEUASQBMAEkATgBHACgAMwAuADUAIAAqACAAUwBUAEQARQBWAC4AUAAoAGEAcgByAGEAeQApACAALwAgAG4AXgAoADEALwAzACkALAAgADEAKQAsAFwAbgAgACAAIAAgAEYAcgBlAGUAZABtAGEAbgAsACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoADIAIAAqACAAaQBxAHIAIAAvACAAbgBeACgAMQAvADMAKQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAGYAaQB4AGUAZAAsACAAIAAgACAAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAHIAYQBuAGcAZQAgAC8AIABiAGkAbgBfAHcAaQBkAHQAaAAsACAAMQAgAC8AIABiAGkAbgBfAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQBuACAAYwBvAHUAbgB0ACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMARgBpAHgAZQBkAD8ALABmAGkAeABlAGQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbgAgADwAPQAgADMAMAAsAE0AQQBYACgAUwB0AHUAcgBnAGUALAAgAFIAaQBjAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAGsAZQB3AGUAZAA/ACwATQBJAE4AKABGAHIAZQBlAGQAbQBhAG4ALAAgADEANQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFMAYwBvAHQAdAAsACAAMQA1ACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQB2AG8AaQBkACAAcwBpAG4AZwBsAGUALQBiAGkAbgAgAG8AdQB0AHAAdQB0ADsAIABjAGEAcAAgAGEAdAAgADEAMAAwAFwAbgAgACAAIAAgAGsAXwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABJAEYAKABrACAAPQAgADEALAAgADUALAAgAGsAKQAsACAAMQAwADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGkAbgAgAGkAbgB0AGUAcgB2AGEAbABcAG4AIAAgACAAIABpAG4AdABlAHIAdgBhAGwALAAgACAAIAAgACAAIAAgAEkARgAoAHIAYQBuAGcAZQAgAD0AIAAwACwAIAAxACwAIABNAEEAWAAoAHIAYQBuAGcAZQAgAC8AIABrAF8ALAAgADAALgAxACkAKQAsAFwAbgAgACAAIAAgAGIAaQBuAF8AdQBwAHAAZQByACwAIAAgACAAIAAgACAAQwBFAEkATABJAE4ARwAoAG0AYQB4ACwAIABpAG4AdABlAHIAdgBhAGwAKQAsAFwAbgAgACAAIAAgAGIAaQBuAF8AbABvAHcAZQByACwAIAAgACAAIAAgACAARgBMAE8ATwBSACgAbQBpAG4ALAAgAGkAbgB0AGUAcgB2AGEAbAApACwAXABuAFwAbgAgACAAIAAgAGIAaQBuAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAMQAgACsAIAAoAGIAaQBuAF8AdQBwAHAAZQByACAALQAgAGIAaQBuAF8AbABvAHcAZQByACkAIAAvACAAaQBuAHQAZQByAHYAYQBsACwALABiAGkAbgBfAGwAbwB3AGUAcgAsAGkAbgB0AGUAcgB2AGEAbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQBuACAAbABhAGIAZQBsAHMAXABuACAAIAAgACAAYgBpAG4AXwBzAHQAYQByAHQALAAgACAAIAAgACAAIABEAFIATwBQACgAYgBpAG4AXwBhAHIAcgAsACAALQAxACkALABcAG4AIAAgACAAIABiAGkAbgBfAGUAbgBkACwAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABiAGkAbgBfAGEAcgByACwAIAAxACkALABcAG4AXABuACAAIAAgACAAYgBpAG4AXwBoAGUAYQBkAGUAcgAsACAAIAAgACAAIAB7AFwAIgBTAHQAYQByAHQAXAAiACwAIABcACIARQBuAGQAXAAiACwAIABcACIAVABvAHQAYQBsAFwAIgB9ACwAXABuACAAIAAgACAAYgBpAG4AXwBsAGEAYgBlAGwAcwAsACAAIAAgACAAIABIAFMAVABBAEMASwAoAFYAUwBUAEEAQwBLACgAXAAiADwAXAAiACwAIABiAGkAbgBfAHMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVABBAEsARQAoAGIAaQBuAF8AcwB0AGEAcgB0ACwAIAAxACkALAAgAGIAaQBuAF8AZQBuAGQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAcgBlAHEAdQBlAG4AYwBpAGUAcwAgAGEAbgBkACAAUABhAHIAZQB0AG8AXABuACAAIAAgACAAZgByAGUAcQAsACAAIAAgACAAIAAgACAAIAAgACAAIABEAFIATwBQACgARgBSAEUAUQBVAEUATgBDAFkAKABhAHIAcgBhAHkALAAgAGIAaQBuAF8AYQByAHIAKQAsACAALQAxACkALABcAG4AIAAgACAAIABQAGEAcgBlAHQAbwAsACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAGYAcgBlAHEALAAgAEwAQQBNAEIARABBACgAdgAsACAAUABFAFIAQwBFAE4AVABPAEYAKAB2ACwAIABmAHIAZQBxACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAGEAcwBzAGUAbQBiAGwAeQBcAG4AIAAgACAAIABzAHQAYQBjAGsALAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAYgBpAG4AXwBoAGUAYQBkAGUAcgAsACAASABTAFQAQQBDAEsAKABiAGkAbgBfAGwAYQBiAGUAbABzACwAIABmAHIAZQBxACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEEAZABkAF8AUABhAHIAZQB0AG8APwAsAFMATwBSAFQAKABIAFMAVABBAEMASwAoAHMAdABhAGMAawAsAFYAUwBUAEEAQwBLACgAXAAiAEMAdQBtAHUAbABhAHQAaQB2AGUAIAAlAFwAIgAsACAAUABhAHIAZQB0AG8AKQApACwAMwAsAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAGMAawApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBHAFIAMQA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBvAGQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABTAHQAYQB0AGkAcwB0AGkAYwBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAdAB1AHIAbgBzACAAYQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAHQAaABlACAAbQBvAHMAdAAgAGYAcgBlAHEAdQBlAG4AdABsAHkAIABvAGMAYwB1AHIAcgBpAG4AZwAgAHYAYQBsAHUAZQBzACAAbwByAFwAbgAgACAAIAAgAHQAZQB4AHQAIABlAG4AdAByAGkAZQBzACAAaQBuACAAYQBuACAAYQByAHIAYQB5AC4AIABTAHUAcABwAG8AcgB0AHMAIABhAG4AIABvAHAAdABpAG8AbgBhAGwAIAB0AG8AdABhAGwAcwAgAGMAbwBsAHUAbQBuACAAcwBoAG8AdwBpAG4AZwBcAG4AIAAgACAAIAB0AGgAZQAgAGMAbwB1AG4AdAAgAG8AZgAgAGUAYQBjAGgAIABtAG8AZABlAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAQQByAHIAYQB5ACAAKAAxAEQAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAFsAaQBuAGMAbAB1AGQAZQBfAHQAbwB0AGEAbABzAF0ALQAgAFQAUgBVAEUAIACSISAAaQBuAGMAbAB1AGQAZQAgAGMAbwB1AG4AdABzACAAbwBmACAAZgByAGUAcQB1AGUAbgB0ACAAdgBhAGwAdQBlAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAGYAIAB0AGgAZQAgAGEAcgByAGEAeQAgAGMAbwBuAHQAYQBpAG4AcwAgAG4AbwAgAHQAZQB4AHQALAAgAE0ATwBEAEUALgBNAFUATABUACAAaQBzACAAdQBzAGUAZAAgAGYAbwByACAAbgB1AG0AZQByAGkAYwAgAG0AbwBkAGUALgBcAG4AIAAgACAAIAAiICAASQBmACAAbgBvACAAcgBlAHAAZQBhAHQAcwAgAGUAeABpAHMAdAAsACAAcgBlAHQAdQByAG4AcwAgAFwAIgAjAE4ATwAtAFIARQBQAEUAQQBUAFMAIQBcACIALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ATQBvAGQAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGkAbgBjAGwAdQBkAGUAXwB0AG8AdABhAGwAcwBdACwAXABuAFwAbgBJAEYAKABDAE8AVQBOAFQAKAAtAC0ASQBTAFQARQBYAFQAKABhAHIAcgBhAHkAKQApACAAPQAgADAALABNAE8ARABFAC4ATQBVAEwAVAAoAGEAcgByAGEAeQApACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE0AZQBzAHMAYQBnAGUAIABmAG8AcgAgAG4AbwAgAHIAZQBwAGUAYQB0AHMAXABuACAAIAAgACAAbQBzAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwBOAE8ALQBSAEUAUABFAEEAVABTACEAXAAiACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAIABhAG4AZAAgAGMAbwBtAHAAdQB0AGUAIABtAG8AZABlACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABWACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAE8ARABFAC4ATQBVAEwAVAAoAFgATQBBAFQAQwBIACgAVgAsACAAVgApACkALABcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAFMATwBSAFQAKABJAEYARQBSAFIATwBSACgASQBOAEQARQBYACgAVgAsACAAaQApACwAIABtAHMAZwApACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsAHMAIABmAG8AcgAgAHIAZQBwAGUAYQB0AGUAZAAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgAGsAZQBlAHAALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgAWABNAEEAVABDAEgAKABWACwAIAByAGUAcwB1AGwAdAApACkALABcAG4AIAAgACAAIAB0AG8AdABhAGwAcwAsACAAIAAgACAAIAAgACAAIAAgAEcAUgBPAFUAUABCAFkAKABWACwAIABWACwAIABDAE8AVQBOAFQAQQAsACAAMAAsACAAMAAsACAALAAgAGsAZQBlAHAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAbABpAHYAZQByACAAdABvAHQAYQBsAHMAIABpAGYAIAByAGUAcQB1AGUAcwB0AGUAZABcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgAaQBuAGMAbAB1AGQAZQBfAHQAbwB0AGEAbABzACwAIAByAGUAcwB1AGwAdAAgADwAPgAgAG0AcwBnACkALAB0AG8AdABhAGwAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcwB1AGwAdAApACwAXABuAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBSADEANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFoAbwBuAGUAUwB0AGEAdAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAKABTAHQAYQB0AGkAcwB0AGkAYwBzACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABIAGkAcwB0AG8AZwByAGEAbQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQQBnAGcAcgBlAGcAYQB0AGUAcwAgAHYAYQBsAHUAZQBzACAAYgB5ACAAXAAiAHoAbwBuAGUAcwBcACIAIABkAGUAdABlAHIAbQBpAG4AZQBkACAAYgB5ACAASABpAHMAdABvAGcAcgBhAG0AuwMuACAAVABoAGUAIABiAGkAbgAgAHcAaQBkAHQAaAAgAGkAcwBcAG4AIAAgACAAIABjAG8AbQBwAHUAdABlAGQAIABhAHMAIAAxADAAXgBtACAAdwBoAGUAcgBlACAAbQAgAGkAcwAgAHQAaABlACAAbQBvAHMAdAAgAGYAcgBlAHEAdQBlAG4AdAAgAGkAbgB0AGUAZwBlAHIAIABMAE8ARwAgAG0AYQBnAG4AaQB0AHUAZABlACAAbwBmAFwAbgAgACAAIAAgAHQAaABlACAAdgBhAGwAdQBlAHMALgAgAFMAdQBwAHAAbwByAHQAcwAgAEUAVABBACAAZgB1AG4AYwB0AGkAbwBuAHMAIABhAG4AZAAgAGMAdQBzAHQAbwBtACAATABBAE0AQgBEAEEAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABOAHUAbQBlAHIAaQBjACAAYQByAHIAYQB5ACAAKAAxAEQAIABvAHIAIAAyAEQAKQAuAFwAbgAgACAAIAAgAFsAZgB1AG4AYwB0AGkAbwBuAF0AIAAgAC0AIABFAFQAQQAgAG8AcgAgAEwAQQBNAEIARABBACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAZgB1AG4AYwB0AGkAbwBuACAAKABkAGUAZgBhAHUAbAB0ACAAUwBVAE0AKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIAByAGUAdAB1AHIAbgAgAGYAdQBuAGMAdABpAG8AbgAoAGcAcgBpAGQAKQAuAFwAbgAgACAAIAAgACIgIABOAG8AbgARIG4AdQBtAGUAcgBpAGMAIABnAHIAaQBkAHMAIAByAGUAdAB1AHIAbgAgACMAVgBBAEwAVQBFACEALgBcAG4AIAAgACAAIAAiICAAWgBvAG4AZQBzACAAYQByAGUAIABhAHMAcwBpAGcAbgBlAGQAIAB2AGkAYQAgAEgAaQBzAHQAbwBnAHIAYQBtALsDIAB1AHMAaQBuAGcAIABhAHUAdABvAG0AYQB0AGkAYwAgAGIAaQBuAG4AaQBuAGcALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AWgBvAG4AZQBTAHQAYQB0ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIABhAGcAZwByAGUAZwBhAHQAaQBvAG4AIABmAHUAbgBjAHQAaQBvAG4AXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgB1AG4AYwB0AGkAbwBuACkALAAgAFMAVQBNACwAIABmAHUAbgBjAHQAaQBvAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAtAC0ALQAgAFYAYQBsAGkAZABhAHQAaQBvAG4AIAAtAC0ALQBcAG4AIAAgACAAIABJAHMATgBvAG4ATgB1AG0APwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABJAFMAVABFAFgAVAAoAGcAcgBpAGQAKQApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAG4APwAsACAAIAAgACAAIAAgACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAUgBPAFcAUwAoAGcAcgBpAGQAKQA9ADEALAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkAPQAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAHMATgBvAG4ATgB1AG0APwAsACAAIAAgACAAIAAgACAAIAAgACAAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAbgB2AGEAbABpAGQARgBuAD8ALAAgACAAIAAgACAAXAAiACMARgBVAE4AQwBUAEkATwBOACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAUwBjAGEAbABhAHIAPwAsACAAIABmAHUAbgBjAHQAaQBvAG4AKABnAHIAaQBkACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIABiAGkAbgAgAHcAaQBkAHQAaAAgAGYAcgBvAG0AIABtAGEAZwBuAGkAdAB1AGQAZQBcAG4AIAAgACAAIABtAGEAZwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAE0ATwBEAEUAKABJAE4AVAAoAEwATwBHACgAZwByAGkAZAApACkAKQAsACAAMQApACwAXABuACAAIAAgACAAYgBpAG4AXwB3AGkAZAB0AGgALAAgACAAIAAgACAAIAAgACAAIAAgADEAMAAgAF4AIABtAGEAZwAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABIAGkAcwB0AG8AZwByAGEAbQAgAGIAaQBuAHMAIAAoAGYAaQByAHMAdAAgAGMAbwBsAHUAbQBuACAAbwBuAGwAeQApAFwAbgAgACAAIAAgAGgAaQBzAHQALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgARABSAE8AUAAoAEgAaQBzAHQAbwBnAHIAYQBtALsDKABnAHIAaQBkACwAIABiAGkAbgBfAHcAaQBkAHQAaAApACwAIAAyACkALAAgACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBzAHMAaQBnAG4AIAB6AG8AbgBlAHMAXABuACAAIAAgACAAegBvAG4AZQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBOAEEAKABYAE0AQQBUAEMASAAoAGcAcgBpAGQALAAgAGgAaQBzAHQALAAgAC0AMQApACwAIAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgAGcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKABnAHIAaQBkACkALABcAG4AIAAgACAAIAB6ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAegBvAG4AZQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAAQQBnAGcAcgBlAGcAYQB0AGUAIABiAHkAIAB6AG8AbgBlAFwAbgAgACAAIAAgAGEAZwBnACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABHAFIATwBVAFAAQgBZACgAegAsACAAZwAsACAAZgB1AG4AYwB0AGkAbwBuACwAIAAsACAAMAApACwAXABuACAAIAAgACAAegBvAG4AZQBfAEkARABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABhAGcAZwAsACAALAAgADEAKQAsAFwAbgAgACAAIAAgAGcAcgBpAGQAXwB2AGEAbAB1AGUAcwAsACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQBnAGcALAAgACwAIAAtADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHIAbwBhAGQAYwBhAHMAdAAgAGEAZwBnAHIAZQBnAGEAdABlAGQAIAB2AGEAbAB1AGUAcwAgAGIAYQBjAGsAIAB0AG8AIABnAHIAaQBkACAAcwBoAGEAcABlAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAegBvAG4AZQBzACwAIAB6AG8AbgBlAF8ASQBEAHMALAAgAGcAcgBpAGQAXwB2AGEAbAB1AGUAcwAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAvACAAWwBUAFgAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ALwAvACAALQAtAC0AIwAjACAAMAA3ACAAFCAgAFQAZQB4AHQAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVABoAGkAcwAgAGMAYQB0AGUAZwBvAHIAeQAgAHAAcgBvAHYAaQBkAGUAcwAgAG8AcABlAHIAYQB0AG8AcgBzACAAdABoAGEAdAAgAG8AdgBlAHIAYwBvAG0AZQAgAGMAbwBtAG0AbwBuACAAbABpAG0AaQB0AGEAdABpAG8AbgBzACAAaQBuAFwAbgAgACAAIAAgAEUAeABjAGUAbAAnAHMAIABuAGEAdABpAHYAZQAgAHQAZQB4AHQAIABlAG4AZwBpAG4AZQAgACgAZQAuAGcALgAsACAAVABFAFgAVABTAFAATABJAFQAIABjAGEAbgBuAG8AdAAgAHMAcABpAGwAbAAgADIARAAgAHIAZQBzAHUAbAB0AHMAOwAgAEIAWQBSAE8AVwBcAG4AIAAgACAAIABjAGEAbgBuAG8AdAAgAGQAZQBwAGwAbwB5ACAAUwBPAFIAVAAgAHQAbwAgAGEAbABpAGcAbgAgAGMAbwBsAHUAbQBuAHMAKQAuACAAVABoAGUAcwBlACAAZgB1AG4AYwB0AGkAbwBuAHMAIABlAG4AYQBiAGwAZQAgAHMAdAByAHUAYwB0AHUAcgBhAGwAXABuACAAIAAgACAAYQBsAGkAZwBuAG0AZQBuAHQALAAgAGUAeAB0AHIAYQBjAHQAaQBvAG4ALAAgAGEAbgBkACAAdAByAGEAbgBzAGYAbwByAG0AYQB0AGkAbwBuACAAbwBmACAAdABlAHgAdAAgAGEAcgByAGEAeQBzACwAIABlAHgAdABlAG4AZABpAG4AZwAgAEUAeABjAGUAbAAnAHMAXABuACAAIAAgACAAYwBhAHAAYQBiAGkAbABpAHQAaQBlAHMAIABmAG8AcgAgAGIAbwB0AGgAIAAxAEQAIABhAG4AZAAgADIARAAgAGkAbgBwAHUAdABzAC4AXABuAFwAbgBGAHUAbgBjAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgAFMAbwByAHQAcwAgAGUAYQBjAGgAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAYQBsAHAAaABhAGIAZQB0AGkAYwBhAGwAbAB5AC4AXABuAFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4ARABpAHMAdABpAG4AYwB0ALsDXABuACAAIAAgACAAIAAgACAAIABDAGEAbABsAHMAIABBAGwAaQBnAG4AuwMgAHQAbwAgAHMAbwByAHQAIABhACAAMgBEACAAYQByAHIAYQB5ACwAIAB0AGgAZQBuACAAcgBlAHQAdQByAG4AcwAgAGQAaQBzAHQAaQBuAGMAdAAgAHYAYQBsAHUAZQBzAC4AXABuAFwAbgAgACAAIAAgACIgIABBAGwAaQBnAG4AVQBuAGkAcQB1AGUAuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAYQBsAGwAcwAgAEEAbABpAGcAbgC7AyAAdABvACAAcwBvAHIAdAAgAGEAIAAyAEQAIABhAHIAcgBhAHkALAAgAHQAaABlAG4AIAByAGUAdAB1AHIAbgBzACAAdQBuAGkAcQB1AGUAIAB2AGEAbAB1AGUAcwAuAFwAbgBcAG4AIAAgACAAIAAiICAAQwBvAGEAbABlAHMAYwBlALsDXABuACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABmAGkAcgBzAHQAIABuAG8AbgARIGUAbQBwAHQAeQAgAHYAYQBsAHUAZQAgAGEAYwByAG8AcwBzACAAbQB1AGwAdABpAHAAbABlACAAMgBEACAAYQByAHIAYQB5AHMAIAAoADIAIAB0AG8AIAA0ACAAaQBuAHAAdQB0AHMAKQAuAFwAbgBcAG4AIAAgACAAIAAiICAARQB4AHAAbABvAGQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABhAG4AIABlAHgAcABsAG8AZABlAGQAIABjAGgAYQByAGEAYwB0AGUAcgAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIAAiICAATgB1AG0AYgBlAHIAcwBPAG4AbAB5ALsDXABuACAAIAAgACAAIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABuAHUAbQBlAHIAaQBjACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIAAiICAAVABlAHgAdABPAG4AbAB5ALsDXABuACAAIAAgACAAIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIAB0AGUAeAB0ACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIAAiICAAUwBwAGwAaQB0ALsDXABuACAAIAAgACAAIAAgACAAIABTAHAAbABpAHQAcwAgADEARAAgAHQAZQB4AHQAIABhAHIAcgBhAHkAcwAgAHUAcwBpAG4AZwAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZAAgAGQAZQBsAGkAbQBpAHQAZQByACwAIAB3AGkAdABoACAAZgB1AGwAbAAgADIARAAgAHMAcABpAGwAbAAgAHMAdQBwAHAAbwByAHQALgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABBAGwAaQBnAG4AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABTAHAAbABpAHQAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAbwByAHQAcwAgAGUAYQBjAGgAIAByAG8AdwAgAGEAbABwAGgAYQBiAGUAdABpAGMAYQBsAGwAeQAgACgAZABlAGYAYQB1AGwAdAApACAAbwByACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAdwBoAGUAbgBcAG4AIAAgACAAIABiAHkAXwBjAG8AbAAgAD0AIABUAFIAVQBFAC4AIABPAHIAaQBlAG4AdABhAHQAaQBvAG4AIABpAHMAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAaQBuAHQAZQByAG4AYQBsAGwAeQAgAHMAbwAgAHQAaABlAFwAbgAgACAAIAAgAHMAYQBtAGUAIABwAGkAcABlAGwAaQBuAGUAIABoAGEAbgBkAGwAZQBzACAAYgBvAHQAaAAgAG0AbwBkAGUAcwAuACAAUwBvAHIAdABpAG4AZwAgAGkAcwAgAGwAZQB4AGkAYwBvAGcAcgBhAHAAaABpAGMAXABuACAAIAAgACAAYQBuAGQAIABjAGEAcwBlABEgcwBlAG4AcwBpAHQAaQB2AGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAYgBlACAAYQBsAGkAZwBuAGUAZAAuAFwAbgAgACAAIAAgAFsAYgB5AF8AYwBvAGwAXQAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwALgAgAFQAUgBVAEUAIACSISAAcwBvAHIAdAAgAGUAYQBjAGgAIABjAG8AbAB1AG0AbgAgAHQAbwBwABEgdABvABEgYgBvAHQAdABvAG0ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBtAGkAdAB0AGUAZAAgAJIhIABzAG8AcgB0ACAAZQBhAGMAaAAgAHIAbwB3ACAAbABlAGYAdAARIHQAbwARIHIAaQBnAGgAdAAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABUAEUAWABUAEoATwBJAE4AIAArACAAUwBwAGwAaQB0ALsDIABmAG8AcgAgAGYAYQBzAHQAIAByAG8AdwARIHcAaQBzAGUAIABjAGEAbgBvAG4AaQBjAGEAbABpAHoAYQB0AGkAbwBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEEAbABpAGcAbgC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIABzAG8AcgB0ACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkAcwBSAG8AdwBTAG8AcgB0AD8ALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAYgB5AF8AYwBvAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAgACgAYQBsAHcAYQB5AHMAIABzAG8AcgB0ACAAcgBvAHcAcwApAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsACAAIAAgACAAIAAgAEkARgAoAEkAcwBSAG8AdwBTAG8AcgB0AD8ALAAgAGEAcgByAGEAeQAsACAAVABSAEEATgBTAFAATwBTAEUAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAbwB3ABEgdwBpAHMAZQAgAHMAbwByAHQAIACSISAAcwBjAGEAbABhAHIAIABqAG8AaQBuACAAdwBpAHQAaAAgAGkAbgB2AGkAcwBpAGIAbABlACAAcwBlAHAAYQByAGEAdABvAHIAXABuACAAIAAgACAAaQBuAHYAaQBzACwAIAAgACAAIAAgACAAVQBOAEkAQwBIAEEAUgAoADgAMgA5ADEAKQAsAFwAbgAgACAAIAAgAFIAbwB3AFMAbwByAHQAuwMsACAAIAAgAEwAQQBNAEIARABBACgAdgAsACAAVABFAFgAVABKAE8ASQBOACgAaQBuAHYAaQBzACwAIAAsACAAUwBPAFIAVAAoAHYALAAgACwAIAAsACAAMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgB2AGUAcgB0ACAAZQBhAGMAaAAgAHIAbwB3ACAAdABvACAAYQAgAGoAbwBpAG4AZQBkACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAagBvAGkAbgBlAGQALAAgACAAIAAgACAAQgBZAFIATwBXACgAYQByAHIAYQB5ACwAIABSAG8AdwBTAG8AcgB0ALsDKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAbABpAHQAIABiAGEAYwBrACAAaQBuAHQAbwAgAGMAbwBsAHUAbQBuAHMAXABuACAAIAAgACAAZQB4ACwAIAAgACAAIAAgACAAIAAgACAAUwBwAGwAaQB0ALsDKABqAG8AaQBuAGUAZAAsACAAaQBuAHYAaQBzACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHMAdABvAHIAZQAgAG8AcgBpAGcAaQBuAGEAbAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIABJAEYAKABJAHMAUgBvAHcAUwBvAHIAdAA/ACwAIABlAHgALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAZQB4ACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABBAGwAaQBnAG4ARABpAHMAdABpAG4AYwB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAQQBsAGkAZwBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAGEAbABsAHMAIABBAGwAaQBnAG4AuwMgAHQAbwAgAGEAbABwAGgAYQBiAGUAdABpAGMAYQBsAGwAeQAgAHMAbwByAHQAIABlAGEAYwBoACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAsACAAdABoAGUAbgAgAHIAZQB0AHUAcgBuAHMAXABuACAAIAAgACAAZABpAHMAdABpAG4AYwB0ACAAdgBhAGwAdQBlAHMAIABhAGwAbwBuAGcAIAB0AGgAZQAgAHMAYQBtAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAYgBlACAAYQBsAGkAZwBuAGUAZAAgAGEAbgBkACAAZABlAGQAdQBwAGwAaQBjAGEAdABlAGQALgBcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0AIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsAC4AIABUAFIAVQBFACAAkiEgAG8AcABlAHIAYQB0AGUAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUALgAgAE8AbQBpAHQAdABlAGQAIACSISAAcgBvAHcAESB3AGkAcwBlAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARABJAFMAVABJAE4AQwBUACAAcgBlAG0AbwB2AGUAcwAgAGUAeABhAGMAdAAgAGQAdQBwAGwAaQBjAGEAdABlAHMALgBcAG4AIAAgACAAIAAiICAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQQBsAGkAZwBuAEQAaQBzAHQAaQBuAGMAdAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAZgBsAGEAZwBcAG4AIAAgACAAIABTAG8AcgB0AEIAeQBDAG8AbAA/ACwAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgB5AF8AYwBvAGwAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAbABpAGcAbgBtAGUAbgB0AFwAbgAgACAAIAAgAGEAbABpAGcAbgBlAGQALAAgACAAIAAgAEEAbABpAGcAbgC7AygAYQByAHIAYQB5ACwAIABiAHkAXwBjAG8AbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBzAHQAaQBuAGMAdAAgAHIAZQBtAG8AdgBhAGwAXABuACAAIAAgACAAdQAsACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABhAGwAaQBnAG4AZQBkACwAIABTAG8AcgB0AEIAeQBDAG8AbAA/ACwAIABUAFIAVQBFACkALABcAG4AXABuACAAIAAgACAAdQBcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEEAbABpAGcAbgBVAG4AaQBxAHUAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEEAbABpAGcAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBhAGwAbABzACAAQQBsAGkAZwBuALsDIAB0AG8AIABhAGwAcABoAGEAYgBlAHQAaQBjAGEAbABsAHkAIABzAG8AcgB0ACAAZQBhAGMAaAAgAHIAbwB3ACAAbwByACAAYwBvAGwAdQBtAG4ALAAgAHQAaABlAG4AIAByAGUAdAB1AHIAbgBzAFwAbgAgACAAIAAgAHUAbgBpAHEAdQBlACAAdgBhAGwAdQBlAHMAIABhAGwAbwBuAGcAIAB0AGgAZQAgAHMAYQBtAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4ALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAYgBlACAAYQBsAGkAZwBuAGUAZAAgAGEAbgBkACAAZABlAGQAdQBwAGwAaQBjAGEAdABlAGQALgBcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0AIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsAC4AIABUAFIAVQBFACAAkiEgAG8AcABlAHIAYQB0AGUAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUALgAgAE8AbQBpAHQAdABlAGQAIACSISAAcgBvAHcAESB3AGkAcwBlAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBOAEkAUQBVAEUAIAByAGUAbQBvAHYAZQBzACAAcgBlAHAAZQBhAHQAZQBkACAAcgBvAHcAcwAvAGMAbwBsAHUAbQBuAHMAIABiAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAZgBpAHIAcwB0ACAAbwBjAGMAdQByAHIAZQBuAGMAZQBzAC4AXABuACAAIAAgACAAIiAgAE8AcgBpAGUAbgB0AGEAdABpAG8AbgAgAGkAcwAgAHAAcgBlAHMAZQByAHYAZQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEEAbABpAGcAbgBVAG4AaQBxAHUAZQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGIAeQBfAGMAbwBsAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAZgBsAGEAZwBcAG4AIAAgACAAIABTAG8AcgB0AEIAeQBDAG8AbAA/ACwAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgB5AF8AYwBvAGwAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAbABpAGcAbgBtAGUAbgB0AFwAbgAgACAAIAAgAGEAbABpAGcAbgBlAGQALAAgACAAIAAgAEEAbABpAGcAbgC7AygAYQByAHIAYQB5ACwAIABiAHkAXwBjAG8AbAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFUAbgBpAHEAdQBlACAAcgBlAG0AbwB2AGEAbABcAG4AIAAgACAAIAB1ACwAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAGEAbABpAGcAbgBlAGQALAAgAFMAbwByAHQAQgB5AEMAbwBsAD8AKQAsAFwAbgBcAG4AIAAgACAAIAB1AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQwBvAGEAbABlAHMAYwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAZgBpAHIAcwB0ACAAbgBvAG4AESBlAG0AcAB0AHkAIAB2AGEAbAB1AGUAIABhAGMAcgBvAHMAcwAgAG0AdQBsAHQAaQBwAGwAZQAgADIARAAgAGEAcgByAGEAeQBzACAAKAAyACAAdABvACAANAAgAGkAbgBwAHUAdABzACkALABcAG4AIAAgACAAIABlAHYAYQBsAHUAYQB0AGUAZAAgAGkAbgAgAHAAcgBpAG8AcgBpAHQAeQAgAG8AcgBkAGUAcgA6AFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGEAcgByAGEAeQBfADEAIACSISAAYQByAHIAYQB5AF8AMgAgAJIhIABhAHIAcgBhAHkAXwAzACAAkiEgAGEAcgByAGEAeQBfADQAIACSISAAZgBpAGwAbABfAHYAYQBsAHUAZQBcAG4AXABuACAAIAAgACAAQQAgAGMAZQBsAGwAIABpAHMAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAXAAiAGUAbQBwAHQAeQBcACIAIABpAGYAIABpAHQAIABtAGEAdABjAGgAZQBzACAAYQBuAHkAIABvAGYAIAB0AGgAZQAgAGYAbwBsAGwAbwB3AGkAbgBnADoAXABuACAAIAAgACAAIAAgACAAIAAiICAATABFAE4AKABjAGUAbABsACkAIAA9ACAAMABcAG4AIAAgACAAIAAgACAAIAAgACIgIABjAGUAbABsACAAPQAgAEYAQQBMAFMARQBcAG4AIAAgACAAIAAgACAAIAAgACIgIABjAGUAbABsACAAPQAgAGkAZwBuAG8AcgBlACAAIAAgACgAdQBzAGUAcgARIHMAcABlAGMAaQBmAGkAZQBkACkAXABuAFwAbgAgACAAIAAgAEUAbQBwAHQAeQAgAGMAZQBsAGwAcwAgAGEAcgBlACAAcwBrAGkAcABwAGUAZAAgAHcAaABlAG4AIABkAGUAdABlAHIAbQBpAG4AaQBuAGcAIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAdgBhAGwAdQBlAC4AIABUAGgAaQBzACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzAFwAbgAgACAAIAAgAHUAcwBlAGYAdQBsACAAZgBvAHIAIAByAGUAYwBvAG0AcABvAHMAaQBuAGcAIABtAGEAcwBrAGUAZAAgAG8AcgAgAGwAYQB5AGUAcgBlAGQAIABhAHIAcgBhAHkAcwAgACgAZQAuAGcALgAsACAAcgBpAG4AZwBzACkAIABpAG4AdABvACAAYQAgAHMAaQBuAGcAbABlAFwAbgAgACAAIAAgAGMAbwBoAGUAcgBlAG4AdAAgAGcAcgBpAGQAIABhAGYAdABlAHIAIAB0AHIAYQBuAHMAZgBvAHIAbQBhAHQAaQBvAG4AcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEAIAAgACAAIAAgACAAIAAtACAAUgBlAHEAdQBpAHIAZQBkACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgAgACAAIAAgACAAIAAgAC0AIABSAGUAcQB1AGkAcgBlAGQAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAA6AFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMwBdACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwA0AF0AIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGkAZwBuAG8AcgBlAF0AIAAgACAAIAAgACAALQAgAFYAYQBsAHUAZQAgAHQAcgBlAGEAdABlAGQAIABhAHMAIABlAG0AcAB0AHkAIABkAHUAcgBpAG4AZwAgAG8AYwBjAHUAcABhAG4AYwB5ACAAZQB2AGEAbAB1AGEAdABpAG8AbgAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACAAIAAtACAAUwBjAGEAbABhAHIAIAB1AHMAZQBkACAAdwBoAGUAbgAgAGEAbABsACAAYQByAHIAYQB5AHMAIABzAHUAcABwAGwAeQAgAGEAbgAgAGUAbQBwAHQAeQAgAHYAYQBsAHUAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AYQBsAGUAcwBjAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsACAAYQByAHIAYQB5AF8AMgAsACAAWwBhAHIAcgBhAHkAXwAzAF0ALAAgAFsAYQByAHIAYQB5AF8ANABdACwAXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBdACwAXABuACAAIAAgACAAWwBmAGkAbABsAF8AdgBhAGwAdQBlAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAYQByAHIAYQB5ACAAcAByAGUAcwBlAG4AYwBlAFwAbgAgACAAIAAgAEkAbgBjAGwAdQBkAGUAMwAsACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADMAKQApACwAXABuACAAIAAgACAASQBuAGMAbAB1AGQAZQA0ACwAIAAgACAAIAAgACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAzACwAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8AMwApACwAIABGAEEATABTAEUALAAgAGEAcgByAGEAeQBfADMAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADQALAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwA0ACkALAAgAEYAQQBMAFMARQAsACAAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbQBwAHQAeQARIHYAYQBsAHUAZQAgAHIAdQBsAGUAcwBcAG4AIAAgACAAIABpAGcAbgBvAHIAZQAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAaQBnAG4AbwByAGUAKQAsACAAXAAiAFwAIgAsACAAaQBnAG4AbwByAGUAKQAsAFwAbgAgACAAIAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUALAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAFwAIgBcACIALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsACAAIAAgACAAIAAgAHcALAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAaACCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5AF8AMgApACwAIAAgACAAIAAgACAAdwCCICwAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIABoAIMgLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAzACkALAAgACAAIAAgACAAIAB3AIMgLAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADMAKQAsAFwAbgAgACAAIAAgAGgAhCAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADQAKQAsACAAIAAgACAAIAAgAHcAhCAsACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuACAAbQBpAHMAbQBhAHQAYwBoAGUAcwBcAG4AIAAgACAAIABTAF8AMgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAGgAIAA8AD4AIABoAIIgLAAgAHcAIAA8AD4AIAB3AIIgKQAsAFwAbgAgACAAIAAgAFMAXwAzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAGMAbAB1AGQAZQAzACAAKgAgAE8AUgAoAGgAIAA8AD4AIABoAIMgLAAgAHcAIAA8AD4AIAB3AIMgKQAsAFwAbgAgACAAIAAgAFMAXwA0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAGMAbAB1AGQAZQA0ACAAKgAgAE8AUgAoAGgAIAA8AD4AIABoAIQgLAAgAHcAIAA8AD4AIAB3AIQgKQAsAFwAbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALAAgAE8AUgAoAFMAXwAyACwAIABTAF8AMwAsACAAUwBfADQAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABTAGgAYQBwAGUATQBpAHMAbQBhAHQAYwBoAD8ALABcACIAIwBEAEkATQBFAE4AUwBJAE8ATgBTACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AYwBjAHUAcABhAG4AYwB5ACAAdABlAHMAdABcAG4AIAAgACAAIABPAGMAYwB1AHAAaQBlAGQAuwMsACAAIABMAEEATQBCAEQAQQAoAGEAcgByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACgAYQByAHIAIAA8AD4AIABGAEEATABTAEUAKQAgACoAKABMAEUATgAoAGEAcgByACkAIAA8AD4AIAAwACkAIAAqACAAKABhAHIAcgAgADwAPgAgAGkAZwBuAG8AcgBlACkAKQApACwAXABuAFwAbgAgACAAIAAgAG0AXwAxACwAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AygAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAbQBfADIALAAgACAAIAAgACAAIAAgACAATwBjAGMAdQBwAGkAZQBkALsDKABhAHIAcgBhAHkAXwAyACkALABcAG4AIAAgACAAIABtAF8AMwAsACAAIAAgACAAIAAgACAAIABPAGMAYwB1AHAAaQBlAGQAuwMoAGEAcgByAGEAeQBfADMAKQAsAFwAbgAgACAAIAAgAG0AXwA0ACwAIAAgACAAIAAgACAAIAAgAE8AYwBjAHUAcABpAGUAZAC7AygAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAcgBpAG8AcgBpAHQAeQAgAGMAaABhAGkAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIABJAEYAKABtAF8AMQAoACkALAAgAGEAcgByAGEAeQBfADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAG0AXwAyACgAKQAsACAAYQByAHIAYQB5AF8AMgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8AMwAoACkALAAgAGEAcgByAGEAeQBfADMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAF8ANAAoACkALAAgAGEAcgByAGEAeQBfADQALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAA1AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARQB4AHAAbABvAGQAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAE0ARwByAGkAZAC7AywAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABhAG4AIABlAHgAcABsAG8AZABlAGQAIABjAGgAYQByAGEAYwB0AGUAcgAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAEUAeABwAGwAbwBzAGkAbwBuACAAYgBlAGgAYQB2AGkAbwByACAAZABlAHAAZQBuAGQAcwAgAG8AbgAgAHQAaABlACAAaQBuAHAAdQB0ACAAcwBoAGEAcABlADoAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAFMAYwBhAGwAYQByAHMAIABlAHgAcABsAG8AZABlACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlAC4AXABuACAAIAAgACAAIAAgACAAIAAiICAAVgBlAHIAdABpAGMAYQBsACAAMQBEACAAYQByAHIAYQB5AHMAIABlAHgAcABsAG8AZABlACAAYwBvAGwAdQBtAG4AESB3AGkAcwBlAC4AXABuACAAIAAgACAAIAAgACAAIAAiICAASABvAHIAaQB6AG8AbgB0AGEAbAAgADEARAAgAGEAcgByAGEAeQBzACAAZQB4AHAAbABvAGQAZQAgAHIAbwB3ABEgdwBpAHMAZQAuAFwAbgAgACAAIAAgACAAIAAgACAAIiAgADIARAAgAGEAcgByAGEAeQBzACAAZQB4AHAAbABvAGQAZQAgAHIAbwB3ABEgdwBpAHMAZQAgAGIAeQAgAGQAZQBmAGEAdQBsAHQALAAgAG8AcgAgAHcAaQBkAHQAaAARIHcAaQBzAGUAIAB3AGgAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAGUAeABwAGwAbwBkAGUAXwAyAEQAXwBiAHkAYwBvAGwAIAA9ACAAVABSAFUARQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAYwBhAG4AIABiAGUAIABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABvAHIAIAAyAEQALgBcAG4AIAAgACAAIABbAGUAeABwAGwAbwBkAGUAXwAyAEQAXwBiAHkAYwBvAGwAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAuACAAVABSAFUARQAgAJIhIABlAHgAcABsAG8AZABlACAAMgBEACAAYQByAHIAYQB5AHMAIAB3AGkAZAB0AGgAESB3AGkAcwBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAG0AaQB0AHQAZQBkACAAkiEgAGUAeABwAGwAbwBkAGUAIAByAG8AdwARIHcAaQBzAGUALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABMAEUATgAoAGEAcgByAGEAeQApACAAZABlAHQAZQByAG0AaQBuAGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAGMAaABhAHIAYQBjAHQAZQByACAAYwBvAHUAbgB0ACAAcABlAHIAIABjAGUAbABsAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAeABwAGwAbwBkAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBlAHgAcABsAG8AZABlAF8AMgBEAF8AYgB5AGMAbwBsAF0ALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAARABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEcAZQBvAG0AZQB0AHIAeQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALAAgACAAIAAgAGgAIAA+ACAAdwAsAFwAbgAgACAAIAAgAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8ALAAgACAAdwAgAD4AIABoACwAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIABBAE4ARAAoAGgAIAA9ACAAMQAsACAAdwAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAMQBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAFgATwBSACgAaAAgAD4AIAAxACwAIAB3ACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA+ACAAMQApACwAXABuACAAIAAgACAARABpAHIATwBtAGkAdAB0AGUAZAA/ACwAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGUAeABwAGwAbwBkAGUAXwAyAEQAXwBiAHkAYwBvAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGMAYQBsAGEAcgAgAGUAeABwAGwAbwBzAGkAbwBuAFwAbgAgACAAIAAgAEUAeABwAGwAbwBkAGUAUwBjAGEAbABhAHIALAAgACAAUgBFAEcARQBYAEUAWABUAFIAQQBDAFQAKABhAHIAcgBhAHkALAAgAFwAIgAuAFwAIgAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwARQB4AHAAbABvAGQAZQBTAGMAYQBsAGEAcgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABNAGEAeABpAG0AdQBtACAAYwBoAGEAcgBhAGMAdABlAHIAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAGUAbABsAHMAXABuACAAIAAgACAAbQAsACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABMAEUATgAoAGEAcgByAGEAeQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIAAxAEQAIABpAG4AZABlAHgAaQBuAGcAIAAtAC0ALQBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsAFMARQBRAFUARQBOAEMARQAoACwAIABtACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAG0AKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIAAyAEQAIABpAG4AZABlAHgAaQBuAGcAIAAoAHYAZQByAHQAaQBjAGEAbAAgAGUAeABwAGwAbwBzAGkAbwBuACkAIAAtAC0ALQBcAG4AIAAgACAAIABpAF8ALAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAUgBlAHMAaQB6AGUAuwMoACAASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKABtACAAKgAgAGgALAAgACwAIAAsACAAMQAgAC8AIABtACkAKQAsACAALAAgAHcAIAApACAAKQAsAFwAbgAgACAAIAAgAGoAXwAsACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAIABSAGUAcwBpAHoAZQC7AygAIABNAEcAcgBpAGQAuwMoAGEAcgByAGEAeQAsACAAMQApACwAIABtACAAKQAgACkALABcAG4AIAAgACAAIABzAHQAYQByAHQAXwBhAHQAXwAsACAAIABMAEEATQBCAEQAQQAoACAAUgBlAHMAaQB6AGUAuwMoACAAUwBFAFEAVQBFAE4AQwBFACgAbQApACwAIABoACwAIAB3ACAAKQAgACkALABcAG4AXABuACAAIAAgACAALwAvACAALQAtAC0AIAAyAEQAIABpAG4AZABlAHgAaQBuAGcAIAAoAGgAbwByAGkAegBvAG4AdABhAGwAIABlAHgAcABsAG8AcwBpAG8AbgApACAALQAtAC0AXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAAgAFIAZQBzAGkAegBlALsDKAAgAE0ARwByAGkAZAC7AygAYQByAHIAYQB5ACkALAAgACwAIABtACAAKQAgACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAUgBlAHMAaQB6AGUAuwMoACAASQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKAAsACAAbQAgACoAIAB3ACwAIAAsACAAMQAgAC8AIABtACkAKQAsACAAaAAgACkAIAApACwAXABuACAAIAAgACAAcwB0AGEAcgB0AF8AYQB0ACwAIAAgACAATABBAE0AQgBEAEEAKAAgAFIAZQBzAGkAegBlALsDKAAgAFMARQBRAFUARQBOAEMARQAoACwAIABtACkALAAgAGgALAAgAHcAIAApACAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABlAHgAcABsAG8AcwBpAG8AbgBcAG4AIAAgACAAIABlAHgAMQBEACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAATQBJAEQAKABhAHIAcgBhAHkALAAgAGkAZAB4ACgAKQAsACAAMQApACAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAyAEQAIABlAHgAcABsAG8AcwBpAG8AbgAgAHYAYQByAGkAYQBuAHQAcwBcAG4AIAAgACAAIABlAHgAMgBEAF8AVgAsACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAATQBJAEQAKABJAE4ARABFAFgAKABhAHIAcgBhAHkALAAgAGkAXwAoACkALAAgAGoAXwAoACkAKQAsACAAcwB0AGEAcgB0AF8AYQB0AF8AKAApACwAIAAxACkAIAApACwAXABuACAAIAAgACAAZQB4ADIARABfAEgALAAgACAAIAAgACAATABBAE0AQgBEAEEAKAAgAE0ASQBEACgASQBOAEQARQBYACgAYQByAHIAYQB5ACwAIABpACgAKQAsACAAIABqACgAKQApACwAIABzAHQAYQByAHQAXwBhAHQAKAApACwAIAAgADEAKQAgACkALABcAG4AXABuACAAIAAgACAALwAvACAAMgBEACAAcwBlAGwAZQBjAHQAaQBvAG4AXABuACAAIAAgACAAZQB4ADIARAAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABEAGkAcgBPAG0AaQB0AHQAZQBkAD8ALABlAHgAMgBEAF8AVgAoACkALABlAHgAMgBEAF8ASAAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAHMAZQBsAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAEkARgAoAEkAcwAxAEQAPwAsACAAZQB4ADEARAAoACkALAAgAGUAeAAyAEQAKAApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYADAANgBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAE4AdQBtAGIAZQByAHMATwBuAGwAeQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAG4AdQBtAGUAcgBpAGMAIABjAGgAYQByAGEAYwB0AGUAcgBzACAAKAAwABMgOQApACAAZgByAG8AbQAgAGEAIABzAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAASQBuAHAAdQB0ACAAcwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAEUAeABwAGwAbwBkAGUAuwMgAGYAbwByACAAYwBoAGEAcgBhAGMAdABlAHIAESBsAGUAdgBlAGwAIABlAHgAcABhAG4AcwBpAG8AbgAuAFwAbgAgACAAIAAgACIgIABDAE8ARABFACgAKQAgAGYAaQBsAHQAZQByAGkAbgBnACAAZQBuAHMAdQByAGUAcwAgAHMAdAByAGkAYwB0ACAAZABpAGcAaQB0ACAAZQB4AHQAcgBhAGMAdABpAG8AbgAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBOAHUAbQBiAGUAcgBzAE8AbgBsAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAIABpAGYAIABhAHIAcgBhAHkAXABuACAAIAAgACAAYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgAVABZAFAARQAoAGEAcgByAGEAeQApACAAPAA+ACAANgA0ACwAIABhAHIAcgBhAHkALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGwAbwBkAGUAIAB0AG8AIABjAGgAYQByAGEAYwB0AGUAcgBzAFwAbgAgACAAIAAgAGUAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwMoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBnAGkAdAAgAG0AYQBzAGsAXABuACAAIAAgACAASwBlAGUAcAAsACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoACgAQwBPAEQARQAoAGUAeAApACAAPgA9ACAANAA4ACkAIAAqACAAKABDAE8ARABFACgAZQB4ACkAIAA8AD0AIAA1ADcAKQAsACAARgBBAEwAUwBFACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHMAawBlAGQAIAByAGUAcwB1AGwAdABcAG4AIAAgACAAIABSAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIABJAEYAKABLAGUAZQBwACwAIABlAHgALAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIAAxAEQAIABjAG8AbgBjAGEAdABlAG4AYQB0AGUAZAAgAG8AdQB0AHAAdQB0AFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABCAFkAUgBPAFcAKABSAGUAcwB1AGwAdAAsACAAQwBPAE4AQwBBAFQAKQAgACsAIAAwACwAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABYADAANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFQAZQB4AHQATwBuAGwAeQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEUAeAB0AHIAYQBjAHQAcwAgAG4AbwBuABEgbgB1AG0AZQByAGkAYwAgAGMAaABhAHIAYQBjAHQAZQByAHMAIABmAHIAbwBtACAAYQAgAHMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgAC0AIABJAG4AcAB1AHQAIABzAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABVAHMAZQBzACAARQB4AHAAbABvAGQAZQC7AyAAZgBvAHIAIABjAGgAYQByAGEAYwB0AGUAcgARIGwAZQB2AGUAbAAgAGUAeABwAGEAbgBzAGkAbwBuAC4AXABuACAAIAAgACAAIiAgAEMAbwBtAHAAbABlAG0AZQBuAHQAcwAgAE4AdQBtAGIAZQByAHMATwBuAGwAeQC7AyAAYgB5ACAAcwBlAGwAZQBjAHQAaQBuAGcAIABhAGwAbAAgAG4AbwBuABEgZABpAGcAaQB0ACAAYwBoAGEAcgBhAGMAdABlAHIAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBUAGUAeAB0AE8AbgBsAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAIABpAGYAIABhAHIAcgBhAHkAXABuACAAIAAgACAAYQByAHIAYQB5ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgAVABZAFAARQAoAGEAcgByAGEAeQApACAAPAA+ACAANgA0ACwAIABhAHIAcgBhAHkALABUAE8AQwBPAEwAKABhAHIAcgBhAHkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGwAbwBkAGUAIAB0AG8AIABjAGgAYQByAGEAYwB0AGUAcgBzAFwAbgAgACAAIAAgAGUAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwMoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwBuABEgZABpAGcAaQB0ACAAbQBhAHMAawBcAG4AIAAgACAAIABLAGUAZQBwACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAKABDAE8ARABFACgAZQB4ACkAIAA8ACAANAA4ACkAIAArACAAKABDAE8ARABFACgAZQB4ACkAIAA+ACAANQA3ACkALAAgAEYAQQBMAFMARQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQBzAGsAZQBkACAAcgBlAHMAdQBsAHQAXABuACAAIAAgACAAUgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAASQBGACgASwBlAGUAcAAsACAAZQB4ACwAIABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAALwAvACAAMQBEACAAYwBvAG4AYwBhAHQAZQBuAGEAdABlAGQAIABvAHUAdABwAHUAdABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAQgBZAFIATwBXACgAUgBlAHMAdQBsAHQALAAgAEMATwBOAEMAQQBUACkALABcACIAXAAiACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAFgAMAA4AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUwBwAGwAaQB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAGUAeAB0AFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAUgBlAGcAZQB4AFMAYQBmAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAcABsAGkAdABzACAAMQBEACAAdABlAHgAdAAgAGEAcgByAGEAeQBzACAAaQBuAHQAbwAgAHQAbwBrAGUAbgBzACAAdQBzAGkAbgBnACAAYQAgAHMAcABlAGMAaQBmAGkAZQBkACAAZABlAGwAaQBtAGkAdABlAHIALgAgAFQAaABlACAAZgB1AG4AYwB0AGkAbwBuAFwAbgAgACAAIAAgAGkAcwAgAHMAaABhAHAAZQARIGEAdwBhAHIAZQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAGEAIAAyAEQAIABzAHAAaQBsAGwAIABhAGwAaQBnAG4AZQBkACAAdABvACAAdABoAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AIABvAGYAIAB0AGgAZQBcAG4AIAAgACAAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgAgAFMAdQBwAHAAbwByAHQAcwAgAG0AdQBsAHQAaQARIGMAaABhAHIAYQBjAHQAZQByACAAZABlAGwAaQBtAGkAdABlAHIAcwAgAGEAbgBkACAAZgB1AGwAbAAgAHIAZQBnAGUAeAARIHMAYQBmAGUAXABuACAAIAAgACAAZQBzAGMAYQBwAGkAbgBnAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgAEEAIAAxAEQAIABhAHIAcgBhAHkAIAAoAHYAZQByAHQAaQBjAGEAbAAgAG8AcgAgAGgAbwByAGkAegBvAG4AdABhAGwAKQAuACAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAG4AbwB0ACAAcwB1AHAAcABvAHIAdABlAGQALgBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAgACAAIAAtACAARABlAGwAaQBtAGkAdABlAHIAIAB1AHMAZQBkACAAdABvACAAcwBwAGwAaQB0ACAAZQBhAGMAaAAgAHQAZQB4AHQAIABlAGwAZQBtAGUAbgB0AC4AIABTAHAAaQBsAGwAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAcwAgAGkAbgBmAGUAcgByAGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAaABhAHAAZQAgAG8AZgAgAGEAcgByAGEAeQAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsADoAXABuACAAIAAgACAAWwBpAGYAXwBuAG8AdABfAGYAbwB1AG4AZABdAFwAbgAgACAAIAAgACAAIAAgACAAVgBhAGwAdQBlACAAcgBlAHQAdQByAG4AZQBkACAAdwBoAGUAbgAgAGEAIAB0AGUAeAB0ACAAZQBsAGUAbQBlAG4AdAAgAGMAbwBuAHQAYQBpAG4AcwAgAG4AbwAgAGQAZQBsAGkAbQBpAHQAZQByAC4AXABuACAAIAAgACAAIAAgACAAIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABcACIAXAAiAC4AXABuAFwAbgAgACAAIAAgAFsAdAByAGUAYQB0AF8AYwBvAG4AcwBlAGMAdQB0AGkAdgBlAF8AZABlAGwAaQBtAGkAdABlAHIAcwBfAGEAcwBfAG8AbgBlAF0AXABuACAAIAAgACAAIAAgACAAIABUAFIAVQBFACAAkiEgAGMAbwBsAGwAYQBwAHMAZQAgAHIAdQBuAHMAIABvAGYAIABjAG8AbgBzAGUAYwB1AHQAaQB2AGUAIABkAGUAbABpAG0AaQB0AGUAcgBzACAAYgBlAGYAbwByAGUAIABzAHAAbABpAHQAdABpAG4AZwAuAFwAbgAgACAAIAAgACAAIAAgACAAVQBzAGUAZgB1AGwAIABmAG8AcgAgAEMAUwBWABEgcwB0AHkAbABlACAAbgBvAHIAbQBhAGwAaQB6AGEAdABpAG8AbgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEMAbwBsAGwAYQBwAHMAZQAgAG0AbwBkAGUAIABwAGUAcgBmAG8AcgBtAHMAIABhACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAIABwAGEAcwBzACAAdwBoAGUAbgAgAGMAbwBuAHMAZQBjAHUAdABpAHYAZQAgAGQAZQBsAGkAbQBpAHQAZQByAHMAIABlAHgAaQBzAHQALgBcAG4AIAAgACAAIAAgACAARgBvAHIAIAB2AGUAcgB5ACAAbABhAHIAZwBlACAAYQByAHIAYQB5AHMAIABvAHIAIABoAGkAZwBoACAAdABvAGsAZQBuACAAYwBvAHUAbgB0AHMALAAgAHQAaABpAHMAIABtAGEAeQAgAGkAbgBjAHIAZQBhAHMAZQAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAgAHQAaQBtAGUALgBcAG4AIAAgACAAIAAiICAARABlAGwAaQBtAGkAdABlAHIAcwAgAGEAcgBlACAAZgB1AGwAbAB5ACAAcgBlAGcAZQB4ABEgZQBzAGMAYQBwAGUAZAAgAHYAaQBhACAAUgBlAGcAZQB4AFMAYQBmAGUAuwMsACAAYQBsAGwAbwB3AGkAbgBnACAAbABpAHQAZQByAGEAbAAgAHUAcwBlACAAbwBmAFwAbgAgACAAIAAgACAAIABtAGUAdABhAGMAaABhAHIAYQBjAHQAZQByAHMAIAAoACoALAAgAD8ALAAgACsALAAgAHwALAAgACgALAAgACkALAAgAFsALAAgAF0ALAAgAF4ALAAgACQALAAgAGUAdABjAC4AKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHAAbABpAHQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIALABcAG4AIAAgACAAIABbAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkAF0ALABcAG4AIAAgACAAIABbAHQAcgBlAGEAdABfAGMAbwBuAHMAZQBjAHUAdABpAHYAZQBfAGQAZQBsAGkAbQBpAHQAZQByAHMAXwBhAHMAXwBvAG4AZQBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAIABvAGYAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAaAAsACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzACAAbwBmACAAZABlAGwAaQBtAGkAdABlAHIAXABuACAAIAAgACAAaACCICwAIABSAE8AVwBTACgAZABlAGwAaQBtAGkAdABlAHIAKQAsAFwAbgAgACAAIAAgAHcAgiAsACAAQwBPAEwAVQBNAE4AUwAoAGQAZQBsAGkAbQBpAHQAZQByACkALABcAG4AXABuACAAIAAgACAALwAvACAATwByAGkAZQBuAHQAYQB0AGkAbwBuACAAYwBoAGUAYwBrAHMAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAIABoACAAPgAgAHcALABcAG4AIAAgACAAIABJAHMAMgBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPgAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAXABuACAAIAAgACAAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQALAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkALAAgAFwAIgBcACIALAAgAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkALABcAG4AIAAgACAAIABDAG8AbABsAGEAcABzAGUARABlAGwAaQBtAD8ALAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAB0AHIAZQBhAHQAXwBjAG8AbgBzAGUAYwB1AHQAaQB2AGUAXwBkAGUAbABpAG0AaQB0AGUAcgBzAF8AYQBzAF8AbwBuAGUAKQApACwAXABuACAAIAAgACAATQB1AGwAdABpAHAAbABlAEQAZQBsAGkAbQA/ACwAIABPAFIAKABoAIIgIAA+ACAAMQAsACAAdwCCICAAPgAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABWAGEAbABpAGQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAEkARgAoAEkAcwAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAIwAyAEQALQBJAE4AUABVAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABNAHUAbAB0AGkAcABsAGUARABlAGwAaQBtAD8ALAAgAFwAIgAjAEQARQBMAEkATQBJAFQARQBSAC0AQQBSAFIAQQBZACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFcAcgBhAHAAIABlAGEAYwBoACAAZQBsAGUAbQBlAG4AdAAgAHcAaQB0AGgAIABkAGUAbABpAG0AaQB0AGUAcgAgAG8AbgAgAGIAbwB0AGgAIABzAGkAZABlAHMAXABuACAAIAAgACAAagBvAGkAbgBlAGQALAAgACAAIAAgACAAIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAgACYAIABhAHIAcgBhAHkAIAAmACAAZABlAGwAaQBtAGkAdABlAHIALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAGcAZQB4ABEgcwBhAGYAZQAgAGQAZQBsAGkAbQBpAHQAZQByAFwAbgAgACAAIAAgAGQAZQBsAGkAbQBfAGIALAAgACAAIAAgACAAIAAgACAAUgBlAGcAZQB4AFMAYQBmAGUAuwMoAGQAZQBsAGkAbQBpAHQAZQByACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAHQAZQBjAHQAIABjAG8AbgBzAGUAYwB1AHQAaQB2AGUAIABkAGUAbABpAG0AaQB0AGUAcgBzAFwAbgAgACAAIAAgAEkAcwBDAG8AbgBzAGUAYwBEAGUAbABpAG0APwAsACAATwBSACgAUgBFAEcARQBYAFQARQBTAFQAKABqAG8AaQBuAGUAZAAsACAAXAAiACgAXAAiACAAJgAgAGQAZQBsAGkAbQBfAGIAIAAmACAAXAAiACkAewAyACwAfQBcACIAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBsAGwAYQBwAHMAZQAgAGMAbwBuAHMAZQBjAHUAdABpAHYAZQAgAGQAZQBsAGkAbQBpAHQAZQByAHMAIABpAGYAIAByAGUAcQB1AGUAcwB0AGUAZABcAG4AIAAgACAAIAB0AGUAeAB0AHMALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgAQwBvAGwAbABhAHAAcwBlAEQAZQBsAGkAbQA/ACwAIABJAHMAQwBvAG4AcwBlAGMARABlAGwAaQBtAD8AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAoAGoAbwBpAG4AZQBkACwAIABcACIAKABcACIAIAAmACAAZABlAGwAaQBtAF8AYgAgACYAIABcACIAKQArAFwAIgAsACAAZABlAGwAaQBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoAbwBpAG4AZQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAGsAZQBuACAAYwBvAHUAbgB0AFwAbgAgACAAIAAgAEwALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAE4AKABkAGUAbABpAG0AaQB0AGUAcgApACwAXABuACAAIAAgACAAdABvAGsAZQBuACwAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAEwARQBOACgAdABlAHgAdABzACkAIAAtACAATABFAE4AKABTAFUAQgBTAFQASQBUAFUAVABFACgAdABlAHgAdABzACwAIABkAGUAbABpAG0AaQB0AGUAcgAsACAAXAAiAFwAIgApACkAKQAgAC8AIABMACAALQAgADEALABcAG4AXABuACAAIAAgACAALwAvACAASQBuAGQAZQB4AGkAbgBnACAAZgBvAHIAIABUAEUAWABUAEEARgBUAEUAUgAvAFQARQBYAFQAQgBFAEYATwBSAEUAXABuACAAIAAgACAAaQBkAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAEkARgAoACgASQBzAFYAZQByAHQAaQBjAGEAbAA/ACkAIAArACAAKABJAHMAUwBjAGEAbABhAHIAPwApACwAUwBFAFEAVQBFAE4AQwBFACgALAAgAHQAbwBrAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAdABvAGsAZQBuACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFAAYQByAHMAZQAgAHQAbwBrAGUAbgBzAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABUAEUAWABUAEEARgBUAEUAUgAoAHQAZQB4AHQAcwAsACAAZABlAGwAaQBtAGkAdABlAHIALAAgAGkAZAB4ACgAKQAsACAALAAgACwAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABlAGwAaQBtAGkAdABlAHIALAAsACAALAAgACwAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAWAAtAEMATwBSAEUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABSAGUAZwBlAHgAUwBhAGYAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdAAgACgAQwBvAHIAZQApAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARQBzAGMAYQBwAGUAcwAgAHIAZQBnAGUAeAAgAG0AZQB0AGEAYwBoAGEAcgBhAGMAdABlAHIAcwAgAGkAbgAgAGEAIABzAHUAcABwAGwAaQBlAGQAIABkAGUAbABpAG0AaQB0AGUAcgAgAHMAbwAgAGkAdAAgAGMAYQBuACAAYgBlACAAdQBzAGUAZABcAG4AIAAgACAAIABzAGEAZgBlAGwAeQAgAGkAbgAgAFIARQBHAEUAWABUAEUAUwBUACwAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAsACAAYQBuAGQAIABSAEUARwBFAFgARQBYAFQAUgBBAEMAVAAgAHAAYQB0AHQAZQByAG4AcwAuACAATQB1AGwAdABpABEgXABuACAAIAAgACAAYwBoAGEAcgBhAGMAdABlAHIAIABkAGUAbABpAG0AaQB0AGUAcgBzACAAYQByAGUAIABwAHIAbwBjAGUAcwBzAGUAZAAgAGMAaABhAHIAYQBjAHQAZQByABEgYgB5ABEgYwBoAGEAcgBhAGMAdABlAHIALAAgAGEAbgBkACAAbwBuAGwAeQBcAG4AIAAgACAAIABjAGgAYQByAGEAYwB0AGUAcgBzACAAdABoAGEAdAAgAHIAZQBxAHUAaQByAGUAIABlAHMAYwBhAHAAaQBuAGcAIABhAHIAZQAgAHAAcgBlAGYAaQB4AGUAZAAgAHcAaQB0AGgAIABcACIAXABcAFwAIgAuAFwAbgBcAG4ARQB4AGEAbQBwAGwAZQA6AFwAbgAgACAAIAAgAD0AUgBlAGcAZQB4AFMAYQBmAGUAuwMoAFwAIgB8AFwAIgApAFwAbgAgACAAIAAgAHIAZQB0AHUAcgBuAHMAOgAgAFwAIgBcAFwAfABcACIAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBnAGUAeABTAGEAZgBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByAHMALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABDAGgAYQByAGEAYwB0AGUAcgBzACAAcgBlAHEAdQBpAHIAaQBuAGcAIABlAHMAYwBhAHAAaQBuAGcAIABpAG4AIABFAHgAYwBlAGwAJwBzACAAUABDAFIARQAyACAAZQBuAGcAaQBuAGUAXABuACAAIAAgACAAbQBlAHQAYQAsACAAIAAgACAAIAAgACAAewBcACIAXABcAFwAIgAsACAAXAAiACsAXAAiACwAIABcACIAKgBcACIALAAgAFwAIgA/AFwAIgAsACAAXAAiAF4AXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAJABcACIALAAgAFwAIgAoAFwAIgAsACAAXAAiACkAXAAiACwAIABcACIAWwBcACIALAAgAFwAIgB8AFwAIgB9ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAbgB1AG0AZQByAGEAdABlACAAZQBhAGMAaAAgAGMAaABhAHIAYQBjAHQAZQByACAAbwBmACAAdABoAGUAIABkAGUAbABpAG0AaQB0AGUAcgBcAG4AIAAgACAAIABjAGgAYQByAHMALAAgACAAIAAgACAAIABSAEUARwBFAFgARQBYAFQAUgBBAEMAVAAoAGQAZQBsAGkAbQBpAHQAZQByAHMALABcACIALgBcACIALAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAASQBkAGUAbgB0AGkAZgB5ACAAbQBlAHQAYQBjAGgAYQByAGEAYwB0AGUAcgBzAFwAbgAgACAAIAAgAEkAcwBNAGUAdABhAD8ALAAgACAAIAAgAEkAUwBOAFUATQBCAEUAUgAoAFgATQBBAFQAQwBIACgAYwBoAGEAcgBzACwAIABtAGUAdABhACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHMAYwBhAHAAZQAgAG8AbgBsAHkAIAB0AGgAbwBzAGUAIAB0AGgAYQB0ACAAcgBlAHEAdQBpAHIAZQAgAGkAdABcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuACwAIAAgACAAIABDAE8ATgBDAEEAVAAoAEkARgAoAEkAcwBNAGUAdABhAD8ALAAgAFwAIgBcAFwAXAAiACAAJgAgAGMAaABhAHIAcwAsACAAYwBoAGEAcgBzACkAKQAsAFwAbgBcAG4AIAAgACAAIABwAGEAdAB0AGUAcgBuAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAvACAAWwBFAE4AXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ALwAvACAALQAtAC0AIwAjACAAMAA4ACAAFCAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwBcAG4ALwAvACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBcAG4ALwAqAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABUAGgAZQAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwAgAGMAYQB0AGUAZwBvAHIAeQAgAHAAcgBvAHYAaQBkAGUAcwAgAGIAaQBuAGEAcgB5ACwAIABHAHIAYQB5ABEgYwBvAGQAZQAsACAAYQBuAGQAIABiAGkAdAARIGwAZQB2AGUAbAAgAHUAdABpAGwAaQB0AGkAZQBzAFwAbgAgACAAIAAgAGQAZQBzAGkAZwBuAGUAZAAgAHQAbwAgAG8AcABlAHIAYQB0AGUAIAB3AGUAbABsACAAYgBlAHkAbwBuAGQAIABFAHgAYwBlAGwAJwBzACAAbgBhAHQAaQB2AGUAIABEAEUAQwAyAEIASQBOACAAbABpAG0AaQB0ACAAbwBmACAANQAxADEALgAgAEEAbABsAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgBzACAAcwB1AHAAcABvAHIAdAAgAGMAbwBuAGMAaQBzAGUAIABiAGkAbgBhAHIAeQAgAHMAdAByAGkAbgBnAHMAIABhAG4AZAAgAHMAaABhAHAAZQARIHAAcgBlAHMAZQByAHYAaQBuAGcAIABhAHIAcgBhAHkAIABiAGUAaABhAHYAaQBvAHIALABcAG4AIAAgACAAIAB3AGkAdABoACAAbwBwAHQAaQBvAG4AYQBsACAAMgBEACAAZQB4AHAAbABvAGQAZQBkACAAYgBpAHQAESBtAGEAdAByAGkAYwBlAHMAIAB3AGgAZQByAGUAIABhAHAAcABsAGkAYwBhAGIAbABlAC4AXABuAFwAbgBGAHUAbgBjAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABCAGkAbgAyAEQAZQBjALsDXABuACAAIAAgACAAIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABjAG8AbgBjAGkAcwBlACAAYgBpAG4AYQByAHkAIABpAG4AdABvACAAZABlAGMAaQBtAGEAbAAgAHYAYQBsAHUAZQBzAC4AXABuAFwAbgAgACAAIAAgACIgIABCAGkAbgAyAEcAcgBhAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAGMAbwBuAGMAaQBzAGUAIABiAGkAbgBhAHIAeQAgAGkAbgB0AG8AIABHAHIAYQB5ABEgYwBvAGQAZQAgAHYAYQBsAHUAZQBzACwAIAB3AGkAdABoACAAbwBwAHQAaQBvAG4AYQBsACAAZQB4AHAAbABvAGQAZQBkACAAZgBvAHIAbQAuAFwAbgBcAG4AIAAgACAAIAAiICAAQgBpAHQAQwBvAHUAbgB0ALsDXABuACAAIAAgACAAIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABpAG4AdABlAGcAZQByAHMAIAB0AG8AIABiAGkAbgBhAHIAeQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAGIAaQB0ACAAYwBvAHUAbgB0AHMALAAgAHAAcgBlAHMAZQByAHYAaQBuAGcAIABpAG4AcAB1AHQAIABzAGgAYQBwAGUALgBcAG4AXABuACAAIAAgACAAIiAgAEQAZQBjADIAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBuAHYAZQByAHQAcwAgAGkAbgB0AGUAZwBlAHIAcwAgAGkAbgB0AG8AIABiAGkAbgBhAHIAeQAgAHYAYQBsAHUAZQBzACwAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIABjAG8AbgBjAGkAcwBlACAAcwB0AHIAaQBuAGcAcwAgAG8AcgBcAG4AIAAgACAAIAAgACAAIAAgAGUAeABwAGwAbwBkAGUAZAAgADIARAAgAGIAaQB0ABEgYQByAHIAYQB5AHMALgBcAG4AXABuACAAIAAgACAAIiAgAEQAZQBjADIARwByAGEAeQC7A1wAbgAgACAAIAAgACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAaQBuAHQAZQBnAGUAcgBzACAAaQBuAHQAbwAgAEcAcgBhAHkAESBjAG8AZABlACAAdgBhAGwAdQBlAHMAIAAoAHcAcgBhAHAAcABlAHIAOgAgAEQAZQBjADIAQgBpAG4AuwMgAJIhIABCAGkAbgAyAEcAcgBhAHkAuwMpAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAATgBlAGcAYQB0AGkAdgBlACAAbgB1AG0AYgBlAHIAcwAgAGEAcgBlACAAbgBvAHQAIABzAHUAcABwAG8AcgB0AGUAZAAgAGYAbwByACAARABlAGMAMgBCAGkAbgC7AyAAbwByACAARABlAGMAMgBHAHIAYQB5ALsDLgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEUATgAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABCAGkAbgAyAEQAZQBjALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABFAG4AZwBpAG4AZQBlAHIAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABFAHgAcABsAG8AZABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABjAG8AbgBjAGkAcwBlACAAYgBpAG4AYQByAHkAIABpAG4AdABvACAAZABlAGMAaQBtAGEAbAAgAHYAYQBsAHUAZQBzAC4AIABTAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABhAG4AZAAgADIARABcAG4AIAAgACAAIABpAG4AcAB1AHQAcwAgAHcAaQB0AGgAIABmAHUAbABsACAAcwBoAGEAcABlACAAcAByAGUAcwBlAHIAdgBhAHQAaQBvAG4ALgAgAEIAaQB0ABEgdwBpAGQAdABoACAAaQBzACAAaQBuAGYAZQByAHIAZQBkACAAYQB1AHQAbwBtAGEAdABpAGMAYQBsAGwAeQBcAG4AIAAgACAAIABhAG4AZAAgAGEAbABsACAAdgBhAGwAdQBlAHMAIABhAHIAZQAgAG4AbwByAG0AYQBsAGkAegBlAGQAIABiAGUAZgBvAHIAZQAgAGUAeABwAGwAbwBzAGkAbwBuAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYgBpAG4AYQByAHkAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAYwBvAG4AYwBpAHMAZQAgAGIAaQBuAGEAcgB5ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABDAG8AbgBjAGkAcwBlACAAZgBvAHIAbQA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMAAxADEAXAAiACwAIABcACIAMAAwADAAMQAxADAAMQAwAFwAIgAsACAAZQB0AGMALgAgACAAKABhAG4AeQAgAHMAaABhAHAAZQApAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE8AdQB0AHAAdQB0ACAAcwBoAGEAcABlACAAbQBhAHQAYwBoAGUAcwAgAGkAbgBwAHUAdAAgAHMAaABhAHAAZQAgACgAcwBjAGEAbABhAHIALAAgAHYAZQByAHQAaQBjAGEAbAAsACAAaABvAHIAaQB6AG8AbgB0AGEAbAAsACAAbwByACAAMgBEACkALgBcAG4AIAAgACAAIAAiICAAUwB1AHAAcABvAHIAdABzACAAYgBpAG4AYQByAHkAIAB2AGEAbAB1AGUAcwAgAGYAYQByACAAYgBlAHkAbwBuAGQAIABFAHgAYwBlAGwAGSBzACAAbgBhAHQAaQB2AGUAIAAxADYAESBkAGkAZwBpAHQAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AaQB0AC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEIAaQBuADIARABlAGMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYgBpAG4AYQByAHkALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAIABvAGYAIABpAG4AcAB1AHQAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYgBpAG4AYQByAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGIAaQBuAGEAcgB5ACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAsACAAIABBAE4ARAAoAHcAIAA+ACAAMQAsACAAaAAgAD0AIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABiAGkAdAARIHcAaQBkAHQAaAAgAGEAbgBkACAAZQB4AHAAbABvAGQAZQBcAG4AIAAgACAAIABiAGkAdABzACwAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgATABFAE4AKABiAGkAbgBhAHIAeQApACkALABcAG4AIAAgACAAIABhAHIAcgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQARQBYAFQAKABiAGkAbgBhAHIAeQAsACAAUgBFAFAAVAAoAFwAIgAwAFwAIgAsACAAYgBpAHQAcwApACkALABcAG4AIAAgACAAIABiAGkAbgBhAHIAeQAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwARQB4AHAAbABvAGQAZQC7AygAYgBpAG4AYQByAHkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAHgAcABsAG8AZABlALsDKABUAE8AQwBPAEwAKABhAHIAcgApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAdABoAFwAbgAgACAAIAAgAHAAbwB3AGUAcgBzACwAIABTAEUAUQBVAEUATgBDAEUAKAAsACAAYgBpAHQAcwAsACAAYgBpAHQAcwAgAC0AIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgAHAALAAgACAAIAAgACAAIABQAE8AVwBFAFIAKAAyACwAIABwAG8AdwBlAHIAcwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAZwBnAHIAZQBnAGEAdABpAG8AbgAgACYAIABkAGUAbABpAHYAZQByAHkAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAEIAWQBSAE8AVwAoAGIAaQBuAGEAcgB5ACAAKgAgAHAALAAgAFMAVQBNACkALABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAASQBGACgATwBSACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwApACwAIAByAGUAcwB1AGwAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwBIAG8AcgBpAHoAbwBuAHQAYQBsAD8ALAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAcgBlAHMAdQBsAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVwBSAEEAUABSAE8AVwBTACgAcgBlAHMAdQBsAHQALAAgAHcAKQApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBFAE4AMAAyAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQgBpAG4AMgBHAHIAYQB5ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABFAG4AZwBpAG4AZQBlAHIAaQBuAGcAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABFAHgAcABsAG8AZABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABiAGkAbgBhAHIAeQAgAGkAbgB0AG8AIABHAHIAYQB5ABEgYwBvAGQAZQAgAHYAYQBsAHUAZQBzAC4AIABTAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAsAFwAbgAgACAAIAAgADEARAAsACAAYQBuAGQAIAAyAEQAIABpAG4AcAB1AHQAcwAuACAATwB1AHQAcAB1AHQAIABjAGEAbgAgAGIAZQAgAHIAZQB0AHUAcgBuAGUAZAAgAGUAaQB0AGgAZQByACAAYQBzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAG8AcgAgAGEAcwBcAG4AIAAgACAAIABjAG8AbgBjAGkAcwBlACAAcgBvAHcAESB3AGkAcwBlACAAcwB0AHIAaQBuAGcAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGIAaQBuAGEAcgB5AFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAGIAaQBuAGEAcgB5ACAAZABhAHQAYQAuAFwAbgBcAG4AIAAgACAAIABbAGMAbwBuAGMAaQBzAGUAXQBcAG4AIAAgACAAIAAgACAAIAAgAE8AcAB0AGkAbwBuAGEAbAAuACAAVABSAFUARQAgAJIhIAByAGUAdAB1AHIAbgAgAEcAcgBhAHkAIABjAG8AZABlACAAYQBzACAAYwBvAG4AYwBhAHQAZQBuAGEAdABlAGQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAIAAgACAAIAAgACAAIABPAG0AaQB0AHQAZQBkACAAkiEgAHIAZQB0AHUAcgBuACAAMgBEACAAZQB4AHAAbABvAGQAZQBkACAARwByAGEAeQARIGMAbwBkAGUAIABiAGkAdAAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAMgBEACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAGQAZQBsAGkAdgBlAHIAZQBkACAAaQBuACAAYwBvAG4AYwBpAHMAZQAgAGYAbwByAG0AYQB0AC4AXABuACAAIAAgACAAIiAgAEcAcgBhAHkAIABjAG8AZABlACAAaQBzACAAYwBvAG0AcAB1AHQAZQBkACAAYQBzADoAIAAgAGcAgCAgAD0AIABiAIAgLAAgACAAZwBiHSAAPQAgAGIAYh0gAFgATwBSACAAYgBiHYsggSAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBCAGkAbgAyAEcAcgBhAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYgBpAG4AYQByAHkALABcAG4AIAAgACAAIABbAGMAbwBuAGMAaQBzAGUAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHUAdABwAHUAdAAgAG0AbwBkAGUAXABuACAAIAAgACAASQBzADIARABHAHIAYQB5AD8ALAAgACAAIAAgACAAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBuAGMAaQBzAGUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAIABvAGYAIABpAG4AcAB1AHQAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYgBpAG4AYQByAHkAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGIAaQBuAGEAcgB5ACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwAsACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAsACAAIABBAE4ARAAoAHcAIAA+ACAAMQAsACAAaAAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAMQBEAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAFgATwBSACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAGIAaQB0AC0AdwBpAGQAdABoACAAYQBuAGQAIABlAHgAcABsAG8AZABlAFwAbgAgACAAIAAgAGIAaQB0AHMALAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABMAEUATgAoAGIAaQBuAGEAcgB5ACkAKQAsAFwAbgAgACAAIAAgAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABFAFgAVAAoAGIAaQBuAGEAcgB5ACwAIABSAEUAUABUACgAXAAiADAAXAAiACwAIABiAGkAdABzACkAKQAsAFwAbgAgACAAIAAgAGIAaQBuAGEAcgB5ACwAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALABFAHgAcABsAG8AZABlALsDKABiAGkAbgBhAHIAeQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAeABwAGwAbwBkAGUAuwMoAFQATwBDAE8ATAAoAGEAcgByACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AbwBzAHQAIABzAGkAZwBuAGkAZgBpAGMAYQBuAHQAIABiAGkAdABcAG4AIAAgACAAIABtAHMAYgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABiAGkAbgBhAHIAeQAsACAALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABYAE8AUgAgAG4AZQBpAGcAaABiAG8AcgBzAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgBJAFQAWABPAFIAKABEAFIATwBQACgAYgBpAG4AYQByAHkALAAgACwAIAAxACkALAAgAEQAUgBPAFAAKABiAGkAbgBhAHIAeQAsACAALAAgAC0AMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGEAeQAgAGMAbwBkAGUAIABhAHIAcgBhAHkAXwAyAEQAXABuACAAIAAgACAAZwByAGEAeQAsACAAIAAgACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAG0AcwBiACwAIAB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAATwB1AHQAcAB1AHQAIABhAG4AZAAgAGQAZQBsAGkAdgBlAHIAeQBcAG4AIAAgACAAIAByAGUAcwB1AGwAdAAsACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgASQBzADIARABHAHIAYQB5AD8ALABJAHMAMQBEAD8AKQAsACAAZwByAGEAeQAsACAAQgBZAFIATwBXACgAZwByAGEAeQAsACAAQwBPAE4AQwBBAFQAKQApACwAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAHMAUwBjAGEAbABhAHIAPwAsAEkAcwBWAGUAcgB0AGkAYwBhAGwAPwApACwAcgBlAHMAdQBsAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBzAEgAbwByAGkAegBvAG4AdABhAGwAPwAsAFQAUgBBAE4AUwBQAE8AUwBFACgAcgBlAHMAdQBsAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVwBSAEEAUABSAE8AVwBTACgAcgBlAHMAdQBsAHQALAB3ACkAKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARQBOADAAMwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEIAaQB0AEMAbwB1AG4AdAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARABlAGMAMgBCAGkAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAHUAbgB0AHMAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAMQARIGIAaQB0AHMAIABpAG4AIAB0AGgAZQAgAGIAaQBuAGEAcgB5ACAAcgBlAHAAcgBlAHMAZQBuAHQAYQB0AGkAbwBuACAAbwBmACAAZQBhAGMAaAAgAGkAbgB0AGUAZwBlAHIALgBcAG4AIAAgACAAIABTAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAsACAAMQBEACwAIABhAG4AZAAgADIARAAgAGkAbgBwAHUAdABzACAAdwBpAHQAaAAgAGYAdQBsAGwAIABzAGgAYQBwAGUAIABwAHIAZQBzAGUAcgB2AGEAdABpAG8AbgAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAG4AIAAgACAALQAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIABuAG8AbgARIG4AZQBnAGEAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABEAGUAYwAyAEIAaQBuALsDKABuACwAMQApACAAdABvACAAbwBiAHQAYQBpAG4AIABlAHgAcABsAG8AZABlAGQAIABiAGkAdAARIG0AYQB0AHIAaQBjAGUAcwAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHMAaABhAHAAZQAgAG0AYQB0AGMAaABlAHMAIABpAG4AcAB1AHQAIABzAGgAYQBwAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQgBpAHQAQwBvAHUAbgB0ALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAG4ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABuACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAG4AKQAsAFwAbgBcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABJAHMAMQBEAD8ALAAgACAAIAAgACAAIAAgACAAWABPAFIAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD4AIAAxACwAIAB3ACAAPgAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0ACAAaQBmACAAMgBEAFwAbgAgACAAIAAgAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALABuACwAVABPAEMATwBMACgAbgApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgB1AG4AYwB0AGkAbwBuACAAKABmAG8AcgAgAG4AbwBuAC0AcwBjAGEAbABhAHIAcwApAFwAbgAgACAAIAAgAGYAbgC7AywAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAHMAVgBlAHIAdABpAGMAYQBsAD8ALABJAHMAMgBEAD8AKQAsAEIAWQBSAE8AVwAsAEIAWQBDAE8ATAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGwAbwBkAGUAZAAgAGIAaQBuAGEAcgB5ACAAYQByAHIAYQB5AF8AMgBEAFwAbgAgACAAIAAgAGIAaQB0AHMALAAgACAAIAAgACAAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDKABuACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAHUAbgB0ACAAYgBpAHQAcwBcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAsACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAFMAVQBNACgAYgBpAHQAcwApACwAZgBuALsDKABiAGkAdABzACwAUwBVAE0AKQApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIABJAEYAKABJAHMAMQBEAD8ALABjAG8AdQBuAHQAcwAsAFcAUgBBAFAAUgBPAFcAUwAoAGMAbwB1AG4AdABzACwAdwApACkALABcAG4AXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBFAE4AMAA0AF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARABlAGMAMgBCAGkAbgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAQwBvAG4AdgBlAHIAdABzACAAbgBvAG4AESBuAGUAZwBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMAIABpAG4AdABvACAAYgBpAG4AYQByAHkALgAgAFMAdQBwAHAAbwByAHQAcwAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAGEAbgBkACAAMgBEAFwAbgAgACAAIAAgAGkAbgBwAHUAdABzACAAdwBpAHQAaAAgAGYAdQBsAGwAIABzAGgAYQBwAGUAIABwAHIAZQBzAGUAcgB2AGEAdABpAG8AbgAuACAAUgBlAHQAdQByAG4AcwAgAGUAaQB0AGgAZQByACAAYwBvAG4AYwBpAHMAZQAgAGIAaQBuAGEAcgB5ACAAcwB0AHIAaQBuAGcAcwBcAG4AIAAgACAAIABvAHIAIABlAHgAcABsAG8AZABlAGQAIAAyAEQAIABiAGkAdAARIGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAbgB1AG0AYgBlAHIAcwBcAG4AIAAgACAAIAAgACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AbwBuABEgbgBlAGcAYQB0AGkAdgBlACAAaQBuAHQAZQBnAGUAcgBzAC4AXABuAFwAbgAgACAAIAAgAFsAQQByAHIAYQB5AF8ARgBvAHIAbQBfADIARABdAFwAbgAgACAAIAAgACAAIAAgACAATwBwAHQAaQBvAG4AYQBsAC4AIABUAFIAVQBFACAAkiEgAHIAZQB0AHUAcgBuACAAZQB4AHAAbABvAGQAZQBkACAAMgBEACAAYgBpAHQAESBhAHIAcgBhAHkAcwAuAFwAbgAgACAAIAAgACAAIAAgACAATwBtAGkAdAB0AGUAZAAgAJIhIAByAGUAdAB1AHIAbgAgAGMAbwBuAGMAaQBzAGUAIABiAGkAbgBhAHIAeQAgAHMAdAByAGkAbgBnAHMALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABTAHUAcABwAG8AcgB0AHMAIABhAHIAYgBpAHQAcgBhAHIAaQBsAHkAIABsAGEAcgBnAGUAIABpAG4AdABlAGcAZQByAHMAIAAoAGIAZQB5AG8AbgBkACAARQB4AGMAZQBsABkgcwAgAG4AYQB0AGkAdgBlACAAQgBJAE4AMgBEAEUAQwAgAGwAaQBtAGkAdABzACkALgBcAG4AIAAgACAAIAAiICAAQwBvAG4AYwBpAHMAZQAgAG8AdQB0AHAAdQB0ACAAYQB2AG8AaQBkAHMAIABzAGMAaQBlAG4AdABpAGYAaQBjACAAbgBvAHQAYQB0AGkAbwBuACAAYQBuAGQAIAAxADYAESBkAGkAZwBpAHQAIABwAHIAZQBjAGkAcwBpAG8AbgAgAGkAcwBzAHUAZQBzAC4AXABuACAAIAAgACAAIiAgADIARAAgAGkAbgBwAHUAdABzACAAcAByAGUAcwBlAHIAdgBlACAAdABoAGUAaQByACAAbwByAGkAZwBpAG4AYQBsACAAcwBoAGEAcABlACAAdwBoAGUAbgAgAGMAbwBuAGMAaQBzAGUAIABvAHUAdABwAHUAdAAgAGkAcwAgAHMAZQBsAGUAYwB0AGUAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBEAGUAYwAyAEIAaQBuALsDPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABuAHUAbQBiAGUAcgBzACwAXABuACAAIAAgACAAWwBBAHIAcgBhAHkAXwBGAG8AcgBtAF8AMgBEAF0ALABcAG4AXABuAC8ALwBDAGgAZQBjAGsAIABuAHUAbQBiAGUAcgBzAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAG4AdQBtAGIAZQByAHMAKQAsACAASQBTAEUAUgBSAE8AUgAoAC0ALQBuAHUAbQBiAGUAcgBzACkALABuAHUAbQBiAGUAcgBzACAAPAAgADAAKQAsACAAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIABzAGgAYQBwAGUAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAG4AdQBtAGIAZQByAHMAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABuAHUAbQBiAGUAcgBzACkALABcAG4AXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAASQBzAFYAZQByAHQAaQBjAGEAbAA/ACwAIAAgACAAaAAgAD4AIAB3ACwAXABuACAAIAAgACAASQBzADIARAA/ACwAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPgAgADEALAB3ACAAPgAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAG4AdQBtAGIAZQByAHMALAAgACAAIAAgACAAIAAgAFQATwBDAE8ATAAoAG4AdQBtAGIAZQByAHMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAG8AcgBtAFwAbgAgACAAIAAgAEkAcwBWAGUAYwB0AG8AcgA/ACwAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAQQByAHIAYQB5AF8ARgBvAHIAbQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AYQB4ACAAYgBpAHQAcwAgAG4AZQBlAGQAZQBkACAAdABvACAAZQB4AHAAcgBlAHMAcwAgAHIAZQBzAHUAbAB0AHMAIABhAHMAIABhAHIAcgBhAHkAXABuACAAIAAgACAAYgBpAHQAcwAsACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABJAEYARQBSAFIATwBSACgASQBOAFQAKABMAE8ARwAoAG4AdQBtAGIAZQByAHMALAAyACkAKQAgACsAIAAxACwAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBvAHIAbQBzACAALQAgADIARAAgAGEAcgByAGEAeQAsACAAYgBpAG4AIAB2AGUAYwB0AG8AcgAgAC0AIABlAGEAZwBlAHIAIABlAHYAYQBsAHUAYQB0AGkAbwBuACAAZABlAGYAZQByAHIAZQBkAFwAbgAgACAAIAAgAGIAaQBuAF8AYQByAHIALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgATQBPAEQAKABCAEkAVABSAFMASABJAEYAVAAoAG4AdQBtAGIAZQByAHMALABTAEUAUQBVAEUATgBDAEUAKAAsAGIAaQB0AHMALABiAGkAdABzACAALQAgADEALAAtADEAKQApACwAMgApACkALABcAG4AIAAgACAAIABiAGkAbgBfAHYAZQBjAHQAbwByACwAIAAgACAAIABMAEEATQBCAEQAQQAoAEIAWQBSAE8AVwAoAGIAaQBuAF8AYQByAHIAKAApACwAQwBPAE4AQwBBAFQAKQApACwAXABuACAAIAAgACAAYgBpAG4AXwByAGUAcwB1AGwAdAAsACAAIAAgACAATABBAE0AQgBEAEEAKABJAEYAKABJAHMAVgBlAGMAdABvAHIAPwAsAGIAaQBuAF8AdgBlAGMAdABvAHIAKAApACwAYgBpAG4AXwBhAHIAcgAoACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQAtAHMAaABhAHAAaQBuAGcAIAAmACAAZABlAGwAaQB2AGUAcgB5AFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgACAAIAAgACAAIAAgAEkARgAoAEkAcwAyAEQAPwAsAFcAUgBBAFAAUgBPAFcAUwAoAGIAaQBuAF8AdgBlAGMAdABvAHIAKAApACwAdwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAEkAcwBTAGMAYQBsAGEAcgA/ACwASQBzAFYAZQByAHQAaQBjAGEAbAA/ACkALABiAGkAbgBfAHIAZQBzAHUAbAB0ACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAUgBBAE4AUwBQAE8AUwBFACgAYgBpAG4AXwByAGUAcwB1AGwAdAAoACkAKQApACkALABcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEUATgAwADUAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABEAGUAYwAyAEcAcgBhAHkAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEQAZQBjADIAQgBpAG4AuwMsACAAQgBpAG4AMgBHAHIAYQB5ALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AbgB2AGUAcgB0AHMAIABuAG8AbgARIG4AZQBnAGEAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAgAGkAbgB0AG8AIABHAHIAYQB5ABEgYwBvAGQAZQAgAHYAYQBsAHUAZQBzAC4AIABTAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAsACAAMQBEACwAXABuACAAIAAgACAAYQBuAGQAIAAyAEQAIABpAG4AcAB1AHQAcwAgAHcAaQB0AGgAIABmAHUAbABsACAAcwBoAGEAcABlACAAcAByAGUAcwBlAHIAdgBhAHQAaQBvAG4ALgAgAE8AdQB0AHAAdQB0ACAAYwBhAG4AIABiAGUAIAByAGUAdAB1AHIAbgBlAGQAIABlAGkAdABoAGUAcgBcAG4AIAAgACAAIABhAHMAIABjAG8AbgBjAGkAcwBlACAARwByAGEAeQARIGMAbwBkAGUAIABzAHQAcgBpAG4AZwBzACAAbwByACAAYQBzACAAZQB4AHAAbABvAGQAZQBkACAAMgBEACAAYgBpAHQAESBhAHIAcgBhAHkAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAG4AdQBtAGIAZQByAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAbgBvAG4AESBuAGUAZwBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMALgBcAG4AXABuACAAIAAgACAAWwBjAG8AbgBjAGkAcwBlAF0AXABuACAAIAAgACAAIAAgACAAIABPAHAAdABpAG8AbgBhAGwALgAgAFQAUgBVAEUAIACSISAAcgBlAHQAdQByAG4AIABHAHIAYQB5ACAAYwBvAGQAZQAgAGEAcwAgAGMAbwBuAGMAYQB0AGUAbgBhAHQAZQBkACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACAAIAAgACAAIAAgACAATwBtAGkAdAB0AGUAZAAgAJIhIAByAGUAdAB1AHIAbgAgAGUAeABwAGwAbwBkAGUAZAAgADIARAAgAEcAcgBhAHkAESBjAG8AZABlACAAYgBpAHQAIABhAHIAcgBhAHkAcwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABEAGUAYwAyAEIAaQBuALsDIAB0AG8AIABvAGIAdABhAGkAbgAgAGIAaQBuAGEAcgB5ACwAIAB0AGgAZQBuACAAQgBpAG4AMgBHAHIAYQB5ALsDIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAdABvACAARwByAGEAeQAgAGMAbwBkAGUALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABzAGgAYQBwAGUAIABtAGEAdABjAGgAZQBzACAAaQBuAHAAdQB0ACAAcwBoAGEAcABlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQBjADIARwByAGEAeQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABuAHUAbQBiAGUAcgAsAFwAbgAgACAAIAAgAFsAYwBvAG4AYwBpAHMAZQBdACwAXABuACAAIAAgACAAQgBpAG4AMgBHAHIAYQB5ALsDKABEAGUAYwAyAEIAaQBuALsDKABuAHUAbQBiAGUAcgApACwAIABjAG8AbgBjAGkAcwBlACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4ALwAvACAAWwBDAEIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ALwAvACAALQAtAC0AIwAjACAAMAA5ACAAFCAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAVABoAGUAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzACAAYwBhAHQAZQBnAG8AcgB5ACAAcAByAG8AdgBpAGQAZQBzACAAaABpAGcAaAARIHAAZQByAGYAbwByAG0AYQBuAGMAZQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABmAG8AcgBcAG4AIAAgACAAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAsACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMALAAgAHMAdQBiAHMAZQB0AHMALAAgAGEAbgBkACAAcgBlAGwAYQB0AGUAZAAgAHMAdAByAHUAYwB0AHUAcgBlAHMALgBcAG4AXABuAEYAdQBuAGMAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAFAAZQByAG0AUgC7A1wAbgAgACAAIAAgACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaQB0AGgAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAIAAoAGsAESB0AHUAcABsAGUAcwAgAGQAcgBhAHcAbgAgAGYAcgBvAG0AIABuACAAaQB0AGUAbQBzACkALgBcAG4AXABuACAAIAAgACAAIiAgAFAAZQByAG0AuwNcAG4AIAAgACAAIAAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoAG8AdQB0ACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AC4AXABuAFwAbgAgACAAIAAgACIgIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwBSALsDXABuACAAIAAgACAAIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAuAFwAbgBcAG4AIAAgACAAIAAiICAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAuwNcAG4AIAAgACAAIAAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAB3AGkAdABoAG8AdQB0ACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AC4AXABuAFwAbgAgACAAIAAgACIgIABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwC7A1wAbgAgACAAIAAgACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABwAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaABlAHIAZQAgAG4AbwAgAGUAbABlAG0AZQBuAHQAIAByAGUAbQBhAGkAbgBzACAAaQBuACAAaQB0AHMAIABvAHIAaQBnAGkAbgBhAGwAIABwAG8AcwBpAHQAaQBvAG4ALgBcAG4AXABuACAAIAAgACAAIiAgAEsAbgBhAHAAUwBhAGMAawC7A1wAbgAgACAAIAAgACAAIAAgACAAUwBvAGwAdgBlAHMAIAB0AGgAZQAgAHMAdQBiAHMAZQB0ABEgcwB1AG0AIAAvACAAawBuAGEAcABzAGEAYwBrACAAZgBlAGEAcwBpAGIAaQBsAGkAdAB5ACAAcAByAG8AYgBsAGUAbQAgAHUAcwBpAG4AZwAgAHYAZQBjAHQAbwByAGkAegBlAGQAXABuACAAIAAgACAAIAAgACAAIABlAG4AdQBtAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGYAaQBsAHQAZQByAGkAbgBnAC4AXABuAFwAbgAgACAAIAAgACIgIABTAHUAYgBzAGUAdABHAGUAbgC7A1wAbgAgACAAIAAgACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABhAGwAbAAgAHMAdQBiAHMAZQB0AHMAIABvAGYAIABhACAAcwBlAHQAIAAoAHQAaABlACAAcABvAHcAZQByACAAcwBlAHQAKQAsACAAcgBlAHQAdQByAG4AZQBkACAAaQBuACAAYgBpAG4AYQByAHkAESBtAGEAcwBrAFwAbgAgACAAIAAgACAAIAAgACAAbwByAGQAZQByAC4AXABuAFwAbgAgACAAIAAgACIgIABTAHUAYgBzAGUAdABTAHUAbQC7A1wAbgAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AcwAgAGEAbABsACAAcwB1AGIAcwBlAHQAcwAgAHcAaABvAHMAZQAgAGUAbABlAG0AZQBuAHQAcwAgAHMAdQBtACAAdABvACAAYQAgAHQAYQByAGcAZQB0ACAAdgBhAGwAdQBlAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQByAGUAIABzAGgAYQBwAGUAESBwAHIAZQBzAGUAcgB2AGkAbgBnACAAYQBuAGQAIAByAGUAdAB1AHIAbgAgADIARAAgAGEAcgByAGEAeQBzACAAdwBoAGUAcgBlACAAZQBhAGMAaAAgAHIAbwB3AFwAbgAgACAAIAAgACAAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABjAG8AbQBiAGkAbgBhAHQAbwByAGkAYQBsACAAbwBiAGoAZQBjAHQALgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAG8AcABlAHIAYQB0AGUAIABvAG4AIABhAHIAcgBhAHkAcwAgAG8AZgAgAGkAdABlAG0AcwAsACAAbgBvAHQAIABqAHUAcwB0ACAAaQBuAHQAZQBnAGUAcgBzAC4AXABuACAAIAAgACAAIiAgAFQAaABlACAAdQBuAGQAZQByAGwAeQBpAG4AZwAgAGEAcgBjAGgAaQB0AGUAYwB0AHUAcgBlACAAdQBzAGUAcwAgAGEAIABmAHUAbgBuAGUAbAAgAG0AbwBkAGUAbAA6ACAAbABhAHIAZwBlACAAZQBuAHUAbQBlAHIAYQB0AGkAbwBuAHMAIABhAHIAZQBcAG4AIAAgACAAIAAgACAAZwBlAG4AZQByAGEAdABlAGQAIABvAG4AYwBlACAAYQBuAGQAIABmAGkAbAB0AGUAcgBlAGQAIABiAHkAIABvAHIAZABlAHIALAAgAHUAbgBpAHEAdQBlAG4AZQBzAHMALAAgAG8AcgAgAHAAbwBzAGkAdABpAG8AbgBhAGwAIABwAHIAZQBkAGkAYwBhAHQAZQBzAC4AXABuAFwAbgBFAG4AdQBtAGUAcgBhAHQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABHAGUAbgBlAHIAYQB0AGkAbgBnACAAZgB1AG4AYwB0AGkAbwBuACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAZQByAG0AUgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABmAHUAbABsACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHwAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwBSALsDIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGUAcgBtALsDIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDXABuACAAIAAgACAAIAAgACAAIAAoAGYAaQBsAHQAZQByACAAcgBlAHAAZQBhAHQAcwApACAAIAAgACAAIAAgACAAIAAoAGYAaQBsAHQAZQByACAAYgB5ACAAbwByAGQAZQByACkAIAAgACAAIAAgACgAZgBpAGwAdABlAHIAIABiAHkAIABwAG8AcwBpAHQAaQBvAG4AKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzALsDXABuACAAIAAgACAAIAAoAGYAaQBsAHQAZQByACAAcgBlAHAAZQBhAHQAcwAgACsAIABvAHIAZABlAHIAKQBcAG4AXABuAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCABEgQwBPAFIARQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAG8AcgBlACAAZwBlAG4AZQByAGEAdABpAG4AZwAgAGYAdQBuAGMAdABpAG8AbgAgAGYAbwByACAAYQBsAGwAIABjAG8AbQBiAGkAbgBhAHQAbwByAGkAYQBsACAAbwBwAGUAcgBhAHQAbwByAHMAIABpAG4AIAB0AGgAZQAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuACAAIAAgACAAYwBhAHQAZQBnAG8AcgB5AC4AIABQAHIAbwBkAHUAYwBlAHMAIABpAG4AZABlAHgAIABtAGEAdAByAGkAYwBlAHMAIABmAG8AcgAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgBzACwAIABjAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwAsACAAbQB1AGwAdABpAHMAZQB0AHMALABcAG4AIAAgACAAIABhAG4AZAAgAGQAZQByAGEAbgBnAGUAbQBlAG4AdABzACAAdQBzAGkAbgBnACAAYQAgAHYAZQBjAHQAbwByAGkAegBlAGQAIABmAHUAbgBuAGUAbAAgAGEAcgBjAGgAaQB0AGUAYwB0AHUAcgBlAC4AIABIAGkAZwBoAGUAcgARIGwAZQB2AGUAbABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4AcwAgACgAUABlAHIAbQBSALsDLAAgAFAAZQByAG0AuwMsACAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAUgC7AywAIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7AywAIABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwC7AykAXABuACAAIAAgACAAYQByAGUAIAB0AGgAaQBuACAAdwByAGEAcABwAGUAcgBzACAAYQByAG8AdQBuAGQAIAB0AGgAaQBzACAAZwBlAG4AZQByAGEAdABvAHIALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXABuACAAIAAgACAAIAAgACAAIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIABvAGYAIABpAHQAZQBtAHMALgAgAEkAdABlAG0AcwAgAG0AYQB5ACAAYgBlACAAbgB1AG0AYgBlAHIAcwAgAG8AcgAgAHQAZQB4AHQALgBcAG4AXABuACAAIAAgACAAawBcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBuAGcAdABoACAAbwBmACAAZQBhAGMAaAAgAHQAdQBwAGwAZQAgACgAawAgAGUiIAAwACkALgAgAE0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIALgBcAG4AXABuACAAIAAgACAAdAB5AHAAZQBcAG4AIAAgACAAIAAgACAAIAAgAFMAZQBsAGUAYwB0AG8AcgAgAGYAbwByACAAdABoAGUAIABjAG8AbQBiAGkAbgBhAHQAbwByAGkAYQBsACAAbQBvAGQAZQA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxACAAkiEgAFAAZQByAG0AdQB0AGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAgAJIhIABQAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgAHcAaQB0AGgAbwB1AHQAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADMAIACSISAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACAAkiEgAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaABvAHUAdAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAANQAgAJIhIABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABBAGwAbAAgAHIAZQBzAHUAbAB0AHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAgAGEAcwAgADIARAAgAGEAcgByAGEAeQBzACAAdwBoAGUAcgBlACAAZQBhAGMAaAAgAHIAbwB3ACAAaQBzACAAbwBuAGUAIAB0AHUAcABsAGUALgBcAG4AIAAgACAAIAAiICAASQBmACAAaQB0AGUAbQBzACAAYQByAGUAIABuAHUAbQBlAHIAaQBjACAAYQBuAGQAIABlAHEAdQBhAGwAIAB0AG8AIABTAEUAUQBVAEUATgBDAEUAKABuACkALAAgAHIAYQB3ACAAaQBuAGQAaQBjAGUAcwAgAGEAcgBlACAAcgBlAHQAdQByAG4AZQBkAC4AXABuACAAIAAgACAAIAAgAE8AdABoAGUAcgB3AGkAcwBlACwAIABpAHQAZQBtAHMAIABhAHIAZQAgAHMAdQBiAHMAdABpAHQAdQB0AGUAZAAgAGkAbgB0AG8AIAB0AGgAZQAgAGkAbgBkAGUAeAAgAGEAcgByAGEAeQBfADIARAAuAFwAbgAgACAAIAAgACIgIABNAGEAeABpAG0AdQBtACAAZQBuAHUAbQBlAHIAYQB0AGkAbwBuACAAcwBpAHoAZQAgAGkAcwAgAGMAYQBwAHAAZQBkACAAYQB0ACAAMQAsADAANAA4ACwANQA3ADYAIAByAG8AdwBzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEUAbgB1AG0AZQByAGEAdABlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGsALABcAG4AIAAgACAAIAB0AHkAcABlACwAXABuAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAGsAKQAsACAAawAgADwAIAAwACwAIABrACAAPgAgAEMATwBVAE4AVABBACgAaQB0AGUAbQBzACkAKQAsACMAVgBBAEwAVQBFACEALABcAG4AXABuACAAIAAgACAASQBGACgAQwBPAFUATgBUAEEAKABrACkAIAA8AD4AIAAxACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEMATwBVAE4AVABBACgAaQB0AGUAbQBzACkAIABeACAAawAgAD4AIAAxADAANAA4ADUANwA2ACwAIwBOAFUATQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAHQAZQBtAHMAXABuACAAIAAgACAAbABpAHMAdAAsACAAIAAgACAAVABPAEMATwBMACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIABuACwAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAGwAaQBzAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIAByAG8AdwBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAG4AIABeACAAawAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGEAcwBlACAAZwBlAG4AZQByAGEAdABvAHIAOgAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdABcAG4AIAAgACAAIABQAF8AcgAsACAAIAAgACAAIABMAEEATQBCAEQAQQAoADEAIAArACAATQBPAEQAKABRAFUATwBUAEkARQBOAFQAKABTAEUAUQBVAEUATgBDAEUAKABpACkALABuACAAXgAgAFMARQBRAFUARQBOAEMARQAoACwAIABrACwAIABrACAALQAgADEALAAgAC0AMQApACkALABuACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGUAcgBtAHUAdABhAHQAaQBvAG4AcwAgACgAbgBvACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0ACkAXABuACAAIAAgACAAUAAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAFAAXwByACgAKQAsAEkAUwBOAEEAKABCAFkAUgBPAFcAKABQAF8AcgAoACkALAAgAE0ATwBEAEUAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwAgAHcAaQB0AGgAIAByAGUAcABsAGEAYwBlAG0AZQBuAHQAXABuACAAIAAgACAAQwBfAHIALAAgACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAFAAXwByACgAKQAsAEIAWQBSAE8AVwAoAFAAXwByACgAKQAsAEwAQQBNAEIARABBACgAcgBvAHcALAAgAEEATgBEACgAcgBvAHcAIAA9ACAAUwBPAFIAVAAoAHIAbwB3ACwALAAsADEAKQApACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAIAAoAG4AbwAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAApAFwAbgAgACAAIAAgAEMALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgARgBJAEwAVABFAFIAKABDAF8AcgAoACkALABJAFMATgBBACgAQgBZAFIATwBXACgAQwBfAHIAKAApACwAIABNAE8ARABFACkAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAHIAYQBuAGcAZQBtAGUAbgB0AHMAXABuACAAIAAgACAARAAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABGAEkATABUAEUAUgAoAFAAXwByACgAKQAsAEIAWQBSAE8AVwAoAFAAXwByACgAKQAsAEwAQQBNAEIARABBACgAcgBvAHcALAAgAE4ATwBUACgATwBSACgAUwBFAFEAVQBFAE4AQwBFACgALAAgAGsAKQAgAD0AIAByAG8AdwApACkAKQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAGcAZQBuAGUAcgBhAHQAbwByAFwAbgAgACAAIAAgAGkAZAB4ACwAIAAgACAAIAAgAEwAQQBNAEIARABBACgAQwBIAE8ATwBTAEUAKAB0AHkAcABlACwAIABQAF8AcgAoACkALAAgAFAAKAApACwAIABDAF8AcgAoACkALAAgAEMAKAApACwAIABEACgAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB1AGIAcwB0AGkAdAB1AHQAZQAgAGkAdABlAG0AcwAgAHUAbgBsAGUAcwBzACAAdABoAGUAeQAgAGEAcgBlACAAZQB4AGEAYwB0AGwAeQAgADEALgAuAG4AXABuACAAIAAgACAATgBvAHQASQBuAHQAPwAsACAATgBPAFQAKABBAE4ARAAoAFMARQBRAFUARQBOAEMARQAoAG4AKQAgAD0AIABsAGkAcwB0ACkAKQAsAFwAbgAgACAAIAAgAGQAZQBsAGkAdgBlAHIALAAgAEkARgAoAE4AbwB0AEkAbgB0AD8ALAAgAEkATgBEAEUAWAAoAGwAaQBzAHQALAAgAGkAZAB4ACgAKQApACwAIABpAGQAeAAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBDAEIAMAAxAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUABlAHIAbQBSALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0ACAAKABrABEgdAB1AHAAbABlAHMAIABkAHIAYQB3AG4AIABmAHIAbwBtACAAbgAgAGkAdABlAG0AcwApAC4AXABuACAAIAAgACAARQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIAByAGUAcwB1AGwAdAAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAIABvAG4AZQAgAHAAZQByAG0AdQB0AGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoACAAawAuACAAUwB1AHAAcABvAHIAdABzAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAGEAbgBkACAAMgBEACAAaQB0AGUAbQAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQBzAC4AIABJAHQAZQBtAHMAIABtAGEAeQAgAGIAZQAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0AC4AXABuAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuAFwAbgAgACAAIAAgACAAIAAgACAATABlAG4AZwB0AGgAIABvAGYAIABlAGEAYwBoACAAdAB1AHAAbABlACAAKABrACAAZSIgADAAKQAuACAATQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABrACwAIAAxACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABlAHIAbQBSALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAXABuACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALAAgADEAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEMAQgAwADIAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABQAGUAcgBtALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuAHMAIAB3AGkAdABoAG8AdQB0ACAAcgBlAHAAbABhAGMAZQBtAGUAbgB0AC4AIABFAGEAYwBoACAAcgBvAHcAIABvAGYAIAB0AGgAZQAgAHIAZQBzAHUAbAB0ACAAcgBlAHAAcgBlAHMAZQBuAHQAcwBcAG4AIAAgACAAIABvAG4AZQAgAGsAESB0AHUAcABsAGUAIABkAHIAYQB3AG4AIABmAHIAbwBtACAAdABoAGUAIABpAG4AcAB1AHQAIABpAHQAZQBtAHMALAAgAHcAaQB0AGgAIABuAG8AIAByAGUAcABlAGEAdABlAGQAIABwAG8AcwBpAHQAaQBvAG4AcwAuACAAUwB1AHAAcABvAHIAdABzAFwAbgAgACAAIAAgAHMAYwBhAGwAYQByACwAIAAxAEQALAAgAGEAbgBkACAAMgBEACAAaQB0AGUAbQAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQBzAC4AIABJAHQAZQBtAHMAIABtAGEAeQAgAGIAZQAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0AC4AXABuAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuAFwAbgAgACAAIAAgACAAIAAgACAATABlAG4AZwB0AGgAIABvAGYAIABlAGEAYwBoACAAdAB1AHAAbABlACAAKABrACAAZSIgADAAKQAuACAATQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABrACwAIAAyACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABlAHIAbQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABpAHQAZQBtAHMALABcAG4AIAAgACAAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgAsAFwAbgAgACAAIAAgAEUAbgB1AG0AZQByAGEAdABlALsDKABpAHQAZQBtAHMALAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAIAAyACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBDAEIAMAAzAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAUgC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAbgB1AG0AZQByAGEAdABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAgACgAbQB1AGwAdABpAHMAZQB0AHMAKQAuACAARQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIAByAGUAcwB1AGwAdABcAG4AIAAgACAAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABrABEgZQBsAGUAbQBlAG4AdAAgAG0AdQBsAHQAaQBzAGUAdAAgAGQAcgBhAHcAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGkAdABlAG0AcwAsACAAdwBoAGUAcgBlACAAbwByAGQAZQByAFwAbgAgACAAIAAgAGQAbwBlAHMAIABuAG8AdAAgAG0AYQB0AHQAZQByACAAYQBuAGQAIAByAGUAcABlAGEAdABlAGQAIABzAGUAbABlAGMAdABpAG8AbgBzACAAYQByAGUAIABhAGwAbABvAHcAZQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQBzAC4AIABJAHQAZQBtAHMAIABtAGEAeQAgAGIAZQAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0AC4AXABuAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAUwBpAHoAZQAgAG8AZgAgAGUAYQBjAGgAIABjAG8AbQBiAGkAbgBhAHQAaQBvAG4AIAAoAGsAIABlIiAAMAApAC4AIABNAHUAcwB0ACAAYgBlACAAYQAgAHMAYwBhAGwAYQByAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAEUAbgB1AG0AZQByAGEAdABlALsDKABpAHQAZQBtAHMALAAgAGsALAAgADMAKQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwBSALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAXABuACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALAAgADMAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEMAQgAwADQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAQwBvAG0AYgBpAG4AYQB0AG8AcgBpAGMAcwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAEUAbgB1AG0AZQByAGEAdABlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgBzACAAdwBpAHQAaABvAHUAdAAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAuACAARQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAdABoAGUAIAByAGUAcwB1AGwAdAAgAHIAZQBwAHIAZQBzAGUAbgB0AHMAXABuACAAIAAgACAAbwBuAGUAIABrABEgZQBsAGUAbQBlAG4AdAAgAHMAdQBiAHMAZQB0ACAAZAByAGEAdwBuACAAZgByAG8AbQAgAHQAaABlACAAaQBuAHAAdQB0ACAAaQB0AGUAbQBzACwAIAB3AGgAZQByAGUAIABvAHIAZABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABtAGEAdAB0AGUAcgBcAG4AIAAgACAAIABhAG4AZAAgAHIAZQBwAGUAYQB0AGUAZAAgAHMAZQBsAGUAYwB0AGkAbwBuAHMAIABhAHIAZQAgAG4AbwB0ACAAYQBsAGwAbwB3AGUAZAAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGkAdABlAG0AcwBcAG4AIAAgACAAIAAgACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAGkAdABlAG0AcwAuACAASQB0AGUAbQBzACAAbQBhAHkAIABiAGUAIABuAHUAbQBiAGUAcgBzACAAbwByACAAdABlAHgAdAAuAFwAbgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAaQB6AGUAIABvAGYAIABlAGEAYwBoACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuACAAKABrACAAZSIgADAAKQAuACAATQB1AHMAdAAgAGIAZQAgAGEAIABzAGMAYQBsAGEAcgAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABrACwAIAA0ACkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQwBvAG0AYgBpAG4AYQB0AGkAbwBuAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAaQB0AGUAbQBzACwAXABuACAAIAAgACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALABcAG4AIAAgACAAIABFAG4AdQBtAGUAcgBhAHQAZQC7AygAaQB0AGUAbQBzACwAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgAsACAANAApAFwAbgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAANQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAZABlAHIAYQBuAGcAZQBtAGUAbgB0AHMAIABvAGYAIABsAGUAbgBnAHQAaAAgAGsALgAgAEEAIABkAGUAcgBhAG4AZwBlAG0AZQBuAHQAIABpAHMAIABhACAAcABlAHIAbQB1AHQAYQB0AGkAbwBuACAAaQBuACAAdwBoAGkAYwBoAFwAbgAgACAAIAAgAG4AbwAgAGUAbABlAG0AZQBuAHQAIABhAHAAcABlAGEAcgBzACAAaQBuACAAaQB0AHMAIABvAHIAaQBnAGkAbgBhAGwAIABwAG8AcwBpAHQAaQBvAG4ALgAgAEUAYQBjAGgAIAByAG8AdwAgAG8AZgAgAHQAaABlACAAcgBlAHMAdQBsAHQAXABuACAAIAAgACAAcgBlAHAAcgBlAHMAZQBuAHQAcwAgAG8AbgBlACAAZABlAHIAYQBuAGcAZQBkACAAawARIHQAdQBwAGwAZQAgAGQAcgBhAHcAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGkAdABlAG0AcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGkAdABlAG0AcwBcAG4AIAAgACAAIAAgACAAIAAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAGkAdABlAG0AcwAuACAASQB0AGUAbQBzACAAbQBhAHkAIABiAGUAIABuAHUAbQBiAGUAcgBzACAAbwByACAAdABlAHgAdAAuAFwAbgBcAG4AIAAgACAAIABpAHQAZQBtAHMAXwBjAGgAbwBzAGUAbgBcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBuAGcAdABoACAAbwBmACAAZQBhAGMAaAAgAHQAdQBwAGwAZQAgACgAawAgAGUiIAAwACkALgAgAE0AdQBzAHQAIABiAGUAIABhACAAcwBjAGEAbABhAHIALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABFAHEAdQBpAHYAYQBsAGUAbgB0ACAAdABvACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAawAsACAANQApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAGkAdABlAG0AcwBfAGMAaABvAHMAZQBuACwAXABuACAAIAAgACAARQBuAHUAbQBlAHIAYQB0AGUAuwMoAGkAdABlAG0AcwAsACAAaQB0AGUAbQBzAF8AYwBoAG8AcwBlAG4ALAAgADUAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEMAQgAwADYAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABLAG4AYQBwAFMAYQBjAGsAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAG8AbAB2AGUAcwAgAHQAaABlACAAMAARIDEAIABrAG4AYQBwAHMAYQBjAGsAIABwAHIAbwBiAGwAZQBtACAAYgB5ACAAZQBuAHUAbQBlAHIAYQB0AGkAbgBnACAAYQBsAGwAIABzAHUAYgBzAGUAdABzACAAbwBmACAAaQB0AGUAbQBzACAAYQBuAGQAXABuACAAIAAgACAAcwBlAGwAZQBjAHQAaQBuAGcAIAB0AGgAZQAgAGYAZQBhAHMAaQBiAGwAZQAgAHAAYQBjAGsAKABzACkAIAB3AGkAdABoACAAbQBhAHgAaQBtAHUAbQAgAHQAbwB0AGEAbAAgAHYAYQBsAHUAZQAuACAAVQBzAGUAcwAgAGEAIABiAHIAdQB0AGUAESBmAG8AcgBjAGUALABcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgBpAHoAZQBkACAAYgBpAHQAESBtAGEAcwBrACAAZwBlAG4AZQByAGEAdABvAHIAIABhAG4AZAAgAHMAdQBwAHAAbwByAHQAcwAgAGIAbwB0AGgAIABuAHUAbQBlAHIAaQBjACAAYQBuAGQAIAB0AGUAeAB0ACAAaQB0AGUAbQAgAGwAYQBiAGUAbABzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAbwBmACAAaQB0AGUAbQAgAGwAYQBiAGUAbABzACAAKABuAHUAbQBiAGUAcgBzACAAbwByACAAdABlAHgAdAApAC4AXABuAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwBcAG4AIAAgACAAIAAgACAAIAAgAEEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIAB2AGEAbAB1AGUAcwAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIAB0AG8AIABlAGEAYwBoACAAaQB0AGUAbQAuAFwAbgBcAG4AIAAgACAAIAB3AGUAaQBnAGgAdABzAFwAbgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAHcAZQBpAGcAaAB0AHMAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAdABvACAAZQBhAGMAaAAgAGkAdABlAG0ALgBcAG4AXABuACAAIAAgACAAYwBhAHAAYQBjAGkAdAB5AFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIAIABuAHUAbQBlAHIAaQBjACAAdwBlAGkAZwBoAHQAIABsAGkAbQBpAHQALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABpAHQAZQBtAHMALAAgAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwAsACAAYQBuAGQAIAB3AGUAaQBnAGgAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AUgBPAFcALgBcAG4AIAAgACAAIAAiICAAYwBhAHAAYQBjAGkAdAB5ACAAaQBzACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAHQAbwAgAGEAIABzAGMAYQBsAGEAcgAgAHcAaQB0AGgAIABJAE4ARABFAFgAKABjAGEAcABhAGMAaQB0AHkALAAxACwAMQApAC4AXABuACAAIAAgACAAIiAgAE0AYQB4AGkAbQB1AG0AIABpAHQAZQBtACAAYwBvAHUAbgB0ACAAaQBzACAAYwBhAHAAcABlAGQAIABhAHQAIAAyADAAIAB0AG8AIABhAHYAbwBpAGQAIABjAG8AbQBiAGkAbgBhAHQAbwByAGkAYQBsACAAZQB4AHAAbABvAHMAaQBvAG4ALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ASwBuAGEAcABTAGEAYwBrALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwAsAFwAbgAgACAAIAAgAHcAZQBpAGcAaAB0AHMALABcAG4AIAAgACAAIABjAGEAcABhAGMAaQB0AHkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAFQAbwBvAE0AYQBuAHkASQB0AGUAbQBzAD8ALAAgACAAIABSAE8AVwBTACgAaQB0AGUAbQBzACkAIAAqACAAQwBPAEwAVQBNAE4AUwAoAGkAdABlAG0AcwApACAAPgAgADIAMAAsAFwAbgAgACAAIAAgAFQAZQB4AHQASQB0AGUAbQBWAGEAbAA/ACwAIAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAHYAYQBsAHUAZQBfAG8AZgBfAGkAdABlAG0AcwApACkALABcAG4AIAAgACAAIABUAGUAeAB0AFcAZQBpAGcAaAB0AHMAPwAsACAAIAAgACAATwBSACgASQBTAFQARQBYAFQAKAB3AGUAaQBnAGgAdABzACkAKQAsAFwAbgAgACAAIAAgAFQAZQB4AHQAQwBhAHAAYQBjAGkAdAB5AD8ALAAgACAAIABPAFIAKABJAFMAVABFAFgAVAAoAGMAYQBwAGEAYwBpAHQAeQApACkALABcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMATQBhAHQAYwBoAD8ALAAgACAATwBSACgAQwBPAFUATgBUAEEAKABpAHQAZQBtAHMAKQAgADwAPgAgAEMATwBVAE4AVABBACgAdgBhAGwAdQBlAF8AbwBmAF8AaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABpAHQAZQBtAHMAKQAgADwAPgAgAEMATwBVAE4AVABBACgAdwBlAGkAZwBoAHQAcwApACkALABcAG4AXABuACAAIAAgACAAcwBjAGUAbgBhAHIAaQBvAHMALAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVABlAHgAdABJAHQAZQBtAFYAYQBsAD8ALABUAGUAeAB0AFcAZQBpAGcAaAB0AHMAPwAsAFQAZQB4AHQAQwBhAHAAYQBjAGkAdAB5AD8ALABTAGgAYQBwAGUATQBpAHMATQBhAHQAYwBoAD8AKQAsAFwAbgBcAG4AIAAgACAAIABlAHgAaQB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAcwBjAGUAbgBhAHIAaQBvAHMAKQAsAFwAbgAgACAAIAAgAGUAcgByAG8AcgBzACwAIAAgACAAIAAgACAAIAAgACAAIAB7AFwAIgAjAFYAQQBMAFUARQAtAEkAVABFAE0AIQBcACIAOwBcACIAIwBWAEEATABVAEUALQBXAEUASQBHAEgAVABTACEAXAAiADsAXAAiACMAVgBBAEwAVQBFAC0AQwBBAFAAQQBDAEkAVABZACEAXAAiADsAXAAiACMASQBOAFAAVQBUAC0ATQBJAFMATQBBAFQAQwBIACEAXAAiAH0ALABcAG4AXABuACAAIAAgACAAYQBsAGUAcgB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAUgBSAEEAWQBUAE8AVABFAFgAVAAoAEYASQBMAFQARQBSACgAZQByAHIAbwByAHMALAAgAHMAYwBlAG4AYQByAGkAbwBzACkAKQAsAFwAbgBcAG4ASQBGACgAVABvAG8ATQBhAG4AeQBJAHQAZQBtAHMAPwAsAFwAIgAjAFQATwBPAC0ATQBBAE4AWQAtAEkAVABFAE0AUwAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABlAHgAaQB0ACwAYQBsAGUAcgB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEYAbABhAHQAdABlAG4AIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIABpAHQAZQBtAHMALAAgACAAIAAgACAAIAAgACAAIAAgAFQATwBSAE8AVwAoAGkAdABlAG0AcwApACwAXABuACAAIAAgACAAdgBhAGwAdQBlAF8AbwBmAF8AaQB0AGUAbQBzACwAIABUAE8AUgBPAFcAKAB2AGEAbAB1AGUAXwBvAGYAXwBpAHQAZQBtAHMAKQAsAFwAbgAgACAAIAAgAHcAZQBpAGcAaAB0AHMALAAgACAAIAAgACAAIAAgACAAVABPAFIATwBXACgAdwBlAGkAZwBoAHQAcwApACwAXABuACAAIAAgACAAYwBhAHAAYQBjAGkAdAB5ACwAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKABjAGEAcABhAGMAaQB0AHkALAAgADEALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAGEAYgBlAGwAcwBcAG4AIAAgACAAIABsAGEAYgBlAGwAcwAsACAAIAAgACAAIAAgACAAIAAgAHsAXAAiAEkAdABlAG0AcwBcACIAOwAgAFwAIgBWAGEAbAB1AGUAXAAiADsAIABcACIAVwBlAGkAZwBoAHQAXAAiADsAIABcACIAUABhAGMAawBcACIAfQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAG4AdQBtAGUAcgBhAHQAaQBvAG4AXABuACAAIAAgACAAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8AVQBOAFQAQQAoAGkAdABlAG0AcwApACwAXABuACAAIAAgACAAQwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAyACAAXgAgAG4AIAAtACAAMQApACwAXABuACAAIAAgACAAYgBpAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAYwAyAEIAaQBuALsDKABDACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAVwBlAGkAZwBoAHQAIABmAGUAYQBzAGkAYgBpAGwAaQB0AHkAXABuACAAIAAgACAAdwBfAGEAcgByACwAIAAgACAAIAAgACAAIAAgACAAIABiAGkAbgAgACoAIAB3AGUAaQBnAGgAdABzACwAXABuACAAIAAgACAAZgBlAGEAcwBpAGIAbABlAD8ALAAgACAAIAAgACAAIABCAFkAUgBPAFcAKAB3AF8AYQByAHIALAAgAFMAVQBNACkAIAA8AD0AIABjAGEAcABhAGMAaQB0AHkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAdQBlACAAYwBvAG0AcAB1AHQAYQB0AGkAbwBuAFwAbgAgACAAIAAgAHYAYQBsAF8AYQByAHIALAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABiAGkAbgAgACoAIAB2AGEAbAB1AGUAXwBvAGYAXwBpAHQAZQBtAHMALAAgAGYAZQBhAHMAaQBiAGwAZQA/ACwAIAAwACkALABcAG4AIAAgACAAIAB0AG8AdABhAGwAcwAsACAAIAAgACAAIAAgACAAIAAgAEIAWQBSAE8AVwAoAHYAYQBsAF8AYQByAHIALAAgAFMAVQBNACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIABvAHAAdABpAG0AYQBsACAAcABhAGMAawAoAHMAKQBcAG4AIAAgACAAIABwAGEAYwBrACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABGAEkATABUAEUAUgAoAHYAYQBsAF8AYQByAHIALAAgAE0AQQBYACgAdABvAHQAYQBsAHMAKQAgAD0AIAB0AG8AdABhAGwAcwAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBpAG4AYQBsACAAdABhAGIAbABlAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAASQBGAE4AQQAoAEgAUwBUAEEAQwBLACgAbABhAGIAZQBsAHMALAAgAFYAUwBUAEEAQwBLACgAaQB0AGUAbQBzACwAIAB2AGEAbAB1AGUAXwBvAGYAXwBpAHQAZQBtAHMALAAgAHcAZQBpAGcAaAB0AHMALAAgAHAAYQBjAGsAKQApACwAXAAiAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAANwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFMAdQBiAHMAZQB0AEcAZQBuALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARABlAGMAMgBCAGkAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIABhAGwAbAAgAG4AbwBuABEgZQBtAHAAdAB5ACAAcwB1AGIAcwBlAHQAcwAgAG8AZgAgAGEAIABzAHUAcABwAGwAaQBlAGQAIABsAGkAcwB0ACAAdQBzAGkAbgBnACAAYgByAHUAdABlABEgZgBvAHIAYwBlAFwAbgAgACAAIAAgAGIAaQB0AG0AYQBzAGsAaQBuAGcALgAgAEUAYQBjAGgAIAByAG8AdwAgAG8AZgAgAHQAaABlACAAcgBlAHMAdQBsAHQAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABzAHUAYgBzAGUAdAAsACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhAFwAbgAgACAAIAAgAGMAbwBtAG0AYQARIHMAZQBwAGEAcgBhAHQAZQBkACAAcwB0AHIAaQBuAGcALgAgAFMAdQBwAHAAbwByAHQAcwAgAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0ACAAaQB0AGUAbQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAcwBlAHQAXABuACAAIAAgACAAIAAgACAAIABBAHIAcgBhAHkAIABvAGYAIABpAHQAZQBtAHMAIAAoAG4AdQBtAGIAZQByAHMAIABvAHIAIAB0AGUAeAB0ACkALgAgAEYAbABhAHQAdABlAG4AZQBkACAAdwBpAHQAaAAgAFQATwBSAE8AVwAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAE0AYQB4AGkAbQB1AG0AIABpAHQAZQBtACAAYwBvAHUAbgB0ACAAaQBzACAAYwBhAHAAcABlAGQAIABhAHQAIAAyADAALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUwB1AGIAcwBlAHQARwBlAG4AuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcwBlAHQALABcAG4AXABuAEkARgAoAFIATwBXAFMAKABzAGUAdAApACAAKgAgAEMATwBMAFUATQBOAFMAKABzAGUAdAApACAAPgAgADIAMAAsAFwAIgAjAFQATwBPAC0ATQBBAE4AWQAtAEkAVABFAE0AUwAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAHMAZQB0ACwAIAAgACAAIABUAE8AUgBPAFcAKABzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGkAdABlAG0AcwBcAG4AIAAgACAAIABuACwAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQB0ACAAbQBhAHMAawBzACAAKABlAHgAYwBsAHUAZABlACAAMAApAFwAbgAgACAAIAAgAEMALAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAyACAAXgAgAG4AIAAtACAAMQApACwAXABuACAAIAAgACAAYgBpAG4ALAAgACAAIAAgAEQAZQBjADIAQgBpAG4AuwMoAEMALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHAAcABsAHkAIABtAGEAcwBrAFwAbgAgACAAIAAgAG0AYQBzAGsAZQBkACwAIABJAEYAKABiAGkAbgAsACAAcwBlAHQALAAgAFwAIgBcACIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgB2AGUAcgB0ACAAZQBhAGMAaAAgAG0AYQBzAGsAZQBkACAAcgBvAHcAIABpAG4AdABvACAAYQAgAGMAbwBtAHAAYQBjAHQAIABzAHUAYgBzAGUAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIABCAFkAUgBPAFcAKABtAGEAcwBrAGUAZAAsACAATABBAE0AQgBEAEEAKAB2ACwAIABUAEUAWABUAEoATwBJAE4AKABcACIALAAgAFwAIgAsACAAMQAsACAAdgApACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAQwBCADAAOABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFMAdQBiAHMAZQB0AFMAdQBtALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABDAG8AbQBiAGkAbgBhAHQAbwByAGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAARABlAGMAMgBCAGkAbgC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHQAdQByAG4AcwAgAGEAbABsACAAcwB1AGIAcwBlAHQAcwAgAG8AZgAgAGEAIABuAHUAbQBlAHIAaQBjACAAcwBlAHQAIAB3AGgAbwBzAGUAIABlAGwAZQBtAGUAbgB0AHMAIABzAHUAbQAgAGUAeABhAGMAdABsAHkAIAB0AG8AIABhACAAdABhAHIAZwBlAHQALgBcAG4AIAAgACAAIABVAHMAZQBzACAAYgByAHUAdABlABEgZgBvAHIAYwBlACAAYgBpAHQAbQBhAHMAawBpAG4AZwAgACgAbgAgAGQiIAAyADAAKQAuACAARQBhAGMAaAAgAHMAdQBiAHMAZQB0ACAAaQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAYQAgAGMAbwBtAHAAYQBjAHQAXABuACAAIAAgACAAYwBvAG0AbQBhABEgcwBlAHAAYQByAGEAdABlAGQAIABzAHQAcgBpAG4AZwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAHMAZQB0AFwAbgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGkAdABlAG0AcwAuACAARgBsAGEAdAB0AGUAbgBlAGQAIAB3AGkAdABoACAAVABPAFIATwBXAC4AIABUAGUAeAB0ACAAaQBzACAAbgBvAHQAIABhAGwAbABvAHcAZQBkAC4AXABuAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0AFwAbgAgACAAIAAgACAAIAAgACAAUwBjAGEAbABhAHIAIABuAHUAbQBlAHIAaQBjACAAdABhAHIAZwBlAHQAIABzAHUAbQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEUAbQBwAHQAeQAgAHMAdQBiAHMAZQB0ACAAaQBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAYwBvAG4AcwB0AHIAdQBjAHQAaQBvAG4AIAAoAGIAaQB0AG0AYQBzAGsAIAAwACAAbwBtAGkAdAB0AGUAZAApAC4AXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBOAE8ALQBTAE8ATABVAFQASQBPAE4AIQBcACIAIABpAGYAIABuAG8AIABzAHUAYgBzAGUAdABzACAAbQBhAHQAYwBoACAAdABoAGUAIAB0AGEAcgBnAGUAdAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBTAHUAYgBzAGUAdABTAHUAbQC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABzAGUAdAAsAFwAbgAgACAAIAAgAHQAYQByAGcAZQB0ACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAcwBjAGEAbABhAHIAXABuACAAIAAgACAAdABhAHIAZwBlAHQALAAgAEkATgBEAEUAWAAoAHQAYQByAGcAZQB0ACwAIAAxACwAIAAxACkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAFQAbwBvAE0AYQBuAHkASQB0AGUAbQBzAD8ALAAgAFIATwBXAFMAKABzAGUAdAApACAAKgAgAEMATwBMAFUATQBOAFMAKABzAGUAdAApACAAPgAgADIAMAAsAFwAbgAgACAAIAAgAFQAZQB4AHQAUwBlAHQAPwAsACAAIAAgACAAIAAgAE8AUgAoAEkAUwBFAFIAUgBPAFIAKAAtAC0AcwBlAHQAKQApACwAXABuACAAIAAgACAAVABlAHgAdABUAGEAcgBnAGUAdAA/ACwAIAAgACAASQBTAEUAUgBSAE8AUgAoAC0ALQB0AGEAcgBnAGUAdAApACwAXABuAFwAbgBJAEYAKABUAG8AbwBNAGEAbgB5AEkAdABlAG0AcwA/ACwAIABcACIAIwBUAE8ATwAtAE0AQQBOAFkALQBJAFQARQBNAFMAIQBcACIALABcAG4AXABuACAAIAAgACAASQBGACgAVABlAHgAdABTAGUAdAA/ACwAIABcACIAIwBUAEUAWABUAC0AUwBFAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABUAGUAeAB0AFQAYQByAGcAZQB0AD8ALAAgAFwAIgAjAFQARQBYAFQALQBUAEEAUgBHAEUAVAAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AFwAbgAgACAAIAAgAHMAZQB0ACwAIAAgACAAIAAgACAAVABPAFIATwBXACgALQAtAHMAZQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAaQB0AGUAbQBzAFwAbgAgACAAIAAgAG4ALAAgACAAIAAgACAAIAAgACAAQwBPAFUATgBUAEEAKABzAGUAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEIAaQB0ACAAbQBhAHMAawBzACAAKABlAHgAYwBsAHUAZABlACAAMAApAFwAbgAgACAAIAAgAEMALAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAMgAgAF4AIABuACAALQAgADEAKQAsAFwAbgAgACAAIAAgAGIAaQBuACwAIAAgACAAIAAgACAARABlAGMAMgBCAGkAbgC7AygAQwAsACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcABwAGwAeQAgAG0AYQBzAGsAXABuACAAIAAgACAAdgBhAGwAXwBhAHIAcgAsACAAIABJAEYAKABiAGkAbgAsACAAcwBlAHQALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AYwBhAHQAZQAgAHQAYQByAGcAZQB0ACAAcwB1AG0AXABuACAAIAAgACAAYgBvAG8AbAAsACAAIAAgACAAIABCAFkAUgBPAFcAKAB2AGEAbABfAGEAcgByACwAIABTAFUATQApACAAPQAgAHQAYQByAGcAZQB0ACwAXABuACAAIAAgACAAZgBvAHUAbgBkACwAIAAgACAAIABGAEkATABUAEUAUgAoAHYAYQBsAF8AYQByAHIALAAgAGIAbwBvAGwALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgB2AGUAcgB0ACAAZQBhAGMAaAAgAHMAdQBiAHMAZQB0ACAAdABvACAAYQAgAGMAbwBtAHAAYQBjAHQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIABDAG8AbgBjAGkAcwBlALsDLAAgAEwAQQBNAEIARABBACgAdgAsACAAVABFAFgAVABKAE8ASQBOACgAXAAiACwAIABcACIALAAgADEALAAgAFQARQBYAFQAKAB2ACwAIABcACIAMAA7AC0AMAA7ADsAXAAiACkAKQApACwAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIABCAFkAUgBPAFcAKABmAG8AdQBuAGQALAAgAEMAbwBuAGMAaQBzAGUAuwMpACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBuAGQAbABlACAAbgBvACAAbQBhAHQAYwBoAGUAcwBcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgAEkARgAoAFMAVQBNACgATABFAE4AKAByAGUAcwB1AGwAdAApACkAIAA9ACAAMAAsACAAXAAiACMATgBPAC0AUwBPAEwAVQBUAEkATwBOACEAXAAiACwAIAByAGUAcwB1AGwAdAApACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AKQApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAvACAAWwBHAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ALwAvACAALQAtAC0AIwAjACAAMQAwACAAFCAgAEcAcgBpAGQAIABEAGkAYQBnAG4AbwBzAHQAaQBjAHMAXABuAC8ALwAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AXABuAC8AKgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwByAGkAZAAgAEQAaQBhAGcAbgBvAHMAdABpAGMAcwAgAGMAbwBuAHQAYQBpAG4AcwAgAGYAdQBuAGMAdABpAG8AbgBzACAAdwBoAG8AcwBlACAAcAB1AHIAcABvAHMAZQAgAGkAcwAgAHQAbwAgAGUAeABwAG8AcwBlACwAIABhAG4AbgBvAHQAYQB0AGUALABcAG4AIAAgACAAIABvAHIAIABlAHgAcABsAGEAaQBuACAAdABoAGUAIABpAG4AdABlAHIAbgBhAGwAIABzAHQAcgB1AGMAdAB1AHIAZQAgAG8AZgAgAGEAIABnAHIAaQBkAC4AIABEAGkAYQBnAG4AbwBzAHQAaQBjAHMAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGEAcgBlAFwAbgAgACAAIAAgAHUAcwBlAGQAIABmAG8AcgAgAGQAZQBiAHUAZwBnAGkAbgBnACwAIABpAG4AdAByAG8AcwBwAGUAYwB0AGkAbwBuACwAIAB2AGkAcwB1AGEAbABpAHoAYQB0AGkAbwBuACwAIABhAG4AZAAgAHMAdAByAHUAYwB0AHUAcgBhAGwAIABhAG4AYQBsAHkAcwBpAHMALgBcAG4AXABuAEYAdQBuAGMAdABpAG8AbgBzADoAXABuACAAIAAgACAAIiAgAFIAZQB2AGUAYQBsALsDXABuACAAIAAgACAAIAAgACAAIABpAG4AcwBwAGUAYwB0AHMAIABhACAAYQByAHIAYQB5AF8AMgBEACAAbwBmACAAZABhAHQAYQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAGUAaQB0AGgAZQByADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACIgIABBACAAdABvAHAALQBsAGUAdgBlAGwAIABzAHUAbQBtAGEAcgB5ACAAbwBmACAAcwBlAG0AYQBuAHQAaQBjACAAbQBlAHQAcgBpAGMAcwAgACgATgB1AG0AYgBlAHIAcwAsACAAVABlAHgAdABzACwAIABFAHIAcgBvAHIAcwAsACAAZQB0AGMALgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAiICAAQQAgAHYAZQByAGIAbwBzAGUALAAgAGMAZQBsAGwALQBiAHkALQBjAGUAbABsACAAbgBhAHIAcgBhAHQAaQBvAG4AIABvAGYAIAB0AGEAZwBzACAAcABlAHIAIABjAGUAbABsAFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsARwBEADAAMQBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFIAZQB2AGUAYQBsALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABHAHIAaQBkACAARABpAGEAZwBuAG8AcwB0AGkAYwBzAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHYAZQBhAGwAuwMgAGkAbgBzAHAAZQBjAHQAcwAgAGEAIABhAHIAcgBhAHkAXwAyAEQAIABvAGYAIABkAGEAdABhACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAZQBpAHQAaABlAHIAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABBACAAdABvAHAALQBsAGUAdgBlAGwAIABzAHUAbQBtAGEAcgB5ACAAbwBmACAAcwBlAG0AYQBuAHQAaQBjACAAbQBlAHQAcgBpAGMAcwAgACgATgB1AG0AYgBlAHIAcwAsACAAVABlAHgAdABzACwAIABFAHIAcgBvAHIAcwAsACAAZQB0AGMALgApAFwAbgAgACAAIAAgACAAIAAgACAAIiAgAEEAIAB2AGUAcgBiAG8AcwBlACwAIABjAGUAbABsAC0AYgB5AC0AYwBlAGwAbAAgAG4AYQByAHIAYQB0AGkAbwBuACAAbwBmACAAdABhAGcAcwAgAHAAZQByACAAYwBlAGwAbABcAG4AIAAgACAAIABTAHUAcABwAG8AcgB0AHMAIABvAHAAdABpAG8AbgBhAGwAIABkAGUAbABpAG0AaQB0AGUAcgAgAGMAbwBuAHQAcgBvAGwAIABhAG4AZAAgAGIAbABhAG4AawAtAGEAdwBhAHIAZQAgAG8AcAB0AGkAbQBpAHoAYQB0AGkAbwBuAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZABhAHQAYQBcAG4AIAAgACAAIAAgACAAIAAgAEQAYQB0AGEAIAB0AG8AIABiAGUAIABpAG4AcwBwAGUAYwB0AGUAZAAgACgAYQBuAHkAIABzAGMAYQBsAGEAcgAsACAAdgBlAGMAdABvAHIALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQApAC4AXABuAFwAbgAgACAAIAAgAEkAcwBWAGUAcgBiAG8AcwBlAD8AIAAgAFsAbwBwAHQAaQBvAG4AYQBsAF0AXABuACAAIAAgACAAIAAgACAAIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgBzACAAYQAgAGEAcgByAGEAeQBfADIARAAgAG8AZgAgAG4AYQByAHIAYQB0AGEAYgBsAGUAIAB0AGEAZwBzACAAcABlAHIAIABjAGUAbABsAC4AXABuACAAIAAgACAAIAAgACAAIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAByAGUAdAB1AHIAbgBzACAAYQAgADkA1wAyACAAcwB1AG0AbQBhAHIAeQAgAHQAYQBiAGwAZQAuAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAG0AaQB0AGUAcgAgACAAIABbAG8AcAB0AGkAbwBuAGEAbABdAFwAbgAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIAIAB1AHMAZQBkACAAaQBuACAAdgBlAHIAYgBvAHMAZQAgAG0AbwBkAGUALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAFwAIgAsACAAXAAiAC4AXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBSAGUAdgBlAGEAbAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABkAGEAdABhACwAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgAFsASQBzAFYAZQByAGIAbwBzAGUAPwBdACwAXABuACAAIAAgACAAWwBkAGUAbABpAG0AaQB0AGUAcgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABkAGEAdABhACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBlAGwAbAAgAG0AZQB0AHIAaQBjACAAbABhAGIAZQBsAHMAXABuACAAIAAgACAAbQBlAHQAcgBpAGMAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAewBcACIATgB1AG0AYgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQB4AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AdQBtAGIAZQByAC0AcwB0AG8AcgBlAGQALQBhAHMALQB0AGUAeAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHIAcgBvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBuAHQAYQBpAG4AcwAgAHMAcABhAGMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbgB0AGEAaQBuAHMAIABzAHAAZQBjAGkAYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAbQB1AGwAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBsAGEAbgBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AZwBpAGMAYQBsAFwAIgB9ACwAXABuAFwAbgAgACAAIAAgAC8ALwAtAC0AIABMAG8AYwBhAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAC0ALQBcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAG0AYQB0AHIAaQBjAGUAcwAgAGEAbgBkACAAZQBuAHMAdQByAGUAIABiAGkAbgBhAHIAeQAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAEIAaQBuALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAdgAsACAAVABPAEMATwBMACgASQBGAEUAUgBSAE8AUgAoAHYALAAgADAAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAG0AbwB2AGUAIABlAHIAcgBvAHIAcwAgAGYAcgBvAG0AIABzAGMAYQBsAGEAcgBzAC4AXABuACAAIAAgACAAUgBlAG0AbwB2AGUATgBBALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAB2ACwAIABJAEYATgBBACgAdgAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAATwBwAHQAaQBvAG4AYQBsACAAZABlAGwAaQBtAGkAdABlAHIAIABmAG8AcgAgAHYAZQByAGIAbwBzAGUAIAByAGUAcABvAHIAdAAuAFwAbgAgACAAIAAgAGQAZQBsAGkAbQBpAHQAZQByACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZABlAGwAaQBtAGkAdABlAHIAKQAsACAAXAAiACwAIABcACIALAAgAGQAZQBsAGkAbQBpAHQAZQByACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBlAHIAYgBvAHMAZQAgAHIAZQBwAG8AcgB0ACAALQAgAHIAZQB0AHUAcgBuAHMAIABuAGEAcgByAGEAdABhAGIAbABlACAAdABhAGcAcwAgAGIAeQAgAGMAZQBsAGwALgAgAFQAZQByAG0AaQBuAGEAdABlAHMAIABlAGEAcgBsAHkAIABpAGYAIABiAGwAYQBuAGsALgBcAG4AIAAgACAAIABHAGUAdABEAGUAdABhAGkAbABzALsDLAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAGEALAAgAGIALAAgAGMALAAgAGQALAAgAGUALAAgAGYALAAgAGcALAAgAGgALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQAsACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAYQAsACAAYgAsACAAYwAsACAAZAAsACAAUgBlAG0AbwB2AGUATgBBALsDKABlACkALAAgAFIAZQBtAG8AdgBlAE4AQQC7AygAZgApACwAIABnACwAIABoACwAIABpACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAZQB0AGEAaQBsACwAIABJAEYAKABoACwAIABcACIAQgBsAGEAbgBrAFwAIgAsACAAVABPAEMATwBMACgASQBGAFMAKABtACwAIABtAGUAdAByAGkAYwBzACkALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABqAG8AaQBuAGUAZAAsACAAVABFAFgAVABKAE8ASQBOACgAZABlAGwAaQBtAGkAdABlAHIALAAgADEALAAgAGQAZQB0AGEAaQBsACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoAbwBpAG4AZQBkACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbABsAHMAIAB3AGkAdABoADoAXABuACAAIAAgACAATgB1AG0AYgBlAHIAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQBUAE8AQwBPAEwAKABJAFMATgBVAE0AQgBFAFIAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAFQAZQB4AHQAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AVABPAEMATwBMACgASQBTAFQARQBYAFQAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAE4AdQBtAGIAZQByAHMAXwBzAHQAbwByAGUAZABfAGEAcwBfAHQAZQB4AHQALAAgAFQATwBDAE8ATAAoAEkAUwBOAFUATQBCAEUAUgAoAEkARgBFAFIAUgBPAFIAKABkAGEAdABhACAAKwAgADAALAAgAFwAIgBcACIAKQApACAAKgAgAEkAUwBUAEUAWABUACgAZABhAHQAYQApACkALABcAG4AIAAgACAAIABDAGUAbABsAHMAXwB3AGkAdABoAF8AZQByAHIAbwByAHMALAAgACAAIAAgACAALQAtAFQATwBDAE8ATAAoAEkAUwBFAFIAUgBPAFIAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAFMAcABhAGMAZQBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AQgBpAG4AuwMoAEwARQBOACgAVABSAEkATQAoAGQAYQB0AGEAKQApACAAPAA+ACAATABFAE4AKABkAGEAdABhACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABQAGEAdAB0AGUAcgBuACAAbQBhAHQAYwBoAGUAcwAgAGYAbwByACAAcwBwAGUAYwBpAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAHMAXABuACAAIAAgACAAcABhAHQAdABlAHIAbgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBbAF4AQQAtAFoAYQAtAHoAMAAtADkAIAAuAF0AfABbAFwAXAB4AHsAMAAwAEEAMAB9AFwAXAB4AHsAMgAwADAAQgB9AC0AXABcAHgAewAyADAAMABEAH0AXQB8AFsAXABcAHQAXABcAG4AXABcAHIAXQB8AFsAXABcAHgAewAxAEYANgAwADAAfQAtAFwAXAB4AHsAMQBGADYANABGAH0AXQBcACIALABcAG4AIAAgACAAIABTAHAAZQBjAGkAYQBsAF8AYwBoAGEAcgBhAGMAdABlAHIAcwAsACAAIAAgACAALQAtAEIAaQBuALsDKABSAEUARwBFAFgAVABFAFMAVAAoAGQAYQB0AGEALAAgAHAAYQB0AHQAZQByAG4AKQApACwAXABuAFwAbgAgACAAIAAgAEYAbwByAG0AdQBsAGEAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AVABPAEMATwBMACgASQBTAEYATwBSAE0AVQBMAEEAKABkAGEAdABhACkAKQAsAFwAbgAgACAAIAAgAEIAbABhAG4AawBzACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AVABPAEMATwBMACgASQBTAEIATABBAE4ASwAoAGQAYQB0AGEAKQApACwAXABuACAAIAAgACAATABvAGcAaQBjAGEAbAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQBUAE8AQwBPAEwAKABJAFMATABPAEcASQBDAEEATAAoAGQAYQB0AGEAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE0AZQB0AHIAaQBjAHMAIABmAGwAYQB0AHQAZQBuAGUAZAAgAHIAbwB3AC0AdwBpAHMAZQAgAGEAbgBkACAAcwB0AGEAYwBrAGUAZAAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5AC4AXABuACAAIAAgACAAbQBlAHQAcgBpAGMAXwBzAHQAYQBjAGsALAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAHUAbQBiAGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAeAB0AHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AdQBtAGIAZQByAHMAXwBzAHQAbwByAGUAZABfAGEAcwBfAHQAZQB4AHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMAZQBsAGwAcwBfAHcAaQB0AGgAXwBlAHIAcgBvAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBwAGEAYwBlAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAcABlAGMAaQBhAGwAXwBjAGgAYQByAGEAYwB0AGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAG8AcgBtAHUAbABhAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAbABhAG4AawBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAG8AZwBpAGMAYQBsACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBlAHQAcgBpAGMAcwAgAHMAdQBtAG0AYQByAGkAegBlAGQAIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAdABvAHQAYQBsAHMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABPAEMATwBMACgAQgBZAEMATwBMACgAbQBlAHQAcgBpAGMAXwBzAHQAYQBjAGsALAAgAFMAVQBNACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8ALQAtACAAUgBlAHAAbwByAHQAaQBuAGcAIAAtAC0AXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAbwBwAC0AbABlAHYAZQBsACAAOQDXADIAIABzAHUAbQBtAGEAcgB5ACAAbwBmACAAZABhAHQAYQAuAFwAbgAgACAAIAAgAFMAdQBtAG0AYQByAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUwBPAFIAVAAoAEgAUwBUAEEAQwBLACgAbQBlAHQAcgBpAGMAcwAsACAAdABvAHQAYQBsAHMAKQAsACAAMgAsACAALQAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAGUAbABsAC0AYgB5AC0AYwBlAGwAbAAgAHIAZQBwAG8AcgB0ACAAbwBmACAAZABhAHQAYQAuAFwAbgAgACAAIAAgAFYAZQByAGIAbwBzAGUALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFcAUgBBAFAAUgBPAFcAUwAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgB1AG0AYgBlAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAeAB0AHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgB1AG0AYgBlAHIAcwBfAHMAdABvAHIAZQBkAF8AYQBzAF8AdABlAHgAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAGUAbABsAHMAXwB3AGkAdABoAF8AZQByAHIAbwByAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBwAGEAYwBlAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBwAGUAYwBpAGEAbABfAGMAaABhAHIAYQBjAHQAZQByAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBvAHIAbQB1AGwAYQBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAbABhAG4AawBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAbwBnAGkAYwBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwBlAHQARABlAHQAYQBpAGwAcwC7AykALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAFIAZQBwAG8AcgB0ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgASQBzAFYAZQByAGIAbwBzAGUAPwApACwAIABTAHUAbQBtAGEAcgB5ACgAKQAsACAAVgBlAHIAYgBvAHMAZQApACwAXABuACAAIAAgACAAUgBlAHAAbwByAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvAC8AIAAtAC0ARQBuAGQAIABvAGYAIABCAGkAZwBTAHAAaQBsAGwAIABNAG8AZAB1AGwAZQAtAC0AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIARABHAHIAaQBkALsDIgAsACIAQwBHAHIAaQBkALsDIgAsACIATQBHAHIAaQBkALsDIgAsACIAVABHAHIAaQBkALsDIgAsACIAUABvAGwAYQByAEcAcgBpAGQAuwMiACwAIgBDAGkAcgBjAGwAZQC7AyIALAAiAEQAaQBhAG0AbwBuAGQAuwMiACwAIgBQAGwAdQBzALsDIgAsACIAUAB5AHIAYQBtAGkAZAC7AyIALAAiAFIAaQBuAGcAuwMiACwAIgBTAHEAdQBhAHIAZQC7AyIALAAiAFQAcgBpAGEAbgBnAGwAZQC7AyIALAAiAFIAZQBTAGgAYQBwAGUAMgBEALsDIgAsACIAUgBlAHMAaQB6AGUAuwMiACwAIgBTAGMAYQBuADIARAC7AyIALAAiAFQAcgBhAHYAZQByAHMAZQC7AyIALAAiAFQAYQBrAGUAQgBsAG8AYwBrALsDIgAsACIARABTAHQAYQBjAGsAuwMiACwAIgBXAHIAYQBwAFIAbwB3AHMAMgBEALsDIgAsACIAVwByAGEAcABDAG8AbABzADIARAC7AyIALAAiAFMAdABhAGkAcgBjAGEAcwBlALsDIgAsACIAVgBhAGwAaQBkAGEAdABlAFMAdABhAGkAcgBjAGEAcwBlALsDIgAsACIAVQBuAFAAaQB2AG8AdAC7AyIALAAiAFoAaQBwALsDIgAsACIAUwBsAGkAYwBlAEIAeQBEAGUAZwC7AyIALAAiAFAAYQBkALsDIgAsACIASQBuAHMAdQBsAGEAdABlAFIAbwB3AHMAuwMiACwAIgBJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7AyIALAAiAE0AYQBnAG4AaQBmAHkAuwMiACwAIgBaAG8AbwBtALsDIgAsACIARABlAGwAZQB0AGUAUgBvAHcAcwC7AyIALAAiAEQAZQBsAGUAdABlAEMAbwBsAHMAuwMiACwAIgBEAGUAbABlAHQAZQBXAGgAZQByAGUAuwMiACwAIgBQAGkAbgBjAGgAuwMiACwAIgBSAGUAbQBvAHYAZQC7AyIALAAiAFMAcQB1AGUAZQB6AGUAuwMiACwAIgBLAHIAbwBuAGUAYwBrAGUAcgBQAHIAbwBkALsDIgAsACIARQB4AGMAbAB1AGQAZQC7AyIALAAiAFMAbgBhAHAAuwMiACwAIgBTAGgAaQBmAHQAuwMiACwAIgBTAGgAaQBmAHQAUgBvAHcAcwC7AyIALAAiAFMAaABpAGYAdABDAG8AbABzALsDIgAsACIARQBtAGIAZQBkALsDIgAsACIASwBlAGUAcABSAG8AdwBzALsDIgAsACIASwBlAGUAcABDAG8AbABzALsDIgAsACIAQgBsAG8AYwBrAE0AYQBwALsDIgAsACIAVgBhAGwAaQBkAGEAdABlAEIAbABvAGMAawBNAGEAcAC7AyIALAAiAEMAbwBuAHYAbwBsAHYAZQC7AyIALAAiAEYAbwBsAGQAuwMiACwAIgBKAG8AaQBuADIARAC7AyIALAAiAEUAYwBoAG8AuwMiACwAIgBSAGUAcABlAGEAdABSAG8AdwBzALsDIgAsACIAUgBlAHAAZQBhAHQAQwBvAGwAcwC7AyIALAAiAFQAZQBzAHMAZQBsAGwAYQB0AGUAuwMiACwAIgBTAHQAcgBlAGEAawC7AyIALAAiAEMAbwB1AG4AdABkAG8AdwBuALsDIgAsACIASQBuAHMAdABhAG4AYwBlALsDIgAsACIAVwBhAHYAZQC7AyIALAAiAEIAeQBEAGkAYQBnALsDIgAsACIARABpAGEAZwBNAGEAcAC7AyIALAAiAEQAaQBhAGcASQBuAGQAZQB4ALsDIgAsACIAVgBhAGwAaQBkAGEAdABlAEQAaQBhAGcAuwMiACwAIgBQAGEAaQByAHcAaQBzAGUAuwMiACwAIgBUAHIAaQBwAGwAZQB3AGkAcwBlALsDIgAsACIAUQB1AGEAZAB3AGkAcwBlALsDIgAsACIARwByAG8AdQBwAGIAeQBCAGkAbgC7AyIALAAiAEcAcgBvAHUAcABiAHkARABhAHQAZQC7AyIALAAiAFYAYQBsAGkAZABhAHQAZQBHAEQAuwMiACwAIgBQAGkAdgBvAHQAYgB5AEMAYQB0ALsDIgAsACIARwByAG8AdQBwAEkAbgBkAGUAeAC7AyIALAAiAE8AYwBjAHUAcgByAGUAbgBjAGUAuwMiACwAIgBPAGMAYwB1AHIAcgBlAG4AYwBlAFIAYQBuAGcAZQC7AyIALAAiAEcAcgBhAGkAbgC7AyIALAAiAE0AbwBvAHIAZQBBAGcAZwC7AyIALAAiAE0AbwBvAHIAZQBTAGUAbABlAGMAdAC7AyIALAAiAEgAaQBzAHQAbwBnAHIAYQBtALsDIgAsACIATQBvAGQAZQC7AyIALAAiAFoAbwBuAGUAUwB0AGEAdAC7AyIALAAiAEEAbABpAGcAbgC7AyIALAAiAEEAbABpAGcAbgBEAGkAcwB0AGkAbgBjAHQAuwMiACwAIgBBAGwAaQBnAG4AVQBuAGkAcQB1AGUAuwMiACwAIgBDAG8AYQBsAGUAcwBjAGUAuwMiACwAIgBFAHgAcABsAG8AZABlALsDIgAsACIATgB1AG0AYgBlAHIAcwBPAG4AbAB5ALsDIgAsACIAVABlAHgAdABPAG4AbAB5ALsDIgAsACIAUwBwAGwAaQB0ALsDIgAsACIAUgBlAGcAZQB4AFMAYQBmAGUAuwMiACwAIgBCAGkAbgAyAEQAZQBjALsDIgAsACIAQgBpAG4AMgBHAHIAYQB5ALsDIgAsACIAQgBpAHQAQwBvAHUAbgB0ALsDIgAsACIARABlAGMAMgBCAGkAbgC7AyIALAAiAEQAZQBjADIARwByAGEAeQC7AyIALAAiAEUAbgB1AG0AZQByAGEAdABlALsDIgAsACIAUABlAHIAbQBSALsDIgAsACIAUABlAHIAbQC7AyIALAAiAEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwMiACwAIgBDAG8AbQBiAGkAbgBhAHQAaQBvAG4AcwC7AyIALAAiAEQAZQByAGEAbgBnAGUAbQBlAG4AdABzALsDIgAsACIASwBuAGEAcABTAGEAYwBrALsDIgAsACIAUwB1AGIAcwBlAHQARwBlAG4AuwMiACwAIgBTAHUAYgBzAGUAdABTAHUAbQC7AyIALAAiAFIAZQB2AGUAYQBsALsDIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBNAEQAWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuACAAIABfAF8AXwBfACAAIAAgACAAXwAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8AXwBfAF8AIAAgACAAIAAgACAAIAAgACAAIAAgAF8AIAAgACAAXwAgACAAIABfACAAXABuACAAfAAgACAAXwAgAFwAXAAgACAAKABfACkAIAAgACAAIAAgACAAIAAgACAAIAAvACAAXwBfAF8AXwB8ACAAIAAgACAAIAAgACAAIAAgACgAXwApACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAIABfACAAIAAgACAAXwBfACAAXwAgACAAfAAgACgAXwBfAF8AIAAgACAAIABfACAAXwBfACAAIAAgACAAXwAgACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAIABfACAAPAAgACAAfAAgAHwAIAAgAC8AIABfAGAAIAB8ACAAIABcAFwAXwBfAF8AIABcAFwAIAAgAHwAIAAnAF8AIABcAFwAIAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAfAAgAHwAIAB8ACAAKABfAHwAIAB8ACAAIABfAF8AXwBfACkAIAB8ACAAfAAgAHwAXwApACAAfAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8AF8AXwBfAF8ALwAgACAAfABfAHwAIAAgAFwAXABfAF8ALAAgAHwAIAB8AF8AXwBfAF8AXwAvACAAIAB8ACAALgBfAF8ALwAgACAAfABfAHwAIAB8AF8AfAAgAHwAXwB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8ALwAgAHwAIAAgACAAIAAgACAAIAAgACAAIAB8ACAAfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABfAF8AXwAvACAAIAAgACAAIAAgACAAIAAgACAAIAB8AF8AfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgBcAG4AdgAgADEALgAyAC4AMABcAG4AXABuAE0AbwBkAHUAbABlADoAIAAgAEIAaQBnAFMAcABpAGwAbABcAG4AUgBlAHAAbwA6ACAAIAAgACAAaAB0AHQAcABzADoALwAvAGcAaQB0AGgAdQBiAC4AYwBvAG0ALwBQAGEAdAByAGkAYwBrADIANwA4ADgALwBCAGkAZwBTAHAAaQBsAGwALQBFAHgAYwBlAGwALQBMAGEAbQBiAGQAYQAtAEwAaQBiAHIAYQByAHkAXABuAEwAaQBjAGUAbgBzAGUAOgAgAE0ASQBUACAAKABzAGUAZQAgAEwASQBDAEUATgBTAEUAIABmAGkAbABlACkAXABuAEEAdQB0AGgAbwByADoAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAEQAYQB0AGUAOgAgACAAIAAgADkALwAxADcALwAyADAAMgA2AFwAbgBcAG4AVgBlAHIAcwBpAG8AbgAgAGgAaQBzAHQAbwByAHkAOgBcAG4AIAAgACAAIAA3AC8ANgAvADIAMAAyADYAIAATICAAIABJAG4AaQB0AGkAYQBsACAAcgBlAGwAZQBhAHMAZQBcAG4AXABuACAAIAAgACAAOQAvADMALwAyADAAMgA2ACAAEyAgACAAQQBkAGQAZQBkACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AyAAYQBuAGQAIABRAHUAYQBkAHcAaQBzAGUAuwMgAHQAbwAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAHAAZABhAHQAZQBkACAARwByAGkAZAAgAEEAbgBhAGwAeQB0AGkAYwBzACAAYwBhAHQAZQBnAG8AcgB5ACAAYgBsAG8AYwBrAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUAcABkAGEAdABlAGQAIABUAGUAcwBzAGUAbABsAGEAdABlALsDIAB0AG8AIABhAGMAYwBlAHAAdAAgADEARAAgAGEAcgByAGEAeQBzAFwAbgBcAG4AIAAgACAAIAA5AC8AMQA3AC8AMgAwADIANgAgABMgIABBAGQAZABlAGQAIABJAG4AcwB0AGEAbgBjAGUAuwMsACAAVwBhAHYAZQC7AywAIABHAHIAbwB1AHAASQBuAGQAZQB4ALsDLAAgAE8AYwBjAHUAcgByAGUAbgBjAGUAuwMsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAbgBkACAATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwMgAHQAbwAgAEcAcgBpAGQAIABBAG4AYQBsAHkAdABpAGMAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAGkAeABlAGQAIAB2AHUAbABuAGUAcgBhAGIAaQBsAGkAdAB5ACAAaQBuACAAQwBvAG4AdgBvAGwAdgBlALsDIAB3AGkAdABoACAAMQBEACAAawBlAHIAbgBlAGwAcwBcAG4AXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAXABuACAAIAAgACAATgBvAG4AZQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEMAbwByAGUAIABtAG8AZAB1AGwAZQAgAGEAZwBnAHIAZQBnAGEAdABvAHIAIABmAG8AcgAgAGEAbABsACAAQgBpAGcAUwBwAGkAbABsACAAZgB1AG4AYwB0AGkAbwBuAHMALgBcAG4AXABuAFAAdQByAHAAbwBzAGUAOgBcAG4AIAAgACAAIABQAHIAbwB2AGkAZABlAHMAIABhACAAcwBpAG4AZwBsAGUAIABpAG0AcABvAHIAdAAgAHAAbwBpAG4AdAAgAGYAbwByACAAdABoAGUAIABlAG4AdABpAHIAZQAgAGwAaQBiAHIAYQByAHkALgBcAG4AXABuAEMAbwBuAHQAZQBuAHQAcwA6AFwAbgAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawAsACAARwByAGkAZAAgAEcAZQBvAG0AZQB0AHIAeQAsACAAMgBEACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwAsACAARwByAGkAZAAgAEEAbABnAGUAYgByAGEALABcAG4AIAAgACAAIABSAGUAcABlAHQAaQB0AGkAbwBuACwAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMALAAgAFQAZQB4AHQALAAgAEUAbgBnAGkAbgBlAGUAcgBpAG4AZwAsAFwAbgAgACAAIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMALAAgAEQAaQBhAGcAbgBvAHMAdABpAGMAcwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4ALQAtAC0AVABhAGIAbABlACAAbwBmACAAQwBvAG4AdABlAG4AdABzAC0ALQAtAFwAbgBcAG4AIwAjACAAMAAxACAALQAgAFsARwBXAF0AIABHAHIAaQBkAHcAbwByAGsAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAVwAwADEAXQAgACAARABHAHIAaQBkALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBXADAAMgBdACAAIABDAEcAcgBpAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFcAMAAzAF0AIAAgAE0ARwByAGkAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAVwAwADQAXQAgACAAVABHAHIAaQBkALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBXADAANQBdACAAIABQAG8AbABhAHIARwByAGkAZAC7A1wAbgBcAG4AIwAjACAAMAAyACAALQAgAFsARwBHAF0AIAAgAEcAcgBpAGQAIABHAGUAbwBtAGUAdAByAHkAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARwAwADEAXQAgACAAQwBpAHIAYwBsAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAAyAF0AIAAgAEQAaQBhAG0AbwBuAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAAzAF0AIAAgAFAAbAB1AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA0AF0AIAAgAFAAeQByAGEAbQBpAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA1AF0AIAAgAFIAaQBuAGcAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEcAMAA2AF0AIAAgAFMAcQB1AGEAcgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBHADAANwBdACAAIABUAHIAaQBhAG4AZwBsAGUAuwNcAG4AXABuACMAIwAgADAAMwAgAC0AIABbAFMAQQBdACAAIAAyAEQAIABBAHIAcgBhAHkAIABTAGgAYQBwAGkAbgBnAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBvAHIAZQAgAFMAaABhAHAAaQBuAGcAIABQAHIAaQBtAGkAdABpAHYAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADEAXQBcAHQAUgBlAFMAaABhAHAAZQAyAEQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMAAyAF0AXAB0AFIAZQBTAGkAegBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAAMwBdAFwAdABTAGMAYQBuADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADQAXQBcAHQAVAByAGEAdgBlAHIAcwBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADAANQBdAFwAdABUAGEAawBlAEIAbABvAGMAawC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADYAXQBcAHQARABTAHQAYQBjAGsAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQBmAGwAbwB3AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADcAXQBcAHQAVwByAGEAcABSAG8AdwBzADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADgAXQBcAHQAVwByAGEAcABDAG8AbABzADIARAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAwADkAXQBcAHQAUwB0AGEAaQByAGMAYQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQAwAF0AXAB0AFUAbgBQAGkAdgBvAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQAxAF0AXAB0AFoAaQBwALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADEAMwBdAFwAdABTAGwAaQBjAGUAQgB5AEQAZQBnALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAZABkAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFMAQQAxADQAXQBcAHQAUABhAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA1AF0AXAB0AEkAbgBzAHUAbABhAHQAZQBSAG8AdwBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAUwBBADEANgBdAFwAdABJAG4AcwB1AGwAYQB0AGUAQwBvAGwAcwC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA3AF0AXAB0AE0AYQBnAG4AaQBmAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBTAEEAMQA4AF0AXAB0AFoAbwBvAG0AuwNcAG4AXABuACMAIwAgADAANAAgAC0AIABbAEcAQQBdACAAIABHAHIAaQBkACAAQQBsAGcAZQBiAHIAYQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAZQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADEAXQBcAHQARABlAGwAZQB0AGUAUgBvAHcAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADIAXQBcAHQARABlAGwAZQB0AGUAQwBvAGwAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADMAXQBcAHQARABlAGwAZQB0AGUAVwBoAGUAcgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAANABdAFwAdABQAGkAbgBjAGgAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMAA1AF0AXAB0AFIAZQBtAG8AdgBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADAANgBdAFwAdABTAHEAdQBlAGUAegBlALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAHgAcABhAG4AcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMAA3AF0AXAB0AEsAcgBvAG4AZQBjAGsAZQByAFAAcgBvAGQAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAaQBsAHQAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADgAXQBcAHQARQB4AGMAbAB1AGQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAwADkAXQBcAHQAUwBuAGEAcAC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBvAGwAbABpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAwAF0AXAB0AFMAaABpAGYAdAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADEAXQBcAHQAUwBoAGkAZgB0AFIAbwB3AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAyAF0AXAB0AFMAaABpAGYAdABDAG8AbABzALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAGUAbABlAGMAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQAzAF0AXAB0AEUAbQBiAGUAZAC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADQAXQBcAHQASwBlAGUAcABSAG8AdwBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEANQBdAFwAdABLAGUAZQBwAEMAbwBsAHMAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAdAByAHUAYwB0AHUAcgBhAGwAIABNAGEAcABwAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAQQAxADYAXQBcAHQAQgBsAG8AYwBrAE0AYQBwALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBBADEANwBdAFwAdABDAG8AbgB2AG8AbAB2AGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQA4AF0AXAB0AEYAbwBsAGQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAEEAMQA5AF0AXAB0AEoAbwBpAG4AMgBEALsDXABuAFwAbgAjACMAIAAwADUAIAAtACAAWwBSAFAAXQAgACAAUgBlAHAAZQB0AGkAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAxAF0AXAB0AEUAYwBoAG8AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAyAF0AXAB0AFIAZQBwAGUAYQB0AFIAbwB3AHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAAzAF0AXAB0AFIAZQBwAGUAYQB0AEMAbwBsAHMAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBSAFAAMAA0AF0AXAB0AFQAZQBzAHMAZQBsAGwAYQB0AGUAuwNcAG4AXABuACMAIwAgADAANgAgAC0AIABbAEcAUgBdACAAIABHAHIAaQBkACAAQQBuAGEAbAB5AHQAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAZQBxAHUAZQBuAGMAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADAAMQBdAFwAdABTAHQAcgBlAGEAawC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADIAXQBcAHQAQwBvAHUAbgB0AGQAbwB3AG4AuwNcAG4AXAB0AFwAdABcAHQAWwBHAFIAMQA2AF0AIAAgAEkAbgBzAHQAYQBuAGMAZQC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADcAXQBcAHQAVwBhAHYAZQC7A1wAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBhAHQAZQBnAG8AcgBpAGMAYQBsACAAQQBuAGEAbAB5AHMAaQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADMAXQBcAHQAQgB5AEQAaQBhAGcAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA0AF0AXAB0AEQAaQBhAGcATQBhAHAAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA1AF0AXAB0AEQAaQBhAGcASQBuAGQAZQB4ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADAANgBdAFwAdABQAGEAaQByAHcAaQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA2AGEAXQBcAHQAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBcAHQAIAAgACAAIAAgACAAIAAgAFsARwBSADAANgBiAF0AIABRAHUAYQBkAHcAaQBzAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA3AF0AXAB0AEcAcgBvAHUAcABiAHkAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMAA4AF0AXAB0AEcAcgBvAHUAcABiAHkARABhAHQAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAwADkAXQBcAHQAUABpAHYAbwB0AGIAeQBDAGEAdAC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADgAXQBcAHQARwByAG8AdQBwAEkAbgBkAGUAeAC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAxADkAXQBcAHQATwBjAGMAdQByAHIAZQBuAGMAZQC7A1wAbgBcAHQAXAB0AFwAdABbAEcAUgAyADAAXQBcAHQATwBjAGMAdQByAHIAZQBuAGMAZQBSAGEAbgBnAGUAuwNcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AZQBpAGcAaABiAG8AcgBoAG8AbwBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARwBSADEAMABdAFwAdABHAHIAYQBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQAxAF0AXAB0AE0AbwBvAHIAZQBBAGcAZwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADIAXQBcAHQATQBvAG8AcgBlAFMAZQBsAGUAYwB0ALsDXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAHQAYQB0AGkAcwB0AGkAYwBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcAUgAxADMAXQBcAHQASABpAHMAdABvAGcAcgBhAG0AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQA0AF0AXAB0AE0AbwBkAGUAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBHAFIAMQA1AF0AXAB0AFoAbwBuAGUAUwB0AGEAdAC7A1wAbgBcAG4AIwAjACAAMAA3ACAALQAgAFsAVABYAF0AIAAgAFQAZQB4AHQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAAMQBdAFwAdABBAGwAaQBnAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAAyAF0AXAB0AEEAbABpAGcAbgBEAGkAcwB0AGkAbgBjAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAAzAF0AXAB0AEEAbABpAGcAbgBVAG4AaQBxAHUAZQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADQAXQBcAHQAQwBvAGEAbABlAHMAYwBlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAANQBdAFwAdABFAHgAcABsAG8AZABlALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAVABYADAANgBdAFwAdABOAHUAbQBiAGUAcgBzAE8AbgBsAHkAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBUAFgAMAA3AF0AXAB0AFQAZQB4AHQATwBuAGwAeQC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAFQAWAAwADgAXQBcAHQAUwBwAGwAaQB0ALsDXABuAFwAbgAjACMAIAAwADgAIAAtACAAWwBFAE4AXQAgACAARQBuAGcAaQBuAGUAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEUATgAwADEAXQBcAHQAQgBpAG4AMgBEAGUAYwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEUATgAwADIAXQBcAHQAQgBpAG4AMgBHAHIAYQB5ALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsARQBOADAAMwBdAFwAdABCAGkAdABDAG8AdQBuAHQAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBFAE4AMAA0AF0AXAB0AEQAZQBjADIAQgBpAG4AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBFAE4AMAA1AF0AXAB0AEQAZQBjADIARwByAGEAeQC7A1wAbgBcAG4AIwAjACAAMAA5ACAALQAgAFsAQwBCAF0AIAAgAEMAbwBtAGIAaQBuAGEAdABvAHIAaQBjAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAAMQBdAFwAdABQAGUAcgBtAFIAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAAyAF0AXAB0AFAAZQByAG0AuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAAzAF0AXAB0AEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzAFIAuwNcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWwBDAEIAMAA0AF0AXAB0AEMAbwBtAGIAaQBuAGEAdABpAG8AbgBzALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAANQBdAFwAdABEAGUAcgBhAG4AZwBlAG0AZQBuAHQAcwC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADYAXQBcAHQASwBuAGEAcABTAGEAYwBrALsDXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFsAQwBCADAANwBdAFwAdABTAHUAYgBzAGUAdABHAGUAbgC7A1wAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEMAQgAwADgAXQBcAHQAUwB1AGIAcwBlAHQAUwB1AG0AuwNcAG4AXABuACMAIwAgADEAMAAgAC0AIABbAEcARABdACAAIABHAHIAaQBkACAARABpAGEAZwBuAG8AcwB0AGkAYwBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABbAEcARAAwADEAXQAgACAAUgBlAHYAZQBhAGwAuwNcAG4AXABuAFwAbgBcAG4AKgAvAFwAbgBcAG4AXABuAFwAbgAvAC8AIABbAEcAVwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAvAC8AIAAtAC0ALQAjACMAIAAwADEAIAAtACAARwByAGkAZAB3AG8AcgBrAFwAbgAvAC8AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFwAbgAvACoAXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawAgAGQAZQBmAGkAbgBlAHMAIAB0AGgAZQAgAGYAbwB1AG4AZABhAHQAaQBvAG4AYQBsACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAHMAeQBzAHQAZQBtAHMAIABmAG8AcgAgADIARAAgAGEAcgByAGEAeQBzAC4AIABFAGEAYwBoAFwAbgAgACAAIAAgAGYAdQBuAGMAdABpAG8AbgAgAHAAcgBvAGQAdQBjAGUAcwAgAGEAIABjAGUAbgB0AGUAcgBlAGQALAAgAHMAeQBtAG0AZQB0AHIAaQBjAGEAbAAgAGcAZQBvAG0AZQB0AHIAaQBjACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAbwBmACAAdABoAGUAIABnAHIAaQBkAC4AXABuAFwAbgBGAHUAbgBjAHQAaQBvAG4AcwA6AFwAbgAgACAAIAAgACIgIABEAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAARABpAHIAZQBjAHQAaQBvAG4AIABnAHIAaQBkACAAKAAwALAALQAzADYAMACwACkAIAB1AHMAaQBuAGcAIABjAGUAbgB0AGUAcgBlAGQAIABDAGEAcgB0AGUAcwBpAGEAbgAgAGEAeABlAHMAXABuAFwAbgAgACAAIAAgACIgIABDAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAAQwBhAHIAdABlAHMAaQBhAG4AIABnAHIAaQBkACAAKAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACwAIABjAGUAbgB0AGUAcgBlAGQAKQBcAG4AXABuACAAIAAgACAAIiAgAE0ARwByAGkAZAC7AyAAIAAgACAAIAAgAC0AIABNAGUAcwBoACAAZwByAGkAZAAgACgAMQARIGIAYQBzAGUAZAAgAHIAbwB3ACAAbwByACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzACkAXABuAFwAbgAgACAAIAAgACIgIABUAEcAcgBpAGQAuwMgACAAIAAgACAAIAAtACAAVABoAHIAZQBzAGgAbwBsAGQAZQBkACAAbQBlAHMAaAAgAGcAcgBpAGQAIAAoAGkAbgBkAGkAYwBlAHMAIAB3AHIAYQBwACAAYQBmAHQAZQByACAAYQAgAGwAaQBtAGkAdAApAFwAbgBcAG4AIAAgACAAIAAiICAAUABvAGwAYQByAEcAcgBpAGQAuwMgACAALQAgAFAAbwBsAGEAcgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAIAAgACAAEyAgAHIAYQBkAGkAYQBsACAAZABpAHMAdABhAG4AYwBlACAAZgByAG8AbQAgAGcAcgBpAGQAIABjAGUAbgB0AGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGgAaQAgABMgIABhAG4AZwBsAGUAIABpAG4AIAByAGEAZABpAGEAbgBzACAAdQBzAGkAbgBnACAAQQBUAEEATgAyACgAeQAsACAAeAApAFwAbgBcAG4AIAAgACAAIAAiICAAUgBlAHMAaQB6AGUAuwMgACAAIAAgACAALQAgAFUAdABpAGwAaQB0AHkAIABmAG8AcgAgAGIAcgBvAGEAZABjAGEAcwB0AGkAbgBnACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAHYAZQBjAHQAbwByAHMAIAB0AG8AIABnAHIAaQBkACAAcwBoAGEAcABlAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAQQBsAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGEAcgBlACAAcwBoAGEAcABlAC0AZAByAGkAdgBlAG4AOgAgAHQAaABlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAcwB1AHAAcABsAGkAZQBkACAAZwByAGkAZAAgAGQAZQB0AGUAcgBtAGkAbgBlAFwAbgAgACAAIAAgAHQAaABlACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGUAeAB0AGUAbgB0AHMALgBcAG4AXABuAEUAeABhAG0AcABsAGUAcwA6AFwAbgAgACAAIAAgAEcAcgBpAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAgACAAMgAgACAAIAAzACAAIAAgADQAIAAgACAANQBcAG4AIAAgACAAIAAgACAAIAAgADYAIAAgACAANwAgACAAIAA4ACAAIAAgADkAIAAgACAAMQAwAFwAbgAgACAAIAAgACAAIAAgACAAMQAxACAAIAAxADIAIAAgADEAMwAgACAAMQA0ACAAIAAxADUAXABuACAAIAAgACAAIAAgACAAIAAxADYAIAAgADEANwAgACAAMQA4ACAAIAAxADkAIAAgADIAMABcAG4AIAAgACAAIAAgACAAIAAgADIAMQAgACAAMgAyACAAIAAyADMAIAAgADIANAAgACAAMgA1AFwAbgBcAG4AIAAgACAAIABEAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQA6AFwAbgAgACAAIAAgACAAIAAgACAAMgAyADUALgAwADAAIAAyADAANgAuADUANwAgADEAOAAwAC4AMAAwACAAMQA1ADMALgA0ADMAIAAxADMANQAuADAAMABcAG4AIAAgACAAIAAgACAAIAAgADIANAAzAC4ANAAzACAAMgAyADUALgAwADAAIAAxADgAMAAuADAAMAAgADEAMwA1AC4AMAAwACAAMQAxADYALgA1ADcAXABuACAAIAAgACAAIAAgACAAIAAyADcAMAAuADAAMAAgADIANwAwAC4AMAAwACAAIAAgADAALgAwADAAIAAgADkAMAAuADAAMAAgACAAOQAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAAgACAAMgA5ADYALgA1ADcAIAAzADEANQAuADAAMAAgACAAIAAwAC4AMAAwACAAIAA0ADUALgAwADAAIAAgADYAMwAuADQAMwBcAG4AIAAgACAAIAAgACAAIAAgADMAMQA1AC4AMAAwACAAMwAzADMALgA0ADMAIAAgACAAMAAuADAAMAAgACAAMgA2AC4ANQA3ACAAIAA0ADUALgAwADAAXABuAFwAbgAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAApACAALQAgAHIAbwB3ACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAtADIAIAAtADIAIAAtADIAIAAtADIAIAAtADIAXABuACAAIAAgACAAIAAgACAAIAAtADEAIAAtADEAIAAtADEAIAAtADEAIAAtADEAXABuACAAIAAgACAAIAAgACAAIAAgADAAIAAgADAAIAAgADAAIAAgADAAIAAgADAAXABuACAAIAAgACAAIAAgACAAIAAgADEAIAAgADEAIAAgADEAIAAgADEAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAAgADIAIAAgADIAIAAgADIAIAAgADIAIAAgADIAXABuAFwAbgAgACAAIAAgAEMARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgAgACAAIAAgACAAIAAgACAALQAyACAALQAxACAAIAAwACAAIAAxACAAIAAyAFwAbgBcAG4AIAAgACAAIABNAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAgAC0AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAxACAAMQAgADEAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAMgAgADIAIAAyACAAMgAgADIAXABuACAAIAAgACAAIAAgACAAIAAzACAAMwAgADMAIAAzACAAMwBcAG4AIAAgACAAIAAgACAAIAAgADQAIAA0ACAANAAgADQAIAA0AFwAbgAgACAAIAAgACAAIAAgACAANQAgADUAIAA1ACAANQAgADUAXABuAFwAbgAgACAAIAAgAE0ARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADQAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAANAAgADUAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAA0ACAANQBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADQAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAANAAgADUAXABuAFwAbgAgACAAIAAgAFQARwByAGkAZAC7AygAZwByAGkAZAAsADMAKQAgAC0AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALAAgAHQAaAByAGUAcwBoAG8AbABkACAAMwA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADEAIAAxACAAMQAgADEAXABuACAAIAAgACAAIAAgACAAIAAyACAAMgAgADIAIAAyACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADMAIAAzACAAMwAgADMAIAAzAFwAbgAgACAAIAAgACAAIAAgACAAMQAgADEAIAAxACAAMQAgADEAXABuACAAIAAgACAAIAAgACAAIAAyACAAMgAgADIAIAAyACAAMgBcAG4AXABuACAAIAAgACAAVABHAHIAaQBkALsDKABnAHIAaQBkACwAMwAsADEAKQAgAC0AIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMALAAgAHQAaAByAGUAcwBoAG8AbABkACAAMwA6AFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAAMQAgADIAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAAxACAAMgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAyACAAMwAgADEAIAAyAFwAbgAgACAAIAAgACAAIAAgACAAMQAgADIAIAAzACAAMQAgADIAXABuACAAIAAgACAAIAAgACAAIAAxACAAMgAgADMAIAAxACAAMgBcAG4AXABuACAAIAAgACAAUABvAGwAYQByAEcAcgBpAGQAuwMoAGcAcgBpAGQAKQAgAC0AIAByADoAXABuACAAIAAgACAAIAAgACAAIAAyAC4AOAAzACAAMgAuADIANAAgADIALgAwADAAIAAyAC4AMgA0ACAAMgAuADgAMwBcAG4AIAAgACAAIAAgACAAIAAgADIALgAyADQAIAAxAC4ANAAxACAAMQAuADAAMAAgADEALgA0ADEAIAAyAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAMgAuADAAMAAgADEALgAwADAAIAAwAC4AMAAwACAAMQAuADAAMAAgADIALgAwADAAXABuACAAIAAgACAAIAAgACAAIAAyAC4AMgA0ACAAMQAuADQAMQAgADEALgAwADAAIAAxAC4ANAAxACAAMgAuADIANABcAG4AIAAgACAAIAAgACAAIAAgADIALgA4ADMAIAAyAC4AMgA0ACAAMgAuADAAMAAgADIALgAyADQAIAAyAC4AOAAzAFwAbgBcAG4AIAAgACAAIABQAG8AbABhAHIARwByAGkAZAC7AygAZwByAGkAZAAsADEAKQAgAC0AIABwAGgAaQA6AFwAbgAgACAAIAAgACAAIAAgACAALQAyAC4AMwA2ACAALQAyAC4AMAAzACAALQAxAC4ANQA3ACAALQAxAC4AMQAxACAALQAwAC4ANwA5AFwAbgAgACAAIAAgACAAIAAgACAALQAyAC4ANgA4ACAALQAyAC4AMwA2ACAALQAxAC4ANQA3ACAALQAwAC4ANwA5ACAALQAwAC4ANAA2AFwAbgAgACAAIAAgACAAIAAgACAAIAAzAC4AMQA0ACAAIAAzAC4AMQA0ACAAIAAwAC4AMAAwACAAIAAwAC4AMAAwACAAIAAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAAgACAAIAAyAC4ANgA4ACAAIAAyAC4AMwA2ACAAIAAxAC4ANQA3ACAAIAAwAC4ANwA5ACAAIAAwAC4ANAA2AFwAbgAgACAAIAAgACAAIAAgACAAIAAyAC4AMwA2ACAAIAAyAC4AMAAzACAAIAAxAC4ANQA3ACAAIAAxAC4AMQAxACAAIAAwAC4ANwA5AFwAbgAqAC8AXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADEAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEQARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAQwBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABjAG8AdQBuAHQAZQByABEgYwBsAG8AYwBrAHcAaQBzAGUAIABkAGkAcgBlAGMAdABpAG8AbgAgAGcAcgBpAGQAIABpAG4AIABkAGUAZwByAGUAZQBzACAAKAAwALAAEyAzADYAMACwACkAIAB1AHMAaQBuAGcAXABuACAAIAAgACAAYwBlAG4AdABlAHIAZQBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMAIABmAHIAbwBtACAAQwBHAHIAaQBkALsDLgBcAG4AXABuACAAIAAgACAAQQBuAGcAbABlACAAYwBvAG4AdgBlAG4AdABpAG8AbgA6AFwAbgAgACAAIAAgACAAIAAgACAAMACwACAAIAAgAD0AIAArAFgAIABkAGkAcgBlAGMAdABpAG8AbgAgACgAcgBpAGcAaAB0ACkAXABuACAAIAAgACAAIAAgACAAIAA5ADAAsAAgACAAPQAgACsAWQAgAGQAaQByAGUAYwB0AGkAbwBuACAAKAB1AHAAKQBcAG4AIAAgACAAIAAgACAAIAAgADEAOAAwALAAIAA9ACAAEyBYACAAZABpAHIAZQBjAHQAaQBvAG4AIAAoAGwAZQBmAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgADIANwAwALAAIAA9ACAAEyBZACAAZABpAHIAZQBjAHQAaQBvAG4AIAAoAGQAbwB3AG4AKQBcAG4AXABuACAAIAAgACAAVABoAGUAIABjAGUAbgB0AGUAcgAgAGMAZQBsAGwAIAAoADAALAAwACkAIAByAGUAdAB1AHIAbgBzACAAMACwACAAdgBpAGEAIABJAEYARQBSAFIATwBSACAAZgBhAGwAbABiAGEAYwBrAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AIAAgACAAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARABHAHIAaQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABSAGEAdwAgAGEAbgBnAGwAZQAgAGkAbgAgAGQAZQBnAHIAZQBlAHMAIAAoAG0AYQB5ACAAYgBlACAAbgBlAGcAYQB0AGkAdgBlACkAXABuACAAIAAgACAAdABoAGUAdABhACwAIABJAEYARQBSAFIATwBSACgARABFAEcAUgBFAEUAUwAoAEEAVABBAE4AMgAoAEMARwByAGkAZAC7AygAZwByAGkAZAApACwAIABDAEcAcgBpAGQAuwMoAGcAcgBpAGQALAAxACkAKQApACwAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAdABvACAAMACwABMgMwA2ADAAsABcAG4AIAAgACAAIABhAG4AZwBsAGUALAAgAE0ATwBEACgAdABoAGUAdABhACAAKwAgADMANgAwACwAIAAzADYAMAApACwAXABuAFwAbgAgACAAIAAgAGEAbgBnAGwAZQBcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADIAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAEMARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYwBlAG4AdABlAHIAZQBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABjAG8AbwByAGQAaQBuAGEAdABlACAAZwByAGkAZABzACAAYQBsAGkAZwBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBoAGEAcABlACAAbwBmACAAYQBcAG4AIAAgACAAIABzAHUAcABwAGwAaQBlAGQAIABhAHIAcgBhAHkALgAgAFIAZQB0AHUAcgBuAHMAIABlAGkAdABoAGUAcgAgAHIAbwB3ACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAbwByACAAYwBvAGwAdQBtAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMALgBcAG4AXABuACAAIAAgACAAQwBvAG8AcgBkAGkAbgBhAHQAZQAgAHIAYQBuAGcAZQBzACAAYQByAGUAIABjAGUAbgB0AGUAcgBlAGQAIABzAHUAYwBoACAAdABoAGEAdAA6AFwAbgAgACAAIAAgACAAIAAgACAAUgBvAHcAOgAgACAALQAoAGgAIAAtACAAMQApACAALwAgADIAIAAgAC4ALgAuACAAIAArACgAaAAgAC0AIAAxACkAIAAvACAAMgBcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBsADoAIAAgAC0AKAB3ACAALQAgADEAKQAgAC8AIAAyACAAIAAuAC4ALgAgACAAKwAoAHcAIAAtACAAMQApACAALwAgADIAXABuAFwAbgAgACAAIAAgAFcAbwByAGsAcwAgAGYAbwByACAAYgBvAHQAaAAgADEARAAgAGEAbgBkACAAMgBEACAAYQByAHIAYQB5AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuACAAYwBvAGwAdQBtAG4AIABjAG8AbwByAGQAaQBuAGEAdABlAHMALgAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAHIAZQB0AHUAcgBuACAAcgBvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBDAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwB0AGEAcgB0AGkAbgBnACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAKABjAGUAbgB0AGUAcgBlAGQAKQBcAG4AIAAgACAAIABpAF8AcwB0AGEAcgB0ACwAIAAtACAAKABoACAALQAgADEAKQAgAC8AIAAyACwAXABuACAAIAAgACAAagBfAHMAdABhAHIAdAAsACAALQAgACgAdwAgAC0AIAAxACkAIAAvACAAMgAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABEAGUAZgBlAHIAcgBlAGQAIABjAG8AbwByAGQAaQBuAGEAdABlACAAZwBlAG4AZQByAGEAdABvAHIAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKABoACwALABpAF8AcwB0AGEAcgB0ACkALAAsAHcAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABSAGUAcwBpAHoAZQC7AygAUwBFAFEAVQBFAE4AQwBFACgALAB3ACwAagBfAHMAdABhAHIAdAApACwAaAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGwAZQBjAHQAIAByAG8AdwAgAG8AcgAgAGMAbwBsAHUAbQBuACAAYwBvAG8AcgBkAGkAbgBhAHQAZQAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgAEkARgAoAFIAbwB3AEkAZAB4AD8ALAAgAGkAKAApACwAIABqACgAKQApACwAXABuAFwAbgAgACAAIAAgAHIAZQBzAHUAbAB0AFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqAFsARwBXADAAMwBdAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAATQBHAHIAaQBkALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABHAHIAaQBkAHcAbwByAGsAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIAByAG8AdwARIGkAbgBkAGUAeAAgAG8AcgAgAGMAbwBsAHUAbQBuABEgaQBuAGQAZQB4ACAAZwByAGkAZABzACAAbQBhAHQAYwBoAGkAbgBnACAAdABoAGUAIABzAGgAYQBwAGUAIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgAGEAcgByAGEAeQAuACAAVABoAGkAcwAgAGkAcwAgAHQAaABlACAARQB4AGMAZQBsACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAG8AZgAgAE0AQQBUAEwAQQBCABkgcwAgAG0AZQBzAGgAZwByAGkAZAAgAG8AcgAgAE4AdQBtAFAAeQAZIHMAIABpAG4AZABpAGMAZQBzAC4AXABuAFwAbgAgACAAIAAgAEIAeQAgAGQAZQBmAGEAdQBsAHQALAAgAE0ARwByAGkAZAC7AyAAcgBlAHQAdQByAG4AcwAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAuACAAVwBoAGUAbgAgAHQAaABlACAAbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAIABpAHMAIABUAFIAVQBFACwAXABuACAAIAAgACAAaQB0ACAAcgBlAHQAdQByAG4AcwAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAgAGkAbgBzAHQAZQBhAGQALgBcAG4AXABuACAAIAAgACAAVwBvAHIAawBzACAAZgBvAHIAIABiAG8AdABoACAAMQBEACAAYQBuAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAuACAATwB1AHQAcAB1AHQAIABhAGwAdwBhAHkAcwAgAG0AYQB0AGMAaABlAHMAIAB0AGgAZQAgAGcAZQBvAG0AZQB0AHIAeQAgAG8AZgAgAHQAaABlAFwAbgAgACAAIAAgAGkAbgBwAHUAdAAgAGcAcgBpAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABnAHIAaQBkACAAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AXABuACAAIAAgACAAWwBjAG8AbABfAGkAbgBkAGUAeABdACAALQAgAEkAZgAgAFQAUgBVAEUALAAgAHIAZQB0AHUAcgBuACAAYwBvAGwAdQBtAG4AIABpAG4AZABpAGMAZQBzAC4AIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIAByAGUAdAB1AHIAbgAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAaQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoAGgAKQAsACwAdwApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcAKQAsAGgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAWwBHAFcAMAA0AF0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABUAEcAcgBpAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAEcAcgBpAGQAdwBvAHIAawBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgAFIAZQBzAGkAegBlALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABHAGUAbgBlAHIAYQB0AGUAcwAgAHIAbwB3ABEgaQBuAGQAZQB4ACAAbwByACAAYwBvAGwAdQBtAG4AESBpAG4AZABlAHgAIABnAHIAaQBkAHMAIAB3AGgAbwBzAGUAIAB2AGEAbAB1AGUAcwAgAHcAcgBhAHAAIAB3AGkAdABoAGkAbgAgAGEAIABzAHAAZQBjAGkAZgBpAGUAZABcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAuACAASQBuAGQAaQBjAGUAcwAgAGMAeQBjAGwAZQAgAGYAcgBvAG0AIAAxACAAdABvACAAdABoAHIAZQBzAGgAbwBsAGQALAAgAHIAZQBwAGUAYQB0AGkAbgBnACAAYQBzACAAbgBlAGUAZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQBcAG4AIAAgACAAIABzAGgAYQBwAGUAIABvAGYAIAB0AGgAZQAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAuAFwAbgBcAG4AIAAgACAAIABCAHkAIABkAGUAZgBhAHUAbAB0ACwAIABUAEcAcgBpAGQAuwMgAHIAZQB0AHUAcgBuAHMAIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALgAgAFcAaABlAG4AIAB0AGgAZQAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAVABSAFUARQAsAFwAbgAgACAAIAAgAGkAdAAgAHIAZQB0AHUAcgBuAHMAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAIABpAG4AcwB0AGUAYQBkAC4AXABuAFwAbgAgACAAIAAgAE4AbwBuABEgaQBuAHQAZQBnAGUAcgAgAHQAaAByAGUAcwBoAG8AbABkAHMAIABhAHIAZQAgAG4AbwByAG0AYQBsAGkAegBlAGQAIAB1AHMAaQBuAGcAIABJAE4AVAAoAHQAaAByAGUAcwBoAG8AbABkACkALgAgAFQAaAByAGUAcwBoAG8AbABkAHMAIABtAHUAcwB0ACAAYgBlAFwAbgAgACAAIAAgAHAAbwBzAGkAdABpAHYAZQAgAGkAbgB0AGUAZwBlAHIAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGcAcgBpAGQAIAAgACAAIAAgACAAIAAgAC0AIABBACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHMAaQB6AGUALgBcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAgACAAIAAtACAATQBhAHgAaQBtAHUAbQAgAGkAbgBkAGUAeAAgAHYAYQBsAHUAZQAgAGIAZQBmAG8AcgBlACAAdwByAGEAcABwAGkAbgBnACAAKABtAHUAcwB0ACAAYgBlACAAPgAgADAAKQAuAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAgAC0AIABJAGYAIABUAFIAVQBFACwAIAByAGUAdAB1AHIAbgAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwAuACAASQBmACAAbwBtAGkAdAB0AGUAZAAsACAAcgBlAHQAdQByAG4AIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVABHAHIAaQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGcAcgBpAGQALABcAG4AIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAB0AGgAcgBlAHMAaABvAGwAZAApACwAIAB0AGgAcgBlAHMAaABvAGwAZAAgADwAPQAgADAAKQAsAFwAIgAjAFQASABSAEUAUwBIAE8ATABEACEAXAAiACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAdABoAHIAZQBzAGgAbwBsAGQAXABuACAAIAAgACAAdAAsACAAIAAgACAAIAAgACAASQBOAFQAKAB0AGgAcgBlAHMAaABvAGwAZAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAdwByAGEAcABwAGUAZAAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAMQAgACsAIABNAE8ARAAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKABoACwALAAwACkALAAsAHcAKQAsACAAdAApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoACAAMQAgACsAIABNAE8ARAAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcALAAwACkALABoACkALAAgAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgBbAEcAVwAwADUAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAA